--- a/Data/sgov.xlsx
+++ b/Data/sgov.xlsx
@@ -472,16 +472,16 @@
         <v>45293</v>
       </c>
       <c r="C2" t="n">
-        <v>90.15840148925781</v>
+        <v>90.15838623046875</v>
       </c>
       <c r="D2" t="n">
-        <v>90.1673931794142</v>
+        <v>90.16737791910336</v>
       </c>
       <c r="E2" t="n">
-        <v>90.14940979910142</v>
+        <v>90.14939454183416</v>
       </c>
       <c r="F2" t="n">
-        <v>90.15840148925781</v>
+        <v>90.15838623046875</v>
       </c>
       <c r="G2" t="n">
         <v>5286200</v>
@@ -495,16 +495,16 @@
         <v>45294</v>
       </c>
       <c r="C3" t="n">
-        <v>90.1673583984375</v>
+        <v>90.16736602783203</v>
       </c>
       <c r="D3" t="n">
-        <v>90.18533491316605</v>
+        <v>90.18534254408165</v>
       </c>
       <c r="E3" t="n">
-        <v>90.1673583984375</v>
+        <v>90.16736602783203</v>
       </c>
       <c r="F3" t="n">
-        <v>90.1673583984375</v>
+        <v>90.16736602783203</v>
       </c>
       <c r="G3" t="n">
         <v>4597300</v>
@@ -518,16 +518,16 @@
         <v>45295</v>
       </c>
       <c r="C4" t="n">
-        <v>90.21232604980469</v>
+        <v>90.21233367919922</v>
       </c>
       <c r="D4" t="n">
-        <v>90.22131773877865</v>
+        <v>90.22132536893363</v>
       </c>
       <c r="E4" t="n">
-        <v>90.21232604980469</v>
+        <v>90.21233367919922</v>
       </c>
       <c r="F4" t="n">
-        <v>90.21232604980469</v>
+        <v>90.21233367919922</v>
       </c>
       <c r="G4" t="n">
         <v>2794100</v>
@@ -564,16 +564,16 @@
         <v>45299</v>
       </c>
       <c r="C6" t="n">
-        <v>90.24826049804688</v>
+        <v>90.248291015625</v>
       </c>
       <c r="D6" t="n">
-        <v>90.24826049804688</v>
+        <v>90.248291015625</v>
       </c>
       <c r="E6" t="n">
-        <v>90.23926881160845</v>
+        <v>90.23929932614602</v>
       </c>
       <c r="F6" t="n">
-        <v>90.24826049804688</v>
+        <v>90.248291015625</v>
       </c>
       <c r="G6" t="n">
         <v>2867500</v>
@@ -587,16 +587,16 @@
         <v>45300</v>
       </c>
       <c r="C7" t="n">
-        <v>90.25727844238281</v>
+        <v>90.25725555419922</v>
       </c>
       <c r="D7" t="n">
-        <v>90.25727844238281</v>
+        <v>90.25725555419922</v>
       </c>
       <c r="E7" t="n">
-        <v>90.24828675332851</v>
+        <v>90.24826386742511</v>
       </c>
       <c r="F7" t="n">
-        <v>90.25727844238281</v>
+        <v>90.25725555419922</v>
       </c>
       <c r="G7" t="n">
         <v>2419800</v>
@@ -610,16 +610,16 @@
         <v>45301</v>
       </c>
       <c r="C8" t="n">
-        <v>90.27524566650391</v>
+        <v>90.27525329589844</v>
       </c>
       <c r="D8" t="n">
-        <v>90.27524566650391</v>
+        <v>90.27525329589844</v>
       </c>
       <c r="E8" t="n">
-        <v>90.26626083702391</v>
+        <v>90.26626846565911</v>
       </c>
       <c r="F8" t="n">
-        <v>90.27524566650391</v>
+        <v>90.27525329589844</v>
       </c>
       <c r="G8" t="n">
         <v>1961400</v>
@@ -633,16 +633,16 @@
         <v>45302</v>
       </c>
       <c r="C9" t="n">
-        <v>90.32920074462891</v>
+        <v>90.32919311523438</v>
       </c>
       <c r="D9" t="n">
-        <v>90.32920074462891</v>
+        <v>90.32919311523438</v>
       </c>
       <c r="E9" t="n">
-        <v>90.31121736602117</v>
+        <v>90.31120973814555</v>
       </c>
       <c r="F9" t="n">
-        <v>90.31121736602117</v>
+        <v>90.31120973814555</v>
       </c>
       <c r="G9" t="n">
         <v>3164900</v>
@@ -679,16 +679,16 @@
         <v>45307</v>
       </c>
       <c r="C11" t="n">
-        <v>90.34717559814453</v>
+        <v>90.34718322753906</v>
       </c>
       <c r="D11" t="n">
-        <v>90.35616728728255</v>
+        <v>90.35617491743638</v>
       </c>
       <c r="E11" t="n">
-        <v>90.34717559814453</v>
+        <v>90.34718322753906</v>
       </c>
       <c r="F11" t="n">
-        <v>90.35616728728255</v>
+        <v>90.35617491743638</v>
       </c>
       <c r="G11" t="n">
         <v>2713000</v>
@@ -725,16 +725,16 @@
         <v>45309</v>
       </c>
       <c r="C13" t="n">
-        <v>90.39212036132812</v>
+        <v>90.39213562011719</v>
       </c>
       <c r="D13" t="n">
-        <v>90.40110519113864</v>
+        <v>90.4011204514444</v>
       </c>
       <c r="E13" t="n">
-        <v>90.39212036132812</v>
+        <v>90.39213562011719</v>
       </c>
       <c r="F13" t="n">
-        <v>90.40110519113864</v>
+        <v>90.4011204514444</v>
       </c>
       <c r="G13" t="n">
         <v>2672000</v>
@@ -748,16 +748,16 @@
         <v>45310</v>
       </c>
       <c r="C14" t="n">
-        <v>90.41909790039062</v>
+        <v>90.41908264160156</v>
       </c>
       <c r="D14" t="n">
-        <v>90.41909790039062</v>
+        <v>90.41908264160156</v>
       </c>
       <c r="E14" t="n">
-        <v>90.40111452161609</v>
+        <v>90.40109926586183</v>
       </c>
       <c r="F14" t="n">
-        <v>90.41010621100335</v>
+        <v>90.4100909537317</v>
       </c>
       <c r="G14" t="n">
         <v>3630100</v>
@@ -771,16 +771,16 @@
         <v>45313</v>
       </c>
       <c r="C15" t="n">
-        <v>90.42805480957031</v>
+        <v>90.42808532714844</v>
       </c>
       <c r="D15" t="n">
-        <v>90.43704649618121</v>
+        <v>90.43707701679384</v>
       </c>
       <c r="E15" t="n">
-        <v>90.41906998160671</v>
+        <v>90.41910049615264</v>
       </c>
       <c r="F15" t="n">
-        <v>90.4325540821994</v>
+        <v>90.43258460129594</v>
       </c>
       <c r="G15" t="n">
         <v>4307000</v>
@@ -794,16 +794,16 @@
         <v>45314</v>
       </c>
       <c r="C16" t="n">
-        <v>90.44606018066406</v>
+        <v>90.446044921875</v>
       </c>
       <c r="D16" t="n">
-        <v>90.44606018066406</v>
+        <v>90.446044921875</v>
       </c>
       <c r="E16" t="n">
-        <v>90.43706849186626</v>
+        <v>90.43705323459413</v>
       </c>
       <c r="F16" t="n">
-        <v>90.43706849186626</v>
+        <v>90.43705323459413</v>
       </c>
       <c r="G16" t="n">
         <v>2066200</v>
@@ -817,16 +817,16 @@
         <v>45315</v>
       </c>
       <c r="C17" t="n">
-        <v>90.45506286621094</v>
+        <v>90.45503234863281</v>
       </c>
       <c r="D17" t="n">
-        <v>90.45506286621094</v>
+        <v>90.45503234863281</v>
       </c>
       <c r="E17" t="n">
-        <v>90.44607117631999</v>
+        <v>90.44604066177547</v>
       </c>
       <c r="F17" t="n">
-        <v>90.44607117631999</v>
+        <v>90.44604066177547</v>
       </c>
       <c r="G17" t="n">
         <v>3441600</v>
@@ -840,16 +840,16 @@
         <v>45316</v>
       </c>
       <c r="C18" t="n">
-        <v>90.49999237060547</v>
+        <v>90.50000762939453</v>
       </c>
       <c r="D18" t="n">
-        <v>90.49999237060547</v>
+        <v>90.50000762939453</v>
       </c>
       <c r="E18" t="n">
-        <v>90.48201585249815</v>
+        <v>90.48203110825628</v>
       </c>
       <c r="F18" t="n">
-        <v>90.48201585249815</v>
+        <v>90.48203110825628</v>
       </c>
       <c r="G18" t="n">
         <v>2426000</v>
@@ -863,16 +863,16 @@
         <v>45317</v>
       </c>
       <c r="C19" t="n">
-        <v>90.49999237060547</v>
+        <v>90.50000762939453</v>
       </c>
       <c r="D19" t="n">
-        <v>90.50898405898346</v>
+        <v>90.50899931928856</v>
       </c>
       <c r="E19" t="n">
-        <v>90.49999237060547</v>
+        <v>90.50000762939453</v>
       </c>
       <c r="F19" t="n">
-        <v>90.50898405898346</v>
+        <v>90.50899931928856</v>
       </c>
       <c r="G19" t="n">
         <v>2059100</v>
@@ -909,16 +909,16 @@
         <v>45321</v>
       </c>
       <c r="C21" t="n">
-        <v>90.53595733642578</v>
+        <v>90.53597259521484</v>
       </c>
       <c r="D21" t="n">
-        <v>90.53595733642578</v>
+        <v>90.53597259521484</v>
       </c>
       <c r="E21" t="n">
-        <v>90.52696564754417</v>
+        <v>90.52698090481779</v>
       </c>
       <c r="F21" t="n">
-        <v>90.52696564754417</v>
+        <v>90.52698090481779</v>
       </c>
       <c r="G21" t="n">
         <v>3741000</v>
@@ -932,16 +932,16 @@
         <v>45322</v>
       </c>
       <c r="C22" t="n">
-        <v>90.53595733642578</v>
+        <v>90.53597259521484</v>
       </c>
       <c r="D22" t="n">
-        <v>90.54494902530739</v>
+        <v>90.5449642856119</v>
       </c>
       <c r="E22" t="n">
-        <v>90.53595733642578</v>
+        <v>90.53597259521484</v>
       </c>
       <c r="F22" t="n">
-        <v>90.53595733642578</v>
+        <v>90.53597259521484</v>
       </c>
       <c r="G22" t="n">
         <v>5171300</v>
@@ -955,16 +955,16 @@
         <v>45323</v>
       </c>
       <c r="C23" t="n">
-        <v>90.58834075927734</v>
+        <v>90.58832550048828</v>
       </c>
       <c r="D23" t="n">
-        <v>90.59737352716907</v>
+        <v>90.59735826685852</v>
       </c>
       <c r="E23" t="n">
-        <v>90.58834075927734</v>
+        <v>90.58832550048828</v>
       </c>
       <c r="F23" t="n">
-        <v>90.59737352716907</v>
+        <v>90.59735826685852</v>
       </c>
       <c r="G23" t="n">
         <v>7038600</v>
@@ -978,16 +978,16 @@
         <v>45324</v>
       </c>
       <c r="C24" t="n">
-        <v>90.59737396240234</v>
+        <v>90.59735870361328</v>
       </c>
       <c r="D24" t="n">
-        <v>90.59737396240234</v>
+        <v>90.59735870361328</v>
       </c>
       <c r="E24" t="n">
-        <v>90.58834119446723</v>
+        <v>90.5883259371995</v>
       </c>
       <c r="F24" t="n">
-        <v>90.59737396240234</v>
+        <v>90.59735870361328</v>
       </c>
       <c r="G24" t="n">
         <v>3864800</v>
@@ -1001,16 +1001,16 @@
         <v>45327</v>
       </c>
       <c r="C25" t="n">
-        <v>90.61542510986328</v>
+        <v>90.61543273925781</v>
       </c>
       <c r="D25" t="n">
-        <v>90.61542510986328</v>
+        <v>90.61543273925781</v>
       </c>
       <c r="E25" t="n">
-        <v>90.60639923265822</v>
+        <v>90.60640686129281</v>
       </c>
       <c r="F25" t="n">
-        <v>90.61542510986328</v>
+        <v>90.61543273925781</v>
       </c>
       <c r="G25" t="n">
         <v>3969400</v>
@@ -1024,16 +1024,16 @@
         <v>45328</v>
       </c>
       <c r="C26" t="n">
-        <v>90.62445831298828</v>
+        <v>90.62447357177734</v>
       </c>
       <c r="D26" t="n">
-        <v>90.6334910802194</v>
+        <v>90.63350634052934</v>
       </c>
       <c r="E26" t="n">
-        <v>90.61542554575718</v>
+        <v>90.61544080302535</v>
       </c>
       <c r="F26" t="n">
-        <v>90.62445831298828</v>
+        <v>90.62447357177734</v>
       </c>
       <c r="G26" t="n">
         <v>2167300</v>
@@ -1070,16 +1070,16 @@
         <v>45330</v>
       </c>
       <c r="C28" t="n">
-        <v>90.66960906982422</v>
+        <v>90.66961669921875</v>
       </c>
       <c r="D28" t="n">
-        <v>90.68766771307108</v>
+        <v>90.68767534398516</v>
       </c>
       <c r="E28" t="n">
-        <v>90.66960906982422</v>
+        <v>90.66961669921875</v>
       </c>
       <c r="F28" t="n">
-        <v>90.66960906982422</v>
+        <v>90.66961669921875</v>
       </c>
       <c r="G28" t="n">
         <v>3838700</v>
@@ -1093,16 +1093,16 @@
         <v>45331</v>
       </c>
       <c r="C29" t="n">
-        <v>90.69672393798828</v>
+        <v>90.69670104980469</v>
       </c>
       <c r="D29" t="n">
-        <v>90.69672393798828</v>
+        <v>90.69670104980469</v>
       </c>
       <c r="E29" t="n">
-        <v>90.68317822955406</v>
+        <v>90.68315534478884</v>
       </c>
       <c r="F29" t="n">
-        <v>90.68769116903748</v>
+        <v>90.68766828313339</v>
       </c>
       <c r="G29" t="n">
         <v>3232500</v>
@@ -1116,16 +1116,16 @@
         <v>45334</v>
       </c>
       <c r="C30" t="n">
-        <v>90.69672393798828</v>
+        <v>90.69670104980469</v>
       </c>
       <c r="D30" t="n">
-        <v>90.71478258590592</v>
+        <v>90.71475969316506</v>
       </c>
       <c r="E30" t="n">
-        <v>90.69672393798828</v>
+        <v>90.69670104980469</v>
       </c>
       <c r="F30" t="n">
-        <v>90.70575670693907</v>
+        <v>90.70573381647597</v>
       </c>
       <c r="G30" t="n">
         <v>2792700</v>
@@ -1139,16 +1139,16 @@
         <v>45335</v>
       </c>
       <c r="C31" t="n">
-        <v>90.71474456787109</v>
+        <v>90.71476745605469</v>
       </c>
       <c r="D31" t="n">
-        <v>90.71474456787109</v>
+        <v>90.71476745605469</v>
       </c>
       <c r="E31" t="n">
-        <v>90.70571869268693</v>
+        <v>90.70574157859322</v>
       </c>
       <c r="F31" t="n">
-        <v>90.71474456787109</v>
+        <v>90.71476745605469</v>
       </c>
       <c r="G31" t="n">
         <v>3009000</v>
@@ -1162,16 +1162,16 @@
         <v>45336</v>
       </c>
       <c r="C32" t="n">
-        <v>90.73281097412109</v>
+        <v>90.73281860351562</v>
       </c>
       <c r="D32" t="n">
-        <v>90.73281097412109</v>
+        <v>90.73281860351562</v>
       </c>
       <c r="E32" t="n">
-        <v>90.72377820886868</v>
+        <v>90.72378583750368</v>
       </c>
       <c r="F32" t="n">
-        <v>90.73281097412109</v>
+        <v>90.73281860351562</v>
       </c>
       <c r="G32" t="n">
         <v>2614100</v>
@@ -1208,16 +1208,16 @@
         <v>45338</v>
       </c>
       <c r="C34" t="n">
-        <v>90.78702545166016</v>
+        <v>90.78701782226562</v>
       </c>
       <c r="D34" t="n">
-        <v>90.79605822006314</v>
+        <v>90.79605058990954</v>
       </c>
       <c r="E34" t="n">
-        <v>90.78702545166016</v>
+        <v>90.78701782226562</v>
       </c>
       <c r="F34" t="n">
-        <v>90.79605822006314</v>
+        <v>90.79605058990954</v>
       </c>
       <c r="G34" t="n">
         <v>2920700</v>
@@ -1277,16 +1277,16 @@
         <v>45344</v>
       </c>
       <c r="C37" t="n">
-        <v>90.8502197265625</v>
+        <v>90.85022735595703</v>
       </c>
       <c r="D37" t="n">
-        <v>90.85925249284537</v>
+        <v>90.85926012299844</v>
       </c>
       <c r="E37" t="n">
-        <v>90.8502197265625</v>
+        <v>90.85022735595703</v>
       </c>
       <c r="F37" t="n">
-        <v>90.8502197265625</v>
+        <v>90.85022735595703</v>
       </c>
       <c r="G37" t="n">
         <v>2452200</v>
@@ -1300,16 +1300,16 @@
         <v>45345</v>
       </c>
       <c r="C38" t="n">
-        <v>90.87731170654297</v>
+        <v>90.87733459472656</v>
       </c>
       <c r="D38" t="n">
-        <v>90.87731170654297</v>
+        <v>90.87733459472656</v>
       </c>
       <c r="E38" t="n">
-        <v>90.8682858301853</v>
+        <v>90.86830871609565</v>
       </c>
       <c r="F38" t="n">
-        <v>90.87731170654297</v>
+        <v>90.87733459472656</v>
       </c>
       <c r="G38" t="n">
         <v>2010100</v>
@@ -1323,16 +1323,16 @@
         <v>45348</v>
       </c>
       <c r="C39" t="n">
-        <v>90.88633728027344</v>
+        <v>90.8863525390625</v>
       </c>
       <c r="D39" t="n">
-        <v>90.89537004589823</v>
+        <v>90.89538530620379</v>
       </c>
       <c r="E39" t="n">
-        <v>90.88633728027344</v>
+        <v>90.8863525390625</v>
       </c>
       <c r="F39" t="n">
-        <v>90.88633728027344</v>
+        <v>90.8863525390625</v>
       </c>
       <c r="G39" t="n">
         <v>2645100</v>
@@ -1346,16 +1346,16 @@
         <v>45349</v>
       </c>
       <c r="C40" t="n">
-        <v>90.90442657470703</v>
+        <v>90.90440368652344</v>
       </c>
       <c r="D40" t="n">
-        <v>90.90442657470703</v>
+        <v>90.90440368652344</v>
       </c>
       <c r="E40" t="n">
-        <v>90.895393806721</v>
+        <v>90.8953709208117</v>
       </c>
       <c r="F40" t="n">
-        <v>90.90442657470703</v>
+        <v>90.90440368652344</v>
       </c>
       <c r="G40" t="n">
         <v>2360300</v>
@@ -1392,16 +1392,16 @@
         <v>45351</v>
       </c>
       <c r="C42" t="n">
-        <v>90.94053649902344</v>
+        <v>90.94052886962891</v>
       </c>
       <c r="D42" t="n">
-        <v>90.94956926627766</v>
+        <v>90.94956163612534</v>
       </c>
       <c r="E42" t="n">
-        <v>90.94053649902344</v>
+        <v>90.94052886962891</v>
       </c>
       <c r="F42" t="n">
-        <v>90.94053649902344</v>
+        <v>90.94052886962891</v>
       </c>
       <c r="G42" t="n">
         <v>5560200</v>
@@ -1438,16 +1438,16 @@
         <v>45355</v>
       </c>
       <c r="C44" t="n">
-        <v>90.97681427001953</v>
+        <v>90.97679901123047</v>
       </c>
       <c r="D44" t="n">
-        <v>90.98587704661217</v>
+        <v>90.98586178630309</v>
       </c>
       <c r="E44" t="n">
-        <v>90.97681427001953</v>
+        <v>90.97679901123047</v>
       </c>
       <c r="F44" t="n">
-        <v>90.97681427001953</v>
+        <v>90.97679901123047</v>
       </c>
       <c r="G44" t="n">
         <v>3613500</v>
@@ -1484,16 +1484,16 @@
         <v>45357</v>
       </c>
       <c r="C46" t="n">
-        <v>91.00402069091797</v>
+        <v>91.00400543212891</v>
       </c>
       <c r="D46" t="n">
-        <v>91.01309038608471</v>
+        <v>91.01307512577493</v>
       </c>
       <c r="E46" t="n">
-        <v>90.99495099575121</v>
+        <v>90.99493573848288</v>
       </c>
       <c r="F46" t="n">
-        <v>91.00402069091797</v>
+        <v>91.00400543212891</v>
       </c>
       <c r="G46" t="n">
         <v>2760000</v>
@@ -1507,16 +1507,16 @@
         <v>45358</v>
       </c>
       <c r="C47" t="n">
-        <v>91.04935455322266</v>
+        <v>91.04934692382812</v>
       </c>
       <c r="D47" t="n">
-        <v>91.04935455322266</v>
+        <v>91.04934692382812</v>
       </c>
       <c r="E47" t="n">
-        <v>91.04028485882247</v>
+        <v>91.04027723018791</v>
       </c>
       <c r="F47" t="n">
-        <v>91.04935455322266</v>
+        <v>91.04934692382812</v>
       </c>
       <c r="G47" t="n">
         <v>2415500</v>
@@ -1530,16 +1530,16 @@
         <v>45359</v>
       </c>
       <c r="C48" t="n">
-        <v>91.05841064453125</v>
+        <v>91.05841827392578</v>
       </c>
       <c r="D48" t="n">
-        <v>91.06748033826561</v>
+        <v>91.06748796842004</v>
       </c>
       <c r="E48" t="n">
-        <v>91.0493478689462</v>
+        <v>91.0493554975814</v>
       </c>
       <c r="F48" t="n">
-        <v>91.06748033826561</v>
+        <v>91.06748796842004</v>
       </c>
       <c r="G48" t="n">
         <v>3748900</v>
@@ -1553,16 +1553,16 @@
         <v>45362</v>
       </c>
       <c r="C49" t="n">
-        <v>91.07656097412109</v>
+        <v>91.07655334472656</v>
       </c>
       <c r="D49" t="n">
-        <v>91.07656097412109</v>
+        <v>91.07655334472656</v>
       </c>
       <c r="E49" t="n">
-        <v>91.06749127929709</v>
+        <v>91.06748365066231</v>
       </c>
       <c r="F49" t="n">
-        <v>91.07656097412109</v>
+        <v>91.07655334472656</v>
       </c>
       <c r="G49" t="n">
         <v>3238400</v>
@@ -1576,16 +1576,16 @@
         <v>45363</v>
       </c>
       <c r="C50" t="n">
-        <v>91.08560180664062</v>
+        <v>91.08562469482422</v>
       </c>
       <c r="D50" t="n">
-        <v>91.09467149927958</v>
+        <v>91.09469438974223</v>
       </c>
       <c r="E50" t="n">
-        <v>91.08560180664062</v>
+        <v>91.08562469482422</v>
       </c>
       <c r="F50" t="n">
-        <v>91.08560180664062</v>
+        <v>91.08562469482422</v>
       </c>
       <c r="G50" t="n">
         <v>2613300</v>
@@ -1599,16 +1599,16 @@
         <v>45364</v>
       </c>
       <c r="C51" t="n">
-        <v>91.09469604492188</v>
+        <v>91.09471130371094</v>
       </c>
       <c r="D51" t="n">
-        <v>91.10376574000468</v>
+        <v>91.10378100031295</v>
       </c>
       <c r="E51" t="n">
-        <v>91.09469604492188</v>
+        <v>91.09471130371094</v>
       </c>
       <c r="F51" t="n">
-        <v>91.09469604492188</v>
+        <v>91.09471130371094</v>
       </c>
       <c r="G51" t="n">
         <v>2249300</v>
@@ -1622,16 +1622,16 @@
         <v>45365</v>
       </c>
       <c r="C52" t="n">
-        <v>91.13094329833984</v>
+        <v>91.13095092773438</v>
       </c>
       <c r="D52" t="n">
-        <v>91.14001299097349</v>
+        <v>91.14002062112732</v>
       </c>
       <c r="E52" t="n">
-        <v>91.13094329833984</v>
+        <v>91.13095092773438</v>
       </c>
       <c r="F52" t="n">
-        <v>91.13094329833984</v>
+        <v>91.13095092773438</v>
       </c>
       <c r="G52" t="n">
         <v>3469600</v>
@@ -1645,16 +1645,16 @@
         <v>45366</v>
       </c>
       <c r="C53" t="n">
-        <v>91.14909362792969</v>
+        <v>91.14910888671875</v>
       </c>
       <c r="D53" t="n">
-        <v>91.14909362792969</v>
+        <v>91.14910888671875</v>
       </c>
       <c r="E53" t="n">
-        <v>91.14003085166847</v>
+        <v>91.14004610894038</v>
       </c>
       <c r="F53" t="n">
-        <v>91.14909362792969</v>
+        <v>91.14910888671875</v>
       </c>
       <c r="G53" t="n">
         <v>3277300</v>
@@ -1668,16 +1668,16 @@
         <v>45369</v>
       </c>
       <c r="C54" t="n">
-        <v>91.15814971923828</v>
+        <v>91.15816497802734</v>
       </c>
       <c r="D54" t="n">
-        <v>91.16721941229589</v>
+        <v>91.1672346726031</v>
       </c>
       <c r="E54" t="n">
-        <v>91.15814971923828</v>
+        <v>91.15816497802734</v>
       </c>
       <c r="F54" t="n">
-        <v>91.16721941229589</v>
+        <v>91.1672346726031</v>
       </c>
       <c r="G54" t="n">
         <v>3576200</v>
@@ -1691,16 +1691,16 @@
         <v>45370</v>
       </c>
       <c r="C55" t="n">
-        <v>91.17629241943359</v>
+        <v>91.17630767822266</v>
       </c>
       <c r="D55" t="n">
-        <v>91.18535519467183</v>
+        <v>91.18537045497759</v>
       </c>
       <c r="E55" t="n">
-        <v>91.17629241943359</v>
+        <v>91.17630767822266</v>
       </c>
       <c r="F55" t="n">
-        <v>91.18535519467183</v>
+        <v>91.18537045497759</v>
       </c>
       <c r="G55" t="n">
         <v>2661900</v>
@@ -1714,16 +1714,16 @@
         <v>45371</v>
       </c>
       <c r="C56" t="n">
-        <v>91.18537902832031</v>
+        <v>91.18537139892578</v>
       </c>
       <c r="D56" t="n">
-        <v>91.19444872407817</v>
+        <v>91.19444109392479</v>
       </c>
       <c r="E56" t="n">
-        <v>91.18537902832031</v>
+        <v>91.18537139892578</v>
       </c>
       <c r="F56" t="n">
-        <v>91.18537902832031</v>
+        <v>91.18537139892578</v>
       </c>
       <c r="G56" t="n">
         <v>2492700</v>
@@ -1737,16 +1737,16 @@
         <v>45372</v>
       </c>
       <c r="C57" t="n">
-        <v>91.22163391113281</v>
+        <v>91.22164154052734</v>
       </c>
       <c r="D57" t="n">
-        <v>91.23070360520224</v>
+        <v>91.23071123535532</v>
       </c>
       <c r="E57" t="n">
-        <v>91.22163391113281</v>
+        <v>91.22164154052734</v>
       </c>
       <c r="F57" t="n">
-        <v>91.22163391113281</v>
+        <v>91.22164154052734</v>
       </c>
       <c r="G57" t="n">
         <v>3547400</v>
@@ -1760,16 +1760,16 @@
         <v>45373</v>
       </c>
       <c r="C58" t="n">
-        <v>91.23976898193359</v>
+        <v>91.23978424072266</v>
       </c>
       <c r="D58" t="n">
-        <v>91.24883175742463</v>
+        <v>91.24884701772933</v>
       </c>
       <c r="E58" t="n">
-        <v>91.23069928829332</v>
+        <v>91.2307145455656</v>
       </c>
       <c r="F58" t="n">
-        <v>91.24883175742463</v>
+        <v>91.24884701772933</v>
       </c>
       <c r="G58" t="n">
         <v>2636700</v>
@@ -1783,16 +1783,16 @@
         <v>45376</v>
       </c>
       <c r="C59" t="n">
-        <v>91.25788879394531</v>
+        <v>91.25791168212891</v>
       </c>
       <c r="D59" t="n">
-        <v>91.26695848632765</v>
+        <v>91.26698137678599</v>
       </c>
       <c r="E59" t="n">
-        <v>91.25788879394531</v>
+        <v>91.25791168212891</v>
       </c>
       <c r="F59" t="n">
-        <v>91.25788879394531</v>
+        <v>91.25791168212891</v>
       </c>
       <c r="G59" t="n">
         <v>2422900</v>
@@ -1875,16 +1875,16 @@
         <v>45383</v>
       </c>
       <c r="C63" t="n">
-        <v>91.34870910644531</v>
+        <v>91.34871673583984</v>
       </c>
       <c r="D63" t="n">
-        <v>91.35781950852548</v>
+        <v>91.3578271386809</v>
       </c>
       <c r="E63" t="n">
-        <v>91.34870910644531</v>
+        <v>91.34871673583984</v>
       </c>
       <c r="F63" t="n">
-        <v>91.35781950852548</v>
+        <v>91.3578271386809</v>
       </c>
       <c r="G63" t="n">
         <v>7395400</v>
@@ -1944,16 +1944,16 @@
         <v>45386</v>
       </c>
       <c r="C66" t="n">
-        <v>91.42156219482422</v>
+        <v>91.42157745361328</v>
       </c>
       <c r="D66" t="n">
-        <v>91.42156219482422</v>
+        <v>91.42157745361328</v>
       </c>
       <c r="E66" t="n">
-        <v>91.4124517943614</v>
+        <v>91.41246705162989</v>
       </c>
       <c r="F66" t="n">
-        <v>91.4124517943614</v>
+        <v>91.41246705162989</v>
       </c>
       <c r="G66" t="n">
         <v>3427500</v>
@@ -1967,16 +1967,16 @@
         <v>45387</v>
       </c>
       <c r="C67" t="n">
-        <v>91.43069458007812</v>
+        <v>91.43067932128906</v>
       </c>
       <c r="D67" t="n">
-        <v>91.439804983424</v>
+        <v>91.43978972311452</v>
       </c>
       <c r="E67" t="n">
-        <v>91.43069458007812</v>
+        <v>91.43067932128906</v>
       </c>
       <c r="F67" t="n">
-        <v>91.439804983424</v>
+        <v>91.43978972311452</v>
       </c>
       <c r="G67" t="n">
         <v>3104200</v>
@@ -1990,16 +1990,16 @@
         <v>45390</v>
       </c>
       <c r="C68" t="n">
-        <v>91.44892120361328</v>
+        <v>91.44890594482422</v>
       </c>
       <c r="D68" t="n">
-        <v>91.44892120361328</v>
+        <v>91.44890594482422</v>
       </c>
       <c r="E68" t="n">
-        <v>91.43981079968792</v>
+        <v>91.43979554241898</v>
       </c>
       <c r="F68" t="n">
-        <v>91.44892120361328</v>
+        <v>91.44890594482422</v>
       </c>
       <c r="G68" t="n">
         <v>3511400</v>
@@ -2013,16 +2013,16 @@
         <v>45391</v>
       </c>
       <c r="C69" t="n">
-        <v>91.45799255371094</v>
+        <v>91.45800018310547</v>
       </c>
       <c r="D69" t="n">
-        <v>91.45799255371094</v>
+        <v>91.45800018310547</v>
       </c>
       <c r="E69" t="n">
-        <v>91.44888215367584</v>
+        <v>91.44888978231037</v>
       </c>
       <c r="F69" t="n">
-        <v>91.45799255371094</v>
+        <v>91.45800018310547</v>
       </c>
       <c r="G69" t="n">
         <v>3578500</v>
@@ -2082,16 +2082,16 @@
         <v>45394</v>
       </c>
       <c r="C72" t="n">
-        <v>91.52177429199219</v>
+        <v>91.52176666259766</v>
       </c>
       <c r="D72" t="n">
-        <v>91.52177429199219</v>
+        <v>91.52176666259766</v>
       </c>
       <c r="E72" t="n">
-        <v>91.51266388968386</v>
+        <v>91.51265626104879</v>
       </c>
       <c r="F72" t="n">
-        <v>91.52177429199219</v>
+        <v>91.52176666259766</v>
       </c>
       <c r="G72" t="n">
         <v>4235400</v>
@@ -2105,16 +2105,16 @@
         <v>45397</v>
       </c>
       <c r="C73" t="n">
-        <v>91.53995513916016</v>
+        <v>91.53997802734375</v>
       </c>
       <c r="D73" t="n">
-        <v>91.53995513916016</v>
+        <v>91.53997802734375</v>
       </c>
       <c r="E73" t="n">
-        <v>91.53084474013694</v>
+        <v>91.53086762604262</v>
       </c>
       <c r="F73" t="n">
-        <v>91.53084474013694</v>
+        <v>91.53086762604262</v>
       </c>
       <c r="G73" t="n">
         <v>4144700</v>
@@ -2128,16 +2128,16 @@
         <v>45398</v>
       </c>
       <c r="C74" t="n">
-        <v>91.53995513916016</v>
+        <v>91.53997802734375</v>
       </c>
       <c r="D74" t="n">
-        <v>91.55816898800823</v>
+        <v>91.55819188074594</v>
       </c>
       <c r="E74" t="n">
-        <v>91.53995513916016</v>
+        <v>91.53997802734375</v>
       </c>
       <c r="F74" t="n">
-        <v>91.54906553818337</v>
+        <v>91.54908842864488</v>
       </c>
       <c r="G74" t="n">
         <v>4850000</v>
@@ -2151,16 +2151,16 @@
         <v>45399</v>
       </c>
       <c r="C75" t="n">
-        <v>91.56732177734375</v>
+        <v>91.56729125976562</v>
       </c>
       <c r="D75" t="n">
-        <v>91.56732177734375</v>
+        <v>91.56729125976562</v>
       </c>
       <c r="E75" t="n">
-        <v>91.55821137410295</v>
+        <v>91.55818085956115</v>
       </c>
       <c r="F75" t="n">
-        <v>91.56732177734375</v>
+        <v>91.56729125976562</v>
       </c>
       <c r="G75" t="n">
         <v>3688400</v>
@@ -2197,16 +2197,16 @@
         <v>45401</v>
       </c>
       <c r="C77" t="n">
-        <v>91.62197875976562</v>
+        <v>91.62193298339844</v>
       </c>
       <c r="D77" t="n">
-        <v>91.62197875976562</v>
+        <v>91.62193298339844</v>
       </c>
       <c r="E77" t="n">
-        <v>91.60376490080353</v>
+        <v>91.60371913353637</v>
       </c>
       <c r="F77" t="n">
-        <v>91.62197875976562</v>
+        <v>91.62193298339844</v>
       </c>
       <c r="G77" t="n">
         <v>3319500</v>
@@ -2220,16 +2220,16 @@
         <v>45404</v>
       </c>
       <c r="C78" t="n">
-        <v>91.63105010986328</v>
+        <v>91.63107299804688</v>
       </c>
       <c r="D78" t="n">
-        <v>91.63105010986328</v>
+        <v>91.63107299804688</v>
       </c>
       <c r="E78" t="n">
-        <v>91.62193970966408</v>
+        <v>91.621962595572</v>
       </c>
       <c r="F78" t="n">
-        <v>91.63105010986328</v>
+        <v>91.63107299804688</v>
       </c>
       <c r="G78" t="n">
         <v>3547400</v>
@@ -2266,16 +2266,16 @@
         <v>45406</v>
       </c>
       <c r="C80" t="n">
-        <v>91.6492919921875</v>
+        <v>91.64927673339844</v>
       </c>
       <c r="D80" t="n">
-        <v>91.65839544528153</v>
+        <v>91.65838018497682</v>
       </c>
       <c r="E80" t="n">
-        <v>91.6492919921875</v>
+        <v>91.64927673339844</v>
       </c>
       <c r="F80" t="n">
-        <v>91.65839544528153</v>
+        <v>91.65838018497682</v>
       </c>
       <c r="G80" t="n">
         <v>3200000</v>
@@ -2289,16 +2289,16 @@
         <v>45407</v>
       </c>
       <c r="C81" t="n">
-        <v>91.69483947753906</v>
+        <v>91.69481658935547</v>
       </c>
       <c r="D81" t="n">
-        <v>91.69483947753906</v>
+        <v>91.69481658935547</v>
       </c>
       <c r="E81" t="n">
-        <v>91.68573602351455</v>
+        <v>91.68571313760329</v>
       </c>
       <c r="F81" t="n">
-        <v>91.69483947753906</v>
+        <v>91.69481658935547</v>
       </c>
       <c r="G81" t="n">
         <v>2705900</v>
@@ -2312,16 +2312,16 @@
         <v>45408</v>
       </c>
       <c r="C82" t="n">
-        <v>91.71303558349609</v>
+        <v>91.71302795410156</v>
       </c>
       <c r="D82" t="n">
-        <v>91.71303558349609</v>
+        <v>91.71302795410156</v>
       </c>
       <c r="E82" t="n">
-        <v>91.70392518272369</v>
+        <v>91.70391755408703</v>
       </c>
       <c r="F82" t="n">
-        <v>91.70392518272369</v>
+        <v>91.70391755408703</v>
       </c>
       <c r="G82" t="n">
         <v>3008600</v>
@@ -2335,16 +2335,16 @@
         <v>45411</v>
       </c>
       <c r="C83" t="n">
-        <v>91.71303558349609</v>
+        <v>91.71302795410156</v>
       </c>
       <c r="D83" t="n">
-        <v>91.72213903506884</v>
+        <v>91.72213140491701</v>
       </c>
       <c r="E83" t="n">
-        <v>91.71303558349609</v>
+        <v>91.71302795410156</v>
       </c>
       <c r="F83" t="n">
-        <v>91.72213903506884</v>
+        <v>91.72213140491701</v>
       </c>
       <c r="G83" t="n">
         <v>2501900</v>
@@ -2381,16 +2381,16 @@
         <v>45413</v>
       </c>
       <c r="C85" t="n">
-        <v>91.75691223144531</v>
+        <v>91.75688934326172</v>
       </c>
       <c r="D85" t="n">
-        <v>91.75691223144531</v>
+        <v>91.75688934326172</v>
       </c>
       <c r="E85" t="n">
-        <v>91.74776992151747</v>
+        <v>91.74774703561437</v>
       </c>
       <c r="F85" t="n">
-        <v>91.75691223144531</v>
+        <v>91.75688934326172</v>
       </c>
       <c r="G85" t="n">
         <v>8406600</v>
@@ -2404,16 +2404,16 @@
         <v>45414</v>
       </c>
       <c r="C86" t="n">
-        <v>91.79349517822266</v>
+        <v>91.79348754882812</v>
       </c>
       <c r="D86" t="n">
-        <v>91.79349517822266</v>
+        <v>91.79348754882812</v>
       </c>
       <c r="E86" t="n">
-        <v>91.78434589015285</v>
+        <v>91.78433826151877</v>
       </c>
       <c r="F86" t="n">
-        <v>91.79349517822266</v>
+        <v>91.79348754882812</v>
       </c>
       <c r="G86" t="n">
         <v>4369600</v>
@@ -2427,16 +2427,16 @@
         <v>45415</v>
       </c>
       <c r="C87" t="n">
-        <v>91.81179046630859</v>
+        <v>91.81179809570312</v>
       </c>
       <c r="D87" t="n">
-        <v>91.81179046630859</v>
+        <v>91.81179809570312</v>
       </c>
       <c r="E87" t="n">
-        <v>91.79349189082433</v>
+        <v>91.79349951869828</v>
       </c>
       <c r="F87" t="n">
-        <v>91.80264117856646</v>
+        <v>91.8026488072007</v>
       </c>
       <c r="G87" t="n">
         <v>4792400</v>
@@ -2450,16 +2450,16 @@
         <v>45418</v>
       </c>
       <c r="C88" t="n">
-        <v>91.82094573974609</v>
+        <v>91.82093811035156</v>
       </c>
       <c r="D88" t="n">
-        <v>91.82094573974609</v>
+        <v>91.82093811035156</v>
       </c>
       <c r="E88" t="n">
-        <v>91.81180342957487</v>
+        <v>91.81179580093996</v>
       </c>
       <c r="F88" t="n">
-        <v>91.81180342957487</v>
+        <v>91.81179580093996</v>
       </c>
       <c r="G88" t="n">
         <v>3623700</v>
@@ -2473,16 +2473,16 @@
         <v>45419</v>
       </c>
       <c r="C89" t="n">
-        <v>91.82094573974609</v>
+        <v>91.82093811035156</v>
       </c>
       <c r="D89" t="n">
-        <v>91.83009502878005</v>
+        <v>91.83008739862531</v>
       </c>
       <c r="E89" t="n">
-        <v>91.82094573974609</v>
+        <v>91.82093811035156</v>
       </c>
       <c r="F89" t="n">
-        <v>91.83009502878005</v>
+        <v>91.83008739862531</v>
       </c>
       <c r="G89" t="n">
         <v>3591500</v>
@@ -2519,16 +2519,16 @@
         <v>45421</v>
       </c>
       <c r="C91" t="n">
-        <v>91.87582397460938</v>
+        <v>91.87583160400391</v>
       </c>
       <c r="D91" t="n">
-        <v>91.88496628373375</v>
+        <v>91.88497391388746</v>
       </c>
       <c r="E91" t="n">
-        <v>91.87582397460938</v>
+        <v>91.87583160400391</v>
       </c>
       <c r="F91" t="n">
-        <v>91.88039512917156</v>
+        <v>91.88040275894568</v>
       </c>
       <c r="G91" t="n">
         <v>2739600</v>
@@ -2565,16 +2565,16 @@
         <v>45425</v>
       </c>
       <c r="C93" t="n">
-        <v>91.91242980957031</v>
+        <v>91.91242218017578</v>
       </c>
       <c r="D93" t="n">
-        <v>91.91242980957031</v>
+        <v>91.91242218017578</v>
       </c>
       <c r="E93" t="n">
-        <v>91.90328052002498</v>
+        <v>91.9032728913899</v>
       </c>
       <c r="F93" t="n">
-        <v>91.91242980957031</v>
+        <v>91.91242218017578</v>
       </c>
       <c r="G93" t="n">
         <v>3317000</v>
@@ -2588,16 +2588,16 @@
         <v>45426</v>
       </c>
       <c r="C94" t="n">
-        <v>91.91242980957031</v>
+        <v>91.91242218017578</v>
       </c>
       <c r="D94" t="n">
-        <v>91.92157212025253</v>
+        <v>91.92156449009912</v>
       </c>
       <c r="E94" t="n">
-        <v>91.91242980957031</v>
+        <v>91.91242218017578</v>
       </c>
       <c r="F94" t="n">
-        <v>91.92157212025253</v>
+        <v>91.92156449009912</v>
       </c>
       <c r="G94" t="n">
         <v>2765800</v>
@@ -2634,16 +2634,16 @@
         <v>45428</v>
       </c>
       <c r="C96" t="n">
-        <v>91.97644805908203</v>
+        <v>91.9764404296875</v>
       </c>
       <c r="D96" t="n">
-        <v>91.98559036849001</v>
+        <v>91.98558273833711</v>
       </c>
       <c r="E96" t="n">
-        <v>91.96729877081192</v>
+        <v>91.96729114217631</v>
       </c>
       <c r="F96" t="n">
-        <v>91.97644805908203</v>
+        <v>91.9764404296875</v>
       </c>
       <c r="G96" t="n">
         <v>3699500</v>
@@ -2703,16 +2703,16 @@
         <v>45433</v>
       </c>
       <c r="C99" t="n">
-        <v>92.01304626464844</v>
+        <v>92.01302337646484</v>
       </c>
       <c r="D99" t="n">
-        <v>92.02219555441108</v>
+        <v>92.02217266395162</v>
       </c>
       <c r="E99" t="n">
-        <v>92.01304626464844</v>
+        <v>92.01302337646484</v>
       </c>
       <c r="F99" t="n">
-        <v>92.01304626464844</v>
+        <v>92.01302337646484</v>
       </c>
       <c r="G99" t="n">
         <v>3774900</v>
@@ -2726,16 +2726,16 @@
         <v>45434</v>
       </c>
       <c r="C100" t="n">
-        <v>92.02216339111328</v>
+        <v>92.02217864990234</v>
       </c>
       <c r="D100" t="n">
-        <v>92.0313126776781</v>
+        <v>92.03132793798427</v>
       </c>
       <c r="E100" t="n">
-        <v>92.02216339111328</v>
+        <v>92.02217864990234</v>
       </c>
       <c r="F100" t="n">
-        <v>92.0313126776781</v>
+        <v>92.03132793798427</v>
       </c>
       <c r="G100" t="n">
         <v>2609000</v>
@@ -2749,16 +2749,16 @@
         <v>45435</v>
       </c>
       <c r="C101" t="n">
-        <v>92.08622741699219</v>
+        <v>92.08619689941406</v>
       </c>
       <c r="D101" t="n">
-        <v>92.08622741699219</v>
+        <v>92.08619689941406</v>
       </c>
       <c r="E101" t="n">
-        <v>92.0770851060142</v>
+        <v>92.07705459146585</v>
       </c>
       <c r="F101" t="n">
-        <v>92.0770851060142</v>
+        <v>92.07705459146585</v>
       </c>
       <c r="G101" t="n">
         <v>3077800</v>
@@ -2772,16 +2772,16 @@
         <v>45436</v>
       </c>
       <c r="C102" t="n">
-        <v>92.09535217285156</v>
+        <v>92.09538269042969</v>
       </c>
       <c r="D102" t="n">
-        <v>92.09535217285156</v>
+        <v>92.09538269042969</v>
       </c>
       <c r="E102" t="n">
-        <v>92.08620288544756</v>
+        <v>92.0862333999939</v>
       </c>
       <c r="F102" t="n">
-        <v>92.09535217285156</v>
+        <v>92.09538269042969</v>
       </c>
       <c r="G102" t="n">
         <v>2512800</v>
@@ -2841,16 +2841,16 @@
         <v>45442</v>
       </c>
       <c r="C105" t="n">
-        <v>92.122802734375</v>
+        <v>92.12279510498047</v>
       </c>
       <c r="D105" t="n">
-        <v>92.13195202274019</v>
+        <v>92.13194439258794</v>
       </c>
       <c r="E105" t="n">
-        <v>92.122802734375</v>
+        <v>92.12279510498047</v>
       </c>
       <c r="F105" t="n">
-        <v>92.122802734375</v>
+        <v>92.12279510498047</v>
       </c>
       <c r="G105" t="n">
         <v>3566800</v>
@@ -2864,16 +2864,16 @@
         <v>45443</v>
       </c>
       <c r="C106" t="n">
-        <v>92.15939331054688</v>
+        <v>92.15940093994141</v>
       </c>
       <c r="D106" t="n">
-        <v>92.15939331054688</v>
+        <v>92.15940093994141</v>
       </c>
       <c r="E106" t="n">
-        <v>92.15024402214182</v>
+        <v>92.15025165077893</v>
       </c>
       <c r="F106" t="n">
-        <v>92.15024402214182</v>
+        <v>92.15025165077893</v>
       </c>
       <c r="G106" t="n">
         <v>7082900</v>
@@ -2887,16 +2887,16 @@
         <v>45446</v>
       </c>
       <c r="C107" t="n">
-        <v>92.17776489257812</v>
+        <v>92.17777252197266</v>
       </c>
       <c r="D107" t="n">
-        <v>92.18694730346745</v>
+        <v>92.18695493362199</v>
       </c>
       <c r="E107" t="n">
-        <v>92.17776489257812</v>
+        <v>92.17777252197266</v>
       </c>
       <c r="F107" t="n">
-        <v>92.17776489257812</v>
+        <v>92.17777252197266</v>
       </c>
       <c r="G107" t="n">
         <v>9568200</v>
@@ -2979,16 +2979,16 @@
         <v>45450</v>
       </c>
       <c r="C111" t="n">
-        <v>92.25128173828125</v>
+        <v>92.25125122070312</v>
       </c>
       <c r="D111" t="n">
-        <v>92.26046415071357</v>
+        <v>92.26043363009782</v>
       </c>
       <c r="E111" t="n">
-        <v>92.25128173828125</v>
+        <v>92.25125122070312</v>
       </c>
       <c r="F111" t="n">
-        <v>92.26046415071357</v>
+        <v>92.26043363009782</v>
       </c>
       <c r="G111" t="n">
         <v>3490400</v>
@@ -3002,16 +3002,16 @@
         <v>45453</v>
       </c>
       <c r="C112" t="n">
-        <v>92.26964569091797</v>
+        <v>92.26963806152344</v>
       </c>
       <c r="D112" t="n">
-        <v>92.27883511204048</v>
+        <v>92.27882748188611</v>
       </c>
       <c r="E112" t="n">
-        <v>92.26964569091797</v>
+        <v>92.26963806152344</v>
       </c>
       <c r="F112" t="n">
-        <v>92.27883511204048</v>
+        <v>92.27882748188611</v>
       </c>
       <c r="G112" t="n">
         <v>2732300</v>
@@ -3025,16 +3025,16 @@
         <v>45454</v>
       </c>
       <c r="C113" t="n">
-        <v>92.28800964355469</v>
+        <v>92.28800201416016</v>
       </c>
       <c r="D113" t="n">
-        <v>92.28800964355469</v>
+        <v>92.28800201416016</v>
       </c>
       <c r="E113" t="n">
-        <v>92.27882723269077</v>
+        <v>92.27881960405534</v>
       </c>
       <c r="F113" t="n">
-        <v>92.28800964355469</v>
+        <v>92.28800201416016</v>
       </c>
       <c r="G113" t="n">
         <v>3320000</v>
@@ -3048,16 +3048,16 @@
         <v>45455</v>
       </c>
       <c r="C114" t="n">
-        <v>92.30640411376953</v>
+        <v>92.306396484375</v>
       </c>
       <c r="D114" t="n">
-        <v>92.30640411376953</v>
+        <v>92.306396484375</v>
       </c>
       <c r="E114" t="n">
-        <v>92.28802526998187</v>
+        <v>92.28801764210641</v>
       </c>
       <c r="F114" t="n">
-        <v>92.29721469187569</v>
+        <v>92.29720706324071</v>
       </c>
       <c r="G114" t="n">
         <v>5355700</v>
@@ -3071,16 +3071,16 @@
         <v>45456</v>
       </c>
       <c r="C115" t="n">
-        <v>92.31558990478516</v>
+        <v>92.31558227539062</v>
       </c>
       <c r="D115" t="n">
-        <v>92.32477231684271</v>
+        <v>92.32476468668929</v>
       </c>
       <c r="E115" t="n">
-        <v>92.30640048325276</v>
+        <v>92.30639285461768</v>
       </c>
       <c r="F115" t="n">
-        <v>92.31558990478516</v>
+        <v>92.31558227539062</v>
       </c>
       <c r="G115" t="n">
         <v>3925700</v>
@@ -3094,16 +3094,16 @@
         <v>45457</v>
       </c>
       <c r="C116" t="n">
-        <v>92.36150360107422</v>
+        <v>92.36151123046875</v>
       </c>
       <c r="D116" t="n">
-        <v>92.36150360107422</v>
+        <v>92.36151123046875</v>
       </c>
       <c r="E116" t="n">
-        <v>92.34313177134166</v>
+        <v>92.34313939921861</v>
       </c>
       <c r="F116" t="n">
-        <v>92.35231418147126</v>
+        <v>92.3523218101067</v>
       </c>
       <c r="G116" t="n">
         <v>3505500</v>
@@ -3117,16 +3117,16 @@
         <v>45460</v>
       </c>
       <c r="C117" t="n">
-        <v>92.37070465087891</v>
+        <v>92.37071228027344</v>
       </c>
       <c r="D117" t="n">
-        <v>92.37070465087891</v>
+        <v>92.37071228027344</v>
       </c>
       <c r="E117" t="n">
-        <v>92.36151523011891</v>
+        <v>92.36152285875446</v>
       </c>
       <c r="F117" t="n">
-        <v>92.37070465087891</v>
+        <v>92.37071228027344</v>
       </c>
       <c r="G117" t="n">
         <v>3493700</v>
@@ -3140,16 +3140,16 @@
         <v>45461</v>
       </c>
       <c r="C118" t="n">
-        <v>92.39826965332031</v>
+        <v>92.39827728271484</v>
       </c>
       <c r="D118" t="n">
-        <v>92.39826965332031</v>
+        <v>92.39827728271484</v>
       </c>
       <c r="E118" t="n">
-        <v>92.3890802321874</v>
+        <v>92.38908786082315</v>
       </c>
       <c r="F118" t="n">
-        <v>92.39826965332031</v>
+        <v>92.39827728271484</v>
       </c>
       <c r="G118" t="n">
         <v>2972000</v>
@@ -3163,16 +3163,16 @@
         <v>45463</v>
       </c>
       <c r="C119" t="n">
-        <v>92.40746307373047</v>
+        <v>92.40745544433594</v>
       </c>
       <c r="D119" t="n">
-        <v>92.41664548578623</v>
+        <v>92.41663785563358</v>
       </c>
       <c r="E119" t="n">
-        <v>92.40746307373047</v>
+        <v>92.40745544433594</v>
       </c>
       <c r="F119" t="n">
-        <v>92.40746307373047</v>
+        <v>92.40745544433594</v>
       </c>
       <c r="G119" t="n">
         <v>3580700</v>
@@ -3186,16 +3186,16 @@
         <v>45464</v>
       </c>
       <c r="C120" t="n">
-        <v>92.44419860839844</v>
+        <v>92.44420623779297</v>
       </c>
       <c r="D120" t="n">
-        <v>92.45338101895015</v>
+        <v>92.45338864910251</v>
       </c>
       <c r="E120" t="n">
-        <v>92.44419860839844</v>
+        <v>92.44420623779297</v>
       </c>
       <c r="F120" t="n">
-        <v>92.44419860839844</v>
+        <v>92.44420623779297</v>
       </c>
       <c r="G120" t="n">
         <v>3460900</v>
@@ -3232,16 +3232,16 @@
         <v>45468</v>
       </c>
       <c r="C122" t="n">
-        <v>92.47176361083984</v>
+        <v>92.47175598144531</v>
       </c>
       <c r="D122" t="n">
-        <v>92.47176361083984</v>
+        <v>92.47175598144531</v>
       </c>
       <c r="E122" t="n">
-        <v>92.46257419044157</v>
+        <v>92.46256656180523</v>
       </c>
       <c r="F122" t="n">
-        <v>92.47176361083984</v>
+        <v>92.47175598144531</v>
       </c>
       <c r="G122" t="n">
         <v>3561700</v>
@@ -3255,16 +3255,16 @@
         <v>45469</v>
       </c>
       <c r="C123" t="n">
-        <v>92.48095703125</v>
+        <v>92.48096466064453</v>
       </c>
       <c r="D123" t="n">
-        <v>92.49013944257143</v>
+        <v>92.49014707272349</v>
       </c>
       <c r="E123" t="n">
-        <v>92.48095703125</v>
+        <v>92.48096466064453</v>
       </c>
       <c r="F123" t="n">
-        <v>92.48187527238214</v>
+        <v>92.48188290185243</v>
       </c>
       <c r="G123" t="n">
         <v>4815500</v>
@@ -3278,16 +3278,16 @@
         <v>45470</v>
       </c>
       <c r="C124" t="n">
-        <v>92.49014282226562</v>
+        <v>92.49013519287109</v>
       </c>
       <c r="D124" t="n">
-        <v>92.49933224339715</v>
+        <v>92.4993246132446</v>
       </c>
       <c r="E124" t="n">
-        <v>92.49014282226562</v>
+        <v>92.49013519287109</v>
       </c>
       <c r="F124" t="n">
-        <v>92.49933224339715</v>
+        <v>92.4993246132446</v>
       </c>
       <c r="G124" t="n">
         <v>3349900</v>
@@ -3301,16 +3301,16 @@
         <v>45471</v>
       </c>
       <c r="C125" t="n">
-        <v>92.52688598632812</v>
+        <v>92.52689361572266</v>
       </c>
       <c r="D125" t="n">
-        <v>92.53607540671368</v>
+        <v>92.53608303686593</v>
       </c>
       <c r="E125" t="n">
-        <v>92.52688598632812</v>
+        <v>92.52689361572266</v>
       </c>
       <c r="F125" t="n">
-        <v>92.52688598632812</v>
+        <v>92.52689361572266</v>
       </c>
       <c r="G125" t="n">
         <v>7427800</v>
@@ -3347,16 +3347,16 @@
         <v>45475</v>
       </c>
       <c r="C127" t="n">
-        <v>92.57209777832031</v>
+        <v>92.57210540771484</v>
       </c>
       <c r="D127" t="n">
-        <v>92.57209777832031</v>
+        <v>92.57210540771484</v>
       </c>
       <c r="E127" t="n">
-        <v>92.56286812584887</v>
+        <v>92.56287575448273</v>
       </c>
       <c r="F127" t="n">
-        <v>92.57209777832031</v>
+        <v>92.57210540771484</v>
       </c>
       <c r="G127" t="n">
         <v>5720900</v>
@@ -3393,16 +3393,16 @@
         <v>45478</v>
       </c>
       <c r="C129" t="n">
-        <v>92.63671112060547</v>
+        <v>92.63670349121094</v>
       </c>
       <c r="D129" t="n">
-        <v>92.63671112060547</v>
+        <v>92.63670349121094</v>
       </c>
       <c r="E129" t="n">
-        <v>92.62748146615579</v>
+        <v>92.62747383752138</v>
       </c>
       <c r="F129" t="n">
-        <v>92.62748146615579</v>
+        <v>92.62747383752138</v>
       </c>
       <c r="G129" t="n">
         <v>3742000</v>
@@ -3416,16 +3416,16 @@
         <v>45481</v>
       </c>
       <c r="C130" t="n">
-        <v>92.65517425537109</v>
+        <v>92.6551513671875</v>
       </c>
       <c r="D130" t="n">
-        <v>92.65517425537109</v>
+        <v>92.6551513671875</v>
       </c>
       <c r="E130" t="n">
-        <v>92.6459446005403</v>
+        <v>92.64592171463667</v>
       </c>
       <c r="F130" t="n">
-        <v>92.6459446005403</v>
+        <v>92.64592171463667</v>
       </c>
       <c r="G130" t="n">
         <v>3263000</v>
@@ -3439,16 +3439,16 @@
         <v>45482</v>
       </c>
       <c r="C131" t="n">
-        <v>92.65517425537109</v>
+        <v>92.6551513671875</v>
       </c>
       <c r="D131" t="n">
-        <v>92.67362652486881</v>
+        <v>92.67360363212704</v>
       </c>
       <c r="E131" t="n">
-        <v>92.65517425537109</v>
+        <v>92.6551513671875</v>
       </c>
       <c r="F131" t="n">
-        <v>92.66439687003802</v>
+        <v>92.66437397957621</v>
       </c>
       <c r="G131" t="n">
         <v>4508000</v>
@@ -3462,16 +3462,16 @@
         <v>45483</v>
       </c>
       <c r="C132" t="n">
-        <v>92.67360687255859</v>
+        <v>92.67362213134766</v>
       </c>
       <c r="D132" t="n">
-        <v>92.68283652543215</v>
+        <v>92.68285178574088</v>
       </c>
       <c r="E132" t="n">
-        <v>92.67360687255859</v>
+        <v>92.67362213134766</v>
       </c>
       <c r="F132" t="n">
-        <v>92.67360687255859</v>
+        <v>92.67362213134766</v>
       </c>
       <c r="G132" t="n">
         <v>4062200</v>
@@ -3508,16 +3508,16 @@
         <v>45485</v>
       </c>
       <c r="C134" t="n">
-        <v>92.73822784423828</v>
+        <v>92.73820495605469</v>
       </c>
       <c r="D134" t="n">
-        <v>92.73822784423828</v>
+        <v>92.73820495605469</v>
       </c>
       <c r="E134" t="n">
-        <v>92.72899818862962</v>
+        <v>92.72897530272394</v>
       </c>
       <c r="F134" t="n">
-        <v>92.73822784423828</v>
+        <v>92.73820495605469</v>
       </c>
       <c r="G134" t="n">
         <v>3369000</v>
@@ -3531,16 +3531,16 @@
         <v>45488</v>
       </c>
       <c r="C135" t="n">
-        <v>92.73822784423828</v>
+        <v>92.73820495605469</v>
       </c>
       <c r="D135" t="n">
-        <v>92.74745749984694</v>
+        <v>92.74743460938542</v>
       </c>
       <c r="E135" t="n">
-        <v>92.73822784423828</v>
+        <v>92.73820495605469</v>
       </c>
       <c r="F135" t="n">
-        <v>92.74745749984694</v>
+        <v>92.74743460938542</v>
       </c>
       <c r="G135" t="n">
         <v>3615100</v>
@@ -3554,16 +3554,16 @@
         <v>45489</v>
       </c>
       <c r="C136" t="n">
-        <v>92.75665283203125</v>
+        <v>92.75667572021484</v>
       </c>
       <c r="D136" t="n">
-        <v>92.75665283203125</v>
+        <v>92.75667572021484</v>
       </c>
       <c r="E136" t="n">
-        <v>92.74743021929977</v>
+        <v>92.74745310520764</v>
       </c>
       <c r="F136" t="n">
-        <v>92.75665283203125</v>
+        <v>92.75667572021484</v>
       </c>
       <c r="G136" t="n">
         <v>3622900</v>
@@ -3577,16 +3577,16 @@
         <v>45490</v>
       </c>
       <c r="C137" t="n">
-        <v>92.76589965820312</v>
+        <v>92.76588439941406</v>
       </c>
       <c r="D137" t="n">
-        <v>92.77051800558623</v>
+        <v>92.77050274603751</v>
       </c>
       <c r="E137" t="n">
-        <v>92.75667000360062</v>
+        <v>92.75665474632972</v>
       </c>
       <c r="F137" t="n">
-        <v>92.76589965820312</v>
+        <v>92.76588439941406</v>
       </c>
       <c r="G137" t="n">
         <v>3822100</v>
@@ -3600,16 +3600,16 @@
         <v>45491</v>
       </c>
       <c r="C138" t="n">
-        <v>92.78433227539062</v>
+        <v>92.78434753417969</v>
       </c>
       <c r="D138" t="n">
-        <v>92.78433227539062</v>
+        <v>92.78434753417969</v>
       </c>
       <c r="E138" t="n">
-        <v>92.77510262344329</v>
+        <v>92.77511788071449</v>
       </c>
       <c r="F138" t="n">
-        <v>92.77510262344329</v>
+        <v>92.77511788071449</v>
       </c>
       <c r="G138" t="n">
         <v>5291400</v>
@@ -3646,16 +3646,16 @@
         <v>45495</v>
       </c>
       <c r="C140" t="n">
-        <v>92.83970642089844</v>
+        <v>92.83971405029297</v>
       </c>
       <c r="D140" t="n">
-        <v>92.83970642089844</v>
+        <v>92.83971405029297</v>
       </c>
       <c r="E140" t="n">
-        <v>92.83047676792572</v>
+        <v>92.83048439656177</v>
       </c>
       <c r="F140" t="n">
-        <v>92.83970642089844</v>
+        <v>92.83971405029297</v>
       </c>
       <c r="G140" t="n">
         <v>3386500</v>
@@ -3669,16 +3669,16 @@
         <v>45496</v>
       </c>
       <c r="C141" t="n">
-        <v>92.84893035888672</v>
+        <v>92.84894561767578</v>
       </c>
       <c r="D141" t="n">
-        <v>92.85815297112931</v>
+        <v>92.85816823143402</v>
       </c>
       <c r="E141" t="n">
-        <v>92.83970070648209</v>
+        <v>92.83971596375436</v>
       </c>
       <c r="F141" t="n">
-        <v>92.84893035888672</v>
+        <v>92.84894561767578</v>
       </c>
       <c r="G141" t="n">
         <v>2829200</v>
@@ -3692,16 +3692,16 @@
         <v>45497</v>
       </c>
       <c r="C142" t="n">
-        <v>92.85817718505859</v>
+        <v>92.858154296875</v>
       </c>
       <c r="D142" t="n">
-        <v>92.86740683986996</v>
+        <v>92.86738394941139</v>
       </c>
       <c r="E142" t="n">
-        <v>92.84895457041108</v>
+        <v>92.84893168450073</v>
       </c>
       <c r="F142" t="n">
-        <v>92.85817718505859</v>
+        <v>92.858154296875</v>
       </c>
       <c r="G142" t="n">
         <v>3474500</v>
@@ -3715,16 +3715,16 @@
         <v>45498</v>
       </c>
       <c r="C143" t="n">
-        <v>92.87663269042969</v>
+        <v>92.87662506103516</v>
       </c>
       <c r="D143" t="n">
-        <v>92.87663269042969</v>
+        <v>92.87662506103516</v>
       </c>
       <c r="E143" t="n">
-        <v>92.86740303599636</v>
+        <v>92.86739540736002</v>
       </c>
       <c r="F143" t="n">
-        <v>92.87663269042969</v>
+        <v>92.87662506103516</v>
       </c>
       <c r="G143" t="n">
         <v>3521700</v>
@@ -3738,16 +3738,16 @@
         <v>45499</v>
       </c>
       <c r="C144" t="n">
-        <v>92.90431213378906</v>
+        <v>92.90428924560547</v>
       </c>
       <c r="D144" t="n">
-        <v>92.91354178797603</v>
+        <v>92.91351889751859</v>
       </c>
       <c r="E144" t="n">
-        <v>92.90431213378906</v>
+        <v>92.90428924560547</v>
       </c>
       <c r="F144" t="n">
-        <v>92.90431213378906</v>
+        <v>92.90428924560547</v>
       </c>
       <c r="G144" t="n">
         <v>3172600</v>
@@ -3761,16 +3761,16 @@
         <v>45502</v>
       </c>
       <c r="C145" t="n">
-        <v>92.93199157714844</v>
+        <v>92.93198394775391</v>
       </c>
       <c r="D145" t="n">
-        <v>92.93199157714844</v>
+        <v>92.93198394775391</v>
       </c>
       <c r="E145" t="n">
-        <v>92.92276192320769</v>
+        <v>92.92275429457088</v>
       </c>
       <c r="F145" t="n">
-        <v>92.92276192320769</v>
+        <v>92.92275429457088</v>
       </c>
       <c r="G145" t="n">
         <v>3259000</v>
@@ -3784,16 +3784,16 @@
         <v>45503</v>
       </c>
       <c r="C146" t="n">
-        <v>92.93199157714844</v>
+        <v>92.93198394775391</v>
       </c>
       <c r="D146" t="n">
-        <v>92.94122123108919</v>
+        <v>92.94121360093693</v>
       </c>
       <c r="E146" t="n">
-        <v>92.93199157714844</v>
+        <v>92.93198394775391</v>
       </c>
       <c r="F146" t="n">
-        <v>92.94122123108919</v>
+        <v>92.94121360093693</v>
       </c>
       <c r="G146" t="n">
         <v>4559900</v>
@@ -3807,16 +3807,16 @@
         <v>45504</v>
       </c>
       <c r="C147" t="n">
-        <v>92.94121551513672</v>
+        <v>92.94122314453125</v>
       </c>
       <c r="D147" t="n">
-        <v>92.95044516850984</v>
+        <v>92.95045279866203</v>
       </c>
       <c r="E147" t="n">
-        <v>92.94121551513672</v>
+        <v>92.94122314453125</v>
       </c>
       <c r="F147" t="n">
-        <v>92.94121551513672</v>
+        <v>92.94122314453125</v>
       </c>
       <c r="G147" t="n">
         <v>7256900</v>
@@ -3853,16 +3853,16 @@
         <v>45506</v>
       </c>
       <c r="C149" t="n">
-        <v>93.01814270019531</v>
+        <v>93.01816558837891</v>
       </c>
       <c r="D149" t="n">
-        <v>93.01814270019531</v>
+        <v>93.01816558837891</v>
       </c>
       <c r="E149" t="n">
-        <v>92.99960706864016</v>
+        <v>92.99962995226285</v>
       </c>
       <c r="F149" t="n">
-        <v>93.00887134843308</v>
+        <v>93.00889423433536</v>
       </c>
       <c r="G149" t="n">
         <v>7927400</v>
@@ -3876,16 +3876,16 @@
         <v>45509</v>
       </c>
       <c r="C150" t="n">
-        <v>93.02743530273438</v>
+        <v>93.02742004394531</v>
       </c>
       <c r="D150" t="n">
-        <v>93.04597093852372</v>
+        <v>93.04595567669436</v>
       </c>
       <c r="E150" t="n">
-        <v>93.01816394885424</v>
+        <v>93.01814869158591</v>
       </c>
       <c r="F150" t="n">
-        <v>93.01816394885424</v>
+        <v>93.01814869158591</v>
       </c>
       <c r="G150" t="n">
         <v>8712900</v>
@@ -3899,16 +3899,16 @@
         <v>45510</v>
       </c>
       <c r="C151" t="n">
-        <v>93.04595184326172</v>
+        <v>93.04594421386719</v>
       </c>
       <c r="D151" t="n">
-        <v>93.04595184326172</v>
+        <v>93.04594421386719</v>
       </c>
       <c r="E151" t="n">
-        <v>93.02741621127633</v>
+        <v>93.02740858340164</v>
       </c>
       <c r="F151" t="n">
-        <v>93.02741621127633</v>
+        <v>93.02740858340164</v>
       </c>
       <c r="G151" t="n">
         <v>5059100</v>
@@ -3922,16 +3922,16 @@
         <v>45511</v>
       </c>
       <c r="C152" t="n">
-        <v>93.04595184326172</v>
+        <v>93.04594421386719</v>
       </c>
       <c r="D152" t="n">
-        <v>93.05522319523915</v>
+        <v>93.0552155650844</v>
       </c>
       <c r="E152" t="n">
-        <v>93.04595184326172</v>
+        <v>93.04594421386719</v>
       </c>
       <c r="F152" t="n">
-        <v>93.04595184326172</v>
+        <v>93.04594421386719</v>
       </c>
       <c r="G152" t="n">
         <v>4611400</v>
@@ -3991,16 +3991,16 @@
         <v>45516</v>
       </c>
       <c r="C155" t="n">
-        <v>93.12010192871094</v>
+        <v>93.12009429931641</v>
       </c>
       <c r="D155" t="n">
-        <v>93.1293732800326</v>
+        <v>93.12936564987847</v>
       </c>
       <c r="E155" t="n">
-        <v>93.11083057738928</v>
+        <v>93.11082294875435</v>
       </c>
       <c r="F155" t="n">
-        <v>93.12010192871094</v>
+        <v>93.12009429931641</v>
       </c>
       <c r="G155" t="n">
         <v>3845400</v>
@@ -4014,16 +4014,16 @@
         <v>45517</v>
       </c>
       <c r="C156" t="n">
-        <v>93.13866424560547</v>
+        <v>93.13864135742188</v>
       </c>
       <c r="D156" t="n">
-        <v>93.13866424560547</v>
+        <v>93.13864135742188</v>
       </c>
       <c r="E156" t="n">
-        <v>93.12939289233132</v>
+        <v>93.12937000642611</v>
       </c>
       <c r="F156" t="n">
-        <v>93.13866424560547</v>
+        <v>93.13864135742188</v>
       </c>
       <c r="G156" t="n">
         <v>4782200</v>
@@ -4037,16 +4037,16 @@
         <v>45518</v>
       </c>
       <c r="C157" t="n">
-        <v>93.15720367431641</v>
+        <v>93.15718841552734</v>
       </c>
       <c r="D157" t="n">
-        <v>93.15720367431641</v>
+        <v>93.15718841552734</v>
       </c>
       <c r="E157" t="n">
-        <v>93.13866803898368</v>
+        <v>93.13865278323068</v>
       </c>
       <c r="F157" t="n">
-        <v>93.14793232066467</v>
+        <v>93.14791706339422</v>
       </c>
       <c r="G157" t="n">
         <v>4327700</v>
@@ -4060,16 +4060,16 @@
         <v>45519</v>
       </c>
       <c r="C158" t="n">
-        <v>93.16645812988281</v>
+        <v>93.16647338867188</v>
       </c>
       <c r="D158" t="n">
-        <v>93.16645812988281</v>
+        <v>93.16647338867188</v>
       </c>
       <c r="E158" t="n">
-        <v>93.14791542594251</v>
+        <v>93.14793068169466</v>
       </c>
       <c r="F158" t="n">
-        <v>93.14791542594251</v>
+        <v>93.14793068169466</v>
       </c>
       <c r="G158" t="n">
         <v>4217800</v>
@@ -4083,16 +4083,16 @@
         <v>45520</v>
       </c>
       <c r="C159" t="n">
-        <v>93.20352935791016</v>
+        <v>93.20355224609375</v>
       </c>
       <c r="D159" t="n">
-        <v>93.20352935791016</v>
+        <v>93.20355224609375</v>
       </c>
       <c r="E159" t="n">
-        <v>93.19425800664706</v>
+        <v>93.19428089255386</v>
       </c>
       <c r="F159" t="n">
-        <v>93.20352935791016</v>
+        <v>93.20355224609375</v>
       </c>
       <c r="G159" t="n">
         <v>3638900</v>
@@ -4129,16 +4129,16 @@
         <v>45524</v>
       </c>
       <c r="C161" t="n">
-        <v>93.22206878662109</v>
+        <v>93.22208404541016</v>
       </c>
       <c r="D161" t="n">
-        <v>93.23134013826194</v>
+        <v>93.23135539856855</v>
       </c>
       <c r="E161" t="n">
-        <v>93.22206878662109</v>
+        <v>93.22208404541016</v>
       </c>
       <c r="F161" t="n">
-        <v>93.23134013826194</v>
+        <v>93.23135539856855</v>
       </c>
       <c r="G161" t="n">
         <v>3084200</v>
@@ -4152,16 +4152,16 @@
         <v>45525</v>
       </c>
       <c r="C162" t="n">
-        <v>93.2498779296875</v>
+        <v>93.24986267089844</v>
       </c>
       <c r="D162" t="n">
-        <v>93.2498779296875</v>
+        <v>93.24986267089844</v>
       </c>
       <c r="E162" t="n">
-        <v>93.23134229794566</v>
+        <v>93.23132704218965</v>
       </c>
       <c r="F162" t="n">
-        <v>93.23134229794566</v>
+        <v>93.23132704218965</v>
       </c>
       <c r="G162" t="n">
         <v>3936000</v>
@@ -4175,16 +4175,16 @@
         <v>45526</v>
       </c>
       <c r="C163" t="n">
-        <v>93.2498779296875</v>
+        <v>93.24986267089844</v>
       </c>
       <c r="D163" t="n">
-        <v>93.2591492815431</v>
+        <v>93.25913402123695</v>
       </c>
       <c r="E163" t="n">
-        <v>93.2498779296875</v>
+        <v>93.24986267089844</v>
       </c>
       <c r="F163" t="n">
-        <v>93.2591492815431</v>
+        <v>93.25913402123695</v>
       </c>
       <c r="G163" t="n">
         <v>3849100</v>
@@ -4221,16 +4221,16 @@
         <v>45530</v>
       </c>
       <c r="C165" t="n">
-        <v>93.30551147460938</v>
+        <v>93.30550384521484</v>
       </c>
       <c r="D165" t="n">
-        <v>93.3147757557373</v>
+        <v>93.31476812558525</v>
       </c>
       <c r="E165" t="n">
-        <v>93.30551147460938</v>
+        <v>93.30550384521484</v>
       </c>
       <c r="F165" t="n">
-        <v>93.30551147460938</v>
+        <v>93.30550384521484</v>
       </c>
       <c r="G165" t="n">
         <v>3969000</v>
@@ -4244,16 +4244,16 @@
         <v>45531</v>
       </c>
       <c r="C166" t="n">
-        <v>93.31474304199219</v>
+        <v>93.31478881835938</v>
       </c>
       <c r="D166" t="n">
-        <v>93.32401439184014</v>
+        <v>93.32406017275547</v>
       </c>
       <c r="E166" t="n">
-        <v>93.31474304199219</v>
+        <v>93.31478881835938</v>
       </c>
       <c r="F166" t="n">
-        <v>93.32401439184014</v>
+        <v>93.32406017275547</v>
       </c>
       <c r="G166" t="n">
         <v>2818100</v>
@@ -4267,16 +4267,16 @@
         <v>45532</v>
       </c>
       <c r="C167" t="n">
-        <v>93.32405853271484</v>
+        <v>93.32402038574219</v>
       </c>
       <c r="D167" t="n">
-        <v>93.33332988694801</v>
+        <v>93.33329173618561</v>
       </c>
       <c r="E167" t="n">
-        <v>93.32405853271484</v>
+        <v>93.32402038574219</v>
       </c>
       <c r="F167" t="n">
-        <v>93.33332988694801</v>
+        <v>93.33329173618561</v>
       </c>
       <c r="G167" t="n">
         <v>3500800</v>
@@ -4290,16 +4290,16 @@
         <v>45533</v>
       </c>
       <c r="C168" t="n">
-        <v>93.33329772949219</v>
+        <v>93.33331298828125</v>
       </c>
       <c r="D168" t="n">
-        <v>93.35183335960097</v>
+        <v>93.35184862142037</v>
       </c>
       <c r="E168" t="n">
-        <v>93.33329772949219</v>
+        <v>93.33331298828125</v>
       </c>
       <c r="F168" t="n">
-        <v>93.34256200856221</v>
+        <v>93.34257726886585</v>
       </c>
       <c r="G168" t="n">
         <v>4537700</v>
@@ -4313,16 +4313,16 @@
         <v>45534</v>
       </c>
       <c r="C169" t="n">
-        <v>93.379638671875</v>
+        <v>93.37964630126953</v>
       </c>
       <c r="D169" t="n">
-        <v>93.38891002274808</v>
+        <v>93.3889176529001</v>
       </c>
       <c r="E169" t="n">
-        <v>93.379638671875</v>
+        <v>93.37964630126953</v>
       </c>
       <c r="F169" t="n">
-        <v>93.379638671875</v>
+        <v>93.37964630126953</v>
       </c>
       <c r="G169" t="n">
         <v>8427400</v>
@@ -4359,16 +4359,16 @@
         <v>45539</v>
       </c>
       <c r="C171" t="n">
-        <v>93.42992401123047</v>
+        <v>93.42994689941406</v>
       </c>
       <c r="D171" t="n">
-        <v>93.43923640626956</v>
+        <v>93.43925929673448</v>
       </c>
       <c r="E171" t="n">
-        <v>93.42992401123047</v>
+        <v>93.42994689941406</v>
       </c>
       <c r="F171" t="n">
-        <v>93.43923640626956</v>
+        <v>93.43925929673448</v>
       </c>
       <c r="G171" t="n">
         <v>7218300</v>
@@ -4382,16 +4382,16 @@
         <v>45540</v>
       </c>
       <c r="C172" t="n">
-        <v>93.45787048339844</v>
+        <v>93.45785522460938</v>
       </c>
       <c r="D172" t="n">
-        <v>93.45787048339844</v>
+        <v>93.45785522460938</v>
       </c>
       <c r="E172" t="n">
-        <v>93.43925279333131</v>
+        <v>93.43923753758195</v>
       </c>
       <c r="F172" t="n">
-        <v>93.44856519000358</v>
+        <v>93.44854993273378</v>
       </c>
       <c r="G172" t="n">
         <v>4833300</v>
@@ -4405,16 +4405,16 @@
         <v>45541</v>
       </c>
       <c r="C173" t="n">
-        <v>93.49510955810547</v>
+        <v>93.49510192871094</v>
       </c>
       <c r="D173" t="n">
-        <v>93.49510955810547</v>
+        <v>93.49510192871094</v>
       </c>
       <c r="E173" t="n">
-        <v>93.48580426504986</v>
+        <v>93.48579663641466</v>
       </c>
       <c r="F173" t="n">
-        <v>93.49510955810547</v>
+        <v>93.49510192871094</v>
       </c>
       <c r="G173" t="n">
         <v>5534600</v>
@@ -4428,16 +4428,16 @@
         <v>45544</v>
       </c>
       <c r="C174" t="n">
-        <v>93.50440979003906</v>
+        <v>93.50442504882812</v>
       </c>
       <c r="D174" t="n">
-        <v>93.51372218516032</v>
+        <v>93.51373744546905</v>
       </c>
       <c r="E174" t="n">
-        <v>93.50440979003906</v>
+        <v>93.50442504882812</v>
       </c>
       <c r="F174" t="n">
-        <v>93.50440979003906</v>
+        <v>93.50442504882812</v>
       </c>
       <c r="G174" t="n">
         <v>5397400</v>
@@ -4497,16 +4497,16 @@
         <v>45547</v>
       </c>
       <c r="C177" t="n">
-        <v>93.53233337402344</v>
+        <v>93.53235626220703</v>
       </c>
       <c r="D177" t="n">
-        <v>93.54164576849772</v>
+        <v>93.54166865896013</v>
       </c>
       <c r="E177" t="n">
-        <v>93.53233337402344</v>
+        <v>93.53235626220703</v>
       </c>
       <c r="F177" t="n">
-        <v>93.54164576849772</v>
+        <v>93.54166865896013</v>
       </c>
       <c r="G177" t="n">
         <v>3912400</v>
@@ -4520,16 +4520,16 @@
         <v>45548</v>
       </c>
       <c r="C178" t="n">
-        <v>93.58820343017578</v>
+        <v>93.58821105957031</v>
       </c>
       <c r="D178" t="n">
-        <v>93.58820343017578</v>
+        <v>93.58821105957031</v>
       </c>
       <c r="E178" t="n">
-        <v>93.56958574253433</v>
+        <v>93.56959337041114</v>
       </c>
       <c r="F178" t="n">
-        <v>93.56958574253433</v>
+        <v>93.56959337041114</v>
       </c>
       <c r="G178" t="n">
         <v>3465200</v>
@@ -4543,16 +4543,16 @@
         <v>45551</v>
       </c>
       <c r="C179" t="n">
-        <v>93.60683441162109</v>
+        <v>93.60682678222656</v>
       </c>
       <c r="D179" t="n">
-        <v>93.60683441162109</v>
+        <v>93.60682678222656</v>
       </c>
       <c r="E179" t="n">
-        <v>93.58820961947146</v>
+        <v>93.58820199159494</v>
       </c>
       <c r="F179" t="n">
-        <v>93.58820961947146</v>
+        <v>93.58820199159494</v>
       </c>
       <c r="G179" t="n">
         <v>3571100</v>
@@ -4566,16 +4566,16 @@
         <v>45552</v>
       </c>
       <c r="C180" t="n">
-        <v>93.60683441162109</v>
+        <v>93.60682678222656</v>
       </c>
       <c r="D180" t="n">
-        <v>93.62545210049379</v>
+        <v>93.62544446958184</v>
       </c>
       <c r="E180" t="n">
-        <v>93.60683441162109</v>
+        <v>93.60682678222656</v>
       </c>
       <c r="F180" t="n">
-        <v>93.61614680769591</v>
+        <v>93.61613917754238</v>
       </c>
       <c r="G180" t="n">
         <v>4452200</v>
@@ -4589,16 +4589,16 @@
         <v>45553</v>
       </c>
       <c r="C181" t="n">
-        <v>93.63475036621094</v>
+        <v>93.63478088378906</v>
       </c>
       <c r="D181" t="n">
-        <v>93.64406276088043</v>
+        <v>93.64409328149367</v>
       </c>
       <c r="E181" t="n">
-        <v>93.62543797154144</v>
+        <v>93.62546848608446</v>
       </c>
       <c r="F181" t="n">
-        <v>93.62543797154144</v>
+        <v>93.62546848608446</v>
       </c>
       <c r="G181" t="n">
         <v>4077700</v>
@@ -4612,16 +4612,16 @@
         <v>45554</v>
       </c>
       <c r="C182" t="n">
-        <v>93.65337371826172</v>
+        <v>93.65338897705078</v>
       </c>
       <c r="D182" t="n">
-        <v>93.6626861134946</v>
+        <v>93.66270137380091</v>
       </c>
       <c r="E182" t="n">
-        <v>93.64406842630514</v>
+        <v>93.6440836835781</v>
       </c>
       <c r="F182" t="n">
-        <v>93.64406842630514</v>
+        <v>93.6440836835781</v>
       </c>
       <c r="G182" t="n">
         <v>5165800</v>
@@ -4635,16 +4635,16 @@
         <v>45555</v>
       </c>
       <c r="C183" t="n">
-        <v>93.69062042236328</v>
+        <v>93.69063568115234</v>
       </c>
       <c r="D183" t="n">
-        <v>93.69993281801626</v>
+        <v>93.69994807832197</v>
       </c>
       <c r="E183" t="n">
-        <v>93.69062042236328</v>
+        <v>93.69063568115234</v>
       </c>
       <c r="F183" t="n">
-        <v>93.69993281801626</v>
+        <v>93.69994807832197</v>
       </c>
       <c r="G183" t="n">
         <v>4244800</v>
@@ -4658,16 +4658,16 @@
         <v>45558</v>
       </c>
       <c r="C184" t="n">
-        <v>93.71856689453125</v>
+        <v>93.71854400634766</v>
       </c>
       <c r="D184" t="n">
-        <v>93.71856689453125</v>
+        <v>93.71854400634766</v>
       </c>
       <c r="E184" t="n">
-        <v>93.69994210138005</v>
+        <v>93.69991921774503</v>
       </c>
       <c r="F184" t="n">
-        <v>93.70925449795564</v>
+        <v>93.70923161204635</v>
       </c>
       <c r="G184" t="n">
         <v>5220900</v>
@@ -4681,16 +4681,16 @@
         <v>45559</v>
       </c>
       <c r="C185" t="n">
-        <v>93.72783660888672</v>
+        <v>93.72788238525391</v>
       </c>
       <c r="D185" t="n">
-        <v>93.72783660888672</v>
+        <v>93.72788238525391</v>
       </c>
       <c r="E185" t="n">
-        <v>93.71853131912071</v>
+        <v>93.71857709094323</v>
       </c>
       <c r="F185" t="n">
-        <v>93.71853131912071</v>
+        <v>93.71857709094323</v>
       </c>
       <c r="G185" t="n">
         <v>3923500</v>
@@ -4704,16 +4704,16 @@
         <v>45560</v>
       </c>
       <c r="C186" t="n">
-        <v>93.72783660888672</v>
+        <v>93.72788238525391</v>
       </c>
       <c r="D186" t="n">
-        <v>93.74646139496799</v>
+        <v>93.74650718043146</v>
       </c>
       <c r="E186" t="n">
-        <v>93.72783660888672</v>
+        <v>93.72788238525391</v>
       </c>
       <c r="F186" t="n">
-        <v>93.73714900192736</v>
+        <v>93.73719478284268</v>
       </c>
       <c r="G186" t="n">
         <v>3372400</v>
@@ -4727,16 +4727,16 @@
         <v>45561</v>
       </c>
       <c r="C187" t="n">
-        <v>93.73719024658203</v>
+        <v>93.7371826171875</v>
       </c>
       <c r="D187" t="n">
-        <v>93.74650264372015</v>
+        <v>93.74649501356767</v>
       </c>
       <c r="E187" t="n">
-        <v>93.73719024658203</v>
+        <v>93.7371826171875</v>
       </c>
       <c r="F187" t="n">
-        <v>93.73719024658203</v>
+        <v>93.7371826171875</v>
       </c>
       <c r="G187" t="n">
         <v>4364400</v>
@@ -4750,16 +4750,16 @@
         <v>45562</v>
       </c>
       <c r="C188" t="n">
-        <v>93.77442932128906</v>
+        <v>93.7744140625</v>
       </c>
       <c r="D188" t="n">
-        <v>93.78374171808849</v>
+        <v>93.78372645778413</v>
       </c>
       <c r="E188" t="n">
-        <v>93.77442932128906</v>
+        <v>93.7744140625</v>
       </c>
       <c r="F188" t="n">
-        <v>93.77442932128906</v>
+        <v>93.7744140625</v>
       </c>
       <c r="G188" t="n">
         <v>4945400</v>
@@ -4773,16 +4773,16 @@
         <v>45565</v>
       </c>
       <c r="C189" t="n">
-        <v>93.77442932128906</v>
+        <v>93.7744140625</v>
       </c>
       <c r="D189" t="n">
-        <v>93.79304701161043</v>
+        <v>93.79303174979192</v>
       </c>
       <c r="E189" t="n">
-        <v>93.77442932128906</v>
+        <v>93.7744140625</v>
       </c>
       <c r="F189" t="n">
-        <v>93.78374171808849</v>
+        <v>93.78372645778413</v>
       </c>
       <c r="G189" t="n">
         <v>9253100</v>
@@ -4796,16 +4796,16 @@
         <v>45566</v>
       </c>
       <c r="C190" t="n">
-        <v>93.81181335449219</v>
+        <v>93.81182098388672</v>
       </c>
       <c r="D190" t="n">
-        <v>93.81181335449219</v>
+        <v>93.81182098388672</v>
       </c>
       <c r="E190" t="n">
-        <v>93.80246103195581</v>
+        <v>93.80246866058975</v>
       </c>
       <c r="F190" t="n">
-        <v>93.81181335449219</v>
+        <v>93.81182098388672</v>
       </c>
       <c r="G190" t="n">
         <v>11569200</v>
@@ -4819,16 +4819,16 @@
         <v>45567</v>
       </c>
       <c r="C191" t="n">
-        <v>93.81181335449219</v>
+        <v>93.81182098388672</v>
       </c>
       <c r="D191" t="n">
-        <v>93.82115854329665</v>
+        <v>93.82116617345119</v>
       </c>
       <c r="E191" t="n">
-        <v>93.81181335449219</v>
+        <v>93.81182098388672</v>
       </c>
       <c r="F191" t="n">
-        <v>93.82115854329665</v>
+        <v>93.82116617345119</v>
       </c>
       <c r="G191" t="n">
         <v>5170300</v>
@@ -4842,16 +4842,16 @@
         <v>45568</v>
       </c>
       <c r="C192" t="n">
-        <v>93.8211669921875</v>
+        <v>93.82115936279297</v>
       </c>
       <c r="D192" t="n">
-        <v>93.83051931556608</v>
+        <v>93.83051168541103</v>
       </c>
       <c r="E192" t="n">
-        <v>93.8211669921875</v>
+        <v>93.82115936279297</v>
       </c>
       <c r="F192" t="n">
-        <v>93.83051931556608</v>
+        <v>93.83051168541103</v>
       </c>
       <c r="G192" t="n">
         <v>4066100</v>
@@ -4865,16 +4865,16 @@
         <v>45569</v>
       </c>
       <c r="C193" t="n">
-        <v>93.85855865478516</v>
+        <v>93.85856628417969</v>
       </c>
       <c r="D193" t="n">
-        <v>93.86791097711776</v>
+        <v>93.86791860727251</v>
       </c>
       <c r="E193" t="n">
-        <v>93.85855865478516</v>
+        <v>93.85856628417969</v>
       </c>
       <c r="F193" t="n">
-        <v>93.86323838281734</v>
+        <v>93.86324601259227</v>
       </c>
       <c r="G193" t="n">
         <v>4987100</v>
@@ -4888,16 +4888,16 @@
         <v>45572</v>
       </c>
       <c r="C194" t="n">
-        <v>93.867919921875</v>
+        <v>93.86789703369141</v>
       </c>
       <c r="D194" t="n">
-        <v>93.87727224509879</v>
+        <v>93.8772493546348</v>
       </c>
       <c r="E194" t="n">
-        <v>93.867919921875</v>
+        <v>93.86789703369141</v>
       </c>
       <c r="F194" t="n">
-        <v>93.867919921875</v>
+        <v>93.86789703369141</v>
       </c>
       <c r="G194" t="n">
         <v>4792500</v>
@@ -4957,16 +4957,16 @@
         <v>45575</v>
       </c>
       <c r="C197" t="n">
-        <v>93.9146728515625</v>
+        <v>93.91468048095703</v>
       </c>
       <c r="D197" t="n">
-        <v>93.9146728515625</v>
+        <v>93.91468048095703</v>
       </c>
       <c r="E197" t="n">
-        <v>93.90532052849332</v>
+        <v>93.9053281571281</v>
       </c>
       <c r="F197" t="n">
-        <v>93.9146728515625</v>
+        <v>93.91468048095703</v>
       </c>
       <c r="G197" t="n">
         <v>3731100</v>
@@ -4980,16 +4980,16 @@
         <v>45576</v>
       </c>
       <c r="C198" t="n">
-        <v>93.95206451416016</v>
+        <v>93.95207977294922</v>
       </c>
       <c r="D198" t="n">
-        <v>93.96140970245301</v>
+        <v>93.96142496275984</v>
       </c>
       <c r="E198" t="n">
-        <v>93.95206451416016</v>
+        <v>93.95207977294922</v>
       </c>
       <c r="F198" t="n">
-        <v>93.95206451416016</v>
+        <v>93.95207977294922</v>
       </c>
       <c r="G198" t="n">
         <v>3778400</v>
@@ -5003,16 +5003,16 @@
         <v>45579</v>
       </c>
       <c r="C199" t="n">
-        <v>93.95206451416016</v>
+        <v>93.95207977294922</v>
       </c>
       <c r="D199" t="n">
-        <v>93.96140970245301</v>
+        <v>93.96142496275984</v>
       </c>
       <c r="E199" t="n">
-        <v>93.95206451416016</v>
+        <v>93.95207977294922</v>
       </c>
       <c r="F199" t="n">
-        <v>93.95206451416016</v>
+        <v>93.95207977294922</v>
       </c>
       <c r="G199" t="n">
         <v>3297100</v>
@@ -5026,16 +5026,16 @@
         <v>45580</v>
       </c>
       <c r="C200" t="n">
-        <v>93.97078704833984</v>
+        <v>93.97077178955078</v>
       </c>
       <c r="D200" t="n">
-        <v>93.97078704833984</v>
+        <v>93.97077178955078</v>
       </c>
       <c r="E200" t="n">
-        <v>93.96143472382499</v>
+        <v>93.96141946655455</v>
       </c>
       <c r="F200" t="n">
-        <v>93.97078704833984</v>
+        <v>93.97077178955078</v>
       </c>
       <c r="G200" t="n">
         <v>3567400</v>
@@ -5118,16 +5118,16 @@
         <v>45586</v>
       </c>
       <c r="C204" t="n">
-        <v>94.04558563232422</v>
+        <v>94.04556274414062</v>
       </c>
       <c r="D204" t="n">
-        <v>94.04558563232422</v>
+        <v>94.04556274414062</v>
       </c>
       <c r="E204" t="n">
-        <v>94.03623330838064</v>
+        <v>94.03621042247316</v>
       </c>
       <c r="F204" t="n">
-        <v>94.03623330838064</v>
+        <v>94.03621042247316</v>
       </c>
       <c r="G204" t="n">
         <v>3940600</v>
@@ -5141,16 +5141,16 @@
         <v>45587</v>
       </c>
       <c r="C205" t="n">
-        <v>94.05491638183594</v>
+        <v>94.05494689941406</v>
       </c>
       <c r="D205" t="n">
-        <v>94.05491638183594</v>
+        <v>94.05494689941406</v>
       </c>
       <c r="E205" t="n">
-        <v>94.04557119306016</v>
+        <v>94.0456017076061</v>
       </c>
       <c r="F205" t="n">
-        <v>94.05491638183594</v>
+        <v>94.05494689941406</v>
       </c>
       <c r="G205" t="n">
         <v>3462800</v>
@@ -5164,16 +5164,16 @@
         <v>45588</v>
       </c>
       <c r="C206" t="n">
-        <v>94.05491638183594</v>
+        <v>94.05494689941406</v>
       </c>
       <c r="D206" t="n">
-        <v>94.07362102685126</v>
+        <v>94.0736515504984</v>
       </c>
       <c r="E206" t="n">
-        <v>94.05491638183594</v>
+        <v>94.05494689941406</v>
       </c>
       <c r="F206" t="n">
-        <v>94.07362102685126</v>
+        <v>94.0736515504984</v>
       </c>
       <c r="G206" t="n">
         <v>3927700</v>
@@ -5187,16 +5187,16 @@
         <v>45589</v>
       </c>
       <c r="C207" t="n">
-        <v>94.08297729492188</v>
+        <v>94.08296203613281</v>
       </c>
       <c r="D207" t="n">
-        <v>94.08297729492188</v>
+        <v>94.08296203613281</v>
       </c>
       <c r="E207" t="n">
-        <v>94.073624972022</v>
+        <v>94.07360971474975</v>
       </c>
       <c r="F207" t="n">
-        <v>94.08297729492188</v>
+        <v>94.08296203613281</v>
       </c>
       <c r="G207" t="n">
         <v>3704500</v>
@@ -5210,16 +5210,16 @@
         <v>45590</v>
       </c>
       <c r="C208" t="n">
-        <v>94.12039947509766</v>
+        <v>94.12036895751953</v>
       </c>
       <c r="D208" t="n">
-        <v>94.12039947509766</v>
+        <v>94.12036895751953</v>
       </c>
       <c r="E208" t="n">
-        <v>94.11104715020825</v>
+        <v>94.11101663566252</v>
       </c>
       <c r="F208" t="n">
-        <v>94.11104715020825</v>
+        <v>94.11101663566252</v>
       </c>
       <c r="G208" t="n">
         <v>5386900</v>
@@ -5233,16 +5233,16 @@
         <v>45593</v>
       </c>
       <c r="C209" t="n">
-        <v>94.12039947509766</v>
+        <v>94.12036895751953</v>
       </c>
       <c r="D209" t="n">
-        <v>94.12974466625334</v>
+        <v>94.12971414564514</v>
       </c>
       <c r="E209" t="n">
-        <v>94.12039947509766</v>
+        <v>94.12036895751953</v>
       </c>
       <c r="F209" t="n">
-        <v>94.12974466625334</v>
+        <v>94.12971414564514</v>
       </c>
       <c r="G209" t="n">
         <v>3471300</v>
@@ -5256,16 +5256,16 @@
         <v>45594</v>
       </c>
       <c r="C210" t="n">
-        <v>94.13906860351562</v>
+        <v>94.13907623291016</v>
       </c>
       <c r="D210" t="n">
-        <v>94.13906860351562</v>
+        <v>94.13907623291016</v>
       </c>
       <c r="E210" t="n">
-        <v>94.1250436872776</v>
+        <v>94.12505131553549</v>
       </c>
       <c r="F210" t="n">
-        <v>94.12971628144642</v>
+        <v>94.129723910083</v>
       </c>
       <c r="G210" t="n">
         <v>3449900</v>
@@ -5279,16 +5279,16 @@
         <v>45595</v>
       </c>
       <c r="C211" t="n">
-        <v>94.13906860351562</v>
+        <v>94.13907623291016</v>
       </c>
       <c r="D211" t="n">
-        <v>94.15776611392248</v>
+        <v>94.15777374483233</v>
       </c>
       <c r="E211" t="n">
-        <v>94.13906860351562</v>
+        <v>94.13907623291016</v>
       </c>
       <c r="F211" t="n">
-        <v>94.14842092558483</v>
+        <v>94.14842855573731</v>
       </c>
       <c r="G211" t="n">
         <v>7059200</v>
@@ -5302,16 +5302,16 @@
         <v>45596</v>
       </c>
       <c r="C212" t="n">
-        <v>94.15779876708984</v>
+        <v>94.15776824951172</v>
       </c>
       <c r="D212" t="n">
-        <v>94.16715109240236</v>
+        <v>94.16712057179303</v>
       </c>
       <c r="E212" t="n">
-        <v>94.14845357551135</v>
+        <v>94.1484230609621</v>
       </c>
       <c r="F212" t="n">
-        <v>94.14845357551135</v>
+        <v>94.1484230609621</v>
       </c>
       <c r="G212" t="n">
         <v>11321100</v>
@@ -5325,16 +5325,16 @@
         <v>45597</v>
       </c>
       <c r="C213" t="n">
-        <v>94.20941162109375</v>
+        <v>94.20941925048828</v>
       </c>
       <c r="D213" t="n">
-        <v>94.20941162109375</v>
+        <v>94.20941925048828</v>
       </c>
       <c r="E213" t="n">
-        <v>94.20002775979395</v>
+        <v>94.20003538842856</v>
       </c>
       <c r="F213" t="n">
-        <v>94.20941162109375</v>
+        <v>94.20941925048828</v>
       </c>
       <c r="G213" t="n">
         <v>13451800</v>
@@ -5348,16 +5348,16 @@
         <v>45600</v>
       </c>
       <c r="C214" t="n">
-        <v>94.21882629394531</v>
+        <v>94.21880340576172</v>
       </c>
       <c r="D214" t="n">
-        <v>94.22727893448958</v>
+        <v>94.22725604425263</v>
       </c>
       <c r="E214" t="n">
-        <v>94.20943526703553</v>
+        <v>94.20941238113326</v>
       </c>
       <c r="F214" t="n">
-        <v>94.21882629394531</v>
+        <v>94.21880340576172</v>
       </c>
       <c r="G214" t="n">
         <v>5041500</v>
@@ -5371,16 +5371,16 @@
         <v>45601</v>
       </c>
       <c r="C215" t="n">
-        <v>94.23757934570312</v>
+        <v>94.23757171630859</v>
       </c>
       <c r="D215" t="n">
-        <v>94.23757934570312</v>
+        <v>94.23757171630859</v>
       </c>
       <c r="E215" t="n">
-        <v>94.21879729766383</v>
+        <v>94.21878966978989</v>
       </c>
       <c r="F215" t="n">
-        <v>94.22818832168348</v>
+        <v>94.22818069304924</v>
       </c>
       <c r="G215" t="n">
         <v>4280500</v>
@@ -5394,16 +5394,16 @@
         <v>45602</v>
       </c>
       <c r="C216" t="n">
-        <v>94.23757934570312</v>
+        <v>94.23757171630859</v>
       </c>
       <c r="D216" t="n">
-        <v>94.24696320647028</v>
+        <v>94.24695557631604</v>
       </c>
       <c r="E216" t="n">
-        <v>94.22818832168348</v>
+        <v>94.22818069304924</v>
       </c>
       <c r="F216" t="n">
-        <v>94.22818832168348</v>
+        <v>94.22818069304924</v>
       </c>
       <c r="G216" t="n">
         <v>9470900</v>
@@ -5417,16 +5417,16 @@
         <v>45603</v>
       </c>
       <c r="C217" t="n">
-        <v>94.25636291503906</v>
+        <v>94.25635528564453</v>
       </c>
       <c r="D217" t="n">
-        <v>94.25636291503906</v>
+        <v>94.25635528564453</v>
       </c>
       <c r="E217" t="n">
-        <v>94.24697189015416</v>
+        <v>94.24696426151975</v>
       </c>
       <c r="F217" t="n">
-        <v>94.24697189015416</v>
+        <v>94.24696426151975</v>
       </c>
       <c r="G217" t="n">
         <v>6188100</v>
@@ -5440,16 +5440,16 @@
         <v>45604</v>
       </c>
       <c r="C218" t="n">
-        <v>94.30330657958984</v>
+        <v>94.30331420898438</v>
       </c>
       <c r="D218" t="n">
-        <v>94.30330657958984</v>
+        <v>94.30331420898438</v>
       </c>
       <c r="E218" t="n">
-        <v>94.28452453067575</v>
+        <v>94.28453215855077</v>
       </c>
       <c r="F218" t="n">
-        <v>94.2939155551328</v>
+        <v>94.29392318376757</v>
       </c>
       <c r="G218" t="n">
         <v>5624200</v>
@@ -5486,16 +5486,16 @@
         <v>45608</v>
       </c>
       <c r="C220" t="n">
-        <v>94.30330657958984</v>
+        <v>94.30331420898438</v>
       </c>
       <c r="D220" t="n">
-        <v>94.31269044079406</v>
+        <v>94.31269807094777</v>
       </c>
       <c r="E220" t="n">
-        <v>94.30330657958984</v>
+        <v>94.30331420898438</v>
       </c>
       <c r="F220" t="n">
-        <v>94.31269044079406</v>
+        <v>94.31269807094777</v>
       </c>
       <c r="G220" t="n">
         <v>4283300</v>
@@ -5555,16 +5555,16 @@
         <v>45611</v>
       </c>
       <c r="C223" t="n">
-        <v>94.37841033935547</v>
+        <v>94.37841796875</v>
       </c>
       <c r="D223" t="n">
-        <v>94.37841033935547</v>
+        <v>94.37841796875</v>
       </c>
       <c r="E223" t="n">
-        <v>94.36902647844418</v>
+        <v>94.36903410708014</v>
       </c>
       <c r="F223" t="n">
-        <v>94.36902647844418</v>
+        <v>94.36903410708014</v>
       </c>
       <c r="G223" t="n">
         <v>5605100</v>
@@ -5578,16 +5578,16 @@
         <v>45614</v>
       </c>
       <c r="C224" t="n">
-        <v>94.38779449462891</v>
+        <v>94.38780975341797</v>
       </c>
       <c r="D224" t="n">
-        <v>94.38779449462891</v>
+        <v>94.38780975341797</v>
       </c>
       <c r="E224" t="n">
-        <v>94.37840347114843</v>
+        <v>94.37841872841933</v>
       </c>
       <c r="F224" t="n">
-        <v>94.38779449462891</v>
+        <v>94.38780975341797</v>
       </c>
       <c r="G224" t="n">
         <v>5567500</v>
@@ -5601,16 +5601,16 @@
         <v>45615</v>
       </c>
       <c r="C225" t="n">
-        <v>94.39719390869141</v>
+        <v>94.39717864990234</v>
       </c>
       <c r="D225" t="n">
-        <v>94.39719390869141</v>
+        <v>94.39717864990234</v>
       </c>
       <c r="E225" t="n">
-        <v>94.3878028843762</v>
+        <v>94.38778762710514</v>
       </c>
       <c r="F225" t="n">
-        <v>94.39719390869141</v>
+        <v>94.39717864990234</v>
       </c>
       <c r="G225" t="n">
         <v>4310900</v>
@@ -5670,16 +5670,16 @@
         <v>45618</v>
       </c>
       <c r="C228" t="n">
-        <v>94.44412231445312</v>
+        <v>94.44415283203125</v>
       </c>
       <c r="D228" t="n">
-        <v>94.45351333753641</v>
+        <v>94.45354385814905</v>
       </c>
       <c r="E228" t="n">
-        <v>94.44412231445312</v>
+        <v>94.44415283203125</v>
       </c>
       <c r="F228" t="n">
-        <v>94.44412231445312</v>
+        <v>94.44415283203125</v>
       </c>
       <c r="G228" t="n">
         <v>4343900</v>
@@ -5693,16 +5693,16 @@
         <v>45621</v>
       </c>
       <c r="C229" t="n">
-        <v>94.45352935791016</v>
+        <v>94.45352172851562</v>
       </c>
       <c r="D229" t="n">
-        <v>94.46292038258626</v>
+        <v>94.46291275243318</v>
       </c>
       <c r="E229" t="n">
-        <v>94.45352935791016</v>
+        <v>94.45352172851562</v>
       </c>
       <c r="F229" t="n">
-        <v>94.45352935791016</v>
+        <v>94.45352172851562</v>
       </c>
       <c r="G229" t="n">
         <v>6020200</v>
@@ -5716,16 +5716,16 @@
         <v>45622</v>
       </c>
       <c r="C230" t="n">
-        <v>94.47229766845703</v>
+        <v>94.47230529785156</v>
       </c>
       <c r="D230" t="n">
-        <v>94.48168152851547</v>
+        <v>94.48168915866783</v>
       </c>
       <c r="E230" t="n">
-        <v>94.46290664514663</v>
+        <v>94.46291427378277</v>
       </c>
       <c r="F230" t="n">
-        <v>94.47229766845703</v>
+        <v>94.47230529785156</v>
       </c>
       <c r="G230" t="n">
         <v>4586900</v>
@@ -5739,16 +5739,16 @@
         <v>45623</v>
       </c>
       <c r="C231" t="n">
-        <v>94.49108123779297</v>
+        <v>94.49109649658203</v>
       </c>
       <c r="D231" t="n">
-        <v>94.50047226196662</v>
+        <v>94.50048752227218</v>
       </c>
       <c r="E231" t="n">
-        <v>94.49108123779297</v>
+        <v>94.49109649658203</v>
       </c>
       <c r="F231" t="n">
-        <v>94.49108123779297</v>
+        <v>94.49109649658203</v>
       </c>
       <c r="G231" t="n">
         <v>5909000</v>
@@ -5785,16 +5785,16 @@
         <v>45628</v>
       </c>
       <c r="C233" t="n">
-        <v>94.54561614990234</v>
+        <v>94.54560852050781</v>
       </c>
       <c r="D233" t="n">
-        <v>94.55504256672454</v>
+        <v>94.55503493656933</v>
       </c>
       <c r="E233" t="n">
-        <v>94.54561614990234</v>
+        <v>94.54560852050781</v>
       </c>
       <c r="F233" t="n">
-        <v>94.55032576318879</v>
+        <v>94.55031813341422</v>
       </c>
       <c r="G233" t="n">
         <v>11471800</v>
@@ -5808,16 +5808,16 @@
         <v>45629</v>
       </c>
       <c r="C234" t="n">
-        <v>94.55502319335938</v>
+        <v>94.55503082275391</v>
       </c>
       <c r="D234" t="n">
-        <v>94.56444241800236</v>
+        <v>94.5644500481569</v>
       </c>
       <c r="E234" t="n">
-        <v>94.55502319335938</v>
+        <v>94.55503082275391</v>
       </c>
       <c r="F234" t="n">
-        <v>94.56444241800236</v>
+        <v>94.5644500481569</v>
       </c>
       <c r="G234" t="n">
         <v>5734100</v>
@@ -5831,16 +5831,16 @@
         <v>45630</v>
       </c>
       <c r="C235" t="n">
-        <v>94.57390594482422</v>
+        <v>94.57389068603516</v>
       </c>
       <c r="D235" t="n">
-        <v>94.58333236341407</v>
+        <v>94.58331710310412</v>
       </c>
       <c r="E235" t="n">
-        <v>94.56447952623438</v>
+        <v>94.56446426896619</v>
       </c>
       <c r="F235" t="n">
-        <v>94.57390594482422</v>
+        <v>94.57389068603516</v>
       </c>
       <c r="G235" t="n">
         <v>5351100</v>
@@ -5900,16 +5900,16 @@
         <v>45635</v>
       </c>
       <c r="C238" t="n">
-        <v>94.63985443115234</v>
+        <v>94.63983917236328</v>
       </c>
       <c r="D238" t="n">
-        <v>94.63985443115234</v>
+        <v>94.63983917236328</v>
       </c>
       <c r="E238" t="n">
-        <v>94.63043520500904</v>
+        <v>94.63041994773863</v>
       </c>
       <c r="F238" t="n">
-        <v>94.63043520500904</v>
+        <v>94.63041994773863</v>
       </c>
       <c r="G238" t="n">
         <v>5539800</v>
@@ -5969,16 +5969,16 @@
         <v>45638</v>
       </c>
       <c r="C241" t="n">
-        <v>94.66810607910156</v>
+        <v>94.66812896728516</v>
       </c>
       <c r="D241" t="n">
-        <v>94.67753249346146</v>
+        <v>94.6775553839241</v>
       </c>
       <c r="E241" t="n">
-        <v>94.66810607910156</v>
+        <v>94.66812896728516</v>
       </c>
       <c r="F241" t="n">
-        <v>94.67753249346146</v>
+        <v>94.6775553839241</v>
       </c>
       <c r="G241" t="n">
         <v>4701000</v>
@@ -5992,16 +5992,16 @@
         <v>45639</v>
       </c>
       <c r="C242" t="n">
-        <v>94.71524047851562</v>
+        <v>94.71524810791016</v>
       </c>
       <c r="D242" t="n">
-        <v>94.71524047851562</v>
+        <v>94.71524810791016</v>
       </c>
       <c r="E242" t="n">
-        <v>94.70581406320848</v>
+        <v>94.70582169184371</v>
       </c>
       <c r="F242" t="n">
-        <v>94.70581406320848</v>
+        <v>94.70582169184371</v>
       </c>
       <c r="G242" t="n">
         <v>4671500</v>
@@ -6015,16 +6015,16 @@
         <v>45642</v>
       </c>
       <c r="C243" t="n">
-        <v>94.72467041015625</v>
+        <v>94.72468566894531</v>
       </c>
       <c r="D243" t="n">
-        <v>94.72467041015625</v>
+        <v>94.72468566894531</v>
       </c>
       <c r="E243" t="n">
-        <v>94.71524399449918</v>
+        <v>94.71525925176978</v>
       </c>
       <c r="F243" t="n">
-        <v>94.72467041015625</v>
+        <v>94.72468566894531</v>
       </c>
       <c r="G243" t="n">
         <v>5598900</v>
@@ -6038,16 +6038,16 @@
         <v>45643</v>
       </c>
       <c r="C244" t="n">
-        <v>94.72467041015625</v>
+        <v>94.72468566894531</v>
       </c>
       <c r="D244" t="n">
-        <v>94.7340896355649</v>
+        <v>94.73410489587128</v>
       </c>
       <c r="E244" t="n">
-        <v>94.72467041015625</v>
+        <v>94.72468566894531</v>
       </c>
       <c r="F244" t="n">
-        <v>94.7340896355649</v>
+        <v>94.73410489587128</v>
       </c>
       <c r="G244" t="n">
         <v>5798500</v>
@@ -6061,16 +6061,16 @@
         <v>45644</v>
       </c>
       <c r="C245" t="n">
-        <v>94.7454833984375</v>
+        <v>94.74547576904297</v>
       </c>
       <c r="D245" t="n">
-        <v>94.7454833984375</v>
+        <v>94.74547576904297</v>
       </c>
       <c r="E245" t="n">
-        <v>94.73602196475615</v>
+        <v>94.7360143361235</v>
       </c>
       <c r="F245" t="n">
-        <v>94.7454833984375</v>
+        <v>94.74547576904297</v>
       </c>
       <c r="G245" t="n">
         <v>11526500</v>
@@ -6107,16 +6107,16 @@
         <v>45646</v>
       </c>
       <c r="C247" t="n">
-        <v>94.7833251953125</v>
+        <v>94.78331756591797</v>
       </c>
       <c r="D247" t="n">
-        <v>94.79278663004159</v>
+        <v>94.79277899988548</v>
       </c>
       <c r="E247" t="n">
-        <v>94.7833251953125</v>
+        <v>94.78331756591797</v>
       </c>
       <c r="F247" t="n">
-        <v>94.78805952115711</v>
+        <v>94.7880518913815</v>
       </c>
       <c r="G247" t="n">
         <v>8898900</v>
@@ -6130,16 +6130,16 @@
         <v>45649</v>
       </c>
       <c r="C248" t="n">
-        <v>94.80223846435547</v>
+        <v>94.80224609375</v>
       </c>
       <c r="D248" t="n">
-        <v>94.80223846435547</v>
+        <v>94.80224609375</v>
       </c>
       <c r="E248" t="n">
-        <v>94.79277703058452</v>
+        <v>94.79278465921763</v>
       </c>
       <c r="F248" t="n">
-        <v>94.80223846435547</v>
+        <v>94.80224609375</v>
       </c>
       <c r="G248" t="n">
         <v>7032500</v>
@@ -6153,16 +6153,16 @@
         <v>45650</v>
       </c>
       <c r="C249" t="n">
-        <v>94.83064270019531</v>
+        <v>94.83062744140625</v>
       </c>
       <c r="D249" t="n">
-        <v>94.83064270019531</v>
+        <v>94.83062744140625</v>
       </c>
       <c r="E249" t="n">
-        <v>94.82118126371542</v>
+        <v>94.82116600644875</v>
       </c>
       <c r="F249" t="n">
-        <v>94.83064270019531</v>
+        <v>94.83062744140625</v>
       </c>
       <c r="G249" t="n">
         <v>4654300</v>
@@ -6176,16 +6176,16 @@
         <v>45652</v>
       </c>
       <c r="C250" t="n">
-        <v>94.84009552001953</v>
+        <v>94.84008026123047</v>
       </c>
       <c r="D250" t="n">
-        <v>94.84009552001953</v>
+        <v>94.84008026123047</v>
       </c>
       <c r="E250" t="n">
-        <v>94.83063408439924</v>
+        <v>94.83061882713243</v>
       </c>
       <c r="F250" t="n">
-        <v>94.84009552001953</v>
+        <v>94.84008026123047</v>
       </c>
       <c r="G250" t="n">
         <v>4974100</v>
@@ -6199,16 +6199,16 @@
         <v>45653</v>
       </c>
       <c r="C251" t="n">
-        <v>94.86845397949219</v>
+        <v>94.86843872070312</v>
       </c>
       <c r="D251" t="n">
-        <v>94.86845397949219</v>
+        <v>94.86843872070312</v>
       </c>
       <c r="E251" t="n">
-        <v>94.85899254572995</v>
+        <v>94.85897728846268</v>
       </c>
       <c r="F251" t="n">
-        <v>94.85899254572995</v>
+        <v>94.85897728846268</v>
       </c>
       <c r="G251" t="n">
         <v>6558000</v>
@@ -6222,16 +6222,16 @@
         <v>45656</v>
       </c>
       <c r="C252" t="n">
-        <v>94.86845397949219</v>
+        <v>94.86843872070312</v>
       </c>
       <c r="D252" t="n">
-        <v>94.87791541325443</v>
+        <v>94.87790015294357</v>
       </c>
       <c r="E252" t="n">
-        <v>94.86845397949219</v>
+        <v>94.86843872070312</v>
       </c>
       <c r="F252" t="n">
-        <v>94.87791541325443</v>
+        <v>94.87790015294357</v>
       </c>
       <c r="G252" t="n">
         <v>6547600</v>
@@ -6245,16 +6245,16 @@
         <v>45657</v>
       </c>
       <c r="C253" t="n">
-        <v>94.89682769775391</v>
+        <v>94.89684295654297</v>
       </c>
       <c r="D253" t="n">
-        <v>94.91574334764803</v>
+        <v>94.9157586094786</v>
       </c>
       <c r="E253" t="n">
-        <v>94.89682769775391</v>
+        <v>94.89684295654297</v>
       </c>
       <c r="F253" t="n">
-        <v>94.90628913118054</v>
+        <v>94.90630439149093</v>
       </c>
       <c r="G253" t="n">
         <v>7371300</v>
@@ -6268,16 +6268,16 @@
         <v>45659</v>
       </c>
       <c r="C254" t="n">
-        <v>94.91575622558594</v>
+        <v>94.91574859619141</v>
       </c>
       <c r="D254" t="n">
-        <v>94.91575622558594</v>
+        <v>94.91574859619141</v>
       </c>
       <c r="E254" t="n">
-        <v>94.90630200783571</v>
+        <v>94.90629437920111</v>
       </c>
       <c r="F254" t="n">
-        <v>94.91575622558594</v>
+        <v>94.91574859619141</v>
       </c>
       <c r="G254" t="n">
         <v>7533100</v>
@@ -6291,16 +6291,16 @@
         <v>45660</v>
       </c>
       <c r="C255" t="n">
-        <v>94.94414520263672</v>
+        <v>94.94412994384766</v>
       </c>
       <c r="D255" t="n">
-        <v>94.95359942085226</v>
+        <v>94.95358416054377</v>
       </c>
       <c r="E255" t="n">
-        <v>94.94414520263672</v>
+        <v>94.94412994384766</v>
       </c>
       <c r="F255" t="n">
-        <v>94.95359942085226</v>
+        <v>94.95358416054377</v>
       </c>
       <c r="G255" t="n">
         <v>6730100</v>
@@ -6314,16 +6314,16 @@
         <v>45663</v>
       </c>
       <c r="C256" t="n">
-        <v>94.94414520263672</v>
+        <v>94.94412994384766</v>
       </c>
       <c r="D256" t="n">
-        <v>94.96306085602826</v>
+        <v>94.9630455941992</v>
       </c>
       <c r="E256" t="n">
-        <v>94.94414520263672</v>
+        <v>94.94412994384766</v>
       </c>
       <c r="F256" t="n">
-        <v>94.95359942085226</v>
+        <v>94.95358416054377</v>
       </c>
       <c r="G256" t="n">
         <v>6938300</v>
@@ -6337,16 +6337,16 @@
         <v>45664</v>
       </c>
       <c r="C257" t="n">
-        <v>94.96305084228516</v>
+        <v>94.96305847167969</v>
       </c>
       <c r="D257" t="n">
-        <v>94.97251227646346</v>
+        <v>94.97251990661813</v>
       </c>
       <c r="E257" t="n">
-        <v>94.96305084228516</v>
+        <v>94.96305847167969</v>
       </c>
       <c r="F257" t="n">
-        <v>94.97251227646346</v>
+        <v>94.97251990661813</v>
       </c>
       <c r="G257" t="n">
         <v>6792100</v>
@@ -6360,16 +6360,16 @@
         <v>45665</v>
       </c>
       <c r="C258" t="n">
-        <v>94.98197174072266</v>
+        <v>94.98195648193359</v>
       </c>
       <c r="D258" t="n">
-        <v>94.98197174072266</v>
+        <v>94.98195648193359</v>
       </c>
       <c r="E258" t="n">
-        <v>94.97251030674057</v>
+        <v>94.97249504947149</v>
       </c>
       <c r="F258" t="n">
-        <v>94.97251030674057</v>
+        <v>94.97249504947149</v>
       </c>
       <c r="G258" t="n">
         <v>6101100</v>
@@ -6383,16 +6383,16 @@
         <v>45667</v>
       </c>
       <c r="C259" t="n">
-        <v>95.01979064941406</v>
+        <v>95.01980590820312</v>
       </c>
       <c r="D259" t="n">
-        <v>95.0292520821621</v>
+        <v>95.02926734247052</v>
       </c>
       <c r="E259" t="n">
-        <v>95.01033643362464</v>
+        <v>95.0103516908955</v>
       </c>
       <c r="F259" t="n">
-        <v>95.01979064941406</v>
+        <v>95.01980590820312</v>
       </c>
       <c r="G259" t="n">
         <v>7644600</v>
@@ -6429,16 +6429,16 @@
         <v>45671</v>
       </c>
       <c r="C261" t="n">
-        <v>95.04821014404297</v>
+        <v>95.04819488525391</v>
       </c>
       <c r="D261" t="n">
-        <v>95.04821014404297</v>
+        <v>95.04819488525391</v>
       </c>
       <c r="E261" t="n">
-        <v>95.03874870779136</v>
+        <v>95.03873345052121</v>
       </c>
       <c r="F261" t="n">
-        <v>95.04821014404297</v>
+        <v>95.04819488525391</v>
       </c>
       <c r="G261" t="n">
         <v>7245400</v>
@@ -6452,16 +6452,16 @@
         <v>45672</v>
       </c>
       <c r="C262" t="n">
-        <v>95.05764770507812</v>
+        <v>95.05764007568359</v>
       </c>
       <c r="D262" t="n">
-        <v>95.05764770507812</v>
+        <v>95.05764007568359</v>
       </c>
       <c r="E262" t="n">
-        <v>95.04819348744461</v>
+        <v>95.04818585880886</v>
       </c>
       <c r="F262" t="n">
-        <v>95.05764770507812</v>
+        <v>95.05764007568359</v>
       </c>
       <c r="G262" t="n">
         <v>6878600</v>
@@ -6475,16 +6475,16 @@
         <v>45673</v>
       </c>
       <c r="C263" t="n">
-        <v>95.05764770507812</v>
+        <v>95.05764007568359</v>
       </c>
       <c r="D263" t="n">
-        <v>95.07657057426523</v>
+        <v>95.07656294335193</v>
       </c>
       <c r="E263" t="n">
-        <v>95.05764770507812</v>
+        <v>95.05764007568359</v>
       </c>
       <c r="F263" t="n">
-        <v>95.06710913967167</v>
+        <v>95.06710150951776</v>
       </c>
       <c r="G263" t="n">
         <v>5352500</v>
@@ -6498,16 +6498,16 @@
         <v>45674</v>
       </c>
       <c r="C264" t="n">
-        <v>95.10492706298828</v>
+        <v>95.10494995117188</v>
       </c>
       <c r="D264" t="n">
-        <v>95.11438849553264</v>
+        <v>95.11441138599326</v>
       </c>
       <c r="E264" t="n">
-        <v>95.09546563044391</v>
+        <v>95.0954885163505</v>
       </c>
       <c r="F264" t="n">
-        <v>95.10492706298828</v>
+        <v>95.10494995117188</v>
       </c>
       <c r="G264" t="n">
         <v>6563000</v>
@@ -6521,16 +6521,16 @@
         <v>45678</v>
       </c>
       <c r="C265" t="n">
-        <v>95.11439514160156</v>
+        <v>95.11441040039062</v>
       </c>
       <c r="D265" t="n">
-        <v>95.12384935784807</v>
+        <v>95.12386461815383</v>
       </c>
       <c r="E265" t="n">
-        <v>95.11439514160156</v>
+        <v>95.11441040039062</v>
       </c>
       <c r="F265" t="n">
-        <v>95.11912224972482</v>
+        <v>95.11913750927222</v>
       </c>
       <c r="G265" t="n">
         <v>7952400</v>
@@ -6567,16 +6567,16 @@
         <v>45680</v>
       </c>
       <c r="C267" t="n">
-        <v>95.14277648925781</v>
+        <v>95.14276885986328</v>
       </c>
       <c r="D267" t="n">
-        <v>95.14277648925781</v>
+        <v>95.14276885986328</v>
       </c>
       <c r="E267" t="n">
-        <v>95.1333150556282</v>
+        <v>95.13330742699237</v>
       </c>
       <c r="F267" t="n">
-        <v>95.14277648925781</v>
+        <v>95.14276885986328</v>
       </c>
       <c r="G267" t="n">
         <v>5085800</v>
@@ -6590,16 +6590,16 @@
         <v>45681</v>
       </c>
       <c r="C268" t="n">
-        <v>95.17115783691406</v>
+        <v>95.17116546630859</v>
       </c>
       <c r="D268" t="n">
-        <v>95.18061927096755</v>
+        <v>95.18062690112056</v>
       </c>
       <c r="E268" t="n">
-        <v>95.17115783691406</v>
+        <v>95.17116546630859</v>
       </c>
       <c r="F268" t="n">
-        <v>95.17115783691406</v>
+        <v>95.17116546630859</v>
       </c>
       <c r="G268" t="n">
         <v>6380000</v>
@@ -6613,16 +6613,16 @@
         <v>45684</v>
       </c>
       <c r="C269" t="n">
-        <v>95.17115783691406</v>
+        <v>95.17116546630859</v>
       </c>
       <c r="D269" t="n">
-        <v>95.19007348806143</v>
+        <v>95.19008111897233</v>
       </c>
       <c r="E269" t="n">
-        <v>95.17115783691406</v>
+        <v>95.17116546630859</v>
       </c>
       <c r="F269" t="n">
-        <v>95.18061927096755</v>
+        <v>95.18062690112056</v>
       </c>
       <c r="G269" t="n">
         <v>9439800</v>
@@ -6636,16 +6636,16 @@
         <v>45685</v>
       </c>
       <c r="C270" t="n">
-        <v>95.19953918457031</v>
+        <v>95.19951629638672</v>
       </c>
       <c r="D270" t="n">
-        <v>95.19953918457031</v>
+        <v>95.19951629638672</v>
       </c>
       <c r="E270" t="n">
-        <v>95.18062353257602</v>
+        <v>95.1806006489402</v>
       </c>
       <c r="F270" t="n">
-        <v>95.1900777500932</v>
+        <v>95.19005486418436</v>
       </c>
       <c r="G270" t="n">
         <v>5857900</v>
@@ -6659,16 +6659,16 @@
         <v>45686</v>
       </c>
       <c r="C271" t="n">
-        <v>95.19953918457031</v>
+        <v>95.19951629638672</v>
       </c>
       <c r="D271" t="n">
-        <v>95.20900061904742</v>
+        <v>95.20897772858909</v>
       </c>
       <c r="E271" t="n">
-        <v>95.19953918457031</v>
+        <v>95.19951629638672</v>
       </c>
       <c r="F271" t="n">
-        <v>95.19953918457031</v>
+        <v>95.19951629638672</v>
       </c>
       <c r="G271" t="n">
         <v>3978700</v>
@@ -6682,16 +6682,16 @@
         <v>45687</v>
       </c>
       <c r="C272" t="n">
-        <v>95.21846771240234</v>
+        <v>95.21846008300781</v>
       </c>
       <c r="D272" t="n">
-        <v>95.22792193048139</v>
+        <v>95.22791430032933</v>
       </c>
       <c r="E272" t="n">
-        <v>95.20900627736293</v>
+        <v>95.20899864872649</v>
       </c>
       <c r="F272" t="n">
-        <v>95.20900627736293</v>
+        <v>95.20899864872649</v>
       </c>
       <c r="G272" t="n">
         <v>8043500</v>
@@ -6797,16 +6797,16 @@
         <v>45694</v>
       </c>
       <c r="C277" t="n">
-        <v>95.29719543457031</v>
+        <v>95.29717254638672</v>
       </c>
       <c r="D277" t="n">
-        <v>95.29719543457031</v>
+        <v>95.29717254638672</v>
       </c>
       <c r="E277" t="n">
-        <v>95.28770700562752</v>
+        <v>95.28768411972284</v>
       </c>
       <c r="F277" t="n">
-        <v>95.29719543457031</v>
+        <v>95.29717254638672</v>
       </c>
       <c r="G277" t="n">
         <v>5804300</v>
@@ -6843,16 +6843,16 @@
         <v>45698</v>
       </c>
       <c r="C279" t="n">
-        <v>95.34465789794922</v>
+        <v>95.34466552734375</v>
       </c>
       <c r="D279" t="n">
-        <v>95.34465789794922</v>
+        <v>95.34466552734375</v>
       </c>
       <c r="E279" t="n">
-        <v>95.33516222679275</v>
+        <v>95.33516985542744</v>
       </c>
       <c r="F279" t="n">
-        <v>95.34465789794922</v>
+        <v>95.34466552734375</v>
       </c>
       <c r="G279" t="n">
         <v>7517800</v>
@@ -6866,16 +6866,16 @@
         <v>45699</v>
       </c>
       <c r="C280" t="n">
-        <v>95.34465789794922</v>
+        <v>95.34466552734375</v>
       </c>
       <c r="D280" t="n">
-        <v>95.35415356910569</v>
+        <v>95.35416119926006</v>
       </c>
       <c r="E280" t="n">
-        <v>95.34465789794922</v>
+        <v>95.34466552734375</v>
       </c>
       <c r="F280" t="n">
-        <v>95.35415356910569</v>
+        <v>95.35416119926006</v>
       </c>
       <c r="G280" t="n">
         <v>6424100</v>
@@ -6889,16 +6889,16 @@
         <v>45700</v>
       </c>
       <c r="C281" t="n">
-        <v>95.35414886474609</v>
+        <v>95.35415649414062</v>
       </c>
       <c r="D281" t="n">
-        <v>95.36363729235957</v>
+        <v>95.36364492251329</v>
       </c>
       <c r="E281" t="n">
-        <v>95.35414886474609</v>
+        <v>95.35415649414062</v>
       </c>
       <c r="F281" t="n">
-        <v>95.35414886474609</v>
+        <v>95.35415649414062</v>
       </c>
       <c r="G281" t="n">
         <v>6618800</v>
@@ -6935,16 +6935,16 @@
         <v>45702</v>
       </c>
       <c r="C283" t="n">
-        <v>95.41111755371094</v>
+        <v>95.41109466552734</v>
       </c>
       <c r="D283" t="n">
-        <v>95.42061322530968</v>
+        <v>95.42059033484817</v>
       </c>
       <c r="E283" t="n">
-        <v>95.41111755371094</v>
+        <v>95.41109466552734</v>
       </c>
       <c r="F283" t="n">
-        <v>95.4158617679727</v>
+        <v>95.41583887865103</v>
       </c>
       <c r="G283" t="n">
         <v>7648100</v>
@@ -6958,16 +6958,16 @@
         <v>45706</v>
       </c>
       <c r="C284" t="n">
-        <v>95.43007659912109</v>
+        <v>95.43010711669922</v>
       </c>
       <c r="D284" t="n">
-        <v>95.43007659912109</v>
+        <v>95.43010711669922</v>
       </c>
       <c r="E284" t="n">
-        <v>95.4205881730887</v>
+        <v>95.42061868763253</v>
       </c>
       <c r="F284" t="n">
-        <v>95.43007659912109</v>
+        <v>95.43010711669922</v>
       </c>
       <c r="G284" t="n">
         <v>15815200</v>
@@ -6981,16 +6981,16 @@
         <v>45707</v>
       </c>
       <c r="C285" t="n">
-        <v>95.43007659912109</v>
+        <v>95.43010711669922</v>
       </c>
       <c r="D285" t="n">
-        <v>95.4395722682268</v>
+        <v>95.43960278884154</v>
       </c>
       <c r="E285" t="n">
-        <v>95.43007659912109</v>
+        <v>95.43010711669922</v>
       </c>
       <c r="F285" t="n">
-        <v>95.4395722682268</v>
+        <v>95.43960278884154</v>
       </c>
       <c r="G285" t="n">
         <v>7277600</v>
@@ -7004,16 +7004,16 @@
         <v>45708</v>
       </c>
       <c r="C286" t="n">
-        <v>95.44907379150391</v>
+        <v>95.44908905029297</v>
       </c>
       <c r="D286" t="n">
-        <v>95.44907379150391</v>
+        <v>95.44908905029297</v>
       </c>
       <c r="E286" t="n">
-        <v>95.43957812181581</v>
+        <v>95.43959337908686</v>
       </c>
       <c r="F286" t="n">
-        <v>95.44907379150391</v>
+        <v>95.44908905029297</v>
       </c>
       <c r="G286" t="n">
         <v>7608000</v>
@@ -7027,16 +7027,16 @@
         <v>45709</v>
       </c>
       <c r="C287" t="n">
-        <v>95.487060546875</v>
+        <v>95.48705291748047</v>
       </c>
       <c r="D287" t="n">
-        <v>95.487060546875</v>
+        <v>95.48705291748047</v>
       </c>
       <c r="E287" t="n">
-        <v>95.47756487606122</v>
+        <v>95.47755724742539</v>
       </c>
       <c r="F287" t="n">
-        <v>95.47756487606122</v>
+        <v>95.47755724742539</v>
       </c>
       <c r="G287" t="n">
         <v>9111000</v>
@@ -7050,16 +7050,16 @@
         <v>45712</v>
       </c>
       <c r="C288" t="n">
-        <v>95.49655151367188</v>
+        <v>95.49655914306641</v>
       </c>
       <c r="D288" t="n">
-        <v>95.49655151367188</v>
+        <v>95.49655914306641</v>
       </c>
       <c r="E288" t="n">
-        <v>95.48706308568042</v>
+        <v>95.48707071431691</v>
       </c>
       <c r="F288" t="n">
-        <v>95.49655151367188</v>
+        <v>95.49655914306641</v>
       </c>
       <c r="G288" t="n">
         <v>9734600</v>
@@ -7119,16 +7119,16 @@
         <v>45715</v>
       </c>
       <c r="C291" t="n">
-        <v>95.53453063964844</v>
+        <v>95.53452301025391</v>
       </c>
       <c r="D291" t="n">
-        <v>95.53453063964844</v>
+        <v>95.53452301025391</v>
       </c>
       <c r="E291" t="n">
-        <v>95.52504221129102</v>
+        <v>95.52503458265423</v>
       </c>
       <c r="F291" t="n">
-        <v>95.53453063964844</v>
+        <v>95.53452301025391</v>
       </c>
       <c r="G291" t="n">
         <v>10807800</v>
@@ -7142,16 +7142,16 @@
         <v>45716</v>
       </c>
       <c r="C292" t="n">
-        <v>95.55351257324219</v>
+        <v>95.55352020263672</v>
       </c>
       <c r="D292" t="n">
-        <v>95.56300824373963</v>
+        <v>95.56301587389234</v>
       </c>
       <c r="E292" t="n">
-        <v>95.55351257324219</v>
+        <v>95.55352020263672</v>
       </c>
       <c r="F292" t="n">
-        <v>95.55351257324219</v>
+        <v>95.55352020263672</v>
       </c>
       <c r="G292" t="n">
         <v>13772600</v>
@@ -7188,16 +7188,16 @@
         <v>45720</v>
       </c>
       <c r="C294" t="n">
-        <v>95.58493041992188</v>
+        <v>95.58493804931641</v>
       </c>
       <c r="D294" t="n">
-        <v>95.58493041992188</v>
+        <v>95.58493804931641</v>
       </c>
       <c r="E294" t="n">
-        <v>95.57540512880422</v>
+        <v>95.57541275743847</v>
       </c>
       <c r="F294" t="n">
-        <v>95.58493041992188</v>
+        <v>95.58493804931641</v>
       </c>
       <c r="G294" t="n">
         <v>11543100</v>
@@ -7211,16 +7211,16 @@
         <v>45721</v>
       </c>
       <c r="C295" t="n">
-        <v>95.58493041992188</v>
+        <v>95.58493804931641</v>
       </c>
       <c r="D295" t="n">
-        <v>95.59444844537123</v>
+        <v>95.59445607552547</v>
       </c>
       <c r="E295" t="n">
-        <v>95.58493041992188</v>
+        <v>95.58493804931641</v>
       </c>
       <c r="F295" t="n">
-        <v>95.58493041992188</v>
+        <v>95.58493804931641</v>
       </c>
       <c r="G295" t="n">
         <v>7162600</v>
@@ -7234,16 +7234,16 @@
         <v>45722</v>
       </c>
       <c r="C296" t="n">
-        <v>95.61351013183594</v>
+        <v>95.61351776123047</v>
       </c>
       <c r="D296" t="n">
-        <v>95.61351013183594</v>
+        <v>95.61351776123047</v>
       </c>
       <c r="E296" t="n">
-        <v>95.59445954738818</v>
+        <v>95.59446717526258</v>
       </c>
       <c r="F296" t="n">
-        <v>95.60398483961205</v>
+        <v>95.60399246824653</v>
       </c>
       <c r="G296" t="n">
         <v>9925500</v>
@@ -7303,16 +7303,16 @@
         <v>45727</v>
       </c>
       <c r="C299" t="n">
-        <v>95.66110229492188</v>
+        <v>95.66111755371094</v>
       </c>
       <c r="D299" t="n">
-        <v>95.66110229492188</v>
+        <v>95.66111755371094</v>
       </c>
       <c r="E299" t="n">
-        <v>95.65158427033386</v>
+        <v>95.65159952760472</v>
       </c>
       <c r="F299" t="n">
-        <v>95.65158427033386</v>
+        <v>95.65159952760472</v>
       </c>
       <c r="G299" t="n">
         <v>11456900</v>
@@ -7326,16 +7326,16 @@
         <v>45728</v>
       </c>
       <c r="C300" t="n">
-        <v>95.66110229492188</v>
+        <v>95.66111755371094</v>
       </c>
       <c r="D300" t="n">
-        <v>95.67062758517753</v>
+        <v>95.67064284548596</v>
       </c>
       <c r="E300" t="n">
-        <v>95.66110229492188</v>
+        <v>95.66111755371094</v>
       </c>
       <c r="F300" t="n">
-        <v>95.67062758517753</v>
+        <v>95.67064284548596</v>
       </c>
       <c r="G300" t="n">
         <v>11307300</v>
@@ -7349,16 +7349,16 @@
         <v>45729</v>
       </c>
       <c r="C301" t="n">
-        <v>95.68972015380859</v>
+        <v>95.68971252441406</v>
       </c>
       <c r="D301" t="n">
-        <v>95.68972015380859</v>
+        <v>95.68971252441406</v>
       </c>
       <c r="E301" t="n">
-        <v>95.67066956493801</v>
+        <v>95.67066193706239</v>
       </c>
       <c r="F301" t="n">
-        <v>95.67066956493801</v>
+        <v>95.67066193706239</v>
       </c>
       <c r="G301" t="n">
         <v>13110600</v>
@@ -7395,16 +7395,16 @@
         <v>45733</v>
       </c>
       <c r="C303" t="n">
-        <v>95.72777557373047</v>
+        <v>95.72779846191406</v>
       </c>
       <c r="D303" t="n">
-        <v>95.72777557373047</v>
+        <v>95.72779846191406</v>
       </c>
       <c r="E303" t="n">
-        <v>95.71825754807078</v>
+        <v>95.71828043397865</v>
       </c>
       <c r="F303" t="n">
-        <v>95.72777557373047</v>
+        <v>95.72779846191406</v>
       </c>
       <c r="G303" t="n">
         <v>9018300</v>
@@ -7510,16 +7510,16 @@
         <v>45740</v>
       </c>
       <c r="C308" t="n">
-        <v>95.80397033691406</v>
+        <v>95.80397796630859</v>
       </c>
       <c r="D308" t="n">
-        <v>95.81349562893458</v>
+        <v>95.81350325908767</v>
       </c>
       <c r="E308" t="n">
-        <v>95.80397033691406</v>
+        <v>95.80397796630859</v>
       </c>
       <c r="F308" t="n">
-        <v>95.8087366157588</v>
+        <v>95.80874424553291</v>
       </c>
       <c r="G308" t="n">
         <v>13854600</v>
@@ -7533,16 +7533,16 @@
         <v>45741</v>
       </c>
       <c r="C309" t="n">
-        <v>95.81350708007812</v>
+        <v>95.81349945068359</v>
       </c>
       <c r="D309" t="n">
-        <v>95.81350708007812</v>
+        <v>95.81349945068359</v>
       </c>
       <c r="E309" t="n">
-        <v>95.80398178691919</v>
+        <v>95.80397415828314</v>
       </c>
       <c r="F309" t="n">
-        <v>95.81350708007812</v>
+        <v>95.81349945068359</v>
       </c>
       <c r="G309" t="n">
         <v>13844800</v>
@@ -7556,16 +7556,16 @@
         <v>45742</v>
       </c>
       <c r="C310" t="n">
-        <v>95.83255004882812</v>
+        <v>95.83254241943359</v>
       </c>
       <c r="D310" t="n">
-        <v>95.83255004882812</v>
+        <v>95.83254241943359</v>
       </c>
       <c r="E310" t="n">
-        <v>95.82303202137399</v>
+        <v>95.8230243927372</v>
       </c>
       <c r="F310" t="n">
-        <v>95.83255004882812</v>
+        <v>95.83254241943359</v>
       </c>
       <c r="G310" t="n">
         <v>12262200</v>
@@ -7579,16 +7579,16 @@
         <v>45743</v>
       </c>
       <c r="C311" t="n">
-        <v>95.84207916259766</v>
+        <v>95.84204864501953</v>
       </c>
       <c r="D311" t="n">
-        <v>95.84207916259766</v>
+        <v>95.84204864501953</v>
       </c>
       <c r="E311" t="n">
-        <v>95.83255386909399</v>
+        <v>95.83252335454887</v>
       </c>
       <c r="F311" t="n">
-        <v>95.84207916259766</v>
+        <v>95.84204864501953</v>
       </c>
       <c r="G311" t="n">
         <v>10022000</v>
@@ -7602,16 +7602,16 @@
         <v>45744</v>
       </c>
       <c r="C312" t="n">
-        <v>95.87063598632812</v>
+        <v>95.87065124511719</v>
       </c>
       <c r="D312" t="n">
-        <v>95.87063598632812</v>
+        <v>95.87065124511719</v>
       </c>
       <c r="E312" t="n">
-        <v>95.86111795966518</v>
+        <v>95.86113321693935</v>
       </c>
       <c r="F312" t="n">
-        <v>95.86111795966518</v>
+        <v>95.86113321693935</v>
       </c>
       <c r="G312" t="n">
         <v>11747100</v>
@@ -7625,16 +7625,16 @@
         <v>45747</v>
       </c>
       <c r="C313" t="n">
-        <v>95.87063598632812</v>
+        <v>95.87065124511719</v>
       </c>
       <c r="D313" t="n">
-        <v>95.88016127866028</v>
+        <v>95.88017653896539</v>
       </c>
       <c r="E313" t="n">
-        <v>95.87063598632812</v>
+        <v>95.87065124511719</v>
       </c>
       <c r="F313" t="n">
-        <v>95.87063598632812</v>
+        <v>95.87065124511719</v>
       </c>
       <c r="G313" t="n">
         <v>18210800</v>
@@ -7671,16 +7671,16 @@
         <v>45749</v>
       </c>
       <c r="C315" t="n">
-        <v>95.90505981445312</v>
+        <v>95.90504455566406</v>
       </c>
       <c r="D315" t="n">
-        <v>95.90505981445312</v>
+        <v>95.90504455566406</v>
       </c>
       <c r="E315" t="n">
-        <v>95.89550166910018</v>
+        <v>95.89548641183185</v>
       </c>
       <c r="F315" t="n">
-        <v>95.90505981445312</v>
+        <v>95.90504455566406</v>
       </c>
       <c r="G315" t="n">
         <v>10658900</v>
@@ -7717,16 +7717,16 @@
         <v>45751</v>
       </c>
       <c r="C317" t="n">
-        <v>95.95282745361328</v>
+        <v>95.95283508300781</v>
       </c>
       <c r="D317" t="n">
-        <v>95.95282745361328</v>
+        <v>95.95283508300781</v>
       </c>
       <c r="E317" t="n">
-        <v>95.94326930983391</v>
+        <v>95.94327693846846</v>
       </c>
       <c r="F317" t="n">
-        <v>95.94326930983391</v>
+        <v>95.94327693846846</v>
       </c>
       <c r="G317" t="n">
         <v>22826300</v>
@@ -7740,16 +7740,16 @@
         <v>45754</v>
       </c>
       <c r="C318" t="n">
-        <v>95.96237182617188</v>
+        <v>95.96236419677734</v>
       </c>
       <c r="D318" t="n">
-        <v>95.96237182617188</v>
+        <v>95.96236419677734</v>
       </c>
       <c r="E318" t="n">
-        <v>95.95282097376501</v>
+        <v>95.9528133451298</v>
       </c>
       <c r="F318" t="n">
-        <v>95.95282097376501</v>
+        <v>95.9528133451298</v>
       </c>
       <c r="G318" t="n">
         <v>22564000</v>
@@ -7763,16 +7763,16 @@
         <v>45755</v>
       </c>
       <c r="C319" t="n">
-        <v>95.96237182617188</v>
+        <v>95.96236419677734</v>
       </c>
       <c r="D319" t="n">
-        <v>95.97192996930578</v>
+        <v>95.97192233915132</v>
       </c>
       <c r="E319" t="n">
-        <v>95.95282097376501</v>
+        <v>95.9528133451298</v>
       </c>
       <c r="F319" t="n">
-        <v>95.95759639996845</v>
+        <v>95.95758877095358</v>
       </c>
       <c r="G319" t="n">
         <v>17116100</v>
@@ -7855,16 +7855,16 @@
         <v>45761</v>
       </c>
       <c r="C323" t="n">
-        <v>96.03884124755859</v>
+        <v>96.03882598876953</v>
       </c>
       <c r="D323" t="n">
-        <v>96.03884124755859</v>
+        <v>96.03882598876953</v>
       </c>
       <c r="E323" t="n">
-        <v>96.02928310254791</v>
+        <v>96.02926784527745</v>
       </c>
       <c r="F323" t="n">
-        <v>96.02928310254791</v>
+        <v>96.02926784527745</v>
       </c>
       <c r="G323" t="n">
         <v>13772300</v>
@@ -7878,16 +7878,16 @@
         <v>45762</v>
       </c>
       <c r="C324" t="n">
-        <v>96.04837799072266</v>
+        <v>96.04840850830078</v>
       </c>
       <c r="D324" t="n">
-        <v>96.04837799072266</v>
+        <v>96.04840850830078</v>
       </c>
       <c r="E324" t="n">
-        <v>96.03881984784175</v>
+        <v>96.03885036238295</v>
       </c>
       <c r="F324" t="n">
-        <v>96.04837799072266</v>
+        <v>96.04840850830078</v>
       </c>
       <c r="G324" t="n">
         <v>10043700</v>
@@ -7924,16 +7924,16 @@
         <v>45764</v>
       </c>
       <c r="C326" t="n">
-        <v>96.10572052001953</v>
+        <v>96.10572814941406</v>
       </c>
       <c r="D326" t="n">
-        <v>96.11527866372128</v>
+        <v>96.11528629387459</v>
       </c>
       <c r="E326" t="n">
-        <v>96.10572052001953</v>
+        <v>96.10572814941406</v>
       </c>
       <c r="F326" t="n">
-        <v>96.11049594650667</v>
+        <v>96.11050357628031</v>
       </c>
       <c r="G326" t="n">
         <v>8652700</v>
@@ -7947,16 +7947,16 @@
         <v>45768</v>
       </c>
       <c r="C327" t="n">
-        <v>96.10572052001953</v>
+        <v>96.10572814941406</v>
       </c>
       <c r="D327" t="n">
-        <v>96.11527866372128</v>
+        <v>96.11528629387459</v>
       </c>
       <c r="E327" t="n">
-        <v>96.10572052001953</v>
+        <v>96.10572814941406</v>
       </c>
       <c r="F327" t="n">
-        <v>96.11527866372128</v>
+        <v>96.11528629387459</v>
       </c>
       <c r="G327" t="n">
         <v>10756100</v>
@@ -7970,16 +7970,16 @@
         <v>45769</v>
       </c>
       <c r="C328" t="n">
-        <v>96.11528778076172</v>
+        <v>96.11527252197266</v>
       </c>
       <c r="D328" t="n">
-        <v>96.12483863464196</v>
+        <v>96.12482337433664</v>
       </c>
       <c r="E328" t="n">
-        <v>96.11528778076172</v>
+        <v>96.11527252197266</v>
       </c>
       <c r="F328" t="n">
-        <v>96.12483863464196</v>
+        <v>96.12482337433664</v>
       </c>
       <c r="G328" t="n">
         <v>11603400</v>
@@ -7993,16 +7993,16 @@
         <v>45770</v>
       </c>
       <c r="C329" t="n">
-        <v>96.14394378662109</v>
+        <v>96.14395141601562</v>
       </c>
       <c r="D329" t="n">
-        <v>96.14394378662109</v>
+        <v>96.14395141601562</v>
       </c>
       <c r="E329" t="n">
-        <v>96.12482749961872</v>
+        <v>96.1248351274963</v>
       </c>
       <c r="F329" t="n">
-        <v>96.13438564311991</v>
+        <v>96.13439327175597</v>
       </c>
       <c r="G329" t="n">
         <v>19135100</v>
@@ -8016,16 +8016,16 @@
         <v>45771</v>
       </c>
       <c r="C330" t="n">
-        <v>96.14394378662109</v>
+        <v>96.14395141601562</v>
       </c>
       <c r="D330" t="n">
-        <v>96.15350193012229</v>
+        <v>96.1535095602753</v>
       </c>
       <c r="E330" t="n">
-        <v>96.14394378662109</v>
+        <v>96.14395141601562</v>
       </c>
       <c r="F330" t="n">
-        <v>96.15350193012229</v>
+        <v>96.1535095602753</v>
       </c>
       <c r="G330" t="n">
         <v>12068700</v>
@@ -8085,16 +8085,16 @@
         <v>45776</v>
       </c>
       <c r="C333" t="n">
-        <v>96.19173431396484</v>
+        <v>96.19171905517578</v>
       </c>
       <c r="D333" t="n">
-        <v>96.20128516744374</v>
+        <v>96.20126990713963</v>
       </c>
       <c r="E333" t="n">
-        <v>96.19173431396484</v>
+        <v>96.19171905517578</v>
       </c>
       <c r="F333" t="n">
-        <v>96.19173431396484</v>
+        <v>96.19171905517578</v>
       </c>
       <c r="G333" t="n">
         <v>8555000</v>
@@ -8108,16 +8108,16 @@
         <v>45777</v>
       </c>
       <c r="C334" t="n">
-        <v>96.22039794921875</v>
+        <v>96.22040557861328</v>
       </c>
       <c r="D334" t="n">
-        <v>96.22039794921875</v>
+        <v>96.22040557861328</v>
       </c>
       <c r="E334" t="n">
-        <v>96.20128166150194</v>
+        <v>96.20128928938072</v>
       </c>
       <c r="F334" t="n">
-        <v>96.20128166150194</v>
+        <v>96.20128928938072</v>
       </c>
       <c r="G334" t="n">
         <v>16040200</v>
@@ -8131,16 +8131,16 @@
         <v>45778</v>
       </c>
       <c r="C335" t="n">
-        <v>96.23477935791016</v>
+        <v>96.23479461669922</v>
       </c>
       <c r="D335" t="n">
-        <v>96.23477935791016</v>
+        <v>96.23479461669922</v>
       </c>
       <c r="E335" t="n">
-        <v>96.22518930762713</v>
+        <v>96.22520456489561</v>
       </c>
       <c r="F335" t="n">
-        <v>96.23477935791016</v>
+        <v>96.23479461669922</v>
       </c>
       <c r="G335" t="n">
         <v>21288700</v>
@@ -8154,16 +8154,16 @@
         <v>45779</v>
       </c>
       <c r="C336" t="n">
-        <v>96.26355743408203</v>
+        <v>96.26354217529297</v>
       </c>
       <c r="D336" t="n">
-        <v>96.26355743408203</v>
+        <v>96.26354217529297</v>
       </c>
       <c r="E336" t="n">
-        <v>96.25396738228072</v>
+        <v>96.25395212501178</v>
       </c>
       <c r="F336" t="n">
-        <v>96.25396738228072</v>
+        <v>96.25395212501178</v>
       </c>
       <c r="G336" t="n">
         <v>13930900</v>
@@ -8177,16 +8177,16 @@
         <v>45782</v>
       </c>
       <c r="C337" t="n">
-        <v>96.27313232421875</v>
+        <v>96.27313995361328</v>
       </c>
       <c r="D337" t="n">
-        <v>96.27313232421875</v>
+        <v>96.27313995361328</v>
       </c>
       <c r="E337" t="n">
-        <v>96.26354227392774</v>
+        <v>96.26354990256227</v>
       </c>
       <c r="F337" t="n">
-        <v>96.27313232421875</v>
+        <v>96.27313995361328</v>
       </c>
       <c r="G337" t="n">
         <v>13223700</v>
@@ -8200,16 +8200,16 @@
         <v>45783</v>
       </c>
       <c r="C338" t="n">
-        <v>96.27313232421875</v>
+        <v>96.27313995361328</v>
       </c>
       <c r="D338" t="n">
-        <v>96.28271505944471</v>
+        <v>96.28272268959864</v>
       </c>
       <c r="E338" t="n">
-        <v>96.27313232421875</v>
+        <v>96.27313995361328</v>
       </c>
       <c r="F338" t="n">
-        <v>96.28271505944471</v>
+        <v>96.28272268959864</v>
       </c>
       <c r="G338" t="n">
         <v>8986000</v>
@@ -8223,16 +8223,16 @@
         <v>45784</v>
       </c>
       <c r="C339" t="n">
-        <v>96.28273010253906</v>
+        <v>96.28270721435547</v>
       </c>
       <c r="D339" t="n">
-        <v>96.29232015432841</v>
+        <v>96.29229726386509</v>
       </c>
       <c r="E339" t="n">
-        <v>96.28273010253906</v>
+        <v>96.28270721435547</v>
       </c>
       <c r="F339" t="n">
-        <v>96.29232015432841</v>
+        <v>96.29229726386509</v>
       </c>
       <c r="G339" t="n">
         <v>8509300</v>
@@ -8246,16 +8246,16 @@
         <v>45785</v>
       </c>
       <c r="C340" t="n">
-        <v>96.31148529052734</v>
+        <v>96.31147766113281</v>
       </c>
       <c r="D340" t="n">
-        <v>96.31148529052734</v>
+        <v>96.31147766113281</v>
       </c>
       <c r="E340" t="n">
-        <v>96.29231250353818</v>
+        <v>96.29230487566245</v>
       </c>
       <c r="F340" t="n">
-        <v>96.30190255456557</v>
+        <v>96.30189492593016</v>
       </c>
       <c r="G340" t="n">
         <v>11931100</v>
@@ -8269,16 +8269,16 @@
         <v>45786</v>
       </c>
       <c r="C341" t="n">
-        <v>96.34026336669922</v>
+        <v>96.34024810791016</v>
       </c>
       <c r="D341" t="n">
-        <v>96.34026336669922</v>
+        <v>96.34024810791016</v>
       </c>
       <c r="E341" t="n">
-        <v>96.33067331488314</v>
+        <v>96.33065805761299</v>
       </c>
       <c r="F341" t="n">
-        <v>96.33067331488314</v>
+        <v>96.33065805761299</v>
       </c>
       <c r="G341" t="n">
         <v>11793700</v>
@@ -8292,16 +8292,16 @@
         <v>45789</v>
       </c>
       <c r="C342" t="n">
-        <v>96.34026336669922</v>
+        <v>96.34024810791016</v>
       </c>
       <c r="D342" t="n">
-        <v>96.34984610344908</v>
+        <v>96.34983084314226</v>
       </c>
       <c r="E342" t="n">
-        <v>96.34026336669922</v>
+        <v>96.34024810791016</v>
       </c>
       <c r="F342" t="n">
-        <v>96.34026336669922</v>
+        <v>96.34024810791016</v>
       </c>
       <c r="G342" t="n">
         <v>16808300</v>
@@ -8315,16 +8315,16 @@
         <v>45790</v>
       </c>
       <c r="C343" t="n">
-        <v>96.35942840576172</v>
+        <v>96.35942077636719</v>
       </c>
       <c r="D343" t="n">
-        <v>96.35942840576172</v>
+        <v>96.35942077636719</v>
       </c>
       <c r="E343" t="n">
-        <v>96.34983835471689</v>
+        <v>96.34983072608168</v>
       </c>
       <c r="F343" t="n">
-        <v>96.34983835471689</v>
+        <v>96.34983072608168</v>
       </c>
       <c r="G343" t="n">
         <v>18174400</v>
@@ -8338,16 +8338,16 @@
         <v>45791</v>
       </c>
       <c r="C344" t="n">
-        <v>96.36900329589844</v>
+        <v>96.36902618408203</v>
       </c>
       <c r="D344" t="n">
-        <v>96.36900329589844</v>
+        <v>96.36902618408203</v>
       </c>
       <c r="E344" t="n">
-        <v>96.35941324636234</v>
+        <v>96.35943613226824</v>
       </c>
       <c r="F344" t="n">
-        <v>96.35941324636234</v>
+        <v>96.35943613226824</v>
       </c>
       <c r="G344" t="n">
         <v>9821100</v>
@@ -8361,16 +8361,16 @@
         <v>45792</v>
       </c>
       <c r="C345" t="n">
-        <v>96.36900329589844</v>
+        <v>96.36902618408203</v>
       </c>
       <c r="D345" t="n">
-        <v>96.37858603037006</v>
+        <v>96.37860892082961</v>
       </c>
       <c r="E345" t="n">
-        <v>96.36900329589844</v>
+        <v>96.36902618408203</v>
       </c>
       <c r="F345" t="n">
-        <v>96.37858603037006</v>
+        <v>96.37860892082961</v>
       </c>
       <c r="G345" t="n">
         <v>10057600</v>
@@ -8407,16 +8407,16 @@
         <v>45796</v>
       </c>
       <c r="C347" t="n">
-        <v>96.41694641113281</v>
+        <v>96.41693878173828</v>
       </c>
       <c r="D347" t="n">
-        <v>96.42653646141467</v>
+        <v>96.42652883126128</v>
       </c>
       <c r="E347" t="n">
-        <v>96.41694641113281</v>
+        <v>96.41693878173828</v>
       </c>
       <c r="F347" t="n">
-        <v>96.42653646141467</v>
+        <v>96.42652883126128</v>
       </c>
       <c r="G347" t="n">
         <v>15759100</v>
@@ -8430,16 +8430,16 @@
         <v>45797</v>
       </c>
       <c r="C348" t="n">
-        <v>96.43612670898438</v>
+        <v>96.43611907958984</v>
       </c>
       <c r="D348" t="n">
-        <v>96.43612670898438</v>
+        <v>96.43611907958984</v>
       </c>
       <c r="E348" t="n">
-        <v>96.42653665868291</v>
+        <v>96.42652903004708</v>
       </c>
       <c r="F348" t="n">
-        <v>96.43612670898438</v>
+        <v>96.43611907958984</v>
       </c>
       <c r="G348" t="n">
         <v>9249100</v>
@@ -8453,16 +8453,16 @@
         <v>45798</v>
       </c>
       <c r="C349" t="n">
-        <v>96.44570922851562</v>
+        <v>96.44571685791016</v>
       </c>
       <c r="D349" t="n">
-        <v>96.44570922851562</v>
+        <v>96.44571685791016</v>
       </c>
       <c r="E349" t="n">
-        <v>96.43612649330065</v>
+        <v>96.43613412193713</v>
       </c>
       <c r="F349" t="n">
-        <v>96.44570922851562</v>
+        <v>96.44571685791016</v>
       </c>
       <c r="G349" t="n">
         <v>11325900</v>
@@ -8476,16 +8476,16 @@
         <v>45799</v>
       </c>
       <c r="C350" t="n">
-        <v>96.46488952636719</v>
+        <v>96.46489715576172</v>
       </c>
       <c r="D350" t="n">
-        <v>96.46488952636719</v>
+        <v>96.46489715576172</v>
       </c>
       <c r="E350" t="n">
-        <v>96.45529947606755</v>
+        <v>96.45530710470361</v>
       </c>
       <c r="F350" t="n">
-        <v>96.45529947606755</v>
+        <v>96.45530710470361</v>
       </c>
       <c r="G350" t="n">
         <v>8901700</v>
@@ -8499,16 +8499,16 @@
         <v>45800</v>
       </c>
       <c r="C351" t="n">
-        <v>96.49365997314453</v>
+        <v>96.49364471435547</v>
       </c>
       <c r="D351" t="n">
-        <v>96.50325002420058</v>
+        <v>96.50323476389502</v>
       </c>
       <c r="E351" t="n">
-        <v>96.49365997314453</v>
+        <v>96.49364471435547</v>
       </c>
       <c r="F351" t="n">
-        <v>96.50325002420058</v>
+        <v>96.50323476389502</v>
       </c>
       <c r="G351" t="n">
         <v>9119400</v>
@@ -8545,16 +8545,16 @@
         <v>45805</v>
       </c>
       <c r="C353" t="n">
-        <v>96.53200531005859</v>
+        <v>96.53202056884766</v>
       </c>
       <c r="D353" t="n">
-        <v>96.53200531005859</v>
+        <v>96.53202056884766</v>
       </c>
       <c r="E353" t="n">
-        <v>96.52241525975282</v>
+        <v>96.522430517026</v>
       </c>
       <c r="F353" t="n">
-        <v>96.52721394243824</v>
+        <v>96.52722920046995</v>
       </c>
       <c r="G353" t="n">
         <v>8415200</v>
@@ -8568,16 +8568,16 @@
         <v>45806</v>
       </c>
       <c r="C354" t="n">
-        <v>96.53200531005859</v>
+        <v>96.53202056884766</v>
       </c>
       <c r="D354" t="n">
-        <v>96.54159536036435</v>
+        <v>96.54161062066933</v>
       </c>
       <c r="E354" t="n">
-        <v>96.52241525975282</v>
+        <v>96.522430517026</v>
       </c>
       <c r="F354" t="n">
-        <v>96.53200531005859</v>
+        <v>96.53202056884766</v>
       </c>
       <c r="G354" t="n">
         <v>10387000</v>
@@ -8591,16 +8591,16 @@
         <v>45807</v>
       </c>
       <c r="C355" t="n">
-        <v>96.56077575683594</v>
+        <v>96.56076812744141</v>
       </c>
       <c r="D355" t="n">
-        <v>96.57036580789759</v>
+        <v>96.57035817774533</v>
       </c>
       <c r="E355" t="n">
-        <v>96.56077575683594</v>
+        <v>96.56076812744141</v>
       </c>
       <c r="F355" t="n">
-        <v>96.56077575683594</v>
+        <v>96.56076812744141</v>
       </c>
       <c r="G355" t="n">
         <v>14209500</v>
@@ -8637,16 +8637,16 @@
         <v>45811</v>
       </c>
       <c r="C357" t="n">
-        <v>96.59735107421875</v>
+        <v>96.59733581542969</v>
       </c>
       <c r="D357" t="n">
-        <v>96.59735107421875</v>
+        <v>96.59733581542969</v>
       </c>
       <c r="E357" t="n">
-        <v>96.58772681014045</v>
+        <v>96.58771155287167</v>
       </c>
       <c r="F357" t="n">
-        <v>96.59254261276087</v>
+        <v>96.59252735473136</v>
       </c>
       <c r="G357" t="n">
         <v>11979500</v>
@@ -8660,16 +8660,16 @@
         <v>45812</v>
       </c>
       <c r="C358" t="n">
-        <v>96.60696411132812</v>
+        <v>96.60695648193359</v>
       </c>
       <c r="D358" t="n">
-        <v>96.60696411132812</v>
+        <v>96.60695648193359</v>
       </c>
       <c r="E358" t="n">
-        <v>96.59733984836828</v>
+        <v>96.59733221973381</v>
       </c>
       <c r="F358" t="n">
-        <v>96.60214830926736</v>
+        <v>96.60214068025316</v>
       </c>
       <c r="G358" t="n">
         <v>8923800</v>
@@ -8683,16 +8683,16 @@
         <v>45813</v>
       </c>
       <c r="C359" t="n">
-        <v>96.61658477783203</v>
+        <v>96.61659240722656</v>
       </c>
       <c r="D359" t="n">
-        <v>96.61658477783203</v>
+        <v>96.61659240722656</v>
       </c>
       <c r="E359" t="n">
-        <v>96.60696051523044</v>
+        <v>96.60696814386499</v>
       </c>
       <c r="F359" t="n">
-        <v>96.61658477783203</v>
+        <v>96.61659240722656</v>
       </c>
       <c r="G359" t="n">
         <v>9915800</v>
@@ -8706,16 +8706,16 @@
         <v>45814</v>
       </c>
       <c r="C360" t="n">
-        <v>96.64546203613281</v>
+        <v>96.64544677734375</v>
       </c>
       <c r="D360" t="n">
-        <v>96.65507895874835</v>
+        <v>96.65506369844093</v>
       </c>
       <c r="E360" t="n">
-        <v>96.64546203613281</v>
+        <v>96.64544677734375</v>
       </c>
       <c r="F360" t="n">
-        <v>96.65027049744057</v>
+        <v>96.65025523789234</v>
       </c>
       <c r="G360" t="n">
         <v>9122400</v>
@@ -8729,16 +8729,16 @@
         <v>45817</v>
       </c>
       <c r="C361" t="n">
-        <v>96.65505981445312</v>
+        <v>96.65506744384766</v>
       </c>
       <c r="D361" t="n">
-        <v>96.66468407632469</v>
+        <v>96.66469170647891</v>
       </c>
       <c r="E361" t="n">
-        <v>96.65505981445312</v>
+        <v>96.65506744384766</v>
       </c>
       <c r="F361" t="n">
-        <v>96.65505981445312</v>
+        <v>96.65506744384766</v>
       </c>
       <c r="G361" t="n">
         <v>9902100</v>
@@ -8775,16 +8775,16 @@
         <v>45819</v>
       </c>
       <c r="C363" t="n">
-        <v>96.68393707275391</v>
+        <v>96.68394470214844</v>
       </c>
       <c r="D363" t="n">
-        <v>96.68393707275391</v>
+        <v>96.68394470214844</v>
       </c>
       <c r="E363" t="n">
-        <v>96.6743128104371</v>
+        <v>96.67432043907218</v>
       </c>
       <c r="F363" t="n">
-        <v>96.67912127101491</v>
+        <v>96.67912890002943</v>
       </c>
       <c r="G363" t="n">
         <v>10138800</v>
@@ -8798,16 +8798,16 @@
         <v>45820</v>
       </c>
       <c r="C364" t="n">
-        <v>96.69355773925781</v>
+        <v>96.69355010986328</v>
       </c>
       <c r="D364" t="n">
-        <v>96.69355773925781</v>
+        <v>96.69355010986328</v>
       </c>
       <c r="E364" t="n">
-        <v>96.68394081772971</v>
+        <v>96.68393318909396</v>
       </c>
       <c r="F364" t="n">
-        <v>96.69355773925781</v>
+        <v>96.69355010986328</v>
       </c>
       <c r="G364" t="n">
         <v>9574900</v>
@@ -8821,16 +8821,16 @@
         <v>45821</v>
       </c>
       <c r="C365" t="n">
-        <v>96.7320556640625</v>
+        <v>96.73204040527344</v>
       </c>
       <c r="D365" t="n">
-        <v>96.7320556640625</v>
+        <v>96.73204040527344</v>
       </c>
       <c r="E365" t="n">
-        <v>96.72243140055555</v>
+        <v>96.72241614328465</v>
       </c>
       <c r="F365" t="n">
-        <v>96.72243140055555</v>
+        <v>96.72241614328465</v>
       </c>
       <c r="G365" t="n">
         <v>7880300</v>
@@ -8844,16 +8844,16 @@
         <v>45824</v>
       </c>
       <c r="C366" t="n">
-        <v>96.7320556640625</v>
+        <v>96.73204040527344</v>
       </c>
       <c r="D366" t="n">
-        <v>96.74167992756945</v>
+        <v>96.74166466726223</v>
       </c>
       <c r="E366" t="n">
-        <v>96.7320556640625</v>
+        <v>96.73204040527344</v>
       </c>
       <c r="F366" t="n">
-        <v>96.74167992756945</v>
+        <v>96.74166466726223</v>
       </c>
       <c r="G366" t="n">
         <v>10286500</v>
@@ -8867,16 +8867,16 @@
         <v>45825</v>
       </c>
       <c r="C367" t="n">
-        <v>96.74167633056641</v>
+        <v>96.74168395996094</v>
       </c>
       <c r="D367" t="n">
-        <v>96.75130059371551</v>
+        <v>96.75130822386905</v>
       </c>
       <c r="E367" t="n">
-        <v>96.74167633056641</v>
+        <v>96.74168395996094</v>
       </c>
       <c r="F367" t="n">
-        <v>96.75130059371551</v>
+        <v>96.75130822386905</v>
       </c>
       <c r="G367" t="n">
         <v>8734500</v>
@@ -8890,16 +8890,16 @@
         <v>45826</v>
       </c>
       <c r="C368" t="n">
-        <v>96.76091003417969</v>
+        <v>96.76091766357422</v>
       </c>
       <c r="D368" t="n">
-        <v>96.77053429658464</v>
+        <v>96.77054192673803</v>
       </c>
       <c r="E368" t="n">
-        <v>96.76091003417969</v>
+        <v>96.76091766357422</v>
       </c>
       <c r="F368" t="n">
-        <v>96.77053429658464</v>
+        <v>96.77054192673803</v>
       </c>
       <c r="G368" t="n">
         <v>9783400</v>
@@ -8936,16 +8936,16 @@
         <v>45831</v>
       </c>
       <c r="C370" t="n">
-        <v>96.81863403320312</v>
+        <v>96.81864166259766</v>
       </c>
       <c r="D370" t="n">
-        <v>96.81863403320312</v>
+        <v>96.81864166259766</v>
       </c>
       <c r="E370" t="n">
-        <v>96.80900977221312</v>
+        <v>96.80901740084924</v>
       </c>
       <c r="F370" t="n">
-        <v>96.81381823212803</v>
+        <v>96.81382586114307</v>
       </c>
       <c r="G370" t="n">
         <v>8847300</v>
@@ -8982,16 +8982,16 @@
         <v>45833</v>
       </c>
       <c r="C372" t="n">
-        <v>96.837890625</v>
+        <v>96.83787536621094</v>
       </c>
       <c r="D372" t="n">
-        <v>96.84751488752164</v>
+        <v>96.84749962721607</v>
       </c>
       <c r="E372" t="n">
-        <v>96.837890625</v>
+        <v>96.83787536621094</v>
       </c>
       <c r="F372" t="n">
-        <v>96.84269908568015</v>
+        <v>96.84268382613341</v>
       </c>
       <c r="G372" t="n">
         <v>8015100</v>
@@ -9028,16 +9028,16 @@
         <v>45835</v>
       </c>
       <c r="C374" t="n">
-        <v>96.88601684570312</v>
+        <v>96.88602447509766</v>
       </c>
       <c r="D374" t="n">
-        <v>96.88601684570312</v>
+        <v>96.88602447509766</v>
       </c>
       <c r="E374" t="n">
-        <v>96.87639258196469</v>
+        <v>96.87640021060137</v>
       </c>
       <c r="F374" t="n">
-        <v>96.88120104325277</v>
+        <v>96.88120867226809</v>
       </c>
       <c r="G374" t="n">
         <v>9742300</v>
@@ -9051,16 +9051,16 @@
         <v>45838</v>
       </c>
       <c r="C375" t="n">
-        <v>96.88601684570312</v>
+        <v>96.88602447509766</v>
       </c>
       <c r="D375" t="n">
-        <v>96.89563376827927</v>
+        <v>96.89564139843111</v>
       </c>
       <c r="E375" t="n">
-        <v>96.88601684570312</v>
+        <v>96.88602447509766</v>
       </c>
       <c r="F375" t="n">
-        <v>96.88601684570312</v>
+        <v>96.88602447509766</v>
       </c>
       <c r="G375" t="n">
         <v>18195600</v>
@@ -9074,16 +9074,16 @@
         <v>45839</v>
       </c>
       <c r="C376" t="n">
-        <v>96.91207885742188</v>
+        <v>96.91207122802734</v>
       </c>
       <c r="D376" t="n">
-        <v>96.91207885742188</v>
+        <v>96.91207122802734</v>
       </c>
       <c r="E376" t="n">
-        <v>96.90242131245242</v>
+        <v>96.90241368381817</v>
       </c>
       <c r="F376" t="n">
-        <v>96.91207885742188</v>
+        <v>96.91207122802734</v>
       </c>
       <c r="G376" t="n">
         <v>24173900</v>
@@ -9097,16 +9097,16 @@
         <v>45840</v>
       </c>
       <c r="C377" t="n">
-        <v>96.91207885742188</v>
+        <v>96.91207122802734</v>
       </c>
       <c r="D377" t="n">
-        <v>96.92172903584292</v>
+        <v>96.92172140568869</v>
       </c>
       <c r="E377" t="n">
-        <v>96.91207885742188</v>
+        <v>96.91207122802734</v>
       </c>
       <c r="F377" t="n">
-        <v>96.92172903584292</v>
+        <v>96.92172140568869</v>
       </c>
       <c r="G377" t="n">
         <v>10850800</v>
@@ -9120,16 +9120,16 @@
         <v>45841</v>
       </c>
       <c r="C378" t="n">
-        <v>96.96035766601562</v>
+        <v>96.96035003662109</v>
       </c>
       <c r="D378" t="n">
-        <v>96.97001521156446</v>
+        <v>96.97000758141002</v>
       </c>
       <c r="E378" t="n">
-        <v>96.96035766601562</v>
+        <v>96.96035003662109</v>
       </c>
       <c r="F378" t="n">
-        <v>96.96035766601562</v>
+        <v>96.96035003662109</v>
       </c>
       <c r="G378" t="n">
         <v>7404700</v>
@@ -9143,16 +9143,16 @@
         <v>45845</v>
       </c>
       <c r="C379" t="n">
-        <v>96.97966766357422</v>
+        <v>96.97966003417969</v>
       </c>
       <c r="D379" t="n">
-        <v>96.97966766357422</v>
+        <v>96.97966003417969</v>
       </c>
       <c r="E379" t="n">
-        <v>96.97001011853261</v>
+        <v>96.97000248989785</v>
       </c>
       <c r="F379" t="n">
-        <v>96.97966766357422</v>
+        <v>96.97966003417969</v>
       </c>
       <c r="G379" t="n">
         <v>12363900</v>
@@ -9212,16 +9212,16 @@
         <v>45848</v>
       </c>
       <c r="C382" t="n">
-        <v>97.00862121582031</v>
+        <v>97.00862884521484</v>
       </c>
       <c r="D382" t="n">
-        <v>97.01827875969551</v>
+        <v>97.01828638984958</v>
       </c>
       <c r="E382" t="n">
-        <v>96.99896367194511</v>
+        <v>96.99897130058011</v>
       </c>
       <c r="F382" t="n">
-        <v>97.00862121582031</v>
+        <v>97.00862884521484</v>
       </c>
       <c r="G382" t="n">
         <v>10071700</v>
@@ -9235,16 +9235,16 @@
         <v>45849</v>
       </c>
       <c r="C383" t="n">
-        <v>97.04724884033203</v>
+        <v>97.0472412109375</v>
       </c>
       <c r="D383" t="n">
-        <v>97.04724884033203</v>
+        <v>97.0472412109375</v>
       </c>
       <c r="E383" t="n">
-        <v>97.03759129597762</v>
+        <v>97.03758366734232</v>
       </c>
       <c r="F383" t="n">
-        <v>97.03759129597762</v>
+        <v>97.03758366734232</v>
       </c>
       <c r="G383" t="n">
         <v>9288900</v>
@@ -9258,16 +9258,16 @@
         <v>45852</v>
       </c>
       <c r="C384" t="n">
-        <v>97.04724884033203</v>
+        <v>97.0472412109375</v>
       </c>
       <c r="D384" t="n">
-        <v>97.05689901813851</v>
+        <v>97.05689138798532</v>
       </c>
       <c r="E384" t="n">
-        <v>97.04724884033203</v>
+        <v>97.0472412109375</v>
       </c>
       <c r="F384" t="n">
-        <v>97.05689901813851</v>
+        <v>97.05689138798532</v>
       </c>
       <c r="G384" t="n">
         <v>10293900</v>
@@ -9281,16 +9281,16 @@
         <v>45853</v>
       </c>
       <c r="C385" t="n">
-        <v>97.05690002441406</v>
+        <v>97.05690765380859</v>
       </c>
       <c r="D385" t="n">
-        <v>97.06655756886862</v>
+        <v>97.06656519902229</v>
       </c>
       <c r="E385" t="n">
-        <v>97.05690002441406</v>
+        <v>97.05690765380859</v>
       </c>
       <c r="F385" t="n">
-        <v>97.06655756886862</v>
+        <v>97.06656519902229</v>
       </c>
       <c r="G385" t="n">
         <v>10207100</v>
@@ -9304,16 +9304,16 @@
         <v>45854</v>
       </c>
       <c r="C386" t="n">
-        <v>97.08586883544922</v>
+        <v>97.08587646484375</v>
       </c>
       <c r="D386" t="n">
-        <v>97.08586883544922</v>
+        <v>97.08587646484375</v>
       </c>
       <c r="E386" t="n">
-        <v>97.07621129137489</v>
+        <v>97.07621892001049</v>
       </c>
       <c r="F386" t="n">
-        <v>97.07621129137489</v>
+        <v>97.07621892001049</v>
       </c>
       <c r="G386" t="n">
         <v>8117900</v>
@@ -9327,16 +9327,16 @@
         <v>45855</v>
       </c>
       <c r="C387" t="n">
-        <v>97.09552764892578</v>
+        <v>97.09552001953125</v>
       </c>
       <c r="D387" t="n">
-        <v>97.09552764892578</v>
+        <v>97.09552001953125</v>
       </c>
       <c r="E387" t="n">
-        <v>97.08587747054088</v>
+        <v>97.08586984190462</v>
       </c>
       <c r="F387" t="n">
-        <v>97.09070255973333</v>
+        <v>97.09069493071793</v>
       </c>
       <c r="G387" t="n">
         <v>9040400</v>
@@ -9350,16 +9350,16 @@
         <v>45856</v>
       </c>
       <c r="C388" t="n">
-        <v>97.12448120117188</v>
+        <v>97.12449645996094</v>
       </c>
       <c r="D388" t="n">
-        <v>97.12448120117188</v>
+        <v>97.12449645996094</v>
       </c>
       <c r="E388" t="n">
-        <v>97.11483102395106</v>
+        <v>97.11484628122402</v>
       </c>
       <c r="F388" t="n">
-        <v>97.11483102395106</v>
+        <v>97.11484628122402</v>
       </c>
       <c r="G388" t="n">
         <v>9399500</v>
@@ -9373,16 +9373,16 @@
         <v>45859</v>
       </c>
       <c r="C389" t="n">
-        <v>97.13414764404297</v>
+        <v>97.13414001464844</v>
       </c>
       <c r="D389" t="n">
-        <v>97.13414764404297</v>
+        <v>97.13414001464844</v>
       </c>
       <c r="E389" t="n">
-        <v>97.12449009938986</v>
+        <v>97.12448247075388</v>
       </c>
       <c r="F389" t="n">
-        <v>97.12449009938986</v>
+        <v>97.12448247075388</v>
       </c>
       <c r="G389" t="n">
         <v>12893000</v>
@@ -9396,16 +9396,16 @@
         <v>45860</v>
       </c>
       <c r="C390" t="n">
-        <v>97.1534423828125</v>
+        <v>97.15345764160156</v>
       </c>
       <c r="D390" t="n">
-        <v>97.1534423828125</v>
+        <v>97.15345764160156</v>
       </c>
       <c r="E390" t="n">
-        <v>97.14378484018235</v>
+        <v>97.1438000974546</v>
       </c>
       <c r="F390" t="n">
-        <v>97.1534423828125</v>
+        <v>97.15345764160156</v>
       </c>
       <c r="G390" t="n">
         <v>9340600</v>
@@ -9419,16 +9419,16 @@
         <v>45861</v>
       </c>
       <c r="C391" t="n">
-        <v>97.16311645507812</v>
+        <v>97.16312408447266</v>
       </c>
       <c r="D391" t="n">
-        <v>97.16311645507812</v>
+        <v>97.16312408447266</v>
       </c>
       <c r="E391" t="n">
-        <v>97.15346627662124</v>
+        <v>97.15347390525802</v>
       </c>
       <c r="F391" t="n">
-        <v>97.16311645507812</v>
+        <v>97.16312408447266</v>
       </c>
       <c r="G391" t="n">
         <v>8056100</v>
@@ -9465,16 +9465,16 @@
         <v>45863</v>
       </c>
       <c r="C393" t="n">
-        <v>97.19207763671875</v>
+        <v>97.19207000732422</v>
       </c>
       <c r="D393" t="n">
-        <v>97.20172781403843</v>
+        <v>97.20172018388638</v>
       </c>
       <c r="E393" t="n">
-        <v>97.19207763671875</v>
+        <v>97.19207000732422</v>
       </c>
       <c r="F393" t="n">
-        <v>97.20172781403843</v>
+        <v>97.20172018388638</v>
       </c>
       <c r="G393" t="n">
         <v>9776600</v>
@@ -9534,16 +9534,16 @@
         <v>45868</v>
       </c>
       <c r="C396" t="n">
-        <v>97.2403564453125</v>
+        <v>97.24036407470703</v>
       </c>
       <c r="D396" t="n">
-        <v>97.2403564453125</v>
+        <v>97.24036407470703</v>
       </c>
       <c r="E396" t="n">
-        <v>97.230698900867</v>
+        <v>97.23070652950381</v>
       </c>
       <c r="F396" t="n">
-        <v>97.230698900867</v>
+        <v>97.23070652950381</v>
       </c>
       <c r="G396" t="n">
         <v>9106000</v>
@@ -9557,16 +9557,16 @@
         <v>45869</v>
       </c>
       <c r="C397" t="n">
-        <v>97.25002288818359</v>
+        <v>97.25000762939453</v>
       </c>
       <c r="D397" t="n">
-        <v>97.25002288818359</v>
+        <v>97.25000762939453</v>
       </c>
       <c r="E397" t="n">
-        <v>97.24036534285442</v>
+        <v>97.24035008558064</v>
       </c>
       <c r="F397" t="n">
-        <v>97.24519043224467</v>
+        <v>97.24517517421383</v>
       </c>
       <c r="G397" t="n">
         <v>19051200</v>
@@ -9695,16 +9695,16 @@
         <v>45877</v>
       </c>
       <c r="C403" t="n">
-        <v>97.36822509765625</v>
+        <v>97.36824035644531</v>
       </c>
       <c r="D403" t="n">
-        <v>97.36822509765625</v>
+        <v>97.36824035644531</v>
       </c>
       <c r="E403" t="n">
-        <v>97.35853271888028</v>
+        <v>97.35854797615043</v>
       </c>
       <c r="F403" t="n">
-        <v>97.36337521170886</v>
+        <v>97.36339046973788</v>
       </c>
       <c r="G403" t="n">
         <v>12066300</v>
@@ -9764,16 +9764,16 @@
         <v>45882</v>
       </c>
       <c r="C406" t="n">
-        <v>97.39730834960938</v>
+        <v>97.39730072021484</v>
       </c>
       <c r="D406" t="n">
-        <v>97.4069933366098</v>
+        <v>97.40698570645661</v>
       </c>
       <c r="E406" t="n">
-        <v>97.3876159694891</v>
+        <v>97.3876083408538</v>
       </c>
       <c r="F406" t="n">
-        <v>97.39730834960938</v>
+        <v>97.39730072021484</v>
       </c>
       <c r="G406" t="n">
         <v>12144800</v>
@@ -9787,16 +9787,16 @@
         <v>45883</v>
       </c>
       <c r="C407" t="n">
-        <v>97.40699005126953</v>
+        <v>97.40699768066406</v>
       </c>
       <c r="D407" t="n">
-        <v>97.4166824310629</v>
+        <v>97.41669006121658</v>
       </c>
       <c r="E407" t="n">
-        <v>97.40699005126953</v>
+        <v>97.40699768066406</v>
       </c>
       <c r="F407" t="n">
-        <v>97.40699005126953</v>
+        <v>97.40699768066406</v>
       </c>
       <c r="G407" t="n">
         <v>9798900</v>
@@ -9810,16 +9810,16 @@
         <v>45884</v>
       </c>
       <c r="C408" t="n">
-        <v>97.43605804443359</v>
+        <v>97.43606567382812</v>
       </c>
       <c r="D408" t="n">
-        <v>97.44574303019824</v>
+        <v>97.44575066035112</v>
       </c>
       <c r="E408" t="n">
-        <v>97.43605804443359</v>
+        <v>97.43606567382812</v>
       </c>
       <c r="F408" t="n">
-        <v>97.44574303019824</v>
+        <v>97.44575066035112</v>
       </c>
       <c r="G408" t="n">
         <v>9493900</v>
@@ -9833,16 +9833,16 @@
         <v>45887</v>
       </c>
       <c r="C409" t="n">
-        <v>97.46514129638672</v>
+        <v>97.46514892578125</v>
       </c>
       <c r="D409" t="n">
-        <v>97.46514129638672</v>
+        <v>97.46514892578125</v>
       </c>
       <c r="E409" t="n">
-        <v>97.44575653593293</v>
+        <v>97.44576416381005</v>
       </c>
       <c r="F409" t="n">
-        <v>97.45544891615982</v>
+        <v>97.45545654479565</v>
       </c>
       <c r="G409" t="n">
         <v>14768500</v>
@@ -9856,16 +9856,16 @@
         <v>45888</v>
       </c>
       <c r="C410" t="n">
-        <v>97.46514129638672</v>
+        <v>97.46514892578125</v>
       </c>
       <c r="D410" t="n">
-        <v>97.47482628349368</v>
+        <v>97.47483391364634</v>
       </c>
       <c r="E410" t="n">
-        <v>97.46514129638672</v>
+        <v>97.46514892578125</v>
       </c>
       <c r="F410" t="n">
-        <v>97.47482628349368</v>
+        <v>97.47483391364634</v>
       </c>
       <c r="G410" t="n">
         <v>10474900</v>
@@ -9948,16 +9948,16 @@
         <v>45894</v>
       </c>
       <c r="C414" t="n">
-        <v>97.54266357421875</v>
+        <v>97.54264831542969</v>
       </c>
       <c r="D414" t="n">
-        <v>97.54266357421875</v>
+        <v>97.54264831542969</v>
       </c>
       <c r="E414" t="n">
-        <v>97.53297119418838</v>
+        <v>97.53295593691551</v>
       </c>
       <c r="F414" t="n">
-        <v>97.53781368764366</v>
+        <v>97.53779842961329</v>
       </c>
       <c r="G414" t="n">
         <v>13556000</v>
@@ -9971,16 +9971,16 @@
         <v>45895</v>
       </c>
       <c r="C415" t="n">
-        <v>97.54266357421875</v>
+        <v>97.54264831542969</v>
       </c>
       <c r="D415" t="n">
-        <v>97.55234856112934</v>
+        <v>97.55233330082524</v>
       </c>
       <c r="E415" t="n">
-        <v>97.54266357421875</v>
+        <v>97.54264831542969</v>
       </c>
       <c r="F415" t="n">
-        <v>97.54750606767405</v>
+        <v>97.54749080812746</v>
       </c>
       <c r="G415" t="n">
         <v>8741600</v>
@@ -9994,16 +9994,16 @@
         <v>45896</v>
       </c>
       <c r="C416" t="n">
-        <v>97.55233764648438</v>
+        <v>97.55235290527344</v>
       </c>
       <c r="D416" t="n">
-        <v>97.56203002543032</v>
+        <v>97.56204528573542</v>
       </c>
       <c r="E416" t="n">
-        <v>97.55233764648438</v>
+        <v>97.55235290527344</v>
       </c>
       <c r="F416" t="n">
-        <v>97.56203002543032</v>
+        <v>97.56204528573542</v>
       </c>
       <c r="G416" t="n">
         <v>7384600</v>
@@ -10040,16 +10040,16 @@
         <v>45898</v>
       </c>
       <c r="C418" t="n">
-        <v>97.62017059326172</v>
+        <v>97.62017822265625</v>
       </c>
       <c r="D418" t="n">
-        <v>97.62017059326172</v>
+        <v>97.62017822265625</v>
       </c>
       <c r="E418" t="n">
-        <v>97.60079322827433</v>
+        <v>97.60080085615444</v>
       </c>
       <c r="F418" t="n">
-        <v>97.60079322827433</v>
+        <v>97.60080085615444</v>
       </c>
       <c r="G418" t="n">
         <v>21369400</v>
@@ -10063,16 +10063,16 @@
         <v>45902</v>
       </c>
       <c r="C419" t="n">
-        <v>97.62989807128906</v>
+        <v>97.62990570068359</v>
       </c>
       <c r="D419" t="n">
-        <v>97.62989807128906</v>
+        <v>97.62990570068359</v>
       </c>
       <c r="E419" t="n">
-        <v>97.62017093166746</v>
+        <v>97.62017856030185</v>
       </c>
       <c r="F419" t="n">
-        <v>97.62989807128906</v>
+        <v>97.62990570068359</v>
       </c>
       <c r="G419" t="n">
         <v>27254500</v>
@@ -10086,16 +10086,16 @@
         <v>45903</v>
       </c>
       <c r="C420" t="n">
-        <v>97.63962554931641</v>
+        <v>97.63963317871094</v>
       </c>
       <c r="D420" t="n">
-        <v>97.63962554931641</v>
+        <v>97.63963317871094</v>
       </c>
       <c r="E420" t="n">
-        <v>97.6298984096611</v>
+        <v>97.62990603829556</v>
       </c>
       <c r="F420" t="n">
-        <v>97.63475826967195</v>
+        <v>97.63476589868615</v>
       </c>
       <c r="G420" t="n">
         <v>14296000</v>
@@ -10109,16 +10109,16 @@
         <v>45904</v>
       </c>
       <c r="C421" t="n">
-        <v>97.65907287597656</v>
+        <v>97.65908050537109</v>
       </c>
       <c r="D421" t="n">
-        <v>97.65907287597656</v>
+        <v>97.65908050537109</v>
       </c>
       <c r="E421" t="n">
-        <v>97.64935315590837</v>
+        <v>97.64936078454357</v>
       </c>
       <c r="F421" t="n">
-        <v>97.65421301594246</v>
+        <v>97.65422064495733</v>
       </c>
       <c r="G421" t="n">
         <v>11300200</v>
@@ -10132,16 +10132,16 @@
         <v>45905</v>
       </c>
       <c r="C422" t="n">
-        <v>97.67852783203125</v>
+        <v>97.67853546142578</v>
       </c>
       <c r="D422" t="n">
-        <v>97.68824755216677</v>
+        <v>97.68825518232049</v>
       </c>
       <c r="E422" t="n">
-        <v>97.67852783203125</v>
+        <v>97.67853546142578</v>
       </c>
       <c r="F422" t="n">
-        <v>97.68824755216677</v>
+        <v>97.68825518232049</v>
       </c>
       <c r="G422" t="n">
         <v>15312000</v>
@@ -10201,16 +10201,16 @@
         <v>45910</v>
       </c>
       <c r="C425" t="n">
-        <v>97.71743011474609</v>
+        <v>97.71744537353516</v>
       </c>
       <c r="D425" t="n">
-        <v>97.72714983499533</v>
+        <v>97.72716509530215</v>
       </c>
       <c r="E425" t="n">
-        <v>97.71743011474609</v>
+        <v>97.71744537353516</v>
       </c>
       <c r="F425" t="n">
-        <v>97.71743011474609</v>
+        <v>97.71744537353516</v>
       </c>
       <c r="G425" t="n">
         <v>9356600</v>
@@ -10247,16 +10247,16 @@
         <v>45912</v>
       </c>
       <c r="C427" t="n">
-        <v>97.76604461669922</v>
+        <v>97.76605224609375</v>
       </c>
       <c r="D427" t="n">
-        <v>97.77577175594963</v>
+        <v>97.77577938610324</v>
       </c>
       <c r="E427" t="n">
-        <v>97.76604461669922</v>
+        <v>97.76605224609375</v>
       </c>
       <c r="F427" t="n">
-        <v>97.76604461669922</v>
+        <v>97.76605224609375</v>
       </c>
       <c r="G427" t="n">
         <v>10482000</v>
@@ -10270,16 +10270,16 @@
         <v>45915</v>
       </c>
       <c r="C428" t="n">
-        <v>97.76604461669922</v>
+        <v>97.76605224609375</v>
       </c>
       <c r="D428" t="n">
-        <v>97.77577175594963</v>
+        <v>97.77577938610324</v>
       </c>
       <c r="E428" t="n">
-        <v>97.76604461669922</v>
+        <v>97.76605224609375</v>
       </c>
       <c r="F428" t="n">
-        <v>97.76604461669922</v>
+        <v>97.76605224609375</v>
       </c>
       <c r="G428" t="n">
         <v>15288300</v>
@@ -10293,16 +10293,16 @@
         <v>45916</v>
       </c>
       <c r="C429" t="n">
-        <v>97.78549957275391</v>
+        <v>97.78550720214844</v>
       </c>
       <c r="D429" t="n">
-        <v>97.79521929243838</v>
+        <v>97.79522692259125</v>
       </c>
       <c r="E429" t="n">
-        <v>97.78549957275391</v>
+        <v>97.78550720214844</v>
       </c>
       <c r="F429" t="n">
-        <v>97.78549957275391</v>
+        <v>97.78550720214844</v>
       </c>
       <c r="G429" t="n">
         <v>11551900</v>
@@ -10316,16 +10316,16 @@
         <v>45917</v>
       </c>
       <c r="C430" t="n">
-        <v>97.79523468017578</v>
+        <v>97.79522705078125</v>
       </c>
       <c r="D430" t="n">
-        <v>97.80496182102412</v>
+        <v>97.80495419087075</v>
       </c>
       <c r="E430" t="n">
-        <v>97.79523468017578</v>
+        <v>97.79522705078125</v>
       </c>
       <c r="F430" t="n">
-        <v>97.80496182102412</v>
+        <v>97.80495419087075</v>
       </c>
       <c r="G430" t="n">
         <v>10381200</v>
@@ -10431,16 +10431,16 @@
         <v>45924</v>
       </c>
       <c r="C435" t="n">
-        <v>97.88274383544922</v>
+        <v>97.88276672363281</v>
       </c>
       <c r="D435" t="n">
-        <v>97.88274383544922</v>
+        <v>97.88276672363281</v>
       </c>
       <c r="E435" t="n">
-        <v>97.87301669661552</v>
+        <v>97.87303958252458</v>
       </c>
       <c r="F435" t="n">
-        <v>97.87787655621588</v>
+        <v>97.87789944326134</v>
       </c>
       <c r="G435" t="n">
         <v>10108500</v>
@@ -10454,16 +10454,16 @@
         <v>45925</v>
       </c>
       <c r="C436" t="n">
-        <v>97.89247894287109</v>
+        <v>97.89247131347656</v>
       </c>
       <c r="D436" t="n">
-        <v>97.89247894287109</v>
+        <v>97.89247131347656</v>
       </c>
       <c r="E436" t="n">
-        <v>97.88275180324558</v>
+        <v>97.88274417460916</v>
       </c>
       <c r="F436" t="n">
-        <v>97.88275180324558</v>
+        <v>97.88274417460916</v>
       </c>
       <c r="G436" t="n">
         <v>10549100</v>
@@ -10477,16 +10477,16 @@
         <v>45926</v>
       </c>
       <c r="C437" t="n">
-        <v>97.92165374755859</v>
+        <v>97.92166137695312</v>
       </c>
       <c r="D437" t="n">
-        <v>97.92165374755859</v>
+        <v>97.92166137695312</v>
       </c>
       <c r="E437" t="n">
-        <v>97.91192660785308</v>
+        <v>97.91193423648973</v>
       </c>
       <c r="F437" t="n">
-        <v>97.91192660785308</v>
+        <v>97.91193423648973</v>
       </c>
       <c r="G437" t="n">
         <v>10688600</v>
@@ -10500,16 +10500,16 @@
         <v>45929</v>
       </c>
       <c r="C438" t="n">
-        <v>97.93136596679688</v>
+        <v>97.93137359619141</v>
       </c>
       <c r="D438" t="n">
-        <v>97.93136596679688</v>
+        <v>97.93137359619141</v>
       </c>
       <c r="E438" t="n">
-        <v>97.92164624746947</v>
+        <v>97.92165387610677</v>
       </c>
       <c r="F438" t="n">
-        <v>97.93136596679688</v>
+        <v>97.93137359619141</v>
       </c>
       <c r="G438" t="n">
         <v>13580800</v>
@@ -10523,16 +10523,16 @@
         <v>45930</v>
       </c>
       <c r="C439" t="n">
-        <v>97.93136596679688</v>
+        <v>97.93137359619141</v>
       </c>
       <c r="D439" t="n">
-        <v>97.94109310575736</v>
+        <v>97.94110073590969</v>
       </c>
       <c r="E439" t="n">
-        <v>97.93136596679688</v>
+        <v>97.93137359619141</v>
       </c>
       <c r="F439" t="n">
-        <v>97.93623324609365</v>
+        <v>97.93624087586737</v>
       </c>
       <c r="G439" t="n">
         <v>22909500</v>
@@ -10569,16 +10569,16 @@
         <v>45932</v>
       </c>
       <c r="C441" t="n">
-        <v>97.95771026611328</v>
+        <v>97.95771789550781</v>
       </c>
       <c r="D441" t="n">
-        <v>97.96747103907319</v>
+        <v>97.96747866922793</v>
       </c>
       <c r="E441" t="n">
-        <v>97.95771026611328</v>
+        <v>97.95771789550781</v>
       </c>
       <c r="F441" t="n">
-        <v>97.96747103907319</v>
+        <v>97.96747866922793</v>
       </c>
       <c r="G441" t="n">
         <v>12870100</v>
@@ -10592,16 +10592,16 @@
         <v>45933</v>
       </c>
       <c r="C442" t="n">
-        <v>97.99674987792969</v>
+        <v>97.99676513671875</v>
       </c>
       <c r="D442" t="n">
-        <v>97.99674987792969</v>
+        <v>97.99676513671875</v>
       </c>
       <c r="E442" t="n">
-        <v>97.98699654986343</v>
+        <v>97.98701180713383</v>
       </c>
       <c r="F442" t="n">
-        <v>97.99674987792969</v>
+        <v>97.99676513671875</v>
       </c>
       <c r="G442" t="n">
         <v>13837400</v>
@@ -10615,16 +10615,16 @@
         <v>45936</v>
       </c>
       <c r="C443" t="n">
-        <v>97.99674987792969</v>
+        <v>97.99676513671875</v>
       </c>
       <c r="D443" t="n">
-        <v>98.00651065128454</v>
+        <v>98.00652591159343</v>
       </c>
       <c r="E443" t="n">
-        <v>97.99674987792969</v>
+        <v>97.99676513671875</v>
       </c>
       <c r="F443" t="n">
-        <v>98.00651065128454</v>
+        <v>98.00652591159343</v>
       </c>
       <c r="G443" t="n">
         <v>13944300</v>
@@ -10638,16 +10638,16 @@
         <v>45937</v>
       </c>
       <c r="C444" t="n">
-        <v>98.01627349853516</v>
+        <v>98.01628112792969</v>
       </c>
       <c r="D444" t="n">
-        <v>98.01627349853516</v>
+        <v>98.01628112792969</v>
       </c>
       <c r="E444" t="n">
-        <v>98.00651272497377</v>
+        <v>98.00652035360855</v>
       </c>
       <c r="F444" t="n">
-        <v>98.01627349853516</v>
+        <v>98.01628112792969</v>
       </c>
       <c r="G444" t="n">
         <v>14289100</v>
@@ -10776,16 +10776,16 @@
         <v>45945</v>
       </c>
       <c r="C450" t="n">
-        <v>98.10410308837891</v>
+        <v>98.10411834716797</v>
       </c>
       <c r="D450" t="n">
-        <v>98.10410308837891</v>
+        <v>98.10411834716797</v>
       </c>
       <c r="E450" t="n">
-        <v>98.09434231432367</v>
+        <v>98.09435757159457</v>
       </c>
       <c r="F450" t="n">
-        <v>98.10410308837891</v>
+        <v>98.10411834716797</v>
       </c>
       <c r="G450" t="n">
         <v>11069100</v>
@@ -10845,16 +10845,16 @@
         <v>45950</v>
       </c>
       <c r="C453" t="n">
-        <v>98.15291595458984</v>
+        <v>98.15290069580078</v>
       </c>
       <c r="D453" t="n">
-        <v>98.15291595458984</v>
+        <v>98.15290069580078</v>
       </c>
       <c r="E453" t="n">
-        <v>98.14315517889962</v>
+        <v>98.14313992162796</v>
       </c>
       <c r="F453" t="n">
-        <v>98.15291595458984</v>
+        <v>98.15290069580078</v>
       </c>
       <c r="G453" t="n">
         <v>16129100</v>
@@ -10868,16 +10868,16 @@
         <v>45951</v>
       </c>
       <c r="C454" t="n">
-        <v>98.17240905761719</v>
+        <v>98.17242431640625</v>
       </c>
       <c r="D454" t="n">
-        <v>98.17240905761719</v>
+        <v>98.17242431640625</v>
       </c>
       <c r="E454" t="n">
-        <v>98.16264828401518</v>
+        <v>98.16266354128715</v>
       </c>
       <c r="F454" t="n">
-        <v>98.16264828401518</v>
+        <v>98.16266354128715</v>
       </c>
       <c r="G454" t="n">
         <v>12061900</v>
@@ -10937,16 +10937,16 @@
         <v>45954</v>
       </c>
       <c r="C457" t="n">
-        <v>98.22120666503906</v>
+        <v>98.22121429443359</v>
       </c>
       <c r="D457" t="n">
-        <v>98.22120666503906</v>
+        <v>98.22121429443359</v>
       </c>
       <c r="E457" t="n">
-        <v>98.21144589131933</v>
+        <v>98.21145351995568</v>
       </c>
       <c r="F457" t="n">
-        <v>98.22120666503906</v>
+        <v>98.22121429443359</v>
       </c>
       <c r="G457" t="n">
         <v>12382000</v>
@@ -10960,16 +10960,16 @@
         <v>45957</v>
       </c>
       <c r="C458" t="n">
-        <v>98.23097229003906</v>
+        <v>98.23097991943359</v>
       </c>
       <c r="D458" t="n">
-        <v>98.2407256189516</v>
+        <v>98.24073324910366</v>
       </c>
       <c r="E458" t="n">
-        <v>98.22121151583728</v>
+        <v>98.22121914447372</v>
       </c>
       <c r="F458" t="n">
-        <v>98.22121151583728</v>
+        <v>98.22121914447372</v>
       </c>
       <c r="G458" t="n">
         <v>26389600</v>
@@ -11006,16 +11006,16 @@
         <v>45959</v>
       </c>
       <c r="C460" t="n">
-        <v>98.25048828125</v>
+        <v>98.25049591064453</v>
       </c>
       <c r="D460" t="n">
-        <v>98.26024905563935</v>
+        <v>98.26025668579183</v>
       </c>
       <c r="E460" t="n">
-        <v>98.25048828125</v>
+        <v>98.25049591064453</v>
       </c>
       <c r="F460" t="n">
-        <v>98.26024905563935</v>
+        <v>98.26025668579183</v>
       </c>
       <c r="G460" t="n">
         <v>14177700</v>
@@ -11075,16 +11075,16 @@
         <v>45964</v>
       </c>
       <c r="C463" t="n">
-        <v>98.31694793701172</v>
+        <v>98.31694030761719</v>
       </c>
       <c r="D463" t="n">
-        <v>98.31694793701172</v>
+        <v>98.31694030761719</v>
       </c>
       <c r="E463" t="n">
-        <v>98.30715332055669</v>
+        <v>98.30714569192223</v>
       </c>
       <c r="F463" t="n">
-        <v>98.31204689323255</v>
+        <v>98.31203926421834</v>
       </c>
       <c r="G463" t="n">
         <v>27049200</v>
@@ -11098,16 +11098,16 @@
         <v>45965</v>
       </c>
       <c r="C464" t="n">
-        <v>98.31694793701172</v>
+        <v>98.31694030761719</v>
       </c>
       <c r="D464" t="n">
-        <v>98.31694793701172</v>
+        <v>98.31694030761719</v>
       </c>
       <c r="E464" t="n">
-        <v>98.31204689323255</v>
+        <v>98.31203926421834</v>
       </c>
       <c r="F464" t="n">
-        <v>98.31694793701172</v>
+        <v>98.31694030761719</v>
       </c>
       <c r="G464" t="n">
         <v>15707500</v>
@@ -11121,16 +11121,16 @@
         <v>45966</v>
       </c>
       <c r="C465" t="n">
-        <v>98.33651733398438</v>
+        <v>98.33653259277344</v>
       </c>
       <c r="D465" t="n">
-        <v>98.33651733398438</v>
+        <v>98.33653259277344</v>
       </c>
       <c r="E465" t="n">
-        <v>98.32673018986331</v>
+        <v>98.3267454471337</v>
       </c>
       <c r="F465" t="n">
-        <v>98.32673018986331</v>
+        <v>98.3267454471337</v>
       </c>
       <c r="G465" t="n">
         <v>11335000</v>
@@ -11144,16 +11144,16 @@
         <v>45967</v>
       </c>
       <c r="C466" t="n">
-        <v>98.3463134765625</v>
+        <v>98.34632110595703</v>
       </c>
       <c r="D466" t="n">
-        <v>98.3463134765625</v>
+        <v>98.34632110595703</v>
       </c>
       <c r="E466" t="n">
-        <v>98.33651886118693</v>
+        <v>98.33652648982164</v>
       </c>
       <c r="F466" t="n">
-        <v>98.3463134765625</v>
+        <v>98.34632110595703</v>
       </c>
       <c r="G466" t="n">
         <v>16658100</v>
@@ -11167,16 +11167,16 @@
         <v>45968</v>
       </c>
       <c r="C467" t="n">
-        <v>98.37570190429688</v>
+        <v>98.37569427490234</v>
       </c>
       <c r="D467" t="n">
-        <v>98.37570190429688</v>
+        <v>98.37569427490234</v>
       </c>
       <c r="E467" t="n">
-        <v>98.3659072877213</v>
+        <v>98.36589965908638</v>
       </c>
       <c r="F467" t="n">
-        <v>98.37570190429688</v>
+        <v>98.37569427490234</v>
       </c>
       <c r="G467" t="n">
         <v>18799000</v>
@@ -11190,16 +11190,16 @@
         <v>45971</v>
       </c>
       <c r="C468" t="n">
-        <v>98.385498046875</v>
+        <v>98.38548278808594</v>
       </c>
       <c r="D468" t="n">
-        <v>98.39529266360249</v>
+        <v>98.39527740329436</v>
       </c>
       <c r="E468" t="n">
-        <v>98.385498046875</v>
+        <v>98.38548278808594</v>
       </c>
       <c r="F468" t="n">
-        <v>98.39529266360249</v>
+        <v>98.39527740329436</v>
       </c>
       <c r="G468" t="n">
         <v>14121900</v>
@@ -11213,16 +11213,16 @@
         <v>45972</v>
       </c>
       <c r="C469" t="n">
-        <v>98.39528656005859</v>
+        <v>98.39529418945312</v>
       </c>
       <c r="D469" t="n">
-        <v>98.39528656005859</v>
+        <v>98.39529418945312</v>
       </c>
       <c r="E469" t="n">
-        <v>98.38549194393867</v>
+        <v>98.38549957257375</v>
       </c>
       <c r="F469" t="n">
-        <v>98.39528656005859</v>
+        <v>98.39529418945312</v>
       </c>
       <c r="G469" t="n">
         <v>8697800</v>
@@ -11236,16 +11236,16 @@
         <v>45973</v>
       </c>
       <c r="C470" t="n">
-        <v>98.40505981445312</v>
+        <v>98.40507507324219</v>
       </c>
       <c r="D470" t="n">
-        <v>98.40505981445312</v>
+        <v>98.40507507324219</v>
       </c>
       <c r="E470" t="n">
-        <v>98.3952726708178</v>
+        <v>98.39528792808926</v>
       </c>
       <c r="F470" t="n">
-        <v>98.3952726708178</v>
+        <v>98.39528792808926</v>
       </c>
       <c r="G470" t="n">
         <v>9067200</v>
@@ -11259,16 +11259,16 @@
         <v>45974</v>
       </c>
       <c r="C471" t="n">
-        <v>98.41486358642578</v>
+        <v>98.41487121582031</v>
       </c>
       <c r="D471" t="n">
-        <v>98.41486358642578</v>
+        <v>98.41487121582031</v>
       </c>
       <c r="E471" t="n">
-        <v>98.40506897077708</v>
+        <v>98.4050765994123</v>
       </c>
       <c r="F471" t="n">
-        <v>98.40506897077708</v>
+        <v>98.4050765994123</v>
       </c>
       <c r="G471" t="n">
         <v>11255600</v>
@@ -11374,16 +11374,16 @@
         <v>45981</v>
       </c>
       <c r="C476" t="n">
-        <v>98.49321746826172</v>
+        <v>98.49320220947266</v>
       </c>
       <c r="D476" t="n">
-        <v>98.49321746826172</v>
+        <v>98.49320220947266</v>
       </c>
       <c r="E476" t="n">
-        <v>98.47362823459777</v>
+        <v>98.47361297884351</v>
       </c>
       <c r="F476" t="n">
-        <v>98.47362823459777</v>
+        <v>98.47361297884351</v>
       </c>
       <c r="G476" t="n">
         <v>15261700</v>
@@ -11397,16 +11397,16 @@
         <v>45982</v>
       </c>
       <c r="C477" t="n">
-        <v>98.51278686523438</v>
+        <v>98.51279449462891</v>
       </c>
       <c r="D477" t="n">
-        <v>98.51278686523438</v>
+        <v>98.51279449462891</v>
       </c>
       <c r="E477" t="n">
-        <v>98.50299224963184</v>
+        <v>98.50299987826783</v>
       </c>
       <c r="F477" t="n">
-        <v>98.51278686523438</v>
+        <v>98.51279449462891</v>
       </c>
       <c r="G477" t="n">
         <v>16446900</v>
@@ -11420,16 +11420,16 @@
         <v>45985</v>
       </c>
       <c r="C478" t="n">
-        <v>98.5225830078125</v>
+        <v>98.52259063720703</v>
       </c>
       <c r="D478" t="n">
-        <v>98.53237762356683</v>
+        <v>98.53238525371985</v>
       </c>
       <c r="E478" t="n">
-        <v>98.5225830078125</v>
+        <v>98.52259063720703</v>
       </c>
       <c r="F478" t="n">
-        <v>98.5225830078125</v>
+        <v>98.52259063720703</v>
       </c>
       <c r="G478" t="n">
         <v>15830800</v>
@@ -11443,16 +11443,16 @@
         <v>45986</v>
       </c>
       <c r="C479" t="n">
-        <v>98.54216766357422</v>
+        <v>98.54217529296875</v>
       </c>
       <c r="D479" t="n">
-        <v>98.54216766357422</v>
+        <v>98.54217529296875</v>
       </c>
       <c r="E479" t="n">
-        <v>98.53238051863511</v>
+        <v>98.53238814727189</v>
       </c>
       <c r="F479" t="n">
-        <v>98.54216766357422</v>
+        <v>98.54217529296875</v>
       </c>
       <c r="G479" t="n">
         <v>19115000</v>
@@ -11489,16 +11489,16 @@
         <v>45989</v>
       </c>
       <c r="C481" t="n">
-        <v>98.58132934570312</v>
+        <v>98.58134460449219</v>
       </c>
       <c r="D481" t="n">
-        <v>98.59112396082016</v>
+        <v>98.59113922112526</v>
       </c>
       <c r="E481" t="n">
-        <v>98.5715422016884</v>
+        <v>98.57155745896257</v>
       </c>
       <c r="F481" t="n">
-        <v>98.58132934570312</v>
+        <v>98.58134460449219</v>
       </c>
       <c r="G481" t="n">
         <v>24417500</v>
@@ -11512,16 +11512,16 @@
         <v>45992</v>
       </c>
       <c r="C482" t="n">
-        <v>98.60391998291016</v>
+        <v>98.60392761230469</v>
       </c>
       <c r="D482" t="n">
-        <v>98.60391998291016</v>
+        <v>98.60392761230469</v>
       </c>
       <c r="E482" t="n">
-        <v>98.59410231425819</v>
+        <v>98.59410994289308</v>
       </c>
       <c r="F482" t="n">
-        <v>98.60391998291016</v>
+        <v>98.60392761230469</v>
       </c>
       <c r="G482" t="n">
         <v>29025600</v>
@@ -11535,16 +11535,16 @@
         <v>45993</v>
       </c>
       <c r="C483" t="n">
-        <v>98.62358093261719</v>
+        <v>98.62357330322266</v>
       </c>
       <c r="D483" t="n">
-        <v>98.62358093261719</v>
+        <v>98.62357330322266</v>
       </c>
       <c r="E483" t="n">
-        <v>98.61375576850331</v>
+        <v>98.61374813986885</v>
       </c>
       <c r="F483" t="n">
-        <v>98.61375576850331</v>
+        <v>98.61374813986885</v>
       </c>
       <c r="G483" t="n">
         <v>14362600</v>
@@ -11558,16 +11558,16 @@
         <v>45994</v>
       </c>
       <c r="C484" t="n">
-        <v>98.63340759277344</v>
+        <v>98.63339233398438</v>
       </c>
       <c r="D484" t="n">
-        <v>98.63831642770265</v>
+        <v>98.63830116815419</v>
       </c>
       <c r="E484" t="n">
-        <v>98.63340759277344</v>
+        <v>98.63339233398438</v>
       </c>
       <c r="F484" t="n">
-        <v>98.63340759277344</v>
+        <v>98.63339233398438</v>
       </c>
       <c r="G484" t="n">
         <v>15531600</v>
@@ -11581,16 +11581,16 @@
         <v>45995</v>
       </c>
       <c r="C485" t="n">
-        <v>98.65303802490234</v>
+        <v>98.65304565429688</v>
       </c>
       <c r="D485" t="n">
-        <v>98.65303802490234</v>
+        <v>98.65304565429688</v>
       </c>
       <c r="E485" t="n">
-        <v>98.6432128618746</v>
+        <v>98.64322049050931</v>
       </c>
       <c r="F485" t="n">
-        <v>98.6432128618746</v>
+        <v>98.64322049050931</v>
       </c>
       <c r="G485" t="n">
         <v>13689600</v>
@@ -11604,16 +11604,16 @@
         <v>45996</v>
       </c>
       <c r="C486" t="n">
-        <v>98.68251800537109</v>
+        <v>98.68251037597656</v>
       </c>
       <c r="D486" t="n">
-        <v>98.68251800537109</v>
+        <v>98.68251037597656</v>
       </c>
       <c r="E486" t="n">
-        <v>98.67269284115001</v>
+        <v>98.67268521251508</v>
       </c>
       <c r="F486" t="n">
-        <v>98.67269284115001</v>
+        <v>98.67268521251508</v>
       </c>
       <c r="G486" t="n">
         <v>17918100</v>
@@ -11627,16 +11627,16 @@
         <v>45999</v>
       </c>
       <c r="C487" t="n">
-        <v>98.68251800537109</v>
+        <v>98.68251037597656</v>
       </c>
       <c r="D487" t="n">
-        <v>98.68251800537109</v>
+        <v>98.68251037597656</v>
       </c>
       <c r="E487" t="n">
-        <v>98.67269284115001</v>
+        <v>98.67268521251508</v>
       </c>
       <c r="F487" t="n">
-        <v>98.68251800537109</v>
+        <v>98.68251037597656</v>
       </c>
       <c r="G487" t="n">
         <v>16657900</v>
@@ -11650,16 +11650,16 @@
         <v>46000</v>
       </c>
       <c r="C488" t="n">
-        <v>98.69234466552734</v>
+        <v>98.69232940673828</v>
       </c>
       <c r="D488" t="n">
-        <v>98.69725350051007</v>
+        <v>98.69723824096205</v>
       </c>
       <c r="E488" t="n">
-        <v>98.69234466552734</v>
+        <v>98.69232940673828</v>
       </c>
       <c r="F488" t="n">
-        <v>98.69234466552734</v>
+        <v>98.69232940673828</v>
       </c>
       <c r="G488" t="n">
         <v>11016400</v>
@@ -11673,16 +11673,16 @@
         <v>46001</v>
       </c>
       <c r="C489" t="n">
-        <v>98.69234466552734</v>
+        <v>98.69232940673828</v>
       </c>
       <c r="D489" t="n">
-        <v>98.70216982989736</v>
+        <v>98.70215456958923</v>
       </c>
       <c r="E489" t="n">
-        <v>98.69234466552734</v>
+        <v>98.69232940673828</v>
       </c>
       <c r="F489" t="n">
-        <v>98.70216982989736</v>
+        <v>98.70215456958923</v>
       </c>
       <c r="G489" t="n">
         <v>12234900</v>
@@ -11696,16 +11696,16 @@
         <v>46002</v>
       </c>
       <c r="C490" t="n">
-        <v>98.71196746826172</v>
+        <v>98.71198272705078</v>
       </c>
       <c r="D490" t="n">
-        <v>98.72179263063791</v>
+        <v>98.72180789094574</v>
       </c>
       <c r="E490" t="n">
-        <v>98.71196746826172</v>
+        <v>98.71198272705078</v>
       </c>
       <c r="F490" t="n">
-        <v>98.71196746826172</v>
+        <v>98.71198272705078</v>
       </c>
       <c r="G490" t="n">
         <v>22343500</v>
@@ -11880,16 +11880,16 @@
         <v>46014</v>
       </c>
       <c r="C498" t="n">
-        <v>98.83296966552734</v>
+        <v>98.83298492431641</v>
       </c>
       <c r="D498" t="n">
-        <v>98.84282648891585</v>
+        <v>98.84284174922669</v>
       </c>
       <c r="E498" t="n">
-        <v>98.83296966552734</v>
+        <v>98.83298492431641</v>
       </c>
       <c r="F498" t="n">
-        <v>98.84282648891585</v>
+        <v>98.84284174922669</v>
       </c>
       <c r="G498" t="n">
         <v>12256200</v>
@@ -11903,16 +11903,16 @@
         <v>46015</v>
       </c>
       <c r="C499" t="n">
-        <v>98.85267639160156</v>
+        <v>98.85268402099609</v>
       </c>
       <c r="D499" t="n">
-        <v>98.86253321504967</v>
+        <v>98.86254084520495</v>
       </c>
       <c r="E499" t="n">
-        <v>98.85267639160156</v>
+        <v>98.85268402099609</v>
       </c>
       <c r="F499" t="n">
-        <v>98.86253321504967</v>
+        <v>98.86254084520495</v>
       </c>
       <c r="G499" t="n">
         <v>7791300</v>
@@ -11949,16 +11949,16 @@
         <v>46020</v>
       </c>
       <c r="C501" t="n">
-        <v>98.90195465087891</v>
+        <v>98.90196228027344</v>
       </c>
       <c r="D501" t="n">
-        <v>98.90195465087891</v>
+        <v>98.90196228027344</v>
       </c>
       <c r="E501" t="n">
-        <v>98.8920978272653</v>
+        <v>98.89210545589947</v>
       </c>
       <c r="F501" t="n">
-        <v>98.8920978272653</v>
+        <v>98.89210545589947</v>
       </c>
       <c r="G501" t="n">
         <v>17350200</v>
@@ -11972,16 +11972,16 @@
         <v>46021</v>
       </c>
       <c r="C502" t="n">
-        <v>98.91181182861328</v>
+        <v>98.91181945800781</v>
       </c>
       <c r="D502" t="n">
-        <v>98.91181182861328</v>
+        <v>98.91181945800781</v>
       </c>
       <c r="E502" t="n">
-        <v>98.90195500496438</v>
+        <v>98.90196263359863</v>
       </c>
       <c r="F502" t="n">
-        <v>98.90687965751208</v>
+        <v>98.90688728652617</v>
       </c>
       <c r="G502" t="n">
         <v>12608900</v>
@@ -11995,16 +11995,16 @@
         <v>46022</v>
       </c>
       <c r="C503" t="n">
-        <v>98.92166137695312</v>
+        <v>98.92166900634766</v>
       </c>
       <c r="D503" t="n">
-        <v>98.93151820062626</v>
+        <v>98.931525830781</v>
       </c>
       <c r="E503" t="n">
-        <v>98.92166137695312</v>
+        <v>98.92166900634766</v>
       </c>
       <c r="F503" t="n">
-        <v>98.93151820062626</v>
+        <v>98.931525830781</v>
       </c>
       <c r="G503" t="n">
         <v>13910900</v>
@@ -12018,16 +12018,16 @@
         <v>46024</v>
       </c>
       <c r="C504" t="n">
-        <v>98.95124053955078</v>
+        <v>98.95123291015625</v>
       </c>
       <c r="D504" t="n">
-        <v>98.96108984553553</v>
+        <v>98.96108221538158</v>
       </c>
       <c r="E504" t="n">
-        <v>98.95124053955078</v>
+        <v>98.95123291015625</v>
       </c>
       <c r="F504" t="n">
-        <v>98.95124053955078</v>
+        <v>98.95123291015625</v>
       </c>
       <c r="G504" t="n">
         <v>19188800</v>
@@ -12041,16 +12041,16 @@
         <v>46027</v>
       </c>
       <c r="C505" t="n">
-        <v>98.96108245849609</v>
+        <v>98.96109008789062</v>
       </c>
       <c r="D505" t="n">
-        <v>98.96601462967449</v>
+        <v>98.96602225944926</v>
       </c>
       <c r="E505" t="n">
-        <v>98.96108245849609</v>
+        <v>98.96109008789062</v>
       </c>
       <c r="F505" t="n">
-        <v>98.96108245849609</v>
+        <v>98.96109008789062</v>
       </c>
       <c r="G505" t="n">
         <v>25006600</v>
@@ -12064,16 +12064,16 @@
         <v>46028</v>
       </c>
       <c r="C506" t="n">
-        <v>98.97093963623047</v>
+        <v>98.97095489501953</v>
       </c>
       <c r="D506" t="n">
-        <v>98.97093963623047</v>
+        <v>98.97095489501953</v>
       </c>
       <c r="E506" t="n">
-        <v>98.97093963623047</v>
+        <v>98.97095489501953</v>
       </c>
       <c r="F506" t="n">
-        <v>98.97093963623047</v>
+        <v>98.97095489501953</v>
       </c>
       <c r="G506" t="n">
         <v>17635000</v>
@@ -12087,16 +12087,16 @@
         <v>46029</v>
       </c>
       <c r="C507" t="n">
-        <v>98.98078918457031</v>
+        <v>98.98080444335938</v>
       </c>
       <c r="D507" t="n">
-        <v>98.98078918457031</v>
+        <v>98.98080444335938</v>
       </c>
       <c r="E507" t="n">
-        <v>98.98078918457031</v>
+        <v>98.98080444335938</v>
       </c>
       <c r="F507" t="n">
-        <v>98.98078918457031</v>
+        <v>98.98080444335938</v>
       </c>
       <c r="G507" t="n">
         <v>14062300</v>
@@ -12133,16 +12133,16 @@
         <v>46031</v>
       </c>
       <c r="C509" t="n">
-        <v>99.01036834716797</v>
+        <v>99.01036071777344</v>
       </c>
       <c r="D509" t="n">
-        <v>99.0202251718958</v>
+        <v>99.02021754174173</v>
       </c>
       <c r="E509" t="n">
-        <v>99.01036834716797</v>
+        <v>99.01036071777344</v>
       </c>
       <c r="F509" t="n">
-        <v>99.0202251718958</v>
+        <v>99.02021754174173</v>
       </c>
       <c r="G509" t="n">
         <v>15053500</v>
@@ -12156,16 +12156,16 @@
         <v>46034</v>
       </c>
       <c r="C510" t="n">
-        <v>99.03005981445312</v>
+        <v>99.03007507324219</v>
       </c>
       <c r="D510" t="n">
-        <v>99.03005981445312</v>
+        <v>99.03007507324219</v>
       </c>
       <c r="E510" t="n">
-        <v>99.02021050973804</v>
+        <v>99.02022576700949</v>
       </c>
       <c r="F510" t="n">
-        <v>99.02021050973804</v>
+        <v>99.02022576700949</v>
       </c>
       <c r="G510" t="n">
         <v>14819400</v>
@@ -12179,16 +12179,16 @@
         <v>46035</v>
       </c>
       <c r="C511" t="n">
-        <v>99.03992462158203</v>
+        <v>99.03993225097656</v>
       </c>
       <c r="D511" t="n">
-        <v>99.03992462158203</v>
+        <v>99.03993225097656</v>
       </c>
       <c r="E511" t="n">
-        <v>99.03006779751914</v>
+        <v>99.03007542615437</v>
       </c>
       <c r="F511" t="n">
-        <v>99.03006779751914</v>
+        <v>99.03007542615437</v>
       </c>
       <c r="G511" t="n">
         <v>14163000</v>
@@ -12202,16 +12202,16 @@
         <v>46036</v>
       </c>
       <c r="C512" t="n">
-        <v>99.04978179931641</v>
+        <v>99.04978942871094</v>
       </c>
       <c r="D512" t="n">
-        <v>99.04978179931641</v>
+        <v>99.04978942871094</v>
       </c>
       <c r="E512" t="n">
-        <v>99.03992497521833</v>
+        <v>99.03993260385363</v>
       </c>
       <c r="F512" t="n">
-        <v>99.04978179931641</v>
+        <v>99.04978942871094</v>
       </c>
       <c r="G512" t="n">
         <v>11851800</v>
@@ -12225,16 +12225,16 @@
         <v>46037</v>
       </c>
       <c r="C513" t="n">
-        <v>99.05963897705078</v>
+        <v>99.05963134765625</v>
       </c>
       <c r="D513" t="n">
-        <v>99.05963897705078</v>
+        <v>99.05963134765625</v>
       </c>
       <c r="E513" t="n">
-        <v>99.04978967072383</v>
+        <v>99.04978204208787</v>
       </c>
       <c r="F513" t="n">
-        <v>99.04978967072383</v>
+        <v>99.04978204208787</v>
       </c>
       <c r="G513" t="n">
         <v>11469500</v>
@@ -12317,16 +12317,16 @@
         <v>46044</v>
       </c>
       <c r="C517" t="n">
-        <v>99.11876678466797</v>
+        <v>99.11875915527344</v>
       </c>
       <c r="D517" t="n">
-        <v>99.11876678466797</v>
+        <v>99.11875915527344</v>
       </c>
       <c r="E517" t="n">
-        <v>99.10890996034576</v>
+        <v>99.10890233170993</v>
       </c>
       <c r="F517" t="n">
-        <v>99.11876678466797</v>
+        <v>99.11875915527344</v>
       </c>
       <c r="G517" t="n">
         <v>13618500</v>
@@ -12363,16 +12363,16 @@
         <v>46048</v>
       </c>
       <c r="C519" t="n">
-        <v>99.15818023681641</v>
+        <v>99.15818786621094</v>
       </c>
       <c r="D519" t="n">
-        <v>99.15818023681641</v>
+        <v>99.15818786621094</v>
       </c>
       <c r="E519" t="n">
-        <v>99.14832341312308</v>
+        <v>99.14833104175922</v>
       </c>
       <c r="F519" t="n">
-        <v>99.15818023681641</v>
+        <v>99.15818786621094</v>
       </c>
       <c r="G519" t="n">
         <v>16872000</v>
@@ -12386,16 +12386,16 @@
         <v>46049</v>
       </c>
       <c r="C520" t="n">
-        <v>99.15818023681641</v>
+        <v>99.15818786621094</v>
       </c>
       <c r="D520" t="n">
-        <v>99.1729617130796</v>
+        <v>99.17296934361146</v>
       </c>
       <c r="E520" t="n">
-        <v>99.15818023681641</v>
+        <v>99.15818786621094</v>
       </c>
       <c r="F520" t="n">
-        <v>99.16802954195617</v>
+        <v>99.16803717210854</v>
       </c>
       <c r="G520" t="n">
         <v>13393600</v>
@@ -12432,16 +12432,16 @@
         <v>46051</v>
       </c>
       <c r="C522" t="n">
-        <v>99.187744140625</v>
+        <v>99.18775177001953</v>
       </c>
       <c r="D522" t="n">
-        <v>99.187744140625</v>
+        <v>99.18775177001953</v>
       </c>
       <c r="E522" t="n">
-        <v>99.17788731683716</v>
+        <v>99.1778949454735</v>
       </c>
       <c r="F522" t="n">
-        <v>99.17788731683716</v>
+        <v>99.1778949454735</v>
       </c>
       <c r="G522" t="n">
         <v>16031700</v>
@@ -12478,16 +12478,16 @@
         <v>46055</v>
       </c>
       <c r="C524" t="n">
-        <v>99.21636199951172</v>
+        <v>99.21635437011719</v>
       </c>
       <c r="D524" t="n">
-        <v>99.22624163068743</v>
+        <v>99.22623400053318</v>
       </c>
       <c r="E524" t="n">
-        <v>99.21636199951172</v>
+        <v>99.21635437011719</v>
       </c>
       <c r="F524" t="n">
-        <v>99.22624163068743</v>
+        <v>99.22623400053318</v>
       </c>
       <c r="G524" t="n">
         <v>31225300</v>
@@ -12501,16 +12501,16 @@
         <v>46056</v>
       </c>
       <c r="C525" t="n">
-        <v>99.23612976074219</v>
+        <v>99.23612213134766</v>
       </c>
       <c r="D525" t="n">
-        <v>99.23612976074219</v>
+        <v>99.23612213134766</v>
       </c>
       <c r="E525" t="n">
-        <v>99.22624258776793</v>
+        <v>99.22623495913354</v>
       </c>
       <c r="F525" t="n">
-        <v>99.23612976074219</v>
+        <v>99.23612213134766</v>
       </c>
       <c r="G525" t="n">
         <v>18150800</v>
@@ -12524,16 +12524,16 @@
         <v>46057</v>
       </c>
       <c r="C526" t="n">
-        <v>99.24601745605469</v>
+        <v>99.24600982666016</v>
       </c>
       <c r="D526" t="n">
-        <v>99.24601745605469</v>
+        <v>99.24600982666016</v>
       </c>
       <c r="E526" t="n">
-        <v>99.23613028302839</v>
+        <v>99.23612265439392</v>
       </c>
       <c r="F526" t="n">
-        <v>99.24107009868989</v>
+        <v>99.24106246967568</v>
       </c>
       <c r="G526" t="n">
         <v>18129400</v>
@@ -12547,16 +12547,16 @@
         <v>46058</v>
       </c>
       <c r="C527" t="n">
-        <v>99.24601745605469</v>
+        <v>99.24600982666016</v>
       </c>
       <c r="D527" t="n">
-        <v>99.25590462908099</v>
+        <v>99.25589699892639</v>
       </c>
       <c r="E527" t="n">
-        <v>99.24601745605469</v>
+        <v>99.24600982666016</v>
       </c>
       <c r="F527" t="n">
-        <v>99.25590462908099</v>
+        <v>99.25589699892639</v>
       </c>
       <c r="G527" t="n">
         <v>20371200</v>
@@ -12570,16 +12570,16 @@
         <v>46059</v>
       </c>
       <c r="C528" t="n">
-        <v>99.27566528320312</v>
+        <v>99.27567291259766</v>
       </c>
       <c r="D528" t="n">
-        <v>99.28555245561691</v>
+        <v>99.28556008577127</v>
       </c>
       <c r="E528" t="n">
-        <v>99.27566528320312</v>
+        <v>99.27567291259766</v>
       </c>
       <c r="F528" t="n">
-        <v>99.27566528320312</v>
+        <v>99.27567291259766</v>
       </c>
       <c r="G528" t="n">
         <v>17381400</v>
@@ -12593,16 +12593,16 @@
         <v>46062</v>
       </c>
       <c r="C529" t="n">
-        <v>99.29544067382812</v>
+        <v>99.29543304443359</v>
       </c>
       <c r="D529" t="n">
-        <v>99.29544067382812</v>
+        <v>99.29543304443359</v>
       </c>
       <c r="E529" t="n">
-        <v>99.28556104226274</v>
+        <v>99.28555341362733</v>
       </c>
       <c r="F529" t="n">
-        <v>99.28556104226274</v>
+        <v>99.28555341362733</v>
       </c>
       <c r="G529" t="n">
         <v>13991600</v>
@@ -12616,16 +12616,16 @@
         <v>46063</v>
       </c>
       <c r="C530" t="n">
-        <v>99.30532836914062</v>
+        <v>99.30532073974609</v>
       </c>
       <c r="D530" t="n">
-        <v>99.30532836914062</v>
+        <v>99.30532073974609</v>
       </c>
       <c r="E530" t="n">
-        <v>99.29544119581978</v>
+        <v>99.29543356718486</v>
       </c>
       <c r="F530" t="n">
-        <v>99.30532836914062</v>
+        <v>99.30532073974609</v>
       </c>
       <c r="G530" t="n">
         <v>14002700</v>
@@ -12639,16 +12639,16 @@
         <v>46064</v>
       </c>
       <c r="C531" t="n">
-        <v>99.30532836914062</v>
+        <v>99.30532073974609</v>
       </c>
       <c r="D531" t="n">
-        <v>99.31521554246146</v>
+        <v>99.31520791230733</v>
       </c>
       <c r="E531" t="n">
-        <v>99.30532836914062</v>
+        <v>99.30532073974609</v>
       </c>
       <c r="F531" t="n">
-        <v>99.31521554246146</v>
+        <v>99.31520791230733</v>
       </c>
       <c r="G531" t="n">
         <v>12584400</v>
@@ -12800,16 +12800,16 @@
         <v>46076</v>
       </c>
       <c r="C538" t="n">
-        <v>99.43382263183594</v>
+        <v>99.43383026123047</v>
       </c>
       <c r="D538" t="n">
-        <v>99.43382263183594</v>
+        <v>99.43383026123047</v>
       </c>
       <c r="E538" t="n">
-        <v>99.42394300109534</v>
+        <v>99.42395062973182</v>
       </c>
       <c r="F538" t="n">
-        <v>99.42888281646563</v>
+        <v>99.42889044548114</v>
       </c>
       <c r="G538" t="n">
         <v>13465400</v>
@@ -12823,16 +12823,16 @@
         <v>46077</v>
       </c>
       <c r="C539" t="n">
-        <v>99.43382263183594</v>
+        <v>99.43383026123047</v>
       </c>
       <c r="D539" t="n">
-        <v>99.44370980427939</v>
+        <v>99.44371743443256</v>
       </c>
       <c r="E539" t="n">
-        <v>99.43382263183594</v>
+        <v>99.43383026123047</v>
       </c>
       <c r="F539" t="n">
-        <v>99.4387699889091</v>
+        <v>99.43877761868323</v>
       </c>
       <c r="G539" t="n">
         <v>12168900</v>
@@ -12846,16 +12846,16 @@
         <v>46078</v>
       </c>
       <c r="C540" t="n">
-        <v>99.44371032714844</v>
+        <v>99.44371795654297</v>
       </c>
       <c r="D540" t="n">
-        <v>99.45359749964389</v>
+        <v>99.45360512979697</v>
       </c>
       <c r="E540" t="n">
-        <v>99.44371032714844</v>
+        <v>99.44371795654297</v>
       </c>
       <c r="F540" t="n">
-        <v>99.45359749964389</v>
+        <v>99.45360512979697</v>
       </c>
       <c r="G540" t="n">
         <v>12532000</v>
@@ -12892,16 +12892,16 @@
         <v>46080</v>
       </c>
       <c r="C542" t="n">
-        <v>99.48324584960938</v>
+        <v>99.48325347900391</v>
       </c>
       <c r="D542" t="n">
-        <v>99.49313302154569</v>
+        <v>99.49314065169848</v>
       </c>
       <c r="E542" t="n">
-        <v>99.48324584960938</v>
+        <v>99.48325347900391</v>
       </c>
       <c r="F542" t="n">
-        <v>99.4881856647263</v>
+        <v>99.48819329449967</v>
       </c>
       <c r="G542" t="n">
         <v>26602400</v>
@@ -12938,16 +12938,16 @@
         <v>46084</v>
       </c>
       <c r="C544" t="n">
-        <v>99.51497650146484</v>
+        <v>99.51496887207031</v>
       </c>
       <c r="D544" t="n">
-        <v>99.51497650146484</v>
+        <v>99.51496887207031</v>
       </c>
       <c r="E544" t="n">
-        <v>99.50506253396671</v>
+        <v>99.50505490533224</v>
       </c>
       <c r="F544" t="n">
-        <v>99.51001573664503</v>
+        <v>99.51000810763082</v>
       </c>
       <c r="G544" t="n">
         <v>19224400</v>
@@ -12961,16 +12961,16 @@
         <v>46085</v>
       </c>
       <c r="C545" t="n">
-        <v>99.51497650146484</v>
+        <v>99.51496887207031</v>
       </c>
       <c r="D545" t="n">
-        <v>99.52489046896297</v>
+        <v>99.52488283880838</v>
       </c>
       <c r="E545" t="n">
-        <v>99.51497650146484</v>
+        <v>99.51496887207031</v>
       </c>
       <c r="F545" t="n">
-        <v>99.51992970414315</v>
+        <v>99.51992207436889</v>
       </c>
       <c r="G545" t="n">
         <v>14325400</v>
@@ -12984,16 +12984,16 @@
         <v>46086</v>
       </c>
       <c r="C546" t="n">
-        <v>99.52488708496094</v>
+        <v>99.52487945556641</v>
       </c>
       <c r="D546" t="n">
-        <v>99.53479348998074</v>
+        <v>99.53478585982681</v>
       </c>
       <c r="E546" t="n">
-        <v>99.52488708496094</v>
+        <v>99.52487945556641</v>
       </c>
       <c r="F546" t="n">
-        <v>99.53479348998074</v>
+        <v>99.53478585982681</v>
       </c>
       <c r="G546" t="n">
         <v>16218200</v>
@@ -13030,16 +13030,16 @@
         <v>46090</v>
       </c>
       <c r="C548" t="n">
-        <v>99.57444763183594</v>
+        <v>99.57444000244141</v>
       </c>
       <c r="D548" t="n">
-        <v>99.57444763183594</v>
+        <v>99.57444000244141</v>
       </c>
       <c r="E548" t="n">
-        <v>99.56453366409391</v>
+        <v>99.564526035459</v>
       </c>
       <c r="F548" t="n">
-        <v>99.56949442903577</v>
+        <v>99.56948680002075</v>
       </c>
       <c r="G548" t="n">
         <v>19053900</v>
@@ -13053,16 +13053,16 @@
         <v>46091</v>
       </c>
       <c r="C549" t="n">
-        <v>99.57444763183594</v>
+        <v>99.57444000244141</v>
       </c>
       <c r="D549" t="n">
-        <v>99.58436159957796</v>
+        <v>99.58435396942383</v>
       </c>
       <c r="E549" t="n">
-        <v>99.57444763183594</v>
+        <v>99.57444000244141</v>
       </c>
       <c r="F549" t="n">
-        <v>99.58138967789786</v>
+        <v>99.58138204797143</v>
       </c>
       <c r="G549" t="n">
         <v>13664200</v>
@@ -13076,16 +13076,16 @@
         <v>46092</v>
       </c>
       <c r="C550" t="n">
-        <v>99.59427642822266</v>
+        <v>99.59426879882812</v>
       </c>
       <c r="D550" t="n">
-        <v>99.59427642822266</v>
+        <v>99.59426879882812</v>
       </c>
       <c r="E550" t="n">
-        <v>99.58436246039494</v>
+        <v>99.58435483175987</v>
       </c>
       <c r="F550" t="n">
-        <v>99.58436246039494</v>
+        <v>99.58435483175987</v>
       </c>
       <c r="G550" t="n">
         <v>12287800</v>
@@ -13168,16 +13168,16 @@
         <v>46098</v>
       </c>
       <c r="C554" t="n">
-        <v>99.65374755859375</v>
+        <v>99.65373992919922</v>
       </c>
       <c r="D554" t="n">
-        <v>99.65374755859375</v>
+        <v>99.65373992919922</v>
       </c>
       <c r="E554" t="n">
-        <v>99.64383359052252</v>
+        <v>99.643825961887</v>
       </c>
       <c r="F554" t="n">
-        <v>99.64879435562911</v>
+        <v>99.64878672661379</v>
       </c>
       <c r="G554" t="n">
         <v>14438300</v>
@@ -13191,16 +13191,16 @@
         <v>46099</v>
       </c>
       <c r="C555" t="n">
-        <v>99.66365814208984</v>
+        <v>99.66365051269531</v>
       </c>
       <c r="D555" t="n">
-        <v>99.66365814208984</v>
+        <v>99.66365051269531</v>
       </c>
       <c r="E555" t="n">
-        <v>99.6537441743553</v>
+        <v>99.6537365457197</v>
       </c>
       <c r="F555" t="n">
-        <v>99.6537441743553</v>
+        <v>99.6537365457197</v>
       </c>
       <c r="G555" t="n">
         <v>14135100</v>
@@ -13214,16 +13214,16 @@
         <v>46100</v>
       </c>
       <c r="C556" t="n">
-        <v>99.66365814208984</v>
+        <v>99.66365051269531</v>
       </c>
       <c r="D556" t="n">
-        <v>99.67356454768272</v>
+        <v>99.67355691752984</v>
       </c>
       <c r="E556" t="n">
-        <v>99.6537441743553</v>
+        <v>99.6537365457197</v>
       </c>
       <c r="F556" t="n">
-        <v>99.66861134488627</v>
+        <v>99.66860371511258</v>
       </c>
       <c r="G556" t="n">
         <v>20345400</v>
@@ -13329,16 +13329,16 @@
         <v>46107</v>
       </c>
       <c r="C561" t="n">
-        <v>99.73303985595703</v>
+        <v>99.7330322265625</v>
       </c>
       <c r="D561" t="n">
-        <v>99.73303985595703</v>
+        <v>99.7330322265625</v>
       </c>
       <c r="E561" t="n">
-        <v>99.72312588831552</v>
+        <v>99.7231182596794</v>
       </c>
       <c r="F561" t="n">
-        <v>99.73303985595703</v>
+        <v>99.7330322265625</v>
       </c>
       <c r="G561" t="n">
         <v>17499400</v>
@@ -13559,16 +13559,16 @@
         <v>46122</v>
       </c>
       <c r="C571" t="n">
-        <v>99.90489196777344</v>
+        <v>99.90489959716797</v>
       </c>
       <c r="D571" t="n">
-        <v>99.90489196777344</v>
+        <v>99.90489959716797</v>
       </c>
       <c r="E571" t="n">
-        <v>99.89494905892218</v>
+        <v>99.8949566875574</v>
       </c>
       <c r="F571" t="n">
-        <v>99.89494905892218</v>
+        <v>99.8949566875574</v>
       </c>
       <c r="G571" t="n">
         <v>18783100</v>
@@ -13674,16 +13674,16 @@
         <v>46129</v>
       </c>
       <c r="C576" t="n">
-        <v>99.96453857421875</v>
+        <v>99.96453094482422</v>
       </c>
       <c r="D576" t="n">
-        <v>99.97448148349987</v>
+        <v>99.97447385334648</v>
       </c>
       <c r="E576" t="n">
-        <v>99.96453857421875</v>
+        <v>99.96453094482422</v>
       </c>
       <c r="F576" t="n">
-        <v>99.96453857421875</v>
+        <v>99.96453094482422</v>
       </c>
       <c r="G576" t="n">
         <v>20660500</v>

--- a/Data/sgov.xlsx
+++ b/Data/sgov.xlsx
@@ -472,16 +472,16 @@
         <v>45293</v>
       </c>
       <c r="C2" t="n">
-        <v>90.15838623046875</v>
+        <v>90.15837860107422</v>
       </c>
       <c r="D2" t="n">
-        <v>90.16737791910336</v>
+        <v>90.16737028894792</v>
       </c>
       <c r="E2" t="n">
-        <v>90.14939454183416</v>
+        <v>90.14938691320052</v>
       </c>
       <c r="F2" t="n">
-        <v>90.15838623046875</v>
+        <v>90.15837860107422</v>
       </c>
       <c r="G2" t="n">
         <v>5286200</v>
@@ -495,16 +495,16 @@
         <v>45294</v>
       </c>
       <c r="C3" t="n">
-        <v>90.16736602783203</v>
+        <v>90.16737365722656</v>
       </c>
       <c r="D3" t="n">
-        <v>90.18534254408165</v>
+        <v>90.18535017499724</v>
       </c>
       <c r="E3" t="n">
-        <v>90.16736602783203</v>
+        <v>90.16737365722656</v>
       </c>
       <c r="F3" t="n">
-        <v>90.16736602783203</v>
+        <v>90.16737365722656</v>
       </c>
       <c r="G3" t="n">
         <v>4597300</v>
@@ -518,16 +518,16 @@
         <v>45295</v>
       </c>
       <c r="C4" t="n">
-        <v>90.21233367919922</v>
+        <v>90.21231842041016</v>
       </c>
       <c r="D4" t="n">
-        <v>90.22132536893363</v>
+        <v>90.22131010862368</v>
       </c>
       <c r="E4" t="n">
-        <v>90.21233367919922</v>
+        <v>90.21231842041016</v>
       </c>
       <c r="F4" t="n">
-        <v>90.21233367919922</v>
+        <v>90.21231842041016</v>
       </c>
       <c r="G4" t="n">
         <v>2794100</v>
@@ -541,16 +541,16 @@
         <v>45296</v>
       </c>
       <c r="C5" t="n">
-        <v>90.22130584716797</v>
+        <v>90.2213134765625</v>
       </c>
       <c r="D5" t="n">
-        <v>90.23029753495679</v>
+        <v>90.23030516511169</v>
       </c>
       <c r="E5" t="n">
-        <v>90.22130584716797</v>
+        <v>90.2213134765625</v>
       </c>
       <c r="F5" t="n">
-        <v>90.22130584716797</v>
+        <v>90.2213134765625</v>
       </c>
       <c r="G5" t="n">
         <v>3491200</v>
@@ -587,16 +587,16 @@
         <v>45300</v>
       </c>
       <c r="C7" t="n">
-        <v>90.25725555419922</v>
+        <v>90.25727081298828</v>
       </c>
       <c r="D7" t="n">
-        <v>90.25725555419922</v>
+        <v>90.25727081298828</v>
       </c>
       <c r="E7" t="n">
-        <v>90.24826386742511</v>
+        <v>90.24827912469404</v>
       </c>
       <c r="F7" t="n">
-        <v>90.25725555419922</v>
+        <v>90.25727081298828</v>
       </c>
       <c r="G7" t="n">
         <v>2419800</v>
@@ -610,16 +610,16 @@
         <v>45301</v>
       </c>
       <c r="C8" t="n">
-        <v>90.27525329589844</v>
+        <v>90.27526092529297</v>
       </c>
       <c r="D8" t="n">
-        <v>90.27525329589844</v>
+        <v>90.27526092529297</v>
       </c>
       <c r="E8" t="n">
-        <v>90.26626846565911</v>
+        <v>90.26627609429431</v>
       </c>
       <c r="F8" t="n">
-        <v>90.27525329589844</v>
+        <v>90.27526092529297</v>
       </c>
       <c r="G8" t="n">
         <v>1961400</v>
@@ -633,16 +633,16 @@
         <v>45302</v>
       </c>
       <c r="C9" t="n">
-        <v>90.32919311523438</v>
+        <v>90.32918548583984</v>
       </c>
       <c r="D9" t="n">
-        <v>90.32919311523438</v>
+        <v>90.32918548583984</v>
       </c>
       <c r="E9" t="n">
-        <v>90.31120973814555</v>
+        <v>90.31120211026995</v>
       </c>
       <c r="F9" t="n">
-        <v>90.31120973814555</v>
+        <v>90.31120211026995</v>
       </c>
       <c r="G9" t="n">
         <v>3164900</v>
@@ -656,16 +656,16 @@
         <v>45303</v>
       </c>
       <c r="C10" t="n">
-        <v>90.33817291259766</v>
+        <v>90.33818817138672</v>
       </c>
       <c r="D10" t="n">
-        <v>90.33817291259766</v>
+        <v>90.33818817138672</v>
       </c>
       <c r="E10" t="n">
-        <v>90.32918808320254</v>
+        <v>90.329203340474</v>
       </c>
       <c r="F10" t="n">
-        <v>90.32918808320254</v>
+        <v>90.329203340474</v>
       </c>
       <c r="G10" t="n">
         <v>2557900</v>
@@ -702,16 +702,16 @@
         <v>45308</v>
       </c>
       <c r="C12" t="n">
-        <v>90.35617065429688</v>
+        <v>90.35617828369141</v>
       </c>
       <c r="D12" t="n">
-        <v>90.36515548512048</v>
+        <v>90.36516311527365</v>
       </c>
       <c r="E12" t="n">
-        <v>90.35617065429688</v>
+        <v>90.35617828369141</v>
       </c>
       <c r="F12" t="n">
-        <v>90.36515548512048</v>
+        <v>90.36516311527365</v>
       </c>
       <c r="G12" t="n">
         <v>2317700</v>
@@ -725,16 +725,16 @@
         <v>45309</v>
       </c>
       <c r="C13" t="n">
-        <v>90.39213562011719</v>
+        <v>90.39212036132812</v>
       </c>
       <c r="D13" t="n">
-        <v>90.4011204514444</v>
+        <v>90.40110519113864</v>
       </c>
       <c r="E13" t="n">
-        <v>90.39213562011719</v>
+        <v>90.39212036132812</v>
       </c>
       <c r="F13" t="n">
-        <v>90.4011204514444</v>
+        <v>90.40110519113864</v>
       </c>
       <c r="G13" t="n">
         <v>2672000</v>
@@ -748,16 +748,16 @@
         <v>45310</v>
       </c>
       <c r="C14" t="n">
-        <v>90.41908264160156</v>
+        <v>90.41910552978516</v>
       </c>
       <c r="D14" t="n">
-        <v>90.41908264160156</v>
+        <v>90.41910552978516</v>
       </c>
       <c r="E14" t="n">
-        <v>90.40109926586183</v>
+        <v>90.40112214949322</v>
       </c>
       <c r="F14" t="n">
-        <v>90.4100909537317</v>
+        <v>90.41011383963918</v>
       </c>
       <c r="G14" t="n">
         <v>3630100</v>
@@ -771,16 +771,16 @@
         <v>45313</v>
       </c>
       <c r="C15" t="n">
-        <v>90.42808532714844</v>
+        <v>90.4281005859375</v>
       </c>
       <c r="D15" t="n">
-        <v>90.43707701679384</v>
+        <v>90.43709227710016</v>
       </c>
       <c r="E15" t="n">
-        <v>90.41910049615264</v>
+        <v>90.41911575342561</v>
       </c>
       <c r="F15" t="n">
-        <v>90.43258460129594</v>
+        <v>90.43259986084422</v>
       </c>
       <c r="G15" t="n">
         <v>4307000</v>
@@ -794,16 +794,16 @@
         <v>45314</v>
       </c>
       <c r="C16" t="n">
-        <v>90.446044921875</v>
+        <v>90.44606781005859</v>
       </c>
       <c r="D16" t="n">
-        <v>90.446044921875</v>
+        <v>90.44606781005859</v>
       </c>
       <c r="E16" t="n">
-        <v>90.43705323459413</v>
+        <v>90.4370761205023</v>
       </c>
       <c r="F16" t="n">
-        <v>90.43705323459413</v>
+        <v>90.4370761205023</v>
       </c>
       <c r="G16" t="n">
         <v>2066200</v>
@@ -817,16 +817,16 @@
         <v>45315</v>
       </c>
       <c r="C17" t="n">
-        <v>90.45503234863281</v>
+        <v>90.45503997802734</v>
       </c>
       <c r="D17" t="n">
-        <v>90.45503234863281</v>
+        <v>90.45503997802734</v>
       </c>
       <c r="E17" t="n">
-        <v>90.44604066177547</v>
+        <v>90.4460482904116</v>
       </c>
       <c r="F17" t="n">
-        <v>90.44604066177547</v>
+        <v>90.4460482904116</v>
       </c>
       <c r="G17" t="n">
         <v>3441600</v>
@@ -886,16 +886,16 @@
         <v>45320</v>
       </c>
       <c r="C20" t="n">
-        <v>90.50899505615234</v>
+        <v>90.50898742675781</v>
       </c>
       <c r="D20" t="n">
-        <v>90.52697157644387</v>
+        <v>90.52696394553402</v>
       </c>
       <c r="E20" t="n">
-        <v>90.50899505615234</v>
+        <v>90.50898742675781</v>
       </c>
       <c r="F20" t="n">
-        <v>90.51798674562285</v>
+        <v>90.51797911547037</v>
       </c>
       <c r="G20" t="n">
         <v>2914400</v>
@@ -909,16 +909,16 @@
         <v>45321</v>
       </c>
       <c r="C21" t="n">
-        <v>90.53597259521484</v>
+        <v>90.53596496582031</v>
       </c>
       <c r="D21" t="n">
-        <v>90.53597259521484</v>
+        <v>90.53596496582031</v>
       </c>
       <c r="E21" t="n">
-        <v>90.52698090481779</v>
+        <v>90.52697327618098</v>
       </c>
       <c r="F21" t="n">
-        <v>90.52698090481779</v>
+        <v>90.52697327618098</v>
       </c>
       <c r="G21" t="n">
         <v>3741000</v>
@@ -932,16 +932,16 @@
         <v>45322</v>
       </c>
       <c r="C22" t="n">
-        <v>90.53597259521484</v>
+        <v>90.53596496582031</v>
       </c>
       <c r="D22" t="n">
-        <v>90.5449642856119</v>
+        <v>90.54495665545964</v>
       </c>
       <c r="E22" t="n">
-        <v>90.53597259521484</v>
+        <v>90.53596496582031</v>
       </c>
       <c r="F22" t="n">
-        <v>90.53597259521484</v>
+        <v>90.53596496582031</v>
       </c>
       <c r="G22" t="n">
         <v>5171300</v>
@@ -955,16 +955,16 @@
         <v>45323</v>
       </c>
       <c r="C23" t="n">
-        <v>90.58832550048828</v>
+        <v>90.58834838867188</v>
       </c>
       <c r="D23" t="n">
-        <v>90.59735826685852</v>
+        <v>90.59738115732434</v>
       </c>
       <c r="E23" t="n">
-        <v>90.58832550048828</v>
+        <v>90.58834838867188</v>
       </c>
       <c r="F23" t="n">
-        <v>90.59735826685852</v>
+        <v>90.59738115732434</v>
       </c>
       <c r="G23" t="n">
         <v>7038600</v>
@@ -978,16 +978,16 @@
         <v>45324</v>
       </c>
       <c r="C24" t="n">
-        <v>90.59735870361328</v>
+        <v>90.59736633300781</v>
       </c>
       <c r="D24" t="n">
-        <v>90.59735870361328</v>
+        <v>90.59736633300781</v>
       </c>
       <c r="E24" t="n">
-        <v>90.5883259371995</v>
+        <v>90.58833356583337</v>
       </c>
       <c r="F24" t="n">
-        <v>90.59735870361328</v>
+        <v>90.59736633300781</v>
       </c>
       <c r="G24" t="n">
         <v>3864800</v>
@@ -1001,16 +1001,16 @@
         <v>45327</v>
       </c>
       <c r="C25" t="n">
-        <v>90.61543273925781</v>
+        <v>90.61544036865234</v>
       </c>
       <c r="D25" t="n">
-        <v>90.61543273925781</v>
+        <v>90.61544036865234</v>
       </c>
       <c r="E25" t="n">
-        <v>90.60640686129281</v>
+        <v>90.6064144899274</v>
       </c>
       <c r="F25" t="n">
-        <v>90.61543273925781</v>
+        <v>90.61544036865234</v>
       </c>
       <c r="G25" t="n">
         <v>3969400</v>
@@ -1024,16 +1024,16 @@
         <v>45328</v>
       </c>
       <c r="C26" t="n">
-        <v>90.62447357177734</v>
+        <v>90.62445068359375</v>
       </c>
       <c r="D26" t="n">
-        <v>90.63350634052934</v>
+        <v>90.63348345006442</v>
       </c>
       <c r="E26" t="n">
-        <v>90.61544080302535</v>
+        <v>90.61541791712308</v>
       </c>
       <c r="F26" t="n">
-        <v>90.62447357177734</v>
+        <v>90.62445068359375</v>
       </c>
       <c r="G26" t="n">
         <v>2167300</v>
@@ -1047,16 +1047,16 @@
         <v>45329</v>
       </c>
       <c r="C27" t="n">
-        <v>90.64252471923828</v>
+        <v>90.64250946044922</v>
       </c>
       <c r="D27" t="n">
-        <v>90.64252471923828</v>
+        <v>90.64250946044922</v>
       </c>
       <c r="E27" t="n">
-        <v>90.63349195192031</v>
+        <v>90.63347669465182</v>
       </c>
       <c r="F27" t="n">
-        <v>90.64252471923828</v>
+        <v>90.64250946044922</v>
       </c>
       <c r="G27" t="n">
         <v>2621200</v>
@@ -1070,16 +1070,16 @@
         <v>45330</v>
       </c>
       <c r="C28" t="n">
-        <v>90.66961669921875</v>
+        <v>90.66960906982422</v>
       </c>
       <c r="D28" t="n">
-        <v>90.68767534398516</v>
+        <v>90.68766771307108</v>
       </c>
       <c r="E28" t="n">
-        <v>90.66961669921875</v>
+        <v>90.66960906982422</v>
       </c>
       <c r="F28" t="n">
-        <v>90.66961669921875</v>
+        <v>90.66960906982422</v>
       </c>
       <c r="G28" t="n">
         <v>3838700</v>
@@ -1093,16 +1093,16 @@
         <v>45331</v>
       </c>
       <c r="C29" t="n">
-        <v>90.69670104980469</v>
+        <v>90.69670867919922</v>
       </c>
       <c r="D29" t="n">
-        <v>90.69670104980469</v>
+        <v>90.69670867919922</v>
       </c>
       <c r="E29" t="n">
-        <v>90.68315534478884</v>
+        <v>90.68316297304392</v>
       </c>
       <c r="F29" t="n">
-        <v>90.68766828313339</v>
+        <v>90.6876759117681</v>
       </c>
       <c r="G29" t="n">
         <v>3232500</v>
@@ -1116,16 +1116,16 @@
         <v>45334</v>
       </c>
       <c r="C30" t="n">
-        <v>90.69670104980469</v>
+        <v>90.69670867919922</v>
       </c>
       <c r="D30" t="n">
-        <v>90.71475969316506</v>
+        <v>90.71476732407868</v>
       </c>
       <c r="E30" t="n">
-        <v>90.69670104980469</v>
+        <v>90.69670867919922</v>
       </c>
       <c r="F30" t="n">
-        <v>90.70573381647597</v>
+        <v>90.70574144663034</v>
       </c>
       <c r="G30" t="n">
         <v>2792700</v>
@@ -1162,16 +1162,16 @@
         <v>45336</v>
       </c>
       <c r="C32" t="n">
-        <v>90.73281860351562</v>
+        <v>90.73284149169922</v>
       </c>
       <c r="D32" t="n">
-        <v>90.73281860351562</v>
+        <v>90.73284149169922</v>
       </c>
       <c r="E32" t="n">
-        <v>90.72378583750368</v>
+        <v>90.72380872340868</v>
       </c>
       <c r="F32" t="n">
-        <v>90.73281860351562</v>
+        <v>90.73284149169922</v>
       </c>
       <c r="G32" t="n">
         <v>2614100</v>
@@ -1185,16 +1185,16 @@
         <v>45337</v>
       </c>
       <c r="C33" t="n">
-        <v>90.77799224853516</v>
+        <v>90.77796936035156</v>
       </c>
       <c r="D33" t="n">
-        <v>90.7870250168949</v>
+        <v>90.78700212643383</v>
       </c>
       <c r="E33" t="n">
-        <v>90.77799224853516</v>
+        <v>90.77796936035156</v>
       </c>
       <c r="F33" t="n">
-        <v>90.7870250168949</v>
+        <v>90.78700212643383</v>
       </c>
       <c r="G33" t="n">
         <v>2577800</v>
@@ -1277,16 +1277,16 @@
         <v>45344</v>
       </c>
       <c r="C37" t="n">
-        <v>90.85022735595703</v>
+        <v>90.8502197265625</v>
       </c>
       <c r="D37" t="n">
-        <v>90.85926012299844</v>
+        <v>90.85925249284537</v>
       </c>
       <c r="E37" t="n">
-        <v>90.85022735595703</v>
+        <v>90.8502197265625</v>
       </c>
       <c r="F37" t="n">
-        <v>90.85022735595703</v>
+        <v>90.8502197265625</v>
       </c>
       <c r="G37" t="n">
         <v>2452200</v>
@@ -1300,16 +1300,16 @@
         <v>45345</v>
       </c>
       <c r="C38" t="n">
-        <v>90.87733459472656</v>
+        <v>90.87732696533203</v>
       </c>
       <c r="D38" t="n">
-        <v>90.87733459472656</v>
+        <v>90.87732696533203</v>
       </c>
       <c r="E38" t="n">
-        <v>90.86830871609565</v>
+        <v>90.86830108745886</v>
       </c>
       <c r="F38" t="n">
-        <v>90.87733459472656</v>
+        <v>90.87732696533203</v>
       </c>
       <c r="G38" t="n">
         <v>2010100</v>
@@ -1346,16 +1346,16 @@
         <v>45349</v>
       </c>
       <c r="C40" t="n">
-        <v>90.90440368652344</v>
+        <v>90.90441131591797</v>
       </c>
       <c r="D40" t="n">
-        <v>90.90440368652344</v>
+        <v>90.90441131591797</v>
       </c>
       <c r="E40" t="n">
-        <v>90.8953709208117</v>
+        <v>90.89537854944814</v>
       </c>
       <c r="F40" t="n">
-        <v>90.90440368652344</v>
+        <v>90.90441131591797</v>
       </c>
       <c r="G40" t="n">
         <v>2360300</v>
@@ -1369,16 +1369,16 @@
         <v>45350</v>
       </c>
       <c r="C41" t="n">
-        <v>90.91343688964844</v>
+        <v>90.91345977783203</v>
       </c>
       <c r="D41" t="n">
-        <v>90.91343688964844</v>
+        <v>90.91345977783203</v>
       </c>
       <c r="E41" t="n">
-        <v>90.90441101319072</v>
+        <v>90.90443389910197</v>
       </c>
       <c r="F41" t="n">
-        <v>90.90441101319072</v>
+        <v>90.90443389910197</v>
       </c>
       <c r="G41" t="n">
         <v>4526200</v>
@@ -1392,16 +1392,16 @@
         <v>45351</v>
       </c>
       <c r="C42" t="n">
-        <v>90.94052886962891</v>
+        <v>90.94053649902344</v>
       </c>
       <c r="D42" t="n">
-        <v>90.94956163612534</v>
+        <v>90.94956926627766</v>
       </c>
       <c r="E42" t="n">
-        <v>90.94052886962891</v>
+        <v>90.94053649902344</v>
       </c>
       <c r="F42" t="n">
-        <v>90.94052886962891</v>
+        <v>90.94053649902344</v>
       </c>
       <c r="G42" t="n">
         <v>5560200</v>
@@ -1415,16 +1415,16 @@
         <v>45352</v>
       </c>
       <c r="C43" t="n">
-        <v>90.96772766113281</v>
+        <v>90.96773529052734</v>
       </c>
       <c r="D43" t="n">
-        <v>90.96772766113281</v>
+        <v>90.96773529052734</v>
       </c>
       <c r="E43" t="n">
-        <v>90.95865796807648</v>
+        <v>90.95866559671036</v>
       </c>
       <c r="F43" t="n">
-        <v>90.96772766113281</v>
+        <v>90.96773529052734</v>
       </c>
       <c r="G43" t="n">
         <v>7579200</v>
@@ -1461,16 +1461,16 @@
         <v>45356</v>
       </c>
       <c r="C45" t="n">
-        <v>90.98587036132812</v>
+        <v>90.98589324951172</v>
       </c>
       <c r="D45" t="n">
-        <v>90.99494005540443</v>
+        <v>90.99496294586957</v>
       </c>
       <c r="E45" t="n">
-        <v>90.98587036132812</v>
+        <v>90.98589324951172</v>
       </c>
       <c r="F45" t="n">
-        <v>90.98587036132812</v>
+        <v>90.98589324951172</v>
       </c>
       <c r="G45" t="n">
         <v>3905300</v>
@@ -1484,16 +1484,16 @@
         <v>45357</v>
       </c>
       <c r="C46" t="n">
-        <v>91.00400543212891</v>
+        <v>91.00401306152344</v>
       </c>
       <c r="D46" t="n">
-        <v>91.01307512577493</v>
+        <v>91.01308275592983</v>
       </c>
       <c r="E46" t="n">
-        <v>90.99493573848288</v>
+        <v>90.99494336711705</v>
       </c>
       <c r="F46" t="n">
-        <v>91.00400543212891</v>
+        <v>91.00401306152344</v>
       </c>
       <c r="G46" t="n">
         <v>2760000</v>
@@ -1507,16 +1507,16 @@
         <v>45358</v>
       </c>
       <c r="C47" t="n">
-        <v>91.04934692382812</v>
+        <v>91.04936218261719</v>
       </c>
       <c r="D47" t="n">
-        <v>91.04934692382812</v>
+        <v>91.04936218261719</v>
       </c>
       <c r="E47" t="n">
-        <v>91.04027723018791</v>
+        <v>91.04029248745701</v>
       </c>
       <c r="F47" t="n">
-        <v>91.04934692382812</v>
+        <v>91.04936218261719</v>
       </c>
       <c r="G47" t="n">
         <v>2415500</v>
@@ -1530,16 +1530,16 @@
         <v>45359</v>
       </c>
       <c r="C48" t="n">
-        <v>91.05841827392578</v>
+        <v>91.05841064453125</v>
       </c>
       <c r="D48" t="n">
-        <v>91.06748796842004</v>
+        <v>91.06748033826561</v>
       </c>
       <c r="E48" t="n">
-        <v>91.0493554975814</v>
+        <v>91.0493478689462</v>
       </c>
       <c r="F48" t="n">
-        <v>91.06748796842004</v>
+        <v>91.06748033826561</v>
       </c>
       <c r="G48" t="n">
         <v>3748900</v>
@@ -1553,16 +1553,16 @@
         <v>45362</v>
       </c>
       <c r="C49" t="n">
-        <v>91.07655334472656</v>
+        <v>91.07654571533203</v>
       </c>
       <c r="D49" t="n">
-        <v>91.07655334472656</v>
+        <v>91.07654571533203</v>
       </c>
       <c r="E49" t="n">
-        <v>91.06748365066231</v>
+        <v>91.06747602202755</v>
       </c>
       <c r="F49" t="n">
-        <v>91.07655334472656</v>
+        <v>91.07654571533203</v>
       </c>
       <c r="G49" t="n">
         <v>3238400</v>
@@ -1576,16 +1576,16 @@
         <v>45363</v>
       </c>
       <c r="C50" t="n">
-        <v>91.08562469482422</v>
+        <v>91.08561706542969</v>
       </c>
       <c r="D50" t="n">
-        <v>91.09469438974223</v>
+        <v>91.09468675958801</v>
       </c>
       <c r="E50" t="n">
-        <v>91.08562469482422</v>
+        <v>91.08561706542969</v>
       </c>
       <c r="F50" t="n">
-        <v>91.08562469482422</v>
+        <v>91.08561706542969</v>
       </c>
       <c r="G50" t="n">
         <v>2613300</v>
@@ -1622,16 +1622,16 @@
         <v>45365</v>
       </c>
       <c r="C52" t="n">
-        <v>91.13095092773438</v>
+        <v>91.13096618652344</v>
       </c>
       <c r="D52" t="n">
-        <v>91.14002062112732</v>
+        <v>91.140035881435</v>
       </c>
       <c r="E52" t="n">
-        <v>91.13095092773438</v>
+        <v>91.13096618652344</v>
       </c>
       <c r="F52" t="n">
-        <v>91.13095092773438</v>
+        <v>91.13096618652344</v>
       </c>
       <c r="G52" t="n">
         <v>3469600</v>
@@ -1645,16 +1645,16 @@
         <v>45366</v>
       </c>
       <c r="C53" t="n">
-        <v>91.14910888671875</v>
+        <v>91.14907073974609</v>
       </c>
       <c r="D53" t="n">
-        <v>91.14910888671875</v>
+        <v>91.14907073974609</v>
       </c>
       <c r="E53" t="n">
-        <v>91.14004610894038</v>
+        <v>91.1400079657606</v>
       </c>
       <c r="F53" t="n">
-        <v>91.14910888671875</v>
+        <v>91.14907073974609</v>
       </c>
       <c r="G53" t="n">
         <v>3277300</v>
@@ -1691,16 +1691,16 @@
         <v>45370</v>
       </c>
       <c r="C55" t="n">
-        <v>91.17630767822266</v>
+        <v>91.17631530761719</v>
       </c>
       <c r="D55" t="n">
-        <v>91.18537045497759</v>
+        <v>91.18537808513047</v>
       </c>
       <c r="E55" t="n">
-        <v>91.17630767822266</v>
+        <v>91.17631530761719</v>
       </c>
       <c r="F55" t="n">
-        <v>91.18537045497759</v>
+        <v>91.18537808513047</v>
       </c>
       <c r="G55" t="n">
         <v>2661900</v>
@@ -1714,16 +1714,16 @@
         <v>45371</v>
       </c>
       <c r="C56" t="n">
-        <v>91.18537139892578</v>
+        <v>91.18536376953125</v>
       </c>
       <c r="D56" t="n">
-        <v>91.19444109392479</v>
+        <v>91.19443346377142</v>
       </c>
       <c r="E56" t="n">
-        <v>91.18537139892578</v>
+        <v>91.18536376953125</v>
       </c>
       <c r="F56" t="n">
-        <v>91.18537139892578</v>
+        <v>91.18536376953125</v>
       </c>
       <c r="G56" t="n">
         <v>2492700</v>
@@ -1737,16 +1737,16 @@
         <v>45372</v>
       </c>
       <c r="C57" t="n">
-        <v>91.22164154052734</v>
+        <v>91.22163391113281</v>
       </c>
       <c r="D57" t="n">
-        <v>91.23071123535532</v>
+        <v>91.23070360520224</v>
       </c>
       <c r="E57" t="n">
-        <v>91.22164154052734</v>
+        <v>91.22163391113281</v>
       </c>
       <c r="F57" t="n">
-        <v>91.22164154052734</v>
+        <v>91.22163391113281</v>
       </c>
       <c r="G57" t="n">
         <v>3547400</v>
@@ -1760,16 +1760,16 @@
         <v>45373</v>
       </c>
       <c r="C58" t="n">
-        <v>91.23978424072266</v>
+        <v>91.23976898193359</v>
       </c>
       <c r="D58" t="n">
-        <v>91.24884701772933</v>
+        <v>91.24883175742463</v>
       </c>
       <c r="E58" t="n">
-        <v>91.2307145455656</v>
+        <v>91.23069928829332</v>
       </c>
       <c r="F58" t="n">
-        <v>91.24884701772933</v>
+        <v>91.24883175742463</v>
       </c>
       <c r="G58" t="n">
         <v>2636700</v>
@@ -1783,16 +1783,16 @@
         <v>45376</v>
       </c>
       <c r="C59" t="n">
-        <v>91.25791168212891</v>
+        <v>91.25791931152344</v>
       </c>
       <c r="D59" t="n">
-        <v>91.26698137678599</v>
+        <v>91.26698900693876</v>
       </c>
       <c r="E59" t="n">
-        <v>91.25791168212891</v>
+        <v>91.25791931152344</v>
       </c>
       <c r="F59" t="n">
-        <v>91.25791168212891</v>
+        <v>91.25791931152344</v>
       </c>
       <c r="G59" t="n">
         <v>2422900</v>
@@ -1806,16 +1806,16 @@
         <v>45377</v>
       </c>
       <c r="C60" t="n">
-        <v>91.26698303222656</v>
+        <v>91.26699066162109</v>
       </c>
       <c r="D60" t="n">
-        <v>91.27605272704815</v>
+        <v>91.27606035720085</v>
       </c>
       <c r="E60" t="n">
-        <v>91.26698303222656</v>
+        <v>91.26699066162109</v>
       </c>
       <c r="F60" t="n">
-        <v>91.26698303222656</v>
+        <v>91.26699066162109</v>
       </c>
       <c r="G60" t="n">
         <v>3181700</v>
@@ -1875,16 +1875,16 @@
         <v>45383</v>
       </c>
       <c r="C63" t="n">
-        <v>91.34871673583984</v>
+        <v>91.34870910644531</v>
       </c>
       <c r="D63" t="n">
-        <v>91.3578271386809</v>
+        <v>91.35781950852548</v>
       </c>
       <c r="E63" t="n">
-        <v>91.34871673583984</v>
+        <v>91.34870910644531</v>
       </c>
       <c r="F63" t="n">
-        <v>91.3578271386809</v>
+        <v>91.35781950852548</v>
       </c>
       <c r="G63" t="n">
         <v>7395400</v>
@@ -1898,16 +1898,16 @@
         <v>45384</v>
       </c>
       <c r="C64" t="n">
-        <v>91.36691284179688</v>
+        <v>91.36693572998047</v>
       </c>
       <c r="D64" t="n">
-        <v>91.36691284179688</v>
+        <v>91.36693572998047</v>
       </c>
       <c r="E64" t="n">
-        <v>91.35780938992566</v>
+        <v>91.35783227582876</v>
       </c>
       <c r="F64" t="n">
-        <v>91.36691284179688</v>
+        <v>91.36693572998047</v>
       </c>
       <c r="G64" t="n">
         <v>4202900</v>
@@ -1921,16 +1921,16 @@
         <v>45385</v>
       </c>
       <c r="C65" t="n">
-        <v>91.37604522705078</v>
+        <v>91.37602996826172</v>
       </c>
       <c r="D65" t="n">
-        <v>91.38515563031378</v>
+        <v>91.38514037000337</v>
       </c>
       <c r="E65" t="n">
-        <v>91.37604522705078</v>
+        <v>91.37602996826172</v>
       </c>
       <c r="F65" t="n">
-        <v>91.37604522705078</v>
+        <v>91.37602996826172</v>
       </c>
       <c r="G65" t="n">
         <v>4333600</v>
@@ -1967,16 +1967,16 @@
         <v>45387</v>
       </c>
       <c r="C67" t="n">
-        <v>91.43067932128906</v>
+        <v>91.43069458007812</v>
       </c>
       <c r="D67" t="n">
-        <v>91.43978972311452</v>
+        <v>91.439804983424</v>
       </c>
       <c r="E67" t="n">
-        <v>91.43067932128906</v>
+        <v>91.43069458007812</v>
       </c>
       <c r="F67" t="n">
-        <v>91.43978972311452</v>
+        <v>91.439804983424</v>
       </c>
       <c r="G67" t="n">
         <v>3104200</v>
@@ -1990,16 +1990,16 @@
         <v>45390</v>
       </c>
       <c r="C68" t="n">
-        <v>91.44890594482422</v>
+        <v>91.44889068603516</v>
       </c>
       <c r="D68" t="n">
-        <v>91.44890594482422</v>
+        <v>91.44889068603516</v>
       </c>
       <c r="E68" t="n">
-        <v>91.43979554241898</v>
+        <v>91.43978028515004</v>
       </c>
       <c r="F68" t="n">
-        <v>91.44890594482422</v>
+        <v>91.44889068603516</v>
       </c>
       <c r="G68" t="n">
         <v>3511400</v>
@@ -2013,16 +2013,16 @@
         <v>45391</v>
       </c>
       <c r="C69" t="n">
-        <v>91.45800018310547</v>
+        <v>91.45802307128906</v>
       </c>
       <c r="D69" t="n">
-        <v>91.45800018310547</v>
+        <v>91.45802307128906</v>
       </c>
       <c r="E69" t="n">
-        <v>91.44888978231037</v>
+        <v>91.44891266821402</v>
       </c>
       <c r="F69" t="n">
-        <v>91.45800018310547</v>
+        <v>91.45802307128906</v>
       </c>
       <c r="G69" t="n">
         <v>3578500</v>
@@ -2036,16 +2036,16 @@
         <v>45392</v>
       </c>
       <c r="C70" t="n">
-        <v>91.47623443603516</v>
+        <v>91.47621154785156</v>
       </c>
       <c r="D70" t="n">
-        <v>91.47623443603516</v>
+        <v>91.47621154785156</v>
       </c>
       <c r="E70" t="n">
-        <v>91.45802057958272</v>
+        <v>91.45799769595641</v>
       </c>
       <c r="F70" t="n">
-        <v>91.46712403320832</v>
+        <v>91.46710114730423</v>
       </c>
       <c r="G70" t="n">
         <v>3893100</v>
@@ -2059,16 +2059,16 @@
         <v>45393</v>
       </c>
       <c r="C71" t="n">
-        <v>91.51265716552734</v>
+        <v>91.51267242431641</v>
       </c>
       <c r="D71" t="n">
-        <v>91.51265716552734</v>
+        <v>91.51267242431641</v>
       </c>
       <c r="E71" t="n">
-        <v>91.50354676388844</v>
+        <v>91.50356202115843</v>
       </c>
       <c r="F71" t="n">
-        <v>91.50354676388844</v>
+        <v>91.50356202115843</v>
       </c>
       <c r="G71" t="n">
         <v>3521100</v>
@@ -2105,16 +2105,16 @@
         <v>45397</v>
       </c>
       <c r="C73" t="n">
-        <v>91.53997802734375</v>
+        <v>91.53999328613281</v>
       </c>
       <c r="D73" t="n">
-        <v>91.53997802734375</v>
+        <v>91.53999328613281</v>
       </c>
       <c r="E73" t="n">
-        <v>91.53086762604262</v>
+        <v>91.53088288331307</v>
       </c>
       <c r="F73" t="n">
-        <v>91.53086762604262</v>
+        <v>91.53088288331307</v>
       </c>
       <c r="G73" t="n">
         <v>4144700</v>
@@ -2128,16 +2128,16 @@
         <v>45398</v>
       </c>
       <c r="C74" t="n">
-        <v>91.53997802734375</v>
+        <v>91.53999328613281</v>
       </c>
       <c r="D74" t="n">
-        <v>91.55819188074594</v>
+        <v>91.55820714257106</v>
       </c>
       <c r="E74" t="n">
-        <v>91.53997802734375</v>
+        <v>91.53999328613281</v>
       </c>
       <c r="F74" t="n">
-        <v>91.54908842864488</v>
+        <v>91.54910368895256</v>
       </c>
       <c r="G74" t="n">
         <v>4850000</v>
@@ -2151,16 +2151,16 @@
         <v>45399</v>
       </c>
       <c r="C75" t="n">
-        <v>91.56729125976562</v>
+        <v>91.56731414794922</v>
       </c>
       <c r="D75" t="n">
-        <v>91.56729125976562</v>
+        <v>91.56731414794922</v>
       </c>
       <c r="E75" t="n">
-        <v>91.55818085956115</v>
+        <v>91.55820374546751</v>
       </c>
       <c r="F75" t="n">
-        <v>91.56729125976562</v>
+        <v>91.56731414794922</v>
       </c>
       <c r="G75" t="n">
         <v>3688400</v>
@@ -2197,16 +2197,16 @@
         <v>45401</v>
       </c>
       <c r="C77" t="n">
-        <v>91.62193298339844</v>
+        <v>91.62195587158203</v>
       </c>
       <c r="D77" t="n">
-        <v>91.62193298339844</v>
+        <v>91.62195587158203</v>
       </c>
       <c r="E77" t="n">
-        <v>91.60371913353637</v>
+        <v>91.60374201716995</v>
       </c>
       <c r="F77" t="n">
-        <v>91.62193298339844</v>
+        <v>91.62195587158203</v>
       </c>
       <c r="G77" t="n">
         <v>3319500</v>
@@ -2220,16 +2220,16 @@
         <v>45404</v>
       </c>
       <c r="C78" t="n">
-        <v>91.63107299804688</v>
+        <v>91.63106536865234</v>
       </c>
       <c r="D78" t="n">
-        <v>91.63107299804688</v>
+        <v>91.63106536865234</v>
       </c>
       <c r="E78" t="n">
-        <v>91.621962595572</v>
+        <v>91.62195496693603</v>
       </c>
       <c r="F78" t="n">
-        <v>91.63107299804688</v>
+        <v>91.63106536865234</v>
       </c>
       <c r="G78" t="n">
         <v>3547400</v>
@@ -2243,16 +2243,16 @@
         <v>45405</v>
       </c>
       <c r="C79" t="n">
-        <v>91.64017486572266</v>
+        <v>91.64019012451172</v>
       </c>
       <c r="D79" t="n">
-        <v>91.64928526734903</v>
+        <v>91.64930052765506</v>
       </c>
       <c r="E79" t="n">
-        <v>91.63106446409627</v>
+        <v>91.63107972136839</v>
       </c>
       <c r="F79" t="n">
-        <v>91.64017486572266</v>
+        <v>91.64019012451172</v>
       </c>
       <c r="G79" t="n">
         <v>4233300</v>
@@ -2266,16 +2266,16 @@
         <v>45406</v>
       </c>
       <c r="C80" t="n">
-        <v>91.64927673339844</v>
+        <v>91.64928436279297</v>
       </c>
       <c r="D80" t="n">
-        <v>91.65838018497682</v>
+        <v>91.65838781512917</v>
       </c>
       <c r="E80" t="n">
-        <v>91.64927673339844</v>
+        <v>91.64928436279297</v>
       </c>
       <c r="F80" t="n">
-        <v>91.65838018497682</v>
+        <v>91.65838781512917</v>
       </c>
       <c r="G80" t="n">
         <v>3200000</v>
@@ -2289,16 +2289,16 @@
         <v>45407</v>
       </c>
       <c r="C81" t="n">
-        <v>91.69481658935547</v>
+        <v>91.69482421875</v>
       </c>
       <c r="D81" t="n">
-        <v>91.69481658935547</v>
+        <v>91.69482421875</v>
       </c>
       <c r="E81" t="n">
-        <v>91.68571313760329</v>
+        <v>91.68572076624038</v>
       </c>
       <c r="F81" t="n">
-        <v>91.69481658935547</v>
+        <v>91.69482421875</v>
       </c>
       <c r="G81" t="n">
         <v>2705900</v>
@@ -2312,16 +2312,16 @@
         <v>45408</v>
       </c>
       <c r="C82" t="n">
-        <v>91.71302795410156</v>
+        <v>91.71303558349609</v>
       </c>
       <c r="D82" t="n">
-        <v>91.71302795410156</v>
+        <v>91.71303558349609</v>
       </c>
       <c r="E82" t="n">
-        <v>91.70391755408703</v>
+        <v>91.70392518272369</v>
       </c>
       <c r="F82" t="n">
-        <v>91.70391755408703</v>
+        <v>91.70392518272369</v>
       </c>
       <c r="G82" t="n">
         <v>3008600</v>
@@ -2335,16 +2335,16 @@
         <v>45411</v>
       </c>
       <c r="C83" t="n">
-        <v>91.71302795410156</v>
+        <v>91.71303558349609</v>
       </c>
       <c r="D83" t="n">
-        <v>91.72213140491701</v>
+        <v>91.72213903506884</v>
       </c>
       <c r="E83" t="n">
-        <v>91.71302795410156</v>
+        <v>91.71303558349609</v>
       </c>
       <c r="F83" t="n">
-        <v>91.72213140491701</v>
+        <v>91.72213903506884</v>
       </c>
       <c r="G83" t="n">
         <v>2501900</v>
@@ -2358,16 +2358,16 @@
         <v>45412</v>
       </c>
       <c r="C84" t="n">
-        <v>91.72216033935547</v>
+        <v>91.72215270996094</v>
       </c>
       <c r="D84" t="n">
-        <v>91.73127074224395</v>
+        <v>91.73126311209163</v>
       </c>
       <c r="E84" t="n">
-        <v>91.72216033935547</v>
+        <v>91.72215270996094</v>
       </c>
       <c r="F84" t="n">
-        <v>91.72216033935547</v>
+        <v>91.72215270996094</v>
       </c>
       <c r="G84" t="n">
         <v>6488000</v>
@@ -2381,16 +2381,16 @@
         <v>45413</v>
       </c>
       <c r="C85" t="n">
-        <v>91.75688934326172</v>
+        <v>91.75691986083984</v>
       </c>
       <c r="D85" t="n">
-        <v>91.75688934326172</v>
+        <v>91.75691986083984</v>
       </c>
       <c r="E85" t="n">
-        <v>91.74774703561437</v>
+        <v>91.74777755015184</v>
       </c>
       <c r="F85" t="n">
-        <v>91.75688934326172</v>
+        <v>91.75691986083984</v>
       </c>
       <c r="G85" t="n">
         <v>8406600</v>
@@ -2404,16 +2404,16 @@
         <v>45414</v>
       </c>
       <c r="C86" t="n">
-        <v>91.79348754882812</v>
+        <v>91.79349517822266</v>
       </c>
       <c r="D86" t="n">
-        <v>91.79348754882812</v>
+        <v>91.79349517822266</v>
       </c>
       <c r="E86" t="n">
-        <v>91.78433826151877</v>
+        <v>91.78434589015285</v>
       </c>
       <c r="F86" t="n">
-        <v>91.79348754882812</v>
+        <v>91.79349517822266</v>
       </c>
       <c r="G86" t="n">
         <v>4369600</v>
@@ -2496,16 +2496,16 @@
         <v>45420</v>
       </c>
       <c r="C90" t="n">
-        <v>91.84838104248047</v>
+        <v>91.84840393066406</v>
       </c>
       <c r="D90" t="n">
-        <v>91.84838104248047</v>
+        <v>91.84840393066406</v>
       </c>
       <c r="E90" t="n">
-        <v>91.8300824669157</v>
+        <v>91.83010535053937</v>
       </c>
       <c r="F90" t="n">
-        <v>91.83923175469809</v>
+        <v>91.83925464060172</v>
       </c>
       <c r="G90" t="n">
         <v>3109400</v>
@@ -2542,16 +2542,16 @@
         <v>45422</v>
       </c>
       <c r="C92" t="n">
-        <v>91.90326690673828</v>
+        <v>91.90325927734375</v>
       </c>
       <c r="D92" t="n">
-        <v>91.90326690673828</v>
+        <v>91.90325927734375</v>
       </c>
       <c r="E92" t="n">
-        <v>91.88496833035812</v>
+        <v>91.88496070248264</v>
       </c>
       <c r="F92" t="n">
-        <v>91.90326690673828</v>
+        <v>91.90325927734375</v>
       </c>
       <c r="G92" t="n">
         <v>3005800</v>
@@ -2611,16 +2611,16 @@
         <v>45427</v>
       </c>
       <c r="C95" t="n">
-        <v>91.93070220947266</v>
+        <v>91.93070983886719</v>
       </c>
       <c r="D95" t="n">
-        <v>91.93985149710711</v>
+        <v>91.93985912726093</v>
       </c>
       <c r="E95" t="n">
-        <v>91.93070220947266</v>
+        <v>91.93070983886719</v>
       </c>
       <c r="F95" t="n">
-        <v>91.93070220947266</v>
+        <v>91.93070983886719</v>
       </c>
       <c r="G95" t="n">
         <v>4228600</v>
@@ -2634,16 +2634,16 @@
         <v>45428</v>
       </c>
       <c r="C96" t="n">
-        <v>91.9764404296875</v>
+        <v>91.97644805908203</v>
       </c>
       <c r="D96" t="n">
-        <v>91.98558273833711</v>
+        <v>91.98559036849001</v>
       </c>
       <c r="E96" t="n">
-        <v>91.96729114217631</v>
+        <v>91.96729877081192</v>
       </c>
       <c r="F96" t="n">
-        <v>91.9764404296875</v>
+        <v>91.97644805908203</v>
       </c>
       <c r="G96" t="n">
         <v>3699500</v>
@@ -2657,16 +2657,16 @@
         <v>45429</v>
       </c>
       <c r="C97" t="n">
-        <v>91.985595703125</v>
+        <v>91.98558807373047</v>
       </c>
       <c r="D97" t="n">
-        <v>91.99474499192573</v>
+        <v>91.99473736177234</v>
       </c>
       <c r="E97" t="n">
-        <v>91.985595703125</v>
+        <v>91.98558807373047</v>
       </c>
       <c r="F97" t="n">
-        <v>91.99474499192573</v>
+        <v>91.99473736177234</v>
       </c>
       <c r="G97" t="n">
         <v>4544200</v>
@@ -2726,16 +2726,16 @@
         <v>45434</v>
       </c>
       <c r="C100" t="n">
-        <v>92.02217864990234</v>
+        <v>92.02218627929688</v>
       </c>
       <c r="D100" t="n">
-        <v>92.03132793798427</v>
+        <v>92.03133556813735</v>
       </c>
       <c r="E100" t="n">
-        <v>92.02217864990234</v>
+        <v>92.02218627929688</v>
       </c>
       <c r="F100" t="n">
-        <v>92.03132793798427</v>
+        <v>92.03133556813735</v>
       </c>
       <c r="G100" t="n">
         <v>2609000</v>
@@ -2749,16 +2749,16 @@
         <v>45435</v>
       </c>
       <c r="C101" t="n">
-        <v>92.08619689941406</v>
+        <v>92.08621215820312</v>
       </c>
       <c r="D101" t="n">
-        <v>92.08619689941406</v>
+        <v>92.08621215820312</v>
       </c>
       <c r="E101" t="n">
-        <v>92.07705459146585</v>
+        <v>92.07706984874001</v>
       </c>
       <c r="F101" t="n">
-        <v>92.07705459146585</v>
+        <v>92.07706984874001</v>
       </c>
       <c r="G101" t="n">
         <v>3077800</v>
@@ -2772,16 +2772,16 @@
         <v>45436</v>
       </c>
       <c r="C102" t="n">
-        <v>92.09538269042969</v>
+        <v>92.09535217285156</v>
       </c>
       <c r="D102" t="n">
-        <v>92.09538269042969</v>
+        <v>92.09535217285156</v>
       </c>
       <c r="E102" t="n">
-        <v>92.0862333999939</v>
+        <v>92.08620288544756</v>
       </c>
       <c r="F102" t="n">
-        <v>92.09538269042969</v>
+        <v>92.09535217285156</v>
       </c>
       <c r="G102" t="n">
         <v>2512800</v>
@@ -2795,16 +2795,16 @@
         <v>45440</v>
       </c>
       <c r="C103" t="n">
-        <v>92.10449981689453</v>
+        <v>92.10451507568359</v>
       </c>
       <c r="D103" t="n">
-        <v>92.10449981689453</v>
+        <v>92.10451507568359</v>
       </c>
       <c r="E103" t="n">
-        <v>92.09535052965379</v>
+        <v>92.0953657869271</v>
       </c>
       <c r="F103" t="n">
-        <v>92.09535052965379</v>
+        <v>92.0953657869271</v>
       </c>
       <c r="G103" t="n">
         <v>3684600</v>
@@ -2818,16 +2818,16 @@
         <v>45441</v>
       </c>
       <c r="C104" t="n">
-        <v>92.10449981689453</v>
+        <v>92.10451507568359</v>
       </c>
       <c r="D104" t="n">
-        <v>92.11364212527393</v>
+        <v>92.11365738557757</v>
       </c>
       <c r="E104" t="n">
-        <v>92.10449981689453</v>
+        <v>92.10451507568359</v>
       </c>
       <c r="F104" t="n">
-        <v>92.11364212527393</v>
+        <v>92.11365738557757</v>
       </c>
       <c r="G104" t="n">
         <v>3971700</v>
@@ -2841,16 +2841,16 @@
         <v>45442</v>
       </c>
       <c r="C105" t="n">
-        <v>92.12279510498047</v>
+        <v>92.12281036376953</v>
       </c>
       <c r="D105" t="n">
-        <v>92.13194439258794</v>
+        <v>92.13195965289245</v>
       </c>
       <c r="E105" t="n">
-        <v>92.12279510498047</v>
+        <v>92.12281036376953</v>
       </c>
       <c r="F105" t="n">
-        <v>92.12279510498047</v>
+        <v>92.12281036376953</v>
       </c>
       <c r="G105" t="n">
         <v>3566800</v>
@@ -2864,16 +2864,16 @@
         <v>45443</v>
       </c>
       <c r="C106" t="n">
-        <v>92.15940093994141</v>
+        <v>92.15937805175781</v>
       </c>
       <c r="D106" t="n">
-        <v>92.15940093994141</v>
+        <v>92.15937805175781</v>
       </c>
       <c r="E106" t="n">
-        <v>92.15025165077893</v>
+        <v>92.15022876486761</v>
       </c>
       <c r="F106" t="n">
-        <v>92.15025165077893</v>
+        <v>92.15022876486761</v>
       </c>
       <c r="G106" t="n">
         <v>7082900</v>
@@ -2887,16 +2887,16 @@
         <v>45446</v>
       </c>
       <c r="C107" t="n">
-        <v>92.17777252197266</v>
+        <v>92.17775726318359</v>
       </c>
       <c r="D107" t="n">
-        <v>92.18695493362199</v>
+        <v>92.18693967331291</v>
       </c>
       <c r="E107" t="n">
-        <v>92.17777252197266</v>
+        <v>92.17775726318359</v>
       </c>
       <c r="F107" t="n">
-        <v>92.17777252197266</v>
+        <v>92.17775726318359</v>
       </c>
       <c r="G107" t="n">
         <v>9568200</v>
@@ -2979,16 +2979,16 @@
         <v>45450</v>
       </c>
       <c r="C111" t="n">
-        <v>92.25125122070312</v>
+        <v>92.25127410888672</v>
       </c>
       <c r="D111" t="n">
-        <v>92.26043363009782</v>
+        <v>92.26045652055964</v>
       </c>
       <c r="E111" t="n">
-        <v>92.25125122070312</v>
+        <v>92.25127410888672</v>
       </c>
       <c r="F111" t="n">
-        <v>92.26043363009782</v>
+        <v>92.26045652055964</v>
       </c>
       <c r="G111" t="n">
         <v>3490400</v>
@@ -3002,16 +3002,16 @@
         <v>45453</v>
       </c>
       <c r="C112" t="n">
-        <v>92.26963806152344</v>
+        <v>92.26964569091797</v>
       </c>
       <c r="D112" t="n">
-        <v>92.27882748188611</v>
+        <v>92.27883511204048</v>
       </c>
       <c r="E112" t="n">
-        <v>92.26963806152344</v>
+        <v>92.26964569091797</v>
       </c>
       <c r="F112" t="n">
-        <v>92.27882748188611</v>
+        <v>92.27883511204048</v>
       </c>
       <c r="G112" t="n">
         <v>2732300</v>
@@ -3025,16 +3025,16 @@
         <v>45454</v>
       </c>
       <c r="C113" t="n">
-        <v>92.28800201416016</v>
+        <v>92.28799438476562</v>
       </c>
       <c r="D113" t="n">
-        <v>92.28800201416016</v>
+        <v>92.28799438476562</v>
       </c>
       <c r="E113" t="n">
-        <v>92.27881960405534</v>
+        <v>92.27881197541993</v>
       </c>
       <c r="F113" t="n">
-        <v>92.28800201416016</v>
+        <v>92.28799438476562</v>
       </c>
       <c r="G113" t="n">
         <v>3320000</v>
@@ -3048,16 +3048,16 @@
         <v>45455</v>
       </c>
       <c r="C114" t="n">
-        <v>92.306396484375</v>
+        <v>92.30638122558594</v>
       </c>
       <c r="D114" t="n">
-        <v>92.306396484375</v>
+        <v>92.30638122558594</v>
       </c>
       <c r="E114" t="n">
-        <v>92.28801764210641</v>
+        <v>92.28800238635547</v>
       </c>
       <c r="F114" t="n">
-        <v>92.29720706324071</v>
+        <v>92.2971918059707</v>
       </c>
       <c r="G114" t="n">
         <v>5355700</v>
@@ -3071,16 +3071,16 @@
         <v>45456</v>
       </c>
       <c r="C115" t="n">
-        <v>92.31558227539062</v>
+        <v>92.31556701660156</v>
       </c>
       <c r="D115" t="n">
-        <v>92.32476468668929</v>
+        <v>92.32474942638248</v>
       </c>
       <c r="E115" t="n">
-        <v>92.30639285461768</v>
+        <v>92.30637759734753</v>
       </c>
       <c r="F115" t="n">
-        <v>92.31558227539062</v>
+        <v>92.31556701660156</v>
       </c>
       <c r="G115" t="n">
         <v>3925700</v>
@@ -3094,16 +3094,16 @@
         <v>45457</v>
       </c>
       <c r="C116" t="n">
-        <v>92.36151123046875</v>
+        <v>92.36151885986328</v>
       </c>
       <c r="D116" t="n">
-        <v>92.36151123046875</v>
+        <v>92.36151885986328</v>
       </c>
       <c r="E116" t="n">
-        <v>92.34313939921861</v>
+        <v>92.34314702709557</v>
       </c>
       <c r="F116" t="n">
-        <v>92.3523218101067</v>
+        <v>92.35232943874216</v>
       </c>
       <c r="G116" t="n">
         <v>3505500</v>
@@ -3117,16 +3117,16 @@
         <v>45460</v>
       </c>
       <c r="C117" t="n">
-        <v>92.37071228027344</v>
+        <v>92.37071990966797</v>
       </c>
       <c r="D117" t="n">
-        <v>92.37071228027344</v>
+        <v>92.37071990966797</v>
       </c>
       <c r="E117" t="n">
-        <v>92.36152285875446</v>
+        <v>92.36153048738997</v>
       </c>
       <c r="F117" t="n">
-        <v>92.37071228027344</v>
+        <v>92.37071990966797</v>
       </c>
       <c r="G117" t="n">
         <v>3493700</v>
@@ -3140,16 +3140,16 @@
         <v>45461</v>
       </c>
       <c r="C118" t="n">
-        <v>92.39827728271484</v>
+        <v>92.39826965332031</v>
       </c>
       <c r="D118" t="n">
-        <v>92.39827728271484</v>
+        <v>92.39826965332031</v>
       </c>
       <c r="E118" t="n">
-        <v>92.38908786082315</v>
+        <v>92.3890802321874</v>
       </c>
       <c r="F118" t="n">
-        <v>92.39827728271484</v>
+        <v>92.39826965332031</v>
       </c>
       <c r="G118" t="n">
         <v>2972000</v>
@@ -3186,16 +3186,16 @@
         <v>45464</v>
       </c>
       <c r="C120" t="n">
-        <v>92.44420623779297</v>
+        <v>92.44422149658203</v>
       </c>
       <c r="D120" t="n">
-        <v>92.45338864910251</v>
+        <v>92.45340390940721</v>
       </c>
       <c r="E120" t="n">
-        <v>92.44420623779297</v>
+        <v>92.44422149658203</v>
       </c>
       <c r="F120" t="n">
-        <v>92.44420623779297</v>
+        <v>92.44422149658203</v>
       </c>
       <c r="G120" t="n">
         <v>3460900</v>
@@ -3209,16 +3209,16 @@
         <v>45467</v>
       </c>
       <c r="C121" t="n">
-        <v>92.45339965820312</v>
+        <v>92.45339202880859</v>
       </c>
       <c r="D121" t="n">
-        <v>92.4625890800812</v>
+        <v>92.46258144992834</v>
       </c>
       <c r="E121" t="n">
-        <v>92.45339965820312</v>
+        <v>92.45339202880859</v>
       </c>
       <c r="F121" t="n">
-        <v>92.4625890800812</v>
+        <v>92.46258144992834</v>
       </c>
       <c r="G121" t="n">
         <v>3369500</v>
@@ -3232,16 +3232,16 @@
         <v>45468</v>
       </c>
       <c r="C122" t="n">
-        <v>92.47175598144531</v>
+        <v>92.47176361083984</v>
       </c>
       <c r="D122" t="n">
-        <v>92.47175598144531</v>
+        <v>92.47176361083984</v>
       </c>
       <c r="E122" t="n">
-        <v>92.46256656180523</v>
+        <v>92.46257419044157</v>
       </c>
       <c r="F122" t="n">
-        <v>92.47175598144531</v>
+        <v>92.47176361083984</v>
       </c>
       <c r="G122" t="n">
         <v>3561700</v>
@@ -3278,16 +3278,16 @@
         <v>45470</v>
       </c>
       <c r="C124" t="n">
-        <v>92.49013519287109</v>
+        <v>92.49014282226562</v>
       </c>
       <c r="D124" t="n">
-        <v>92.4993246132446</v>
+        <v>92.49933224339715</v>
       </c>
       <c r="E124" t="n">
-        <v>92.49013519287109</v>
+        <v>92.49014282226562</v>
       </c>
       <c r="F124" t="n">
-        <v>92.4993246132446</v>
+        <v>92.49933224339715</v>
       </c>
       <c r="G124" t="n">
         <v>3349900</v>
@@ -3301,16 +3301,16 @@
         <v>45471</v>
       </c>
       <c r="C125" t="n">
-        <v>92.52689361572266</v>
+        <v>92.52690124511719</v>
       </c>
       <c r="D125" t="n">
-        <v>92.53608303686593</v>
+        <v>92.53609066701819</v>
       </c>
       <c r="E125" t="n">
-        <v>92.52689361572266</v>
+        <v>92.52690124511719</v>
       </c>
       <c r="F125" t="n">
-        <v>92.52689361572266</v>
+        <v>92.52690124511719</v>
       </c>
       <c r="G125" t="n">
         <v>7427800</v>
@@ -3347,16 +3347,16 @@
         <v>45475</v>
       </c>
       <c r="C127" t="n">
-        <v>92.57210540771484</v>
+        <v>92.57209777832031</v>
       </c>
       <c r="D127" t="n">
-        <v>92.57210540771484</v>
+        <v>92.57209777832031</v>
       </c>
       <c r="E127" t="n">
-        <v>92.56287575448273</v>
+        <v>92.56286812584887</v>
       </c>
       <c r="F127" t="n">
-        <v>92.57210540771484</v>
+        <v>92.57209777832031</v>
       </c>
       <c r="G127" t="n">
         <v>5720900</v>
@@ -3370,16 +3370,16 @@
         <v>45476</v>
       </c>
       <c r="C128" t="n">
-        <v>92.59979248046875</v>
+        <v>92.59978485107422</v>
       </c>
       <c r="D128" t="n">
-        <v>92.59979248046875</v>
+        <v>92.59978485107422</v>
       </c>
       <c r="E128" t="n">
-        <v>92.590562826723</v>
+        <v>92.59055519808891</v>
       </c>
       <c r="F128" t="n">
-        <v>92.59979248046875</v>
+        <v>92.59978485107422</v>
       </c>
       <c r="G128" t="n">
         <v>3986000</v>
@@ -3393,16 +3393,16 @@
         <v>45478</v>
       </c>
       <c r="C129" t="n">
-        <v>92.63670349121094</v>
+        <v>92.63672637939453</v>
       </c>
       <c r="D129" t="n">
-        <v>92.63670349121094</v>
+        <v>92.63672637939453</v>
       </c>
       <c r="E129" t="n">
-        <v>92.62747383752138</v>
+        <v>92.62749672342457</v>
       </c>
       <c r="F129" t="n">
-        <v>92.62747383752138</v>
+        <v>92.62749672342457</v>
       </c>
       <c r="G129" t="n">
         <v>3742000</v>
@@ -3416,16 +3416,16 @@
         <v>45481</v>
       </c>
       <c r="C130" t="n">
-        <v>92.6551513671875</v>
+        <v>92.65515899658203</v>
       </c>
       <c r="D130" t="n">
-        <v>92.6551513671875</v>
+        <v>92.65515899658203</v>
       </c>
       <c r="E130" t="n">
-        <v>92.64592171463667</v>
+        <v>92.64592934327121</v>
       </c>
       <c r="F130" t="n">
-        <v>92.64592171463667</v>
+        <v>92.64592934327121</v>
       </c>
       <c r="G130" t="n">
         <v>3263000</v>
@@ -3439,16 +3439,16 @@
         <v>45482</v>
       </c>
       <c r="C131" t="n">
-        <v>92.6551513671875</v>
+        <v>92.65515899658203</v>
       </c>
       <c r="D131" t="n">
-        <v>92.67360363212704</v>
+        <v>92.67361126304097</v>
       </c>
       <c r="E131" t="n">
-        <v>92.6551513671875</v>
+        <v>92.65515899658203</v>
       </c>
       <c r="F131" t="n">
-        <v>92.66437397957621</v>
+        <v>92.66438160973014</v>
       </c>
       <c r="G131" t="n">
         <v>4508000</v>
@@ -3462,16 +3462,16 @@
         <v>45483</v>
       </c>
       <c r="C132" t="n">
-        <v>92.67362213134766</v>
+        <v>92.67361450195312</v>
       </c>
       <c r="D132" t="n">
-        <v>92.68285178574088</v>
+        <v>92.68284415558651</v>
       </c>
       <c r="E132" t="n">
-        <v>92.67362213134766</v>
+        <v>92.67361450195312</v>
       </c>
       <c r="F132" t="n">
-        <v>92.67362213134766</v>
+        <v>92.67361450195312</v>
       </c>
       <c r="G132" t="n">
         <v>4062200</v>
@@ -3485,16 +3485,16 @@
         <v>45484</v>
       </c>
       <c r="C133" t="n">
-        <v>92.69205474853516</v>
+        <v>92.69207000732422</v>
       </c>
       <c r="D133" t="n">
-        <v>92.69205474853516</v>
+        <v>92.69207000732422</v>
       </c>
       <c r="E133" t="n">
-        <v>92.68283213626073</v>
+        <v>92.68284739353157</v>
       </c>
       <c r="F133" t="n">
-        <v>92.68283213626073</v>
+        <v>92.68284739353157</v>
       </c>
       <c r="G133" t="n">
         <v>4195600</v>
@@ -3554,16 +3554,16 @@
         <v>45489</v>
       </c>
       <c r="C136" t="n">
-        <v>92.75667572021484</v>
+        <v>92.75666809082031</v>
       </c>
       <c r="D136" t="n">
-        <v>92.75667572021484</v>
+        <v>92.75666809082031</v>
       </c>
       <c r="E136" t="n">
-        <v>92.74745310520764</v>
+        <v>92.74744547657168</v>
       </c>
       <c r="F136" t="n">
-        <v>92.75667572021484</v>
+        <v>92.75666809082031</v>
       </c>
       <c r="G136" t="n">
         <v>3622900</v>
@@ -3577,16 +3577,16 @@
         <v>45490</v>
       </c>
       <c r="C137" t="n">
-        <v>92.76588439941406</v>
+        <v>92.76587677001953</v>
       </c>
       <c r="D137" t="n">
-        <v>92.77050274603751</v>
+        <v>92.77049511626313</v>
       </c>
       <c r="E137" t="n">
-        <v>92.75665474632972</v>
+        <v>92.75664711769426</v>
       </c>
       <c r="F137" t="n">
-        <v>92.76588439941406</v>
+        <v>92.76587677001953</v>
       </c>
       <c r="G137" t="n">
         <v>3822100</v>
@@ -3646,16 +3646,16 @@
         <v>45495</v>
       </c>
       <c r="C140" t="n">
-        <v>92.83971405029297</v>
+        <v>92.8397216796875</v>
       </c>
       <c r="D140" t="n">
-        <v>92.83971405029297</v>
+        <v>92.8397216796875</v>
       </c>
       <c r="E140" t="n">
-        <v>92.83048439656177</v>
+        <v>92.83049202519783</v>
       </c>
       <c r="F140" t="n">
-        <v>92.83971405029297</v>
+        <v>92.8397216796875</v>
       </c>
       <c r="G140" t="n">
         <v>3386500</v>
@@ -3669,16 +3669,16 @@
         <v>45496</v>
       </c>
       <c r="C141" t="n">
-        <v>92.84894561767578</v>
+        <v>92.84893798828125</v>
       </c>
       <c r="D141" t="n">
-        <v>92.85816823143402</v>
+        <v>92.85816060128167</v>
       </c>
       <c r="E141" t="n">
-        <v>92.83971596375436</v>
+        <v>92.83970833511823</v>
       </c>
       <c r="F141" t="n">
-        <v>92.84894561767578</v>
+        <v>92.84893798828125</v>
       </c>
       <c r="G141" t="n">
         <v>2829200</v>
@@ -3692,16 +3692,16 @@
         <v>45497</v>
       </c>
       <c r="C142" t="n">
-        <v>92.858154296875</v>
+        <v>92.85816192626953</v>
       </c>
       <c r="D142" t="n">
-        <v>92.86738394941139</v>
+        <v>92.86739157956426</v>
       </c>
       <c r="E142" t="n">
-        <v>92.84893168450073</v>
+        <v>92.84893931313751</v>
       </c>
       <c r="F142" t="n">
-        <v>92.858154296875</v>
+        <v>92.85816192626953</v>
       </c>
       <c r="G142" t="n">
         <v>3474500</v>
@@ -3715,16 +3715,16 @@
         <v>45498</v>
       </c>
       <c r="C143" t="n">
-        <v>92.87662506103516</v>
+        <v>92.87661743164062</v>
       </c>
       <c r="D143" t="n">
-        <v>92.87662506103516</v>
+        <v>92.87661743164062</v>
       </c>
       <c r="E143" t="n">
-        <v>92.86739540736002</v>
+        <v>92.86738777872365</v>
       </c>
       <c r="F143" t="n">
-        <v>92.87662506103516</v>
+        <v>92.87661743164062</v>
       </c>
       <c r="G143" t="n">
         <v>3521700</v>
@@ -3738,16 +3738,16 @@
         <v>45499</v>
       </c>
       <c r="C144" t="n">
-        <v>92.90428924560547</v>
+        <v>92.90430450439453</v>
       </c>
       <c r="D144" t="n">
-        <v>92.91351889751859</v>
+        <v>92.91353415782355</v>
       </c>
       <c r="E144" t="n">
-        <v>92.90428924560547</v>
+        <v>92.90430450439453</v>
       </c>
       <c r="F144" t="n">
-        <v>92.90428924560547</v>
+        <v>92.90430450439453</v>
       </c>
       <c r="G144" t="n">
         <v>3172600</v>
@@ -3807,16 +3807,16 @@
         <v>45504</v>
       </c>
       <c r="C147" t="n">
-        <v>92.94122314453125</v>
+        <v>92.94121551513672</v>
       </c>
       <c r="D147" t="n">
-        <v>92.95045279866203</v>
+        <v>92.95044516850984</v>
       </c>
       <c r="E147" t="n">
-        <v>92.94122314453125</v>
+        <v>92.94121551513672</v>
       </c>
       <c r="F147" t="n">
-        <v>92.94122314453125</v>
+        <v>92.94121551513672</v>
       </c>
       <c r="G147" t="n">
         <v>7256900</v>
@@ -3830,16 +3830,16 @@
         <v>45505</v>
       </c>
       <c r="C148" t="n">
-        <v>92.97180938720703</v>
+        <v>92.97179412841797</v>
       </c>
       <c r="D148" t="n">
-        <v>92.97180938720703</v>
+        <v>92.97179412841797</v>
       </c>
       <c r="E148" t="n">
-        <v>92.96253803451719</v>
+        <v>92.96252277724977</v>
       </c>
       <c r="F148" t="n">
-        <v>92.97180938720703</v>
+        <v>92.97179412841797</v>
       </c>
       <c r="G148" t="n">
         <v>11015600</v>
@@ -3853,16 +3853,16 @@
         <v>45506</v>
       </c>
       <c r="C149" t="n">
-        <v>93.01816558837891</v>
+        <v>93.01814270019531</v>
       </c>
       <c r="D149" t="n">
-        <v>93.01816558837891</v>
+        <v>93.01814270019531</v>
       </c>
       <c r="E149" t="n">
-        <v>92.99962995226285</v>
+        <v>92.99960706864016</v>
       </c>
       <c r="F149" t="n">
-        <v>93.00889423433536</v>
+        <v>93.00887134843308</v>
       </c>
       <c r="G149" t="n">
         <v>7927400</v>
@@ -3876,16 +3876,16 @@
         <v>45509</v>
       </c>
       <c r="C150" t="n">
-        <v>93.02742004394531</v>
+        <v>93.02741241455078</v>
       </c>
       <c r="D150" t="n">
-        <v>93.04595567669436</v>
+        <v>93.04594804577968</v>
       </c>
       <c r="E150" t="n">
-        <v>93.01814869158591</v>
+        <v>93.01814106295174</v>
       </c>
       <c r="F150" t="n">
-        <v>93.01814869158591</v>
+        <v>93.01814106295174</v>
       </c>
       <c r="G150" t="n">
         <v>8712900</v>
@@ -3945,16 +3945,16 @@
         <v>45512</v>
       </c>
       <c r="C153" t="n">
-        <v>93.07377624511719</v>
+        <v>93.07375335693359</v>
       </c>
       <c r="D153" t="n">
-        <v>93.07377624511719</v>
+        <v>93.07375335693359</v>
       </c>
       <c r="E153" t="n">
-        <v>93.05523353910115</v>
+        <v>93.05521065547747</v>
       </c>
       <c r="F153" t="n">
-        <v>93.06450489210917</v>
+        <v>93.06448200620552</v>
       </c>
       <c r="G153" t="n">
         <v>3903300</v>
@@ -3968,16 +3968,16 @@
         <v>45513</v>
       </c>
       <c r="C154" t="n">
-        <v>93.10157775878906</v>
+        <v>93.10158538818359</v>
       </c>
       <c r="D154" t="n">
-        <v>93.11084203928218</v>
+        <v>93.11084966943589</v>
       </c>
       <c r="E154" t="n">
-        <v>93.0923064063261</v>
+        <v>93.09231403496088</v>
       </c>
       <c r="F154" t="n">
-        <v>93.10157775878906</v>
+        <v>93.10158538818359</v>
       </c>
       <c r="G154" t="n">
         <v>5548300</v>
@@ -3991,16 +3991,16 @@
         <v>45516</v>
       </c>
       <c r="C155" t="n">
-        <v>93.12009429931641</v>
+        <v>93.12010955810547</v>
       </c>
       <c r="D155" t="n">
-        <v>93.12936564987847</v>
+        <v>93.12938091018674</v>
       </c>
       <c r="E155" t="n">
-        <v>93.11082294875435</v>
+        <v>93.1108382060242</v>
       </c>
       <c r="F155" t="n">
-        <v>93.12009429931641</v>
+        <v>93.12010955810547</v>
       </c>
       <c r="G155" t="n">
         <v>3845400</v>
@@ -4014,16 +4014,16 @@
         <v>45517</v>
       </c>
       <c r="C156" t="n">
-        <v>93.13864135742188</v>
+        <v>93.13865661621094</v>
       </c>
       <c r="D156" t="n">
-        <v>93.13864135742188</v>
+        <v>93.13865661621094</v>
       </c>
       <c r="E156" t="n">
-        <v>93.12937000642611</v>
+        <v>93.12938526369626</v>
       </c>
       <c r="F156" t="n">
-        <v>93.13864135742188</v>
+        <v>93.13865661621094</v>
       </c>
       <c r="G156" t="n">
         <v>4782200</v>
@@ -4037,16 +4037,16 @@
         <v>45518</v>
       </c>
       <c r="C157" t="n">
-        <v>93.15718841552734</v>
+        <v>93.15718078613281</v>
       </c>
       <c r="D157" t="n">
-        <v>93.15718841552734</v>
+        <v>93.15718078613281</v>
       </c>
       <c r="E157" t="n">
-        <v>93.13865278323068</v>
+        <v>93.13864515535418</v>
       </c>
       <c r="F157" t="n">
-        <v>93.14791706339422</v>
+        <v>93.14790943475899</v>
       </c>
       <c r="G157" t="n">
         <v>4327700</v>
@@ -4060,16 +4060,16 @@
         <v>45519</v>
       </c>
       <c r="C158" t="n">
-        <v>93.16647338867188</v>
+        <v>93.16648101806641</v>
       </c>
       <c r="D158" t="n">
-        <v>93.16647338867188</v>
+        <v>93.16648101806641</v>
       </c>
       <c r="E158" t="n">
-        <v>93.14793068169466</v>
+        <v>93.14793830957073</v>
       </c>
       <c r="F158" t="n">
-        <v>93.14793068169466</v>
+        <v>93.14793830957073</v>
       </c>
       <c r="G158" t="n">
         <v>4217800</v>
@@ -4083,16 +4083,16 @@
         <v>45520</v>
       </c>
       <c r="C159" t="n">
-        <v>93.20355224609375</v>
+        <v>93.20354461669922</v>
       </c>
       <c r="D159" t="n">
-        <v>93.20355224609375</v>
+        <v>93.20354461669922</v>
       </c>
       <c r="E159" t="n">
-        <v>93.19428089255386</v>
+        <v>93.19427326391828</v>
       </c>
       <c r="F159" t="n">
-        <v>93.20355224609375</v>
+        <v>93.20354461669922</v>
       </c>
       <c r="G159" t="n">
         <v>3638900</v>
@@ -4106,16 +4106,16 @@
         <v>45523</v>
       </c>
       <c r="C160" t="n">
-        <v>93.21280670166016</v>
+        <v>93.21279907226562</v>
       </c>
       <c r="D160" t="n">
-        <v>93.22207805422271</v>
+        <v>93.22207042406932</v>
       </c>
       <c r="E160" t="n">
-        <v>93.21280670166016</v>
+        <v>93.21279907226562</v>
       </c>
       <c r="F160" t="n">
-        <v>93.21280670166016</v>
+        <v>93.21279907226562</v>
       </c>
       <c r="G160" t="n">
         <v>3930700</v>
@@ -4129,16 +4129,16 @@
         <v>45524</v>
       </c>
       <c r="C161" t="n">
-        <v>93.22208404541016</v>
+        <v>93.22207641601562</v>
       </c>
       <c r="D161" t="n">
-        <v>93.23135539856855</v>
+        <v>93.23134776841523</v>
       </c>
       <c r="E161" t="n">
-        <v>93.22208404541016</v>
+        <v>93.22207641601562</v>
       </c>
       <c r="F161" t="n">
-        <v>93.23135539856855</v>
+        <v>93.23134776841523</v>
       </c>
       <c r="G161" t="n">
         <v>3084200</v>
@@ -4152,16 +4152,16 @@
         <v>45525</v>
       </c>
       <c r="C162" t="n">
-        <v>93.24986267089844</v>
+        <v>93.2498779296875</v>
       </c>
       <c r="D162" t="n">
-        <v>93.24986267089844</v>
+        <v>93.2498779296875</v>
       </c>
       <c r="E162" t="n">
-        <v>93.23132704218965</v>
+        <v>93.23134229794566</v>
       </c>
       <c r="F162" t="n">
-        <v>93.23132704218965</v>
+        <v>93.23134229794566</v>
       </c>
       <c r="G162" t="n">
         <v>3936000</v>
@@ -4175,16 +4175,16 @@
         <v>45526</v>
       </c>
       <c r="C163" t="n">
-        <v>93.24986267089844</v>
+        <v>93.2498779296875</v>
       </c>
       <c r="D163" t="n">
-        <v>93.25913402123695</v>
+        <v>93.2591492815431</v>
       </c>
       <c r="E163" t="n">
-        <v>93.24986267089844</v>
+        <v>93.2498779296875</v>
       </c>
       <c r="F163" t="n">
-        <v>93.25913402123695</v>
+        <v>93.2591492815431</v>
       </c>
       <c r="G163" t="n">
         <v>3849100</v>
@@ -4244,16 +4244,16 @@
         <v>45531</v>
       </c>
       <c r="C166" t="n">
-        <v>93.31478881835938</v>
+        <v>93.31477355957031</v>
       </c>
       <c r="D166" t="n">
-        <v>93.32406017275547</v>
+        <v>93.32404491245036</v>
       </c>
       <c r="E166" t="n">
-        <v>93.31478881835938</v>
+        <v>93.31477355957031</v>
       </c>
       <c r="F166" t="n">
-        <v>93.32406017275547</v>
+        <v>93.32404491245036</v>
       </c>
       <c r="G166" t="n">
         <v>2818100</v>
@@ -4267,16 +4267,16 @@
         <v>45532</v>
       </c>
       <c r="C167" t="n">
-        <v>93.32402038574219</v>
+        <v>93.32403564453125</v>
       </c>
       <c r="D167" t="n">
-        <v>93.33329173618561</v>
+        <v>93.33330699649056</v>
       </c>
       <c r="E167" t="n">
-        <v>93.32402038574219</v>
+        <v>93.32403564453125</v>
       </c>
       <c r="F167" t="n">
-        <v>93.33329173618561</v>
+        <v>93.33330699649056</v>
       </c>
       <c r="G167" t="n">
         <v>3500800</v>
@@ -4336,16 +4336,16 @@
         <v>45538</v>
       </c>
       <c r="C170" t="n">
-        <v>93.42062377929688</v>
+        <v>93.42061614990234</v>
       </c>
       <c r="D170" t="n">
-        <v>93.42062377929688</v>
+        <v>93.42061614990234</v>
       </c>
       <c r="E170" t="n">
-        <v>93.41131848632243</v>
+        <v>93.41131085768782</v>
       </c>
       <c r="F170" t="n">
-        <v>93.42062377929688</v>
+        <v>93.42061614990234</v>
       </c>
       <c r="G170" t="n">
         <v>11846700</v>
@@ -4359,16 +4359,16 @@
         <v>45539</v>
       </c>
       <c r="C171" t="n">
-        <v>93.42994689941406</v>
+        <v>93.429931640625</v>
       </c>
       <c r="D171" t="n">
-        <v>93.43925929673448</v>
+        <v>93.43924403642453</v>
       </c>
       <c r="E171" t="n">
-        <v>93.42994689941406</v>
+        <v>93.429931640625</v>
       </c>
       <c r="F171" t="n">
-        <v>93.43925929673448</v>
+        <v>93.43924403642453</v>
       </c>
       <c r="G171" t="n">
         <v>7218300</v>
@@ -4405,16 +4405,16 @@
         <v>45541</v>
       </c>
       <c r="C173" t="n">
-        <v>93.49510192871094</v>
+        <v>93.4951171875</v>
       </c>
       <c r="D173" t="n">
-        <v>93.49510192871094</v>
+        <v>93.4951171875</v>
       </c>
       <c r="E173" t="n">
-        <v>93.48579663641466</v>
+        <v>93.48581189368507</v>
       </c>
       <c r="F173" t="n">
-        <v>93.49510192871094</v>
+        <v>93.4951171875</v>
       </c>
       <c r="G173" t="n">
         <v>5534600</v>
@@ -4428,16 +4428,16 @@
         <v>45544</v>
       </c>
       <c r="C174" t="n">
-        <v>93.50442504882812</v>
+        <v>93.50440979003906</v>
       </c>
       <c r="D174" t="n">
-        <v>93.51373744546905</v>
+        <v>93.51372218516032</v>
       </c>
       <c r="E174" t="n">
-        <v>93.50442504882812</v>
+        <v>93.50440979003906</v>
       </c>
       <c r="F174" t="n">
-        <v>93.50442504882812</v>
+        <v>93.50440979003906</v>
       </c>
       <c r="G174" t="n">
         <v>5397400</v>
@@ -4451,16 +4451,16 @@
         <v>45545</v>
       </c>
       <c r="C175" t="n">
-        <v>93.52302551269531</v>
+        <v>93.52304077148438</v>
       </c>
       <c r="D175" t="n">
-        <v>93.52302551269531</v>
+        <v>93.52304077148438</v>
       </c>
       <c r="E175" t="n">
-        <v>93.50440782612006</v>
+        <v>93.50442308187154</v>
       </c>
       <c r="F175" t="n">
-        <v>93.52302551269531</v>
+        <v>93.52304077148438</v>
       </c>
       <c r="G175" t="n">
         <v>4143900</v>
@@ -4474,16 +4474,16 @@
         <v>45546</v>
       </c>
       <c r="C176" t="n">
-        <v>93.52302551269531</v>
+        <v>93.52304077148438</v>
       </c>
       <c r="D176" t="n">
-        <v>93.53233790762097</v>
+        <v>93.5323531679294</v>
       </c>
       <c r="E176" t="n">
-        <v>93.52302551269531</v>
+        <v>93.52304077148438</v>
       </c>
       <c r="F176" t="n">
-        <v>93.52302551269531</v>
+        <v>93.52304077148438</v>
       </c>
       <c r="G176" t="n">
         <v>4500100</v>
@@ -4497,16 +4497,16 @@
         <v>45547</v>
       </c>
       <c r="C177" t="n">
-        <v>93.53235626220703</v>
+        <v>93.53234100341797</v>
       </c>
       <c r="D177" t="n">
-        <v>93.54166865896013</v>
+        <v>93.54165339865186</v>
       </c>
       <c r="E177" t="n">
-        <v>93.53235626220703</v>
+        <v>93.53234100341797</v>
       </c>
       <c r="F177" t="n">
-        <v>93.54166865896013</v>
+        <v>93.54165339865186</v>
       </c>
       <c r="G177" t="n">
         <v>3912400</v>
@@ -4543,16 +4543,16 @@
         <v>45551</v>
       </c>
       <c r="C179" t="n">
-        <v>93.60682678222656</v>
+        <v>93.60684204101562</v>
       </c>
       <c r="D179" t="n">
-        <v>93.60682678222656</v>
+        <v>93.60684204101562</v>
       </c>
       <c r="E179" t="n">
-        <v>93.58820199159494</v>
+        <v>93.58821724734798</v>
       </c>
       <c r="F179" t="n">
-        <v>93.58820199159494</v>
+        <v>93.58821724734798</v>
       </c>
       <c r="G179" t="n">
         <v>3571100</v>
@@ -4566,16 +4566,16 @@
         <v>45552</v>
       </c>
       <c r="C180" t="n">
-        <v>93.60682678222656</v>
+        <v>93.60684204101562</v>
       </c>
       <c r="D180" t="n">
-        <v>93.62544446958184</v>
+        <v>93.62545973140574</v>
       </c>
       <c r="E180" t="n">
-        <v>93.60682678222656</v>
+        <v>93.60684204101562</v>
       </c>
       <c r="F180" t="n">
-        <v>93.61613917754238</v>
+        <v>93.61615443784945</v>
       </c>
       <c r="G180" t="n">
         <v>4452200</v>
@@ -4589,16 +4589,16 @@
         <v>45553</v>
       </c>
       <c r="C181" t="n">
-        <v>93.63478088378906</v>
+        <v>93.63475799560547</v>
       </c>
       <c r="D181" t="n">
-        <v>93.64409328149367</v>
+        <v>93.64407039103374</v>
       </c>
       <c r="E181" t="n">
-        <v>93.62546848608446</v>
+        <v>93.6254456001772</v>
       </c>
       <c r="F181" t="n">
-        <v>93.62546848608446</v>
+        <v>93.6254456001772</v>
       </c>
       <c r="G181" t="n">
         <v>4077700</v>
@@ -4612,16 +4612,16 @@
         <v>45554</v>
       </c>
       <c r="C182" t="n">
-        <v>93.65338897705078</v>
+        <v>93.65336608886719</v>
       </c>
       <c r="D182" t="n">
-        <v>93.66270137380091</v>
+        <v>93.66267848334145</v>
       </c>
       <c r="E182" t="n">
-        <v>93.6440836835781</v>
+        <v>93.64406079766864</v>
       </c>
       <c r="F182" t="n">
-        <v>93.6440836835781</v>
+        <v>93.64406079766864</v>
       </c>
       <c r="G182" t="n">
         <v>5165800</v>
@@ -4635,16 +4635,16 @@
         <v>45555</v>
       </c>
       <c r="C183" t="n">
-        <v>93.69063568115234</v>
+        <v>93.69062042236328</v>
       </c>
       <c r="D183" t="n">
-        <v>93.69994807832197</v>
+        <v>93.69993281801626</v>
       </c>
       <c r="E183" t="n">
-        <v>93.69063568115234</v>
+        <v>93.69062042236328</v>
       </c>
       <c r="F183" t="n">
-        <v>93.69994807832197</v>
+        <v>93.69993281801626</v>
       </c>
       <c r="G183" t="n">
         <v>4244800</v>
@@ -4658,16 +4658,16 @@
         <v>45558</v>
       </c>
       <c r="C184" t="n">
-        <v>93.71854400634766</v>
+        <v>93.71855926513672</v>
       </c>
       <c r="D184" t="n">
-        <v>93.71854400634766</v>
+        <v>93.71855926513672</v>
       </c>
       <c r="E184" t="n">
-        <v>93.69991921774503</v>
+        <v>93.6999344735017</v>
       </c>
       <c r="F184" t="n">
-        <v>93.70923161204635</v>
+        <v>93.70924686931922</v>
       </c>
       <c r="G184" t="n">
         <v>5220900</v>
@@ -4681,16 +4681,16 @@
         <v>45559</v>
       </c>
       <c r="C185" t="n">
-        <v>93.72788238525391</v>
+        <v>93.72786712646484</v>
       </c>
       <c r="D185" t="n">
-        <v>93.72788238525391</v>
+        <v>93.72786712646484</v>
       </c>
       <c r="E185" t="n">
-        <v>93.71857709094323</v>
+        <v>93.71856183366906</v>
       </c>
       <c r="F185" t="n">
-        <v>93.71857709094323</v>
+        <v>93.71856183366906</v>
       </c>
       <c r="G185" t="n">
         <v>3923500</v>
@@ -4704,16 +4704,16 @@
         <v>45560</v>
       </c>
       <c r="C186" t="n">
-        <v>93.72788238525391</v>
+        <v>93.72786712646484</v>
       </c>
       <c r="D186" t="n">
-        <v>93.74650718043146</v>
+        <v>93.7464919186103</v>
       </c>
       <c r="E186" t="n">
-        <v>93.72788238525391</v>
+        <v>93.72786712646484</v>
       </c>
       <c r="F186" t="n">
-        <v>93.73719478284268</v>
+        <v>93.73717952253757</v>
       </c>
       <c r="G186" t="n">
         <v>3372400</v>
@@ -4727,16 +4727,16 @@
         <v>45561</v>
       </c>
       <c r="C187" t="n">
-        <v>93.7371826171875</v>
+        <v>93.73717498779297</v>
       </c>
       <c r="D187" t="n">
-        <v>93.74649501356767</v>
+        <v>93.74648738341519</v>
       </c>
       <c r="E187" t="n">
-        <v>93.7371826171875</v>
+        <v>93.73717498779297</v>
       </c>
       <c r="F187" t="n">
-        <v>93.7371826171875</v>
+        <v>93.73717498779297</v>
       </c>
       <c r="G187" t="n">
         <v>4364400</v>
@@ -4750,16 +4750,16 @@
         <v>45562</v>
       </c>
       <c r="C188" t="n">
-        <v>93.7744140625</v>
+        <v>93.77442169189453</v>
       </c>
       <c r="D188" t="n">
-        <v>93.78372645778413</v>
+        <v>93.78373408793631</v>
       </c>
       <c r="E188" t="n">
-        <v>93.7744140625</v>
+        <v>93.77442169189453</v>
       </c>
       <c r="F188" t="n">
-        <v>93.7744140625</v>
+        <v>93.77442169189453</v>
       </c>
       <c r="G188" t="n">
         <v>4945400</v>
@@ -4773,16 +4773,16 @@
         <v>45565</v>
       </c>
       <c r="C189" t="n">
-        <v>93.7744140625</v>
+        <v>93.77442169189453</v>
       </c>
       <c r="D189" t="n">
-        <v>93.79303174979192</v>
+        <v>93.79303938070117</v>
       </c>
       <c r="E189" t="n">
-        <v>93.7744140625</v>
+        <v>93.77442169189453</v>
       </c>
       <c r="F189" t="n">
-        <v>93.78372645778413</v>
+        <v>93.78373408793631</v>
       </c>
       <c r="G189" t="n">
         <v>9253100</v>
@@ -4796,16 +4796,16 @@
         <v>45566</v>
       </c>
       <c r="C190" t="n">
-        <v>93.81182098388672</v>
+        <v>93.81181335449219</v>
       </c>
       <c r="D190" t="n">
-        <v>93.81182098388672</v>
+        <v>93.81181335449219</v>
       </c>
       <c r="E190" t="n">
-        <v>93.80246866058975</v>
+        <v>93.80246103195581</v>
       </c>
       <c r="F190" t="n">
-        <v>93.81182098388672</v>
+        <v>93.81181335449219</v>
       </c>
       <c r="G190" t="n">
         <v>11569200</v>
@@ -4819,16 +4819,16 @@
         <v>45567</v>
       </c>
       <c r="C191" t="n">
-        <v>93.81182098388672</v>
+        <v>93.81181335449219</v>
       </c>
       <c r="D191" t="n">
-        <v>93.82116617345119</v>
+        <v>93.82115854329665</v>
       </c>
       <c r="E191" t="n">
-        <v>93.81182098388672</v>
+        <v>93.81181335449219</v>
       </c>
       <c r="F191" t="n">
-        <v>93.82116617345119</v>
+        <v>93.82115854329665</v>
       </c>
       <c r="G191" t="n">
         <v>5170300</v>
@@ -4842,16 +4842,16 @@
         <v>45568</v>
       </c>
       <c r="C192" t="n">
-        <v>93.82115936279297</v>
+        <v>93.82115173339844</v>
       </c>
       <c r="D192" t="n">
-        <v>93.83051168541103</v>
+        <v>93.83050405525599</v>
       </c>
       <c r="E192" t="n">
-        <v>93.82115936279297</v>
+        <v>93.82115173339844</v>
       </c>
       <c r="F192" t="n">
-        <v>93.83051168541103</v>
+        <v>93.83050405525599</v>
       </c>
       <c r="G192" t="n">
         <v>4066100</v>
@@ -4888,16 +4888,16 @@
         <v>45572</v>
       </c>
       <c r="C194" t="n">
-        <v>93.86789703369141</v>
+        <v>93.86792755126953</v>
       </c>
       <c r="D194" t="n">
-        <v>93.8772493546348</v>
+        <v>93.87727987525348</v>
       </c>
       <c r="E194" t="n">
-        <v>93.86789703369141</v>
+        <v>93.86792755126953</v>
       </c>
       <c r="F194" t="n">
-        <v>93.86789703369141</v>
+        <v>93.86792755126953</v>
       </c>
       <c r="G194" t="n">
         <v>4792500</v>
@@ -4911,16 +4911,16 @@
         <v>45573</v>
       </c>
       <c r="C195" t="n">
-        <v>93.87726593017578</v>
+        <v>93.87725830078125</v>
       </c>
       <c r="D195" t="n">
-        <v>93.88661825277048</v>
+        <v>93.88661062261588</v>
       </c>
       <c r="E195" t="n">
-        <v>93.87726593017578</v>
+        <v>93.87725830078125</v>
       </c>
       <c r="F195" t="n">
-        <v>93.87726593017578</v>
+        <v>93.87725830078125</v>
       </c>
       <c r="G195" t="n">
         <v>3923100</v>
@@ -4934,16 +4934,16 @@
         <v>45574</v>
       </c>
       <c r="C196" t="n">
-        <v>93.89597320556641</v>
+        <v>93.89598083496094</v>
       </c>
       <c r="D196" t="n">
-        <v>93.90532552913362</v>
+        <v>93.90533315928806</v>
       </c>
       <c r="E196" t="n">
-        <v>93.8866280157319</v>
+        <v>93.88663564436709</v>
       </c>
       <c r="F196" t="n">
-        <v>93.89597320556641</v>
+        <v>93.89598083496094</v>
       </c>
       <c r="G196" t="n">
         <v>4024800</v>
@@ -4957,16 +4957,16 @@
         <v>45575</v>
       </c>
       <c r="C197" t="n">
-        <v>93.91468048095703</v>
+        <v>93.91466522216797</v>
       </c>
       <c r="D197" t="n">
-        <v>93.91468048095703</v>
+        <v>93.91466522216797</v>
       </c>
       <c r="E197" t="n">
-        <v>93.9053281571281</v>
+        <v>93.90531289985854</v>
       </c>
       <c r="F197" t="n">
-        <v>93.91468048095703</v>
+        <v>93.91466522216797</v>
       </c>
       <c r="G197" t="n">
         <v>3731100</v>
@@ -5026,16 +5026,16 @@
         <v>45580</v>
       </c>
       <c r="C200" t="n">
-        <v>93.97077178955078</v>
+        <v>93.97078704833984</v>
       </c>
       <c r="D200" t="n">
-        <v>93.97077178955078</v>
+        <v>93.97078704833984</v>
       </c>
       <c r="E200" t="n">
-        <v>93.96141946655455</v>
+        <v>93.96143472382499</v>
       </c>
       <c r="F200" t="n">
-        <v>93.97077178955078</v>
+        <v>93.97078704833984</v>
       </c>
       <c r="G200" t="n">
         <v>3567400</v>
@@ -5095,16 +5095,16 @@
         <v>45583</v>
       </c>
       <c r="C203" t="n">
-        <v>94.02687072753906</v>
+        <v>94.02687835693359</v>
       </c>
       <c r="D203" t="n">
-        <v>94.03622305046243</v>
+        <v>94.03623068061582</v>
       </c>
       <c r="E203" t="n">
-        <v>94.0175255383479</v>
+        <v>94.01753316698415</v>
       </c>
       <c r="F203" t="n">
-        <v>94.03622305046243</v>
+        <v>94.03623068061582</v>
       </c>
       <c r="G203" t="n">
         <v>3970200</v>
@@ -5118,16 +5118,16 @@
         <v>45586</v>
       </c>
       <c r="C204" t="n">
-        <v>94.04556274414062</v>
+        <v>94.04559326171875</v>
       </c>
       <c r="D204" t="n">
-        <v>94.04556274414062</v>
+        <v>94.04559326171875</v>
       </c>
       <c r="E204" t="n">
-        <v>94.03621042247316</v>
+        <v>94.03624093701647</v>
       </c>
       <c r="F204" t="n">
-        <v>94.03621042247316</v>
+        <v>94.03624093701647</v>
       </c>
       <c r="G204" t="n">
         <v>3940600</v>
@@ -5141,16 +5141,16 @@
         <v>45587</v>
       </c>
       <c r="C205" t="n">
-        <v>94.05494689941406</v>
+        <v>94.05493927001953</v>
       </c>
       <c r="D205" t="n">
-        <v>94.05494689941406</v>
+        <v>94.05493927001953</v>
       </c>
       <c r="E205" t="n">
-        <v>94.0456017076061</v>
+        <v>94.04559407896961</v>
       </c>
       <c r="F205" t="n">
-        <v>94.05494689941406</v>
+        <v>94.05493927001953</v>
       </c>
       <c r="G205" t="n">
         <v>3462800</v>
@@ -5164,16 +5164,16 @@
         <v>45588</v>
       </c>
       <c r="C206" t="n">
-        <v>94.05494689941406</v>
+        <v>94.05493927001953</v>
       </c>
       <c r="D206" t="n">
-        <v>94.0736515504984</v>
+        <v>94.07364391958662</v>
       </c>
       <c r="E206" t="n">
-        <v>94.05494689941406</v>
+        <v>94.05493927001953</v>
       </c>
       <c r="F206" t="n">
-        <v>94.0736515504984</v>
+        <v>94.07364391958662</v>
       </c>
       <c r="G206" t="n">
         <v>3927700</v>
@@ -5187,16 +5187,16 @@
         <v>45589</v>
       </c>
       <c r="C207" t="n">
-        <v>94.08296203613281</v>
+        <v>94.08297729492188</v>
       </c>
       <c r="D207" t="n">
-        <v>94.08296203613281</v>
+        <v>94.08297729492188</v>
       </c>
       <c r="E207" t="n">
-        <v>94.07360971474975</v>
+        <v>94.073624972022</v>
       </c>
       <c r="F207" t="n">
-        <v>94.08296203613281</v>
+        <v>94.08297729492188</v>
       </c>
       <c r="G207" t="n">
         <v>3704500</v>
@@ -5210,16 +5210,16 @@
         <v>45590</v>
       </c>
       <c r="C208" t="n">
-        <v>94.12036895751953</v>
+        <v>94.12037658691406</v>
       </c>
       <c r="D208" t="n">
-        <v>94.12036895751953</v>
+        <v>94.12037658691406</v>
       </c>
       <c r="E208" t="n">
-        <v>94.11101663566252</v>
+        <v>94.11102426429896</v>
       </c>
       <c r="F208" t="n">
-        <v>94.11101663566252</v>
+        <v>94.11102426429896</v>
       </c>
       <c r="G208" t="n">
         <v>5386900</v>
@@ -5233,16 +5233,16 @@
         <v>45593</v>
       </c>
       <c r="C209" t="n">
-        <v>94.12036895751953</v>
+        <v>94.12037658691406</v>
       </c>
       <c r="D209" t="n">
-        <v>94.12971414564514</v>
+        <v>94.12972177579719</v>
       </c>
       <c r="E209" t="n">
-        <v>94.12036895751953</v>
+        <v>94.12037658691406</v>
       </c>
       <c r="F209" t="n">
-        <v>94.12971414564514</v>
+        <v>94.12972177579719</v>
       </c>
       <c r="G209" t="n">
         <v>3471300</v>
@@ -5256,16 +5256,16 @@
         <v>45594</v>
       </c>
       <c r="C210" t="n">
-        <v>94.13907623291016</v>
+        <v>94.13908386230469</v>
       </c>
       <c r="D210" t="n">
-        <v>94.13907623291016</v>
+        <v>94.13908386230469</v>
       </c>
       <c r="E210" t="n">
-        <v>94.12505131553549</v>
+        <v>94.12505894379339</v>
       </c>
       <c r="F210" t="n">
-        <v>94.129723910083</v>
+        <v>94.12973153871958</v>
       </c>
       <c r="G210" t="n">
         <v>3449900</v>
@@ -5279,16 +5279,16 @@
         <v>45595</v>
       </c>
       <c r="C211" t="n">
-        <v>94.13907623291016</v>
+        <v>94.13908386230469</v>
       </c>
       <c r="D211" t="n">
-        <v>94.15777374483233</v>
+        <v>94.15778137574219</v>
       </c>
       <c r="E211" t="n">
-        <v>94.13907623291016</v>
+        <v>94.13908386230469</v>
       </c>
       <c r="F211" t="n">
-        <v>94.14842855573731</v>
+        <v>94.14843618588979</v>
       </c>
       <c r="G211" t="n">
         <v>7059200</v>
@@ -5302,16 +5302,16 @@
         <v>45596</v>
       </c>
       <c r="C212" t="n">
-        <v>94.15776824951172</v>
+        <v>94.15777587890625</v>
       </c>
       <c r="D212" t="n">
-        <v>94.16712057179303</v>
+        <v>94.16712820194537</v>
       </c>
       <c r="E212" t="n">
-        <v>94.1484230609621</v>
+        <v>94.14843068959942</v>
       </c>
       <c r="F212" t="n">
-        <v>94.1484230609621</v>
+        <v>94.14843068959942</v>
       </c>
       <c r="G212" t="n">
         <v>11321100</v>
@@ -5325,16 +5325,16 @@
         <v>45597</v>
       </c>
       <c r="C213" t="n">
-        <v>94.20941925048828</v>
+        <v>94.20941162109375</v>
       </c>
       <c r="D213" t="n">
-        <v>94.20941925048828</v>
+        <v>94.20941162109375</v>
       </c>
       <c r="E213" t="n">
-        <v>94.20003538842856</v>
+        <v>94.20002775979395</v>
       </c>
       <c r="F213" t="n">
-        <v>94.20941925048828</v>
+        <v>94.20941162109375</v>
       </c>
       <c r="G213" t="n">
         <v>13451800</v>
@@ -5348,16 +5348,16 @@
         <v>45600</v>
       </c>
       <c r="C214" t="n">
-        <v>94.21880340576172</v>
+        <v>94.21881103515625</v>
       </c>
       <c r="D214" t="n">
-        <v>94.22725604425263</v>
+        <v>94.22726367433162</v>
       </c>
       <c r="E214" t="n">
-        <v>94.20941238113326</v>
+        <v>94.20942000976736</v>
       </c>
       <c r="F214" t="n">
-        <v>94.21880340576172</v>
+        <v>94.21881103515625</v>
       </c>
       <c r="G214" t="n">
         <v>5041500</v>
@@ -5417,16 +5417,16 @@
         <v>45603</v>
       </c>
       <c r="C217" t="n">
-        <v>94.25635528564453</v>
+        <v>94.25636291503906</v>
       </c>
       <c r="D217" t="n">
-        <v>94.25635528564453</v>
+        <v>94.25636291503906</v>
       </c>
       <c r="E217" t="n">
-        <v>94.24696426151975</v>
+        <v>94.24697189015416</v>
       </c>
       <c r="F217" t="n">
-        <v>94.24696426151975</v>
+        <v>94.24697189015416</v>
       </c>
       <c r="G217" t="n">
         <v>6188100</v>
@@ -5463,16 +5463,16 @@
         <v>45607</v>
       </c>
       <c r="C219" t="n">
-        <v>94.29391479492188</v>
+        <v>94.29393768310547</v>
       </c>
       <c r="D219" t="n">
-        <v>94.3033058193032</v>
+        <v>94.3033287097663</v>
       </c>
       <c r="E219" t="n">
-        <v>94.2892228643576</v>
+        <v>94.28924575140231</v>
       </c>
       <c r="F219" t="n">
-        <v>94.29391479492188</v>
+        <v>94.29393768310547</v>
       </c>
       <c r="G219" t="n">
         <v>4443700</v>
@@ -5509,16 +5509,16 @@
         <v>45609</v>
       </c>
       <c r="C221" t="n">
-        <v>94.33147430419922</v>
+        <v>94.33148193359375</v>
       </c>
       <c r="D221" t="n">
-        <v>94.33147430419922</v>
+        <v>94.33148193359375</v>
       </c>
       <c r="E221" t="n">
-        <v>94.31269225492385</v>
+        <v>94.31269988279932</v>
       </c>
       <c r="F221" t="n">
-        <v>94.32208327956153</v>
+        <v>94.32209090819653</v>
       </c>
       <c r="G221" t="n">
         <v>4818000</v>
@@ -5532,16 +5532,16 @@
         <v>45610</v>
       </c>
       <c r="C222" t="n">
-        <v>94.33147430419922</v>
+        <v>94.33148193359375</v>
       </c>
       <c r="D222" t="n">
-        <v>94.3408653288369</v>
+        <v>94.34087295899096</v>
       </c>
       <c r="E222" t="n">
-        <v>94.33147430419922</v>
+        <v>94.33148193359375</v>
       </c>
       <c r="F222" t="n">
-        <v>94.3408653288369</v>
+        <v>94.34087295899096</v>
       </c>
       <c r="G222" t="n">
         <v>4353200</v>
@@ -5555,16 +5555,16 @@
         <v>45611</v>
       </c>
       <c r="C223" t="n">
-        <v>94.37841796875</v>
+        <v>94.37842559814453</v>
       </c>
       <c r="D223" t="n">
-        <v>94.37841796875</v>
+        <v>94.37842559814453</v>
       </c>
       <c r="E223" t="n">
-        <v>94.36903410708014</v>
+        <v>94.3690417357161</v>
       </c>
       <c r="F223" t="n">
-        <v>94.36903410708014</v>
+        <v>94.3690417357161</v>
       </c>
       <c r="G223" t="n">
         <v>5605100</v>
@@ -5601,16 +5601,16 @@
         <v>45615</v>
       </c>
       <c r="C225" t="n">
-        <v>94.39717864990234</v>
+        <v>94.397216796875</v>
       </c>
       <c r="D225" t="n">
-        <v>94.39717864990234</v>
+        <v>94.397216796875</v>
       </c>
       <c r="E225" t="n">
-        <v>94.38778762710514</v>
+        <v>94.38782577028277</v>
       </c>
       <c r="F225" t="n">
-        <v>94.39717864990234</v>
+        <v>94.397216796875</v>
       </c>
       <c r="G225" t="n">
         <v>4310900</v>
@@ -5670,16 +5670,16 @@
         <v>45618</v>
       </c>
       <c r="C228" t="n">
-        <v>94.44415283203125</v>
+        <v>94.44414520263672</v>
       </c>
       <c r="D228" t="n">
-        <v>94.45354385814905</v>
+        <v>94.45353622799588</v>
       </c>
       <c r="E228" t="n">
-        <v>94.44415283203125</v>
+        <v>94.44414520263672</v>
       </c>
       <c r="F228" t="n">
-        <v>94.44415283203125</v>
+        <v>94.44414520263672</v>
       </c>
       <c r="G228" t="n">
         <v>4343900</v>
@@ -5693,16 +5693,16 @@
         <v>45621</v>
       </c>
       <c r="C229" t="n">
-        <v>94.45352172851562</v>
+        <v>94.45352935791016</v>
       </c>
       <c r="D229" t="n">
-        <v>94.46291275243318</v>
+        <v>94.46292038258626</v>
       </c>
       <c r="E229" t="n">
-        <v>94.45352172851562</v>
+        <v>94.45352935791016</v>
       </c>
       <c r="F229" t="n">
-        <v>94.45352172851562</v>
+        <v>94.45352935791016</v>
       </c>
       <c r="G229" t="n">
         <v>6020200</v>
@@ -5739,16 +5739,16 @@
         <v>45623</v>
       </c>
       <c r="C231" t="n">
-        <v>94.49109649658203</v>
+        <v>94.49108123779297</v>
       </c>
       <c r="D231" t="n">
-        <v>94.50048752227218</v>
+        <v>94.50047226196662</v>
       </c>
       <c r="E231" t="n">
-        <v>94.49109649658203</v>
+        <v>94.49108123779297</v>
       </c>
       <c r="F231" t="n">
-        <v>94.49109649658203</v>
+        <v>94.49108123779297</v>
       </c>
       <c r="G231" t="n">
         <v>5909000</v>
@@ -5877,16 +5877,16 @@
         <v>45632</v>
       </c>
       <c r="C237" t="n">
-        <v>94.63042449951172</v>
+        <v>94.63043212890625</v>
       </c>
       <c r="D237" t="n">
-        <v>94.63042449951172</v>
+        <v>94.63043212890625</v>
       </c>
       <c r="E237" t="n">
-        <v>94.62099808418584</v>
+        <v>94.62100571282039</v>
       </c>
       <c r="F237" t="n">
-        <v>94.63042449951172</v>
+        <v>94.63043212890625</v>
       </c>
       <c r="G237" t="n">
         <v>4779000</v>
@@ -5900,16 +5900,16 @@
         <v>45635</v>
       </c>
       <c r="C238" t="n">
-        <v>94.63983917236328</v>
+        <v>94.63985443115234</v>
       </c>
       <c r="D238" t="n">
-        <v>94.63983917236328</v>
+        <v>94.63985443115234</v>
       </c>
       <c r="E238" t="n">
-        <v>94.63041994773863</v>
+        <v>94.63043520500904</v>
       </c>
       <c r="F238" t="n">
-        <v>94.63041994773863</v>
+        <v>94.63043520500904</v>
       </c>
       <c r="G238" t="n">
         <v>5539800</v>
@@ -5969,16 +5969,16 @@
         <v>45638</v>
       </c>
       <c r="C241" t="n">
-        <v>94.66812896728516</v>
+        <v>94.66813659667969</v>
       </c>
       <c r="D241" t="n">
-        <v>94.6775553839241</v>
+        <v>94.67756301407832</v>
       </c>
       <c r="E241" t="n">
-        <v>94.66812896728516</v>
+        <v>94.66813659667969</v>
       </c>
       <c r="F241" t="n">
-        <v>94.6775553839241</v>
+        <v>94.67756301407832</v>
       </c>
       <c r="G241" t="n">
         <v>4701000</v>
@@ -5992,16 +5992,16 @@
         <v>45639</v>
       </c>
       <c r="C242" t="n">
-        <v>94.71524810791016</v>
+        <v>94.71526336669922</v>
       </c>
       <c r="D242" t="n">
-        <v>94.71524810791016</v>
+        <v>94.71526336669922</v>
       </c>
       <c r="E242" t="n">
-        <v>94.70582169184371</v>
+        <v>94.70583694911416</v>
       </c>
       <c r="F242" t="n">
-        <v>94.70582169184371</v>
+        <v>94.70583694911416</v>
       </c>
       <c r="G242" t="n">
         <v>4671500</v>
@@ -6015,16 +6015,16 @@
         <v>45642</v>
       </c>
       <c r="C243" t="n">
-        <v>94.72468566894531</v>
+        <v>94.72467041015625</v>
       </c>
       <c r="D243" t="n">
-        <v>94.72468566894531</v>
+        <v>94.72467041015625</v>
       </c>
       <c r="E243" t="n">
-        <v>94.71525925176978</v>
+        <v>94.71524399449918</v>
       </c>
       <c r="F243" t="n">
-        <v>94.72468566894531</v>
+        <v>94.72467041015625</v>
       </c>
       <c r="G243" t="n">
         <v>5598900</v>
@@ -6038,16 +6038,16 @@
         <v>45643</v>
       </c>
       <c r="C244" t="n">
-        <v>94.72468566894531</v>
+        <v>94.72467041015625</v>
       </c>
       <c r="D244" t="n">
-        <v>94.73410489587128</v>
+        <v>94.7340896355649</v>
       </c>
       <c r="E244" t="n">
-        <v>94.72468566894531</v>
+        <v>94.72467041015625</v>
       </c>
       <c r="F244" t="n">
-        <v>94.73410489587128</v>
+        <v>94.7340896355649</v>
       </c>
       <c r="G244" t="n">
         <v>5798500</v>
@@ -6061,16 +6061,16 @@
         <v>45644</v>
       </c>
       <c r="C245" t="n">
-        <v>94.74547576904297</v>
+        <v>94.74549102783203</v>
       </c>
       <c r="D245" t="n">
-        <v>94.74547576904297</v>
+        <v>94.74549102783203</v>
       </c>
       <c r="E245" t="n">
-        <v>94.7360143361235</v>
+        <v>94.73602959338879</v>
       </c>
       <c r="F245" t="n">
-        <v>94.74547576904297</v>
+        <v>94.74549102783203</v>
       </c>
       <c r="G245" t="n">
         <v>11526500</v>
@@ -6130,16 +6130,16 @@
         <v>45649</v>
       </c>
       <c r="C248" t="n">
-        <v>94.80224609375</v>
+        <v>94.80223083496094</v>
       </c>
       <c r="D248" t="n">
-        <v>94.80224609375</v>
+        <v>94.80223083496094</v>
       </c>
       <c r="E248" t="n">
-        <v>94.79278465921763</v>
+        <v>94.79276940195142</v>
       </c>
       <c r="F248" t="n">
-        <v>94.80224609375</v>
+        <v>94.80223083496094</v>
       </c>
       <c r="G248" t="n">
         <v>7032500</v>
@@ -6153,16 +6153,16 @@
         <v>45650</v>
       </c>
       <c r="C249" t="n">
-        <v>94.83062744140625</v>
+        <v>94.83063507080078</v>
       </c>
       <c r="D249" t="n">
-        <v>94.83062744140625</v>
+        <v>94.83063507080078</v>
       </c>
       <c r="E249" t="n">
-        <v>94.82116600644875</v>
+        <v>94.82117363508208</v>
       </c>
       <c r="F249" t="n">
-        <v>94.83062744140625</v>
+        <v>94.83063507080078</v>
       </c>
       <c r="G249" t="n">
         <v>4654300</v>
@@ -6176,16 +6176,16 @@
         <v>45652</v>
       </c>
       <c r="C250" t="n">
-        <v>94.84008026123047</v>
+        <v>94.84006500244141</v>
       </c>
       <c r="D250" t="n">
-        <v>94.84008026123047</v>
+        <v>94.84006500244141</v>
       </c>
       <c r="E250" t="n">
-        <v>94.83061882713243</v>
+        <v>94.83060356986562</v>
       </c>
       <c r="F250" t="n">
-        <v>94.84008026123047</v>
+        <v>94.84006500244141</v>
       </c>
       <c r="G250" t="n">
         <v>4974100</v>
@@ -6199,16 +6199,16 @@
         <v>45653</v>
       </c>
       <c r="C251" t="n">
-        <v>94.86843872070312</v>
+        <v>94.86846923828125</v>
       </c>
       <c r="D251" t="n">
-        <v>94.86843872070312</v>
+        <v>94.86846923828125</v>
       </c>
       <c r="E251" t="n">
-        <v>94.85897728846268</v>
+        <v>94.85900780299723</v>
       </c>
       <c r="F251" t="n">
-        <v>94.85897728846268</v>
+        <v>94.85900780299723</v>
       </c>
       <c r="G251" t="n">
         <v>6558000</v>
@@ -6222,16 +6222,16 @@
         <v>45656</v>
       </c>
       <c r="C252" t="n">
-        <v>94.86843872070312</v>
+        <v>94.86846923828125</v>
       </c>
       <c r="D252" t="n">
-        <v>94.87790015294357</v>
+        <v>94.87793067356529</v>
       </c>
       <c r="E252" t="n">
-        <v>94.86843872070312</v>
+        <v>94.86846923828125</v>
       </c>
       <c r="F252" t="n">
-        <v>94.87790015294357</v>
+        <v>94.87793067356529</v>
       </c>
       <c r="G252" t="n">
         <v>6547600</v>
@@ -6245,16 +6245,16 @@
         <v>45657</v>
       </c>
       <c r="C253" t="n">
-        <v>94.89684295654297</v>
+        <v>94.89683532714844</v>
       </c>
       <c r="D253" t="n">
-        <v>94.9157586094786</v>
+        <v>94.91575097856332</v>
       </c>
       <c r="E253" t="n">
-        <v>94.89684295654297</v>
+        <v>94.89683532714844</v>
       </c>
       <c r="F253" t="n">
-        <v>94.90630439149093</v>
+        <v>94.90629676133574</v>
       </c>
       <c r="G253" t="n">
         <v>7371300</v>
@@ -6268,16 +6268,16 @@
         <v>45659</v>
       </c>
       <c r="C254" t="n">
-        <v>94.91574859619141</v>
+        <v>94.91574096679688</v>
       </c>
       <c r="D254" t="n">
-        <v>94.91574859619141</v>
+        <v>94.91574096679688</v>
       </c>
       <c r="E254" t="n">
-        <v>94.90629437920111</v>
+        <v>94.90628675056652</v>
       </c>
       <c r="F254" t="n">
-        <v>94.91574859619141</v>
+        <v>94.91574096679688</v>
       </c>
       <c r="G254" t="n">
         <v>7533100</v>
@@ -6360,16 +6360,16 @@
         <v>45665</v>
       </c>
       <c r="C258" t="n">
-        <v>94.98195648193359</v>
+        <v>94.98197174072266</v>
       </c>
       <c r="D258" t="n">
-        <v>94.98195648193359</v>
+        <v>94.98197174072266</v>
       </c>
       <c r="E258" t="n">
-        <v>94.97249504947149</v>
+        <v>94.97251030674057</v>
       </c>
       <c r="F258" t="n">
-        <v>94.97249504947149</v>
+        <v>94.97251030674057</v>
       </c>
       <c r="G258" t="n">
         <v>6101100</v>
@@ -6383,16 +6383,16 @@
         <v>45667</v>
       </c>
       <c r="C259" t="n">
-        <v>95.01980590820312</v>
+        <v>95.01982116699219</v>
       </c>
       <c r="D259" t="n">
-        <v>95.02926734247052</v>
+        <v>95.02928260277895</v>
       </c>
       <c r="E259" t="n">
-        <v>95.0103516908955</v>
+        <v>95.01036694816635</v>
       </c>
       <c r="F259" t="n">
-        <v>95.01980590820312</v>
+        <v>95.01982116699219</v>
       </c>
       <c r="G259" t="n">
         <v>7644600</v>
@@ -6406,16 +6406,16 @@
         <v>45670</v>
       </c>
       <c r="C260" t="n">
-        <v>95.03872680664062</v>
+        <v>95.03873443603516</v>
       </c>
       <c r="D260" t="n">
-        <v>95.03872680664062</v>
+        <v>95.03873443603516</v>
       </c>
       <c r="E260" t="n">
-        <v>95.02926537256936</v>
+        <v>95.02927300120436</v>
       </c>
       <c r="F260" t="n">
-        <v>95.03399248112518</v>
+        <v>95.03400011013966</v>
       </c>
       <c r="G260" t="n">
         <v>7647300</v>
@@ -6452,16 +6452,16 @@
         <v>45672</v>
       </c>
       <c r="C262" t="n">
-        <v>95.05764007568359</v>
+        <v>95.05766296386719</v>
       </c>
       <c r="D262" t="n">
-        <v>95.05764007568359</v>
+        <v>95.05766296386719</v>
       </c>
       <c r="E262" t="n">
-        <v>95.04818585880886</v>
+        <v>95.04820874471606</v>
       </c>
       <c r="F262" t="n">
-        <v>95.05764007568359</v>
+        <v>95.05766296386719</v>
       </c>
       <c r="G262" t="n">
         <v>6878600</v>
@@ -6475,16 +6475,16 @@
         <v>45673</v>
       </c>
       <c r="C263" t="n">
-        <v>95.05764007568359</v>
+        <v>95.05766296386719</v>
       </c>
       <c r="D263" t="n">
-        <v>95.07656294335193</v>
+        <v>95.07658583609181</v>
       </c>
       <c r="E263" t="n">
-        <v>95.05764007568359</v>
+        <v>95.05766296386719</v>
       </c>
       <c r="F263" t="n">
-        <v>95.06710150951776</v>
+        <v>95.06712439997951</v>
       </c>
       <c r="G263" t="n">
         <v>5352500</v>
@@ -6498,16 +6498,16 @@
         <v>45674</v>
       </c>
       <c r="C264" t="n">
-        <v>95.10494995117188</v>
+        <v>95.10495758056641</v>
       </c>
       <c r="D264" t="n">
-        <v>95.11441138599326</v>
+        <v>95.11441901614678</v>
       </c>
       <c r="E264" t="n">
-        <v>95.0954885163505</v>
+        <v>95.09549614498603</v>
       </c>
       <c r="F264" t="n">
-        <v>95.10494995117188</v>
+        <v>95.10495758056641</v>
       </c>
       <c r="G264" t="n">
         <v>6563000</v>
@@ -6521,16 +6521,16 @@
         <v>45678</v>
       </c>
       <c r="C265" t="n">
-        <v>95.11441040039062</v>
+        <v>95.11439514160156</v>
       </c>
       <c r="D265" t="n">
-        <v>95.12386461815383</v>
+        <v>95.12384935784807</v>
       </c>
       <c r="E265" t="n">
-        <v>95.11441040039062</v>
+        <v>95.11439514160156</v>
       </c>
       <c r="F265" t="n">
-        <v>95.11913750927222</v>
+        <v>95.11912224972482</v>
       </c>
       <c r="G265" t="n">
         <v>7952400</v>
@@ -6544,16 +6544,16 @@
         <v>45679</v>
       </c>
       <c r="C266" t="n">
-        <v>95.13332366943359</v>
+        <v>95.13333129882812</v>
       </c>
       <c r="D266" t="n">
-        <v>95.13332366943359</v>
+        <v>95.13333129882812</v>
       </c>
       <c r="E266" t="n">
-        <v>95.12386223494731</v>
+        <v>95.12386986358305</v>
       </c>
       <c r="F266" t="n">
-        <v>95.12386223494731</v>
+        <v>95.12386986358305</v>
       </c>
       <c r="G266" t="n">
         <v>5717600</v>
@@ -6567,16 +6567,16 @@
         <v>45680</v>
       </c>
       <c r="C267" t="n">
-        <v>95.14276885986328</v>
+        <v>95.14279174804688</v>
       </c>
       <c r="D267" t="n">
-        <v>95.14276885986328</v>
+        <v>95.14279174804688</v>
       </c>
       <c r="E267" t="n">
-        <v>95.13330742699237</v>
+        <v>95.13333031289986</v>
       </c>
       <c r="F267" t="n">
-        <v>95.14276885986328</v>
+        <v>95.14279174804688</v>
       </c>
       <c r="G267" t="n">
         <v>5085800</v>
@@ -6636,16 +6636,16 @@
         <v>45685</v>
       </c>
       <c r="C270" t="n">
-        <v>95.19951629638672</v>
+        <v>95.19953155517578</v>
       </c>
       <c r="D270" t="n">
-        <v>95.19951629638672</v>
+        <v>95.19953155517578</v>
       </c>
       <c r="E270" t="n">
-        <v>95.1806006489402</v>
+        <v>95.18061590469742</v>
       </c>
       <c r="F270" t="n">
-        <v>95.19005486418436</v>
+        <v>95.19007012145691</v>
       </c>
       <c r="G270" t="n">
         <v>5857900</v>
@@ -6659,16 +6659,16 @@
         <v>45686</v>
       </c>
       <c r="C271" t="n">
-        <v>95.19951629638672</v>
+        <v>95.19953155517578</v>
       </c>
       <c r="D271" t="n">
-        <v>95.20897772858909</v>
+        <v>95.20899298889465</v>
       </c>
       <c r="E271" t="n">
-        <v>95.19951629638672</v>
+        <v>95.19953155517578</v>
       </c>
       <c r="F271" t="n">
-        <v>95.19951629638672</v>
+        <v>95.19953155517578</v>
       </c>
       <c r="G271" t="n">
         <v>3978700</v>
@@ -6682,16 +6682,16 @@
         <v>45687</v>
       </c>
       <c r="C272" t="n">
-        <v>95.21846008300781</v>
+        <v>95.21845245361328</v>
       </c>
       <c r="D272" t="n">
-        <v>95.22791430032933</v>
+        <v>95.22790667017728</v>
       </c>
       <c r="E272" t="n">
-        <v>95.20899864872649</v>
+        <v>95.20899102009007</v>
       </c>
       <c r="F272" t="n">
-        <v>95.20899864872649</v>
+        <v>95.20899102009007</v>
       </c>
       <c r="G272" t="n">
         <v>8043500</v>
@@ -6728,16 +6728,16 @@
         <v>45691</v>
       </c>
       <c r="C274" t="n">
-        <v>95.25920104980469</v>
+        <v>95.25920867919922</v>
       </c>
       <c r="D274" t="n">
-        <v>95.25920104980469</v>
+        <v>95.25920867919922</v>
       </c>
       <c r="E274" t="n">
-        <v>95.24971262274842</v>
+        <v>95.24972025138301</v>
       </c>
       <c r="F274" t="n">
-        <v>95.24971262274842</v>
+        <v>95.24972025138301</v>
       </c>
       <c r="G274" t="n">
         <v>16436200</v>
@@ -6797,16 +6797,16 @@
         <v>45694</v>
       </c>
       <c r="C277" t="n">
-        <v>95.29717254638672</v>
+        <v>95.29719543457031</v>
       </c>
       <c r="D277" t="n">
-        <v>95.29717254638672</v>
+        <v>95.29719543457031</v>
       </c>
       <c r="E277" t="n">
-        <v>95.28768411972284</v>
+        <v>95.28770700562752</v>
       </c>
       <c r="F277" t="n">
-        <v>95.29717254638672</v>
+        <v>95.29719543457031</v>
       </c>
       <c r="G277" t="n">
         <v>5804300</v>
@@ -6820,16 +6820,16 @@
         <v>45695</v>
       </c>
       <c r="C278" t="n">
-        <v>95.32566070556641</v>
+        <v>95.32565307617188</v>
       </c>
       <c r="D278" t="n">
-        <v>95.33514913234477</v>
+        <v>95.33514150219082</v>
       </c>
       <c r="E278" t="n">
-        <v>95.31616503571418</v>
+        <v>95.31615740707963</v>
       </c>
       <c r="F278" t="n">
-        <v>95.33514913234477</v>
+        <v>95.33514150219082</v>
       </c>
       <c r="G278" t="n">
         <v>6758700</v>
@@ -6843,16 +6843,16 @@
         <v>45698</v>
       </c>
       <c r="C279" t="n">
-        <v>95.34466552734375</v>
+        <v>95.34465026855469</v>
       </c>
       <c r="D279" t="n">
-        <v>95.34466552734375</v>
+        <v>95.34465026855469</v>
       </c>
       <c r="E279" t="n">
-        <v>95.33516985542744</v>
+        <v>95.33515459815804</v>
       </c>
       <c r="F279" t="n">
-        <v>95.34466552734375</v>
+        <v>95.34465026855469</v>
       </c>
       <c r="G279" t="n">
         <v>7517800</v>
@@ -6866,16 +6866,16 @@
         <v>45699</v>
       </c>
       <c r="C280" t="n">
-        <v>95.34466552734375</v>
+        <v>95.34465026855469</v>
       </c>
       <c r="D280" t="n">
-        <v>95.35416119926006</v>
+        <v>95.35414593895132</v>
       </c>
       <c r="E280" t="n">
-        <v>95.34466552734375</v>
+        <v>95.34465026855469</v>
       </c>
       <c r="F280" t="n">
-        <v>95.35416119926006</v>
+        <v>95.35414593895132</v>
       </c>
       <c r="G280" t="n">
         <v>6424100</v>
@@ -6889,16 +6889,16 @@
         <v>45700</v>
       </c>
       <c r="C281" t="n">
-        <v>95.35415649414062</v>
+        <v>95.35414123535156</v>
       </c>
       <c r="D281" t="n">
-        <v>95.36364492251329</v>
+        <v>95.36362966220587</v>
       </c>
       <c r="E281" t="n">
-        <v>95.35415649414062</v>
+        <v>95.35414123535156</v>
       </c>
       <c r="F281" t="n">
-        <v>95.35415649414062</v>
+        <v>95.35414123535156</v>
       </c>
       <c r="G281" t="n">
         <v>6618800</v>
@@ -6912,16 +6912,16 @@
         <v>45701</v>
       </c>
       <c r="C282" t="n">
-        <v>95.37313842773438</v>
+        <v>95.37312316894531</v>
       </c>
       <c r="D282" t="n">
-        <v>95.37313842773438</v>
+        <v>95.37312316894531</v>
       </c>
       <c r="E282" t="n">
-        <v>95.3636427565023</v>
+        <v>95.36362749923244</v>
       </c>
       <c r="F282" t="n">
-        <v>95.37313842773438</v>
+        <v>95.37312316894531</v>
       </c>
       <c r="G282" t="n">
         <v>5690100</v>
@@ -6935,16 +6935,16 @@
         <v>45702</v>
       </c>
       <c r="C283" t="n">
-        <v>95.41109466552734</v>
+        <v>95.41110992431641</v>
       </c>
       <c r="D283" t="n">
-        <v>95.42059033484817</v>
+        <v>95.42060559515583</v>
       </c>
       <c r="E283" t="n">
-        <v>95.41109466552734</v>
+        <v>95.41110992431641</v>
       </c>
       <c r="F283" t="n">
-        <v>95.41583887865103</v>
+        <v>95.41585413819881</v>
       </c>
       <c r="G283" t="n">
         <v>7648100</v>
@@ -6958,16 +6958,16 @@
         <v>45706</v>
       </c>
       <c r="C284" t="n">
-        <v>95.43010711669922</v>
+        <v>95.43009948730469</v>
       </c>
       <c r="D284" t="n">
-        <v>95.43010711669922</v>
+        <v>95.43009948730469</v>
       </c>
       <c r="E284" t="n">
-        <v>95.42061868763253</v>
+        <v>95.42061105899657</v>
       </c>
       <c r="F284" t="n">
-        <v>95.43010711669922</v>
+        <v>95.43009948730469</v>
       </c>
       <c r="G284" t="n">
         <v>15815200</v>
@@ -6981,16 +6981,16 @@
         <v>45707</v>
       </c>
       <c r="C285" t="n">
-        <v>95.43010711669922</v>
+        <v>95.43009948730469</v>
       </c>
       <c r="D285" t="n">
-        <v>95.43960278884154</v>
+        <v>95.43959515868785</v>
       </c>
       <c r="E285" t="n">
-        <v>95.43010711669922</v>
+        <v>95.43009948730469</v>
       </c>
       <c r="F285" t="n">
-        <v>95.43960278884154</v>
+        <v>95.43959515868785</v>
       </c>
       <c r="G285" t="n">
         <v>7277600</v>
@@ -7004,16 +7004,16 @@
         <v>45708</v>
       </c>
       <c r="C286" t="n">
-        <v>95.44908905029297</v>
+        <v>95.44908142089844</v>
       </c>
       <c r="D286" t="n">
-        <v>95.44908905029297</v>
+        <v>95.44908142089844</v>
       </c>
       <c r="E286" t="n">
-        <v>95.43959337908686</v>
+        <v>95.43958575045134</v>
       </c>
       <c r="F286" t="n">
-        <v>95.44908905029297</v>
+        <v>95.44908142089844</v>
       </c>
       <c r="G286" t="n">
         <v>7608000</v>
@@ -7027,16 +7027,16 @@
         <v>45709</v>
       </c>
       <c r="C287" t="n">
-        <v>95.48705291748047</v>
+        <v>95.487060546875</v>
       </c>
       <c r="D287" t="n">
-        <v>95.48705291748047</v>
+        <v>95.487060546875</v>
       </c>
       <c r="E287" t="n">
-        <v>95.47755724742539</v>
+        <v>95.47756487606122</v>
       </c>
       <c r="F287" t="n">
-        <v>95.47755724742539</v>
+        <v>95.47756487606122</v>
       </c>
       <c r="G287" t="n">
         <v>9111000</v>
@@ -7050,16 +7050,16 @@
         <v>45712</v>
       </c>
       <c r="C288" t="n">
-        <v>95.49655914306641</v>
+        <v>95.49657440185547</v>
       </c>
       <c r="D288" t="n">
-        <v>95.49655914306641</v>
+        <v>95.49657440185547</v>
       </c>
       <c r="E288" t="n">
-        <v>95.48707071431691</v>
+        <v>95.48708597158989</v>
       </c>
       <c r="F288" t="n">
-        <v>95.49655914306641</v>
+        <v>95.49657440185547</v>
       </c>
       <c r="G288" t="n">
         <v>9734600</v>
@@ -7073,16 +7073,16 @@
         <v>45713</v>
       </c>
       <c r="C289" t="n">
-        <v>95.50603485107422</v>
+        <v>95.50604248046875</v>
       </c>
       <c r="D289" t="n">
-        <v>95.50603485107422</v>
+        <v>95.50604248046875</v>
       </c>
       <c r="E289" t="n">
-        <v>95.49653918123424</v>
+        <v>95.49654680987022</v>
       </c>
       <c r="F289" t="n">
-        <v>95.49653918123424</v>
+        <v>95.49654680987022</v>
       </c>
       <c r="G289" t="n">
         <v>10827700</v>
@@ -7096,16 +7096,16 @@
         <v>45714</v>
       </c>
       <c r="C290" t="n">
-        <v>95.50603485107422</v>
+        <v>95.50604248046875</v>
       </c>
       <c r="D290" t="n">
-        <v>95.5155305209142</v>
+        <v>95.51553815106729</v>
       </c>
       <c r="E290" t="n">
-        <v>95.50603485107422</v>
+        <v>95.50604248046875</v>
       </c>
       <c r="F290" t="n">
-        <v>95.50603485107422</v>
+        <v>95.50604248046875</v>
       </c>
       <c r="G290" t="n">
         <v>9536300</v>
@@ -7119,16 +7119,16 @@
         <v>45715</v>
       </c>
       <c r="C291" t="n">
-        <v>95.53452301025391</v>
+        <v>95.53453826904297</v>
       </c>
       <c r="D291" t="n">
-        <v>95.53452301025391</v>
+        <v>95.53453826904297</v>
       </c>
       <c r="E291" t="n">
-        <v>95.52503458265423</v>
+        <v>95.5250498399278</v>
       </c>
       <c r="F291" t="n">
-        <v>95.53452301025391</v>
+        <v>95.53453826904297</v>
       </c>
       <c r="G291" t="n">
         <v>10807800</v>
@@ -7165,16 +7165,16 @@
         <v>45719</v>
       </c>
       <c r="C293" t="n">
-        <v>95.57541656494141</v>
+        <v>95.57542419433594</v>
       </c>
       <c r="D293" t="n">
-        <v>95.57541656494141</v>
+        <v>95.57542419433594</v>
       </c>
       <c r="E293" t="n">
-        <v>95.56589127268401</v>
+        <v>95.56589890131818</v>
       </c>
       <c r="F293" t="n">
-        <v>95.57541656494141</v>
+        <v>95.57542419433594</v>
       </c>
       <c r="G293" t="n">
         <v>17436600</v>
@@ -7234,16 +7234,16 @@
         <v>45722</v>
       </c>
       <c r="C296" t="n">
-        <v>95.61351776123047</v>
+        <v>95.61351013183594</v>
       </c>
       <c r="D296" t="n">
-        <v>95.61351776123047</v>
+        <v>95.61351013183594</v>
       </c>
       <c r="E296" t="n">
-        <v>95.59446717526258</v>
+        <v>95.59445954738818</v>
       </c>
       <c r="F296" t="n">
-        <v>95.60399246824653</v>
+        <v>95.60398483961205</v>
       </c>
       <c r="G296" t="n">
         <v>9925500</v>
@@ -7303,16 +7303,16 @@
         <v>45727</v>
       </c>
       <c r="C299" t="n">
-        <v>95.66111755371094</v>
+        <v>95.6611328125</v>
       </c>
       <c r="D299" t="n">
-        <v>95.66111755371094</v>
+        <v>95.6611328125</v>
       </c>
       <c r="E299" t="n">
-        <v>95.65159952760472</v>
+        <v>95.65161478487556</v>
       </c>
       <c r="F299" t="n">
-        <v>95.65159952760472</v>
+        <v>95.65161478487556</v>
       </c>
       <c r="G299" t="n">
         <v>11456900</v>
@@ -7326,16 +7326,16 @@
         <v>45728</v>
       </c>
       <c r="C300" t="n">
-        <v>95.66111755371094</v>
+        <v>95.6611328125</v>
       </c>
       <c r="D300" t="n">
-        <v>95.67064284548596</v>
+        <v>95.67065810579437</v>
       </c>
       <c r="E300" t="n">
-        <v>95.66111755371094</v>
+        <v>95.6611328125</v>
       </c>
       <c r="F300" t="n">
-        <v>95.67064284548596</v>
+        <v>95.67065810579437</v>
       </c>
       <c r="G300" t="n">
         <v>11307300</v>
@@ -7372,16 +7372,16 @@
         <v>45730</v>
       </c>
       <c r="C302" t="n">
-        <v>95.71826934814453</v>
+        <v>95.71829223632812</v>
       </c>
       <c r="D302" t="n">
-        <v>95.71826934814453</v>
+        <v>95.71829223632812</v>
       </c>
       <c r="E302" t="n">
-        <v>95.70874405564213</v>
+        <v>95.70876694154803</v>
       </c>
       <c r="F302" t="n">
-        <v>95.71826934814453</v>
+        <v>95.71829223632812</v>
       </c>
       <c r="G302" t="n">
         <v>11421900</v>
@@ -7418,16 +7418,16 @@
         <v>45734</v>
       </c>
       <c r="C304" t="n">
-        <v>95.73731994628906</v>
+        <v>95.73731231689453</v>
       </c>
       <c r="D304" t="n">
-        <v>95.73731994628906</v>
+        <v>95.73731231689453</v>
       </c>
       <c r="E304" t="n">
-        <v>95.72779465306246</v>
+        <v>95.727787024427</v>
       </c>
       <c r="F304" t="n">
-        <v>95.73731994628906</v>
+        <v>95.73731231689453</v>
       </c>
       <c r="G304" t="n">
         <v>9213100</v>
@@ -7441,16 +7441,16 @@
         <v>45735</v>
       </c>
       <c r="C305" t="n">
-        <v>95.75635528564453</v>
+        <v>95.75638580322266</v>
       </c>
       <c r="D305" t="n">
-        <v>95.75635528564453</v>
+        <v>95.75638580322266</v>
       </c>
       <c r="E305" t="n">
-        <v>95.74682999393463</v>
+        <v>95.74686050847703</v>
       </c>
       <c r="F305" t="n">
-        <v>95.74682999393463</v>
+        <v>95.74686050847703</v>
       </c>
       <c r="G305" t="n">
         <v>13584800</v>
@@ -7464,16 +7464,16 @@
         <v>45736</v>
       </c>
       <c r="C306" t="n">
-        <v>95.75635528564453</v>
+        <v>95.75638580322266</v>
       </c>
       <c r="D306" t="n">
-        <v>95.76587331168571</v>
+        <v>95.76590383229723</v>
       </c>
       <c r="E306" t="n">
-        <v>95.75635528564453</v>
+        <v>95.75638580322266</v>
       </c>
       <c r="F306" t="n">
-        <v>95.76587331168571</v>
+        <v>95.76590383229723</v>
       </c>
       <c r="G306" t="n">
         <v>12648500</v>
@@ -7533,16 +7533,16 @@
         <v>45741</v>
       </c>
       <c r="C309" t="n">
-        <v>95.81349945068359</v>
+        <v>95.81351470947266</v>
       </c>
       <c r="D309" t="n">
-        <v>95.81349945068359</v>
+        <v>95.81351470947266</v>
       </c>
       <c r="E309" t="n">
-        <v>95.80397415828314</v>
+        <v>95.80398941555525</v>
       </c>
       <c r="F309" t="n">
-        <v>95.81349945068359</v>
+        <v>95.81351470947266</v>
       </c>
       <c r="G309" t="n">
         <v>13844800</v>
@@ -7579,16 +7579,16 @@
         <v>45743</v>
       </c>
       <c r="C311" t="n">
-        <v>95.84204864501953</v>
+        <v>95.84207153320312</v>
       </c>
       <c r="D311" t="n">
-        <v>95.84204864501953</v>
+        <v>95.84207153320312</v>
       </c>
       <c r="E311" t="n">
-        <v>95.83252335454887</v>
+        <v>95.8325462404577</v>
       </c>
       <c r="F311" t="n">
-        <v>95.84204864501953</v>
+        <v>95.84207153320312</v>
       </c>
       <c r="G311" t="n">
         <v>10022000</v>
@@ -7602,16 +7602,16 @@
         <v>45744</v>
       </c>
       <c r="C312" t="n">
-        <v>95.87065124511719</v>
+        <v>95.87064361572266</v>
       </c>
       <c r="D312" t="n">
-        <v>95.87065124511719</v>
+        <v>95.87064361572266</v>
       </c>
       <c r="E312" t="n">
-        <v>95.86113321693935</v>
+        <v>95.86112558830226</v>
       </c>
       <c r="F312" t="n">
-        <v>95.86113321693935</v>
+        <v>95.86112558830226</v>
       </c>
       <c r="G312" t="n">
         <v>11747100</v>
@@ -7625,16 +7625,16 @@
         <v>45747</v>
       </c>
       <c r="C313" t="n">
-        <v>95.87065124511719</v>
+        <v>95.87064361572266</v>
       </c>
       <c r="D313" t="n">
-        <v>95.88017653896539</v>
+        <v>95.88016890881283</v>
       </c>
       <c r="E313" t="n">
-        <v>95.87065124511719</v>
+        <v>95.87064361572266</v>
       </c>
       <c r="F313" t="n">
-        <v>95.87065124511719</v>
+        <v>95.87064361572266</v>
       </c>
       <c r="G313" t="n">
         <v>18210800</v>
@@ -7648,16 +7648,16 @@
         <v>45748</v>
       </c>
       <c r="C314" t="n">
-        <v>95.89548492431641</v>
+        <v>95.89547729492188</v>
       </c>
       <c r="D314" t="n">
-        <v>95.89548492431641</v>
+        <v>95.89547729492188</v>
       </c>
       <c r="E314" t="n">
-        <v>95.88592678063245</v>
+        <v>95.88591915199837</v>
       </c>
       <c r="F314" t="n">
-        <v>95.89548492431641</v>
+        <v>95.89547729492188</v>
       </c>
       <c r="G314" t="n">
         <v>21033200</v>
@@ -7671,16 +7671,16 @@
         <v>45749</v>
       </c>
       <c r="C315" t="n">
-        <v>95.90504455566406</v>
+        <v>95.90505218505859</v>
       </c>
       <c r="D315" t="n">
-        <v>95.90504455566406</v>
+        <v>95.90505218505859</v>
       </c>
       <c r="E315" t="n">
-        <v>95.89548641183185</v>
+        <v>95.89549404046602</v>
       </c>
       <c r="F315" t="n">
-        <v>95.90504455566406</v>
+        <v>95.90505218505859</v>
       </c>
       <c r="G315" t="n">
         <v>10658900</v>
@@ -7717,16 +7717,16 @@
         <v>45751</v>
       </c>
       <c r="C317" t="n">
-        <v>95.95283508300781</v>
+        <v>95.95281982421875</v>
       </c>
       <c r="D317" t="n">
-        <v>95.95283508300781</v>
+        <v>95.95281982421875</v>
       </c>
       <c r="E317" t="n">
-        <v>95.94327693846846</v>
+        <v>95.94326168119937</v>
       </c>
       <c r="F317" t="n">
-        <v>95.94327693846846</v>
+        <v>95.94326168119937</v>
       </c>
       <c r="G317" t="n">
         <v>22826300</v>
@@ -7740,16 +7740,16 @@
         <v>45754</v>
       </c>
       <c r="C318" t="n">
-        <v>95.96236419677734</v>
+        <v>95.96238708496094</v>
       </c>
       <c r="D318" t="n">
-        <v>95.96236419677734</v>
+        <v>95.96238708496094</v>
       </c>
       <c r="E318" t="n">
-        <v>95.9528133451298</v>
+        <v>95.95283623103541</v>
       </c>
       <c r="F318" t="n">
-        <v>95.9528133451298</v>
+        <v>95.95283623103541</v>
       </c>
       <c r="G318" t="n">
         <v>22564000</v>
@@ -7763,16 +7763,16 @@
         <v>45755</v>
       </c>
       <c r="C319" t="n">
-        <v>95.96236419677734</v>
+        <v>95.96238708496094</v>
       </c>
       <c r="D319" t="n">
-        <v>95.97192233915132</v>
+        <v>95.97194522961465</v>
       </c>
       <c r="E319" t="n">
-        <v>95.9528133451298</v>
+        <v>95.95283623103541</v>
       </c>
       <c r="F319" t="n">
-        <v>95.95758877095358</v>
+        <v>95.95761165799817</v>
       </c>
       <c r="G319" t="n">
         <v>17116100</v>
@@ -7786,16 +7786,16 @@
         <v>45756</v>
       </c>
       <c r="C320" t="n">
-        <v>95.98149871826172</v>
+        <v>95.98149108886719</v>
       </c>
       <c r="D320" t="n">
-        <v>95.98149871826172</v>
+        <v>95.98149108886719</v>
       </c>
       <c r="E320" t="n">
-        <v>95.97194057407167</v>
+        <v>95.97193294543689</v>
       </c>
       <c r="F320" t="n">
-        <v>95.97194057407167</v>
+        <v>95.97193294543689</v>
       </c>
       <c r="G320" t="n">
         <v>21838800</v>
@@ -7809,16 +7809,16 @@
         <v>45757</v>
       </c>
       <c r="C321" t="n">
-        <v>95.98149871826172</v>
+        <v>95.98149108886719</v>
       </c>
       <c r="D321" t="n">
-        <v>95.99104957172395</v>
+        <v>95.99104194157023</v>
       </c>
       <c r="E321" t="n">
-        <v>95.98149871826172</v>
+        <v>95.98149108886719</v>
       </c>
       <c r="F321" t="n">
-        <v>95.98149871826172</v>
+        <v>95.98149108886719</v>
       </c>
       <c r="G321" t="n">
         <v>16851500</v>
@@ -7832,16 +7832,16 @@
         <v>45758</v>
       </c>
       <c r="C322" t="n">
-        <v>96.02927398681641</v>
+        <v>96.02925872802734</v>
       </c>
       <c r="D322" t="n">
-        <v>96.02927398681641</v>
+        <v>96.02925872802734</v>
       </c>
       <c r="E322" t="n">
-        <v>96.01972313344081</v>
+        <v>96.01970787616935</v>
       </c>
       <c r="F322" t="n">
-        <v>96.02449856012861</v>
+        <v>96.02448330209835</v>
       </c>
       <c r="G322" t="n">
         <v>12916600</v>
@@ -7855,16 +7855,16 @@
         <v>45761</v>
       </c>
       <c r="C323" t="n">
-        <v>96.03882598876953</v>
+        <v>96.03884124755859</v>
       </c>
       <c r="D323" t="n">
-        <v>96.03882598876953</v>
+        <v>96.03884124755859</v>
       </c>
       <c r="E323" t="n">
-        <v>96.02926784527745</v>
+        <v>96.02928310254791</v>
       </c>
       <c r="F323" t="n">
-        <v>96.02926784527745</v>
+        <v>96.02928310254791</v>
       </c>
       <c r="G323" t="n">
         <v>13772300</v>
@@ -7878,16 +7878,16 @@
         <v>45762</v>
       </c>
       <c r="C324" t="n">
-        <v>96.04840850830078</v>
+        <v>96.04837799072266</v>
       </c>
       <c r="D324" t="n">
-        <v>96.04840850830078</v>
+        <v>96.04837799072266</v>
       </c>
       <c r="E324" t="n">
-        <v>96.03885036238295</v>
+        <v>96.03881984784175</v>
       </c>
       <c r="F324" t="n">
-        <v>96.04840850830078</v>
+        <v>96.04837799072266</v>
       </c>
       <c r="G324" t="n">
         <v>10043700</v>
@@ -7901,16 +7901,16 @@
         <v>45763</v>
       </c>
       <c r="C325" t="n">
-        <v>96.0675048828125</v>
+        <v>96.06749725341797</v>
       </c>
       <c r="D325" t="n">
-        <v>96.0675048828125</v>
+        <v>96.06749725341797</v>
       </c>
       <c r="E325" t="n">
-        <v>96.05794673815093</v>
+        <v>96.05793910951549</v>
       </c>
       <c r="F325" t="n">
-        <v>96.06272945584581</v>
+        <v>96.06272182683053</v>
       </c>
       <c r="G325" t="n">
         <v>8840000</v>
@@ -7924,16 +7924,16 @@
         <v>45764</v>
       </c>
       <c r="C326" t="n">
-        <v>96.10572814941406</v>
+        <v>96.10572052001953</v>
       </c>
       <c r="D326" t="n">
-        <v>96.11528629387459</v>
+        <v>96.11527866372128</v>
       </c>
       <c r="E326" t="n">
-        <v>96.10572814941406</v>
+        <v>96.10572052001953</v>
       </c>
       <c r="F326" t="n">
-        <v>96.11050357628031</v>
+        <v>96.11049594650667</v>
       </c>
       <c r="G326" t="n">
         <v>8652700</v>
@@ -7947,16 +7947,16 @@
         <v>45768</v>
       </c>
       <c r="C327" t="n">
-        <v>96.10572814941406</v>
+        <v>96.10572052001953</v>
       </c>
       <c r="D327" t="n">
-        <v>96.11528629387459</v>
+        <v>96.11527866372128</v>
       </c>
       <c r="E327" t="n">
-        <v>96.10572814941406</v>
+        <v>96.10572052001953</v>
       </c>
       <c r="F327" t="n">
-        <v>96.11528629387459</v>
+        <v>96.11527866372128</v>
       </c>
       <c r="G327" t="n">
         <v>10756100</v>
@@ -7970,16 +7970,16 @@
         <v>45769</v>
       </c>
       <c r="C328" t="n">
-        <v>96.11527252197266</v>
+        <v>96.11528015136719</v>
       </c>
       <c r="D328" t="n">
-        <v>96.12482337433664</v>
+        <v>96.12483100448931</v>
       </c>
       <c r="E328" t="n">
-        <v>96.11527252197266</v>
+        <v>96.11528015136719</v>
       </c>
       <c r="F328" t="n">
-        <v>96.12482337433664</v>
+        <v>96.12483100448931</v>
       </c>
       <c r="G328" t="n">
         <v>11603400</v>
@@ -7993,16 +7993,16 @@
         <v>45770</v>
       </c>
       <c r="C329" t="n">
-        <v>96.14395141601562</v>
+        <v>96.14394378662109</v>
       </c>
       <c r="D329" t="n">
-        <v>96.14395141601562</v>
+        <v>96.14394378662109</v>
       </c>
       <c r="E329" t="n">
-        <v>96.1248351274963</v>
+        <v>96.12482749961872</v>
       </c>
       <c r="F329" t="n">
-        <v>96.13439327175597</v>
+        <v>96.13438564311991</v>
       </c>
       <c r="G329" t="n">
         <v>19135100</v>
@@ -8016,16 +8016,16 @@
         <v>45771</v>
       </c>
       <c r="C330" t="n">
-        <v>96.14395141601562</v>
+        <v>96.14394378662109</v>
       </c>
       <c r="D330" t="n">
-        <v>96.1535095602753</v>
+        <v>96.15350193012229</v>
       </c>
       <c r="E330" t="n">
-        <v>96.14395141601562</v>
+        <v>96.14394378662109</v>
       </c>
       <c r="F330" t="n">
-        <v>96.1535095602753</v>
+        <v>96.15350193012229</v>
       </c>
       <c r="G330" t="n">
         <v>12068700</v>
@@ -8039,16 +8039,16 @@
         <v>45772</v>
       </c>
       <c r="C331" t="n">
-        <v>96.18217468261719</v>
+        <v>96.18216705322266</v>
       </c>
       <c r="D331" t="n">
-        <v>96.18217468261719</v>
+        <v>96.18216705322266</v>
       </c>
       <c r="E331" t="n">
-        <v>96.17261653855823</v>
+        <v>96.17260890992188</v>
       </c>
       <c r="F331" t="n">
-        <v>96.18217468261719</v>
+        <v>96.18216705322266</v>
       </c>
       <c r="G331" t="n">
         <v>8822700</v>
@@ -8062,16 +8062,16 @@
         <v>45775</v>
       </c>
       <c r="C332" t="n">
-        <v>96.18217468261719</v>
+        <v>96.18216705322266</v>
       </c>
       <c r="D332" t="n">
-        <v>96.19173282667613</v>
+        <v>96.19172519652344</v>
       </c>
       <c r="E332" t="n">
-        <v>96.18217468261719</v>
+        <v>96.18216705322266</v>
       </c>
       <c r="F332" t="n">
-        <v>96.18217468261719</v>
+        <v>96.18216705322266</v>
       </c>
       <c r="G332" t="n">
         <v>9127900</v>
@@ -8085,16 +8085,16 @@
         <v>45776</v>
       </c>
       <c r="C333" t="n">
-        <v>96.19171905517578</v>
+        <v>96.19172668457031</v>
       </c>
       <c r="D333" t="n">
-        <v>96.20126990713963</v>
+        <v>96.20127753729169</v>
       </c>
       <c r="E333" t="n">
-        <v>96.19171905517578</v>
+        <v>96.19172668457031</v>
       </c>
       <c r="F333" t="n">
-        <v>96.19171905517578</v>
+        <v>96.19172668457031</v>
       </c>
       <c r="G333" t="n">
         <v>8555000</v>
@@ -8108,16 +8108,16 @@
         <v>45777</v>
       </c>
       <c r="C334" t="n">
-        <v>96.22040557861328</v>
+        <v>96.22039031982422</v>
       </c>
       <c r="D334" t="n">
-        <v>96.22040557861328</v>
+        <v>96.22039031982422</v>
       </c>
       <c r="E334" t="n">
-        <v>96.20128928938072</v>
+        <v>96.20127403362315</v>
       </c>
       <c r="F334" t="n">
-        <v>96.20128928938072</v>
+        <v>96.20127403362315</v>
       </c>
       <c r="G334" t="n">
         <v>16040200</v>
@@ -8131,16 +8131,16 @@
         <v>45778</v>
       </c>
       <c r="C335" t="n">
-        <v>96.23479461669922</v>
+        <v>96.23477935791016</v>
       </c>
       <c r="D335" t="n">
-        <v>96.23479461669922</v>
+        <v>96.23477935791016</v>
       </c>
       <c r="E335" t="n">
-        <v>96.22520456489561</v>
+        <v>96.22518930762713</v>
       </c>
       <c r="F335" t="n">
-        <v>96.23479461669922</v>
+        <v>96.23477935791016</v>
       </c>
       <c r="G335" t="n">
         <v>21288700</v>
@@ -8154,16 +8154,16 @@
         <v>45779</v>
       </c>
       <c r="C336" t="n">
-        <v>96.26354217529297</v>
+        <v>96.2635498046875</v>
       </c>
       <c r="D336" t="n">
-        <v>96.26354217529297</v>
+        <v>96.2635498046875</v>
       </c>
       <c r="E336" t="n">
-        <v>96.25395212501178</v>
+        <v>96.25395975364626</v>
       </c>
       <c r="F336" t="n">
-        <v>96.25395212501178</v>
+        <v>96.25395975364626</v>
       </c>
       <c r="G336" t="n">
         <v>13930900</v>
@@ -8177,16 +8177,16 @@
         <v>45782</v>
       </c>
       <c r="C337" t="n">
-        <v>96.27313995361328</v>
+        <v>96.27312469482422</v>
       </c>
       <c r="D337" t="n">
-        <v>96.27313995361328</v>
+        <v>96.27312469482422</v>
       </c>
       <c r="E337" t="n">
-        <v>96.26354990256227</v>
+        <v>96.26353464529318</v>
       </c>
       <c r="F337" t="n">
-        <v>96.27313995361328</v>
+        <v>96.27312469482422</v>
       </c>
       <c r="G337" t="n">
         <v>13223700</v>
@@ -8200,16 +8200,16 @@
         <v>45783</v>
       </c>
       <c r="C338" t="n">
-        <v>96.27313995361328</v>
+        <v>96.27312469482422</v>
       </c>
       <c r="D338" t="n">
-        <v>96.28272268959864</v>
+        <v>96.28270742929077</v>
       </c>
       <c r="E338" t="n">
-        <v>96.27313995361328</v>
+        <v>96.27312469482422</v>
       </c>
       <c r="F338" t="n">
-        <v>96.28272268959864</v>
+        <v>96.28270742929077</v>
       </c>
       <c r="G338" t="n">
         <v>8986000</v>
@@ -8223,16 +8223,16 @@
         <v>45784</v>
       </c>
       <c r="C339" t="n">
-        <v>96.28270721435547</v>
+        <v>96.28273773193359</v>
       </c>
       <c r="D339" t="n">
-        <v>96.29229726386509</v>
+        <v>96.29232778448286</v>
       </c>
       <c r="E339" t="n">
-        <v>96.28270721435547</v>
+        <v>96.28273773193359</v>
       </c>
       <c r="F339" t="n">
-        <v>96.29229726386509</v>
+        <v>96.29232778448286</v>
       </c>
       <c r="G339" t="n">
         <v>8509300</v>
@@ -8269,16 +8269,16 @@
         <v>45786</v>
       </c>
       <c r="C341" t="n">
-        <v>96.34024810791016</v>
+        <v>96.34026336669922</v>
       </c>
       <c r="D341" t="n">
-        <v>96.34024810791016</v>
+        <v>96.34026336669922</v>
       </c>
       <c r="E341" t="n">
-        <v>96.33065805761299</v>
+        <v>96.33067331488314</v>
       </c>
       <c r="F341" t="n">
-        <v>96.33065805761299</v>
+        <v>96.33067331488314</v>
       </c>
       <c r="G341" t="n">
         <v>11793700</v>
@@ -8292,16 +8292,16 @@
         <v>45789</v>
       </c>
       <c r="C342" t="n">
-        <v>96.34024810791016</v>
+        <v>96.34026336669922</v>
       </c>
       <c r="D342" t="n">
-        <v>96.34983084314226</v>
+        <v>96.34984610344908</v>
       </c>
       <c r="E342" t="n">
-        <v>96.34024810791016</v>
+        <v>96.34026336669922</v>
       </c>
       <c r="F342" t="n">
-        <v>96.34024810791016</v>
+        <v>96.34026336669922</v>
       </c>
       <c r="G342" t="n">
         <v>16808300</v>
@@ -8315,16 +8315,16 @@
         <v>45790</v>
       </c>
       <c r="C343" t="n">
-        <v>96.35942077636719</v>
+        <v>96.35941314697266</v>
       </c>
       <c r="D343" t="n">
-        <v>96.35942077636719</v>
+        <v>96.35941314697266</v>
       </c>
       <c r="E343" t="n">
-        <v>96.34983072608168</v>
+        <v>96.34982309744645</v>
       </c>
       <c r="F343" t="n">
-        <v>96.34983072608168</v>
+        <v>96.34982309744645</v>
       </c>
       <c r="G343" t="n">
         <v>18174400</v>
@@ -8338,16 +8338,16 @@
         <v>45791</v>
       </c>
       <c r="C344" t="n">
-        <v>96.36902618408203</v>
+        <v>96.36901092529297</v>
       </c>
       <c r="D344" t="n">
-        <v>96.36902618408203</v>
+        <v>96.36901092529297</v>
       </c>
       <c r="E344" t="n">
-        <v>96.35943613226824</v>
+        <v>96.35942087499764</v>
       </c>
       <c r="F344" t="n">
-        <v>96.35943613226824</v>
+        <v>96.35942087499764</v>
       </c>
       <c r="G344" t="n">
         <v>9821100</v>
@@ -8361,16 +8361,16 @@
         <v>45792</v>
       </c>
       <c r="C345" t="n">
-        <v>96.36902618408203</v>
+        <v>96.36901092529297</v>
       </c>
       <c r="D345" t="n">
-        <v>96.37860892082961</v>
+        <v>96.37859366052324</v>
       </c>
       <c r="E345" t="n">
-        <v>96.36902618408203</v>
+        <v>96.36901092529297</v>
       </c>
       <c r="F345" t="n">
-        <v>96.37860892082961</v>
+        <v>96.37859366052324</v>
       </c>
       <c r="G345" t="n">
         <v>10057600</v>
@@ -8384,16 +8384,16 @@
         <v>45793</v>
       </c>
       <c r="C346" t="n">
-        <v>96.40736389160156</v>
+        <v>96.40737152099609</v>
       </c>
       <c r="D346" t="n">
-        <v>96.4169466268398</v>
+        <v>96.41695425699268</v>
       </c>
       <c r="E346" t="n">
-        <v>96.40736389160156</v>
+        <v>96.40737152099609</v>
       </c>
       <c r="F346" t="n">
-        <v>96.40736389160156</v>
+        <v>96.40737152099609</v>
       </c>
       <c r="G346" t="n">
         <v>10109300</v>
@@ -8430,16 +8430,16 @@
         <v>45797</v>
       </c>
       <c r="C348" t="n">
-        <v>96.43611907958984</v>
+        <v>96.43613433837891</v>
       </c>
       <c r="D348" t="n">
-        <v>96.43611907958984</v>
+        <v>96.43613433837891</v>
       </c>
       <c r="E348" t="n">
-        <v>96.42652903004708</v>
+        <v>96.42654428731873</v>
       </c>
       <c r="F348" t="n">
-        <v>96.43611907958984</v>
+        <v>96.43613433837891</v>
       </c>
       <c r="G348" t="n">
         <v>9249100</v>
@@ -8476,16 +8476,16 @@
         <v>45799</v>
       </c>
       <c r="C350" t="n">
-        <v>96.46489715576172</v>
+        <v>96.46488189697266</v>
       </c>
       <c r="D350" t="n">
-        <v>96.46489715576172</v>
+        <v>96.46488189697266</v>
       </c>
       <c r="E350" t="n">
-        <v>96.45530710470361</v>
+        <v>96.4552918474315</v>
       </c>
       <c r="F350" t="n">
-        <v>96.45530710470361</v>
+        <v>96.4552918474315</v>
       </c>
       <c r="G350" t="n">
         <v>8901700</v>
@@ -8499,16 +8499,16 @@
         <v>45800</v>
       </c>
       <c r="C351" t="n">
-        <v>96.49364471435547</v>
+        <v>96.49365234375</v>
       </c>
       <c r="D351" t="n">
-        <v>96.50323476389502</v>
+        <v>96.5032423940478</v>
       </c>
       <c r="E351" t="n">
-        <v>96.49364471435547</v>
+        <v>96.49365234375</v>
       </c>
       <c r="F351" t="n">
-        <v>96.50323476389502</v>
+        <v>96.5032423940478</v>
       </c>
       <c r="G351" t="n">
         <v>9119400</v>
@@ -8522,16 +8522,16 @@
         <v>45804</v>
       </c>
       <c r="C352" t="n">
-        <v>96.50324249267578</v>
+        <v>96.50322723388672</v>
       </c>
       <c r="D352" t="n">
-        <v>96.51283254298339</v>
+        <v>96.51281728267797</v>
       </c>
       <c r="E352" t="n">
-        <v>96.50324249267578</v>
+        <v>96.50322723388672</v>
       </c>
       <c r="F352" t="n">
-        <v>96.51283254298339</v>
+        <v>96.51281728267797</v>
       </c>
       <c r="G352" t="n">
         <v>10526600</v>
@@ -8545,16 +8545,16 @@
         <v>45805</v>
       </c>
       <c r="C353" t="n">
-        <v>96.53202056884766</v>
+        <v>96.53200531005859</v>
       </c>
       <c r="D353" t="n">
-        <v>96.53202056884766</v>
+        <v>96.53200531005859</v>
       </c>
       <c r="E353" t="n">
-        <v>96.522430517026</v>
+        <v>96.52241525975282</v>
       </c>
       <c r="F353" t="n">
-        <v>96.52722920046995</v>
+        <v>96.52721394243824</v>
       </c>
       <c r="G353" t="n">
         <v>8415200</v>
@@ -8568,16 +8568,16 @@
         <v>45806</v>
       </c>
       <c r="C354" t="n">
-        <v>96.53202056884766</v>
+        <v>96.53200531005859</v>
       </c>
       <c r="D354" t="n">
-        <v>96.54161062066933</v>
+        <v>96.54159536036435</v>
       </c>
       <c r="E354" t="n">
-        <v>96.522430517026</v>
+        <v>96.52241525975282</v>
       </c>
       <c r="F354" t="n">
-        <v>96.53202056884766</v>
+        <v>96.53200531005859</v>
       </c>
       <c r="G354" t="n">
         <v>10387000</v>
@@ -8591,16 +8591,16 @@
         <v>45807</v>
       </c>
       <c r="C355" t="n">
-        <v>96.56076812744141</v>
+        <v>96.56077575683594</v>
       </c>
       <c r="D355" t="n">
-        <v>96.57035817774533</v>
+        <v>96.57036580789759</v>
       </c>
       <c r="E355" t="n">
-        <v>96.56076812744141</v>
+        <v>96.56077575683594</v>
       </c>
       <c r="F355" t="n">
-        <v>96.56076812744141</v>
+        <v>96.56077575683594</v>
       </c>
       <c r="G355" t="n">
         <v>14209500</v>
@@ -8614,16 +8614,16 @@
         <v>45810</v>
       </c>
       <c r="C356" t="n">
-        <v>96.58769989013672</v>
+        <v>96.58771514892578</v>
       </c>
       <c r="D356" t="n">
-        <v>96.58769989013672</v>
+        <v>96.58771514892578</v>
       </c>
       <c r="E356" t="n">
-        <v>96.57808296990129</v>
+        <v>96.57809822717108</v>
       </c>
       <c r="F356" t="n">
-        <v>96.58769989013672</v>
+        <v>96.58771514892578</v>
       </c>
       <c r="G356" t="n">
         <v>21934000</v>
@@ -8637,16 +8637,16 @@
         <v>45811</v>
       </c>
       <c r="C357" t="n">
-        <v>96.59733581542969</v>
+        <v>96.59732818603516</v>
       </c>
       <c r="D357" t="n">
-        <v>96.59733581542969</v>
+        <v>96.59732818603516</v>
       </c>
       <c r="E357" t="n">
-        <v>96.58771155287167</v>
+        <v>96.58770392423726</v>
       </c>
       <c r="F357" t="n">
-        <v>96.59252735473136</v>
+        <v>96.5925197257166</v>
       </c>
       <c r="G357" t="n">
         <v>11979500</v>
@@ -8660,16 +8660,16 @@
         <v>45812</v>
       </c>
       <c r="C358" t="n">
-        <v>96.60695648193359</v>
+        <v>96.60696411132812</v>
       </c>
       <c r="D358" t="n">
-        <v>96.60695648193359</v>
+        <v>96.60696411132812</v>
       </c>
       <c r="E358" t="n">
-        <v>96.59733221973381</v>
+        <v>96.59733984836828</v>
       </c>
       <c r="F358" t="n">
-        <v>96.60214068025316</v>
+        <v>96.60214830926736</v>
       </c>
       <c r="G358" t="n">
         <v>8923800</v>
@@ -8683,16 +8683,16 @@
         <v>45813</v>
       </c>
       <c r="C359" t="n">
-        <v>96.61659240722656</v>
+        <v>96.6165771484375</v>
       </c>
       <c r="D359" t="n">
-        <v>96.61659240722656</v>
+        <v>96.6165771484375</v>
       </c>
       <c r="E359" t="n">
-        <v>96.60696814386499</v>
+        <v>96.60695288659591</v>
       </c>
       <c r="F359" t="n">
-        <v>96.61659240722656</v>
+        <v>96.6165771484375</v>
       </c>
       <c r="G359" t="n">
         <v>9915800</v>
@@ -8706,16 +8706,16 @@
         <v>45814</v>
       </c>
       <c r="C360" t="n">
-        <v>96.64544677734375</v>
+        <v>96.64545440673828</v>
       </c>
       <c r="D360" t="n">
-        <v>96.65506369844093</v>
+        <v>96.65507132859463</v>
       </c>
       <c r="E360" t="n">
-        <v>96.64544677734375</v>
+        <v>96.64545440673828</v>
       </c>
       <c r="F360" t="n">
-        <v>96.65025523789234</v>
+        <v>96.65026286766646</v>
       </c>
       <c r="G360" t="n">
         <v>9122400</v>
@@ -8729,16 +8729,16 @@
         <v>45817</v>
       </c>
       <c r="C361" t="n">
-        <v>96.65506744384766</v>
+        <v>96.65505981445312</v>
       </c>
       <c r="D361" t="n">
-        <v>96.66469170647891</v>
+        <v>96.66468407632469</v>
       </c>
       <c r="E361" t="n">
-        <v>96.65506744384766</v>
+        <v>96.65505981445312</v>
       </c>
       <c r="F361" t="n">
-        <v>96.65506744384766</v>
+        <v>96.65505981445312</v>
       </c>
       <c r="G361" t="n">
         <v>9902100</v>
@@ -8752,16 +8752,16 @@
         <v>45818</v>
       </c>
       <c r="C362" t="n">
-        <v>96.66468811035156</v>
+        <v>96.66469573974609</v>
       </c>
       <c r="D362" t="n">
-        <v>96.67431237262477</v>
+        <v>96.67432000277891</v>
       </c>
       <c r="E362" t="n">
-        <v>96.66468811035156</v>
+        <v>96.66469573974609</v>
       </c>
       <c r="F362" t="n">
-        <v>96.6694965709076</v>
+        <v>96.66950420068163</v>
       </c>
       <c r="G362" t="n">
         <v>9201800</v>
@@ -8775,16 +8775,16 @@
         <v>45819</v>
       </c>
       <c r="C363" t="n">
-        <v>96.68394470214844</v>
+        <v>96.68395233154297</v>
       </c>
       <c r="D363" t="n">
-        <v>96.68394470214844</v>
+        <v>96.68395233154297</v>
       </c>
       <c r="E363" t="n">
-        <v>96.67432043907218</v>
+        <v>96.67432806770725</v>
       </c>
       <c r="F363" t="n">
-        <v>96.67912890002943</v>
+        <v>96.67913652904394</v>
       </c>
       <c r="G363" t="n">
         <v>10138800</v>
@@ -8798,16 +8798,16 @@
         <v>45820</v>
       </c>
       <c r="C364" t="n">
-        <v>96.69355010986328</v>
+        <v>96.69356536865234</v>
       </c>
       <c r="D364" t="n">
-        <v>96.69355010986328</v>
+        <v>96.69356536865234</v>
       </c>
       <c r="E364" t="n">
-        <v>96.68393318909396</v>
+        <v>96.68394844636542</v>
       </c>
       <c r="F364" t="n">
-        <v>96.69355010986328</v>
+        <v>96.69356536865234</v>
       </c>
       <c r="G364" t="n">
         <v>9574900</v>
@@ -8867,16 +8867,16 @@
         <v>45825</v>
       </c>
       <c r="C367" t="n">
-        <v>96.74168395996094</v>
+        <v>96.74166870117188</v>
       </c>
       <c r="D367" t="n">
-        <v>96.75130822386905</v>
+        <v>96.75129296356198</v>
       </c>
       <c r="E367" t="n">
-        <v>96.74168395996094</v>
+        <v>96.74166870117188</v>
       </c>
       <c r="F367" t="n">
-        <v>96.75130822386905</v>
+        <v>96.75129296356198</v>
       </c>
       <c r="G367" t="n">
         <v>8734500</v>
@@ -8890,16 +8890,16 @@
         <v>45826</v>
       </c>
       <c r="C368" t="n">
-        <v>96.76091766357422</v>
+        <v>96.76090240478516</v>
       </c>
       <c r="D368" t="n">
-        <v>96.77054192673803</v>
+        <v>96.77052666643127</v>
       </c>
       <c r="E368" t="n">
-        <v>96.76091766357422</v>
+        <v>96.76090240478516</v>
       </c>
       <c r="F368" t="n">
-        <v>96.77054192673803</v>
+        <v>96.77052666643127</v>
       </c>
       <c r="G368" t="n">
         <v>9783400</v>
@@ -8913,16 +8913,16 @@
         <v>45828</v>
       </c>
       <c r="C369" t="n">
-        <v>96.79939270019531</v>
+        <v>96.79940032958984</v>
       </c>
       <c r="D369" t="n">
-        <v>96.80901696190008</v>
+        <v>96.80902459205316</v>
       </c>
       <c r="E369" t="n">
-        <v>96.79939270019531</v>
+        <v>96.79940032958984</v>
       </c>
       <c r="F369" t="n">
-        <v>96.80420850162805</v>
+        <v>96.80421613140216</v>
       </c>
       <c r="G369" t="n">
         <v>9399400</v>
@@ -8936,16 +8936,16 @@
         <v>45831</v>
       </c>
       <c r="C370" t="n">
-        <v>96.81864166259766</v>
+        <v>96.81865692138672</v>
       </c>
       <c r="D370" t="n">
-        <v>96.81864166259766</v>
+        <v>96.81865692138672</v>
       </c>
       <c r="E370" t="n">
-        <v>96.80901740084924</v>
+        <v>96.80903265812152</v>
       </c>
       <c r="F370" t="n">
-        <v>96.81382586114307</v>
+        <v>96.81384111917316</v>
       </c>
       <c r="G370" t="n">
         <v>8847300</v>
@@ -8959,16 +8959,16 @@
         <v>45832</v>
       </c>
       <c r="C371" t="n">
-        <v>96.82827758789062</v>
+        <v>96.82826232910156</v>
       </c>
       <c r="D371" t="n">
-        <v>96.837901851528</v>
+        <v>96.8378865912223</v>
       </c>
       <c r="E371" t="n">
-        <v>96.82827758789062</v>
+        <v>96.82826232910156</v>
       </c>
       <c r="F371" t="n">
-        <v>96.83309339029041</v>
+        <v>96.83307813074245</v>
       </c>
       <c r="G371" t="n">
         <v>10132100</v>
@@ -8982,16 +8982,16 @@
         <v>45833</v>
       </c>
       <c r="C372" t="n">
-        <v>96.83787536621094</v>
+        <v>96.837890625</v>
       </c>
       <c r="D372" t="n">
-        <v>96.84749962721607</v>
+        <v>96.84751488752164</v>
       </c>
       <c r="E372" t="n">
-        <v>96.83787536621094</v>
+        <v>96.837890625</v>
       </c>
       <c r="F372" t="n">
-        <v>96.84268382613341</v>
+        <v>96.84269908568015</v>
       </c>
       <c r="G372" t="n">
         <v>8015100</v>
@@ -9005,16 +9005,16 @@
         <v>45834</v>
       </c>
       <c r="C373" t="n">
-        <v>96.84751129150391</v>
+        <v>96.84749603271484</v>
       </c>
       <c r="D373" t="n">
-        <v>96.85713555366819</v>
+        <v>96.85712029336277</v>
       </c>
       <c r="E373" t="n">
-        <v>96.84751129150391</v>
+        <v>96.84749603271484</v>
       </c>
       <c r="F373" t="n">
-        <v>96.85713555366819</v>
+        <v>96.85712029336277</v>
       </c>
       <c r="G373" t="n">
         <v>9277700</v>
@@ -9028,16 +9028,16 @@
         <v>45835</v>
       </c>
       <c r="C374" t="n">
-        <v>96.88602447509766</v>
+        <v>96.88600158691406</v>
       </c>
       <c r="D374" t="n">
-        <v>96.88602447509766</v>
+        <v>96.88600158691406</v>
       </c>
       <c r="E374" t="n">
-        <v>96.87640021060137</v>
+        <v>96.87637732469139</v>
       </c>
       <c r="F374" t="n">
-        <v>96.88120867226809</v>
+        <v>96.88118578522216</v>
       </c>
       <c r="G374" t="n">
         <v>9742300</v>
@@ -9051,16 +9051,16 @@
         <v>45838</v>
       </c>
       <c r="C375" t="n">
-        <v>96.88602447509766</v>
+        <v>96.88600158691406</v>
       </c>
       <c r="D375" t="n">
-        <v>96.89564139843111</v>
+        <v>96.89561850797561</v>
       </c>
       <c r="E375" t="n">
-        <v>96.88602447509766</v>
+        <v>96.88600158691406</v>
       </c>
       <c r="F375" t="n">
-        <v>96.88602447509766</v>
+        <v>96.88600158691406</v>
       </c>
       <c r="G375" t="n">
         <v>18195600</v>
@@ -9074,16 +9074,16 @@
         <v>45839</v>
       </c>
       <c r="C376" t="n">
-        <v>96.91207122802734</v>
+        <v>96.91207885742188</v>
       </c>
       <c r="D376" t="n">
-        <v>96.91207122802734</v>
+        <v>96.91207885742188</v>
       </c>
       <c r="E376" t="n">
-        <v>96.90241368381817</v>
+        <v>96.90242131245242</v>
       </c>
       <c r="F376" t="n">
-        <v>96.91207122802734</v>
+        <v>96.91207885742188</v>
       </c>
       <c r="G376" t="n">
         <v>24173900</v>
@@ -9097,16 +9097,16 @@
         <v>45840</v>
       </c>
       <c r="C377" t="n">
-        <v>96.91207122802734</v>
+        <v>96.91207885742188</v>
       </c>
       <c r="D377" t="n">
-        <v>96.92172140568869</v>
+        <v>96.92172903584292</v>
       </c>
       <c r="E377" t="n">
-        <v>96.91207122802734</v>
+        <v>96.91207885742188</v>
       </c>
       <c r="F377" t="n">
-        <v>96.92172140568869</v>
+        <v>96.92172903584292</v>
       </c>
       <c r="G377" t="n">
         <v>10850800</v>
@@ -9120,16 +9120,16 @@
         <v>45841</v>
       </c>
       <c r="C378" t="n">
-        <v>96.96035003662109</v>
+        <v>96.96035766601562</v>
       </c>
       <c r="D378" t="n">
-        <v>96.97000758141002</v>
+        <v>96.97001521156446</v>
       </c>
       <c r="E378" t="n">
-        <v>96.96035003662109</v>
+        <v>96.96035766601562</v>
       </c>
       <c r="F378" t="n">
-        <v>96.96035003662109</v>
+        <v>96.96035766601562</v>
       </c>
       <c r="G378" t="n">
         <v>7404700</v>
@@ -9143,16 +9143,16 @@
         <v>45845</v>
       </c>
       <c r="C379" t="n">
-        <v>96.97966003417969</v>
+        <v>96.97967529296875</v>
       </c>
       <c r="D379" t="n">
-        <v>96.97966003417969</v>
+        <v>96.97967529296875</v>
       </c>
       <c r="E379" t="n">
-        <v>96.97000248989785</v>
+        <v>96.97001774716739</v>
       </c>
       <c r="F379" t="n">
-        <v>96.97966003417969</v>
+        <v>96.97967529296875</v>
       </c>
       <c r="G379" t="n">
         <v>12363900</v>
@@ -9166,16 +9166,16 @@
         <v>45846</v>
       </c>
       <c r="C380" t="n">
-        <v>96.99896240234375</v>
+        <v>96.99897766113281</v>
       </c>
       <c r="D380" t="n">
-        <v>96.99896240234375</v>
+        <v>96.99897766113281</v>
       </c>
       <c r="E380" t="n">
-        <v>96.97965468139364</v>
+        <v>96.97966993714543</v>
       </c>
       <c r="F380" t="n">
-        <v>96.98930485859495</v>
+        <v>96.9893201158648</v>
       </c>
       <c r="G380" t="n">
         <v>13107800</v>
@@ -9189,16 +9189,16 @@
         <v>45847</v>
       </c>
       <c r="C381" t="n">
-        <v>96.98930358886719</v>
+        <v>96.98931121826172</v>
       </c>
       <c r="D381" t="n">
-        <v>96.99896113248955</v>
+        <v>96.99896876264377</v>
       </c>
       <c r="E381" t="n">
-        <v>96.98930358886719</v>
+        <v>96.98931121826172</v>
       </c>
       <c r="F381" t="n">
-        <v>96.99896113248955</v>
+        <v>96.99896876264377</v>
       </c>
       <c r="G381" t="n">
         <v>11156600</v>
@@ -9212,16 +9212,16 @@
         <v>45848</v>
       </c>
       <c r="C382" t="n">
-        <v>97.00862884521484</v>
+        <v>97.00862121582031</v>
       </c>
       <c r="D382" t="n">
-        <v>97.01828638984958</v>
+        <v>97.01827875969551</v>
       </c>
       <c r="E382" t="n">
-        <v>96.99897130058011</v>
+        <v>96.99896367194511</v>
       </c>
       <c r="F382" t="n">
-        <v>97.00862884521484</v>
+        <v>97.00862121582031</v>
       </c>
       <c r="G382" t="n">
         <v>10071700</v>
@@ -9327,16 +9327,16 @@
         <v>45855</v>
       </c>
       <c r="C387" t="n">
-        <v>97.09552001953125</v>
+        <v>97.09551239013672</v>
       </c>
       <c r="D387" t="n">
-        <v>97.09552001953125</v>
+        <v>97.09551239013672</v>
       </c>
       <c r="E387" t="n">
-        <v>97.08586984190462</v>
+        <v>97.08586221326836</v>
       </c>
       <c r="F387" t="n">
-        <v>97.09069493071793</v>
+        <v>97.09068730170253</v>
       </c>
       <c r="G387" t="n">
         <v>9040400</v>
@@ -9350,16 +9350,16 @@
         <v>45856</v>
       </c>
       <c r="C388" t="n">
-        <v>97.12449645996094</v>
+        <v>97.12448883056641</v>
       </c>
       <c r="D388" t="n">
-        <v>97.12449645996094</v>
+        <v>97.12448883056641</v>
       </c>
       <c r="E388" t="n">
-        <v>97.11484628122402</v>
+        <v>97.11483865258754</v>
       </c>
       <c r="F388" t="n">
-        <v>97.11484628122402</v>
+        <v>97.11483865258754</v>
       </c>
       <c r="G388" t="n">
         <v>9399500</v>
@@ -9396,16 +9396,16 @@
         <v>45860</v>
       </c>
       <c r="C390" t="n">
-        <v>97.15345764160156</v>
+        <v>97.15346527099609</v>
       </c>
       <c r="D390" t="n">
-        <v>97.15345764160156</v>
+        <v>97.15346527099609</v>
       </c>
       <c r="E390" t="n">
-        <v>97.1438000974546</v>
+        <v>97.14380772609073</v>
       </c>
       <c r="F390" t="n">
-        <v>97.15345764160156</v>
+        <v>97.15346527099609</v>
       </c>
       <c r="G390" t="n">
         <v>9340600</v>
@@ -9419,16 +9419,16 @@
         <v>45861</v>
       </c>
       <c r="C391" t="n">
-        <v>97.16312408447266</v>
+        <v>97.16310882568359</v>
       </c>
       <c r="D391" t="n">
-        <v>97.16312408447266</v>
+        <v>97.16310882568359</v>
       </c>
       <c r="E391" t="n">
-        <v>97.15347390525802</v>
+        <v>97.15345864798445</v>
       </c>
       <c r="F391" t="n">
-        <v>97.16312408447266</v>
+        <v>97.16310882568359</v>
       </c>
       <c r="G391" t="n">
         <v>8056100</v>
@@ -9442,16 +9442,16 @@
         <v>45862</v>
       </c>
       <c r="C392" t="n">
-        <v>97.17276000976562</v>
+        <v>97.17276763916016</v>
       </c>
       <c r="D392" t="n">
-        <v>97.17276000976562</v>
+        <v>97.17276763916016</v>
       </c>
       <c r="E392" t="n">
-        <v>97.16310246615073</v>
+        <v>97.16311009478702</v>
       </c>
       <c r="F392" t="n">
-        <v>97.16310246615073</v>
+        <v>97.16311009478702</v>
       </c>
       <c r="G392" t="n">
         <v>10701600</v>
@@ -9465,16 +9465,16 @@
         <v>45863</v>
       </c>
       <c r="C393" t="n">
-        <v>97.19207000732422</v>
+        <v>97.19208526611328</v>
       </c>
       <c r="D393" t="n">
-        <v>97.20172018388638</v>
+        <v>97.20173544419048</v>
       </c>
       <c r="E393" t="n">
-        <v>97.19207000732422</v>
+        <v>97.19208526611328</v>
       </c>
       <c r="F393" t="n">
-        <v>97.20172018388638</v>
+        <v>97.20173544419048</v>
       </c>
       <c r="G393" t="n">
         <v>9776600</v>
@@ -9488,16 +9488,16 @@
         <v>45866</v>
       </c>
       <c r="C394" t="n">
-        <v>97.22105407714844</v>
+        <v>97.22103881835938</v>
       </c>
       <c r="D394" t="n">
-        <v>97.22105407714844</v>
+        <v>97.22103881835938</v>
       </c>
       <c r="E394" t="n">
-        <v>97.21139653217107</v>
+        <v>97.21138127489775</v>
       </c>
       <c r="F394" t="n">
-        <v>97.21622162138554</v>
+        <v>97.21620636335493</v>
       </c>
       <c r="G394" t="n">
         <v>11581000</v>
@@ -9511,16 +9511,16 @@
         <v>45867</v>
       </c>
       <c r="C395" t="n">
-        <v>97.22105407714844</v>
+        <v>97.22103881835938</v>
       </c>
       <c r="D395" t="n">
-        <v>97.23070425557738</v>
+        <v>97.23068899527374</v>
       </c>
       <c r="E395" t="n">
-        <v>97.22105407714844</v>
+        <v>97.22103881835938</v>
       </c>
       <c r="F395" t="n">
-        <v>97.22105407714844</v>
+        <v>97.22103881835938</v>
       </c>
       <c r="G395" t="n">
         <v>8622300</v>
@@ -9534,16 +9534,16 @@
         <v>45868</v>
       </c>
       <c r="C396" t="n">
-        <v>97.24036407470703</v>
+        <v>97.2403564453125</v>
       </c>
       <c r="D396" t="n">
-        <v>97.24036407470703</v>
+        <v>97.2403564453125</v>
       </c>
       <c r="E396" t="n">
-        <v>97.23070652950381</v>
+        <v>97.230698900867</v>
       </c>
       <c r="F396" t="n">
-        <v>97.23070652950381</v>
+        <v>97.230698900867</v>
       </c>
       <c r="G396" t="n">
         <v>9106000</v>
@@ -9626,16 +9626,16 @@
         <v>45874</v>
       </c>
       <c r="C400" t="n">
-        <v>97.31008911132812</v>
+        <v>97.31009674072266</v>
       </c>
       <c r="D400" t="n">
-        <v>97.31008911132812</v>
+        <v>97.31009674072266</v>
       </c>
       <c r="E400" t="n">
-        <v>97.30040412458681</v>
+        <v>97.30041175322201</v>
       </c>
       <c r="F400" t="n">
-        <v>97.30040412458681</v>
+        <v>97.30041175322201</v>
       </c>
       <c r="G400" t="n">
         <v>12350300</v>
@@ -9695,16 +9695,16 @@
         <v>45877</v>
       </c>
       <c r="C403" t="n">
-        <v>97.36824035644531</v>
+        <v>97.36824798583984</v>
       </c>
       <c r="D403" t="n">
-        <v>97.36824035644531</v>
+        <v>97.36824798583984</v>
       </c>
       <c r="E403" t="n">
-        <v>97.35854797615043</v>
+        <v>97.35855560478551</v>
       </c>
       <c r="F403" t="n">
-        <v>97.36339046973788</v>
+        <v>97.3633980987524</v>
       </c>
       <c r="G403" t="n">
         <v>12066300</v>
@@ -9718,16 +9718,16 @@
         <v>45880</v>
       </c>
       <c r="C404" t="n">
-        <v>97.37791442871094</v>
+        <v>97.37792205810547</v>
       </c>
       <c r="D404" t="n">
-        <v>97.37791442871094</v>
+        <v>97.37792205810547</v>
       </c>
       <c r="E404" t="n">
-        <v>97.36822944262161</v>
+        <v>97.36823707125734</v>
       </c>
       <c r="F404" t="n">
-        <v>97.37791442871094</v>
+        <v>97.37792205810547</v>
       </c>
       <c r="G404" t="n">
         <v>12940300</v>
@@ -9741,16 +9741,16 @@
         <v>45881</v>
       </c>
       <c r="C405" t="n">
-        <v>97.37791442871094</v>
+        <v>97.37792205810547</v>
       </c>
       <c r="D405" t="n">
-        <v>97.38760680791941</v>
+        <v>97.38761443807333</v>
       </c>
       <c r="E405" t="n">
-        <v>97.37791442871094</v>
+        <v>97.37792205810547</v>
       </c>
       <c r="F405" t="n">
-        <v>97.38760680791941</v>
+        <v>97.38761443807333</v>
       </c>
       <c r="G405" t="n">
         <v>12918200</v>
@@ -9764,16 +9764,16 @@
         <v>45882</v>
       </c>
       <c r="C406" t="n">
-        <v>97.39730072021484</v>
+        <v>97.39730834960938</v>
       </c>
       <c r="D406" t="n">
-        <v>97.40698570645661</v>
+        <v>97.4069933366098</v>
       </c>
       <c r="E406" t="n">
-        <v>97.3876083408538</v>
+        <v>97.3876159694891</v>
       </c>
       <c r="F406" t="n">
-        <v>97.39730072021484</v>
+        <v>97.39730834960938</v>
       </c>
       <c r="G406" t="n">
         <v>12144800</v>
@@ -9833,16 +9833,16 @@
         <v>45887</v>
       </c>
       <c r="C409" t="n">
-        <v>97.46514892578125</v>
+        <v>97.46513366699219</v>
       </c>
       <c r="D409" t="n">
-        <v>97.46514892578125</v>
+        <v>97.46513366699219</v>
       </c>
       <c r="E409" t="n">
-        <v>97.44576416381005</v>
+        <v>97.4457489080558</v>
       </c>
       <c r="F409" t="n">
-        <v>97.45545654479565</v>
+        <v>97.455441287524</v>
       </c>
       <c r="G409" t="n">
         <v>14768500</v>
@@ -9856,16 +9856,16 @@
         <v>45888</v>
       </c>
       <c r="C410" t="n">
-        <v>97.46514892578125</v>
+        <v>97.46513366699219</v>
       </c>
       <c r="D410" t="n">
-        <v>97.47483391364634</v>
+        <v>97.47481865334103</v>
       </c>
       <c r="E410" t="n">
-        <v>97.46514892578125</v>
+        <v>97.46513366699219</v>
       </c>
       <c r="F410" t="n">
-        <v>97.47483391364634</v>
+        <v>97.47481865334103</v>
       </c>
       <c r="G410" t="n">
         <v>10474900</v>
@@ -9879,16 +9879,16 @@
         <v>45889</v>
       </c>
       <c r="C411" t="n">
-        <v>97.48450469970703</v>
+        <v>97.48451995849609</v>
       </c>
       <c r="D411" t="n">
-        <v>97.48450469970703</v>
+        <v>97.48451995849609</v>
       </c>
       <c r="E411" t="n">
-        <v>97.47481232086851</v>
+        <v>97.47482757814046</v>
       </c>
       <c r="F411" t="n">
-        <v>97.48450469970703</v>
+        <v>97.48451995849609</v>
       </c>
       <c r="G411" t="n">
         <v>10922100</v>
@@ -9902,16 +9902,16 @@
         <v>45890</v>
       </c>
       <c r="C412" t="n">
-        <v>97.48450469970703</v>
+        <v>97.48451995849609</v>
       </c>
       <c r="D412" t="n">
-        <v>97.49419707854555</v>
+        <v>97.49421233885172</v>
       </c>
       <c r="E412" t="n">
-        <v>97.48450469970703</v>
+        <v>97.48451995849609</v>
       </c>
       <c r="F412" t="n">
-        <v>97.49419707854555</v>
+        <v>97.49421233885172</v>
       </c>
       <c r="G412" t="n">
         <v>8765300</v>
@@ -9948,16 +9948,16 @@
         <v>45894</v>
       </c>
       <c r="C414" t="n">
-        <v>97.54264831542969</v>
+        <v>97.54265594482422</v>
       </c>
       <c r="D414" t="n">
-        <v>97.54264831542969</v>
+        <v>97.54265594482422</v>
       </c>
       <c r="E414" t="n">
-        <v>97.53295593691551</v>
+        <v>97.53296356555194</v>
       </c>
       <c r="F414" t="n">
-        <v>97.53779842961329</v>
+        <v>97.53780605862848</v>
       </c>
       <c r="G414" t="n">
         <v>13556000</v>
@@ -9971,16 +9971,16 @@
         <v>45895</v>
       </c>
       <c r="C415" t="n">
-        <v>97.54264831542969</v>
+        <v>97.54265594482422</v>
       </c>
       <c r="D415" t="n">
-        <v>97.55233330082524</v>
+        <v>97.55234093097729</v>
       </c>
       <c r="E415" t="n">
-        <v>97.54264831542969</v>
+        <v>97.54265594482422</v>
       </c>
       <c r="F415" t="n">
-        <v>97.54749080812746</v>
+        <v>97.54749843790076</v>
       </c>
       <c r="G415" t="n">
         <v>8741600</v>
@@ -9994,16 +9994,16 @@
         <v>45896</v>
       </c>
       <c r="C416" t="n">
-        <v>97.55235290527344</v>
+        <v>97.55233764648438</v>
       </c>
       <c r="D416" t="n">
-        <v>97.56204528573542</v>
+        <v>97.56203002543032</v>
       </c>
       <c r="E416" t="n">
-        <v>97.55235290527344</v>
+        <v>97.55233764648438</v>
       </c>
       <c r="F416" t="n">
-        <v>97.56204528573542</v>
+        <v>97.56203002543032</v>
       </c>
       <c r="G416" t="n">
         <v>7384600</v>
@@ -10040,16 +10040,16 @@
         <v>45898</v>
       </c>
       <c r="C418" t="n">
-        <v>97.62017822265625</v>
+        <v>97.62018585205078</v>
       </c>
       <c r="D418" t="n">
-        <v>97.62017822265625</v>
+        <v>97.62018585205078</v>
       </c>
       <c r="E418" t="n">
-        <v>97.60080085615444</v>
+        <v>97.60080848403456</v>
       </c>
       <c r="F418" t="n">
-        <v>97.60080085615444</v>
+        <v>97.60080848403456</v>
       </c>
       <c r="G418" t="n">
         <v>21369400</v>
@@ -10086,16 +10086,16 @@
         <v>45903</v>
       </c>
       <c r="C420" t="n">
-        <v>97.63963317871094</v>
+        <v>97.63964080810547</v>
       </c>
       <c r="D420" t="n">
-        <v>97.63963317871094</v>
+        <v>97.63964080810547</v>
       </c>
       <c r="E420" t="n">
-        <v>97.62990603829556</v>
+        <v>97.62991366693002</v>
       </c>
       <c r="F420" t="n">
-        <v>97.63476589868615</v>
+        <v>97.63477352770036</v>
       </c>
       <c r="G420" t="n">
         <v>14296000</v>
@@ -10155,16 +10155,16 @@
         <v>45908</v>
       </c>
       <c r="C423" t="n">
-        <v>97.70771026611328</v>
+        <v>97.70770263671875</v>
       </c>
       <c r="D423" t="n">
-        <v>97.70771026611328</v>
+        <v>97.70770263671875</v>
       </c>
       <c r="E423" t="n">
-        <v>97.69798312550439</v>
+        <v>97.69797549686939</v>
       </c>
       <c r="F423" t="n">
-        <v>97.70284298599168</v>
+        <v>97.70283535697719</v>
       </c>
       <c r="G423" t="n">
         <v>12715100</v>
@@ -10178,16 +10178,16 @@
         <v>45909</v>
       </c>
       <c r="C424" t="n">
-        <v>97.70771026611328</v>
+        <v>97.70770263671875</v>
       </c>
       <c r="D424" t="n">
-        <v>97.71743740672217</v>
+        <v>97.71742977656811</v>
       </c>
       <c r="E424" t="n">
-        <v>97.70771026611328</v>
+        <v>97.70770263671875</v>
       </c>
       <c r="F424" t="n">
-        <v>97.71743740672217</v>
+        <v>97.71742977656811</v>
       </c>
       <c r="G424" t="n">
         <v>11005500</v>
@@ -10247,16 +10247,16 @@
         <v>45912</v>
       </c>
       <c r="C427" t="n">
-        <v>97.76605224609375</v>
+        <v>97.76606750488281</v>
       </c>
       <c r="D427" t="n">
-        <v>97.77577938610324</v>
+        <v>97.77579464641046</v>
       </c>
       <c r="E427" t="n">
-        <v>97.76605224609375</v>
+        <v>97.76606750488281</v>
       </c>
       <c r="F427" t="n">
-        <v>97.76605224609375</v>
+        <v>97.76606750488281</v>
       </c>
       <c r="G427" t="n">
         <v>10482000</v>
@@ -10270,16 +10270,16 @@
         <v>45915</v>
       </c>
       <c r="C428" t="n">
-        <v>97.76605224609375</v>
+        <v>97.76606750488281</v>
       </c>
       <c r="D428" t="n">
-        <v>97.77577938610324</v>
+        <v>97.77579464641046</v>
       </c>
       <c r="E428" t="n">
-        <v>97.76605224609375</v>
+        <v>97.76606750488281</v>
       </c>
       <c r="F428" t="n">
-        <v>97.76605224609375</v>
+        <v>97.76606750488281</v>
       </c>
       <c r="G428" t="n">
         <v>15288300</v>
@@ -10316,16 +10316,16 @@
         <v>45917</v>
       </c>
       <c r="C430" t="n">
-        <v>97.79522705078125</v>
+        <v>97.79521942138672</v>
       </c>
       <c r="D430" t="n">
-        <v>97.80495419087075</v>
+        <v>97.80494656071735</v>
       </c>
       <c r="E430" t="n">
-        <v>97.79522705078125</v>
+        <v>97.79521942138672</v>
       </c>
       <c r="F430" t="n">
-        <v>97.80495419087075</v>
+        <v>97.80494656071735</v>
       </c>
       <c r="G430" t="n">
         <v>10381200</v>
@@ -10339,16 +10339,16 @@
         <v>45918</v>
       </c>
       <c r="C431" t="n">
-        <v>97.81468963623047</v>
+        <v>97.81468200683594</v>
       </c>
       <c r="D431" t="n">
-        <v>97.81468963623047</v>
+        <v>97.81468200683594</v>
       </c>
       <c r="E431" t="n">
-        <v>97.80496249531507</v>
+        <v>97.80495486667922</v>
       </c>
       <c r="F431" t="n">
-        <v>97.81468963623047</v>
+        <v>97.81468200683594</v>
       </c>
       <c r="G431" t="n">
         <v>13414500</v>
@@ -10362,16 +10362,16 @@
         <v>45919</v>
       </c>
       <c r="C432" t="n">
-        <v>97.85358428955078</v>
+        <v>97.85357666015625</v>
       </c>
       <c r="D432" t="n">
-        <v>97.85358428955078</v>
+        <v>97.85357666015625</v>
       </c>
       <c r="E432" t="n">
-        <v>97.84385714928058</v>
+        <v>97.84384952064445</v>
       </c>
       <c r="F432" t="n">
-        <v>97.84385714928058</v>
+        <v>97.84384952064445</v>
       </c>
       <c r="G432" t="n">
         <v>11174000</v>
@@ -10385,16 +10385,16 @@
         <v>45922</v>
       </c>
       <c r="C433" t="n">
-        <v>97.85358428955078</v>
+        <v>97.85357666015625</v>
       </c>
       <c r="D433" t="n">
-        <v>97.86330401018691</v>
+        <v>97.86329638003455</v>
       </c>
       <c r="E433" t="n">
-        <v>97.85358428955078</v>
+        <v>97.85357666015625</v>
       </c>
       <c r="F433" t="n">
-        <v>97.85358428955078</v>
+        <v>97.85357666015625</v>
       </c>
       <c r="G433" t="n">
         <v>12279500</v>
@@ -10431,16 +10431,16 @@
         <v>45924</v>
       </c>
       <c r="C435" t="n">
-        <v>97.88276672363281</v>
+        <v>97.88275909423828</v>
       </c>
       <c r="D435" t="n">
-        <v>97.88276672363281</v>
+        <v>97.88275909423828</v>
       </c>
       <c r="E435" t="n">
-        <v>97.87303958252458</v>
+        <v>97.87303195388823</v>
       </c>
       <c r="F435" t="n">
-        <v>97.87789944326134</v>
+        <v>97.8778918142462</v>
       </c>
       <c r="G435" t="n">
         <v>10108500</v>
@@ -10454,16 +10454,16 @@
         <v>45925</v>
       </c>
       <c r="C436" t="n">
-        <v>97.89247131347656</v>
+        <v>97.89247894287109</v>
       </c>
       <c r="D436" t="n">
-        <v>97.89247131347656</v>
+        <v>97.89247894287109</v>
       </c>
       <c r="E436" t="n">
-        <v>97.88274417460916</v>
+        <v>97.88275180324558</v>
       </c>
       <c r="F436" t="n">
-        <v>97.88274417460916</v>
+        <v>97.88275180324558</v>
       </c>
       <c r="G436" t="n">
         <v>10549100</v>
@@ -10546,16 +10546,16 @@
         <v>45931</v>
       </c>
       <c r="C440" t="n">
-        <v>97.94796752929688</v>
+        <v>97.94797515869141</v>
       </c>
       <c r="D440" t="n">
-        <v>97.95772085802308</v>
+        <v>97.95772848817732</v>
       </c>
       <c r="E440" t="n">
-        <v>97.94796752929688</v>
+        <v>97.94797515869141</v>
       </c>
       <c r="F440" t="n">
-        <v>97.95772085802308</v>
+        <v>97.95772848817732</v>
       </c>
       <c r="G440" t="n">
         <v>26613600</v>
@@ -10569,16 +10569,16 @@
         <v>45932</v>
       </c>
       <c r="C441" t="n">
-        <v>97.95771789550781</v>
+        <v>97.95773315429688</v>
       </c>
       <c r="D441" t="n">
-        <v>97.96747866922793</v>
+        <v>97.96749392953743</v>
       </c>
       <c r="E441" t="n">
-        <v>97.95771789550781</v>
+        <v>97.95773315429688</v>
       </c>
       <c r="F441" t="n">
-        <v>97.96747866922793</v>
+        <v>97.96749392953743</v>
       </c>
       <c r="G441" t="n">
         <v>12870100</v>
@@ -10638,16 +10638,16 @@
         <v>45937</v>
       </c>
       <c r="C444" t="n">
-        <v>98.01628112792969</v>
+        <v>98.01628875732422</v>
       </c>
       <c r="D444" t="n">
-        <v>98.01628112792969</v>
+        <v>98.01628875732422</v>
       </c>
       <c r="E444" t="n">
-        <v>98.00652035360855</v>
+        <v>98.00652798224331</v>
       </c>
       <c r="F444" t="n">
-        <v>98.01628112792969</v>
+        <v>98.01628875732422</v>
       </c>
       <c r="G444" t="n">
         <v>14289100</v>
@@ -10684,16 +10684,16 @@
         <v>45939</v>
       </c>
       <c r="C446" t="n">
-        <v>98.03579711914062</v>
+        <v>98.03580474853516</v>
       </c>
       <c r="D446" t="n">
-        <v>98.04555789364973</v>
+        <v>98.04556552380387</v>
       </c>
       <c r="E446" t="n">
-        <v>98.02603634463152</v>
+        <v>98.02604397326645</v>
       </c>
       <c r="F446" t="n">
-        <v>98.04555789364973</v>
+        <v>98.04556552380387</v>
       </c>
       <c r="G446" t="n">
         <v>15718900</v>
@@ -10707,16 +10707,16 @@
         <v>45940</v>
       </c>
       <c r="C447" t="n">
-        <v>98.08460235595703</v>
+        <v>98.0845947265625</v>
       </c>
       <c r="D447" t="n">
-        <v>98.08460235595703</v>
+        <v>98.0845947265625</v>
       </c>
       <c r="E447" t="n">
-        <v>98.06508080518547</v>
+        <v>98.06507317730942</v>
       </c>
       <c r="F447" t="n">
-        <v>98.07484158057125</v>
+        <v>98.07483395193596</v>
       </c>
       <c r="G447" t="n">
         <v>18966600</v>
@@ -10730,16 +10730,16 @@
         <v>45943</v>
       </c>
       <c r="C448" t="n">
-        <v>98.07483673095703</v>
+        <v>98.07484436035156</v>
       </c>
       <c r="D448" t="n">
-        <v>98.08459750586016</v>
+        <v>98.08460513601399</v>
       </c>
       <c r="E448" t="n">
-        <v>98.07483673095703</v>
+        <v>98.07484436035156</v>
       </c>
       <c r="F448" t="n">
-        <v>98.07483673095703</v>
+        <v>98.07484436035156</v>
       </c>
       <c r="G448" t="n">
         <v>14453500</v>
@@ -10753,16 +10753,16 @@
         <v>45944</v>
       </c>
       <c r="C449" t="n">
-        <v>98.08460235595703</v>
+        <v>98.0845947265625</v>
       </c>
       <c r="D449" t="n">
-        <v>98.09435568605265</v>
+        <v>98.09434805589947</v>
       </c>
       <c r="E449" t="n">
-        <v>98.08460235595703</v>
+        <v>98.0845947265625</v>
       </c>
       <c r="F449" t="n">
-        <v>98.08460235595703</v>
+        <v>98.0845947265625</v>
       </c>
       <c r="G449" t="n">
         <v>13475000</v>
@@ -10799,16 +10799,16 @@
         <v>45946</v>
       </c>
       <c r="C451" t="n">
-        <v>98.11386871337891</v>
+        <v>98.11387634277344</v>
       </c>
       <c r="D451" t="n">
-        <v>98.11386871337891</v>
+        <v>98.11387634277344</v>
       </c>
       <c r="E451" t="n">
-        <v>98.10410793884108</v>
+        <v>98.1041155674766</v>
       </c>
       <c r="F451" t="n">
-        <v>98.11386871337891</v>
+        <v>98.11387634277344</v>
       </c>
       <c r="G451" t="n">
         <v>12394500</v>
@@ -10845,16 +10845,16 @@
         <v>45950</v>
       </c>
       <c r="C453" t="n">
-        <v>98.15290069580078</v>
+        <v>98.15290832519531</v>
       </c>
       <c r="D453" t="n">
-        <v>98.15290069580078</v>
+        <v>98.15290832519531</v>
       </c>
       <c r="E453" t="n">
-        <v>98.14313992162796</v>
+        <v>98.14314755026379</v>
       </c>
       <c r="F453" t="n">
-        <v>98.15290069580078</v>
+        <v>98.15290832519531</v>
       </c>
       <c r="G453" t="n">
         <v>16129100</v>
@@ -10868,16 +10868,16 @@
         <v>45951</v>
       </c>
       <c r="C454" t="n">
-        <v>98.17242431640625</v>
+        <v>98.17241668701172</v>
       </c>
       <c r="D454" t="n">
-        <v>98.17242431640625</v>
+        <v>98.17241668701172</v>
       </c>
       <c r="E454" t="n">
-        <v>98.16266354128715</v>
+        <v>98.16265591265116</v>
       </c>
       <c r="F454" t="n">
-        <v>98.16266354128715</v>
+        <v>98.16265591265116</v>
       </c>
       <c r="G454" t="n">
         <v>12061900</v>
@@ -10914,16 +10914,16 @@
         <v>45953</v>
       </c>
       <c r="C456" t="n">
-        <v>98.19194030761719</v>
+        <v>98.19194793701172</v>
       </c>
       <c r="D456" t="n">
-        <v>98.19194030761719</v>
+        <v>98.19194793701172</v>
       </c>
       <c r="E456" t="n">
-        <v>98.18217953305069</v>
+        <v>98.18218716168681</v>
       </c>
       <c r="F456" t="n">
-        <v>98.19194030761719</v>
+        <v>98.19194793701172</v>
       </c>
       <c r="G456" t="n">
         <v>10658100</v>
@@ -10937,16 +10937,16 @@
         <v>45954</v>
       </c>
       <c r="C457" t="n">
-        <v>98.22121429443359</v>
+        <v>98.22120666503906</v>
       </c>
       <c r="D457" t="n">
-        <v>98.22121429443359</v>
+        <v>98.22120666503906</v>
       </c>
       <c r="E457" t="n">
-        <v>98.21145351995568</v>
+        <v>98.21144589131933</v>
       </c>
       <c r="F457" t="n">
-        <v>98.22121429443359</v>
+        <v>98.22120666503906</v>
       </c>
       <c r="G457" t="n">
         <v>12382000</v>
@@ -10960,16 +10960,16 @@
         <v>45957</v>
       </c>
       <c r="C458" t="n">
-        <v>98.23097991943359</v>
+        <v>98.23096466064453</v>
       </c>
       <c r="D458" t="n">
-        <v>98.24073324910366</v>
+        <v>98.24071798879955</v>
       </c>
       <c r="E458" t="n">
-        <v>98.22121914447372</v>
+        <v>98.22120388720086</v>
       </c>
       <c r="F458" t="n">
-        <v>98.22121914447372</v>
+        <v>98.22120388720086</v>
       </c>
       <c r="G458" t="n">
         <v>26389600</v>
@@ -10983,16 +10983,16 @@
         <v>45958</v>
       </c>
       <c r="C459" t="n">
-        <v>98.24073028564453</v>
+        <v>98.24072265625</v>
       </c>
       <c r="D459" t="n">
-        <v>98.25049106030998</v>
+        <v>98.25048343015742</v>
       </c>
       <c r="E459" t="n">
-        <v>98.24073028564453</v>
+        <v>98.24072265625</v>
       </c>
       <c r="F459" t="n">
-        <v>98.24073028564453</v>
+        <v>98.24072265625</v>
       </c>
       <c r="G459" t="n">
         <v>11134700</v>
@@ -11006,16 +11006,16 @@
         <v>45959</v>
       </c>
       <c r="C460" t="n">
-        <v>98.25049591064453</v>
+        <v>98.25048065185547</v>
       </c>
       <c r="D460" t="n">
-        <v>98.26025668579183</v>
+        <v>98.26024142548688</v>
       </c>
       <c r="E460" t="n">
-        <v>98.25049591064453</v>
+        <v>98.25048065185547</v>
       </c>
       <c r="F460" t="n">
-        <v>98.26025668579183</v>
+        <v>98.26024142548688</v>
       </c>
       <c r="G460" t="n">
         <v>14177700</v>
@@ -11029,16 +11029,16 @@
         <v>45960</v>
       </c>
       <c r="C461" t="n">
-        <v>98.26024627685547</v>
+        <v>98.26025390625</v>
       </c>
       <c r="D461" t="n">
-        <v>98.26999960567962</v>
+        <v>98.27000723583144</v>
       </c>
       <c r="E461" t="n">
-        <v>98.26024627685547</v>
+        <v>98.26025390625</v>
       </c>
       <c r="F461" t="n">
-        <v>98.26024627685547</v>
+        <v>98.26025390625</v>
       </c>
       <c r="G461" t="n">
         <v>12370700</v>
@@ -11052,16 +11052,16 @@
         <v>45961</v>
       </c>
       <c r="C462" t="n">
-        <v>98.28952789306641</v>
+        <v>98.28951263427734</v>
       </c>
       <c r="D462" t="n">
-        <v>98.29928866784897</v>
+        <v>98.29927340754462</v>
       </c>
       <c r="E462" t="n">
-        <v>98.28952789306641</v>
+        <v>98.28951263427734</v>
       </c>
       <c r="F462" t="n">
-        <v>98.29440455781285</v>
+        <v>98.29438929826671</v>
       </c>
       <c r="G462" t="n">
         <v>23254100</v>
@@ -11075,16 +11075,16 @@
         <v>45964</v>
       </c>
       <c r="C463" t="n">
-        <v>98.31694030761719</v>
+        <v>98.31694793701172</v>
       </c>
       <c r="D463" t="n">
-        <v>98.31694030761719</v>
+        <v>98.31694793701172</v>
       </c>
       <c r="E463" t="n">
-        <v>98.30714569192223</v>
+        <v>98.30715332055669</v>
       </c>
       <c r="F463" t="n">
-        <v>98.31203926421834</v>
+        <v>98.31204689323255</v>
       </c>
       <c r="G463" t="n">
         <v>27049200</v>
@@ -11098,16 +11098,16 @@
         <v>45965</v>
       </c>
       <c r="C464" t="n">
-        <v>98.31694030761719</v>
+        <v>98.31694793701172</v>
       </c>
       <c r="D464" t="n">
-        <v>98.31694030761719</v>
+        <v>98.31694793701172</v>
       </c>
       <c r="E464" t="n">
-        <v>98.31203926421834</v>
+        <v>98.31204689323255</v>
       </c>
       <c r="F464" t="n">
-        <v>98.31694030761719</v>
+        <v>98.31694793701172</v>
       </c>
       <c r="G464" t="n">
         <v>15707500</v>
@@ -11121,16 +11121,16 @@
         <v>45966</v>
       </c>
       <c r="C465" t="n">
-        <v>98.33653259277344</v>
+        <v>98.33651733398438</v>
       </c>
       <c r="D465" t="n">
-        <v>98.33653259277344</v>
+        <v>98.33651733398438</v>
       </c>
       <c r="E465" t="n">
-        <v>98.3267454471337</v>
+        <v>98.32673018986331</v>
       </c>
       <c r="F465" t="n">
-        <v>98.3267454471337</v>
+        <v>98.32673018986331</v>
       </c>
       <c r="G465" t="n">
         <v>11335000</v>
@@ -11144,16 +11144,16 @@
         <v>45967</v>
       </c>
       <c r="C466" t="n">
-        <v>98.34632110595703</v>
+        <v>98.3463134765625</v>
       </c>
       <c r="D466" t="n">
-        <v>98.34632110595703</v>
+        <v>98.3463134765625</v>
       </c>
       <c r="E466" t="n">
-        <v>98.33652648982164</v>
+        <v>98.33651886118693</v>
       </c>
       <c r="F466" t="n">
-        <v>98.34632110595703</v>
+        <v>98.3463134765625</v>
       </c>
       <c r="G466" t="n">
         <v>16658100</v>
@@ -11190,16 +11190,16 @@
         <v>45971</v>
       </c>
       <c r="C468" t="n">
-        <v>98.38548278808594</v>
+        <v>98.385498046875</v>
       </c>
       <c r="D468" t="n">
-        <v>98.39527740329436</v>
+        <v>98.39529266360249</v>
       </c>
       <c r="E468" t="n">
-        <v>98.38548278808594</v>
+        <v>98.385498046875</v>
       </c>
       <c r="F468" t="n">
-        <v>98.39527740329436</v>
+        <v>98.39529266360249</v>
       </c>
       <c r="G468" t="n">
         <v>14121900</v>
@@ -11213,16 +11213,16 @@
         <v>45972</v>
       </c>
       <c r="C469" t="n">
-        <v>98.39529418945312</v>
+        <v>98.39528656005859</v>
       </c>
       <c r="D469" t="n">
-        <v>98.39529418945312</v>
+        <v>98.39528656005859</v>
       </c>
       <c r="E469" t="n">
-        <v>98.38549957257375</v>
+        <v>98.38549194393867</v>
       </c>
       <c r="F469" t="n">
-        <v>98.39529418945312</v>
+        <v>98.39528656005859</v>
       </c>
       <c r="G469" t="n">
         <v>8697800</v>
@@ -11259,16 +11259,16 @@
         <v>45974</v>
       </c>
       <c r="C471" t="n">
-        <v>98.41487121582031</v>
+        <v>98.41486358642578</v>
       </c>
       <c r="D471" t="n">
-        <v>98.41487121582031</v>
+        <v>98.41486358642578</v>
       </c>
       <c r="E471" t="n">
-        <v>98.4050765994123</v>
+        <v>98.40506897077708</v>
       </c>
       <c r="F471" t="n">
-        <v>98.4050765994123</v>
+        <v>98.40506897077708</v>
       </c>
       <c r="G471" t="n">
         <v>11255600</v>
@@ -11282,16 +11282,16 @@
         <v>45975</v>
       </c>
       <c r="C472" t="n">
-        <v>98.44424438476562</v>
+        <v>98.44425964355469</v>
       </c>
       <c r="D472" t="n">
-        <v>98.44424438476562</v>
+        <v>98.44425964355469</v>
       </c>
       <c r="E472" t="n">
-        <v>98.43444976867691</v>
+        <v>98.43446502594782</v>
       </c>
       <c r="F472" t="n">
-        <v>98.44424438476562</v>
+        <v>98.44425964355469</v>
       </c>
       <c r="G472" t="n">
         <v>13522500</v>
@@ -11305,16 +11305,16 @@
         <v>45978</v>
       </c>
       <c r="C473" t="n">
-        <v>98.45404052734375</v>
+        <v>98.45404815673828</v>
       </c>
       <c r="D473" t="n">
-        <v>98.45404052734375</v>
+        <v>98.45404815673828</v>
       </c>
       <c r="E473" t="n">
-        <v>98.44424591110318</v>
+        <v>98.4442535397387</v>
       </c>
       <c r="F473" t="n">
-        <v>98.44914695477505</v>
+        <v>98.44915458379036</v>
       </c>
       <c r="G473" t="n">
         <v>15032800</v>
@@ -11328,16 +11328,16 @@
         <v>45979</v>
       </c>
       <c r="C474" t="n">
-        <v>98.45404052734375</v>
+        <v>98.45404815673828</v>
       </c>
       <c r="D474" t="n">
-        <v>98.46383514358433</v>
+        <v>98.46384277373785</v>
       </c>
       <c r="E474" t="n">
-        <v>98.45404052734375</v>
+        <v>98.45404815673828</v>
       </c>
       <c r="F474" t="n">
-        <v>98.45404052734375</v>
+        <v>98.45404815673828</v>
       </c>
       <c r="G474" t="n">
         <v>13130300</v>
@@ -11374,16 +11374,16 @@
         <v>45981</v>
       </c>
       <c r="C476" t="n">
-        <v>98.49320220947266</v>
+        <v>98.49321746826172</v>
       </c>
       <c r="D476" t="n">
-        <v>98.49320220947266</v>
+        <v>98.49321746826172</v>
       </c>
       <c r="E476" t="n">
-        <v>98.47361297884351</v>
+        <v>98.47362823459777</v>
       </c>
       <c r="F476" t="n">
-        <v>98.47361297884351</v>
+        <v>98.47362823459777</v>
       </c>
       <c r="G476" t="n">
         <v>15261700</v>
@@ -11420,16 +11420,16 @@
         <v>45985</v>
       </c>
       <c r="C478" t="n">
-        <v>98.52259063720703</v>
+        <v>98.5225830078125</v>
       </c>
       <c r="D478" t="n">
-        <v>98.53238525371985</v>
+        <v>98.53237762356683</v>
       </c>
       <c r="E478" t="n">
-        <v>98.52259063720703</v>
+        <v>98.5225830078125</v>
       </c>
       <c r="F478" t="n">
-        <v>98.52259063720703</v>
+        <v>98.5225830078125</v>
       </c>
       <c r="G478" t="n">
         <v>15830800</v>
@@ -11443,16 +11443,16 @@
         <v>45986</v>
       </c>
       <c r="C479" t="n">
-        <v>98.54217529296875</v>
+        <v>98.54216766357422</v>
       </c>
       <c r="D479" t="n">
-        <v>98.54217529296875</v>
+        <v>98.54216766357422</v>
       </c>
       <c r="E479" t="n">
-        <v>98.53238814727189</v>
+        <v>98.53238051863511</v>
       </c>
       <c r="F479" t="n">
-        <v>98.54217529296875</v>
+        <v>98.54216766357422</v>
       </c>
       <c r="G479" t="n">
         <v>19115000</v>
@@ -11466,16 +11466,16 @@
         <v>45987</v>
       </c>
       <c r="C480" t="n">
-        <v>98.55196380615234</v>
+        <v>98.55195617675781</v>
       </c>
       <c r="D480" t="n">
-        <v>98.56175842234617</v>
+        <v>98.56175079219341</v>
       </c>
       <c r="E480" t="n">
-        <v>98.55196380615234</v>
+        <v>98.55195617675781</v>
       </c>
       <c r="F480" t="n">
-        <v>98.55196380615234</v>
+        <v>98.55195617675781</v>
       </c>
       <c r="G480" t="n">
         <v>11948500</v>
@@ -11489,16 +11489,16 @@
         <v>45989</v>
       </c>
       <c r="C481" t="n">
-        <v>98.58134460449219</v>
+        <v>98.58133697509766</v>
       </c>
       <c r="D481" t="n">
-        <v>98.59113922112526</v>
+        <v>98.59113159097269</v>
       </c>
       <c r="E481" t="n">
-        <v>98.57155745896257</v>
+        <v>98.57154983032548</v>
       </c>
       <c r="F481" t="n">
-        <v>98.58134460449219</v>
+        <v>98.58133697509766</v>
       </c>
       <c r="G481" t="n">
         <v>24417500</v>
@@ -11535,16 +11535,16 @@
         <v>45993</v>
       </c>
       <c r="C483" t="n">
-        <v>98.62357330322266</v>
+        <v>98.62358093261719</v>
       </c>
       <c r="D483" t="n">
-        <v>98.62357330322266</v>
+        <v>98.62358093261719</v>
       </c>
       <c r="E483" t="n">
-        <v>98.61374813986885</v>
+        <v>98.61375576850331</v>
       </c>
       <c r="F483" t="n">
-        <v>98.61374813986885</v>
+        <v>98.61375576850331</v>
       </c>
       <c r="G483" t="n">
         <v>14362600</v>
@@ -11558,16 +11558,16 @@
         <v>45994</v>
       </c>
       <c r="C484" t="n">
-        <v>98.63339233398438</v>
+        <v>98.63340759277344</v>
       </c>
       <c r="D484" t="n">
-        <v>98.63830116815419</v>
+        <v>98.63831642770265</v>
       </c>
       <c r="E484" t="n">
-        <v>98.63339233398438</v>
+        <v>98.63340759277344</v>
       </c>
       <c r="F484" t="n">
-        <v>98.63339233398438</v>
+        <v>98.63340759277344</v>
       </c>
       <c r="G484" t="n">
         <v>15531600</v>
@@ -11604,16 +11604,16 @@
         <v>45996</v>
       </c>
       <c r="C486" t="n">
-        <v>98.68251037597656</v>
+        <v>98.68251800537109</v>
       </c>
       <c r="D486" t="n">
-        <v>98.68251037597656</v>
+        <v>98.68251800537109</v>
       </c>
       <c r="E486" t="n">
-        <v>98.67268521251508</v>
+        <v>98.67269284115001</v>
       </c>
       <c r="F486" t="n">
-        <v>98.67268521251508</v>
+        <v>98.67269284115001</v>
       </c>
       <c r="G486" t="n">
         <v>17918100</v>
@@ -11627,16 +11627,16 @@
         <v>45999</v>
       </c>
       <c r="C487" t="n">
-        <v>98.68251037597656</v>
+        <v>98.68251800537109</v>
       </c>
       <c r="D487" t="n">
-        <v>98.68251037597656</v>
+        <v>98.68251800537109</v>
       </c>
       <c r="E487" t="n">
-        <v>98.67268521251508</v>
+        <v>98.67269284115001</v>
       </c>
       <c r="F487" t="n">
-        <v>98.68251037597656</v>
+        <v>98.68251800537109</v>
       </c>
       <c r="G487" t="n">
         <v>16657900</v>
@@ -11650,16 +11650,16 @@
         <v>46000</v>
       </c>
       <c r="C488" t="n">
-        <v>98.69232940673828</v>
+        <v>98.69234466552734</v>
       </c>
       <c r="D488" t="n">
-        <v>98.69723824096205</v>
+        <v>98.69725350051007</v>
       </c>
       <c r="E488" t="n">
-        <v>98.69232940673828</v>
+        <v>98.69234466552734</v>
       </c>
       <c r="F488" t="n">
-        <v>98.69232940673828</v>
+        <v>98.69234466552734</v>
       </c>
       <c r="G488" t="n">
         <v>11016400</v>
@@ -11673,16 +11673,16 @@
         <v>46001</v>
       </c>
       <c r="C489" t="n">
-        <v>98.69232940673828</v>
+        <v>98.69234466552734</v>
       </c>
       <c r="D489" t="n">
-        <v>98.70215456958923</v>
+        <v>98.70216982989736</v>
       </c>
       <c r="E489" t="n">
-        <v>98.69232940673828</v>
+        <v>98.69234466552734</v>
       </c>
       <c r="F489" t="n">
-        <v>98.70215456958923</v>
+        <v>98.70216982989736</v>
       </c>
       <c r="G489" t="n">
         <v>12234900</v>
@@ -11719,16 +11719,16 @@
         <v>46003</v>
       </c>
       <c r="C491" t="n">
-        <v>98.75127410888672</v>
+        <v>98.75128173828125</v>
       </c>
       <c r="D491" t="n">
-        <v>98.75127410888672</v>
+        <v>98.75128173828125</v>
       </c>
       <c r="E491" t="n">
-        <v>98.7414489451688</v>
+        <v>98.74145657380426</v>
       </c>
       <c r="F491" t="n">
-        <v>98.7414489451688</v>
+        <v>98.74145657380426</v>
       </c>
       <c r="G491" t="n">
         <v>13320200</v>
@@ -11742,16 +11742,16 @@
         <v>46006</v>
       </c>
       <c r="C492" t="n">
-        <v>98.75127410888672</v>
+        <v>98.75128173828125</v>
       </c>
       <c r="D492" t="n">
-        <v>98.76109927260465</v>
+        <v>98.76110690275826</v>
       </c>
       <c r="E492" t="n">
-        <v>98.75127410888672</v>
+        <v>98.75128173828125</v>
       </c>
       <c r="F492" t="n">
-        <v>98.75127410888672</v>
+        <v>98.75128173828125</v>
       </c>
       <c r="G492" t="n">
         <v>14767900</v>
@@ -11765,16 +11765,16 @@
         <v>46007</v>
       </c>
       <c r="C493" t="n">
-        <v>98.76110076904297</v>
+        <v>98.7611083984375</v>
       </c>
       <c r="D493" t="n">
-        <v>98.77092593290978</v>
+        <v>98.77093356306331</v>
       </c>
       <c r="E493" t="n">
-        <v>98.76110076904297</v>
+        <v>98.7611083984375</v>
       </c>
       <c r="F493" t="n">
-        <v>98.77092593290978</v>
+        <v>98.77093356306331</v>
       </c>
       <c r="G493" t="n">
         <v>10701200</v>
@@ -11880,16 +11880,16 @@
         <v>46014</v>
       </c>
       <c r="C498" t="n">
-        <v>98.83298492431641</v>
+        <v>98.83297729492188</v>
       </c>
       <c r="D498" t="n">
-        <v>98.84284174922669</v>
+        <v>98.84283411907127</v>
       </c>
       <c r="E498" t="n">
-        <v>98.83298492431641</v>
+        <v>98.83297729492188</v>
       </c>
       <c r="F498" t="n">
-        <v>98.84284174922669</v>
+        <v>98.84283411907127</v>
       </c>
       <c r="G498" t="n">
         <v>12256200</v>
@@ -11949,16 +11949,16 @@
         <v>46020</v>
       </c>
       <c r="C501" t="n">
-        <v>98.90196228027344</v>
+        <v>98.90196990966797</v>
       </c>
       <c r="D501" t="n">
-        <v>98.90196228027344</v>
+        <v>98.90196990966797</v>
       </c>
       <c r="E501" t="n">
-        <v>98.89210545589947</v>
+        <v>98.89211308453363</v>
       </c>
       <c r="F501" t="n">
-        <v>98.89210545589947</v>
+        <v>98.89211308453363</v>
       </c>
       <c r="G501" t="n">
         <v>17350200</v>
@@ -12018,16 +12018,16 @@
         <v>46024</v>
       </c>
       <c r="C504" t="n">
-        <v>98.95123291015625</v>
+        <v>98.95124053955078</v>
       </c>
       <c r="D504" t="n">
-        <v>98.96108221538158</v>
+        <v>98.96108984553553</v>
       </c>
       <c r="E504" t="n">
-        <v>98.95123291015625</v>
+        <v>98.95124053955078</v>
       </c>
       <c r="F504" t="n">
-        <v>98.95123291015625</v>
+        <v>98.95124053955078</v>
       </c>
       <c r="G504" t="n">
         <v>19188800</v>
@@ -12041,16 +12041,16 @@
         <v>46027</v>
       </c>
       <c r="C505" t="n">
-        <v>98.96109008789062</v>
+        <v>98.96108245849609</v>
       </c>
       <c r="D505" t="n">
-        <v>98.96602225944926</v>
+        <v>98.96601462967449</v>
       </c>
       <c r="E505" t="n">
-        <v>98.96109008789062</v>
+        <v>98.96108245849609</v>
       </c>
       <c r="F505" t="n">
-        <v>98.96109008789062</v>
+        <v>98.96108245849609</v>
       </c>
       <c r="G505" t="n">
         <v>25006600</v>
@@ -12064,16 +12064,16 @@
         <v>46028</v>
       </c>
       <c r="C506" t="n">
-        <v>98.97095489501953</v>
+        <v>98.970947265625</v>
       </c>
       <c r="D506" t="n">
-        <v>98.97095489501953</v>
+        <v>98.970947265625</v>
       </c>
       <c r="E506" t="n">
-        <v>98.97095489501953</v>
+        <v>98.970947265625</v>
       </c>
       <c r="F506" t="n">
-        <v>98.97095489501953</v>
+        <v>98.970947265625</v>
       </c>
       <c r="G506" t="n">
         <v>17635000</v>
@@ -12087,16 +12087,16 @@
         <v>46029</v>
       </c>
       <c r="C507" t="n">
-        <v>98.98080444335938</v>
+        <v>98.98079681396484</v>
       </c>
       <c r="D507" t="n">
-        <v>98.98080444335938</v>
+        <v>98.98079681396484</v>
       </c>
       <c r="E507" t="n">
-        <v>98.98080444335938</v>
+        <v>98.98079681396484</v>
       </c>
       <c r="F507" t="n">
-        <v>98.98080444335938</v>
+        <v>98.98079681396484</v>
       </c>
       <c r="G507" t="n">
         <v>14062300</v>
@@ -12133,16 +12133,16 @@
         <v>46031</v>
       </c>
       <c r="C509" t="n">
-        <v>99.01036071777344</v>
+        <v>99.01036834716797</v>
       </c>
       <c r="D509" t="n">
-        <v>99.02021754174173</v>
+        <v>99.0202251718958</v>
       </c>
       <c r="E509" t="n">
-        <v>99.01036071777344</v>
+        <v>99.01036834716797</v>
       </c>
       <c r="F509" t="n">
-        <v>99.02021754174173</v>
+        <v>99.0202251718958</v>
       </c>
       <c r="G509" t="n">
         <v>15053500</v>
@@ -12225,16 +12225,16 @@
         <v>46037</v>
       </c>
       <c r="C513" t="n">
-        <v>99.05963134765625</v>
+        <v>99.05963897705078</v>
       </c>
       <c r="D513" t="n">
-        <v>99.05963134765625</v>
+        <v>99.05963897705078</v>
       </c>
       <c r="E513" t="n">
-        <v>99.04978204208787</v>
+        <v>99.04978967072383</v>
       </c>
       <c r="F513" t="n">
-        <v>99.04978204208787</v>
+        <v>99.04978967072383</v>
       </c>
       <c r="G513" t="n">
         <v>11469500</v>
@@ -12317,16 +12317,16 @@
         <v>46044</v>
       </c>
       <c r="C517" t="n">
-        <v>99.11875915527344</v>
+        <v>99.11876678466797</v>
       </c>
       <c r="D517" t="n">
-        <v>99.11875915527344</v>
+        <v>99.11876678466797</v>
       </c>
       <c r="E517" t="n">
-        <v>99.10890233170993</v>
+        <v>99.10890996034576</v>
       </c>
       <c r="F517" t="n">
-        <v>99.11875915527344</v>
+        <v>99.11876678466797</v>
       </c>
       <c r="G517" t="n">
         <v>13618500</v>
@@ -12409,16 +12409,16 @@
         <v>46050</v>
       </c>
       <c r="C521" t="n">
-        <v>99.17788696289062</v>
+        <v>99.17789459228516</v>
       </c>
       <c r="D521" t="n">
-        <v>99.17788696289062</v>
+        <v>99.17789459228516</v>
       </c>
       <c r="E521" t="n">
-        <v>99.16803013913795</v>
+        <v>99.16803776777424</v>
       </c>
       <c r="F521" t="n">
-        <v>99.16803013913795</v>
+        <v>99.16803776777424</v>
       </c>
       <c r="G521" t="n">
         <v>11987500</v>
@@ -12432,16 +12432,16 @@
         <v>46051</v>
       </c>
       <c r="C522" t="n">
-        <v>99.18775177001953</v>
+        <v>99.187744140625</v>
       </c>
       <c r="D522" t="n">
-        <v>99.18775177001953</v>
+        <v>99.187744140625</v>
       </c>
       <c r="E522" t="n">
-        <v>99.1778949454735</v>
+        <v>99.17788731683716</v>
       </c>
       <c r="F522" t="n">
-        <v>99.1778949454735</v>
+        <v>99.17788731683716</v>
       </c>
       <c r="G522" t="n">
         <v>16031700</v>
@@ -12455,16 +12455,16 @@
         <v>46052</v>
       </c>
       <c r="C523" t="n">
-        <v>99.20745849609375</v>
+        <v>99.20745086669922</v>
       </c>
       <c r="D523" t="n">
-        <v>99.21731532069894</v>
+        <v>99.21730769054639</v>
       </c>
       <c r="E523" t="n">
-        <v>99.20745849609375</v>
+        <v>99.20745086669922</v>
       </c>
       <c r="F523" t="n">
-        <v>99.20745849609375</v>
+        <v>99.20745086669922</v>
       </c>
       <c r="G523" t="n">
         <v>29215200</v>
@@ -12501,16 +12501,16 @@
         <v>46056</v>
       </c>
       <c r="C525" t="n">
-        <v>99.23612213134766</v>
+        <v>99.23612976074219</v>
       </c>
       <c r="D525" t="n">
-        <v>99.23612213134766</v>
+        <v>99.23612976074219</v>
       </c>
       <c r="E525" t="n">
-        <v>99.22623495913354</v>
+        <v>99.22624258776793</v>
       </c>
       <c r="F525" t="n">
-        <v>99.23612213134766</v>
+        <v>99.23612976074219</v>
       </c>
       <c r="G525" t="n">
         <v>18150800</v>
@@ -12524,16 +12524,16 @@
         <v>46057</v>
       </c>
       <c r="C526" t="n">
-        <v>99.24600982666016</v>
+        <v>99.24601745605469</v>
       </c>
       <c r="D526" t="n">
-        <v>99.24600982666016</v>
+        <v>99.24601745605469</v>
       </c>
       <c r="E526" t="n">
-        <v>99.23612265439392</v>
+        <v>99.23613028302839</v>
       </c>
       <c r="F526" t="n">
-        <v>99.24106246967568</v>
+        <v>99.24107009868989</v>
       </c>
       <c r="G526" t="n">
         <v>18129400</v>
@@ -12547,16 +12547,16 @@
         <v>46058</v>
       </c>
       <c r="C527" t="n">
-        <v>99.24600982666016</v>
+        <v>99.24601745605469</v>
       </c>
       <c r="D527" t="n">
-        <v>99.25589699892639</v>
+        <v>99.25590462908099</v>
       </c>
       <c r="E527" t="n">
-        <v>99.24600982666016</v>
+        <v>99.24601745605469</v>
       </c>
       <c r="F527" t="n">
-        <v>99.25589699892639</v>
+        <v>99.25590462908099</v>
       </c>
       <c r="G527" t="n">
         <v>20371200</v>
@@ -12570,16 +12570,16 @@
         <v>46059</v>
       </c>
       <c r="C528" t="n">
-        <v>99.27567291259766</v>
+        <v>99.27566528320312</v>
       </c>
       <c r="D528" t="n">
-        <v>99.28556008577127</v>
+        <v>99.28555245561691</v>
       </c>
       <c r="E528" t="n">
-        <v>99.27567291259766</v>
+        <v>99.27566528320312</v>
       </c>
       <c r="F528" t="n">
-        <v>99.27567291259766</v>
+        <v>99.27566528320312</v>
       </c>
       <c r="G528" t="n">
         <v>17381400</v>
@@ -12593,16 +12593,16 @@
         <v>46062</v>
       </c>
       <c r="C529" t="n">
-        <v>99.29543304443359</v>
+        <v>99.29544067382812</v>
       </c>
       <c r="D529" t="n">
-        <v>99.29543304443359</v>
+        <v>99.29544067382812</v>
       </c>
       <c r="E529" t="n">
-        <v>99.28555341362733</v>
+        <v>99.28556104226274</v>
       </c>
       <c r="F529" t="n">
-        <v>99.28555341362733</v>
+        <v>99.28556104226274</v>
       </c>
       <c r="G529" t="n">
         <v>13991600</v>
@@ -12616,16 +12616,16 @@
         <v>46063</v>
       </c>
       <c r="C530" t="n">
-        <v>99.30532073974609</v>
+        <v>99.30532836914062</v>
       </c>
       <c r="D530" t="n">
-        <v>99.30532073974609</v>
+        <v>99.30532836914062</v>
       </c>
       <c r="E530" t="n">
-        <v>99.29543356718486</v>
+        <v>99.29544119581978</v>
       </c>
       <c r="F530" t="n">
-        <v>99.30532073974609</v>
+        <v>99.30532836914062</v>
       </c>
       <c r="G530" t="n">
         <v>14002700</v>
@@ -12639,16 +12639,16 @@
         <v>46064</v>
       </c>
       <c r="C531" t="n">
-        <v>99.30532073974609</v>
+        <v>99.30532836914062</v>
       </c>
       <c r="D531" t="n">
-        <v>99.31520791230733</v>
+        <v>99.31521554246146</v>
       </c>
       <c r="E531" t="n">
-        <v>99.30532073974609</v>
+        <v>99.30532836914062</v>
       </c>
       <c r="F531" t="n">
-        <v>99.31520791230733</v>
+        <v>99.31521554246146</v>
       </c>
       <c r="G531" t="n">
         <v>12584400</v>
@@ -12685,16 +12685,16 @@
         <v>46066</v>
       </c>
       <c r="C533" t="n">
-        <v>99.36463165283203</v>
+        <v>99.3646240234375</v>
       </c>
       <c r="D533" t="n">
-        <v>99.36463165283203</v>
+        <v>99.3646240234375</v>
       </c>
       <c r="E533" t="n">
-        <v>99.35475202167932</v>
+        <v>99.35474439304336</v>
       </c>
       <c r="F533" t="n">
-        <v>99.36463165283203</v>
+        <v>99.3646240234375</v>
       </c>
       <c r="G533" t="n">
         <v>14917200</v>
@@ -12708,16 +12708,16 @@
         <v>46070</v>
       </c>
       <c r="C534" t="n">
-        <v>99.36463165283203</v>
+        <v>99.3646240234375</v>
       </c>
       <c r="D534" t="n">
-        <v>99.3745188256879</v>
+        <v>99.37451119553421</v>
       </c>
       <c r="E534" t="n">
-        <v>99.36463165283203</v>
+        <v>99.3646240234375</v>
       </c>
       <c r="F534" t="n">
-        <v>99.36957901011155</v>
+        <v>99.36957138033715</v>
       </c>
       <c r="G534" t="n">
         <v>14976200</v>
@@ -12731,16 +12731,16 @@
         <v>46071</v>
       </c>
       <c r="C535" t="n">
-        <v>99.38440704345703</v>
+        <v>99.38441467285156</v>
       </c>
       <c r="D535" t="n">
-        <v>99.38440704345703</v>
+        <v>99.38441467285156</v>
       </c>
       <c r="E535" t="n">
-        <v>99.37451987049721</v>
+        <v>99.37452749913272</v>
       </c>
       <c r="F535" t="n">
-        <v>99.38440704345703</v>
+        <v>99.38441467285156</v>
       </c>
       <c r="G535" t="n">
         <v>10207300</v>
@@ -12754,16 +12754,16 @@
         <v>46072</v>
       </c>
       <c r="C536" t="n">
-        <v>99.394287109375</v>
+        <v>99.39429473876953</v>
       </c>
       <c r="D536" t="n">
-        <v>99.394287109375</v>
+        <v>99.39429473876953</v>
       </c>
       <c r="E536" t="n">
-        <v>99.38439993712214</v>
+        <v>99.38440756575774</v>
       </c>
       <c r="F536" t="n">
-        <v>99.394287109375</v>
+        <v>99.39429473876953</v>
       </c>
       <c r="G536" t="n">
         <v>11292100</v>
@@ -12800,16 +12800,16 @@
         <v>46076</v>
       </c>
       <c r="C538" t="n">
-        <v>99.43383026123047</v>
+        <v>99.43382263183594</v>
       </c>
       <c r="D538" t="n">
-        <v>99.43383026123047</v>
+        <v>99.43382263183594</v>
       </c>
       <c r="E538" t="n">
-        <v>99.42395062973182</v>
+        <v>99.42394300109534</v>
       </c>
       <c r="F538" t="n">
-        <v>99.42889044548114</v>
+        <v>99.42888281646563</v>
       </c>
       <c r="G538" t="n">
         <v>13465400</v>
@@ -12823,16 +12823,16 @@
         <v>46077</v>
       </c>
       <c r="C539" t="n">
-        <v>99.43383026123047</v>
+        <v>99.43382263183594</v>
       </c>
       <c r="D539" t="n">
-        <v>99.44371743443256</v>
+        <v>99.44370980427939</v>
       </c>
       <c r="E539" t="n">
-        <v>99.43383026123047</v>
+        <v>99.43382263183594</v>
       </c>
       <c r="F539" t="n">
-        <v>99.43877761868323</v>
+        <v>99.4387699889091</v>
       </c>
       <c r="G539" t="n">
         <v>12168900</v>
@@ -12846,16 +12846,16 @@
         <v>46078</v>
       </c>
       <c r="C540" t="n">
-        <v>99.44371795654297</v>
+        <v>99.44371032714844</v>
       </c>
       <c r="D540" t="n">
-        <v>99.45360512979697</v>
+        <v>99.45359749964389</v>
       </c>
       <c r="E540" t="n">
-        <v>99.44371795654297</v>
+        <v>99.44371032714844</v>
       </c>
       <c r="F540" t="n">
-        <v>99.45360512979697</v>
+        <v>99.45359749964389</v>
       </c>
       <c r="G540" t="n">
         <v>12532000</v>
@@ -12915,16 +12915,16 @@
         <v>46083</v>
       </c>
       <c r="C543" t="n">
-        <v>99.49514770507812</v>
+        <v>99.49514007568359</v>
       </c>
       <c r="D543" t="n">
-        <v>99.50506167249043</v>
+        <v>99.50505404233567</v>
       </c>
       <c r="E543" t="n">
-        <v>99.49514770507812</v>
+        <v>99.49514007568359</v>
       </c>
       <c r="F543" t="n">
-        <v>99.50010846985499</v>
+        <v>99.50010084008005</v>
       </c>
       <c r="G543" t="n">
         <v>33993400</v>
@@ -12938,16 +12938,16 @@
         <v>46084</v>
       </c>
       <c r="C544" t="n">
-        <v>99.51496887207031</v>
+        <v>99.51497650146484</v>
       </c>
       <c r="D544" t="n">
-        <v>99.51496887207031</v>
+        <v>99.51497650146484</v>
       </c>
       <c r="E544" t="n">
-        <v>99.50505490533224</v>
+        <v>99.50506253396671</v>
       </c>
       <c r="F544" t="n">
-        <v>99.51000810763082</v>
+        <v>99.51001573664503</v>
       </c>
       <c r="G544" t="n">
         <v>19224400</v>
@@ -12961,16 +12961,16 @@
         <v>46085</v>
       </c>
       <c r="C545" t="n">
-        <v>99.51496887207031</v>
+        <v>99.51497650146484</v>
       </c>
       <c r="D545" t="n">
-        <v>99.52488283880838</v>
+        <v>99.52489046896297</v>
       </c>
       <c r="E545" t="n">
-        <v>99.51496887207031</v>
+        <v>99.51497650146484</v>
       </c>
       <c r="F545" t="n">
-        <v>99.51992207436889</v>
+        <v>99.51992970414315</v>
       </c>
       <c r="G545" t="n">
         <v>14325400</v>
@@ -12984,16 +12984,16 @@
         <v>46086</v>
       </c>
       <c r="C546" t="n">
-        <v>99.52487945556641</v>
+        <v>99.52489471435547</v>
       </c>
       <c r="D546" t="n">
-        <v>99.53478585982681</v>
+        <v>99.53480112013467</v>
       </c>
       <c r="E546" t="n">
-        <v>99.52487945556641</v>
+        <v>99.52489471435547</v>
       </c>
       <c r="F546" t="n">
-        <v>99.53478585982681</v>
+        <v>99.53480112013467</v>
       </c>
       <c r="G546" t="n">
         <v>16218200</v>
@@ -13007,16 +13007,16 @@
         <v>46087</v>
       </c>
       <c r="C547" t="n">
-        <v>99.56452941894531</v>
+        <v>99.56452178955078</v>
       </c>
       <c r="D547" t="n">
-        <v>99.56452941894531</v>
+        <v>99.56452178955078</v>
       </c>
       <c r="E547" t="n">
-        <v>99.55462301376734</v>
+        <v>99.55461538513191</v>
       </c>
       <c r="F547" t="n">
-        <v>99.55462301376734</v>
+        <v>99.55461538513191</v>
       </c>
       <c r="G547" t="n">
         <v>18921300</v>
@@ -13030,16 +13030,16 @@
         <v>46090</v>
       </c>
       <c r="C548" t="n">
-        <v>99.57444000244141</v>
+        <v>99.57444763183594</v>
       </c>
       <c r="D548" t="n">
-        <v>99.57444000244141</v>
+        <v>99.57444763183594</v>
       </c>
       <c r="E548" t="n">
-        <v>99.564526035459</v>
+        <v>99.56453366409391</v>
       </c>
       <c r="F548" t="n">
-        <v>99.56948680002075</v>
+        <v>99.56949442903577</v>
       </c>
       <c r="G548" t="n">
         <v>19053900</v>
@@ -13053,16 +13053,16 @@
         <v>46091</v>
       </c>
       <c r="C549" t="n">
-        <v>99.57444000244141</v>
+        <v>99.57444763183594</v>
       </c>
       <c r="D549" t="n">
-        <v>99.58435396942383</v>
+        <v>99.58436159957796</v>
       </c>
       <c r="E549" t="n">
-        <v>99.57444000244141</v>
+        <v>99.57444763183594</v>
       </c>
       <c r="F549" t="n">
-        <v>99.58138204797143</v>
+        <v>99.58138967789786</v>
       </c>
       <c r="G549" t="n">
         <v>13664200</v>
@@ -13076,16 +13076,16 @@
         <v>46092</v>
       </c>
       <c r="C550" t="n">
-        <v>99.59426879882812</v>
+        <v>99.59427642822266</v>
       </c>
       <c r="D550" t="n">
-        <v>99.59426879882812</v>
+        <v>99.59427642822266</v>
       </c>
       <c r="E550" t="n">
-        <v>99.58435483175987</v>
+        <v>99.58436246039494</v>
       </c>
       <c r="F550" t="n">
-        <v>99.58435483175987</v>
+        <v>99.58436246039494</v>
       </c>
       <c r="G550" t="n">
         <v>12287800</v>
@@ -13237,16 +13237,16 @@
         <v>46101</v>
       </c>
       <c r="C557" t="n">
-        <v>99.69338226318359</v>
+        <v>99.69338989257812</v>
       </c>
       <c r="D557" t="n">
-        <v>99.69338226318359</v>
+        <v>99.69338989257812</v>
       </c>
       <c r="E557" t="n">
-        <v>99.68346829646536</v>
+        <v>99.68347592510119</v>
       </c>
       <c r="F557" t="n">
-        <v>99.69338226318359</v>
+        <v>99.69338989257812</v>
       </c>
       <c r="G557" t="n">
         <v>23039600</v>
@@ -13260,16 +13260,16 @@
         <v>46104</v>
       </c>
       <c r="C558" t="n">
-        <v>99.69338226318359</v>
+        <v>99.69338989257812</v>
       </c>
       <c r="D558" t="n">
-        <v>99.71320263447916</v>
+        <v>99.71321026539052</v>
       </c>
       <c r="E558" t="n">
-        <v>99.69338226318359</v>
+        <v>99.69338989257812</v>
       </c>
       <c r="F558" t="n">
-        <v>99.70328866776093</v>
+        <v>99.70329629791358</v>
       </c>
       <c r="G558" t="n">
         <v>33994300</v>
@@ -13329,16 +13329,16 @@
         <v>46107</v>
       </c>
       <c r="C561" t="n">
-        <v>99.7330322265625</v>
+        <v>99.73303985595703</v>
       </c>
       <c r="D561" t="n">
-        <v>99.7330322265625</v>
+        <v>99.73303985595703</v>
       </c>
       <c r="E561" t="n">
-        <v>99.7231182596794</v>
+        <v>99.72312588831552</v>
       </c>
       <c r="F561" t="n">
-        <v>99.7330322265625</v>
+        <v>99.73303985595703</v>
       </c>
       <c r="G561" t="n">
         <v>17499400</v>
@@ -13375,16 +13375,16 @@
         <v>46111</v>
       </c>
       <c r="C563" t="n">
-        <v>99.77268218994141</v>
+        <v>99.77268981933594</v>
       </c>
       <c r="D563" t="n">
-        <v>99.77268218994141</v>
+        <v>99.77268981933594</v>
       </c>
       <c r="E563" t="n">
-        <v>99.76276822289356</v>
+        <v>99.76277585152998</v>
       </c>
       <c r="F563" t="n">
-        <v>99.76276822289356</v>
+        <v>99.76277585152998</v>
       </c>
       <c r="G563" t="n">
         <v>19102700</v>
@@ -13398,16 +13398,16 @@
         <v>46112</v>
       </c>
       <c r="C564" t="n">
-        <v>99.77268218994141</v>
+        <v>99.77268981933594</v>
       </c>
       <c r="D564" t="n">
-        <v>99.78258859484811</v>
+        <v>99.78259622500016</v>
       </c>
       <c r="E564" t="n">
-        <v>99.77268218994141</v>
+        <v>99.77268981933594</v>
       </c>
       <c r="F564" t="n">
-        <v>99.77268218994141</v>
+        <v>99.77268981933594</v>
       </c>
       <c r="G564" t="n">
         <v>36976800</v>
@@ -13559,16 +13559,16 @@
         <v>46122</v>
       </c>
       <c r="C571" t="n">
-        <v>99.90489959716797</v>
+        <v>99.90489196777344</v>
       </c>
       <c r="D571" t="n">
-        <v>99.90489959716797</v>
+        <v>99.90489196777344</v>
       </c>
       <c r="E571" t="n">
-        <v>99.8949566875574</v>
+        <v>99.89494905892218</v>
       </c>
       <c r="F571" t="n">
-        <v>99.8949566875574</v>
+        <v>99.89494905892218</v>
       </c>
       <c r="G571" t="n">
         <v>18783100</v>
@@ -13674,16 +13674,16 @@
         <v>46129</v>
       </c>
       <c r="C576" t="n">
-        <v>99.96453094482422</v>
+        <v>99.96453857421875</v>
       </c>
       <c r="D576" t="n">
-        <v>99.97447385334648</v>
+        <v>99.97448148349987</v>
       </c>
       <c r="E576" t="n">
-        <v>99.96453094482422</v>
+        <v>99.96453857421875</v>
       </c>
       <c r="F576" t="n">
-        <v>99.96453094482422</v>
+        <v>99.96453857421875</v>
       </c>
       <c r="G576" t="n">
         <v>20660500</v>

--- a/Data/sgov.xlsx
+++ b/Data/sgov.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G610"/>
+  <dimension ref="A1:G612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,16 +472,16 @@
         <v>45293</v>
       </c>
       <c r="C2" t="n">
-        <v>90.15837860107422</v>
+        <v>90.15839385986328</v>
       </c>
       <c r="D2" t="n">
-        <v>90.16737028894792</v>
+        <v>90.16738554925877</v>
       </c>
       <c r="E2" t="n">
-        <v>90.14938691320052</v>
+        <v>90.14940217046778</v>
       </c>
       <c r="F2" t="n">
-        <v>90.15837860107422</v>
+        <v>90.15839385986328</v>
       </c>
       <c r="G2" t="n">
         <v>5286200</v>
@@ -495,16 +495,16 @@
         <v>45294</v>
       </c>
       <c r="C3" t="n">
-        <v>90.16737365722656</v>
+        <v>90.16736602783203</v>
       </c>
       <c r="D3" t="n">
-        <v>90.18535017499724</v>
+        <v>90.18534254408165</v>
       </c>
       <c r="E3" t="n">
-        <v>90.16737365722656</v>
+        <v>90.16736602783203</v>
       </c>
       <c r="F3" t="n">
-        <v>90.16737365722656</v>
+        <v>90.16736602783203</v>
       </c>
       <c r="G3" t="n">
         <v>4597300</v>
@@ -518,16 +518,16 @@
         <v>45295</v>
       </c>
       <c r="C4" t="n">
-        <v>90.21231842041016</v>
+        <v>90.21234130859375</v>
       </c>
       <c r="D4" t="n">
-        <v>90.22131010862368</v>
+        <v>90.2213329990886</v>
       </c>
       <c r="E4" t="n">
-        <v>90.21231842041016</v>
+        <v>90.21234130859375</v>
       </c>
       <c r="F4" t="n">
-        <v>90.21231842041016</v>
+        <v>90.21234130859375</v>
       </c>
       <c r="G4" t="n">
         <v>2794100</v>
@@ -564,16 +564,16 @@
         <v>45299</v>
       </c>
       <c r="C6" t="n">
-        <v>90.248291015625</v>
+        <v>90.24826812744141</v>
       </c>
       <c r="D6" t="n">
-        <v>90.248291015625</v>
+        <v>90.24826812744141</v>
       </c>
       <c r="E6" t="n">
-        <v>90.23929932614602</v>
+        <v>90.23927644024286</v>
       </c>
       <c r="F6" t="n">
-        <v>90.248291015625</v>
+        <v>90.24826812744141</v>
       </c>
       <c r="G6" t="n">
         <v>2867500</v>
@@ -587,16 +587,16 @@
         <v>45300</v>
       </c>
       <c r="C7" t="n">
-        <v>90.25727081298828</v>
+        <v>90.25729370117188</v>
       </c>
       <c r="D7" t="n">
-        <v>90.25727081298828</v>
+        <v>90.25729370117188</v>
       </c>
       <c r="E7" t="n">
-        <v>90.24827912469404</v>
+        <v>90.24830201059746</v>
       </c>
       <c r="F7" t="n">
-        <v>90.25727081298828</v>
+        <v>90.25729370117188</v>
       </c>
       <c r="G7" t="n">
         <v>2419800</v>
@@ -610,16 +610,16 @@
         <v>45301</v>
       </c>
       <c r="C8" t="n">
-        <v>90.27526092529297</v>
+        <v>90.27523040771484</v>
       </c>
       <c r="D8" t="n">
-        <v>90.27526092529297</v>
+        <v>90.27523040771484</v>
       </c>
       <c r="E8" t="n">
-        <v>90.26627609429431</v>
+        <v>90.2662455797535</v>
       </c>
       <c r="F8" t="n">
-        <v>90.27526092529297</v>
+        <v>90.27523040771484</v>
       </c>
       <c r="G8" t="n">
         <v>1961400</v>
@@ -633,16 +633,16 @@
         <v>45302</v>
       </c>
       <c r="C9" t="n">
-        <v>90.32918548583984</v>
+        <v>90.32920074462891</v>
       </c>
       <c r="D9" t="n">
-        <v>90.32918548583984</v>
+        <v>90.32920074462891</v>
       </c>
       <c r="E9" t="n">
-        <v>90.31120211026995</v>
+        <v>90.31121736602117</v>
       </c>
       <c r="F9" t="n">
-        <v>90.31120211026995</v>
+        <v>90.31121736602117</v>
       </c>
       <c r="G9" t="n">
         <v>3164900</v>
@@ -679,16 +679,16 @@
         <v>45307</v>
       </c>
       <c r="C11" t="n">
-        <v>90.34718322753906</v>
+        <v>90.34719085693359</v>
       </c>
       <c r="D11" t="n">
-        <v>90.35617491743638</v>
+        <v>90.35618254759022</v>
       </c>
       <c r="E11" t="n">
-        <v>90.34718322753906</v>
+        <v>90.34719085693359</v>
       </c>
       <c r="F11" t="n">
-        <v>90.35617491743638</v>
+        <v>90.35618254759022</v>
       </c>
       <c r="G11" t="n">
         <v>2713000</v>
@@ -725,16 +725,16 @@
         <v>45309</v>
       </c>
       <c r="C13" t="n">
-        <v>90.39212036132812</v>
+        <v>90.39211273193359</v>
       </c>
       <c r="D13" t="n">
-        <v>90.40110519113864</v>
+        <v>90.40109756098575</v>
       </c>
       <c r="E13" t="n">
-        <v>90.39212036132812</v>
+        <v>90.39211273193359</v>
       </c>
       <c r="F13" t="n">
-        <v>90.40110519113864</v>
+        <v>90.40109756098575</v>
       </c>
       <c r="G13" t="n">
         <v>2672000</v>
@@ -748,16 +748,16 @@
         <v>45310</v>
       </c>
       <c r="C14" t="n">
-        <v>90.41910552978516</v>
+        <v>90.41907501220703</v>
       </c>
       <c r="D14" t="n">
-        <v>90.41910552978516</v>
+        <v>90.41907501220703</v>
       </c>
       <c r="E14" t="n">
-        <v>90.40112214949322</v>
+        <v>90.40109163798471</v>
       </c>
       <c r="F14" t="n">
-        <v>90.41011383963918</v>
+        <v>90.41008332509587</v>
       </c>
       <c r="G14" t="n">
         <v>3630100</v>
@@ -771,16 +771,16 @@
         <v>45313</v>
       </c>
       <c r="C15" t="n">
-        <v>90.4281005859375</v>
+        <v>90.42808532714844</v>
       </c>
       <c r="D15" t="n">
-        <v>90.43709227710016</v>
+        <v>90.43707701679384</v>
       </c>
       <c r="E15" t="n">
-        <v>90.41911575342561</v>
+        <v>90.41910049615264</v>
       </c>
       <c r="F15" t="n">
-        <v>90.43259986084422</v>
+        <v>90.43258460129594</v>
       </c>
       <c r="G15" t="n">
         <v>4307000</v>
@@ -794,16 +794,16 @@
         <v>45314</v>
       </c>
       <c r="C16" t="n">
-        <v>90.44606781005859</v>
+        <v>90.44605255126953</v>
       </c>
       <c r="D16" t="n">
-        <v>90.44606781005859</v>
+        <v>90.44605255126953</v>
       </c>
       <c r="E16" t="n">
-        <v>90.4370761205023</v>
+        <v>90.43706086323019</v>
       </c>
       <c r="F16" t="n">
-        <v>90.4370761205023</v>
+        <v>90.43706086323019</v>
       </c>
       <c r="G16" t="n">
         <v>2066200</v>
@@ -817,16 +817,16 @@
         <v>45315</v>
       </c>
       <c r="C17" t="n">
-        <v>90.45503997802734</v>
+        <v>90.45507049560547</v>
       </c>
       <c r="D17" t="n">
-        <v>90.45503997802734</v>
+        <v>90.45507049560547</v>
       </c>
       <c r="E17" t="n">
-        <v>90.4460482904116</v>
+        <v>90.44607880495612</v>
       </c>
       <c r="F17" t="n">
-        <v>90.4460482904116</v>
+        <v>90.44607880495612</v>
       </c>
       <c r="G17" t="n">
         <v>3441600</v>
@@ -840,16 +840,16 @@
         <v>45316</v>
       </c>
       <c r="C18" t="n">
-        <v>90.50000762939453</v>
+        <v>90.49998474121094</v>
       </c>
       <c r="D18" t="n">
-        <v>90.50000762939453</v>
+        <v>90.49998474121094</v>
       </c>
       <c r="E18" t="n">
-        <v>90.48203110825628</v>
+        <v>90.48200822461909</v>
       </c>
       <c r="F18" t="n">
-        <v>90.48203110825628</v>
+        <v>90.48200822461909</v>
       </c>
       <c r="G18" t="n">
         <v>2426000</v>
@@ -863,16 +863,16 @@
         <v>45317</v>
       </c>
       <c r="C19" t="n">
-        <v>90.50000762939453</v>
+        <v>90.49998474121094</v>
       </c>
       <c r="D19" t="n">
-        <v>90.50899931928856</v>
+        <v>90.50897642883089</v>
       </c>
       <c r="E19" t="n">
-        <v>90.50000762939453</v>
+        <v>90.49998474121094</v>
       </c>
       <c r="F19" t="n">
-        <v>90.50899931928856</v>
+        <v>90.50897642883089</v>
       </c>
       <c r="G19" t="n">
         <v>2059100</v>
@@ -886,16 +886,16 @@
         <v>45320</v>
       </c>
       <c r="C20" t="n">
-        <v>90.50898742675781</v>
+        <v>90.50899505615234</v>
       </c>
       <c r="D20" t="n">
-        <v>90.52696394553402</v>
+        <v>90.52697157644387</v>
       </c>
       <c r="E20" t="n">
-        <v>90.50898742675781</v>
+        <v>90.50899505615234</v>
       </c>
       <c r="F20" t="n">
-        <v>90.51797911547037</v>
+        <v>90.51798674562285</v>
       </c>
       <c r="G20" t="n">
         <v>2914400</v>
@@ -909,16 +909,16 @@
         <v>45321</v>
       </c>
       <c r="C21" t="n">
-        <v>90.53596496582031</v>
+        <v>90.53594970703125</v>
       </c>
       <c r="D21" t="n">
-        <v>90.53596496582031</v>
+        <v>90.53594970703125</v>
       </c>
       <c r="E21" t="n">
-        <v>90.52697327618098</v>
+        <v>90.52695801890737</v>
       </c>
       <c r="F21" t="n">
-        <v>90.52697327618098</v>
+        <v>90.52695801890737</v>
       </c>
       <c r="G21" t="n">
         <v>3741000</v>
@@ -932,16 +932,16 @@
         <v>45322</v>
       </c>
       <c r="C22" t="n">
-        <v>90.53596496582031</v>
+        <v>90.53594970703125</v>
       </c>
       <c r="D22" t="n">
-        <v>90.54495665545964</v>
+        <v>90.54494139515513</v>
       </c>
       <c r="E22" t="n">
-        <v>90.53596496582031</v>
+        <v>90.53594970703125</v>
       </c>
       <c r="F22" t="n">
-        <v>90.53596496582031</v>
+        <v>90.53594970703125</v>
       </c>
       <c r="G22" t="n">
         <v>5171300</v>
@@ -955,16 +955,16 @@
         <v>45323</v>
       </c>
       <c r="C23" t="n">
-        <v>90.58834838867188</v>
+        <v>90.58831024169922</v>
       </c>
       <c r="D23" t="n">
-        <v>90.59738115732434</v>
+        <v>90.59734300654796</v>
       </c>
       <c r="E23" t="n">
-        <v>90.58834838867188</v>
+        <v>90.58831024169922</v>
       </c>
       <c r="F23" t="n">
-        <v>90.59738115732434</v>
+        <v>90.59734300654796</v>
       </c>
       <c r="G23" t="n">
         <v>7038600</v>
@@ -1001,16 +1001,16 @@
         <v>45327</v>
       </c>
       <c r="C25" t="n">
-        <v>90.61544036865234</v>
+        <v>90.61540985107422</v>
       </c>
       <c r="D25" t="n">
-        <v>90.61544036865234</v>
+        <v>90.61540985107422</v>
       </c>
       <c r="E25" t="n">
-        <v>90.6064144899274</v>
+        <v>90.60638397538904</v>
       </c>
       <c r="F25" t="n">
-        <v>90.61544036865234</v>
+        <v>90.61540985107422</v>
       </c>
       <c r="G25" t="n">
         <v>3969400</v>
@@ -1024,16 +1024,16 @@
         <v>45328</v>
       </c>
       <c r="C26" t="n">
-        <v>90.62445068359375</v>
+        <v>90.62447357177734</v>
       </c>
       <c r="D26" t="n">
-        <v>90.63348345006442</v>
+        <v>90.63350634052934</v>
       </c>
       <c r="E26" t="n">
-        <v>90.61541791712308</v>
+        <v>90.61544080302535</v>
       </c>
       <c r="F26" t="n">
-        <v>90.62445068359375</v>
+        <v>90.62447357177734</v>
       </c>
       <c r="G26" t="n">
         <v>2167300</v>
@@ -1047,16 +1047,16 @@
         <v>45329</v>
       </c>
       <c r="C27" t="n">
-        <v>90.64250946044922</v>
+        <v>90.64253997802734</v>
       </c>
       <c r="D27" t="n">
-        <v>90.64250946044922</v>
+        <v>90.64253997802734</v>
       </c>
       <c r="E27" t="n">
-        <v>90.63347669465182</v>
+        <v>90.63350720918878</v>
       </c>
       <c r="F27" t="n">
-        <v>90.64250946044922</v>
+        <v>90.64253997802734</v>
       </c>
       <c r="G27" t="n">
         <v>2621200</v>
@@ -1070,16 +1070,16 @@
         <v>45330</v>
       </c>
       <c r="C28" t="n">
-        <v>90.66960906982422</v>
+        <v>90.66961669921875</v>
       </c>
       <c r="D28" t="n">
-        <v>90.68766771307108</v>
+        <v>90.68767534398516</v>
       </c>
       <c r="E28" t="n">
-        <v>90.66960906982422</v>
+        <v>90.66961669921875</v>
       </c>
       <c r="F28" t="n">
-        <v>90.66960906982422</v>
+        <v>90.66961669921875</v>
       </c>
       <c r="G28" t="n">
         <v>3838700</v>
@@ -1093,16 +1093,16 @@
         <v>45331</v>
       </c>
       <c r="C29" t="n">
-        <v>90.69670867919922</v>
+        <v>90.69672393798828</v>
       </c>
       <c r="D29" t="n">
-        <v>90.69670867919922</v>
+        <v>90.69672393798828</v>
       </c>
       <c r="E29" t="n">
-        <v>90.68316297304392</v>
+        <v>90.68317822955406</v>
       </c>
       <c r="F29" t="n">
-        <v>90.6876759117681</v>
+        <v>90.68769116903748</v>
       </c>
       <c r="G29" t="n">
         <v>3232500</v>
@@ -1116,16 +1116,16 @@
         <v>45334</v>
       </c>
       <c r="C30" t="n">
-        <v>90.69670867919922</v>
+        <v>90.69672393798828</v>
       </c>
       <c r="D30" t="n">
-        <v>90.71476732407868</v>
+        <v>90.71478258590592</v>
       </c>
       <c r="E30" t="n">
-        <v>90.69670867919922</v>
+        <v>90.69672393798828</v>
       </c>
       <c r="F30" t="n">
-        <v>90.70574144663034</v>
+        <v>90.70575670693907</v>
       </c>
       <c r="G30" t="n">
         <v>2792700</v>
@@ -1139,16 +1139,16 @@
         <v>45335</v>
       </c>
       <c r="C31" t="n">
-        <v>90.71476745605469</v>
+        <v>90.71474456787109</v>
       </c>
       <c r="D31" t="n">
-        <v>90.71476745605469</v>
+        <v>90.71474456787109</v>
       </c>
       <c r="E31" t="n">
-        <v>90.70574157859322</v>
+        <v>90.70571869268693</v>
       </c>
       <c r="F31" t="n">
-        <v>90.71476745605469</v>
+        <v>90.71474456787109</v>
       </c>
       <c r="G31" t="n">
         <v>3009000</v>
@@ -1162,16 +1162,16 @@
         <v>45336</v>
       </c>
       <c r="C32" t="n">
-        <v>90.73284149169922</v>
+        <v>90.73282623291016</v>
       </c>
       <c r="D32" t="n">
-        <v>90.73284149169922</v>
+        <v>90.73282623291016</v>
       </c>
       <c r="E32" t="n">
-        <v>90.72380872340868</v>
+        <v>90.72379346613867</v>
       </c>
       <c r="F32" t="n">
-        <v>90.73284149169922</v>
+        <v>90.73282623291016</v>
       </c>
       <c r="G32" t="n">
         <v>2614100</v>
@@ -1185,16 +1185,16 @@
         <v>45337</v>
       </c>
       <c r="C33" t="n">
-        <v>90.77796936035156</v>
+        <v>90.77799224853516</v>
       </c>
       <c r="D33" t="n">
-        <v>90.78700212643383</v>
+        <v>90.7870250168949</v>
       </c>
       <c r="E33" t="n">
-        <v>90.77796936035156</v>
+        <v>90.77799224853516</v>
       </c>
       <c r="F33" t="n">
-        <v>90.78700212643383</v>
+        <v>90.7870250168949</v>
       </c>
       <c r="G33" t="n">
         <v>2577800</v>
@@ -1208,16 +1208,16 @@
         <v>45338</v>
       </c>
       <c r="C34" t="n">
-        <v>90.78701782226562</v>
+        <v>90.78701019287109</v>
       </c>
       <c r="D34" t="n">
-        <v>90.79605058990954</v>
+        <v>90.79604295975592</v>
       </c>
       <c r="E34" t="n">
-        <v>90.78701782226562</v>
+        <v>90.78701019287109</v>
       </c>
       <c r="F34" t="n">
-        <v>90.79605058990954</v>
+        <v>90.79604295975592</v>
       </c>
       <c r="G34" t="n">
         <v>2920700</v>
@@ -1254,16 +1254,16 @@
         <v>45343</v>
       </c>
       <c r="C36" t="n">
-        <v>90.81410980224609</v>
+        <v>90.81410217285156</v>
       </c>
       <c r="D36" t="n">
-        <v>90.83217533764672</v>
+        <v>90.83216770673448</v>
       </c>
       <c r="E36" t="n">
-        <v>90.81410980224609</v>
+        <v>90.81410217285156</v>
       </c>
       <c r="F36" t="n">
-        <v>90.8231425699464</v>
+        <v>90.82313493979302</v>
       </c>
       <c r="G36" t="n">
         <v>2302700</v>
@@ -1300,16 +1300,16 @@
         <v>45345</v>
       </c>
       <c r="C38" t="n">
-        <v>90.87732696533203</v>
+        <v>90.87730407714844</v>
       </c>
       <c r="D38" t="n">
-        <v>90.87732696533203</v>
+        <v>90.87730407714844</v>
       </c>
       <c r="E38" t="n">
-        <v>90.86830108745886</v>
+        <v>90.86827820154851</v>
       </c>
       <c r="F38" t="n">
-        <v>90.87732696533203</v>
+        <v>90.87730407714844</v>
       </c>
       <c r="G38" t="n">
         <v>2010100</v>
@@ -1323,16 +1323,16 @@
         <v>45348</v>
       </c>
       <c r="C39" t="n">
-        <v>90.8863525390625</v>
+        <v>90.88633728027344</v>
       </c>
       <c r="D39" t="n">
-        <v>90.89538530620379</v>
+        <v>90.89537004589823</v>
       </c>
       <c r="E39" t="n">
-        <v>90.8863525390625</v>
+        <v>90.88633728027344</v>
       </c>
       <c r="F39" t="n">
-        <v>90.8863525390625</v>
+        <v>90.88633728027344</v>
       </c>
       <c r="G39" t="n">
         <v>2645100</v>
@@ -1346,16 +1346,16 @@
         <v>45349</v>
       </c>
       <c r="C40" t="n">
-        <v>90.90441131591797</v>
+        <v>90.9044189453125</v>
       </c>
       <c r="D40" t="n">
-        <v>90.90441131591797</v>
+        <v>90.9044189453125</v>
       </c>
       <c r="E40" t="n">
-        <v>90.89537854944814</v>
+        <v>90.89538617808456</v>
       </c>
       <c r="F40" t="n">
-        <v>90.90441131591797</v>
+        <v>90.9044189453125</v>
       </c>
       <c r="G40" t="n">
         <v>2360300</v>
@@ -1369,16 +1369,16 @@
         <v>45350</v>
       </c>
       <c r="C41" t="n">
-        <v>90.91345977783203</v>
+        <v>90.91344451904297</v>
       </c>
       <c r="D41" t="n">
-        <v>90.91345977783203</v>
+        <v>90.91344451904297</v>
       </c>
       <c r="E41" t="n">
-        <v>90.90443389910197</v>
+        <v>90.9044186418278</v>
       </c>
       <c r="F41" t="n">
-        <v>90.90443389910197</v>
+        <v>90.9044186418278</v>
       </c>
       <c r="G41" t="n">
         <v>4526200</v>
@@ -1392,16 +1392,16 @@
         <v>45351</v>
       </c>
       <c r="C42" t="n">
-        <v>90.94053649902344</v>
+        <v>90.94052886962891</v>
       </c>
       <c r="D42" t="n">
-        <v>90.94956926627766</v>
+        <v>90.94956163612534</v>
       </c>
       <c r="E42" t="n">
-        <v>90.94053649902344</v>
+        <v>90.94052886962891</v>
       </c>
       <c r="F42" t="n">
-        <v>90.94053649902344</v>
+        <v>90.94052886962891</v>
       </c>
       <c r="G42" t="n">
         <v>5560200</v>
@@ -1415,16 +1415,16 @@
         <v>45352</v>
       </c>
       <c r="C43" t="n">
-        <v>90.96773529052734</v>
+        <v>90.96776580810547</v>
       </c>
       <c r="D43" t="n">
-        <v>90.96773529052734</v>
+        <v>90.96776580810547</v>
       </c>
       <c r="E43" t="n">
-        <v>90.95866559671036</v>
+        <v>90.9586961112458</v>
       </c>
       <c r="F43" t="n">
-        <v>90.96773529052734</v>
+        <v>90.96776580810547</v>
       </c>
       <c r="G43" t="n">
         <v>7579200</v>
@@ -1461,16 +1461,16 @@
         <v>45356</v>
       </c>
       <c r="C45" t="n">
-        <v>90.98589324951172</v>
+        <v>90.98586273193359</v>
       </c>
       <c r="D45" t="n">
-        <v>90.99496294586957</v>
+        <v>90.99493242524937</v>
       </c>
       <c r="E45" t="n">
-        <v>90.98589324951172</v>
+        <v>90.98586273193359</v>
       </c>
       <c r="F45" t="n">
-        <v>90.98589324951172</v>
+        <v>90.98586273193359</v>
       </c>
       <c r="G45" t="n">
         <v>3905300</v>
@@ -1484,16 +1484,16 @@
         <v>45357</v>
       </c>
       <c r="C46" t="n">
-        <v>91.00401306152344</v>
+        <v>91.00399780273438</v>
       </c>
       <c r="D46" t="n">
-        <v>91.01308275592983</v>
+        <v>91.01306749562004</v>
       </c>
       <c r="E46" t="n">
-        <v>90.99494336711705</v>
+        <v>90.99492810984871</v>
       </c>
       <c r="F46" t="n">
-        <v>91.00401306152344</v>
+        <v>91.00399780273438</v>
       </c>
       <c r="G46" t="n">
         <v>2760000</v>
@@ -1507,16 +1507,16 @@
         <v>45358</v>
       </c>
       <c r="C47" t="n">
-        <v>91.04936218261719</v>
+        <v>91.04936981201172</v>
       </c>
       <c r="D47" t="n">
-        <v>91.04936218261719</v>
+        <v>91.04936981201172</v>
       </c>
       <c r="E47" t="n">
-        <v>91.04029248745701</v>
+        <v>91.04030011609154</v>
       </c>
       <c r="F47" t="n">
-        <v>91.04936218261719</v>
+        <v>91.04936981201172</v>
       </c>
       <c r="G47" t="n">
         <v>2415500</v>
@@ -1553,16 +1553,16 @@
         <v>45362</v>
       </c>
       <c r="C49" t="n">
-        <v>91.07654571533203</v>
+        <v>91.07656860351562</v>
       </c>
       <c r="D49" t="n">
-        <v>91.07654571533203</v>
+        <v>91.07656860351562</v>
       </c>
       <c r="E49" t="n">
-        <v>91.06747602202755</v>
+        <v>91.06749890793186</v>
       </c>
       <c r="F49" t="n">
-        <v>91.07654571533203</v>
+        <v>91.07656860351562</v>
       </c>
       <c r="G49" t="n">
         <v>3238400</v>
@@ -1576,16 +1576,16 @@
         <v>45363</v>
       </c>
       <c r="C50" t="n">
-        <v>91.08561706542969</v>
+        <v>91.08560943603516</v>
       </c>
       <c r="D50" t="n">
-        <v>91.09468675958801</v>
+        <v>91.0946791294338</v>
       </c>
       <c r="E50" t="n">
-        <v>91.08561706542969</v>
+        <v>91.08560943603516</v>
       </c>
       <c r="F50" t="n">
-        <v>91.08561706542969</v>
+        <v>91.08560943603516</v>
       </c>
       <c r="G50" t="n">
         <v>2613300</v>
@@ -1599,16 +1599,16 @@
         <v>45364</v>
       </c>
       <c r="C51" t="n">
-        <v>91.09471130371094</v>
+        <v>91.09469604492188</v>
       </c>
       <c r="D51" t="n">
-        <v>91.10378100031295</v>
+        <v>91.10376574000468</v>
       </c>
       <c r="E51" t="n">
-        <v>91.09471130371094</v>
+        <v>91.09469604492188</v>
       </c>
       <c r="F51" t="n">
-        <v>91.09471130371094</v>
+        <v>91.09469604492188</v>
       </c>
       <c r="G51" t="n">
         <v>2249300</v>
@@ -1645,16 +1645,16 @@
         <v>45366</v>
       </c>
       <c r="C53" t="n">
-        <v>91.14907073974609</v>
+        <v>91.14910888671875</v>
       </c>
       <c r="D53" t="n">
-        <v>91.14907073974609</v>
+        <v>91.14910888671875</v>
       </c>
       <c r="E53" t="n">
-        <v>91.1400079657606</v>
+        <v>91.14004610894038</v>
       </c>
       <c r="F53" t="n">
-        <v>91.14907073974609</v>
+        <v>91.14910888671875</v>
       </c>
       <c r="G53" t="n">
         <v>3277300</v>
@@ -1668,16 +1668,16 @@
         <v>45369</v>
       </c>
       <c r="C54" t="n">
-        <v>91.15816497802734</v>
+        <v>91.15814971923828</v>
       </c>
       <c r="D54" t="n">
-        <v>91.1672346726031</v>
+        <v>91.16721941229589</v>
       </c>
       <c r="E54" t="n">
-        <v>91.15816497802734</v>
+        <v>91.15814971923828</v>
       </c>
       <c r="F54" t="n">
-        <v>91.1672346726031</v>
+        <v>91.16721941229589</v>
       </c>
       <c r="G54" t="n">
         <v>3576200</v>
@@ -1691,16 +1691,16 @@
         <v>45370</v>
       </c>
       <c r="C55" t="n">
-        <v>91.17631530761719</v>
+        <v>91.17630767822266</v>
       </c>
       <c r="D55" t="n">
-        <v>91.18537808513047</v>
+        <v>91.18537045497759</v>
       </c>
       <c r="E55" t="n">
-        <v>91.17631530761719</v>
+        <v>91.17630767822266</v>
       </c>
       <c r="F55" t="n">
-        <v>91.18537808513047</v>
+        <v>91.18537045497759</v>
       </c>
       <c r="G55" t="n">
         <v>2661900</v>
@@ -1714,16 +1714,16 @@
         <v>45371</v>
       </c>
       <c r="C56" t="n">
-        <v>91.18536376953125</v>
+        <v>91.18535614013672</v>
       </c>
       <c r="D56" t="n">
-        <v>91.19443346377142</v>
+        <v>91.19442583361803</v>
       </c>
       <c r="E56" t="n">
-        <v>91.18536376953125</v>
+        <v>91.18535614013672</v>
       </c>
       <c r="F56" t="n">
-        <v>91.18536376953125</v>
+        <v>91.18535614013672</v>
       </c>
       <c r="G56" t="n">
         <v>2492700</v>
@@ -1737,16 +1737,16 @@
         <v>45372</v>
       </c>
       <c r="C57" t="n">
-        <v>91.22163391113281</v>
+        <v>91.22162628173828</v>
       </c>
       <c r="D57" t="n">
-        <v>91.23070360520224</v>
+        <v>91.23069597504916</v>
       </c>
       <c r="E57" t="n">
-        <v>91.22163391113281</v>
+        <v>91.22162628173828</v>
       </c>
       <c r="F57" t="n">
-        <v>91.22163391113281</v>
+        <v>91.22162628173828</v>
       </c>
       <c r="G57" t="n">
         <v>3547400</v>
@@ -1760,16 +1760,16 @@
         <v>45373</v>
       </c>
       <c r="C58" t="n">
-        <v>91.23976898193359</v>
+        <v>91.23977661132812</v>
       </c>
       <c r="D58" t="n">
-        <v>91.24883175742463</v>
+        <v>91.24883938757698</v>
       </c>
       <c r="E58" t="n">
-        <v>91.23069928829332</v>
+        <v>91.23070691692946</v>
       </c>
       <c r="F58" t="n">
-        <v>91.24883175742463</v>
+        <v>91.24883938757698</v>
       </c>
       <c r="G58" t="n">
         <v>2636700</v>
@@ -1783,16 +1783,16 @@
         <v>45376</v>
       </c>
       <c r="C59" t="n">
-        <v>91.25791931152344</v>
+        <v>91.25790405273438</v>
       </c>
       <c r="D59" t="n">
-        <v>91.26698900693876</v>
+        <v>91.26697374663321</v>
       </c>
       <c r="E59" t="n">
-        <v>91.25791931152344</v>
+        <v>91.25790405273438</v>
       </c>
       <c r="F59" t="n">
-        <v>91.25791931152344</v>
+        <v>91.25790405273438</v>
       </c>
       <c r="G59" t="n">
         <v>2422900</v>
@@ -1875,16 +1875,16 @@
         <v>45383</v>
       </c>
       <c r="C63" t="n">
-        <v>91.34870910644531</v>
+        <v>91.34871673583984</v>
       </c>
       <c r="D63" t="n">
-        <v>91.35781950852548</v>
+        <v>91.3578271386809</v>
       </c>
       <c r="E63" t="n">
-        <v>91.34870910644531</v>
+        <v>91.34871673583984</v>
       </c>
       <c r="F63" t="n">
-        <v>91.35781950852548</v>
+        <v>91.3578271386809</v>
       </c>
       <c r="G63" t="n">
         <v>7395400</v>
@@ -1898,16 +1898,16 @@
         <v>45384</v>
       </c>
       <c r="C64" t="n">
-        <v>91.36693572998047</v>
+        <v>91.36692810058594</v>
       </c>
       <c r="D64" t="n">
-        <v>91.36693572998047</v>
+        <v>91.36692810058594</v>
       </c>
       <c r="E64" t="n">
-        <v>91.35783227582876</v>
+        <v>91.35782464719441</v>
       </c>
       <c r="F64" t="n">
-        <v>91.36693572998047</v>
+        <v>91.36692810058594</v>
       </c>
       <c r="G64" t="n">
         <v>4202900</v>
@@ -1921,16 +1921,16 @@
         <v>45385</v>
       </c>
       <c r="C65" t="n">
-        <v>91.37602996826172</v>
+        <v>91.37604522705078</v>
       </c>
       <c r="D65" t="n">
-        <v>91.38514037000337</v>
+        <v>91.38515563031378</v>
       </c>
       <c r="E65" t="n">
-        <v>91.37602996826172</v>
+        <v>91.37604522705078</v>
       </c>
       <c r="F65" t="n">
-        <v>91.37602996826172</v>
+        <v>91.37604522705078</v>
       </c>
       <c r="G65" t="n">
         <v>4333600</v>
@@ -1944,16 +1944,16 @@
         <v>45386</v>
       </c>
       <c r="C66" t="n">
-        <v>91.42157745361328</v>
+        <v>91.42156982421875</v>
       </c>
       <c r="D66" t="n">
-        <v>91.42157745361328</v>
+        <v>91.42156982421875</v>
       </c>
       <c r="E66" t="n">
-        <v>91.41246705162989</v>
+        <v>91.41245942299565</v>
       </c>
       <c r="F66" t="n">
-        <v>91.41246705162989</v>
+        <v>91.41245942299565</v>
       </c>
       <c r="G66" t="n">
         <v>3427500</v>
@@ -1967,16 +1967,16 @@
         <v>45387</v>
       </c>
       <c r="C67" t="n">
-        <v>91.43069458007812</v>
+        <v>91.43067932128906</v>
       </c>
       <c r="D67" t="n">
-        <v>91.439804983424</v>
+        <v>91.43978972311452</v>
       </c>
       <c r="E67" t="n">
-        <v>91.43069458007812</v>
+        <v>91.43067932128906</v>
       </c>
       <c r="F67" t="n">
-        <v>91.439804983424</v>
+        <v>91.43978972311452</v>
       </c>
       <c r="G67" t="n">
         <v>3104200</v>
@@ -2013,16 +2013,16 @@
         <v>45391</v>
       </c>
       <c r="C69" t="n">
-        <v>91.45802307128906</v>
+        <v>91.4580078125</v>
       </c>
       <c r="D69" t="n">
-        <v>91.45802307128906</v>
+        <v>91.4580078125</v>
       </c>
       <c r="E69" t="n">
-        <v>91.44891266821402</v>
+        <v>91.44889741094494</v>
       </c>
       <c r="F69" t="n">
-        <v>91.45802307128906</v>
+        <v>91.4580078125</v>
       </c>
       <c r="G69" t="n">
         <v>3578500</v>
@@ -2036,16 +2036,16 @@
         <v>45392</v>
       </c>
       <c r="C70" t="n">
-        <v>91.47621154785156</v>
+        <v>91.47624969482422</v>
       </c>
       <c r="D70" t="n">
-        <v>91.47621154785156</v>
+        <v>91.47624969482422</v>
       </c>
       <c r="E70" t="n">
-        <v>91.45799769595641</v>
+        <v>91.4580358353336</v>
       </c>
       <c r="F70" t="n">
-        <v>91.46710114730423</v>
+        <v>91.46713929047772</v>
       </c>
       <c r="G70" t="n">
         <v>3893100</v>
@@ -2059,16 +2059,16 @@
         <v>45393</v>
       </c>
       <c r="C71" t="n">
-        <v>91.51267242431641</v>
+        <v>91.51264953613281</v>
       </c>
       <c r="D71" t="n">
-        <v>91.51267242431641</v>
+        <v>91.51264953613281</v>
       </c>
       <c r="E71" t="n">
-        <v>91.50356202115843</v>
+        <v>91.50353913525345</v>
       </c>
       <c r="F71" t="n">
-        <v>91.50356202115843</v>
+        <v>91.50353913525345</v>
       </c>
       <c r="G71" t="n">
         <v>3521100</v>
@@ -2082,16 +2082,16 @@
         <v>45394</v>
       </c>
       <c r="C72" t="n">
-        <v>91.52176666259766</v>
+        <v>91.52178192138672</v>
       </c>
       <c r="D72" t="n">
-        <v>91.52176666259766</v>
+        <v>91.52178192138672</v>
       </c>
       <c r="E72" t="n">
-        <v>91.51265626104879</v>
+        <v>91.51267151831894</v>
       </c>
       <c r="F72" t="n">
-        <v>91.52176666259766</v>
+        <v>91.52178192138672</v>
       </c>
       <c r="G72" t="n">
         <v>4235400</v>
@@ -2105,16 +2105,16 @@
         <v>45397</v>
       </c>
       <c r="C73" t="n">
-        <v>91.53999328613281</v>
+        <v>91.53998565673828</v>
       </c>
       <c r="D73" t="n">
-        <v>91.53999328613281</v>
+        <v>91.53998565673828</v>
       </c>
       <c r="E73" t="n">
-        <v>91.53088288331307</v>
+        <v>91.53087525467784</v>
       </c>
       <c r="F73" t="n">
-        <v>91.53088288331307</v>
+        <v>91.53087525467784</v>
       </c>
       <c r="G73" t="n">
         <v>4144700</v>
@@ -2128,16 +2128,16 @@
         <v>45398</v>
       </c>
       <c r="C74" t="n">
-        <v>91.53999328613281</v>
+        <v>91.53998565673828</v>
       </c>
       <c r="D74" t="n">
-        <v>91.55820714257106</v>
+        <v>91.5581995116585</v>
       </c>
       <c r="E74" t="n">
-        <v>91.53999328613281</v>
+        <v>91.53998565673828</v>
       </c>
       <c r="F74" t="n">
-        <v>91.54910368895256</v>
+        <v>91.54909605879871</v>
       </c>
       <c r="G74" t="n">
         <v>4850000</v>
@@ -2197,16 +2197,16 @@
         <v>45401</v>
       </c>
       <c r="C77" t="n">
-        <v>91.62195587158203</v>
+        <v>91.6219482421875</v>
       </c>
       <c r="D77" t="n">
-        <v>91.62195587158203</v>
+        <v>91.6219482421875</v>
       </c>
       <c r="E77" t="n">
-        <v>91.60374201716995</v>
+        <v>91.60373438929209</v>
       </c>
       <c r="F77" t="n">
-        <v>91.62195587158203</v>
+        <v>91.6219482421875</v>
       </c>
       <c r="G77" t="n">
         <v>3319500</v>
@@ -2220,16 +2220,16 @@
         <v>45404</v>
       </c>
       <c r="C78" t="n">
-        <v>91.63106536865234</v>
+        <v>91.63105773925781</v>
       </c>
       <c r="D78" t="n">
-        <v>91.63106536865234</v>
+        <v>91.63105773925781</v>
       </c>
       <c r="E78" t="n">
-        <v>91.62195496693603</v>
+        <v>91.62194733830005</v>
       </c>
       <c r="F78" t="n">
-        <v>91.63106536865234</v>
+        <v>91.63105773925781</v>
       </c>
       <c r="G78" t="n">
         <v>3547400</v>
@@ -2243,16 +2243,16 @@
         <v>45405</v>
       </c>
       <c r="C79" t="n">
-        <v>91.64019012451172</v>
+        <v>91.64017486572266</v>
       </c>
       <c r="D79" t="n">
-        <v>91.64930052765506</v>
+        <v>91.64928526734903</v>
       </c>
       <c r="E79" t="n">
-        <v>91.63107972136839</v>
+        <v>91.63106446409627</v>
       </c>
       <c r="F79" t="n">
-        <v>91.64019012451172</v>
+        <v>91.64017486572266</v>
       </c>
       <c r="G79" t="n">
         <v>4233300</v>
@@ -2266,16 +2266,16 @@
         <v>45406</v>
       </c>
       <c r="C80" t="n">
-        <v>91.64928436279297</v>
+        <v>91.64927673339844</v>
       </c>
       <c r="D80" t="n">
-        <v>91.65838781512917</v>
+        <v>91.65838018497682</v>
       </c>
       <c r="E80" t="n">
-        <v>91.64928436279297</v>
+        <v>91.64927673339844</v>
       </c>
       <c r="F80" t="n">
-        <v>91.65838781512917</v>
+        <v>91.65838018497682</v>
       </c>
       <c r="G80" t="n">
         <v>3200000</v>
@@ -2289,16 +2289,16 @@
         <v>45407</v>
       </c>
       <c r="C81" t="n">
-        <v>91.69482421875</v>
+        <v>91.69481658935547</v>
       </c>
       <c r="D81" t="n">
-        <v>91.69482421875</v>
+        <v>91.69481658935547</v>
       </c>
       <c r="E81" t="n">
-        <v>91.68572076624038</v>
+        <v>91.68571313760329</v>
       </c>
       <c r="F81" t="n">
-        <v>91.69482421875</v>
+        <v>91.69481658935547</v>
       </c>
       <c r="G81" t="n">
         <v>2705900</v>
@@ -2312,16 +2312,16 @@
         <v>45408</v>
       </c>
       <c r="C82" t="n">
-        <v>91.71303558349609</v>
+        <v>91.71302795410156</v>
       </c>
       <c r="D82" t="n">
-        <v>91.71303558349609</v>
+        <v>91.71302795410156</v>
       </c>
       <c r="E82" t="n">
-        <v>91.70392518272369</v>
+        <v>91.70391755408703</v>
       </c>
       <c r="F82" t="n">
-        <v>91.70392518272369</v>
+        <v>91.70391755408703</v>
       </c>
       <c r="G82" t="n">
         <v>3008600</v>
@@ -2335,16 +2335,16 @@
         <v>45411</v>
       </c>
       <c r="C83" t="n">
-        <v>91.71303558349609</v>
+        <v>91.71302795410156</v>
       </c>
       <c r="D83" t="n">
-        <v>91.72213903506884</v>
+        <v>91.72213140491701</v>
       </c>
       <c r="E83" t="n">
-        <v>91.71303558349609</v>
+        <v>91.71302795410156</v>
       </c>
       <c r="F83" t="n">
-        <v>91.72213903506884</v>
+        <v>91.72213140491701</v>
       </c>
       <c r="G83" t="n">
         <v>2501900</v>
@@ -2358,16 +2358,16 @@
         <v>45412</v>
       </c>
       <c r="C84" t="n">
-        <v>91.72215270996094</v>
+        <v>91.72216033935547</v>
       </c>
       <c r="D84" t="n">
-        <v>91.73126311209163</v>
+        <v>91.73127074224395</v>
       </c>
       <c r="E84" t="n">
-        <v>91.72215270996094</v>
+        <v>91.72216033935547</v>
       </c>
       <c r="F84" t="n">
-        <v>91.72215270996094</v>
+        <v>91.72216033935547</v>
       </c>
       <c r="G84" t="n">
         <v>6488000</v>
@@ -2381,16 +2381,16 @@
         <v>45413</v>
       </c>
       <c r="C85" t="n">
-        <v>91.75691986083984</v>
+        <v>91.75689697265625</v>
       </c>
       <c r="D85" t="n">
-        <v>91.75691986083984</v>
+        <v>91.75689697265625</v>
       </c>
       <c r="E85" t="n">
-        <v>91.74777755015184</v>
+        <v>91.74775466424873</v>
       </c>
       <c r="F85" t="n">
-        <v>91.75691986083984</v>
+        <v>91.75689697265625</v>
       </c>
       <c r="G85" t="n">
         <v>8406600</v>
@@ -2427,16 +2427,16 @@
         <v>45415</v>
       </c>
       <c r="C87" t="n">
-        <v>91.81179809570312</v>
+        <v>91.81179046630859</v>
       </c>
       <c r="D87" t="n">
-        <v>91.81179809570312</v>
+        <v>91.81179046630859</v>
       </c>
       <c r="E87" t="n">
-        <v>91.79349951869828</v>
+        <v>91.79349189082433</v>
       </c>
       <c r="F87" t="n">
-        <v>91.8026488072007</v>
+        <v>91.80264117856646</v>
       </c>
       <c r="G87" t="n">
         <v>4792400</v>
@@ -2496,16 +2496,16 @@
         <v>45420</v>
       </c>
       <c r="C90" t="n">
-        <v>91.84840393066406</v>
+        <v>91.848388671875</v>
       </c>
       <c r="D90" t="n">
-        <v>91.84840393066406</v>
+        <v>91.848388671875</v>
       </c>
       <c r="E90" t="n">
-        <v>91.83010535053937</v>
+        <v>91.83009009479026</v>
       </c>
       <c r="F90" t="n">
-        <v>91.83925464060172</v>
+        <v>91.83923938333263</v>
       </c>
       <c r="G90" t="n">
         <v>3109400</v>
@@ -2519,16 +2519,16 @@
         <v>45421</v>
       </c>
       <c r="C91" t="n">
-        <v>91.87583160400391</v>
+        <v>91.87583923339844</v>
       </c>
       <c r="D91" t="n">
-        <v>91.88497391388746</v>
+        <v>91.88498154404117</v>
       </c>
       <c r="E91" t="n">
-        <v>91.87583160400391</v>
+        <v>91.87583923339844</v>
       </c>
       <c r="F91" t="n">
-        <v>91.88040275894568</v>
+        <v>91.8804103887198</v>
       </c>
       <c r="G91" t="n">
         <v>2739600</v>
@@ -2542,16 +2542,16 @@
         <v>45422</v>
       </c>
       <c r="C92" t="n">
-        <v>91.90325927734375</v>
+        <v>91.90327453613281</v>
       </c>
       <c r="D92" t="n">
-        <v>91.90325927734375</v>
+        <v>91.90327453613281</v>
       </c>
       <c r="E92" t="n">
-        <v>91.88496070248264</v>
+        <v>91.88497595823358</v>
       </c>
       <c r="F92" t="n">
-        <v>91.90325927734375</v>
+        <v>91.90327453613281</v>
       </c>
       <c r="G92" t="n">
         <v>3005800</v>
@@ -2565,16 +2565,16 @@
         <v>45425</v>
       </c>
       <c r="C93" t="n">
-        <v>91.91242218017578</v>
+        <v>91.91242980957031</v>
       </c>
       <c r="D93" t="n">
-        <v>91.91242218017578</v>
+        <v>91.91242980957031</v>
       </c>
       <c r="E93" t="n">
-        <v>91.9032728913899</v>
+        <v>91.90328052002498</v>
       </c>
       <c r="F93" t="n">
-        <v>91.91242218017578</v>
+        <v>91.91242980957031</v>
       </c>
       <c r="G93" t="n">
         <v>3317000</v>
@@ -2588,16 +2588,16 @@
         <v>45426</v>
       </c>
       <c r="C94" t="n">
-        <v>91.91242218017578</v>
+        <v>91.91242980957031</v>
       </c>
       <c r="D94" t="n">
-        <v>91.92156449009912</v>
+        <v>91.92157212025253</v>
       </c>
       <c r="E94" t="n">
-        <v>91.91242218017578</v>
+        <v>91.91242980957031</v>
       </c>
       <c r="F94" t="n">
-        <v>91.92156449009912</v>
+        <v>91.92157212025253</v>
       </c>
       <c r="G94" t="n">
         <v>2765800</v>
@@ -2611,16 +2611,16 @@
         <v>45427</v>
       </c>
       <c r="C95" t="n">
-        <v>91.93070983886719</v>
+        <v>91.93072509765625</v>
       </c>
       <c r="D95" t="n">
-        <v>91.93985912726093</v>
+        <v>91.93987438756861</v>
       </c>
       <c r="E95" t="n">
-        <v>91.93070983886719</v>
+        <v>91.93072509765625</v>
       </c>
       <c r="F95" t="n">
-        <v>91.93070983886719</v>
+        <v>91.93072509765625</v>
       </c>
       <c r="G95" t="n">
         <v>4228600</v>
@@ -2634,16 +2634,16 @@
         <v>45428</v>
       </c>
       <c r="C96" t="n">
-        <v>91.97644805908203</v>
+        <v>91.9764404296875</v>
       </c>
       <c r="D96" t="n">
-        <v>91.98559036849001</v>
+        <v>91.98558273833711</v>
       </c>
       <c r="E96" t="n">
-        <v>91.96729877081192</v>
+        <v>91.96729114217631</v>
       </c>
       <c r="F96" t="n">
-        <v>91.97644805908203</v>
+        <v>91.9764404296875</v>
       </c>
       <c r="G96" t="n">
         <v>3699500</v>
@@ -2657,16 +2657,16 @@
         <v>45429</v>
       </c>
       <c r="C97" t="n">
-        <v>91.98558807373047</v>
+        <v>91.985595703125</v>
       </c>
       <c r="D97" t="n">
-        <v>91.99473736177234</v>
+        <v>91.99474499192573</v>
       </c>
       <c r="E97" t="n">
-        <v>91.98558807373047</v>
+        <v>91.985595703125</v>
       </c>
       <c r="F97" t="n">
-        <v>91.99473736177234</v>
+        <v>91.99474499192573</v>
       </c>
       <c r="G97" t="n">
         <v>4544200</v>
@@ -2703,16 +2703,16 @@
         <v>45433</v>
       </c>
       <c r="C99" t="n">
-        <v>92.01302337646484</v>
+        <v>92.01303863525391</v>
       </c>
       <c r="D99" t="n">
-        <v>92.02217266395162</v>
+        <v>92.02218792425793</v>
       </c>
       <c r="E99" t="n">
-        <v>92.01302337646484</v>
+        <v>92.01303863525391</v>
       </c>
       <c r="F99" t="n">
-        <v>92.01302337646484</v>
+        <v>92.01303863525391</v>
       </c>
       <c r="G99" t="n">
         <v>3774900</v>
@@ -2726,16 +2726,16 @@
         <v>45434</v>
       </c>
       <c r="C100" t="n">
-        <v>92.02218627929688</v>
+        <v>92.02217102050781</v>
       </c>
       <c r="D100" t="n">
-        <v>92.03133556813735</v>
+        <v>92.03132030783118</v>
       </c>
       <c r="E100" t="n">
-        <v>92.02218627929688</v>
+        <v>92.02217102050781</v>
       </c>
       <c r="F100" t="n">
-        <v>92.03133556813735</v>
+        <v>92.03132030783118</v>
       </c>
       <c r="G100" t="n">
         <v>2609000</v>
@@ -2772,16 +2772,16 @@
         <v>45436</v>
       </c>
       <c r="C102" t="n">
-        <v>92.09535217285156</v>
+        <v>92.09535980224609</v>
       </c>
       <c r="D102" t="n">
-        <v>92.09535217285156</v>
+        <v>92.09535980224609</v>
       </c>
       <c r="E102" t="n">
-        <v>92.08620288544756</v>
+        <v>92.08621051408414</v>
       </c>
       <c r="F102" t="n">
-        <v>92.09535217285156</v>
+        <v>92.09535980224609</v>
       </c>
       <c r="G102" t="n">
         <v>2512800</v>
@@ -2795,16 +2795,16 @@
         <v>45440</v>
       </c>
       <c r="C103" t="n">
-        <v>92.10451507568359</v>
+        <v>92.10449981689453</v>
       </c>
       <c r="D103" t="n">
-        <v>92.10451507568359</v>
+        <v>92.10449981689453</v>
       </c>
       <c r="E103" t="n">
-        <v>92.0953657869271</v>
+        <v>92.09535052965379</v>
       </c>
       <c r="F103" t="n">
-        <v>92.0953657869271</v>
+        <v>92.09535052965379</v>
       </c>
       <c r="G103" t="n">
         <v>3684600</v>
@@ -2818,16 +2818,16 @@
         <v>45441</v>
       </c>
       <c r="C104" t="n">
-        <v>92.10451507568359</v>
+        <v>92.10449981689453</v>
       </c>
       <c r="D104" t="n">
-        <v>92.11365738557757</v>
+        <v>92.11364212527393</v>
       </c>
       <c r="E104" t="n">
-        <v>92.10451507568359</v>
+        <v>92.10449981689453</v>
       </c>
       <c r="F104" t="n">
-        <v>92.11365738557757</v>
+        <v>92.11364212527393</v>
       </c>
       <c r="G104" t="n">
         <v>3971700</v>
@@ -2841,16 +2841,16 @@
         <v>45442</v>
       </c>
       <c r="C105" t="n">
-        <v>92.12281036376953</v>
+        <v>92.122802734375</v>
       </c>
       <c r="D105" t="n">
-        <v>92.13195965289245</v>
+        <v>92.13195202274019</v>
       </c>
       <c r="E105" t="n">
-        <v>92.12281036376953</v>
+        <v>92.122802734375</v>
       </c>
       <c r="F105" t="n">
-        <v>92.12281036376953</v>
+        <v>92.122802734375</v>
       </c>
       <c r="G105" t="n">
         <v>3566800</v>
@@ -2864,16 +2864,16 @@
         <v>45443</v>
       </c>
       <c r="C106" t="n">
-        <v>92.15937805175781</v>
+        <v>92.15938568115234</v>
       </c>
       <c r="D106" t="n">
-        <v>92.15937805175781</v>
+        <v>92.15938568115234</v>
       </c>
       <c r="E106" t="n">
-        <v>92.15022876486761</v>
+        <v>92.15023639350471</v>
       </c>
       <c r="F106" t="n">
-        <v>92.15022876486761</v>
+        <v>92.15023639350471</v>
       </c>
       <c r="G106" t="n">
         <v>7082900</v>
@@ -2887,16 +2887,16 @@
         <v>45446</v>
       </c>
       <c r="C107" t="n">
-        <v>92.17775726318359</v>
+        <v>92.17777252197266</v>
       </c>
       <c r="D107" t="n">
-        <v>92.18693967331291</v>
+        <v>92.18695493362199</v>
       </c>
       <c r="E107" t="n">
-        <v>92.17775726318359</v>
+        <v>92.17777252197266</v>
       </c>
       <c r="F107" t="n">
-        <v>92.17775726318359</v>
+        <v>92.17777252197266</v>
       </c>
       <c r="G107" t="n">
         <v>9568200</v>
@@ -2910,16 +2910,16 @@
         <v>45447</v>
       </c>
       <c r="C108" t="n">
-        <v>92.19614410400391</v>
+        <v>92.19613647460938</v>
       </c>
       <c r="D108" t="n">
-        <v>92.19614410400391</v>
+        <v>92.19613647460938</v>
       </c>
       <c r="E108" t="n">
-        <v>92.18695468290501</v>
+        <v>92.18694705427092</v>
       </c>
       <c r="F108" t="n">
-        <v>92.19614410400391</v>
+        <v>92.19613647460938</v>
       </c>
       <c r="G108" t="n">
         <v>5355900</v>
@@ -2933,16 +2933,16 @@
         <v>45448</v>
       </c>
       <c r="C109" t="n">
-        <v>92.21451568603516</v>
+        <v>92.21450042724609</v>
       </c>
       <c r="D109" t="n">
-        <v>92.21451568603516</v>
+        <v>92.21450042724609</v>
       </c>
       <c r="E109" t="n">
-        <v>92.20532626565976</v>
+        <v>92.20531100839128</v>
       </c>
       <c r="F109" t="n">
-        <v>92.20532626565976</v>
+        <v>92.20531100839128</v>
       </c>
       <c r="G109" t="n">
         <v>4285300</v>
@@ -2956,16 +2956,16 @@
         <v>45449</v>
       </c>
       <c r="C110" t="n">
-        <v>92.21451568603516</v>
+        <v>92.21450042724609</v>
       </c>
       <c r="D110" t="n">
-        <v>92.22369809693659</v>
+        <v>92.22368283662811</v>
       </c>
       <c r="E110" t="n">
-        <v>92.21451568603516</v>
+        <v>92.21450042724609</v>
       </c>
       <c r="F110" t="n">
-        <v>92.22369809693659</v>
+        <v>92.22368283662811</v>
       </c>
       <c r="G110" t="n">
         <v>3376100</v>
@@ -2979,16 +2979,16 @@
         <v>45450</v>
       </c>
       <c r="C111" t="n">
-        <v>92.25127410888672</v>
+        <v>92.25126647949219</v>
       </c>
       <c r="D111" t="n">
-        <v>92.26045652055964</v>
+        <v>92.2604488904057</v>
       </c>
       <c r="E111" t="n">
-        <v>92.25127410888672</v>
+        <v>92.25126647949219</v>
       </c>
       <c r="F111" t="n">
-        <v>92.26045652055964</v>
+        <v>92.2604488904057</v>
       </c>
       <c r="G111" t="n">
         <v>3490400</v>
@@ -3002,16 +3002,16 @@
         <v>45453</v>
       </c>
       <c r="C112" t="n">
-        <v>92.26964569091797</v>
+        <v>92.26966857910156</v>
       </c>
       <c r="D112" t="n">
-        <v>92.27883511204048</v>
+        <v>92.27885800250358</v>
       </c>
       <c r="E112" t="n">
-        <v>92.26964569091797</v>
+        <v>92.26966857910156</v>
       </c>
       <c r="F112" t="n">
-        <v>92.27883511204048</v>
+        <v>92.27885800250358</v>
       </c>
       <c r="G112" t="n">
         <v>2732300</v>
@@ -3025,16 +3025,16 @@
         <v>45454</v>
       </c>
       <c r="C113" t="n">
-        <v>92.28799438476562</v>
+        <v>92.28800964355469</v>
       </c>
       <c r="D113" t="n">
-        <v>92.28799438476562</v>
+        <v>92.28800964355469</v>
       </c>
       <c r="E113" t="n">
-        <v>92.27881197541993</v>
+        <v>92.27882723269077</v>
       </c>
       <c r="F113" t="n">
-        <v>92.28799438476562</v>
+        <v>92.28800964355469</v>
       </c>
       <c r="G113" t="n">
         <v>3320000</v>
@@ -3048,16 +3048,16 @@
         <v>45455</v>
       </c>
       <c r="C114" t="n">
-        <v>92.30638122558594</v>
+        <v>92.30640411376953</v>
       </c>
       <c r="D114" t="n">
-        <v>92.30638122558594</v>
+        <v>92.30640411376953</v>
       </c>
       <c r="E114" t="n">
-        <v>92.28800238635547</v>
+        <v>92.28802526998187</v>
       </c>
       <c r="F114" t="n">
-        <v>92.2971918059707</v>
+        <v>92.29721469187569</v>
       </c>
       <c r="G114" t="n">
         <v>5355700</v>
@@ -3071,16 +3071,16 @@
         <v>45456</v>
       </c>
       <c r="C115" t="n">
-        <v>92.31556701660156</v>
+        <v>92.31558227539062</v>
       </c>
       <c r="D115" t="n">
-        <v>92.32474942638248</v>
+        <v>92.32476468668929</v>
       </c>
       <c r="E115" t="n">
-        <v>92.30637759734753</v>
+        <v>92.30639285461768</v>
       </c>
       <c r="F115" t="n">
-        <v>92.31556701660156</v>
+        <v>92.31558227539062</v>
       </c>
       <c r="G115" t="n">
         <v>3925700</v>
@@ -3140,16 +3140,16 @@
         <v>45461</v>
       </c>
       <c r="C118" t="n">
-        <v>92.39826965332031</v>
+        <v>92.39825439453125</v>
       </c>
       <c r="D118" t="n">
-        <v>92.39826965332031</v>
+        <v>92.39825439453125</v>
       </c>
       <c r="E118" t="n">
-        <v>92.3890802321874</v>
+        <v>92.3890649749159</v>
       </c>
       <c r="F118" t="n">
-        <v>92.39826965332031</v>
+        <v>92.39825439453125</v>
       </c>
       <c r="G118" t="n">
         <v>2972000</v>
@@ -3186,16 +3186,16 @@
         <v>45464</v>
       </c>
       <c r="C120" t="n">
-        <v>92.44422149658203</v>
+        <v>92.44419860839844</v>
       </c>
       <c r="D120" t="n">
-        <v>92.45340390940721</v>
+        <v>92.45338101895015</v>
       </c>
       <c r="E120" t="n">
-        <v>92.44422149658203</v>
+        <v>92.44419860839844</v>
       </c>
       <c r="F120" t="n">
-        <v>92.44422149658203</v>
+        <v>92.44419860839844</v>
       </c>
       <c r="G120" t="n">
         <v>3460900</v>
@@ -3232,16 +3232,16 @@
         <v>45468</v>
       </c>
       <c r="C122" t="n">
-        <v>92.47176361083984</v>
+        <v>92.47177886962891</v>
       </c>
       <c r="D122" t="n">
-        <v>92.47176361083984</v>
+        <v>92.47177886962891</v>
       </c>
       <c r="E122" t="n">
-        <v>92.46257419044157</v>
+        <v>92.46258944771429</v>
       </c>
       <c r="F122" t="n">
-        <v>92.47176361083984</v>
+        <v>92.47177886962891</v>
       </c>
       <c r="G122" t="n">
         <v>3561700</v>
@@ -3255,16 +3255,16 @@
         <v>45469</v>
       </c>
       <c r="C123" t="n">
-        <v>92.48096466064453</v>
+        <v>92.48095703125</v>
       </c>
       <c r="D123" t="n">
-        <v>92.49014707272349</v>
+        <v>92.49013944257143</v>
       </c>
       <c r="E123" t="n">
-        <v>92.48096466064453</v>
+        <v>92.48095703125</v>
       </c>
       <c r="F123" t="n">
-        <v>92.48188290185243</v>
+        <v>92.48187527238214</v>
       </c>
       <c r="G123" t="n">
         <v>4815500</v>
@@ -3278,16 +3278,16 @@
         <v>45470</v>
       </c>
       <c r="C124" t="n">
-        <v>92.49014282226562</v>
+        <v>92.49015045166016</v>
       </c>
       <c r="D124" t="n">
-        <v>92.49933224339715</v>
+        <v>92.4993398735497</v>
       </c>
       <c r="E124" t="n">
-        <v>92.49014282226562</v>
+        <v>92.49015045166016</v>
       </c>
       <c r="F124" t="n">
-        <v>92.49933224339715</v>
+        <v>92.4993398735497</v>
       </c>
       <c r="G124" t="n">
         <v>3349900</v>
@@ -3324,16 +3324,16 @@
         <v>45474</v>
       </c>
       <c r="C126" t="n">
-        <v>92.56287384033203</v>
+        <v>92.56288146972656</v>
       </c>
       <c r="D126" t="n">
-        <v>92.56287384033203</v>
+        <v>92.56288146972656</v>
       </c>
       <c r="E126" t="n">
-        <v>92.55365122745329</v>
+        <v>92.55365885608765</v>
       </c>
       <c r="F126" t="n">
-        <v>92.56287384033203</v>
+        <v>92.56288146972656</v>
       </c>
       <c r="G126" t="n">
         <v>9965300</v>
@@ -3393,16 +3393,16 @@
         <v>45478</v>
       </c>
       <c r="C129" t="n">
-        <v>92.63672637939453</v>
+        <v>92.63671112060547</v>
       </c>
       <c r="D129" t="n">
-        <v>92.63672637939453</v>
+        <v>92.63671112060547</v>
       </c>
       <c r="E129" t="n">
-        <v>92.62749672342457</v>
+        <v>92.62748146615579</v>
       </c>
       <c r="F129" t="n">
-        <v>92.62749672342457</v>
+        <v>92.62748146615579</v>
       </c>
       <c r="G129" t="n">
         <v>3742000</v>
@@ -3416,16 +3416,16 @@
         <v>45481</v>
       </c>
       <c r="C130" t="n">
-        <v>92.65515899658203</v>
+        <v>92.65514373779297</v>
       </c>
       <c r="D130" t="n">
-        <v>92.65515899658203</v>
+        <v>92.65514373779297</v>
       </c>
       <c r="E130" t="n">
-        <v>92.64592934327121</v>
+        <v>92.64591408600212</v>
       </c>
       <c r="F130" t="n">
-        <v>92.64592934327121</v>
+        <v>92.64591408600212</v>
       </c>
       <c r="G130" t="n">
         <v>3263000</v>
@@ -3439,16 +3439,16 @@
         <v>45482</v>
       </c>
       <c r="C131" t="n">
-        <v>92.65515899658203</v>
+        <v>92.65514373779297</v>
       </c>
       <c r="D131" t="n">
-        <v>92.67361126304097</v>
+        <v>92.67359600121311</v>
       </c>
       <c r="E131" t="n">
-        <v>92.65515899658203</v>
+        <v>92.65514373779297</v>
       </c>
       <c r="F131" t="n">
-        <v>92.66438160973014</v>
+        <v>92.66436634942227</v>
       </c>
       <c r="G131" t="n">
         <v>4508000</v>
@@ -3485,16 +3485,16 @@
         <v>45484</v>
       </c>
       <c r="C133" t="n">
-        <v>92.69207000732422</v>
+        <v>92.69206237792969</v>
       </c>
       <c r="D133" t="n">
-        <v>92.69207000732422</v>
+        <v>92.69206237792969</v>
       </c>
       <c r="E133" t="n">
-        <v>92.68284739353157</v>
+        <v>92.68283976489614</v>
       </c>
       <c r="F133" t="n">
-        <v>92.68284739353157</v>
+        <v>92.68283976489614</v>
       </c>
       <c r="G133" t="n">
         <v>4195600</v>
@@ -3508,16 +3508,16 @@
         <v>45485</v>
       </c>
       <c r="C134" t="n">
-        <v>92.73820495605469</v>
+        <v>92.73821258544922</v>
       </c>
       <c r="D134" t="n">
-        <v>92.73820495605469</v>
+        <v>92.73821258544922</v>
       </c>
       <c r="E134" t="n">
-        <v>92.72897530272394</v>
+        <v>92.72898293135917</v>
       </c>
       <c r="F134" t="n">
-        <v>92.73820495605469</v>
+        <v>92.73821258544922</v>
       </c>
       <c r="G134" t="n">
         <v>3369000</v>
@@ -3531,16 +3531,16 @@
         <v>45488</v>
       </c>
       <c r="C135" t="n">
-        <v>92.73820495605469</v>
+        <v>92.73821258544922</v>
       </c>
       <c r="D135" t="n">
-        <v>92.74743460938542</v>
+        <v>92.74744223953927</v>
       </c>
       <c r="E135" t="n">
-        <v>92.73820495605469</v>
+        <v>92.73821258544922</v>
       </c>
       <c r="F135" t="n">
-        <v>92.74743460938542</v>
+        <v>92.74744223953927</v>
       </c>
       <c r="G135" t="n">
         <v>3615100</v>
@@ -3554,16 +3554,16 @@
         <v>45489</v>
       </c>
       <c r="C136" t="n">
-        <v>92.75666809082031</v>
+        <v>92.75667572021484</v>
       </c>
       <c r="D136" t="n">
-        <v>92.75666809082031</v>
+        <v>92.75667572021484</v>
       </c>
       <c r="E136" t="n">
-        <v>92.74744547657168</v>
+        <v>92.74745310520764</v>
       </c>
       <c r="F136" t="n">
-        <v>92.75666809082031</v>
+        <v>92.75667572021484</v>
       </c>
       <c r="G136" t="n">
         <v>3622900</v>
@@ -3577,16 +3577,16 @@
         <v>45490</v>
       </c>
       <c r="C137" t="n">
-        <v>92.76587677001953</v>
+        <v>92.76589965820312</v>
       </c>
       <c r="D137" t="n">
-        <v>92.77049511626313</v>
+        <v>92.77051800558623</v>
       </c>
       <c r="E137" t="n">
-        <v>92.75664711769426</v>
+        <v>92.75667000360062</v>
       </c>
       <c r="F137" t="n">
-        <v>92.76587677001953</v>
+        <v>92.76589965820312</v>
       </c>
       <c r="G137" t="n">
         <v>3822100</v>
@@ -3600,16 +3600,16 @@
         <v>45491</v>
       </c>
       <c r="C138" t="n">
-        <v>92.78434753417969</v>
+        <v>92.78433227539062</v>
       </c>
       <c r="D138" t="n">
-        <v>92.78434753417969</v>
+        <v>92.78433227539062</v>
       </c>
       <c r="E138" t="n">
-        <v>92.77511788071449</v>
+        <v>92.77510262344329</v>
       </c>
       <c r="F138" t="n">
-        <v>92.77511788071449</v>
+        <v>92.77510262344329</v>
       </c>
       <c r="G138" t="n">
         <v>5291400</v>
@@ -3669,16 +3669,16 @@
         <v>45496</v>
       </c>
       <c r="C141" t="n">
-        <v>92.84893798828125</v>
+        <v>92.84893035888672</v>
       </c>
       <c r="D141" t="n">
-        <v>92.85816060128167</v>
+        <v>92.85815297112931</v>
       </c>
       <c r="E141" t="n">
-        <v>92.83970833511823</v>
+        <v>92.83970070648209</v>
       </c>
       <c r="F141" t="n">
-        <v>92.84893798828125</v>
+        <v>92.84893035888672</v>
       </c>
       <c r="G141" t="n">
         <v>2829200</v>
@@ -3692,16 +3692,16 @@
         <v>45497</v>
       </c>
       <c r="C142" t="n">
-        <v>92.85816192626953</v>
+        <v>92.85816955566406</v>
       </c>
       <c r="D142" t="n">
-        <v>92.86739157956426</v>
+        <v>92.86739920971711</v>
       </c>
       <c r="E142" t="n">
-        <v>92.84893931313751</v>
+        <v>92.8489469417743</v>
       </c>
       <c r="F142" t="n">
-        <v>92.85816192626953</v>
+        <v>92.85816955566406</v>
       </c>
       <c r="G142" t="n">
         <v>3474500</v>
@@ -3715,16 +3715,16 @@
         <v>45498</v>
       </c>
       <c r="C143" t="n">
-        <v>92.87661743164062</v>
+        <v>92.87664794921875</v>
       </c>
       <c r="D143" t="n">
-        <v>92.87661743164062</v>
+        <v>92.87664794921875</v>
       </c>
       <c r="E143" t="n">
-        <v>92.86738777872365</v>
+        <v>92.86741829326908</v>
       </c>
       <c r="F143" t="n">
-        <v>92.87661743164062</v>
+        <v>92.87664794921875</v>
       </c>
       <c r="G143" t="n">
         <v>3521700</v>
@@ -3738,16 +3738,16 @@
         <v>45499</v>
       </c>
       <c r="C144" t="n">
-        <v>92.90430450439453</v>
+        <v>92.90431213378906</v>
       </c>
       <c r="D144" t="n">
-        <v>92.91353415782355</v>
+        <v>92.91354178797603</v>
       </c>
       <c r="E144" t="n">
-        <v>92.90430450439453</v>
+        <v>92.90431213378906</v>
       </c>
       <c r="F144" t="n">
-        <v>92.90430450439453</v>
+        <v>92.90431213378906</v>
       </c>
       <c r="G144" t="n">
         <v>3172600</v>
@@ -3807,16 +3807,16 @@
         <v>45504</v>
       </c>
       <c r="C147" t="n">
-        <v>92.94121551513672</v>
+        <v>92.94118499755859</v>
       </c>
       <c r="D147" t="n">
-        <v>92.95044516850984</v>
+        <v>92.95041464790113</v>
       </c>
       <c r="E147" t="n">
-        <v>92.94121551513672</v>
+        <v>92.94118499755859</v>
       </c>
       <c r="F147" t="n">
-        <v>92.94121551513672</v>
+        <v>92.94118499755859</v>
       </c>
       <c r="G147" t="n">
         <v>7256900</v>
@@ -3853,16 +3853,16 @@
         <v>45506</v>
       </c>
       <c r="C149" t="n">
-        <v>93.01814270019531</v>
+        <v>93.01812744140625</v>
       </c>
       <c r="D149" t="n">
-        <v>93.01814270019531</v>
+        <v>93.01812744140625</v>
       </c>
       <c r="E149" t="n">
-        <v>92.99960706864016</v>
+        <v>92.99959181289171</v>
       </c>
       <c r="F149" t="n">
-        <v>93.00887134843308</v>
+        <v>93.00885609116492</v>
       </c>
       <c r="G149" t="n">
         <v>7927400</v>
@@ -3876,16 +3876,16 @@
         <v>45509</v>
       </c>
       <c r="C150" t="n">
-        <v>93.02741241455078</v>
+        <v>93.02742767333984</v>
       </c>
       <c r="D150" t="n">
-        <v>93.04594804577968</v>
+        <v>93.04596330760904</v>
       </c>
       <c r="E150" t="n">
-        <v>93.01814106295174</v>
+        <v>93.01815632022007</v>
       </c>
       <c r="F150" t="n">
-        <v>93.01814106295174</v>
+        <v>93.01815632022007</v>
       </c>
       <c r="G150" t="n">
         <v>8712900</v>
@@ -3945,16 +3945,16 @@
         <v>45512</v>
       </c>
       <c r="C153" t="n">
-        <v>93.07375335693359</v>
+        <v>93.07374572753906</v>
       </c>
       <c r="D153" t="n">
-        <v>93.07375335693359</v>
+        <v>93.07374572753906</v>
       </c>
       <c r="E153" t="n">
-        <v>93.05521065547747</v>
+        <v>93.05520302760291</v>
       </c>
       <c r="F153" t="n">
-        <v>93.06448200620552</v>
+        <v>93.06447437757099</v>
       </c>
       <c r="G153" t="n">
         <v>3903300</v>
@@ -4014,16 +4014,16 @@
         <v>45517</v>
       </c>
       <c r="C156" t="n">
-        <v>93.13865661621094</v>
+        <v>93.13864898681641</v>
       </c>
       <c r="D156" t="n">
-        <v>93.13865661621094</v>
+        <v>93.13864898681641</v>
       </c>
       <c r="E156" t="n">
-        <v>93.12938526369626</v>
+        <v>93.12937763506119</v>
       </c>
       <c r="F156" t="n">
-        <v>93.13865661621094</v>
+        <v>93.13864898681641</v>
       </c>
       <c r="G156" t="n">
         <v>4782200</v>
@@ -4037,16 +4037,16 @@
         <v>45518</v>
       </c>
       <c r="C157" t="n">
-        <v>93.15718078613281</v>
+        <v>93.15721130371094</v>
       </c>
       <c r="D157" t="n">
-        <v>93.15718078613281</v>
+        <v>93.15721130371094</v>
       </c>
       <c r="E157" t="n">
-        <v>93.13864515535418</v>
+        <v>93.13867566686018</v>
       </c>
       <c r="F157" t="n">
-        <v>93.14790943475899</v>
+        <v>93.1479399492999</v>
       </c>
       <c r="G157" t="n">
         <v>4327700</v>
@@ -4060,16 +4060,16 @@
         <v>45519</v>
       </c>
       <c r="C158" t="n">
-        <v>93.16648101806641</v>
+        <v>93.16645050048828</v>
       </c>
       <c r="D158" t="n">
-        <v>93.16648101806641</v>
+        <v>93.16645050048828</v>
       </c>
       <c r="E158" t="n">
-        <v>93.14793830957073</v>
+        <v>93.14790779806644</v>
       </c>
       <c r="F158" t="n">
-        <v>93.14793830957073</v>
+        <v>93.14790779806644</v>
       </c>
       <c r="G158" t="n">
         <v>4217800</v>
@@ -4083,16 +4083,16 @@
         <v>45520</v>
       </c>
       <c r="C159" t="n">
-        <v>93.20354461669922</v>
+        <v>93.20355224609375</v>
       </c>
       <c r="D159" t="n">
-        <v>93.20354461669922</v>
+        <v>93.20355224609375</v>
       </c>
       <c r="E159" t="n">
-        <v>93.19427326391828</v>
+        <v>93.19428089255386</v>
       </c>
       <c r="F159" t="n">
-        <v>93.20354461669922</v>
+        <v>93.20355224609375</v>
       </c>
       <c r="G159" t="n">
         <v>3638900</v>
@@ -4106,16 +4106,16 @@
         <v>45523</v>
       </c>
       <c r="C160" t="n">
-        <v>93.21279907226562</v>
+        <v>93.21280670166016</v>
       </c>
       <c r="D160" t="n">
-        <v>93.22207042406932</v>
+        <v>93.22207805422271</v>
       </c>
       <c r="E160" t="n">
-        <v>93.21279907226562</v>
+        <v>93.21280670166016</v>
       </c>
       <c r="F160" t="n">
-        <v>93.21279907226562</v>
+        <v>93.21280670166016</v>
       </c>
       <c r="G160" t="n">
         <v>3930700</v>
@@ -4129,16 +4129,16 @@
         <v>45524</v>
       </c>
       <c r="C161" t="n">
-        <v>93.22207641601562</v>
+        <v>93.22206115722656</v>
       </c>
       <c r="D161" t="n">
-        <v>93.23134776841523</v>
+        <v>93.23133250810862</v>
       </c>
       <c r="E161" t="n">
-        <v>93.22207641601562</v>
+        <v>93.22206115722656</v>
       </c>
       <c r="F161" t="n">
-        <v>93.23134776841523</v>
+        <v>93.23133250810862</v>
       </c>
       <c r="G161" t="n">
         <v>3084200</v>
@@ -4152,16 +4152,16 @@
         <v>45525</v>
       </c>
       <c r="C162" t="n">
-        <v>93.2498779296875</v>
+        <v>93.24988555908203</v>
       </c>
       <c r="D162" t="n">
-        <v>93.2498779296875</v>
+        <v>93.24988555908203</v>
       </c>
       <c r="E162" t="n">
-        <v>93.23134229794566</v>
+        <v>93.23134992582368</v>
       </c>
       <c r="F162" t="n">
-        <v>93.23134229794566</v>
+        <v>93.23134992582368</v>
       </c>
       <c r="G162" t="n">
         <v>3936000</v>
@@ -4175,16 +4175,16 @@
         <v>45526</v>
       </c>
       <c r="C163" t="n">
-        <v>93.2498779296875</v>
+        <v>93.24988555908203</v>
       </c>
       <c r="D163" t="n">
-        <v>93.2591492815431</v>
+        <v>93.25915691169619</v>
       </c>
       <c r="E163" t="n">
-        <v>93.2498779296875</v>
+        <v>93.24988555908203</v>
       </c>
       <c r="F163" t="n">
-        <v>93.2591492815431</v>
+        <v>93.25915691169619</v>
       </c>
       <c r="G163" t="n">
         <v>3849100</v>
@@ -4221,16 +4221,16 @@
         <v>45530</v>
       </c>
       <c r="C165" t="n">
-        <v>93.30550384521484</v>
+        <v>93.30551147460938</v>
       </c>
       <c r="D165" t="n">
-        <v>93.31476812558525</v>
+        <v>93.3147757557373</v>
       </c>
       <c r="E165" t="n">
-        <v>93.30550384521484</v>
+        <v>93.30551147460938</v>
       </c>
       <c r="F165" t="n">
-        <v>93.30550384521484</v>
+        <v>93.30551147460938</v>
       </c>
       <c r="G165" t="n">
         <v>3969000</v>
@@ -4267,16 +4267,16 @@
         <v>45532</v>
       </c>
       <c r="C167" t="n">
-        <v>93.32403564453125</v>
+        <v>93.32402801513672</v>
       </c>
       <c r="D167" t="n">
-        <v>93.33330699649056</v>
+        <v>93.33329936633808</v>
       </c>
       <c r="E167" t="n">
-        <v>93.32403564453125</v>
+        <v>93.32402801513672</v>
       </c>
       <c r="F167" t="n">
-        <v>93.33330699649056</v>
+        <v>93.33329936633808</v>
       </c>
       <c r="G167" t="n">
         <v>3500800</v>
@@ -4290,16 +4290,16 @@
         <v>45533</v>
       </c>
       <c r="C168" t="n">
-        <v>93.33331298828125</v>
+        <v>93.33332824707031</v>
       </c>
       <c r="D168" t="n">
-        <v>93.35184862142037</v>
+        <v>93.35186388323977</v>
       </c>
       <c r="E168" t="n">
-        <v>93.33331298828125</v>
+        <v>93.33332824707031</v>
       </c>
       <c r="F168" t="n">
-        <v>93.34257726886585</v>
+        <v>93.34259252916951</v>
       </c>
       <c r="G168" t="n">
         <v>4537700</v>
@@ -4313,16 +4313,16 @@
         <v>45534</v>
       </c>
       <c r="C169" t="n">
-        <v>93.37964630126953</v>
+        <v>93.37966156005859</v>
       </c>
       <c r="D169" t="n">
-        <v>93.3889176529001</v>
+        <v>93.38893291320416</v>
       </c>
       <c r="E169" t="n">
-        <v>93.37964630126953</v>
+        <v>93.37966156005859</v>
       </c>
       <c r="F169" t="n">
-        <v>93.37964630126953</v>
+        <v>93.37966156005859</v>
       </c>
       <c r="G169" t="n">
         <v>8427400</v>
@@ -4336,16 +4336,16 @@
         <v>45538</v>
       </c>
       <c r="C170" t="n">
-        <v>93.42061614990234</v>
+        <v>93.42062377929688</v>
       </c>
       <c r="D170" t="n">
-        <v>93.42061614990234</v>
+        <v>93.42062377929688</v>
       </c>
       <c r="E170" t="n">
-        <v>93.41131085768782</v>
+        <v>93.41131848632243</v>
       </c>
       <c r="F170" t="n">
-        <v>93.42061614990234</v>
+        <v>93.42062377929688</v>
       </c>
       <c r="G170" t="n">
         <v>11846700</v>
@@ -4359,16 +4359,16 @@
         <v>45539</v>
       </c>
       <c r="C171" t="n">
-        <v>93.429931640625</v>
+        <v>93.42992401123047</v>
       </c>
       <c r="D171" t="n">
-        <v>93.43924403642453</v>
+        <v>93.43923640626956</v>
       </c>
       <c r="E171" t="n">
-        <v>93.429931640625</v>
+        <v>93.42992401123047</v>
       </c>
       <c r="F171" t="n">
-        <v>93.43924403642453</v>
+        <v>93.43923640626956</v>
       </c>
       <c r="G171" t="n">
         <v>7218300</v>
@@ -4405,16 +4405,16 @@
         <v>45541</v>
       </c>
       <c r="C173" t="n">
-        <v>93.4951171875</v>
+        <v>93.49510955810547</v>
       </c>
       <c r="D173" t="n">
-        <v>93.4951171875</v>
+        <v>93.49510955810547</v>
       </c>
       <c r="E173" t="n">
-        <v>93.48581189368507</v>
+        <v>93.48580426504986</v>
       </c>
       <c r="F173" t="n">
-        <v>93.4951171875</v>
+        <v>93.49510955810547</v>
       </c>
       <c r="G173" t="n">
         <v>5534600</v>
@@ -4451,16 +4451,16 @@
         <v>45545</v>
       </c>
       <c r="C175" t="n">
-        <v>93.52304077148438</v>
+        <v>93.52302551269531</v>
       </c>
       <c r="D175" t="n">
-        <v>93.52304077148438</v>
+        <v>93.52302551269531</v>
       </c>
       <c r="E175" t="n">
-        <v>93.50442308187154</v>
+        <v>93.50440782612006</v>
       </c>
       <c r="F175" t="n">
-        <v>93.52304077148438</v>
+        <v>93.52302551269531</v>
       </c>
       <c r="G175" t="n">
         <v>4143900</v>
@@ -4474,16 +4474,16 @@
         <v>45546</v>
       </c>
       <c r="C176" t="n">
-        <v>93.52304077148438</v>
+        <v>93.52302551269531</v>
       </c>
       <c r="D176" t="n">
-        <v>93.5323531679294</v>
+        <v>93.53233790762097</v>
       </c>
       <c r="E176" t="n">
-        <v>93.52304077148438</v>
+        <v>93.52302551269531</v>
       </c>
       <c r="F176" t="n">
-        <v>93.52304077148438</v>
+        <v>93.52302551269531</v>
       </c>
       <c r="G176" t="n">
         <v>4500100</v>
@@ -4497,16 +4497,16 @@
         <v>45547</v>
       </c>
       <c r="C177" t="n">
-        <v>93.53234100341797</v>
+        <v>93.53235626220703</v>
       </c>
       <c r="D177" t="n">
-        <v>93.54165339865186</v>
+        <v>93.54166865896013</v>
       </c>
       <c r="E177" t="n">
-        <v>93.53234100341797</v>
+        <v>93.53235626220703</v>
       </c>
       <c r="F177" t="n">
-        <v>93.54165339865186</v>
+        <v>93.54166865896013</v>
       </c>
       <c r="G177" t="n">
         <v>3912400</v>
@@ -4543,16 +4543,16 @@
         <v>45551</v>
       </c>
       <c r="C179" t="n">
-        <v>93.60684204101562</v>
+        <v>93.60681915283203</v>
       </c>
       <c r="D179" t="n">
-        <v>93.60684204101562</v>
+        <v>93.60681915283203</v>
       </c>
       <c r="E179" t="n">
-        <v>93.58821724734798</v>
+        <v>93.58819436371842</v>
       </c>
       <c r="F179" t="n">
-        <v>93.58821724734798</v>
+        <v>93.58819436371842</v>
       </c>
       <c r="G179" t="n">
         <v>3571100</v>
@@ -4566,16 +4566,16 @@
         <v>45552</v>
       </c>
       <c r="C180" t="n">
-        <v>93.60684204101562</v>
+        <v>93.60681915283203</v>
       </c>
       <c r="D180" t="n">
-        <v>93.62545973140574</v>
+        <v>93.62543683866987</v>
       </c>
       <c r="E180" t="n">
-        <v>93.60684204101562</v>
+        <v>93.60681915283203</v>
       </c>
       <c r="F180" t="n">
-        <v>93.61615443784945</v>
+        <v>93.61613154738885</v>
       </c>
       <c r="G180" t="n">
         <v>4452200</v>
@@ -4612,16 +4612,16 @@
         <v>45554</v>
       </c>
       <c r="C182" t="n">
-        <v>93.65336608886719</v>
+        <v>93.65337371826172</v>
       </c>
       <c r="D182" t="n">
-        <v>93.66267848334145</v>
+        <v>93.6626861134946</v>
       </c>
       <c r="E182" t="n">
-        <v>93.64406079766864</v>
+        <v>93.64406842630514</v>
       </c>
       <c r="F182" t="n">
-        <v>93.64406079766864</v>
+        <v>93.64406842630514</v>
       </c>
       <c r="G182" t="n">
         <v>5165800</v>
@@ -4658,16 +4658,16 @@
         <v>45558</v>
       </c>
       <c r="C184" t="n">
-        <v>93.71855926513672</v>
+        <v>93.71856689453125</v>
       </c>
       <c r="D184" t="n">
-        <v>93.71855926513672</v>
+        <v>93.71856689453125</v>
       </c>
       <c r="E184" t="n">
-        <v>93.6999344735017</v>
+        <v>93.69994210138005</v>
       </c>
       <c r="F184" t="n">
-        <v>93.70924686931922</v>
+        <v>93.70925449795564</v>
       </c>
       <c r="G184" t="n">
         <v>5220900</v>
@@ -4842,16 +4842,16 @@
         <v>45568</v>
       </c>
       <c r="C192" t="n">
-        <v>93.82115173339844</v>
+        <v>93.8211669921875</v>
       </c>
       <c r="D192" t="n">
-        <v>93.83050405525599</v>
+        <v>93.83051931556608</v>
       </c>
       <c r="E192" t="n">
-        <v>93.82115173339844</v>
+        <v>93.8211669921875</v>
       </c>
       <c r="F192" t="n">
-        <v>93.83050405525599</v>
+        <v>93.83051931556608</v>
       </c>
       <c r="G192" t="n">
         <v>4066100</v>
@@ -4865,16 +4865,16 @@
         <v>45569</v>
       </c>
       <c r="C193" t="n">
-        <v>93.85856628417969</v>
+        <v>93.85855865478516</v>
       </c>
       <c r="D193" t="n">
-        <v>93.86791860727251</v>
+        <v>93.86791097711776</v>
       </c>
       <c r="E193" t="n">
-        <v>93.85856628417969</v>
+        <v>93.85855865478516</v>
       </c>
       <c r="F193" t="n">
-        <v>93.86324601259227</v>
+        <v>93.86323838281734</v>
       </c>
       <c r="G193" t="n">
         <v>4987100</v>
@@ -4888,16 +4888,16 @@
         <v>45572</v>
       </c>
       <c r="C194" t="n">
-        <v>93.86792755126953</v>
+        <v>93.86790466308594</v>
       </c>
       <c r="D194" t="n">
-        <v>93.87727987525348</v>
+        <v>93.87725698478947</v>
       </c>
       <c r="E194" t="n">
-        <v>93.86792755126953</v>
+        <v>93.86790466308594</v>
       </c>
       <c r="F194" t="n">
-        <v>93.86792755126953</v>
+        <v>93.86790466308594</v>
       </c>
       <c r="G194" t="n">
         <v>4792500</v>
@@ -4911,16 +4911,16 @@
         <v>45573</v>
       </c>
       <c r="C195" t="n">
-        <v>93.87725830078125</v>
+        <v>93.87726593017578</v>
       </c>
       <c r="D195" t="n">
-        <v>93.88661062261588</v>
+        <v>93.88661825277048</v>
       </c>
       <c r="E195" t="n">
-        <v>93.87725830078125</v>
+        <v>93.87726593017578</v>
       </c>
       <c r="F195" t="n">
-        <v>93.87725830078125</v>
+        <v>93.87726593017578</v>
       </c>
       <c r="G195" t="n">
         <v>3923100</v>
@@ -4934,16 +4934,16 @@
         <v>45574</v>
       </c>
       <c r="C196" t="n">
-        <v>93.89598083496094</v>
+        <v>93.89596557617188</v>
       </c>
       <c r="D196" t="n">
-        <v>93.90533315928806</v>
+        <v>93.90531789897918</v>
       </c>
       <c r="E196" t="n">
-        <v>93.88663564436709</v>
+        <v>93.8866203870967</v>
       </c>
       <c r="F196" t="n">
-        <v>93.89598083496094</v>
+        <v>93.89596557617188</v>
       </c>
       <c r="G196" t="n">
         <v>4024800</v>
@@ -4957,16 +4957,16 @@
         <v>45575</v>
       </c>
       <c r="C197" t="n">
-        <v>93.91466522216797</v>
+        <v>93.91468048095703</v>
       </c>
       <c r="D197" t="n">
-        <v>93.91466522216797</v>
+        <v>93.91468048095703</v>
       </c>
       <c r="E197" t="n">
-        <v>93.90531289985854</v>
+        <v>93.9053281571281</v>
       </c>
       <c r="F197" t="n">
-        <v>93.91466522216797</v>
+        <v>93.91468048095703</v>
       </c>
       <c r="G197" t="n">
         <v>3731100</v>
@@ -4980,16 +4980,16 @@
         <v>45576</v>
       </c>
       <c r="C198" t="n">
-        <v>93.95207977294922</v>
+        <v>93.95206451416016</v>
       </c>
       <c r="D198" t="n">
-        <v>93.96142496275984</v>
+        <v>93.96140970245301</v>
       </c>
       <c r="E198" t="n">
-        <v>93.95207977294922</v>
+        <v>93.95206451416016</v>
       </c>
       <c r="F198" t="n">
-        <v>93.95207977294922</v>
+        <v>93.95206451416016</v>
       </c>
       <c r="G198" t="n">
         <v>3778400</v>
@@ -5003,16 +5003,16 @@
         <v>45579</v>
       </c>
       <c r="C199" t="n">
-        <v>93.95207977294922</v>
+        <v>93.95206451416016</v>
       </c>
       <c r="D199" t="n">
-        <v>93.96142496275984</v>
+        <v>93.96140970245301</v>
       </c>
       <c r="E199" t="n">
-        <v>93.95207977294922</v>
+        <v>93.95206451416016</v>
       </c>
       <c r="F199" t="n">
-        <v>93.95207977294922</v>
+        <v>93.95206451416016</v>
       </c>
       <c r="G199" t="n">
         <v>3297100</v>
@@ -5026,16 +5026,16 @@
         <v>45580</v>
       </c>
       <c r="C200" t="n">
-        <v>93.97078704833984</v>
+        <v>93.97079467773438</v>
       </c>
       <c r="D200" t="n">
-        <v>93.97078704833984</v>
+        <v>93.97079467773438</v>
       </c>
       <c r="E200" t="n">
-        <v>93.96143472382499</v>
+        <v>93.96144235246022</v>
       </c>
       <c r="F200" t="n">
-        <v>93.97078704833984</v>
+        <v>93.97079467773438</v>
       </c>
       <c r="G200" t="n">
         <v>3567400</v>
@@ -5095,16 +5095,16 @@
         <v>45583</v>
       </c>
       <c r="C203" t="n">
-        <v>94.02687835693359</v>
+        <v>94.02687072753906</v>
       </c>
       <c r="D203" t="n">
-        <v>94.03623068061582</v>
+        <v>94.03622305046243</v>
       </c>
       <c r="E203" t="n">
-        <v>94.01753316698415</v>
+        <v>94.0175255383479</v>
       </c>
       <c r="F203" t="n">
-        <v>94.03623068061582</v>
+        <v>94.03622305046243</v>
       </c>
       <c r="G203" t="n">
         <v>3970200</v>
@@ -5118,16 +5118,16 @@
         <v>45586</v>
       </c>
       <c r="C204" t="n">
-        <v>94.04559326171875</v>
+        <v>94.04557037353516</v>
       </c>
       <c r="D204" t="n">
-        <v>94.04559326171875</v>
+        <v>94.04557037353516</v>
       </c>
       <c r="E204" t="n">
-        <v>94.03624093701647</v>
+        <v>94.03621805110899</v>
       </c>
       <c r="F204" t="n">
-        <v>94.03624093701647</v>
+        <v>94.03621805110899</v>
       </c>
       <c r="G204" t="n">
         <v>3940600</v>
@@ -5141,16 +5141,16 @@
         <v>45587</v>
       </c>
       <c r="C205" t="n">
-        <v>94.05493927001953</v>
+        <v>94.05491638183594</v>
       </c>
       <c r="D205" t="n">
-        <v>94.05493927001953</v>
+        <v>94.05491638183594</v>
       </c>
       <c r="E205" t="n">
-        <v>94.04559407896961</v>
+        <v>94.04557119306016</v>
       </c>
       <c r="F205" t="n">
-        <v>94.05493927001953</v>
+        <v>94.05491638183594</v>
       </c>
       <c r="G205" t="n">
         <v>3462800</v>
@@ -5164,16 +5164,16 @@
         <v>45588</v>
       </c>
       <c r="C206" t="n">
-        <v>94.05493927001953</v>
+        <v>94.05491638183594</v>
       </c>
       <c r="D206" t="n">
-        <v>94.07364391958662</v>
+        <v>94.07362102685126</v>
       </c>
       <c r="E206" t="n">
-        <v>94.05493927001953</v>
+        <v>94.05491638183594</v>
       </c>
       <c r="F206" t="n">
-        <v>94.07364391958662</v>
+        <v>94.07362102685126</v>
       </c>
       <c r="G206" t="n">
         <v>3927700</v>
@@ -5210,16 +5210,16 @@
         <v>45590</v>
       </c>
       <c r="C208" t="n">
-        <v>94.12037658691406</v>
+        <v>94.12038421630859</v>
       </c>
       <c r="D208" t="n">
-        <v>94.12037658691406</v>
+        <v>94.12038421630859</v>
       </c>
       <c r="E208" t="n">
-        <v>94.11102426429896</v>
+        <v>94.11103189293539</v>
       </c>
       <c r="F208" t="n">
-        <v>94.11102426429896</v>
+        <v>94.11103189293539</v>
       </c>
       <c r="G208" t="n">
         <v>5386900</v>
@@ -5233,16 +5233,16 @@
         <v>45593</v>
       </c>
       <c r="C209" t="n">
-        <v>94.12037658691406</v>
+        <v>94.12038421630859</v>
       </c>
       <c r="D209" t="n">
-        <v>94.12972177579719</v>
+        <v>94.12972940594925</v>
       </c>
       <c r="E209" t="n">
-        <v>94.12037658691406</v>
+        <v>94.12038421630859</v>
       </c>
       <c r="F209" t="n">
-        <v>94.12972177579719</v>
+        <v>94.12972940594925</v>
       </c>
       <c r="G209" t="n">
         <v>3471300</v>
@@ -5256,16 +5256,16 @@
         <v>45594</v>
       </c>
       <c r="C210" t="n">
-        <v>94.13908386230469</v>
+        <v>94.13906860351562</v>
       </c>
       <c r="D210" t="n">
-        <v>94.13908386230469</v>
+        <v>94.13906860351562</v>
       </c>
       <c r="E210" t="n">
-        <v>94.12505894379339</v>
+        <v>94.1250436872776</v>
       </c>
       <c r="F210" t="n">
-        <v>94.12973153871958</v>
+        <v>94.12971628144642</v>
       </c>
       <c r="G210" t="n">
         <v>3449900</v>
@@ -5279,16 +5279,16 @@
         <v>45595</v>
       </c>
       <c r="C211" t="n">
-        <v>94.13908386230469</v>
+        <v>94.13906860351562</v>
       </c>
       <c r="D211" t="n">
-        <v>94.15778137574219</v>
+        <v>94.15776611392248</v>
       </c>
       <c r="E211" t="n">
-        <v>94.13908386230469</v>
+        <v>94.13906860351562</v>
       </c>
       <c r="F211" t="n">
-        <v>94.14843618588979</v>
+        <v>94.14842092558483</v>
       </c>
       <c r="G211" t="n">
         <v>7059200</v>
@@ -5325,16 +5325,16 @@
         <v>45597</v>
       </c>
       <c r="C213" t="n">
-        <v>94.20941162109375</v>
+        <v>94.20941925048828</v>
       </c>
       <c r="D213" t="n">
-        <v>94.20941162109375</v>
+        <v>94.20941925048828</v>
       </c>
       <c r="E213" t="n">
-        <v>94.20002775979395</v>
+        <v>94.20003538842856</v>
       </c>
       <c r="F213" t="n">
-        <v>94.20941162109375</v>
+        <v>94.20941925048828</v>
       </c>
       <c r="G213" t="n">
         <v>13451800</v>
@@ -5348,16 +5348,16 @@
         <v>45600</v>
       </c>
       <c r="C214" t="n">
-        <v>94.21881103515625</v>
+        <v>94.21880340576172</v>
       </c>
       <c r="D214" t="n">
-        <v>94.22726367433162</v>
+        <v>94.22725604425263</v>
       </c>
       <c r="E214" t="n">
-        <v>94.20942000976736</v>
+        <v>94.20941238113326</v>
       </c>
       <c r="F214" t="n">
-        <v>94.21881103515625</v>
+        <v>94.21880340576172</v>
       </c>
       <c r="G214" t="n">
         <v>5041500</v>
@@ -5371,16 +5371,16 @@
         <v>45601</v>
       </c>
       <c r="C215" t="n">
-        <v>94.23757171630859</v>
+        <v>94.23760223388672</v>
       </c>
       <c r="D215" t="n">
-        <v>94.23757171630859</v>
+        <v>94.23760223388672</v>
       </c>
       <c r="E215" t="n">
-        <v>94.21878966978989</v>
+        <v>94.21882018128569</v>
       </c>
       <c r="F215" t="n">
-        <v>94.22818069304924</v>
+        <v>94.22821120758621</v>
       </c>
       <c r="G215" t="n">
         <v>4280500</v>
@@ -5394,16 +5394,16 @@
         <v>45602</v>
       </c>
       <c r="C216" t="n">
-        <v>94.23757171630859</v>
+        <v>94.23760223388672</v>
       </c>
       <c r="D216" t="n">
-        <v>94.24695557631604</v>
+        <v>94.246986096933</v>
       </c>
       <c r="E216" t="n">
-        <v>94.22818069304924</v>
+        <v>94.22821120758621</v>
       </c>
       <c r="F216" t="n">
-        <v>94.22818069304924</v>
+        <v>94.22821120758621</v>
       </c>
       <c r="G216" t="n">
         <v>9470900</v>
@@ -5417,16 +5417,16 @@
         <v>45603</v>
       </c>
       <c r="C217" t="n">
-        <v>94.25636291503906</v>
+        <v>94.25634765625</v>
       </c>
       <c r="D217" t="n">
-        <v>94.25636291503906</v>
+        <v>94.25634765625</v>
       </c>
       <c r="E217" t="n">
-        <v>94.24697189015416</v>
+        <v>94.24695663288537</v>
       </c>
       <c r="F217" t="n">
-        <v>94.24697189015416</v>
+        <v>94.24695663288537</v>
       </c>
       <c r="G217" t="n">
         <v>6188100</v>
@@ -5463,16 +5463,16 @@
         <v>45607</v>
       </c>
       <c r="C219" t="n">
-        <v>94.29393768310547</v>
+        <v>94.29390716552734</v>
       </c>
       <c r="D219" t="n">
-        <v>94.3033287097663</v>
+        <v>94.30329818914883</v>
       </c>
       <c r="E219" t="n">
-        <v>94.28924575140231</v>
+        <v>94.28921523534268</v>
       </c>
       <c r="F219" t="n">
-        <v>94.29393768310547</v>
+        <v>94.29390716552734</v>
       </c>
       <c r="G219" t="n">
         <v>4443700</v>
@@ -5509,16 +5509,16 @@
         <v>45609</v>
       </c>
       <c r="C221" t="n">
-        <v>94.33148193359375</v>
+        <v>94.33146667480469</v>
       </c>
       <c r="D221" t="n">
-        <v>94.33148193359375</v>
+        <v>94.33146667480469</v>
       </c>
       <c r="E221" t="n">
-        <v>94.31269988279932</v>
+        <v>94.3126846270484</v>
       </c>
       <c r="F221" t="n">
-        <v>94.32209090819653</v>
+        <v>94.32207565092654</v>
       </c>
       <c r="G221" t="n">
         <v>4818000</v>
@@ -5532,16 +5532,16 @@
         <v>45610</v>
       </c>
       <c r="C222" t="n">
-        <v>94.33148193359375</v>
+        <v>94.33146667480469</v>
       </c>
       <c r="D222" t="n">
-        <v>94.34087295899096</v>
+        <v>94.34085769868284</v>
       </c>
       <c r="E222" t="n">
-        <v>94.33148193359375</v>
+        <v>94.33146667480469</v>
       </c>
       <c r="F222" t="n">
-        <v>94.34087295899096</v>
+        <v>94.34085769868284</v>
       </c>
       <c r="G222" t="n">
         <v>4353200</v>
@@ -5555,16 +5555,16 @@
         <v>45611</v>
       </c>
       <c r="C223" t="n">
-        <v>94.37842559814453</v>
+        <v>94.37841033935547</v>
       </c>
       <c r="D223" t="n">
-        <v>94.37842559814453</v>
+        <v>94.37841033935547</v>
       </c>
       <c r="E223" t="n">
-        <v>94.3690417357161</v>
+        <v>94.36902647844418</v>
       </c>
       <c r="F223" t="n">
-        <v>94.3690417357161</v>
+        <v>94.36902647844418</v>
       </c>
       <c r="G223" t="n">
         <v>5605100</v>
@@ -5578,16 +5578,16 @@
         <v>45614</v>
       </c>
       <c r="C224" t="n">
-        <v>94.38780975341797</v>
+        <v>94.38780212402344</v>
       </c>
       <c r="D224" t="n">
-        <v>94.38780975341797</v>
+        <v>94.38780212402344</v>
       </c>
       <c r="E224" t="n">
-        <v>94.37841872841933</v>
+        <v>94.37841109978388</v>
       </c>
       <c r="F224" t="n">
-        <v>94.38780975341797</v>
+        <v>94.38780212402344</v>
       </c>
       <c r="G224" t="n">
         <v>5567500</v>
@@ -5601,16 +5601,16 @@
         <v>45615</v>
       </c>
       <c r="C225" t="n">
-        <v>94.397216796875</v>
+        <v>94.39717864990234</v>
       </c>
       <c r="D225" t="n">
-        <v>94.397216796875</v>
+        <v>94.39717864990234</v>
       </c>
       <c r="E225" t="n">
-        <v>94.38782577028277</v>
+        <v>94.38778762710514</v>
       </c>
       <c r="F225" t="n">
-        <v>94.397216796875</v>
+        <v>94.39717864990234</v>
       </c>
       <c r="G225" t="n">
         <v>4310900</v>
@@ -5624,16 +5624,16 @@
         <v>45616</v>
       </c>
       <c r="C226" t="n">
-        <v>94.41597747802734</v>
+        <v>94.41596221923828</v>
       </c>
       <c r="D226" t="n">
-        <v>94.41597747802734</v>
+        <v>94.41596221923828</v>
       </c>
       <c r="E226" t="n">
-        <v>94.39720259092282</v>
+        <v>94.397187335168</v>
       </c>
       <c r="F226" t="n">
-        <v>94.40659361610177</v>
+        <v>94.40657835882925</v>
       </c>
       <c r="G226" t="n">
         <v>4133000</v>
@@ -5647,16 +5647,16 @@
         <v>45617</v>
       </c>
       <c r="C227" t="n">
-        <v>94.41597747802734</v>
+        <v>94.41596221923828</v>
       </c>
       <c r="D227" t="n">
-        <v>94.4253685032063</v>
+        <v>94.42535324289952</v>
       </c>
       <c r="E227" t="n">
-        <v>94.41597747802734</v>
+        <v>94.41596221923828</v>
       </c>
       <c r="F227" t="n">
-        <v>94.4253685032063</v>
+        <v>94.42535324289952</v>
       </c>
       <c r="G227" t="n">
         <v>4410700</v>
@@ -5670,16 +5670,16 @@
         <v>45618</v>
       </c>
       <c r="C228" t="n">
-        <v>94.44414520263672</v>
+        <v>94.44413757324219</v>
       </c>
       <c r="D228" t="n">
-        <v>94.45353622799588</v>
+        <v>94.45352859784272</v>
       </c>
       <c r="E228" t="n">
-        <v>94.44414520263672</v>
+        <v>94.44413757324219</v>
       </c>
       <c r="F228" t="n">
-        <v>94.44414520263672</v>
+        <v>94.44413757324219</v>
       </c>
       <c r="G228" t="n">
         <v>4343900</v>
@@ -5693,16 +5693,16 @@
         <v>45621</v>
       </c>
       <c r="C229" t="n">
-        <v>94.45352935791016</v>
+        <v>94.45352172851562</v>
       </c>
       <c r="D229" t="n">
-        <v>94.46292038258626</v>
+        <v>94.46291275243318</v>
       </c>
       <c r="E229" t="n">
-        <v>94.45352935791016</v>
+        <v>94.45352172851562</v>
       </c>
       <c r="F229" t="n">
-        <v>94.45352935791016</v>
+        <v>94.45352172851562</v>
       </c>
       <c r="G229" t="n">
         <v>6020200</v>
@@ -5716,16 +5716,16 @@
         <v>45622</v>
       </c>
       <c r="C230" t="n">
-        <v>94.47230529785156</v>
+        <v>94.47231292724609</v>
       </c>
       <c r="D230" t="n">
-        <v>94.48168915866783</v>
+        <v>94.48169678882019</v>
       </c>
       <c r="E230" t="n">
-        <v>94.46291427378277</v>
+        <v>94.4629219024189</v>
       </c>
       <c r="F230" t="n">
-        <v>94.47230529785156</v>
+        <v>94.47231292724609</v>
       </c>
       <c r="G230" t="n">
         <v>4586900</v>
@@ -5739,16 +5739,16 @@
         <v>45623</v>
       </c>
       <c r="C231" t="n">
-        <v>94.49108123779297</v>
+        <v>94.49106597900391</v>
       </c>
       <c r="D231" t="n">
-        <v>94.50047226196662</v>
+        <v>94.50045700166106</v>
       </c>
       <c r="E231" t="n">
-        <v>94.49108123779297</v>
+        <v>94.49106597900391</v>
       </c>
       <c r="F231" t="n">
-        <v>94.49108123779297</v>
+        <v>94.49106597900391</v>
       </c>
       <c r="G231" t="n">
         <v>5909000</v>
@@ -5762,16 +5762,16 @@
         <v>45625</v>
       </c>
       <c r="C232" t="n">
-        <v>94.52864074707031</v>
+        <v>94.52864837646484</v>
       </c>
       <c r="D232" t="n">
-        <v>94.53803177149987</v>
+        <v>94.53803940165234</v>
       </c>
       <c r="E232" t="n">
-        <v>94.52864074707031</v>
+        <v>94.52864837646484</v>
       </c>
       <c r="F232" t="n">
-        <v>94.52864074707031</v>
+        <v>94.52864837646484</v>
       </c>
       <c r="G232" t="n">
         <v>6581100</v>
@@ -5785,16 +5785,16 @@
         <v>45628</v>
       </c>
       <c r="C233" t="n">
-        <v>94.54560852050781</v>
+        <v>94.54560089111328</v>
       </c>
       <c r="D233" t="n">
-        <v>94.55503493656933</v>
+        <v>94.55502730641413</v>
       </c>
       <c r="E233" t="n">
-        <v>94.54560852050781</v>
+        <v>94.54560089111328</v>
       </c>
       <c r="F233" t="n">
-        <v>94.55031813341422</v>
+        <v>94.55031050363964</v>
       </c>
       <c r="G233" t="n">
         <v>11471800</v>
@@ -5808,16 +5808,16 @@
         <v>45629</v>
       </c>
       <c r="C234" t="n">
-        <v>94.55503082275391</v>
+        <v>94.55503845214844</v>
       </c>
       <c r="D234" t="n">
-        <v>94.5644500481569</v>
+        <v>94.56445767831146</v>
       </c>
       <c r="E234" t="n">
-        <v>94.55503082275391</v>
+        <v>94.55503845214844</v>
       </c>
       <c r="F234" t="n">
-        <v>94.5644500481569</v>
+        <v>94.56445767831146</v>
       </c>
       <c r="G234" t="n">
         <v>5734100</v>
@@ -5831,16 +5831,16 @@
         <v>45630</v>
       </c>
       <c r="C235" t="n">
-        <v>94.57389068603516</v>
+        <v>94.57388305664062</v>
       </c>
       <c r="D235" t="n">
-        <v>94.58331710310412</v>
+        <v>94.58330947294915</v>
       </c>
       <c r="E235" t="n">
-        <v>94.56446426896619</v>
+        <v>94.5644566403321</v>
       </c>
       <c r="F235" t="n">
-        <v>94.57389068603516</v>
+        <v>94.57388305664062</v>
       </c>
       <c r="G235" t="n">
         <v>5351100</v>
@@ -5854,16 +5854,16 @@
         <v>45631</v>
       </c>
       <c r="C236" t="n">
-        <v>94.58330535888672</v>
+        <v>94.58329772949219</v>
       </c>
       <c r="D236" t="n">
-        <v>94.59273177478522</v>
+        <v>94.59272414463034</v>
       </c>
       <c r="E236" t="n">
-        <v>94.58330535888672</v>
+        <v>94.58329772949219</v>
       </c>
       <c r="F236" t="n">
-        <v>94.58330535888672</v>
+        <v>94.58329772949219</v>
       </c>
       <c r="G236" t="n">
         <v>4870100</v>
@@ -5877,16 +5877,16 @@
         <v>45632</v>
       </c>
       <c r="C237" t="n">
-        <v>94.63043212890625</v>
+        <v>94.63042449951172</v>
       </c>
       <c r="D237" t="n">
-        <v>94.63043212890625</v>
+        <v>94.63042449951172</v>
       </c>
       <c r="E237" t="n">
-        <v>94.62100571282039</v>
+        <v>94.62099808418584</v>
       </c>
       <c r="F237" t="n">
-        <v>94.63043212890625</v>
+        <v>94.63042449951172</v>
       </c>
       <c r="G237" t="n">
         <v>4779000</v>
@@ -5900,16 +5900,16 @@
         <v>45635</v>
       </c>
       <c r="C238" t="n">
-        <v>94.63985443115234</v>
+        <v>94.63983917236328</v>
       </c>
       <c r="D238" t="n">
-        <v>94.63985443115234</v>
+        <v>94.63983917236328</v>
       </c>
       <c r="E238" t="n">
-        <v>94.63043520500904</v>
+        <v>94.63041994773863</v>
       </c>
       <c r="F238" t="n">
-        <v>94.63043520500904</v>
+        <v>94.63041994773863</v>
       </c>
       <c r="G238" t="n">
         <v>5539800</v>
@@ -5969,16 +5969,16 @@
         <v>45638</v>
       </c>
       <c r="C241" t="n">
-        <v>94.66813659667969</v>
+        <v>94.66812896728516</v>
       </c>
       <c r="D241" t="n">
-        <v>94.67756301407832</v>
+        <v>94.6775553839241</v>
       </c>
       <c r="E241" t="n">
-        <v>94.66813659667969</v>
+        <v>94.66812896728516</v>
       </c>
       <c r="F241" t="n">
-        <v>94.67756301407832</v>
+        <v>94.6775553839241</v>
       </c>
       <c r="G241" t="n">
         <v>4701000</v>
@@ -5992,16 +5992,16 @@
         <v>45639</v>
       </c>
       <c r="C242" t="n">
-        <v>94.71526336669922</v>
+        <v>94.71524810791016</v>
       </c>
       <c r="D242" t="n">
-        <v>94.71526336669922</v>
+        <v>94.71524810791016</v>
       </c>
       <c r="E242" t="n">
-        <v>94.70583694911416</v>
+        <v>94.70582169184371</v>
       </c>
       <c r="F242" t="n">
-        <v>94.70583694911416</v>
+        <v>94.70582169184371</v>
       </c>
       <c r="G242" t="n">
         <v>4671500</v>
@@ -6015,16 +6015,16 @@
         <v>45642</v>
       </c>
       <c r="C243" t="n">
-        <v>94.72467041015625</v>
+        <v>94.72468566894531</v>
       </c>
       <c r="D243" t="n">
-        <v>94.72467041015625</v>
+        <v>94.72468566894531</v>
       </c>
       <c r="E243" t="n">
-        <v>94.71524399449918</v>
+        <v>94.71525925176978</v>
       </c>
       <c r="F243" t="n">
-        <v>94.72467041015625</v>
+        <v>94.72468566894531</v>
       </c>
       <c r="G243" t="n">
         <v>5598900</v>
@@ -6038,16 +6038,16 @@
         <v>45643</v>
       </c>
       <c r="C244" t="n">
-        <v>94.72467041015625</v>
+        <v>94.72468566894531</v>
       </c>
       <c r="D244" t="n">
-        <v>94.7340896355649</v>
+        <v>94.73410489587128</v>
       </c>
       <c r="E244" t="n">
-        <v>94.72467041015625</v>
+        <v>94.72468566894531</v>
       </c>
       <c r="F244" t="n">
-        <v>94.7340896355649</v>
+        <v>94.73410489587128</v>
       </c>
       <c r="G244" t="n">
         <v>5798500</v>
@@ -6107,16 +6107,16 @@
         <v>45646</v>
       </c>
       <c r="C247" t="n">
-        <v>94.78331756591797</v>
+        <v>94.7833251953125</v>
       </c>
       <c r="D247" t="n">
-        <v>94.79277899988548</v>
+        <v>94.79278663004159</v>
       </c>
       <c r="E247" t="n">
-        <v>94.78331756591797</v>
+        <v>94.7833251953125</v>
       </c>
       <c r="F247" t="n">
-        <v>94.7880518913815</v>
+        <v>94.78805952115711</v>
       </c>
       <c r="G247" t="n">
         <v>8898900</v>
@@ -6153,16 +6153,16 @@
         <v>45650</v>
       </c>
       <c r="C249" t="n">
-        <v>94.83063507080078</v>
+        <v>94.83062744140625</v>
       </c>
       <c r="D249" t="n">
-        <v>94.83063507080078</v>
+        <v>94.83062744140625</v>
       </c>
       <c r="E249" t="n">
-        <v>94.82117363508208</v>
+        <v>94.82116600644875</v>
       </c>
       <c r="F249" t="n">
-        <v>94.83063507080078</v>
+        <v>94.83062744140625</v>
       </c>
       <c r="G249" t="n">
         <v>4654300</v>
@@ -6176,16 +6176,16 @@
         <v>45652</v>
       </c>
       <c r="C250" t="n">
-        <v>94.84006500244141</v>
+        <v>94.840087890625</v>
       </c>
       <c r="D250" t="n">
-        <v>94.84006500244141</v>
+        <v>94.840087890625</v>
       </c>
       <c r="E250" t="n">
-        <v>94.83060356986562</v>
+        <v>94.83062645576584</v>
       </c>
       <c r="F250" t="n">
-        <v>94.84006500244141</v>
+        <v>94.840087890625</v>
       </c>
       <c r="G250" t="n">
         <v>4974100</v>
@@ -6199,16 +6199,16 @@
         <v>45653</v>
       </c>
       <c r="C251" t="n">
-        <v>94.86846923828125</v>
+        <v>94.86845397949219</v>
       </c>
       <c r="D251" t="n">
-        <v>94.86846923828125</v>
+        <v>94.86845397949219</v>
       </c>
       <c r="E251" t="n">
-        <v>94.85900780299723</v>
+        <v>94.85899254572995</v>
       </c>
       <c r="F251" t="n">
-        <v>94.85900780299723</v>
+        <v>94.85899254572995</v>
       </c>
       <c r="G251" t="n">
         <v>6558000</v>
@@ -6222,16 +6222,16 @@
         <v>45656</v>
       </c>
       <c r="C252" t="n">
-        <v>94.86846923828125</v>
+        <v>94.86845397949219</v>
       </c>
       <c r="D252" t="n">
-        <v>94.87793067356529</v>
+        <v>94.87791541325443</v>
       </c>
       <c r="E252" t="n">
-        <v>94.86846923828125</v>
+        <v>94.86845397949219</v>
       </c>
       <c r="F252" t="n">
-        <v>94.87793067356529</v>
+        <v>94.87791541325443</v>
       </c>
       <c r="G252" t="n">
         <v>6547600</v>
@@ -6245,16 +6245,16 @@
         <v>45657</v>
       </c>
       <c r="C253" t="n">
-        <v>94.89683532714844</v>
+        <v>94.89682769775391</v>
       </c>
       <c r="D253" t="n">
-        <v>94.91575097856332</v>
+        <v>94.91574334764803</v>
       </c>
       <c r="E253" t="n">
-        <v>94.89683532714844</v>
+        <v>94.89682769775391</v>
       </c>
       <c r="F253" t="n">
-        <v>94.90629676133574</v>
+        <v>94.90628913118054</v>
       </c>
       <c r="G253" t="n">
         <v>7371300</v>
@@ -6268,16 +6268,16 @@
         <v>45659</v>
       </c>
       <c r="C254" t="n">
-        <v>94.91574096679688</v>
+        <v>94.91575622558594</v>
       </c>
       <c r="D254" t="n">
-        <v>94.91574096679688</v>
+        <v>94.91575622558594</v>
       </c>
       <c r="E254" t="n">
-        <v>94.90628675056652</v>
+        <v>94.90630200783571</v>
       </c>
       <c r="F254" t="n">
-        <v>94.91574096679688</v>
+        <v>94.91575622558594</v>
       </c>
       <c r="G254" t="n">
         <v>7533100</v>
@@ -6291,16 +6291,16 @@
         <v>45660</v>
       </c>
       <c r="C255" t="n">
-        <v>94.94412994384766</v>
+        <v>94.94413757324219</v>
       </c>
       <c r="D255" t="n">
-        <v>94.95358416054377</v>
+        <v>94.95359179069801</v>
       </c>
       <c r="E255" t="n">
-        <v>94.94412994384766</v>
+        <v>94.94413757324219</v>
       </c>
       <c r="F255" t="n">
-        <v>94.95358416054377</v>
+        <v>94.95359179069801</v>
       </c>
       <c r="G255" t="n">
         <v>6730100</v>
@@ -6314,16 +6314,16 @@
         <v>45663</v>
       </c>
       <c r="C256" t="n">
-        <v>94.94412994384766</v>
+        <v>94.94413757324219</v>
       </c>
       <c r="D256" t="n">
-        <v>94.9630455941992</v>
+        <v>94.96305322511373</v>
       </c>
       <c r="E256" t="n">
-        <v>94.94412994384766</v>
+        <v>94.94413757324219</v>
       </c>
       <c r="F256" t="n">
-        <v>94.95358416054377</v>
+        <v>94.95359179069801</v>
       </c>
       <c r="G256" t="n">
         <v>6938300</v>
@@ -6337,16 +6337,16 @@
         <v>45664</v>
       </c>
       <c r="C257" t="n">
-        <v>94.96305847167969</v>
+        <v>94.96303558349609</v>
       </c>
       <c r="D257" t="n">
-        <v>94.97251990661813</v>
+        <v>94.97249701615412</v>
       </c>
       <c r="E257" t="n">
-        <v>94.96305847167969</v>
+        <v>94.96303558349609</v>
       </c>
       <c r="F257" t="n">
-        <v>94.97251990661813</v>
+        <v>94.97249701615412</v>
       </c>
       <c r="G257" t="n">
         <v>6792100</v>
@@ -6360,16 +6360,16 @@
         <v>45665</v>
       </c>
       <c r="C258" t="n">
-        <v>94.98197174072266</v>
+        <v>94.98196411132812</v>
       </c>
       <c r="D258" t="n">
-        <v>94.98197174072266</v>
+        <v>94.98196411132812</v>
       </c>
       <c r="E258" t="n">
-        <v>94.97251030674057</v>
+        <v>94.97250267810604</v>
       </c>
       <c r="F258" t="n">
-        <v>94.97251030674057</v>
+        <v>94.97250267810604</v>
       </c>
       <c r="G258" t="n">
         <v>6101100</v>
@@ -6383,16 +6383,16 @@
         <v>45667</v>
       </c>
       <c r="C259" t="n">
-        <v>95.01982116699219</v>
+        <v>95.01979827880859</v>
       </c>
       <c r="D259" t="n">
-        <v>95.02928260277895</v>
+        <v>95.0292597123163</v>
       </c>
       <c r="E259" t="n">
-        <v>95.01036694816635</v>
+        <v>95.01034406226007</v>
       </c>
       <c r="F259" t="n">
-        <v>95.01982116699219</v>
+        <v>95.01979827880859</v>
       </c>
       <c r="G259" t="n">
         <v>7644600</v>
@@ -6406,16 +6406,16 @@
         <v>45670</v>
       </c>
       <c r="C260" t="n">
-        <v>95.03873443603516</v>
+        <v>95.03872680664062</v>
       </c>
       <c r="D260" t="n">
-        <v>95.03873443603516</v>
+        <v>95.03872680664062</v>
       </c>
       <c r="E260" t="n">
-        <v>95.02927300120436</v>
+        <v>95.02926537256936</v>
       </c>
       <c r="F260" t="n">
-        <v>95.03400011013966</v>
+        <v>95.03399248112518</v>
       </c>
       <c r="G260" t="n">
         <v>7647300</v>
@@ -6429,16 +6429,16 @@
         <v>45671</v>
       </c>
       <c r="C261" t="n">
-        <v>95.04819488525391</v>
+        <v>95.04820251464844</v>
       </c>
       <c r="D261" t="n">
-        <v>95.04819488525391</v>
+        <v>95.04820251464844</v>
       </c>
       <c r="E261" t="n">
-        <v>95.03873345052121</v>
+        <v>95.03874107915628</v>
       </c>
       <c r="F261" t="n">
-        <v>95.04819488525391</v>
+        <v>95.04820251464844</v>
       </c>
       <c r="G261" t="n">
         <v>7245400</v>
@@ -6452,16 +6452,16 @@
         <v>45672</v>
       </c>
       <c r="C262" t="n">
-        <v>95.05766296386719</v>
+        <v>95.05765533447266</v>
       </c>
       <c r="D262" t="n">
-        <v>95.05766296386719</v>
+        <v>95.05765533447266</v>
       </c>
       <c r="E262" t="n">
-        <v>95.04820874471606</v>
+        <v>95.04820111608032</v>
       </c>
       <c r="F262" t="n">
-        <v>95.05766296386719</v>
+        <v>95.05765533447266</v>
       </c>
       <c r="G262" t="n">
         <v>6878600</v>
@@ -6475,16 +6475,16 @@
         <v>45673</v>
       </c>
       <c r="C263" t="n">
-        <v>95.05766296386719</v>
+        <v>95.05765533447266</v>
       </c>
       <c r="D263" t="n">
-        <v>95.07658583609181</v>
+        <v>95.07657820517852</v>
       </c>
       <c r="E263" t="n">
-        <v>95.05766296386719</v>
+        <v>95.05765533447266</v>
       </c>
       <c r="F263" t="n">
-        <v>95.06712439997951</v>
+        <v>95.06711676982559</v>
       </c>
       <c r="G263" t="n">
         <v>5352500</v>
@@ -6498,16 +6498,16 @@
         <v>45674</v>
       </c>
       <c r="C264" t="n">
-        <v>95.10495758056641</v>
+        <v>95.10494232177734</v>
       </c>
       <c r="D264" t="n">
-        <v>95.11441901614678</v>
+        <v>95.11440375583972</v>
       </c>
       <c r="E264" t="n">
-        <v>95.09549614498603</v>
+        <v>95.09548088771497</v>
       </c>
       <c r="F264" t="n">
-        <v>95.10495758056641</v>
+        <v>95.10494232177734</v>
       </c>
       <c r="G264" t="n">
         <v>6563000</v>
@@ -6521,16 +6521,16 @@
         <v>45678</v>
       </c>
       <c r="C265" t="n">
-        <v>95.11439514160156</v>
+        <v>95.11440277099609</v>
       </c>
       <c r="D265" t="n">
-        <v>95.12384935784807</v>
+        <v>95.12385698800095</v>
       </c>
       <c r="E265" t="n">
-        <v>95.11439514160156</v>
+        <v>95.11440277099609</v>
       </c>
       <c r="F265" t="n">
-        <v>95.11912224972482</v>
+        <v>95.11912987949853</v>
       </c>
       <c r="G265" t="n">
         <v>7952400</v>
@@ -6544,16 +6544,16 @@
         <v>45679</v>
       </c>
       <c r="C266" t="n">
-        <v>95.13333129882812</v>
+        <v>95.13332366943359</v>
       </c>
       <c r="D266" t="n">
-        <v>95.13333129882812</v>
+        <v>95.13332366943359</v>
       </c>
       <c r="E266" t="n">
-        <v>95.12386986358305</v>
+        <v>95.12386223494731</v>
       </c>
       <c r="F266" t="n">
-        <v>95.12386986358305</v>
+        <v>95.12386223494731</v>
       </c>
       <c r="G266" t="n">
         <v>5717600</v>
@@ -6636,16 +6636,16 @@
         <v>45685</v>
       </c>
       <c r="C270" t="n">
-        <v>95.19953155517578</v>
+        <v>95.19952392578125</v>
       </c>
       <c r="D270" t="n">
-        <v>95.19953155517578</v>
+        <v>95.19952392578125</v>
       </c>
       <c r="E270" t="n">
-        <v>95.18061590469742</v>
+        <v>95.1806082768188</v>
       </c>
       <c r="F270" t="n">
-        <v>95.19007012145691</v>
+        <v>95.19006249282063</v>
       </c>
       <c r="G270" t="n">
         <v>5857900</v>
@@ -6659,16 +6659,16 @@
         <v>45686</v>
       </c>
       <c r="C271" t="n">
-        <v>95.19953155517578</v>
+        <v>95.19952392578125</v>
       </c>
       <c r="D271" t="n">
-        <v>95.20899298889465</v>
+        <v>95.20898535874186</v>
       </c>
       <c r="E271" t="n">
-        <v>95.19953155517578</v>
+        <v>95.19952392578125</v>
       </c>
       <c r="F271" t="n">
-        <v>95.19953155517578</v>
+        <v>95.19952392578125</v>
       </c>
       <c r="G271" t="n">
         <v>3978700</v>
@@ -6705,16 +6705,16 @@
         <v>45688</v>
       </c>
       <c r="C273" t="n">
-        <v>95.23737335205078</v>
+        <v>95.23736572265625</v>
       </c>
       <c r="D273" t="n">
-        <v>95.24683478609539</v>
+        <v>95.24682715594292</v>
       </c>
       <c r="E273" t="n">
-        <v>95.23737335205078</v>
+        <v>95.23736572265625</v>
       </c>
       <c r="F273" t="n">
-        <v>95.24683478609539</v>
+        <v>95.24682715594292</v>
       </c>
       <c r="G273" t="n">
         <v>12373000</v>
@@ -6728,16 +6728,16 @@
         <v>45691</v>
       </c>
       <c r="C274" t="n">
-        <v>95.25920867919922</v>
+        <v>95.25919342041016</v>
       </c>
       <c r="D274" t="n">
-        <v>95.25920867919922</v>
+        <v>95.25919342041016</v>
       </c>
       <c r="E274" t="n">
-        <v>95.24972025138301</v>
+        <v>95.24970499411383</v>
       </c>
       <c r="F274" t="n">
-        <v>95.24972025138301</v>
+        <v>95.24970499411383</v>
       </c>
       <c r="G274" t="n">
         <v>16436200</v>
@@ -6751,16 +6751,16 @@
         <v>45692</v>
       </c>
       <c r="C275" t="n">
-        <v>95.2781982421875</v>
+        <v>95.27820587158203</v>
       </c>
       <c r="D275" t="n">
-        <v>95.2781982421875</v>
+        <v>95.27820587158203</v>
       </c>
       <c r="E275" t="n">
-        <v>95.2687025714739</v>
+        <v>95.26871020010807</v>
       </c>
       <c r="F275" t="n">
-        <v>95.2781982421875</v>
+        <v>95.27820587158203</v>
       </c>
       <c r="G275" t="n">
         <v>7866600</v>
@@ -6774,16 +6774,16 @@
         <v>45693</v>
       </c>
       <c r="C276" t="n">
-        <v>95.2781982421875</v>
+        <v>95.27820587158203</v>
       </c>
       <c r="D276" t="n">
-        <v>95.28769391290109</v>
+        <v>95.28770154305599</v>
       </c>
       <c r="E276" t="n">
-        <v>95.2781982421875</v>
+        <v>95.27820587158203</v>
       </c>
       <c r="F276" t="n">
-        <v>95.28769391290109</v>
+        <v>95.28770154305599</v>
       </c>
       <c r="G276" t="n">
         <v>7100900</v>
@@ -6797,16 +6797,16 @@
         <v>45694</v>
       </c>
       <c r="C277" t="n">
-        <v>95.29719543457031</v>
+        <v>95.29718780517578</v>
       </c>
       <c r="D277" t="n">
-        <v>95.29719543457031</v>
+        <v>95.29718780517578</v>
       </c>
       <c r="E277" t="n">
-        <v>95.28770700562752</v>
+        <v>95.28769937699263</v>
       </c>
       <c r="F277" t="n">
-        <v>95.29719543457031</v>
+        <v>95.29718780517578</v>
       </c>
       <c r="G277" t="n">
         <v>5804300</v>
@@ -6820,16 +6820,16 @@
         <v>45695</v>
       </c>
       <c r="C278" t="n">
-        <v>95.32565307617188</v>
+        <v>95.32566833496094</v>
       </c>
       <c r="D278" t="n">
-        <v>95.33514150219082</v>
+        <v>95.3351567624987</v>
       </c>
       <c r="E278" t="n">
-        <v>95.31615740707963</v>
+        <v>95.31617266434873</v>
       </c>
       <c r="F278" t="n">
-        <v>95.33514150219082</v>
+        <v>95.3351567624987</v>
       </c>
       <c r="G278" t="n">
         <v>6758700</v>
@@ -6889,16 +6889,16 @@
         <v>45700</v>
       </c>
       <c r="C281" t="n">
-        <v>95.35414123535156</v>
+        <v>95.35416412353516</v>
       </c>
       <c r="D281" t="n">
-        <v>95.36362966220587</v>
+        <v>95.36365255266701</v>
       </c>
       <c r="E281" t="n">
-        <v>95.35414123535156</v>
+        <v>95.35416412353516</v>
       </c>
       <c r="F281" t="n">
-        <v>95.35414123535156</v>
+        <v>95.35416412353516</v>
       </c>
       <c r="G281" t="n">
         <v>6618800</v>
@@ -6912,16 +6912,16 @@
         <v>45701</v>
       </c>
       <c r="C282" t="n">
-        <v>95.37312316894531</v>
+        <v>95.37313842773438</v>
       </c>
       <c r="D282" t="n">
-        <v>95.37312316894531</v>
+        <v>95.37313842773438</v>
       </c>
       <c r="E282" t="n">
-        <v>95.36362749923244</v>
+        <v>95.3636427565023</v>
       </c>
       <c r="F282" t="n">
-        <v>95.37312316894531</v>
+        <v>95.37313842773438</v>
       </c>
       <c r="G282" t="n">
         <v>5690100</v>
@@ -6935,16 +6935,16 @@
         <v>45702</v>
       </c>
       <c r="C283" t="n">
-        <v>95.41110992431641</v>
+        <v>95.4111328125</v>
       </c>
       <c r="D283" t="n">
-        <v>95.42060559515583</v>
+        <v>95.42062848561736</v>
       </c>
       <c r="E283" t="n">
-        <v>95.41110992431641</v>
+        <v>95.4111328125</v>
       </c>
       <c r="F283" t="n">
-        <v>95.41585413819881</v>
+        <v>95.41587702752049</v>
       </c>
       <c r="G283" t="n">
         <v>7648100</v>
@@ -7004,16 +7004,16 @@
         <v>45708</v>
       </c>
       <c r="C286" t="n">
-        <v>95.44908142089844</v>
+        <v>95.44906616210938</v>
       </c>
       <c r="D286" t="n">
-        <v>95.44908142089844</v>
+        <v>95.44906616210938</v>
       </c>
       <c r="E286" t="n">
-        <v>95.43958575045134</v>
+        <v>95.43957049318028</v>
       </c>
       <c r="F286" t="n">
-        <v>95.44908142089844</v>
+        <v>95.44906616210938</v>
       </c>
       <c r="G286" t="n">
         <v>7608000</v>
@@ -7027,16 +7027,16 @@
         <v>45709</v>
       </c>
       <c r="C287" t="n">
-        <v>95.487060546875</v>
+        <v>95.48704528808594</v>
       </c>
       <c r="D287" t="n">
-        <v>95.487060546875</v>
+        <v>95.48704528808594</v>
       </c>
       <c r="E287" t="n">
-        <v>95.47756487606122</v>
+        <v>95.47754961878957</v>
       </c>
       <c r="F287" t="n">
-        <v>95.47756487606122</v>
+        <v>95.47754961878957</v>
       </c>
       <c r="G287" t="n">
         <v>9111000</v>
@@ -7050,16 +7050,16 @@
         <v>45712</v>
       </c>
       <c r="C288" t="n">
-        <v>95.49657440185547</v>
+        <v>95.49654388427734</v>
       </c>
       <c r="D288" t="n">
-        <v>95.49657440185547</v>
+        <v>95.49654388427734</v>
       </c>
       <c r="E288" t="n">
-        <v>95.48708597158989</v>
+        <v>95.48705545704394</v>
       </c>
       <c r="F288" t="n">
-        <v>95.49657440185547</v>
+        <v>95.49654388427734</v>
       </c>
       <c r="G288" t="n">
         <v>9734600</v>
@@ -7073,16 +7073,16 @@
         <v>45713</v>
       </c>
       <c r="C289" t="n">
-        <v>95.50604248046875</v>
+        <v>95.50602722167969</v>
       </c>
       <c r="D289" t="n">
-        <v>95.50604248046875</v>
+        <v>95.50602722167969</v>
       </c>
       <c r="E289" t="n">
-        <v>95.49654680987022</v>
+        <v>95.49653155259826</v>
       </c>
       <c r="F289" t="n">
-        <v>95.49654680987022</v>
+        <v>95.49653155259826</v>
       </c>
       <c r="G289" t="n">
         <v>10827700</v>
@@ -7096,16 +7096,16 @@
         <v>45714</v>
       </c>
       <c r="C290" t="n">
-        <v>95.50604248046875</v>
+        <v>95.50602722167969</v>
       </c>
       <c r="D290" t="n">
-        <v>95.51553815106729</v>
+        <v>95.5155228907611</v>
       </c>
       <c r="E290" t="n">
-        <v>95.50604248046875</v>
+        <v>95.50602722167969</v>
       </c>
       <c r="F290" t="n">
-        <v>95.50604248046875</v>
+        <v>95.50602722167969</v>
       </c>
       <c r="G290" t="n">
         <v>9536300</v>
@@ -7119,16 +7119,16 @@
         <v>45715</v>
       </c>
       <c r="C291" t="n">
-        <v>95.53453826904297</v>
+        <v>95.53453063964844</v>
       </c>
       <c r="D291" t="n">
-        <v>95.53453826904297</v>
+        <v>95.53453063964844</v>
       </c>
       <c r="E291" t="n">
-        <v>95.5250498399278</v>
+        <v>95.52504221129102</v>
       </c>
       <c r="F291" t="n">
-        <v>95.53453826904297</v>
+        <v>95.53453063964844</v>
       </c>
       <c r="G291" t="n">
         <v>10807800</v>
@@ -7234,16 +7234,16 @@
         <v>45722</v>
       </c>
       <c r="C296" t="n">
-        <v>95.61351013183594</v>
+        <v>95.61351776123047</v>
       </c>
       <c r="D296" t="n">
-        <v>95.61351013183594</v>
+        <v>95.61351776123047</v>
       </c>
       <c r="E296" t="n">
-        <v>95.59445954738818</v>
+        <v>95.59446717526258</v>
       </c>
       <c r="F296" t="n">
-        <v>95.60398483961205</v>
+        <v>95.60399246824653</v>
       </c>
       <c r="G296" t="n">
         <v>9925500</v>
@@ -7257,16 +7257,16 @@
         <v>45723</v>
       </c>
       <c r="C297" t="n">
-        <v>95.64208984375</v>
+        <v>95.64208221435547</v>
       </c>
       <c r="D297" t="n">
-        <v>95.64208984375</v>
+        <v>95.64208221435547</v>
       </c>
       <c r="E297" t="n">
-        <v>95.63256455042055</v>
+        <v>95.63255692178585</v>
       </c>
       <c r="F297" t="n">
-        <v>95.64208984375</v>
+        <v>95.64208221435547</v>
       </c>
       <c r="G297" t="n">
         <v>8962400</v>
@@ -7280,16 +7280,16 @@
         <v>45726</v>
       </c>
       <c r="C298" t="n">
-        <v>95.64208984375</v>
+        <v>95.64208221435547</v>
       </c>
       <c r="D298" t="n">
-        <v>95.65161513707946</v>
+        <v>95.65160750692509</v>
       </c>
       <c r="E298" t="n">
-        <v>95.64208984375</v>
+        <v>95.64208221435547</v>
       </c>
       <c r="F298" t="n">
-        <v>95.65161513707946</v>
+        <v>95.65160750692509</v>
       </c>
       <c r="G298" t="n">
         <v>14768100</v>
@@ -7303,16 +7303,16 @@
         <v>45727</v>
       </c>
       <c r="C299" t="n">
-        <v>95.6611328125</v>
+        <v>95.66112518310547</v>
       </c>
       <c r="D299" t="n">
-        <v>95.6611328125</v>
+        <v>95.66112518310547</v>
       </c>
       <c r="E299" t="n">
-        <v>95.65161478487556</v>
+        <v>95.65160715624013</v>
       </c>
       <c r="F299" t="n">
-        <v>95.65161478487556</v>
+        <v>95.65160715624013</v>
       </c>
       <c r="G299" t="n">
         <v>11456900</v>
@@ -7326,16 +7326,16 @@
         <v>45728</v>
       </c>
       <c r="C300" t="n">
-        <v>95.6611328125</v>
+        <v>95.66112518310547</v>
       </c>
       <c r="D300" t="n">
-        <v>95.67065810579437</v>
+        <v>95.67065047564017</v>
       </c>
       <c r="E300" t="n">
-        <v>95.6611328125</v>
+        <v>95.66112518310547</v>
       </c>
       <c r="F300" t="n">
-        <v>95.67065810579437</v>
+        <v>95.67065047564017</v>
       </c>
       <c r="G300" t="n">
         <v>11307300</v>
@@ -7372,16 +7372,16 @@
         <v>45730</v>
       </c>
       <c r="C302" t="n">
-        <v>95.71829223632812</v>
+        <v>95.71826934814453</v>
       </c>
       <c r="D302" t="n">
-        <v>95.71829223632812</v>
+        <v>95.71826934814453</v>
       </c>
       <c r="E302" t="n">
-        <v>95.70876694154803</v>
+        <v>95.70874405564213</v>
       </c>
       <c r="F302" t="n">
-        <v>95.71829223632812</v>
+        <v>95.71826934814453</v>
       </c>
       <c r="G302" t="n">
         <v>11421900</v>
@@ -7418,16 +7418,16 @@
         <v>45734</v>
       </c>
       <c r="C304" t="n">
-        <v>95.73731231689453</v>
+        <v>95.73731994628906</v>
       </c>
       <c r="D304" t="n">
-        <v>95.73731231689453</v>
+        <v>95.73731994628906</v>
       </c>
       <c r="E304" t="n">
-        <v>95.727787024427</v>
+        <v>95.72779465306246</v>
       </c>
       <c r="F304" t="n">
-        <v>95.73731231689453</v>
+        <v>95.73731994628906</v>
       </c>
       <c r="G304" t="n">
         <v>9213100</v>
@@ -7441,16 +7441,16 @@
         <v>45735</v>
       </c>
       <c r="C305" t="n">
-        <v>95.75638580322266</v>
+        <v>95.75636291503906</v>
       </c>
       <c r="D305" t="n">
-        <v>95.75638580322266</v>
+        <v>95.75636291503906</v>
       </c>
       <c r="E305" t="n">
-        <v>95.74686050847703</v>
+        <v>95.74683762257023</v>
       </c>
       <c r="F305" t="n">
-        <v>95.74686050847703</v>
+        <v>95.74683762257023</v>
       </c>
       <c r="G305" t="n">
         <v>13584800</v>
@@ -7464,16 +7464,16 @@
         <v>45736</v>
       </c>
       <c r="C306" t="n">
-        <v>95.75638580322266</v>
+        <v>95.75636291503906</v>
       </c>
       <c r="D306" t="n">
-        <v>95.76590383229723</v>
+        <v>95.76588094183857</v>
       </c>
       <c r="E306" t="n">
-        <v>95.75638580322266</v>
+        <v>95.75636291503906</v>
       </c>
       <c r="F306" t="n">
-        <v>95.76590383229723</v>
+        <v>95.76588094183857</v>
       </c>
       <c r="G306" t="n">
         <v>12648500</v>
@@ -7487,16 +7487,16 @@
         <v>45737</v>
       </c>
       <c r="C307" t="n">
-        <v>95.78493499755859</v>
+        <v>95.78491973876953</v>
       </c>
       <c r="D307" t="n">
-        <v>95.794453024703</v>
+        <v>95.7944377643977</v>
       </c>
       <c r="E307" t="n">
-        <v>95.78493499755859</v>
+        <v>95.78491973876953</v>
       </c>
       <c r="F307" t="n">
-        <v>95.794453024703</v>
+        <v>95.7944377643977</v>
       </c>
       <c r="G307" t="n">
         <v>13101800</v>
@@ -7510,16 +7510,16 @@
         <v>45740</v>
       </c>
       <c r="C308" t="n">
-        <v>95.80397796630859</v>
+        <v>95.80396270751953</v>
       </c>
       <c r="D308" t="n">
-        <v>95.81350325908767</v>
+        <v>95.8134879987815</v>
       </c>
       <c r="E308" t="n">
-        <v>95.80397796630859</v>
+        <v>95.80396270751953</v>
       </c>
       <c r="F308" t="n">
-        <v>95.80874424553291</v>
+        <v>95.80872898598471</v>
       </c>
       <c r="G308" t="n">
         <v>13854600</v>
@@ -7533,16 +7533,16 @@
         <v>45741</v>
       </c>
       <c r="C309" t="n">
-        <v>95.81351470947266</v>
+        <v>95.81349182128906</v>
       </c>
       <c r="D309" t="n">
-        <v>95.81351470947266</v>
+        <v>95.81349182128906</v>
       </c>
       <c r="E309" t="n">
-        <v>95.80398941555525</v>
+        <v>95.80396652964708</v>
       </c>
       <c r="F309" t="n">
-        <v>95.81351470947266</v>
+        <v>95.81349182128906</v>
       </c>
       <c r="G309" t="n">
         <v>13844800</v>
@@ -7556,16 +7556,16 @@
         <v>45742</v>
       </c>
       <c r="C310" t="n">
-        <v>95.83254241943359</v>
+        <v>95.83255004882812</v>
       </c>
       <c r="D310" t="n">
-        <v>95.83254241943359</v>
+        <v>95.83255004882812</v>
       </c>
       <c r="E310" t="n">
-        <v>95.8230243927372</v>
+        <v>95.82303202137399</v>
       </c>
       <c r="F310" t="n">
-        <v>95.83254241943359</v>
+        <v>95.83255004882812</v>
       </c>
       <c r="G310" t="n">
         <v>12262200</v>
@@ -7602,16 +7602,16 @@
         <v>45744</v>
       </c>
       <c r="C312" t="n">
-        <v>95.87064361572266</v>
+        <v>95.87065124511719</v>
       </c>
       <c r="D312" t="n">
-        <v>95.87064361572266</v>
+        <v>95.87065124511719</v>
       </c>
       <c r="E312" t="n">
-        <v>95.86112558830226</v>
+        <v>95.86113321693935</v>
       </c>
       <c r="F312" t="n">
-        <v>95.86112558830226</v>
+        <v>95.86113321693935</v>
       </c>
       <c r="G312" t="n">
         <v>11747100</v>
@@ -7625,16 +7625,16 @@
         <v>45747</v>
       </c>
       <c r="C313" t="n">
-        <v>95.87064361572266</v>
+        <v>95.87065124511719</v>
       </c>
       <c r="D313" t="n">
-        <v>95.88016890881283</v>
+        <v>95.88017653896539</v>
       </c>
       <c r="E313" t="n">
-        <v>95.87064361572266</v>
+        <v>95.87065124511719</v>
       </c>
       <c r="F313" t="n">
-        <v>95.87064361572266</v>
+        <v>95.87065124511719</v>
       </c>
       <c r="G313" t="n">
         <v>18210800</v>
@@ -7648,16 +7648,16 @@
         <v>45748</v>
       </c>
       <c r="C314" t="n">
-        <v>95.89547729492188</v>
+        <v>95.89548492431641</v>
       </c>
       <c r="D314" t="n">
-        <v>95.89547729492188</v>
+        <v>95.89548492431641</v>
       </c>
       <c r="E314" t="n">
-        <v>95.88591915199837</v>
+        <v>95.88592678063245</v>
       </c>
       <c r="F314" t="n">
-        <v>95.89547729492188</v>
+        <v>95.89548492431641</v>
       </c>
       <c r="G314" t="n">
         <v>21033200</v>
@@ -7671,16 +7671,16 @@
         <v>45749</v>
       </c>
       <c r="C315" t="n">
-        <v>95.90505218505859</v>
+        <v>95.90504455566406</v>
       </c>
       <c r="D315" t="n">
-        <v>95.90505218505859</v>
+        <v>95.90504455566406</v>
       </c>
       <c r="E315" t="n">
-        <v>95.89549404046602</v>
+        <v>95.89548641183185</v>
       </c>
       <c r="F315" t="n">
-        <v>95.90505218505859</v>
+        <v>95.90504455566406</v>
       </c>
       <c r="G315" t="n">
         <v>10658900</v>
@@ -7717,16 +7717,16 @@
         <v>45751</v>
       </c>
       <c r="C317" t="n">
-        <v>95.95281982421875</v>
+        <v>95.95282745361328</v>
       </c>
       <c r="D317" t="n">
-        <v>95.95281982421875</v>
+        <v>95.95282745361328</v>
       </c>
       <c r="E317" t="n">
-        <v>95.94326168119937</v>
+        <v>95.94326930983391</v>
       </c>
       <c r="F317" t="n">
-        <v>95.94326168119937</v>
+        <v>95.94326930983391</v>
       </c>
       <c r="G317" t="n">
         <v>22826300</v>
@@ -7740,16 +7740,16 @@
         <v>45754</v>
       </c>
       <c r="C318" t="n">
-        <v>95.96238708496094</v>
+        <v>95.96237182617188</v>
       </c>
       <c r="D318" t="n">
-        <v>95.96238708496094</v>
+        <v>95.96237182617188</v>
       </c>
       <c r="E318" t="n">
-        <v>95.95283623103541</v>
+        <v>95.95282097376501</v>
       </c>
       <c r="F318" t="n">
-        <v>95.95283623103541</v>
+        <v>95.95282097376501</v>
       </c>
       <c r="G318" t="n">
         <v>22564000</v>
@@ -7763,16 +7763,16 @@
         <v>45755</v>
       </c>
       <c r="C319" t="n">
-        <v>95.96238708496094</v>
+        <v>95.96237182617188</v>
       </c>
       <c r="D319" t="n">
-        <v>95.97194522961465</v>
+        <v>95.97192996930578</v>
       </c>
       <c r="E319" t="n">
-        <v>95.95283623103541</v>
+        <v>95.95282097376501</v>
       </c>
       <c r="F319" t="n">
-        <v>95.95761165799817</v>
+        <v>95.95759639996845</v>
       </c>
       <c r="G319" t="n">
         <v>17116100</v>
@@ -7786,16 +7786,16 @@
         <v>45756</v>
       </c>
       <c r="C320" t="n">
-        <v>95.98149108886719</v>
+        <v>95.98149871826172</v>
       </c>
       <c r="D320" t="n">
-        <v>95.98149108886719</v>
+        <v>95.98149871826172</v>
       </c>
       <c r="E320" t="n">
-        <v>95.97193294543689</v>
+        <v>95.97194057407167</v>
       </c>
       <c r="F320" t="n">
-        <v>95.97193294543689</v>
+        <v>95.97194057407167</v>
       </c>
       <c r="G320" t="n">
         <v>21838800</v>
@@ -7809,16 +7809,16 @@
         <v>45757</v>
       </c>
       <c r="C321" t="n">
-        <v>95.98149108886719</v>
+        <v>95.98149871826172</v>
       </c>
       <c r="D321" t="n">
-        <v>95.99104194157023</v>
+        <v>95.99104957172395</v>
       </c>
       <c r="E321" t="n">
-        <v>95.98149108886719</v>
+        <v>95.98149871826172</v>
       </c>
       <c r="F321" t="n">
-        <v>95.98149108886719</v>
+        <v>95.98149871826172</v>
       </c>
       <c r="G321" t="n">
         <v>16851500</v>
@@ -7832,16 +7832,16 @@
         <v>45758</v>
       </c>
       <c r="C322" t="n">
-        <v>96.02925872802734</v>
+        <v>96.02927398681641</v>
       </c>
       <c r="D322" t="n">
-        <v>96.02925872802734</v>
+        <v>96.02927398681641</v>
       </c>
       <c r="E322" t="n">
-        <v>96.01970787616935</v>
+        <v>96.01972313344081</v>
       </c>
       <c r="F322" t="n">
-        <v>96.02448330209835</v>
+        <v>96.02449856012861</v>
       </c>
       <c r="G322" t="n">
         <v>12916600</v>
@@ -7855,16 +7855,16 @@
         <v>45761</v>
       </c>
       <c r="C323" t="n">
-        <v>96.03884124755859</v>
+        <v>96.03884887695312</v>
       </c>
       <c r="D323" t="n">
-        <v>96.03884124755859</v>
+        <v>96.03884887695312</v>
       </c>
       <c r="E323" t="n">
-        <v>96.02928310254791</v>
+        <v>96.02929073118312</v>
       </c>
       <c r="F323" t="n">
-        <v>96.02928310254791</v>
+        <v>96.02929073118312</v>
       </c>
       <c r="G323" t="n">
         <v>13772300</v>
@@ -7878,16 +7878,16 @@
         <v>45762</v>
       </c>
       <c r="C324" t="n">
-        <v>96.04837799072266</v>
+        <v>96.04838562011719</v>
       </c>
       <c r="D324" t="n">
-        <v>96.04837799072266</v>
+        <v>96.04838562011719</v>
       </c>
       <c r="E324" t="n">
-        <v>96.03881984784175</v>
+        <v>96.03882747647705</v>
       </c>
       <c r="F324" t="n">
-        <v>96.04837799072266</v>
+        <v>96.04838562011719</v>
       </c>
       <c r="G324" t="n">
         <v>10043700</v>
@@ -7924,16 +7924,16 @@
         <v>45764</v>
       </c>
       <c r="C326" t="n">
-        <v>96.10572052001953</v>
+        <v>96.105712890625</v>
       </c>
       <c r="D326" t="n">
-        <v>96.11527866372128</v>
+        <v>96.11527103356798</v>
       </c>
       <c r="E326" t="n">
-        <v>96.10572052001953</v>
+        <v>96.105712890625</v>
       </c>
       <c r="F326" t="n">
-        <v>96.11049594650667</v>
+        <v>96.11048831673305</v>
       </c>
       <c r="G326" t="n">
         <v>8652700</v>
@@ -7947,16 +7947,16 @@
         <v>45768</v>
       </c>
       <c r="C327" t="n">
-        <v>96.10572052001953</v>
+        <v>96.105712890625</v>
       </c>
       <c r="D327" t="n">
-        <v>96.11527866372128</v>
+        <v>96.11527103356798</v>
       </c>
       <c r="E327" t="n">
-        <v>96.10572052001953</v>
+        <v>96.105712890625</v>
       </c>
       <c r="F327" t="n">
-        <v>96.11527866372128</v>
+        <v>96.11527103356798</v>
       </c>
       <c r="G327" t="n">
         <v>10756100</v>
@@ -7970,16 +7970,16 @@
         <v>45769</v>
       </c>
       <c r="C328" t="n">
-        <v>96.11528015136719</v>
+        <v>96.11526489257812</v>
       </c>
       <c r="D328" t="n">
-        <v>96.12483100448931</v>
+        <v>96.12481574418399</v>
       </c>
       <c r="E328" t="n">
-        <v>96.11528015136719</v>
+        <v>96.11526489257812</v>
       </c>
       <c r="F328" t="n">
-        <v>96.12483100448931</v>
+        <v>96.12481574418399</v>
       </c>
       <c r="G328" t="n">
         <v>11603400</v>
@@ -7993,16 +7993,16 @@
         <v>45770</v>
       </c>
       <c r="C329" t="n">
-        <v>96.14394378662109</v>
+        <v>96.14393615722656</v>
       </c>
       <c r="D329" t="n">
-        <v>96.14394378662109</v>
+        <v>96.14393615722656</v>
       </c>
       <c r="E329" t="n">
-        <v>96.12482749961872</v>
+        <v>96.12481987174114</v>
       </c>
       <c r="F329" t="n">
-        <v>96.13438564311991</v>
+        <v>96.13437801448384</v>
       </c>
       <c r="G329" t="n">
         <v>19135100</v>
@@ -8016,16 +8016,16 @@
         <v>45771</v>
       </c>
       <c r="C330" t="n">
-        <v>96.14394378662109</v>
+        <v>96.14393615722656</v>
       </c>
       <c r="D330" t="n">
-        <v>96.15350193012229</v>
+        <v>96.15349429996927</v>
       </c>
       <c r="E330" t="n">
-        <v>96.14394378662109</v>
+        <v>96.14393615722656</v>
       </c>
       <c r="F330" t="n">
-        <v>96.15350193012229</v>
+        <v>96.15349429996927</v>
       </c>
       <c r="G330" t="n">
         <v>12068700</v>
@@ -8039,16 +8039,16 @@
         <v>45772</v>
       </c>
       <c r="C331" t="n">
-        <v>96.18216705322266</v>
+        <v>96.18217468261719</v>
       </c>
       <c r="D331" t="n">
-        <v>96.18216705322266</v>
+        <v>96.18217468261719</v>
       </c>
       <c r="E331" t="n">
-        <v>96.17260890992188</v>
+        <v>96.17261653855823</v>
       </c>
       <c r="F331" t="n">
-        <v>96.18216705322266</v>
+        <v>96.18217468261719</v>
       </c>
       <c r="G331" t="n">
         <v>8822700</v>
@@ -8062,16 +8062,16 @@
         <v>45775</v>
       </c>
       <c r="C332" t="n">
-        <v>96.18216705322266</v>
+        <v>96.18217468261719</v>
       </c>
       <c r="D332" t="n">
-        <v>96.19172519652344</v>
+        <v>96.19173282667613</v>
       </c>
       <c r="E332" t="n">
-        <v>96.18216705322266</v>
+        <v>96.18217468261719</v>
       </c>
       <c r="F332" t="n">
-        <v>96.18216705322266</v>
+        <v>96.18217468261719</v>
       </c>
       <c r="G332" t="n">
         <v>9127900</v>
@@ -8085,16 +8085,16 @@
         <v>45776</v>
       </c>
       <c r="C333" t="n">
-        <v>96.19172668457031</v>
+        <v>96.19173431396484</v>
       </c>
       <c r="D333" t="n">
-        <v>96.20127753729169</v>
+        <v>96.20128516744374</v>
       </c>
       <c r="E333" t="n">
-        <v>96.19172668457031</v>
+        <v>96.19173431396484</v>
       </c>
       <c r="F333" t="n">
-        <v>96.19172668457031</v>
+        <v>96.19173431396484</v>
       </c>
       <c r="G333" t="n">
         <v>8555000</v>
@@ -8108,16 +8108,16 @@
         <v>45777</v>
       </c>
       <c r="C334" t="n">
-        <v>96.22039031982422</v>
+        <v>96.22039794921875</v>
       </c>
       <c r="D334" t="n">
-        <v>96.22039031982422</v>
+        <v>96.22039794921875</v>
       </c>
       <c r="E334" t="n">
-        <v>96.20127403362315</v>
+        <v>96.20128166150194</v>
       </c>
       <c r="F334" t="n">
-        <v>96.20127403362315</v>
+        <v>96.20128166150194</v>
       </c>
       <c r="G334" t="n">
         <v>16040200</v>
@@ -8131,16 +8131,16 @@
         <v>45778</v>
       </c>
       <c r="C335" t="n">
-        <v>96.23477935791016</v>
+        <v>96.23477172851562</v>
       </c>
       <c r="D335" t="n">
-        <v>96.23477935791016</v>
+        <v>96.23477172851562</v>
       </c>
       <c r="E335" t="n">
-        <v>96.22518930762713</v>
+        <v>96.22518167899288</v>
       </c>
       <c r="F335" t="n">
-        <v>96.23477935791016</v>
+        <v>96.23477172851562</v>
       </c>
       <c r="G335" t="n">
         <v>21288700</v>
@@ -8154,16 +8154,16 @@
         <v>45779</v>
       </c>
       <c r="C336" t="n">
-        <v>96.2635498046875</v>
+        <v>96.26354217529297</v>
       </c>
       <c r="D336" t="n">
-        <v>96.2635498046875</v>
+        <v>96.26354217529297</v>
       </c>
       <c r="E336" t="n">
-        <v>96.25395975364626</v>
+        <v>96.25395212501178</v>
       </c>
       <c r="F336" t="n">
-        <v>96.25395975364626</v>
+        <v>96.25395212501178</v>
       </c>
       <c r="G336" t="n">
         <v>13930900</v>
@@ -8177,16 +8177,16 @@
         <v>45782</v>
       </c>
       <c r="C337" t="n">
-        <v>96.27312469482422</v>
+        <v>96.27313995361328</v>
       </c>
       <c r="D337" t="n">
-        <v>96.27312469482422</v>
+        <v>96.27313995361328</v>
       </c>
       <c r="E337" t="n">
-        <v>96.26353464529318</v>
+        <v>96.26354990256227</v>
       </c>
       <c r="F337" t="n">
-        <v>96.27312469482422</v>
+        <v>96.27313995361328</v>
       </c>
       <c r="G337" t="n">
         <v>13223700</v>
@@ -8200,16 +8200,16 @@
         <v>45783</v>
       </c>
       <c r="C338" t="n">
-        <v>96.27312469482422</v>
+        <v>96.27313995361328</v>
       </c>
       <c r="D338" t="n">
-        <v>96.28270742929077</v>
+        <v>96.28272268959864</v>
       </c>
       <c r="E338" t="n">
-        <v>96.27312469482422</v>
+        <v>96.27313995361328</v>
       </c>
       <c r="F338" t="n">
-        <v>96.28270742929077</v>
+        <v>96.28272268959864</v>
       </c>
       <c r="G338" t="n">
         <v>8986000</v>
@@ -8223,16 +8223,16 @@
         <v>45784</v>
       </c>
       <c r="C339" t="n">
-        <v>96.28273773193359</v>
+        <v>96.28271484375</v>
       </c>
       <c r="D339" t="n">
-        <v>96.29232778448286</v>
+        <v>96.29230489401954</v>
       </c>
       <c r="E339" t="n">
-        <v>96.28273773193359</v>
+        <v>96.28271484375</v>
       </c>
       <c r="F339" t="n">
-        <v>96.29232778448286</v>
+        <v>96.29230489401954</v>
       </c>
       <c r="G339" t="n">
         <v>8509300</v>
@@ -8246,16 +8246,16 @@
         <v>45785</v>
       </c>
       <c r="C340" t="n">
-        <v>96.31147766113281</v>
+        <v>96.31148529052734</v>
       </c>
       <c r="D340" t="n">
-        <v>96.31147766113281</v>
+        <v>96.31148529052734</v>
       </c>
       <c r="E340" t="n">
-        <v>96.29230487566245</v>
+        <v>96.29231250353818</v>
       </c>
       <c r="F340" t="n">
-        <v>96.30189492593016</v>
+        <v>96.30190255456557</v>
       </c>
       <c r="G340" t="n">
         <v>11931100</v>
@@ -8269,16 +8269,16 @@
         <v>45786</v>
       </c>
       <c r="C341" t="n">
-        <v>96.34026336669922</v>
+        <v>96.34025573730469</v>
       </c>
       <c r="D341" t="n">
-        <v>96.34026336669922</v>
+        <v>96.34025573730469</v>
       </c>
       <c r="E341" t="n">
-        <v>96.33067331488314</v>
+        <v>96.33066568624807</v>
       </c>
       <c r="F341" t="n">
-        <v>96.33067331488314</v>
+        <v>96.33066568624807</v>
       </c>
       <c r="G341" t="n">
         <v>11793700</v>
@@ -8292,16 +8292,16 @@
         <v>45789</v>
       </c>
       <c r="C342" t="n">
-        <v>96.34026336669922</v>
+        <v>96.34025573730469</v>
       </c>
       <c r="D342" t="n">
-        <v>96.34984610344908</v>
+        <v>96.34983847329568</v>
       </c>
       <c r="E342" t="n">
-        <v>96.34026336669922</v>
+        <v>96.34025573730469</v>
       </c>
       <c r="F342" t="n">
-        <v>96.34026336669922</v>
+        <v>96.34025573730469</v>
       </c>
       <c r="G342" t="n">
         <v>16808300</v>
@@ -8315,16 +8315,16 @@
         <v>45790</v>
       </c>
       <c r="C343" t="n">
-        <v>96.35941314697266</v>
+        <v>96.35944366455078</v>
       </c>
       <c r="D343" t="n">
-        <v>96.35941314697266</v>
+        <v>96.35944366455078</v>
       </c>
       <c r="E343" t="n">
-        <v>96.34982309744645</v>
+        <v>96.34985361198736</v>
       </c>
       <c r="F343" t="n">
-        <v>96.34982309744645</v>
+        <v>96.34985361198736</v>
       </c>
       <c r="G343" t="n">
         <v>18174400</v>
@@ -8407,16 +8407,16 @@
         <v>45796</v>
       </c>
       <c r="C347" t="n">
-        <v>96.41693878173828</v>
+        <v>96.41694641113281</v>
       </c>
       <c r="D347" t="n">
-        <v>96.42652883126128</v>
+        <v>96.42653646141467</v>
       </c>
       <c r="E347" t="n">
-        <v>96.41693878173828</v>
+        <v>96.41694641113281</v>
       </c>
       <c r="F347" t="n">
-        <v>96.42652883126128</v>
+        <v>96.42653646141467</v>
       </c>
       <c r="G347" t="n">
         <v>15759100</v>
@@ -8430,16 +8430,16 @@
         <v>45797</v>
       </c>
       <c r="C348" t="n">
-        <v>96.43613433837891</v>
+        <v>96.43612670898438</v>
       </c>
       <c r="D348" t="n">
-        <v>96.43613433837891</v>
+        <v>96.43612670898438</v>
       </c>
       <c r="E348" t="n">
-        <v>96.42654428731873</v>
+        <v>96.42653665868291</v>
       </c>
       <c r="F348" t="n">
-        <v>96.43613433837891</v>
+        <v>96.43612670898438</v>
       </c>
       <c r="G348" t="n">
         <v>9249100</v>
@@ -8453,16 +8453,16 @@
         <v>45798</v>
       </c>
       <c r="C349" t="n">
-        <v>96.44571685791016</v>
+        <v>96.44570159912109</v>
       </c>
       <c r="D349" t="n">
-        <v>96.44571685791016</v>
+        <v>96.44570159912109</v>
       </c>
       <c r="E349" t="n">
-        <v>96.43613412193713</v>
+        <v>96.43611886466417</v>
       </c>
       <c r="F349" t="n">
-        <v>96.44571685791016</v>
+        <v>96.44570159912109</v>
       </c>
       <c r="G349" t="n">
         <v>11325900</v>
@@ -8476,16 +8476,16 @@
         <v>45799</v>
       </c>
       <c r="C350" t="n">
-        <v>96.46488189697266</v>
+        <v>96.46488952636719</v>
       </c>
       <c r="D350" t="n">
-        <v>96.46488189697266</v>
+        <v>96.46488952636719</v>
       </c>
       <c r="E350" t="n">
-        <v>96.4552918474315</v>
+        <v>96.45529947606755</v>
       </c>
       <c r="F350" t="n">
-        <v>96.4552918474315</v>
+        <v>96.45529947606755</v>
       </c>
       <c r="G350" t="n">
         <v>8901700</v>
@@ -8499,16 +8499,16 @@
         <v>45800</v>
       </c>
       <c r="C351" t="n">
-        <v>96.49365234375</v>
+        <v>96.49363708496094</v>
       </c>
       <c r="D351" t="n">
-        <v>96.5032423940478</v>
+        <v>96.50322713374224</v>
       </c>
       <c r="E351" t="n">
-        <v>96.49365234375</v>
+        <v>96.49363708496094</v>
       </c>
       <c r="F351" t="n">
-        <v>96.5032423940478</v>
+        <v>96.50322713374224</v>
       </c>
       <c r="G351" t="n">
         <v>9119400</v>
@@ -8522,16 +8522,16 @@
         <v>45804</v>
       </c>
       <c r="C352" t="n">
-        <v>96.50322723388672</v>
+        <v>96.50325012207031</v>
       </c>
       <c r="D352" t="n">
-        <v>96.51281728267797</v>
+        <v>96.5128401731361</v>
       </c>
       <c r="E352" t="n">
-        <v>96.50322723388672</v>
+        <v>96.50325012207031</v>
       </c>
       <c r="F352" t="n">
-        <v>96.51281728267797</v>
+        <v>96.5128401731361</v>
       </c>
       <c r="G352" t="n">
         <v>10526600</v>
@@ -8545,16 +8545,16 @@
         <v>45805</v>
       </c>
       <c r="C353" t="n">
-        <v>96.53200531005859</v>
+        <v>96.53199768066406</v>
       </c>
       <c r="D353" t="n">
-        <v>96.53200531005859</v>
+        <v>96.53199768066406</v>
       </c>
       <c r="E353" t="n">
-        <v>96.52241525975282</v>
+        <v>96.52240763111624</v>
       </c>
       <c r="F353" t="n">
-        <v>96.52721394243824</v>
+        <v>96.5272063134224</v>
       </c>
       <c r="G353" t="n">
         <v>8415200</v>
@@ -8568,16 +8568,16 @@
         <v>45806</v>
       </c>
       <c r="C354" t="n">
-        <v>96.53200531005859</v>
+        <v>96.53199768066406</v>
       </c>
       <c r="D354" t="n">
-        <v>96.54159536036435</v>
+        <v>96.54158773021189</v>
       </c>
       <c r="E354" t="n">
-        <v>96.52241525975282</v>
+        <v>96.52240763111624</v>
       </c>
       <c r="F354" t="n">
-        <v>96.53200531005859</v>
+        <v>96.53199768066406</v>
       </c>
       <c r="G354" t="n">
         <v>10387000</v>
@@ -8591,16 +8591,16 @@
         <v>45807</v>
       </c>
       <c r="C355" t="n">
-        <v>96.56077575683594</v>
+        <v>96.56076049804688</v>
       </c>
       <c r="D355" t="n">
-        <v>96.57036580789759</v>
+        <v>96.57035054759308</v>
       </c>
       <c r="E355" t="n">
-        <v>96.56077575683594</v>
+        <v>96.56076049804688</v>
       </c>
       <c r="F355" t="n">
-        <v>96.56077575683594</v>
+        <v>96.56076049804688</v>
       </c>
       <c r="G355" t="n">
         <v>14209500</v>
@@ -8660,16 +8660,16 @@
         <v>45812</v>
       </c>
       <c r="C358" t="n">
-        <v>96.60696411132812</v>
+        <v>96.60694885253906</v>
       </c>
       <c r="D358" t="n">
-        <v>96.60696411132812</v>
+        <v>96.60694885253906</v>
       </c>
       <c r="E358" t="n">
-        <v>96.59733984836828</v>
+        <v>96.59732459109935</v>
       </c>
       <c r="F358" t="n">
-        <v>96.60214830926736</v>
+        <v>96.60213305123895</v>
       </c>
       <c r="G358" t="n">
         <v>8923800</v>
@@ -8706,16 +8706,16 @@
         <v>45814</v>
       </c>
       <c r="C360" t="n">
-        <v>96.64545440673828</v>
+        <v>96.64546203613281</v>
       </c>
       <c r="D360" t="n">
-        <v>96.65507132859463</v>
+        <v>96.65507895874835</v>
       </c>
       <c r="E360" t="n">
-        <v>96.64545440673828</v>
+        <v>96.64546203613281</v>
       </c>
       <c r="F360" t="n">
-        <v>96.65026286766646</v>
+        <v>96.65027049744057</v>
       </c>
       <c r="G360" t="n">
         <v>9122400</v>
@@ -8729,16 +8729,16 @@
         <v>45817</v>
       </c>
       <c r="C361" t="n">
-        <v>96.65505981445312</v>
+        <v>96.65506744384766</v>
       </c>
       <c r="D361" t="n">
-        <v>96.66468407632469</v>
+        <v>96.66469170647891</v>
       </c>
       <c r="E361" t="n">
-        <v>96.65505981445312</v>
+        <v>96.65506744384766</v>
       </c>
       <c r="F361" t="n">
-        <v>96.65505981445312</v>
+        <v>96.65506744384766</v>
       </c>
       <c r="G361" t="n">
         <v>9902100</v>
@@ -8775,16 +8775,16 @@
         <v>45819</v>
       </c>
       <c r="C363" t="n">
-        <v>96.68395233154297</v>
+        <v>96.68394470214844</v>
       </c>
       <c r="D363" t="n">
-        <v>96.68395233154297</v>
+        <v>96.68394470214844</v>
       </c>
       <c r="E363" t="n">
-        <v>96.67432806770725</v>
+        <v>96.67432043907218</v>
       </c>
       <c r="F363" t="n">
-        <v>96.67913652904394</v>
+        <v>96.67912890002943</v>
       </c>
       <c r="G363" t="n">
         <v>10138800</v>
@@ -8798,16 +8798,16 @@
         <v>45820</v>
       </c>
       <c r="C364" t="n">
-        <v>96.69356536865234</v>
+        <v>96.69355010986328</v>
       </c>
       <c r="D364" t="n">
-        <v>96.69356536865234</v>
+        <v>96.69355010986328</v>
       </c>
       <c r="E364" t="n">
-        <v>96.68394844636542</v>
+        <v>96.68393318909396</v>
       </c>
       <c r="F364" t="n">
-        <v>96.69356536865234</v>
+        <v>96.69355010986328</v>
       </c>
       <c r="G364" t="n">
         <v>9574900</v>
@@ -8867,16 +8867,16 @@
         <v>45825</v>
       </c>
       <c r="C367" t="n">
-        <v>96.74166870117188</v>
+        <v>96.74166107177734</v>
       </c>
       <c r="D367" t="n">
-        <v>96.75129296356198</v>
+        <v>96.75128533340843</v>
       </c>
       <c r="E367" t="n">
-        <v>96.74166870117188</v>
+        <v>96.74166107177734</v>
       </c>
       <c r="F367" t="n">
-        <v>96.75129296356198</v>
+        <v>96.75128533340843</v>
       </c>
       <c r="G367" t="n">
         <v>8734500</v>
@@ -8890,16 +8890,16 @@
         <v>45826</v>
       </c>
       <c r="C368" t="n">
-        <v>96.76090240478516</v>
+        <v>96.76091003417969</v>
       </c>
       <c r="D368" t="n">
-        <v>96.77052666643127</v>
+        <v>96.77053429658464</v>
       </c>
       <c r="E368" t="n">
-        <v>96.76090240478516</v>
+        <v>96.76091003417969</v>
       </c>
       <c r="F368" t="n">
-        <v>96.77052666643127</v>
+        <v>96.77053429658464</v>
       </c>
       <c r="G368" t="n">
         <v>9783400</v>
@@ -8913,16 +8913,16 @@
         <v>45828</v>
       </c>
       <c r="C369" t="n">
-        <v>96.79940032958984</v>
+        <v>96.79939270019531</v>
       </c>
       <c r="D369" t="n">
-        <v>96.80902459205316</v>
+        <v>96.80901696190008</v>
       </c>
       <c r="E369" t="n">
-        <v>96.79940032958984</v>
+        <v>96.79939270019531</v>
       </c>
       <c r="F369" t="n">
-        <v>96.80421613140216</v>
+        <v>96.80420850162805</v>
       </c>
       <c r="G369" t="n">
         <v>9399400</v>
@@ -8936,16 +8936,16 @@
         <v>45831</v>
       </c>
       <c r="C370" t="n">
-        <v>96.81865692138672</v>
+        <v>96.81864929199219</v>
       </c>
       <c r="D370" t="n">
-        <v>96.81865692138672</v>
+        <v>96.81864929199219</v>
       </c>
       <c r="E370" t="n">
-        <v>96.80903265812152</v>
+        <v>96.80902502948538</v>
       </c>
       <c r="F370" t="n">
-        <v>96.81384111917316</v>
+        <v>96.81383349015812</v>
       </c>
       <c r="G370" t="n">
         <v>8847300</v>
@@ -8959,16 +8959,16 @@
         <v>45832</v>
       </c>
       <c r="C371" t="n">
-        <v>96.82826232910156</v>
+        <v>96.82826995849609</v>
       </c>
       <c r="D371" t="n">
-        <v>96.8378865912223</v>
+        <v>96.83789422137515</v>
       </c>
       <c r="E371" t="n">
-        <v>96.82826232910156</v>
+        <v>96.82826995849609</v>
       </c>
       <c r="F371" t="n">
-        <v>96.83307813074245</v>
+        <v>96.83308576051643</v>
       </c>
       <c r="G371" t="n">
         <v>10132100</v>
@@ -8982,16 +8982,16 @@
         <v>45833</v>
       </c>
       <c r="C372" t="n">
-        <v>96.837890625</v>
+        <v>96.83787536621094</v>
       </c>
       <c r="D372" t="n">
-        <v>96.84751488752164</v>
+        <v>96.84749962721607</v>
       </c>
       <c r="E372" t="n">
-        <v>96.837890625</v>
+        <v>96.83787536621094</v>
       </c>
       <c r="F372" t="n">
-        <v>96.84269908568015</v>
+        <v>96.84268382613341</v>
       </c>
       <c r="G372" t="n">
         <v>8015100</v>
@@ -9005,16 +9005,16 @@
         <v>45834</v>
       </c>
       <c r="C373" t="n">
-        <v>96.84749603271484</v>
+        <v>96.84751892089844</v>
       </c>
       <c r="D373" t="n">
-        <v>96.85712029336277</v>
+        <v>96.85714318382088</v>
       </c>
       <c r="E373" t="n">
-        <v>96.84749603271484</v>
+        <v>96.84751892089844</v>
       </c>
       <c r="F373" t="n">
-        <v>96.85712029336277</v>
+        <v>96.85714318382088</v>
       </c>
       <c r="G373" t="n">
         <v>9277700</v>
@@ -9028,16 +9028,16 @@
         <v>45835</v>
       </c>
       <c r="C374" t="n">
-        <v>96.88600158691406</v>
+        <v>96.88600921630859</v>
       </c>
       <c r="D374" t="n">
-        <v>96.88600158691406</v>
+        <v>96.88600921630859</v>
       </c>
       <c r="E374" t="n">
-        <v>96.87637732469139</v>
+        <v>96.87638495332804</v>
       </c>
       <c r="F374" t="n">
-        <v>96.88118578522216</v>
+        <v>96.88119341423747</v>
       </c>
       <c r="G374" t="n">
         <v>9742300</v>
@@ -9051,16 +9051,16 @@
         <v>45838</v>
       </c>
       <c r="C375" t="n">
-        <v>96.88600158691406</v>
+        <v>96.88600921630859</v>
       </c>
       <c r="D375" t="n">
-        <v>96.89561850797561</v>
+        <v>96.89562613812744</v>
       </c>
       <c r="E375" t="n">
-        <v>96.88600158691406</v>
+        <v>96.88600921630859</v>
       </c>
       <c r="F375" t="n">
-        <v>96.88600158691406</v>
+        <v>96.88600921630859</v>
       </c>
       <c r="G375" t="n">
         <v>18195600</v>
@@ -9074,16 +9074,16 @@
         <v>45839</v>
       </c>
       <c r="C376" t="n">
-        <v>96.91207885742188</v>
+        <v>96.91207122802734</v>
       </c>
       <c r="D376" t="n">
-        <v>96.91207885742188</v>
+        <v>96.91207122802734</v>
       </c>
       <c r="E376" t="n">
-        <v>96.90242131245242</v>
+        <v>96.90241368381817</v>
       </c>
       <c r="F376" t="n">
-        <v>96.91207885742188</v>
+        <v>96.91207122802734</v>
       </c>
       <c r="G376" t="n">
         <v>24173900</v>
@@ -9097,16 +9097,16 @@
         <v>45840</v>
       </c>
       <c r="C377" t="n">
-        <v>96.91207885742188</v>
+        <v>96.91207122802734</v>
       </c>
       <c r="D377" t="n">
-        <v>96.92172903584292</v>
+        <v>96.92172140568869</v>
       </c>
       <c r="E377" t="n">
-        <v>96.91207885742188</v>
+        <v>96.91207122802734</v>
       </c>
       <c r="F377" t="n">
-        <v>96.92172903584292</v>
+        <v>96.92172140568869</v>
       </c>
       <c r="G377" t="n">
         <v>10850800</v>
@@ -9120,16 +9120,16 @@
         <v>45841</v>
       </c>
       <c r="C378" t="n">
-        <v>96.96035766601562</v>
+        <v>96.96035003662109</v>
       </c>
       <c r="D378" t="n">
-        <v>96.97001521156446</v>
+        <v>96.97000758141002</v>
       </c>
       <c r="E378" t="n">
-        <v>96.96035766601562</v>
+        <v>96.96035003662109</v>
       </c>
       <c r="F378" t="n">
-        <v>96.96035766601562</v>
+        <v>96.96035003662109</v>
       </c>
       <c r="G378" t="n">
         <v>7404700</v>
@@ -9143,16 +9143,16 @@
         <v>45845</v>
       </c>
       <c r="C379" t="n">
-        <v>96.97967529296875</v>
+        <v>96.97968292236328</v>
       </c>
       <c r="D379" t="n">
-        <v>96.97967529296875</v>
+        <v>96.97968292236328</v>
       </c>
       <c r="E379" t="n">
-        <v>96.97001774716739</v>
+        <v>96.97002537580215</v>
       </c>
       <c r="F379" t="n">
-        <v>96.97967529296875</v>
+        <v>96.97968292236328</v>
       </c>
       <c r="G379" t="n">
         <v>12363900</v>
@@ -9212,16 +9212,16 @@
         <v>45848</v>
       </c>
       <c r="C382" t="n">
-        <v>97.00862121582031</v>
+        <v>97.00861358642578</v>
       </c>
       <c r="D382" t="n">
-        <v>97.01827875969551</v>
+        <v>97.01827112954146</v>
       </c>
       <c r="E382" t="n">
-        <v>96.99896367194511</v>
+        <v>96.99895604331012</v>
       </c>
       <c r="F382" t="n">
-        <v>97.00862121582031</v>
+        <v>97.00861358642578</v>
       </c>
       <c r="G382" t="n">
         <v>10071700</v>
@@ -9235,16 +9235,16 @@
         <v>45849</v>
       </c>
       <c r="C383" t="n">
-        <v>97.0472412109375</v>
+        <v>97.04724884033203</v>
       </c>
       <c r="D383" t="n">
-        <v>97.0472412109375</v>
+        <v>97.04724884033203</v>
       </c>
       <c r="E383" t="n">
-        <v>97.03758366734232</v>
+        <v>97.03759129597762</v>
       </c>
       <c r="F383" t="n">
-        <v>97.03758366734232</v>
+        <v>97.03759129597762</v>
       </c>
       <c r="G383" t="n">
         <v>9288900</v>
@@ -9258,16 +9258,16 @@
         <v>45852</v>
       </c>
       <c r="C384" t="n">
-        <v>97.0472412109375</v>
+        <v>97.04724884033203</v>
       </c>
       <c r="D384" t="n">
-        <v>97.05689138798532</v>
+        <v>97.05689901813851</v>
       </c>
       <c r="E384" t="n">
-        <v>97.0472412109375</v>
+        <v>97.04724884033203</v>
       </c>
       <c r="F384" t="n">
-        <v>97.05689138798532</v>
+        <v>97.05689901813851</v>
       </c>
       <c r="G384" t="n">
         <v>10293900</v>
@@ -9281,16 +9281,16 @@
         <v>45853</v>
       </c>
       <c r="C385" t="n">
-        <v>97.05690765380859</v>
+        <v>97.05689239501953</v>
       </c>
       <c r="D385" t="n">
-        <v>97.06656519902229</v>
+        <v>97.06654993871493</v>
       </c>
       <c r="E385" t="n">
-        <v>97.05690765380859</v>
+        <v>97.05689239501953</v>
       </c>
       <c r="F385" t="n">
-        <v>97.06656519902229</v>
+        <v>97.06654993871493</v>
       </c>
       <c r="G385" t="n">
         <v>10207100</v>
@@ -9304,16 +9304,16 @@
         <v>45854</v>
       </c>
       <c r="C386" t="n">
-        <v>97.08587646484375</v>
+        <v>97.08586883544922</v>
       </c>
       <c r="D386" t="n">
-        <v>97.08587646484375</v>
+        <v>97.08586883544922</v>
       </c>
       <c r="E386" t="n">
-        <v>97.07621892001049</v>
+        <v>97.07621129137489</v>
       </c>
       <c r="F386" t="n">
-        <v>97.07621892001049</v>
+        <v>97.07621129137489</v>
       </c>
       <c r="G386" t="n">
         <v>8117900</v>
@@ -9327,16 +9327,16 @@
         <v>45855</v>
       </c>
       <c r="C387" t="n">
-        <v>97.09551239013672</v>
+        <v>97.09552001953125</v>
       </c>
       <c r="D387" t="n">
-        <v>97.09551239013672</v>
+        <v>97.09552001953125</v>
       </c>
       <c r="E387" t="n">
-        <v>97.08586221326836</v>
+        <v>97.08586984190462</v>
       </c>
       <c r="F387" t="n">
-        <v>97.09068730170253</v>
+        <v>97.09069493071793</v>
       </c>
       <c r="G387" t="n">
         <v>9040400</v>
@@ -9350,16 +9350,16 @@
         <v>45856</v>
       </c>
       <c r="C388" t="n">
-        <v>97.12448883056641</v>
+        <v>97.12449645996094</v>
       </c>
       <c r="D388" t="n">
-        <v>97.12448883056641</v>
+        <v>97.12449645996094</v>
       </c>
       <c r="E388" t="n">
-        <v>97.11483865258754</v>
+        <v>97.11484628122402</v>
       </c>
       <c r="F388" t="n">
-        <v>97.11483865258754</v>
+        <v>97.11484628122402</v>
       </c>
       <c r="G388" t="n">
         <v>9399500</v>
@@ -9396,16 +9396,16 @@
         <v>45860</v>
       </c>
       <c r="C390" t="n">
-        <v>97.15346527099609</v>
+        <v>97.15345764160156</v>
       </c>
       <c r="D390" t="n">
-        <v>97.15346527099609</v>
+        <v>97.15345764160156</v>
       </c>
       <c r="E390" t="n">
-        <v>97.14380772609073</v>
+        <v>97.1438000974546</v>
       </c>
       <c r="F390" t="n">
-        <v>97.15346527099609</v>
+        <v>97.15345764160156</v>
       </c>
       <c r="G390" t="n">
         <v>9340600</v>
@@ -9419,16 +9419,16 @@
         <v>45861</v>
       </c>
       <c r="C391" t="n">
-        <v>97.16310882568359</v>
+        <v>97.16312408447266</v>
       </c>
       <c r="D391" t="n">
-        <v>97.16310882568359</v>
+        <v>97.16312408447266</v>
       </c>
       <c r="E391" t="n">
-        <v>97.15345864798445</v>
+        <v>97.15347390525802</v>
       </c>
       <c r="F391" t="n">
-        <v>97.16310882568359</v>
+        <v>97.16312408447266</v>
       </c>
       <c r="G391" t="n">
         <v>8056100</v>
@@ -9580,16 +9580,16 @@
         <v>45870</v>
       </c>
       <c r="C398" t="n">
-        <v>97.28102111816406</v>
+        <v>97.28102874755859</v>
       </c>
       <c r="D398" t="n">
-        <v>97.29071349819972</v>
+        <v>97.29072112835438</v>
       </c>
       <c r="E398" t="n">
-        <v>97.28102111816406</v>
+        <v>97.28102874755859</v>
       </c>
       <c r="F398" t="n">
-        <v>97.28102111816406</v>
+        <v>97.28102874755859</v>
       </c>
       <c r="G398" t="n">
         <v>26832500</v>
@@ -9603,16 +9603,16 @@
         <v>45873</v>
       </c>
       <c r="C399" t="n">
-        <v>97.30040740966797</v>
+        <v>97.30039978027344</v>
       </c>
       <c r="D399" t="n">
-        <v>97.30040740966797</v>
+        <v>97.30039978027344</v>
       </c>
       <c r="E399" t="n">
-        <v>97.29071502947977</v>
+        <v>97.29070740084522</v>
       </c>
       <c r="F399" t="n">
-        <v>97.29555752301393</v>
+        <v>97.29554989399966</v>
       </c>
       <c r="G399" t="n">
         <v>14766400</v>
@@ -9649,16 +9649,16 @@
         <v>45875</v>
       </c>
       <c r="C401" t="n">
-        <v>97.31977844238281</v>
+        <v>97.31978607177734</v>
       </c>
       <c r="D401" t="n">
-        <v>97.31977844238281</v>
+        <v>97.31978607177734</v>
       </c>
       <c r="E401" t="n">
-        <v>97.31008606282549</v>
+        <v>97.31009369146018</v>
       </c>
       <c r="F401" t="n">
-        <v>97.31977844238281</v>
+        <v>97.31978607177734</v>
       </c>
       <c r="G401" t="n">
         <v>10653900</v>
@@ -9672,16 +9672,16 @@
         <v>45876</v>
       </c>
       <c r="C402" t="n">
-        <v>97.31977844238281</v>
+        <v>97.31978607177734</v>
       </c>
       <c r="D402" t="n">
-        <v>97.32947082194013</v>
+        <v>97.32947845209449</v>
       </c>
       <c r="E402" t="n">
-        <v>97.31977844238281</v>
+        <v>97.31978607177734</v>
       </c>
       <c r="F402" t="n">
-        <v>97.32947082194013</v>
+        <v>97.32947845209449</v>
       </c>
       <c r="G402" t="n">
         <v>10823000</v>
@@ -9695,16 +9695,16 @@
         <v>45877</v>
       </c>
       <c r="C403" t="n">
-        <v>97.36824798583984</v>
+        <v>97.36823272705078</v>
       </c>
       <c r="D403" t="n">
-        <v>97.36824798583984</v>
+        <v>97.36823272705078</v>
       </c>
       <c r="E403" t="n">
-        <v>97.35855560478551</v>
+        <v>97.35854034751536</v>
       </c>
       <c r="F403" t="n">
-        <v>97.3633980987524</v>
+        <v>97.36338284072336</v>
       </c>
       <c r="G403" t="n">
         <v>12066300</v>
@@ -9718,16 +9718,16 @@
         <v>45880</v>
       </c>
       <c r="C404" t="n">
-        <v>97.37792205810547</v>
+        <v>97.3779296875</v>
       </c>
       <c r="D404" t="n">
-        <v>97.37792205810547</v>
+        <v>97.3779296875</v>
       </c>
       <c r="E404" t="n">
-        <v>97.36823707125734</v>
+        <v>97.36824469989307</v>
       </c>
       <c r="F404" t="n">
-        <v>97.37792205810547</v>
+        <v>97.3779296875</v>
       </c>
       <c r="G404" t="n">
         <v>12940300</v>
@@ -9741,16 +9741,16 @@
         <v>45881</v>
       </c>
       <c r="C405" t="n">
-        <v>97.37792205810547</v>
+        <v>97.3779296875</v>
       </c>
       <c r="D405" t="n">
-        <v>97.38761443807333</v>
+        <v>97.38762206822724</v>
       </c>
       <c r="E405" t="n">
-        <v>97.37792205810547</v>
+        <v>97.3779296875</v>
       </c>
       <c r="F405" t="n">
-        <v>97.38761443807333</v>
+        <v>97.38762206822724</v>
       </c>
       <c r="G405" t="n">
         <v>12918200</v>
@@ -9764,16 +9764,16 @@
         <v>45882</v>
       </c>
       <c r="C406" t="n">
-        <v>97.39730834960938</v>
+        <v>97.39730072021484</v>
       </c>
       <c r="D406" t="n">
-        <v>97.4069933366098</v>
+        <v>97.40698570645661</v>
       </c>
       <c r="E406" t="n">
-        <v>97.3876159694891</v>
+        <v>97.3876083408538</v>
       </c>
       <c r="F406" t="n">
-        <v>97.39730834960938</v>
+        <v>97.39730072021484</v>
       </c>
       <c r="G406" t="n">
         <v>12144800</v>
@@ -9787,16 +9787,16 @@
         <v>45883</v>
       </c>
       <c r="C407" t="n">
-        <v>97.40699768066406</v>
+        <v>97.40699005126953</v>
       </c>
       <c r="D407" t="n">
-        <v>97.41669006121658</v>
+        <v>97.4166824310629</v>
       </c>
       <c r="E407" t="n">
-        <v>97.40699768066406</v>
+        <v>97.40699005126953</v>
       </c>
       <c r="F407" t="n">
-        <v>97.40699768066406</v>
+        <v>97.40699005126953</v>
       </c>
       <c r="G407" t="n">
         <v>9798900</v>
@@ -9833,16 +9833,16 @@
         <v>45887</v>
       </c>
       <c r="C409" t="n">
-        <v>97.46513366699219</v>
+        <v>97.46514129638672</v>
       </c>
       <c r="D409" t="n">
-        <v>97.46513366699219</v>
+        <v>97.46514129638672</v>
       </c>
       <c r="E409" t="n">
-        <v>97.4457489080558</v>
+        <v>97.44575653593293</v>
       </c>
       <c r="F409" t="n">
-        <v>97.455441287524</v>
+        <v>97.45544891615982</v>
       </c>
       <c r="G409" t="n">
         <v>14768500</v>
@@ -9856,16 +9856,16 @@
         <v>45888</v>
       </c>
       <c r="C410" t="n">
-        <v>97.46513366699219</v>
+        <v>97.46514129638672</v>
       </c>
       <c r="D410" t="n">
-        <v>97.47481865334103</v>
+        <v>97.47482628349368</v>
       </c>
       <c r="E410" t="n">
-        <v>97.46513366699219</v>
+        <v>97.46514129638672</v>
       </c>
       <c r="F410" t="n">
-        <v>97.47481865334103</v>
+        <v>97.47482628349368</v>
       </c>
       <c r="G410" t="n">
         <v>10474900</v>
@@ -9948,16 +9948,16 @@
         <v>45894</v>
       </c>
       <c r="C414" t="n">
-        <v>97.54265594482422</v>
+        <v>97.54266357421875</v>
       </c>
       <c r="D414" t="n">
-        <v>97.54265594482422</v>
+        <v>97.54266357421875</v>
       </c>
       <c r="E414" t="n">
-        <v>97.53296356555194</v>
+        <v>97.53297119418838</v>
       </c>
       <c r="F414" t="n">
-        <v>97.53780605862848</v>
+        <v>97.53781368764366</v>
       </c>
       <c r="G414" t="n">
         <v>13556000</v>
@@ -9971,16 +9971,16 @@
         <v>45895</v>
       </c>
       <c r="C415" t="n">
-        <v>97.54265594482422</v>
+        <v>97.54266357421875</v>
       </c>
       <c r="D415" t="n">
-        <v>97.55234093097729</v>
+        <v>97.55234856112934</v>
       </c>
       <c r="E415" t="n">
-        <v>97.54265594482422</v>
+        <v>97.54266357421875</v>
       </c>
       <c r="F415" t="n">
-        <v>97.54749843790076</v>
+        <v>97.54750606767405</v>
       </c>
       <c r="G415" t="n">
         <v>8741600</v>
@@ -9994,16 +9994,16 @@
         <v>45896</v>
       </c>
       <c r="C416" t="n">
-        <v>97.55233764648438</v>
+        <v>97.55234527587891</v>
       </c>
       <c r="D416" t="n">
-        <v>97.56203002543032</v>
+        <v>97.56203765558288</v>
       </c>
       <c r="E416" t="n">
-        <v>97.55233764648438</v>
+        <v>97.55234527587891</v>
       </c>
       <c r="F416" t="n">
-        <v>97.56203002543032</v>
+        <v>97.56203765558288</v>
       </c>
       <c r="G416" t="n">
         <v>7384600</v>
@@ -10040,16 +10040,16 @@
         <v>45898</v>
       </c>
       <c r="C418" t="n">
-        <v>97.62018585205078</v>
+        <v>97.62017822265625</v>
       </c>
       <c r="D418" t="n">
-        <v>97.62018585205078</v>
+        <v>97.62017822265625</v>
       </c>
       <c r="E418" t="n">
-        <v>97.60080848403456</v>
+        <v>97.60080085615444</v>
       </c>
       <c r="F418" t="n">
-        <v>97.60080848403456</v>
+        <v>97.60080085615444</v>
       </c>
       <c r="G418" t="n">
         <v>21369400</v>
@@ -10109,16 +10109,16 @@
         <v>45904</v>
       </c>
       <c r="C421" t="n">
-        <v>97.65908050537109</v>
+        <v>97.65907287597656</v>
       </c>
       <c r="D421" t="n">
-        <v>97.65908050537109</v>
+        <v>97.65907287597656</v>
       </c>
       <c r="E421" t="n">
-        <v>97.64936078454357</v>
+        <v>97.64935315590837</v>
       </c>
       <c r="F421" t="n">
-        <v>97.65422064495733</v>
+        <v>97.65421301594246</v>
       </c>
       <c r="G421" t="n">
         <v>11300200</v>
@@ -10132,16 +10132,16 @@
         <v>45905</v>
       </c>
       <c r="C422" t="n">
-        <v>97.67853546142578</v>
+        <v>97.67854309082031</v>
       </c>
       <c r="D422" t="n">
-        <v>97.68825518232049</v>
+        <v>97.68826281247419</v>
       </c>
       <c r="E422" t="n">
-        <v>97.67853546142578</v>
+        <v>97.67854309082031</v>
       </c>
       <c r="F422" t="n">
-        <v>97.68825518232049</v>
+        <v>97.68826281247419</v>
       </c>
       <c r="G422" t="n">
         <v>15312000</v>
@@ -10155,16 +10155,16 @@
         <v>45908</v>
       </c>
       <c r="C423" t="n">
-        <v>97.70770263671875</v>
+        <v>97.70769500732422</v>
       </c>
       <c r="D423" t="n">
-        <v>97.70770263671875</v>
+        <v>97.70769500732422</v>
       </c>
       <c r="E423" t="n">
-        <v>97.69797549686939</v>
+        <v>97.6979678682344</v>
       </c>
       <c r="F423" t="n">
-        <v>97.70283535697719</v>
+        <v>97.70282772796271</v>
       </c>
       <c r="G423" t="n">
         <v>12715100</v>
@@ -10178,16 +10178,16 @@
         <v>45909</v>
       </c>
       <c r="C424" t="n">
-        <v>97.70770263671875</v>
+        <v>97.70769500732422</v>
       </c>
       <c r="D424" t="n">
-        <v>97.71742977656811</v>
+        <v>97.71742214641404</v>
       </c>
       <c r="E424" t="n">
-        <v>97.70770263671875</v>
+        <v>97.70769500732422</v>
       </c>
       <c r="F424" t="n">
-        <v>97.71742977656811</v>
+        <v>97.71742214641404</v>
       </c>
       <c r="G424" t="n">
         <v>11005500</v>
@@ -10201,16 +10201,16 @@
         <v>45910</v>
       </c>
       <c r="C425" t="n">
-        <v>97.71744537353516</v>
+        <v>97.71743774414062</v>
       </c>
       <c r="D425" t="n">
-        <v>97.72716509530215</v>
+        <v>97.72715746514874</v>
       </c>
       <c r="E425" t="n">
-        <v>97.71744537353516</v>
+        <v>97.71743774414062</v>
       </c>
       <c r="F425" t="n">
-        <v>97.71744537353516</v>
+        <v>97.71743774414062</v>
       </c>
       <c r="G425" t="n">
         <v>9356600</v>
@@ -10224,16 +10224,16 @@
         <v>45911</v>
       </c>
       <c r="C426" t="n">
-        <v>97.73688507080078</v>
+        <v>97.73687744140625</v>
       </c>
       <c r="D426" t="n">
-        <v>97.73688507080078</v>
+        <v>97.73687744140625</v>
       </c>
       <c r="E426" t="n">
-        <v>97.72715793011203</v>
+        <v>97.7271503014768</v>
       </c>
       <c r="F426" t="n">
-        <v>97.7320252102736</v>
+        <v>97.73201758125843</v>
       </c>
       <c r="G426" t="n">
         <v>9136600</v>
@@ -10247,16 +10247,16 @@
         <v>45912</v>
       </c>
       <c r="C427" t="n">
-        <v>97.76606750488281</v>
+        <v>97.76605987548828</v>
       </c>
       <c r="D427" t="n">
-        <v>97.77579464641046</v>
+        <v>97.77578701625686</v>
       </c>
       <c r="E427" t="n">
-        <v>97.76606750488281</v>
+        <v>97.76605987548828</v>
       </c>
       <c r="F427" t="n">
-        <v>97.76606750488281</v>
+        <v>97.76605987548828</v>
       </c>
       <c r="G427" t="n">
         <v>10482000</v>
@@ -10270,16 +10270,16 @@
         <v>45915</v>
       </c>
       <c r="C428" t="n">
-        <v>97.76606750488281</v>
+        <v>97.76605987548828</v>
       </c>
       <c r="D428" t="n">
-        <v>97.77579464641046</v>
+        <v>97.77578701625686</v>
       </c>
       <c r="E428" t="n">
-        <v>97.76606750488281</v>
+        <v>97.76605987548828</v>
       </c>
       <c r="F428" t="n">
-        <v>97.76606750488281</v>
+        <v>97.76605987548828</v>
       </c>
       <c r="G428" t="n">
         <v>15288300</v>
@@ -10316,16 +10316,16 @@
         <v>45917</v>
       </c>
       <c r="C430" t="n">
-        <v>97.79521942138672</v>
+        <v>97.79523468017578</v>
       </c>
       <c r="D430" t="n">
-        <v>97.80494656071735</v>
+        <v>97.80496182102412</v>
       </c>
       <c r="E430" t="n">
-        <v>97.79521942138672</v>
+        <v>97.79523468017578</v>
       </c>
       <c r="F430" t="n">
-        <v>97.80494656071735</v>
+        <v>97.80496182102412</v>
       </c>
       <c r="G430" t="n">
         <v>10381200</v>
@@ -10362,16 +10362,16 @@
         <v>45919</v>
       </c>
       <c r="C432" t="n">
-        <v>97.85357666015625</v>
+        <v>97.85358428955078</v>
       </c>
       <c r="D432" t="n">
-        <v>97.85357666015625</v>
+        <v>97.85358428955078</v>
       </c>
       <c r="E432" t="n">
-        <v>97.84384952064445</v>
+        <v>97.84385714928058</v>
       </c>
       <c r="F432" t="n">
-        <v>97.84384952064445</v>
+        <v>97.84385714928058</v>
       </c>
       <c r="G432" t="n">
         <v>11174000</v>
@@ -10385,16 +10385,16 @@
         <v>45922</v>
       </c>
       <c r="C433" t="n">
-        <v>97.85357666015625</v>
+        <v>97.85358428955078</v>
       </c>
       <c r="D433" t="n">
-        <v>97.86329638003455</v>
+        <v>97.86330401018691</v>
       </c>
       <c r="E433" t="n">
-        <v>97.85357666015625</v>
+        <v>97.85358428955078</v>
       </c>
       <c r="F433" t="n">
-        <v>97.85357666015625</v>
+        <v>97.85358428955078</v>
       </c>
       <c r="G433" t="n">
         <v>12279500</v>
@@ -10408,16 +10408,16 @@
         <v>45923</v>
       </c>
       <c r="C434" t="n">
-        <v>97.87303161621094</v>
+        <v>97.87303924560547</v>
       </c>
       <c r="D434" t="n">
-        <v>97.87303161621094</v>
+        <v>97.87303924560547</v>
       </c>
       <c r="E434" t="n">
-        <v>97.86330447589445</v>
+        <v>97.86331210453073</v>
       </c>
       <c r="F434" t="n">
-        <v>97.86817175586975</v>
+        <v>97.86817938488544</v>
       </c>
       <c r="G434" t="n">
         <v>11191700</v>
@@ -10431,16 +10431,16 @@
         <v>45924</v>
       </c>
       <c r="C435" t="n">
-        <v>97.88275909423828</v>
+        <v>97.88276672363281</v>
       </c>
       <c r="D435" t="n">
-        <v>97.88275909423828</v>
+        <v>97.88276672363281</v>
       </c>
       <c r="E435" t="n">
-        <v>97.87303195388823</v>
+        <v>97.87303958252458</v>
       </c>
       <c r="F435" t="n">
-        <v>97.8778918142462</v>
+        <v>97.87789944326134</v>
       </c>
       <c r="G435" t="n">
         <v>10108500</v>
@@ -10454,16 +10454,16 @@
         <v>45925</v>
       </c>
       <c r="C436" t="n">
-        <v>97.89247894287109</v>
+        <v>97.89248657226562</v>
       </c>
       <c r="D436" t="n">
-        <v>97.89247894287109</v>
+        <v>97.89248657226562</v>
       </c>
       <c r="E436" t="n">
-        <v>97.88275180324558</v>
+        <v>97.88275943188202</v>
       </c>
       <c r="F436" t="n">
-        <v>97.88275180324558</v>
+        <v>97.88275943188202</v>
       </c>
       <c r="G436" t="n">
         <v>10549100</v>
@@ -10477,16 +10477,16 @@
         <v>45926</v>
       </c>
       <c r="C437" t="n">
-        <v>97.92166137695312</v>
+        <v>97.92165374755859</v>
       </c>
       <c r="D437" t="n">
-        <v>97.92166137695312</v>
+        <v>97.92165374755859</v>
       </c>
       <c r="E437" t="n">
-        <v>97.91193423648973</v>
+        <v>97.91192660785308</v>
       </c>
       <c r="F437" t="n">
-        <v>97.91193423648973</v>
+        <v>97.91192660785308</v>
       </c>
       <c r="G437" t="n">
         <v>10688600</v>
@@ -10569,16 +10569,16 @@
         <v>45932</v>
       </c>
       <c r="C441" t="n">
-        <v>97.95773315429688</v>
+        <v>97.95772552490234</v>
       </c>
       <c r="D441" t="n">
-        <v>97.96749392953743</v>
+        <v>97.96748629938267</v>
       </c>
       <c r="E441" t="n">
-        <v>97.95773315429688</v>
+        <v>97.95772552490234</v>
       </c>
       <c r="F441" t="n">
-        <v>97.96749392953743</v>
+        <v>97.96748629938267</v>
       </c>
       <c r="G441" t="n">
         <v>12870100</v>
@@ -10638,16 +10638,16 @@
         <v>45937</v>
       </c>
       <c r="C444" t="n">
-        <v>98.01628875732422</v>
+        <v>98.01628112792969</v>
       </c>
       <c r="D444" t="n">
-        <v>98.01628875732422</v>
+        <v>98.01628112792969</v>
       </c>
       <c r="E444" t="n">
-        <v>98.00652798224331</v>
+        <v>98.00652035360855</v>
       </c>
       <c r="F444" t="n">
-        <v>98.01628875732422</v>
+        <v>98.01628112792969</v>
       </c>
       <c r="G444" t="n">
         <v>14289100</v>
@@ -10661,16 +10661,16 @@
         <v>45938</v>
       </c>
       <c r="C445" t="n">
-        <v>98.02603912353516</v>
+        <v>98.02603149414062</v>
       </c>
       <c r="D445" t="n">
-        <v>98.02603912353516</v>
+        <v>98.02603149414062</v>
       </c>
       <c r="E445" t="n">
-        <v>98.01628579403904</v>
+        <v>98.01627816540361</v>
       </c>
       <c r="F445" t="n">
-        <v>98.02603912353516</v>
+        <v>98.02603149414062</v>
       </c>
       <c r="G445" t="n">
         <v>16811200</v>
@@ -10707,16 +10707,16 @@
         <v>45940</v>
       </c>
       <c r="C447" t="n">
-        <v>98.0845947265625</v>
+        <v>98.08458709716797</v>
       </c>
       <c r="D447" t="n">
-        <v>98.0845947265625</v>
+        <v>98.08458709716797</v>
       </c>
       <c r="E447" t="n">
-        <v>98.06507317730942</v>
+        <v>98.06506554943334</v>
       </c>
       <c r="F447" t="n">
-        <v>98.07483395193596</v>
+        <v>98.07482632330066</v>
       </c>
       <c r="G447" t="n">
         <v>18966600</v>
@@ -10730,16 +10730,16 @@
         <v>45943</v>
       </c>
       <c r="C448" t="n">
-        <v>98.07484436035156</v>
+        <v>98.07483673095703</v>
       </c>
       <c r="D448" t="n">
-        <v>98.08460513601399</v>
+        <v>98.08459750586016</v>
       </c>
       <c r="E448" t="n">
-        <v>98.07484436035156</v>
+        <v>98.07483673095703</v>
       </c>
       <c r="F448" t="n">
-        <v>98.07484436035156</v>
+        <v>98.07483673095703</v>
       </c>
       <c r="G448" t="n">
         <v>14453500</v>
@@ -10753,16 +10753,16 @@
         <v>45944</v>
       </c>
       <c r="C449" t="n">
-        <v>98.0845947265625</v>
+        <v>98.08458709716797</v>
       </c>
       <c r="D449" t="n">
-        <v>98.09434805589947</v>
+        <v>98.0943404257463</v>
       </c>
       <c r="E449" t="n">
-        <v>98.0845947265625</v>
+        <v>98.08458709716797</v>
       </c>
       <c r="F449" t="n">
-        <v>98.0845947265625</v>
+        <v>98.08458709716797</v>
       </c>
       <c r="G449" t="n">
         <v>13475000</v>
@@ -10776,16 +10776,16 @@
         <v>45945</v>
       </c>
       <c r="C450" t="n">
-        <v>98.10411834716797</v>
+        <v>98.10410308837891</v>
       </c>
       <c r="D450" t="n">
-        <v>98.10411834716797</v>
+        <v>98.10410308837891</v>
       </c>
       <c r="E450" t="n">
-        <v>98.09435757159457</v>
+        <v>98.09434231432367</v>
       </c>
       <c r="F450" t="n">
-        <v>98.10411834716797</v>
+        <v>98.10410308837891</v>
       </c>
       <c r="G450" t="n">
         <v>11069100</v>
@@ -10822,16 +10822,16 @@
         <v>45947</v>
       </c>
       <c r="C452" t="n">
-        <v>98.14314270019531</v>
+        <v>98.14313507080078</v>
       </c>
       <c r="D452" t="n">
-        <v>98.14314270019531</v>
+        <v>98.14313507080078</v>
       </c>
       <c r="E452" t="n">
-        <v>98.13338192574615</v>
+        <v>98.13337429711039</v>
       </c>
       <c r="F452" t="n">
-        <v>98.13826603561544</v>
+        <v>98.13825840660002</v>
       </c>
       <c r="G452" t="n">
         <v>14603500</v>
@@ -10845,16 +10845,16 @@
         <v>45950</v>
       </c>
       <c r="C453" t="n">
-        <v>98.15290832519531</v>
+        <v>98.15290069580078</v>
       </c>
       <c r="D453" t="n">
-        <v>98.15290832519531</v>
+        <v>98.15290069580078</v>
       </c>
       <c r="E453" t="n">
-        <v>98.14314755026379</v>
+        <v>98.14313992162796</v>
       </c>
       <c r="F453" t="n">
-        <v>98.15290832519531</v>
+        <v>98.15290069580078</v>
       </c>
       <c r="G453" t="n">
         <v>16129100</v>
@@ -10868,16 +10868,16 @@
         <v>45951</v>
       </c>
       <c r="C454" t="n">
-        <v>98.17241668701172</v>
+        <v>98.17242431640625</v>
       </c>
       <c r="D454" t="n">
-        <v>98.17241668701172</v>
+        <v>98.17242431640625</v>
       </c>
       <c r="E454" t="n">
-        <v>98.16265591265116</v>
+        <v>98.16266354128715</v>
       </c>
       <c r="F454" t="n">
-        <v>98.16265591265116</v>
+        <v>98.16266354128715</v>
       </c>
       <c r="G454" t="n">
         <v>12061900</v>
@@ -10891,16 +10891,16 @@
         <v>45952</v>
       </c>
       <c r="C455" t="n">
-        <v>98.18218231201172</v>
+        <v>98.18218994140625</v>
       </c>
       <c r="D455" t="n">
-        <v>98.18218231201172</v>
+        <v>98.18218994140625</v>
       </c>
       <c r="E455" t="n">
-        <v>98.17242153716894</v>
+        <v>98.172429165805</v>
       </c>
       <c r="F455" t="n">
-        <v>98.18218231201172</v>
+        <v>98.18218994140625</v>
       </c>
       <c r="G455" t="n">
         <v>9089900</v>
@@ -10914,16 +10914,16 @@
         <v>45953</v>
       </c>
       <c r="C456" t="n">
-        <v>98.19194793701172</v>
+        <v>98.19194030761719</v>
       </c>
       <c r="D456" t="n">
-        <v>98.19194793701172</v>
+        <v>98.19194030761719</v>
       </c>
       <c r="E456" t="n">
-        <v>98.18218716168681</v>
+        <v>98.18217953305069</v>
       </c>
       <c r="F456" t="n">
-        <v>98.19194793701172</v>
+        <v>98.19194030761719</v>
       </c>
       <c r="G456" t="n">
         <v>10658100</v>
@@ -10937,16 +10937,16 @@
         <v>45954</v>
       </c>
       <c r="C457" t="n">
-        <v>98.22120666503906</v>
+        <v>98.22122192382812</v>
       </c>
       <c r="D457" t="n">
-        <v>98.22120666503906</v>
+        <v>98.22122192382812</v>
       </c>
       <c r="E457" t="n">
-        <v>98.21144589131933</v>
+        <v>98.21146114859204</v>
       </c>
       <c r="F457" t="n">
-        <v>98.22120666503906</v>
+        <v>98.22122192382812</v>
       </c>
       <c r="G457" t="n">
         <v>12382000</v>
@@ -10960,16 +10960,16 @@
         <v>45957</v>
       </c>
       <c r="C458" t="n">
-        <v>98.23096466064453</v>
+        <v>98.23097229003906</v>
       </c>
       <c r="D458" t="n">
-        <v>98.24071798879955</v>
+        <v>98.2407256189516</v>
       </c>
       <c r="E458" t="n">
-        <v>98.22120388720086</v>
+        <v>98.22121151583728</v>
       </c>
       <c r="F458" t="n">
-        <v>98.22120388720086</v>
+        <v>98.22121151583728</v>
       </c>
       <c r="G458" t="n">
         <v>26389600</v>
@@ -10983,16 +10983,16 @@
         <v>45958</v>
       </c>
       <c r="C459" t="n">
-        <v>98.24072265625</v>
+        <v>98.24073791503906</v>
       </c>
       <c r="D459" t="n">
-        <v>98.25048343015742</v>
+        <v>98.25049869046254</v>
       </c>
       <c r="E459" t="n">
-        <v>98.24072265625</v>
+        <v>98.24073791503906</v>
       </c>
       <c r="F459" t="n">
-        <v>98.24072265625</v>
+        <v>98.24073791503906</v>
       </c>
       <c r="G459" t="n">
         <v>11134700</v>
@@ -11006,16 +11006,16 @@
         <v>45959</v>
       </c>
       <c r="C460" t="n">
-        <v>98.25048065185547</v>
+        <v>98.25048828125</v>
       </c>
       <c r="D460" t="n">
-        <v>98.26024142548688</v>
+        <v>98.26024905563935</v>
       </c>
       <c r="E460" t="n">
-        <v>98.25048065185547</v>
+        <v>98.25048828125</v>
       </c>
       <c r="F460" t="n">
-        <v>98.26024142548688</v>
+        <v>98.26024905563935</v>
       </c>
       <c r="G460" t="n">
         <v>14177700</v>
@@ -11029,16 +11029,16 @@
         <v>45960</v>
       </c>
       <c r="C461" t="n">
-        <v>98.26025390625</v>
+        <v>98.26026153564453</v>
       </c>
       <c r="D461" t="n">
-        <v>98.27000723583144</v>
+        <v>98.27001486598327</v>
       </c>
       <c r="E461" t="n">
-        <v>98.26025390625</v>
+        <v>98.26026153564453</v>
       </c>
       <c r="F461" t="n">
-        <v>98.26025390625</v>
+        <v>98.26026153564453</v>
       </c>
       <c r="G461" t="n">
         <v>12370700</v>
@@ -11052,16 +11052,16 @@
         <v>45961</v>
       </c>
       <c r="C462" t="n">
-        <v>98.28951263427734</v>
+        <v>98.28952026367188</v>
       </c>
       <c r="D462" t="n">
-        <v>98.29927340754462</v>
+        <v>98.29928103769679</v>
       </c>
       <c r="E462" t="n">
-        <v>98.28951263427734</v>
+        <v>98.28952026367188</v>
       </c>
       <c r="F462" t="n">
-        <v>98.29438929826671</v>
+        <v>98.29439692803977</v>
       </c>
       <c r="G462" t="n">
         <v>23254100</v>
@@ -11121,16 +11121,16 @@
         <v>45966</v>
       </c>
       <c r="C465" t="n">
-        <v>98.33651733398438</v>
+        <v>98.33652496337891</v>
       </c>
       <c r="D465" t="n">
-        <v>98.33651733398438</v>
+        <v>98.33652496337891</v>
       </c>
       <c r="E465" t="n">
-        <v>98.32673018986331</v>
+        <v>98.32673781849851</v>
       </c>
       <c r="F465" t="n">
-        <v>98.32673018986331</v>
+        <v>98.32673781849851</v>
       </c>
       <c r="G465" t="n">
         <v>11335000</v>
@@ -11144,16 +11144,16 @@
         <v>45967</v>
       </c>
       <c r="C466" t="n">
-        <v>98.3463134765625</v>
+        <v>98.34632110595703</v>
       </c>
       <c r="D466" t="n">
-        <v>98.3463134765625</v>
+        <v>98.34632110595703</v>
       </c>
       <c r="E466" t="n">
-        <v>98.33651886118693</v>
+        <v>98.33652648982164</v>
       </c>
       <c r="F466" t="n">
-        <v>98.3463134765625</v>
+        <v>98.34632110595703</v>
       </c>
       <c r="G466" t="n">
         <v>16658100</v>
@@ -11167,16 +11167,16 @@
         <v>45968</v>
       </c>
       <c r="C467" t="n">
-        <v>98.37569427490234</v>
+        <v>98.37570190429688</v>
       </c>
       <c r="D467" t="n">
-        <v>98.37569427490234</v>
+        <v>98.37570190429688</v>
       </c>
       <c r="E467" t="n">
-        <v>98.36589965908638</v>
+        <v>98.3659072877213</v>
       </c>
       <c r="F467" t="n">
-        <v>98.37569427490234</v>
+        <v>98.37570190429688</v>
       </c>
       <c r="G467" t="n">
         <v>18799000</v>
@@ -11190,16 +11190,16 @@
         <v>45971</v>
       </c>
       <c r="C468" t="n">
-        <v>98.385498046875</v>
+        <v>98.38550567626953</v>
       </c>
       <c r="D468" t="n">
-        <v>98.39529266360249</v>
+        <v>98.39530029375656</v>
       </c>
       <c r="E468" t="n">
-        <v>98.385498046875</v>
+        <v>98.38550567626953</v>
       </c>
       <c r="F468" t="n">
-        <v>98.39529266360249</v>
+        <v>98.39530029375656</v>
       </c>
       <c r="G468" t="n">
         <v>14121900</v>
@@ -11213,16 +11213,16 @@
         <v>45972</v>
       </c>
       <c r="C469" t="n">
-        <v>98.39528656005859</v>
+        <v>98.39529418945312</v>
       </c>
       <c r="D469" t="n">
-        <v>98.39528656005859</v>
+        <v>98.39529418945312</v>
       </c>
       <c r="E469" t="n">
-        <v>98.38549194393867</v>
+        <v>98.38549957257375</v>
       </c>
       <c r="F469" t="n">
-        <v>98.39528656005859</v>
+        <v>98.39529418945312</v>
       </c>
       <c r="G469" t="n">
         <v>8697800</v>
@@ -11236,16 +11236,16 @@
         <v>45973</v>
       </c>
       <c r="C470" t="n">
-        <v>98.40507507324219</v>
+        <v>98.40506744384766</v>
       </c>
       <c r="D470" t="n">
-        <v>98.40507507324219</v>
+        <v>98.40506744384766</v>
       </c>
       <c r="E470" t="n">
-        <v>98.39528792808926</v>
+        <v>98.39528029945352</v>
       </c>
       <c r="F470" t="n">
-        <v>98.39528792808926</v>
+        <v>98.39528029945352</v>
       </c>
       <c r="G470" t="n">
         <v>9067200</v>
@@ -11282,16 +11282,16 @@
         <v>45975</v>
       </c>
       <c r="C472" t="n">
-        <v>98.44425964355469</v>
+        <v>98.44424438476562</v>
       </c>
       <c r="D472" t="n">
-        <v>98.44425964355469</v>
+        <v>98.44424438476562</v>
       </c>
       <c r="E472" t="n">
-        <v>98.43446502594782</v>
+        <v>98.43444976867691</v>
       </c>
       <c r="F472" t="n">
-        <v>98.44425964355469</v>
+        <v>98.44424438476562</v>
       </c>
       <c r="G472" t="n">
         <v>13522500</v>
@@ -11305,16 +11305,16 @@
         <v>45978</v>
       </c>
       <c r="C473" t="n">
-        <v>98.45404815673828</v>
+        <v>98.45404052734375</v>
       </c>
       <c r="D473" t="n">
-        <v>98.45404815673828</v>
+        <v>98.45404052734375</v>
       </c>
       <c r="E473" t="n">
-        <v>98.4442535397387</v>
+        <v>98.44424591110318</v>
       </c>
       <c r="F473" t="n">
-        <v>98.44915458379036</v>
+        <v>98.44914695477505</v>
       </c>
       <c r="G473" t="n">
         <v>15032800</v>
@@ -11328,16 +11328,16 @@
         <v>45979</v>
       </c>
       <c r="C474" t="n">
-        <v>98.45404815673828</v>
+        <v>98.45404052734375</v>
       </c>
       <c r="D474" t="n">
-        <v>98.46384277373785</v>
+        <v>98.46383514358433</v>
       </c>
       <c r="E474" t="n">
-        <v>98.45404815673828</v>
+        <v>98.45404052734375</v>
       </c>
       <c r="F474" t="n">
-        <v>98.45404815673828</v>
+        <v>98.45404052734375</v>
       </c>
       <c r="G474" t="n">
         <v>13130300</v>
@@ -11374,16 +11374,16 @@
         <v>45981</v>
       </c>
       <c r="C476" t="n">
-        <v>98.49321746826172</v>
+        <v>98.49320983886719</v>
       </c>
       <c r="D476" t="n">
-        <v>98.49321746826172</v>
+        <v>98.49320983886719</v>
       </c>
       <c r="E476" t="n">
-        <v>98.47362823459777</v>
+        <v>98.47362060672063</v>
       </c>
       <c r="F476" t="n">
-        <v>98.47362823459777</v>
+        <v>98.47362060672063</v>
       </c>
       <c r="G476" t="n">
         <v>15261700</v>
@@ -11397,16 +11397,16 @@
         <v>45982</v>
       </c>
       <c r="C477" t="n">
-        <v>98.51279449462891</v>
+        <v>98.51278686523438</v>
       </c>
       <c r="D477" t="n">
-        <v>98.51279449462891</v>
+        <v>98.51278686523438</v>
       </c>
       <c r="E477" t="n">
-        <v>98.50299987826783</v>
+        <v>98.50299224963184</v>
       </c>
       <c r="F477" t="n">
-        <v>98.51279449462891</v>
+        <v>98.51278686523438</v>
       </c>
       <c r="G477" t="n">
         <v>16446900</v>
@@ -11420,16 +11420,16 @@
         <v>45985</v>
       </c>
       <c r="C478" t="n">
-        <v>98.5225830078125</v>
+        <v>98.52259063720703</v>
       </c>
       <c r="D478" t="n">
-        <v>98.53237762356683</v>
+        <v>98.53238525371985</v>
       </c>
       <c r="E478" t="n">
-        <v>98.5225830078125</v>
+        <v>98.52259063720703</v>
       </c>
       <c r="F478" t="n">
-        <v>98.5225830078125</v>
+        <v>98.52259063720703</v>
       </c>
       <c r="G478" t="n">
         <v>15830800</v>
@@ -11489,16 +11489,16 @@
         <v>45989</v>
       </c>
       <c r="C481" t="n">
-        <v>98.58133697509766</v>
+        <v>98.58134460449219</v>
       </c>
       <c r="D481" t="n">
-        <v>98.59113159097269</v>
+        <v>98.59113922112526</v>
       </c>
       <c r="E481" t="n">
-        <v>98.57154983032548</v>
+        <v>98.57155745896257</v>
       </c>
       <c r="F481" t="n">
-        <v>98.58133697509766</v>
+        <v>98.58134460449219</v>
       </c>
       <c r="G481" t="n">
         <v>24417500</v>
@@ -11512,16 +11512,16 @@
         <v>45992</v>
       </c>
       <c r="C482" t="n">
-        <v>98.60392761230469</v>
+        <v>98.60391998291016</v>
       </c>
       <c r="D482" t="n">
-        <v>98.60392761230469</v>
+        <v>98.60391998291016</v>
       </c>
       <c r="E482" t="n">
-        <v>98.59410994289308</v>
+        <v>98.59410231425819</v>
       </c>
       <c r="F482" t="n">
-        <v>98.60392761230469</v>
+        <v>98.60391998291016</v>
       </c>
       <c r="G482" t="n">
         <v>29025600</v>
@@ -11581,16 +11581,16 @@
         <v>45995</v>
       </c>
       <c r="C485" t="n">
-        <v>98.65304565429688</v>
+        <v>98.65303802490234</v>
       </c>
       <c r="D485" t="n">
-        <v>98.65304565429688</v>
+        <v>98.65303802490234</v>
       </c>
       <c r="E485" t="n">
-        <v>98.64322049050931</v>
+        <v>98.6432128618746</v>
       </c>
       <c r="F485" t="n">
-        <v>98.64322049050931</v>
+        <v>98.6432128618746</v>
       </c>
       <c r="G485" t="n">
         <v>13689600</v>
@@ -11696,16 +11696,16 @@
         <v>46002</v>
       </c>
       <c r="C490" t="n">
-        <v>98.71198272705078</v>
+        <v>98.71197509765625</v>
       </c>
       <c r="D490" t="n">
-        <v>98.72180789094574</v>
+        <v>98.72180026079182</v>
       </c>
       <c r="E490" t="n">
-        <v>98.71198272705078</v>
+        <v>98.71197509765625</v>
       </c>
       <c r="F490" t="n">
-        <v>98.71198272705078</v>
+        <v>98.71197509765625</v>
       </c>
       <c r="G490" t="n">
         <v>22343500</v>
@@ -11765,16 +11765,16 @@
         <v>46007</v>
       </c>
       <c r="C493" t="n">
-        <v>98.7611083984375</v>
+        <v>98.76111602783203</v>
       </c>
       <c r="D493" t="n">
-        <v>98.77093356306331</v>
+        <v>98.77094119321683</v>
       </c>
       <c r="E493" t="n">
-        <v>98.7611083984375</v>
+        <v>98.76111602783203</v>
       </c>
       <c r="F493" t="n">
-        <v>98.77093356306331</v>
+        <v>98.77094119321683</v>
       </c>
       <c r="G493" t="n">
         <v>10701200</v>
@@ -11788,16 +11788,16 @@
         <v>46008</v>
       </c>
       <c r="C494" t="n">
-        <v>98.78073883056641</v>
+        <v>98.78074645996094</v>
       </c>
       <c r="D494" t="n">
-        <v>98.78073883056641</v>
+        <v>98.78074645996094</v>
       </c>
       <c r="E494" t="n">
-        <v>98.77092116157804</v>
+        <v>98.7709287902143</v>
       </c>
       <c r="F494" t="n">
-        <v>98.77092116157804</v>
+        <v>98.7709287902143</v>
       </c>
       <c r="G494" t="n">
         <v>13788200</v>
@@ -11811,16 +11811,16 @@
         <v>46009</v>
       </c>
       <c r="C495" t="n">
-        <v>98.78073883056641</v>
+        <v>98.78074645996094</v>
       </c>
       <c r="D495" t="n">
-        <v>98.79056399395857</v>
+        <v>98.79057162411196</v>
       </c>
       <c r="E495" t="n">
-        <v>98.78073883056641</v>
+        <v>98.78074645996094</v>
       </c>
       <c r="F495" t="n">
-        <v>98.79056399395857</v>
+        <v>98.79057162411196</v>
       </c>
       <c r="G495" t="n">
         <v>20890600</v>
@@ -11880,16 +11880,16 @@
         <v>46014</v>
       </c>
       <c r="C498" t="n">
-        <v>98.83297729492188</v>
+        <v>98.83296966552734</v>
       </c>
       <c r="D498" t="n">
-        <v>98.84283411907127</v>
+        <v>98.84282648891585</v>
       </c>
       <c r="E498" t="n">
-        <v>98.83297729492188</v>
+        <v>98.83296966552734</v>
       </c>
       <c r="F498" t="n">
-        <v>98.84283411907127</v>
+        <v>98.84282648891585</v>
       </c>
       <c r="G498" t="n">
         <v>12256200</v>
@@ -11949,16 +11949,16 @@
         <v>46020</v>
       </c>
       <c r="C501" t="n">
-        <v>98.90196990966797</v>
+        <v>98.90195465087891</v>
       </c>
       <c r="D501" t="n">
-        <v>98.90196990966797</v>
+        <v>98.90195465087891</v>
       </c>
       <c r="E501" t="n">
-        <v>98.89211308453363</v>
+        <v>98.8920978272653</v>
       </c>
       <c r="F501" t="n">
-        <v>98.89211308453363</v>
+        <v>98.8920978272653</v>
       </c>
       <c r="G501" t="n">
         <v>17350200</v>
@@ -11972,16 +11972,16 @@
         <v>46021</v>
       </c>
       <c r="C502" t="n">
-        <v>98.91181945800781</v>
+        <v>98.91181182861328</v>
       </c>
       <c r="D502" t="n">
-        <v>98.91181945800781</v>
+        <v>98.91181182861328</v>
       </c>
       <c r="E502" t="n">
-        <v>98.90196263359863</v>
+        <v>98.90195500496438</v>
       </c>
       <c r="F502" t="n">
-        <v>98.90688728652617</v>
+        <v>98.90687965751208</v>
       </c>
       <c r="G502" t="n">
         <v>12608900</v>
@@ -11995,16 +11995,16 @@
         <v>46022</v>
       </c>
       <c r="C503" t="n">
-        <v>98.92166900634766</v>
+        <v>98.92166137695312</v>
       </c>
       <c r="D503" t="n">
-        <v>98.931525830781</v>
+        <v>98.93151820062626</v>
       </c>
       <c r="E503" t="n">
-        <v>98.92166900634766</v>
+        <v>98.92166137695312</v>
       </c>
       <c r="F503" t="n">
-        <v>98.931525830781</v>
+        <v>98.93151820062626</v>
       </c>
       <c r="G503" t="n">
         <v>13910900</v>
@@ -12064,16 +12064,16 @@
         <v>46028</v>
       </c>
       <c r="C506" t="n">
-        <v>98.970947265625</v>
+        <v>98.97093963623047</v>
       </c>
       <c r="D506" t="n">
-        <v>98.970947265625</v>
+        <v>98.97093963623047</v>
       </c>
       <c r="E506" t="n">
-        <v>98.970947265625</v>
+        <v>98.97093963623047</v>
       </c>
       <c r="F506" t="n">
-        <v>98.970947265625</v>
+        <v>98.97093963623047</v>
       </c>
       <c r="G506" t="n">
         <v>17635000</v>
@@ -12087,16 +12087,16 @@
         <v>46029</v>
       </c>
       <c r="C507" t="n">
-        <v>98.98079681396484</v>
+        <v>98.98078918457031</v>
       </c>
       <c r="D507" t="n">
-        <v>98.98079681396484</v>
+        <v>98.98078918457031</v>
       </c>
       <c r="E507" t="n">
-        <v>98.98079681396484</v>
+        <v>98.98078918457031</v>
       </c>
       <c r="F507" t="n">
-        <v>98.98079681396484</v>
+        <v>98.98078918457031</v>
       </c>
       <c r="G507" t="n">
         <v>14062300</v>
@@ -12156,16 +12156,16 @@
         <v>46034</v>
       </c>
       <c r="C510" t="n">
-        <v>99.03007507324219</v>
+        <v>99.03006744384766</v>
       </c>
       <c r="D510" t="n">
-        <v>99.03007507324219</v>
+        <v>99.03006744384766</v>
       </c>
       <c r="E510" t="n">
-        <v>99.02022576700949</v>
+        <v>99.02021813837376</v>
       </c>
       <c r="F510" t="n">
-        <v>99.02022576700949</v>
+        <v>99.02021813837376</v>
       </c>
       <c r="G510" t="n">
         <v>14819400</v>
@@ -12179,16 +12179,16 @@
         <v>46035</v>
       </c>
       <c r="C511" t="n">
-        <v>99.03993225097656</v>
+        <v>99.03992462158203</v>
       </c>
       <c r="D511" t="n">
-        <v>99.03993225097656</v>
+        <v>99.03992462158203</v>
       </c>
       <c r="E511" t="n">
-        <v>99.03007542615437</v>
+        <v>99.03006779751914</v>
       </c>
       <c r="F511" t="n">
-        <v>99.03007542615437</v>
+        <v>99.03006779751914</v>
       </c>
       <c r="G511" t="n">
         <v>14163000</v>
@@ -12202,16 +12202,16 @@
         <v>46036</v>
       </c>
       <c r="C512" t="n">
-        <v>99.04978942871094</v>
+        <v>99.04977416992188</v>
       </c>
       <c r="D512" t="n">
-        <v>99.04978942871094</v>
+        <v>99.04977416992188</v>
       </c>
       <c r="E512" t="n">
-        <v>99.03993260385363</v>
+        <v>99.03991734658302</v>
       </c>
       <c r="F512" t="n">
-        <v>99.04978942871094</v>
+        <v>99.04977416992188</v>
       </c>
       <c r="G512" t="n">
         <v>11851800</v>
@@ -12248,16 +12248,16 @@
         <v>46038</v>
       </c>
       <c r="C514" t="n">
-        <v>99.09905242919922</v>
+        <v>99.09906005859375</v>
       </c>
       <c r="D514" t="n">
-        <v>99.09905242919922</v>
+        <v>99.09906005859375</v>
       </c>
       <c r="E514" t="n">
-        <v>99.08427095209834</v>
+        <v>99.08427858035489</v>
       </c>
       <c r="F514" t="n">
-        <v>99.08920312350128</v>
+        <v>99.08921075213753</v>
       </c>
       <c r="G514" t="n">
         <v>14766800</v>
@@ -12271,16 +12271,16 @@
         <v>46042</v>
       </c>
       <c r="C515" t="n">
-        <v>99.09905242919922</v>
+        <v>99.09906005859375</v>
       </c>
       <c r="D515" t="n">
-        <v>99.10890925345112</v>
+        <v>99.10891688360451</v>
       </c>
       <c r="E515" t="n">
-        <v>99.09905242919922</v>
+        <v>99.09906005859375</v>
       </c>
       <c r="F515" t="n">
-        <v>99.09905242919922</v>
+        <v>99.09906005859375</v>
       </c>
       <c r="G515" t="n">
         <v>19394600</v>
@@ -12294,16 +12294,16 @@
         <v>46043</v>
       </c>
       <c r="C516" t="n">
-        <v>99.09905242919922</v>
+        <v>99.09906005859375</v>
       </c>
       <c r="D516" t="n">
-        <v>99.11876607770303</v>
+        <v>99.11877370861527</v>
       </c>
       <c r="E516" t="n">
-        <v>99.09905242919922</v>
+        <v>99.09906005859375</v>
       </c>
       <c r="F516" t="n">
-        <v>99.10398460060216</v>
+        <v>99.10399223037641</v>
       </c>
       <c r="G516" t="n">
         <v>17502100</v>
@@ -12340,16 +12340,16 @@
         <v>46045</v>
       </c>
       <c r="C518" t="n">
-        <v>99.14833068847656</v>
+        <v>99.14833831787109</v>
       </c>
       <c r="D518" t="n">
-        <v>99.14833068847656</v>
+        <v>99.14833831787109</v>
       </c>
       <c r="E518" t="n">
-        <v>99.13847386405996</v>
+        <v>99.13848149269603</v>
       </c>
       <c r="F518" t="n">
-        <v>99.14833068847656</v>
+        <v>99.14833831787109</v>
       </c>
       <c r="G518" t="n">
         <v>12143000</v>
@@ -12432,16 +12432,16 @@
         <v>46051</v>
       </c>
       <c r="C522" t="n">
-        <v>99.187744140625</v>
+        <v>99.18775177001953</v>
       </c>
       <c r="D522" t="n">
-        <v>99.187744140625</v>
+        <v>99.18775177001953</v>
       </c>
       <c r="E522" t="n">
-        <v>99.17788731683716</v>
+        <v>99.1778949454735</v>
       </c>
       <c r="F522" t="n">
-        <v>99.17788731683716</v>
+        <v>99.1778949454735</v>
       </c>
       <c r="G522" t="n">
         <v>16031700</v>
@@ -12455,16 +12455,16 @@
         <v>46052</v>
       </c>
       <c r="C523" t="n">
-        <v>99.20745086669922</v>
+        <v>99.20745849609375</v>
       </c>
       <c r="D523" t="n">
-        <v>99.21730769054639</v>
+        <v>99.21731532069894</v>
       </c>
       <c r="E523" t="n">
-        <v>99.20745086669922</v>
+        <v>99.20745849609375</v>
       </c>
       <c r="F523" t="n">
-        <v>99.20745086669922</v>
+        <v>99.20745849609375</v>
       </c>
       <c r="G523" t="n">
         <v>29215200</v>
@@ -14468,7 +14468,53 @@
         <v>100.4550018310547</v>
       </c>
       <c r="G610" t="n">
-        <v>27080303</v>
+        <v>27836900</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="1" t="n">
+        <v>609</v>
+      </c>
+      <c r="B611" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="C611" t="n">
+        <v>100.4599990844727</v>
+      </c>
+      <c r="D611" t="n">
+        <v>100.4700012207031</v>
+      </c>
+      <c r="E611" t="n">
+        <v>100.4499969482422</v>
+      </c>
+      <c r="F611" t="n">
+        <v>100.4499969482422</v>
+      </c>
+      <c r="G611" t="n">
+        <v>24095700</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="1" t="n">
+        <v>610</v>
+      </c>
+      <c r="B612" s="2" t="n">
+        <v>46182</v>
+      </c>
+      <c r="C612" t="n">
+        <v>100.4630966186523</v>
+      </c>
+      <c r="D612" t="n">
+        <v>100.4700012207031</v>
+      </c>
+      <c r="E612" t="n">
+        <v>100.4599990844727</v>
+      </c>
+      <c r="F612" t="n">
+        <v>100.4700012207031</v>
+      </c>
+      <c r="G612" t="n">
+        <v>24819903</v>
       </c>
     </row>
   </sheetData>

--- a/Data/sgov.xlsx
+++ b/Data/sgov.xlsx
@@ -472,16 +472,16 @@
         <v>45293</v>
       </c>
       <c r="C2" t="n">
-        <v>90.15839385986328</v>
+        <v>90.15837097167969</v>
       </c>
       <c r="D2" t="n">
-        <v>90.16738554925877</v>
+        <v>90.1673626587925</v>
       </c>
       <c r="E2" t="n">
-        <v>90.14940217046778</v>
+        <v>90.14937928456688</v>
       </c>
       <c r="F2" t="n">
-        <v>90.15839385986328</v>
+        <v>90.15837097167969</v>
       </c>
       <c r="G2" t="n">
         <v>5286200</v>
@@ -495,16 +495,16 @@
         <v>45294</v>
       </c>
       <c r="C3" t="n">
-        <v>90.16736602783203</v>
+        <v>90.16737365722656</v>
       </c>
       <c r="D3" t="n">
-        <v>90.18534254408165</v>
+        <v>90.18535017499724</v>
       </c>
       <c r="E3" t="n">
-        <v>90.16736602783203</v>
+        <v>90.16737365722656</v>
       </c>
       <c r="F3" t="n">
-        <v>90.16736602783203</v>
+        <v>90.16737365722656</v>
       </c>
       <c r="G3" t="n">
         <v>4597300</v>
@@ -518,16 +518,16 @@
         <v>45295</v>
       </c>
       <c r="C4" t="n">
-        <v>90.21234130859375</v>
+        <v>90.21230316162109</v>
       </c>
       <c r="D4" t="n">
-        <v>90.2213329990886</v>
+        <v>90.22129484831375</v>
       </c>
       <c r="E4" t="n">
-        <v>90.21234130859375</v>
+        <v>90.21230316162109</v>
       </c>
       <c r="F4" t="n">
-        <v>90.21234130859375</v>
+        <v>90.21230316162109</v>
       </c>
       <c r="G4" t="n">
         <v>2794100</v>
@@ -541,16 +541,16 @@
         <v>45296</v>
       </c>
       <c r="C5" t="n">
-        <v>90.2213134765625</v>
+        <v>90.22132873535156</v>
       </c>
       <c r="D5" t="n">
-        <v>90.23030516511169</v>
+        <v>90.23032042542148</v>
       </c>
       <c r="E5" t="n">
-        <v>90.2213134765625</v>
+        <v>90.22132873535156</v>
       </c>
       <c r="F5" t="n">
-        <v>90.2213134765625</v>
+        <v>90.22132873535156</v>
       </c>
       <c r="G5" t="n">
         <v>3491200</v>
@@ -564,16 +564,16 @@
         <v>45299</v>
       </c>
       <c r="C6" t="n">
-        <v>90.24826812744141</v>
+        <v>90.24827575683594</v>
       </c>
       <c r="D6" t="n">
-        <v>90.24826812744141</v>
+        <v>90.24827575683594</v>
       </c>
       <c r="E6" t="n">
-        <v>90.23927644024286</v>
+        <v>90.23928406887724</v>
       </c>
       <c r="F6" t="n">
-        <v>90.24826812744141</v>
+        <v>90.24827575683594</v>
       </c>
       <c r="G6" t="n">
         <v>2867500</v>
@@ -587,16 +587,16 @@
         <v>45300</v>
       </c>
       <c r="C7" t="n">
-        <v>90.25729370117188</v>
+        <v>90.25727844238281</v>
       </c>
       <c r="D7" t="n">
-        <v>90.25729370117188</v>
+        <v>90.25727844238281</v>
       </c>
       <c r="E7" t="n">
-        <v>90.24830201059746</v>
+        <v>90.24828675332851</v>
       </c>
       <c r="F7" t="n">
-        <v>90.25729370117188</v>
+        <v>90.25727844238281</v>
       </c>
       <c r="G7" t="n">
         <v>2419800</v>
@@ -610,16 +610,16 @@
         <v>45301</v>
       </c>
       <c r="C8" t="n">
-        <v>90.27523040771484</v>
+        <v>90.27524566650391</v>
       </c>
       <c r="D8" t="n">
-        <v>90.27523040771484</v>
+        <v>90.27524566650391</v>
       </c>
       <c r="E8" t="n">
-        <v>90.2662455797535</v>
+        <v>90.26626083702391</v>
       </c>
       <c r="F8" t="n">
-        <v>90.27523040771484</v>
+        <v>90.27524566650391</v>
       </c>
       <c r="G8" t="n">
         <v>1961400</v>
@@ -633,16 +633,16 @@
         <v>45302</v>
       </c>
       <c r="C9" t="n">
-        <v>90.32920074462891</v>
+        <v>90.32919311523438</v>
       </c>
       <c r="D9" t="n">
-        <v>90.32920074462891</v>
+        <v>90.32919311523438</v>
       </c>
       <c r="E9" t="n">
-        <v>90.31121736602117</v>
+        <v>90.31120973814555</v>
       </c>
       <c r="F9" t="n">
-        <v>90.31121736602117</v>
+        <v>90.31120973814555</v>
       </c>
       <c r="G9" t="n">
         <v>3164900</v>
@@ -656,16 +656,16 @@
         <v>45303</v>
       </c>
       <c r="C10" t="n">
-        <v>90.33818817138672</v>
+        <v>90.33817291259766</v>
       </c>
       <c r="D10" t="n">
-        <v>90.33818817138672</v>
+        <v>90.33817291259766</v>
       </c>
       <c r="E10" t="n">
-        <v>90.329203340474</v>
+        <v>90.32918808320254</v>
       </c>
       <c r="F10" t="n">
-        <v>90.329203340474</v>
+        <v>90.32918808320254</v>
       </c>
       <c r="G10" t="n">
         <v>2557900</v>
@@ -679,16 +679,16 @@
         <v>45307</v>
       </c>
       <c r="C11" t="n">
-        <v>90.34719085693359</v>
+        <v>90.34716033935547</v>
       </c>
       <c r="D11" t="n">
-        <v>90.35618254759022</v>
+        <v>90.35615202697488</v>
       </c>
       <c r="E11" t="n">
-        <v>90.34719085693359</v>
+        <v>90.34716033935547</v>
       </c>
       <c r="F11" t="n">
-        <v>90.35618254759022</v>
+        <v>90.35615202697488</v>
       </c>
       <c r="G11" t="n">
         <v>2713000</v>
@@ -702,16 +702,16 @@
         <v>45308</v>
       </c>
       <c r="C12" t="n">
-        <v>90.35617828369141</v>
+        <v>90.35617065429688</v>
       </c>
       <c r="D12" t="n">
-        <v>90.36516311527365</v>
+        <v>90.36515548512048</v>
       </c>
       <c r="E12" t="n">
-        <v>90.35617828369141</v>
+        <v>90.35617065429688</v>
       </c>
       <c r="F12" t="n">
-        <v>90.36516311527365</v>
+        <v>90.36515548512048</v>
       </c>
       <c r="G12" t="n">
         <v>2317700</v>
@@ -725,16 +725,16 @@
         <v>45309</v>
       </c>
       <c r="C13" t="n">
-        <v>90.39211273193359</v>
+        <v>90.39212036132812</v>
       </c>
       <c r="D13" t="n">
-        <v>90.40109756098575</v>
+        <v>90.40110519113864</v>
       </c>
       <c r="E13" t="n">
-        <v>90.39211273193359</v>
+        <v>90.39212036132812</v>
       </c>
       <c r="F13" t="n">
-        <v>90.40109756098575</v>
+        <v>90.40110519113864</v>
       </c>
       <c r="G13" t="n">
         <v>2672000</v>
@@ -748,16 +748,16 @@
         <v>45310</v>
       </c>
       <c r="C14" t="n">
-        <v>90.41907501220703</v>
+        <v>90.41909027099609</v>
       </c>
       <c r="D14" t="n">
-        <v>90.41907501220703</v>
+        <v>90.41909027099609</v>
       </c>
       <c r="E14" t="n">
-        <v>90.40109163798471</v>
+        <v>90.40110689373897</v>
       </c>
       <c r="F14" t="n">
-        <v>90.41008332509587</v>
+        <v>90.41009858236752</v>
       </c>
       <c r="G14" t="n">
         <v>3630100</v>
@@ -771,16 +771,16 @@
         <v>45313</v>
       </c>
       <c r="C15" t="n">
-        <v>90.42808532714844</v>
+        <v>90.42809295654297</v>
       </c>
       <c r="D15" t="n">
-        <v>90.43707701679384</v>
+        <v>90.437084646947</v>
       </c>
       <c r="E15" t="n">
-        <v>90.41910049615264</v>
+        <v>90.41910812478913</v>
       </c>
       <c r="F15" t="n">
-        <v>90.43258460129594</v>
+        <v>90.43259223107009</v>
       </c>
       <c r="G15" t="n">
         <v>4307000</v>
@@ -817,16 +817,16 @@
         <v>45315</v>
       </c>
       <c r="C17" t="n">
-        <v>90.45507049560547</v>
+        <v>90.45505523681641</v>
       </c>
       <c r="D17" t="n">
-        <v>90.45507049560547</v>
+        <v>90.45505523681641</v>
       </c>
       <c r="E17" t="n">
-        <v>90.44607880495612</v>
+        <v>90.44606354768386</v>
       </c>
       <c r="F17" t="n">
-        <v>90.44607880495612</v>
+        <v>90.44606354768386</v>
       </c>
       <c r="G17" t="n">
         <v>3441600</v>
@@ -840,16 +840,16 @@
         <v>45316</v>
       </c>
       <c r="C18" t="n">
-        <v>90.49998474121094</v>
+        <v>90.5</v>
       </c>
       <c r="D18" t="n">
-        <v>90.49998474121094</v>
+        <v>90.5</v>
       </c>
       <c r="E18" t="n">
-        <v>90.48200822461909</v>
+        <v>90.48202348037722</v>
       </c>
       <c r="F18" t="n">
-        <v>90.48200822461909</v>
+        <v>90.48202348037722</v>
       </c>
       <c r="G18" t="n">
         <v>2426000</v>
@@ -863,16 +863,16 @@
         <v>45317</v>
       </c>
       <c r="C19" t="n">
-        <v>90.49998474121094</v>
+        <v>90.5</v>
       </c>
       <c r="D19" t="n">
-        <v>90.50897642883089</v>
+        <v>90.50899168913601</v>
       </c>
       <c r="E19" t="n">
-        <v>90.49998474121094</v>
+        <v>90.5</v>
       </c>
       <c r="F19" t="n">
-        <v>90.50897642883089</v>
+        <v>90.50899168913601</v>
       </c>
       <c r="G19" t="n">
         <v>2059100</v>
@@ -886,16 +886,16 @@
         <v>45320</v>
       </c>
       <c r="C20" t="n">
-        <v>90.50899505615234</v>
+        <v>90.50897979736328</v>
       </c>
       <c r="D20" t="n">
-        <v>90.52697157644387</v>
+        <v>90.52695631462417</v>
       </c>
       <c r="E20" t="n">
-        <v>90.50899505615234</v>
+        <v>90.50897979736328</v>
       </c>
       <c r="F20" t="n">
-        <v>90.51798674562285</v>
+        <v>90.51797148531789</v>
       </c>
       <c r="G20" t="n">
         <v>2914400</v>
@@ -909,16 +909,16 @@
         <v>45321</v>
       </c>
       <c r="C21" t="n">
-        <v>90.53594970703125</v>
+        <v>90.53594207763672</v>
       </c>
       <c r="D21" t="n">
-        <v>90.53594970703125</v>
+        <v>90.53594207763672</v>
       </c>
       <c r="E21" t="n">
-        <v>90.52695801890737</v>
+        <v>90.52695039027056</v>
       </c>
       <c r="F21" t="n">
-        <v>90.52695801890737</v>
+        <v>90.52695039027056</v>
       </c>
       <c r="G21" t="n">
         <v>3741000</v>
@@ -932,16 +932,16 @@
         <v>45322</v>
       </c>
       <c r="C22" t="n">
-        <v>90.53594970703125</v>
+        <v>90.53594207763672</v>
       </c>
       <c r="D22" t="n">
-        <v>90.54494139515513</v>
+        <v>90.54493376500288</v>
       </c>
       <c r="E22" t="n">
-        <v>90.53594970703125</v>
+        <v>90.53594207763672</v>
       </c>
       <c r="F22" t="n">
-        <v>90.53594970703125</v>
+        <v>90.53594207763672</v>
       </c>
       <c r="G22" t="n">
         <v>5171300</v>
@@ -955,16 +955,16 @@
         <v>45323</v>
       </c>
       <c r="C23" t="n">
-        <v>90.58831024169922</v>
+        <v>90.58833312988281</v>
       </c>
       <c r="D23" t="n">
-        <v>90.59734300654796</v>
+        <v>90.5973658970138</v>
       </c>
       <c r="E23" t="n">
-        <v>90.58831024169922</v>
+        <v>90.58833312988281</v>
       </c>
       <c r="F23" t="n">
-        <v>90.59734300654796</v>
+        <v>90.5973658970138</v>
       </c>
       <c r="G23" t="n">
         <v>7038600</v>
@@ -978,16 +978,16 @@
         <v>45324</v>
       </c>
       <c r="C24" t="n">
-        <v>90.59736633300781</v>
+        <v>90.59735870361328</v>
       </c>
       <c r="D24" t="n">
-        <v>90.59736633300781</v>
+        <v>90.59735870361328</v>
       </c>
       <c r="E24" t="n">
-        <v>90.58833356583337</v>
+        <v>90.5883259371995</v>
       </c>
       <c r="F24" t="n">
-        <v>90.59736633300781</v>
+        <v>90.59735870361328</v>
       </c>
       <c r="G24" t="n">
         <v>3864800</v>
@@ -1001,16 +1001,16 @@
         <v>45327</v>
       </c>
       <c r="C25" t="n">
-        <v>90.61540985107422</v>
+        <v>90.61544799804688</v>
       </c>
       <c r="D25" t="n">
-        <v>90.61540985107422</v>
+        <v>90.61544799804688</v>
       </c>
       <c r="E25" t="n">
-        <v>90.60638397538904</v>
+        <v>90.60642211856201</v>
       </c>
       <c r="F25" t="n">
-        <v>90.61540985107422</v>
+        <v>90.61544799804688</v>
       </c>
       <c r="G25" t="n">
         <v>3969400</v>
@@ -1024,16 +1024,16 @@
         <v>45328</v>
       </c>
       <c r="C26" t="n">
-        <v>90.62447357177734</v>
+        <v>90.62442779541016</v>
       </c>
       <c r="D26" t="n">
-        <v>90.63350634052934</v>
+        <v>90.6334605595995</v>
       </c>
       <c r="E26" t="n">
-        <v>90.61544080302535</v>
+        <v>90.61539503122081</v>
       </c>
       <c r="F26" t="n">
-        <v>90.62447357177734</v>
+        <v>90.62442779541016</v>
       </c>
       <c r="G26" t="n">
         <v>2167300</v>
@@ -1047,16 +1047,16 @@
         <v>45329</v>
       </c>
       <c r="C27" t="n">
-        <v>90.64253997802734</v>
+        <v>90.64251708984375</v>
       </c>
       <c r="D27" t="n">
-        <v>90.64253997802734</v>
+        <v>90.64251708984375</v>
       </c>
       <c r="E27" t="n">
-        <v>90.63350720918878</v>
+        <v>90.63348432328605</v>
       </c>
       <c r="F27" t="n">
-        <v>90.64253997802734</v>
+        <v>90.64251708984375</v>
       </c>
       <c r="G27" t="n">
         <v>2621200</v>
@@ -1070,16 +1070,16 @@
         <v>45330</v>
       </c>
       <c r="C28" t="n">
-        <v>90.66961669921875</v>
+        <v>90.66960906982422</v>
       </c>
       <c r="D28" t="n">
-        <v>90.68767534398516</v>
+        <v>90.68766771307108</v>
       </c>
       <c r="E28" t="n">
-        <v>90.66961669921875</v>
+        <v>90.66960906982422</v>
       </c>
       <c r="F28" t="n">
-        <v>90.66961669921875</v>
+        <v>90.66960906982422</v>
       </c>
       <c r="G28" t="n">
         <v>3838700</v>
@@ -1093,16 +1093,16 @@
         <v>45331</v>
       </c>
       <c r="C29" t="n">
-        <v>90.69672393798828</v>
+        <v>90.69670104980469</v>
       </c>
       <c r="D29" t="n">
-        <v>90.69672393798828</v>
+        <v>90.69670104980469</v>
       </c>
       <c r="E29" t="n">
-        <v>90.68317822955406</v>
+        <v>90.68315534478884</v>
       </c>
       <c r="F29" t="n">
-        <v>90.68769116903748</v>
+        <v>90.68766828313339</v>
       </c>
       <c r="G29" t="n">
         <v>3232500</v>
@@ -1116,16 +1116,16 @@
         <v>45334</v>
       </c>
       <c r="C30" t="n">
-        <v>90.69672393798828</v>
+        <v>90.69670104980469</v>
       </c>
       <c r="D30" t="n">
-        <v>90.71478258590592</v>
+        <v>90.71475969316506</v>
       </c>
       <c r="E30" t="n">
-        <v>90.69672393798828</v>
+        <v>90.69670104980469</v>
       </c>
       <c r="F30" t="n">
-        <v>90.70575670693907</v>
+        <v>90.70573381647597</v>
       </c>
       <c r="G30" t="n">
         <v>2792700</v>
@@ -1139,16 +1139,16 @@
         <v>45335</v>
       </c>
       <c r="C31" t="n">
-        <v>90.71474456787109</v>
+        <v>90.71476745605469</v>
       </c>
       <c r="D31" t="n">
-        <v>90.71474456787109</v>
+        <v>90.71476745605469</v>
       </c>
       <c r="E31" t="n">
-        <v>90.70571869268693</v>
+        <v>90.70574157859322</v>
       </c>
       <c r="F31" t="n">
-        <v>90.71474456787109</v>
+        <v>90.71476745605469</v>
       </c>
       <c r="G31" t="n">
         <v>3009000</v>
@@ -1185,16 +1185,16 @@
         <v>45337</v>
       </c>
       <c r="C33" t="n">
-        <v>90.77799224853516</v>
+        <v>90.77798461914062</v>
       </c>
       <c r="D33" t="n">
-        <v>90.7870250168949</v>
+        <v>90.7870173867412</v>
       </c>
       <c r="E33" t="n">
-        <v>90.77799224853516</v>
+        <v>90.77798461914062</v>
       </c>
       <c r="F33" t="n">
-        <v>90.7870250168949</v>
+        <v>90.7870173867412</v>
       </c>
       <c r="G33" t="n">
         <v>2577800</v>
@@ -1208,16 +1208,16 @@
         <v>45338</v>
       </c>
       <c r="C34" t="n">
-        <v>90.78701019287109</v>
+        <v>90.78702545166016</v>
       </c>
       <c r="D34" t="n">
-        <v>90.79604295975592</v>
+        <v>90.79605822006314</v>
       </c>
       <c r="E34" t="n">
-        <v>90.78701019287109</v>
+        <v>90.78702545166016</v>
       </c>
       <c r="F34" t="n">
-        <v>90.79604295975592</v>
+        <v>90.79605822006314</v>
       </c>
       <c r="G34" t="n">
         <v>2920700</v>
@@ -1231,16 +1231,16 @@
         <v>45342</v>
       </c>
       <c r="C35" t="n">
-        <v>90.80507659912109</v>
+        <v>90.80506896972656</v>
       </c>
       <c r="D35" t="n">
-        <v>90.81410247611029</v>
+        <v>90.8140948459574</v>
       </c>
       <c r="E35" t="n">
-        <v>90.79604383214948</v>
+        <v>90.79603620351386</v>
       </c>
       <c r="F35" t="n">
-        <v>90.80507659912109</v>
+        <v>90.80506896972656</v>
       </c>
       <c r="G35" t="n">
         <v>3268600</v>
@@ -1254,16 +1254,16 @@
         <v>45343</v>
       </c>
       <c r="C36" t="n">
-        <v>90.81410217285156</v>
+        <v>90.81411743164062</v>
       </c>
       <c r="D36" t="n">
-        <v>90.83216770673448</v>
+        <v>90.83218296855895</v>
       </c>
       <c r="E36" t="n">
-        <v>90.81410217285156</v>
+        <v>90.81411743164062</v>
       </c>
       <c r="F36" t="n">
-        <v>90.82313493979302</v>
+        <v>90.82315020009979</v>
       </c>
       <c r="G36" t="n">
         <v>2302700</v>
@@ -1277,16 +1277,16 @@
         <v>45344</v>
       </c>
       <c r="C37" t="n">
-        <v>90.8502197265625</v>
+        <v>90.85021209716797</v>
       </c>
       <c r="D37" t="n">
-        <v>90.85925249284537</v>
+        <v>90.85924486269228</v>
       </c>
       <c r="E37" t="n">
-        <v>90.8502197265625</v>
+        <v>90.85021209716797</v>
       </c>
       <c r="F37" t="n">
-        <v>90.8502197265625</v>
+        <v>90.85021209716797</v>
       </c>
       <c r="G37" t="n">
         <v>2452200</v>
@@ -1300,16 +1300,16 @@
         <v>45345</v>
       </c>
       <c r="C38" t="n">
-        <v>90.87730407714844</v>
+        <v>90.87731170654297</v>
       </c>
       <c r="D38" t="n">
-        <v>90.87730407714844</v>
+        <v>90.87731170654297</v>
       </c>
       <c r="E38" t="n">
-        <v>90.86827820154851</v>
+        <v>90.8682858301853</v>
       </c>
       <c r="F38" t="n">
-        <v>90.87730407714844</v>
+        <v>90.87731170654297</v>
       </c>
       <c r="G38" t="n">
         <v>2010100</v>
@@ -1323,16 +1323,16 @@
         <v>45348</v>
       </c>
       <c r="C39" t="n">
-        <v>90.88633728027344</v>
+        <v>90.88632965087891</v>
       </c>
       <c r="D39" t="n">
-        <v>90.89537004589823</v>
+        <v>90.89536241574544</v>
       </c>
       <c r="E39" t="n">
-        <v>90.88633728027344</v>
+        <v>90.88632965087891</v>
       </c>
       <c r="F39" t="n">
-        <v>90.88633728027344</v>
+        <v>90.88632965087891</v>
       </c>
       <c r="G39" t="n">
         <v>2645100</v>
@@ -1369,16 +1369,16 @@
         <v>45350</v>
       </c>
       <c r="C41" t="n">
-        <v>90.91344451904297</v>
+        <v>90.91343688964844</v>
       </c>
       <c r="D41" t="n">
-        <v>90.91344451904297</v>
+        <v>90.91343688964844</v>
       </c>
       <c r="E41" t="n">
-        <v>90.9044186418278</v>
+        <v>90.90441101319072</v>
       </c>
       <c r="F41" t="n">
-        <v>90.9044186418278</v>
+        <v>90.90441101319072</v>
       </c>
       <c r="G41" t="n">
         <v>4526200</v>
@@ -1392,16 +1392,16 @@
         <v>45351</v>
       </c>
       <c r="C42" t="n">
-        <v>90.94052886962891</v>
+        <v>90.94054412841797</v>
       </c>
       <c r="D42" t="n">
-        <v>90.94956163612534</v>
+        <v>90.94957689642999</v>
       </c>
       <c r="E42" t="n">
-        <v>90.94052886962891</v>
+        <v>90.94054412841797</v>
       </c>
       <c r="F42" t="n">
-        <v>90.94052886962891</v>
+        <v>90.94054412841797</v>
       </c>
       <c r="G42" t="n">
         <v>5560200</v>
@@ -1415,16 +1415,16 @@
         <v>45352</v>
       </c>
       <c r="C43" t="n">
-        <v>90.96776580810547</v>
+        <v>90.96774291992188</v>
       </c>
       <c r="D43" t="n">
-        <v>90.96776580810547</v>
+        <v>90.96774291992188</v>
       </c>
       <c r="E43" t="n">
-        <v>90.9586961112458</v>
+        <v>90.95867322534421</v>
       </c>
       <c r="F43" t="n">
-        <v>90.96776580810547</v>
+        <v>90.96774291992188</v>
       </c>
       <c r="G43" t="n">
         <v>7579200</v>
@@ -1438,16 +1438,16 @@
         <v>45355</v>
       </c>
       <c r="C44" t="n">
-        <v>90.97679901123047</v>
+        <v>90.97681427001953</v>
       </c>
       <c r="D44" t="n">
-        <v>90.98586178630309</v>
+        <v>90.98587704661217</v>
       </c>
       <c r="E44" t="n">
-        <v>90.97679901123047</v>
+        <v>90.97681427001953</v>
       </c>
       <c r="F44" t="n">
-        <v>90.97679901123047</v>
+        <v>90.97681427001953</v>
       </c>
       <c r="G44" t="n">
         <v>3613500</v>
@@ -1484,16 +1484,16 @@
         <v>45357</v>
       </c>
       <c r="C46" t="n">
-        <v>91.00399780273438</v>
+        <v>91.00400543212891</v>
       </c>
       <c r="D46" t="n">
-        <v>91.01306749562004</v>
+        <v>91.01307512577493</v>
       </c>
       <c r="E46" t="n">
-        <v>90.99492810984871</v>
+        <v>90.99493573848288</v>
       </c>
       <c r="F46" t="n">
-        <v>91.00399780273438</v>
+        <v>91.00400543212891</v>
       </c>
       <c r="G46" t="n">
         <v>2760000</v>
@@ -1507,16 +1507,16 @@
         <v>45358</v>
       </c>
       <c r="C47" t="n">
-        <v>91.04936981201172</v>
+        <v>91.04934692382812</v>
       </c>
       <c r="D47" t="n">
-        <v>91.04936981201172</v>
+        <v>91.04934692382812</v>
       </c>
       <c r="E47" t="n">
-        <v>91.04030011609154</v>
+        <v>91.04027723018791</v>
       </c>
       <c r="F47" t="n">
-        <v>91.04936981201172</v>
+        <v>91.04934692382812</v>
       </c>
       <c r="G47" t="n">
         <v>2415500</v>
@@ -1530,16 +1530,16 @@
         <v>45359</v>
       </c>
       <c r="C48" t="n">
-        <v>91.05841064453125</v>
+        <v>91.05843353271484</v>
       </c>
       <c r="D48" t="n">
-        <v>91.06748033826561</v>
+        <v>91.06750322872892</v>
       </c>
       <c r="E48" t="n">
-        <v>91.0493478689462</v>
+        <v>91.04937075485179</v>
       </c>
       <c r="F48" t="n">
-        <v>91.06748033826561</v>
+        <v>91.06750322872892</v>
       </c>
       <c r="G48" t="n">
         <v>3748900</v>
@@ -1553,16 +1553,16 @@
         <v>45362</v>
       </c>
       <c r="C49" t="n">
-        <v>91.07656860351562</v>
+        <v>91.0765380859375</v>
       </c>
       <c r="D49" t="n">
-        <v>91.07656860351562</v>
+        <v>91.0765380859375</v>
       </c>
       <c r="E49" t="n">
-        <v>91.06749890793186</v>
+        <v>91.06746839339277</v>
       </c>
       <c r="F49" t="n">
-        <v>91.07656860351562</v>
+        <v>91.0765380859375</v>
       </c>
       <c r="G49" t="n">
         <v>3238400</v>
@@ -1576,16 +1576,16 @@
         <v>45363</v>
       </c>
       <c r="C50" t="n">
-        <v>91.08560943603516</v>
+        <v>91.08561706542969</v>
       </c>
       <c r="D50" t="n">
-        <v>91.0946791294338</v>
+        <v>91.09468675958801</v>
       </c>
       <c r="E50" t="n">
-        <v>91.08560943603516</v>
+        <v>91.08561706542969</v>
       </c>
       <c r="F50" t="n">
-        <v>91.08560943603516</v>
+        <v>91.08561706542969</v>
       </c>
       <c r="G50" t="n">
         <v>2613300</v>
@@ -1599,16 +1599,16 @@
         <v>45364</v>
       </c>
       <c r="C51" t="n">
-        <v>91.09469604492188</v>
+        <v>91.09468841552734</v>
       </c>
       <c r="D51" t="n">
-        <v>91.10376574000468</v>
+        <v>91.10375810985053</v>
       </c>
       <c r="E51" t="n">
-        <v>91.09469604492188</v>
+        <v>91.09468841552734</v>
       </c>
       <c r="F51" t="n">
-        <v>91.09469604492188</v>
+        <v>91.09468841552734</v>
       </c>
       <c r="G51" t="n">
         <v>2249300</v>
@@ -1645,16 +1645,16 @@
         <v>45366</v>
       </c>
       <c r="C53" t="n">
-        <v>91.14910888671875</v>
+        <v>91.14908599853516</v>
       </c>
       <c r="D53" t="n">
-        <v>91.14910888671875</v>
+        <v>91.14908599853516</v>
       </c>
       <c r="E53" t="n">
-        <v>91.14004610894038</v>
+        <v>91.14002322303251</v>
       </c>
       <c r="F53" t="n">
-        <v>91.14910888671875</v>
+        <v>91.14908599853516</v>
       </c>
       <c r="G53" t="n">
         <v>3277300</v>
@@ -1668,16 +1668,16 @@
         <v>45369</v>
       </c>
       <c r="C54" t="n">
-        <v>91.15814971923828</v>
+        <v>91.15816497802734</v>
       </c>
       <c r="D54" t="n">
-        <v>91.16721941229589</v>
+        <v>91.1672346726031</v>
       </c>
       <c r="E54" t="n">
-        <v>91.15814971923828</v>
+        <v>91.15816497802734</v>
       </c>
       <c r="F54" t="n">
-        <v>91.16721941229589</v>
+        <v>91.1672346726031</v>
       </c>
       <c r="G54" t="n">
         <v>3576200</v>
@@ -1691,16 +1691,16 @@
         <v>45370</v>
       </c>
       <c r="C55" t="n">
-        <v>91.17630767822266</v>
+        <v>91.17632293701172</v>
       </c>
       <c r="D55" t="n">
-        <v>91.18537045497759</v>
+        <v>91.18538571528335</v>
       </c>
       <c r="E55" t="n">
-        <v>91.17630767822266</v>
+        <v>91.17632293701172</v>
       </c>
       <c r="F55" t="n">
-        <v>91.18537045497759</v>
+        <v>91.18538571528335</v>
       </c>
       <c r="G55" t="n">
         <v>2661900</v>
@@ -1737,16 +1737,16 @@
         <v>45372</v>
       </c>
       <c r="C57" t="n">
-        <v>91.22162628173828</v>
+        <v>91.22161865234375</v>
       </c>
       <c r="D57" t="n">
-        <v>91.23069597504916</v>
+        <v>91.23068834489608</v>
       </c>
       <c r="E57" t="n">
-        <v>91.22162628173828</v>
+        <v>91.22161865234375</v>
       </c>
       <c r="F57" t="n">
-        <v>91.22162628173828</v>
+        <v>91.22161865234375</v>
       </c>
       <c r="G57" t="n">
         <v>3547400</v>
@@ -1783,16 +1783,16 @@
         <v>45376</v>
       </c>
       <c r="C59" t="n">
-        <v>91.25790405273438</v>
+        <v>91.25791931152344</v>
       </c>
       <c r="D59" t="n">
-        <v>91.26697374663321</v>
+        <v>91.26698900693876</v>
       </c>
       <c r="E59" t="n">
-        <v>91.25790405273438</v>
+        <v>91.25791931152344</v>
       </c>
       <c r="F59" t="n">
-        <v>91.25790405273438</v>
+        <v>91.25791931152344</v>
       </c>
       <c r="G59" t="n">
         <v>2422900</v>
@@ -1806,16 +1806,16 @@
         <v>45377</v>
       </c>
       <c r="C60" t="n">
-        <v>91.26699066162109</v>
+        <v>91.2669677734375</v>
       </c>
       <c r="D60" t="n">
-        <v>91.27606035720085</v>
+        <v>91.27603746674274</v>
       </c>
       <c r="E60" t="n">
-        <v>91.26699066162109</v>
+        <v>91.2669677734375</v>
       </c>
       <c r="F60" t="n">
-        <v>91.26699066162109</v>
+        <v>91.2669677734375</v>
       </c>
       <c r="G60" t="n">
         <v>3181700</v>
@@ -1829,16 +1829,16 @@
         <v>45378</v>
       </c>
       <c r="C61" t="n">
-        <v>91.31230926513672</v>
+        <v>91.31231689453125</v>
       </c>
       <c r="D61" t="n">
-        <v>91.32137895912348</v>
+        <v>91.3213865892758</v>
       </c>
       <c r="E61" t="n">
-        <v>91.31230926513672</v>
+        <v>91.31231689453125</v>
       </c>
       <c r="F61" t="n">
-        <v>91.32137895912348</v>
+        <v>91.3213865892758</v>
       </c>
       <c r="G61" t="n">
         <v>2990800</v>
@@ -1852,16 +1852,16 @@
         <v>45379</v>
       </c>
       <c r="C62" t="n">
-        <v>91.32138824462891</v>
+        <v>91.32136535644531</v>
       </c>
       <c r="D62" t="n">
-        <v>91.33045793953788</v>
+        <v>91.33043504908112</v>
       </c>
       <c r="E62" t="n">
-        <v>91.32138824462891</v>
+        <v>91.32136535644531</v>
       </c>
       <c r="F62" t="n">
-        <v>91.33045793953788</v>
+        <v>91.33043504908112</v>
       </c>
       <c r="G62" t="n">
         <v>5425800</v>
@@ -1898,16 +1898,16 @@
         <v>45384</v>
       </c>
       <c r="C64" t="n">
-        <v>91.36692810058594</v>
+        <v>91.36692047119141</v>
       </c>
       <c r="D64" t="n">
-        <v>91.36692810058594</v>
+        <v>91.36692047119141</v>
       </c>
       <c r="E64" t="n">
-        <v>91.35782464719441</v>
+        <v>91.35781701856003</v>
       </c>
       <c r="F64" t="n">
-        <v>91.36692810058594</v>
+        <v>91.36692047119141</v>
       </c>
       <c r="G64" t="n">
         <v>4202900</v>
@@ -1921,16 +1921,16 @@
         <v>45385</v>
       </c>
       <c r="C65" t="n">
-        <v>91.37604522705078</v>
+        <v>91.37603759765625</v>
       </c>
       <c r="D65" t="n">
-        <v>91.38515563031378</v>
+        <v>91.38514800015857</v>
       </c>
       <c r="E65" t="n">
-        <v>91.37604522705078</v>
+        <v>91.37603759765625</v>
       </c>
       <c r="F65" t="n">
-        <v>91.37604522705078</v>
+        <v>91.37603759765625</v>
       </c>
       <c r="G65" t="n">
         <v>4333600</v>
@@ -1944,16 +1944,16 @@
         <v>45386</v>
       </c>
       <c r="C66" t="n">
-        <v>91.42156982421875</v>
+        <v>91.42158508300781</v>
       </c>
       <c r="D66" t="n">
-        <v>91.42156982421875</v>
+        <v>91.42158508300781</v>
       </c>
       <c r="E66" t="n">
-        <v>91.41245942299565</v>
+        <v>91.41247468026413</v>
       </c>
       <c r="F66" t="n">
-        <v>91.41245942299565</v>
+        <v>91.41247468026413</v>
       </c>
       <c r="G66" t="n">
         <v>3427500</v>
@@ -1967,16 +1967,16 @@
         <v>45387</v>
       </c>
       <c r="C67" t="n">
-        <v>91.43067932128906</v>
+        <v>91.43069458007812</v>
       </c>
       <c r="D67" t="n">
-        <v>91.43978972311452</v>
+        <v>91.439804983424</v>
       </c>
       <c r="E67" t="n">
-        <v>91.43067932128906</v>
+        <v>91.43069458007812</v>
       </c>
       <c r="F67" t="n">
-        <v>91.43978972311452</v>
+        <v>91.439804983424</v>
       </c>
       <c r="G67" t="n">
         <v>3104200</v>
@@ -1990,16 +1990,16 @@
         <v>45390</v>
       </c>
       <c r="C68" t="n">
-        <v>91.44889068603516</v>
+        <v>91.44890594482422</v>
       </c>
       <c r="D68" t="n">
-        <v>91.44889068603516</v>
+        <v>91.44890594482422</v>
       </c>
       <c r="E68" t="n">
-        <v>91.43978028515004</v>
+        <v>91.43979554241898</v>
       </c>
       <c r="F68" t="n">
-        <v>91.44889068603516</v>
+        <v>91.44890594482422</v>
       </c>
       <c r="G68" t="n">
         <v>3511400</v>
@@ -2036,16 +2036,16 @@
         <v>45392</v>
       </c>
       <c r="C70" t="n">
-        <v>91.47624969482422</v>
+        <v>91.47621917724609</v>
       </c>
       <c r="D70" t="n">
-        <v>91.47624969482422</v>
+        <v>91.47621917724609</v>
       </c>
       <c r="E70" t="n">
-        <v>91.4580358353336</v>
+        <v>91.45800532383184</v>
       </c>
       <c r="F70" t="n">
-        <v>91.46713929047772</v>
+        <v>91.46710877593893</v>
       </c>
       <c r="G70" t="n">
         <v>3893100</v>
@@ -2082,16 +2082,16 @@
         <v>45394</v>
       </c>
       <c r="C72" t="n">
-        <v>91.52178192138672</v>
+        <v>91.52177429199219</v>
       </c>
       <c r="D72" t="n">
-        <v>91.52178192138672</v>
+        <v>91.52177429199219</v>
       </c>
       <c r="E72" t="n">
-        <v>91.51267151831894</v>
+        <v>91.51266388968386</v>
       </c>
       <c r="F72" t="n">
-        <v>91.52178192138672</v>
+        <v>91.52177429199219</v>
       </c>
       <c r="G72" t="n">
         <v>4235400</v>
@@ -2105,16 +2105,16 @@
         <v>45397</v>
       </c>
       <c r="C73" t="n">
-        <v>91.53998565673828</v>
+        <v>91.53997039794922</v>
       </c>
       <c r="D73" t="n">
-        <v>91.53998565673828</v>
+        <v>91.53997039794922</v>
       </c>
       <c r="E73" t="n">
-        <v>91.53087525467784</v>
+        <v>91.53085999740739</v>
       </c>
       <c r="F73" t="n">
-        <v>91.53087525467784</v>
+        <v>91.53085999740739</v>
       </c>
       <c r="G73" t="n">
         <v>4144700</v>
@@ -2128,16 +2128,16 @@
         <v>45398</v>
       </c>
       <c r="C74" t="n">
-        <v>91.53998565673828</v>
+        <v>91.53997039794922</v>
       </c>
       <c r="D74" t="n">
-        <v>91.5581995116585</v>
+        <v>91.55818424983336</v>
       </c>
       <c r="E74" t="n">
-        <v>91.53998565673828</v>
+        <v>91.53997039794922</v>
       </c>
       <c r="F74" t="n">
-        <v>91.54909605879871</v>
+        <v>91.54908079849103</v>
       </c>
       <c r="G74" t="n">
         <v>4850000</v>
@@ -2151,16 +2151,16 @@
         <v>45399</v>
       </c>
       <c r="C75" t="n">
-        <v>91.56731414794922</v>
+        <v>91.56729888916016</v>
       </c>
       <c r="D75" t="n">
-        <v>91.56731414794922</v>
+        <v>91.56729888916016</v>
       </c>
       <c r="E75" t="n">
-        <v>91.55820374546751</v>
+        <v>91.55818848819661</v>
       </c>
       <c r="F75" t="n">
-        <v>91.56731414794922</v>
+        <v>91.56729888916016</v>
       </c>
       <c r="G75" t="n">
         <v>3688400</v>
@@ -2220,16 +2220,16 @@
         <v>45404</v>
       </c>
       <c r="C78" t="n">
-        <v>91.63105773925781</v>
+        <v>91.63106536865234</v>
       </c>
       <c r="D78" t="n">
-        <v>91.63105773925781</v>
+        <v>91.63106536865234</v>
       </c>
       <c r="E78" t="n">
-        <v>91.62194733830005</v>
+        <v>91.62195496693603</v>
       </c>
       <c r="F78" t="n">
-        <v>91.63105773925781</v>
+        <v>91.63106536865234</v>
       </c>
       <c r="G78" t="n">
         <v>3547400</v>
@@ -2243,16 +2243,16 @@
         <v>45405</v>
       </c>
       <c r="C79" t="n">
-        <v>91.64017486572266</v>
+        <v>91.64019012451172</v>
       </c>
       <c r="D79" t="n">
-        <v>91.64928526734903</v>
+        <v>91.64930052765506</v>
       </c>
       <c r="E79" t="n">
-        <v>91.63106446409627</v>
+        <v>91.63107972136839</v>
       </c>
       <c r="F79" t="n">
-        <v>91.64017486572266</v>
+        <v>91.64019012451172</v>
       </c>
       <c r="G79" t="n">
         <v>4233300</v>
@@ -2266,16 +2266,16 @@
         <v>45406</v>
       </c>
       <c r="C80" t="n">
-        <v>91.64927673339844</v>
+        <v>91.6492919921875</v>
       </c>
       <c r="D80" t="n">
-        <v>91.65838018497682</v>
+        <v>91.65839544528153</v>
       </c>
       <c r="E80" t="n">
-        <v>91.64927673339844</v>
+        <v>91.6492919921875</v>
       </c>
       <c r="F80" t="n">
-        <v>91.65838018497682</v>
+        <v>91.65839544528153</v>
       </c>
       <c r="G80" t="n">
         <v>3200000</v>
@@ -2289,16 +2289,16 @@
         <v>45407</v>
       </c>
       <c r="C81" t="n">
-        <v>91.69481658935547</v>
+        <v>91.69483184814453</v>
       </c>
       <c r="D81" t="n">
-        <v>91.69481658935547</v>
+        <v>91.69483184814453</v>
       </c>
       <c r="E81" t="n">
-        <v>91.68571313760329</v>
+        <v>91.68572839487747</v>
       </c>
       <c r="F81" t="n">
-        <v>91.69481658935547</v>
+        <v>91.69483184814453</v>
       </c>
       <c r="G81" t="n">
         <v>2705900</v>
@@ -2312,16 +2312,16 @@
         <v>45408</v>
       </c>
       <c r="C82" t="n">
-        <v>91.71302795410156</v>
+        <v>91.71305847167969</v>
       </c>
       <c r="D82" t="n">
-        <v>91.71302795410156</v>
+        <v>91.71305847167969</v>
       </c>
       <c r="E82" t="n">
-        <v>91.70391755408703</v>
+        <v>91.70394806863366</v>
       </c>
       <c r="F82" t="n">
-        <v>91.70391755408703</v>
+        <v>91.70394806863366</v>
       </c>
       <c r="G82" t="n">
         <v>3008600</v>
@@ -2335,16 +2335,16 @@
         <v>45411</v>
       </c>
       <c r="C83" t="n">
-        <v>91.71302795410156</v>
+        <v>91.71305847167969</v>
       </c>
       <c r="D83" t="n">
-        <v>91.72213140491701</v>
+        <v>91.7221619255243</v>
       </c>
       <c r="E83" t="n">
-        <v>91.71302795410156</v>
+        <v>91.71305847167969</v>
       </c>
       <c r="F83" t="n">
-        <v>91.72213140491701</v>
+        <v>91.7221619255243</v>
       </c>
       <c r="G83" t="n">
         <v>2501900</v>
@@ -2358,16 +2358,16 @@
         <v>45412</v>
       </c>
       <c r="C84" t="n">
-        <v>91.72216033935547</v>
+        <v>91.72213745117188</v>
       </c>
       <c r="D84" t="n">
-        <v>91.73127074224395</v>
+        <v>91.73124785178696</v>
       </c>
       <c r="E84" t="n">
-        <v>91.72216033935547</v>
+        <v>91.72213745117188</v>
       </c>
       <c r="F84" t="n">
-        <v>91.72216033935547</v>
+        <v>91.72213745117188</v>
       </c>
       <c r="G84" t="n">
         <v>6488000</v>
@@ -2381,16 +2381,16 @@
         <v>45413</v>
       </c>
       <c r="C85" t="n">
-        <v>91.75689697265625</v>
+        <v>91.75691223144531</v>
       </c>
       <c r="D85" t="n">
-        <v>91.75689697265625</v>
+        <v>91.75691223144531</v>
       </c>
       <c r="E85" t="n">
-        <v>91.74775466424873</v>
+        <v>91.74776992151747</v>
       </c>
       <c r="F85" t="n">
-        <v>91.75689697265625</v>
+        <v>91.75691223144531</v>
       </c>
       <c r="G85" t="n">
         <v>8406600</v>
@@ -2427,16 +2427,16 @@
         <v>45415</v>
       </c>
       <c r="C87" t="n">
-        <v>91.81179046630859</v>
+        <v>91.81181335449219</v>
       </c>
       <c r="D87" t="n">
-        <v>91.81179046630859</v>
+        <v>91.81181335449219</v>
       </c>
       <c r="E87" t="n">
-        <v>91.79349189082433</v>
+        <v>91.79351477444618</v>
       </c>
       <c r="F87" t="n">
-        <v>91.80264117856646</v>
+        <v>91.80266406446918</v>
       </c>
       <c r="G87" t="n">
         <v>4792400</v>
@@ -2450,16 +2450,16 @@
         <v>45418</v>
       </c>
       <c r="C88" t="n">
-        <v>91.82093811035156</v>
+        <v>91.82095336914062</v>
       </c>
       <c r="D88" t="n">
-        <v>91.82093811035156</v>
+        <v>91.82095336914062</v>
       </c>
       <c r="E88" t="n">
-        <v>91.81179580093996</v>
+        <v>91.81181105820977</v>
       </c>
       <c r="F88" t="n">
-        <v>91.81179580093996</v>
+        <v>91.81181105820977</v>
       </c>
       <c r="G88" t="n">
         <v>3623700</v>
@@ -2473,16 +2473,16 @@
         <v>45419</v>
       </c>
       <c r="C89" t="n">
-        <v>91.82093811035156</v>
+        <v>91.82095336914062</v>
       </c>
       <c r="D89" t="n">
-        <v>91.83008739862531</v>
+        <v>91.83010265893481</v>
       </c>
       <c r="E89" t="n">
-        <v>91.82093811035156</v>
+        <v>91.82095336914062</v>
       </c>
       <c r="F89" t="n">
-        <v>91.83008739862531</v>
+        <v>91.83010265893481</v>
       </c>
       <c r="G89" t="n">
         <v>3591500</v>
@@ -2496,16 +2496,16 @@
         <v>45420</v>
       </c>
       <c r="C90" t="n">
-        <v>91.848388671875</v>
+        <v>91.84838104248047</v>
       </c>
       <c r="D90" t="n">
-        <v>91.848388671875</v>
+        <v>91.84838104248047</v>
       </c>
       <c r="E90" t="n">
-        <v>91.83009009479026</v>
+        <v>91.8300824669157</v>
       </c>
       <c r="F90" t="n">
-        <v>91.83923938333263</v>
+        <v>91.83923175469809</v>
       </c>
       <c r="G90" t="n">
         <v>3109400</v>
@@ -2519,16 +2519,16 @@
         <v>45421</v>
       </c>
       <c r="C91" t="n">
-        <v>91.87583923339844</v>
+        <v>91.87582397460938</v>
       </c>
       <c r="D91" t="n">
-        <v>91.88498154404117</v>
+        <v>91.88496628373375</v>
       </c>
       <c r="E91" t="n">
-        <v>91.87583923339844</v>
+        <v>91.87582397460938</v>
       </c>
       <c r="F91" t="n">
-        <v>91.8804103887198</v>
+        <v>91.88039512917156</v>
       </c>
       <c r="G91" t="n">
         <v>2739600</v>
@@ -2542,16 +2542,16 @@
         <v>45422</v>
       </c>
       <c r="C92" t="n">
-        <v>91.90327453613281</v>
+        <v>91.90325927734375</v>
       </c>
       <c r="D92" t="n">
-        <v>91.90327453613281</v>
+        <v>91.90325927734375</v>
       </c>
       <c r="E92" t="n">
-        <v>91.88497595823358</v>
+        <v>91.88496070248264</v>
       </c>
       <c r="F92" t="n">
-        <v>91.90327453613281</v>
+        <v>91.90325927734375</v>
       </c>
       <c r="G92" t="n">
         <v>3005800</v>
@@ -2565,16 +2565,16 @@
         <v>45425</v>
       </c>
       <c r="C93" t="n">
-        <v>91.91242980957031</v>
+        <v>91.91241455078125</v>
       </c>
       <c r="D93" t="n">
-        <v>91.91242980957031</v>
+        <v>91.91241455078125</v>
       </c>
       <c r="E93" t="n">
-        <v>91.90328052002498</v>
+        <v>91.90326526275483</v>
       </c>
       <c r="F93" t="n">
-        <v>91.91242980957031</v>
+        <v>91.91241455078125</v>
       </c>
       <c r="G93" t="n">
         <v>3317000</v>
@@ -2588,16 +2588,16 @@
         <v>45426</v>
       </c>
       <c r="C94" t="n">
-        <v>91.91242980957031</v>
+        <v>91.91241455078125</v>
       </c>
       <c r="D94" t="n">
-        <v>91.92157212025253</v>
+        <v>91.92155685994571</v>
       </c>
       <c r="E94" t="n">
-        <v>91.91242980957031</v>
+        <v>91.91241455078125</v>
       </c>
       <c r="F94" t="n">
-        <v>91.92157212025253</v>
+        <v>91.92155685994571</v>
       </c>
       <c r="G94" t="n">
         <v>2765800</v>
@@ -2611,16 +2611,16 @@
         <v>45427</v>
       </c>
       <c r="C95" t="n">
-        <v>91.93072509765625</v>
+        <v>91.93070983886719</v>
       </c>
       <c r="D95" t="n">
-        <v>91.93987438756861</v>
+        <v>91.93985912726093</v>
       </c>
       <c r="E95" t="n">
-        <v>91.93072509765625</v>
+        <v>91.93070983886719</v>
       </c>
       <c r="F95" t="n">
-        <v>91.93072509765625</v>
+        <v>91.93070983886719</v>
       </c>
       <c r="G95" t="n">
         <v>4228600</v>
@@ -2634,16 +2634,16 @@
         <v>45428</v>
       </c>
       <c r="C96" t="n">
-        <v>91.9764404296875</v>
+        <v>91.97644805908203</v>
       </c>
       <c r="D96" t="n">
-        <v>91.98558273833711</v>
+        <v>91.98559036849001</v>
       </c>
       <c r="E96" t="n">
-        <v>91.96729114217631</v>
+        <v>91.96729877081192</v>
       </c>
       <c r="F96" t="n">
-        <v>91.9764404296875</v>
+        <v>91.97644805908203</v>
       </c>
       <c r="G96" t="n">
         <v>3699500</v>
@@ -2657,16 +2657,16 @@
         <v>45429</v>
       </c>
       <c r="C97" t="n">
-        <v>91.985595703125</v>
+        <v>91.98560333251953</v>
       </c>
       <c r="D97" t="n">
-        <v>91.99474499192573</v>
+        <v>91.9947526220791</v>
       </c>
       <c r="E97" t="n">
-        <v>91.985595703125</v>
+        <v>91.98560333251953</v>
       </c>
       <c r="F97" t="n">
-        <v>91.99474499192573</v>
+        <v>91.9947526220791</v>
       </c>
       <c r="G97" t="n">
         <v>4544200</v>
@@ -2703,16 +2703,16 @@
         <v>45433</v>
       </c>
       <c r="C99" t="n">
-        <v>92.01303863525391</v>
+        <v>92.01301574707031</v>
       </c>
       <c r="D99" t="n">
-        <v>92.02218792425793</v>
+        <v>92.02216503379846</v>
       </c>
       <c r="E99" t="n">
-        <v>92.01303863525391</v>
+        <v>92.01301574707031</v>
       </c>
       <c r="F99" t="n">
-        <v>92.01303863525391</v>
+        <v>92.01301574707031</v>
       </c>
       <c r="G99" t="n">
         <v>3774900</v>
@@ -2726,16 +2726,16 @@
         <v>45434</v>
       </c>
       <c r="C100" t="n">
-        <v>92.02217102050781</v>
+        <v>92.02218627929688</v>
       </c>
       <c r="D100" t="n">
-        <v>92.03132030783118</v>
+        <v>92.03133556813735</v>
       </c>
       <c r="E100" t="n">
-        <v>92.02217102050781</v>
+        <v>92.02218627929688</v>
       </c>
       <c r="F100" t="n">
-        <v>92.03132030783118</v>
+        <v>92.03133556813735</v>
       </c>
       <c r="G100" t="n">
         <v>2609000</v>
@@ -2772,16 +2772,16 @@
         <v>45436</v>
       </c>
       <c r="C102" t="n">
-        <v>92.09535980224609</v>
+        <v>92.09536743164062</v>
       </c>
       <c r="D102" t="n">
-        <v>92.09535980224609</v>
+        <v>92.09536743164062</v>
       </c>
       <c r="E102" t="n">
-        <v>92.08621051408414</v>
+        <v>92.08621814272074</v>
       </c>
       <c r="F102" t="n">
-        <v>92.09535980224609</v>
+        <v>92.09536743164062</v>
       </c>
       <c r="G102" t="n">
         <v>2512800</v>
@@ -2795,16 +2795,16 @@
         <v>45440</v>
       </c>
       <c r="C103" t="n">
-        <v>92.10449981689453</v>
+        <v>92.10452270507812</v>
       </c>
       <c r="D103" t="n">
-        <v>92.10449981689453</v>
+        <v>92.10452270507812</v>
       </c>
       <c r="E103" t="n">
-        <v>92.09535052965379</v>
+        <v>92.09537341556376</v>
       </c>
       <c r="F103" t="n">
-        <v>92.09535052965379</v>
+        <v>92.09537341556376</v>
       </c>
       <c r="G103" t="n">
         <v>3684600</v>
@@ -2818,16 +2818,16 @@
         <v>45441</v>
       </c>
       <c r="C104" t="n">
-        <v>92.10449981689453</v>
+        <v>92.10452270507812</v>
       </c>
       <c r="D104" t="n">
-        <v>92.11364212527393</v>
+        <v>92.1136650157294</v>
       </c>
       <c r="E104" t="n">
-        <v>92.10449981689453</v>
+        <v>92.10452270507812</v>
       </c>
       <c r="F104" t="n">
-        <v>92.11364212527393</v>
+        <v>92.1136650157294</v>
       </c>
       <c r="G104" t="n">
         <v>3971700</v>
@@ -2841,16 +2841,16 @@
         <v>45442</v>
       </c>
       <c r="C105" t="n">
-        <v>92.122802734375</v>
+        <v>92.12279510498047</v>
       </c>
       <c r="D105" t="n">
-        <v>92.13195202274019</v>
+        <v>92.13194439258794</v>
       </c>
       <c r="E105" t="n">
-        <v>92.122802734375</v>
+        <v>92.12279510498047</v>
       </c>
       <c r="F105" t="n">
-        <v>92.122802734375</v>
+        <v>92.12279510498047</v>
       </c>
       <c r="G105" t="n">
         <v>3566800</v>
@@ -2864,16 +2864,16 @@
         <v>45443</v>
       </c>
       <c r="C106" t="n">
-        <v>92.15938568115234</v>
+        <v>92.15940093994141</v>
       </c>
       <c r="D106" t="n">
-        <v>92.15938568115234</v>
+        <v>92.15940093994141</v>
       </c>
       <c r="E106" t="n">
-        <v>92.15023639350471</v>
+        <v>92.15025165077893</v>
       </c>
       <c r="F106" t="n">
-        <v>92.15023639350471</v>
+        <v>92.15025165077893</v>
       </c>
       <c r="G106" t="n">
         <v>7082900</v>
@@ -2887,16 +2887,16 @@
         <v>45446</v>
       </c>
       <c r="C107" t="n">
-        <v>92.17777252197266</v>
+        <v>92.17778015136719</v>
       </c>
       <c r="D107" t="n">
-        <v>92.18695493362199</v>
+        <v>92.18696256377655</v>
       </c>
       <c r="E107" t="n">
-        <v>92.17777252197266</v>
+        <v>92.17778015136719</v>
       </c>
       <c r="F107" t="n">
-        <v>92.17777252197266</v>
+        <v>92.17778015136719</v>
       </c>
       <c r="G107" t="n">
         <v>9568200</v>
@@ -2933,16 +2933,16 @@
         <v>45448</v>
       </c>
       <c r="C109" t="n">
-        <v>92.21450042724609</v>
+        <v>92.21452331542969</v>
       </c>
       <c r="D109" t="n">
-        <v>92.21450042724609</v>
+        <v>92.21452331542969</v>
       </c>
       <c r="E109" t="n">
-        <v>92.20531100839128</v>
+        <v>92.205333894294</v>
       </c>
       <c r="F109" t="n">
-        <v>92.20531100839128</v>
+        <v>92.205333894294</v>
       </c>
       <c r="G109" t="n">
         <v>4285300</v>
@@ -2956,16 +2956,16 @@
         <v>45449</v>
       </c>
       <c r="C110" t="n">
-        <v>92.21450042724609</v>
+        <v>92.21452331542969</v>
       </c>
       <c r="D110" t="n">
-        <v>92.22368283662811</v>
+        <v>92.22370572709083</v>
       </c>
       <c r="E110" t="n">
-        <v>92.21450042724609</v>
+        <v>92.21452331542969</v>
       </c>
       <c r="F110" t="n">
-        <v>92.22368283662811</v>
+        <v>92.22370572709083</v>
       </c>
       <c r="G110" t="n">
         <v>3376100</v>
@@ -2979,16 +2979,16 @@
         <v>45450</v>
       </c>
       <c r="C111" t="n">
-        <v>92.25126647949219</v>
+        <v>92.25125885009766</v>
       </c>
       <c r="D111" t="n">
-        <v>92.2604488904057</v>
+        <v>92.26044126025177</v>
       </c>
       <c r="E111" t="n">
-        <v>92.25126647949219</v>
+        <v>92.25125885009766</v>
       </c>
       <c r="F111" t="n">
-        <v>92.2604488904057</v>
+        <v>92.26044126025177</v>
       </c>
       <c r="G111" t="n">
         <v>3490400</v>
@@ -3002,16 +3002,16 @@
         <v>45453</v>
       </c>
       <c r="C112" t="n">
-        <v>92.26966857910156</v>
+        <v>92.26964569091797</v>
       </c>
       <c r="D112" t="n">
-        <v>92.27885800250358</v>
+        <v>92.27883511204048</v>
       </c>
       <c r="E112" t="n">
-        <v>92.26966857910156</v>
+        <v>92.26964569091797</v>
       </c>
       <c r="F112" t="n">
-        <v>92.27885800250358</v>
+        <v>92.27883511204048</v>
       </c>
       <c r="G112" t="n">
         <v>2732300</v>
@@ -3048,16 +3048,16 @@
         <v>45455</v>
       </c>
       <c r="C114" t="n">
-        <v>92.30640411376953</v>
+        <v>92.306396484375</v>
       </c>
       <c r="D114" t="n">
-        <v>92.30640411376953</v>
+        <v>92.306396484375</v>
       </c>
       <c r="E114" t="n">
-        <v>92.28802526998187</v>
+        <v>92.28801764210641</v>
       </c>
       <c r="F114" t="n">
-        <v>92.29721469187569</v>
+        <v>92.29720706324071</v>
       </c>
       <c r="G114" t="n">
         <v>5355700</v>
@@ -3071,16 +3071,16 @@
         <v>45456</v>
       </c>
       <c r="C115" t="n">
-        <v>92.31558227539062</v>
+        <v>92.31558990478516</v>
       </c>
       <c r="D115" t="n">
-        <v>92.32476468668929</v>
+        <v>92.32477231684271</v>
       </c>
       <c r="E115" t="n">
-        <v>92.30639285461768</v>
+        <v>92.30640048325276</v>
       </c>
       <c r="F115" t="n">
-        <v>92.31558227539062</v>
+        <v>92.31558990478516</v>
       </c>
       <c r="G115" t="n">
         <v>3925700</v>
@@ -3094,16 +3094,16 @@
         <v>45457</v>
       </c>
       <c r="C116" t="n">
-        <v>92.36151885986328</v>
+        <v>92.36151123046875</v>
       </c>
       <c r="D116" t="n">
-        <v>92.36151885986328</v>
+        <v>92.36151123046875</v>
       </c>
       <c r="E116" t="n">
-        <v>92.34314702709557</v>
+        <v>92.34313939921861</v>
       </c>
       <c r="F116" t="n">
-        <v>92.35232943874216</v>
+        <v>92.3523218101067</v>
       </c>
       <c r="G116" t="n">
         <v>3505500</v>
@@ -3117,16 +3117,16 @@
         <v>45460</v>
       </c>
       <c r="C117" t="n">
-        <v>92.37071990966797</v>
+        <v>92.37070465087891</v>
       </c>
       <c r="D117" t="n">
-        <v>92.37071990966797</v>
+        <v>92.37070465087891</v>
       </c>
       <c r="E117" t="n">
-        <v>92.36153048738997</v>
+        <v>92.36151523011891</v>
       </c>
       <c r="F117" t="n">
-        <v>92.37071990966797</v>
+        <v>92.37070465087891</v>
       </c>
       <c r="G117" t="n">
         <v>3493700</v>
@@ -3140,16 +3140,16 @@
         <v>45461</v>
       </c>
       <c r="C118" t="n">
-        <v>92.39825439453125</v>
+        <v>92.39826965332031</v>
       </c>
       <c r="D118" t="n">
-        <v>92.39825439453125</v>
+        <v>92.39826965332031</v>
       </c>
       <c r="E118" t="n">
-        <v>92.3890649749159</v>
+        <v>92.3890802321874</v>
       </c>
       <c r="F118" t="n">
-        <v>92.39825439453125</v>
+        <v>92.39826965332031</v>
       </c>
       <c r="G118" t="n">
         <v>2972000</v>
@@ -3209,16 +3209,16 @@
         <v>45467</v>
       </c>
       <c r="C121" t="n">
-        <v>92.45339202880859</v>
+        <v>92.45338439941406</v>
       </c>
       <c r="D121" t="n">
-        <v>92.46258144992834</v>
+        <v>92.46257381977549</v>
       </c>
       <c r="E121" t="n">
-        <v>92.45339202880859</v>
+        <v>92.45338439941406</v>
       </c>
       <c r="F121" t="n">
-        <v>92.46258144992834</v>
+        <v>92.46257381977549</v>
       </c>
       <c r="G121" t="n">
         <v>3369500</v>
@@ -3232,16 +3232,16 @@
         <v>45468</v>
       </c>
       <c r="C122" t="n">
-        <v>92.47177886962891</v>
+        <v>92.47176361083984</v>
       </c>
       <c r="D122" t="n">
-        <v>92.47177886962891</v>
+        <v>92.47176361083984</v>
       </c>
       <c r="E122" t="n">
-        <v>92.46258944771429</v>
+        <v>92.46257419044157</v>
       </c>
       <c r="F122" t="n">
-        <v>92.47177886962891</v>
+        <v>92.47176361083984</v>
       </c>
       <c r="G122" t="n">
         <v>3561700</v>
@@ -3278,16 +3278,16 @@
         <v>45470</v>
       </c>
       <c r="C124" t="n">
-        <v>92.49015045166016</v>
+        <v>92.49013519287109</v>
       </c>
       <c r="D124" t="n">
-        <v>92.4993398735497</v>
+        <v>92.4993246132446</v>
       </c>
       <c r="E124" t="n">
-        <v>92.49015045166016</v>
+        <v>92.49013519287109</v>
       </c>
       <c r="F124" t="n">
-        <v>92.4993398735497</v>
+        <v>92.4993246132446</v>
       </c>
       <c r="G124" t="n">
         <v>3349900</v>
@@ -3301,16 +3301,16 @@
         <v>45471</v>
       </c>
       <c r="C125" t="n">
-        <v>92.52690124511719</v>
+        <v>92.52688598632812</v>
       </c>
       <c r="D125" t="n">
-        <v>92.53609066701819</v>
+        <v>92.53607540671368</v>
       </c>
       <c r="E125" t="n">
-        <v>92.52690124511719</v>
+        <v>92.52688598632812</v>
       </c>
       <c r="F125" t="n">
-        <v>92.52690124511719</v>
+        <v>92.52688598632812</v>
       </c>
       <c r="G125" t="n">
         <v>7427800</v>
@@ -3347,16 +3347,16 @@
         <v>45475</v>
       </c>
       <c r="C127" t="n">
-        <v>92.57209777832031</v>
+        <v>92.57210540771484</v>
       </c>
       <c r="D127" t="n">
-        <v>92.57209777832031</v>
+        <v>92.57210540771484</v>
       </c>
       <c r="E127" t="n">
-        <v>92.56286812584887</v>
+        <v>92.56287575448273</v>
       </c>
       <c r="F127" t="n">
-        <v>92.57209777832031</v>
+        <v>92.57210540771484</v>
       </c>
       <c r="G127" t="n">
         <v>5720900</v>
@@ -3370,16 +3370,16 @@
         <v>45476</v>
       </c>
       <c r="C128" t="n">
-        <v>92.59978485107422</v>
+        <v>92.59979248046875</v>
       </c>
       <c r="D128" t="n">
-        <v>92.59978485107422</v>
+        <v>92.59979248046875</v>
       </c>
       <c r="E128" t="n">
-        <v>92.59055519808891</v>
+        <v>92.590562826723</v>
       </c>
       <c r="F128" t="n">
-        <v>92.59978485107422</v>
+        <v>92.59979248046875</v>
       </c>
       <c r="G128" t="n">
         <v>3986000</v>
@@ -3393,16 +3393,16 @@
         <v>45478</v>
       </c>
       <c r="C129" t="n">
-        <v>92.63671112060547</v>
+        <v>92.63670349121094</v>
       </c>
       <c r="D129" t="n">
-        <v>92.63671112060547</v>
+        <v>92.63670349121094</v>
       </c>
       <c r="E129" t="n">
-        <v>92.62748146615579</v>
+        <v>92.62747383752138</v>
       </c>
       <c r="F129" t="n">
-        <v>92.62748146615579</v>
+        <v>92.62747383752138</v>
       </c>
       <c r="G129" t="n">
         <v>3742000</v>
@@ -3416,16 +3416,16 @@
         <v>45481</v>
       </c>
       <c r="C130" t="n">
-        <v>92.65514373779297</v>
+        <v>92.65515899658203</v>
       </c>
       <c r="D130" t="n">
-        <v>92.65514373779297</v>
+        <v>92.65515899658203</v>
       </c>
       <c r="E130" t="n">
-        <v>92.64591408600212</v>
+        <v>92.64592934327121</v>
       </c>
       <c r="F130" t="n">
-        <v>92.64591408600212</v>
+        <v>92.64592934327121</v>
       </c>
       <c r="G130" t="n">
         <v>3263000</v>
@@ -3439,16 +3439,16 @@
         <v>45482</v>
       </c>
       <c r="C131" t="n">
-        <v>92.65514373779297</v>
+        <v>92.65515899658203</v>
       </c>
       <c r="D131" t="n">
-        <v>92.67359600121311</v>
+        <v>92.67361126304097</v>
       </c>
       <c r="E131" t="n">
-        <v>92.65514373779297</v>
+        <v>92.65515899658203</v>
       </c>
       <c r="F131" t="n">
-        <v>92.66436634942227</v>
+        <v>92.66438160973014</v>
       </c>
       <c r="G131" t="n">
         <v>4508000</v>
@@ -3462,16 +3462,16 @@
         <v>45483</v>
       </c>
       <c r="C132" t="n">
-        <v>92.67361450195312</v>
+        <v>92.67360687255859</v>
       </c>
       <c r="D132" t="n">
-        <v>92.68284415558651</v>
+        <v>92.68283652543215</v>
       </c>
       <c r="E132" t="n">
-        <v>92.67361450195312</v>
+        <v>92.67360687255859</v>
       </c>
       <c r="F132" t="n">
-        <v>92.67361450195312</v>
+        <v>92.67360687255859</v>
       </c>
       <c r="G132" t="n">
         <v>4062200</v>
@@ -3508,16 +3508,16 @@
         <v>45485</v>
       </c>
       <c r="C134" t="n">
-        <v>92.73821258544922</v>
+        <v>92.73822021484375</v>
       </c>
       <c r="D134" t="n">
-        <v>92.73821258544922</v>
+        <v>92.73822021484375</v>
       </c>
       <c r="E134" t="n">
-        <v>92.72898293135917</v>
+        <v>92.72899055999439</v>
       </c>
       <c r="F134" t="n">
-        <v>92.73821258544922</v>
+        <v>92.73822021484375</v>
       </c>
       <c r="G134" t="n">
         <v>3369000</v>
@@ -3531,16 +3531,16 @@
         <v>45488</v>
       </c>
       <c r="C135" t="n">
-        <v>92.73821258544922</v>
+        <v>92.73822021484375</v>
       </c>
       <c r="D135" t="n">
-        <v>92.74744223953927</v>
+        <v>92.7474498696931</v>
       </c>
       <c r="E135" t="n">
-        <v>92.73821258544922</v>
+        <v>92.73822021484375</v>
       </c>
       <c r="F135" t="n">
-        <v>92.74744223953927</v>
+        <v>92.7474498696931</v>
       </c>
       <c r="G135" t="n">
         <v>3615100</v>
@@ -3554,16 +3554,16 @@
         <v>45489</v>
       </c>
       <c r="C136" t="n">
-        <v>92.75667572021484</v>
+        <v>92.75666809082031</v>
       </c>
       <c r="D136" t="n">
-        <v>92.75667572021484</v>
+        <v>92.75666809082031</v>
       </c>
       <c r="E136" t="n">
-        <v>92.74745310520764</v>
+        <v>92.74744547657168</v>
       </c>
       <c r="F136" t="n">
-        <v>92.75667572021484</v>
+        <v>92.75666809082031</v>
       </c>
       <c r="G136" t="n">
         <v>3622900</v>
@@ -3577,16 +3577,16 @@
         <v>45490</v>
       </c>
       <c r="C137" t="n">
-        <v>92.76589965820312</v>
+        <v>92.76588439941406</v>
       </c>
       <c r="D137" t="n">
-        <v>92.77051800558623</v>
+        <v>92.77050274603751</v>
       </c>
       <c r="E137" t="n">
-        <v>92.75667000360062</v>
+        <v>92.75665474632972</v>
       </c>
       <c r="F137" t="n">
-        <v>92.76589965820312</v>
+        <v>92.76588439941406</v>
       </c>
       <c r="G137" t="n">
         <v>3822100</v>
@@ -3600,16 +3600,16 @@
         <v>45491</v>
       </c>
       <c r="C138" t="n">
-        <v>92.78433227539062</v>
+        <v>92.78435516357422</v>
       </c>
       <c r="D138" t="n">
-        <v>92.78433227539062</v>
+        <v>92.78435516357422</v>
       </c>
       <c r="E138" t="n">
-        <v>92.77510262344329</v>
+        <v>92.77512550935009</v>
       </c>
       <c r="F138" t="n">
-        <v>92.77510262344329</v>
+        <v>92.77512550935009</v>
       </c>
       <c r="G138" t="n">
         <v>5291400</v>
@@ -3623,16 +3623,16 @@
         <v>45492</v>
       </c>
       <c r="C139" t="n">
-        <v>92.82125091552734</v>
+        <v>92.82125854492188</v>
       </c>
       <c r="D139" t="n">
-        <v>92.82125091552734</v>
+        <v>92.82125854492188</v>
       </c>
       <c r="E139" t="n">
-        <v>92.81202830233946</v>
+        <v>92.81203593097594</v>
       </c>
       <c r="F139" t="n">
-        <v>92.82125091552734</v>
+        <v>92.82125854492188</v>
       </c>
       <c r="G139" t="n">
         <v>2993600</v>
@@ -3692,16 +3692,16 @@
         <v>45497</v>
       </c>
       <c r="C142" t="n">
-        <v>92.85816955566406</v>
+        <v>92.85816192626953</v>
       </c>
       <c r="D142" t="n">
-        <v>92.86739920971711</v>
+        <v>92.86739157956426</v>
       </c>
       <c r="E142" t="n">
-        <v>92.8489469417743</v>
+        <v>92.84893931313751</v>
       </c>
       <c r="F142" t="n">
-        <v>92.85816955566406</v>
+        <v>92.85816192626953</v>
       </c>
       <c r="G142" t="n">
         <v>3474500</v>
@@ -3715,16 +3715,16 @@
         <v>45498</v>
       </c>
       <c r="C143" t="n">
-        <v>92.87664794921875</v>
+        <v>92.87660980224609</v>
       </c>
       <c r="D143" t="n">
-        <v>92.87664794921875</v>
+        <v>92.87660980224609</v>
       </c>
       <c r="E143" t="n">
-        <v>92.86741829326908</v>
+        <v>92.8673801500873</v>
       </c>
       <c r="F143" t="n">
-        <v>92.87664794921875</v>
+        <v>92.87660980224609</v>
       </c>
       <c r="G143" t="n">
         <v>3521700</v>
@@ -3738,16 +3738,16 @@
         <v>45499</v>
       </c>
       <c r="C144" t="n">
-        <v>92.90431213378906</v>
+        <v>92.90430450439453</v>
       </c>
       <c r="D144" t="n">
-        <v>92.91354178797603</v>
+        <v>92.91353415782355</v>
       </c>
       <c r="E144" t="n">
-        <v>92.90431213378906</v>
+        <v>92.90430450439453</v>
       </c>
       <c r="F144" t="n">
-        <v>92.90431213378906</v>
+        <v>92.90430450439453</v>
       </c>
       <c r="G144" t="n">
         <v>3172600</v>
@@ -3807,16 +3807,16 @@
         <v>45504</v>
       </c>
       <c r="C147" t="n">
-        <v>92.94118499755859</v>
+        <v>92.94123840332031</v>
       </c>
       <c r="D147" t="n">
-        <v>92.95041464790113</v>
+        <v>92.95046805896638</v>
       </c>
       <c r="E147" t="n">
-        <v>92.94118499755859</v>
+        <v>92.94123840332031</v>
       </c>
       <c r="F147" t="n">
-        <v>92.94118499755859</v>
+        <v>92.94123840332031</v>
       </c>
       <c r="G147" t="n">
         <v>7256900</v>
@@ -3830,16 +3830,16 @@
         <v>45505</v>
       </c>
       <c r="C148" t="n">
-        <v>92.97179412841797</v>
+        <v>92.97181701660156</v>
       </c>
       <c r="D148" t="n">
-        <v>92.97179412841797</v>
+        <v>92.97181701660156</v>
       </c>
       <c r="E148" t="n">
-        <v>92.96252277724977</v>
+        <v>92.96254566315092</v>
       </c>
       <c r="F148" t="n">
-        <v>92.97179412841797</v>
+        <v>92.97181701660156</v>
       </c>
       <c r="G148" t="n">
         <v>11015600</v>
@@ -3853,16 +3853,16 @@
         <v>45506</v>
       </c>
       <c r="C149" t="n">
-        <v>93.01812744140625</v>
+        <v>93.01815795898438</v>
       </c>
       <c r="D149" t="n">
-        <v>93.01812744140625</v>
+        <v>93.01815795898438</v>
       </c>
       <c r="E149" t="n">
-        <v>92.99959181289171</v>
+        <v>92.99962232438862</v>
       </c>
       <c r="F149" t="n">
-        <v>93.00885609116492</v>
+        <v>93.00888660570126</v>
       </c>
       <c r="G149" t="n">
         <v>7927400</v>
@@ -3876,16 +3876,16 @@
         <v>45509</v>
       </c>
       <c r="C150" t="n">
-        <v>93.02742767333984</v>
+        <v>93.02741241455078</v>
       </c>
       <c r="D150" t="n">
-        <v>93.04596330760904</v>
+        <v>93.04594804577968</v>
       </c>
       <c r="E150" t="n">
-        <v>93.01815632022007</v>
+        <v>93.01814106295174</v>
       </c>
       <c r="F150" t="n">
-        <v>93.01815632022007</v>
+        <v>93.01814106295174</v>
       </c>
       <c r="G150" t="n">
         <v>8712900</v>
@@ -3899,16 +3899,16 @@
         <v>45510</v>
       </c>
       <c r="C151" t="n">
-        <v>93.04594421386719</v>
+        <v>93.04593658447266</v>
       </c>
       <c r="D151" t="n">
-        <v>93.04594421386719</v>
+        <v>93.04593658447266</v>
       </c>
       <c r="E151" t="n">
-        <v>93.02740858340164</v>
+        <v>93.02740095552696</v>
       </c>
       <c r="F151" t="n">
-        <v>93.02740858340164</v>
+        <v>93.02740095552696</v>
       </c>
       <c r="G151" t="n">
         <v>5059100</v>
@@ -3922,16 +3922,16 @@
         <v>45511</v>
       </c>
       <c r="C152" t="n">
-        <v>93.04594421386719</v>
+        <v>93.04593658447266</v>
       </c>
       <c r="D152" t="n">
-        <v>93.0552155650844</v>
+        <v>93.05520793492965</v>
       </c>
       <c r="E152" t="n">
-        <v>93.04594421386719</v>
+        <v>93.04593658447266</v>
       </c>
       <c r="F152" t="n">
-        <v>93.04594421386719</v>
+        <v>93.04593658447266</v>
       </c>
       <c r="G152" t="n">
         <v>4611400</v>
@@ -3945,16 +3945,16 @@
         <v>45512</v>
       </c>
       <c r="C153" t="n">
-        <v>93.07374572753906</v>
+        <v>93.07376861572266</v>
       </c>
       <c r="D153" t="n">
-        <v>93.07374572753906</v>
+        <v>93.07376861572266</v>
       </c>
       <c r="E153" t="n">
-        <v>93.05520302760291</v>
+        <v>93.05522591122659</v>
       </c>
       <c r="F153" t="n">
-        <v>93.06447437757099</v>
+        <v>93.06449726347462</v>
       </c>
       <c r="G153" t="n">
         <v>3903300</v>
@@ -3968,16 +3968,16 @@
         <v>45513</v>
       </c>
       <c r="C154" t="n">
-        <v>93.10158538818359</v>
+        <v>93.10157775878906</v>
       </c>
       <c r="D154" t="n">
-        <v>93.11084966943589</v>
+        <v>93.11084203928218</v>
       </c>
       <c r="E154" t="n">
-        <v>93.09231403496088</v>
+        <v>93.0923064063261</v>
       </c>
       <c r="F154" t="n">
-        <v>93.10158538818359</v>
+        <v>93.10157775878906</v>
       </c>
       <c r="G154" t="n">
         <v>5548300</v>
@@ -3991,16 +3991,16 @@
         <v>45516</v>
       </c>
       <c r="C155" t="n">
-        <v>93.12010955810547</v>
+        <v>93.12012481689453</v>
       </c>
       <c r="D155" t="n">
-        <v>93.12938091018674</v>
+        <v>93.12939617049503</v>
       </c>
       <c r="E155" t="n">
-        <v>93.1108382060242</v>
+        <v>93.11085346329405</v>
       </c>
       <c r="F155" t="n">
-        <v>93.12010955810547</v>
+        <v>93.12012481689453</v>
       </c>
       <c r="G155" t="n">
         <v>3845400</v>
@@ -4037,16 +4037,16 @@
         <v>45518</v>
       </c>
       <c r="C157" t="n">
-        <v>93.15721130371094</v>
+        <v>93.15720367431641</v>
       </c>
       <c r="D157" t="n">
-        <v>93.15721130371094</v>
+        <v>93.15720367431641</v>
       </c>
       <c r="E157" t="n">
-        <v>93.13867566686018</v>
+        <v>93.13866803898368</v>
       </c>
       <c r="F157" t="n">
-        <v>93.1479399492999</v>
+        <v>93.14793232066467</v>
       </c>
       <c r="G157" t="n">
         <v>4327700</v>
@@ -4060,16 +4060,16 @@
         <v>45519</v>
       </c>
       <c r="C158" t="n">
-        <v>93.16645050048828</v>
+        <v>93.16645812988281</v>
       </c>
       <c r="D158" t="n">
-        <v>93.16645050048828</v>
+        <v>93.16645812988281</v>
       </c>
       <c r="E158" t="n">
-        <v>93.14790779806644</v>
+        <v>93.14791542594251</v>
       </c>
       <c r="F158" t="n">
-        <v>93.14790779806644</v>
+        <v>93.14791542594251</v>
       </c>
       <c r="G158" t="n">
         <v>4217800</v>
@@ -4083,16 +4083,16 @@
         <v>45520</v>
       </c>
       <c r="C159" t="n">
-        <v>93.20355224609375</v>
+        <v>93.20354461669922</v>
       </c>
       <c r="D159" t="n">
-        <v>93.20355224609375</v>
+        <v>93.20354461669922</v>
       </c>
       <c r="E159" t="n">
-        <v>93.19428089255386</v>
+        <v>93.19427326391828</v>
       </c>
       <c r="F159" t="n">
-        <v>93.20355224609375</v>
+        <v>93.20354461669922</v>
       </c>
       <c r="G159" t="n">
         <v>3638900</v>
@@ -4106,16 +4106,16 @@
         <v>45523</v>
       </c>
       <c r="C160" t="n">
-        <v>93.21280670166016</v>
+        <v>93.21279907226562</v>
       </c>
       <c r="D160" t="n">
-        <v>93.22207805422271</v>
+        <v>93.22207042406932</v>
       </c>
       <c r="E160" t="n">
-        <v>93.21280670166016</v>
+        <v>93.21279907226562</v>
       </c>
       <c r="F160" t="n">
-        <v>93.21280670166016</v>
+        <v>93.21279907226562</v>
       </c>
       <c r="G160" t="n">
         <v>3930700</v>
@@ -4221,16 +4221,16 @@
         <v>45530</v>
       </c>
       <c r="C165" t="n">
-        <v>93.30551147460938</v>
+        <v>93.30550384521484</v>
       </c>
       <c r="D165" t="n">
-        <v>93.3147757557373</v>
+        <v>93.31476812558525</v>
       </c>
       <c r="E165" t="n">
-        <v>93.30551147460938</v>
+        <v>93.30550384521484</v>
       </c>
       <c r="F165" t="n">
-        <v>93.30551147460938</v>
+        <v>93.30550384521484</v>
       </c>
       <c r="G165" t="n">
         <v>3969000</v>
@@ -4267,16 +4267,16 @@
         <v>45532</v>
       </c>
       <c r="C167" t="n">
-        <v>93.32402801513672</v>
+        <v>93.32403564453125</v>
       </c>
       <c r="D167" t="n">
-        <v>93.33329936633808</v>
+        <v>93.33330699649056</v>
       </c>
       <c r="E167" t="n">
-        <v>93.32402801513672</v>
+        <v>93.32403564453125</v>
       </c>
       <c r="F167" t="n">
-        <v>93.33329936633808</v>
+        <v>93.33330699649056</v>
       </c>
       <c r="G167" t="n">
         <v>3500800</v>
@@ -4290,16 +4290,16 @@
         <v>45533</v>
       </c>
       <c r="C168" t="n">
-        <v>93.33332824707031</v>
+        <v>93.33330535888672</v>
       </c>
       <c r="D168" t="n">
-        <v>93.35186388323977</v>
+        <v>93.35184099051068</v>
       </c>
       <c r="E168" t="n">
-        <v>93.33332824707031</v>
+        <v>93.33330535888672</v>
       </c>
       <c r="F168" t="n">
-        <v>93.34259252916951</v>
+        <v>93.34256963871402</v>
       </c>
       <c r="G168" t="n">
         <v>4537700</v>
@@ -4313,16 +4313,16 @@
         <v>45534</v>
       </c>
       <c r="C169" t="n">
-        <v>93.37966156005859</v>
+        <v>93.37965393066406</v>
       </c>
       <c r="D169" t="n">
-        <v>93.38893291320416</v>
+        <v>93.38892528305213</v>
       </c>
       <c r="E169" t="n">
-        <v>93.37966156005859</v>
+        <v>93.37965393066406</v>
       </c>
       <c r="F169" t="n">
-        <v>93.37966156005859</v>
+        <v>93.37965393066406</v>
       </c>
       <c r="G169" t="n">
         <v>8427400</v>
@@ -4359,16 +4359,16 @@
         <v>45539</v>
       </c>
       <c r="C171" t="n">
-        <v>93.42992401123047</v>
+        <v>93.429931640625</v>
       </c>
       <c r="D171" t="n">
-        <v>93.43923640626956</v>
+        <v>93.43924403642453</v>
       </c>
       <c r="E171" t="n">
-        <v>93.42992401123047</v>
+        <v>93.429931640625</v>
       </c>
       <c r="F171" t="n">
-        <v>93.43923640626956</v>
+        <v>93.43924403642453</v>
       </c>
       <c r="G171" t="n">
         <v>7218300</v>
@@ -4405,16 +4405,16 @@
         <v>45541</v>
       </c>
       <c r="C173" t="n">
-        <v>93.49510955810547</v>
+        <v>93.49509429931641</v>
       </c>
       <c r="D173" t="n">
-        <v>93.49510955810547</v>
+        <v>93.49509429931641</v>
       </c>
       <c r="E173" t="n">
-        <v>93.48580426504986</v>
+        <v>93.48578900777946</v>
       </c>
       <c r="F173" t="n">
-        <v>93.49510955810547</v>
+        <v>93.49509429931641</v>
       </c>
       <c r="G173" t="n">
         <v>5534600</v>
@@ -4428,16 +4428,16 @@
         <v>45544</v>
       </c>
       <c r="C174" t="n">
-        <v>93.50440979003906</v>
+        <v>93.50441741943359</v>
       </c>
       <c r="D174" t="n">
-        <v>93.51372218516032</v>
+        <v>93.51372981531469</v>
       </c>
       <c r="E174" t="n">
-        <v>93.50440979003906</v>
+        <v>93.50441741943359</v>
       </c>
       <c r="F174" t="n">
-        <v>93.50440979003906</v>
+        <v>93.50441741943359</v>
       </c>
       <c r="G174" t="n">
         <v>5397400</v>
@@ -4497,16 +4497,16 @@
         <v>45547</v>
       </c>
       <c r="C177" t="n">
-        <v>93.53235626220703</v>
+        <v>93.5323486328125</v>
       </c>
       <c r="D177" t="n">
-        <v>93.54166865896013</v>
+        <v>93.541661028806</v>
       </c>
       <c r="E177" t="n">
-        <v>93.53235626220703</v>
+        <v>93.5323486328125</v>
       </c>
       <c r="F177" t="n">
-        <v>93.54166865896013</v>
+        <v>93.541661028806</v>
       </c>
       <c r="G177" t="n">
         <v>3912400</v>
@@ -4543,16 +4543,16 @@
         <v>45551</v>
       </c>
       <c r="C179" t="n">
-        <v>93.60681915283203</v>
+        <v>93.60683441162109</v>
       </c>
       <c r="D179" t="n">
-        <v>93.60681915283203</v>
+        <v>93.60683441162109</v>
       </c>
       <c r="E179" t="n">
-        <v>93.58819436371842</v>
+        <v>93.58820961947146</v>
       </c>
       <c r="F179" t="n">
-        <v>93.58819436371842</v>
+        <v>93.58820961947146</v>
       </c>
       <c r="G179" t="n">
         <v>3571100</v>
@@ -4566,16 +4566,16 @@
         <v>45552</v>
       </c>
       <c r="C180" t="n">
-        <v>93.60681915283203</v>
+        <v>93.60683441162109</v>
       </c>
       <c r="D180" t="n">
-        <v>93.62543683866987</v>
+        <v>93.62545210049379</v>
       </c>
       <c r="E180" t="n">
-        <v>93.60681915283203</v>
+        <v>93.60683441162109</v>
       </c>
       <c r="F180" t="n">
-        <v>93.61613154738885</v>
+        <v>93.61614680769591</v>
       </c>
       <c r="G180" t="n">
         <v>4452200</v>
@@ -4612,16 +4612,16 @@
         <v>45554</v>
       </c>
       <c r="C182" t="n">
-        <v>93.65337371826172</v>
+        <v>93.65336608886719</v>
       </c>
       <c r="D182" t="n">
-        <v>93.6626861134946</v>
+        <v>93.66267848334145</v>
       </c>
       <c r="E182" t="n">
-        <v>93.64406842630514</v>
+        <v>93.64406079766864</v>
       </c>
       <c r="F182" t="n">
-        <v>93.64406842630514</v>
+        <v>93.64406079766864</v>
       </c>
       <c r="G182" t="n">
         <v>5165800</v>
@@ -4635,16 +4635,16 @@
         <v>45555</v>
       </c>
       <c r="C183" t="n">
-        <v>93.69062042236328</v>
+        <v>93.69059753417969</v>
       </c>
       <c r="D183" t="n">
-        <v>93.69993281801626</v>
+        <v>93.69990992755768</v>
       </c>
       <c r="E183" t="n">
-        <v>93.69062042236328</v>
+        <v>93.69059753417969</v>
       </c>
       <c r="F183" t="n">
-        <v>93.69993281801626</v>
+        <v>93.69990992755768</v>
       </c>
       <c r="G183" t="n">
         <v>4244800</v>
@@ -4658,16 +4658,16 @@
         <v>45558</v>
       </c>
       <c r="C184" t="n">
-        <v>93.71856689453125</v>
+        <v>93.71855926513672</v>
       </c>
       <c r="D184" t="n">
-        <v>93.71856689453125</v>
+        <v>93.71855926513672</v>
       </c>
       <c r="E184" t="n">
-        <v>93.69994210138005</v>
+        <v>93.6999344735017</v>
       </c>
       <c r="F184" t="n">
-        <v>93.70925449795564</v>
+        <v>93.70924686931922</v>
       </c>
       <c r="G184" t="n">
         <v>5220900</v>
@@ -4681,16 +4681,16 @@
         <v>45559</v>
       </c>
       <c r="C185" t="n">
-        <v>93.72786712646484</v>
+        <v>93.72785186767578</v>
       </c>
       <c r="D185" t="n">
-        <v>93.72786712646484</v>
+        <v>93.72785186767578</v>
       </c>
       <c r="E185" t="n">
-        <v>93.71856183366906</v>
+        <v>93.71854657639489</v>
       </c>
       <c r="F185" t="n">
-        <v>93.71856183366906</v>
+        <v>93.71854657639489</v>
       </c>
       <c r="G185" t="n">
         <v>3923500</v>
@@ -4704,16 +4704,16 @@
         <v>45560</v>
       </c>
       <c r="C186" t="n">
-        <v>93.72786712646484</v>
+        <v>93.72785186767578</v>
       </c>
       <c r="D186" t="n">
-        <v>93.7464919186103</v>
+        <v>93.74647665678914</v>
       </c>
       <c r="E186" t="n">
-        <v>93.72786712646484</v>
+        <v>93.72785186767578</v>
       </c>
       <c r="F186" t="n">
-        <v>93.73717952253757</v>
+        <v>93.73716426223247</v>
       </c>
       <c r="G186" t="n">
         <v>3372400</v>
@@ -4727,16 +4727,16 @@
         <v>45561</v>
       </c>
       <c r="C187" t="n">
-        <v>93.73717498779297</v>
+        <v>93.73716735839844</v>
       </c>
       <c r="D187" t="n">
-        <v>93.74648738341519</v>
+        <v>93.74647975326272</v>
       </c>
       <c r="E187" t="n">
-        <v>93.73717498779297</v>
+        <v>93.73716735839844</v>
       </c>
       <c r="F187" t="n">
-        <v>93.73717498779297</v>
+        <v>93.73716735839844</v>
       </c>
       <c r="G187" t="n">
         <v>4364400</v>
@@ -4750,16 +4750,16 @@
         <v>45562</v>
       </c>
       <c r="C188" t="n">
-        <v>93.77442169189453</v>
+        <v>93.77442932128906</v>
       </c>
       <c r="D188" t="n">
-        <v>93.78373408793631</v>
+        <v>93.78374171808849</v>
       </c>
       <c r="E188" t="n">
-        <v>93.77442169189453</v>
+        <v>93.77442932128906</v>
       </c>
       <c r="F188" t="n">
-        <v>93.77442169189453</v>
+        <v>93.77442932128906</v>
       </c>
       <c r="G188" t="n">
         <v>4945400</v>
@@ -4773,16 +4773,16 @@
         <v>45565</v>
       </c>
       <c r="C189" t="n">
-        <v>93.77442169189453</v>
+        <v>93.77442932128906</v>
       </c>
       <c r="D189" t="n">
-        <v>93.79303938070117</v>
+        <v>93.79304701161043</v>
       </c>
       <c r="E189" t="n">
-        <v>93.77442169189453</v>
+        <v>93.77442932128906</v>
       </c>
       <c r="F189" t="n">
-        <v>93.78373408793631</v>
+        <v>93.78374171808849</v>
       </c>
       <c r="G189" t="n">
         <v>9253100</v>
@@ -4796,16 +4796,16 @@
         <v>45566</v>
       </c>
       <c r="C190" t="n">
-        <v>93.81181335449219</v>
+        <v>93.81183624267578</v>
       </c>
       <c r="D190" t="n">
-        <v>93.81181335449219</v>
+        <v>93.81183624267578</v>
       </c>
       <c r="E190" t="n">
-        <v>93.80246103195581</v>
+        <v>93.80248391785763</v>
       </c>
       <c r="F190" t="n">
-        <v>93.81181335449219</v>
+        <v>93.81183624267578</v>
       </c>
       <c r="G190" t="n">
         <v>11569200</v>
@@ -4819,16 +4819,16 @@
         <v>45567</v>
       </c>
       <c r="C191" t="n">
-        <v>93.81181335449219</v>
+        <v>93.81183624267578</v>
       </c>
       <c r="D191" t="n">
-        <v>93.82115854329665</v>
+        <v>93.82118143376027</v>
       </c>
       <c r="E191" t="n">
-        <v>93.81181335449219</v>
+        <v>93.81183624267578</v>
       </c>
       <c r="F191" t="n">
-        <v>93.82115854329665</v>
+        <v>93.82118143376027</v>
       </c>
       <c r="G191" t="n">
         <v>5170300</v>
@@ -4934,16 +4934,16 @@
         <v>45574</v>
       </c>
       <c r="C196" t="n">
-        <v>93.89596557617188</v>
+        <v>93.89595794677734</v>
       </c>
       <c r="D196" t="n">
-        <v>93.90531789897918</v>
+        <v>93.90531026882472</v>
       </c>
       <c r="E196" t="n">
-        <v>93.8866203870967</v>
+        <v>93.8866127584615</v>
       </c>
       <c r="F196" t="n">
-        <v>93.89596557617188</v>
+        <v>93.89595794677734</v>
       </c>
       <c r="G196" t="n">
         <v>4024800</v>
@@ -4957,16 +4957,16 @@
         <v>45575</v>
       </c>
       <c r="C197" t="n">
-        <v>93.91468048095703</v>
+        <v>93.9146728515625</v>
       </c>
       <c r="D197" t="n">
-        <v>93.91468048095703</v>
+        <v>93.9146728515625</v>
       </c>
       <c r="E197" t="n">
-        <v>93.9053281571281</v>
+        <v>93.90532052849332</v>
       </c>
       <c r="F197" t="n">
-        <v>93.91468048095703</v>
+        <v>93.9146728515625</v>
       </c>
       <c r="G197" t="n">
         <v>3731100</v>
@@ -4980,16 +4980,16 @@
         <v>45576</v>
       </c>
       <c r="C198" t="n">
-        <v>93.95206451416016</v>
+        <v>93.95207977294922</v>
       </c>
       <c r="D198" t="n">
-        <v>93.96140970245301</v>
+        <v>93.96142496275984</v>
       </c>
       <c r="E198" t="n">
-        <v>93.95206451416016</v>
+        <v>93.95207977294922</v>
       </c>
       <c r="F198" t="n">
-        <v>93.95206451416016</v>
+        <v>93.95207977294922</v>
       </c>
       <c r="G198" t="n">
         <v>3778400</v>
@@ -5003,16 +5003,16 @@
         <v>45579</v>
       </c>
       <c r="C199" t="n">
-        <v>93.95206451416016</v>
+        <v>93.95207977294922</v>
       </c>
       <c r="D199" t="n">
-        <v>93.96140970245301</v>
+        <v>93.96142496275984</v>
       </c>
       <c r="E199" t="n">
-        <v>93.95206451416016</v>
+        <v>93.95207977294922</v>
       </c>
       <c r="F199" t="n">
-        <v>93.95206451416016</v>
+        <v>93.95207977294922</v>
       </c>
       <c r="G199" t="n">
         <v>3297100</v>
@@ -5026,16 +5026,16 @@
         <v>45580</v>
       </c>
       <c r="C200" t="n">
-        <v>93.97079467773438</v>
+        <v>93.97076416015625</v>
       </c>
       <c r="D200" t="n">
-        <v>93.97079467773438</v>
+        <v>93.97076416015625</v>
       </c>
       <c r="E200" t="n">
-        <v>93.96144235246022</v>
+        <v>93.96141183791931</v>
       </c>
       <c r="F200" t="n">
-        <v>93.97079467773438</v>
+        <v>93.97076416015625</v>
       </c>
       <c r="G200" t="n">
         <v>3567400</v>
@@ -5049,16 +5049,16 @@
         <v>45581</v>
       </c>
       <c r="C201" t="n">
-        <v>93.98947143554688</v>
+        <v>93.98946380615234</v>
       </c>
       <c r="D201" t="n">
-        <v>93.98947143554688</v>
+        <v>93.98946380615234</v>
       </c>
       <c r="E201" t="n">
-        <v>93.98012624607075</v>
+        <v>93.9801186174348</v>
       </c>
       <c r="F201" t="n">
-        <v>93.98012624607075</v>
+        <v>93.9801186174348</v>
       </c>
       <c r="G201" t="n">
         <v>3809900</v>
@@ -5072,16 +5072,16 @@
         <v>45582</v>
       </c>
       <c r="C202" t="n">
-        <v>93.98947143554688</v>
+        <v>93.98946380615234</v>
       </c>
       <c r="D202" t="n">
-        <v>93.99882375875542</v>
+        <v>93.99881612860175</v>
       </c>
       <c r="E202" t="n">
-        <v>93.98947143554688</v>
+        <v>93.98946380615234</v>
       </c>
       <c r="F202" t="n">
-        <v>93.98947143554688</v>
+        <v>93.98946380615234</v>
       </c>
       <c r="G202" t="n">
         <v>3575500</v>
@@ -5095,16 +5095,16 @@
         <v>45583</v>
       </c>
       <c r="C203" t="n">
-        <v>94.02687072753906</v>
+        <v>94.02686309814453</v>
       </c>
       <c r="D203" t="n">
-        <v>94.03622305046243</v>
+        <v>94.03621542030905</v>
       </c>
       <c r="E203" t="n">
-        <v>94.0175255383479</v>
+        <v>94.01751790971164</v>
       </c>
       <c r="F203" t="n">
-        <v>94.03622305046243</v>
+        <v>94.03621542030905</v>
       </c>
       <c r="G203" t="n">
         <v>3970200</v>
@@ -5118,16 +5118,16 @@
         <v>45586</v>
       </c>
       <c r="C204" t="n">
-        <v>94.04557037353516</v>
+        <v>94.04558563232422</v>
       </c>
       <c r="D204" t="n">
-        <v>94.04557037353516</v>
+        <v>94.04558563232422</v>
       </c>
       <c r="E204" t="n">
-        <v>94.03621805110899</v>
+        <v>94.03623330838064</v>
       </c>
       <c r="F204" t="n">
-        <v>94.03621805110899</v>
+        <v>94.03623330838064</v>
       </c>
       <c r="G204" t="n">
         <v>3940600</v>
@@ -5141,16 +5141,16 @@
         <v>45587</v>
       </c>
       <c r="C205" t="n">
-        <v>94.05491638183594</v>
+        <v>94.05490875244141</v>
       </c>
       <c r="D205" t="n">
-        <v>94.05491638183594</v>
+        <v>94.05490875244141</v>
       </c>
       <c r="E205" t="n">
-        <v>94.04557119306016</v>
+        <v>94.04556356442367</v>
       </c>
       <c r="F205" t="n">
-        <v>94.05491638183594</v>
+        <v>94.05490875244141</v>
       </c>
       <c r="G205" t="n">
         <v>3462800</v>
@@ -5164,16 +5164,16 @@
         <v>45588</v>
       </c>
       <c r="C206" t="n">
-        <v>94.05491638183594</v>
+        <v>94.05490875244141</v>
       </c>
       <c r="D206" t="n">
-        <v>94.07362102685126</v>
+        <v>94.07361339593947</v>
       </c>
       <c r="E206" t="n">
-        <v>94.05491638183594</v>
+        <v>94.05490875244141</v>
       </c>
       <c r="F206" t="n">
-        <v>94.07362102685126</v>
+        <v>94.07361339593947</v>
       </c>
       <c r="G206" t="n">
         <v>3927700</v>
@@ -5187,16 +5187,16 @@
         <v>45589</v>
       </c>
       <c r="C207" t="n">
-        <v>94.08297729492188</v>
+        <v>94.08298492431641</v>
       </c>
       <c r="D207" t="n">
-        <v>94.08297729492188</v>
+        <v>94.08298492431641</v>
       </c>
       <c r="E207" t="n">
-        <v>94.073624972022</v>
+        <v>94.07363260065813</v>
       </c>
       <c r="F207" t="n">
-        <v>94.08297729492188</v>
+        <v>94.08298492431641</v>
       </c>
       <c r="G207" t="n">
         <v>3704500</v>
@@ -5210,16 +5210,16 @@
         <v>45590</v>
       </c>
       <c r="C208" t="n">
-        <v>94.12038421630859</v>
+        <v>94.12039184570312</v>
       </c>
       <c r="D208" t="n">
-        <v>94.12038421630859</v>
+        <v>94.12039184570312</v>
       </c>
       <c r="E208" t="n">
-        <v>94.11103189293539</v>
+        <v>94.11103952157183</v>
       </c>
       <c r="F208" t="n">
-        <v>94.11103189293539</v>
+        <v>94.11103952157183</v>
       </c>
       <c r="G208" t="n">
         <v>5386900</v>
@@ -5233,16 +5233,16 @@
         <v>45593</v>
       </c>
       <c r="C209" t="n">
-        <v>94.12038421630859</v>
+        <v>94.12039184570312</v>
       </c>
       <c r="D209" t="n">
-        <v>94.12972940594925</v>
+        <v>94.12973703610129</v>
       </c>
       <c r="E209" t="n">
-        <v>94.12038421630859</v>
+        <v>94.12039184570312</v>
       </c>
       <c r="F209" t="n">
-        <v>94.12972940594925</v>
+        <v>94.12973703610129</v>
       </c>
       <c r="G209" t="n">
         <v>3471300</v>
@@ -5256,16 +5256,16 @@
         <v>45594</v>
       </c>
       <c r="C210" t="n">
-        <v>94.13906860351562</v>
+        <v>94.13907623291016</v>
       </c>
       <c r="D210" t="n">
-        <v>94.13906860351562</v>
+        <v>94.13907623291016</v>
       </c>
       <c r="E210" t="n">
-        <v>94.1250436872776</v>
+        <v>94.12505131553549</v>
       </c>
       <c r="F210" t="n">
-        <v>94.12971628144642</v>
+        <v>94.129723910083</v>
       </c>
       <c r="G210" t="n">
         <v>3449900</v>
@@ -5279,16 +5279,16 @@
         <v>45595</v>
       </c>
       <c r="C211" t="n">
-        <v>94.13906860351562</v>
+        <v>94.13907623291016</v>
       </c>
       <c r="D211" t="n">
-        <v>94.15776611392248</v>
+        <v>94.15777374483233</v>
       </c>
       <c r="E211" t="n">
-        <v>94.13906860351562</v>
+        <v>94.13907623291016</v>
       </c>
       <c r="F211" t="n">
-        <v>94.14842092558483</v>
+        <v>94.14842855573731</v>
       </c>
       <c r="G211" t="n">
         <v>7059200</v>
@@ -5302,16 +5302,16 @@
         <v>45596</v>
       </c>
       <c r="C212" t="n">
-        <v>94.15777587890625</v>
+        <v>94.15778350830078</v>
       </c>
       <c r="D212" t="n">
-        <v>94.16712820194537</v>
+        <v>94.16713583209771</v>
       </c>
       <c r="E212" t="n">
-        <v>94.14843068959942</v>
+        <v>94.14843831823674</v>
       </c>
       <c r="F212" t="n">
-        <v>94.14843068959942</v>
+        <v>94.14843831823674</v>
       </c>
       <c r="G212" t="n">
         <v>11321100</v>
@@ -5348,16 +5348,16 @@
         <v>45600</v>
       </c>
       <c r="C214" t="n">
-        <v>94.21880340576172</v>
+        <v>94.21879577636719</v>
       </c>
       <c r="D214" t="n">
-        <v>94.22725604425263</v>
+        <v>94.22724841417364</v>
       </c>
       <c r="E214" t="n">
-        <v>94.20941238113326</v>
+        <v>94.20940475249917</v>
       </c>
       <c r="F214" t="n">
-        <v>94.21880340576172</v>
+        <v>94.21879577636719</v>
       </c>
       <c r="G214" t="n">
         <v>5041500</v>
@@ -5371,16 +5371,16 @@
         <v>45601</v>
       </c>
       <c r="C215" t="n">
-        <v>94.23760223388672</v>
+        <v>94.23757934570312</v>
       </c>
       <c r="D215" t="n">
-        <v>94.23760223388672</v>
+        <v>94.23757934570312</v>
       </c>
       <c r="E215" t="n">
-        <v>94.21882018128569</v>
+        <v>94.21879729766383</v>
       </c>
       <c r="F215" t="n">
-        <v>94.22821120758621</v>
+        <v>94.22818832168348</v>
       </c>
       <c r="G215" t="n">
         <v>4280500</v>
@@ -5394,16 +5394,16 @@
         <v>45602</v>
       </c>
       <c r="C216" t="n">
-        <v>94.23760223388672</v>
+        <v>94.23757934570312</v>
       </c>
       <c r="D216" t="n">
-        <v>94.246986096933</v>
+        <v>94.24696320647028</v>
       </c>
       <c r="E216" t="n">
-        <v>94.22821120758621</v>
+        <v>94.22818832168348</v>
       </c>
       <c r="F216" t="n">
-        <v>94.22821120758621</v>
+        <v>94.22818832168348</v>
       </c>
       <c r="G216" t="n">
         <v>9470900</v>
@@ -5417,16 +5417,16 @@
         <v>45603</v>
       </c>
       <c r="C217" t="n">
-        <v>94.25634765625</v>
+        <v>94.25635528564453</v>
       </c>
       <c r="D217" t="n">
-        <v>94.25634765625</v>
+        <v>94.25635528564453</v>
       </c>
       <c r="E217" t="n">
-        <v>94.24695663288537</v>
+        <v>94.24696426151975</v>
       </c>
       <c r="F217" t="n">
-        <v>94.24695663288537</v>
+        <v>94.24696426151975</v>
       </c>
       <c r="G217" t="n">
         <v>6188100</v>
@@ -5440,16 +5440,16 @@
         <v>45604</v>
       </c>
       <c r="C218" t="n">
-        <v>94.30331420898438</v>
+        <v>94.30332183837891</v>
       </c>
       <c r="D218" t="n">
-        <v>94.30331420898438</v>
+        <v>94.30332183837891</v>
       </c>
       <c r="E218" t="n">
-        <v>94.28453215855077</v>
+        <v>94.28453978642578</v>
       </c>
       <c r="F218" t="n">
-        <v>94.29392318376757</v>
+        <v>94.29393081240234</v>
       </c>
       <c r="G218" t="n">
         <v>5624200</v>
@@ -5463,16 +5463,16 @@
         <v>45607</v>
       </c>
       <c r="C219" t="n">
-        <v>94.29390716552734</v>
+        <v>94.29393005371094</v>
       </c>
       <c r="D219" t="n">
-        <v>94.30329818914883</v>
+        <v>94.30332107961193</v>
       </c>
       <c r="E219" t="n">
-        <v>94.28921523534268</v>
+        <v>94.2892381223874</v>
       </c>
       <c r="F219" t="n">
-        <v>94.29390716552734</v>
+        <v>94.29393005371094</v>
       </c>
       <c r="G219" t="n">
         <v>4443700</v>
@@ -5486,16 +5486,16 @@
         <v>45608</v>
       </c>
       <c r="C220" t="n">
-        <v>94.30331420898438</v>
+        <v>94.30332183837891</v>
       </c>
       <c r="D220" t="n">
-        <v>94.31269807094777</v>
+        <v>94.31270570110148</v>
       </c>
       <c r="E220" t="n">
-        <v>94.30331420898438</v>
+        <v>94.30332183837891</v>
       </c>
       <c r="F220" t="n">
-        <v>94.31269807094777</v>
+        <v>94.31270570110148</v>
       </c>
       <c r="G220" t="n">
         <v>4283300</v>
@@ -5509,16 +5509,16 @@
         <v>45609</v>
       </c>
       <c r="C221" t="n">
-        <v>94.33146667480469</v>
+        <v>94.33148193359375</v>
       </c>
       <c r="D221" t="n">
-        <v>94.33146667480469</v>
+        <v>94.33148193359375</v>
       </c>
       <c r="E221" t="n">
-        <v>94.3126846270484</v>
+        <v>94.31269988279932</v>
       </c>
       <c r="F221" t="n">
-        <v>94.32207565092654</v>
+        <v>94.32209090819653</v>
       </c>
       <c r="G221" t="n">
         <v>4818000</v>
@@ -5532,16 +5532,16 @@
         <v>45610</v>
       </c>
       <c r="C222" t="n">
-        <v>94.33146667480469</v>
+        <v>94.33148193359375</v>
       </c>
       <c r="D222" t="n">
-        <v>94.34085769868284</v>
+        <v>94.34087295899096</v>
       </c>
       <c r="E222" t="n">
-        <v>94.33146667480469</v>
+        <v>94.33148193359375</v>
       </c>
       <c r="F222" t="n">
-        <v>94.34085769868284</v>
+        <v>94.34087295899096</v>
       </c>
       <c r="G222" t="n">
         <v>4353200</v>
@@ -5578,16 +5578,16 @@
         <v>45614</v>
       </c>
       <c r="C224" t="n">
-        <v>94.38780212402344</v>
+        <v>94.38780975341797</v>
       </c>
       <c r="D224" t="n">
-        <v>94.38780212402344</v>
+        <v>94.38780975341797</v>
       </c>
       <c r="E224" t="n">
-        <v>94.37841109978388</v>
+        <v>94.37841872841933</v>
       </c>
       <c r="F224" t="n">
-        <v>94.38780212402344</v>
+        <v>94.38780975341797</v>
       </c>
       <c r="G224" t="n">
         <v>5567500</v>
@@ -5601,16 +5601,16 @@
         <v>45615</v>
       </c>
       <c r="C225" t="n">
-        <v>94.39717864990234</v>
+        <v>94.39719390869141</v>
       </c>
       <c r="D225" t="n">
-        <v>94.39717864990234</v>
+        <v>94.39719390869141</v>
       </c>
       <c r="E225" t="n">
-        <v>94.38778762710514</v>
+        <v>94.3878028843762</v>
       </c>
       <c r="F225" t="n">
-        <v>94.39717864990234</v>
+        <v>94.39719390869141</v>
       </c>
       <c r="G225" t="n">
         <v>4310900</v>
@@ -5624,16 +5624,16 @@
         <v>45616</v>
       </c>
       <c r="C226" t="n">
-        <v>94.41596221923828</v>
+        <v>94.41596984863281</v>
       </c>
       <c r="D226" t="n">
-        <v>94.41596221923828</v>
+        <v>94.41596984863281</v>
       </c>
       <c r="E226" t="n">
-        <v>94.397187335168</v>
+        <v>94.39719496304541</v>
       </c>
       <c r="F226" t="n">
-        <v>94.40657835882925</v>
+        <v>94.4065859874655</v>
       </c>
       <c r="G226" t="n">
         <v>4133000</v>
@@ -5647,16 +5647,16 @@
         <v>45617</v>
       </c>
       <c r="C227" t="n">
-        <v>94.41596221923828</v>
+        <v>94.41596984863281</v>
       </c>
       <c r="D227" t="n">
-        <v>94.42535324289952</v>
+        <v>94.42536087305291</v>
       </c>
       <c r="E227" t="n">
-        <v>94.41596221923828</v>
+        <v>94.41596984863281</v>
       </c>
       <c r="F227" t="n">
-        <v>94.42535324289952</v>
+        <v>94.42536087305291</v>
       </c>
       <c r="G227" t="n">
         <v>4410700</v>
@@ -5716,16 +5716,16 @@
         <v>45622</v>
       </c>
       <c r="C230" t="n">
-        <v>94.47231292724609</v>
+        <v>94.47232818603516</v>
       </c>
       <c r="D230" t="n">
-        <v>94.48169678882019</v>
+        <v>94.48171204912488</v>
       </c>
       <c r="E230" t="n">
-        <v>94.4629219024189</v>
+        <v>94.46293715969117</v>
       </c>
       <c r="F230" t="n">
-        <v>94.47231292724609</v>
+        <v>94.47232818603516</v>
       </c>
       <c r="G230" t="n">
         <v>4586900</v>
@@ -5739,16 +5739,16 @@
         <v>45623</v>
       </c>
       <c r="C231" t="n">
-        <v>94.49106597900391</v>
+        <v>94.49108123779297</v>
       </c>
       <c r="D231" t="n">
-        <v>94.50045700166106</v>
+        <v>94.50047226196662</v>
       </c>
       <c r="E231" t="n">
-        <v>94.49106597900391</v>
+        <v>94.49108123779297</v>
       </c>
       <c r="F231" t="n">
-        <v>94.49106597900391</v>
+        <v>94.49108123779297</v>
       </c>
       <c r="G231" t="n">
         <v>5909000</v>
@@ -5762,16 +5762,16 @@
         <v>45625</v>
       </c>
       <c r="C232" t="n">
-        <v>94.52864837646484</v>
+        <v>94.52863311767578</v>
       </c>
       <c r="D232" t="n">
-        <v>94.53803940165234</v>
+        <v>94.53802414134739</v>
       </c>
       <c r="E232" t="n">
-        <v>94.52864837646484</v>
+        <v>94.52863311767578</v>
       </c>
       <c r="F232" t="n">
-        <v>94.52864837646484</v>
+        <v>94.52863311767578</v>
       </c>
       <c r="G232" t="n">
         <v>6581100</v>
@@ -5808,16 +5808,16 @@
         <v>45629</v>
       </c>
       <c r="C234" t="n">
-        <v>94.55503845214844</v>
+        <v>94.55504608154297</v>
       </c>
       <c r="D234" t="n">
-        <v>94.56445767831146</v>
+        <v>94.564465308466</v>
       </c>
       <c r="E234" t="n">
-        <v>94.55503845214844</v>
+        <v>94.55504608154297</v>
       </c>
       <c r="F234" t="n">
-        <v>94.56445767831146</v>
+        <v>94.564465308466</v>
       </c>
       <c r="G234" t="n">
         <v>5734100</v>
@@ -5854,16 +5854,16 @@
         <v>45631</v>
       </c>
       <c r="C236" t="n">
-        <v>94.58329772949219</v>
+        <v>94.58330535888672</v>
       </c>
       <c r="D236" t="n">
-        <v>94.59272414463034</v>
+        <v>94.59273177478522</v>
       </c>
       <c r="E236" t="n">
-        <v>94.58329772949219</v>
+        <v>94.58330535888672</v>
       </c>
       <c r="F236" t="n">
-        <v>94.58329772949219</v>
+        <v>94.58330535888672</v>
       </c>
       <c r="G236" t="n">
         <v>4870100</v>
@@ -5877,16 +5877,16 @@
         <v>45632</v>
       </c>
       <c r="C237" t="n">
-        <v>94.63042449951172</v>
+        <v>94.63043975830078</v>
       </c>
       <c r="D237" t="n">
-        <v>94.63042449951172</v>
+        <v>94.63043975830078</v>
       </c>
       <c r="E237" t="n">
-        <v>94.62099808418584</v>
+        <v>94.62101334145494</v>
       </c>
       <c r="F237" t="n">
-        <v>94.63042449951172</v>
+        <v>94.63043975830078</v>
       </c>
       <c r="G237" t="n">
         <v>4779000</v>
@@ -5900,16 +5900,16 @@
         <v>45635</v>
       </c>
       <c r="C238" t="n">
-        <v>94.63983917236328</v>
+        <v>94.63984680175781</v>
       </c>
       <c r="D238" t="n">
-        <v>94.63983917236328</v>
+        <v>94.63984680175781</v>
       </c>
       <c r="E238" t="n">
-        <v>94.63041994773863</v>
+        <v>94.63042757637383</v>
       </c>
       <c r="F238" t="n">
-        <v>94.63041994773863</v>
+        <v>94.63042757637383</v>
       </c>
       <c r="G238" t="n">
         <v>5539800</v>
@@ -5969,16 +5969,16 @@
         <v>45638</v>
       </c>
       <c r="C241" t="n">
-        <v>94.66812896728516</v>
+        <v>94.66809844970703</v>
       </c>
       <c r="D241" t="n">
-        <v>94.6775553839241</v>
+        <v>94.67752486330724</v>
       </c>
       <c r="E241" t="n">
-        <v>94.66812896728516</v>
+        <v>94.66809844970703</v>
       </c>
       <c r="F241" t="n">
-        <v>94.6775553839241</v>
+        <v>94.67752486330724</v>
       </c>
       <c r="G241" t="n">
         <v>4701000</v>
@@ -5992,16 +5992,16 @@
         <v>45639</v>
       </c>
       <c r="C242" t="n">
-        <v>94.71524810791016</v>
+        <v>94.71525573730469</v>
       </c>
       <c r="D242" t="n">
-        <v>94.71524810791016</v>
+        <v>94.71525573730469</v>
       </c>
       <c r="E242" t="n">
-        <v>94.70582169184371</v>
+        <v>94.70582932047894</v>
       </c>
       <c r="F242" t="n">
-        <v>94.70582169184371</v>
+        <v>94.70582932047894</v>
       </c>
       <c r="G242" t="n">
         <v>4671500</v>
@@ -6015,16 +6015,16 @@
         <v>45642</v>
       </c>
       <c r="C243" t="n">
-        <v>94.72468566894531</v>
+        <v>94.72467041015625</v>
       </c>
       <c r="D243" t="n">
-        <v>94.72468566894531</v>
+        <v>94.72467041015625</v>
       </c>
       <c r="E243" t="n">
-        <v>94.71525925176978</v>
+        <v>94.71524399449918</v>
       </c>
       <c r="F243" t="n">
-        <v>94.72468566894531</v>
+        <v>94.72467041015625</v>
       </c>
       <c r="G243" t="n">
         <v>5598900</v>
@@ -6038,16 +6038,16 @@
         <v>45643</v>
       </c>
       <c r="C244" t="n">
-        <v>94.72468566894531</v>
+        <v>94.72467041015625</v>
       </c>
       <c r="D244" t="n">
-        <v>94.73410489587128</v>
+        <v>94.7340896355649</v>
       </c>
       <c r="E244" t="n">
-        <v>94.72468566894531</v>
+        <v>94.72467041015625</v>
       </c>
       <c r="F244" t="n">
-        <v>94.73410489587128</v>
+        <v>94.7340896355649</v>
       </c>
       <c r="G244" t="n">
         <v>5798500</v>
@@ -6061,16 +6061,16 @@
         <v>45644</v>
       </c>
       <c r="C245" t="n">
-        <v>94.74549102783203</v>
+        <v>94.74547576904297</v>
       </c>
       <c r="D245" t="n">
-        <v>94.74549102783203</v>
+        <v>94.74547576904297</v>
       </c>
       <c r="E245" t="n">
-        <v>94.73602959338879</v>
+        <v>94.7360143361235</v>
       </c>
       <c r="F245" t="n">
-        <v>94.74549102783203</v>
+        <v>94.74547576904297</v>
       </c>
       <c r="G245" t="n">
         <v>11526500</v>
@@ -6153,16 +6153,16 @@
         <v>45650</v>
       </c>
       <c r="C249" t="n">
-        <v>94.83062744140625</v>
+        <v>94.83061981201172</v>
       </c>
       <c r="D249" t="n">
-        <v>94.83062744140625</v>
+        <v>94.83061981201172</v>
       </c>
       <c r="E249" t="n">
-        <v>94.82116600644875</v>
+        <v>94.82115837781542</v>
       </c>
       <c r="F249" t="n">
-        <v>94.83062744140625</v>
+        <v>94.83061981201172</v>
       </c>
       <c r="G249" t="n">
         <v>4654300</v>
@@ -6176,16 +6176,16 @@
         <v>45652</v>
       </c>
       <c r="C250" t="n">
-        <v>94.840087890625</v>
+        <v>94.84007263183594</v>
       </c>
       <c r="D250" t="n">
-        <v>94.840087890625</v>
+        <v>94.84007263183594</v>
       </c>
       <c r="E250" t="n">
-        <v>94.83062645576584</v>
+        <v>94.83061119849903</v>
       </c>
       <c r="F250" t="n">
-        <v>94.840087890625</v>
+        <v>94.84007263183594</v>
       </c>
       <c r="G250" t="n">
         <v>4974100</v>
@@ -6199,16 +6199,16 @@
         <v>45653</v>
       </c>
       <c r="C251" t="n">
-        <v>94.86845397949219</v>
+        <v>94.86846160888672</v>
       </c>
       <c r="D251" t="n">
-        <v>94.86845397949219</v>
+        <v>94.86846160888672</v>
       </c>
       <c r="E251" t="n">
-        <v>94.85899254572995</v>
+        <v>94.85900017436359</v>
       </c>
       <c r="F251" t="n">
-        <v>94.85899254572995</v>
+        <v>94.85900017436359</v>
       </c>
       <c r="G251" t="n">
         <v>6558000</v>
@@ -6222,16 +6222,16 @@
         <v>45656</v>
       </c>
       <c r="C252" t="n">
-        <v>94.86845397949219</v>
+        <v>94.86846160888672</v>
       </c>
       <c r="D252" t="n">
-        <v>94.87791541325443</v>
+        <v>94.87792304340985</v>
       </c>
       <c r="E252" t="n">
-        <v>94.86845397949219</v>
+        <v>94.86846160888672</v>
       </c>
       <c r="F252" t="n">
-        <v>94.87791541325443</v>
+        <v>94.87792304340985</v>
       </c>
       <c r="G252" t="n">
         <v>6547600</v>
@@ -6268,16 +6268,16 @@
         <v>45659</v>
       </c>
       <c r="C254" t="n">
-        <v>94.91575622558594</v>
+        <v>94.91576385498047</v>
       </c>
       <c r="D254" t="n">
-        <v>94.91575622558594</v>
+        <v>94.91576385498047</v>
       </c>
       <c r="E254" t="n">
-        <v>94.90630200783571</v>
+        <v>94.90630963647031</v>
       </c>
       <c r="F254" t="n">
-        <v>94.91575622558594</v>
+        <v>94.91576385498047</v>
       </c>
       <c r="G254" t="n">
         <v>7533100</v>
@@ -6291,16 +6291,16 @@
         <v>45660</v>
       </c>
       <c r="C255" t="n">
-        <v>94.94413757324219</v>
+        <v>94.94415283203125</v>
       </c>
       <c r="D255" t="n">
-        <v>94.95359179069801</v>
+        <v>94.9536070510065</v>
       </c>
       <c r="E255" t="n">
-        <v>94.94413757324219</v>
+        <v>94.94415283203125</v>
       </c>
       <c r="F255" t="n">
-        <v>94.95359179069801</v>
+        <v>94.9536070510065</v>
       </c>
       <c r="G255" t="n">
         <v>6730100</v>
@@ -6314,16 +6314,16 @@
         <v>45663</v>
       </c>
       <c r="C256" t="n">
-        <v>94.94413757324219</v>
+        <v>94.94415283203125</v>
       </c>
       <c r="D256" t="n">
-        <v>94.96305322511373</v>
+        <v>94.96306848694279</v>
       </c>
       <c r="E256" t="n">
-        <v>94.94413757324219</v>
+        <v>94.94415283203125</v>
       </c>
       <c r="F256" t="n">
-        <v>94.95359179069801</v>
+        <v>94.9536070510065</v>
       </c>
       <c r="G256" t="n">
         <v>6938300</v>
@@ -6337,16 +6337,16 @@
         <v>45664</v>
       </c>
       <c r="C257" t="n">
-        <v>94.96303558349609</v>
+        <v>94.96304321289062</v>
       </c>
       <c r="D257" t="n">
-        <v>94.97249701615412</v>
+        <v>94.97250464630879</v>
       </c>
       <c r="E257" t="n">
-        <v>94.96303558349609</v>
+        <v>94.96304321289062</v>
       </c>
       <c r="F257" t="n">
-        <v>94.97249701615412</v>
+        <v>94.97250464630879</v>
       </c>
       <c r="G257" t="n">
         <v>6792100</v>
@@ -6360,16 +6360,16 @@
         <v>45665</v>
       </c>
       <c r="C258" t="n">
-        <v>94.98196411132812</v>
+        <v>94.98197937011719</v>
       </c>
       <c r="D258" t="n">
-        <v>94.98196411132812</v>
+        <v>94.98197937011719</v>
       </c>
       <c r="E258" t="n">
-        <v>94.97250267810604</v>
+        <v>94.97251793537512</v>
       </c>
       <c r="F258" t="n">
-        <v>94.97250267810604</v>
+        <v>94.97251793537512</v>
       </c>
       <c r="G258" t="n">
         <v>6101100</v>
@@ -6383,16 +6383,16 @@
         <v>45667</v>
       </c>
       <c r="C259" t="n">
-        <v>95.01979827880859</v>
+        <v>95.01979064941406</v>
       </c>
       <c r="D259" t="n">
-        <v>95.0292597123163</v>
+        <v>95.0292520821621</v>
       </c>
       <c r="E259" t="n">
-        <v>95.01034406226007</v>
+        <v>95.01033643362464</v>
       </c>
       <c r="F259" t="n">
-        <v>95.01979827880859</v>
+        <v>95.01979064941406</v>
       </c>
       <c r="G259" t="n">
         <v>7644600</v>
@@ -6429,16 +6429,16 @@
         <v>45671</v>
       </c>
       <c r="C261" t="n">
-        <v>95.04820251464844</v>
+        <v>95.04819488525391</v>
       </c>
       <c r="D261" t="n">
-        <v>95.04820251464844</v>
+        <v>95.04819488525391</v>
       </c>
       <c r="E261" t="n">
-        <v>95.03874107915628</v>
+        <v>95.03873345052121</v>
       </c>
       <c r="F261" t="n">
-        <v>95.04820251464844</v>
+        <v>95.04819488525391</v>
       </c>
       <c r="G261" t="n">
         <v>7245400</v>
@@ -6452,16 +6452,16 @@
         <v>45672</v>
       </c>
       <c r="C262" t="n">
-        <v>95.05765533447266</v>
+        <v>95.05763244628906</v>
       </c>
       <c r="D262" t="n">
-        <v>95.05765533447266</v>
+        <v>95.05763244628906</v>
       </c>
       <c r="E262" t="n">
-        <v>95.04820111608032</v>
+        <v>95.04817823017314</v>
       </c>
       <c r="F262" t="n">
-        <v>95.05765533447266</v>
+        <v>95.05763244628906</v>
       </c>
       <c r="G262" t="n">
         <v>6878600</v>
@@ -6475,16 +6475,16 @@
         <v>45673</v>
       </c>
       <c r="C263" t="n">
-        <v>95.05765533447266</v>
+        <v>95.05763244628906</v>
       </c>
       <c r="D263" t="n">
-        <v>95.07657820517852</v>
+        <v>95.07655531243863</v>
       </c>
       <c r="E263" t="n">
-        <v>95.05765533447266</v>
+        <v>95.05763244628906</v>
       </c>
       <c r="F263" t="n">
-        <v>95.06711676982559</v>
+        <v>95.06709387936384</v>
       </c>
       <c r="G263" t="n">
         <v>5352500</v>
@@ -6521,16 +6521,16 @@
         <v>45678</v>
       </c>
       <c r="C265" t="n">
-        <v>95.11440277099609</v>
+        <v>95.11438751220703</v>
       </c>
       <c r="D265" t="n">
-        <v>95.12385698800095</v>
+        <v>95.12384172769519</v>
       </c>
       <c r="E265" t="n">
-        <v>95.11440277099609</v>
+        <v>95.11438751220703</v>
       </c>
       <c r="F265" t="n">
-        <v>95.11912987949853</v>
+        <v>95.11911461995111</v>
       </c>
       <c r="G265" t="n">
         <v>7952400</v>
@@ -6567,16 +6567,16 @@
         <v>45680</v>
       </c>
       <c r="C267" t="n">
-        <v>95.14279174804688</v>
+        <v>95.14277648925781</v>
       </c>
       <c r="D267" t="n">
-        <v>95.14279174804688</v>
+        <v>95.14277648925781</v>
       </c>
       <c r="E267" t="n">
-        <v>95.13333031289986</v>
+        <v>95.1333150556282</v>
       </c>
       <c r="F267" t="n">
-        <v>95.14279174804688</v>
+        <v>95.14277648925781</v>
       </c>
       <c r="G267" t="n">
         <v>5085800</v>
@@ -6590,16 +6590,16 @@
         <v>45681</v>
       </c>
       <c r="C268" t="n">
-        <v>95.17116546630859</v>
+        <v>95.17115020751953</v>
       </c>
       <c r="D268" t="n">
-        <v>95.18062690112056</v>
+        <v>95.18061164081455</v>
       </c>
       <c r="E268" t="n">
-        <v>95.17116546630859</v>
+        <v>95.17115020751953</v>
       </c>
       <c r="F268" t="n">
-        <v>95.17116546630859</v>
+        <v>95.17115020751953</v>
       </c>
       <c r="G268" t="n">
         <v>6380000</v>
@@ -6613,16 +6613,16 @@
         <v>45684</v>
       </c>
       <c r="C269" t="n">
-        <v>95.17116546630859</v>
+        <v>95.17115020751953</v>
       </c>
       <c r="D269" t="n">
-        <v>95.19008111897233</v>
+        <v>95.19006585715051</v>
       </c>
       <c r="E269" t="n">
-        <v>95.17116546630859</v>
+        <v>95.17115020751953</v>
       </c>
       <c r="F269" t="n">
-        <v>95.18062690112056</v>
+        <v>95.18061164081455</v>
       </c>
       <c r="G269" t="n">
         <v>9439800</v>
@@ -6636,16 +6636,16 @@
         <v>45685</v>
       </c>
       <c r="C270" t="n">
-        <v>95.19952392578125</v>
+        <v>95.19953918457031</v>
       </c>
       <c r="D270" t="n">
-        <v>95.19952392578125</v>
+        <v>95.19953918457031</v>
       </c>
       <c r="E270" t="n">
-        <v>95.1806082768188</v>
+        <v>95.18062353257602</v>
       </c>
       <c r="F270" t="n">
-        <v>95.19006249282063</v>
+        <v>95.1900777500932</v>
       </c>
       <c r="G270" t="n">
         <v>5857900</v>
@@ -6659,16 +6659,16 @@
         <v>45686</v>
       </c>
       <c r="C271" t="n">
-        <v>95.19952392578125</v>
+        <v>95.19953918457031</v>
       </c>
       <c r="D271" t="n">
-        <v>95.20898535874186</v>
+        <v>95.20900061904742</v>
       </c>
       <c r="E271" t="n">
-        <v>95.19952392578125</v>
+        <v>95.19953918457031</v>
       </c>
       <c r="F271" t="n">
-        <v>95.19952392578125</v>
+        <v>95.19953918457031</v>
       </c>
       <c r="G271" t="n">
         <v>3978700</v>
@@ -6682,16 +6682,16 @@
         <v>45687</v>
       </c>
       <c r="C272" t="n">
-        <v>95.21845245361328</v>
+        <v>95.21846771240234</v>
       </c>
       <c r="D272" t="n">
-        <v>95.22790667017728</v>
+        <v>95.22792193048139</v>
       </c>
       <c r="E272" t="n">
-        <v>95.20899102009007</v>
+        <v>95.20900627736293</v>
       </c>
       <c r="F272" t="n">
-        <v>95.20899102009007</v>
+        <v>95.20900627736293</v>
       </c>
       <c r="G272" t="n">
         <v>8043500</v>
@@ -6705,16 +6705,16 @@
         <v>45688</v>
       </c>
       <c r="C273" t="n">
-        <v>95.23736572265625</v>
+        <v>95.23738098144531</v>
       </c>
       <c r="D273" t="n">
-        <v>95.24682715594292</v>
+        <v>95.24684241624787</v>
       </c>
       <c r="E273" t="n">
-        <v>95.23736572265625</v>
+        <v>95.23738098144531</v>
       </c>
       <c r="F273" t="n">
-        <v>95.24682715594292</v>
+        <v>95.24684241624787</v>
       </c>
       <c r="G273" t="n">
         <v>12373000</v>
@@ -6728,16 +6728,16 @@
         <v>45691</v>
       </c>
       <c r="C274" t="n">
-        <v>95.25919342041016</v>
+        <v>95.25920867919922</v>
       </c>
       <c r="D274" t="n">
-        <v>95.25919342041016</v>
+        <v>95.25920867919922</v>
       </c>
       <c r="E274" t="n">
-        <v>95.24970499411383</v>
+        <v>95.24972025138301</v>
       </c>
       <c r="F274" t="n">
-        <v>95.24970499411383</v>
+        <v>95.24972025138301</v>
       </c>
       <c r="G274" t="n">
         <v>16436200</v>
@@ -6751,16 +6751,16 @@
         <v>45692</v>
       </c>
       <c r="C275" t="n">
-        <v>95.27820587158203</v>
+        <v>95.2781982421875</v>
       </c>
       <c r="D275" t="n">
-        <v>95.27820587158203</v>
+        <v>95.2781982421875</v>
       </c>
       <c r="E275" t="n">
-        <v>95.26871020010807</v>
+        <v>95.2687025714739</v>
       </c>
       <c r="F275" t="n">
-        <v>95.27820587158203</v>
+        <v>95.2781982421875</v>
       </c>
       <c r="G275" t="n">
         <v>7866600</v>
@@ -6774,16 +6774,16 @@
         <v>45693</v>
       </c>
       <c r="C276" t="n">
-        <v>95.27820587158203</v>
+        <v>95.2781982421875</v>
       </c>
       <c r="D276" t="n">
-        <v>95.28770154305599</v>
+        <v>95.28769391290109</v>
       </c>
       <c r="E276" t="n">
-        <v>95.27820587158203</v>
+        <v>95.2781982421875</v>
       </c>
       <c r="F276" t="n">
-        <v>95.28770154305599</v>
+        <v>95.28769391290109</v>
       </c>
       <c r="G276" t="n">
         <v>7100900</v>
@@ -6820,16 +6820,16 @@
         <v>45695</v>
       </c>
       <c r="C278" t="n">
-        <v>95.32566833496094</v>
+        <v>95.32566070556641</v>
       </c>
       <c r="D278" t="n">
-        <v>95.3351567624987</v>
+        <v>95.33514913234477</v>
       </c>
       <c r="E278" t="n">
-        <v>95.31617266434873</v>
+        <v>95.31616503571418</v>
       </c>
       <c r="F278" t="n">
-        <v>95.3351567624987</v>
+        <v>95.33514913234477</v>
       </c>
       <c r="G278" t="n">
         <v>6758700</v>
@@ -6843,16 +6843,16 @@
         <v>45698</v>
       </c>
       <c r="C279" t="n">
-        <v>95.34465026855469</v>
+        <v>95.34463500976562</v>
       </c>
       <c r="D279" t="n">
-        <v>95.34465026855469</v>
+        <v>95.34463500976562</v>
       </c>
       <c r="E279" t="n">
-        <v>95.33515459815804</v>
+        <v>95.33513934088865</v>
       </c>
       <c r="F279" t="n">
-        <v>95.34465026855469</v>
+        <v>95.34463500976562</v>
       </c>
       <c r="G279" t="n">
         <v>7517800</v>
@@ -6866,16 +6866,16 @@
         <v>45699</v>
       </c>
       <c r="C280" t="n">
-        <v>95.34465026855469</v>
+        <v>95.34463500976562</v>
       </c>
       <c r="D280" t="n">
-        <v>95.35414593895132</v>
+        <v>95.35413067864259</v>
       </c>
       <c r="E280" t="n">
-        <v>95.34465026855469</v>
+        <v>95.34463500976562</v>
       </c>
       <c r="F280" t="n">
-        <v>95.35414593895132</v>
+        <v>95.35413067864259</v>
       </c>
       <c r="G280" t="n">
         <v>6424100</v>
@@ -6889,16 +6889,16 @@
         <v>45700</v>
       </c>
       <c r="C281" t="n">
-        <v>95.35416412353516</v>
+        <v>95.35414123535156</v>
       </c>
       <c r="D281" t="n">
-        <v>95.36365255266701</v>
+        <v>95.36362966220587</v>
       </c>
       <c r="E281" t="n">
-        <v>95.35416412353516</v>
+        <v>95.35414123535156</v>
       </c>
       <c r="F281" t="n">
-        <v>95.35416412353516</v>
+        <v>95.35414123535156</v>
       </c>
       <c r="G281" t="n">
         <v>6618800</v>
@@ -6935,16 +6935,16 @@
         <v>45702</v>
       </c>
       <c r="C283" t="n">
-        <v>95.4111328125</v>
+        <v>95.41110992431641</v>
       </c>
       <c r="D283" t="n">
-        <v>95.42062848561736</v>
+        <v>95.42060559515583</v>
       </c>
       <c r="E283" t="n">
-        <v>95.4111328125</v>
+        <v>95.41110992431641</v>
       </c>
       <c r="F283" t="n">
-        <v>95.41587702752049</v>
+        <v>95.41585413819881</v>
       </c>
       <c r="G283" t="n">
         <v>7648100</v>
@@ -7004,16 +7004,16 @@
         <v>45708</v>
       </c>
       <c r="C286" t="n">
-        <v>95.44906616210938</v>
+        <v>95.44908142089844</v>
       </c>
       <c r="D286" t="n">
-        <v>95.44906616210938</v>
+        <v>95.44908142089844</v>
       </c>
       <c r="E286" t="n">
-        <v>95.43957049318028</v>
+        <v>95.43958575045134</v>
       </c>
       <c r="F286" t="n">
-        <v>95.44906616210938</v>
+        <v>95.44908142089844</v>
       </c>
       <c r="G286" t="n">
         <v>7608000</v>
@@ -7027,16 +7027,16 @@
         <v>45709</v>
       </c>
       <c r="C287" t="n">
-        <v>95.48704528808594</v>
+        <v>95.48706817626953</v>
       </c>
       <c r="D287" t="n">
-        <v>95.48704528808594</v>
+        <v>95.48706817626953</v>
       </c>
       <c r="E287" t="n">
-        <v>95.47754961878957</v>
+        <v>95.47757250469705</v>
       </c>
       <c r="F287" t="n">
-        <v>95.47754961878957</v>
+        <v>95.47757250469705</v>
       </c>
       <c r="G287" t="n">
         <v>9111000</v>
@@ -7050,16 +7050,16 @@
         <v>45712</v>
       </c>
       <c r="C288" t="n">
-        <v>95.49654388427734</v>
+        <v>95.49655914306641</v>
       </c>
       <c r="D288" t="n">
-        <v>95.49654388427734</v>
+        <v>95.49655914306641</v>
       </c>
       <c r="E288" t="n">
-        <v>95.48705545704394</v>
+        <v>95.48707071431691</v>
       </c>
       <c r="F288" t="n">
-        <v>95.49654388427734</v>
+        <v>95.49655914306641</v>
       </c>
       <c r="G288" t="n">
         <v>9734600</v>
@@ -7073,16 +7073,16 @@
         <v>45713</v>
       </c>
       <c r="C289" t="n">
-        <v>95.50602722167969</v>
+        <v>95.50604248046875</v>
       </c>
       <c r="D289" t="n">
-        <v>95.50602722167969</v>
+        <v>95.50604248046875</v>
       </c>
       <c r="E289" t="n">
-        <v>95.49653155259826</v>
+        <v>95.49654680987022</v>
       </c>
       <c r="F289" t="n">
-        <v>95.49653155259826</v>
+        <v>95.49654680987022</v>
       </c>
       <c r="G289" t="n">
         <v>10827700</v>
@@ -7096,16 +7096,16 @@
         <v>45714</v>
       </c>
       <c r="C290" t="n">
-        <v>95.50602722167969</v>
+        <v>95.50604248046875</v>
       </c>
       <c r="D290" t="n">
-        <v>95.5155228907611</v>
+        <v>95.51553815106729</v>
       </c>
       <c r="E290" t="n">
-        <v>95.50602722167969</v>
+        <v>95.50604248046875</v>
       </c>
       <c r="F290" t="n">
-        <v>95.50602722167969</v>
+        <v>95.50604248046875</v>
       </c>
       <c r="G290" t="n">
         <v>9536300</v>
@@ -7119,16 +7119,16 @@
         <v>45715</v>
       </c>
       <c r="C291" t="n">
-        <v>95.53453063964844</v>
+        <v>95.53451538085938</v>
       </c>
       <c r="D291" t="n">
-        <v>95.53453063964844</v>
+        <v>95.53451538085938</v>
       </c>
       <c r="E291" t="n">
-        <v>95.52504221129102</v>
+        <v>95.52502695401745</v>
       </c>
       <c r="F291" t="n">
-        <v>95.53453063964844</v>
+        <v>95.53451538085938</v>
       </c>
       <c r="G291" t="n">
         <v>10807800</v>
@@ -7165,16 +7165,16 @@
         <v>45719</v>
       </c>
       <c r="C293" t="n">
-        <v>95.57542419433594</v>
+        <v>95.57541656494141</v>
       </c>
       <c r="D293" t="n">
-        <v>95.57542419433594</v>
+        <v>95.57541656494141</v>
       </c>
       <c r="E293" t="n">
-        <v>95.56589890131818</v>
+        <v>95.56589127268401</v>
       </c>
       <c r="F293" t="n">
-        <v>95.57542419433594</v>
+        <v>95.57541656494141</v>
       </c>
       <c r="G293" t="n">
         <v>17436600</v>
@@ -7234,16 +7234,16 @@
         <v>45722</v>
       </c>
       <c r="C296" t="n">
-        <v>95.61351776123047</v>
+        <v>95.61350250244141</v>
       </c>
       <c r="D296" t="n">
-        <v>95.61351776123047</v>
+        <v>95.61350250244141</v>
       </c>
       <c r="E296" t="n">
-        <v>95.59446717526258</v>
+        <v>95.59445191951377</v>
       </c>
       <c r="F296" t="n">
-        <v>95.60399246824653</v>
+        <v>95.60397721097759</v>
       </c>
       <c r="G296" t="n">
         <v>9925500</v>
@@ -7257,16 +7257,16 @@
         <v>45723</v>
       </c>
       <c r="C297" t="n">
-        <v>95.64208221435547</v>
+        <v>95.64207458496094</v>
       </c>
       <c r="D297" t="n">
-        <v>95.64208221435547</v>
+        <v>95.64207458496094</v>
       </c>
       <c r="E297" t="n">
-        <v>95.63255692178585</v>
+        <v>95.63254929315114</v>
       </c>
       <c r="F297" t="n">
-        <v>95.64208221435547</v>
+        <v>95.64207458496094</v>
       </c>
       <c r="G297" t="n">
         <v>8962400</v>
@@ -7280,16 +7280,16 @@
         <v>45726</v>
       </c>
       <c r="C298" t="n">
-        <v>95.64208221435547</v>
+        <v>95.64207458496094</v>
       </c>
       <c r="D298" t="n">
-        <v>95.65160750692509</v>
+        <v>95.65159987677072</v>
       </c>
       <c r="E298" t="n">
-        <v>95.64208221435547</v>
+        <v>95.64207458496094</v>
       </c>
       <c r="F298" t="n">
-        <v>95.65160750692509</v>
+        <v>95.65159987677072</v>
       </c>
       <c r="G298" t="n">
         <v>14768100</v>
@@ -7303,16 +7303,16 @@
         <v>45727</v>
       </c>
       <c r="C299" t="n">
-        <v>95.66112518310547</v>
+        <v>95.66111755371094</v>
       </c>
       <c r="D299" t="n">
-        <v>95.66112518310547</v>
+        <v>95.66111755371094</v>
       </c>
       <c r="E299" t="n">
-        <v>95.65160715624013</v>
+        <v>95.65159952760472</v>
       </c>
       <c r="F299" t="n">
-        <v>95.65160715624013</v>
+        <v>95.65159952760472</v>
       </c>
       <c r="G299" t="n">
         <v>11456900</v>
@@ -7326,16 +7326,16 @@
         <v>45728</v>
       </c>
       <c r="C300" t="n">
-        <v>95.66112518310547</v>
+        <v>95.66111755371094</v>
       </c>
       <c r="D300" t="n">
-        <v>95.67065047564017</v>
+        <v>95.67064284548596</v>
       </c>
       <c r="E300" t="n">
-        <v>95.66112518310547</v>
+        <v>95.66111755371094</v>
       </c>
       <c r="F300" t="n">
-        <v>95.67065047564017</v>
+        <v>95.67064284548596</v>
       </c>
       <c r="G300" t="n">
         <v>11307300</v>
@@ -7349,16 +7349,16 @@
         <v>45729</v>
       </c>
       <c r="C301" t="n">
-        <v>95.68971252441406</v>
+        <v>95.68970489501953</v>
       </c>
       <c r="D301" t="n">
-        <v>95.68971252441406</v>
+        <v>95.68970489501953</v>
       </c>
       <c r="E301" t="n">
-        <v>95.67066193706239</v>
+        <v>95.67065430918677</v>
       </c>
       <c r="F301" t="n">
-        <v>95.67066193706239</v>
+        <v>95.67065430918677</v>
       </c>
       <c r="G301" t="n">
         <v>13110600</v>
@@ -7418,16 +7418,16 @@
         <v>45734</v>
       </c>
       <c r="C304" t="n">
-        <v>95.73731994628906</v>
+        <v>95.73731231689453</v>
       </c>
       <c r="D304" t="n">
-        <v>95.73731994628906</v>
+        <v>95.73731231689453</v>
       </c>
       <c r="E304" t="n">
-        <v>95.72779465306246</v>
+        <v>95.727787024427</v>
       </c>
       <c r="F304" t="n">
-        <v>95.73731994628906</v>
+        <v>95.73731231689453</v>
       </c>
       <c r="G304" t="n">
         <v>9213100</v>
@@ -7441,16 +7441,16 @@
         <v>45735</v>
       </c>
       <c r="C305" t="n">
-        <v>95.75636291503906</v>
+        <v>95.75635528564453</v>
       </c>
       <c r="D305" t="n">
-        <v>95.75636291503906</v>
+        <v>95.75635528564453</v>
       </c>
       <c r="E305" t="n">
-        <v>95.74683762257023</v>
+        <v>95.74682999393463</v>
       </c>
       <c r="F305" t="n">
-        <v>95.74683762257023</v>
+        <v>95.74682999393463</v>
       </c>
       <c r="G305" t="n">
         <v>13584800</v>
@@ -7464,16 +7464,16 @@
         <v>45736</v>
       </c>
       <c r="C306" t="n">
-        <v>95.75636291503906</v>
+        <v>95.75635528564453</v>
       </c>
       <c r="D306" t="n">
-        <v>95.76588094183857</v>
+        <v>95.76587331168571</v>
       </c>
       <c r="E306" t="n">
-        <v>95.75636291503906</v>
+        <v>95.75635528564453</v>
       </c>
       <c r="F306" t="n">
-        <v>95.76588094183857</v>
+        <v>95.76587331168571</v>
       </c>
       <c r="G306" t="n">
         <v>12648500</v>
@@ -7487,16 +7487,16 @@
         <v>45737</v>
       </c>
       <c r="C307" t="n">
-        <v>95.78491973876953</v>
+        <v>95.78493499755859</v>
       </c>
       <c r="D307" t="n">
-        <v>95.7944377643977</v>
+        <v>95.794453024703</v>
       </c>
       <c r="E307" t="n">
-        <v>95.78491973876953</v>
+        <v>95.78493499755859</v>
       </c>
       <c r="F307" t="n">
-        <v>95.7944377643977</v>
+        <v>95.794453024703</v>
       </c>
       <c r="G307" t="n">
         <v>13101800</v>
@@ -7533,16 +7533,16 @@
         <v>45741</v>
       </c>
       <c r="C309" t="n">
-        <v>95.81349182128906</v>
+        <v>95.81350708007812</v>
       </c>
       <c r="D309" t="n">
-        <v>95.81349182128906</v>
+        <v>95.81350708007812</v>
       </c>
       <c r="E309" t="n">
-        <v>95.80396652964708</v>
+        <v>95.80398178691919</v>
       </c>
       <c r="F309" t="n">
-        <v>95.81349182128906</v>
+        <v>95.81350708007812</v>
       </c>
       <c r="G309" t="n">
         <v>13844800</v>
@@ -7556,16 +7556,16 @@
         <v>45742</v>
       </c>
       <c r="C310" t="n">
-        <v>95.83255004882812</v>
+        <v>95.83254241943359</v>
       </c>
       <c r="D310" t="n">
-        <v>95.83255004882812</v>
+        <v>95.83254241943359</v>
       </c>
       <c r="E310" t="n">
-        <v>95.82303202137399</v>
+        <v>95.8230243927372</v>
       </c>
       <c r="F310" t="n">
-        <v>95.83255004882812</v>
+        <v>95.83254241943359</v>
       </c>
       <c r="G310" t="n">
         <v>12262200</v>
@@ -7602,16 +7602,16 @@
         <v>45744</v>
       </c>
       <c r="C312" t="n">
-        <v>95.87065124511719</v>
+        <v>95.87064361572266</v>
       </c>
       <c r="D312" t="n">
-        <v>95.87065124511719</v>
+        <v>95.87064361572266</v>
       </c>
       <c r="E312" t="n">
-        <v>95.86113321693935</v>
+        <v>95.86112558830226</v>
       </c>
       <c r="F312" t="n">
-        <v>95.86113321693935</v>
+        <v>95.86112558830226</v>
       </c>
       <c r="G312" t="n">
         <v>11747100</v>
@@ -7625,16 +7625,16 @@
         <v>45747</v>
       </c>
       <c r="C313" t="n">
-        <v>95.87065124511719</v>
+        <v>95.87064361572266</v>
       </c>
       <c r="D313" t="n">
-        <v>95.88017653896539</v>
+        <v>95.88016890881283</v>
       </c>
       <c r="E313" t="n">
-        <v>95.87065124511719</v>
+        <v>95.87064361572266</v>
       </c>
       <c r="F313" t="n">
-        <v>95.87065124511719</v>
+        <v>95.87064361572266</v>
       </c>
       <c r="G313" t="n">
         <v>18210800</v>
@@ -7717,16 +7717,16 @@
         <v>45751</v>
       </c>
       <c r="C317" t="n">
-        <v>95.95282745361328</v>
+        <v>95.95281982421875</v>
       </c>
       <c r="D317" t="n">
-        <v>95.95282745361328</v>
+        <v>95.95281982421875</v>
       </c>
       <c r="E317" t="n">
-        <v>95.94326930983391</v>
+        <v>95.94326168119937</v>
       </c>
       <c r="F317" t="n">
-        <v>95.94326930983391</v>
+        <v>95.94326168119937</v>
       </c>
       <c r="G317" t="n">
         <v>22826300</v>
@@ -7740,16 +7740,16 @@
         <v>45754</v>
       </c>
       <c r="C318" t="n">
-        <v>95.96237182617188</v>
+        <v>95.96237945556641</v>
       </c>
       <c r="D318" t="n">
-        <v>95.96237182617188</v>
+        <v>95.96237945556641</v>
       </c>
       <c r="E318" t="n">
-        <v>95.95282097376501</v>
+        <v>95.95282860240022</v>
       </c>
       <c r="F318" t="n">
-        <v>95.95282097376501</v>
+        <v>95.95282860240022</v>
       </c>
       <c r="G318" t="n">
         <v>22564000</v>
@@ -7763,16 +7763,16 @@
         <v>45755</v>
       </c>
       <c r="C319" t="n">
-        <v>95.96237182617188</v>
+        <v>95.96237945556641</v>
       </c>
       <c r="D319" t="n">
-        <v>95.97192996930578</v>
+        <v>95.97193759946022</v>
       </c>
       <c r="E319" t="n">
-        <v>95.95282097376501</v>
+        <v>95.95282860240022</v>
       </c>
       <c r="F319" t="n">
-        <v>95.95759639996845</v>
+        <v>95.95760402898331</v>
       </c>
       <c r="G319" t="n">
         <v>17116100</v>
@@ -7832,16 +7832,16 @@
         <v>45758</v>
       </c>
       <c r="C322" t="n">
-        <v>96.02927398681641</v>
+        <v>96.02926635742188</v>
       </c>
       <c r="D322" t="n">
-        <v>96.02927398681641</v>
+        <v>96.02926635742188</v>
       </c>
       <c r="E322" t="n">
-        <v>96.01972313344081</v>
+        <v>96.01971550480508</v>
       </c>
       <c r="F322" t="n">
-        <v>96.02449856012861</v>
+        <v>96.02449093111348</v>
       </c>
       <c r="G322" t="n">
         <v>12916600</v>
@@ -7855,16 +7855,16 @@
         <v>45761</v>
       </c>
       <c r="C323" t="n">
-        <v>96.03884887695312</v>
+        <v>96.038818359375</v>
       </c>
       <c r="D323" t="n">
-        <v>96.03884887695312</v>
+        <v>96.038818359375</v>
       </c>
       <c r="E323" t="n">
-        <v>96.02929073118312</v>
+        <v>96.02926021664223</v>
       </c>
       <c r="F323" t="n">
-        <v>96.02929073118312</v>
+        <v>96.02926021664223</v>
       </c>
       <c r="G323" t="n">
         <v>13772300</v>
@@ -7970,16 +7970,16 @@
         <v>45769</v>
       </c>
       <c r="C328" t="n">
-        <v>96.11526489257812</v>
+        <v>96.11528015136719</v>
       </c>
       <c r="D328" t="n">
-        <v>96.12481574418399</v>
+        <v>96.12483100448931</v>
       </c>
       <c r="E328" t="n">
-        <v>96.11526489257812</v>
+        <v>96.11528015136719</v>
       </c>
       <c r="F328" t="n">
-        <v>96.12481574418399</v>
+        <v>96.12483100448931</v>
       </c>
       <c r="G328" t="n">
         <v>11603400</v>
@@ -7993,16 +7993,16 @@
         <v>45770</v>
       </c>
       <c r="C329" t="n">
-        <v>96.14393615722656</v>
+        <v>96.14395141601562</v>
       </c>
       <c r="D329" t="n">
-        <v>96.14393615722656</v>
+        <v>96.14395141601562</v>
       </c>
       <c r="E329" t="n">
-        <v>96.12481987174114</v>
+        <v>96.1248351274963</v>
       </c>
       <c r="F329" t="n">
-        <v>96.13437801448384</v>
+        <v>96.13439327175597</v>
       </c>
       <c r="G329" t="n">
         <v>19135100</v>
@@ -8016,16 +8016,16 @@
         <v>45771</v>
       </c>
       <c r="C330" t="n">
-        <v>96.14393615722656</v>
+        <v>96.14395141601562</v>
       </c>
       <c r="D330" t="n">
-        <v>96.15349429996927</v>
+        <v>96.1535095602753</v>
       </c>
       <c r="E330" t="n">
-        <v>96.14393615722656</v>
+        <v>96.14395141601562</v>
       </c>
       <c r="F330" t="n">
-        <v>96.15349429996927</v>
+        <v>96.1535095602753</v>
       </c>
       <c r="G330" t="n">
         <v>12068700</v>
@@ -8039,16 +8039,16 @@
         <v>45772</v>
       </c>
       <c r="C331" t="n">
-        <v>96.18217468261719</v>
+        <v>96.18215942382812</v>
       </c>
       <c r="D331" t="n">
-        <v>96.18217468261719</v>
+        <v>96.18215942382812</v>
       </c>
       <c r="E331" t="n">
-        <v>96.17261653855823</v>
+        <v>96.17260128128551</v>
       </c>
       <c r="F331" t="n">
-        <v>96.18217468261719</v>
+        <v>96.18215942382812</v>
       </c>
       <c r="G331" t="n">
         <v>8822700</v>
@@ -8062,16 +8062,16 @@
         <v>45775</v>
       </c>
       <c r="C332" t="n">
-        <v>96.18217468261719</v>
+        <v>96.18215942382812</v>
       </c>
       <c r="D332" t="n">
-        <v>96.19173282667613</v>
+        <v>96.19171756637073</v>
       </c>
       <c r="E332" t="n">
-        <v>96.18217468261719</v>
+        <v>96.18215942382812</v>
       </c>
       <c r="F332" t="n">
-        <v>96.18217468261719</v>
+        <v>96.18215942382812</v>
       </c>
       <c r="G332" t="n">
         <v>9127900</v>
@@ -8085,16 +8085,16 @@
         <v>45776</v>
       </c>
       <c r="C333" t="n">
-        <v>96.19173431396484</v>
+        <v>96.19172668457031</v>
       </c>
       <c r="D333" t="n">
-        <v>96.20128516744374</v>
+        <v>96.20127753729169</v>
       </c>
       <c r="E333" t="n">
-        <v>96.19173431396484</v>
+        <v>96.19172668457031</v>
       </c>
       <c r="F333" t="n">
-        <v>96.19173431396484</v>
+        <v>96.19172668457031</v>
       </c>
       <c r="G333" t="n">
         <v>8555000</v>
@@ -8108,16 +8108,16 @@
         <v>45777</v>
       </c>
       <c r="C334" t="n">
-        <v>96.22039794921875</v>
+        <v>96.22039031982422</v>
       </c>
       <c r="D334" t="n">
-        <v>96.22039794921875</v>
+        <v>96.22039031982422</v>
       </c>
       <c r="E334" t="n">
-        <v>96.20128166150194</v>
+        <v>96.20127403362315</v>
       </c>
       <c r="F334" t="n">
-        <v>96.20128166150194</v>
+        <v>96.20127403362315</v>
       </c>
       <c r="G334" t="n">
         <v>16040200</v>
@@ -8154,16 +8154,16 @@
         <v>45779</v>
       </c>
       <c r="C336" t="n">
-        <v>96.26354217529297</v>
+        <v>96.2635498046875</v>
       </c>
       <c r="D336" t="n">
-        <v>96.26354217529297</v>
+        <v>96.2635498046875</v>
       </c>
       <c r="E336" t="n">
-        <v>96.25395212501178</v>
+        <v>96.25395975364626</v>
       </c>
       <c r="F336" t="n">
-        <v>96.25395212501178</v>
+        <v>96.25395975364626</v>
       </c>
       <c r="G336" t="n">
         <v>13930900</v>
@@ -8177,16 +8177,16 @@
         <v>45782</v>
       </c>
       <c r="C337" t="n">
-        <v>96.27313995361328</v>
+        <v>96.27313232421875</v>
       </c>
       <c r="D337" t="n">
-        <v>96.27313995361328</v>
+        <v>96.27313232421875</v>
       </c>
       <c r="E337" t="n">
-        <v>96.26354990256227</v>
+        <v>96.26354227392774</v>
       </c>
       <c r="F337" t="n">
-        <v>96.27313995361328</v>
+        <v>96.27313232421875</v>
       </c>
       <c r="G337" t="n">
         <v>13223700</v>
@@ -8200,16 +8200,16 @@
         <v>45783</v>
       </c>
       <c r="C338" t="n">
-        <v>96.27313995361328</v>
+        <v>96.27313232421875</v>
       </c>
       <c r="D338" t="n">
-        <v>96.28272268959864</v>
+        <v>96.28271505944471</v>
       </c>
       <c r="E338" t="n">
-        <v>96.27313995361328</v>
+        <v>96.27313232421875</v>
       </c>
       <c r="F338" t="n">
-        <v>96.28272268959864</v>
+        <v>96.28271505944471</v>
       </c>
       <c r="G338" t="n">
         <v>8986000</v>
@@ -8223,16 +8223,16 @@
         <v>45784</v>
       </c>
       <c r="C339" t="n">
-        <v>96.28271484375</v>
+        <v>96.28270721435547</v>
       </c>
       <c r="D339" t="n">
-        <v>96.29230489401954</v>
+        <v>96.29229726386509</v>
       </c>
       <c r="E339" t="n">
-        <v>96.28271484375</v>
+        <v>96.28270721435547</v>
       </c>
       <c r="F339" t="n">
-        <v>96.29230489401954</v>
+        <v>96.29229726386509</v>
       </c>
       <c r="G339" t="n">
         <v>8509300</v>
@@ -8246,16 +8246,16 @@
         <v>45785</v>
       </c>
       <c r="C340" t="n">
-        <v>96.31148529052734</v>
+        <v>96.31147003173828</v>
       </c>
       <c r="D340" t="n">
-        <v>96.31148529052734</v>
+        <v>96.31147003173828</v>
       </c>
       <c r="E340" t="n">
-        <v>96.29231250353818</v>
+        <v>96.29229724778671</v>
       </c>
       <c r="F340" t="n">
-        <v>96.30190255456557</v>
+        <v>96.30188729729473</v>
       </c>
       <c r="G340" t="n">
         <v>11931100</v>
@@ -8269,16 +8269,16 @@
         <v>45786</v>
       </c>
       <c r="C341" t="n">
-        <v>96.34025573730469</v>
+        <v>96.34026336669922</v>
       </c>
       <c r="D341" t="n">
-        <v>96.34025573730469</v>
+        <v>96.34026336669922</v>
       </c>
       <c r="E341" t="n">
-        <v>96.33066568624807</v>
+        <v>96.33067331488314</v>
       </c>
       <c r="F341" t="n">
-        <v>96.33066568624807</v>
+        <v>96.33067331488314</v>
       </c>
       <c r="G341" t="n">
         <v>11793700</v>
@@ -8292,16 +8292,16 @@
         <v>45789</v>
       </c>
       <c r="C342" t="n">
-        <v>96.34025573730469</v>
+        <v>96.34026336669922</v>
       </c>
       <c r="D342" t="n">
-        <v>96.34983847329568</v>
+        <v>96.34984610344908</v>
       </c>
       <c r="E342" t="n">
-        <v>96.34025573730469</v>
+        <v>96.34026336669922</v>
       </c>
       <c r="F342" t="n">
-        <v>96.34025573730469</v>
+        <v>96.34026336669922</v>
       </c>
       <c r="G342" t="n">
         <v>16808300</v>
@@ -8315,16 +8315,16 @@
         <v>45790</v>
       </c>
       <c r="C343" t="n">
-        <v>96.35944366455078</v>
+        <v>96.35942840576172</v>
       </c>
       <c r="D343" t="n">
-        <v>96.35944366455078</v>
+        <v>96.35942840576172</v>
       </c>
       <c r="E343" t="n">
-        <v>96.34985361198736</v>
+        <v>96.34983835471689</v>
       </c>
       <c r="F343" t="n">
-        <v>96.34985361198736</v>
+        <v>96.34983835471689</v>
       </c>
       <c r="G343" t="n">
         <v>18174400</v>
@@ -8384,16 +8384,16 @@
         <v>45793</v>
       </c>
       <c r="C346" t="n">
-        <v>96.40737152099609</v>
+        <v>96.40736389160156</v>
       </c>
       <c r="D346" t="n">
-        <v>96.41695425699268</v>
+        <v>96.4169466268398</v>
       </c>
       <c r="E346" t="n">
-        <v>96.40737152099609</v>
+        <v>96.40736389160156</v>
       </c>
       <c r="F346" t="n">
-        <v>96.40737152099609</v>
+        <v>96.40736389160156</v>
       </c>
       <c r="G346" t="n">
         <v>10109300</v>
@@ -8430,16 +8430,16 @@
         <v>45797</v>
       </c>
       <c r="C348" t="n">
-        <v>96.43612670898438</v>
+        <v>96.43613433837891</v>
       </c>
       <c r="D348" t="n">
-        <v>96.43612670898438</v>
+        <v>96.43613433837891</v>
       </c>
       <c r="E348" t="n">
-        <v>96.42653665868291</v>
+        <v>96.42654428731873</v>
       </c>
       <c r="F348" t="n">
-        <v>96.43612670898438</v>
+        <v>96.43613433837891</v>
       </c>
       <c r="G348" t="n">
         <v>9249100</v>
@@ -8453,16 +8453,16 @@
         <v>45798</v>
       </c>
       <c r="C349" t="n">
-        <v>96.44570159912109</v>
+        <v>96.44571685791016</v>
       </c>
       <c r="D349" t="n">
-        <v>96.44570159912109</v>
+        <v>96.44571685791016</v>
       </c>
       <c r="E349" t="n">
-        <v>96.43611886466417</v>
+        <v>96.43613412193713</v>
       </c>
       <c r="F349" t="n">
-        <v>96.44570159912109</v>
+        <v>96.44571685791016</v>
       </c>
       <c r="G349" t="n">
         <v>11325900</v>
@@ -8476,16 +8476,16 @@
         <v>45799</v>
       </c>
       <c r="C350" t="n">
-        <v>96.46488952636719</v>
+        <v>96.46490478515625</v>
       </c>
       <c r="D350" t="n">
-        <v>96.46488952636719</v>
+        <v>96.46490478515625</v>
       </c>
       <c r="E350" t="n">
-        <v>96.45529947606755</v>
+        <v>96.45531473333966</v>
       </c>
       <c r="F350" t="n">
-        <v>96.45529947606755</v>
+        <v>96.45531473333966</v>
       </c>
       <c r="G350" t="n">
         <v>8901700</v>
@@ -8499,16 +8499,16 @@
         <v>45800</v>
       </c>
       <c r="C351" t="n">
-        <v>96.49363708496094</v>
+        <v>96.49365234375</v>
       </c>
       <c r="D351" t="n">
-        <v>96.50322713374224</v>
+        <v>96.5032423940478</v>
       </c>
       <c r="E351" t="n">
-        <v>96.49363708496094</v>
+        <v>96.49365234375</v>
       </c>
       <c r="F351" t="n">
-        <v>96.50322713374224</v>
+        <v>96.5032423940478</v>
       </c>
       <c r="G351" t="n">
         <v>9119400</v>
@@ -8522,16 +8522,16 @@
         <v>45804</v>
       </c>
       <c r="C352" t="n">
-        <v>96.50325012207031</v>
+        <v>96.50324249267578</v>
       </c>
       <c r="D352" t="n">
-        <v>96.5128401731361</v>
+        <v>96.51283254298339</v>
       </c>
       <c r="E352" t="n">
-        <v>96.50325012207031</v>
+        <v>96.50324249267578</v>
       </c>
       <c r="F352" t="n">
-        <v>96.5128401731361</v>
+        <v>96.51283254298339</v>
       </c>
       <c r="G352" t="n">
         <v>10526600</v>
@@ -8591,16 +8591,16 @@
         <v>45807</v>
       </c>
       <c r="C355" t="n">
-        <v>96.56076049804688</v>
+        <v>96.56076812744141</v>
       </c>
       <c r="D355" t="n">
-        <v>96.57035054759308</v>
+        <v>96.57035817774533</v>
       </c>
       <c r="E355" t="n">
-        <v>96.56076049804688</v>
+        <v>96.56076812744141</v>
       </c>
       <c r="F355" t="n">
-        <v>96.56076049804688</v>
+        <v>96.56076812744141</v>
       </c>
       <c r="G355" t="n">
         <v>14209500</v>
@@ -8660,16 +8660,16 @@
         <v>45812</v>
       </c>
       <c r="C358" t="n">
-        <v>96.60694885253906</v>
+        <v>96.60697174072266</v>
       </c>
       <c r="D358" t="n">
-        <v>96.60694885253906</v>
+        <v>96.60697174072266</v>
       </c>
       <c r="E358" t="n">
-        <v>96.59732459109935</v>
+        <v>96.59734747700276</v>
       </c>
       <c r="F358" t="n">
-        <v>96.60213305123895</v>
+        <v>96.60215593828157</v>
       </c>
       <c r="G358" t="n">
         <v>8923800</v>
@@ -8706,16 +8706,16 @@
         <v>45814</v>
       </c>
       <c r="C360" t="n">
-        <v>96.64546203613281</v>
+        <v>96.64544677734375</v>
       </c>
       <c r="D360" t="n">
-        <v>96.65507895874835</v>
+        <v>96.65506369844093</v>
       </c>
       <c r="E360" t="n">
-        <v>96.64546203613281</v>
+        <v>96.64544677734375</v>
       </c>
       <c r="F360" t="n">
-        <v>96.65027049744057</v>
+        <v>96.65025523789234</v>
       </c>
       <c r="G360" t="n">
         <v>9122400</v>
@@ -8775,16 +8775,16 @@
         <v>45819</v>
       </c>
       <c r="C363" t="n">
-        <v>96.68394470214844</v>
+        <v>96.68392944335938</v>
       </c>
       <c r="D363" t="n">
-        <v>96.68394470214844</v>
+        <v>96.68392944335938</v>
       </c>
       <c r="E363" t="n">
-        <v>96.67432043907218</v>
+        <v>96.67430518180203</v>
       </c>
       <c r="F363" t="n">
-        <v>96.67912890002943</v>
+        <v>96.6791136420004</v>
       </c>
       <c r="G363" t="n">
         <v>10138800</v>
@@ -8798,16 +8798,16 @@
         <v>45820</v>
       </c>
       <c r="C364" t="n">
-        <v>96.69355010986328</v>
+        <v>96.69355773925781</v>
       </c>
       <c r="D364" t="n">
-        <v>96.69355010986328</v>
+        <v>96.69355773925781</v>
       </c>
       <c r="E364" t="n">
-        <v>96.68393318909396</v>
+        <v>96.68394081772971</v>
       </c>
       <c r="F364" t="n">
-        <v>96.69355010986328</v>
+        <v>96.69355773925781</v>
       </c>
       <c r="G364" t="n">
         <v>9574900</v>
@@ -8821,16 +8821,16 @@
         <v>45821</v>
       </c>
       <c r="C365" t="n">
-        <v>96.73204040527344</v>
+        <v>96.7320556640625</v>
       </c>
       <c r="D365" t="n">
-        <v>96.73204040527344</v>
+        <v>96.7320556640625</v>
       </c>
       <c r="E365" t="n">
-        <v>96.72241614328465</v>
+        <v>96.72243140055555</v>
       </c>
       <c r="F365" t="n">
-        <v>96.72241614328465</v>
+        <v>96.72243140055555</v>
       </c>
       <c r="G365" t="n">
         <v>7880300</v>
@@ -8844,16 +8844,16 @@
         <v>45824</v>
       </c>
       <c r="C366" t="n">
-        <v>96.73204040527344</v>
+        <v>96.7320556640625</v>
       </c>
       <c r="D366" t="n">
-        <v>96.74166466726223</v>
+        <v>96.74167992756945</v>
       </c>
       <c r="E366" t="n">
-        <v>96.73204040527344</v>
+        <v>96.7320556640625</v>
       </c>
       <c r="F366" t="n">
-        <v>96.74166466726223</v>
+        <v>96.74167992756945</v>
       </c>
       <c r="G366" t="n">
         <v>10286500</v>
@@ -8890,16 +8890,16 @@
         <v>45826</v>
       </c>
       <c r="C368" t="n">
-        <v>96.76091003417969</v>
+        <v>96.76090240478516</v>
       </c>
       <c r="D368" t="n">
-        <v>96.77053429658464</v>
+        <v>96.77052666643127</v>
       </c>
       <c r="E368" t="n">
-        <v>96.76091003417969</v>
+        <v>96.76090240478516</v>
       </c>
       <c r="F368" t="n">
-        <v>96.77053429658464</v>
+        <v>96.77052666643127</v>
       </c>
       <c r="G368" t="n">
         <v>9783400</v>
@@ -8936,16 +8936,16 @@
         <v>45831</v>
       </c>
       <c r="C370" t="n">
-        <v>96.81864929199219</v>
+        <v>96.81864166259766</v>
       </c>
       <c r="D370" t="n">
-        <v>96.81864929199219</v>
+        <v>96.81864166259766</v>
       </c>
       <c r="E370" t="n">
-        <v>96.80902502948538</v>
+        <v>96.80901740084924</v>
       </c>
       <c r="F370" t="n">
-        <v>96.81383349015812</v>
+        <v>96.81382586114307</v>
       </c>
       <c r="G370" t="n">
         <v>8847300</v>
@@ -8959,16 +8959,16 @@
         <v>45832</v>
       </c>
       <c r="C371" t="n">
-        <v>96.82826995849609</v>
+        <v>96.82828521728516</v>
       </c>
       <c r="D371" t="n">
-        <v>96.83789422137515</v>
+        <v>96.83790948168087</v>
       </c>
       <c r="E371" t="n">
-        <v>96.82826995849609</v>
+        <v>96.82828521728516</v>
       </c>
       <c r="F371" t="n">
-        <v>96.83308576051643</v>
+        <v>96.8331010200644</v>
       </c>
       <c r="G371" t="n">
         <v>10132100</v>
@@ -8982,16 +8982,16 @@
         <v>45833</v>
       </c>
       <c r="C372" t="n">
-        <v>96.83787536621094</v>
+        <v>96.837890625</v>
       </c>
       <c r="D372" t="n">
-        <v>96.84749962721607</v>
+        <v>96.84751488752164</v>
       </c>
       <c r="E372" t="n">
-        <v>96.83787536621094</v>
+        <v>96.837890625</v>
       </c>
       <c r="F372" t="n">
-        <v>96.84268382613341</v>
+        <v>96.84269908568015</v>
       </c>
       <c r="G372" t="n">
         <v>8015100</v>
@@ -9028,16 +9028,16 @@
         <v>45835</v>
       </c>
       <c r="C374" t="n">
-        <v>96.88600921630859</v>
+        <v>96.88600158691406</v>
       </c>
       <c r="D374" t="n">
-        <v>96.88600921630859</v>
+        <v>96.88600158691406</v>
       </c>
       <c r="E374" t="n">
-        <v>96.87638495332804</v>
+        <v>96.87637732469139</v>
       </c>
       <c r="F374" t="n">
-        <v>96.88119341423747</v>
+        <v>96.88118578522216</v>
       </c>
       <c r="G374" t="n">
         <v>9742300</v>
@@ -9051,16 +9051,16 @@
         <v>45838</v>
       </c>
       <c r="C375" t="n">
-        <v>96.88600921630859</v>
+        <v>96.88600158691406</v>
       </c>
       <c r="D375" t="n">
-        <v>96.89562613812744</v>
+        <v>96.89561850797561</v>
       </c>
       <c r="E375" t="n">
-        <v>96.88600921630859</v>
+        <v>96.88600158691406</v>
       </c>
       <c r="F375" t="n">
-        <v>96.88600921630859</v>
+        <v>96.88600158691406</v>
       </c>
       <c r="G375" t="n">
         <v>18195600</v>
@@ -9120,16 +9120,16 @@
         <v>45841</v>
       </c>
       <c r="C378" t="n">
-        <v>96.96035003662109</v>
+        <v>96.96036529541016</v>
       </c>
       <c r="D378" t="n">
-        <v>96.97000758141002</v>
+        <v>96.9700228417189</v>
       </c>
       <c r="E378" t="n">
-        <v>96.96035003662109</v>
+        <v>96.96036529541016</v>
       </c>
       <c r="F378" t="n">
-        <v>96.96035003662109</v>
+        <v>96.96036529541016</v>
       </c>
       <c r="G378" t="n">
         <v>7404700</v>
@@ -9143,16 +9143,16 @@
         <v>45845</v>
       </c>
       <c r="C379" t="n">
-        <v>96.97968292236328</v>
+        <v>96.97966003417969</v>
       </c>
       <c r="D379" t="n">
-        <v>96.97968292236328</v>
+        <v>96.97966003417969</v>
       </c>
       <c r="E379" t="n">
-        <v>96.97002537580215</v>
+        <v>96.97000248989785</v>
       </c>
       <c r="F379" t="n">
-        <v>96.97968292236328</v>
+        <v>96.97966003417969</v>
       </c>
       <c r="G379" t="n">
         <v>12363900</v>
@@ -9212,16 +9212,16 @@
         <v>45848</v>
       </c>
       <c r="C382" t="n">
-        <v>97.00861358642578</v>
+        <v>97.00862121582031</v>
       </c>
       <c r="D382" t="n">
-        <v>97.01827112954146</v>
+        <v>97.01827875969551</v>
       </c>
       <c r="E382" t="n">
-        <v>96.99895604331012</v>
+        <v>96.99896367194511</v>
       </c>
       <c r="F382" t="n">
-        <v>97.00861358642578</v>
+        <v>97.00862121582031</v>
       </c>
       <c r="G382" t="n">
         <v>10071700</v>
@@ -9281,16 +9281,16 @@
         <v>45853</v>
       </c>
       <c r="C385" t="n">
-        <v>97.05689239501953</v>
+        <v>97.05690002441406</v>
       </c>
       <c r="D385" t="n">
-        <v>97.06654993871493</v>
+        <v>97.06655756886862</v>
       </c>
       <c r="E385" t="n">
-        <v>97.05689239501953</v>
+        <v>97.05690002441406</v>
       </c>
       <c r="F385" t="n">
-        <v>97.06654993871493</v>
+        <v>97.06655756886862</v>
       </c>
       <c r="G385" t="n">
         <v>10207100</v>
@@ -9373,16 +9373,16 @@
         <v>45859</v>
       </c>
       <c r="C389" t="n">
-        <v>97.13414001464844</v>
+        <v>97.13413238525391</v>
       </c>
       <c r="D389" t="n">
-        <v>97.13414001464844</v>
+        <v>97.13413238525391</v>
       </c>
       <c r="E389" t="n">
-        <v>97.12448247075388</v>
+        <v>97.12447484211791</v>
       </c>
       <c r="F389" t="n">
-        <v>97.12448247075388</v>
+        <v>97.12447484211791</v>
       </c>
       <c r="G389" t="n">
         <v>12893000</v>
@@ -9396,16 +9396,16 @@
         <v>45860</v>
       </c>
       <c r="C390" t="n">
-        <v>97.15345764160156</v>
+        <v>97.15345001220703</v>
       </c>
       <c r="D390" t="n">
-        <v>97.15345764160156</v>
+        <v>97.15345001220703</v>
       </c>
       <c r="E390" t="n">
-        <v>97.1438000974546</v>
+        <v>97.14379246881848</v>
       </c>
       <c r="F390" t="n">
-        <v>97.15345764160156</v>
+        <v>97.15345001220703</v>
       </c>
       <c r="G390" t="n">
         <v>9340600</v>
@@ -9419,16 +9419,16 @@
         <v>45861</v>
       </c>
       <c r="C391" t="n">
-        <v>97.16312408447266</v>
+        <v>97.16313171386719</v>
       </c>
       <c r="D391" t="n">
-        <v>97.16312408447266</v>
+        <v>97.16313171386719</v>
       </c>
       <c r="E391" t="n">
-        <v>97.15347390525802</v>
+        <v>97.15348153389481</v>
       </c>
       <c r="F391" t="n">
-        <v>97.16312408447266</v>
+        <v>97.16313171386719</v>
       </c>
       <c r="G391" t="n">
         <v>8056100</v>
@@ -9442,16 +9442,16 @@
         <v>45862</v>
       </c>
       <c r="C392" t="n">
-        <v>97.17276763916016</v>
+        <v>97.17277526855469</v>
       </c>
       <c r="D392" t="n">
-        <v>97.17276763916016</v>
+        <v>97.17277526855469</v>
       </c>
       <c r="E392" t="n">
-        <v>97.16311009478702</v>
+        <v>97.1631177234233</v>
       </c>
       <c r="F392" t="n">
-        <v>97.16311009478702</v>
+        <v>97.1631177234233</v>
       </c>
       <c r="G392" t="n">
         <v>10701600</v>
@@ -9557,16 +9557,16 @@
         <v>45869</v>
       </c>
       <c r="C397" t="n">
-        <v>97.25000762939453</v>
+        <v>97.25</v>
       </c>
       <c r="D397" t="n">
-        <v>97.25000762939453</v>
+        <v>97.25</v>
       </c>
       <c r="E397" t="n">
-        <v>97.24035008558064</v>
+        <v>97.24034245694376</v>
       </c>
       <c r="F397" t="n">
-        <v>97.24517517421383</v>
+        <v>97.2451675451984</v>
       </c>
       <c r="G397" t="n">
         <v>19051200</v>
@@ -9580,16 +9580,16 @@
         <v>45870</v>
       </c>
       <c r="C398" t="n">
-        <v>97.28102874755859</v>
+        <v>97.28101348876953</v>
       </c>
       <c r="D398" t="n">
-        <v>97.29072112835438</v>
+        <v>97.29070586804504</v>
       </c>
       <c r="E398" t="n">
-        <v>97.28102874755859</v>
+        <v>97.28101348876953</v>
       </c>
       <c r="F398" t="n">
-        <v>97.28102874755859</v>
+        <v>97.28101348876953</v>
       </c>
       <c r="G398" t="n">
         <v>26832500</v>
@@ -9626,16 +9626,16 @@
         <v>45874</v>
       </c>
       <c r="C400" t="n">
-        <v>97.31009674072266</v>
+        <v>97.31010437011719</v>
       </c>
       <c r="D400" t="n">
-        <v>97.31009674072266</v>
+        <v>97.31010437011719</v>
       </c>
       <c r="E400" t="n">
-        <v>97.30041175322201</v>
+        <v>97.30041938185722</v>
       </c>
       <c r="F400" t="n">
-        <v>97.30041175322201</v>
+        <v>97.30041938185722</v>
       </c>
       <c r="G400" t="n">
         <v>12350300</v>
@@ -9718,16 +9718,16 @@
         <v>45880</v>
       </c>
       <c r="C404" t="n">
-        <v>97.3779296875</v>
+        <v>97.37792205810547</v>
       </c>
       <c r="D404" t="n">
-        <v>97.3779296875</v>
+        <v>97.37792205810547</v>
       </c>
       <c r="E404" t="n">
-        <v>97.36824469989307</v>
+        <v>97.36823707125734</v>
       </c>
       <c r="F404" t="n">
-        <v>97.3779296875</v>
+        <v>97.37792205810547</v>
       </c>
       <c r="G404" t="n">
         <v>12940300</v>
@@ -9741,16 +9741,16 @@
         <v>45881</v>
       </c>
       <c r="C405" t="n">
-        <v>97.3779296875</v>
+        <v>97.37792205810547</v>
       </c>
       <c r="D405" t="n">
-        <v>97.38762206822724</v>
+        <v>97.38761443807333</v>
       </c>
       <c r="E405" t="n">
-        <v>97.3779296875</v>
+        <v>97.37792205810547</v>
       </c>
       <c r="F405" t="n">
-        <v>97.38762206822724</v>
+        <v>97.38761443807333</v>
       </c>
       <c r="G405" t="n">
         <v>12918200</v>
@@ -9833,16 +9833,16 @@
         <v>45887</v>
       </c>
       <c r="C409" t="n">
-        <v>97.46514129638672</v>
+        <v>97.46513366699219</v>
       </c>
       <c r="D409" t="n">
-        <v>97.46514129638672</v>
+        <v>97.46513366699219</v>
       </c>
       <c r="E409" t="n">
-        <v>97.44575653593293</v>
+        <v>97.4457489080558</v>
       </c>
       <c r="F409" t="n">
-        <v>97.45544891615982</v>
+        <v>97.455441287524</v>
       </c>
       <c r="G409" t="n">
         <v>14768500</v>
@@ -9856,16 +9856,16 @@
         <v>45888</v>
       </c>
       <c r="C410" t="n">
-        <v>97.46514129638672</v>
+        <v>97.46513366699219</v>
       </c>
       <c r="D410" t="n">
-        <v>97.47482628349368</v>
+        <v>97.47481865334103</v>
       </c>
       <c r="E410" t="n">
-        <v>97.46514129638672</v>
+        <v>97.46513366699219</v>
       </c>
       <c r="F410" t="n">
-        <v>97.47482628349368</v>
+        <v>97.47481865334103</v>
       </c>
       <c r="G410" t="n">
         <v>10474900</v>
@@ -9879,16 +9879,16 @@
         <v>45889</v>
       </c>
       <c r="C411" t="n">
-        <v>97.48451995849609</v>
+        <v>97.48450469970703</v>
       </c>
       <c r="D411" t="n">
-        <v>97.48451995849609</v>
+        <v>97.48450469970703</v>
       </c>
       <c r="E411" t="n">
-        <v>97.47482757814046</v>
+        <v>97.47481232086851</v>
       </c>
       <c r="F411" t="n">
-        <v>97.48451995849609</v>
+        <v>97.48450469970703</v>
       </c>
       <c r="G411" t="n">
         <v>10922100</v>
@@ -9902,16 +9902,16 @@
         <v>45890</v>
       </c>
       <c r="C412" t="n">
-        <v>97.48451995849609</v>
+        <v>97.48450469970703</v>
       </c>
       <c r="D412" t="n">
-        <v>97.49421233885172</v>
+        <v>97.49419707854555</v>
       </c>
       <c r="E412" t="n">
-        <v>97.48451995849609</v>
+        <v>97.48450469970703</v>
       </c>
       <c r="F412" t="n">
-        <v>97.49421233885172</v>
+        <v>97.49419707854555</v>
       </c>
       <c r="G412" t="n">
         <v>8765300</v>
@@ -9925,16 +9925,16 @@
         <v>45891</v>
       </c>
       <c r="C413" t="n">
-        <v>97.52327728271484</v>
+        <v>97.52328491210938</v>
       </c>
       <c r="D413" t="n">
-        <v>97.52327728271484</v>
+        <v>97.52328491210938</v>
       </c>
       <c r="E413" t="n">
-        <v>97.51358490283667</v>
+        <v>97.51359253147295</v>
       </c>
       <c r="F413" t="n">
-        <v>97.52327728271484</v>
+        <v>97.52328491210938</v>
       </c>
       <c r="G413" t="n">
         <v>13160400</v>
@@ -10017,16 +10017,16 @@
         <v>45897</v>
       </c>
       <c r="C417" t="n">
-        <v>97.56203460693359</v>
+        <v>97.56204223632812</v>
       </c>
       <c r="D417" t="n">
-        <v>97.57172698633468</v>
+        <v>97.57173461648718</v>
       </c>
       <c r="E417" t="n">
-        <v>97.56203460693359</v>
+        <v>97.56204223632812</v>
       </c>
       <c r="F417" t="n">
-        <v>97.56687710007449</v>
+        <v>97.56688472984771</v>
       </c>
       <c r="G417" t="n">
         <v>8816600</v>
@@ -10086,16 +10086,16 @@
         <v>45903</v>
       </c>
       <c r="C420" t="n">
-        <v>97.63964080810547</v>
+        <v>97.63963317871094</v>
       </c>
       <c r="D420" t="n">
-        <v>97.63964080810547</v>
+        <v>97.63963317871094</v>
       </c>
       <c r="E420" t="n">
-        <v>97.62991366693002</v>
+        <v>97.62990603829556</v>
       </c>
       <c r="F420" t="n">
-        <v>97.63477352770036</v>
+        <v>97.63476589868615</v>
       </c>
       <c r="G420" t="n">
         <v>14296000</v>
@@ -10109,16 +10109,16 @@
         <v>45904</v>
       </c>
       <c r="C421" t="n">
-        <v>97.65907287597656</v>
+        <v>97.65908050537109</v>
       </c>
       <c r="D421" t="n">
-        <v>97.65907287597656</v>
+        <v>97.65908050537109</v>
       </c>
       <c r="E421" t="n">
-        <v>97.64935315590837</v>
+        <v>97.64936078454357</v>
       </c>
       <c r="F421" t="n">
-        <v>97.65421301594246</v>
+        <v>97.65422064495733</v>
       </c>
       <c r="G421" t="n">
         <v>11300200</v>
@@ -10132,16 +10132,16 @@
         <v>45905</v>
       </c>
       <c r="C422" t="n">
-        <v>97.67854309082031</v>
+        <v>97.67855072021484</v>
       </c>
       <c r="D422" t="n">
-        <v>97.68826281247419</v>
+        <v>97.68827044262791</v>
       </c>
       <c r="E422" t="n">
-        <v>97.67854309082031</v>
+        <v>97.67855072021484</v>
       </c>
       <c r="F422" t="n">
-        <v>97.68826281247419</v>
+        <v>97.68827044262791</v>
       </c>
       <c r="G422" t="n">
         <v>15312000</v>
@@ -10224,16 +10224,16 @@
         <v>45911</v>
       </c>
       <c r="C426" t="n">
-        <v>97.73687744140625</v>
+        <v>97.73688507080078</v>
       </c>
       <c r="D426" t="n">
-        <v>97.73687744140625</v>
+        <v>97.73688507080078</v>
       </c>
       <c r="E426" t="n">
-        <v>97.7271503014768</v>
+        <v>97.72715793011203</v>
       </c>
       <c r="F426" t="n">
-        <v>97.73201758125843</v>
+        <v>97.7320252102736</v>
       </c>
       <c r="G426" t="n">
         <v>9136600</v>
@@ -10247,16 +10247,16 @@
         <v>45912</v>
       </c>
       <c r="C427" t="n">
-        <v>97.76605987548828</v>
+        <v>97.76605224609375</v>
       </c>
       <c r="D427" t="n">
-        <v>97.77578701625686</v>
+        <v>97.77577938610324</v>
       </c>
       <c r="E427" t="n">
-        <v>97.76605987548828</v>
+        <v>97.76605224609375</v>
       </c>
       <c r="F427" t="n">
-        <v>97.76605987548828</v>
+        <v>97.76605224609375</v>
       </c>
       <c r="G427" t="n">
         <v>10482000</v>
@@ -10270,16 +10270,16 @@
         <v>45915</v>
       </c>
       <c r="C428" t="n">
-        <v>97.76605987548828</v>
+        <v>97.76605224609375</v>
       </c>
       <c r="D428" t="n">
-        <v>97.77578701625686</v>
+        <v>97.77577938610324</v>
       </c>
       <c r="E428" t="n">
-        <v>97.76605987548828</v>
+        <v>97.76605224609375</v>
       </c>
       <c r="F428" t="n">
-        <v>97.76605987548828</v>
+        <v>97.76605224609375</v>
       </c>
       <c r="G428" t="n">
         <v>15288300</v>
@@ -10293,16 +10293,16 @@
         <v>45916</v>
       </c>
       <c r="C429" t="n">
-        <v>97.78550720214844</v>
+        <v>97.78551483154297</v>
       </c>
       <c r="D429" t="n">
-        <v>97.79522692259125</v>
+        <v>97.79523455274413</v>
       </c>
       <c r="E429" t="n">
-        <v>97.78550720214844</v>
+        <v>97.78551483154297</v>
       </c>
       <c r="F429" t="n">
-        <v>97.78550720214844</v>
+        <v>97.78551483154297</v>
       </c>
       <c r="G429" t="n">
         <v>11551900</v>
@@ -10316,16 +10316,16 @@
         <v>45917</v>
       </c>
       <c r="C430" t="n">
-        <v>97.79523468017578</v>
+        <v>97.79522705078125</v>
       </c>
       <c r="D430" t="n">
-        <v>97.80496182102412</v>
+        <v>97.80495419087075</v>
       </c>
       <c r="E430" t="n">
-        <v>97.79523468017578</v>
+        <v>97.79522705078125</v>
       </c>
       <c r="F430" t="n">
-        <v>97.80496182102412</v>
+        <v>97.80495419087075</v>
       </c>
       <c r="G430" t="n">
         <v>10381200</v>
@@ -10339,16 +10339,16 @@
         <v>45918</v>
       </c>
       <c r="C431" t="n">
-        <v>97.81468200683594</v>
+        <v>97.81467437744141</v>
       </c>
       <c r="D431" t="n">
-        <v>97.81468200683594</v>
+        <v>97.81467437744141</v>
       </c>
       <c r="E431" t="n">
-        <v>97.80495486667922</v>
+        <v>97.8049472380434</v>
       </c>
       <c r="F431" t="n">
-        <v>97.81468200683594</v>
+        <v>97.81467437744141</v>
       </c>
       <c r="G431" t="n">
         <v>13414500</v>
@@ -10362,16 +10362,16 @@
         <v>45919</v>
       </c>
       <c r="C432" t="n">
-        <v>97.85358428955078</v>
+        <v>97.85359191894531</v>
       </c>
       <c r="D432" t="n">
-        <v>97.85358428955078</v>
+        <v>97.85359191894531</v>
       </c>
       <c r="E432" t="n">
-        <v>97.84385714928058</v>
+        <v>97.84386477791671</v>
       </c>
       <c r="F432" t="n">
-        <v>97.84385714928058</v>
+        <v>97.84386477791671</v>
       </c>
       <c r="G432" t="n">
         <v>11174000</v>
@@ -10385,16 +10385,16 @@
         <v>45922</v>
       </c>
       <c r="C433" t="n">
-        <v>97.85358428955078</v>
+        <v>97.85359191894531</v>
       </c>
       <c r="D433" t="n">
-        <v>97.86330401018691</v>
+        <v>97.86331164033926</v>
       </c>
       <c r="E433" t="n">
-        <v>97.85358428955078</v>
+        <v>97.85359191894531</v>
       </c>
       <c r="F433" t="n">
-        <v>97.85358428955078</v>
+        <v>97.85359191894531</v>
       </c>
       <c r="G433" t="n">
         <v>12279500</v>
@@ -10408,16 +10408,16 @@
         <v>45923</v>
       </c>
       <c r="C434" t="n">
-        <v>97.87303924560547</v>
+        <v>97.87303161621094</v>
       </c>
       <c r="D434" t="n">
-        <v>97.87303924560547</v>
+        <v>97.87303161621094</v>
       </c>
       <c r="E434" t="n">
-        <v>97.86331210453073</v>
+        <v>97.86330447589445</v>
       </c>
       <c r="F434" t="n">
-        <v>97.86817938488544</v>
+        <v>97.86817175586975</v>
       </c>
       <c r="G434" t="n">
         <v>11191700</v>
@@ -10431,16 +10431,16 @@
         <v>45924</v>
       </c>
       <c r="C435" t="n">
-        <v>97.88276672363281</v>
+        <v>97.88275909423828</v>
       </c>
       <c r="D435" t="n">
-        <v>97.88276672363281</v>
+        <v>97.88275909423828</v>
       </c>
       <c r="E435" t="n">
-        <v>97.87303958252458</v>
+        <v>97.87303195388823</v>
       </c>
       <c r="F435" t="n">
-        <v>97.87789944326134</v>
+        <v>97.8778918142462</v>
       </c>
       <c r="G435" t="n">
         <v>10108500</v>
@@ -10454,16 +10454,16 @@
         <v>45925</v>
       </c>
       <c r="C436" t="n">
-        <v>97.89248657226562</v>
+        <v>97.89247894287109</v>
       </c>
       <c r="D436" t="n">
-        <v>97.89248657226562</v>
+        <v>97.89247894287109</v>
       </c>
       <c r="E436" t="n">
-        <v>97.88275943188202</v>
+        <v>97.88275180324558</v>
       </c>
       <c r="F436" t="n">
-        <v>97.88275943188202</v>
+        <v>97.88275180324558</v>
       </c>
       <c r="G436" t="n">
         <v>10549100</v>
@@ -10500,16 +10500,16 @@
         <v>45929</v>
       </c>
       <c r="C438" t="n">
-        <v>97.93137359619141</v>
+        <v>97.93138122558594</v>
       </c>
       <c r="D438" t="n">
-        <v>97.93137359619141</v>
+        <v>97.93138122558594</v>
       </c>
       <c r="E438" t="n">
-        <v>97.92165387610677</v>
+        <v>97.92166150474409</v>
       </c>
       <c r="F438" t="n">
-        <v>97.93137359619141</v>
+        <v>97.93138122558594</v>
       </c>
       <c r="G438" t="n">
         <v>13580800</v>
@@ -10523,16 +10523,16 @@
         <v>45930</v>
       </c>
       <c r="C439" t="n">
-        <v>97.93137359619141</v>
+        <v>97.93138122558594</v>
       </c>
       <c r="D439" t="n">
-        <v>97.94110073590969</v>
+        <v>97.94110836606202</v>
       </c>
       <c r="E439" t="n">
-        <v>97.93137359619141</v>
+        <v>97.93138122558594</v>
       </c>
       <c r="F439" t="n">
-        <v>97.93624087586737</v>
+        <v>97.9362485056411</v>
       </c>
       <c r="G439" t="n">
         <v>22909500</v>
@@ -10546,16 +10546,16 @@
         <v>45931</v>
       </c>
       <c r="C440" t="n">
-        <v>97.94797515869141</v>
+        <v>97.94796752929688</v>
       </c>
       <c r="D440" t="n">
-        <v>97.95772848817732</v>
+        <v>97.95772085802308</v>
       </c>
       <c r="E440" t="n">
-        <v>97.94797515869141</v>
+        <v>97.94796752929688</v>
       </c>
       <c r="F440" t="n">
-        <v>97.95772848817732</v>
+        <v>97.95772085802308</v>
       </c>
       <c r="G440" t="n">
         <v>26613600</v>
@@ -10592,16 +10592,16 @@
         <v>45933</v>
       </c>
       <c r="C442" t="n">
-        <v>97.99676513671875</v>
+        <v>97.99675750732422</v>
       </c>
       <c r="D442" t="n">
-        <v>97.99676513671875</v>
+        <v>97.99675750732422</v>
       </c>
       <c r="E442" t="n">
-        <v>97.98701180713383</v>
+        <v>97.98700417849862</v>
       </c>
       <c r="F442" t="n">
-        <v>97.99676513671875</v>
+        <v>97.99675750732422</v>
       </c>
       <c r="G442" t="n">
         <v>13837400</v>
@@ -10615,16 +10615,16 @@
         <v>45936</v>
       </c>
       <c r="C443" t="n">
-        <v>97.99676513671875</v>
+        <v>97.99675750732422</v>
       </c>
       <c r="D443" t="n">
-        <v>98.00652591159343</v>
+        <v>98.00651828143899</v>
       </c>
       <c r="E443" t="n">
-        <v>97.99676513671875</v>
+        <v>97.99675750732422</v>
       </c>
       <c r="F443" t="n">
-        <v>98.00652591159343</v>
+        <v>98.00651828143899</v>
       </c>
       <c r="G443" t="n">
         <v>13944300</v>
@@ -10661,16 +10661,16 @@
         <v>45938</v>
       </c>
       <c r="C445" t="n">
-        <v>98.02603149414062</v>
+        <v>98.02604675292969</v>
       </c>
       <c r="D445" t="n">
-        <v>98.02603149414062</v>
+        <v>98.02604675292969</v>
       </c>
       <c r="E445" t="n">
-        <v>98.01627816540361</v>
+        <v>98.01629342267447</v>
       </c>
       <c r="F445" t="n">
-        <v>98.02603149414062</v>
+        <v>98.02604675292969</v>
       </c>
       <c r="G445" t="n">
         <v>16811200</v>
@@ -10684,16 +10684,16 @@
         <v>45939</v>
       </c>
       <c r="C446" t="n">
-        <v>98.03580474853516</v>
+        <v>98.03579711914062</v>
       </c>
       <c r="D446" t="n">
-        <v>98.04556552380387</v>
+        <v>98.04555789364973</v>
       </c>
       <c r="E446" t="n">
-        <v>98.02604397326645</v>
+        <v>98.02603634463152</v>
       </c>
       <c r="F446" t="n">
-        <v>98.04556552380387</v>
+        <v>98.04555789364973</v>
       </c>
       <c r="G446" t="n">
         <v>15718900</v>
@@ -10707,16 +10707,16 @@
         <v>45940</v>
       </c>
       <c r="C447" t="n">
-        <v>98.08458709716797</v>
+        <v>98.08460235595703</v>
       </c>
       <c r="D447" t="n">
-        <v>98.08458709716797</v>
+        <v>98.08460235595703</v>
       </c>
       <c r="E447" t="n">
-        <v>98.06506554943334</v>
+        <v>98.06508080518547</v>
       </c>
       <c r="F447" t="n">
-        <v>98.07482632330066</v>
+        <v>98.07484158057125</v>
       </c>
       <c r="G447" t="n">
         <v>18966600</v>
@@ -10730,16 +10730,16 @@
         <v>45943</v>
       </c>
       <c r="C448" t="n">
-        <v>98.07483673095703</v>
+        <v>98.0748291015625</v>
       </c>
       <c r="D448" t="n">
-        <v>98.08459750586016</v>
+        <v>98.08458987570631</v>
       </c>
       <c r="E448" t="n">
-        <v>98.07483673095703</v>
+        <v>98.0748291015625</v>
       </c>
       <c r="F448" t="n">
-        <v>98.07483673095703</v>
+        <v>98.0748291015625</v>
       </c>
       <c r="G448" t="n">
         <v>14453500</v>
@@ -10753,16 +10753,16 @@
         <v>45944</v>
       </c>
       <c r="C449" t="n">
-        <v>98.08458709716797</v>
+        <v>98.08460235595703</v>
       </c>
       <c r="D449" t="n">
-        <v>98.0943404257463</v>
+        <v>98.09435568605265</v>
       </c>
       <c r="E449" t="n">
-        <v>98.08458709716797</v>
+        <v>98.08460235595703</v>
       </c>
       <c r="F449" t="n">
-        <v>98.08458709716797</v>
+        <v>98.08460235595703</v>
       </c>
       <c r="G449" t="n">
         <v>13475000</v>
@@ -10776,16 +10776,16 @@
         <v>45945</v>
       </c>
       <c r="C450" t="n">
-        <v>98.10410308837891</v>
+        <v>98.10411071777344</v>
       </c>
       <c r="D450" t="n">
-        <v>98.10410308837891</v>
+        <v>98.10411071777344</v>
       </c>
       <c r="E450" t="n">
-        <v>98.09434231432367</v>
+        <v>98.09434994295911</v>
       </c>
       <c r="F450" t="n">
-        <v>98.10410308837891</v>
+        <v>98.10411071777344</v>
       </c>
       <c r="G450" t="n">
         <v>11069100</v>
@@ -10822,16 +10822,16 @@
         <v>45947</v>
       </c>
       <c r="C452" t="n">
-        <v>98.14313507080078</v>
+        <v>98.14315032958984</v>
       </c>
       <c r="D452" t="n">
-        <v>98.14313507080078</v>
+        <v>98.14315032958984</v>
       </c>
       <c r="E452" t="n">
-        <v>98.13337429711039</v>
+        <v>98.13338955438189</v>
       </c>
       <c r="F452" t="n">
-        <v>98.13825840660002</v>
+        <v>98.13827366463087</v>
       </c>
       <c r="G452" t="n">
         <v>14603500</v>
@@ -10845,16 +10845,16 @@
         <v>45950</v>
       </c>
       <c r="C453" t="n">
-        <v>98.15290069580078</v>
+        <v>98.15291595458984</v>
       </c>
       <c r="D453" t="n">
-        <v>98.15290069580078</v>
+        <v>98.15291595458984</v>
       </c>
       <c r="E453" t="n">
-        <v>98.14313992162796</v>
+        <v>98.14315517889962</v>
       </c>
       <c r="F453" t="n">
-        <v>98.15290069580078</v>
+        <v>98.15291595458984</v>
       </c>
       <c r="G453" t="n">
         <v>16129100</v>
@@ -10868,16 +10868,16 @@
         <v>45951</v>
       </c>
       <c r="C454" t="n">
-        <v>98.17242431640625</v>
+        <v>98.17241668701172</v>
       </c>
       <c r="D454" t="n">
-        <v>98.17242431640625</v>
+        <v>98.17241668701172</v>
       </c>
       <c r="E454" t="n">
-        <v>98.16266354128715</v>
+        <v>98.16265591265116</v>
       </c>
       <c r="F454" t="n">
-        <v>98.16266354128715</v>
+        <v>98.16265591265116</v>
       </c>
       <c r="G454" t="n">
         <v>12061900</v>
@@ -10891,16 +10891,16 @@
         <v>45952</v>
       </c>
       <c r="C455" t="n">
-        <v>98.18218994140625</v>
+        <v>98.18217468261719</v>
       </c>
       <c r="D455" t="n">
-        <v>98.18218994140625</v>
+        <v>98.18217468261719</v>
       </c>
       <c r="E455" t="n">
-        <v>98.172429165805</v>
+        <v>98.17241390853287</v>
       </c>
       <c r="F455" t="n">
-        <v>98.18218994140625</v>
+        <v>98.18217468261719</v>
       </c>
       <c r="G455" t="n">
         <v>9089900</v>
@@ -10914,16 +10914,16 @@
         <v>45953</v>
       </c>
       <c r="C456" t="n">
-        <v>98.19194030761719</v>
+        <v>98.19193267822266</v>
       </c>
       <c r="D456" t="n">
-        <v>98.19194030761719</v>
+        <v>98.19193267822266</v>
       </c>
       <c r="E456" t="n">
-        <v>98.18217953305069</v>
+        <v>98.18217190441455</v>
       </c>
       <c r="F456" t="n">
-        <v>98.19194030761719</v>
+        <v>98.19193267822266</v>
       </c>
       <c r="G456" t="n">
         <v>10658100</v>
@@ -10937,16 +10937,16 @@
         <v>45954</v>
       </c>
       <c r="C457" t="n">
-        <v>98.22122192382812</v>
+        <v>98.22121429443359</v>
       </c>
       <c r="D457" t="n">
-        <v>98.22122192382812</v>
+        <v>98.22121429443359</v>
       </c>
       <c r="E457" t="n">
-        <v>98.21146114859204</v>
+        <v>98.21145351995568</v>
       </c>
       <c r="F457" t="n">
-        <v>98.22122192382812</v>
+        <v>98.22121429443359</v>
       </c>
       <c r="G457" t="n">
         <v>12382000</v>
@@ -10983,16 +10983,16 @@
         <v>45958</v>
       </c>
       <c r="C459" t="n">
-        <v>98.24073791503906</v>
+        <v>98.24072265625</v>
       </c>
       <c r="D459" t="n">
-        <v>98.25049869046254</v>
+        <v>98.25048343015742</v>
       </c>
       <c r="E459" t="n">
-        <v>98.24073791503906</v>
+        <v>98.24072265625</v>
       </c>
       <c r="F459" t="n">
-        <v>98.24073791503906</v>
+        <v>98.24072265625</v>
       </c>
       <c r="G459" t="n">
         <v>11134700</v>
@@ -11006,16 +11006,16 @@
         <v>45959</v>
       </c>
       <c r="C460" t="n">
-        <v>98.25048828125</v>
+        <v>98.25048065185547</v>
       </c>
       <c r="D460" t="n">
-        <v>98.26024905563935</v>
+        <v>98.26024142548688</v>
       </c>
       <c r="E460" t="n">
-        <v>98.25048828125</v>
+        <v>98.25048065185547</v>
       </c>
       <c r="F460" t="n">
-        <v>98.26024905563935</v>
+        <v>98.26024142548688</v>
       </c>
       <c r="G460" t="n">
         <v>14177700</v>
@@ -11029,16 +11029,16 @@
         <v>45960</v>
       </c>
       <c r="C461" t="n">
-        <v>98.26026153564453</v>
+        <v>98.26025390625</v>
       </c>
       <c r="D461" t="n">
-        <v>98.27001486598327</v>
+        <v>98.27000723583144</v>
       </c>
       <c r="E461" t="n">
-        <v>98.26026153564453</v>
+        <v>98.26025390625</v>
       </c>
       <c r="F461" t="n">
-        <v>98.26026153564453</v>
+        <v>98.26025390625</v>
       </c>
       <c r="G461" t="n">
         <v>12370700</v>
@@ -11052,16 +11052,16 @@
         <v>45961</v>
       </c>
       <c r="C462" t="n">
-        <v>98.28952026367188</v>
+        <v>98.28952789306641</v>
       </c>
       <c r="D462" t="n">
-        <v>98.29928103769679</v>
+        <v>98.29928866784897</v>
       </c>
       <c r="E462" t="n">
-        <v>98.28952026367188</v>
+        <v>98.28952789306641</v>
       </c>
       <c r="F462" t="n">
-        <v>98.29439692803977</v>
+        <v>98.29440455781285</v>
       </c>
       <c r="G462" t="n">
         <v>23254100</v>
@@ -11075,16 +11075,16 @@
         <v>45964</v>
       </c>
       <c r="C463" t="n">
-        <v>98.31694793701172</v>
+        <v>98.31693267822266</v>
       </c>
       <c r="D463" t="n">
-        <v>98.31694793701172</v>
+        <v>98.31693267822266</v>
       </c>
       <c r="E463" t="n">
-        <v>98.30715332055669</v>
+        <v>98.30713806328775</v>
       </c>
       <c r="F463" t="n">
-        <v>98.31204689323255</v>
+        <v>98.31203163520412</v>
       </c>
       <c r="G463" t="n">
         <v>27049200</v>
@@ -11098,16 +11098,16 @@
         <v>45965</v>
       </c>
       <c r="C464" t="n">
-        <v>98.31694793701172</v>
+        <v>98.31693267822266</v>
       </c>
       <c r="D464" t="n">
-        <v>98.31694793701172</v>
+        <v>98.31693267822266</v>
       </c>
       <c r="E464" t="n">
-        <v>98.31204689323255</v>
+        <v>98.31203163520412</v>
       </c>
       <c r="F464" t="n">
-        <v>98.31694793701172</v>
+        <v>98.31693267822266</v>
       </c>
       <c r="G464" t="n">
         <v>15707500</v>
@@ -11144,16 +11144,16 @@
         <v>45967</v>
       </c>
       <c r="C466" t="n">
-        <v>98.34632110595703</v>
+        <v>98.34632873535156</v>
       </c>
       <c r="D466" t="n">
-        <v>98.34632110595703</v>
+        <v>98.34632873535156</v>
       </c>
       <c r="E466" t="n">
-        <v>98.33652648982164</v>
+        <v>98.33653411845633</v>
       </c>
       <c r="F466" t="n">
-        <v>98.34632110595703</v>
+        <v>98.34632873535156</v>
       </c>
       <c r="G466" t="n">
         <v>16658100</v>
@@ -11190,16 +11190,16 @@
         <v>45971</v>
       </c>
       <c r="C468" t="n">
-        <v>98.38550567626953</v>
+        <v>98.385498046875</v>
       </c>
       <c r="D468" t="n">
-        <v>98.39530029375656</v>
+        <v>98.39529266360249</v>
       </c>
       <c r="E468" t="n">
-        <v>98.38550567626953</v>
+        <v>98.385498046875</v>
       </c>
       <c r="F468" t="n">
-        <v>98.39530029375656</v>
+        <v>98.39529266360249</v>
       </c>
       <c r="G468" t="n">
         <v>14121900</v>
@@ -11213,16 +11213,16 @@
         <v>45972</v>
       </c>
       <c r="C469" t="n">
-        <v>98.39529418945312</v>
+        <v>98.39528656005859</v>
       </c>
       <c r="D469" t="n">
-        <v>98.39529418945312</v>
+        <v>98.39528656005859</v>
       </c>
       <c r="E469" t="n">
-        <v>98.38549957257375</v>
+        <v>98.38549194393867</v>
       </c>
       <c r="F469" t="n">
-        <v>98.39529418945312</v>
+        <v>98.39528656005859</v>
       </c>
       <c r="G469" t="n">
         <v>8697800</v>
@@ -11259,16 +11259,16 @@
         <v>45974</v>
       </c>
       <c r="C471" t="n">
-        <v>98.41486358642578</v>
+        <v>98.41487121582031</v>
       </c>
       <c r="D471" t="n">
-        <v>98.41486358642578</v>
+        <v>98.41487121582031</v>
       </c>
       <c r="E471" t="n">
-        <v>98.40506897077708</v>
+        <v>98.4050765994123</v>
       </c>
       <c r="F471" t="n">
-        <v>98.40506897077708</v>
+        <v>98.4050765994123</v>
       </c>
       <c r="G471" t="n">
         <v>11255600</v>
@@ -11374,16 +11374,16 @@
         <v>45981</v>
       </c>
       <c r="C476" t="n">
-        <v>98.49320983886719</v>
+        <v>98.49321746826172</v>
       </c>
       <c r="D476" t="n">
-        <v>98.49320983886719</v>
+        <v>98.49321746826172</v>
       </c>
       <c r="E476" t="n">
-        <v>98.47362060672063</v>
+        <v>98.47362823459777</v>
       </c>
       <c r="F476" t="n">
-        <v>98.47362060672063</v>
+        <v>98.47362823459777</v>
       </c>
       <c r="G476" t="n">
         <v>15261700</v>
@@ -11397,16 +11397,16 @@
         <v>45982</v>
       </c>
       <c r="C477" t="n">
-        <v>98.51278686523438</v>
+        <v>98.51277923583984</v>
       </c>
       <c r="D477" t="n">
-        <v>98.51278686523438</v>
+        <v>98.51277923583984</v>
       </c>
       <c r="E477" t="n">
-        <v>98.50299224963184</v>
+        <v>98.50298462099586</v>
       </c>
       <c r="F477" t="n">
-        <v>98.51278686523438</v>
+        <v>98.51277923583984</v>
       </c>
       <c r="G477" t="n">
         <v>16446900</v>
@@ -11420,16 +11420,16 @@
         <v>45985</v>
       </c>
       <c r="C478" t="n">
-        <v>98.52259063720703</v>
+        <v>98.5225830078125</v>
       </c>
       <c r="D478" t="n">
-        <v>98.53238525371985</v>
+        <v>98.53237762356683</v>
       </c>
       <c r="E478" t="n">
-        <v>98.52259063720703</v>
+        <v>98.5225830078125</v>
       </c>
       <c r="F478" t="n">
-        <v>98.52259063720703</v>
+        <v>98.5225830078125</v>
       </c>
       <c r="G478" t="n">
         <v>15830800</v>
@@ -11466,16 +11466,16 @@
         <v>45987</v>
       </c>
       <c r="C480" t="n">
-        <v>98.55195617675781</v>
+        <v>98.55196380615234</v>
       </c>
       <c r="D480" t="n">
-        <v>98.56175079219341</v>
+        <v>98.56175842234617</v>
       </c>
       <c r="E480" t="n">
-        <v>98.55195617675781</v>
+        <v>98.55196380615234</v>
       </c>
       <c r="F480" t="n">
-        <v>98.55195617675781</v>
+        <v>98.55196380615234</v>
       </c>
       <c r="G480" t="n">
         <v>11948500</v>
@@ -11489,16 +11489,16 @@
         <v>45989</v>
       </c>
       <c r="C481" t="n">
-        <v>98.58134460449219</v>
+        <v>98.58132934570312</v>
       </c>
       <c r="D481" t="n">
-        <v>98.59113922112526</v>
+        <v>98.59112396082016</v>
       </c>
       <c r="E481" t="n">
-        <v>98.57155745896257</v>
+        <v>98.5715422016884</v>
       </c>
       <c r="F481" t="n">
-        <v>98.58134460449219</v>
+        <v>98.58132934570312</v>
       </c>
       <c r="G481" t="n">
         <v>24417500</v>
@@ -11512,16 +11512,16 @@
         <v>45992</v>
       </c>
       <c r="C482" t="n">
-        <v>98.60391998291016</v>
+        <v>98.60391235351562</v>
       </c>
       <c r="D482" t="n">
-        <v>98.60391998291016</v>
+        <v>98.60391235351562</v>
       </c>
       <c r="E482" t="n">
-        <v>98.59410231425819</v>
+        <v>98.59409468562329</v>
       </c>
       <c r="F482" t="n">
-        <v>98.60391998291016</v>
+        <v>98.60391235351562</v>
       </c>
       <c r="G482" t="n">
         <v>29025600</v>
@@ -11535,16 +11535,16 @@
         <v>45993</v>
       </c>
       <c r="C483" t="n">
-        <v>98.62358093261719</v>
+        <v>98.62357330322266</v>
       </c>
       <c r="D483" t="n">
-        <v>98.62358093261719</v>
+        <v>98.62357330322266</v>
       </c>
       <c r="E483" t="n">
-        <v>98.61375576850331</v>
+        <v>98.61374813986885</v>
       </c>
       <c r="F483" t="n">
-        <v>98.61375576850331</v>
+        <v>98.61374813986885</v>
       </c>
       <c r="G483" t="n">
         <v>14362600</v>
@@ -11581,16 +11581,16 @@
         <v>45995</v>
       </c>
       <c r="C485" t="n">
-        <v>98.65303802490234</v>
+        <v>98.65304565429688</v>
       </c>
       <c r="D485" t="n">
-        <v>98.65303802490234</v>
+        <v>98.65304565429688</v>
       </c>
       <c r="E485" t="n">
-        <v>98.6432128618746</v>
+        <v>98.64322049050931</v>
       </c>
       <c r="F485" t="n">
-        <v>98.6432128618746</v>
+        <v>98.64322049050931</v>
       </c>
       <c r="G485" t="n">
         <v>13689600</v>
@@ -11650,16 +11650,16 @@
         <v>46000</v>
       </c>
       <c r="C488" t="n">
-        <v>98.69234466552734</v>
+        <v>98.69235229492188</v>
       </c>
       <c r="D488" t="n">
-        <v>98.69725350051007</v>
+        <v>98.69726113028409</v>
       </c>
       <c r="E488" t="n">
-        <v>98.69234466552734</v>
+        <v>98.69235229492188</v>
       </c>
       <c r="F488" t="n">
-        <v>98.69234466552734</v>
+        <v>98.69235229492188</v>
       </c>
       <c r="G488" t="n">
         <v>11016400</v>
@@ -11673,16 +11673,16 @@
         <v>46001</v>
       </c>
       <c r="C489" t="n">
-        <v>98.69234466552734</v>
+        <v>98.69235229492188</v>
       </c>
       <c r="D489" t="n">
-        <v>98.70216982989736</v>
+        <v>98.70217746005143</v>
       </c>
       <c r="E489" t="n">
-        <v>98.69234466552734</v>
+        <v>98.69235229492188</v>
       </c>
       <c r="F489" t="n">
-        <v>98.70216982989736</v>
+        <v>98.70217746005143</v>
       </c>
       <c r="G489" t="n">
         <v>12234900</v>
@@ -11696,16 +11696,16 @@
         <v>46002</v>
       </c>
       <c r="C490" t="n">
-        <v>98.71197509765625</v>
+        <v>98.71198272705078</v>
       </c>
       <c r="D490" t="n">
-        <v>98.72180026079182</v>
+        <v>98.72180789094574</v>
       </c>
       <c r="E490" t="n">
-        <v>98.71197509765625</v>
+        <v>98.71198272705078</v>
       </c>
       <c r="F490" t="n">
-        <v>98.71197509765625</v>
+        <v>98.71198272705078</v>
       </c>
       <c r="G490" t="n">
         <v>22343500</v>
@@ -11719,16 +11719,16 @@
         <v>46003</v>
       </c>
       <c r="C491" t="n">
-        <v>98.75128173828125</v>
+        <v>98.75127410888672</v>
       </c>
       <c r="D491" t="n">
-        <v>98.75128173828125</v>
+        <v>98.75127410888672</v>
       </c>
       <c r="E491" t="n">
-        <v>98.74145657380426</v>
+        <v>98.7414489451688</v>
       </c>
       <c r="F491" t="n">
-        <v>98.74145657380426</v>
+        <v>98.7414489451688</v>
       </c>
       <c r="G491" t="n">
         <v>13320200</v>
@@ -11742,16 +11742,16 @@
         <v>46006</v>
       </c>
       <c r="C492" t="n">
-        <v>98.75128173828125</v>
+        <v>98.75127410888672</v>
       </c>
       <c r="D492" t="n">
-        <v>98.76110690275826</v>
+        <v>98.76109927260465</v>
       </c>
       <c r="E492" t="n">
-        <v>98.75128173828125</v>
+        <v>98.75127410888672</v>
       </c>
       <c r="F492" t="n">
-        <v>98.75128173828125</v>
+        <v>98.75127410888672</v>
       </c>
       <c r="G492" t="n">
         <v>14767900</v>
@@ -11765,16 +11765,16 @@
         <v>46007</v>
       </c>
       <c r="C493" t="n">
-        <v>98.76111602783203</v>
+        <v>98.76110076904297</v>
       </c>
       <c r="D493" t="n">
-        <v>98.77094119321683</v>
+        <v>98.77092593290978</v>
       </c>
       <c r="E493" t="n">
-        <v>98.76111602783203</v>
+        <v>98.76110076904297</v>
       </c>
       <c r="F493" t="n">
-        <v>98.77094119321683</v>
+        <v>98.77092593290978</v>
       </c>
       <c r="G493" t="n">
         <v>10701200</v>
@@ -11788,16 +11788,16 @@
         <v>46008</v>
       </c>
       <c r="C494" t="n">
-        <v>98.78074645996094</v>
+        <v>98.78075408935547</v>
       </c>
       <c r="D494" t="n">
-        <v>98.78074645996094</v>
+        <v>98.78075408935547</v>
       </c>
       <c r="E494" t="n">
-        <v>98.7709287902143</v>
+        <v>98.77093641885057</v>
       </c>
       <c r="F494" t="n">
-        <v>98.7709287902143</v>
+        <v>98.77093641885057</v>
       </c>
       <c r="G494" t="n">
         <v>13788200</v>
@@ -11811,16 +11811,16 @@
         <v>46009</v>
       </c>
       <c r="C495" t="n">
-        <v>98.78074645996094</v>
+        <v>98.78075408935547</v>
       </c>
       <c r="D495" t="n">
-        <v>98.79057162411196</v>
+        <v>98.79057925426535</v>
       </c>
       <c r="E495" t="n">
-        <v>98.78074645996094</v>
+        <v>98.78075408935547</v>
       </c>
       <c r="F495" t="n">
-        <v>98.79057162411196</v>
+        <v>98.79057925426535</v>
       </c>
       <c r="G495" t="n">
         <v>20890600</v>
@@ -11834,16 +11834,16 @@
         <v>46010</v>
       </c>
       <c r="C496" t="n">
-        <v>98.8231201171875</v>
+        <v>98.82312774658203</v>
       </c>
       <c r="D496" t="n">
-        <v>98.8231201171875</v>
+        <v>98.82312774658203</v>
       </c>
       <c r="E496" t="n">
-        <v>98.81326329307338</v>
+        <v>98.81327092170693</v>
       </c>
       <c r="F496" t="n">
-        <v>98.8231201171875</v>
+        <v>98.82312774658203</v>
       </c>
       <c r="G496" t="n">
         <v>18203600</v>
@@ -11857,16 +11857,16 @@
         <v>46013</v>
       </c>
       <c r="C497" t="n">
-        <v>98.8231201171875</v>
+        <v>98.82312774658203</v>
       </c>
       <c r="D497" t="n">
-        <v>98.83297694130162</v>
+        <v>98.83298457145713</v>
       </c>
       <c r="E497" t="n">
-        <v>98.8231201171875</v>
+        <v>98.82312774658203</v>
       </c>
       <c r="F497" t="n">
-        <v>98.8231201171875</v>
+        <v>98.82312774658203</v>
       </c>
       <c r="G497" t="n">
         <v>17890900</v>
@@ -11880,16 +11880,16 @@
         <v>46014</v>
       </c>
       <c r="C498" t="n">
-        <v>98.83296966552734</v>
+        <v>98.83297729492188</v>
       </c>
       <c r="D498" t="n">
-        <v>98.84282648891585</v>
+        <v>98.84283411907127</v>
       </c>
       <c r="E498" t="n">
-        <v>98.83296966552734</v>
+        <v>98.83297729492188</v>
       </c>
       <c r="F498" t="n">
-        <v>98.84282648891585</v>
+        <v>98.84283411907127</v>
       </c>
       <c r="G498" t="n">
         <v>12256200</v>
@@ -11926,16 +11926,16 @@
         <v>46017</v>
       </c>
       <c r="C500" t="n">
-        <v>98.88224792480469</v>
+        <v>98.88225555419922</v>
       </c>
       <c r="D500" t="n">
-        <v>98.88718009623345</v>
+        <v>98.88718772600853</v>
       </c>
       <c r="E500" t="n">
-        <v>98.88224792480469</v>
+        <v>98.88225555419922</v>
       </c>
       <c r="F500" t="n">
-        <v>98.88224792480469</v>
+        <v>98.88225555419922</v>
       </c>
       <c r="G500" t="n">
         <v>12664300</v>
@@ -11972,16 +11972,16 @@
         <v>46021</v>
       </c>
       <c r="C502" t="n">
-        <v>98.91181182861328</v>
+        <v>98.91181945800781</v>
       </c>
       <c r="D502" t="n">
-        <v>98.91181182861328</v>
+        <v>98.91181945800781</v>
       </c>
       <c r="E502" t="n">
-        <v>98.90195500496438</v>
+        <v>98.90196263359863</v>
       </c>
       <c r="F502" t="n">
-        <v>98.90687965751208</v>
+        <v>98.90688728652617</v>
       </c>
       <c r="G502" t="n">
         <v>12608900</v>
@@ -11995,16 +11995,16 @@
         <v>46022</v>
       </c>
       <c r="C503" t="n">
-        <v>98.92166137695312</v>
+        <v>98.92166900634766</v>
       </c>
       <c r="D503" t="n">
-        <v>98.93151820062626</v>
+        <v>98.931525830781</v>
       </c>
       <c r="E503" t="n">
-        <v>98.92166137695312</v>
+        <v>98.92166900634766</v>
       </c>
       <c r="F503" t="n">
-        <v>98.93151820062626</v>
+        <v>98.931525830781</v>
       </c>
       <c r="G503" t="n">
         <v>13910900</v>
@@ -12018,16 +12018,16 @@
         <v>46024</v>
       </c>
       <c r="C504" t="n">
-        <v>98.95124053955078</v>
+        <v>98.95124816894531</v>
       </c>
       <c r="D504" t="n">
-        <v>98.96108984553553</v>
+        <v>98.96109747568946</v>
       </c>
       <c r="E504" t="n">
-        <v>98.95124053955078</v>
+        <v>98.95124816894531</v>
       </c>
       <c r="F504" t="n">
-        <v>98.95124053955078</v>
+        <v>98.95124816894531</v>
       </c>
       <c r="G504" t="n">
         <v>19188800</v>
@@ -12041,16 +12041,16 @@
         <v>46027</v>
       </c>
       <c r="C505" t="n">
-        <v>98.96108245849609</v>
+        <v>98.96109008789062</v>
       </c>
       <c r="D505" t="n">
-        <v>98.96601462967449</v>
+        <v>98.96602225944926</v>
       </c>
       <c r="E505" t="n">
-        <v>98.96108245849609</v>
+        <v>98.96109008789062</v>
       </c>
       <c r="F505" t="n">
-        <v>98.96108245849609</v>
+        <v>98.96109008789062</v>
       </c>
       <c r="G505" t="n">
         <v>25006600</v>
@@ -12064,16 +12064,16 @@
         <v>46028</v>
       </c>
       <c r="C506" t="n">
-        <v>98.97093963623047</v>
+        <v>98.970947265625</v>
       </c>
       <c r="D506" t="n">
-        <v>98.97093963623047</v>
+        <v>98.970947265625</v>
       </c>
       <c r="E506" t="n">
-        <v>98.97093963623047</v>
+        <v>98.970947265625</v>
       </c>
       <c r="F506" t="n">
-        <v>98.97093963623047</v>
+        <v>98.970947265625</v>
       </c>
       <c r="G506" t="n">
         <v>17635000</v>
@@ -12087,16 +12087,16 @@
         <v>46029</v>
       </c>
       <c r="C507" t="n">
-        <v>98.98078918457031</v>
+        <v>98.98079681396484</v>
       </c>
       <c r="D507" t="n">
-        <v>98.98078918457031</v>
+        <v>98.98079681396484</v>
       </c>
       <c r="E507" t="n">
-        <v>98.98078918457031</v>
+        <v>98.98079681396484</v>
       </c>
       <c r="F507" t="n">
-        <v>98.98078918457031</v>
+        <v>98.98079681396484</v>
       </c>
       <c r="G507" t="n">
         <v>14062300</v>
@@ -12133,16 +12133,16 @@
         <v>46031</v>
       </c>
       <c r="C509" t="n">
-        <v>99.01036834716797</v>
+        <v>99.0103759765625</v>
       </c>
       <c r="D509" t="n">
-        <v>99.0202251718958</v>
+        <v>99.02023280204986</v>
       </c>
       <c r="E509" t="n">
-        <v>99.01036834716797</v>
+        <v>99.0103759765625</v>
       </c>
       <c r="F509" t="n">
-        <v>99.0202251718958</v>
+        <v>99.02023280204986</v>
       </c>
       <c r="G509" t="n">
         <v>15053500</v>
@@ -12179,16 +12179,16 @@
         <v>46035</v>
       </c>
       <c r="C511" t="n">
-        <v>99.03992462158203</v>
+        <v>99.03993225097656</v>
       </c>
       <c r="D511" t="n">
-        <v>99.03992462158203</v>
+        <v>99.03993225097656</v>
       </c>
       <c r="E511" t="n">
-        <v>99.03006779751914</v>
+        <v>99.03007542615437</v>
       </c>
       <c r="F511" t="n">
-        <v>99.03006779751914</v>
+        <v>99.03007542615437</v>
       </c>
       <c r="G511" t="n">
         <v>14163000</v>
@@ -12202,16 +12202,16 @@
         <v>46036</v>
       </c>
       <c r="C512" t="n">
-        <v>99.04977416992188</v>
+        <v>99.04978179931641</v>
       </c>
       <c r="D512" t="n">
-        <v>99.04977416992188</v>
+        <v>99.04978179931641</v>
       </c>
       <c r="E512" t="n">
-        <v>99.03991734658302</v>
+        <v>99.03992497521833</v>
       </c>
       <c r="F512" t="n">
-        <v>99.04977416992188</v>
+        <v>99.04978179931641</v>
       </c>
       <c r="G512" t="n">
         <v>11851800</v>
@@ -12225,16 +12225,16 @@
         <v>46037</v>
       </c>
       <c r="C513" t="n">
-        <v>99.05963897705078</v>
+        <v>99.05963134765625</v>
       </c>
       <c r="D513" t="n">
-        <v>99.05963897705078</v>
+        <v>99.05963134765625</v>
       </c>
       <c r="E513" t="n">
-        <v>99.04978967072383</v>
+        <v>99.04978204208787</v>
       </c>
       <c r="F513" t="n">
-        <v>99.04978967072383</v>
+        <v>99.04978204208787</v>
       </c>
       <c r="G513" t="n">
         <v>11469500</v>
@@ -12340,16 +12340,16 @@
         <v>46045</v>
       </c>
       <c r="C518" t="n">
-        <v>99.14833831787109</v>
+        <v>99.14833068847656</v>
       </c>
       <c r="D518" t="n">
-        <v>99.14833831787109</v>
+        <v>99.14833068847656</v>
       </c>
       <c r="E518" t="n">
-        <v>99.13848149269603</v>
+        <v>99.13847386405996</v>
       </c>
       <c r="F518" t="n">
-        <v>99.14833831787109</v>
+        <v>99.14833068847656</v>
       </c>
       <c r="G518" t="n">
         <v>12143000</v>
@@ -12363,16 +12363,16 @@
         <v>46048</v>
       </c>
       <c r="C519" t="n">
-        <v>99.15818786621094</v>
+        <v>99.15818023681641</v>
       </c>
       <c r="D519" t="n">
-        <v>99.15818786621094</v>
+        <v>99.15818023681641</v>
       </c>
       <c r="E519" t="n">
-        <v>99.14833104175922</v>
+        <v>99.14832341312308</v>
       </c>
       <c r="F519" t="n">
-        <v>99.15818786621094</v>
+        <v>99.15818023681641</v>
       </c>
       <c r="G519" t="n">
         <v>16872000</v>
@@ -12386,16 +12386,16 @@
         <v>46049</v>
       </c>
       <c r="C520" t="n">
-        <v>99.15818786621094</v>
+        <v>99.15818023681641</v>
       </c>
       <c r="D520" t="n">
-        <v>99.17296934361146</v>
+        <v>99.1729617130796</v>
       </c>
       <c r="E520" t="n">
-        <v>99.15818786621094</v>
+        <v>99.15818023681641</v>
       </c>
       <c r="F520" t="n">
-        <v>99.16803717210854</v>
+        <v>99.16802954195617</v>
       </c>
       <c r="G520" t="n">
         <v>13393600</v>
@@ -12616,16 +12616,16 @@
         <v>46063</v>
       </c>
       <c r="C530" t="n">
-        <v>99.30532836914062</v>
+        <v>99.30532073974609</v>
       </c>
       <c r="D530" t="n">
-        <v>99.30532836914062</v>
+        <v>99.30532073974609</v>
       </c>
       <c r="E530" t="n">
-        <v>99.29544119581978</v>
+        <v>99.29543356718486</v>
       </c>
       <c r="F530" t="n">
-        <v>99.30532836914062</v>
+        <v>99.30532073974609</v>
       </c>
       <c r="G530" t="n">
         <v>14002700</v>
@@ -12639,16 +12639,16 @@
         <v>46064</v>
       </c>
       <c r="C531" t="n">
-        <v>99.30532836914062</v>
+        <v>99.30532073974609</v>
       </c>
       <c r="D531" t="n">
-        <v>99.31521554246146</v>
+        <v>99.31520791230733</v>
       </c>
       <c r="E531" t="n">
-        <v>99.30532836914062</v>
+        <v>99.30532073974609</v>
       </c>
       <c r="F531" t="n">
-        <v>99.31521554246146</v>
+        <v>99.31520791230733</v>
       </c>
       <c r="G531" t="n">
         <v>12584400</v>
@@ -12662,16 +12662,16 @@
         <v>46065</v>
       </c>
       <c r="C532" t="n">
-        <v>99.32509613037109</v>
+        <v>99.32510375976562</v>
       </c>
       <c r="D532" t="n">
-        <v>99.32509613037109</v>
+        <v>99.32510375976562</v>
       </c>
       <c r="E532" t="n">
-        <v>99.31520895770579</v>
+        <v>99.31521658634087</v>
       </c>
       <c r="F532" t="n">
-        <v>99.31520895770579</v>
+        <v>99.31521658634087</v>
       </c>
       <c r="G532" t="n">
         <v>16593900</v>
@@ -12731,16 +12731,16 @@
         <v>46071</v>
       </c>
       <c r="C535" t="n">
-        <v>99.38441467285156</v>
+        <v>99.38440704345703</v>
       </c>
       <c r="D535" t="n">
-        <v>99.38441467285156</v>
+        <v>99.38440704345703</v>
       </c>
       <c r="E535" t="n">
-        <v>99.37452749913272</v>
+        <v>99.37451987049721</v>
       </c>
       <c r="F535" t="n">
-        <v>99.38441467285156</v>
+        <v>99.38440704345703</v>
       </c>
       <c r="G535" t="n">
         <v>10207300</v>
@@ -12846,16 +12846,16 @@
         <v>46078</v>
       </c>
       <c r="C540" t="n">
-        <v>99.44371032714844</v>
+        <v>99.44370269775391</v>
       </c>
       <c r="D540" t="n">
-        <v>99.45359749964389</v>
+        <v>99.4535898694908</v>
       </c>
       <c r="E540" t="n">
-        <v>99.44371032714844</v>
+        <v>99.44370269775391</v>
       </c>
       <c r="F540" t="n">
-        <v>99.45359749964389</v>
+        <v>99.4535898694908</v>
       </c>
       <c r="G540" t="n">
         <v>12532000</v>
@@ -12984,16 +12984,16 @@
         <v>46086</v>
       </c>
       <c r="C546" t="n">
-        <v>99.52489471435547</v>
+        <v>99.52488708496094</v>
       </c>
       <c r="D546" t="n">
-        <v>99.53480112013467</v>
+        <v>99.53479348998074</v>
       </c>
       <c r="E546" t="n">
-        <v>99.52489471435547</v>
+        <v>99.52488708496094</v>
       </c>
       <c r="F546" t="n">
-        <v>99.53480112013467</v>
+        <v>99.53479348998074</v>
       </c>
       <c r="G546" t="n">
         <v>16218200</v>
@@ -13007,16 +13007,16 @@
         <v>46087</v>
       </c>
       <c r="C547" t="n">
-        <v>99.56452178955078</v>
+        <v>99.56452941894531</v>
       </c>
       <c r="D547" t="n">
-        <v>99.56452178955078</v>
+        <v>99.56452941894531</v>
       </c>
       <c r="E547" t="n">
-        <v>99.55461538513191</v>
+        <v>99.55462301376734</v>
       </c>
       <c r="F547" t="n">
-        <v>99.55461538513191</v>
+        <v>99.55462301376734</v>
       </c>
       <c r="G547" t="n">
         <v>18921300</v>
@@ -13030,16 +13030,16 @@
         <v>46090</v>
       </c>
       <c r="C548" t="n">
-        <v>99.57444763183594</v>
+        <v>99.57444000244141</v>
       </c>
       <c r="D548" t="n">
-        <v>99.57444763183594</v>
+        <v>99.57444000244141</v>
       </c>
       <c r="E548" t="n">
-        <v>99.56453366409391</v>
+        <v>99.564526035459</v>
       </c>
       <c r="F548" t="n">
-        <v>99.56949442903577</v>
+        <v>99.56948680002075</v>
       </c>
       <c r="G548" t="n">
         <v>19053900</v>
@@ -13053,16 +13053,16 @@
         <v>46091</v>
       </c>
       <c r="C549" t="n">
-        <v>99.57444763183594</v>
+        <v>99.57444000244141</v>
       </c>
       <c r="D549" t="n">
-        <v>99.58436159957796</v>
+        <v>99.58435396942383</v>
       </c>
       <c r="E549" t="n">
-        <v>99.57444763183594</v>
+        <v>99.57444000244141</v>
       </c>
       <c r="F549" t="n">
-        <v>99.58138967789786</v>
+        <v>99.58138204797143</v>
       </c>
       <c r="G549" t="n">
         <v>13664200</v>
@@ -13329,16 +13329,16 @@
         <v>46107</v>
       </c>
       <c r="C561" t="n">
-        <v>99.73303985595703</v>
+        <v>99.7330322265625</v>
       </c>
       <c r="D561" t="n">
-        <v>99.73303985595703</v>
+        <v>99.7330322265625</v>
       </c>
       <c r="E561" t="n">
-        <v>99.72312588831552</v>
+        <v>99.7231182596794</v>
       </c>
       <c r="F561" t="n">
-        <v>99.73303985595703</v>
+        <v>99.7330322265625</v>
       </c>
       <c r="G561" t="n">
         <v>17499400</v>
@@ -13375,16 +13375,16 @@
         <v>46111</v>
       </c>
       <c r="C563" t="n">
-        <v>99.77268981933594</v>
+        <v>99.77268218994141</v>
       </c>
       <c r="D563" t="n">
-        <v>99.77268981933594</v>
+        <v>99.77268218994141</v>
       </c>
       <c r="E563" t="n">
-        <v>99.76277585152998</v>
+        <v>99.76276822289356</v>
       </c>
       <c r="F563" t="n">
-        <v>99.76277585152998</v>
+        <v>99.76276822289356</v>
       </c>
       <c r="G563" t="n">
         <v>19102700</v>
@@ -13398,16 +13398,16 @@
         <v>46112</v>
       </c>
       <c r="C564" t="n">
-        <v>99.77268981933594</v>
+        <v>99.77268218994141</v>
       </c>
       <c r="D564" t="n">
-        <v>99.78259622500016</v>
+        <v>99.78258859484811</v>
       </c>
       <c r="E564" t="n">
-        <v>99.77268981933594</v>
+        <v>99.77268218994141</v>
       </c>
       <c r="F564" t="n">
-        <v>99.77268981933594</v>
+        <v>99.77268218994141</v>
       </c>
       <c r="G564" t="n">
         <v>36976800</v>
@@ -14502,7 +14502,7 @@
         <v>46182</v>
       </c>
       <c r="C612" t="n">
-        <v>100.4630966186523</v>
+        <v>100.4700012207031</v>
       </c>
       <c r="D612" t="n">
         <v>100.4700012207031</v>
@@ -14514,7 +14514,7 @@
         <v>100.4700012207031</v>
       </c>
       <c r="G612" t="n">
-        <v>24819903</v>
+        <v>24957045</v>
       </c>
     </row>
   </sheetData>

--- a/Data/sgov.xlsx
+++ b/Data/sgov.xlsx
@@ -472,16 +472,16 @@
         <v>45293</v>
       </c>
       <c r="C2" t="n">
-        <v>90.15837097167969</v>
+        <v>90.15839385986328</v>
       </c>
       <c r="D2" t="n">
-        <v>90.1673626587925</v>
+        <v>90.16738554925877</v>
       </c>
       <c r="E2" t="n">
-        <v>90.14937928456688</v>
+        <v>90.14940217046778</v>
       </c>
       <c r="F2" t="n">
-        <v>90.15837097167969</v>
+        <v>90.15839385986328</v>
       </c>
       <c r="G2" t="n">
         <v>5286200</v>
@@ -495,16 +495,16 @@
         <v>45294</v>
       </c>
       <c r="C3" t="n">
-        <v>90.16737365722656</v>
+        <v>90.16738128662109</v>
       </c>
       <c r="D3" t="n">
-        <v>90.18535017499724</v>
+        <v>90.18535780591283</v>
       </c>
       <c r="E3" t="n">
-        <v>90.16737365722656</v>
+        <v>90.16738128662109</v>
       </c>
       <c r="F3" t="n">
-        <v>90.16737365722656</v>
+        <v>90.16738128662109</v>
       </c>
       <c r="G3" t="n">
         <v>4597300</v>
@@ -518,16 +518,16 @@
         <v>45295</v>
       </c>
       <c r="C4" t="n">
-        <v>90.21230316162109</v>
+        <v>90.21231842041016</v>
       </c>
       <c r="D4" t="n">
-        <v>90.22129484831375</v>
+        <v>90.22131010862368</v>
       </c>
       <c r="E4" t="n">
-        <v>90.21230316162109</v>
+        <v>90.21231842041016</v>
       </c>
       <c r="F4" t="n">
-        <v>90.21230316162109</v>
+        <v>90.21231842041016</v>
       </c>
       <c r="G4" t="n">
         <v>2794100</v>
@@ -541,16 +541,16 @@
         <v>45296</v>
       </c>
       <c r="C5" t="n">
-        <v>90.22132873535156</v>
+        <v>90.2213134765625</v>
       </c>
       <c r="D5" t="n">
-        <v>90.23032042542148</v>
+        <v>90.23030516511169</v>
       </c>
       <c r="E5" t="n">
-        <v>90.22132873535156</v>
+        <v>90.2213134765625</v>
       </c>
       <c r="F5" t="n">
-        <v>90.22132873535156</v>
+        <v>90.2213134765625</v>
       </c>
       <c r="G5" t="n">
         <v>3491200</v>
@@ -564,16 +564,16 @@
         <v>45299</v>
       </c>
       <c r="C6" t="n">
-        <v>90.24827575683594</v>
+        <v>90.24829864501953</v>
       </c>
       <c r="D6" t="n">
-        <v>90.24827575683594</v>
+        <v>90.24829864501953</v>
       </c>
       <c r="E6" t="n">
-        <v>90.23928406887724</v>
+        <v>90.23930695478043</v>
       </c>
       <c r="F6" t="n">
-        <v>90.24827575683594</v>
+        <v>90.24829864501953</v>
       </c>
       <c r="G6" t="n">
         <v>2867500</v>
@@ -610,16 +610,16 @@
         <v>45301</v>
       </c>
       <c r="C8" t="n">
-        <v>90.27524566650391</v>
+        <v>90.2752685546875</v>
       </c>
       <c r="D8" t="n">
-        <v>90.27524566650391</v>
+        <v>90.2752685546875</v>
       </c>
       <c r="E8" t="n">
-        <v>90.26626083702391</v>
+        <v>90.2662837229295</v>
       </c>
       <c r="F8" t="n">
-        <v>90.27524566650391</v>
+        <v>90.2752685546875</v>
       </c>
       <c r="G8" t="n">
         <v>1961400</v>
@@ -633,16 +633,16 @@
         <v>45302</v>
       </c>
       <c r="C9" t="n">
-        <v>90.32919311523438</v>
+        <v>90.32920074462891</v>
       </c>
       <c r="D9" t="n">
-        <v>90.32919311523438</v>
+        <v>90.32920074462891</v>
       </c>
       <c r="E9" t="n">
-        <v>90.31120973814555</v>
+        <v>90.31121736602117</v>
       </c>
       <c r="F9" t="n">
-        <v>90.31120973814555</v>
+        <v>90.31121736602117</v>
       </c>
       <c r="G9" t="n">
         <v>3164900</v>
@@ -656,16 +656,16 @@
         <v>45303</v>
       </c>
       <c r="C10" t="n">
-        <v>90.33817291259766</v>
+        <v>90.33819580078125</v>
       </c>
       <c r="D10" t="n">
-        <v>90.33817291259766</v>
+        <v>90.33819580078125</v>
       </c>
       <c r="E10" t="n">
-        <v>90.32918808320254</v>
+        <v>90.32921096910974</v>
       </c>
       <c r="F10" t="n">
-        <v>90.32918808320254</v>
+        <v>90.32921096910974</v>
       </c>
       <c r="G10" t="n">
         <v>2557900</v>
@@ -679,16 +679,16 @@
         <v>45307</v>
       </c>
       <c r="C11" t="n">
-        <v>90.34716033935547</v>
+        <v>90.34716796875</v>
       </c>
       <c r="D11" t="n">
-        <v>90.35615202697488</v>
+        <v>90.35615965712871</v>
       </c>
       <c r="E11" t="n">
-        <v>90.34716033935547</v>
+        <v>90.34716796875</v>
       </c>
       <c r="F11" t="n">
-        <v>90.35615202697488</v>
+        <v>90.35615965712871</v>
       </c>
       <c r="G11" t="n">
         <v>2713000</v>
@@ -702,16 +702,16 @@
         <v>45308</v>
       </c>
       <c r="C12" t="n">
-        <v>90.35617065429688</v>
+        <v>90.35617828369141</v>
       </c>
       <c r="D12" t="n">
-        <v>90.36515548512048</v>
+        <v>90.36516311527365</v>
       </c>
       <c r="E12" t="n">
-        <v>90.35617065429688</v>
+        <v>90.35617828369141</v>
       </c>
       <c r="F12" t="n">
-        <v>90.36515548512048</v>
+        <v>90.36516311527365</v>
       </c>
       <c r="G12" t="n">
         <v>2317700</v>
@@ -725,16 +725,16 @@
         <v>45309</v>
       </c>
       <c r="C13" t="n">
-        <v>90.39212036132812</v>
+        <v>90.39213562011719</v>
       </c>
       <c r="D13" t="n">
-        <v>90.40110519113864</v>
+        <v>90.4011204514444</v>
       </c>
       <c r="E13" t="n">
-        <v>90.39212036132812</v>
+        <v>90.39213562011719</v>
       </c>
       <c r="F13" t="n">
-        <v>90.40110519113864</v>
+        <v>90.4011204514444</v>
       </c>
       <c r="G13" t="n">
         <v>2672000</v>
@@ -748,16 +748,16 @@
         <v>45310</v>
       </c>
       <c r="C14" t="n">
-        <v>90.41909027099609</v>
+        <v>90.41910552978516</v>
       </c>
       <c r="D14" t="n">
-        <v>90.41909027099609</v>
+        <v>90.41910552978516</v>
       </c>
       <c r="E14" t="n">
-        <v>90.40110689373897</v>
+        <v>90.40112214949322</v>
       </c>
       <c r="F14" t="n">
-        <v>90.41009858236752</v>
+        <v>90.41011383963918</v>
       </c>
       <c r="G14" t="n">
         <v>3630100</v>
@@ -771,16 +771,16 @@
         <v>45313</v>
       </c>
       <c r="C15" t="n">
-        <v>90.42809295654297</v>
+        <v>90.42805480957031</v>
       </c>
       <c r="D15" t="n">
-        <v>90.437084646947</v>
+        <v>90.43704649618121</v>
       </c>
       <c r="E15" t="n">
-        <v>90.41910812478913</v>
+        <v>90.41906998160671</v>
       </c>
       <c r="F15" t="n">
-        <v>90.43259223107009</v>
+        <v>90.4325540821994</v>
       </c>
       <c r="G15" t="n">
         <v>4307000</v>
@@ -794,16 +794,16 @@
         <v>45314</v>
       </c>
       <c r="C16" t="n">
-        <v>90.44605255126953</v>
+        <v>90.44606018066406</v>
       </c>
       <c r="D16" t="n">
-        <v>90.44605255126953</v>
+        <v>90.44606018066406</v>
       </c>
       <c r="E16" t="n">
-        <v>90.43706086323019</v>
+        <v>90.43706849186626</v>
       </c>
       <c r="F16" t="n">
-        <v>90.43706086323019</v>
+        <v>90.43706849186626</v>
       </c>
       <c r="G16" t="n">
         <v>2066200</v>
@@ -817,16 +817,16 @@
         <v>45315</v>
       </c>
       <c r="C17" t="n">
-        <v>90.45505523681641</v>
+        <v>90.45503997802734</v>
       </c>
       <c r="D17" t="n">
-        <v>90.45505523681641</v>
+        <v>90.45503997802734</v>
       </c>
       <c r="E17" t="n">
-        <v>90.44606354768386</v>
+        <v>90.4460482904116</v>
       </c>
       <c r="F17" t="n">
-        <v>90.44606354768386</v>
+        <v>90.4460482904116</v>
       </c>
       <c r="G17" t="n">
         <v>3441600</v>
@@ -886,16 +886,16 @@
         <v>45320</v>
       </c>
       <c r="C20" t="n">
-        <v>90.50897979736328</v>
+        <v>90.50899505615234</v>
       </c>
       <c r="D20" t="n">
-        <v>90.52695631462417</v>
+        <v>90.52697157644387</v>
       </c>
       <c r="E20" t="n">
-        <v>90.50897979736328</v>
+        <v>90.50899505615234</v>
       </c>
       <c r="F20" t="n">
-        <v>90.51797148531789</v>
+        <v>90.51798674562285</v>
       </c>
       <c r="G20" t="n">
         <v>2914400</v>
@@ -955,16 +955,16 @@
         <v>45323</v>
       </c>
       <c r="C23" t="n">
-        <v>90.58833312988281</v>
+        <v>90.58834075927734</v>
       </c>
       <c r="D23" t="n">
-        <v>90.5973658970138</v>
+        <v>90.59737352716907</v>
       </c>
       <c r="E23" t="n">
-        <v>90.58833312988281</v>
+        <v>90.58834075927734</v>
       </c>
       <c r="F23" t="n">
-        <v>90.5973658970138</v>
+        <v>90.59737352716907</v>
       </c>
       <c r="G23" t="n">
         <v>7038600</v>
@@ -978,16 +978,16 @@
         <v>45324</v>
       </c>
       <c r="C24" t="n">
-        <v>90.59735870361328</v>
+        <v>90.59737396240234</v>
       </c>
       <c r="D24" t="n">
-        <v>90.59735870361328</v>
+        <v>90.59737396240234</v>
       </c>
       <c r="E24" t="n">
-        <v>90.5883259371995</v>
+        <v>90.58834119446723</v>
       </c>
       <c r="F24" t="n">
-        <v>90.59735870361328</v>
+        <v>90.59737396240234</v>
       </c>
       <c r="G24" t="n">
         <v>3864800</v>
@@ -1001,16 +1001,16 @@
         <v>45327</v>
       </c>
       <c r="C25" t="n">
-        <v>90.61544799804688</v>
+        <v>90.61543273925781</v>
       </c>
       <c r="D25" t="n">
-        <v>90.61544799804688</v>
+        <v>90.61543273925781</v>
       </c>
       <c r="E25" t="n">
-        <v>90.60642211856201</v>
+        <v>90.60640686129281</v>
       </c>
       <c r="F25" t="n">
-        <v>90.61544799804688</v>
+        <v>90.61543273925781</v>
       </c>
       <c r="G25" t="n">
         <v>3969400</v>
@@ -1024,16 +1024,16 @@
         <v>45328</v>
       </c>
       <c r="C26" t="n">
-        <v>90.62442779541016</v>
+        <v>90.62445831298828</v>
       </c>
       <c r="D26" t="n">
-        <v>90.6334605595995</v>
+        <v>90.6334910802194</v>
       </c>
       <c r="E26" t="n">
-        <v>90.61539503122081</v>
+        <v>90.61542554575718</v>
       </c>
       <c r="F26" t="n">
-        <v>90.62442779541016</v>
+        <v>90.62445831298828</v>
       </c>
       <c r="G26" t="n">
         <v>2167300</v>
@@ -1070,16 +1070,16 @@
         <v>45330</v>
       </c>
       <c r="C28" t="n">
-        <v>90.66960906982422</v>
+        <v>90.66959381103516</v>
       </c>
       <c r="D28" t="n">
-        <v>90.68766771307108</v>
+        <v>90.68765245124293</v>
       </c>
       <c r="E28" t="n">
-        <v>90.66960906982422</v>
+        <v>90.66959381103516</v>
       </c>
       <c r="F28" t="n">
-        <v>90.66960906982422</v>
+        <v>90.66959381103516</v>
       </c>
       <c r="G28" t="n">
         <v>3838700</v>
@@ -1093,16 +1093,16 @@
         <v>45331</v>
       </c>
       <c r="C29" t="n">
-        <v>90.69670104980469</v>
+        <v>90.69670867919922</v>
       </c>
       <c r="D29" t="n">
-        <v>90.69670104980469</v>
+        <v>90.69670867919922</v>
       </c>
       <c r="E29" t="n">
-        <v>90.68315534478884</v>
+        <v>90.68316297304392</v>
       </c>
       <c r="F29" t="n">
-        <v>90.68766828313339</v>
+        <v>90.6876759117681</v>
       </c>
       <c r="G29" t="n">
         <v>3232500</v>
@@ -1116,16 +1116,16 @@
         <v>45334</v>
       </c>
       <c r="C30" t="n">
-        <v>90.69670104980469</v>
+        <v>90.69670867919922</v>
       </c>
       <c r="D30" t="n">
-        <v>90.71475969316506</v>
+        <v>90.71476732407868</v>
       </c>
       <c r="E30" t="n">
-        <v>90.69670104980469</v>
+        <v>90.69670867919922</v>
       </c>
       <c r="F30" t="n">
-        <v>90.70573381647597</v>
+        <v>90.70574144663034</v>
       </c>
       <c r="G30" t="n">
         <v>2792700</v>
@@ -1139,16 +1139,16 @@
         <v>45335</v>
       </c>
       <c r="C31" t="n">
-        <v>90.71476745605469</v>
+        <v>90.71479034423828</v>
       </c>
       <c r="D31" t="n">
-        <v>90.71476745605469</v>
+        <v>90.71479034423828</v>
       </c>
       <c r="E31" t="n">
-        <v>90.70574157859322</v>
+        <v>90.7057644644995</v>
       </c>
       <c r="F31" t="n">
-        <v>90.71476745605469</v>
+        <v>90.71479034423828</v>
       </c>
       <c r="G31" t="n">
         <v>3009000</v>
@@ -1185,16 +1185,16 @@
         <v>45337</v>
       </c>
       <c r="C33" t="n">
-        <v>90.77798461914062</v>
+        <v>90.77797698974609</v>
       </c>
       <c r="D33" t="n">
-        <v>90.7870173867412</v>
+        <v>90.78700975658751</v>
       </c>
       <c r="E33" t="n">
-        <v>90.77798461914062</v>
+        <v>90.77797698974609</v>
       </c>
       <c r="F33" t="n">
-        <v>90.7870173867412</v>
+        <v>90.78700975658751</v>
       </c>
       <c r="G33" t="n">
         <v>2577800</v>
@@ -1208,16 +1208,16 @@
         <v>45338</v>
       </c>
       <c r="C34" t="n">
-        <v>90.78702545166016</v>
+        <v>90.78704071044922</v>
       </c>
       <c r="D34" t="n">
-        <v>90.79605822006314</v>
+        <v>90.79607348037037</v>
       </c>
       <c r="E34" t="n">
-        <v>90.78702545166016</v>
+        <v>90.78704071044922</v>
       </c>
       <c r="F34" t="n">
-        <v>90.79605822006314</v>
+        <v>90.79607348037037</v>
       </c>
       <c r="G34" t="n">
         <v>2920700</v>
@@ -1231,16 +1231,16 @@
         <v>45342</v>
       </c>
       <c r="C35" t="n">
-        <v>90.80506896972656</v>
+        <v>90.80507659912109</v>
       </c>
       <c r="D35" t="n">
-        <v>90.8140948459574</v>
+        <v>90.81410247611029</v>
       </c>
       <c r="E35" t="n">
-        <v>90.79603620351386</v>
+        <v>90.79604383214948</v>
       </c>
       <c r="F35" t="n">
-        <v>90.80506896972656</v>
+        <v>90.80507659912109</v>
       </c>
       <c r="G35" t="n">
         <v>3268600</v>
@@ -1254,16 +1254,16 @@
         <v>45343</v>
       </c>
       <c r="C36" t="n">
-        <v>90.81411743164062</v>
+        <v>90.81410217285156</v>
       </c>
       <c r="D36" t="n">
-        <v>90.83218296855895</v>
+        <v>90.83216770673448</v>
       </c>
       <c r="E36" t="n">
-        <v>90.81411743164062</v>
+        <v>90.81410217285156</v>
       </c>
       <c r="F36" t="n">
-        <v>90.82315020009979</v>
+        <v>90.82313493979302</v>
       </c>
       <c r="G36" t="n">
         <v>2302700</v>
@@ -1277,16 +1277,16 @@
         <v>45344</v>
       </c>
       <c r="C37" t="n">
-        <v>90.85021209716797</v>
+        <v>90.85024261474609</v>
       </c>
       <c r="D37" t="n">
-        <v>90.85924486269228</v>
+        <v>90.85927538330462</v>
       </c>
       <c r="E37" t="n">
-        <v>90.85021209716797</v>
+        <v>90.85024261474609</v>
       </c>
       <c r="F37" t="n">
-        <v>90.85021209716797</v>
+        <v>90.85024261474609</v>
       </c>
       <c r="G37" t="n">
         <v>2452200</v>
@@ -1323,16 +1323,16 @@
         <v>45348</v>
       </c>
       <c r="C39" t="n">
-        <v>90.88632965087891</v>
+        <v>90.88636016845703</v>
       </c>
       <c r="D39" t="n">
-        <v>90.89536241574544</v>
+        <v>90.89539293635657</v>
       </c>
       <c r="E39" t="n">
-        <v>90.88632965087891</v>
+        <v>90.88636016845703</v>
       </c>
       <c r="F39" t="n">
-        <v>90.88632965087891</v>
+        <v>90.88636016845703</v>
       </c>
       <c r="G39" t="n">
         <v>2645100</v>
@@ -1346,16 +1346,16 @@
         <v>45349</v>
       </c>
       <c r="C40" t="n">
-        <v>90.9044189453125</v>
+        <v>90.90442657470703</v>
       </c>
       <c r="D40" t="n">
-        <v>90.9044189453125</v>
+        <v>90.90442657470703</v>
       </c>
       <c r="E40" t="n">
-        <v>90.89538617808456</v>
+        <v>90.895393806721</v>
       </c>
       <c r="F40" t="n">
-        <v>90.9044189453125</v>
+        <v>90.90442657470703</v>
       </c>
       <c r="G40" t="n">
         <v>2360300</v>
@@ -1369,16 +1369,16 @@
         <v>45350</v>
       </c>
       <c r="C41" t="n">
-        <v>90.91343688964844</v>
+        <v>90.91345977783203</v>
       </c>
       <c r="D41" t="n">
-        <v>90.91343688964844</v>
+        <v>90.91345977783203</v>
       </c>
       <c r="E41" t="n">
-        <v>90.90441101319072</v>
+        <v>90.90443389910197</v>
       </c>
       <c r="F41" t="n">
-        <v>90.90441101319072</v>
+        <v>90.90443389910197</v>
       </c>
       <c r="G41" t="n">
         <v>4526200</v>
@@ -1392,16 +1392,16 @@
         <v>45351</v>
       </c>
       <c r="C42" t="n">
-        <v>90.94054412841797</v>
+        <v>90.94053649902344</v>
       </c>
       <c r="D42" t="n">
-        <v>90.94957689642999</v>
+        <v>90.94956926627766</v>
       </c>
       <c r="E42" t="n">
-        <v>90.94054412841797</v>
+        <v>90.94053649902344</v>
       </c>
       <c r="F42" t="n">
-        <v>90.94054412841797</v>
+        <v>90.94053649902344</v>
       </c>
       <c r="G42" t="n">
         <v>5560200</v>
@@ -1415,16 +1415,16 @@
         <v>45352</v>
       </c>
       <c r="C43" t="n">
-        <v>90.96774291992188</v>
+        <v>90.96775054931641</v>
       </c>
       <c r="D43" t="n">
-        <v>90.96774291992188</v>
+        <v>90.96775054931641</v>
       </c>
       <c r="E43" t="n">
-        <v>90.95867322534421</v>
+        <v>90.95868085397808</v>
       </c>
       <c r="F43" t="n">
-        <v>90.96774291992188</v>
+        <v>90.96775054931641</v>
       </c>
       <c r="G43" t="n">
         <v>7579200</v>
@@ -1461,16 +1461,16 @@
         <v>45356</v>
       </c>
       <c r="C45" t="n">
-        <v>90.98586273193359</v>
+        <v>90.98588562011719</v>
       </c>
       <c r="D45" t="n">
-        <v>90.99493242524937</v>
+        <v>90.99495531571452</v>
       </c>
       <c r="E45" t="n">
-        <v>90.98586273193359</v>
+        <v>90.98588562011719</v>
       </c>
       <c r="F45" t="n">
-        <v>90.98586273193359</v>
+        <v>90.98588562011719</v>
       </c>
       <c r="G45" t="n">
         <v>3905300</v>
@@ -1507,16 +1507,16 @@
         <v>45358</v>
       </c>
       <c r="C47" t="n">
-        <v>91.04934692382812</v>
+        <v>91.04936981201172</v>
       </c>
       <c r="D47" t="n">
-        <v>91.04934692382812</v>
+        <v>91.04936981201172</v>
       </c>
       <c r="E47" t="n">
-        <v>91.04027723018791</v>
+        <v>91.04030011609154</v>
       </c>
       <c r="F47" t="n">
-        <v>91.04934692382812</v>
+        <v>91.04936981201172</v>
       </c>
       <c r="G47" t="n">
         <v>2415500</v>
@@ -1553,16 +1553,16 @@
         <v>45362</v>
       </c>
       <c r="C49" t="n">
-        <v>91.0765380859375</v>
+        <v>91.07654571533203</v>
       </c>
       <c r="D49" t="n">
-        <v>91.0765380859375</v>
+        <v>91.07654571533203</v>
       </c>
       <c r="E49" t="n">
-        <v>91.06746839339277</v>
+        <v>91.06747602202755</v>
       </c>
       <c r="F49" t="n">
-        <v>91.0765380859375</v>
+        <v>91.07654571533203</v>
       </c>
       <c r="G49" t="n">
         <v>3238400</v>
@@ -1576,16 +1576,16 @@
         <v>45363</v>
       </c>
       <c r="C50" t="n">
-        <v>91.08561706542969</v>
+        <v>91.08563232421875</v>
       </c>
       <c r="D50" t="n">
-        <v>91.09468675958801</v>
+        <v>91.09470201989645</v>
       </c>
       <c r="E50" t="n">
-        <v>91.08561706542969</v>
+        <v>91.08563232421875</v>
       </c>
       <c r="F50" t="n">
-        <v>91.08561706542969</v>
+        <v>91.08563232421875</v>
       </c>
       <c r="G50" t="n">
         <v>2613300</v>
@@ -1599,16 +1599,16 @@
         <v>45364</v>
       </c>
       <c r="C51" t="n">
-        <v>91.09468841552734</v>
+        <v>91.09469604492188</v>
       </c>
       <c r="D51" t="n">
-        <v>91.10375810985053</v>
+        <v>91.10376574000468</v>
       </c>
       <c r="E51" t="n">
-        <v>91.09468841552734</v>
+        <v>91.09469604492188</v>
       </c>
       <c r="F51" t="n">
-        <v>91.09468841552734</v>
+        <v>91.09469604492188</v>
       </c>
       <c r="G51" t="n">
         <v>2249300</v>
@@ -1622,16 +1622,16 @@
         <v>45365</v>
       </c>
       <c r="C52" t="n">
-        <v>91.13096618652344</v>
+        <v>91.13095855712891</v>
       </c>
       <c r="D52" t="n">
-        <v>91.140035881435</v>
+        <v>91.14002825128117</v>
       </c>
       <c r="E52" t="n">
-        <v>91.13096618652344</v>
+        <v>91.13095855712891</v>
       </c>
       <c r="F52" t="n">
-        <v>91.13096618652344</v>
+        <v>91.13095855712891</v>
       </c>
       <c r="G52" t="n">
         <v>3469600</v>
@@ -1645,16 +1645,16 @@
         <v>45366</v>
       </c>
       <c r="C53" t="n">
-        <v>91.14908599853516</v>
+        <v>91.14907836914062</v>
       </c>
       <c r="D53" t="n">
-        <v>91.14908599853516</v>
+        <v>91.14907836914062</v>
       </c>
       <c r="E53" t="n">
-        <v>91.14002322303251</v>
+        <v>91.14001559439656</v>
       </c>
       <c r="F53" t="n">
-        <v>91.14908599853516</v>
+        <v>91.14907836914062</v>
       </c>
       <c r="G53" t="n">
         <v>3277300</v>
@@ -1668,16 +1668,16 @@
         <v>45369</v>
       </c>
       <c r="C54" t="n">
-        <v>91.15816497802734</v>
+        <v>91.15818023681641</v>
       </c>
       <c r="D54" t="n">
-        <v>91.1672346726031</v>
+        <v>91.16724993291032</v>
       </c>
       <c r="E54" t="n">
-        <v>91.15816497802734</v>
+        <v>91.15818023681641</v>
       </c>
       <c r="F54" t="n">
-        <v>91.1672346726031</v>
+        <v>91.16724993291032</v>
       </c>
       <c r="G54" t="n">
         <v>3576200</v>
@@ -1691,16 +1691,16 @@
         <v>45370</v>
       </c>
       <c r="C55" t="n">
-        <v>91.17632293701172</v>
+        <v>91.17629241943359</v>
       </c>
       <c r="D55" t="n">
-        <v>91.18538571528335</v>
+        <v>91.18535519467183</v>
       </c>
       <c r="E55" t="n">
-        <v>91.17632293701172</v>
+        <v>91.17629241943359</v>
       </c>
       <c r="F55" t="n">
-        <v>91.18538571528335</v>
+        <v>91.18535519467183</v>
       </c>
       <c r="G55" t="n">
         <v>2661900</v>
@@ -1714,16 +1714,16 @@
         <v>45371</v>
       </c>
       <c r="C56" t="n">
-        <v>91.18535614013672</v>
+        <v>91.18537139892578</v>
       </c>
       <c r="D56" t="n">
-        <v>91.19442583361803</v>
+        <v>91.19444109392479</v>
       </c>
       <c r="E56" t="n">
-        <v>91.18535614013672</v>
+        <v>91.18537139892578</v>
       </c>
       <c r="F56" t="n">
-        <v>91.18535614013672</v>
+        <v>91.18537139892578</v>
       </c>
       <c r="G56" t="n">
         <v>2492700</v>
@@ -1737,16 +1737,16 @@
         <v>45372</v>
       </c>
       <c r="C57" t="n">
-        <v>91.22161865234375</v>
+        <v>91.22164916992188</v>
       </c>
       <c r="D57" t="n">
-        <v>91.23068834489608</v>
+        <v>91.23071886550841</v>
       </c>
       <c r="E57" t="n">
-        <v>91.22161865234375</v>
+        <v>91.22164916992188</v>
       </c>
       <c r="F57" t="n">
-        <v>91.22161865234375</v>
+        <v>91.22164916992188</v>
       </c>
       <c r="G57" t="n">
         <v>3547400</v>
@@ -1760,16 +1760,16 @@
         <v>45373</v>
       </c>
       <c r="C58" t="n">
-        <v>91.23977661132812</v>
+        <v>91.23976898193359</v>
       </c>
       <c r="D58" t="n">
-        <v>91.24883938757698</v>
+        <v>91.24883175742463</v>
       </c>
       <c r="E58" t="n">
-        <v>91.23070691692946</v>
+        <v>91.23069928829332</v>
       </c>
       <c r="F58" t="n">
-        <v>91.24883938757698</v>
+        <v>91.24883175742463</v>
       </c>
       <c r="G58" t="n">
         <v>2636700</v>
@@ -1783,16 +1783,16 @@
         <v>45376</v>
       </c>
       <c r="C59" t="n">
-        <v>91.25791931152344</v>
+        <v>91.25792694091797</v>
       </c>
       <c r="D59" t="n">
-        <v>91.26698900693876</v>
+        <v>91.26699663709155</v>
       </c>
       <c r="E59" t="n">
-        <v>91.25791931152344</v>
+        <v>91.25792694091797</v>
       </c>
       <c r="F59" t="n">
-        <v>91.25791931152344</v>
+        <v>91.25792694091797</v>
       </c>
       <c r="G59" t="n">
         <v>2422900</v>
@@ -1806,16 +1806,16 @@
         <v>45377</v>
       </c>
       <c r="C60" t="n">
-        <v>91.2669677734375</v>
+        <v>91.26697540283203</v>
       </c>
       <c r="D60" t="n">
-        <v>91.27603746674274</v>
+        <v>91.27604509689544</v>
       </c>
       <c r="E60" t="n">
-        <v>91.2669677734375</v>
+        <v>91.26697540283203</v>
       </c>
       <c r="F60" t="n">
-        <v>91.2669677734375</v>
+        <v>91.26697540283203</v>
       </c>
       <c r="G60" t="n">
         <v>3181700</v>
@@ -1829,16 +1829,16 @@
         <v>45378</v>
       </c>
       <c r="C61" t="n">
-        <v>91.31231689453125</v>
+        <v>91.31230926513672</v>
       </c>
       <c r="D61" t="n">
-        <v>91.3213865892758</v>
+        <v>91.32137895912348</v>
       </c>
       <c r="E61" t="n">
-        <v>91.31231689453125</v>
+        <v>91.31230926513672</v>
       </c>
       <c r="F61" t="n">
-        <v>91.3213865892758</v>
+        <v>91.32137895912348</v>
       </c>
       <c r="G61" t="n">
         <v>2990800</v>
@@ -1852,16 +1852,16 @@
         <v>45379</v>
       </c>
       <c r="C62" t="n">
-        <v>91.32136535644531</v>
+        <v>91.32138824462891</v>
       </c>
       <c r="D62" t="n">
-        <v>91.33043504908112</v>
+        <v>91.33045793953788</v>
       </c>
       <c r="E62" t="n">
-        <v>91.32136535644531</v>
+        <v>91.32138824462891</v>
       </c>
       <c r="F62" t="n">
-        <v>91.33043504908112</v>
+        <v>91.33045793953788</v>
       </c>
       <c r="G62" t="n">
         <v>5425800</v>
@@ -1875,16 +1875,16 @@
         <v>45383</v>
       </c>
       <c r="C63" t="n">
-        <v>91.34871673583984</v>
+        <v>91.34870147705078</v>
       </c>
       <c r="D63" t="n">
-        <v>91.3578271386809</v>
+        <v>91.35781187837004</v>
       </c>
       <c r="E63" t="n">
-        <v>91.34871673583984</v>
+        <v>91.34870147705078</v>
       </c>
       <c r="F63" t="n">
-        <v>91.3578271386809</v>
+        <v>91.35781187837004</v>
       </c>
       <c r="G63" t="n">
         <v>7395400</v>
@@ -1898,16 +1898,16 @@
         <v>45384</v>
       </c>
       <c r="C64" t="n">
-        <v>91.36692047119141</v>
+        <v>91.36692810058594</v>
       </c>
       <c r="D64" t="n">
-        <v>91.36692047119141</v>
+        <v>91.36692810058594</v>
       </c>
       <c r="E64" t="n">
-        <v>91.35781701856003</v>
+        <v>91.35782464719441</v>
       </c>
       <c r="F64" t="n">
-        <v>91.36692047119141</v>
+        <v>91.36692810058594</v>
       </c>
       <c r="G64" t="n">
         <v>4202900</v>
@@ -1921,16 +1921,16 @@
         <v>45385</v>
       </c>
       <c r="C65" t="n">
-        <v>91.37603759765625</v>
+        <v>91.37604522705078</v>
       </c>
       <c r="D65" t="n">
-        <v>91.38514800015857</v>
+        <v>91.38515563031378</v>
       </c>
       <c r="E65" t="n">
-        <v>91.37603759765625</v>
+        <v>91.37604522705078</v>
       </c>
       <c r="F65" t="n">
-        <v>91.37603759765625</v>
+        <v>91.37604522705078</v>
       </c>
       <c r="G65" t="n">
         <v>4333600</v>
@@ -1944,16 +1944,16 @@
         <v>45386</v>
       </c>
       <c r="C66" t="n">
-        <v>91.42158508300781</v>
+        <v>91.42156982421875</v>
       </c>
       <c r="D66" t="n">
-        <v>91.42158508300781</v>
+        <v>91.42156982421875</v>
       </c>
       <c r="E66" t="n">
-        <v>91.41247468026413</v>
+        <v>91.41245942299565</v>
       </c>
       <c r="F66" t="n">
-        <v>91.41247468026413</v>
+        <v>91.41245942299565</v>
       </c>
       <c r="G66" t="n">
         <v>3427500</v>
@@ -1990,16 +1990,16 @@
         <v>45390</v>
       </c>
       <c r="C68" t="n">
-        <v>91.44890594482422</v>
+        <v>91.44889831542969</v>
       </c>
       <c r="D68" t="n">
-        <v>91.44890594482422</v>
+        <v>91.44889831542969</v>
       </c>
       <c r="E68" t="n">
-        <v>91.43979554241898</v>
+        <v>91.43978791378451</v>
       </c>
       <c r="F68" t="n">
-        <v>91.44890594482422</v>
+        <v>91.44889831542969</v>
       </c>
       <c r="G68" t="n">
         <v>3511400</v>
@@ -2013,16 +2013,16 @@
         <v>45391</v>
       </c>
       <c r="C69" t="n">
-        <v>91.4580078125</v>
+        <v>91.45802307128906</v>
       </c>
       <c r="D69" t="n">
-        <v>91.4580078125</v>
+        <v>91.45802307128906</v>
       </c>
       <c r="E69" t="n">
-        <v>91.44889741094494</v>
+        <v>91.44891266821402</v>
       </c>
       <c r="F69" t="n">
-        <v>91.4580078125</v>
+        <v>91.45802307128906</v>
       </c>
       <c r="G69" t="n">
         <v>3578500</v>
@@ -2036,16 +2036,16 @@
         <v>45392</v>
       </c>
       <c r="C70" t="n">
-        <v>91.47621917724609</v>
+        <v>91.47622680664062</v>
       </c>
       <c r="D70" t="n">
-        <v>91.47621917724609</v>
+        <v>91.47622680664062</v>
       </c>
       <c r="E70" t="n">
-        <v>91.45800532383184</v>
+        <v>91.45801295170727</v>
       </c>
       <c r="F70" t="n">
-        <v>91.46710877593893</v>
+        <v>91.46711640457362</v>
       </c>
       <c r="G70" t="n">
         <v>3893100</v>
@@ -2082,16 +2082,16 @@
         <v>45394</v>
       </c>
       <c r="C72" t="n">
-        <v>91.52177429199219</v>
+        <v>91.52176666259766</v>
       </c>
       <c r="D72" t="n">
-        <v>91.52177429199219</v>
+        <v>91.52176666259766</v>
       </c>
       <c r="E72" t="n">
-        <v>91.51266388968386</v>
+        <v>91.51265626104879</v>
       </c>
       <c r="F72" t="n">
-        <v>91.52177429199219</v>
+        <v>91.52176666259766</v>
       </c>
       <c r="G72" t="n">
         <v>4235400</v>
@@ -2105,16 +2105,16 @@
         <v>45397</v>
       </c>
       <c r="C73" t="n">
-        <v>91.53997039794922</v>
+        <v>91.53997802734375</v>
       </c>
       <c r="D73" t="n">
-        <v>91.53997039794922</v>
+        <v>91.53997802734375</v>
       </c>
       <c r="E73" t="n">
-        <v>91.53085999740739</v>
+        <v>91.53086762604262</v>
       </c>
       <c r="F73" t="n">
-        <v>91.53085999740739</v>
+        <v>91.53086762604262</v>
       </c>
       <c r="G73" t="n">
         <v>4144700</v>
@@ -2128,16 +2128,16 @@
         <v>45398</v>
       </c>
       <c r="C74" t="n">
-        <v>91.53997039794922</v>
+        <v>91.53997802734375</v>
       </c>
       <c r="D74" t="n">
-        <v>91.55818424983336</v>
+        <v>91.55819188074594</v>
       </c>
       <c r="E74" t="n">
-        <v>91.53997039794922</v>
+        <v>91.53997802734375</v>
       </c>
       <c r="F74" t="n">
-        <v>91.54908079849103</v>
+        <v>91.54908842864488</v>
       </c>
       <c r="G74" t="n">
         <v>4850000</v>
@@ -2151,16 +2151,16 @@
         <v>45399</v>
       </c>
       <c r="C75" t="n">
-        <v>91.56729888916016</v>
+        <v>91.56731414794922</v>
       </c>
       <c r="D75" t="n">
-        <v>91.56729888916016</v>
+        <v>91.56731414794922</v>
       </c>
       <c r="E75" t="n">
-        <v>91.55818848819661</v>
+        <v>91.55820374546751</v>
       </c>
       <c r="F75" t="n">
-        <v>91.56729888916016</v>
+        <v>91.56731414794922</v>
       </c>
       <c r="G75" t="n">
         <v>3688400</v>
@@ -2197,16 +2197,16 @@
         <v>45401</v>
       </c>
       <c r="C77" t="n">
-        <v>91.6219482421875</v>
+        <v>91.62194061279297</v>
       </c>
       <c r="D77" t="n">
-        <v>91.6219482421875</v>
+        <v>91.62194061279297</v>
       </c>
       <c r="E77" t="n">
-        <v>91.60373438929209</v>
+        <v>91.60372676141424</v>
       </c>
       <c r="F77" t="n">
-        <v>91.6219482421875</v>
+        <v>91.62194061279297</v>
       </c>
       <c r="G77" t="n">
         <v>3319500</v>
@@ -2220,16 +2220,16 @@
         <v>45404</v>
       </c>
       <c r="C78" t="n">
-        <v>91.63106536865234</v>
+        <v>91.63108825683594</v>
       </c>
       <c r="D78" t="n">
-        <v>91.63106536865234</v>
+        <v>91.63108825683594</v>
       </c>
       <c r="E78" t="n">
-        <v>91.62195496693603</v>
+        <v>91.62197785284397</v>
       </c>
       <c r="F78" t="n">
-        <v>91.63106536865234</v>
+        <v>91.63108825683594</v>
       </c>
       <c r="G78" t="n">
         <v>3547400</v>
@@ -2243,16 +2243,16 @@
         <v>45405</v>
       </c>
       <c r="C79" t="n">
-        <v>91.64019012451172</v>
+        <v>91.64015960693359</v>
       </c>
       <c r="D79" t="n">
-        <v>91.64930052765506</v>
+        <v>91.64927000704303</v>
       </c>
       <c r="E79" t="n">
-        <v>91.63107972136839</v>
+        <v>91.63104920682416</v>
       </c>
       <c r="F79" t="n">
-        <v>91.64019012451172</v>
+        <v>91.64015960693359</v>
       </c>
       <c r="G79" t="n">
         <v>4233300</v>
@@ -2266,16 +2266,16 @@
         <v>45406</v>
       </c>
       <c r="C80" t="n">
-        <v>91.6492919921875</v>
+        <v>91.64928436279297</v>
       </c>
       <c r="D80" t="n">
-        <v>91.65839544528153</v>
+        <v>91.65838781512917</v>
       </c>
       <c r="E80" t="n">
-        <v>91.6492919921875</v>
+        <v>91.64928436279297</v>
       </c>
       <c r="F80" t="n">
-        <v>91.65839544528153</v>
+        <v>91.65838781512917</v>
       </c>
       <c r="G80" t="n">
         <v>3200000</v>
@@ -2312,16 +2312,16 @@
         <v>45408</v>
       </c>
       <c r="C82" t="n">
-        <v>91.71305847167969</v>
+        <v>91.71303558349609</v>
       </c>
       <c r="D82" t="n">
-        <v>91.71305847167969</v>
+        <v>91.71303558349609</v>
       </c>
       <c r="E82" t="n">
-        <v>91.70394806863366</v>
+        <v>91.70392518272369</v>
       </c>
       <c r="F82" t="n">
-        <v>91.70394806863366</v>
+        <v>91.70392518272369</v>
       </c>
       <c r="G82" t="n">
         <v>3008600</v>
@@ -2335,16 +2335,16 @@
         <v>45411</v>
       </c>
       <c r="C83" t="n">
-        <v>91.71305847167969</v>
+        <v>91.71303558349609</v>
       </c>
       <c r="D83" t="n">
-        <v>91.7221619255243</v>
+        <v>91.72213903506884</v>
       </c>
       <c r="E83" t="n">
-        <v>91.71305847167969</v>
+        <v>91.71303558349609</v>
       </c>
       <c r="F83" t="n">
-        <v>91.7221619255243</v>
+        <v>91.72213903506884</v>
       </c>
       <c r="G83" t="n">
         <v>2501900</v>
@@ -2358,16 +2358,16 @@
         <v>45412</v>
       </c>
       <c r="C84" t="n">
-        <v>91.72213745117188</v>
+        <v>91.72215270996094</v>
       </c>
       <c r="D84" t="n">
-        <v>91.73124785178696</v>
+        <v>91.73126311209163</v>
       </c>
       <c r="E84" t="n">
-        <v>91.72213745117188</v>
+        <v>91.72215270996094</v>
       </c>
       <c r="F84" t="n">
-        <v>91.72213745117188</v>
+        <v>91.72215270996094</v>
       </c>
       <c r="G84" t="n">
         <v>6488000</v>
@@ -2381,16 +2381,16 @@
         <v>45413</v>
       </c>
       <c r="C85" t="n">
-        <v>91.75691223144531</v>
+        <v>91.75691986083984</v>
       </c>
       <c r="D85" t="n">
-        <v>91.75691223144531</v>
+        <v>91.75691986083984</v>
       </c>
       <c r="E85" t="n">
-        <v>91.74776992151747</v>
+        <v>91.74777755015184</v>
       </c>
       <c r="F85" t="n">
-        <v>91.75691223144531</v>
+        <v>91.75691986083984</v>
       </c>
       <c r="G85" t="n">
         <v>8406600</v>
@@ -2404,16 +2404,16 @@
         <v>45414</v>
       </c>
       <c r="C86" t="n">
-        <v>91.79349517822266</v>
+        <v>91.79350280761719</v>
       </c>
       <c r="D86" t="n">
-        <v>91.79349517822266</v>
+        <v>91.79350280761719</v>
       </c>
       <c r="E86" t="n">
-        <v>91.78434589015285</v>
+        <v>91.78435351878694</v>
       </c>
       <c r="F86" t="n">
-        <v>91.79349517822266</v>
+        <v>91.79350280761719</v>
       </c>
       <c r="G86" t="n">
         <v>4369600</v>
@@ -2427,16 +2427,16 @@
         <v>45415</v>
       </c>
       <c r="C87" t="n">
-        <v>91.81181335449219</v>
+        <v>91.81179046630859</v>
       </c>
       <c r="D87" t="n">
-        <v>91.81181335449219</v>
+        <v>91.81179046630859</v>
       </c>
       <c r="E87" t="n">
-        <v>91.79351477444618</v>
+        <v>91.79349189082433</v>
       </c>
       <c r="F87" t="n">
-        <v>91.80266406446918</v>
+        <v>91.80264117856646</v>
       </c>
       <c r="G87" t="n">
         <v>4792400</v>
@@ -2496,16 +2496,16 @@
         <v>45420</v>
       </c>
       <c r="C90" t="n">
-        <v>91.84838104248047</v>
+        <v>91.84840393066406</v>
       </c>
       <c r="D90" t="n">
-        <v>91.84838104248047</v>
+        <v>91.84840393066406</v>
       </c>
       <c r="E90" t="n">
-        <v>91.8300824669157</v>
+        <v>91.83010535053937</v>
       </c>
       <c r="F90" t="n">
-        <v>91.83923175469809</v>
+        <v>91.83925464060172</v>
       </c>
       <c r="G90" t="n">
         <v>3109400</v>
@@ -2519,16 +2519,16 @@
         <v>45421</v>
       </c>
       <c r="C91" t="n">
-        <v>91.87582397460938</v>
+        <v>91.87583160400391</v>
       </c>
       <c r="D91" t="n">
-        <v>91.88496628373375</v>
+        <v>91.88497391388746</v>
       </c>
       <c r="E91" t="n">
-        <v>91.87582397460938</v>
+        <v>91.87583160400391</v>
       </c>
       <c r="F91" t="n">
-        <v>91.88039512917156</v>
+        <v>91.88040275894568</v>
       </c>
       <c r="G91" t="n">
         <v>2739600</v>
@@ -2542,16 +2542,16 @@
         <v>45422</v>
       </c>
       <c r="C92" t="n">
-        <v>91.90325927734375</v>
+        <v>91.90326690673828</v>
       </c>
       <c r="D92" t="n">
-        <v>91.90325927734375</v>
+        <v>91.90326690673828</v>
       </c>
       <c r="E92" t="n">
-        <v>91.88496070248264</v>
+        <v>91.88496833035812</v>
       </c>
       <c r="F92" t="n">
-        <v>91.90325927734375</v>
+        <v>91.90326690673828</v>
       </c>
       <c r="G92" t="n">
         <v>3005800</v>
@@ -2565,16 +2565,16 @@
         <v>45425</v>
       </c>
       <c r="C93" t="n">
-        <v>91.91241455078125</v>
+        <v>91.91242218017578</v>
       </c>
       <c r="D93" t="n">
-        <v>91.91241455078125</v>
+        <v>91.91242218017578</v>
       </c>
       <c r="E93" t="n">
-        <v>91.90326526275483</v>
+        <v>91.9032728913899</v>
       </c>
       <c r="F93" t="n">
-        <v>91.91241455078125</v>
+        <v>91.91242218017578</v>
       </c>
       <c r="G93" t="n">
         <v>3317000</v>
@@ -2588,16 +2588,16 @@
         <v>45426</v>
       </c>
       <c r="C94" t="n">
-        <v>91.91241455078125</v>
+        <v>91.91242218017578</v>
       </c>
       <c r="D94" t="n">
-        <v>91.92155685994571</v>
+        <v>91.92156449009912</v>
       </c>
       <c r="E94" t="n">
-        <v>91.91241455078125</v>
+        <v>91.91242218017578</v>
       </c>
       <c r="F94" t="n">
-        <v>91.92155685994571</v>
+        <v>91.92156449009912</v>
       </c>
       <c r="G94" t="n">
         <v>2765800</v>
@@ -2657,16 +2657,16 @@
         <v>45429</v>
       </c>
       <c r="C97" t="n">
-        <v>91.98560333251953</v>
+        <v>91.985595703125</v>
       </c>
       <c r="D97" t="n">
-        <v>91.9947526220791</v>
+        <v>91.99474499192573</v>
       </c>
       <c r="E97" t="n">
-        <v>91.98560333251953</v>
+        <v>91.985595703125</v>
       </c>
       <c r="F97" t="n">
-        <v>91.9947526220791</v>
+        <v>91.99474499192573</v>
       </c>
       <c r="G97" t="n">
         <v>4544200</v>
@@ -2680,16 +2680,16 @@
         <v>45432</v>
       </c>
       <c r="C98" t="n">
-        <v>91.99473571777344</v>
+        <v>91.99474334716797</v>
       </c>
       <c r="D98" t="n">
-        <v>92.0038850056518</v>
+        <v>92.00389263580512</v>
       </c>
       <c r="E98" t="n">
-        <v>91.99473571777344</v>
+        <v>91.99474334716797</v>
       </c>
       <c r="F98" t="n">
-        <v>92.0038850056518</v>
+        <v>92.00389263580512</v>
       </c>
       <c r="G98" t="n">
         <v>3341000</v>
@@ -2703,16 +2703,16 @@
         <v>45433</v>
       </c>
       <c r="C99" t="n">
-        <v>92.01301574707031</v>
+        <v>92.01302337646484</v>
       </c>
       <c r="D99" t="n">
-        <v>92.02216503379846</v>
+        <v>92.02217266395162</v>
       </c>
       <c r="E99" t="n">
-        <v>92.01301574707031</v>
+        <v>92.01302337646484</v>
       </c>
       <c r="F99" t="n">
-        <v>92.01301574707031</v>
+        <v>92.01302337646484</v>
       </c>
       <c r="G99" t="n">
         <v>3774900</v>
@@ -2726,16 +2726,16 @@
         <v>45434</v>
       </c>
       <c r="C100" t="n">
-        <v>92.02218627929688</v>
+        <v>92.02220153808594</v>
       </c>
       <c r="D100" t="n">
-        <v>92.03133556813735</v>
+        <v>92.03135082844351</v>
       </c>
       <c r="E100" t="n">
-        <v>92.02218627929688</v>
+        <v>92.02220153808594</v>
       </c>
       <c r="F100" t="n">
-        <v>92.03133556813735</v>
+        <v>92.03135082844351</v>
       </c>
       <c r="G100" t="n">
         <v>2609000</v>
@@ -2749,16 +2749,16 @@
         <v>45435</v>
       </c>
       <c r="C101" t="n">
-        <v>92.08621215820312</v>
+        <v>92.08621978759766</v>
       </c>
       <c r="D101" t="n">
-        <v>92.08621215820312</v>
+        <v>92.08621978759766</v>
       </c>
       <c r="E101" t="n">
-        <v>92.07706984874001</v>
+        <v>92.0770774773771</v>
       </c>
       <c r="F101" t="n">
-        <v>92.07706984874001</v>
+        <v>92.0770774773771</v>
       </c>
       <c r="G101" t="n">
         <v>3077800</v>
@@ -2795,16 +2795,16 @@
         <v>45440</v>
       </c>
       <c r="C103" t="n">
-        <v>92.10452270507812</v>
+        <v>92.1044921875</v>
       </c>
       <c r="D103" t="n">
-        <v>92.10452270507812</v>
+        <v>92.1044921875</v>
       </c>
       <c r="E103" t="n">
-        <v>92.09537341556376</v>
+        <v>92.09534290101713</v>
       </c>
       <c r="F103" t="n">
-        <v>92.09537341556376</v>
+        <v>92.09534290101713</v>
       </c>
       <c r="G103" t="n">
         <v>3684600</v>
@@ -2818,16 +2818,16 @@
         <v>45441</v>
       </c>
       <c r="C104" t="n">
-        <v>92.10452270507812</v>
+        <v>92.1044921875</v>
       </c>
       <c r="D104" t="n">
-        <v>92.1136650157294</v>
+        <v>92.1136344951221</v>
       </c>
       <c r="E104" t="n">
-        <v>92.10452270507812</v>
+        <v>92.1044921875</v>
       </c>
       <c r="F104" t="n">
-        <v>92.1136650157294</v>
+        <v>92.1136344951221</v>
       </c>
       <c r="G104" t="n">
         <v>3971700</v>
@@ -2841,16 +2841,16 @@
         <v>45442</v>
       </c>
       <c r="C105" t="n">
-        <v>92.12279510498047</v>
+        <v>92.12281036376953</v>
       </c>
       <c r="D105" t="n">
-        <v>92.13194439258794</v>
+        <v>92.13195965289245</v>
       </c>
       <c r="E105" t="n">
-        <v>92.12279510498047</v>
+        <v>92.12281036376953</v>
       </c>
       <c r="F105" t="n">
-        <v>92.12279510498047</v>
+        <v>92.12281036376953</v>
       </c>
       <c r="G105" t="n">
         <v>3566800</v>
@@ -2864,16 +2864,16 @@
         <v>45443</v>
       </c>
       <c r="C106" t="n">
-        <v>92.15940093994141</v>
+        <v>92.15938568115234</v>
       </c>
       <c r="D106" t="n">
-        <v>92.15940093994141</v>
+        <v>92.15938568115234</v>
       </c>
       <c r="E106" t="n">
-        <v>92.15025165077893</v>
+        <v>92.15023639350471</v>
       </c>
       <c r="F106" t="n">
-        <v>92.15025165077893</v>
+        <v>92.15023639350471</v>
       </c>
       <c r="G106" t="n">
         <v>7082900</v>
@@ -2887,16 +2887,16 @@
         <v>45446</v>
       </c>
       <c r="C107" t="n">
-        <v>92.17778015136719</v>
+        <v>92.17775726318359</v>
       </c>
       <c r="D107" t="n">
-        <v>92.18696256377655</v>
+        <v>92.18693967331291</v>
       </c>
       <c r="E107" t="n">
-        <v>92.17778015136719</v>
+        <v>92.17775726318359</v>
       </c>
       <c r="F107" t="n">
-        <v>92.17778015136719</v>
+        <v>92.17775726318359</v>
       </c>
       <c r="G107" t="n">
         <v>9568200</v>
@@ -2910,16 +2910,16 @@
         <v>45447</v>
       </c>
       <c r="C108" t="n">
-        <v>92.19613647460938</v>
+        <v>92.19614410400391</v>
       </c>
       <c r="D108" t="n">
-        <v>92.19613647460938</v>
+        <v>92.19614410400391</v>
       </c>
       <c r="E108" t="n">
-        <v>92.18694705427092</v>
+        <v>92.18695468290501</v>
       </c>
       <c r="F108" t="n">
-        <v>92.19613647460938</v>
+        <v>92.19614410400391</v>
       </c>
       <c r="G108" t="n">
         <v>5355900</v>
@@ -2933,16 +2933,16 @@
         <v>45448</v>
       </c>
       <c r="C109" t="n">
-        <v>92.21452331542969</v>
+        <v>92.21453857421875</v>
       </c>
       <c r="D109" t="n">
-        <v>92.21452331542969</v>
+        <v>92.21453857421875</v>
       </c>
       <c r="E109" t="n">
-        <v>92.205333894294</v>
+        <v>92.20534915156249</v>
       </c>
       <c r="F109" t="n">
-        <v>92.205333894294</v>
+        <v>92.20534915156249</v>
       </c>
       <c r="G109" t="n">
         <v>4285300</v>
@@ -2956,16 +2956,16 @@
         <v>45449</v>
       </c>
       <c r="C110" t="n">
-        <v>92.21452331542969</v>
+        <v>92.21453857421875</v>
       </c>
       <c r="D110" t="n">
-        <v>92.22370572709083</v>
+        <v>92.22372098739932</v>
       </c>
       <c r="E110" t="n">
-        <v>92.21452331542969</v>
+        <v>92.21453857421875</v>
       </c>
       <c r="F110" t="n">
-        <v>92.22370572709083</v>
+        <v>92.22372098739932</v>
       </c>
       <c r="G110" t="n">
         <v>3376100</v>
@@ -2979,16 +2979,16 @@
         <v>45450</v>
       </c>
       <c r="C111" t="n">
-        <v>92.25125885009766</v>
+        <v>92.25126647949219</v>
       </c>
       <c r="D111" t="n">
-        <v>92.26044126025177</v>
+        <v>92.2604488904057</v>
       </c>
       <c r="E111" t="n">
-        <v>92.25125885009766</v>
+        <v>92.25126647949219</v>
       </c>
       <c r="F111" t="n">
-        <v>92.26044126025177</v>
+        <v>92.2604488904057</v>
       </c>
       <c r="G111" t="n">
         <v>3490400</v>
@@ -3002,16 +3002,16 @@
         <v>45453</v>
       </c>
       <c r="C112" t="n">
-        <v>92.26964569091797</v>
+        <v>92.26966094970703</v>
       </c>
       <c r="D112" t="n">
-        <v>92.27883511204048</v>
+        <v>92.27885037234921</v>
       </c>
       <c r="E112" t="n">
-        <v>92.26964569091797</v>
+        <v>92.26966094970703</v>
       </c>
       <c r="F112" t="n">
-        <v>92.27883511204048</v>
+        <v>92.27885037234921</v>
       </c>
       <c r="G112" t="n">
         <v>2732300</v>
@@ -3071,16 +3071,16 @@
         <v>45456</v>
       </c>
       <c r="C115" t="n">
-        <v>92.31558990478516</v>
+        <v>92.31558227539062</v>
       </c>
       <c r="D115" t="n">
-        <v>92.32477231684271</v>
+        <v>92.32476468668929</v>
       </c>
       <c r="E115" t="n">
-        <v>92.30640048325276</v>
+        <v>92.30639285461768</v>
       </c>
       <c r="F115" t="n">
-        <v>92.31558990478516</v>
+        <v>92.31558227539062</v>
       </c>
       <c r="G115" t="n">
         <v>3925700</v>
@@ -3094,16 +3094,16 @@
         <v>45457</v>
       </c>
       <c r="C116" t="n">
-        <v>92.36151123046875</v>
+        <v>92.36150360107422</v>
       </c>
       <c r="D116" t="n">
-        <v>92.36151123046875</v>
+        <v>92.36150360107422</v>
       </c>
       <c r="E116" t="n">
-        <v>92.34313939921861</v>
+        <v>92.34313177134166</v>
       </c>
       <c r="F116" t="n">
-        <v>92.3523218101067</v>
+        <v>92.35231418147126</v>
       </c>
       <c r="G116" t="n">
         <v>3505500</v>
@@ -3117,16 +3117,16 @@
         <v>45460</v>
       </c>
       <c r="C117" t="n">
-        <v>92.37070465087891</v>
+        <v>92.37071228027344</v>
       </c>
       <c r="D117" t="n">
-        <v>92.37070465087891</v>
+        <v>92.37071228027344</v>
       </c>
       <c r="E117" t="n">
-        <v>92.36151523011891</v>
+        <v>92.36152285875446</v>
       </c>
       <c r="F117" t="n">
-        <v>92.37070465087891</v>
+        <v>92.37071228027344</v>
       </c>
       <c r="G117" t="n">
         <v>3493700</v>
@@ -3140,16 +3140,16 @@
         <v>45461</v>
       </c>
       <c r="C118" t="n">
-        <v>92.39826965332031</v>
+        <v>92.39826202392578</v>
       </c>
       <c r="D118" t="n">
-        <v>92.39826965332031</v>
+        <v>92.39826202392578</v>
       </c>
       <c r="E118" t="n">
-        <v>92.3890802321874</v>
+        <v>92.38907260355165</v>
       </c>
       <c r="F118" t="n">
-        <v>92.39826965332031</v>
+        <v>92.39826202392578</v>
       </c>
       <c r="G118" t="n">
         <v>2972000</v>
@@ -3186,16 +3186,16 @@
         <v>45464</v>
       </c>
       <c r="C120" t="n">
-        <v>92.44419860839844</v>
+        <v>92.44420623779297</v>
       </c>
       <c r="D120" t="n">
-        <v>92.45338101895015</v>
+        <v>92.45338864910251</v>
       </c>
       <c r="E120" t="n">
-        <v>92.44419860839844</v>
+        <v>92.44420623779297</v>
       </c>
       <c r="F120" t="n">
-        <v>92.44419860839844</v>
+        <v>92.44420623779297</v>
       </c>
       <c r="G120" t="n">
         <v>3460900</v>
@@ -3209,16 +3209,16 @@
         <v>45467</v>
       </c>
       <c r="C121" t="n">
-        <v>92.45338439941406</v>
+        <v>92.45339202880859</v>
       </c>
       <c r="D121" t="n">
-        <v>92.46257381977549</v>
+        <v>92.46258144992834</v>
       </c>
       <c r="E121" t="n">
-        <v>92.45338439941406</v>
+        <v>92.45339202880859</v>
       </c>
       <c r="F121" t="n">
-        <v>92.46257381977549</v>
+        <v>92.46258144992834</v>
       </c>
       <c r="G121" t="n">
         <v>3369500</v>
@@ -3232,16 +3232,16 @@
         <v>45468</v>
       </c>
       <c r="C122" t="n">
-        <v>92.47176361083984</v>
+        <v>92.47177886962891</v>
       </c>
       <c r="D122" t="n">
-        <v>92.47176361083984</v>
+        <v>92.47177886962891</v>
       </c>
       <c r="E122" t="n">
-        <v>92.46257419044157</v>
+        <v>92.46258944771429</v>
       </c>
       <c r="F122" t="n">
-        <v>92.47176361083984</v>
+        <v>92.47177886962891</v>
       </c>
       <c r="G122" t="n">
         <v>3561700</v>
@@ -3255,16 +3255,16 @@
         <v>45469</v>
       </c>
       <c r="C123" t="n">
-        <v>92.48095703125</v>
+        <v>92.48094177246094</v>
       </c>
       <c r="D123" t="n">
-        <v>92.49013944257143</v>
+        <v>92.49012418226734</v>
       </c>
       <c r="E123" t="n">
-        <v>92.48095703125</v>
+        <v>92.48094177246094</v>
       </c>
       <c r="F123" t="n">
-        <v>92.48187527238214</v>
+        <v>92.48186001344158</v>
       </c>
       <c r="G123" t="n">
         <v>4815500</v>
@@ -3278,16 +3278,16 @@
         <v>45470</v>
       </c>
       <c r="C124" t="n">
-        <v>92.49013519287109</v>
+        <v>92.49014282226562</v>
       </c>
       <c r="D124" t="n">
-        <v>92.4993246132446</v>
+        <v>92.49933224339715</v>
       </c>
       <c r="E124" t="n">
-        <v>92.49013519287109</v>
+        <v>92.49014282226562</v>
       </c>
       <c r="F124" t="n">
-        <v>92.4993246132446</v>
+        <v>92.49933224339715</v>
       </c>
       <c r="G124" t="n">
         <v>3349900</v>
@@ -3301,16 +3301,16 @@
         <v>45471</v>
       </c>
       <c r="C125" t="n">
-        <v>92.52688598632812</v>
+        <v>92.52687072753906</v>
       </c>
       <c r="D125" t="n">
-        <v>92.53607540671368</v>
+        <v>92.53606014640917</v>
       </c>
       <c r="E125" t="n">
-        <v>92.52688598632812</v>
+        <v>92.52687072753906</v>
       </c>
       <c r="F125" t="n">
-        <v>92.52688598632812</v>
+        <v>92.52687072753906</v>
       </c>
       <c r="G125" t="n">
         <v>7427800</v>
@@ -3324,16 +3324,16 @@
         <v>45474</v>
       </c>
       <c r="C126" t="n">
-        <v>92.56288146972656</v>
+        <v>92.56287384033203</v>
       </c>
       <c r="D126" t="n">
-        <v>92.56288146972656</v>
+        <v>92.56287384033203</v>
       </c>
       <c r="E126" t="n">
-        <v>92.55365885608765</v>
+        <v>92.55365122745329</v>
       </c>
       <c r="F126" t="n">
-        <v>92.56288146972656</v>
+        <v>92.56287384033203</v>
       </c>
       <c r="G126" t="n">
         <v>9965300</v>
@@ -3347,16 +3347,16 @@
         <v>45475</v>
       </c>
       <c r="C127" t="n">
-        <v>92.57210540771484</v>
+        <v>92.57211303710938</v>
       </c>
       <c r="D127" t="n">
-        <v>92.57210540771484</v>
+        <v>92.57211303710938</v>
       </c>
       <c r="E127" t="n">
-        <v>92.56287575448273</v>
+        <v>92.5628833831166</v>
       </c>
       <c r="F127" t="n">
-        <v>92.57210540771484</v>
+        <v>92.57211303710938</v>
       </c>
       <c r="G127" t="n">
         <v>5720900</v>
@@ -3393,16 +3393,16 @@
         <v>45478</v>
       </c>
       <c r="C129" t="n">
-        <v>92.63670349121094</v>
+        <v>92.63669586181641</v>
       </c>
       <c r="D129" t="n">
-        <v>92.63670349121094</v>
+        <v>92.63669586181641</v>
       </c>
       <c r="E129" t="n">
-        <v>92.62747383752138</v>
+        <v>92.627466208887</v>
       </c>
       <c r="F129" t="n">
-        <v>92.62747383752138</v>
+        <v>92.627466208887</v>
       </c>
       <c r="G129" t="n">
         <v>3742000</v>
@@ -3462,16 +3462,16 @@
         <v>45483</v>
       </c>
       <c r="C132" t="n">
-        <v>92.67360687255859</v>
+        <v>92.67362213134766</v>
       </c>
       <c r="D132" t="n">
-        <v>92.68283652543215</v>
+        <v>92.68285178574088</v>
       </c>
       <c r="E132" t="n">
-        <v>92.67360687255859</v>
+        <v>92.67362213134766</v>
       </c>
       <c r="F132" t="n">
-        <v>92.67360687255859</v>
+        <v>92.67362213134766</v>
       </c>
       <c r="G132" t="n">
         <v>4062200</v>
@@ -3485,16 +3485,16 @@
         <v>45484</v>
       </c>
       <c r="C133" t="n">
-        <v>92.69206237792969</v>
+        <v>92.69205474853516</v>
       </c>
       <c r="D133" t="n">
-        <v>92.69206237792969</v>
+        <v>92.69205474853516</v>
       </c>
       <c r="E133" t="n">
-        <v>92.68283976489614</v>
+        <v>92.68283213626073</v>
       </c>
       <c r="F133" t="n">
-        <v>92.68283976489614</v>
+        <v>92.68283213626073</v>
       </c>
       <c r="G133" t="n">
         <v>4195600</v>
@@ -3508,16 +3508,16 @@
         <v>45485</v>
       </c>
       <c r="C134" t="n">
-        <v>92.73822021484375</v>
+        <v>92.73820495605469</v>
       </c>
       <c r="D134" t="n">
-        <v>92.73822021484375</v>
+        <v>92.73820495605469</v>
       </c>
       <c r="E134" t="n">
-        <v>92.72899055999439</v>
+        <v>92.72897530272394</v>
       </c>
       <c r="F134" t="n">
-        <v>92.73822021484375</v>
+        <v>92.73820495605469</v>
       </c>
       <c r="G134" t="n">
         <v>3369000</v>
@@ -3531,16 +3531,16 @@
         <v>45488</v>
       </c>
       <c r="C135" t="n">
-        <v>92.73822021484375</v>
+        <v>92.73820495605469</v>
       </c>
       <c r="D135" t="n">
-        <v>92.7474498696931</v>
+        <v>92.74743460938542</v>
       </c>
       <c r="E135" t="n">
-        <v>92.73822021484375</v>
+        <v>92.73820495605469</v>
       </c>
       <c r="F135" t="n">
-        <v>92.7474498696931</v>
+        <v>92.74743460938542</v>
       </c>
       <c r="G135" t="n">
         <v>3615100</v>
@@ -3554,16 +3554,16 @@
         <v>45489</v>
       </c>
       <c r="C136" t="n">
-        <v>92.75666809082031</v>
+        <v>92.75664520263672</v>
       </c>
       <c r="D136" t="n">
-        <v>92.75666809082031</v>
+        <v>92.75664520263672</v>
       </c>
       <c r="E136" t="n">
-        <v>92.74744547657168</v>
+        <v>92.74742259066382</v>
       </c>
       <c r="F136" t="n">
-        <v>92.75666809082031</v>
+        <v>92.75664520263672</v>
       </c>
       <c r="G136" t="n">
         <v>3622900</v>
@@ -3577,16 +3577,16 @@
         <v>45490</v>
       </c>
       <c r="C137" t="n">
-        <v>92.76588439941406</v>
+        <v>92.765869140625</v>
       </c>
       <c r="D137" t="n">
-        <v>92.77050274603751</v>
+        <v>92.77048748648878</v>
       </c>
       <c r="E137" t="n">
-        <v>92.75665474632972</v>
+        <v>92.75663948905881</v>
       </c>
       <c r="F137" t="n">
-        <v>92.76588439941406</v>
+        <v>92.765869140625</v>
       </c>
       <c r="G137" t="n">
         <v>3822100</v>
@@ -3600,16 +3600,16 @@
         <v>45491</v>
       </c>
       <c r="C138" t="n">
-        <v>92.78435516357422</v>
+        <v>92.78433990478516</v>
       </c>
       <c r="D138" t="n">
-        <v>92.78435516357422</v>
+        <v>92.78433990478516</v>
       </c>
       <c r="E138" t="n">
-        <v>92.77512550935009</v>
+        <v>92.77511025207889</v>
       </c>
       <c r="F138" t="n">
-        <v>92.77512550935009</v>
+        <v>92.77511025207889</v>
       </c>
       <c r="G138" t="n">
         <v>5291400</v>
@@ -3623,16 +3623,16 @@
         <v>45492</v>
       </c>
       <c r="C139" t="n">
-        <v>92.82125854492188</v>
+        <v>92.82125091552734</v>
       </c>
       <c r="D139" t="n">
-        <v>92.82125854492188</v>
+        <v>92.82125091552734</v>
       </c>
       <c r="E139" t="n">
-        <v>92.81203593097594</v>
+        <v>92.81202830233946</v>
       </c>
       <c r="F139" t="n">
-        <v>92.82125854492188</v>
+        <v>92.82125091552734</v>
       </c>
       <c r="G139" t="n">
         <v>2993600</v>
@@ -3669,16 +3669,16 @@
         <v>45496</v>
       </c>
       <c r="C141" t="n">
-        <v>92.84893035888672</v>
+        <v>92.84893798828125</v>
       </c>
       <c r="D141" t="n">
-        <v>92.85815297112931</v>
+        <v>92.85816060128167</v>
       </c>
       <c r="E141" t="n">
-        <v>92.83970070648209</v>
+        <v>92.83970833511823</v>
       </c>
       <c r="F141" t="n">
-        <v>92.84893035888672</v>
+        <v>92.84893798828125</v>
       </c>
       <c r="G141" t="n">
         <v>2829200</v>
@@ -3715,16 +3715,16 @@
         <v>45498</v>
       </c>
       <c r="C143" t="n">
-        <v>92.87660980224609</v>
+        <v>92.87663269042969</v>
       </c>
       <c r="D143" t="n">
-        <v>92.87660980224609</v>
+        <v>92.87663269042969</v>
       </c>
       <c r="E143" t="n">
-        <v>92.8673801500873</v>
+        <v>92.86740303599636</v>
       </c>
       <c r="F143" t="n">
-        <v>92.87660980224609</v>
+        <v>92.87663269042969</v>
       </c>
       <c r="G143" t="n">
         <v>3521700</v>
@@ -3761,16 +3761,16 @@
         <v>45502</v>
       </c>
       <c r="C145" t="n">
-        <v>92.93198394775391</v>
+        <v>92.93197631835938</v>
       </c>
       <c r="D145" t="n">
-        <v>92.93198394775391</v>
+        <v>92.93197631835938</v>
       </c>
       <c r="E145" t="n">
-        <v>92.92275429457088</v>
+        <v>92.92274666593407</v>
       </c>
       <c r="F145" t="n">
-        <v>92.92275429457088</v>
+        <v>92.92274666593407</v>
       </c>
       <c r="G145" t="n">
         <v>3259000</v>
@@ -3784,16 +3784,16 @@
         <v>45503</v>
       </c>
       <c r="C146" t="n">
-        <v>92.93198394775391</v>
+        <v>92.93197631835938</v>
       </c>
       <c r="D146" t="n">
-        <v>92.94121360093693</v>
+        <v>92.94120597078468</v>
       </c>
       <c r="E146" t="n">
-        <v>92.93198394775391</v>
+        <v>92.93197631835938</v>
       </c>
       <c r="F146" t="n">
-        <v>92.94121360093693</v>
+        <v>92.94120597078468</v>
       </c>
       <c r="G146" t="n">
         <v>4559900</v>
@@ -3807,16 +3807,16 @@
         <v>45504</v>
       </c>
       <c r="C147" t="n">
-        <v>92.94123840332031</v>
+        <v>92.94119262695312</v>
       </c>
       <c r="D147" t="n">
-        <v>92.95046805896638</v>
+        <v>92.95042227805331</v>
       </c>
       <c r="E147" t="n">
-        <v>92.94123840332031</v>
+        <v>92.94119262695312</v>
       </c>
       <c r="F147" t="n">
-        <v>92.94123840332031</v>
+        <v>92.94119262695312</v>
       </c>
       <c r="G147" t="n">
         <v>7256900</v>
@@ -3853,16 +3853,16 @@
         <v>45506</v>
       </c>
       <c r="C149" t="n">
-        <v>93.01815795898438</v>
+        <v>93.01815032958984</v>
       </c>
       <c r="D149" t="n">
-        <v>93.01815795898438</v>
+        <v>93.01815032958984</v>
       </c>
       <c r="E149" t="n">
-        <v>92.99962232438862</v>
+        <v>92.9996146965144</v>
       </c>
       <c r="F149" t="n">
-        <v>93.00888660570126</v>
+        <v>93.00887897706717</v>
       </c>
       <c r="G149" t="n">
         <v>7927400</v>
@@ -3876,16 +3876,16 @@
         <v>45509</v>
       </c>
       <c r="C150" t="n">
-        <v>93.02741241455078</v>
+        <v>93.02742767333984</v>
       </c>
       <c r="D150" t="n">
-        <v>93.04594804577968</v>
+        <v>93.04596330760904</v>
       </c>
       <c r="E150" t="n">
-        <v>93.01814106295174</v>
+        <v>93.01815632022007</v>
       </c>
       <c r="F150" t="n">
-        <v>93.01814106295174</v>
+        <v>93.01815632022007</v>
       </c>
       <c r="G150" t="n">
         <v>8712900</v>
@@ -3899,16 +3899,16 @@
         <v>45510</v>
       </c>
       <c r="C151" t="n">
-        <v>93.04593658447266</v>
+        <v>93.04595184326172</v>
       </c>
       <c r="D151" t="n">
-        <v>93.04593658447266</v>
+        <v>93.04595184326172</v>
       </c>
       <c r="E151" t="n">
-        <v>93.02740095552696</v>
+        <v>93.02741621127633</v>
       </c>
       <c r="F151" t="n">
-        <v>93.02740095552696</v>
+        <v>93.02741621127633</v>
       </c>
       <c r="G151" t="n">
         <v>5059100</v>
@@ -3922,16 +3922,16 @@
         <v>45511</v>
       </c>
       <c r="C152" t="n">
-        <v>93.04593658447266</v>
+        <v>93.04595184326172</v>
       </c>
       <c r="D152" t="n">
-        <v>93.05520793492965</v>
+        <v>93.05522319523915</v>
       </c>
       <c r="E152" t="n">
-        <v>93.04593658447266</v>
+        <v>93.04595184326172</v>
       </c>
       <c r="F152" t="n">
-        <v>93.04593658447266</v>
+        <v>93.04595184326172</v>
       </c>
       <c r="G152" t="n">
         <v>4611400</v>
@@ -3968,16 +3968,16 @@
         <v>45513</v>
       </c>
       <c r="C154" t="n">
-        <v>93.10157775878906</v>
+        <v>93.10157012939453</v>
       </c>
       <c r="D154" t="n">
-        <v>93.11084203928218</v>
+        <v>93.11083440912847</v>
       </c>
       <c r="E154" t="n">
-        <v>93.0923064063261</v>
+        <v>93.09229877769133</v>
       </c>
       <c r="F154" t="n">
-        <v>93.10157775878906</v>
+        <v>93.10157012939453</v>
       </c>
       <c r="G154" t="n">
         <v>5548300</v>
@@ -3991,16 +3991,16 @@
         <v>45516</v>
       </c>
       <c r="C155" t="n">
-        <v>93.12012481689453</v>
+        <v>93.12010955810547</v>
       </c>
       <c r="D155" t="n">
-        <v>93.12939617049503</v>
+        <v>93.12938091018674</v>
       </c>
       <c r="E155" t="n">
-        <v>93.11085346329405</v>
+        <v>93.1108382060242</v>
       </c>
       <c r="F155" t="n">
-        <v>93.12012481689453</v>
+        <v>93.12010955810547</v>
       </c>
       <c r="G155" t="n">
         <v>3845400</v>
@@ -4037,16 +4037,16 @@
         <v>45518</v>
       </c>
       <c r="C157" t="n">
-        <v>93.15720367431641</v>
+        <v>93.15718841552734</v>
       </c>
       <c r="D157" t="n">
-        <v>93.15720367431641</v>
+        <v>93.15718841552734</v>
       </c>
       <c r="E157" t="n">
-        <v>93.13866803898368</v>
+        <v>93.13865278323068</v>
       </c>
       <c r="F157" t="n">
-        <v>93.14793232066467</v>
+        <v>93.14791706339422</v>
       </c>
       <c r="G157" t="n">
         <v>4327700</v>
@@ -4060,16 +4060,16 @@
         <v>45519</v>
       </c>
       <c r="C158" t="n">
-        <v>93.16645812988281</v>
+        <v>93.16645050048828</v>
       </c>
       <c r="D158" t="n">
-        <v>93.16645812988281</v>
+        <v>93.16645050048828</v>
       </c>
       <c r="E158" t="n">
-        <v>93.14791542594251</v>
+        <v>93.14790779806644</v>
       </c>
       <c r="F158" t="n">
-        <v>93.14791542594251</v>
+        <v>93.14790779806644</v>
       </c>
       <c r="G158" t="n">
         <v>4217800</v>
@@ -4083,16 +4083,16 @@
         <v>45520</v>
       </c>
       <c r="C159" t="n">
-        <v>93.20354461669922</v>
+        <v>93.20352935791016</v>
       </c>
       <c r="D159" t="n">
-        <v>93.20354461669922</v>
+        <v>93.20352935791016</v>
       </c>
       <c r="E159" t="n">
-        <v>93.19427326391828</v>
+        <v>93.19425800664706</v>
       </c>
       <c r="F159" t="n">
-        <v>93.20354461669922</v>
+        <v>93.20352935791016</v>
       </c>
       <c r="G159" t="n">
         <v>3638900</v>
@@ -4106,16 +4106,16 @@
         <v>45523</v>
       </c>
       <c r="C160" t="n">
-        <v>93.21279907226562</v>
+        <v>93.21280670166016</v>
       </c>
       <c r="D160" t="n">
-        <v>93.22207042406932</v>
+        <v>93.22207805422271</v>
       </c>
       <c r="E160" t="n">
-        <v>93.21279907226562</v>
+        <v>93.21280670166016</v>
       </c>
       <c r="F160" t="n">
-        <v>93.21279907226562</v>
+        <v>93.21280670166016</v>
       </c>
       <c r="G160" t="n">
         <v>3930700</v>
@@ -4129,16 +4129,16 @@
         <v>45524</v>
       </c>
       <c r="C161" t="n">
-        <v>93.22206115722656</v>
+        <v>93.22208404541016</v>
       </c>
       <c r="D161" t="n">
-        <v>93.23133250810862</v>
+        <v>93.23135539856855</v>
       </c>
       <c r="E161" t="n">
-        <v>93.22206115722656</v>
+        <v>93.22208404541016</v>
       </c>
       <c r="F161" t="n">
-        <v>93.23133250810862</v>
+        <v>93.23135539856855</v>
       </c>
       <c r="G161" t="n">
         <v>3084200</v>
@@ -4152,16 +4152,16 @@
         <v>45525</v>
       </c>
       <c r="C162" t="n">
-        <v>93.24988555908203</v>
+        <v>93.24989318847656</v>
       </c>
       <c r="D162" t="n">
-        <v>93.24988555908203</v>
+        <v>93.24989318847656</v>
       </c>
       <c r="E162" t="n">
-        <v>93.23134992582368</v>
+        <v>93.23135755370167</v>
       </c>
       <c r="F162" t="n">
-        <v>93.23134992582368</v>
+        <v>93.23135755370167</v>
       </c>
       <c r="G162" t="n">
         <v>3936000</v>
@@ -4175,16 +4175,16 @@
         <v>45526</v>
       </c>
       <c r="C163" t="n">
-        <v>93.24988555908203</v>
+        <v>93.24989318847656</v>
       </c>
       <c r="D163" t="n">
-        <v>93.25915691169619</v>
+        <v>93.25916454184927</v>
       </c>
       <c r="E163" t="n">
-        <v>93.24988555908203</v>
+        <v>93.24989318847656</v>
       </c>
       <c r="F163" t="n">
-        <v>93.25915691169619</v>
+        <v>93.25916454184927</v>
       </c>
       <c r="G163" t="n">
         <v>3849100</v>
@@ -4198,16 +4198,16 @@
         <v>45527</v>
       </c>
       <c r="C164" t="n">
-        <v>93.28696441650391</v>
+        <v>93.28695678710938</v>
       </c>
       <c r="D164" t="n">
-        <v>93.29623576916964</v>
+        <v>93.29622813901686</v>
       </c>
       <c r="E164" t="n">
-        <v>93.28696441650391</v>
+        <v>93.28695678710938</v>
       </c>
       <c r="F164" t="n">
-        <v>93.29623576916964</v>
+        <v>93.29622813901686</v>
       </c>
       <c r="G164" t="n">
         <v>3549900</v>
@@ -4221,16 +4221,16 @@
         <v>45530</v>
       </c>
       <c r="C165" t="n">
-        <v>93.30550384521484</v>
+        <v>93.30549621582031</v>
       </c>
       <c r="D165" t="n">
-        <v>93.31476812558525</v>
+        <v>93.31476049543321</v>
       </c>
       <c r="E165" t="n">
-        <v>93.30550384521484</v>
+        <v>93.30549621582031</v>
       </c>
       <c r="F165" t="n">
-        <v>93.30550384521484</v>
+        <v>93.30549621582031</v>
       </c>
       <c r="G165" t="n">
         <v>3969000</v>
@@ -4244,16 +4244,16 @@
         <v>45531</v>
       </c>
       <c r="C166" t="n">
-        <v>93.31477355957031</v>
+        <v>93.31476593017578</v>
       </c>
       <c r="D166" t="n">
-        <v>93.32404491245036</v>
+        <v>93.32403728229781</v>
       </c>
       <c r="E166" t="n">
-        <v>93.31477355957031</v>
+        <v>93.31476593017578</v>
       </c>
       <c r="F166" t="n">
-        <v>93.32404491245036</v>
+        <v>93.32403728229781</v>
       </c>
       <c r="G166" t="n">
         <v>2818100</v>
@@ -4290,16 +4290,16 @@
         <v>45533</v>
       </c>
       <c r="C168" t="n">
-        <v>93.33330535888672</v>
+        <v>93.33331298828125</v>
       </c>
       <c r="D168" t="n">
-        <v>93.35184099051068</v>
+        <v>93.35184862142037</v>
       </c>
       <c r="E168" t="n">
-        <v>93.33330535888672</v>
+        <v>93.33331298828125</v>
       </c>
       <c r="F168" t="n">
-        <v>93.34256963871402</v>
+        <v>93.34257726886585</v>
       </c>
       <c r="G168" t="n">
         <v>4537700</v>
@@ -4359,16 +4359,16 @@
         <v>45539</v>
       </c>
       <c r="C171" t="n">
-        <v>93.429931640625</v>
+        <v>93.42995452880859</v>
       </c>
       <c r="D171" t="n">
-        <v>93.43924403642453</v>
+        <v>93.43926692688945</v>
       </c>
       <c r="E171" t="n">
-        <v>93.429931640625</v>
+        <v>93.42995452880859</v>
       </c>
       <c r="F171" t="n">
-        <v>93.43924403642453</v>
+        <v>93.43926692688945</v>
       </c>
       <c r="G171" t="n">
         <v>7218300</v>
@@ -4382,16 +4382,16 @@
         <v>45540</v>
       </c>
       <c r="C172" t="n">
-        <v>93.45785522460938</v>
+        <v>93.45787811279297</v>
       </c>
       <c r="D172" t="n">
-        <v>93.45785522460938</v>
+        <v>93.45787811279297</v>
       </c>
       <c r="E172" t="n">
-        <v>93.43923753758195</v>
+        <v>93.439260421206</v>
       </c>
       <c r="F172" t="n">
-        <v>93.44854993273378</v>
+        <v>93.44857281863847</v>
       </c>
       <c r="G172" t="n">
         <v>4833300</v>
@@ -4405,16 +4405,16 @@
         <v>45541</v>
       </c>
       <c r="C173" t="n">
-        <v>93.49509429931641</v>
+        <v>93.49510192871094</v>
       </c>
       <c r="D173" t="n">
-        <v>93.49509429931641</v>
+        <v>93.49510192871094</v>
       </c>
       <c r="E173" t="n">
-        <v>93.48578900777946</v>
+        <v>93.48579663641466</v>
       </c>
       <c r="F173" t="n">
-        <v>93.49509429931641</v>
+        <v>93.49510192871094</v>
       </c>
       <c r="G173" t="n">
         <v>5534600</v>
@@ -4428,16 +4428,16 @@
         <v>45544</v>
       </c>
       <c r="C174" t="n">
-        <v>93.50441741943359</v>
+        <v>93.50443267822266</v>
       </c>
       <c r="D174" t="n">
-        <v>93.51372981531469</v>
+        <v>93.51374507562342</v>
       </c>
       <c r="E174" t="n">
-        <v>93.50441741943359</v>
+        <v>93.50443267822266</v>
       </c>
       <c r="F174" t="n">
-        <v>93.50441741943359</v>
+        <v>93.50443267822266</v>
       </c>
       <c r="G174" t="n">
         <v>5397400</v>
@@ -4451,16 +4451,16 @@
         <v>45545</v>
       </c>
       <c r="C175" t="n">
-        <v>93.52302551269531</v>
+        <v>93.52301788330078</v>
       </c>
       <c r="D175" t="n">
-        <v>93.52302551269531</v>
+        <v>93.52301788330078</v>
       </c>
       <c r="E175" t="n">
-        <v>93.50440782612006</v>
+        <v>93.50440019824431</v>
       </c>
       <c r="F175" t="n">
-        <v>93.52302551269531</v>
+        <v>93.52301788330078</v>
       </c>
       <c r="G175" t="n">
         <v>4143900</v>
@@ -4474,16 +4474,16 @@
         <v>45546</v>
       </c>
       <c r="C176" t="n">
-        <v>93.52302551269531</v>
+        <v>93.52301788330078</v>
       </c>
       <c r="D176" t="n">
-        <v>93.53233790762097</v>
+        <v>93.53233027746676</v>
       </c>
       <c r="E176" t="n">
-        <v>93.52302551269531</v>
+        <v>93.52301788330078</v>
       </c>
       <c r="F176" t="n">
-        <v>93.52302551269531</v>
+        <v>93.52301788330078</v>
       </c>
       <c r="G176" t="n">
         <v>4500100</v>
@@ -4520,16 +4520,16 @@
         <v>45548</v>
       </c>
       <c r="C178" t="n">
-        <v>93.58821105957031</v>
+        <v>93.58819580078125</v>
       </c>
       <c r="D178" t="n">
-        <v>93.58821105957031</v>
+        <v>93.58819580078125</v>
       </c>
       <c r="E178" t="n">
-        <v>93.56959337041114</v>
+        <v>93.56957811465753</v>
       </c>
       <c r="F178" t="n">
-        <v>93.56959337041114</v>
+        <v>93.56957811465753</v>
       </c>
       <c r="G178" t="n">
         <v>3465200</v>
@@ -4543,16 +4543,16 @@
         <v>45551</v>
       </c>
       <c r="C179" t="n">
-        <v>93.60683441162109</v>
+        <v>93.60682678222656</v>
       </c>
       <c r="D179" t="n">
-        <v>93.60683441162109</v>
+        <v>93.60682678222656</v>
       </c>
       <c r="E179" t="n">
-        <v>93.58820961947146</v>
+        <v>93.58820199159494</v>
       </c>
       <c r="F179" t="n">
-        <v>93.58820961947146</v>
+        <v>93.58820199159494</v>
       </c>
       <c r="G179" t="n">
         <v>3571100</v>
@@ -4566,16 +4566,16 @@
         <v>45552</v>
       </c>
       <c r="C180" t="n">
-        <v>93.60683441162109</v>
+        <v>93.60682678222656</v>
       </c>
       <c r="D180" t="n">
-        <v>93.62545210049379</v>
+        <v>93.62544446958184</v>
       </c>
       <c r="E180" t="n">
-        <v>93.60683441162109</v>
+        <v>93.60682678222656</v>
       </c>
       <c r="F180" t="n">
-        <v>93.61614680769591</v>
+        <v>93.61613917754238</v>
       </c>
       <c r="G180" t="n">
         <v>4452200</v>
@@ -4589,16 +4589,16 @@
         <v>45553</v>
       </c>
       <c r="C181" t="n">
-        <v>93.63475799560547</v>
+        <v>93.634765625</v>
       </c>
       <c r="D181" t="n">
-        <v>93.64407039103374</v>
+        <v>93.64407802118704</v>
       </c>
       <c r="E181" t="n">
-        <v>93.6254456001772</v>
+        <v>93.62545322881296</v>
       </c>
       <c r="F181" t="n">
-        <v>93.6254456001772</v>
+        <v>93.62545322881296</v>
       </c>
       <c r="G181" t="n">
         <v>4077700</v>
@@ -4612,16 +4612,16 @@
         <v>45554</v>
       </c>
       <c r="C182" t="n">
-        <v>93.65336608886719</v>
+        <v>93.65337371826172</v>
       </c>
       <c r="D182" t="n">
-        <v>93.66267848334145</v>
+        <v>93.6626861134946</v>
       </c>
       <c r="E182" t="n">
-        <v>93.64406079766864</v>
+        <v>93.64406842630514</v>
       </c>
       <c r="F182" t="n">
-        <v>93.64406079766864</v>
+        <v>93.64406842630514</v>
       </c>
       <c r="G182" t="n">
         <v>5165800</v>
@@ -4635,16 +4635,16 @@
         <v>45555</v>
       </c>
       <c r="C183" t="n">
-        <v>93.69059753417969</v>
+        <v>93.69061279296875</v>
       </c>
       <c r="D183" t="n">
-        <v>93.69990992755768</v>
+        <v>93.6999251878634</v>
       </c>
       <c r="E183" t="n">
-        <v>93.69059753417969</v>
+        <v>93.69061279296875</v>
       </c>
       <c r="F183" t="n">
-        <v>93.69990992755768</v>
+        <v>93.6999251878634</v>
       </c>
       <c r="G183" t="n">
         <v>4244800</v>
@@ -4658,16 +4658,16 @@
         <v>45558</v>
       </c>
       <c r="C184" t="n">
-        <v>93.71855926513672</v>
+        <v>93.71855163574219</v>
       </c>
       <c r="D184" t="n">
-        <v>93.71855926513672</v>
+        <v>93.71855163574219</v>
       </c>
       <c r="E184" t="n">
-        <v>93.6999344735017</v>
+        <v>93.69992684562337</v>
       </c>
       <c r="F184" t="n">
-        <v>93.70924686931922</v>
+        <v>93.70923924068278</v>
       </c>
       <c r="G184" t="n">
         <v>5220900</v>
@@ -4681,16 +4681,16 @@
         <v>45559</v>
       </c>
       <c r="C185" t="n">
-        <v>93.72785186767578</v>
+        <v>93.72785949707031</v>
       </c>
       <c r="D185" t="n">
-        <v>93.72785186767578</v>
+        <v>93.72785949707031</v>
       </c>
       <c r="E185" t="n">
-        <v>93.71854657639489</v>
+        <v>93.71855420503198</v>
       </c>
       <c r="F185" t="n">
-        <v>93.71854657639489</v>
+        <v>93.71855420503198</v>
       </c>
       <c r="G185" t="n">
         <v>3923500</v>
@@ -4704,16 +4704,16 @@
         <v>45560</v>
       </c>
       <c r="C186" t="n">
-        <v>93.72785186767578</v>
+        <v>93.72785949707031</v>
       </c>
       <c r="D186" t="n">
-        <v>93.74647665678914</v>
+        <v>93.74648428769973</v>
       </c>
       <c r="E186" t="n">
-        <v>93.72785186767578</v>
+        <v>93.72785949707031</v>
       </c>
       <c r="F186" t="n">
-        <v>93.73716426223247</v>
+        <v>93.73717189238502</v>
       </c>
       <c r="G186" t="n">
         <v>3372400</v>
@@ -4727,16 +4727,16 @@
         <v>45561</v>
       </c>
       <c r="C187" t="n">
-        <v>93.73716735839844</v>
+        <v>93.73717498779297</v>
       </c>
       <c r="D187" t="n">
-        <v>93.74647975326272</v>
+        <v>93.74648738341519</v>
       </c>
       <c r="E187" t="n">
-        <v>93.73716735839844</v>
+        <v>93.73717498779297</v>
       </c>
       <c r="F187" t="n">
-        <v>93.73716735839844</v>
+        <v>93.73717498779297</v>
       </c>
       <c r="G187" t="n">
         <v>4364400</v>
@@ -4750,16 +4750,16 @@
         <v>45562</v>
       </c>
       <c r="C188" t="n">
-        <v>93.77442932128906</v>
+        <v>93.77440643310547</v>
       </c>
       <c r="D188" t="n">
-        <v>93.78374171808849</v>
+        <v>93.78371882763196</v>
       </c>
       <c r="E188" t="n">
-        <v>93.77442932128906</v>
+        <v>93.77440643310547</v>
       </c>
       <c r="F188" t="n">
-        <v>93.77442932128906</v>
+        <v>93.77440643310547</v>
       </c>
       <c r="G188" t="n">
         <v>4945400</v>
@@ -4773,16 +4773,16 @@
         <v>45565</v>
       </c>
       <c r="C189" t="n">
-        <v>93.77442932128906</v>
+        <v>93.77440643310547</v>
       </c>
       <c r="D189" t="n">
-        <v>93.79304701161043</v>
+        <v>93.79302411888267</v>
       </c>
       <c r="E189" t="n">
-        <v>93.77442932128906</v>
+        <v>93.77440643310547</v>
       </c>
       <c r="F189" t="n">
-        <v>93.78374171808849</v>
+        <v>93.78371882763196</v>
       </c>
       <c r="G189" t="n">
         <v>9253100</v>
@@ -4796,16 +4796,16 @@
         <v>45566</v>
       </c>
       <c r="C190" t="n">
-        <v>93.81183624267578</v>
+        <v>93.81181335449219</v>
       </c>
       <c r="D190" t="n">
-        <v>93.81183624267578</v>
+        <v>93.81181335449219</v>
       </c>
       <c r="E190" t="n">
-        <v>93.80248391785763</v>
+        <v>93.80246103195581</v>
       </c>
       <c r="F190" t="n">
-        <v>93.81183624267578</v>
+        <v>93.81181335449219</v>
       </c>
       <c r="G190" t="n">
         <v>11569200</v>
@@ -4819,16 +4819,16 @@
         <v>45567</v>
       </c>
       <c r="C191" t="n">
-        <v>93.81183624267578</v>
+        <v>93.81181335449219</v>
       </c>
       <c r="D191" t="n">
-        <v>93.82118143376027</v>
+        <v>93.82115854329665</v>
       </c>
       <c r="E191" t="n">
-        <v>93.81183624267578</v>
+        <v>93.81181335449219</v>
       </c>
       <c r="F191" t="n">
-        <v>93.82118143376027</v>
+        <v>93.82115854329665</v>
       </c>
       <c r="G191" t="n">
         <v>5170300</v>
@@ -4865,16 +4865,16 @@
         <v>45569</v>
       </c>
       <c r="C193" t="n">
-        <v>93.85855865478516</v>
+        <v>93.85858154296875</v>
       </c>
       <c r="D193" t="n">
-        <v>93.86791097711776</v>
+        <v>93.86793386758201</v>
       </c>
       <c r="E193" t="n">
-        <v>93.85855865478516</v>
+        <v>93.85858154296875</v>
       </c>
       <c r="F193" t="n">
-        <v>93.86323838281734</v>
+        <v>93.86326127214213</v>
       </c>
       <c r="G193" t="n">
         <v>4987100</v>
@@ -4888,16 +4888,16 @@
         <v>45572</v>
       </c>
       <c r="C194" t="n">
-        <v>93.86790466308594</v>
+        <v>93.86789703369141</v>
       </c>
       <c r="D194" t="n">
-        <v>93.87725698478947</v>
+        <v>93.8772493546348</v>
       </c>
       <c r="E194" t="n">
-        <v>93.86790466308594</v>
+        <v>93.86789703369141</v>
       </c>
       <c r="F194" t="n">
-        <v>93.86790466308594</v>
+        <v>93.86789703369141</v>
       </c>
       <c r="G194" t="n">
         <v>4792500</v>
@@ -4911,16 +4911,16 @@
         <v>45573</v>
       </c>
       <c r="C195" t="n">
-        <v>93.87726593017578</v>
+        <v>93.87728881835938</v>
       </c>
       <c r="D195" t="n">
-        <v>93.88661825277048</v>
+        <v>93.88664114323426</v>
       </c>
       <c r="E195" t="n">
-        <v>93.87726593017578</v>
+        <v>93.87728881835938</v>
       </c>
       <c r="F195" t="n">
-        <v>93.87726593017578</v>
+        <v>93.87728881835938</v>
       </c>
       <c r="G195" t="n">
         <v>3923100</v>
@@ -4934,16 +4934,16 @@
         <v>45574</v>
       </c>
       <c r="C196" t="n">
-        <v>93.89595794677734</v>
+        <v>93.89597320556641</v>
       </c>
       <c r="D196" t="n">
-        <v>93.90531026882472</v>
+        <v>93.90532552913362</v>
       </c>
       <c r="E196" t="n">
-        <v>93.8866127584615</v>
+        <v>93.8866280157319</v>
       </c>
       <c r="F196" t="n">
-        <v>93.89595794677734</v>
+        <v>93.89597320556641</v>
       </c>
       <c r="G196" t="n">
         <v>4024800</v>
@@ -4957,16 +4957,16 @@
         <v>45575</v>
       </c>
       <c r="C197" t="n">
-        <v>93.9146728515625</v>
+        <v>93.91468811035156</v>
       </c>
       <c r="D197" t="n">
-        <v>93.9146728515625</v>
+        <v>93.91468811035156</v>
       </c>
       <c r="E197" t="n">
-        <v>93.90532052849332</v>
+        <v>93.90533578576286</v>
       </c>
       <c r="F197" t="n">
-        <v>93.9146728515625</v>
+        <v>93.91468811035156</v>
       </c>
       <c r="G197" t="n">
         <v>3731100</v>
@@ -4980,16 +4980,16 @@
         <v>45576</v>
       </c>
       <c r="C198" t="n">
-        <v>93.95207977294922</v>
+        <v>93.95206451416016</v>
       </c>
       <c r="D198" t="n">
-        <v>93.96142496275984</v>
+        <v>93.96140970245301</v>
       </c>
       <c r="E198" t="n">
-        <v>93.95207977294922</v>
+        <v>93.95206451416016</v>
       </c>
       <c r="F198" t="n">
-        <v>93.95207977294922</v>
+        <v>93.95206451416016</v>
       </c>
       <c r="G198" t="n">
         <v>3778400</v>
@@ -5003,16 +5003,16 @@
         <v>45579</v>
       </c>
       <c r="C199" t="n">
-        <v>93.95207977294922</v>
+        <v>93.95206451416016</v>
       </c>
       <c r="D199" t="n">
-        <v>93.96142496275984</v>
+        <v>93.96140970245301</v>
       </c>
       <c r="E199" t="n">
-        <v>93.95207977294922</v>
+        <v>93.95206451416016</v>
       </c>
       <c r="F199" t="n">
-        <v>93.95207977294922</v>
+        <v>93.95206451416016</v>
       </c>
       <c r="G199" t="n">
         <v>3297100</v>
@@ -5026,16 +5026,16 @@
         <v>45580</v>
       </c>
       <c r="C200" t="n">
-        <v>93.97076416015625</v>
+        <v>93.97077178955078</v>
       </c>
       <c r="D200" t="n">
-        <v>93.97076416015625</v>
+        <v>93.97077178955078</v>
       </c>
       <c r="E200" t="n">
-        <v>93.96141183791931</v>
+        <v>93.96141946655455</v>
       </c>
       <c r="F200" t="n">
-        <v>93.97076416015625</v>
+        <v>93.97077178955078</v>
       </c>
       <c r="G200" t="n">
         <v>3567400</v>
@@ -5049,16 +5049,16 @@
         <v>45581</v>
       </c>
       <c r="C201" t="n">
-        <v>93.98946380615234</v>
+        <v>93.98945617675781</v>
       </c>
       <c r="D201" t="n">
-        <v>93.98946380615234</v>
+        <v>93.98945617675781</v>
       </c>
       <c r="E201" t="n">
-        <v>93.9801186174348</v>
+        <v>93.98011098879884</v>
       </c>
       <c r="F201" t="n">
-        <v>93.9801186174348</v>
+        <v>93.98011098879884</v>
       </c>
       <c r="G201" t="n">
         <v>3809900</v>
@@ -5072,16 +5072,16 @@
         <v>45582</v>
       </c>
       <c r="C202" t="n">
-        <v>93.98946380615234</v>
+        <v>93.98945617675781</v>
       </c>
       <c r="D202" t="n">
-        <v>93.99881612860175</v>
+        <v>93.99880849844806</v>
       </c>
       <c r="E202" t="n">
-        <v>93.98946380615234</v>
+        <v>93.98945617675781</v>
       </c>
       <c r="F202" t="n">
-        <v>93.98946380615234</v>
+        <v>93.98945617675781</v>
       </c>
       <c r="G202" t="n">
         <v>3575500</v>
@@ -5095,16 +5095,16 @@
         <v>45583</v>
       </c>
       <c r="C203" t="n">
-        <v>94.02686309814453</v>
+        <v>94.02687835693359</v>
       </c>
       <c r="D203" t="n">
-        <v>94.03621542030905</v>
+        <v>94.03623068061582</v>
       </c>
       <c r="E203" t="n">
-        <v>94.01751790971164</v>
+        <v>94.01753316698415</v>
       </c>
       <c r="F203" t="n">
-        <v>94.03621542030905</v>
+        <v>94.03623068061582</v>
       </c>
       <c r="G203" t="n">
         <v>3970200</v>
@@ -5118,16 +5118,16 @@
         <v>45586</v>
       </c>
       <c r="C204" t="n">
-        <v>94.04558563232422</v>
+        <v>94.04556274414062</v>
       </c>
       <c r="D204" t="n">
-        <v>94.04558563232422</v>
+        <v>94.04556274414062</v>
       </c>
       <c r="E204" t="n">
-        <v>94.03623330838064</v>
+        <v>94.03621042247316</v>
       </c>
       <c r="F204" t="n">
-        <v>94.03623330838064</v>
+        <v>94.03621042247316</v>
       </c>
       <c r="G204" t="n">
         <v>3940600</v>
@@ -5141,16 +5141,16 @@
         <v>45587</v>
       </c>
       <c r="C205" t="n">
-        <v>94.05490875244141</v>
+        <v>94.05492401123047</v>
       </c>
       <c r="D205" t="n">
-        <v>94.05490875244141</v>
+        <v>94.05492401123047</v>
       </c>
       <c r="E205" t="n">
-        <v>94.04556356442367</v>
+        <v>94.04557882169665</v>
       </c>
       <c r="F205" t="n">
-        <v>94.05490875244141</v>
+        <v>94.05492401123047</v>
       </c>
       <c r="G205" t="n">
         <v>3462800</v>
@@ -5164,16 +5164,16 @@
         <v>45588</v>
       </c>
       <c r="C206" t="n">
-        <v>94.05490875244141</v>
+        <v>94.05492401123047</v>
       </c>
       <c r="D206" t="n">
-        <v>94.07361339593947</v>
+        <v>94.07362865776304</v>
       </c>
       <c r="E206" t="n">
-        <v>94.05490875244141</v>
+        <v>94.05492401123047</v>
       </c>
       <c r="F206" t="n">
-        <v>94.07361339593947</v>
+        <v>94.07362865776304</v>
       </c>
       <c r="G206" t="n">
         <v>3927700</v>
@@ -5187,16 +5187,16 @@
         <v>45589</v>
       </c>
       <c r="C207" t="n">
-        <v>94.08298492431641</v>
+        <v>94.08297729492188</v>
       </c>
       <c r="D207" t="n">
-        <v>94.08298492431641</v>
+        <v>94.08297729492188</v>
       </c>
       <c r="E207" t="n">
-        <v>94.07363260065813</v>
+        <v>94.073624972022</v>
       </c>
       <c r="F207" t="n">
-        <v>94.08298492431641</v>
+        <v>94.08297729492188</v>
       </c>
       <c r="G207" t="n">
         <v>3704500</v>
@@ -5210,16 +5210,16 @@
         <v>45590</v>
       </c>
       <c r="C208" t="n">
-        <v>94.12039184570312</v>
+        <v>94.12037658691406</v>
       </c>
       <c r="D208" t="n">
-        <v>94.12039184570312</v>
+        <v>94.12037658691406</v>
       </c>
       <c r="E208" t="n">
-        <v>94.11103952157183</v>
+        <v>94.11102426429896</v>
       </c>
       <c r="F208" t="n">
-        <v>94.11103952157183</v>
+        <v>94.11102426429896</v>
       </c>
       <c r="G208" t="n">
         <v>5386900</v>
@@ -5233,16 +5233,16 @@
         <v>45593</v>
       </c>
       <c r="C209" t="n">
-        <v>94.12039184570312</v>
+        <v>94.12037658691406</v>
       </c>
       <c r="D209" t="n">
-        <v>94.12973703610129</v>
+        <v>94.12972177579719</v>
       </c>
       <c r="E209" t="n">
-        <v>94.12039184570312</v>
+        <v>94.12037658691406</v>
       </c>
       <c r="F209" t="n">
-        <v>94.12973703610129</v>
+        <v>94.12972177579719</v>
       </c>
       <c r="G209" t="n">
         <v>3471300</v>
@@ -5256,16 +5256,16 @@
         <v>45594</v>
       </c>
       <c r="C210" t="n">
-        <v>94.13907623291016</v>
+        <v>94.13908386230469</v>
       </c>
       <c r="D210" t="n">
-        <v>94.13907623291016</v>
+        <v>94.13908386230469</v>
       </c>
       <c r="E210" t="n">
-        <v>94.12505131553549</v>
+        <v>94.12505894379339</v>
       </c>
       <c r="F210" t="n">
-        <v>94.129723910083</v>
+        <v>94.12973153871958</v>
       </c>
       <c r="G210" t="n">
         <v>3449900</v>
@@ -5279,16 +5279,16 @@
         <v>45595</v>
       </c>
       <c r="C211" t="n">
-        <v>94.13907623291016</v>
+        <v>94.13908386230469</v>
       </c>
       <c r="D211" t="n">
-        <v>94.15777374483233</v>
+        <v>94.15778137574219</v>
       </c>
       <c r="E211" t="n">
-        <v>94.13907623291016</v>
+        <v>94.13908386230469</v>
       </c>
       <c r="F211" t="n">
-        <v>94.14842855573731</v>
+        <v>94.14843618588979</v>
       </c>
       <c r="G211" t="n">
         <v>7059200</v>
@@ -5325,16 +5325,16 @@
         <v>45597</v>
       </c>
       <c r="C213" t="n">
-        <v>94.20941925048828</v>
+        <v>94.20941162109375</v>
       </c>
       <c r="D213" t="n">
-        <v>94.20941925048828</v>
+        <v>94.20941162109375</v>
       </c>
       <c r="E213" t="n">
-        <v>94.20003538842856</v>
+        <v>94.20002775979395</v>
       </c>
       <c r="F213" t="n">
-        <v>94.20941925048828</v>
+        <v>94.20941162109375</v>
       </c>
       <c r="G213" t="n">
         <v>13451800</v>
@@ -5348,16 +5348,16 @@
         <v>45600</v>
       </c>
       <c r="C214" t="n">
-        <v>94.21879577636719</v>
+        <v>94.21878814697266</v>
       </c>
       <c r="D214" t="n">
-        <v>94.22724841417364</v>
+        <v>94.22724078409466</v>
       </c>
       <c r="E214" t="n">
-        <v>94.20940475249917</v>
+        <v>94.20939712386507</v>
       </c>
       <c r="F214" t="n">
-        <v>94.21879577636719</v>
+        <v>94.21878814697266</v>
       </c>
       <c r="G214" t="n">
         <v>5041500</v>
@@ -5417,16 +5417,16 @@
         <v>45603</v>
       </c>
       <c r="C217" t="n">
-        <v>94.25635528564453</v>
+        <v>94.25634002685547</v>
       </c>
       <c r="D217" t="n">
-        <v>94.25635528564453</v>
+        <v>94.25634002685547</v>
       </c>
       <c r="E217" t="n">
-        <v>94.24696426151975</v>
+        <v>94.24694900425096</v>
       </c>
       <c r="F217" t="n">
-        <v>94.24696426151975</v>
+        <v>94.24694900425096</v>
       </c>
       <c r="G217" t="n">
         <v>6188100</v>
@@ -5440,16 +5440,16 @@
         <v>45604</v>
       </c>
       <c r="C218" t="n">
-        <v>94.30332183837891</v>
+        <v>94.30331420898438</v>
       </c>
       <c r="D218" t="n">
-        <v>94.30332183837891</v>
+        <v>94.30331420898438</v>
       </c>
       <c r="E218" t="n">
-        <v>94.28453978642578</v>
+        <v>94.28453215855077</v>
       </c>
       <c r="F218" t="n">
-        <v>94.29393081240234</v>
+        <v>94.29392318376757</v>
       </c>
       <c r="G218" t="n">
         <v>5624200</v>
@@ -5486,16 +5486,16 @@
         <v>45608</v>
       </c>
       <c r="C220" t="n">
-        <v>94.30332183837891</v>
+        <v>94.30331420898438</v>
       </c>
       <c r="D220" t="n">
-        <v>94.31270570110148</v>
+        <v>94.31269807094777</v>
       </c>
       <c r="E220" t="n">
-        <v>94.30332183837891</v>
+        <v>94.30331420898438</v>
       </c>
       <c r="F220" t="n">
-        <v>94.31270570110148</v>
+        <v>94.31269807094777</v>
       </c>
       <c r="G220" t="n">
         <v>4283300</v>
@@ -5509,16 +5509,16 @@
         <v>45609</v>
       </c>
       <c r="C221" t="n">
-        <v>94.33148193359375</v>
+        <v>94.33147430419922</v>
       </c>
       <c r="D221" t="n">
-        <v>94.33148193359375</v>
+        <v>94.33147430419922</v>
       </c>
       <c r="E221" t="n">
-        <v>94.31269988279932</v>
+        <v>94.31269225492385</v>
       </c>
       <c r="F221" t="n">
-        <v>94.32209090819653</v>
+        <v>94.32208327956153</v>
       </c>
       <c r="G221" t="n">
         <v>4818000</v>
@@ -5532,16 +5532,16 @@
         <v>45610</v>
       </c>
       <c r="C222" t="n">
-        <v>94.33148193359375</v>
+        <v>94.33147430419922</v>
       </c>
       <c r="D222" t="n">
-        <v>94.34087295899096</v>
+        <v>94.3408653288369</v>
       </c>
       <c r="E222" t="n">
-        <v>94.33148193359375</v>
+        <v>94.33147430419922</v>
       </c>
       <c r="F222" t="n">
-        <v>94.34087295899096</v>
+        <v>94.3408653288369</v>
       </c>
       <c r="G222" t="n">
         <v>4353200</v>
@@ -5578,16 +5578,16 @@
         <v>45614</v>
       </c>
       <c r="C224" t="n">
-        <v>94.38780975341797</v>
+        <v>94.3878173828125</v>
       </c>
       <c r="D224" t="n">
-        <v>94.38780975341797</v>
+        <v>94.3878173828125</v>
       </c>
       <c r="E224" t="n">
-        <v>94.37841872841933</v>
+        <v>94.37842635705479</v>
       </c>
       <c r="F224" t="n">
-        <v>94.38780975341797</v>
+        <v>94.3878173828125</v>
       </c>
       <c r="G224" t="n">
         <v>5567500</v>
@@ -5601,16 +5601,16 @@
         <v>45615</v>
       </c>
       <c r="C225" t="n">
-        <v>94.39719390869141</v>
+        <v>94.39718627929688</v>
       </c>
       <c r="D225" t="n">
-        <v>94.39719390869141</v>
+        <v>94.39718627929688</v>
       </c>
       <c r="E225" t="n">
-        <v>94.3878028843762</v>
+        <v>94.38779525574067</v>
       </c>
       <c r="F225" t="n">
-        <v>94.39719390869141</v>
+        <v>94.39718627929688</v>
       </c>
       <c r="G225" t="n">
         <v>4310900</v>
@@ -5624,16 +5624,16 @@
         <v>45616</v>
       </c>
       <c r="C226" t="n">
-        <v>94.41596984863281</v>
+        <v>94.41596221923828</v>
       </c>
       <c r="D226" t="n">
-        <v>94.41596984863281</v>
+        <v>94.41596221923828</v>
       </c>
       <c r="E226" t="n">
-        <v>94.39719496304541</v>
+        <v>94.397187335168</v>
       </c>
       <c r="F226" t="n">
-        <v>94.4065859874655</v>
+        <v>94.40657835882925</v>
       </c>
       <c r="G226" t="n">
         <v>4133000</v>
@@ -5647,16 +5647,16 @@
         <v>45617</v>
       </c>
       <c r="C227" t="n">
-        <v>94.41596984863281</v>
+        <v>94.41596221923828</v>
       </c>
       <c r="D227" t="n">
-        <v>94.42536087305291</v>
+        <v>94.42535324289952</v>
       </c>
       <c r="E227" t="n">
-        <v>94.41596984863281</v>
+        <v>94.41596221923828</v>
       </c>
       <c r="F227" t="n">
-        <v>94.42536087305291</v>
+        <v>94.42535324289952</v>
       </c>
       <c r="G227" t="n">
         <v>4410700</v>
@@ -5693,16 +5693,16 @@
         <v>45621</v>
       </c>
       <c r="C229" t="n">
-        <v>94.45352172851562</v>
+        <v>94.45351409912109</v>
       </c>
       <c r="D229" t="n">
-        <v>94.46291275243318</v>
+        <v>94.46290512228009</v>
       </c>
       <c r="E229" t="n">
-        <v>94.45352172851562</v>
+        <v>94.45351409912109</v>
       </c>
       <c r="F229" t="n">
-        <v>94.45352172851562</v>
+        <v>94.45351409912109</v>
       </c>
       <c r="G229" t="n">
         <v>6020200</v>
@@ -5716,16 +5716,16 @@
         <v>45622</v>
       </c>
       <c r="C230" t="n">
-        <v>94.47232818603516</v>
+        <v>94.47230529785156</v>
       </c>
       <c r="D230" t="n">
-        <v>94.48171204912488</v>
+        <v>94.48168915866783</v>
       </c>
       <c r="E230" t="n">
-        <v>94.46293715969117</v>
+        <v>94.46291427378277</v>
       </c>
       <c r="F230" t="n">
-        <v>94.47232818603516</v>
+        <v>94.47230529785156</v>
       </c>
       <c r="G230" t="n">
         <v>4586900</v>
@@ -5739,16 +5739,16 @@
         <v>45623</v>
       </c>
       <c r="C231" t="n">
-        <v>94.49108123779297</v>
+        <v>94.49109649658203</v>
       </c>
       <c r="D231" t="n">
-        <v>94.50047226196662</v>
+        <v>94.50048752227218</v>
       </c>
       <c r="E231" t="n">
-        <v>94.49108123779297</v>
+        <v>94.49109649658203</v>
       </c>
       <c r="F231" t="n">
-        <v>94.49108123779297</v>
+        <v>94.49109649658203</v>
       </c>
       <c r="G231" t="n">
         <v>5909000</v>
@@ -5785,16 +5785,16 @@
         <v>45628</v>
       </c>
       <c r="C233" t="n">
-        <v>94.54560089111328</v>
+        <v>94.54561614990234</v>
       </c>
       <c r="D233" t="n">
-        <v>94.55502730641413</v>
+        <v>94.55504256672454</v>
       </c>
       <c r="E233" t="n">
-        <v>94.54560089111328</v>
+        <v>94.54561614990234</v>
       </c>
       <c r="F233" t="n">
-        <v>94.55031050363964</v>
+        <v>94.55032576318879</v>
       </c>
       <c r="G233" t="n">
         <v>11471800</v>
@@ -5808,16 +5808,16 @@
         <v>45629</v>
       </c>
       <c r="C234" t="n">
-        <v>94.55504608154297</v>
+        <v>94.55502319335938</v>
       </c>
       <c r="D234" t="n">
-        <v>94.564465308466</v>
+        <v>94.56444241800236</v>
       </c>
       <c r="E234" t="n">
-        <v>94.55504608154297</v>
+        <v>94.55502319335938</v>
       </c>
       <c r="F234" t="n">
-        <v>94.564465308466</v>
+        <v>94.56444241800236</v>
       </c>
       <c r="G234" t="n">
         <v>5734100</v>
@@ -5831,16 +5831,16 @@
         <v>45630</v>
       </c>
       <c r="C235" t="n">
-        <v>94.57388305664062</v>
+        <v>94.57386779785156</v>
       </c>
       <c r="D235" t="n">
-        <v>94.58330947294915</v>
+        <v>94.5832942126392</v>
       </c>
       <c r="E235" t="n">
-        <v>94.5644566403321</v>
+        <v>94.56444138306392</v>
       </c>
       <c r="F235" t="n">
-        <v>94.57388305664062</v>
+        <v>94.57386779785156</v>
       </c>
       <c r="G235" t="n">
         <v>5351100</v>
@@ -5854,16 +5854,16 @@
         <v>45631</v>
       </c>
       <c r="C236" t="n">
-        <v>94.58330535888672</v>
+        <v>94.58332061767578</v>
       </c>
       <c r="D236" t="n">
-        <v>94.59273177478522</v>
+        <v>94.59274703509502</v>
       </c>
       <c r="E236" t="n">
-        <v>94.58330535888672</v>
+        <v>94.58332061767578</v>
       </c>
       <c r="F236" t="n">
-        <v>94.58330535888672</v>
+        <v>94.58332061767578</v>
       </c>
       <c r="G236" t="n">
         <v>4870100</v>
@@ -5877,16 +5877,16 @@
         <v>45632</v>
       </c>
       <c r="C237" t="n">
-        <v>94.63043975830078</v>
+        <v>94.63042449951172</v>
       </c>
       <c r="D237" t="n">
-        <v>94.63043975830078</v>
+        <v>94.63042449951172</v>
       </c>
       <c r="E237" t="n">
-        <v>94.62101334145494</v>
+        <v>94.62099808418584</v>
       </c>
       <c r="F237" t="n">
-        <v>94.63043975830078</v>
+        <v>94.63042449951172</v>
       </c>
       <c r="G237" t="n">
         <v>4779000</v>
@@ -5923,16 +5923,16 @@
         <v>45636</v>
       </c>
       <c r="C239" t="n">
-        <v>94.65870666503906</v>
+        <v>94.65871429443359</v>
       </c>
       <c r="D239" t="n">
-        <v>94.65870666503906</v>
+        <v>94.65871429443359</v>
       </c>
       <c r="E239" t="n">
-        <v>94.64928024870643</v>
+        <v>94.64928787734119</v>
       </c>
       <c r="F239" t="n">
-        <v>94.64928024870643</v>
+        <v>94.64928787734119</v>
       </c>
       <c r="G239" t="n">
         <v>5293500</v>
@@ -5946,16 +5946,16 @@
         <v>45637</v>
       </c>
       <c r="C240" t="n">
-        <v>94.65870666503906</v>
+        <v>94.65871429443359</v>
       </c>
       <c r="D240" t="n">
-        <v>94.66812589112278</v>
+        <v>94.66813352127649</v>
       </c>
       <c r="E240" t="n">
-        <v>94.65870666503906</v>
+        <v>94.65871429443359</v>
       </c>
       <c r="F240" t="n">
-        <v>94.66812589112278</v>
+        <v>94.66813352127649</v>
       </c>
       <c r="G240" t="n">
         <v>4855300</v>
@@ -5969,16 +5969,16 @@
         <v>45638</v>
       </c>
       <c r="C241" t="n">
-        <v>94.66809844970703</v>
+        <v>94.66812133789062</v>
       </c>
       <c r="D241" t="n">
-        <v>94.67752486330724</v>
+        <v>94.67754775376989</v>
       </c>
       <c r="E241" t="n">
-        <v>94.66809844970703</v>
+        <v>94.66812133789062</v>
       </c>
       <c r="F241" t="n">
-        <v>94.67752486330724</v>
+        <v>94.67754775376989</v>
       </c>
       <c r="G241" t="n">
         <v>4701000</v>
@@ -5992,16 +5992,16 @@
         <v>45639</v>
       </c>
       <c r="C242" t="n">
-        <v>94.71525573730469</v>
+        <v>94.71524810791016</v>
       </c>
       <c r="D242" t="n">
-        <v>94.71525573730469</v>
+        <v>94.71524810791016</v>
       </c>
       <c r="E242" t="n">
-        <v>94.70582932047894</v>
+        <v>94.70582169184371</v>
       </c>
       <c r="F242" t="n">
-        <v>94.70582932047894</v>
+        <v>94.70582169184371</v>
       </c>
       <c r="G242" t="n">
         <v>4671500</v>
@@ -6015,16 +6015,16 @@
         <v>45642</v>
       </c>
       <c r="C243" t="n">
-        <v>94.72467041015625</v>
+        <v>94.72466278076172</v>
       </c>
       <c r="D243" t="n">
-        <v>94.72467041015625</v>
+        <v>94.72466278076172</v>
       </c>
       <c r="E243" t="n">
-        <v>94.71524399449918</v>
+        <v>94.71523636586389</v>
       </c>
       <c r="F243" t="n">
-        <v>94.72467041015625</v>
+        <v>94.72466278076172</v>
       </c>
       <c r="G243" t="n">
         <v>5598900</v>
@@ -6038,16 +6038,16 @@
         <v>45643</v>
       </c>
       <c r="C244" t="n">
-        <v>94.72467041015625</v>
+        <v>94.72466278076172</v>
       </c>
       <c r="D244" t="n">
-        <v>94.7340896355649</v>
+        <v>94.73408200541174</v>
       </c>
       <c r="E244" t="n">
-        <v>94.72467041015625</v>
+        <v>94.72466278076172</v>
       </c>
       <c r="F244" t="n">
-        <v>94.7340896355649</v>
+        <v>94.73408200541174</v>
       </c>
       <c r="G244" t="n">
         <v>5798500</v>
@@ -6061,16 +6061,16 @@
         <v>45644</v>
       </c>
       <c r="C245" t="n">
-        <v>94.74547576904297</v>
+        <v>94.74550628662109</v>
       </c>
       <c r="D245" t="n">
-        <v>94.74547576904297</v>
+        <v>94.74550628662109</v>
       </c>
       <c r="E245" t="n">
-        <v>94.7360143361235</v>
+        <v>94.7360448506541</v>
       </c>
       <c r="F245" t="n">
-        <v>94.74547576904297</v>
+        <v>94.74550628662109</v>
       </c>
       <c r="G245" t="n">
         <v>11526500</v>
@@ -6130,16 +6130,16 @@
         <v>45649</v>
       </c>
       <c r="C248" t="n">
-        <v>94.80223083496094</v>
+        <v>94.80225372314453</v>
       </c>
       <c r="D248" t="n">
-        <v>94.80223083496094</v>
+        <v>94.80225372314453</v>
       </c>
       <c r="E248" t="n">
-        <v>94.79276940195142</v>
+        <v>94.79279228785073</v>
       </c>
       <c r="F248" t="n">
-        <v>94.80223083496094</v>
+        <v>94.80225372314453</v>
       </c>
       <c r="G248" t="n">
         <v>7032500</v>
@@ -6176,16 +6176,16 @@
         <v>45652</v>
       </c>
       <c r="C250" t="n">
-        <v>94.84007263183594</v>
+        <v>94.84009552001953</v>
       </c>
       <c r="D250" t="n">
-        <v>94.84007263183594</v>
+        <v>94.84009552001953</v>
       </c>
       <c r="E250" t="n">
-        <v>94.83061119849903</v>
+        <v>94.83063408439924</v>
       </c>
       <c r="F250" t="n">
-        <v>94.84007263183594</v>
+        <v>94.84009552001953</v>
       </c>
       <c r="G250" t="n">
         <v>4974100</v>
@@ -6199,16 +6199,16 @@
         <v>45653</v>
       </c>
       <c r="C251" t="n">
-        <v>94.86846160888672</v>
+        <v>94.86844635009766</v>
       </c>
       <c r="D251" t="n">
-        <v>94.86846160888672</v>
+        <v>94.86844635009766</v>
       </c>
       <c r="E251" t="n">
-        <v>94.85900017436359</v>
+        <v>94.85898491709632</v>
       </c>
       <c r="F251" t="n">
-        <v>94.85900017436359</v>
+        <v>94.85898491709632</v>
       </c>
       <c r="G251" t="n">
         <v>6558000</v>
@@ -6222,16 +6222,16 @@
         <v>45656</v>
       </c>
       <c r="C252" t="n">
-        <v>94.86846160888672</v>
+        <v>94.86844635009766</v>
       </c>
       <c r="D252" t="n">
-        <v>94.87792304340985</v>
+        <v>94.87790778309899</v>
       </c>
       <c r="E252" t="n">
-        <v>94.86846160888672</v>
+        <v>94.86844635009766</v>
       </c>
       <c r="F252" t="n">
-        <v>94.87792304340985</v>
+        <v>94.87790778309899</v>
       </c>
       <c r="G252" t="n">
         <v>6547600</v>
@@ -6245,16 +6245,16 @@
         <v>45657</v>
       </c>
       <c r="C253" t="n">
-        <v>94.89682769775391</v>
+        <v>94.89684295654297</v>
       </c>
       <c r="D253" t="n">
-        <v>94.91574334764803</v>
+        <v>94.9157586094786</v>
       </c>
       <c r="E253" t="n">
-        <v>94.89682769775391</v>
+        <v>94.89684295654297</v>
       </c>
       <c r="F253" t="n">
-        <v>94.90628913118054</v>
+        <v>94.90630439149093</v>
       </c>
       <c r="G253" t="n">
         <v>7371300</v>
@@ -6268,16 +6268,16 @@
         <v>45659</v>
       </c>
       <c r="C254" t="n">
-        <v>94.91576385498047</v>
+        <v>94.91575622558594</v>
       </c>
       <c r="D254" t="n">
-        <v>94.91576385498047</v>
+        <v>94.91575622558594</v>
       </c>
       <c r="E254" t="n">
-        <v>94.90630963647031</v>
+        <v>94.90630200783571</v>
       </c>
       <c r="F254" t="n">
-        <v>94.91576385498047</v>
+        <v>94.91575622558594</v>
       </c>
       <c r="G254" t="n">
         <v>7533100</v>
@@ -6291,16 +6291,16 @@
         <v>45660</v>
       </c>
       <c r="C255" t="n">
-        <v>94.94415283203125</v>
+        <v>94.94412994384766</v>
       </c>
       <c r="D255" t="n">
-        <v>94.9536070510065</v>
+        <v>94.95358416054377</v>
       </c>
       <c r="E255" t="n">
-        <v>94.94415283203125</v>
+        <v>94.94412994384766</v>
       </c>
       <c r="F255" t="n">
-        <v>94.9536070510065</v>
+        <v>94.95358416054377</v>
       </c>
       <c r="G255" t="n">
         <v>6730100</v>
@@ -6314,16 +6314,16 @@
         <v>45663</v>
       </c>
       <c r="C256" t="n">
-        <v>94.94415283203125</v>
+        <v>94.94412994384766</v>
       </c>
       <c r="D256" t="n">
-        <v>94.96306848694279</v>
+        <v>94.9630455941992</v>
       </c>
       <c r="E256" t="n">
-        <v>94.94415283203125</v>
+        <v>94.94412994384766</v>
       </c>
       <c r="F256" t="n">
-        <v>94.9536070510065</v>
+        <v>94.95358416054377</v>
       </c>
       <c r="G256" t="n">
         <v>6938300</v>
@@ -6337,16 +6337,16 @@
         <v>45664</v>
       </c>
       <c r="C257" t="n">
-        <v>94.96304321289062</v>
+        <v>94.96303558349609</v>
       </c>
       <c r="D257" t="n">
-        <v>94.97250464630879</v>
+        <v>94.97249701615412</v>
       </c>
       <c r="E257" t="n">
-        <v>94.96304321289062</v>
+        <v>94.96303558349609</v>
       </c>
       <c r="F257" t="n">
-        <v>94.97250464630879</v>
+        <v>94.97249701615412</v>
       </c>
       <c r="G257" t="n">
         <v>6792100</v>
@@ -6360,16 +6360,16 @@
         <v>45665</v>
       </c>
       <c r="C258" t="n">
-        <v>94.98197937011719</v>
+        <v>94.98197174072266</v>
       </c>
       <c r="D258" t="n">
-        <v>94.98197937011719</v>
+        <v>94.98197174072266</v>
       </c>
       <c r="E258" t="n">
-        <v>94.97251793537512</v>
+        <v>94.97251030674057</v>
       </c>
       <c r="F258" t="n">
-        <v>94.97251793537512</v>
+        <v>94.97251030674057</v>
       </c>
       <c r="G258" t="n">
         <v>6101100</v>
@@ -6383,16 +6383,16 @@
         <v>45667</v>
       </c>
       <c r="C259" t="n">
-        <v>95.01979064941406</v>
+        <v>95.01980590820312</v>
       </c>
       <c r="D259" t="n">
-        <v>95.0292520821621</v>
+        <v>95.02926734247052</v>
       </c>
       <c r="E259" t="n">
-        <v>95.01033643362464</v>
+        <v>95.0103516908955</v>
       </c>
       <c r="F259" t="n">
-        <v>95.01979064941406</v>
+        <v>95.01980590820312</v>
       </c>
       <c r="G259" t="n">
         <v>7644600</v>
@@ -6452,16 +6452,16 @@
         <v>45672</v>
       </c>
       <c r="C262" t="n">
-        <v>95.05763244628906</v>
+        <v>95.05767059326172</v>
       </c>
       <c r="D262" t="n">
-        <v>95.05763244628906</v>
+        <v>95.05767059326172</v>
       </c>
       <c r="E262" t="n">
-        <v>95.04817823017314</v>
+        <v>95.04821637335179</v>
       </c>
       <c r="F262" t="n">
-        <v>95.05763244628906</v>
+        <v>95.05767059326172</v>
       </c>
       <c r="G262" t="n">
         <v>6878600</v>
@@ -6475,16 +6475,16 @@
         <v>45673</v>
       </c>
       <c r="C263" t="n">
-        <v>95.05763244628906</v>
+        <v>95.05767059326172</v>
       </c>
       <c r="D263" t="n">
-        <v>95.07655531243863</v>
+        <v>95.07659346700511</v>
       </c>
       <c r="E263" t="n">
-        <v>95.05763244628906</v>
+        <v>95.05767059326172</v>
       </c>
       <c r="F263" t="n">
-        <v>95.06709387936384</v>
+        <v>95.06713203013342</v>
       </c>
       <c r="G263" t="n">
         <v>5352500</v>
@@ -6498,16 +6498,16 @@
         <v>45674</v>
       </c>
       <c r="C264" t="n">
-        <v>95.10494232177734</v>
+        <v>95.10493469238281</v>
       </c>
       <c r="D264" t="n">
-        <v>95.11440375583972</v>
+        <v>95.11439612568618</v>
       </c>
       <c r="E264" t="n">
-        <v>95.09548088771497</v>
+        <v>95.09547325907944</v>
       </c>
       <c r="F264" t="n">
-        <v>95.10494232177734</v>
+        <v>95.10493469238281</v>
       </c>
       <c r="G264" t="n">
         <v>6563000</v>
@@ -6521,16 +6521,16 @@
         <v>45678</v>
       </c>
       <c r="C265" t="n">
-        <v>95.11438751220703</v>
+        <v>95.11440277099609</v>
       </c>
       <c r="D265" t="n">
-        <v>95.12384172769519</v>
+        <v>95.12385698800095</v>
       </c>
       <c r="E265" t="n">
-        <v>95.11438751220703</v>
+        <v>95.11440277099609</v>
       </c>
       <c r="F265" t="n">
-        <v>95.11911461995111</v>
+        <v>95.11912987949853</v>
       </c>
       <c r="G265" t="n">
         <v>7952400</v>
@@ -6544,16 +6544,16 @@
         <v>45679</v>
       </c>
       <c r="C266" t="n">
-        <v>95.13332366943359</v>
+        <v>95.13333892822266</v>
       </c>
       <c r="D266" t="n">
-        <v>95.13332366943359</v>
+        <v>95.13333892822266</v>
       </c>
       <c r="E266" t="n">
-        <v>95.12386223494731</v>
+        <v>95.12387749221881</v>
       </c>
       <c r="F266" t="n">
-        <v>95.12386223494731</v>
+        <v>95.12387749221881</v>
       </c>
       <c r="G266" t="n">
         <v>5717600</v>
@@ -6590,16 +6590,16 @@
         <v>45681</v>
       </c>
       <c r="C268" t="n">
-        <v>95.17115020751953</v>
+        <v>95.17116546630859</v>
       </c>
       <c r="D268" t="n">
-        <v>95.18061164081455</v>
+        <v>95.18062690112056</v>
       </c>
       <c r="E268" t="n">
-        <v>95.17115020751953</v>
+        <v>95.17116546630859</v>
       </c>
       <c r="F268" t="n">
-        <v>95.17115020751953</v>
+        <v>95.17116546630859</v>
       </c>
       <c r="G268" t="n">
         <v>6380000</v>
@@ -6613,16 +6613,16 @@
         <v>45684</v>
       </c>
       <c r="C269" t="n">
-        <v>95.17115020751953</v>
+        <v>95.17116546630859</v>
       </c>
       <c r="D269" t="n">
-        <v>95.19006585715051</v>
+        <v>95.19008111897233</v>
       </c>
       <c r="E269" t="n">
-        <v>95.17115020751953</v>
+        <v>95.17116546630859</v>
       </c>
       <c r="F269" t="n">
-        <v>95.18061164081455</v>
+        <v>95.18062690112056</v>
       </c>
       <c r="G269" t="n">
         <v>9439800</v>
@@ -6682,16 +6682,16 @@
         <v>45687</v>
       </c>
       <c r="C272" t="n">
-        <v>95.21846771240234</v>
+        <v>95.21846008300781</v>
       </c>
       <c r="D272" t="n">
-        <v>95.22792193048139</v>
+        <v>95.22791430032933</v>
       </c>
       <c r="E272" t="n">
-        <v>95.20900627736293</v>
+        <v>95.20899864872649</v>
       </c>
       <c r="F272" t="n">
-        <v>95.20900627736293</v>
+        <v>95.20899864872649</v>
       </c>
       <c r="G272" t="n">
         <v>8043500</v>
@@ -6705,16 +6705,16 @@
         <v>45688</v>
       </c>
       <c r="C273" t="n">
-        <v>95.23738098144531</v>
+        <v>95.23736572265625</v>
       </c>
       <c r="D273" t="n">
-        <v>95.24684241624787</v>
+        <v>95.24682715594292</v>
       </c>
       <c r="E273" t="n">
-        <v>95.23738098144531</v>
+        <v>95.23736572265625</v>
       </c>
       <c r="F273" t="n">
-        <v>95.24684241624787</v>
+        <v>95.24682715594292</v>
       </c>
       <c r="G273" t="n">
         <v>12373000</v>
@@ -6751,16 +6751,16 @@
         <v>45692</v>
       </c>
       <c r="C275" t="n">
-        <v>95.2781982421875</v>
+        <v>95.27820587158203</v>
       </c>
       <c r="D275" t="n">
-        <v>95.2781982421875</v>
+        <v>95.27820587158203</v>
       </c>
       <c r="E275" t="n">
-        <v>95.2687025714739</v>
+        <v>95.26871020010807</v>
       </c>
       <c r="F275" t="n">
-        <v>95.2781982421875</v>
+        <v>95.27820587158203</v>
       </c>
       <c r="G275" t="n">
         <v>7866600</v>
@@ -6774,16 +6774,16 @@
         <v>45693</v>
       </c>
       <c r="C276" t="n">
-        <v>95.2781982421875</v>
+        <v>95.27820587158203</v>
       </c>
       <c r="D276" t="n">
-        <v>95.28769391290109</v>
+        <v>95.28770154305599</v>
       </c>
       <c r="E276" t="n">
-        <v>95.2781982421875</v>
+        <v>95.27820587158203</v>
       </c>
       <c r="F276" t="n">
-        <v>95.28769391290109</v>
+        <v>95.28770154305599</v>
       </c>
       <c r="G276" t="n">
         <v>7100900</v>
@@ -6797,16 +6797,16 @@
         <v>45694</v>
       </c>
       <c r="C277" t="n">
-        <v>95.29718780517578</v>
+        <v>95.29716491699219</v>
       </c>
       <c r="D277" t="n">
-        <v>95.29718780517578</v>
+        <v>95.29716491699219</v>
       </c>
       <c r="E277" t="n">
-        <v>95.28769937699263</v>
+        <v>95.28767649108794</v>
       </c>
       <c r="F277" t="n">
-        <v>95.29718780517578</v>
+        <v>95.29716491699219</v>
       </c>
       <c r="G277" t="n">
         <v>5804300</v>
@@ -6843,16 +6843,16 @@
         <v>45698</v>
       </c>
       <c r="C279" t="n">
-        <v>95.34463500976562</v>
+        <v>95.34466552734375</v>
       </c>
       <c r="D279" t="n">
-        <v>95.34463500976562</v>
+        <v>95.34466552734375</v>
       </c>
       <c r="E279" t="n">
-        <v>95.33513934088865</v>
+        <v>95.33516985542744</v>
       </c>
       <c r="F279" t="n">
-        <v>95.34463500976562</v>
+        <v>95.34466552734375</v>
       </c>
       <c r="G279" t="n">
         <v>7517800</v>
@@ -6866,16 +6866,16 @@
         <v>45699</v>
       </c>
       <c r="C280" t="n">
-        <v>95.34463500976562</v>
+        <v>95.34466552734375</v>
       </c>
       <c r="D280" t="n">
-        <v>95.35413067864259</v>
+        <v>95.35416119926006</v>
       </c>
       <c r="E280" t="n">
-        <v>95.34463500976562</v>
+        <v>95.34466552734375</v>
       </c>
       <c r="F280" t="n">
-        <v>95.35413067864259</v>
+        <v>95.35416119926006</v>
       </c>
       <c r="G280" t="n">
         <v>6424100</v>
@@ -6889,16 +6889,16 @@
         <v>45700</v>
       </c>
       <c r="C281" t="n">
-        <v>95.35414123535156</v>
+        <v>95.35415649414062</v>
       </c>
       <c r="D281" t="n">
-        <v>95.36362966220587</v>
+        <v>95.36364492251329</v>
       </c>
       <c r="E281" t="n">
-        <v>95.35414123535156</v>
+        <v>95.35415649414062</v>
       </c>
       <c r="F281" t="n">
-        <v>95.35414123535156</v>
+        <v>95.35415649414062</v>
       </c>
       <c r="G281" t="n">
         <v>6618800</v>
@@ -6912,16 +6912,16 @@
         <v>45701</v>
       </c>
       <c r="C282" t="n">
-        <v>95.37313842773438</v>
+        <v>95.37313079833984</v>
       </c>
       <c r="D282" t="n">
-        <v>95.37313842773438</v>
+        <v>95.37313079833984</v>
       </c>
       <c r="E282" t="n">
-        <v>95.3636427565023</v>
+        <v>95.36363512786737</v>
       </c>
       <c r="F282" t="n">
-        <v>95.37313842773438</v>
+        <v>95.37313079833984</v>
       </c>
       <c r="G282" t="n">
         <v>5690100</v>
@@ -6958,16 +6958,16 @@
         <v>45706</v>
       </c>
       <c r="C284" t="n">
-        <v>95.43009948730469</v>
+        <v>95.43009185791016</v>
       </c>
       <c r="D284" t="n">
-        <v>95.43009948730469</v>
+        <v>95.43009185791016</v>
       </c>
       <c r="E284" t="n">
-        <v>95.42061105899657</v>
+        <v>95.42060343036061</v>
       </c>
       <c r="F284" t="n">
-        <v>95.43009948730469</v>
+        <v>95.43009185791016</v>
       </c>
       <c r="G284" t="n">
         <v>15815200</v>
@@ -6981,16 +6981,16 @@
         <v>45707</v>
       </c>
       <c r="C285" t="n">
-        <v>95.43009948730469</v>
+        <v>95.43009185791016</v>
       </c>
       <c r="D285" t="n">
-        <v>95.43959515868785</v>
+        <v>95.43958752853416</v>
       </c>
       <c r="E285" t="n">
-        <v>95.43009948730469</v>
+        <v>95.43009185791016</v>
       </c>
       <c r="F285" t="n">
-        <v>95.43959515868785</v>
+        <v>95.43958752853416</v>
       </c>
       <c r="G285" t="n">
         <v>7277600</v>
@@ -7004,16 +7004,16 @@
         <v>45708</v>
       </c>
       <c r="C286" t="n">
-        <v>95.44908142089844</v>
+        <v>95.44907379150391</v>
       </c>
       <c r="D286" t="n">
-        <v>95.44908142089844</v>
+        <v>95.44907379150391</v>
       </c>
       <c r="E286" t="n">
-        <v>95.43958575045134</v>
+        <v>95.43957812181581</v>
       </c>
       <c r="F286" t="n">
-        <v>95.44908142089844</v>
+        <v>95.44907379150391</v>
       </c>
       <c r="G286" t="n">
         <v>7608000</v>
@@ -7027,16 +7027,16 @@
         <v>45709</v>
       </c>
       <c r="C287" t="n">
-        <v>95.48706817626953</v>
+        <v>95.48705291748047</v>
       </c>
       <c r="D287" t="n">
-        <v>95.48706817626953</v>
+        <v>95.48705291748047</v>
       </c>
       <c r="E287" t="n">
-        <v>95.47757250469705</v>
+        <v>95.47755724742539</v>
       </c>
       <c r="F287" t="n">
-        <v>95.47757250469705</v>
+        <v>95.47755724742539</v>
       </c>
       <c r="G287" t="n">
         <v>9111000</v>
@@ -7050,16 +7050,16 @@
         <v>45712</v>
       </c>
       <c r="C288" t="n">
-        <v>95.49655914306641</v>
+        <v>95.49655151367188</v>
       </c>
       <c r="D288" t="n">
-        <v>95.49655914306641</v>
+        <v>95.49655151367188</v>
       </c>
       <c r="E288" t="n">
-        <v>95.48707071431691</v>
+        <v>95.48706308568042</v>
       </c>
       <c r="F288" t="n">
-        <v>95.49655914306641</v>
+        <v>95.49655151367188</v>
       </c>
       <c r="G288" t="n">
         <v>9734600</v>
@@ -7073,16 +7073,16 @@
         <v>45713</v>
       </c>
       <c r="C289" t="n">
-        <v>95.50604248046875</v>
+        <v>95.50602722167969</v>
       </c>
       <c r="D289" t="n">
-        <v>95.50604248046875</v>
+        <v>95.50602722167969</v>
       </c>
       <c r="E289" t="n">
-        <v>95.49654680987022</v>
+        <v>95.49653155259826</v>
       </c>
       <c r="F289" t="n">
-        <v>95.49654680987022</v>
+        <v>95.49653155259826</v>
       </c>
       <c r="G289" t="n">
         <v>10827700</v>
@@ -7096,16 +7096,16 @@
         <v>45714</v>
       </c>
       <c r="C290" t="n">
-        <v>95.50604248046875</v>
+        <v>95.50602722167969</v>
       </c>
       <c r="D290" t="n">
-        <v>95.51553815106729</v>
+        <v>95.5155228907611</v>
       </c>
       <c r="E290" t="n">
-        <v>95.50604248046875</v>
+        <v>95.50602722167969</v>
       </c>
       <c r="F290" t="n">
-        <v>95.50604248046875</v>
+        <v>95.50602722167969</v>
       </c>
       <c r="G290" t="n">
         <v>9536300</v>
@@ -7119,16 +7119,16 @@
         <v>45715</v>
       </c>
       <c r="C291" t="n">
-        <v>95.53451538085938</v>
+        <v>95.53452301025391</v>
       </c>
       <c r="D291" t="n">
-        <v>95.53451538085938</v>
+        <v>95.53452301025391</v>
       </c>
       <c r="E291" t="n">
-        <v>95.52502695401745</v>
+        <v>95.52503458265423</v>
       </c>
       <c r="F291" t="n">
-        <v>95.53451538085938</v>
+        <v>95.53452301025391</v>
       </c>
       <c r="G291" t="n">
         <v>10807800</v>
@@ -7142,16 +7142,16 @@
         <v>45716</v>
       </c>
       <c r="C292" t="n">
-        <v>95.55352020263672</v>
+        <v>95.55351257324219</v>
       </c>
       <c r="D292" t="n">
-        <v>95.56301587389234</v>
+        <v>95.56300824373963</v>
       </c>
       <c r="E292" t="n">
-        <v>95.55352020263672</v>
+        <v>95.55351257324219</v>
       </c>
       <c r="F292" t="n">
-        <v>95.55352020263672</v>
+        <v>95.55351257324219</v>
       </c>
       <c r="G292" t="n">
         <v>13772600</v>
@@ -7165,16 +7165,16 @@
         <v>45719</v>
       </c>
       <c r="C293" t="n">
-        <v>95.57541656494141</v>
+        <v>95.57542419433594</v>
       </c>
       <c r="D293" t="n">
-        <v>95.57541656494141</v>
+        <v>95.57542419433594</v>
       </c>
       <c r="E293" t="n">
-        <v>95.56589127268401</v>
+        <v>95.56589890131818</v>
       </c>
       <c r="F293" t="n">
-        <v>95.57541656494141</v>
+        <v>95.57542419433594</v>
       </c>
       <c r="G293" t="n">
         <v>17436600</v>
@@ -7188,16 +7188,16 @@
         <v>45720</v>
       </c>
       <c r="C294" t="n">
-        <v>95.58493804931641</v>
+        <v>95.58494567871094</v>
       </c>
       <c r="D294" t="n">
-        <v>95.58493804931641</v>
+        <v>95.58494567871094</v>
       </c>
       <c r="E294" t="n">
-        <v>95.57541275743847</v>
+        <v>95.57542038607271</v>
       </c>
       <c r="F294" t="n">
-        <v>95.58493804931641</v>
+        <v>95.58494567871094</v>
       </c>
       <c r="G294" t="n">
         <v>11543100</v>
@@ -7211,16 +7211,16 @@
         <v>45721</v>
       </c>
       <c r="C295" t="n">
-        <v>95.58493804931641</v>
+        <v>95.58494567871094</v>
       </c>
       <c r="D295" t="n">
-        <v>95.59445607552547</v>
+        <v>95.59446370567971</v>
       </c>
       <c r="E295" t="n">
-        <v>95.58493804931641</v>
+        <v>95.58494567871094</v>
       </c>
       <c r="F295" t="n">
-        <v>95.58493804931641</v>
+        <v>95.58494567871094</v>
       </c>
       <c r="G295" t="n">
         <v>7162600</v>
@@ -7234,16 +7234,16 @@
         <v>45722</v>
       </c>
       <c r="C296" t="n">
-        <v>95.61350250244141</v>
+        <v>95.613525390625</v>
       </c>
       <c r="D296" t="n">
-        <v>95.61350250244141</v>
+        <v>95.613525390625</v>
       </c>
       <c r="E296" t="n">
-        <v>95.59445191951377</v>
+        <v>95.59447480313699</v>
       </c>
       <c r="F296" t="n">
-        <v>95.60397721097759</v>
+        <v>95.60400009688099</v>
       </c>
       <c r="G296" t="n">
         <v>9925500</v>
@@ -7257,16 +7257,16 @@
         <v>45723</v>
       </c>
       <c r="C297" t="n">
-        <v>95.64207458496094</v>
+        <v>95.64209747314453</v>
       </c>
       <c r="D297" t="n">
-        <v>95.64207458496094</v>
+        <v>95.64209747314453</v>
       </c>
       <c r="E297" t="n">
-        <v>95.63254929315114</v>
+        <v>95.63257217905524</v>
       </c>
       <c r="F297" t="n">
-        <v>95.64207458496094</v>
+        <v>95.64209747314453</v>
       </c>
       <c r="G297" t="n">
         <v>8962400</v>
@@ -7280,16 +7280,16 @@
         <v>45726</v>
       </c>
       <c r="C298" t="n">
-        <v>95.64207458496094</v>
+        <v>95.64209747314453</v>
       </c>
       <c r="D298" t="n">
-        <v>95.65159987677072</v>
+        <v>95.65162276723382</v>
       </c>
       <c r="E298" t="n">
-        <v>95.64207458496094</v>
+        <v>95.64209747314453</v>
       </c>
       <c r="F298" t="n">
-        <v>95.65159987677072</v>
+        <v>95.65162276723382</v>
       </c>
       <c r="G298" t="n">
         <v>14768100</v>
@@ -7303,16 +7303,16 @@
         <v>45727</v>
       </c>
       <c r="C299" t="n">
-        <v>95.66111755371094</v>
+        <v>95.66112518310547</v>
       </c>
       <c r="D299" t="n">
-        <v>95.66111755371094</v>
+        <v>95.66112518310547</v>
       </c>
       <c r="E299" t="n">
-        <v>95.65159952760472</v>
+        <v>95.65160715624013</v>
       </c>
       <c r="F299" t="n">
-        <v>95.65159952760472</v>
+        <v>95.65160715624013</v>
       </c>
       <c r="G299" t="n">
         <v>11456900</v>
@@ -7326,16 +7326,16 @@
         <v>45728</v>
       </c>
       <c r="C300" t="n">
-        <v>95.66111755371094</v>
+        <v>95.66112518310547</v>
       </c>
       <c r="D300" t="n">
-        <v>95.67064284548596</v>
+        <v>95.67065047564017</v>
       </c>
       <c r="E300" t="n">
-        <v>95.66111755371094</v>
+        <v>95.66112518310547</v>
       </c>
       <c r="F300" t="n">
-        <v>95.67064284548596</v>
+        <v>95.67065047564017</v>
       </c>
       <c r="G300" t="n">
         <v>11307300</v>
@@ -7372,16 +7372,16 @@
         <v>45730</v>
       </c>
       <c r="C302" t="n">
-        <v>95.71826934814453</v>
+        <v>95.71825408935547</v>
       </c>
       <c r="D302" t="n">
-        <v>95.71826934814453</v>
+        <v>95.71825408935547</v>
       </c>
       <c r="E302" t="n">
-        <v>95.70874405564213</v>
+        <v>95.70872879837152</v>
       </c>
       <c r="F302" t="n">
-        <v>95.71826934814453</v>
+        <v>95.71825408935547</v>
       </c>
       <c r="G302" t="n">
         <v>11421900</v>
@@ -7395,16 +7395,16 @@
         <v>45733</v>
       </c>
       <c r="C303" t="n">
-        <v>95.72779846191406</v>
+        <v>95.72779083251953</v>
       </c>
       <c r="D303" t="n">
-        <v>95.72779846191406</v>
+        <v>95.72779083251953</v>
       </c>
       <c r="E303" t="n">
-        <v>95.71828043397865</v>
+        <v>95.71827280534269</v>
       </c>
       <c r="F303" t="n">
-        <v>95.72779846191406</v>
+        <v>95.72779083251953</v>
       </c>
       <c r="G303" t="n">
         <v>9018300</v>
@@ -7441,16 +7441,16 @@
         <v>45735</v>
       </c>
       <c r="C305" t="n">
-        <v>95.75635528564453</v>
+        <v>95.75636291503906</v>
       </c>
       <c r="D305" t="n">
-        <v>95.75635528564453</v>
+        <v>95.75636291503906</v>
       </c>
       <c r="E305" t="n">
-        <v>95.74682999393463</v>
+        <v>95.74683762257023</v>
       </c>
       <c r="F305" t="n">
-        <v>95.74682999393463</v>
+        <v>95.74683762257023</v>
       </c>
       <c r="G305" t="n">
         <v>13584800</v>
@@ -7464,16 +7464,16 @@
         <v>45736</v>
       </c>
       <c r="C306" t="n">
-        <v>95.75635528564453</v>
+        <v>95.75636291503906</v>
       </c>
       <c r="D306" t="n">
-        <v>95.76587331168571</v>
+        <v>95.76588094183857</v>
       </c>
       <c r="E306" t="n">
-        <v>95.75635528564453</v>
+        <v>95.75636291503906</v>
       </c>
       <c r="F306" t="n">
-        <v>95.76587331168571</v>
+        <v>95.76588094183857</v>
       </c>
       <c r="G306" t="n">
         <v>12648500</v>
@@ -7510,16 +7510,16 @@
         <v>45740</v>
       </c>
       <c r="C308" t="n">
-        <v>95.80396270751953</v>
+        <v>95.80397033691406</v>
       </c>
       <c r="D308" t="n">
-        <v>95.8134879987815</v>
+        <v>95.81349562893458</v>
       </c>
       <c r="E308" t="n">
-        <v>95.80396270751953</v>
+        <v>95.80397033691406</v>
       </c>
       <c r="F308" t="n">
-        <v>95.80872898598471</v>
+        <v>95.8087366157588</v>
       </c>
       <c r="G308" t="n">
         <v>13854600</v>
@@ -7579,16 +7579,16 @@
         <v>45743</v>
       </c>
       <c r="C311" t="n">
-        <v>95.84207153320312</v>
+        <v>95.84207916259766</v>
       </c>
       <c r="D311" t="n">
-        <v>95.84207153320312</v>
+        <v>95.84207916259766</v>
       </c>
       <c r="E311" t="n">
-        <v>95.8325462404577</v>
+        <v>95.83255386909399</v>
       </c>
       <c r="F311" t="n">
-        <v>95.84207153320312</v>
+        <v>95.84207916259766</v>
       </c>
       <c r="G311" t="n">
         <v>10022000</v>
@@ -7648,16 +7648,16 @@
         <v>45748</v>
       </c>
       <c r="C314" t="n">
-        <v>95.89548492431641</v>
+        <v>95.89549255371094</v>
       </c>
       <c r="D314" t="n">
-        <v>95.89548492431641</v>
+        <v>95.89549255371094</v>
       </c>
       <c r="E314" t="n">
-        <v>95.88592678063245</v>
+        <v>95.88593440926654</v>
       </c>
       <c r="F314" t="n">
-        <v>95.89548492431641</v>
+        <v>95.89549255371094</v>
       </c>
       <c r="G314" t="n">
         <v>21033200</v>
@@ -7694,16 +7694,16 @@
         <v>45750</v>
       </c>
       <c r="C316" t="n">
-        <v>95.92414855957031</v>
+        <v>95.92414093017578</v>
       </c>
       <c r="D316" t="n">
-        <v>95.92414855957031</v>
+        <v>95.92414093017578</v>
       </c>
       <c r="E316" t="n">
-        <v>95.90503956362811</v>
+        <v>95.90503193575341</v>
       </c>
       <c r="F316" t="n">
-        <v>95.91459770696281</v>
+        <v>95.9145900783279</v>
       </c>
       <c r="G316" t="n">
         <v>13988800</v>
@@ -7717,16 +7717,16 @@
         <v>45751</v>
       </c>
       <c r="C317" t="n">
-        <v>95.95281982421875</v>
+        <v>95.95282745361328</v>
       </c>
       <c r="D317" t="n">
-        <v>95.95281982421875</v>
+        <v>95.95282745361328</v>
       </c>
       <c r="E317" t="n">
-        <v>95.94326168119937</v>
+        <v>95.94326930983391</v>
       </c>
       <c r="F317" t="n">
-        <v>95.94326168119937</v>
+        <v>95.94326930983391</v>
       </c>
       <c r="G317" t="n">
         <v>22826300</v>
@@ -7740,16 +7740,16 @@
         <v>45754</v>
       </c>
       <c r="C318" t="n">
-        <v>95.96237945556641</v>
+        <v>95.96237182617188</v>
       </c>
       <c r="D318" t="n">
-        <v>95.96237945556641</v>
+        <v>95.96237182617188</v>
       </c>
       <c r="E318" t="n">
-        <v>95.95282860240022</v>
+        <v>95.95282097376501</v>
       </c>
       <c r="F318" t="n">
-        <v>95.95282860240022</v>
+        <v>95.95282097376501</v>
       </c>
       <c r="G318" t="n">
         <v>22564000</v>
@@ -7763,16 +7763,16 @@
         <v>45755</v>
       </c>
       <c r="C319" t="n">
-        <v>95.96237945556641</v>
+        <v>95.96237182617188</v>
       </c>
       <c r="D319" t="n">
-        <v>95.97193759946022</v>
+        <v>95.97192996930578</v>
       </c>
       <c r="E319" t="n">
-        <v>95.95282860240022</v>
+        <v>95.95282097376501</v>
       </c>
       <c r="F319" t="n">
-        <v>95.95760402898331</v>
+        <v>95.95759639996845</v>
       </c>
       <c r="G319" t="n">
         <v>17116100</v>
@@ -7786,16 +7786,16 @@
         <v>45756</v>
       </c>
       <c r="C320" t="n">
-        <v>95.98149871826172</v>
+        <v>95.98150634765625</v>
       </c>
       <c r="D320" t="n">
-        <v>95.98149871826172</v>
+        <v>95.98150634765625</v>
       </c>
       <c r="E320" t="n">
-        <v>95.97194057407167</v>
+        <v>95.97194820270643</v>
       </c>
       <c r="F320" t="n">
-        <v>95.97194057407167</v>
+        <v>95.97194820270643</v>
       </c>
       <c r="G320" t="n">
         <v>21838800</v>
@@ -7809,16 +7809,16 @@
         <v>45757</v>
       </c>
       <c r="C321" t="n">
-        <v>95.98149871826172</v>
+        <v>95.98150634765625</v>
       </c>
       <c r="D321" t="n">
-        <v>95.99104957172395</v>
+        <v>95.99105720187765</v>
       </c>
       <c r="E321" t="n">
-        <v>95.98149871826172</v>
+        <v>95.98150634765625</v>
       </c>
       <c r="F321" t="n">
-        <v>95.98149871826172</v>
+        <v>95.98150634765625</v>
       </c>
       <c r="G321" t="n">
         <v>16851500</v>
@@ -7832,16 +7832,16 @@
         <v>45758</v>
       </c>
       <c r="C322" t="n">
-        <v>96.02926635742188</v>
+        <v>96.02928924560547</v>
       </c>
       <c r="D322" t="n">
-        <v>96.02926635742188</v>
+        <v>96.02928924560547</v>
       </c>
       <c r="E322" t="n">
-        <v>96.01971550480508</v>
+        <v>96.01973839071226</v>
       </c>
       <c r="F322" t="n">
-        <v>96.02449093111348</v>
+        <v>96.02451381815887</v>
       </c>
       <c r="G322" t="n">
         <v>12916600</v>
@@ -7855,16 +7855,16 @@
         <v>45761</v>
       </c>
       <c r="C323" t="n">
-        <v>96.038818359375</v>
+        <v>96.03883361816406</v>
       </c>
       <c r="D323" t="n">
-        <v>96.038818359375</v>
+        <v>96.03883361816406</v>
       </c>
       <c r="E323" t="n">
-        <v>96.02926021664223</v>
+        <v>96.02927547391268</v>
       </c>
       <c r="F323" t="n">
-        <v>96.02926021664223</v>
+        <v>96.02927547391268</v>
       </c>
       <c r="G323" t="n">
         <v>13772300</v>
@@ -7878,16 +7878,16 @@
         <v>45762</v>
       </c>
       <c r="C324" t="n">
-        <v>96.04838562011719</v>
+        <v>96.04837036132812</v>
       </c>
       <c r="D324" t="n">
-        <v>96.04838562011719</v>
+        <v>96.04837036132812</v>
       </c>
       <c r="E324" t="n">
-        <v>96.03882747647705</v>
+        <v>96.03881221920645</v>
       </c>
       <c r="F324" t="n">
-        <v>96.04838562011719</v>
+        <v>96.04837036132812</v>
       </c>
       <c r="G324" t="n">
         <v>10043700</v>
@@ -7924,16 +7924,16 @@
         <v>45764</v>
       </c>
       <c r="C326" t="n">
-        <v>96.105712890625</v>
+        <v>96.10572814941406</v>
       </c>
       <c r="D326" t="n">
-        <v>96.11527103356798</v>
+        <v>96.11528629387459</v>
       </c>
       <c r="E326" t="n">
-        <v>96.105712890625</v>
+        <v>96.10572814941406</v>
       </c>
       <c r="F326" t="n">
-        <v>96.11048831673305</v>
+        <v>96.11050357628031</v>
       </c>
       <c r="G326" t="n">
         <v>8652700</v>
@@ -7947,16 +7947,16 @@
         <v>45768</v>
       </c>
       <c r="C327" t="n">
-        <v>96.105712890625</v>
+        <v>96.10572814941406</v>
       </c>
       <c r="D327" t="n">
-        <v>96.11527103356798</v>
+        <v>96.11528629387459</v>
       </c>
       <c r="E327" t="n">
-        <v>96.105712890625</v>
+        <v>96.10572814941406</v>
       </c>
       <c r="F327" t="n">
-        <v>96.11527103356798</v>
+        <v>96.11528629387459</v>
       </c>
       <c r="G327" t="n">
         <v>10756100</v>
@@ -8039,16 +8039,16 @@
         <v>45772</v>
       </c>
       <c r="C331" t="n">
-        <v>96.18215942382812</v>
+        <v>96.18216705322266</v>
       </c>
       <c r="D331" t="n">
-        <v>96.18215942382812</v>
+        <v>96.18216705322266</v>
       </c>
       <c r="E331" t="n">
-        <v>96.17260128128551</v>
+        <v>96.17260890992188</v>
       </c>
       <c r="F331" t="n">
-        <v>96.18215942382812</v>
+        <v>96.18216705322266</v>
       </c>
       <c r="G331" t="n">
         <v>8822700</v>
@@ -8062,16 +8062,16 @@
         <v>45775</v>
       </c>
       <c r="C332" t="n">
-        <v>96.18215942382812</v>
+        <v>96.18216705322266</v>
       </c>
       <c r="D332" t="n">
-        <v>96.19171756637073</v>
+        <v>96.19172519652344</v>
       </c>
       <c r="E332" t="n">
-        <v>96.18215942382812</v>
+        <v>96.18216705322266</v>
       </c>
       <c r="F332" t="n">
-        <v>96.18215942382812</v>
+        <v>96.18216705322266</v>
       </c>
       <c r="G332" t="n">
         <v>9127900</v>
@@ -8085,16 +8085,16 @@
         <v>45776</v>
       </c>
       <c r="C333" t="n">
-        <v>96.19172668457031</v>
+        <v>96.19173431396484</v>
       </c>
       <c r="D333" t="n">
-        <v>96.20127753729169</v>
+        <v>96.20128516744374</v>
       </c>
       <c r="E333" t="n">
-        <v>96.19172668457031</v>
+        <v>96.19173431396484</v>
       </c>
       <c r="F333" t="n">
-        <v>96.19172668457031</v>
+        <v>96.19173431396484</v>
       </c>
       <c r="G333" t="n">
         <v>8555000</v>
@@ -8108,16 +8108,16 @@
         <v>45777</v>
       </c>
       <c r="C334" t="n">
-        <v>96.22039031982422</v>
+        <v>96.22040557861328</v>
       </c>
       <c r="D334" t="n">
-        <v>96.22039031982422</v>
+        <v>96.22040557861328</v>
       </c>
       <c r="E334" t="n">
-        <v>96.20127403362315</v>
+        <v>96.20128928938072</v>
       </c>
       <c r="F334" t="n">
-        <v>96.20127403362315</v>
+        <v>96.20128928938072</v>
       </c>
       <c r="G334" t="n">
         <v>16040200</v>
@@ -8131,16 +8131,16 @@
         <v>45778</v>
       </c>
       <c r="C335" t="n">
-        <v>96.23477172851562</v>
+        <v>96.23477935791016</v>
       </c>
       <c r="D335" t="n">
-        <v>96.23477172851562</v>
+        <v>96.23477935791016</v>
       </c>
       <c r="E335" t="n">
-        <v>96.22518167899288</v>
+        <v>96.22518930762713</v>
       </c>
       <c r="F335" t="n">
-        <v>96.23477172851562</v>
+        <v>96.23477935791016</v>
       </c>
       <c r="G335" t="n">
         <v>21288700</v>
@@ -8154,16 +8154,16 @@
         <v>45779</v>
       </c>
       <c r="C336" t="n">
-        <v>96.2635498046875</v>
+        <v>96.26355743408203</v>
       </c>
       <c r="D336" t="n">
-        <v>96.2635498046875</v>
+        <v>96.26355743408203</v>
       </c>
       <c r="E336" t="n">
-        <v>96.25395975364626</v>
+        <v>96.25396738228072</v>
       </c>
       <c r="F336" t="n">
-        <v>96.25395975364626</v>
+        <v>96.25396738228072</v>
       </c>
       <c r="G336" t="n">
         <v>13930900</v>
@@ -8223,16 +8223,16 @@
         <v>45784</v>
       </c>
       <c r="C339" t="n">
-        <v>96.28270721435547</v>
+        <v>96.28273010253906</v>
       </c>
       <c r="D339" t="n">
-        <v>96.29229726386509</v>
+        <v>96.29232015432841</v>
       </c>
       <c r="E339" t="n">
-        <v>96.28270721435547</v>
+        <v>96.28273010253906</v>
       </c>
       <c r="F339" t="n">
-        <v>96.29229726386509</v>
+        <v>96.29232015432841</v>
       </c>
       <c r="G339" t="n">
         <v>8509300</v>
@@ -8246,16 +8246,16 @@
         <v>45785</v>
       </c>
       <c r="C340" t="n">
-        <v>96.31147003173828</v>
+        <v>96.31148529052734</v>
       </c>
       <c r="D340" t="n">
-        <v>96.31147003173828</v>
+        <v>96.31148529052734</v>
       </c>
       <c r="E340" t="n">
-        <v>96.29229724778671</v>
+        <v>96.29231250353818</v>
       </c>
       <c r="F340" t="n">
-        <v>96.30188729729473</v>
+        <v>96.30190255456557</v>
       </c>
       <c r="G340" t="n">
         <v>11931100</v>
@@ -8269,16 +8269,16 @@
         <v>45786</v>
       </c>
       <c r="C341" t="n">
-        <v>96.34026336669922</v>
+        <v>96.34024047851562</v>
       </c>
       <c r="D341" t="n">
-        <v>96.34026336669922</v>
+        <v>96.34024047851562</v>
       </c>
       <c r="E341" t="n">
-        <v>96.33067331488314</v>
+        <v>96.33065042897792</v>
       </c>
       <c r="F341" t="n">
-        <v>96.33067331488314</v>
+        <v>96.33065042897792</v>
       </c>
       <c r="G341" t="n">
         <v>11793700</v>
@@ -8292,16 +8292,16 @@
         <v>45789</v>
       </c>
       <c r="C342" t="n">
-        <v>96.34026336669922</v>
+        <v>96.34024047851562</v>
       </c>
       <c r="D342" t="n">
-        <v>96.34984610344908</v>
+        <v>96.34982321298885</v>
       </c>
       <c r="E342" t="n">
-        <v>96.34026336669922</v>
+        <v>96.34024047851562</v>
       </c>
       <c r="F342" t="n">
-        <v>96.34026336669922</v>
+        <v>96.34024047851562</v>
       </c>
       <c r="G342" t="n">
         <v>16808300</v>
@@ -8315,16 +8315,16 @@
         <v>45790</v>
       </c>
       <c r="C343" t="n">
-        <v>96.35942840576172</v>
+        <v>96.35943603515625</v>
       </c>
       <c r="D343" t="n">
-        <v>96.35942840576172</v>
+        <v>96.35943603515625</v>
       </c>
       <c r="E343" t="n">
-        <v>96.34983835471689</v>
+        <v>96.34984598335213</v>
       </c>
       <c r="F343" t="n">
-        <v>96.34983835471689</v>
+        <v>96.34984598335213</v>
       </c>
       <c r="G343" t="n">
         <v>18174400</v>
@@ -8338,16 +8338,16 @@
         <v>45791</v>
       </c>
       <c r="C344" t="n">
-        <v>96.36901092529297</v>
+        <v>96.36899566650391</v>
       </c>
       <c r="D344" t="n">
-        <v>96.36901092529297</v>
+        <v>96.36899566650391</v>
       </c>
       <c r="E344" t="n">
-        <v>96.35942087499764</v>
+        <v>96.35940561772703</v>
       </c>
       <c r="F344" t="n">
-        <v>96.35942087499764</v>
+        <v>96.35940561772703</v>
       </c>
       <c r="G344" t="n">
         <v>9821100</v>
@@ -8361,16 +8361,16 @@
         <v>45792</v>
       </c>
       <c r="C345" t="n">
-        <v>96.36901092529297</v>
+        <v>96.36899566650391</v>
       </c>
       <c r="D345" t="n">
-        <v>96.37859366052324</v>
+        <v>96.37857840021688</v>
       </c>
       <c r="E345" t="n">
-        <v>96.36901092529297</v>
+        <v>96.36899566650391</v>
       </c>
       <c r="F345" t="n">
-        <v>96.37859366052324</v>
+        <v>96.37857840021688</v>
       </c>
       <c r="G345" t="n">
         <v>10057600</v>
@@ -8430,16 +8430,16 @@
         <v>45797</v>
       </c>
       <c r="C348" t="n">
-        <v>96.43613433837891</v>
+        <v>96.43611907958984</v>
       </c>
       <c r="D348" t="n">
-        <v>96.43613433837891</v>
+        <v>96.43611907958984</v>
       </c>
       <c r="E348" t="n">
-        <v>96.42654428731873</v>
+        <v>96.42652903004708</v>
       </c>
       <c r="F348" t="n">
-        <v>96.43613433837891</v>
+        <v>96.43611907958984</v>
       </c>
       <c r="G348" t="n">
         <v>9249100</v>
@@ -8476,16 +8476,16 @@
         <v>45799</v>
       </c>
       <c r="C350" t="n">
-        <v>96.46490478515625</v>
+        <v>96.46488952636719</v>
       </c>
       <c r="D350" t="n">
-        <v>96.46490478515625</v>
+        <v>96.46488952636719</v>
       </c>
       <c r="E350" t="n">
-        <v>96.45531473333966</v>
+        <v>96.45529947606755</v>
       </c>
       <c r="F350" t="n">
-        <v>96.45531473333966</v>
+        <v>96.45529947606755</v>
       </c>
       <c r="G350" t="n">
         <v>8901700</v>
@@ -8499,16 +8499,16 @@
         <v>45800</v>
       </c>
       <c r="C351" t="n">
-        <v>96.49365234375</v>
+        <v>96.49366760253906</v>
       </c>
       <c r="D351" t="n">
-        <v>96.5032423940478</v>
+        <v>96.50325765435336</v>
       </c>
       <c r="E351" t="n">
-        <v>96.49365234375</v>
+        <v>96.49366760253906</v>
       </c>
       <c r="F351" t="n">
-        <v>96.5032423940478</v>
+        <v>96.50325765435336</v>
       </c>
       <c r="G351" t="n">
         <v>9119400</v>
@@ -8522,16 +8522,16 @@
         <v>45804</v>
       </c>
       <c r="C352" t="n">
-        <v>96.50324249267578</v>
+        <v>96.50323486328125</v>
       </c>
       <c r="D352" t="n">
-        <v>96.51283254298339</v>
+        <v>96.51282491283068</v>
       </c>
       <c r="E352" t="n">
-        <v>96.50324249267578</v>
+        <v>96.50323486328125</v>
       </c>
       <c r="F352" t="n">
-        <v>96.51283254298339</v>
+        <v>96.51282491283068</v>
       </c>
       <c r="G352" t="n">
         <v>10526600</v>
@@ -8545,16 +8545,16 @@
         <v>45805</v>
       </c>
       <c r="C353" t="n">
-        <v>96.53199768066406</v>
+        <v>96.53200531005859</v>
       </c>
       <c r="D353" t="n">
-        <v>96.53199768066406</v>
+        <v>96.53200531005859</v>
       </c>
       <c r="E353" t="n">
-        <v>96.52240763111624</v>
+        <v>96.52241525975282</v>
       </c>
       <c r="F353" t="n">
-        <v>96.5272063134224</v>
+        <v>96.52721394243824</v>
       </c>
       <c r="G353" t="n">
         <v>8415200</v>
@@ -8568,16 +8568,16 @@
         <v>45806</v>
       </c>
       <c r="C354" t="n">
-        <v>96.53199768066406</v>
+        <v>96.53200531005859</v>
       </c>
       <c r="D354" t="n">
-        <v>96.54158773021189</v>
+        <v>96.54159536036435</v>
       </c>
       <c r="E354" t="n">
-        <v>96.52240763111624</v>
+        <v>96.52241525975282</v>
       </c>
       <c r="F354" t="n">
-        <v>96.53199768066406</v>
+        <v>96.53200531005859</v>
       </c>
       <c r="G354" t="n">
         <v>10387000</v>
@@ -8614,16 +8614,16 @@
         <v>45810</v>
       </c>
       <c r="C356" t="n">
-        <v>96.58771514892578</v>
+        <v>96.58770751953125</v>
       </c>
       <c r="D356" t="n">
-        <v>96.58771514892578</v>
+        <v>96.58770751953125</v>
       </c>
       <c r="E356" t="n">
-        <v>96.57809822717108</v>
+        <v>96.57809059853618</v>
       </c>
       <c r="F356" t="n">
-        <v>96.58771514892578</v>
+        <v>96.58770751953125</v>
       </c>
       <c r="G356" t="n">
         <v>21934000</v>
@@ -8683,16 +8683,16 @@
         <v>45813</v>
       </c>
       <c r="C359" t="n">
-        <v>96.6165771484375</v>
+        <v>96.61658477783203</v>
       </c>
       <c r="D359" t="n">
-        <v>96.6165771484375</v>
+        <v>96.61658477783203</v>
       </c>
       <c r="E359" t="n">
-        <v>96.60695288659591</v>
+        <v>96.60696051523044</v>
       </c>
       <c r="F359" t="n">
-        <v>96.6165771484375</v>
+        <v>96.61658477783203</v>
       </c>
       <c r="G359" t="n">
         <v>9915800</v>
@@ -8706,16 +8706,16 @@
         <v>45814</v>
       </c>
       <c r="C360" t="n">
-        <v>96.64544677734375</v>
+        <v>96.64545440673828</v>
       </c>
       <c r="D360" t="n">
-        <v>96.65506369844093</v>
+        <v>96.65507132859463</v>
       </c>
       <c r="E360" t="n">
-        <v>96.64544677734375</v>
+        <v>96.64545440673828</v>
       </c>
       <c r="F360" t="n">
-        <v>96.65025523789234</v>
+        <v>96.65026286766646</v>
       </c>
       <c r="G360" t="n">
         <v>9122400</v>
@@ -8752,16 +8752,16 @@
         <v>45818</v>
       </c>
       <c r="C362" t="n">
-        <v>96.66469573974609</v>
+        <v>96.66468811035156</v>
       </c>
       <c r="D362" t="n">
-        <v>96.67432000277891</v>
+        <v>96.67431237262477</v>
       </c>
       <c r="E362" t="n">
-        <v>96.66469573974609</v>
+        <v>96.66468811035156</v>
       </c>
       <c r="F362" t="n">
-        <v>96.66950420068163</v>
+        <v>96.6694965709076</v>
       </c>
       <c r="G362" t="n">
         <v>9201800</v>
@@ -8798,16 +8798,16 @@
         <v>45820</v>
       </c>
       <c r="C364" t="n">
-        <v>96.69355773925781</v>
+        <v>96.69356536865234</v>
       </c>
       <c r="D364" t="n">
-        <v>96.69355773925781</v>
+        <v>96.69356536865234</v>
       </c>
       <c r="E364" t="n">
-        <v>96.68394081772971</v>
+        <v>96.68394844636542</v>
       </c>
       <c r="F364" t="n">
-        <v>96.69355773925781</v>
+        <v>96.69356536865234</v>
       </c>
       <c r="G364" t="n">
         <v>9574900</v>
@@ -8821,16 +8821,16 @@
         <v>45821</v>
       </c>
       <c r="C365" t="n">
-        <v>96.7320556640625</v>
+        <v>96.73203277587891</v>
       </c>
       <c r="D365" t="n">
-        <v>96.7320556640625</v>
+        <v>96.73203277587891</v>
       </c>
       <c r="E365" t="n">
-        <v>96.72243140055555</v>
+        <v>96.7224085146492</v>
       </c>
       <c r="F365" t="n">
-        <v>96.72243140055555</v>
+        <v>96.7224085146492</v>
       </c>
       <c r="G365" t="n">
         <v>7880300</v>
@@ -8844,16 +8844,16 @@
         <v>45824</v>
       </c>
       <c r="C366" t="n">
-        <v>96.7320556640625</v>
+        <v>96.73203277587891</v>
       </c>
       <c r="D366" t="n">
-        <v>96.74167992756945</v>
+        <v>96.74165703710862</v>
       </c>
       <c r="E366" t="n">
-        <v>96.7320556640625</v>
+        <v>96.73203277587891</v>
       </c>
       <c r="F366" t="n">
-        <v>96.74167992756945</v>
+        <v>96.74165703710862</v>
       </c>
       <c r="G366" t="n">
         <v>10286500</v>
@@ -8867,16 +8867,16 @@
         <v>45825</v>
       </c>
       <c r="C367" t="n">
-        <v>96.74166107177734</v>
+        <v>96.74166870117188</v>
       </c>
       <c r="D367" t="n">
-        <v>96.75128533340843</v>
+        <v>96.75129296356198</v>
       </c>
       <c r="E367" t="n">
-        <v>96.74166107177734</v>
+        <v>96.74166870117188</v>
       </c>
       <c r="F367" t="n">
-        <v>96.75128533340843</v>
+        <v>96.75129296356198</v>
       </c>
       <c r="G367" t="n">
         <v>8734500</v>
@@ -8913,16 +8913,16 @@
         <v>45828</v>
       </c>
       <c r="C369" t="n">
-        <v>96.79939270019531</v>
+        <v>96.79940032958984</v>
       </c>
       <c r="D369" t="n">
-        <v>96.80901696190008</v>
+        <v>96.80902459205316</v>
       </c>
       <c r="E369" t="n">
-        <v>96.79939270019531</v>
+        <v>96.79940032958984</v>
       </c>
       <c r="F369" t="n">
-        <v>96.80420850162805</v>
+        <v>96.80421613140216</v>
       </c>
       <c r="G369" t="n">
         <v>9399400</v>
@@ -8936,16 +8936,16 @@
         <v>45831</v>
       </c>
       <c r="C370" t="n">
-        <v>96.81864166259766</v>
+        <v>96.81864929199219</v>
       </c>
       <c r="D370" t="n">
-        <v>96.81864166259766</v>
+        <v>96.81864929199219</v>
       </c>
       <c r="E370" t="n">
-        <v>96.80901740084924</v>
+        <v>96.80902502948538</v>
       </c>
       <c r="F370" t="n">
-        <v>96.81382586114307</v>
+        <v>96.81383349015812</v>
       </c>
       <c r="G370" t="n">
         <v>8847300</v>
@@ -8959,16 +8959,16 @@
         <v>45832</v>
       </c>
       <c r="C371" t="n">
-        <v>96.82828521728516</v>
+        <v>96.82827758789062</v>
       </c>
       <c r="D371" t="n">
-        <v>96.83790948168087</v>
+        <v>96.837901851528</v>
       </c>
       <c r="E371" t="n">
-        <v>96.82828521728516</v>
+        <v>96.82827758789062</v>
       </c>
       <c r="F371" t="n">
-        <v>96.8331010200644</v>
+        <v>96.83309339029041</v>
       </c>
       <c r="G371" t="n">
         <v>10132100</v>
@@ -8982,16 +8982,16 @@
         <v>45833</v>
       </c>
       <c r="C372" t="n">
-        <v>96.837890625</v>
+        <v>96.83789825439453</v>
       </c>
       <c r="D372" t="n">
-        <v>96.84751488752164</v>
+        <v>96.84752251767441</v>
       </c>
       <c r="E372" t="n">
-        <v>96.837890625</v>
+        <v>96.83789825439453</v>
       </c>
       <c r="F372" t="n">
-        <v>96.84269908568015</v>
+        <v>96.8427067154535</v>
       </c>
       <c r="G372" t="n">
         <v>8015100</v>
@@ -9005,16 +9005,16 @@
         <v>45834</v>
       </c>
       <c r="C373" t="n">
-        <v>96.84751892089844</v>
+        <v>96.84751129150391</v>
       </c>
       <c r="D373" t="n">
-        <v>96.85714318382088</v>
+        <v>96.85713555366819</v>
       </c>
       <c r="E373" t="n">
-        <v>96.84751892089844</v>
+        <v>96.84751129150391</v>
       </c>
       <c r="F373" t="n">
-        <v>96.85714318382088</v>
+        <v>96.85713555366819</v>
       </c>
       <c r="G373" t="n">
         <v>9277700</v>
@@ -9028,16 +9028,16 @@
         <v>45835</v>
       </c>
       <c r="C374" t="n">
-        <v>96.88600158691406</v>
+        <v>96.88600921630859</v>
       </c>
       <c r="D374" t="n">
-        <v>96.88600158691406</v>
+        <v>96.88600921630859</v>
       </c>
       <c r="E374" t="n">
-        <v>96.87637732469139</v>
+        <v>96.87638495332804</v>
       </c>
       <c r="F374" t="n">
-        <v>96.88118578522216</v>
+        <v>96.88119341423747</v>
       </c>
       <c r="G374" t="n">
         <v>9742300</v>
@@ -9051,16 +9051,16 @@
         <v>45838</v>
       </c>
       <c r="C375" t="n">
-        <v>96.88600158691406</v>
+        <v>96.88600921630859</v>
       </c>
       <c r="D375" t="n">
-        <v>96.89561850797561</v>
+        <v>96.89562613812744</v>
       </c>
       <c r="E375" t="n">
-        <v>96.88600158691406</v>
+        <v>96.88600921630859</v>
       </c>
       <c r="F375" t="n">
-        <v>96.88600158691406</v>
+        <v>96.88600921630859</v>
       </c>
       <c r="G375" t="n">
         <v>18195600</v>
@@ -9074,16 +9074,16 @@
         <v>45839</v>
       </c>
       <c r="C376" t="n">
-        <v>96.91207122802734</v>
+        <v>96.91207885742188</v>
       </c>
       <c r="D376" t="n">
-        <v>96.91207122802734</v>
+        <v>96.91207885742188</v>
       </c>
       <c r="E376" t="n">
-        <v>96.90241368381817</v>
+        <v>96.90242131245242</v>
       </c>
       <c r="F376" t="n">
-        <v>96.91207122802734</v>
+        <v>96.91207885742188</v>
       </c>
       <c r="G376" t="n">
         <v>24173900</v>
@@ -9097,16 +9097,16 @@
         <v>45840</v>
       </c>
       <c r="C377" t="n">
-        <v>96.91207122802734</v>
+        <v>96.91207885742188</v>
       </c>
       <c r="D377" t="n">
-        <v>96.92172140568869</v>
+        <v>96.92172903584292</v>
       </c>
       <c r="E377" t="n">
-        <v>96.91207122802734</v>
+        <v>96.91207885742188</v>
       </c>
       <c r="F377" t="n">
-        <v>96.92172140568869</v>
+        <v>96.92172903584292</v>
       </c>
       <c r="G377" t="n">
         <v>10850800</v>
@@ -9120,16 +9120,16 @@
         <v>45841</v>
       </c>
       <c r="C378" t="n">
-        <v>96.96036529541016</v>
+        <v>96.96035003662109</v>
       </c>
       <c r="D378" t="n">
-        <v>96.9700228417189</v>
+        <v>96.97000758141002</v>
       </c>
       <c r="E378" t="n">
-        <v>96.96036529541016</v>
+        <v>96.96035003662109</v>
       </c>
       <c r="F378" t="n">
-        <v>96.96036529541016</v>
+        <v>96.96035003662109</v>
       </c>
       <c r="G378" t="n">
         <v>7404700</v>
@@ -9143,16 +9143,16 @@
         <v>45845</v>
       </c>
       <c r="C379" t="n">
-        <v>96.97966003417969</v>
+        <v>96.97967529296875</v>
       </c>
       <c r="D379" t="n">
-        <v>96.97966003417969</v>
+        <v>96.97967529296875</v>
       </c>
       <c r="E379" t="n">
-        <v>96.97000248989785</v>
+        <v>96.97001774716739</v>
       </c>
       <c r="F379" t="n">
-        <v>96.97966003417969</v>
+        <v>96.97967529296875</v>
       </c>
       <c r="G379" t="n">
         <v>12363900</v>
@@ -9166,16 +9166,16 @@
         <v>45846</v>
       </c>
       <c r="C380" t="n">
-        <v>96.99897766113281</v>
+        <v>96.99897003173828</v>
       </c>
       <c r="D380" t="n">
-        <v>96.99897766113281</v>
+        <v>96.99897003173828</v>
       </c>
       <c r="E380" t="n">
-        <v>96.97966993714543</v>
+        <v>96.97966230926953</v>
       </c>
       <c r="F380" t="n">
-        <v>96.9893201158648</v>
+        <v>96.98931248722988</v>
       </c>
       <c r="G380" t="n">
         <v>13107800</v>
@@ -9189,16 +9189,16 @@
         <v>45847</v>
       </c>
       <c r="C381" t="n">
-        <v>96.98931121826172</v>
+        <v>96.98930358886719</v>
       </c>
       <c r="D381" t="n">
-        <v>96.99896876264377</v>
+        <v>96.99896113248955</v>
       </c>
       <c r="E381" t="n">
-        <v>96.98931121826172</v>
+        <v>96.98930358886719</v>
       </c>
       <c r="F381" t="n">
-        <v>96.99896876264377</v>
+        <v>96.99896113248955</v>
       </c>
       <c r="G381" t="n">
         <v>11156600</v>
@@ -9212,16 +9212,16 @@
         <v>45848</v>
       </c>
       <c r="C382" t="n">
-        <v>97.00862121582031</v>
+        <v>97.00863647460938</v>
       </c>
       <c r="D382" t="n">
-        <v>97.01827875969551</v>
+        <v>97.01829402000364</v>
       </c>
       <c r="E382" t="n">
-        <v>96.99896367194511</v>
+        <v>96.99897892921511</v>
       </c>
       <c r="F382" t="n">
-        <v>97.00862121582031</v>
+        <v>97.00863647460938</v>
       </c>
       <c r="G382" t="n">
         <v>10071700</v>
@@ -9235,16 +9235,16 @@
         <v>45849</v>
       </c>
       <c r="C383" t="n">
-        <v>97.04724884033203</v>
+        <v>97.0472412109375</v>
       </c>
       <c r="D383" t="n">
-        <v>97.04724884033203</v>
+        <v>97.0472412109375</v>
       </c>
       <c r="E383" t="n">
-        <v>97.03759129597762</v>
+        <v>97.03758366734232</v>
       </c>
       <c r="F383" t="n">
-        <v>97.03759129597762</v>
+        <v>97.03758366734232</v>
       </c>
       <c r="G383" t="n">
         <v>9288900</v>
@@ -9258,16 +9258,16 @@
         <v>45852</v>
       </c>
       <c r="C384" t="n">
-        <v>97.04724884033203</v>
+        <v>97.0472412109375</v>
       </c>
       <c r="D384" t="n">
-        <v>97.05689901813851</v>
+        <v>97.05689138798532</v>
       </c>
       <c r="E384" t="n">
-        <v>97.04724884033203</v>
+        <v>97.0472412109375</v>
       </c>
       <c r="F384" t="n">
-        <v>97.05689901813851</v>
+        <v>97.05689138798532</v>
       </c>
       <c r="G384" t="n">
         <v>10293900</v>
@@ -9350,16 +9350,16 @@
         <v>45856</v>
       </c>
       <c r="C388" t="n">
-        <v>97.12449645996094</v>
+        <v>97.12448883056641</v>
       </c>
       <c r="D388" t="n">
-        <v>97.12449645996094</v>
+        <v>97.12448883056641</v>
       </c>
       <c r="E388" t="n">
-        <v>97.11484628122402</v>
+        <v>97.11483865258754</v>
       </c>
       <c r="F388" t="n">
-        <v>97.11484628122402</v>
+        <v>97.11483865258754</v>
       </c>
       <c r="G388" t="n">
         <v>9399500</v>
@@ -9373,16 +9373,16 @@
         <v>45859</v>
       </c>
       <c r="C389" t="n">
-        <v>97.13413238525391</v>
+        <v>97.13414001464844</v>
       </c>
       <c r="D389" t="n">
-        <v>97.13413238525391</v>
+        <v>97.13414001464844</v>
       </c>
       <c r="E389" t="n">
-        <v>97.12447484211791</v>
+        <v>97.12448247075388</v>
       </c>
       <c r="F389" t="n">
-        <v>97.12447484211791</v>
+        <v>97.12448247075388</v>
       </c>
       <c r="G389" t="n">
         <v>12893000</v>
@@ -9396,16 +9396,16 @@
         <v>45860</v>
       </c>
       <c r="C390" t="n">
-        <v>97.15345001220703</v>
+        <v>97.15346527099609</v>
       </c>
       <c r="D390" t="n">
-        <v>97.15345001220703</v>
+        <v>97.15346527099609</v>
       </c>
       <c r="E390" t="n">
-        <v>97.14379246881848</v>
+        <v>97.14380772609073</v>
       </c>
       <c r="F390" t="n">
-        <v>97.15345001220703</v>
+        <v>97.15346527099609</v>
       </c>
       <c r="G390" t="n">
         <v>9340600</v>
@@ -9419,16 +9419,16 @@
         <v>45861</v>
       </c>
       <c r="C391" t="n">
-        <v>97.16313171386719</v>
+        <v>97.16310882568359</v>
       </c>
       <c r="D391" t="n">
-        <v>97.16313171386719</v>
+        <v>97.16310882568359</v>
       </c>
       <c r="E391" t="n">
-        <v>97.15348153389481</v>
+        <v>97.15345864798445</v>
       </c>
       <c r="F391" t="n">
-        <v>97.16313171386719</v>
+        <v>97.16310882568359</v>
       </c>
       <c r="G391" t="n">
         <v>8056100</v>
@@ -9465,16 +9465,16 @@
         <v>45863</v>
       </c>
       <c r="C393" t="n">
-        <v>97.19208526611328</v>
+        <v>97.19207763671875</v>
       </c>
       <c r="D393" t="n">
-        <v>97.20173544419048</v>
+        <v>97.20172781403843</v>
       </c>
       <c r="E393" t="n">
-        <v>97.19208526611328</v>
+        <v>97.19207763671875</v>
       </c>
       <c r="F393" t="n">
-        <v>97.20173544419048</v>
+        <v>97.20172781403843</v>
       </c>
       <c r="G393" t="n">
         <v>9776600</v>
@@ -9488,16 +9488,16 @@
         <v>45866</v>
       </c>
       <c r="C394" t="n">
-        <v>97.22103881835938</v>
+        <v>97.22105407714844</v>
       </c>
       <c r="D394" t="n">
-        <v>97.22103881835938</v>
+        <v>97.22105407714844</v>
       </c>
       <c r="E394" t="n">
-        <v>97.21138127489775</v>
+        <v>97.21139653217107</v>
       </c>
       <c r="F394" t="n">
-        <v>97.21620636335493</v>
+        <v>97.21622162138554</v>
       </c>
       <c r="G394" t="n">
         <v>11581000</v>
@@ -9511,16 +9511,16 @@
         <v>45867</v>
       </c>
       <c r="C395" t="n">
-        <v>97.22103881835938</v>
+        <v>97.22105407714844</v>
       </c>
       <c r="D395" t="n">
-        <v>97.23068899527374</v>
+        <v>97.23070425557738</v>
       </c>
       <c r="E395" t="n">
-        <v>97.22103881835938</v>
+        <v>97.22105407714844</v>
       </c>
       <c r="F395" t="n">
-        <v>97.22103881835938</v>
+        <v>97.22105407714844</v>
       </c>
       <c r="G395" t="n">
         <v>8622300</v>
@@ -9534,16 +9534,16 @@
         <v>45868</v>
       </c>
       <c r="C396" t="n">
-        <v>97.2403564453125</v>
+        <v>97.24034881591797</v>
       </c>
       <c r="D396" t="n">
-        <v>97.2403564453125</v>
+        <v>97.24034881591797</v>
       </c>
       <c r="E396" t="n">
-        <v>97.230698900867</v>
+        <v>97.23069127223019</v>
       </c>
       <c r="F396" t="n">
-        <v>97.230698900867</v>
+        <v>97.23069127223019</v>
       </c>
       <c r="G396" t="n">
         <v>9106000</v>
@@ -9557,16 +9557,16 @@
         <v>45869</v>
       </c>
       <c r="C397" t="n">
-        <v>97.25</v>
+        <v>97.25001525878906</v>
       </c>
       <c r="D397" t="n">
-        <v>97.25</v>
+        <v>97.25001525878906</v>
       </c>
       <c r="E397" t="n">
-        <v>97.24034245694376</v>
+        <v>97.24035771421754</v>
       </c>
       <c r="F397" t="n">
-        <v>97.2451675451984</v>
+        <v>97.24518280322924</v>
       </c>
       <c r="G397" t="n">
         <v>19051200</v>
@@ -9603,16 +9603,16 @@
         <v>45873</v>
       </c>
       <c r="C399" t="n">
-        <v>97.30039978027344</v>
+        <v>97.30040740966797</v>
       </c>
       <c r="D399" t="n">
-        <v>97.30039978027344</v>
+        <v>97.30040740966797</v>
       </c>
       <c r="E399" t="n">
-        <v>97.29070740084522</v>
+        <v>97.29071502947977</v>
       </c>
       <c r="F399" t="n">
-        <v>97.29554989399966</v>
+        <v>97.29555752301393</v>
       </c>
       <c r="G399" t="n">
         <v>14766400</v>
@@ -9626,16 +9626,16 @@
         <v>45874</v>
       </c>
       <c r="C400" t="n">
-        <v>97.31010437011719</v>
+        <v>97.31008911132812</v>
       </c>
       <c r="D400" t="n">
-        <v>97.31010437011719</v>
+        <v>97.31008911132812</v>
       </c>
       <c r="E400" t="n">
-        <v>97.30041938185722</v>
+        <v>97.30040412458681</v>
       </c>
       <c r="F400" t="n">
-        <v>97.30041938185722</v>
+        <v>97.30040412458681</v>
       </c>
       <c r="G400" t="n">
         <v>12350300</v>
@@ -9718,16 +9718,16 @@
         <v>45880</v>
       </c>
       <c r="C404" t="n">
-        <v>97.37792205810547</v>
+        <v>97.37793731689453</v>
       </c>
       <c r="D404" t="n">
-        <v>97.37792205810547</v>
+        <v>97.37793731689453</v>
       </c>
       <c r="E404" t="n">
-        <v>97.36823707125734</v>
+        <v>97.3682523285288</v>
       </c>
       <c r="F404" t="n">
-        <v>97.37792205810547</v>
+        <v>97.37793731689453</v>
       </c>
       <c r="G404" t="n">
         <v>12940300</v>
@@ -9741,16 +9741,16 @@
         <v>45881</v>
       </c>
       <c r="C405" t="n">
-        <v>97.37792205810547</v>
+        <v>97.37793731689453</v>
       </c>
       <c r="D405" t="n">
-        <v>97.38761443807333</v>
+        <v>97.38762969838115</v>
       </c>
       <c r="E405" t="n">
-        <v>97.37792205810547</v>
+        <v>97.37793731689453</v>
       </c>
       <c r="F405" t="n">
-        <v>97.38761443807333</v>
+        <v>97.38762969838115</v>
       </c>
       <c r="G405" t="n">
         <v>12918200</v>
@@ -9787,16 +9787,16 @@
         <v>45883</v>
       </c>
       <c r="C407" t="n">
-        <v>97.40699005126953</v>
+        <v>97.406982421875</v>
       </c>
       <c r="D407" t="n">
-        <v>97.4166824310629</v>
+        <v>97.41667480090922</v>
       </c>
       <c r="E407" t="n">
-        <v>97.40699005126953</v>
+        <v>97.406982421875</v>
       </c>
       <c r="F407" t="n">
-        <v>97.40699005126953</v>
+        <v>97.406982421875</v>
       </c>
       <c r="G407" t="n">
         <v>9798900</v>
@@ -9925,16 +9925,16 @@
         <v>45891</v>
       </c>
       <c r="C413" t="n">
-        <v>97.52328491210938</v>
+        <v>97.52327728271484</v>
       </c>
       <c r="D413" t="n">
-        <v>97.52328491210938</v>
+        <v>97.52327728271484</v>
       </c>
       <c r="E413" t="n">
-        <v>97.51359253147295</v>
+        <v>97.51358490283667</v>
       </c>
       <c r="F413" t="n">
-        <v>97.52328491210938</v>
+        <v>97.52327728271484</v>
       </c>
       <c r="G413" t="n">
         <v>13160400</v>
@@ -9948,16 +9948,16 @@
         <v>45894</v>
       </c>
       <c r="C414" t="n">
-        <v>97.54266357421875</v>
+        <v>97.54267120361328</v>
       </c>
       <c r="D414" t="n">
-        <v>97.54266357421875</v>
+        <v>97.54267120361328</v>
       </c>
       <c r="E414" t="n">
-        <v>97.53297119418838</v>
+        <v>97.5329788228248</v>
       </c>
       <c r="F414" t="n">
-        <v>97.53781368764366</v>
+        <v>97.53782131665886</v>
       </c>
       <c r="G414" t="n">
         <v>13556000</v>
@@ -9971,16 +9971,16 @@
         <v>45895</v>
       </c>
       <c r="C415" t="n">
-        <v>97.54266357421875</v>
+        <v>97.54267120361328</v>
       </c>
       <c r="D415" t="n">
-        <v>97.55234856112934</v>
+        <v>97.55235619128139</v>
       </c>
       <c r="E415" t="n">
-        <v>97.54266357421875</v>
+        <v>97.54267120361328</v>
       </c>
       <c r="F415" t="n">
-        <v>97.54750606767405</v>
+        <v>97.54751369744734</v>
       </c>
       <c r="G415" t="n">
         <v>8741600</v>
@@ -9994,16 +9994,16 @@
         <v>45896</v>
       </c>
       <c r="C416" t="n">
-        <v>97.55234527587891</v>
+        <v>97.55235290527344</v>
       </c>
       <c r="D416" t="n">
-        <v>97.56203765558288</v>
+        <v>97.56204528573542</v>
       </c>
       <c r="E416" t="n">
-        <v>97.55234527587891</v>
+        <v>97.55235290527344</v>
       </c>
       <c r="F416" t="n">
-        <v>97.56203765558288</v>
+        <v>97.56204528573542</v>
       </c>
       <c r="G416" t="n">
         <v>7384600</v>
@@ -10040,16 +10040,16 @@
         <v>45898</v>
       </c>
       <c r="C418" t="n">
-        <v>97.62017822265625</v>
+        <v>97.62017059326172</v>
       </c>
       <c r="D418" t="n">
-        <v>97.62017822265625</v>
+        <v>97.62017059326172</v>
       </c>
       <c r="E418" t="n">
-        <v>97.60080085615444</v>
+        <v>97.60079322827433</v>
       </c>
       <c r="F418" t="n">
-        <v>97.60080085615444</v>
+        <v>97.60079322827433</v>
       </c>
       <c r="G418" t="n">
         <v>21369400</v>
@@ -10063,16 +10063,16 @@
         <v>45902</v>
       </c>
       <c r="C419" t="n">
-        <v>97.62990570068359</v>
+        <v>97.62989044189453</v>
       </c>
       <c r="D419" t="n">
-        <v>97.62990570068359</v>
+        <v>97.62989044189453</v>
       </c>
       <c r="E419" t="n">
-        <v>97.62017856030185</v>
+        <v>97.62016330303307</v>
       </c>
       <c r="F419" t="n">
-        <v>97.62990570068359</v>
+        <v>97.62989044189453</v>
       </c>
       <c r="G419" t="n">
         <v>27254500</v>
@@ -10086,16 +10086,16 @@
         <v>45903</v>
       </c>
       <c r="C420" t="n">
-        <v>97.63963317871094</v>
+        <v>97.6396484375</v>
       </c>
       <c r="D420" t="n">
-        <v>97.63963317871094</v>
+        <v>97.6396484375</v>
       </c>
       <c r="E420" t="n">
-        <v>97.62990603829556</v>
+        <v>97.62992129556449</v>
       </c>
       <c r="F420" t="n">
-        <v>97.63476589868615</v>
+        <v>97.63478115671457</v>
       </c>
       <c r="G420" t="n">
         <v>14296000</v>
@@ -10109,16 +10109,16 @@
         <v>45904</v>
       </c>
       <c r="C421" t="n">
-        <v>97.65908050537109</v>
+        <v>97.65908813476562</v>
       </c>
       <c r="D421" t="n">
-        <v>97.65908050537109</v>
+        <v>97.65908813476562</v>
       </c>
       <c r="E421" t="n">
-        <v>97.64936078454357</v>
+        <v>97.64936841317878</v>
       </c>
       <c r="F421" t="n">
-        <v>97.65422064495733</v>
+        <v>97.65422827397219</v>
       </c>
       <c r="G421" t="n">
         <v>11300200</v>
@@ -10132,16 +10132,16 @@
         <v>45905</v>
       </c>
       <c r="C422" t="n">
-        <v>97.67855072021484</v>
+        <v>97.67852783203125</v>
       </c>
       <c r="D422" t="n">
-        <v>97.68827044262791</v>
+        <v>97.68824755216677</v>
       </c>
       <c r="E422" t="n">
-        <v>97.67855072021484</v>
+        <v>97.67852783203125</v>
       </c>
       <c r="F422" t="n">
-        <v>97.68827044262791</v>
+        <v>97.68824755216677</v>
       </c>
       <c r="G422" t="n">
         <v>15312000</v>
@@ -10155,16 +10155,16 @@
         <v>45908</v>
       </c>
       <c r="C423" t="n">
-        <v>97.70769500732422</v>
+        <v>97.70771026611328</v>
       </c>
       <c r="D423" t="n">
-        <v>97.70769500732422</v>
+        <v>97.70771026611328</v>
       </c>
       <c r="E423" t="n">
-        <v>97.6979678682344</v>
+        <v>97.69798312550439</v>
       </c>
       <c r="F423" t="n">
-        <v>97.70282772796271</v>
+        <v>97.70284298599168</v>
       </c>
       <c r="G423" t="n">
         <v>12715100</v>
@@ -10178,16 +10178,16 @@
         <v>45909</v>
       </c>
       <c r="C424" t="n">
-        <v>97.70769500732422</v>
+        <v>97.70771026611328</v>
       </c>
       <c r="D424" t="n">
-        <v>97.71742214641404</v>
+        <v>97.71743740672217</v>
       </c>
       <c r="E424" t="n">
-        <v>97.70769500732422</v>
+        <v>97.70771026611328</v>
       </c>
       <c r="F424" t="n">
-        <v>97.71742214641404</v>
+        <v>97.71743740672217</v>
       </c>
       <c r="G424" t="n">
         <v>11005500</v>
@@ -10201,16 +10201,16 @@
         <v>45910</v>
       </c>
       <c r="C425" t="n">
-        <v>97.71743774414062</v>
+        <v>97.71744537353516</v>
       </c>
       <c r="D425" t="n">
-        <v>97.72715746514874</v>
+        <v>97.72716509530215</v>
       </c>
       <c r="E425" t="n">
-        <v>97.71743774414062</v>
+        <v>97.71744537353516</v>
       </c>
       <c r="F425" t="n">
-        <v>97.71743774414062</v>
+        <v>97.71744537353516</v>
       </c>
       <c r="G425" t="n">
         <v>9356600</v>
@@ -10224,16 +10224,16 @@
         <v>45911</v>
       </c>
       <c r="C426" t="n">
-        <v>97.73688507080078</v>
+        <v>97.73687744140625</v>
       </c>
       <c r="D426" t="n">
-        <v>97.73688507080078</v>
+        <v>97.73687744140625</v>
       </c>
       <c r="E426" t="n">
-        <v>97.72715793011203</v>
+        <v>97.7271503014768</v>
       </c>
       <c r="F426" t="n">
-        <v>97.7320252102736</v>
+        <v>97.73201758125843</v>
       </c>
       <c r="G426" t="n">
         <v>9136600</v>
@@ -10247,16 +10247,16 @@
         <v>45912</v>
       </c>
       <c r="C427" t="n">
-        <v>97.76605224609375</v>
+        <v>97.76604461669922</v>
       </c>
       <c r="D427" t="n">
-        <v>97.77577938610324</v>
+        <v>97.77577175594963</v>
       </c>
       <c r="E427" t="n">
-        <v>97.76605224609375</v>
+        <v>97.76604461669922</v>
       </c>
       <c r="F427" t="n">
-        <v>97.76605224609375</v>
+        <v>97.76604461669922</v>
       </c>
       <c r="G427" t="n">
         <v>10482000</v>
@@ -10270,16 +10270,16 @@
         <v>45915</v>
       </c>
       <c r="C428" t="n">
-        <v>97.76605224609375</v>
+        <v>97.76604461669922</v>
       </c>
       <c r="D428" t="n">
-        <v>97.77577938610324</v>
+        <v>97.77577175594963</v>
       </c>
       <c r="E428" t="n">
-        <v>97.76605224609375</v>
+        <v>97.76604461669922</v>
       </c>
       <c r="F428" t="n">
-        <v>97.76605224609375</v>
+        <v>97.76604461669922</v>
       </c>
       <c r="G428" t="n">
         <v>15288300</v>
@@ -10293,16 +10293,16 @@
         <v>45916</v>
       </c>
       <c r="C429" t="n">
-        <v>97.78551483154297</v>
+        <v>97.78549957275391</v>
       </c>
       <c r="D429" t="n">
-        <v>97.79523455274413</v>
+        <v>97.79521929243838</v>
       </c>
       <c r="E429" t="n">
-        <v>97.78551483154297</v>
+        <v>97.78549957275391</v>
       </c>
       <c r="F429" t="n">
-        <v>97.78551483154297</v>
+        <v>97.78549957275391</v>
       </c>
       <c r="G429" t="n">
         <v>11551900</v>
@@ -10339,16 +10339,16 @@
         <v>45918</v>
       </c>
       <c r="C431" t="n">
-        <v>97.81467437744141</v>
+        <v>97.81468200683594</v>
       </c>
       <c r="D431" t="n">
-        <v>97.81467437744141</v>
+        <v>97.81468200683594</v>
       </c>
       <c r="E431" t="n">
-        <v>97.8049472380434</v>
+        <v>97.80495486667922</v>
       </c>
       <c r="F431" t="n">
-        <v>97.81467437744141</v>
+        <v>97.81468200683594</v>
       </c>
       <c r="G431" t="n">
         <v>13414500</v>
@@ -10362,16 +10362,16 @@
         <v>45919</v>
       </c>
       <c r="C432" t="n">
-        <v>97.85359191894531</v>
+        <v>97.85357666015625</v>
       </c>
       <c r="D432" t="n">
-        <v>97.85359191894531</v>
+        <v>97.85357666015625</v>
       </c>
       <c r="E432" t="n">
-        <v>97.84386477791671</v>
+        <v>97.84384952064445</v>
       </c>
       <c r="F432" t="n">
-        <v>97.84386477791671</v>
+        <v>97.84384952064445</v>
       </c>
       <c r="G432" t="n">
         <v>11174000</v>
@@ -10385,16 +10385,16 @@
         <v>45922</v>
       </c>
       <c r="C433" t="n">
-        <v>97.85359191894531</v>
+        <v>97.85357666015625</v>
       </c>
       <c r="D433" t="n">
-        <v>97.86331164033926</v>
+        <v>97.86329638003455</v>
       </c>
       <c r="E433" t="n">
-        <v>97.85359191894531</v>
+        <v>97.85357666015625</v>
       </c>
       <c r="F433" t="n">
-        <v>97.85359191894531</v>
+        <v>97.85357666015625</v>
       </c>
       <c r="G433" t="n">
         <v>12279500</v>
@@ -10408,16 +10408,16 @@
         <v>45923</v>
       </c>
       <c r="C434" t="n">
-        <v>97.87303161621094</v>
+        <v>97.87302398681641</v>
       </c>
       <c r="D434" t="n">
-        <v>97.87303161621094</v>
+        <v>97.87302398681641</v>
       </c>
       <c r="E434" t="n">
-        <v>97.86330447589445</v>
+        <v>97.86329684725817</v>
       </c>
       <c r="F434" t="n">
-        <v>97.86817175586975</v>
+        <v>97.86816412685405</v>
       </c>
       <c r="G434" t="n">
         <v>11191700</v>
@@ -10454,16 +10454,16 @@
         <v>45925</v>
       </c>
       <c r="C436" t="n">
-        <v>97.89247894287109</v>
+        <v>97.89248657226562</v>
       </c>
       <c r="D436" t="n">
-        <v>97.89247894287109</v>
+        <v>97.89248657226562</v>
       </c>
       <c r="E436" t="n">
-        <v>97.88275180324558</v>
+        <v>97.88275943188202</v>
       </c>
       <c r="F436" t="n">
-        <v>97.88275180324558</v>
+        <v>97.88275943188202</v>
       </c>
       <c r="G436" t="n">
         <v>10549100</v>
@@ -10477,16 +10477,16 @@
         <v>45926</v>
       </c>
       <c r="C437" t="n">
-        <v>97.92165374755859</v>
+        <v>97.92166137695312</v>
       </c>
       <c r="D437" t="n">
-        <v>97.92165374755859</v>
+        <v>97.92166137695312</v>
       </c>
       <c r="E437" t="n">
-        <v>97.91192660785308</v>
+        <v>97.91193423648973</v>
       </c>
       <c r="F437" t="n">
-        <v>97.91192660785308</v>
+        <v>97.91193423648973</v>
       </c>
       <c r="G437" t="n">
         <v>10688600</v>
@@ -10500,16 +10500,16 @@
         <v>45929</v>
       </c>
       <c r="C438" t="n">
-        <v>97.93138122558594</v>
+        <v>97.93137359619141</v>
       </c>
       <c r="D438" t="n">
-        <v>97.93138122558594</v>
+        <v>97.93137359619141</v>
       </c>
       <c r="E438" t="n">
-        <v>97.92166150474409</v>
+        <v>97.92165387610677</v>
       </c>
       <c r="F438" t="n">
-        <v>97.93138122558594</v>
+        <v>97.93137359619141</v>
       </c>
       <c r="G438" t="n">
         <v>13580800</v>
@@ -10523,16 +10523,16 @@
         <v>45930</v>
       </c>
       <c r="C439" t="n">
-        <v>97.93138122558594</v>
+        <v>97.93137359619141</v>
       </c>
       <c r="D439" t="n">
-        <v>97.94110836606202</v>
+        <v>97.94110073590969</v>
       </c>
       <c r="E439" t="n">
-        <v>97.93138122558594</v>
+        <v>97.93137359619141</v>
       </c>
       <c r="F439" t="n">
-        <v>97.9362485056411</v>
+        <v>97.93624087586737</v>
       </c>
       <c r="G439" t="n">
         <v>22909500</v>
@@ -10569,16 +10569,16 @@
         <v>45932</v>
       </c>
       <c r="C441" t="n">
-        <v>97.95772552490234</v>
+        <v>97.95771789550781</v>
       </c>
       <c r="D441" t="n">
-        <v>97.96748629938267</v>
+        <v>97.96747866922793</v>
       </c>
       <c r="E441" t="n">
-        <v>97.95772552490234</v>
+        <v>97.95771789550781</v>
       </c>
       <c r="F441" t="n">
-        <v>97.96748629938267</v>
+        <v>97.96747866922793</v>
       </c>
       <c r="G441" t="n">
         <v>12870100</v>
@@ -10592,16 +10592,16 @@
         <v>45933</v>
       </c>
       <c r="C442" t="n">
-        <v>97.99675750732422</v>
+        <v>97.99677276611328</v>
       </c>
       <c r="D442" t="n">
-        <v>97.99675750732422</v>
+        <v>97.99677276611328</v>
       </c>
       <c r="E442" t="n">
-        <v>97.98700417849862</v>
+        <v>97.98701943576903</v>
       </c>
       <c r="F442" t="n">
-        <v>97.99675750732422</v>
+        <v>97.99677276611328</v>
       </c>
       <c r="G442" t="n">
         <v>13837400</v>
@@ -10615,16 +10615,16 @@
         <v>45936</v>
       </c>
       <c r="C443" t="n">
-        <v>97.99675750732422</v>
+        <v>97.99677276611328</v>
       </c>
       <c r="D443" t="n">
-        <v>98.00651828143899</v>
+        <v>98.00653354174787</v>
       </c>
       <c r="E443" t="n">
-        <v>97.99675750732422</v>
+        <v>97.99677276611328</v>
       </c>
       <c r="F443" t="n">
-        <v>98.00651828143899</v>
+        <v>98.00653354174787</v>
       </c>
       <c r="G443" t="n">
         <v>13944300</v>
@@ -10661,16 +10661,16 @@
         <v>45938</v>
       </c>
       <c r="C445" t="n">
-        <v>98.02604675292969</v>
+        <v>98.02603149414062</v>
       </c>
       <c r="D445" t="n">
-        <v>98.02604675292969</v>
+        <v>98.02603149414062</v>
       </c>
       <c r="E445" t="n">
-        <v>98.01629342267447</v>
+        <v>98.01627816540361</v>
       </c>
       <c r="F445" t="n">
-        <v>98.02604675292969</v>
+        <v>98.02603149414062</v>
       </c>
       <c r="G445" t="n">
         <v>16811200</v>
@@ -10684,16 +10684,16 @@
         <v>45939</v>
       </c>
       <c r="C446" t="n">
-        <v>98.03579711914062</v>
+        <v>98.03580474853516</v>
       </c>
       <c r="D446" t="n">
-        <v>98.04555789364973</v>
+        <v>98.04556552380387</v>
       </c>
       <c r="E446" t="n">
-        <v>98.02603634463152</v>
+        <v>98.02604397326645</v>
       </c>
       <c r="F446" t="n">
-        <v>98.04555789364973</v>
+        <v>98.04556552380387</v>
       </c>
       <c r="G446" t="n">
         <v>15718900</v>
@@ -10707,16 +10707,16 @@
         <v>45940</v>
       </c>
       <c r="C447" t="n">
-        <v>98.08460235595703</v>
+        <v>98.08458709716797</v>
       </c>
       <c r="D447" t="n">
-        <v>98.08460235595703</v>
+        <v>98.08458709716797</v>
       </c>
       <c r="E447" t="n">
-        <v>98.06508080518547</v>
+        <v>98.06506554943334</v>
       </c>
       <c r="F447" t="n">
-        <v>98.07484158057125</v>
+        <v>98.07482632330066</v>
       </c>
       <c r="G447" t="n">
         <v>18966600</v>
@@ -10753,16 +10753,16 @@
         <v>45944</v>
       </c>
       <c r="C449" t="n">
-        <v>98.08460235595703</v>
+        <v>98.08458709716797</v>
       </c>
       <c r="D449" t="n">
-        <v>98.09435568605265</v>
+        <v>98.0943404257463</v>
       </c>
       <c r="E449" t="n">
-        <v>98.08460235595703</v>
+        <v>98.08458709716797</v>
       </c>
       <c r="F449" t="n">
-        <v>98.08460235595703</v>
+        <v>98.08458709716797</v>
       </c>
       <c r="G449" t="n">
         <v>13475000</v>
@@ -10776,16 +10776,16 @@
         <v>45945</v>
       </c>
       <c r="C450" t="n">
-        <v>98.10411071777344</v>
+        <v>98.10410308837891</v>
       </c>
       <c r="D450" t="n">
-        <v>98.10411071777344</v>
+        <v>98.10410308837891</v>
       </c>
       <c r="E450" t="n">
-        <v>98.09434994295911</v>
+        <v>98.09434231432367</v>
       </c>
       <c r="F450" t="n">
-        <v>98.10411071777344</v>
+        <v>98.10410308837891</v>
       </c>
       <c r="G450" t="n">
         <v>11069100</v>
@@ -10799,16 +10799,16 @@
         <v>45946</v>
       </c>
       <c r="C451" t="n">
-        <v>98.11387634277344</v>
+        <v>98.11386871337891</v>
       </c>
       <c r="D451" t="n">
-        <v>98.11387634277344</v>
+        <v>98.11386871337891</v>
       </c>
       <c r="E451" t="n">
-        <v>98.1041155674766</v>
+        <v>98.10410793884108</v>
       </c>
       <c r="F451" t="n">
-        <v>98.11387634277344</v>
+        <v>98.11386871337891</v>
       </c>
       <c r="G451" t="n">
         <v>12394500</v>
@@ -10822,16 +10822,16 @@
         <v>45947</v>
       </c>
       <c r="C452" t="n">
-        <v>98.14315032958984</v>
+        <v>98.14314270019531</v>
       </c>
       <c r="D452" t="n">
-        <v>98.14315032958984</v>
+        <v>98.14314270019531</v>
       </c>
       <c r="E452" t="n">
-        <v>98.13338955438189</v>
+        <v>98.13338192574615</v>
       </c>
       <c r="F452" t="n">
-        <v>98.13827366463087</v>
+        <v>98.13826603561544</v>
       </c>
       <c r="G452" t="n">
         <v>14603500</v>
@@ -10845,16 +10845,16 @@
         <v>45950</v>
       </c>
       <c r="C453" t="n">
-        <v>98.15291595458984</v>
+        <v>98.15290832519531</v>
       </c>
       <c r="D453" t="n">
-        <v>98.15291595458984</v>
+        <v>98.15290832519531</v>
       </c>
       <c r="E453" t="n">
-        <v>98.14315517889962</v>
+        <v>98.14314755026379</v>
       </c>
       <c r="F453" t="n">
-        <v>98.15291595458984</v>
+        <v>98.15290832519531</v>
       </c>
       <c r="G453" t="n">
         <v>16129100</v>
@@ -10868,16 +10868,16 @@
         <v>45951</v>
       </c>
       <c r="C454" t="n">
-        <v>98.17241668701172</v>
+        <v>98.17242431640625</v>
       </c>
       <c r="D454" t="n">
-        <v>98.17241668701172</v>
+        <v>98.17242431640625</v>
       </c>
       <c r="E454" t="n">
-        <v>98.16265591265116</v>
+        <v>98.16266354128715</v>
       </c>
       <c r="F454" t="n">
-        <v>98.16265591265116</v>
+        <v>98.16266354128715</v>
       </c>
       <c r="G454" t="n">
         <v>12061900</v>
@@ -10937,16 +10937,16 @@
         <v>45954</v>
       </c>
       <c r="C457" t="n">
-        <v>98.22121429443359</v>
+        <v>98.22122192382812</v>
       </c>
       <c r="D457" t="n">
-        <v>98.22121429443359</v>
+        <v>98.22122192382812</v>
       </c>
       <c r="E457" t="n">
-        <v>98.21145351995568</v>
+        <v>98.21146114859204</v>
       </c>
       <c r="F457" t="n">
-        <v>98.22121429443359</v>
+        <v>98.22122192382812</v>
       </c>
       <c r="G457" t="n">
         <v>12382000</v>
@@ -10983,16 +10983,16 @@
         <v>45958</v>
       </c>
       <c r="C459" t="n">
-        <v>98.24072265625</v>
+        <v>98.24073028564453</v>
       </c>
       <c r="D459" t="n">
-        <v>98.25048343015742</v>
+        <v>98.25049106030998</v>
       </c>
       <c r="E459" t="n">
-        <v>98.24072265625</v>
+        <v>98.24073028564453</v>
       </c>
       <c r="F459" t="n">
-        <v>98.24072265625</v>
+        <v>98.24073028564453</v>
       </c>
       <c r="G459" t="n">
         <v>11134700</v>
@@ -11006,16 +11006,16 @@
         <v>45959</v>
       </c>
       <c r="C460" t="n">
-        <v>98.25048065185547</v>
+        <v>98.25047302246094</v>
       </c>
       <c r="D460" t="n">
-        <v>98.26024142548688</v>
+        <v>98.2602337953344</v>
       </c>
       <c r="E460" t="n">
-        <v>98.25048065185547</v>
+        <v>98.25047302246094</v>
       </c>
       <c r="F460" t="n">
-        <v>98.26024142548688</v>
+        <v>98.2602337953344</v>
       </c>
       <c r="G460" t="n">
         <v>14177700</v>
@@ -11052,16 +11052,16 @@
         <v>45961</v>
       </c>
       <c r="C462" t="n">
-        <v>98.28952789306641</v>
+        <v>98.28952026367188</v>
       </c>
       <c r="D462" t="n">
-        <v>98.29928866784897</v>
+        <v>98.29928103769679</v>
       </c>
       <c r="E462" t="n">
-        <v>98.28952789306641</v>
+        <v>98.28952026367188</v>
       </c>
       <c r="F462" t="n">
-        <v>98.29440455781285</v>
+        <v>98.29439692803977</v>
       </c>
       <c r="G462" t="n">
         <v>23254100</v>
@@ -11075,16 +11075,16 @@
         <v>45964</v>
       </c>
       <c r="C463" t="n">
-        <v>98.31693267822266</v>
+        <v>98.31695556640625</v>
       </c>
       <c r="D463" t="n">
-        <v>98.31693267822266</v>
+        <v>98.31695556640625</v>
       </c>
       <c r="E463" t="n">
-        <v>98.30713806328775</v>
+        <v>98.30716094919116</v>
       </c>
       <c r="F463" t="n">
-        <v>98.31203163520412</v>
+        <v>98.31205452224675</v>
       </c>
       <c r="G463" t="n">
         <v>27049200</v>
@@ -11098,16 +11098,16 @@
         <v>45965</v>
       </c>
       <c r="C464" t="n">
-        <v>98.31693267822266</v>
+        <v>98.31695556640625</v>
       </c>
       <c r="D464" t="n">
-        <v>98.31693267822266</v>
+        <v>98.31695556640625</v>
       </c>
       <c r="E464" t="n">
-        <v>98.31203163520412</v>
+        <v>98.31205452224675</v>
       </c>
       <c r="F464" t="n">
-        <v>98.31693267822266</v>
+        <v>98.31695556640625</v>
       </c>
       <c r="G464" t="n">
         <v>15707500</v>
@@ -11121,16 +11121,16 @@
         <v>45966</v>
       </c>
       <c r="C465" t="n">
-        <v>98.33652496337891</v>
+        <v>98.33653259277344</v>
       </c>
       <c r="D465" t="n">
-        <v>98.33652496337891</v>
+        <v>98.33653259277344</v>
       </c>
       <c r="E465" t="n">
-        <v>98.32673781849851</v>
+        <v>98.3267454471337</v>
       </c>
       <c r="F465" t="n">
-        <v>98.32673781849851</v>
+        <v>98.3267454471337</v>
       </c>
       <c r="G465" t="n">
         <v>11335000</v>
@@ -11144,16 +11144,16 @@
         <v>45967</v>
       </c>
       <c r="C466" t="n">
-        <v>98.34632873535156</v>
+        <v>98.3463134765625</v>
       </c>
       <c r="D466" t="n">
-        <v>98.34632873535156</v>
+        <v>98.3463134765625</v>
       </c>
       <c r="E466" t="n">
-        <v>98.33653411845633</v>
+        <v>98.33651886118693</v>
       </c>
       <c r="F466" t="n">
-        <v>98.34632873535156</v>
+        <v>98.3463134765625</v>
       </c>
       <c r="G466" t="n">
         <v>16658100</v>
@@ -11190,16 +11190,16 @@
         <v>45971</v>
       </c>
       <c r="C468" t="n">
-        <v>98.385498046875</v>
+        <v>98.38549041748047</v>
       </c>
       <c r="D468" t="n">
-        <v>98.39529266360249</v>
+        <v>98.39528503344843</v>
       </c>
       <c r="E468" t="n">
-        <v>98.385498046875</v>
+        <v>98.38549041748047</v>
       </c>
       <c r="F468" t="n">
-        <v>98.39529266360249</v>
+        <v>98.39528503344843</v>
       </c>
       <c r="G468" t="n">
         <v>14121900</v>
@@ -11213,16 +11213,16 @@
         <v>45972</v>
       </c>
       <c r="C469" t="n">
-        <v>98.39528656005859</v>
+        <v>98.39529418945312</v>
       </c>
       <c r="D469" t="n">
-        <v>98.39528656005859</v>
+        <v>98.39529418945312</v>
       </c>
       <c r="E469" t="n">
-        <v>98.38549194393867</v>
+        <v>98.38549957257375</v>
       </c>
       <c r="F469" t="n">
-        <v>98.39528656005859</v>
+        <v>98.39529418945312</v>
       </c>
       <c r="G469" t="n">
         <v>8697800</v>
@@ -11236,16 +11236,16 @@
         <v>45973</v>
       </c>
       <c r="C470" t="n">
-        <v>98.40506744384766</v>
+        <v>98.40507507324219</v>
       </c>
       <c r="D470" t="n">
-        <v>98.40506744384766</v>
+        <v>98.40507507324219</v>
       </c>
       <c r="E470" t="n">
-        <v>98.39528029945352</v>
+        <v>98.39528792808926</v>
       </c>
       <c r="F470" t="n">
-        <v>98.39528029945352</v>
+        <v>98.39528792808926</v>
       </c>
       <c r="G470" t="n">
         <v>9067200</v>
@@ -11259,16 +11259,16 @@
         <v>45974</v>
       </c>
       <c r="C471" t="n">
-        <v>98.41487121582031</v>
+        <v>98.41486358642578</v>
       </c>
       <c r="D471" t="n">
-        <v>98.41487121582031</v>
+        <v>98.41486358642578</v>
       </c>
       <c r="E471" t="n">
-        <v>98.4050765994123</v>
+        <v>98.40506897077708</v>
       </c>
       <c r="F471" t="n">
-        <v>98.4050765994123</v>
+        <v>98.40506897077708</v>
       </c>
       <c r="G471" t="n">
         <v>11255600</v>
@@ -11282,16 +11282,16 @@
         <v>45975</v>
       </c>
       <c r="C472" t="n">
-        <v>98.44424438476562</v>
+        <v>98.44423675537109</v>
       </c>
       <c r="D472" t="n">
-        <v>98.44424438476562</v>
+        <v>98.44423675537109</v>
       </c>
       <c r="E472" t="n">
-        <v>98.43444976867691</v>
+        <v>98.43444214004147</v>
       </c>
       <c r="F472" t="n">
-        <v>98.44424438476562</v>
+        <v>98.44423675537109</v>
       </c>
       <c r="G472" t="n">
         <v>13522500</v>
@@ -11374,16 +11374,16 @@
         <v>45981</v>
       </c>
       <c r="C476" t="n">
-        <v>98.49321746826172</v>
+        <v>98.49320983886719</v>
       </c>
       <c r="D476" t="n">
-        <v>98.49321746826172</v>
+        <v>98.49320983886719</v>
       </c>
       <c r="E476" t="n">
-        <v>98.47362823459777</v>
+        <v>98.47362060672063</v>
       </c>
       <c r="F476" t="n">
-        <v>98.47362823459777</v>
+        <v>98.47362060672063</v>
       </c>
       <c r="G476" t="n">
         <v>15261700</v>
@@ -11397,16 +11397,16 @@
         <v>45982</v>
       </c>
       <c r="C477" t="n">
-        <v>98.51277923583984</v>
+        <v>98.51279449462891</v>
       </c>
       <c r="D477" t="n">
-        <v>98.51277923583984</v>
+        <v>98.51279449462891</v>
       </c>
       <c r="E477" t="n">
-        <v>98.50298462099586</v>
+        <v>98.50299987826783</v>
       </c>
       <c r="F477" t="n">
-        <v>98.51277923583984</v>
+        <v>98.51279449462891</v>
       </c>
       <c r="G477" t="n">
         <v>16446900</v>
@@ -11443,16 +11443,16 @@
         <v>45986</v>
       </c>
       <c r="C479" t="n">
-        <v>98.54216766357422</v>
+        <v>98.54216003417969</v>
       </c>
       <c r="D479" t="n">
-        <v>98.54216766357422</v>
+        <v>98.54216003417969</v>
       </c>
       <c r="E479" t="n">
-        <v>98.53238051863511</v>
+        <v>98.53237288999831</v>
       </c>
       <c r="F479" t="n">
-        <v>98.54216766357422</v>
+        <v>98.54216003417969</v>
       </c>
       <c r="G479" t="n">
         <v>19115000</v>
@@ -11466,16 +11466,16 @@
         <v>45987</v>
       </c>
       <c r="C480" t="n">
-        <v>98.55196380615234</v>
+        <v>98.55195617675781</v>
       </c>
       <c r="D480" t="n">
-        <v>98.56175842234617</v>
+        <v>98.56175079219341</v>
       </c>
       <c r="E480" t="n">
-        <v>98.55196380615234</v>
+        <v>98.55195617675781</v>
       </c>
       <c r="F480" t="n">
-        <v>98.55196380615234</v>
+        <v>98.55195617675781</v>
       </c>
       <c r="G480" t="n">
         <v>11948500</v>
@@ -11489,16 +11489,16 @@
         <v>45989</v>
       </c>
       <c r="C481" t="n">
-        <v>98.58132934570312</v>
+        <v>98.58133697509766</v>
       </c>
       <c r="D481" t="n">
-        <v>98.59112396082016</v>
+        <v>98.59113159097269</v>
       </c>
       <c r="E481" t="n">
-        <v>98.5715422016884</v>
+        <v>98.57154983032548</v>
       </c>
       <c r="F481" t="n">
-        <v>98.58132934570312</v>
+        <v>98.58133697509766</v>
       </c>
       <c r="G481" t="n">
         <v>24417500</v>
@@ -11512,16 +11512,16 @@
         <v>45992</v>
       </c>
       <c r="C482" t="n">
-        <v>98.60391235351562</v>
+        <v>98.60392761230469</v>
       </c>
       <c r="D482" t="n">
-        <v>98.60391235351562</v>
+        <v>98.60392761230469</v>
       </c>
       <c r="E482" t="n">
-        <v>98.59409468562329</v>
+        <v>98.59410994289308</v>
       </c>
       <c r="F482" t="n">
-        <v>98.60391235351562</v>
+        <v>98.60392761230469</v>
       </c>
       <c r="G482" t="n">
         <v>29025600</v>
@@ -11535,16 +11535,16 @@
         <v>45993</v>
       </c>
       <c r="C483" t="n">
-        <v>98.62357330322266</v>
+        <v>98.62359619140625</v>
       </c>
       <c r="D483" t="n">
-        <v>98.62357330322266</v>
+        <v>98.62359619140625</v>
       </c>
       <c r="E483" t="n">
-        <v>98.61374813986885</v>
+        <v>98.61377102577225</v>
       </c>
       <c r="F483" t="n">
-        <v>98.61374813986885</v>
+        <v>98.61377102577225</v>
       </c>
       <c r="G483" t="n">
         <v>14362600</v>
@@ -11604,16 +11604,16 @@
         <v>45996</v>
       </c>
       <c r="C486" t="n">
-        <v>98.68251800537109</v>
+        <v>98.68252563476562</v>
       </c>
       <c r="D486" t="n">
-        <v>98.68251800537109</v>
+        <v>98.68252563476562</v>
       </c>
       <c r="E486" t="n">
-        <v>98.67269284115001</v>
+        <v>98.67270046978493</v>
       </c>
       <c r="F486" t="n">
-        <v>98.67269284115001</v>
+        <v>98.67270046978493</v>
       </c>
       <c r="G486" t="n">
         <v>17918100</v>
@@ -11627,16 +11627,16 @@
         <v>45999</v>
       </c>
       <c r="C487" t="n">
-        <v>98.68251800537109</v>
+        <v>98.68252563476562</v>
       </c>
       <c r="D487" t="n">
-        <v>98.68251800537109</v>
+        <v>98.68252563476562</v>
       </c>
       <c r="E487" t="n">
-        <v>98.67269284115001</v>
+        <v>98.67270046978493</v>
       </c>
       <c r="F487" t="n">
-        <v>98.68251800537109</v>
+        <v>98.68252563476562</v>
       </c>
       <c r="G487" t="n">
         <v>16657900</v>
@@ -11650,16 +11650,16 @@
         <v>46000</v>
       </c>
       <c r="C488" t="n">
-        <v>98.69235229492188</v>
+        <v>98.69233703613281</v>
       </c>
       <c r="D488" t="n">
-        <v>98.69726113028409</v>
+        <v>98.69724587073607</v>
       </c>
       <c r="E488" t="n">
-        <v>98.69235229492188</v>
+        <v>98.69233703613281</v>
       </c>
       <c r="F488" t="n">
-        <v>98.69235229492188</v>
+        <v>98.69233703613281</v>
       </c>
       <c r="G488" t="n">
         <v>11016400</v>
@@ -11673,16 +11673,16 @@
         <v>46001</v>
       </c>
       <c r="C489" t="n">
-        <v>98.69235229492188</v>
+        <v>98.69233703613281</v>
       </c>
       <c r="D489" t="n">
-        <v>98.70217746005143</v>
+        <v>98.7021621997433</v>
       </c>
       <c r="E489" t="n">
-        <v>98.69235229492188</v>
+        <v>98.69233703613281</v>
       </c>
       <c r="F489" t="n">
-        <v>98.70217746005143</v>
+        <v>98.7021621997433</v>
       </c>
       <c r="G489" t="n">
         <v>12234900</v>
@@ -11696,16 +11696,16 @@
         <v>46002</v>
       </c>
       <c r="C490" t="n">
-        <v>98.71198272705078</v>
+        <v>98.71199035644531</v>
       </c>
       <c r="D490" t="n">
-        <v>98.72180789094574</v>
+        <v>98.72181552109964</v>
       </c>
       <c r="E490" t="n">
-        <v>98.71198272705078</v>
+        <v>98.71199035644531</v>
       </c>
       <c r="F490" t="n">
-        <v>98.71198272705078</v>
+        <v>98.71199035644531</v>
       </c>
       <c r="G490" t="n">
         <v>22343500</v>
@@ -11719,16 +11719,16 @@
         <v>46003</v>
       </c>
       <c r="C491" t="n">
-        <v>98.75127410888672</v>
+        <v>98.75126647949219</v>
       </c>
       <c r="D491" t="n">
-        <v>98.75127410888672</v>
+        <v>98.75126647949219</v>
       </c>
       <c r="E491" t="n">
-        <v>98.7414489451688</v>
+        <v>98.74144131653334</v>
       </c>
       <c r="F491" t="n">
-        <v>98.7414489451688</v>
+        <v>98.74144131653334</v>
       </c>
       <c r="G491" t="n">
         <v>13320200</v>
@@ -11742,16 +11742,16 @@
         <v>46006</v>
       </c>
       <c r="C492" t="n">
-        <v>98.75127410888672</v>
+        <v>98.75126647949219</v>
       </c>
       <c r="D492" t="n">
-        <v>98.76109927260465</v>
+        <v>98.76109164245103</v>
       </c>
       <c r="E492" t="n">
-        <v>98.75127410888672</v>
+        <v>98.75126647949219</v>
       </c>
       <c r="F492" t="n">
-        <v>98.75127410888672</v>
+        <v>98.75126647949219</v>
       </c>
       <c r="G492" t="n">
         <v>14767900</v>
@@ -11788,16 +11788,16 @@
         <v>46008</v>
       </c>
       <c r="C494" t="n">
-        <v>98.78075408935547</v>
+        <v>98.78074645996094</v>
       </c>
       <c r="D494" t="n">
-        <v>98.78075408935547</v>
+        <v>98.78074645996094</v>
       </c>
       <c r="E494" t="n">
-        <v>98.77093641885057</v>
+        <v>98.7709287902143</v>
       </c>
       <c r="F494" t="n">
-        <v>98.77093641885057</v>
+        <v>98.7709287902143</v>
       </c>
       <c r="G494" t="n">
         <v>13788200</v>
@@ -11811,16 +11811,16 @@
         <v>46009</v>
       </c>
       <c r="C495" t="n">
-        <v>98.78075408935547</v>
+        <v>98.78074645996094</v>
       </c>
       <c r="D495" t="n">
-        <v>98.79057925426535</v>
+        <v>98.79057162411196</v>
       </c>
       <c r="E495" t="n">
-        <v>98.78075408935547</v>
+        <v>98.78074645996094</v>
       </c>
       <c r="F495" t="n">
-        <v>98.79057925426535</v>
+        <v>98.79057162411196</v>
       </c>
       <c r="G495" t="n">
         <v>20890600</v>
@@ -11834,16 +11834,16 @@
         <v>46010</v>
       </c>
       <c r="C496" t="n">
-        <v>98.82312774658203</v>
+        <v>98.8231201171875</v>
       </c>
       <c r="D496" t="n">
-        <v>98.82312774658203</v>
+        <v>98.8231201171875</v>
       </c>
       <c r="E496" t="n">
-        <v>98.81327092170693</v>
+        <v>98.81326329307338</v>
       </c>
       <c r="F496" t="n">
-        <v>98.82312774658203</v>
+        <v>98.8231201171875</v>
       </c>
       <c r="G496" t="n">
         <v>18203600</v>
@@ -11857,16 +11857,16 @@
         <v>46013</v>
       </c>
       <c r="C497" t="n">
-        <v>98.82312774658203</v>
+        <v>98.8231201171875</v>
       </c>
       <c r="D497" t="n">
-        <v>98.83298457145713</v>
+        <v>98.83297694130162</v>
       </c>
       <c r="E497" t="n">
-        <v>98.82312774658203</v>
+        <v>98.8231201171875</v>
       </c>
       <c r="F497" t="n">
-        <v>98.82312774658203</v>
+        <v>98.8231201171875</v>
       </c>
       <c r="G497" t="n">
         <v>17890900</v>
@@ -11903,16 +11903,16 @@
         <v>46015</v>
       </c>
       <c r="C499" t="n">
-        <v>98.85268402099609</v>
+        <v>98.85269165039062</v>
       </c>
       <c r="D499" t="n">
-        <v>98.86254084520495</v>
+        <v>98.86254847536023</v>
       </c>
       <c r="E499" t="n">
-        <v>98.85268402099609</v>
+        <v>98.85269165039062</v>
       </c>
       <c r="F499" t="n">
-        <v>98.86254084520495</v>
+        <v>98.86254847536023</v>
       </c>
       <c r="G499" t="n">
         <v>7791300</v>
@@ -11926,16 +11926,16 @@
         <v>46017</v>
       </c>
       <c r="C500" t="n">
-        <v>98.88225555419922</v>
+        <v>98.88224792480469</v>
       </c>
       <c r="D500" t="n">
-        <v>98.88718772600853</v>
+        <v>98.88718009623345</v>
       </c>
       <c r="E500" t="n">
-        <v>98.88225555419922</v>
+        <v>98.88224792480469</v>
       </c>
       <c r="F500" t="n">
-        <v>98.88225555419922</v>
+        <v>98.88224792480469</v>
       </c>
       <c r="G500" t="n">
         <v>12664300</v>
@@ -11949,16 +11949,16 @@
         <v>46020</v>
       </c>
       <c r="C501" t="n">
-        <v>98.90195465087891</v>
+        <v>98.90196228027344</v>
       </c>
       <c r="D501" t="n">
-        <v>98.90195465087891</v>
+        <v>98.90196228027344</v>
       </c>
       <c r="E501" t="n">
-        <v>98.8920978272653</v>
+        <v>98.89210545589947</v>
       </c>
       <c r="F501" t="n">
-        <v>98.8920978272653</v>
+        <v>98.89210545589947</v>
       </c>
       <c r="G501" t="n">
         <v>17350200</v>
@@ -11995,16 +11995,16 @@
         <v>46022</v>
       </c>
       <c r="C503" t="n">
-        <v>98.92166900634766</v>
+        <v>98.92166137695312</v>
       </c>
       <c r="D503" t="n">
-        <v>98.931525830781</v>
+        <v>98.93151820062626</v>
       </c>
       <c r="E503" t="n">
-        <v>98.92166900634766</v>
+        <v>98.92166137695312</v>
       </c>
       <c r="F503" t="n">
-        <v>98.931525830781</v>
+        <v>98.93151820062626</v>
       </c>
       <c r="G503" t="n">
         <v>13910900</v>
@@ -12133,16 +12133,16 @@
         <v>46031</v>
       </c>
       <c r="C509" t="n">
-        <v>99.0103759765625</v>
+        <v>99.01036834716797</v>
       </c>
       <c r="D509" t="n">
-        <v>99.02023280204986</v>
+        <v>99.0202251718958</v>
       </c>
       <c r="E509" t="n">
-        <v>99.0103759765625</v>
+        <v>99.01036834716797</v>
       </c>
       <c r="F509" t="n">
-        <v>99.02023280204986</v>
+        <v>99.0202251718958</v>
       </c>
       <c r="G509" t="n">
         <v>15053500</v>
@@ -12156,16 +12156,16 @@
         <v>46034</v>
       </c>
       <c r="C510" t="n">
-        <v>99.03006744384766</v>
+        <v>99.03008270263672</v>
       </c>
       <c r="D510" t="n">
-        <v>99.03006744384766</v>
+        <v>99.03008270263672</v>
       </c>
       <c r="E510" t="n">
-        <v>99.02021813837376</v>
+        <v>99.02023339564522</v>
       </c>
       <c r="F510" t="n">
-        <v>99.02021813837376</v>
+        <v>99.02023339564522</v>
       </c>
       <c r="G510" t="n">
         <v>14819400</v>
@@ -12179,16 +12179,16 @@
         <v>46035</v>
       </c>
       <c r="C511" t="n">
-        <v>99.03993225097656</v>
+        <v>99.03992462158203</v>
       </c>
       <c r="D511" t="n">
-        <v>99.03993225097656</v>
+        <v>99.03992462158203</v>
       </c>
       <c r="E511" t="n">
-        <v>99.03007542615437</v>
+        <v>99.03006779751914</v>
       </c>
       <c r="F511" t="n">
-        <v>99.03007542615437</v>
+        <v>99.03006779751914</v>
       </c>
       <c r="G511" t="n">
         <v>14163000</v>
@@ -12248,16 +12248,16 @@
         <v>46038</v>
       </c>
       <c r="C514" t="n">
-        <v>99.09906005859375</v>
+        <v>99.09905242919922</v>
       </c>
       <c r="D514" t="n">
-        <v>99.09906005859375</v>
+        <v>99.09905242919922</v>
       </c>
       <c r="E514" t="n">
-        <v>99.08427858035489</v>
+        <v>99.08427095209834</v>
       </c>
       <c r="F514" t="n">
-        <v>99.08921075213753</v>
+        <v>99.08920312350128</v>
       </c>
       <c r="G514" t="n">
         <v>14766800</v>
@@ -12271,16 +12271,16 @@
         <v>46042</v>
       </c>
       <c r="C515" t="n">
-        <v>99.09906005859375</v>
+        <v>99.09905242919922</v>
       </c>
       <c r="D515" t="n">
-        <v>99.10891688360451</v>
+        <v>99.10890925345112</v>
       </c>
       <c r="E515" t="n">
-        <v>99.09906005859375</v>
+        <v>99.09905242919922</v>
       </c>
       <c r="F515" t="n">
-        <v>99.09906005859375</v>
+        <v>99.09905242919922</v>
       </c>
       <c r="G515" t="n">
         <v>19394600</v>
@@ -12294,16 +12294,16 @@
         <v>46043</v>
       </c>
       <c r="C516" t="n">
-        <v>99.09906005859375</v>
+        <v>99.09905242919922</v>
       </c>
       <c r="D516" t="n">
-        <v>99.11877370861527</v>
+        <v>99.11876607770303</v>
       </c>
       <c r="E516" t="n">
-        <v>99.09906005859375</v>
+        <v>99.09905242919922</v>
       </c>
       <c r="F516" t="n">
-        <v>99.10399223037641</v>
+        <v>99.10398460060216</v>
       </c>
       <c r="G516" t="n">
         <v>17502100</v>
@@ -12317,16 +12317,16 @@
         <v>46044</v>
       </c>
       <c r="C517" t="n">
-        <v>99.11876678466797</v>
+        <v>99.11875915527344</v>
       </c>
       <c r="D517" t="n">
-        <v>99.11876678466797</v>
+        <v>99.11875915527344</v>
       </c>
       <c r="E517" t="n">
-        <v>99.10890996034576</v>
+        <v>99.10890233170993</v>
       </c>
       <c r="F517" t="n">
-        <v>99.11876678466797</v>
+        <v>99.11875915527344</v>
       </c>
       <c r="G517" t="n">
         <v>13618500</v>
@@ -12409,16 +12409,16 @@
         <v>46050</v>
       </c>
       <c r="C521" t="n">
-        <v>99.17789459228516</v>
+        <v>99.17788696289062</v>
       </c>
       <c r="D521" t="n">
-        <v>99.17789459228516</v>
+        <v>99.17788696289062</v>
       </c>
       <c r="E521" t="n">
-        <v>99.16803776777424</v>
+        <v>99.16803013913795</v>
       </c>
       <c r="F521" t="n">
-        <v>99.16803776777424</v>
+        <v>99.16803013913795</v>
       </c>
       <c r="G521" t="n">
         <v>11987500</v>
@@ -12501,16 +12501,16 @@
         <v>46056</v>
       </c>
       <c r="C525" t="n">
-        <v>99.23612976074219</v>
+        <v>99.23612213134766</v>
       </c>
       <c r="D525" t="n">
-        <v>99.23612976074219</v>
+        <v>99.23612213134766</v>
       </c>
       <c r="E525" t="n">
-        <v>99.22624258776793</v>
+        <v>99.22623495913354</v>
       </c>
       <c r="F525" t="n">
-        <v>99.23612976074219</v>
+        <v>99.23612213134766</v>
       </c>
       <c r="G525" t="n">
         <v>18150800</v>
@@ -12593,16 +12593,16 @@
         <v>46062</v>
       </c>
       <c r="C529" t="n">
-        <v>99.29544067382812</v>
+        <v>99.29542541503906</v>
       </c>
       <c r="D529" t="n">
-        <v>99.29544067382812</v>
+        <v>99.29542541503906</v>
       </c>
       <c r="E529" t="n">
-        <v>99.28556104226274</v>
+        <v>99.2855457849919</v>
       </c>
       <c r="F529" t="n">
-        <v>99.28556104226274</v>
+        <v>99.2855457849919</v>
       </c>
       <c r="G529" t="n">
         <v>13991600</v>
@@ -12616,16 +12616,16 @@
         <v>46063</v>
       </c>
       <c r="C530" t="n">
-        <v>99.30532073974609</v>
+        <v>99.30532836914062</v>
       </c>
       <c r="D530" t="n">
-        <v>99.30532073974609</v>
+        <v>99.30532836914062</v>
       </c>
       <c r="E530" t="n">
-        <v>99.29543356718486</v>
+        <v>99.29544119581978</v>
       </c>
       <c r="F530" t="n">
-        <v>99.30532073974609</v>
+        <v>99.30532836914062</v>
       </c>
       <c r="G530" t="n">
         <v>14002700</v>
@@ -12639,16 +12639,16 @@
         <v>46064</v>
       </c>
       <c r="C531" t="n">
-        <v>99.30532073974609</v>
+        <v>99.30532836914062</v>
       </c>
       <c r="D531" t="n">
-        <v>99.31520791230733</v>
+        <v>99.31521554246146</v>
       </c>
       <c r="E531" t="n">
-        <v>99.30532073974609</v>
+        <v>99.30532836914062</v>
       </c>
       <c r="F531" t="n">
-        <v>99.31520791230733</v>
+        <v>99.31521554246146</v>
       </c>
       <c r="G531" t="n">
         <v>12584400</v>
@@ -12685,16 +12685,16 @@
         <v>46066</v>
       </c>
       <c r="C533" t="n">
-        <v>99.3646240234375</v>
+        <v>99.36463165283203</v>
       </c>
       <c r="D533" t="n">
-        <v>99.3646240234375</v>
+        <v>99.36463165283203</v>
       </c>
       <c r="E533" t="n">
-        <v>99.35474439304336</v>
+        <v>99.35475202167932</v>
       </c>
       <c r="F533" t="n">
-        <v>99.3646240234375</v>
+        <v>99.36463165283203</v>
       </c>
       <c r="G533" t="n">
         <v>14917200</v>
@@ -12708,16 +12708,16 @@
         <v>46070</v>
       </c>
       <c r="C534" t="n">
-        <v>99.3646240234375</v>
+        <v>99.36463165283203</v>
       </c>
       <c r="D534" t="n">
-        <v>99.37451119553421</v>
+        <v>99.3745188256879</v>
       </c>
       <c r="E534" t="n">
-        <v>99.3646240234375</v>
+        <v>99.36463165283203</v>
       </c>
       <c r="F534" t="n">
-        <v>99.36957138033715</v>
+        <v>99.36957901011155</v>
       </c>
       <c r="G534" t="n">
         <v>14976200</v>
@@ -12754,16 +12754,16 @@
         <v>46072</v>
       </c>
       <c r="C536" t="n">
-        <v>99.39429473876953</v>
+        <v>99.394287109375</v>
       </c>
       <c r="D536" t="n">
-        <v>99.39429473876953</v>
+        <v>99.394287109375</v>
       </c>
       <c r="E536" t="n">
-        <v>99.38440756575774</v>
+        <v>99.38439993712214</v>
       </c>
       <c r="F536" t="n">
-        <v>99.39429473876953</v>
+        <v>99.394287109375</v>
       </c>
       <c r="G536" t="n">
         <v>11292100</v>
@@ -12777,16 +12777,16 @@
         <v>46073</v>
       </c>
       <c r="C537" t="n">
-        <v>99.41405487060547</v>
+        <v>99.4140625</v>
       </c>
       <c r="D537" t="n">
-        <v>99.42394204295366</v>
+        <v>99.42394967310696</v>
       </c>
       <c r="E537" t="n">
-        <v>99.41405487060547</v>
+        <v>99.4140625</v>
       </c>
       <c r="F537" t="n">
-        <v>99.42394204295366</v>
+        <v>99.42394967310696</v>
       </c>
       <c r="G537" t="n">
         <v>13490000</v>
@@ -12846,16 +12846,16 @@
         <v>46078</v>
       </c>
       <c r="C540" t="n">
-        <v>99.44370269775391</v>
+        <v>99.44371032714844</v>
       </c>
       <c r="D540" t="n">
-        <v>99.4535898694908</v>
+        <v>99.45359749964389</v>
       </c>
       <c r="E540" t="n">
-        <v>99.44370269775391</v>
+        <v>99.44371032714844</v>
       </c>
       <c r="F540" t="n">
-        <v>99.4535898694908</v>
+        <v>99.45359749964389</v>
       </c>
       <c r="G540" t="n">
         <v>12532000</v>
@@ -12892,16 +12892,16 @@
         <v>46080</v>
       </c>
       <c r="C542" t="n">
-        <v>99.48325347900391</v>
+        <v>99.48324584960938</v>
       </c>
       <c r="D542" t="n">
-        <v>99.49314065169848</v>
+        <v>99.49313302154569</v>
       </c>
       <c r="E542" t="n">
-        <v>99.48325347900391</v>
+        <v>99.48324584960938</v>
       </c>
       <c r="F542" t="n">
-        <v>99.48819329449967</v>
+        <v>99.4881856647263</v>
       </c>
       <c r="G542" t="n">
         <v>26602400</v>
@@ -12984,16 +12984,16 @@
         <v>46086</v>
       </c>
       <c r="C546" t="n">
-        <v>99.52488708496094</v>
+        <v>99.52489471435547</v>
       </c>
       <c r="D546" t="n">
-        <v>99.53479348998074</v>
+        <v>99.53480112013467</v>
       </c>
       <c r="E546" t="n">
-        <v>99.52488708496094</v>
+        <v>99.52489471435547</v>
       </c>
       <c r="F546" t="n">
-        <v>99.53479348998074</v>
+        <v>99.53480112013467</v>
       </c>
       <c r="G546" t="n">
         <v>16218200</v>
@@ -13007,16 +13007,16 @@
         <v>46087</v>
       </c>
       <c r="C547" t="n">
-        <v>99.56452941894531</v>
+        <v>99.56452178955078</v>
       </c>
       <c r="D547" t="n">
-        <v>99.56452941894531</v>
+        <v>99.56452178955078</v>
       </c>
       <c r="E547" t="n">
-        <v>99.55462301376734</v>
+        <v>99.55461538513191</v>
       </c>
       <c r="F547" t="n">
-        <v>99.55462301376734</v>
+        <v>99.55461538513191</v>
       </c>
       <c r="G547" t="n">
         <v>18921300</v>
@@ -13030,16 +13030,16 @@
         <v>46090</v>
       </c>
       <c r="C548" t="n">
-        <v>99.57444000244141</v>
+        <v>99.57444763183594</v>
       </c>
       <c r="D548" t="n">
-        <v>99.57444000244141</v>
+        <v>99.57444763183594</v>
       </c>
       <c r="E548" t="n">
-        <v>99.564526035459</v>
+        <v>99.56453366409391</v>
       </c>
       <c r="F548" t="n">
-        <v>99.56948680002075</v>
+        <v>99.56949442903577</v>
       </c>
       <c r="G548" t="n">
         <v>19053900</v>
@@ -13053,16 +13053,16 @@
         <v>46091</v>
       </c>
       <c r="C549" t="n">
-        <v>99.57444000244141</v>
+        <v>99.57444763183594</v>
       </c>
       <c r="D549" t="n">
-        <v>99.58435396942383</v>
+        <v>99.58436159957796</v>
       </c>
       <c r="E549" t="n">
-        <v>99.57444000244141</v>
+        <v>99.57444763183594</v>
       </c>
       <c r="F549" t="n">
-        <v>99.58138204797143</v>
+        <v>99.58138967789786</v>
       </c>
       <c r="G549" t="n">
         <v>13664200</v>
@@ -13329,16 +13329,16 @@
         <v>46107</v>
       </c>
       <c r="C561" t="n">
-        <v>99.7330322265625</v>
+        <v>99.73303985595703</v>
       </c>
       <c r="D561" t="n">
-        <v>99.7330322265625</v>
+        <v>99.73303985595703</v>
       </c>
       <c r="E561" t="n">
-        <v>99.7231182596794</v>
+        <v>99.72312588831552</v>
       </c>
       <c r="F561" t="n">
-        <v>99.7330322265625</v>
+        <v>99.73303985595703</v>
       </c>
       <c r="G561" t="n">
         <v>17499400</v>
@@ -13375,16 +13375,16 @@
         <v>46111</v>
       </c>
       <c r="C563" t="n">
-        <v>99.77268218994141</v>
+        <v>99.77268981933594</v>
       </c>
       <c r="D563" t="n">
-        <v>99.77268218994141</v>
+        <v>99.77268981933594</v>
       </c>
       <c r="E563" t="n">
-        <v>99.76276822289356</v>
+        <v>99.76277585152998</v>
       </c>
       <c r="F563" t="n">
-        <v>99.76276822289356</v>
+        <v>99.76277585152998</v>
       </c>
       <c r="G563" t="n">
         <v>19102700</v>
@@ -13398,16 +13398,16 @@
         <v>46112</v>
       </c>
       <c r="C564" t="n">
-        <v>99.77268218994141</v>
+        <v>99.77268981933594</v>
       </c>
       <c r="D564" t="n">
-        <v>99.78258859484811</v>
+        <v>99.78259622500016</v>
       </c>
       <c r="E564" t="n">
-        <v>99.77268218994141</v>
+        <v>99.77268981933594</v>
       </c>
       <c r="F564" t="n">
-        <v>99.77268218994141</v>
+        <v>99.77268981933594</v>
       </c>
       <c r="G564" t="n">
         <v>36976800</v>

--- a/Data/sgov.xlsx
+++ b/Data/sgov.xlsx
@@ -472,16 +472,16 @@
         <v>45293</v>
       </c>
       <c r="C2" t="n">
-        <v>90.15839385986328</v>
+        <v>90.15837097167969</v>
       </c>
       <c r="D2" t="n">
-        <v>90.16738554925877</v>
+        <v>90.1673626587925</v>
       </c>
       <c r="E2" t="n">
-        <v>90.14940217046778</v>
+        <v>90.14937928456688</v>
       </c>
       <c r="F2" t="n">
-        <v>90.15839385986328</v>
+        <v>90.15837097167969</v>
       </c>
       <c r="G2" t="n">
         <v>5286200</v>
@@ -518,16 +518,16 @@
         <v>45295</v>
       </c>
       <c r="C4" t="n">
-        <v>90.21231842041016</v>
+        <v>90.21231079101562</v>
       </c>
       <c r="D4" t="n">
-        <v>90.22131010862368</v>
+        <v>90.22130247846871</v>
       </c>
       <c r="E4" t="n">
-        <v>90.21231842041016</v>
+        <v>90.21231079101562</v>
       </c>
       <c r="F4" t="n">
-        <v>90.21231842041016</v>
+        <v>90.21231079101562</v>
       </c>
       <c r="G4" t="n">
         <v>2794100</v>
@@ -541,16 +541,16 @@
         <v>45296</v>
       </c>
       <c r="C5" t="n">
-        <v>90.2213134765625</v>
+        <v>90.22130584716797</v>
       </c>
       <c r="D5" t="n">
-        <v>90.23030516511169</v>
+        <v>90.23029753495679</v>
       </c>
       <c r="E5" t="n">
-        <v>90.2213134765625</v>
+        <v>90.22130584716797</v>
       </c>
       <c r="F5" t="n">
-        <v>90.2213134765625</v>
+        <v>90.22130584716797</v>
       </c>
       <c r="G5" t="n">
         <v>3491200</v>
@@ -564,16 +564,16 @@
         <v>45299</v>
       </c>
       <c r="C6" t="n">
-        <v>90.24829864501953</v>
+        <v>90.248291015625</v>
       </c>
       <c r="D6" t="n">
-        <v>90.24829864501953</v>
+        <v>90.248291015625</v>
       </c>
       <c r="E6" t="n">
-        <v>90.23930695478043</v>
+        <v>90.23929932614602</v>
       </c>
       <c r="F6" t="n">
-        <v>90.24829864501953</v>
+        <v>90.248291015625</v>
       </c>
       <c r="G6" t="n">
         <v>2867500</v>
@@ -610,16 +610,16 @@
         <v>45301</v>
       </c>
       <c r="C8" t="n">
-        <v>90.2752685546875</v>
+        <v>90.27524566650391</v>
       </c>
       <c r="D8" t="n">
-        <v>90.2752685546875</v>
+        <v>90.27524566650391</v>
       </c>
       <c r="E8" t="n">
-        <v>90.2662837229295</v>
+        <v>90.26626083702391</v>
       </c>
       <c r="F8" t="n">
-        <v>90.2752685546875</v>
+        <v>90.27524566650391</v>
       </c>
       <c r="G8" t="n">
         <v>1961400</v>
@@ -633,16 +633,16 @@
         <v>45302</v>
       </c>
       <c r="C9" t="n">
-        <v>90.32920074462891</v>
+        <v>90.32918548583984</v>
       </c>
       <c r="D9" t="n">
-        <v>90.32920074462891</v>
+        <v>90.32918548583984</v>
       </c>
       <c r="E9" t="n">
-        <v>90.31121736602117</v>
+        <v>90.31120211026995</v>
       </c>
       <c r="F9" t="n">
-        <v>90.31121736602117</v>
+        <v>90.31120211026995</v>
       </c>
       <c r="G9" t="n">
         <v>3164900</v>
@@ -656,16 +656,16 @@
         <v>45303</v>
       </c>
       <c r="C10" t="n">
-        <v>90.33819580078125</v>
+        <v>90.33816528320312</v>
       </c>
       <c r="D10" t="n">
-        <v>90.33819580078125</v>
+        <v>90.33816528320312</v>
       </c>
       <c r="E10" t="n">
-        <v>90.32921096910974</v>
+        <v>90.32918045456681</v>
       </c>
       <c r="F10" t="n">
-        <v>90.32921096910974</v>
+        <v>90.32918045456681</v>
       </c>
       <c r="G10" t="n">
         <v>2557900</v>
@@ -679,16 +679,16 @@
         <v>45307</v>
       </c>
       <c r="C11" t="n">
-        <v>90.34716796875</v>
+        <v>90.34715270996094</v>
       </c>
       <c r="D11" t="n">
-        <v>90.35615965712871</v>
+        <v>90.35614439682104</v>
       </c>
       <c r="E11" t="n">
-        <v>90.34716796875</v>
+        <v>90.34715270996094</v>
       </c>
       <c r="F11" t="n">
-        <v>90.35615965712871</v>
+        <v>90.35614439682104</v>
       </c>
       <c r="G11" t="n">
         <v>2713000</v>
@@ -702,16 +702,16 @@
         <v>45308</v>
       </c>
       <c r="C12" t="n">
-        <v>90.35617828369141</v>
+        <v>90.35617065429688</v>
       </c>
       <c r="D12" t="n">
-        <v>90.36516311527365</v>
+        <v>90.36515548512048</v>
       </c>
       <c r="E12" t="n">
-        <v>90.35617828369141</v>
+        <v>90.35617065429688</v>
       </c>
       <c r="F12" t="n">
-        <v>90.36516311527365</v>
+        <v>90.36515548512048</v>
       </c>
       <c r="G12" t="n">
         <v>2317700</v>
@@ -748,16 +748,16 @@
         <v>45310</v>
       </c>
       <c r="C14" t="n">
-        <v>90.41910552978516</v>
+        <v>90.41909027099609</v>
       </c>
       <c r="D14" t="n">
-        <v>90.41910552978516</v>
+        <v>90.41909027099609</v>
       </c>
       <c r="E14" t="n">
-        <v>90.40112214949322</v>
+        <v>90.40110689373897</v>
       </c>
       <c r="F14" t="n">
-        <v>90.41011383963918</v>
+        <v>90.41009858236752</v>
       </c>
       <c r="G14" t="n">
         <v>3630100</v>
@@ -771,16 +771,16 @@
         <v>45313</v>
       </c>
       <c r="C15" t="n">
-        <v>90.42805480957031</v>
+        <v>90.4281005859375</v>
       </c>
       <c r="D15" t="n">
-        <v>90.43704649618121</v>
+        <v>90.43709227710016</v>
       </c>
       <c r="E15" t="n">
-        <v>90.41906998160671</v>
+        <v>90.41911575342561</v>
       </c>
       <c r="F15" t="n">
-        <v>90.4325540821994</v>
+        <v>90.43259986084422</v>
       </c>
       <c r="G15" t="n">
         <v>4307000</v>
@@ -817,16 +817,16 @@
         <v>45315</v>
       </c>
       <c r="C17" t="n">
-        <v>90.45503997802734</v>
+        <v>90.45506286621094</v>
       </c>
       <c r="D17" t="n">
-        <v>90.45503997802734</v>
+        <v>90.45506286621094</v>
       </c>
       <c r="E17" t="n">
-        <v>90.4460482904116</v>
+        <v>90.44607117631999</v>
       </c>
       <c r="F17" t="n">
-        <v>90.4460482904116</v>
+        <v>90.44607117631999</v>
       </c>
       <c r="G17" t="n">
         <v>3441600</v>
@@ -840,16 +840,16 @@
         <v>45316</v>
       </c>
       <c r="C18" t="n">
-        <v>90.5</v>
+        <v>90.49999237060547</v>
       </c>
       <c r="D18" t="n">
-        <v>90.5</v>
+        <v>90.49999237060547</v>
       </c>
       <c r="E18" t="n">
-        <v>90.48202348037722</v>
+        <v>90.48201585249815</v>
       </c>
       <c r="F18" t="n">
-        <v>90.48202348037722</v>
+        <v>90.48201585249815</v>
       </c>
       <c r="G18" t="n">
         <v>2426000</v>
@@ -863,16 +863,16 @@
         <v>45317</v>
       </c>
       <c r="C19" t="n">
-        <v>90.5</v>
+        <v>90.49999237060547</v>
       </c>
       <c r="D19" t="n">
-        <v>90.50899168913601</v>
+        <v>90.50898405898346</v>
       </c>
       <c r="E19" t="n">
-        <v>90.5</v>
+        <v>90.49999237060547</v>
       </c>
       <c r="F19" t="n">
-        <v>90.50899168913601</v>
+        <v>90.50898405898346</v>
       </c>
       <c r="G19" t="n">
         <v>2059100</v>
@@ -909,16 +909,16 @@
         <v>45321</v>
       </c>
       <c r="C21" t="n">
-        <v>90.53594207763672</v>
+        <v>90.53594970703125</v>
       </c>
       <c r="D21" t="n">
-        <v>90.53594207763672</v>
+        <v>90.53594970703125</v>
       </c>
       <c r="E21" t="n">
-        <v>90.52695039027056</v>
+        <v>90.52695801890737</v>
       </c>
       <c r="F21" t="n">
-        <v>90.52695039027056</v>
+        <v>90.52695801890737</v>
       </c>
       <c r="G21" t="n">
         <v>3741000</v>
@@ -932,16 +932,16 @@
         <v>45322</v>
       </c>
       <c r="C22" t="n">
-        <v>90.53594207763672</v>
+        <v>90.53594970703125</v>
       </c>
       <c r="D22" t="n">
-        <v>90.54493376500288</v>
+        <v>90.54494139515513</v>
       </c>
       <c r="E22" t="n">
-        <v>90.53594207763672</v>
+        <v>90.53594970703125</v>
       </c>
       <c r="F22" t="n">
-        <v>90.53594207763672</v>
+        <v>90.53594970703125</v>
       </c>
       <c r="G22" t="n">
         <v>5171300</v>
@@ -978,16 +978,16 @@
         <v>45324</v>
       </c>
       <c r="C24" t="n">
-        <v>90.59737396240234</v>
+        <v>90.59735870361328</v>
       </c>
       <c r="D24" t="n">
-        <v>90.59737396240234</v>
+        <v>90.59735870361328</v>
       </c>
       <c r="E24" t="n">
-        <v>90.58834119446723</v>
+        <v>90.5883259371995</v>
       </c>
       <c r="F24" t="n">
-        <v>90.59737396240234</v>
+        <v>90.59735870361328</v>
       </c>
       <c r="G24" t="n">
         <v>3864800</v>
@@ -1001,16 +1001,16 @@
         <v>45327</v>
       </c>
       <c r="C25" t="n">
-        <v>90.61543273925781</v>
+        <v>90.61542510986328</v>
       </c>
       <c r="D25" t="n">
-        <v>90.61543273925781</v>
+        <v>90.61542510986328</v>
       </c>
       <c r="E25" t="n">
-        <v>90.60640686129281</v>
+        <v>90.60639923265822</v>
       </c>
       <c r="F25" t="n">
-        <v>90.61543273925781</v>
+        <v>90.61542510986328</v>
       </c>
       <c r="G25" t="n">
         <v>3969400</v>
@@ -1024,16 +1024,16 @@
         <v>45328</v>
       </c>
       <c r="C26" t="n">
-        <v>90.62445831298828</v>
+        <v>90.62446594238281</v>
       </c>
       <c r="D26" t="n">
-        <v>90.6334910802194</v>
+        <v>90.63349871037437</v>
       </c>
       <c r="E26" t="n">
-        <v>90.61542554575718</v>
+        <v>90.61543317439127</v>
       </c>
       <c r="F26" t="n">
-        <v>90.62445831298828</v>
+        <v>90.62446594238281</v>
       </c>
       <c r="G26" t="n">
         <v>2167300</v>
@@ -1047,16 +1047,16 @@
         <v>45329</v>
       </c>
       <c r="C27" t="n">
-        <v>90.64251708984375</v>
+        <v>90.64250183105469</v>
       </c>
       <c r="D27" t="n">
-        <v>90.64251708984375</v>
+        <v>90.64250183105469</v>
       </c>
       <c r="E27" t="n">
-        <v>90.63348432328605</v>
+        <v>90.63346906601757</v>
       </c>
       <c r="F27" t="n">
-        <v>90.64251708984375</v>
+        <v>90.64250183105469</v>
       </c>
       <c r="G27" t="n">
         <v>2621200</v>
@@ -1070,16 +1070,16 @@
         <v>45330</v>
       </c>
       <c r="C28" t="n">
-        <v>90.66959381103516</v>
+        <v>90.66961669921875</v>
       </c>
       <c r="D28" t="n">
-        <v>90.68765245124293</v>
+        <v>90.68767534398516</v>
       </c>
       <c r="E28" t="n">
-        <v>90.66959381103516</v>
+        <v>90.66961669921875</v>
       </c>
       <c r="F28" t="n">
-        <v>90.66959381103516</v>
+        <v>90.66961669921875</v>
       </c>
       <c r="G28" t="n">
         <v>3838700</v>
@@ -1093,16 +1093,16 @@
         <v>45331</v>
       </c>
       <c r="C29" t="n">
-        <v>90.69670867919922</v>
+        <v>90.69669342041016</v>
       </c>
       <c r="D29" t="n">
-        <v>90.69670867919922</v>
+        <v>90.69669342041016</v>
       </c>
       <c r="E29" t="n">
-        <v>90.68316297304392</v>
+        <v>90.68314771653378</v>
       </c>
       <c r="F29" t="n">
-        <v>90.6876759117681</v>
+        <v>90.6876606544987</v>
       </c>
       <c r="G29" t="n">
         <v>3232500</v>
@@ -1116,16 +1116,16 @@
         <v>45334</v>
       </c>
       <c r="C30" t="n">
-        <v>90.69670867919922</v>
+        <v>90.69669342041016</v>
       </c>
       <c r="D30" t="n">
-        <v>90.71476732407868</v>
+        <v>90.71475206225145</v>
       </c>
       <c r="E30" t="n">
-        <v>90.69670867919922</v>
+        <v>90.69669342041016</v>
       </c>
       <c r="F30" t="n">
-        <v>90.70574144663034</v>
+        <v>90.70572618632161</v>
       </c>
       <c r="G30" t="n">
         <v>2792700</v>
@@ -1139,16 +1139,16 @@
         <v>45335</v>
       </c>
       <c r="C31" t="n">
-        <v>90.71479034423828</v>
+        <v>90.71475219726562</v>
       </c>
       <c r="D31" t="n">
-        <v>90.71479034423828</v>
+        <v>90.71475219726562</v>
       </c>
       <c r="E31" t="n">
-        <v>90.7057644644995</v>
+        <v>90.70572632132237</v>
       </c>
       <c r="F31" t="n">
-        <v>90.71479034423828</v>
+        <v>90.71475219726562</v>
       </c>
       <c r="G31" t="n">
         <v>3009000</v>
@@ -1185,16 +1185,16 @@
         <v>45337</v>
       </c>
       <c r="C33" t="n">
-        <v>90.77797698974609</v>
+        <v>90.77799224853516</v>
       </c>
       <c r="D33" t="n">
-        <v>90.78700975658751</v>
+        <v>90.7870250168949</v>
       </c>
       <c r="E33" t="n">
-        <v>90.77797698974609</v>
+        <v>90.77799224853516</v>
       </c>
       <c r="F33" t="n">
-        <v>90.78700975658751</v>
+        <v>90.7870250168949</v>
       </c>
       <c r="G33" t="n">
         <v>2577800</v>
@@ -1208,16 +1208,16 @@
         <v>45338</v>
       </c>
       <c r="C34" t="n">
-        <v>90.78704071044922</v>
+        <v>90.78701019287109</v>
       </c>
       <c r="D34" t="n">
-        <v>90.79607348037037</v>
+        <v>90.79604295975592</v>
       </c>
       <c r="E34" t="n">
-        <v>90.78704071044922</v>
+        <v>90.78701019287109</v>
       </c>
       <c r="F34" t="n">
-        <v>90.79607348037037</v>
+        <v>90.79604295975592</v>
       </c>
       <c r="G34" t="n">
         <v>2920700</v>
@@ -1254,16 +1254,16 @@
         <v>45343</v>
       </c>
       <c r="C36" t="n">
-        <v>90.81410217285156</v>
+        <v>90.8140869140625</v>
       </c>
       <c r="D36" t="n">
-        <v>90.83216770673448</v>
+        <v>90.83215244491001</v>
       </c>
       <c r="E36" t="n">
-        <v>90.81410217285156</v>
+        <v>90.8140869140625</v>
       </c>
       <c r="F36" t="n">
-        <v>90.82313493979302</v>
+        <v>90.82311967948625</v>
       </c>
       <c r="G36" t="n">
         <v>2302700</v>
@@ -1277,16 +1277,16 @@
         <v>45344</v>
       </c>
       <c r="C37" t="n">
-        <v>90.85024261474609</v>
+        <v>90.85023498535156</v>
       </c>
       <c r="D37" t="n">
-        <v>90.85927538330462</v>
+        <v>90.85926775315153</v>
       </c>
       <c r="E37" t="n">
-        <v>90.85024261474609</v>
+        <v>90.85023498535156</v>
       </c>
       <c r="F37" t="n">
-        <v>90.85024261474609</v>
+        <v>90.85023498535156</v>
       </c>
       <c r="G37" t="n">
         <v>2452200</v>
@@ -1323,16 +1323,16 @@
         <v>45348</v>
       </c>
       <c r="C39" t="n">
-        <v>90.88636016845703</v>
+        <v>90.88634490966797</v>
       </c>
       <c r="D39" t="n">
-        <v>90.89539293635657</v>
+        <v>90.89537767605101</v>
       </c>
       <c r="E39" t="n">
-        <v>90.88636016845703</v>
+        <v>90.88634490966797</v>
       </c>
       <c r="F39" t="n">
-        <v>90.88636016845703</v>
+        <v>90.88634490966797</v>
       </c>
       <c r="G39" t="n">
         <v>2645100</v>
@@ -1346,16 +1346,16 @@
         <v>45349</v>
       </c>
       <c r="C40" t="n">
-        <v>90.90442657470703</v>
+        <v>90.9044189453125</v>
       </c>
       <c r="D40" t="n">
-        <v>90.90442657470703</v>
+        <v>90.9044189453125</v>
       </c>
       <c r="E40" t="n">
-        <v>90.895393806721</v>
+        <v>90.89538617808456</v>
       </c>
       <c r="F40" t="n">
-        <v>90.90442657470703</v>
+        <v>90.9044189453125</v>
       </c>
       <c r="G40" t="n">
         <v>2360300</v>
@@ -1369,16 +1369,16 @@
         <v>45350</v>
       </c>
       <c r="C41" t="n">
-        <v>90.91345977783203</v>
+        <v>90.9134521484375</v>
       </c>
       <c r="D41" t="n">
-        <v>90.91345977783203</v>
+        <v>90.9134521484375</v>
       </c>
       <c r="E41" t="n">
-        <v>90.90443389910197</v>
+        <v>90.90442627046488</v>
       </c>
       <c r="F41" t="n">
-        <v>90.90443389910197</v>
+        <v>90.90442627046488</v>
       </c>
       <c r="G41" t="n">
         <v>4526200</v>
@@ -1392,16 +1392,16 @@
         <v>45351</v>
       </c>
       <c r="C42" t="n">
-        <v>90.94053649902344</v>
+        <v>90.94052886962891</v>
       </c>
       <c r="D42" t="n">
-        <v>90.94956926627766</v>
+        <v>90.94956163612534</v>
       </c>
       <c r="E42" t="n">
-        <v>90.94053649902344</v>
+        <v>90.94052886962891</v>
       </c>
       <c r="F42" t="n">
-        <v>90.94053649902344</v>
+        <v>90.94052886962891</v>
       </c>
       <c r="G42" t="n">
         <v>5560200</v>
@@ -1415,16 +1415,16 @@
         <v>45352</v>
       </c>
       <c r="C43" t="n">
-        <v>90.96775054931641</v>
+        <v>90.96772766113281</v>
       </c>
       <c r="D43" t="n">
-        <v>90.96775054931641</v>
+        <v>90.96772766113281</v>
       </c>
       <c r="E43" t="n">
-        <v>90.95868085397808</v>
+        <v>90.95865796807648</v>
       </c>
       <c r="F43" t="n">
-        <v>90.96775054931641</v>
+        <v>90.96772766113281</v>
       </c>
       <c r="G43" t="n">
         <v>7579200</v>
@@ -1438,16 +1438,16 @@
         <v>45355</v>
       </c>
       <c r="C44" t="n">
-        <v>90.97681427001953</v>
+        <v>90.976806640625</v>
       </c>
       <c r="D44" t="n">
-        <v>90.98587704661217</v>
+        <v>90.98586941645763</v>
       </c>
       <c r="E44" t="n">
-        <v>90.97681427001953</v>
+        <v>90.976806640625</v>
       </c>
       <c r="F44" t="n">
-        <v>90.97681427001953</v>
+        <v>90.976806640625</v>
       </c>
       <c r="G44" t="n">
         <v>3613500</v>
@@ -1461,16 +1461,16 @@
         <v>45356</v>
       </c>
       <c r="C45" t="n">
-        <v>90.98588562011719</v>
+        <v>90.98587036132812</v>
       </c>
       <c r="D45" t="n">
-        <v>90.99495531571452</v>
+        <v>90.99494005540443</v>
       </c>
       <c r="E45" t="n">
-        <v>90.98588562011719</v>
+        <v>90.98587036132812</v>
       </c>
       <c r="F45" t="n">
-        <v>90.98588562011719</v>
+        <v>90.98587036132812</v>
       </c>
       <c r="G45" t="n">
         <v>3905300</v>
@@ -1484,16 +1484,16 @@
         <v>45357</v>
       </c>
       <c r="C46" t="n">
-        <v>91.00400543212891</v>
+        <v>91.00399017333984</v>
       </c>
       <c r="D46" t="n">
-        <v>91.01307512577493</v>
+        <v>91.01305986546514</v>
       </c>
       <c r="E46" t="n">
-        <v>90.99493573848288</v>
+        <v>90.99492048121455</v>
       </c>
       <c r="F46" t="n">
-        <v>91.00400543212891</v>
+        <v>91.00399017333984</v>
       </c>
       <c r="G46" t="n">
         <v>2760000</v>
@@ -1530,16 +1530,16 @@
         <v>45359</v>
       </c>
       <c r="C48" t="n">
-        <v>91.05843353271484</v>
+        <v>91.05842590332031</v>
       </c>
       <c r="D48" t="n">
-        <v>91.06750322872892</v>
+        <v>91.06749559857448</v>
       </c>
       <c r="E48" t="n">
-        <v>91.04937075485179</v>
+        <v>91.04936312621659</v>
       </c>
       <c r="F48" t="n">
-        <v>91.06750322872892</v>
+        <v>91.06749559857448</v>
       </c>
       <c r="G48" t="n">
         <v>3748900</v>
@@ -1553,16 +1553,16 @@
         <v>45362</v>
       </c>
       <c r="C49" t="n">
-        <v>91.07654571533203</v>
+        <v>91.0765380859375</v>
       </c>
       <c r="D49" t="n">
-        <v>91.07654571533203</v>
+        <v>91.0765380859375</v>
       </c>
       <c r="E49" t="n">
-        <v>91.06747602202755</v>
+        <v>91.06746839339277</v>
       </c>
       <c r="F49" t="n">
-        <v>91.07654571533203</v>
+        <v>91.0765380859375</v>
       </c>
       <c r="G49" t="n">
         <v>3238400</v>
@@ -1576,16 +1576,16 @@
         <v>45363</v>
       </c>
       <c r="C50" t="n">
-        <v>91.08563232421875</v>
+        <v>91.08560943603516</v>
       </c>
       <c r="D50" t="n">
-        <v>91.09470201989645</v>
+        <v>91.0946791294338</v>
       </c>
       <c r="E50" t="n">
-        <v>91.08563232421875</v>
+        <v>91.08560943603516</v>
       </c>
       <c r="F50" t="n">
-        <v>91.08563232421875</v>
+        <v>91.08560943603516</v>
       </c>
       <c r="G50" t="n">
         <v>2613300</v>
@@ -1599,16 +1599,16 @@
         <v>45364</v>
       </c>
       <c r="C51" t="n">
-        <v>91.09469604492188</v>
+        <v>91.09468078613281</v>
       </c>
       <c r="D51" t="n">
-        <v>91.10376574000468</v>
+        <v>91.1037504796964</v>
       </c>
       <c r="E51" t="n">
-        <v>91.09469604492188</v>
+        <v>91.09468078613281</v>
       </c>
       <c r="F51" t="n">
-        <v>91.09469604492188</v>
+        <v>91.09468078613281</v>
       </c>
       <c r="G51" t="n">
         <v>2249300</v>
@@ -1645,16 +1645,16 @@
         <v>45366</v>
       </c>
       <c r="C53" t="n">
-        <v>91.14907836914062</v>
+        <v>91.14910125732422</v>
       </c>
       <c r="D53" t="n">
-        <v>91.14907836914062</v>
+        <v>91.14910125732422</v>
       </c>
       <c r="E53" t="n">
-        <v>91.14001559439656</v>
+        <v>91.14003848030443</v>
       </c>
       <c r="F53" t="n">
-        <v>91.14907836914062</v>
+        <v>91.14910125732422</v>
       </c>
       <c r="G53" t="n">
         <v>3277300</v>
@@ -1668,16 +1668,16 @@
         <v>45369</v>
       </c>
       <c r="C54" t="n">
-        <v>91.15818023681641</v>
+        <v>91.15815734863281</v>
       </c>
       <c r="D54" t="n">
-        <v>91.16724993291032</v>
+        <v>91.16722704244948</v>
       </c>
       <c r="E54" t="n">
-        <v>91.15818023681641</v>
+        <v>91.15815734863281</v>
       </c>
       <c r="F54" t="n">
-        <v>91.16724993291032</v>
+        <v>91.16722704244948</v>
       </c>
       <c r="G54" t="n">
         <v>3576200</v>
@@ -1691,16 +1691,16 @@
         <v>45370</v>
       </c>
       <c r="C55" t="n">
-        <v>91.17629241943359</v>
+        <v>91.17630004882812</v>
       </c>
       <c r="D55" t="n">
-        <v>91.18535519467183</v>
+        <v>91.18536282482471</v>
       </c>
       <c r="E55" t="n">
-        <v>91.17629241943359</v>
+        <v>91.17630004882812</v>
       </c>
       <c r="F55" t="n">
-        <v>91.18535519467183</v>
+        <v>91.18536282482471</v>
       </c>
       <c r="G55" t="n">
         <v>2661900</v>
@@ -1714,16 +1714,16 @@
         <v>45371</v>
       </c>
       <c r="C56" t="n">
-        <v>91.18537139892578</v>
+        <v>91.18534851074219</v>
       </c>
       <c r="D56" t="n">
-        <v>91.19444109392479</v>
+        <v>91.19441820346465</v>
       </c>
       <c r="E56" t="n">
-        <v>91.18537139892578</v>
+        <v>91.18534851074219</v>
       </c>
       <c r="F56" t="n">
-        <v>91.18537139892578</v>
+        <v>91.18534851074219</v>
       </c>
       <c r="G56" t="n">
         <v>2492700</v>
@@ -1760,16 +1760,16 @@
         <v>45373</v>
       </c>
       <c r="C58" t="n">
-        <v>91.23976898193359</v>
+        <v>91.23977661132812</v>
       </c>
       <c r="D58" t="n">
-        <v>91.24883175742463</v>
+        <v>91.24883938757698</v>
       </c>
       <c r="E58" t="n">
-        <v>91.23069928829332</v>
+        <v>91.23070691692946</v>
       </c>
       <c r="F58" t="n">
-        <v>91.24883175742463</v>
+        <v>91.24883938757698</v>
       </c>
       <c r="G58" t="n">
         <v>2636700</v>
@@ -1783,16 +1783,16 @@
         <v>45376</v>
       </c>
       <c r="C59" t="n">
-        <v>91.25792694091797</v>
+        <v>91.25790405273438</v>
       </c>
       <c r="D59" t="n">
-        <v>91.26699663709155</v>
+        <v>91.26697374663321</v>
       </c>
       <c r="E59" t="n">
-        <v>91.25792694091797</v>
+        <v>91.25790405273438</v>
       </c>
       <c r="F59" t="n">
-        <v>91.25792694091797</v>
+        <v>91.25790405273438</v>
       </c>
       <c r="G59" t="n">
         <v>2422900</v>
@@ -1852,16 +1852,16 @@
         <v>45379</v>
       </c>
       <c r="C62" t="n">
-        <v>91.32138824462891</v>
+        <v>91.32137298583984</v>
       </c>
       <c r="D62" t="n">
-        <v>91.33045793953788</v>
+        <v>91.33044267923337</v>
       </c>
       <c r="E62" t="n">
-        <v>91.32138824462891</v>
+        <v>91.32137298583984</v>
       </c>
       <c r="F62" t="n">
-        <v>91.33045793953788</v>
+        <v>91.33044267923337</v>
       </c>
       <c r="G62" t="n">
         <v>5425800</v>
@@ -1875,16 +1875,16 @@
         <v>45383</v>
       </c>
       <c r="C63" t="n">
-        <v>91.34870147705078</v>
+        <v>91.34870910644531</v>
       </c>
       <c r="D63" t="n">
-        <v>91.35781187837004</v>
+        <v>91.35781950852548</v>
       </c>
       <c r="E63" t="n">
-        <v>91.34870147705078</v>
+        <v>91.34870910644531</v>
       </c>
       <c r="F63" t="n">
-        <v>91.35781187837004</v>
+        <v>91.35781950852548</v>
       </c>
       <c r="G63" t="n">
         <v>7395400</v>
@@ -1898,16 +1898,16 @@
         <v>45384</v>
       </c>
       <c r="C64" t="n">
-        <v>91.36692810058594</v>
+        <v>91.366943359375</v>
       </c>
       <c r="D64" t="n">
-        <v>91.36692810058594</v>
+        <v>91.366943359375</v>
       </c>
       <c r="E64" t="n">
-        <v>91.35782464719441</v>
+        <v>91.35783990446313</v>
       </c>
       <c r="F64" t="n">
-        <v>91.36692810058594</v>
+        <v>91.366943359375</v>
       </c>
       <c r="G64" t="n">
         <v>4202900</v>
@@ -1921,16 +1921,16 @@
         <v>45385</v>
       </c>
       <c r="C65" t="n">
-        <v>91.37604522705078</v>
+        <v>91.37602996826172</v>
       </c>
       <c r="D65" t="n">
-        <v>91.38515563031378</v>
+        <v>91.38514037000337</v>
       </c>
       <c r="E65" t="n">
-        <v>91.37604522705078</v>
+        <v>91.37602996826172</v>
       </c>
       <c r="F65" t="n">
-        <v>91.37604522705078</v>
+        <v>91.37602996826172</v>
       </c>
       <c r="G65" t="n">
         <v>4333600</v>
@@ -1967,16 +1967,16 @@
         <v>45387</v>
       </c>
       <c r="C67" t="n">
-        <v>91.43069458007812</v>
+        <v>91.43067932128906</v>
       </c>
       <c r="D67" t="n">
-        <v>91.439804983424</v>
+        <v>91.43978972311452</v>
       </c>
       <c r="E67" t="n">
-        <v>91.43069458007812</v>
+        <v>91.43067932128906</v>
       </c>
       <c r="F67" t="n">
-        <v>91.439804983424</v>
+        <v>91.43978972311452</v>
       </c>
       <c r="G67" t="n">
         <v>3104200</v>
@@ -2059,16 +2059,16 @@
         <v>45393</v>
       </c>
       <c r="C71" t="n">
-        <v>91.51264953613281</v>
+        <v>91.51263427734375</v>
       </c>
       <c r="D71" t="n">
-        <v>91.51264953613281</v>
+        <v>91.51263427734375</v>
       </c>
       <c r="E71" t="n">
-        <v>91.50353913525345</v>
+        <v>91.50352387798345</v>
       </c>
       <c r="F71" t="n">
-        <v>91.50353913525345</v>
+        <v>91.50352387798345</v>
       </c>
       <c r="G71" t="n">
         <v>3521100</v>
@@ -2082,16 +2082,16 @@
         <v>45394</v>
       </c>
       <c r="C72" t="n">
-        <v>91.52176666259766</v>
+        <v>91.52179718017578</v>
       </c>
       <c r="D72" t="n">
-        <v>91.52176666259766</v>
+        <v>91.52179718017578</v>
       </c>
       <c r="E72" t="n">
-        <v>91.51265626104879</v>
+        <v>91.51268677558909</v>
       </c>
       <c r="F72" t="n">
-        <v>91.52176666259766</v>
+        <v>91.52179718017578</v>
       </c>
       <c r="G72" t="n">
         <v>4235400</v>
@@ -2105,16 +2105,16 @@
         <v>45397</v>
       </c>
       <c r="C73" t="n">
-        <v>91.53997802734375</v>
+        <v>91.53999328613281</v>
       </c>
       <c r="D73" t="n">
-        <v>91.53997802734375</v>
+        <v>91.53999328613281</v>
       </c>
       <c r="E73" t="n">
-        <v>91.53086762604262</v>
+        <v>91.53088288331307</v>
       </c>
       <c r="F73" t="n">
-        <v>91.53086762604262</v>
+        <v>91.53088288331307</v>
       </c>
       <c r="G73" t="n">
         <v>4144700</v>
@@ -2128,16 +2128,16 @@
         <v>45398</v>
       </c>
       <c r="C74" t="n">
-        <v>91.53997802734375</v>
+        <v>91.53999328613281</v>
       </c>
       <c r="D74" t="n">
-        <v>91.55819188074594</v>
+        <v>91.55820714257106</v>
       </c>
       <c r="E74" t="n">
-        <v>91.53997802734375</v>
+        <v>91.53999328613281</v>
       </c>
       <c r="F74" t="n">
-        <v>91.54908842864488</v>
+        <v>91.54910368895256</v>
       </c>
       <c r="G74" t="n">
         <v>4850000</v>
@@ -2151,16 +2151,16 @@
         <v>45399</v>
       </c>
       <c r="C75" t="n">
-        <v>91.56731414794922</v>
+        <v>91.56732177734375</v>
       </c>
       <c r="D75" t="n">
-        <v>91.56731414794922</v>
+        <v>91.56732177734375</v>
       </c>
       <c r="E75" t="n">
-        <v>91.55820374546751</v>
+        <v>91.55821137410295</v>
       </c>
       <c r="F75" t="n">
-        <v>91.56731414794922</v>
+        <v>91.56732177734375</v>
       </c>
       <c r="G75" t="n">
         <v>3688400</v>
@@ -2197,16 +2197,16 @@
         <v>45401</v>
       </c>
       <c r="C77" t="n">
-        <v>91.62194061279297</v>
+        <v>91.62195587158203</v>
       </c>
       <c r="D77" t="n">
-        <v>91.62194061279297</v>
+        <v>91.62195587158203</v>
       </c>
       <c r="E77" t="n">
-        <v>91.60372676141424</v>
+        <v>91.60374201716995</v>
       </c>
       <c r="F77" t="n">
-        <v>91.62194061279297</v>
+        <v>91.62195587158203</v>
       </c>
       <c r="G77" t="n">
         <v>3319500</v>
@@ -2220,16 +2220,16 @@
         <v>45404</v>
       </c>
       <c r="C78" t="n">
-        <v>91.63108825683594</v>
+        <v>91.63106536865234</v>
       </c>
       <c r="D78" t="n">
-        <v>91.63108825683594</v>
+        <v>91.63106536865234</v>
       </c>
       <c r="E78" t="n">
-        <v>91.62197785284397</v>
+        <v>91.62195496693603</v>
       </c>
       <c r="F78" t="n">
-        <v>91.63108825683594</v>
+        <v>91.63106536865234</v>
       </c>
       <c r="G78" t="n">
         <v>3547400</v>
@@ -2243,16 +2243,16 @@
         <v>45405</v>
       </c>
       <c r="C79" t="n">
-        <v>91.64015960693359</v>
+        <v>91.64016723632812</v>
       </c>
       <c r="D79" t="n">
-        <v>91.64927000704303</v>
+        <v>91.64927763719604</v>
       </c>
       <c r="E79" t="n">
-        <v>91.63104920682416</v>
+        <v>91.63105683546023</v>
       </c>
       <c r="F79" t="n">
-        <v>91.64015960693359</v>
+        <v>91.64016723632812</v>
       </c>
       <c r="G79" t="n">
         <v>4233300</v>
@@ -2266,16 +2266,16 @@
         <v>45406</v>
       </c>
       <c r="C80" t="n">
-        <v>91.64928436279297</v>
+        <v>91.6492919921875</v>
       </c>
       <c r="D80" t="n">
-        <v>91.65838781512917</v>
+        <v>91.65839544528153</v>
       </c>
       <c r="E80" t="n">
-        <v>91.64928436279297</v>
+        <v>91.6492919921875</v>
       </c>
       <c r="F80" t="n">
-        <v>91.65838781512917</v>
+        <v>91.65839544528153</v>
       </c>
       <c r="G80" t="n">
         <v>3200000</v>
@@ -2312,16 +2312,16 @@
         <v>45408</v>
       </c>
       <c r="C82" t="n">
-        <v>91.71303558349609</v>
+        <v>91.71304321289062</v>
       </c>
       <c r="D82" t="n">
-        <v>91.71303558349609</v>
+        <v>91.71304321289062</v>
       </c>
       <c r="E82" t="n">
-        <v>91.70392518272369</v>
+        <v>91.70393281136035</v>
       </c>
       <c r="F82" t="n">
-        <v>91.70392518272369</v>
+        <v>91.70393281136035</v>
       </c>
       <c r="G82" t="n">
         <v>3008600</v>
@@ -2335,16 +2335,16 @@
         <v>45411</v>
       </c>
       <c r="C83" t="n">
-        <v>91.71303558349609</v>
+        <v>91.71304321289062</v>
       </c>
       <c r="D83" t="n">
-        <v>91.72213903506884</v>
+        <v>91.72214666522066</v>
       </c>
       <c r="E83" t="n">
-        <v>91.71303558349609</v>
+        <v>91.71304321289062</v>
       </c>
       <c r="F83" t="n">
-        <v>91.72213903506884</v>
+        <v>91.72214666522066</v>
       </c>
       <c r="G83" t="n">
         <v>2501900</v>
@@ -2358,16 +2358,16 @@
         <v>45412</v>
       </c>
       <c r="C84" t="n">
-        <v>91.72215270996094</v>
+        <v>91.72214508056641</v>
       </c>
       <c r="D84" t="n">
-        <v>91.73126311209163</v>
+        <v>91.73125548193929</v>
       </c>
       <c r="E84" t="n">
-        <v>91.72215270996094</v>
+        <v>91.72214508056641</v>
       </c>
       <c r="F84" t="n">
-        <v>91.72215270996094</v>
+        <v>91.72214508056641</v>
       </c>
       <c r="G84" t="n">
         <v>6488000</v>
@@ -2427,16 +2427,16 @@
         <v>45415</v>
       </c>
       <c r="C87" t="n">
-        <v>91.81179046630859</v>
+        <v>91.81178283691406</v>
       </c>
       <c r="D87" t="n">
-        <v>91.81179046630859</v>
+        <v>91.81178283691406</v>
       </c>
       <c r="E87" t="n">
-        <v>91.79349189082433</v>
+        <v>91.79348426295037</v>
       </c>
       <c r="F87" t="n">
-        <v>91.80264117856646</v>
+        <v>91.80263354993221</v>
       </c>
       <c r="G87" t="n">
         <v>4792400</v>
@@ -2450,16 +2450,16 @@
         <v>45418</v>
       </c>
       <c r="C88" t="n">
-        <v>91.82095336914062</v>
+        <v>91.82093811035156</v>
       </c>
       <c r="D88" t="n">
-        <v>91.82095336914062</v>
+        <v>91.82093811035156</v>
       </c>
       <c r="E88" t="n">
-        <v>91.81181105820977</v>
+        <v>91.81179580093996</v>
       </c>
       <c r="F88" t="n">
-        <v>91.81181105820977</v>
+        <v>91.81179580093996</v>
       </c>
       <c r="G88" t="n">
         <v>3623700</v>
@@ -2473,16 +2473,16 @@
         <v>45419</v>
       </c>
       <c r="C89" t="n">
-        <v>91.82095336914062</v>
+        <v>91.82093811035156</v>
       </c>
       <c r="D89" t="n">
-        <v>91.83010265893481</v>
+        <v>91.83008739862531</v>
       </c>
       <c r="E89" t="n">
-        <v>91.82095336914062</v>
+        <v>91.82093811035156</v>
       </c>
       <c r="F89" t="n">
-        <v>91.83010265893481</v>
+        <v>91.83008739862531</v>
       </c>
       <c r="G89" t="n">
         <v>3591500</v>
@@ -2496,16 +2496,16 @@
         <v>45420</v>
       </c>
       <c r="C90" t="n">
-        <v>91.84840393066406</v>
+        <v>91.848388671875</v>
       </c>
       <c r="D90" t="n">
-        <v>91.84840393066406</v>
+        <v>91.848388671875</v>
       </c>
       <c r="E90" t="n">
-        <v>91.83010535053937</v>
+        <v>91.83009009479026</v>
       </c>
       <c r="F90" t="n">
-        <v>91.83925464060172</v>
+        <v>91.83923938333263</v>
       </c>
       <c r="G90" t="n">
         <v>3109400</v>
@@ -2542,16 +2542,16 @@
         <v>45422</v>
       </c>
       <c r="C92" t="n">
-        <v>91.90326690673828</v>
+        <v>91.90325927734375</v>
       </c>
       <c r="D92" t="n">
-        <v>91.90326690673828</v>
+        <v>91.90325927734375</v>
       </c>
       <c r="E92" t="n">
-        <v>91.88496833035812</v>
+        <v>91.88496070248264</v>
       </c>
       <c r="F92" t="n">
-        <v>91.90326690673828</v>
+        <v>91.90325927734375</v>
       </c>
       <c r="G92" t="n">
         <v>3005800</v>
@@ -2565,16 +2565,16 @@
         <v>45425</v>
       </c>
       <c r="C93" t="n">
-        <v>91.91242218017578</v>
+        <v>91.91244506835938</v>
       </c>
       <c r="D93" t="n">
-        <v>91.91242218017578</v>
+        <v>91.91244506835938</v>
       </c>
       <c r="E93" t="n">
-        <v>91.9032728913899</v>
+        <v>91.90329577729513</v>
       </c>
       <c r="F93" t="n">
-        <v>91.91242218017578</v>
+        <v>91.91244506835938</v>
       </c>
       <c r="G93" t="n">
         <v>3317000</v>
@@ -2588,16 +2588,16 @@
         <v>45426</v>
       </c>
       <c r="C94" t="n">
-        <v>91.91242218017578</v>
+        <v>91.91244506835938</v>
       </c>
       <c r="D94" t="n">
-        <v>91.92156449009912</v>
+        <v>91.92158738055934</v>
       </c>
       <c r="E94" t="n">
-        <v>91.91242218017578</v>
+        <v>91.91244506835938</v>
       </c>
       <c r="F94" t="n">
-        <v>91.92156449009912</v>
+        <v>91.92158738055934</v>
       </c>
       <c r="G94" t="n">
         <v>2765800</v>
@@ -2634,16 +2634,16 @@
         <v>45428</v>
       </c>
       <c r="C96" t="n">
-        <v>91.97644805908203</v>
+        <v>91.97646331787109</v>
       </c>
       <c r="D96" t="n">
-        <v>91.98559036849001</v>
+        <v>91.98560562879577</v>
       </c>
       <c r="E96" t="n">
-        <v>91.96729877081192</v>
+        <v>91.96731402808312</v>
       </c>
       <c r="F96" t="n">
-        <v>91.97644805908203</v>
+        <v>91.97646331787109</v>
       </c>
       <c r="G96" t="n">
         <v>3699500</v>
@@ -2657,16 +2657,16 @@
         <v>45429</v>
       </c>
       <c r="C97" t="n">
-        <v>91.985595703125</v>
+        <v>91.98558807373047</v>
       </c>
       <c r="D97" t="n">
-        <v>91.99474499192573</v>
+        <v>91.99473736177234</v>
       </c>
       <c r="E97" t="n">
-        <v>91.985595703125</v>
+        <v>91.98558807373047</v>
       </c>
       <c r="F97" t="n">
-        <v>91.99474499192573</v>
+        <v>91.99473736177234</v>
       </c>
       <c r="G97" t="n">
         <v>4544200</v>
@@ -2680,16 +2680,16 @@
         <v>45432</v>
       </c>
       <c r="C98" t="n">
-        <v>91.99474334716797</v>
+        <v>91.99475860595703</v>
       </c>
       <c r="D98" t="n">
-        <v>92.00389263580512</v>
+        <v>92.00390789611173</v>
       </c>
       <c r="E98" t="n">
-        <v>91.99474334716797</v>
+        <v>91.99475860595703</v>
       </c>
       <c r="F98" t="n">
-        <v>92.00389263580512</v>
+        <v>92.00390789611173</v>
       </c>
       <c r="G98" t="n">
         <v>3341000</v>
@@ -2703,16 +2703,16 @@
         <v>45433</v>
       </c>
       <c r="C99" t="n">
-        <v>92.01302337646484</v>
+        <v>92.01304626464844</v>
       </c>
       <c r="D99" t="n">
-        <v>92.02217266395162</v>
+        <v>92.02219555441108</v>
       </c>
       <c r="E99" t="n">
-        <v>92.01302337646484</v>
+        <v>92.01304626464844</v>
       </c>
       <c r="F99" t="n">
-        <v>92.01302337646484</v>
+        <v>92.01304626464844</v>
       </c>
       <c r="G99" t="n">
         <v>3774900</v>
@@ -2726,16 +2726,16 @@
         <v>45434</v>
       </c>
       <c r="C100" t="n">
-        <v>92.02220153808594</v>
+        <v>92.02217864990234</v>
       </c>
       <c r="D100" t="n">
-        <v>92.03135082844351</v>
+        <v>92.03132793798427</v>
       </c>
       <c r="E100" t="n">
-        <v>92.02220153808594</v>
+        <v>92.02217864990234</v>
       </c>
       <c r="F100" t="n">
-        <v>92.03135082844351</v>
+        <v>92.03132793798427</v>
       </c>
       <c r="G100" t="n">
         <v>2609000</v>
@@ -2772,16 +2772,16 @@
         <v>45436</v>
       </c>
       <c r="C102" t="n">
-        <v>92.09536743164062</v>
+        <v>92.09535217285156</v>
       </c>
       <c r="D102" t="n">
-        <v>92.09536743164062</v>
+        <v>92.09535217285156</v>
       </c>
       <c r="E102" t="n">
-        <v>92.08621814272074</v>
+        <v>92.08620288544756</v>
       </c>
       <c r="F102" t="n">
-        <v>92.09536743164062</v>
+        <v>92.09535217285156</v>
       </c>
       <c r="G102" t="n">
         <v>2512800</v>
@@ -2795,16 +2795,16 @@
         <v>45440</v>
       </c>
       <c r="C103" t="n">
-        <v>92.1044921875</v>
+        <v>92.10447692871094</v>
       </c>
       <c r="D103" t="n">
-        <v>92.1044921875</v>
+        <v>92.10447692871094</v>
       </c>
       <c r="E103" t="n">
-        <v>92.09534290101713</v>
+        <v>92.09532764374381</v>
       </c>
       <c r="F103" t="n">
-        <v>92.09534290101713</v>
+        <v>92.09532764374381</v>
       </c>
       <c r="G103" t="n">
         <v>3684600</v>
@@ -2818,16 +2818,16 @@
         <v>45441</v>
       </c>
       <c r="C104" t="n">
-        <v>92.1044921875</v>
+        <v>92.10447692871094</v>
       </c>
       <c r="D104" t="n">
-        <v>92.1136344951221</v>
+        <v>92.11361923481844</v>
       </c>
       <c r="E104" t="n">
-        <v>92.1044921875</v>
+        <v>92.10447692871094</v>
       </c>
       <c r="F104" t="n">
-        <v>92.1136344951221</v>
+        <v>92.11361923481844</v>
       </c>
       <c r="G104" t="n">
         <v>3971700</v>
@@ -2841,16 +2841,16 @@
         <v>45442</v>
       </c>
       <c r="C105" t="n">
-        <v>92.12281036376953</v>
+        <v>92.12279510498047</v>
       </c>
       <c r="D105" t="n">
-        <v>92.13195965289245</v>
+        <v>92.13194439258794</v>
       </c>
       <c r="E105" t="n">
-        <v>92.12281036376953</v>
+        <v>92.12279510498047</v>
       </c>
       <c r="F105" t="n">
-        <v>92.12281036376953</v>
+        <v>92.12279510498047</v>
       </c>
       <c r="G105" t="n">
         <v>3566800</v>
@@ -2864,16 +2864,16 @@
         <v>45443</v>
       </c>
       <c r="C106" t="n">
-        <v>92.15938568115234</v>
+        <v>92.15940856933594</v>
       </c>
       <c r="D106" t="n">
-        <v>92.15938568115234</v>
+        <v>92.15940856933594</v>
       </c>
       <c r="E106" t="n">
-        <v>92.15023639350471</v>
+        <v>92.15025927941603</v>
       </c>
       <c r="F106" t="n">
-        <v>92.15023639350471</v>
+        <v>92.15025927941603</v>
       </c>
       <c r="G106" t="n">
         <v>7082900</v>
@@ -2887,16 +2887,16 @@
         <v>45446</v>
       </c>
       <c r="C107" t="n">
-        <v>92.17775726318359</v>
+        <v>92.17778015136719</v>
       </c>
       <c r="D107" t="n">
-        <v>92.18693967331291</v>
+        <v>92.18696256377655</v>
       </c>
       <c r="E107" t="n">
-        <v>92.17775726318359</v>
+        <v>92.17778015136719</v>
       </c>
       <c r="F107" t="n">
-        <v>92.17775726318359</v>
+        <v>92.17778015136719</v>
       </c>
       <c r="G107" t="n">
         <v>9568200</v>
@@ -2933,16 +2933,16 @@
         <v>45448</v>
       </c>
       <c r="C109" t="n">
-        <v>92.21453857421875</v>
+        <v>92.21450805664062</v>
       </c>
       <c r="D109" t="n">
-        <v>92.21453857421875</v>
+        <v>92.21450805664062</v>
       </c>
       <c r="E109" t="n">
-        <v>92.20534915156249</v>
+        <v>92.20531863702551</v>
       </c>
       <c r="F109" t="n">
-        <v>92.20534915156249</v>
+        <v>92.20531863702551</v>
       </c>
       <c r="G109" t="n">
         <v>4285300</v>
@@ -2956,16 +2956,16 @@
         <v>45449</v>
       </c>
       <c r="C110" t="n">
-        <v>92.21453857421875</v>
+        <v>92.21450805664062</v>
       </c>
       <c r="D110" t="n">
-        <v>92.22372098739932</v>
+        <v>92.22369046678234</v>
       </c>
       <c r="E110" t="n">
-        <v>92.21453857421875</v>
+        <v>92.21450805664062</v>
       </c>
       <c r="F110" t="n">
-        <v>92.22372098739932</v>
+        <v>92.22369046678234</v>
       </c>
       <c r="G110" t="n">
         <v>3376100</v>
@@ -2979,16 +2979,16 @@
         <v>45450</v>
       </c>
       <c r="C111" t="n">
-        <v>92.25126647949219</v>
+        <v>92.25127410888672</v>
       </c>
       <c r="D111" t="n">
-        <v>92.2604488904057</v>
+        <v>92.26045652055964</v>
       </c>
       <c r="E111" t="n">
-        <v>92.25126647949219</v>
+        <v>92.25127410888672</v>
       </c>
       <c r="F111" t="n">
-        <v>92.2604488904057</v>
+        <v>92.26045652055964</v>
       </c>
       <c r="G111" t="n">
         <v>3490400</v>
@@ -3002,16 +3002,16 @@
         <v>45453</v>
       </c>
       <c r="C112" t="n">
-        <v>92.26966094970703</v>
+        <v>92.26963806152344</v>
       </c>
       <c r="D112" t="n">
-        <v>92.27885037234921</v>
+        <v>92.27882748188611</v>
       </c>
       <c r="E112" t="n">
-        <v>92.26966094970703</v>
+        <v>92.26963806152344</v>
       </c>
       <c r="F112" t="n">
-        <v>92.27885037234921</v>
+        <v>92.27882748188611</v>
       </c>
       <c r="G112" t="n">
         <v>2732300</v>
@@ -3048,16 +3048,16 @@
         <v>45455</v>
       </c>
       <c r="C114" t="n">
-        <v>92.306396484375</v>
+        <v>92.30638122558594</v>
       </c>
       <c r="D114" t="n">
-        <v>92.306396484375</v>
+        <v>92.30638122558594</v>
       </c>
       <c r="E114" t="n">
-        <v>92.28801764210641</v>
+        <v>92.28800238635547</v>
       </c>
       <c r="F114" t="n">
-        <v>92.29720706324071</v>
+        <v>92.2971918059707</v>
       </c>
       <c r="G114" t="n">
         <v>5355700</v>
@@ -3071,16 +3071,16 @@
         <v>45456</v>
       </c>
       <c r="C115" t="n">
-        <v>92.31558227539062</v>
+        <v>92.31560516357422</v>
       </c>
       <c r="D115" t="n">
-        <v>92.32476468668929</v>
+        <v>92.32478757714952</v>
       </c>
       <c r="E115" t="n">
-        <v>92.30639285461768</v>
+        <v>92.30641574052291</v>
       </c>
       <c r="F115" t="n">
-        <v>92.31558227539062</v>
+        <v>92.31560516357422</v>
       </c>
       <c r="G115" t="n">
         <v>3925700</v>
@@ -3094,16 +3094,16 @@
         <v>45457</v>
       </c>
       <c r="C116" t="n">
-        <v>92.36150360107422</v>
+        <v>92.36151123046875</v>
       </c>
       <c r="D116" t="n">
-        <v>92.36150360107422</v>
+        <v>92.36151123046875</v>
       </c>
       <c r="E116" t="n">
-        <v>92.34313177134166</v>
+        <v>92.34313939921861</v>
       </c>
       <c r="F116" t="n">
-        <v>92.35231418147126</v>
+        <v>92.3523218101067</v>
       </c>
       <c r="G116" t="n">
         <v>3505500</v>
@@ -3117,16 +3117,16 @@
         <v>45460</v>
       </c>
       <c r="C117" t="n">
-        <v>92.37071228027344</v>
+        <v>92.37068176269531</v>
       </c>
       <c r="D117" t="n">
-        <v>92.37071228027344</v>
+        <v>92.37068176269531</v>
       </c>
       <c r="E117" t="n">
-        <v>92.36152285875446</v>
+        <v>92.36149234421234</v>
       </c>
       <c r="F117" t="n">
-        <v>92.37071228027344</v>
+        <v>92.37068176269531</v>
       </c>
       <c r="G117" t="n">
         <v>3493700</v>
@@ -3140,16 +3140,16 @@
         <v>45461</v>
       </c>
       <c r="C118" t="n">
-        <v>92.39826202392578</v>
+        <v>92.39828491210938</v>
       </c>
       <c r="D118" t="n">
-        <v>92.39826202392578</v>
+        <v>92.39828491210938</v>
       </c>
       <c r="E118" t="n">
-        <v>92.38907260355165</v>
+        <v>92.38909548945891</v>
       </c>
       <c r="F118" t="n">
-        <v>92.39826202392578</v>
+        <v>92.39828491210938</v>
       </c>
       <c r="G118" t="n">
         <v>2972000</v>
@@ -3186,16 +3186,16 @@
         <v>45464</v>
       </c>
       <c r="C120" t="n">
-        <v>92.44420623779297</v>
+        <v>92.4442138671875</v>
       </c>
       <c r="D120" t="n">
-        <v>92.45338864910251</v>
+        <v>92.45339627925487</v>
       </c>
       <c r="E120" t="n">
-        <v>92.44420623779297</v>
+        <v>92.4442138671875</v>
       </c>
       <c r="F120" t="n">
-        <v>92.44420623779297</v>
+        <v>92.4442138671875</v>
       </c>
       <c r="G120" t="n">
         <v>3460900</v>
@@ -3209,16 +3209,16 @@
         <v>45467</v>
       </c>
       <c r="C121" t="n">
-        <v>92.45339202880859</v>
+        <v>92.45337677001953</v>
       </c>
       <c r="D121" t="n">
-        <v>92.46258144992834</v>
+        <v>92.46256618962263</v>
       </c>
       <c r="E121" t="n">
-        <v>92.45339202880859</v>
+        <v>92.45337677001953</v>
       </c>
       <c r="F121" t="n">
-        <v>92.46258144992834</v>
+        <v>92.46256618962263</v>
       </c>
       <c r="G121" t="n">
         <v>3369500</v>
@@ -3255,16 +3255,16 @@
         <v>45469</v>
       </c>
       <c r="C123" t="n">
-        <v>92.48094177246094</v>
+        <v>92.48094940185547</v>
       </c>
       <c r="D123" t="n">
-        <v>92.49012418226734</v>
+        <v>92.49013181241939</v>
       </c>
       <c r="E123" t="n">
-        <v>92.48094177246094</v>
+        <v>92.48094940185547</v>
       </c>
       <c r="F123" t="n">
-        <v>92.48186001344158</v>
+        <v>92.48186764291187</v>
       </c>
       <c r="G123" t="n">
         <v>4815500</v>
@@ -3301,16 +3301,16 @@
         <v>45471</v>
       </c>
       <c r="C125" t="n">
-        <v>92.52687072753906</v>
+        <v>92.52687835693359</v>
       </c>
       <c r="D125" t="n">
-        <v>92.53606014640917</v>
+        <v>92.53606777656142</v>
       </c>
       <c r="E125" t="n">
-        <v>92.52687072753906</v>
+        <v>92.52687835693359</v>
       </c>
       <c r="F125" t="n">
-        <v>92.52687072753906</v>
+        <v>92.52687835693359</v>
       </c>
       <c r="G125" t="n">
         <v>7427800</v>
@@ -3324,16 +3324,16 @@
         <v>45474</v>
       </c>
       <c r="C126" t="n">
-        <v>92.56287384033203</v>
+        <v>92.56288146972656</v>
       </c>
       <c r="D126" t="n">
-        <v>92.56287384033203</v>
+        <v>92.56288146972656</v>
       </c>
       <c r="E126" t="n">
-        <v>92.55365122745329</v>
+        <v>92.55365885608765</v>
       </c>
       <c r="F126" t="n">
-        <v>92.56287384033203</v>
+        <v>92.56288146972656</v>
       </c>
       <c r="G126" t="n">
         <v>9965300</v>
@@ -3347,16 +3347,16 @@
         <v>45475</v>
       </c>
       <c r="C127" t="n">
-        <v>92.57211303710938</v>
+        <v>92.57209014892578</v>
       </c>
       <c r="D127" t="n">
-        <v>92.57211303710938</v>
+        <v>92.57209014892578</v>
       </c>
       <c r="E127" t="n">
-        <v>92.5628833831166</v>
+        <v>92.562860497215</v>
       </c>
       <c r="F127" t="n">
-        <v>92.57211303710938</v>
+        <v>92.57209014892578</v>
       </c>
       <c r="G127" t="n">
         <v>5720900</v>
@@ -3393,16 +3393,16 @@
         <v>45478</v>
       </c>
       <c r="C129" t="n">
-        <v>92.63669586181641</v>
+        <v>92.63671112060547</v>
       </c>
       <c r="D129" t="n">
-        <v>92.63669586181641</v>
+        <v>92.63671112060547</v>
       </c>
       <c r="E129" t="n">
-        <v>92.627466208887</v>
+        <v>92.62748146615579</v>
       </c>
       <c r="F129" t="n">
-        <v>92.627466208887</v>
+        <v>92.62748146615579</v>
       </c>
       <c r="G129" t="n">
         <v>3742000</v>
@@ -3416,16 +3416,16 @@
         <v>45481</v>
       </c>
       <c r="C130" t="n">
-        <v>92.65515899658203</v>
+        <v>92.65516662597656</v>
       </c>
       <c r="D130" t="n">
-        <v>92.65515899658203</v>
+        <v>92.65516662597656</v>
       </c>
       <c r="E130" t="n">
-        <v>92.64592934327121</v>
+        <v>92.64593697190575</v>
       </c>
       <c r="F130" t="n">
-        <v>92.64592934327121</v>
+        <v>92.64593697190575</v>
       </c>
       <c r="G130" t="n">
         <v>3263000</v>
@@ -3439,16 +3439,16 @@
         <v>45482</v>
       </c>
       <c r="C131" t="n">
-        <v>92.65515899658203</v>
+        <v>92.65516662597656</v>
       </c>
       <c r="D131" t="n">
-        <v>92.67361126304097</v>
+        <v>92.67361889395488</v>
       </c>
       <c r="E131" t="n">
-        <v>92.65515899658203</v>
+        <v>92.65516662597656</v>
       </c>
       <c r="F131" t="n">
-        <v>92.66438160973014</v>
+        <v>92.66438923988407</v>
       </c>
       <c r="G131" t="n">
         <v>4508000</v>
@@ -3462,16 +3462,16 @@
         <v>45483</v>
       </c>
       <c r="C132" t="n">
-        <v>92.67362213134766</v>
+        <v>92.67361450195312</v>
       </c>
       <c r="D132" t="n">
-        <v>92.68285178574088</v>
+        <v>92.68284415558651</v>
       </c>
       <c r="E132" t="n">
-        <v>92.67362213134766</v>
+        <v>92.67361450195312</v>
       </c>
       <c r="F132" t="n">
-        <v>92.67362213134766</v>
+        <v>92.67361450195312</v>
       </c>
       <c r="G132" t="n">
         <v>4062200</v>
@@ -3508,16 +3508,16 @@
         <v>45485</v>
       </c>
       <c r="C134" t="n">
-        <v>92.73820495605469</v>
+        <v>92.73821258544922</v>
       </c>
       <c r="D134" t="n">
-        <v>92.73820495605469</v>
+        <v>92.73821258544922</v>
       </c>
       <c r="E134" t="n">
-        <v>92.72897530272394</v>
+        <v>92.72898293135917</v>
       </c>
       <c r="F134" t="n">
-        <v>92.73820495605469</v>
+        <v>92.73821258544922</v>
       </c>
       <c r="G134" t="n">
         <v>3369000</v>
@@ -3531,16 +3531,16 @@
         <v>45488</v>
       </c>
       <c r="C135" t="n">
-        <v>92.73820495605469</v>
+        <v>92.73821258544922</v>
       </c>
       <c r="D135" t="n">
-        <v>92.74743460938542</v>
+        <v>92.74744223953927</v>
       </c>
       <c r="E135" t="n">
-        <v>92.73820495605469</v>
+        <v>92.73821258544922</v>
       </c>
       <c r="F135" t="n">
-        <v>92.74743460938542</v>
+        <v>92.74744223953927</v>
       </c>
       <c r="G135" t="n">
         <v>3615100</v>
@@ -3554,16 +3554,16 @@
         <v>45489</v>
       </c>
       <c r="C136" t="n">
-        <v>92.75664520263672</v>
+        <v>92.75666046142578</v>
       </c>
       <c r="D136" t="n">
-        <v>92.75664520263672</v>
+        <v>92.75666046142578</v>
       </c>
       <c r="E136" t="n">
-        <v>92.74742259066382</v>
+        <v>92.74743784793573</v>
       </c>
       <c r="F136" t="n">
-        <v>92.75664520263672</v>
+        <v>92.75666046142578</v>
       </c>
       <c r="G136" t="n">
         <v>3622900</v>
@@ -3577,16 +3577,16 @@
         <v>45490</v>
       </c>
       <c r="C137" t="n">
-        <v>92.765869140625</v>
+        <v>92.76588439941406</v>
       </c>
       <c r="D137" t="n">
-        <v>92.77048748648878</v>
+        <v>92.77050274603751</v>
       </c>
       <c r="E137" t="n">
-        <v>92.75663948905881</v>
+        <v>92.75665474632972</v>
       </c>
       <c r="F137" t="n">
-        <v>92.765869140625</v>
+        <v>92.76588439941406</v>
       </c>
       <c r="G137" t="n">
         <v>3822100</v>
@@ -3600,16 +3600,16 @@
         <v>45491</v>
       </c>
       <c r="C138" t="n">
-        <v>92.78433990478516</v>
+        <v>92.78435516357422</v>
       </c>
       <c r="D138" t="n">
-        <v>92.78433990478516</v>
+        <v>92.78435516357422</v>
       </c>
       <c r="E138" t="n">
-        <v>92.77511025207889</v>
+        <v>92.77512550935009</v>
       </c>
       <c r="F138" t="n">
-        <v>92.77511025207889</v>
+        <v>92.77512550935009</v>
       </c>
       <c r="G138" t="n">
         <v>5291400</v>
@@ -3623,16 +3623,16 @@
         <v>45492</v>
       </c>
       <c r="C139" t="n">
-        <v>92.82125091552734</v>
+        <v>92.82126617431641</v>
       </c>
       <c r="D139" t="n">
-        <v>92.82125091552734</v>
+        <v>92.82126617431641</v>
       </c>
       <c r="E139" t="n">
-        <v>92.81202830233946</v>
+        <v>92.81204355961242</v>
       </c>
       <c r="F139" t="n">
-        <v>92.82125091552734</v>
+        <v>92.82126617431641</v>
       </c>
       <c r="G139" t="n">
         <v>2993600</v>
@@ -3669,16 +3669,16 @@
         <v>45496</v>
       </c>
       <c r="C141" t="n">
-        <v>92.84893798828125</v>
+        <v>92.84894561767578</v>
       </c>
       <c r="D141" t="n">
-        <v>92.85816060128167</v>
+        <v>92.85816823143402</v>
       </c>
       <c r="E141" t="n">
-        <v>92.83970833511823</v>
+        <v>92.83971596375436</v>
       </c>
       <c r="F141" t="n">
-        <v>92.84893798828125</v>
+        <v>92.84894561767578</v>
       </c>
       <c r="G141" t="n">
         <v>2829200</v>
@@ -3692,16 +3692,16 @@
         <v>45497</v>
       </c>
       <c r="C142" t="n">
-        <v>92.85816192626953</v>
+        <v>92.858154296875</v>
       </c>
       <c r="D142" t="n">
-        <v>92.86739157956426</v>
+        <v>92.86738394941139</v>
       </c>
       <c r="E142" t="n">
-        <v>92.84893931313751</v>
+        <v>92.84893168450073</v>
       </c>
       <c r="F142" t="n">
-        <v>92.85816192626953</v>
+        <v>92.858154296875</v>
       </c>
       <c r="G142" t="n">
         <v>3474500</v>
@@ -3715,16 +3715,16 @@
         <v>45498</v>
       </c>
       <c r="C143" t="n">
-        <v>92.87663269042969</v>
+        <v>92.87662506103516</v>
       </c>
       <c r="D143" t="n">
-        <v>92.87663269042969</v>
+        <v>92.87662506103516</v>
       </c>
       <c r="E143" t="n">
-        <v>92.86740303599636</v>
+        <v>92.86739540736002</v>
       </c>
       <c r="F143" t="n">
-        <v>92.87663269042969</v>
+        <v>92.87662506103516</v>
       </c>
       <c r="G143" t="n">
         <v>3521700</v>
@@ -3738,16 +3738,16 @@
         <v>45499</v>
       </c>
       <c r="C144" t="n">
-        <v>92.90430450439453</v>
+        <v>92.904296875</v>
       </c>
       <c r="D144" t="n">
-        <v>92.91353415782355</v>
+        <v>92.91352652767107</v>
       </c>
       <c r="E144" t="n">
-        <v>92.90430450439453</v>
+        <v>92.904296875</v>
       </c>
       <c r="F144" t="n">
-        <v>92.90430450439453</v>
+        <v>92.904296875</v>
       </c>
       <c r="G144" t="n">
         <v>3172600</v>
@@ -3807,16 +3807,16 @@
         <v>45504</v>
       </c>
       <c r="C147" t="n">
-        <v>92.94119262695312</v>
+        <v>92.94120788574219</v>
       </c>
       <c r="D147" t="n">
-        <v>92.95042227805331</v>
+        <v>92.95043753835766</v>
       </c>
       <c r="E147" t="n">
-        <v>92.94119262695312</v>
+        <v>92.94120788574219</v>
       </c>
       <c r="F147" t="n">
-        <v>92.94119262695312</v>
+        <v>92.94120788574219</v>
       </c>
       <c r="G147" t="n">
         <v>7256900</v>
@@ -3830,16 +3830,16 @@
         <v>45505</v>
       </c>
       <c r="C148" t="n">
-        <v>92.97181701660156</v>
+        <v>92.97177886962891</v>
       </c>
       <c r="D148" t="n">
-        <v>92.97181701660156</v>
+        <v>92.97177886962891</v>
       </c>
       <c r="E148" t="n">
-        <v>92.96254566315092</v>
+        <v>92.96250751998235</v>
       </c>
       <c r="F148" t="n">
-        <v>92.97181701660156</v>
+        <v>92.97177886962891</v>
       </c>
       <c r="G148" t="n">
         <v>11015600</v>
@@ -3853,16 +3853,16 @@
         <v>45506</v>
       </c>
       <c r="C149" t="n">
-        <v>93.01815032958984</v>
+        <v>93.01814270019531</v>
       </c>
       <c r="D149" t="n">
-        <v>93.01815032958984</v>
+        <v>93.01814270019531</v>
       </c>
       <c r="E149" t="n">
-        <v>92.9996146965144</v>
+        <v>92.99960706864016</v>
       </c>
       <c r="F149" t="n">
-        <v>93.00887897706717</v>
+        <v>93.00887134843308</v>
       </c>
       <c r="G149" t="n">
         <v>7927400</v>
@@ -3876,16 +3876,16 @@
         <v>45509</v>
       </c>
       <c r="C150" t="n">
-        <v>93.02742767333984</v>
+        <v>93.02742004394531</v>
       </c>
       <c r="D150" t="n">
-        <v>93.04596330760904</v>
+        <v>93.04595567669436</v>
       </c>
       <c r="E150" t="n">
-        <v>93.01815632022007</v>
+        <v>93.01814869158591</v>
       </c>
       <c r="F150" t="n">
-        <v>93.01815632022007</v>
+        <v>93.01814869158591</v>
       </c>
       <c r="G150" t="n">
         <v>8712900</v>
@@ -3899,16 +3899,16 @@
         <v>45510</v>
       </c>
       <c r="C151" t="n">
-        <v>93.04595184326172</v>
+        <v>93.04595947265625</v>
       </c>
       <c r="D151" t="n">
-        <v>93.04595184326172</v>
+        <v>93.04595947265625</v>
       </c>
       <c r="E151" t="n">
-        <v>93.02741621127633</v>
+        <v>93.02742383915101</v>
       </c>
       <c r="F151" t="n">
-        <v>93.02741621127633</v>
+        <v>93.02742383915101</v>
       </c>
       <c r="G151" t="n">
         <v>5059100</v>
@@ -3922,16 +3922,16 @@
         <v>45511</v>
       </c>
       <c r="C152" t="n">
-        <v>93.04595184326172</v>
+        <v>93.04595947265625</v>
       </c>
       <c r="D152" t="n">
-        <v>93.05522319523915</v>
+        <v>93.05523082539389</v>
       </c>
       <c r="E152" t="n">
-        <v>93.04595184326172</v>
+        <v>93.04595947265625</v>
       </c>
       <c r="F152" t="n">
-        <v>93.04595184326172</v>
+        <v>93.04595947265625</v>
       </c>
       <c r="G152" t="n">
         <v>4611400</v>
@@ -3945,16 +3945,16 @@
         <v>45512</v>
       </c>
       <c r="C153" t="n">
-        <v>93.07376861572266</v>
+        <v>93.07377624511719</v>
       </c>
       <c r="D153" t="n">
-        <v>93.07376861572266</v>
+        <v>93.07377624511719</v>
       </c>
       <c r="E153" t="n">
-        <v>93.05522591122659</v>
+        <v>93.05523353910115</v>
       </c>
       <c r="F153" t="n">
-        <v>93.06449726347462</v>
+        <v>93.06450489210917</v>
       </c>
       <c r="G153" t="n">
         <v>3903300</v>
@@ -3991,16 +3991,16 @@
         <v>45516</v>
       </c>
       <c r="C155" t="n">
-        <v>93.12010955810547</v>
+        <v>93.1201171875</v>
       </c>
       <c r="D155" t="n">
-        <v>93.12938091018674</v>
+        <v>93.12938854034087</v>
       </c>
       <c r="E155" t="n">
-        <v>93.1108382060242</v>
+        <v>93.11084583465912</v>
       </c>
       <c r="F155" t="n">
-        <v>93.12010955810547</v>
+        <v>93.1201171875</v>
       </c>
       <c r="G155" t="n">
         <v>3845400</v>
@@ -4014,16 +4014,16 @@
         <v>45517</v>
       </c>
       <c r="C156" t="n">
-        <v>93.13864898681641</v>
+        <v>93.138671875</v>
       </c>
       <c r="D156" t="n">
-        <v>93.13864898681641</v>
+        <v>93.138671875</v>
       </c>
       <c r="E156" t="n">
-        <v>93.12937763506119</v>
+        <v>93.1294005209664</v>
       </c>
       <c r="F156" t="n">
-        <v>93.13864898681641</v>
+        <v>93.138671875</v>
       </c>
       <c r="G156" t="n">
         <v>4782200</v>
@@ -4083,16 +4083,16 @@
         <v>45520</v>
       </c>
       <c r="C159" t="n">
-        <v>93.20352935791016</v>
+        <v>93.20354461669922</v>
       </c>
       <c r="D159" t="n">
-        <v>93.20352935791016</v>
+        <v>93.20354461669922</v>
       </c>
       <c r="E159" t="n">
-        <v>93.19425800664706</v>
+        <v>93.19427326391828</v>
       </c>
       <c r="F159" t="n">
-        <v>93.20352935791016</v>
+        <v>93.20354461669922</v>
       </c>
       <c r="G159" t="n">
         <v>3638900</v>
@@ -4129,16 +4129,16 @@
         <v>45524</v>
       </c>
       <c r="C161" t="n">
-        <v>93.22208404541016</v>
+        <v>93.22209167480469</v>
       </c>
       <c r="D161" t="n">
-        <v>93.23135539856855</v>
+        <v>93.23136302872186</v>
       </c>
       <c r="E161" t="n">
-        <v>93.22208404541016</v>
+        <v>93.22209167480469</v>
       </c>
       <c r="F161" t="n">
-        <v>93.23135539856855</v>
+        <v>93.23136302872186</v>
       </c>
       <c r="G161" t="n">
         <v>3084200</v>
@@ -4152,16 +4152,16 @@
         <v>45525</v>
       </c>
       <c r="C162" t="n">
-        <v>93.24989318847656</v>
+        <v>93.24988555908203</v>
       </c>
       <c r="D162" t="n">
-        <v>93.24989318847656</v>
+        <v>93.24988555908203</v>
       </c>
       <c r="E162" t="n">
-        <v>93.23135755370167</v>
+        <v>93.23134992582368</v>
       </c>
       <c r="F162" t="n">
-        <v>93.23135755370167</v>
+        <v>93.23134992582368</v>
       </c>
       <c r="G162" t="n">
         <v>3936000</v>
@@ -4175,16 +4175,16 @@
         <v>45526</v>
       </c>
       <c r="C163" t="n">
-        <v>93.24989318847656</v>
+        <v>93.24988555908203</v>
       </c>
       <c r="D163" t="n">
-        <v>93.25916454184927</v>
+        <v>93.25915691169619</v>
       </c>
       <c r="E163" t="n">
-        <v>93.24989318847656</v>
+        <v>93.24988555908203</v>
       </c>
       <c r="F163" t="n">
-        <v>93.25916454184927</v>
+        <v>93.25915691169619</v>
       </c>
       <c r="G163" t="n">
         <v>3849100</v>
@@ -4198,16 +4198,16 @@
         <v>45527</v>
       </c>
       <c r="C164" t="n">
-        <v>93.28695678710938</v>
+        <v>93.28697204589844</v>
       </c>
       <c r="D164" t="n">
-        <v>93.29622813901686</v>
+        <v>93.29624339932242</v>
       </c>
       <c r="E164" t="n">
-        <v>93.28695678710938</v>
+        <v>93.28697204589844</v>
       </c>
       <c r="F164" t="n">
-        <v>93.29622813901686</v>
+        <v>93.29624339932242</v>
       </c>
       <c r="G164" t="n">
         <v>3549900</v>
@@ -4221,16 +4221,16 @@
         <v>45530</v>
       </c>
       <c r="C165" t="n">
-        <v>93.30549621582031</v>
+        <v>93.30547332763672</v>
       </c>
       <c r="D165" t="n">
-        <v>93.31476049543321</v>
+        <v>93.31473760497704</v>
       </c>
       <c r="E165" t="n">
-        <v>93.30549621582031</v>
+        <v>93.30547332763672</v>
       </c>
       <c r="F165" t="n">
-        <v>93.30549621582031</v>
+        <v>93.30547332763672</v>
       </c>
       <c r="G165" t="n">
         <v>3969000</v>
@@ -4244,16 +4244,16 @@
         <v>45531</v>
       </c>
       <c r="C166" t="n">
-        <v>93.31476593017578</v>
+        <v>93.31477355957031</v>
       </c>
       <c r="D166" t="n">
-        <v>93.32403728229781</v>
+        <v>93.32404491245036</v>
       </c>
       <c r="E166" t="n">
-        <v>93.31476593017578</v>
+        <v>93.31477355957031</v>
       </c>
       <c r="F166" t="n">
-        <v>93.32403728229781</v>
+        <v>93.32404491245036</v>
       </c>
       <c r="G166" t="n">
         <v>2818100</v>
@@ -4267,16 +4267,16 @@
         <v>45532</v>
       </c>
       <c r="C167" t="n">
-        <v>93.32403564453125</v>
+        <v>93.32402801513672</v>
       </c>
       <c r="D167" t="n">
-        <v>93.33330699649056</v>
+        <v>93.33329936633808</v>
       </c>
       <c r="E167" t="n">
-        <v>93.32403564453125</v>
+        <v>93.32402801513672</v>
       </c>
       <c r="F167" t="n">
-        <v>93.33330699649056</v>
+        <v>93.33329936633808</v>
       </c>
       <c r="G167" t="n">
         <v>3500800</v>
@@ -4290,16 +4290,16 @@
         <v>45533</v>
       </c>
       <c r="C168" t="n">
-        <v>93.33331298828125</v>
+        <v>93.33329010009766</v>
       </c>
       <c r="D168" t="n">
-        <v>93.35184862142037</v>
+        <v>93.35182572869128</v>
       </c>
       <c r="E168" t="n">
-        <v>93.33331298828125</v>
+        <v>93.33329010009766</v>
       </c>
       <c r="F168" t="n">
-        <v>93.34257726886585</v>
+        <v>93.34255437841038</v>
       </c>
       <c r="G168" t="n">
         <v>4537700</v>
@@ -4313,16 +4313,16 @@
         <v>45534</v>
       </c>
       <c r="C169" t="n">
-        <v>93.37965393066406</v>
+        <v>93.37966918945312</v>
       </c>
       <c r="D169" t="n">
-        <v>93.38892528305213</v>
+        <v>93.3889405433562</v>
       </c>
       <c r="E169" t="n">
-        <v>93.37965393066406</v>
+        <v>93.37966918945312</v>
       </c>
       <c r="F169" t="n">
-        <v>93.37965393066406</v>
+        <v>93.37966918945312</v>
       </c>
       <c r="G169" t="n">
         <v>8427400</v>
@@ -4359,16 +4359,16 @@
         <v>45539</v>
       </c>
       <c r="C171" t="n">
-        <v>93.42995452880859</v>
+        <v>93.429931640625</v>
       </c>
       <c r="D171" t="n">
-        <v>93.43926692688945</v>
+        <v>93.43924403642453</v>
       </c>
       <c r="E171" t="n">
-        <v>93.42995452880859</v>
+        <v>93.429931640625</v>
       </c>
       <c r="F171" t="n">
-        <v>93.43926692688945</v>
+        <v>93.43924403642453</v>
       </c>
       <c r="G171" t="n">
         <v>7218300</v>
@@ -4382,16 +4382,16 @@
         <v>45540</v>
       </c>
       <c r="C172" t="n">
-        <v>93.45787811279297</v>
+        <v>93.45786285400391</v>
       </c>
       <c r="D172" t="n">
-        <v>93.45787811279297</v>
+        <v>93.45786285400391</v>
       </c>
       <c r="E172" t="n">
-        <v>93.439260421206</v>
+        <v>93.43924516545663</v>
       </c>
       <c r="F172" t="n">
-        <v>93.44857281863847</v>
+        <v>93.44855756136867</v>
       </c>
       <c r="G172" t="n">
         <v>4833300</v>
@@ -4428,16 +4428,16 @@
         <v>45544</v>
       </c>
       <c r="C174" t="n">
-        <v>93.50443267822266</v>
+        <v>93.50440979003906</v>
       </c>
       <c r="D174" t="n">
-        <v>93.51374507562342</v>
+        <v>93.51372218516032</v>
       </c>
       <c r="E174" t="n">
-        <v>93.50443267822266</v>
+        <v>93.50440979003906</v>
       </c>
       <c r="F174" t="n">
-        <v>93.50443267822266</v>
+        <v>93.50440979003906</v>
       </c>
       <c r="G174" t="n">
         <v>5397400</v>
@@ -4451,16 +4451,16 @@
         <v>45545</v>
       </c>
       <c r="C175" t="n">
-        <v>93.52301788330078</v>
+        <v>93.52302551269531</v>
       </c>
       <c r="D175" t="n">
-        <v>93.52301788330078</v>
+        <v>93.52302551269531</v>
       </c>
       <c r="E175" t="n">
-        <v>93.50440019824431</v>
+        <v>93.50440782612006</v>
       </c>
       <c r="F175" t="n">
-        <v>93.52301788330078</v>
+        <v>93.52302551269531</v>
       </c>
       <c r="G175" t="n">
         <v>4143900</v>
@@ -4474,16 +4474,16 @@
         <v>45546</v>
       </c>
       <c r="C176" t="n">
-        <v>93.52301788330078</v>
+        <v>93.52302551269531</v>
       </c>
       <c r="D176" t="n">
-        <v>93.53233027746676</v>
+        <v>93.53233790762097</v>
       </c>
       <c r="E176" t="n">
-        <v>93.52301788330078</v>
+        <v>93.52302551269531</v>
       </c>
       <c r="F176" t="n">
-        <v>93.52301788330078</v>
+        <v>93.52302551269531</v>
       </c>
       <c r="G176" t="n">
         <v>4500100</v>
@@ -4520,16 +4520,16 @@
         <v>45548</v>
       </c>
       <c r="C178" t="n">
-        <v>93.58819580078125</v>
+        <v>93.58821105957031</v>
       </c>
       <c r="D178" t="n">
-        <v>93.58819580078125</v>
+        <v>93.58821105957031</v>
       </c>
       <c r="E178" t="n">
-        <v>93.56957811465753</v>
+        <v>93.56959337041114</v>
       </c>
       <c r="F178" t="n">
-        <v>93.56957811465753</v>
+        <v>93.56959337041114</v>
       </c>
       <c r="G178" t="n">
         <v>3465200</v>
@@ -4543,16 +4543,16 @@
         <v>45551</v>
       </c>
       <c r="C179" t="n">
-        <v>93.60682678222656</v>
+        <v>93.60681915283203</v>
       </c>
       <c r="D179" t="n">
-        <v>93.60682678222656</v>
+        <v>93.60681915283203</v>
       </c>
       <c r="E179" t="n">
-        <v>93.58820199159494</v>
+        <v>93.58819436371842</v>
       </c>
       <c r="F179" t="n">
-        <v>93.58820199159494</v>
+        <v>93.58819436371842</v>
       </c>
       <c r="G179" t="n">
         <v>3571100</v>
@@ -4566,16 +4566,16 @@
         <v>45552</v>
       </c>
       <c r="C180" t="n">
-        <v>93.60682678222656</v>
+        <v>93.60681915283203</v>
       </c>
       <c r="D180" t="n">
-        <v>93.62544446958184</v>
+        <v>93.62543683866987</v>
       </c>
       <c r="E180" t="n">
-        <v>93.60682678222656</v>
+        <v>93.60681915283203</v>
       </c>
       <c r="F180" t="n">
-        <v>93.61613917754238</v>
+        <v>93.61613154738885</v>
       </c>
       <c r="G180" t="n">
         <v>4452200</v>
@@ -4589,16 +4589,16 @@
         <v>45553</v>
       </c>
       <c r="C181" t="n">
-        <v>93.634765625</v>
+        <v>93.63477325439453</v>
       </c>
       <c r="D181" t="n">
-        <v>93.64407802118704</v>
+        <v>93.64408565134035</v>
       </c>
       <c r="E181" t="n">
-        <v>93.62545322881296</v>
+        <v>93.6254608574487</v>
       </c>
       <c r="F181" t="n">
-        <v>93.62545322881296</v>
+        <v>93.6254608574487</v>
       </c>
       <c r="G181" t="n">
         <v>4077700</v>
@@ -4612,16 +4612,16 @@
         <v>45554</v>
       </c>
       <c r="C182" t="n">
-        <v>93.65337371826172</v>
+        <v>93.65339660644531</v>
       </c>
       <c r="D182" t="n">
-        <v>93.6626861134946</v>
+        <v>93.66270900395408</v>
       </c>
       <c r="E182" t="n">
-        <v>93.64406842630514</v>
+        <v>93.64409131221458</v>
       </c>
       <c r="F182" t="n">
-        <v>93.64406842630514</v>
+        <v>93.64409131221458</v>
       </c>
       <c r="G182" t="n">
         <v>5165800</v>
@@ -4658,16 +4658,16 @@
         <v>45558</v>
       </c>
       <c r="C184" t="n">
-        <v>93.71855163574219</v>
+        <v>93.71853637695312</v>
       </c>
       <c r="D184" t="n">
-        <v>93.71855163574219</v>
+        <v>93.71853637695312</v>
       </c>
       <c r="E184" t="n">
-        <v>93.69992684562337</v>
+        <v>93.6999115898667</v>
       </c>
       <c r="F184" t="n">
-        <v>93.70923924068278</v>
+        <v>93.70922398340991</v>
       </c>
       <c r="G184" t="n">
         <v>5220900</v>
@@ -4681,16 +4681,16 @@
         <v>45559</v>
       </c>
       <c r="C185" t="n">
-        <v>93.72785949707031</v>
+        <v>93.72786712646484</v>
       </c>
       <c r="D185" t="n">
-        <v>93.72785949707031</v>
+        <v>93.72786712646484</v>
       </c>
       <c r="E185" t="n">
-        <v>93.71855420503198</v>
+        <v>93.71856183366906</v>
       </c>
       <c r="F185" t="n">
-        <v>93.71855420503198</v>
+        <v>93.71856183366906</v>
       </c>
       <c r="G185" t="n">
         <v>3923500</v>
@@ -4704,16 +4704,16 @@
         <v>45560</v>
       </c>
       <c r="C186" t="n">
-        <v>93.72785949707031</v>
+        <v>93.72786712646484</v>
       </c>
       <c r="D186" t="n">
-        <v>93.74648428769973</v>
+        <v>93.7464919186103</v>
       </c>
       <c r="E186" t="n">
-        <v>93.72785949707031</v>
+        <v>93.72786712646484</v>
       </c>
       <c r="F186" t="n">
-        <v>93.73717189238502</v>
+        <v>93.73717952253757</v>
       </c>
       <c r="G186" t="n">
         <v>3372400</v>
@@ -4727,16 +4727,16 @@
         <v>45561</v>
       </c>
       <c r="C187" t="n">
-        <v>93.73717498779297</v>
+        <v>93.73715972900391</v>
       </c>
       <c r="D187" t="n">
-        <v>93.74648738341519</v>
+        <v>93.74647212311024</v>
       </c>
       <c r="E187" t="n">
-        <v>93.73717498779297</v>
+        <v>93.73715972900391</v>
       </c>
       <c r="F187" t="n">
-        <v>93.73717498779297</v>
+        <v>93.73715972900391</v>
       </c>
       <c r="G187" t="n">
         <v>4364400</v>
@@ -4750,16 +4750,16 @@
         <v>45562</v>
       </c>
       <c r="C188" t="n">
-        <v>93.77440643310547</v>
+        <v>93.77442169189453</v>
       </c>
       <c r="D188" t="n">
-        <v>93.78371882763196</v>
+        <v>93.78373408793631</v>
       </c>
       <c r="E188" t="n">
-        <v>93.77440643310547</v>
+        <v>93.77442169189453</v>
       </c>
       <c r="F188" t="n">
-        <v>93.77440643310547</v>
+        <v>93.77442169189453</v>
       </c>
       <c r="G188" t="n">
         <v>4945400</v>
@@ -4773,16 +4773,16 @@
         <v>45565</v>
       </c>
       <c r="C189" t="n">
-        <v>93.77440643310547</v>
+        <v>93.77442169189453</v>
       </c>
       <c r="D189" t="n">
-        <v>93.79302411888267</v>
+        <v>93.79303938070117</v>
       </c>
       <c r="E189" t="n">
-        <v>93.77440643310547</v>
+        <v>93.77442169189453</v>
       </c>
       <c r="F189" t="n">
-        <v>93.78371882763196</v>
+        <v>93.78373408793631</v>
       </c>
       <c r="G189" t="n">
         <v>9253100</v>
@@ -4796,16 +4796,16 @@
         <v>45566</v>
       </c>
       <c r="C190" t="n">
-        <v>93.81181335449219</v>
+        <v>93.81182861328125</v>
       </c>
       <c r="D190" t="n">
-        <v>93.81181335449219</v>
+        <v>93.81182861328125</v>
       </c>
       <c r="E190" t="n">
-        <v>93.80246103195581</v>
+        <v>93.80247628922369</v>
       </c>
       <c r="F190" t="n">
-        <v>93.81181335449219</v>
+        <v>93.81182861328125</v>
       </c>
       <c r="G190" t="n">
         <v>11569200</v>
@@ -4819,16 +4819,16 @@
         <v>45567</v>
       </c>
       <c r="C191" t="n">
-        <v>93.81181335449219</v>
+        <v>93.81182861328125</v>
       </c>
       <c r="D191" t="n">
-        <v>93.82115854329665</v>
+        <v>93.82117380360573</v>
       </c>
       <c r="E191" t="n">
-        <v>93.81181335449219</v>
+        <v>93.81182861328125</v>
       </c>
       <c r="F191" t="n">
-        <v>93.82115854329665</v>
+        <v>93.82117380360573</v>
       </c>
       <c r="G191" t="n">
         <v>5170300</v>
@@ -4842,16 +4842,16 @@
         <v>45568</v>
       </c>
       <c r="C192" t="n">
-        <v>93.8211669921875</v>
+        <v>93.82115936279297</v>
       </c>
       <c r="D192" t="n">
-        <v>93.83051931556608</v>
+        <v>93.83051168541103</v>
       </c>
       <c r="E192" t="n">
-        <v>93.8211669921875</v>
+        <v>93.82115936279297</v>
       </c>
       <c r="F192" t="n">
-        <v>93.83051931556608</v>
+        <v>93.83051168541103</v>
       </c>
       <c r="G192" t="n">
         <v>4066100</v>
@@ -4865,16 +4865,16 @@
         <v>45569</v>
       </c>
       <c r="C193" t="n">
-        <v>93.85858154296875</v>
+        <v>93.85856628417969</v>
       </c>
       <c r="D193" t="n">
-        <v>93.86793386758201</v>
+        <v>93.86791860727251</v>
       </c>
       <c r="E193" t="n">
-        <v>93.85858154296875</v>
+        <v>93.85856628417969</v>
       </c>
       <c r="F193" t="n">
-        <v>93.86326127214213</v>
+        <v>93.86324601259227</v>
       </c>
       <c r="G193" t="n">
         <v>4987100</v>
@@ -4888,16 +4888,16 @@
         <v>45572</v>
       </c>
       <c r="C194" t="n">
-        <v>93.86789703369141</v>
+        <v>93.86793518066406</v>
       </c>
       <c r="D194" t="n">
-        <v>93.8772493546348</v>
+        <v>93.87728750540813</v>
       </c>
       <c r="E194" t="n">
-        <v>93.86789703369141</v>
+        <v>93.86793518066406</v>
       </c>
       <c r="F194" t="n">
-        <v>93.86789703369141</v>
+        <v>93.86793518066406</v>
       </c>
       <c r="G194" t="n">
         <v>4792500</v>
@@ -4911,16 +4911,16 @@
         <v>45573</v>
       </c>
       <c r="C195" t="n">
-        <v>93.87728881835938</v>
+        <v>93.87728118896484</v>
       </c>
       <c r="D195" t="n">
-        <v>93.88664114323426</v>
+        <v>93.88663351307966</v>
       </c>
       <c r="E195" t="n">
-        <v>93.87728881835938</v>
+        <v>93.87728118896484</v>
       </c>
       <c r="F195" t="n">
-        <v>93.87728881835938</v>
+        <v>93.87728118896484</v>
       </c>
       <c r="G195" t="n">
         <v>3923100</v>
@@ -4934,16 +4934,16 @@
         <v>45574</v>
       </c>
       <c r="C196" t="n">
-        <v>93.89597320556641</v>
+        <v>93.89596557617188</v>
       </c>
       <c r="D196" t="n">
-        <v>93.90532552913362</v>
+        <v>93.90531789897918</v>
       </c>
       <c r="E196" t="n">
-        <v>93.8866280157319</v>
+        <v>93.8866203870967</v>
       </c>
       <c r="F196" t="n">
-        <v>93.89597320556641</v>
+        <v>93.89596557617188</v>
       </c>
       <c r="G196" t="n">
         <v>4024800</v>
@@ -4957,16 +4957,16 @@
         <v>45575</v>
       </c>
       <c r="C197" t="n">
-        <v>93.91468811035156</v>
+        <v>93.91465759277344</v>
       </c>
       <c r="D197" t="n">
-        <v>93.91468811035156</v>
+        <v>93.91465759277344</v>
       </c>
       <c r="E197" t="n">
-        <v>93.90533578576286</v>
+        <v>93.90530527122378</v>
       </c>
       <c r="F197" t="n">
-        <v>93.91468811035156</v>
+        <v>93.91465759277344</v>
       </c>
       <c r="G197" t="n">
         <v>3731100</v>
@@ -4980,16 +4980,16 @@
         <v>45576</v>
       </c>
       <c r="C198" t="n">
-        <v>93.95206451416016</v>
+        <v>93.95209503173828</v>
       </c>
       <c r="D198" t="n">
-        <v>93.96140970245301</v>
+        <v>93.96144022306665</v>
       </c>
       <c r="E198" t="n">
-        <v>93.95206451416016</v>
+        <v>93.95209503173828</v>
       </c>
       <c r="F198" t="n">
-        <v>93.95206451416016</v>
+        <v>93.95209503173828</v>
       </c>
       <c r="G198" t="n">
         <v>3778400</v>
@@ -5003,16 +5003,16 @@
         <v>45579</v>
       </c>
       <c r="C199" t="n">
-        <v>93.95206451416016</v>
+        <v>93.95209503173828</v>
       </c>
       <c r="D199" t="n">
-        <v>93.96140970245301</v>
+        <v>93.96144022306665</v>
       </c>
       <c r="E199" t="n">
-        <v>93.95206451416016</v>
+        <v>93.95209503173828</v>
       </c>
       <c r="F199" t="n">
-        <v>93.95206451416016</v>
+        <v>93.95209503173828</v>
       </c>
       <c r="G199" t="n">
         <v>3297100</v>
@@ -5026,16 +5026,16 @@
         <v>45580</v>
       </c>
       <c r="C200" t="n">
-        <v>93.97077178955078</v>
+        <v>93.97076416015625</v>
       </c>
       <c r="D200" t="n">
-        <v>93.97077178955078</v>
+        <v>93.97076416015625</v>
       </c>
       <c r="E200" t="n">
-        <v>93.96141946655455</v>
+        <v>93.96141183791931</v>
       </c>
       <c r="F200" t="n">
-        <v>93.97077178955078</v>
+        <v>93.97076416015625</v>
       </c>
       <c r="G200" t="n">
         <v>3567400</v>
@@ -5049,16 +5049,16 @@
         <v>45581</v>
       </c>
       <c r="C201" t="n">
-        <v>93.98945617675781</v>
+        <v>93.98947143554688</v>
       </c>
       <c r="D201" t="n">
-        <v>93.98945617675781</v>
+        <v>93.98947143554688</v>
       </c>
       <c r="E201" t="n">
-        <v>93.98011098879884</v>
+        <v>93.98012624607075</v>
       </c>
       <c r="F201" t="n">
-        <v>93.98011098879884</v>
+        <v>93.98012624607075</v>
       </c>
       <c r="G201" t="n">
         <v>3809900</v>
@@ -5072,16 +5072,16 @@
         <v>45582</v>
       </c>
       <c r="C202" t="n">
-        <v>93.98945617675781</v>
+        <v>93.98947143554688</v>
       </c>
       <c r="D202" t="n">
-        <v>93.99880849844806</v>
+        <v>93.99882375875542</v>
       </c>
       <c r="E202" t="n">
-        <v>93.98945617675781</v>
+        <v>93.98947143554688</v>
       </c>
       <c r="F202" t="n">
-        <v>93.98945617675781</v>
+        <v>93.98947143554688</v>
       </c>
       <c r="G202" t="n">
         <v>3575500</v>
@@ -5118,16 +5118,16 @@
         <v>45586</v>
       </c>
       <c r="C204" t="n">
-        <v>94.04556274414062</v>
+        <v>94.04557800292969</v>
       </c>
       <c r="D204" t="n">
-        <v>94.04556274414062</v>
+        <v>94.04557800292969</v>
       </c>
       <c r="E204" t="n">
-        <v>94.03621042247316</v>
+        <v>94.03622567974483</v>
       </c>
       <c r="F204" t="n">
-        <v>94.03621042247316</v>
+        <v>94.03622567974483</v>
       </c>
       <c r="G204" t="n">
         <v>3940600</v>
@@ -5141,16 +5141,16 @@
         <v>45587</v>
       </c>
       <c r="C205" t="n">
-        <v>94.05492401123047</v>
+        <v>94.054931640625</v>
       </c>
       <c r="D205" t="n">
-        <v>94.05492401123047</v>
+        <v>94.054931640625</v>
       </c>
       <c r="E205" t="n">
-        <v>94.04557882169665</v>
+        <v>94.04558645033313</v>
       </c>
       <c r="F205" t="n">
-        <v>94.05492401123047</v>
+        <v>94.054931640625</v>
       </c>
       <c r="G205" t="n">
         <v>3462800</v>
@@ -5164,16 +5164,16 @@
         <v>45588</v>
       </c>
       <c r="C206" t="n">
-        <v>94.05492401123047</v>
+        <v>94.054931640625</v>
       </c>
       <c r="D206" t="n">
-        <v>94.07362865776304</v>
+        <v>94.07363628867482</v>
       </c>
       <c r="E206" t="n">
-        <v>94.05492401123047</v>
+        <v>94.054931640625</v>
       </c>
       <c r="F206" t="n">
-        <v>94.07362865776304</v>
+        <v>94.07363628867482</v>
       </c>
       <c r="G206" t="n">
         <v>3927700</v>
@@ -5187,16 +5187,16 @@
         <v>45589</v>
       </c>
       <c r="C207" t="n">
-        <v>94.08297729492188</v>
+        <v>94.08296966552734</v>
       </c>
       <c r="D207" t="n">
-        <v>94.08297729492188</v>
+        <v>94.08296966552734</v>
       </c>
       <c r="E207" t="n">
-        <v>94.073624972022</v>
+        <v>94.07361734338588</v>
       </c>
       <c r="F207" t="n">
-        <v>94.08297729492188</v>
+        <v>94.08296966552734</v>
       </c>
       <c r="G207" t="n">
         <v>3704500</v>
@@ -5210,16 +5210,16 @@
         <v>45590</v>
       </c>
       <c r="C208" t="n">
-        <v>94.12037658691406</v>
+        <v>94.12036895751953</v>
       </c>
       <c r="D208" t="n">
-        <v>94.12037658691406</v>
+        <v>94.12036895751953</v>
       </c>
       <c r="E208" t="n">
-        <v>94.11102426429896</v>
+        <v>94.11101663566252</v>
       </c>
       <c r="F208" t="n">
-        <v>94.11102426429896</v>
+        <v>94.11101663566252</v>
       </c>
       <c r="G208" t="n">
         <v>5386900</v>
@@ -5233,16 +5233,16 @@
         <v>45593</v>
       </c>
       <c r="C209" t="n">
-        <v>94.12037658691406</v>
+        <v>94.12036895751953</v>
       </c>
       <c r="D209" t="n">
-        <v>94.12972177579719</v>
+        <v>94.12971414564514</v>
       </c>
       <c r="E209" t="n">
-        <v>94.12037658691406</v>
+        <v>94.12036895751953</v>
       </c>
       <c r="F209" t="n">
-        <v>94.12972177579719</v>
+        <v>94.12971414564514</v>
       </c>
       <c r="G209" t="n">
         <v>3471300</v>
@@ -5256,16 +5256,16 @@
         <v>45594</v>
       </c>
       <c r="C210" t="n">
-        <v>94.13908386230469</v>
+        <v>94.13906860351562</v>
       </c>
       <c r="D210" t="n">
-        <v>94.13908386230469</v>
+        <v>94.13906860351562</v>
       </c>
       <c r="E210" t="n">
-        <v>94.12505894379339</v>
+        <v>94.1250436872776</v>
       </c>
       <c r="F210" t="n">
-        <v>94.12973153871958</v>
+        <v>94.12971628144642</v>
       </c>
       <c r="G210" t="n">
         <v>3449900</v>
@@ -5279,16 +5279,16 @@
         <v>45595</v>
       </c>
       <c r="C211" t="n">
-        <v>94.13908386230469</v>
+        <v>94.13906860351562</v>
       </c>
       <c r="D211" t="n">
-        <v>94.15778137574219</v>
+        <v>94.15776611392248</v>
       </c>
       <c r="E211" t="n">
-        <v>94.13908386230469</v>
+        <v>94.13906860351562</v>
       </c>
       <c r="F211" t="n">
-        <v>94.14843618588979</v>
+        <v>94.14842092558483</v>
       </c>
       <c r="G211" t="n">
         <v>7059200</v>
@@ -5302,16 +5302,16 @@
         <v>45596</v>
       </c>
       <c r="C212" t="n">
-        <v>94.15778350830078</v>
+        <v>94.15776824951172</v>
       </c>
       <c r="D212" t="n">
-        <v>94.16713583209771</v>
+        <v>94.16712057179303</v>
       </c>
       <c r="E212" t="n">
-        <v>94.14843831823674</v>
+        <v>94.1484230609621</v>
       </c>
       <c r="F212" t="n">
-        <v>94.14843831823674</v>
+        <v>94.1484230609621</v>
       </c>
       <c r="G212" t="n">
         <v>11321100</v>
@@ -5325,16 +5325,16 @@
         <v>45597</v>
       </c>
       <c r="C213" t="n">
-        <v>94.20941162109375</v>
+        <v>94.20940399169922</v>
       </c>
       <c r="D213" t="n">
-        <v>94.20941162109375</v>
+        <v>94.20940399169922</v>
       </c>
       <c r="E213" t="n">
-        <v>94.20002775979395</v>
+        <v>94.20002013115936</v>
       </c>
       <c r="F213" t="n">
-        <v>94.20941162109375</v>
+        <v>94.20940399169922</v>
       </c>
       <c r="G213" t="n">
         <v>13451800</v>
@@ -5348,16 +5348,16 @@
         <v>45600</v>
       </c>
       <c r="C214" t="n">
-        <v>94.21878814697266</v>
+        <v>94.21881103515625</v>
       </c>
       <c r="D214" t="n">
-        <v>94.22724078409466</v>
+        <v>94.22726367433162</v>
       </c>
       <c r="E214" t="n">
-        <v>94.20939712386507</v>
+        <v>94.20942000976736</v>
       </c>
       <c r="F214" t="n">
-        <v>94.21878814697266</v>
+        <v>94.21881103515625</v>
       </c>
       <c r="G214" t="n">
         <v>5041500</v>
@@ -5417,16 +5417,16 @@
         <v>45603</v>
       </c>
       <c r="C217" t="n">
-        <v>94.25634002685547</v>
+        <v>94.25637054443359</v>
       </c>
       <c r="D217" t="n">
-        <v>94.25634002685547</v>
+        <v>94.25637054443359</v>
       </c>
       <c r="E217" t="n">
-        <v>94.24694900425096</v>
+        <v>94.24697951878854</v>
       </c>
       <c r="F217" t="n">
-        <v>94.24694900425096</v>
+        <v>94.24697951878854</v>
       </c>
       <c r="G217" t="n">
         <v>6188100</v>
@@ -5440,16 +5440,16 @@
         <v>45604</v>
       </c>
       <c r="C218" t="n">
-        <v>94.30331420898438</v>
+        <v>94.30329895019531</v>
       </c>
       <c r="D218" t="n">
-        <v>94.30331420898438</v>
+        <v>94.30329895019531</v>
       </c>
       <c r="E218" t="n">
-        <v>94.28453215855077</v>
+        <v>94.28451690280075</v>
       </c>
       <c r="F218" t="n">
-        <v>94.29392318376757</v>
+        <v>94.29390792649804</v>
       </c>
       <c r="G218" t="n">
         <v>5624200</v>
@@ -5463,16 +5463,16 @@
         <v>45607</v>
       </c>
       <c r="C219" t="n">
-        <v>94.29393005371094</v>
+        <v>94.29391479492188</v>
       </c>
       <c r="D219" t="n">
-        <v>94.30332107961193</v>
+        <v>94.3033058193032</v>
       </c>
       <c r="E219" t="n">
-        <v>94.2892381223874</v>
+        <v>94.2892228643576</v>
       </c>
       <c r="F219" t="n">
-        <v>94.29393005371094</v>
+        <v>94.29391479492188</v>
       </c>
       <c r="G219" t="n">
         <v>4443700</v>
@@ -5486,16 +5486,16 @@
         <v>45608</v>
       </c>
       <c r="C220" t="n">
-        <v>94.30331420898438</v>
+        <v>94.30329895019531</v>
       </c>
       <c r="D220" t="n">
-        <v>94.31269807094777</v>
+        <v>94.31268281064035</v>
       </c>
       <c r="E220" t="n">
-        <v>94.30331420898438</v>
+        <v>94.30329895019531</v>
       </c>
       <c r="F220" t="n">
-        <v>94.31269807094777</v>
+        <v>94.31268281064035</v>
       </c>
       <c r="G220" t="n">
         <v>4283300</v>
@@ -5509,16 +5509,16 @@
         <v>45609</v>
       </c>
       <c r="C221" t="n">
-        <v>94.33147430419922</v>
+        <v>94.33145904541016</v>
       </c>
       <c r="D221" t="n">
-        <v>94.33147430419922</v>
+        <v>94.33145904541016</v>
       </c>
       <c r="E221" t="n">
-        <v>94.31269225492385</v>
+        <v>94.31267699917292</v>
       </c>
       <c r="F221" t="n">
-        <v>94.32208327956153</v>
+        <v>94.32206802229155</v>
       </c>
       <c r="G221" t="n">
         <v>4818000</v>
@@ -5532,16 +5532,16 @@
         <v>45610</v>
       </c>
       <c r="C222" t="n">
-        <v>94.33147430419922</v>
+        <v>94.33145904541016</v>
       </c>
       <c r="D222" t="n">
-        <v>94.3408653288369</v>
+        <v>94.34085006852878</v>
       </c>
       <c r="E222" t="n">
-        <v>94.33147430419922</v>
+        <v>94.33145904541016</v>
       </c>
       <c r="F222" t="n">
-        <v>94.3408653288369</v>
+        <v>94.34085006852878</v>
       </c>
       <c r="G222" t="n">
         <v>4353200</v>
@@ -5578,16 +5578,16 @@
         <v>45614</v>
       </c>
       <c r="C224" t="n">
-        <v>94.3878173828125</v>
+        <v>94.38780212402344</v>
       </c>
       <c r="D224" t="n">
-        <v>94.3878173828125</v>
+        <v>94.38780212402344</v>
       </c>
       <c r="E224" t="n">
-        <v>94.37842635705479</v>
+        <v>94.37841109978388</v>
       </c>
       <c r="F224" t="n">
-        <v>94.3878173828125</v>
+        <v>94.38780212402344</v>
       </c>
       <c r="G224" t="n">
         <v>5567500</v>
@@ -5601,16 +5601,16 @@
         <v>45615</v>
       </c>
       <c r="C225" t="n">
-        <v>94.39718627929688</v>
+        <v>94.39717864990234</v>
       </c>
       <c r="D225" t="n">
-        <v>94.39718627929688</v>
+        <v>94.39717864990234</v>
       </c>
       <c r="E225" t="n">
-        <v>94.38779525574067</v>
+        <v>94.38778762710514</v>
       </c>
       <c r="F225" t="n">
-        <v>94.39718627929688</v>
+        <v>94.39717864990234</v>
       </c>
       <c r="G225" t="n">
         <v>4310900</v>
@@ -5624,16 +5624,16 @@
         <v>45616</v>
       </c>
       <c r="C226" t="n">
-        <v>94.41596221923828</v>
+        <v>94.41598510742188</v>
       </c>
       <c r="D226" t="n">
-        <v>94.41596221923828</v>
+        <v>94.41598510742188</v>
       </c>
       <c r="E226" t="n">
-        <v>94.397187335168</v>
+        <v>94.39721021880021</v>
       </c>
       <c r="F226" t="n">
-        <v>94.40657835882925</v>
+        <v>94.40660124473803</v>
       </c>
       <c r="G226" t="n">
         <v>4133000</v>
@@ -5647,16 +5647,16 @@
         <v>45617</v>
       </c>
       <c r="C227" t="n">
-        <v>94.41596221923828</v>
+        <v>94.41598510742188</v>
       </c>
       <c r="D227" t="n">
-        <v>94.42535324289952</v>
+        <v>94.42537613335968</v>
       </c>
       <c r="E227" t="n">
-        <v>94.41596221923828</v>
+        <v>94.41598510742188</v>
       </c>
       <c r="F227" t="n">
-        <v>94.42535324289952</v>
+        <v>94.42537613335968</v>
       </c>
       <c r="G227" t="n">
         <v>4410700</v>
@@ -5670,16 +5670,16 @@
         <v>45618</v>
       </c>
       <c r="C228" t="n">
-        <v>94.44413757324219</v>
+        <v>94.44414520263672</v>
       </c>
       <c r="D228" t="n">
-        <v>94.45352859784272</v>
+        <v>94.45353622799588</v>
       </c>
       <c r="E228" t="n">
-        <v>94.44413757324219</v>
+        <v>94.44414520263672</v>
       </c>
       <c r="F228" t="n">
-        <v>94.44413757324219</v>
+        <v>94.44414520263672</v>
       </c>
       <c r="G228" t="n">
         <v>4343900</v>
@@ -5693,16 +5693,16 @@
         <v>45621</v>
       </c>
       <c r="C229" t="n">
-        <v>94.45351409912109</v>
+        <v>94.45352935791016</v>
       </c>
       <c r="D229" t="n">
-        <v>94.46290512228009</v>
+        <v>94.46292038258626</v>
       </c>
       <c r="E229" t="n">
-        <v>94.45351409912109</v>
+        <v>94.45352935791016</v>
       </c>
       <c r="F229" t="n">
-        <v>94.45351409912109</v>
+        <v>94.45352935791016</v>
       </c>
       <c r="G229" t="n">
         <v>6020200</v>
@@ -5716,16 +5716,16 @@
         <v>45622</v>
       </c>
       <c r="C230" t="n">
-        <v>94.47230529785156</v>
+        <v>94.47231292724609</v>
       </c>
       <c r="D230" t="n">
-        <v>94.48168915866783</v>
+        <v>94.48169678882019</v>
       </c>
       <c r="E230" t="n">
-        <v>94.46291427378277</v>
+        <v>94.4629219024189</v>
       </c>
       <c r="F230" t="n">
-        <v>94.47230529785156</v>
+        <v>94.47231292724609</v>
       </c>
       <c r="G230" t="n">
         <v>4586900</v>
@@ -5762,16 +5762,16 @@
         <v>45625</v>
       </c>
       <c r="C232" t="n">
-        <v>94.52863311767578</v>
+        <v>94.52862548828125</v>
       </c>
       <c r="D232" t="n">
-        <v>94.53802414134739</v>
+        <v>94.5380165111949</v>
       </c>
       <c r="E232" t="n">
-        <v>94.52863311767578</v>
+        <v>94.52862548828125</v>
       </c>
       <c r="F232" t="n">
-        <v>94.52863311767578</v>
+        <v>94.52862548828125</v>
       </c>
       <c r="G232" t="n">
         <v>6581100</v>
@@ -5785,16 +5785,16 @@
         <v>45628</v>
       </c>
       <c r="C233" t="n">
-        <v>94.54561614990234</v>
+        <v>94.54559326171875</v>
       </c>
       <c r="D233" t="n">
-        <v>94.55504256672454</v>
+        <v>94.55501967625894</v>
       </c>
       <c r="E233" t="n">
-        <v>94.54561614990234</v>
+        <v>94.54559326171875</v>
       </c>
       <c r="F233" t="n">
-        <v>94.55032576318879</v>
+        <v>94.55030287386506</v>
       </c>
       <c r="G233" t="n">
         <v>11471800</v>
@@ -5808,16 +5808,16 @@
         <v>45629</v>
       </c>
       <c r="C234" t="n">
-        <v>94.55502319335938</v>
+        <v>94.55504608154297</v>
       </c>
       <c r="D234" t="n">
-        <v>94.56444241800236</v>
+        <v>94.564465308466</v>
       </c>
       <c r="E234" t="n">
-        <v>94.55502319335938</v>
+        <v>94.55504608154297</v>
       </c>
       <c r="F234" t="n">
-        <v>94.56444241800236</v>
+        <v>94.564465308466</v>
       </c>
       <c r="G234" t="n">
         <v>5734100</v>
@@ -5831,16 +5831,16 @@
         <v>45630</v>
       </c>
       <c r="C235" t="n">
-        <v>94.57386779785156</v>
+        <v>94.57389068603516</v>
       </c>
       <c r="D235" t="n">
-        <v>94.5832942126392</v>
+        <v>94.58331710310412</v>
       </c>
       <c r="E235" t="n">
-        <v>94.56444138306392</v>
+        <v>94.56446426896619</v>
       </c>
       <c r="F235" t="n">
-        <v>94.57386779785156</v>
+        <v>94.57389068603516</v>
       </c>
       <c r="G235" t="n">
         <v>5351100</v>
@@ -5854,16 +5854,16 @@
         <v>45631</v>
       </c>
       <c r="C236" t="n">
-        <v>94.58332061767578</v>
+        <v>94.58330535888672</v>
       </c>
       <c r="D236" t="n">
-        <v>94.59274703509502</v>
+        <v>94.59273177478522</v>
       </c>
       <c r="E236" t="n">
-        <v>94.58332061767578</v>
+        <v>94.58330535888672</v>
       </c>
       <c r="F236" t="n">
-        <v>94.58332061767578</v>
+        <v>94.58330535888672</v>
       </c>
       <c r="G236" t="n">
         <v>4870100</v>
@@ -5877,16 +5877,16 @@
         <v>45632</v>
       </c>
       <c r="C237" t="n">
-        <v>94.63042449951172</v>
+        <v>94.63043975830078</v>
       </c>
       <c r="D237" t="n">
-        <v>94.63042449951172</v>
+        <v>94.63043975830078</v>
       </c>
       <c r="E237" t="n">
-        <v>94.62099808418584</v>
+        <v>94.62101334145494</v>
       </c>
       <c r="F237" t="n">
-        <v>94.63042449951172</v>
+        <v>94.63043975830078</v>
       </c>
       <c r="G237" t="n">
         <v>4779000</v>
@@ -5900,16 +5900,16 @@
         <v>45635</v>
       </c>
       <c r="C238" t="n">
-        <v>94.63984680175781</v>
+        <v>94.63985443115234</v>
       </c>
       <c r="D238" t="n">
-        <v>94.63984680175781</v>
+        <v>94.63985443115234</v>
       </c>
       <c r="E238" t="n">
-        <v>94.63042757637383</v>
+        <v>94.63043520500904</v>
       </c>
       <c r="F238" t="n">
-        <v>94.63042757637383</v>
+        <v>94.63043520500904</v>
       </c>
       <c r="G238" t="n">
         <v>5539800</v>
@@ -5923,16 +5923,16 @@
         <v>45636</v>
       </c>
       <c r="C239" t="n">
-        <v>94.65871429443359</v>
+        <v>94.65869140625</v>
       </c>
       <c r="D239" t="n">
-        <v>94.65871429443359</v>
+        <v>94.65869140625</v>
       </c>
       <c r="E239" t="n">
-        <v>94.64928787734119</v>
+        <v>94.64926499143688</v>
       </c>
       <c r="F239" t="n">
-        <v>94.64928787734119</v>
+        <v>94.64926499143688</v>
       </c>
       <c r="G239" t="n">
         <v>5293500</v>
@@ -5946,16 +5946,16 @@
         <v>45637</v>
       </c>
       <c r="C240" t="n">
-        <v>94.65871429443359</v>
+        <v>94.65869140625</v>
       </c>
       <c r="D240" t="n">
-        <v>94.66813352127649</v>
+        <v>94.66811063081535</v>
       </c>
       <c r="E240" t="n">
-        <v>94.65871429443359</v>
+        <v>94.65869140625</v>
       </c>
       <c r="F240" t="n">
-        <v>94.66813352127649</v>
+        <v>94.66811063081535</v>
       </c>
       <c r="G240" t="n">
         <v>4855300</v>
@@ -5969,16 +5969,16 @@
         <v>45638</v>
       </c>
       <c r="C241" t="n">
-        <v>94.66812133789062</v>
+        <v>94.66812896728516</v>
       </c>
       <c r="D241" t="n">
-        <v>94.67754775376989</v>
+        <v>94.6775553839241</v>
       </c>
       <c r="E241" t="n">
-        <v>94.66812133789062</v>
+        <v>94.66812896728516</v>
       </c>
       <c r="F241" t="n">
-        <v>94.67754775376989</v>
+        <v>94.6775553839241</v>
       </c>
       <c r="G241" t="n">
         <v>4701000</v>
@@ -5992,16 +5992,16 @@
         <v>45639</v>
       </c>
       <c r="C242" t="n">
-        <v>94.71524810791016</v>
+        <v>94.71524047851562</v>
       </c>
       <c r="D242" t="n">
-        <v>94.71524810791016</v>
+        <v>94.71524047851562</v>
       </c>
       <c r="E242" t="n">
-        <v>94.70582169184371</v>
+        <v>94.70581406320848</v>
       </c>
       <c r="F242" t="n">
-        <v>94.70582169184371</v>
+        <v>94.70581406320848</v>
       </c>
       <c r="G242" t="n">
         <v>4671500</v>
@@ -6015,16 +6015,16 @@
         <v>45642</v>
       </c>
       <c r="C243" t="n">
-        <v>94.72466278076172</v>
+        <v>94.72467041015625</v>
       </c>
       <c r="D243" t="n">
-        <v>94.72466278076172</v>
+        <v>94.72467041015625</v>
       </c>
       <c r="E243" t="n">
-        <v>94.71523636586389</v>
+        <v>94.71524399449918</v>
       </c>
       <c r="F243" t="n">
-        <v>94.72466278076172</v>
+        <v>94.72467041015625</v>
       </c>
       <c r="G243" t="n">
         <v>5598900</v>
@@ -6038,16 +6038,16 @@
         <v>45643</v>
       </c>
       <c r="C244" t="n">
-        <v>94.72466278076172</v>
+        <v>94.72467041015625</v>
       </c>
       <c r="D244" t="n">
-        <v>94.73408200541174</v>
+        <v>94.7340896355649</v>
       </c>
       <c r="E244" t="n">
-        <v>94.72466278076172</v>
+        <v>94.72467041015625</v>
       </c>
       <c r="F244" t="n">
-        <v>94.73408200541174</v>
+        <v>94.7340896355649</v>
       </c>
       <c r="G244" t="n">
         <v>5798500</v>
@@ -6061,16 +6061,16 @@
         <v>45644</v>
       </c>
       <c r="C245" t="n">
-        <v>94.74550628662109</v>
+        <v>94.74549865722656</v>
       </c>
       <c r="D245" t="n">
-        <v>94.74550628662109</v>
+        <v>94.74549865722656</v>
       </c>
       <c r="E245" t="n">
-        <v>94.7360448506541</v>
+        <v>94.73603722202144</v>
       </c>
       <c r="F245" t="n">
-        <v>94.74550628662109</v>
+        <v>94.74549865722656</v>
       </c>
       <c r="G245" t="n">
         <v>11526500</v>
@@ -6107,16 +6107,16 @@
         <v>45646</v>
       </c>
       <c r="C247" t="n">
-        <v>94.7833251953125</v>
+        <v>94.78333282470703</v>
       </c>
       <c r="D247" t="n">
-        <v>94.79278663004159</v>
+        <v>94.7927942601977</v>
       </c>
       <c r="E247" t="n">
-        <v>94.7833251953125</v>
+        <v>94.78333282470703</v>
       </c>
       <c r="F247" t="n">
-        <v>94.78805952115711</v>
+        <v>94.78806715093272</v>
       </c>
       <c r="G247" t="n">
         <v>8898900</v>
@@ -6130,16 +6130,16 @@
         <v>45649</v>
       </c>
       <c r="C248" t="n">
-        <v>94.80225372314453</v>
+        <v>94.80223846435547</v>
       </c>
       <c r="D248" t="n">
-        <v>94.80225372314453</v>
+        <v>94.80223846435547</v>
       </c>
       <c r="E248" t="n">
-        <v>94.79279228785073</v>
+        <v>94.79277703058452</v>
       </c>
       <c r="F248" t="n">
-        <v>94.80225372314453</v>
+        <v>94.80223846435547</v>
       </c>
       <c r="G248" t="n">
         <v>7032500</v>
@@ -6153,16 +6153,16 @@
         <v>45650</v>
       </c>
       <c r="C249" t="n">
-        <v>94.83061981201172</v>
+        <v>94.83061218261719</v>
       </c>
       <c r="D249" t="n">
-        <v>94.83061981201172</v>
+        <v>94.83061218261719</v>
       </c>
       <c r="E249" t="n">
-        <v>94.82115837781542</v>
+        <v>94.82115074918208</v>
       </c>
       <c r="F249" t="n">
-        <v>94.83061981201172</v>
+        <v>94.83061218261719</v>
       </c>
       <c r="G249" t="n">
         <v>4654300</v>
@@ -6176,16 +6176,16 @@
         <v>45652</v>
       </c>
       <c r="C250" t="n">
-        <v>94.84009552001953</v>
+        <v>94.84008026123047</v>
       </c>
       <c r="D250" t="n">
-        <v>94.84009552001953</v>
+        <v>94.84008026123047</v>
       </c>
       <c r="E250" t="n">
-        <v>94.83063408439924</v>
+        <v>94.83061882713243</v>
       </c>
       <c r="F250" t="n">
-        <v>94.84009552001953</v>
+        <v>94.84008026123047</v>
       </c>
       <c r="G250" t="n">
         <v>4974100</v>
@@ -6199,16 +6199,16 @@
         <v>45653</v>
       </c>
       <c r="C251" t="n">
-        <v>94.86844635009766</v>
+        <v>94.86845397949219</v>
       </c>
       <c r="D251" t="n">
-        <v>94.86844635009766</v>
+        <v>94.86845397949219</v>
       </c>
       <c r="E251" t="n">
-        <v>94.85898491709632</v>
+        <v>94.85899254572995</v>
       </c>
       <c r="F251" t="n">
-        <v>94.85898491709632</v>
+        <v>94.85899254572995</v>
       </c>
       <c r="G251" t="n">
         <v>6558000</v>
@@ -6222,16 +6222,16 @@
         <v>45656</v>
       </c>
       <c r="C252" t="n">
-        <v>94.86844635009766</v>
+        <v>94.86845397949219</v>
       </c>
       <c r="D252" t="n">
-        <v>94.87790778309899</v>
+        <v>94.87791541325443</v>
       </c>
       <c r="E252" t="n">
-        <v>94.86844635009766</v>
+        <v>94.86845397949219</v>
       </c>
       <c r="F252" t="n">
-        <v>94.87790778309899</v>
+        <v>94.87791541325443</v>
       </c>
       <c r="G252" t="n">
         <v>6547600</v>
@@ -6245,16 +6245,16 @@
         <v>45657</v>
       </c>
       <c r="C253" t="n">
-        <v>94.89684295654297</v>
+        <v>94.89682006835938</v>
       </c>
       <c r="D253" t="n">
-        <v>94.9157586094786</v>
+        <v>94.91573571673274</v>
       </c>
       <c r="E253" t="n">
-        <v>94.89684295654297</v>
+        <v>94.89682006835938</v>
       </c>
       <c r="F253" t="n">
-        <v>94.90630439149093</v>
+        <v>94.90628150102533</v>
       </c>
       <c r="G253" t="n">
         <v>7371300</v>
@@ -6268,16 +6268,16 @@
         <v>45659</v>
       </c>
       <c r="C254" t="n">
-        <v>94.91575622558594</v>
+        <v>94.91574096679688</v>
       </c>
       <c r="D254" t="n">
-        <v>94.91575622558594</v>
+        <v>94.91574096679688</v>
       </c>
       <c r="E254" t="n">
-        <v>94.90630200783571</v>
+        <v>94.90628675056652</v>
       </c>
       <c r="F254" t="n">
-        <v>94.91575622558594</v>
+        <v>94.91574096679688</v>
       </c>
       <c r="G254" t="n">
         <v>7533100</v>
@@ -6291,16 +6291,16 @@
         <v>45660</v>
       </c>
       <c r="C255" t="n">
-        <v>94.94412994384766</v>
+        <v>94.94413757324219</v>
       </c>
       <c r="D255" t="n">
-        <v>94.95358416054377</v>
+        <v>94.95359179069801</v>
       </c>
       <c r="E255" t="n">
-        <v>94.94412994384766</v>
+        <v>94.94413757324219</v>
       </c>
       <c r="F255" t="n">
-        <v>94.95358416054377</v>
+        <v>94.95359179069801</v>
       </c>
       <c r="G255" t="n">
         <v>6730100</v>
@@ -6314,16 +6314,16 @@
         <v>45663</v>
       </c>
       <c r="C256" t="n">
-        <v>94.94412994384766</v>
+        <v>94.94413757324219</v>
       </c>
       <c r="D256" t="n">
-        <v>94.9630455941992</v>
+        <v>94.96305322511373</v>
       </c>
       <c r="E256" t="n">
-        <v>94.94412994384766</v>
+        <v>94.94413757324219</v>
       </c>
       <c r="F256" t="n">
-        <v>94.95358416054377</v>
+        <v>94.95359179069801</v>
       </c>
       <c r="G256" t="n">
         <v>6938300</v>
@@ -6337,16 +6337,16 @@
         <v>45664</v>
       </c>
       <c r="C257" t="n">
-        <v>94.96303558349609</v>
+        <v>94.96304321289062</v>
       </c>
       <c r="D257" t="n">
-        <v>94.97249701615412</v>
+        <v>94.97250464630879</v>
       </c>
       <c r="E257" t="n">
-        <v>94.96303558349609</v>
+        <v>94.96304321289062</v>
       </c>
       <c r="F257" t="n">
-        <v>94.97249701615412</v>
+        <v>94.97250464630879</v>
       </c>
       <c r="G257" t="n">
         <v>6792100</v>
@@ -6360,16 +6360,16 @@
         <v>45665</v>
       </c>
       <c r="C258" t="n">
-        <v>94.98197174072266</v>
+        <v>94.98198699951172</v>
       </c>
       <c r="D258" t="n">
-        <v>94.98197174072266</v>
+        <v>94.98198699951172</v>
       </c>
       <c r="E258" t="n">
-        <v>94.97251030674057</v>
+        <v>94.97252556400967</v>
       </c>
       <c r="F258" t="n">
-        <v>94.97251030674057</v>
+        <v>94.97252556400967</v>
       </c>
       <c r="G258" t="n">
         <v>6101100</v>
@@ -6383,16 +6383,16 @@
         <v>45667</v>
       </c>
       <c r="C259" t="n">
-        <v>95.01980590820312</v>
+        <v>95.01979827880859</v>
       </c>
       <c r="D259" t="n">
-        <v>95.02926734247052</v>
+        <v>95.0292597123163</v>
       </c>
       <c r="E259" t="n">
-        <v>95.0103516908955</v>
+        <v>95.01034406226007</v>
       </c>
       <c r="F259" t="n">
-        <v>95.01980590820312</v>
+        <v>95.01979827880859</v>
       </c>
       <c r="G259" t="n">
         <v>7644600</v>
@@ -6406,16 +6406,16 @@
         <v>45670</v>
       </c>
       <c r="C260" t="n">
-        <v>95.03872680664062</v>
+        <v>95.03871917724609</v>
       </c>
       <c r="D260" t="n">
-        <v>95.03872680664062</v>
+        <v>95.03871917724609</v>
       </c>
       <c r="E260" t="n">
-        <v>95.02926537256936</v>
+        <v>95.02925774393435</v>
       </c>
       <c r="F260" t="n">
-        <v>95.03399248112518</v>
+        <v>95.03398485211071</v>
       </c>
       <c r="G260" t="n">
         <v>7647300</v>
@@ -6429,16 +6429,16 @@
         <v>45671</v>
       </c>
       <c r="C261" t="n">
-        <v>95.04819488525391</v>
+        <v>95.04820251464844</v>
       </c>
       <c r="D261" t="n">
-        <v>95.04819488525391</v>
+        <v>95.04820251464844</v>
       </c>
       <c r="E261" t="n">
-        <v>95.03873345052121</v>
+        <v>95.03874107915628</v>
       </c>
       <c r="F261" t="n">
-        <v>95.04819488525391</v>
+        <v>95.04820251464844</v>
       </c>
       <c r="G261" t="n">
         <v>7245400</v>
@@ -6452,16 +6452,16 @@
         <v>45672</v>
       </c>
       <c r="C262" t="n">
-        <v>95.05767059326172</v>
+        <v>95.05764007568359</v>
       </c>
       <c r="D262" t="n">
-        <v>95.05767059326172</v>
+        <v>95.05764007568359</v>
       </c>
       <c r="E262" t="n">
-        <v>95.04821637335179</v>
+        <v>95.04818585880886</v>
       </c>
       <c r="F262" t="n">
-        <v>95.05767059326172</v>
+        <v>95.05764007568359</v>
       </c>
       <c r="G262" t="n">
         <v>6878600</v>
@@ -6475,16 +6475,16 @@
         <v>45673</v>
       </c>
       <c r="C263" t="n">
-        <v>95.05767059326172</v>
+        <v>95.05764007568359</v>
       </c>
       <c r="D263" t="n">
-        <v>95.07659346700511</v>
+        <v>95.07656294335193</v>
       </c>
       <c r="E263" t="n">
-        <v>95.05767059326172</v>
+        <v>95.05764007568359</v>
       </c>
       <c r="F263" t="n">
-        <v>95.06713203013342</v>
+        <v>95.06710150951776</v>
       </c>
       <c r="G263" t="n">
         <v>5352500</v>
@@ -6544,16 +6544,16 @@
         <v>45679</v>
       </c>
       <c r="C266" t="n">
-        <v>95.13333892822266</v>
+        <v>95.13333129882812</v>
       </c>
       <c r="D266" t="n">
-        <v>95.13333892822266</v>
+        <v>95.13333129882812</v>
       </c>
       <c r="E266" t="n">
-        <v>95.12387749221881</v>
+        <v>95.12386986358305</v>
       </c>
       <c r="F266" t="n">
-        <v>95.12387749221881</v>
+        <v>95.12386986358305</v>
       </c>
       <c r="G266" t="n">
         <v>5717600</v>
@@ -6567,16 +6567,16 @@
         <v>45680</v>
       </c>
       <c r="C267" t="n">
-        <v>95.14277648925781</v>
+        <v>95.14278411865234</v>
       </c>
       <c r="D267" t="n">
-        <v>95.14277648925781</v>
+        <v>95.14278411865234</v>
       </c>
       <c r="E267" t="n">
-        <v>95.1333150556282</v>
+        <v>95.13332268426403</v>
       </c>
       <c r="F267" t="n">
-        <v>95.14277648925781</v>
+        <v>95.14278411865234</v>
       </c>
       <c r="G267" t="n">
         <v>5085800</v>
@@ -6636,16 +6636,16 @@
         <v>45685</v>
       </c>
       <c r="C270" t="n">
-        <v>95.19953918457031</v>
+        <v>95.19954681396484</v>
       </c>
       <c r="D270" t="n">
-        <v>95.19953918457031</v>
+        <v>95.19954681396484</v>
       </c>
       <c r="E270" t="n">
-        <v>95.18062353257602</v>
+        <v>95.18063116045464</v>
       </c>
       <c r="F270" t="n">
-        <v>95.1900777500932</v>
+        <v>95.19008537872948</v>
       </c>
       <c r="G270" t="n">
         <v>5857900</v>
@@ -6659,16 +6659,16 @@
         <v>45686</v>
       </c>
       <c r="C271" t="n">
-        <v>95.19953918457031</v>
+        <v>95.19954681396484</v>
       </c>
       <c r="D271" t="n">
-        <v>95.20900061904742</v>
+        <v>95.20900824920021</v>
       </c>
       <c r="E271" t="n">
-        <v>95.19953918457031</v>
+        <v>95.19954681396484</v>
       </c>
       <c r="F271" t="n">
-        <v>95.19953918457031</v>
+        <v>95.19954681396484</v>
       </c>
       <c r="G271" t="n">
         <v>3978700</v>
@@ -6705,16 +6705,16 @@
         <v>45688</v>
       </c>
       <c r="C273" t="n">
-        <v>95.23736572265625</v>
+        <v>95.23735809326172</v>
       </c>
       <c r="D273" t="n">
-        <v>95.24682715594292</v>
+        <v>95.24681952579044</v>
       </c>
       <c r="E273" t="n">
-        <v>95.23736572265625</v>
+        <v>95.23735809326172</v>
       </c>
       <c r="F273" t="n">
-        <v>95.24682715594292</v>
+        <v>95.24681952579044</v>
       </c>
       <c r="G273" t="n">
         <v>12373000</v>
@@ -6728,16 +6728,16 @@
         <v>45691</v>
       </c>
       <c r="C274" t="n">
-        <v>95.25920867919922</v>
+        <v>95.25920104980469</v>
       </c>
       <c r="D274" t="n">
-        <v>95.25920867919922</v>
+        <v>95.25920104980469</v>
       </c>
       <c r="E274" t="n">
-        <v>95.24972025138301</v>
+        <v>95.24971262274842</v>
       </c>
       <c r="F274" t="n">
-        <v>95.24972025138301</v>
+        <v>95.24971262274842</v>
       </c>
       <c r="G274" t="n">
         <v>16436200</v>
@@ -6751,16 +6751,16 @@
         <v>45692</v>
       </c>
       <c r="C275" t="n">
-        <v>95.27820587158203</v>
+        <v>95.27819061279297</v>
       </c>
       <c r="D275" t="n">
-        <v>95.27820587158203</v>
+        <v>95.27819061279297</v>
       </c>
       <c r="E275" t="n">
-        <v>95.26871020010807</v>
+        <v>95.26869494283973</v>
       </c>
       <c r="F275" t="n">
-        <v>95.27820587158203</v>
+        <v>95.27819061279297</v>
       </c>
       <c r="G275" t="n">
         <v>7866600</v>
@@ -6774,16 +6774,16 @@
         <v>45693</v>
       </c>
       <c r="C276" t="n">
-        <v>95.27820587158203</v>
+        <v>95.27819061279297</v>
       </c>
       <c r="D276" t="n">
-        <v>95.28770154305599</v>
+        <v>95.28768628274619</v>
       </c>
       <c r="E276" t="n">
-        <v>95.27820587158203</v>
+        <v>95.27819061279297</v>
       </c>
       <c r="F276" t="n">
-        <v>95.28770154305599</v>
+        <v>95.28768628274619</v>
       </c>
       <c r="G276" t="n">
         <v>7100900</v>
@@ -6797,16 +6797,16 @@
         <v>45694</v>
       </c>
       <c r="C277" t="n">
-        <v>95.29716491699219</v>
+        <v>95.29718017578125</v>
       </c>
       <c r="D277" t="n">
-        <v>95.29716491699219</v>
+        <v>95.29718017578125</v>
       </c>
       <c r="E277" t="n">
-        <v>95.28767649108794</v>
+        <v>95.28769174835773</v>
       </c>
       <c r="F277" t="n">
-        <v>95.29716491699219</v>
+        <v>95.29718017578125</v>
       </c>
       <c r="G277" t="n">
         <v>5804300</v>
@@ -6820,16 +6820,16 @@
         <v>45695</v>
       </c>
       <c r="C278" t="n">
-        <v>95.32566070556641</v>
+        <v>95.32567596435547</v>
       </c>
       <c r="D278" t="n">
-        <v>95.33514913234477</v>
+        <v>95.33516439265264</v>
       </c>
       <c r="E278" t="n">
-        <v>95.31616503571418</v>
+        <v>95.31618029298328</v>
       </c>
       <c r="F278" t="n">
-        <v>95.33514913234477</v>
+        <v>95.33516439265264</v>
       </c>
       <c r="G278" t="n">
         <v>6758700</v>
@@ -6843,16 +6843,16 @@
         <v>45698</v>
       </c>
       <c r="C279" t="n">
-        <v>95.34466552734375</v>
+        <v>95.34464263916016</v>
       </c>
       <c r="D279" t="n">
-        <v>95.34466552734375</v>
+        <v>95.34464263916016</v>
       </c>
       <c r="E279" t="n">
-        <v>95.33516985542744</v>
+        <v>95.33514696952335</v>
       </c>
       <c r="F279" t="n">
-        <v>95.34466552734375</v>
+        <v>95.34464263916016</v>
       </c>
       <c r="G279" t="n">
         <v>7517800</v>
@@ -6866,16 +6866,16 @@
         <v>45699</v>
       </c>
       <c r="C280" t="n">
-        <v>95.34466552734375</v>
+        <v>95.34464263916016</v>
       </c>
       <c r="D280" t="n">
-        <v>95.35416119926006</v>
+        <v>95.35413830879696</v>
       </c>
       <c r="E280" t="n">
-        <v>95.34466552734375</v>
+        <v>95.34464263916016</v>
       </c>
       <c r="F280" t="n">
-        <v>95.35416119926006</v>
+        <v>95.35413830879696</v>
       </c>
       <c r="G280" t="n">
         <v>6424100</v>
@@ -6889,16 +6889,16 @@
         <v>45700</v>
       </c>
       <c r="C281" t="n">
-        <v>95.35415649414062</v>
+        <v>95.35414886474609</v>
       </c>
       <c r="D281" t="n">
-        <v>95.36364492251329</v>
+        <v>95.36363729235957</v>
       </c>
       <c r="E281" t="n">
-        <v>95.35415649414062</v>
+        <v>95.35414886474609</v>
       </c>
       <c r="F281" t="n">
-        <v>95.35415649414062</v>
+        <v>95.35414886474609</v>
       </c>
       <c r="G281" t="n">
         <v>6618800</v>
@@ -6912,16 +6912,16 @@
         <v>45701</v>
       </c>
       <c r="C282" t="n">
-        <v>95.37313079833984</v>
+        <v>95.37312316894531</v>
       </c>
       <c r="D282" t="n">
-        <v>95.37313079833984</v>
+        <v>95.37312316894531</v>
       </c>
       <c r="E282" t="n">
-        <v>95.36363512786737</v>
+        <v>95.36362749923244</v>
       </c>
       <c r="F282" t="n">
-        <v>95.37313079833984</v>
+        <v>95.37312316894531</v>
       </c>
       <c r="G282" t="n">
         <v>5690100</v>
@@ -7004,16 +7004,16 @@
         <v>45708</v>
       </c>
       <c r="C286" t="n">
-        <v>95.44907379150391</v>
+        <v>95.44908905029297</v>
       </c>
       <c r="D286" t="n">
-        <v>95.44907379150391</v>
+        <v>95.44908905029297</v>
       </c>
       <c r="E286" t="n">
-        <v>95.43957812181581</v>
+        <v>95.43959337908686</v>
       </c>
       <c r="F286" t="n">
-        <v>95.44907379150391</v>
+        <v>95.44908905029297</v>
       </c>
       <c r="G286" t="n">
         <v>7608000</v>
@@ -7027,16 +7027,16 @@
         <v>45709</v>
       </c>
       <c r="C287" t="n">
-        <v>95.48705291748047</v>
+        <v>95.487060546875</v>
       </c>
       <c r="D287" t="n">
-        <v>95.48705291748047</v>
+        <v>95.487060546875</v>
       </c>
       <c r="E287" t="n">
-        <v>95.47755724742539</v>
+        <v>95.47756487606122</v>
       </c>
       <c r="F287" t="n">
-        <v>95.47755724742539</v>
+        <v>95.47756487606122</v>
       </c>
       <c r="G287" t="n">
         <v>9111000</v>
@@ -7073,16 +7073,16 @@
         <v>45713</v>
       </c>
       <c r="C289" t="n">
-        <v>95.50602722167969</v>
+        <v>95.50605773925781</v>
       </c>
       <c r="D289" t="n">
-        <v>95.50602722167969</v>
+        <v>95.50605773925781</v>
       </c>
       <c r="E289" t="n">
-        <v>95.49653155259826</v>
+        <v>95.49656206714219</v>
       </c>
       <c r="F289" t="n">
-        <v>95.49653155259826</v>
+        <v>95.49656206714219</v>
       </c>
       <c r="G289" t="n">
         <v>10827700</v>
@@ -7096,16 +7096,16 @@
         <v>45714</v>
       </c>
       <c r="C290" t="n">
-        <v>95.50602722167969</v>
+        <v>95.50605773925781</v>
       </c>
       <c r="D290" t="n">
-        <v>95.5155228907611</v>
+        <v>95.51555341137345</v>
       </c>
       <c r="E290" t="n">
-        <v>95.50602722167969</v>
+        <v>95.50605773925781</v>
       </c>
       <c r="F290" t="n">
-        <v>95.50602722167969</v>
+        <v>95.50605773925781</v>
       </c>
       <c r="G290" t="n">
         <v>9536300</v>
@@ -7119,16 +7119,16 @@
         <v>45715</v>
       </c>
       <c r="C291" t="n">
-        <v>95.53452301025391</v>
+        <v>95.53451538085938</v>
       </c>
       <c r="D291" t="n">
-        <v>95.53452301025391</v>
+        <v>95.53451538085938</v>
       </c>
       <c r="E291" t="n">
-        <v>95.52503458265423</v>
+        <v>95.52502695401745</v>
       </c>
       <c r="F291" t="n">
-        <v>95.53452301025391</v>
+        <v>95.53451538085938</v>
       </c>
       <c r="G291" t="n">
         <v>10807800</v>
@@ -7165,16 +7165,16 @@
         <v>45719</v>
       </c>
       <c r="C293" t="n">
-        <v>95.57542419433594</v>
+        <v>95.57540893554688</v>
       </c>
       <c r="D293" t="n">
-        <v>95.57542419433594</v>
+        <v>95.57540893554688</v>
       </c>
       <c r="E293" t="n">
-        <v>95.56589890131818</v>
+        <v>95.56588364404985</v>
       </c>
       <c r="F293" t="n">
-        <v>95.57542419433594</v>
+        <v>95.57540893554688</v>
       </c>
       <c r="G293" t="n">
         <v>17436600</v>
@@ -7234,16 +7234,16 @@
         <v>45722</v>
       </c>
       <c r="C296" t="n">
-        <v>95.613525390625</v>
+        <v>95.61351013183594</v>
       </c>
       <c r="D296" t="n">
-        <v>95.613525390625</v>
+        <v>95.61351013183594</v>
       </c>
       <c r="E296" t="n">
-        <v>95.59447480313699</v>
+        <v>95.59445954738818</v>
       </c>
       <c r="F296" t="n">
-        <v>95.60400009688099</v>
+        <v>95.60398483961205</v>
       </c>
       <c r="G296" t="n">
         <v>9925500</v>
@@ -7257,16 +7257,16 @@
         <v>45723</v>
       </c>
       <c r="C297" t="n">
-        <v>95.64209747314453</v>
+        <v>95.64207458496094</v>
       </c>
       <c r="D297" t="n">
-        <v>95.64209747314453</v>
+        <v>95.64207458496094</v>
       </c>
       <c r="E297" t="n">
-        <v>95.63257217905524</v>
+        <v>95.63254929315114</v>
       </c>
       <c r="F297" t="n">
-        <v>95.64209747314453</v>
+        <v>95.64207458496094</v>
       </c>
       <c r="G297" t="n">
         <v>8962400</v>
@@ -7280,16 +7280,16 @@
         <v>45726</v>
       </c>
       <c r="C298" t="n">
-        <v>95.64209747314453</v>
+        <v>95.64207458496094</v>
       </c>
       <c r="D298" t="n">
-        <v>95.65162276723382</v>
+        <v>95.65159987677072</v>
       </c>
       <c r="E298" t="n">
-        <v>95.64209747314453</v>
+        <v>95.64207458496094</v>
       </c>
       <c r="F298" t="n">
-        <v>95.65162276723382</v>
+        <v>95.65159987677072</v>
       </c>
       <c r="G298" t="n">
         <v>14768100</v>
@@ -7303,16 +7303,16 @@
         <v>45727</v>
       </c>
       <c r="C299" t="n">
-        <v>95.66112518310547</v>
+        <v>95.66111755371094</v>
       </c>
       <c r="D299" t="n">
-        <v>95.66112518310547</v>
+        <v>95.66111755371094</v>
       </c>
       <c r="E299" t="n">
-        <v>95.65160715624013</v>
+        <v>95.65159952760472</v>
       </c>
       <c r="F299" t="n">
-        <v>95.65160715624013</v>
+        <v>95.65159952760472</v>
       </c>
       <c r="G299" t="n">
         <v>11456900</v>
@@ -7326,16 +7326,16 @@
         <v>45728</v>
       </c>
       <c r="C300" t="n">
-        <v>95.66112518310547</v>
+        <v>95.66111755371094</v>
       </c>
       <c r="D300" t="n">
-        <v>95.67065047564017</v>
+        <v>95.67064284548596</v>
       </c>
       <c r="E300" t="n">
-        <v>95.66112518310547</v>
+        <v>95.66111755371094</v>
       </c>
       <c r="F300" t="n">
-        <v>95.67065047564017</v>
+        <v>95.67064284548596</v>
       </c>
       <c r="G300" t="n">
         <v>11307300</v>
@@ -7372,16 +7372,16 @@
         <v>45730</v>
       </c>
       <c r="C302" t="n">
-        <v>95.71825408935547</v>
+        <v>95.71826171875</v>
       </c>
       <c r="D302" t="n">
-        <v>95.71825408935547</v>
+        <v>95.71826171875</v>
       </c>
       <c r="E302" t="n">
-        <v>95.70872879837152</v>
+        <v>95.70873642700683</v>
       </c>
       <c r="F302" t="n">
-        <v>95.71825408935547</v>
+        <v>95.71826171875</v>
       </c>
       <c r="G302" t="n">
         <v>11421900</v>
@@ -7510,16 +7510,16 @@
         <v>45740</v>
       </c>
       <c r="C308" t="n">
-        <v>95.80397033691406</v>
+        <v>95.80399322509766</v>
       </c>
       <c r="D308" t="n">
-        <v>95.81349562893458</v>
+        <v>95.81351851939382</v>
       </c>
       <c r="E308" t="n">
-        <v>95.80397033691406</v>
+        <v>95.80399322509766</v>
       </c>
       <c r="F308" t="n">
-        <v>95.8087366157588</v>
+        <v>95.8087595050811</v>
       </c>
       <c r="G308" t="n">
         <v>13854600</v>
@@ -7556,16 +7556,16 @@
         <v>45742</v>
       </c>
       <c r="C310" t="n">
-        <v>95.83254241943359</v>
+        <v>95.83253479003906</v>
       </c>
       <c r="D310" t="n">
-        <v>95.83254241943359</v>
+        <v>95.83253479003906</v>
       </c>
       <c r="E310" t="n">
-        <v>95.8230243927372</v>
+        <v>95.82301676410042</v>
       </c>
       <c r="F310" t="n">
-        <v>95.83254241943359</v>
+        <v>95.83253479003906</v>
       </c>
       <c r="G310" t="n">
         <v>12262200</v>
@@ -7602,16 +7602,16 @@
         <v>45744</v>
       </c>
       <c r="C312" t="n">
-        <v>95.87064361572266</v>
+        <v>95.87065124511719</v>
       </c>
       <c r="D312" t="n">
-        <v>95.87064361572266</v>
+        <v>95.87065124511719</v>
       </c>
       <c r="E312" t="n">
-        <v>95.86112558830226</v>
+        <v>95.86113321693935</v>
       </c>
       <c r="F312" t="n">
-        <v>95.86112558830226</v>
+        <v>95.86113321693935</v>
       </c>
       <c r="G312" t="n">
         <v>11747100</v>
@@ -7625,16 +7625,16 @@
         <v>45747</v>
       </c>
       <c r="C313" t="n">
-        <v>95.87064361572266</v>
+        <v>95.87065124511719</v>
       </c>
       <c r="D313" t="n">
-        <v>95.88016890881283</v>
+        <v>95.88017653896539</v>
       </c>
       <c r="E313" t="n">
-        <v>95.87064361572266</v>
+        <v>95.87065124511719</v>
       </c>
       <c r="F313" t="n">
-        <v>95.87064361572266</v>
+        <v>95.87065124511719</v>
       </c>
       <c r="G313" t="n">
         <v>18210800</v>
@@ -7648,16 +7648,16 @@
         <v>45748</v>
       </c>
       <c r="C314" t="n">
-        <v>95.89549255371094</v>
+        <v>95.89550018310547</v>
       </c>
       <c r="D314" t="n">
-        <v>95.89549255371094</v>
+        <v>95.89550018310547</v>
       </c>
       <c r="E314" t="n">
-        <v>95.88593440926654</v>
+        <v>95.88594203790063</v>
       </c>
       <c r="F314" t="n">
-        <v>95.89549255371094</v>
+        <v>95.89550018310547</v>
       </c>
       <c r="G314" t="n">
         <v>21033200</v>
@@ -7694,16 +7694,16 @@
         <v>45750</v>
       </c>
       <c r="C316" t="n">
-        <v>95.92414093017578</v>
+        <v>95.92415618896484</v>
       </c>
       <c r="D316" t="n">
-        <v>95.92414093017578</v>
+        <v>95.92415618896484</v>
       </c>
       <c r="E316" t="n">
-        <v>95.90503193575341</v>
+        <v>95.90504719150279</v>
       </c>
       <c r="F316" t="n">
-        <v>95.9145900783279</v>
+        <v>95.9146053355977</v>
       </c>
       <c r="G316" t="n">
         <v>13988800</v>
@@ -7717,16 +7717,16 @@
         <v>45751</v>
       </c>
       <c r="C317" t="n">
-        <v>95.95282745361328</v>
+        <v>95.95285034179688</v>
       </c>
       <c r="D317" t="n">
-        <v>95.95282745361328</v>
+        <v>95.95285034179688</v>
       </c>
       <c r="E317" t="n">
-        <v>95.94326930983391</v>
+        <v>95.94329219573754</v>
       </c>
       <c r="F317" t="n">
-        <v>95.94326930983391</v>
+        <v>95.94329219573754</v>
       </c>
       <c r="G317" t="n">
         <v>22826300</v>
@@ -7740,16 +7740,16 @@
         <v>45754</v>
       </c>
       <c r="C318" t="n">
-        <v>95.96237182617188</v>
+        <v>95.96238708496094</v>
       </c>
       <c r="D318" t="n">
-        <v>95.96237182617188</v>
+        <v>95.96238708496094</v>
       </c>
       <c r="E318" t="n">
-        <v>95.95282097376501</v>
+        <v>95.95283623103541</v>
       </c>
       <c r="F318" t="n">
-        <v>95.95282097376501</v>
+        <v>95.95283623103541</v>
       </c>
       <c r="G318" t="n">
         <v>22564000</v>
@@ -7763,16 +7763,16 @@
         <v>45755</v>
       </c>
       <c r="C319" t="n">
-        <v>95.96237182617188</v>
+        <v>95.96238708496094</v>
       </c>
       <c r="D319" t="n">
-        <v>95.97192996930578</v>
+        <v>95.97194522961465</v>
       </c>
       <c r="E319" t="n">
-        <v>95.95282097376501</v>
+        <v>95.95283623103541</v>
       </c>
       <c r="F319" t="n">
-        <v>95.95759639996845</v>
+        <v>95.95761165799817</v>
       </c>
       <c r="G319" t="n">
         <v>17116100</v>
@@ -7786,16 +7786,16 @@
         <v>45756</v>
       </c>
       <c r="C320" t="n">
-        <v>95.98150634765625</v>
+        <v>95.98149108886719</v>
       </c>
       <c r="D320" t="n">
-        <v>95.98150634765625</v>
+        <v>95.98149108886719</v>
       </c>
       <c r="E320" t="n">
-        <v>95.97194820270643</v>
+        <v>95.97193294543689</v>
       </c>
       <c r="F320" t="n">
-        <v>95.97194820270643</v>
+        <v>95.97193294543689</v>
       </c>
       <c r="G320" t="n">
         <v>21838800</v>
@@ -7809,16 +7809,16 @@
         <v>45757</v>
       </c>
       <c r="C321" t="n">
-        <v>95.98150634765625</v>
+        <v>95.98149108886719</v>
       </c>
       <c r="D321" t="n">
-        <v>95.99105720187765</v>
+        <v>95.99104194157023</v>
       </c>
       <c r="E321" t="n">
-        <v>95.98150634765625</v>
+        <v>95.98149108886719</v>
       </c>
       <c r="F321" t="n">
-        <v>95.98150634765625</v>
+        <v>95.98149108886719</v>
       </c>
       <c r="G321" t="n">
         <v>16851500</v>
@@ -7832,16 +7832,16 @@
         <v>45758</v>
       </c>
       <c r="C322" t="n">
-        <v>96.02928924560547</v>
+        <v>96.02928161621094</v>
       </c>
       <c r="D322" t="n">
-        <v>96.02928924560547</v>
+        <v>96.02928161621094</v>
       </c>
       <c r="E322" t="n">
-        <v>96.01973839071226</v>
+        <v>96.01973076207653</v>
       </c>
       <c r="F322" t="n">
-        <v>96.02451381815887</v>
+        <v>96.02450618914374</v>
       </c>
       <c r="G322" t="n">
         <v>12916600</v>
@@ -7878,16 +7878,16 @@
         <v>45762</v>
       </c>
       <c r="C324" t="n">
-        <v>96.04837036132812</v>
+        <v>96.04837799072266</v>
       </c>
       <c r="D324" t="n">
-        <v>96.04837036132812</v>
+        <v>96.04837799072266</v>
       </c>
       <c r="E324" t="n">
-        <v>96.03881221920645</v>
+        <v>96.03881984784175</v>
       </c>
       <c r="F324" t="n">
-        <v>96.04837036132812</v>
+        <v>96.04837799072266</v>
       </c>
       <c r="G324" t="n">
         <v>10043700</v>
@@ -7901,16 +7901,16 @@
         <v>45763</v>
       </c>
       <c r="C325" t="n">
-        <v>96.06749725341797</v>
+        <v>96.06748962402344</v>
       </c>
       <c r="D325" t="n">
-        <v>96.06749725341797</v>
+        <v>96.06748962402344</v>
       </c>
       <c r="E325" t="n">
-        <v>96.05793910951549</v>
+        <v>96.05793148088003</v>
       </c>
       <c r="F325" t="n">
-        <v>96.06272182683053</v>
+        <v>96.06271419781525</v>
       </c>
       <c r="G325" t="n">
         <v>8840000</v>
@@ -7993,16 +7993,16 @@
         <v>45770</v>
       </c>
       <c r="C329" t="n">
-        <v>96.14395141601562</v>
+        <v>96.14396667480469</v>
       </c>
       <c r="D329" t="n">
-        <v>96.14395141601562</v>
+        <v>96.14396667480469</v>
       </c>
       <c r="E329" t="n">
-        <v>96.1248351274963</v>
+        <v>96.12485038325146</v>
       </c>
       <c r="F329" t="n">
-        <v>96.13439327175597</v>
+        <v>96.13440852902808</v>
       </c>
       <c r="G329" t="n">
         <v>19135100</v>
@@ -8016,16 +8016,16 @@
         <v>45771</v>
       </c>
       <c r="C330" t="n">
-        <v>96.14395141601562</v>
+        <v>96.14396667480469</v>
       </c>
       <c r="D330" t="n">
-        <v>96.1535095602753</v>
+        <v>96.15352482058131</v>
       </c>
       <c r="E330" t="n">
-        <v>96.14395141601562</v>
+        <v>96.14396667480469</v>
       </c>
       <c r="F330" t="n">
-        <v>96.1535095602753</v>
+        <v>96.15352482058131</v>
       </c>
       <c r="G330" t="n">
         <v>12068700</v>
@@ -8039,16 +8039,16 @@
         <v>45772</v>
       </c>
       <c r="C331" t="n">
-        <v>96.18216705322266</v>
+        <v>96.18217468261719</v>
       </c>
       <c r="D331" t="n">
-        <v>96.18216705322266</v>
+        <v>96.18217468261719</v>
       </c>
       <c r="E331" t="n">
-        <v>96.17260890992188</v>
+        <v>96.17261653855823</v>
       </c>
       <c r="F331" t="n">
-        <v>96.18216705322266</v>
+        <v>96.18217468261719</v>
       </c>
       <c r="G331" t="n">
         <v>8822700</v>
@@ -8062,16 +8062,16 @@
         <v>45775</v>
       </c>
       <c r="C332" t="n">
-        <v>96.18216705322266</v>
+        <v>96.18217468261719</v>
       </c>
       <c r="D332" t="n">
-        <v>96.19172519652344</v>
+        <v>96.19173282667613</v>
       </c>
       <c r="E332" t="n">
-        <v>96.18216705322266</v>
+        <v>96.18217468261719</v>
       </c>
       <c r="F332" t="n">
-        <v>96.18216705322266</v>
+        <v>96.18217468261719</v>
       </c>
       <c r="G332" t="n">
         <v>9127900</v>
@@ -8085,16 +8085,16 @@
         <v>45776</v>
       </c>
       <c r="C333" t="n">
-        <v>96.19173431396484</v>
+        <v>96.19174194335938</v>
       </c>
       <c r="D333" t="n">
-        <v>96.20128516744374</v>
+        <v>96.2012927975958</v>
       </c>
       <c r="E333" t="n">
-        <v>96.19173431396484</v>
+        <v>96.19174194335938</v>
       </c>
       <c r="F333" t="n">
-        <v>96.19173431396484</v>
+        <v>96.19174194335938</v>
       </c>
       <c r="G333" t="n">
         <v>8555000</v>
@@ -8108,16 +8108,16 @@
         <v>45777</v>
       </c>
       <c r="C334" t="n">
-        <v>96.22040557861328</v>
+        <v>96.22039794921875</v>
       </c>
       <c r="D334" t="n">
-        <v>96.22040557861328</v>
+        <v>96.22039794921875</v>
       </c>
       <c r="E334" t="n">
-        <v>96.20128928938072</v>
+        <v>96.20128166150194</v>
       </c>
       <c r="F334" t="n">
-        <v>96.20128928938072</v>
+        <v>96.20128166150194</v>
       </c>
       <c r="G334" t="n">
         <v>16040200</v>
@@ -8131,16 +8131,16 @@
         <v>45778</v>
       </c>
       <c r="C335" t="n">
-        <v>96.23477935791016</v>
+        <v>96.23478698730469</v>
       </c>
       <c r="D335" t="n">
-        <v>96.23477935791016</v>
+        <v>96.23478698730469</v>
       </c>
       <c r="E335" t="n">
-        <v>96.22518930762713</v>
+        <v>96.22519693626137</v>
       </c>
       <c r="F335" t="n">
-        <v>96.23477935791016</v>
+        <v>96.23478698730469</v>
       </c>
       <c r="G335" t="n">
         <v>21288700</v>
@@ -8177,16 +8177,16 @@
         <v>45782</v>
       </c>
       <c r="C337" t="n">
-        <v>96.27313232421875</v>
+        <v>96.27313995361328</v>
       </c>
       <c r="D337" t="n">
-        <v>96.27313232421875</v>
+        <v>96.27313995361328</v>
       </c>
       <c r="E337" t="n">
-        <v>96.26354227392774</v>
+        <v>96.26354990256227</v>
       </c>
       <c r="F337" t="n">
-        <v>96.27313232421875</v>
+        <v>96.27313995361328</v>
       </c>
       <c r="G337" t="n">
         <v>13223700</v>
@@ -8200,16 +8200,16 @@
         <v>45783</v>
       </c>
       <c r="C338" t="n">
-        <v>96.27313232421875</v>
+        <v>96.27313995361328</v>
       </c>
       <c r="D338" t="n">
-        <v>96.28271505944471</v>
+        <v>96.28272268959864</v>
       </c>
       <c r="E338" t="n">
-        <v>96.27313232421875</v>
+        <v>96.27313995361328</v>
       </c>
       <c r="F338" t="n">
-        <v>96.28271505944471</v>
+        <v>96.28272268959864</v>
       </c>
       <c r="G338" t="n">
         <v>8986000</v>
@@ -8223,16 +8223,16 @@
         <v>45784</v>
       </c>
       <c r="C339" t="n">
-        <v>96.28273010253906</v>
+        <v>96.28271484375</v>
       </c>
       <c r="D339" t="n">
-        <v>96.29232015432841</v>
+        <v>96.29230489401954</v>
       </c>
       <c r="E339" t="n">
-        <v>96.28273010253906</v>
+        <v>96.28271484375</v>
       </c>
       <c r="F339" t="n">
-        <v>96.29232015432841</v>
+        <v>96.29230489401954</v>
       </c>
       <c r="G339" t="n">
         <v>8509300</v>
@@ -8246,16 +8246,16 @@
         <v>45785</v>
       </c>
       <c r="C340" t="n">
-        <v>96.31148529052734</v>
+        <v>96.31147003173828</v>
       </c>
       <c r="D340" t="n">
-        <v>96.31148529052734</v>
+        <v>96.31147003173828</v>
       </c>
       <c r="E340" t="n">
-        <v>96.29231250353818</v>
+        <v>96.29229724778671</v>
       </c>
       <c r="F340" t="n">
-        <v>96.30190255456557</v>
+        <v>96.30188729729473</v>
       </c>
       <c r="G340" t="n">
         <v>11931100</v>
@@ -8269,16 +8269,16 @@
         <v>45786</v>
       </c>
       <c r="C341" t="n">
-        <v>96.34024047851562</v>
+        <v>96.34025573730469</v>
       </c>
       <c r="D341" t="n">
-        <v>96.34024047851562</v>
+        <v>96.34025573730469</v>
       </c>
       <c r="E341" t="n">
-        <v>96.33065042897792</v>
+        <v>96.33066568624807</v>
       </c>
       <c r="F341" t="n">
-        <v>96.33065042897792</v>
+        <v>96.33066568624807</v>
       </c>
       <c r="G341" t="n">
         <v>11793700</v>
@@ -8292,16 +8292,16 @@
         <v>45789</v>
       </c>
       <c r="C342" t="n">
-        <v>96.34024047851562</v>
+        <v>96.34025573730469</v>
       </c>
       <c r="D342" t="n">
-        <v>96.34982321298885</v>
+        <v>96.34983847329568</v>
       </c>
       <c r="E342" t="n">
-        <v>96.34024047851562</v>
+        <v>96.34025573730469</v>
       </c>
       <c r="F342" t="n">
-        <v>96.34024047851562</v>
+        <v>96.34025573730469</v>
       </c>
       <c r="G342" t="n">
         <v>16808300</v>
@@ -8315,16 +8315,16 @@
         <v>45790</v>
       </c>
       <c r="C343" t="n">
-        <v>96.35943603515625</v>
+        <v>96.35942077636719</v>
       </c>
       <c r="D343" t="n">
-        <v>96.35943603515625</v>
+        <v>96.35942077636719</v>
       </c>
       <c r="E343" t="n">
-        <v>96.34984598335213</v>
+        <v>96.34983072608168</v>
       </c>
       <c r="F343" t="n">
-        <v>96.34984598335213</v>
+        <v>96.34983072608168</v>
       </c>
       <c r="G343" t="n">
         <v>18174400</v>
@@ -8338,16 +8338,16 @@
         <v>45791</v>
       </c>
       <c r="C344" t="n">
-        <v>96.36899566650391</v>
+        <v>96.3690185546875</v>
       </c>
       <c r="D344" t="n">
-        <v>96.36899566650391</v>
+        <v>96.3690185546875</v>
       </c>
       <c r="E344" t="n">
-        <v>96.35940561772703</v>
+        <v>96.35942850363294</v>
       </c>
       <c r="F344" t="n">
-        <v>96.35940561772703</v>
+        <v>96.35942850363294</v>
       </c>
       <c r="G344" t="n">
         <v>9821100</v>
@@ -8361,16 +8361,16 @@
         <v>45792</v>
       </c>
       <c r="C345" t="n">
-        <v>96.36899566650391</v>
+        <v>96.3690185546875</v>
       </c>
       <c r="D345" t="n">
-        <v>96.37857840021688</v>
+        <v>96.37860129067643</v>
       </c>
       <c r="E345" t="n">
-        <v>96.36899566650391</v>
+        <v>96.3690185546875</v>
       </c>
       <c r="F345" t="n">
-        <v>96.37857840021688</v>
+        <v>96.37860129067643</v>
       </c>
       <c r="G345" t="n">
         <v>10057600</v>
@@ -8407,16 +8407,16 @@
         <v>45796</v>
       </c>
       <c r="C347" t="n">
-        <v>96.41694641113281</v>
+        <v>96.41695404052734</v>
       </c>
       <c r="D347" t="n">
-        <v>96.42653646141467</v>
+        <v>96.42654409156805</v>
       </c>
       <c r="E347" t="n">
-        <v>96.41694641113281</v>
+        <v>96.41695404052734</v>
       </c>
       <c r="F347" t="n">
-        <v>96.42653646141467</v>
+        <v>96.42654409156805</v>
       </c>
       <c r="G347" t="n">
         <v>15759100</v>
@@ -8430,16 +8430,16 @@
         <v>45797</v>
       </c>
       <c r="C348" t="n">
-        <v>96.43611907958984</v>
+        <v>96.43612670898438</v>
       </c>
       <c r="D348" t="n">
-        <v>96.43611907958984</v>
+        <v>96.43612670898438</v>
       </c>
       <c r="E348" t="n">
-        <v>96.42652903004708</v>
+        <v>96.42653665868291</v>
       </c>
       <c r="F348" t="n">
-        <v>96.43611907958984</v>
+        <v>96.43612670898438</v>
       </c>
       <c r="G348" t="n">
         <v>9249100</v>
@@ -8476,16 +8476,16 @@
         <v>45799</v>
       </c>
       <c r="C350" t="n">
-        <v>96.46488952636719</v>
+        <v>96.46489715576172</v>
       </c>
       <c r="D350" t="n">
-        <v>96.46488952636719</v>
+        <v>96.46489715576172</v>
       </c>
       <c r="E350" t="n">
-        <v>96.45529947606755</v>
+        <v>96.45530710470361</v>
       </c>
       <c r="F350" t="n">
-        <v>96.45529947606755</v>
+        <v>96.45530710470361</v>
       </c>
       <c r="G350" t="n">
         <v>8901700</v>
@@ -8499,16 +8499,16 @@
         <v>45800</v>
       </c>
       <c r="C351" t="n">
-        <v>96.49366760253906</v>
+        <v>96.49365234375</v>
       </c>
       <c r="D351" t="n">
-        <v>96.50325765435336</v>
+        <v>96.5032423940478</v>
       </c>
       <c r="E351" t="n">
-        <v>96.49366760253906</v>
+        <v>96.49365234375</v>
       </c>
       <c r="F351" t="n">
-        <v>96.50325765435336</v>
+        <v>96.5032423940478</v>
       </c>
       <c r="G351" t="n">
         <v>9119400</v>
@@ -8522,16 +8522,16 @@
         <v>45804</v>
       </c>
       <c r="C352" t="n">
-        <v>96.50323486328125</v>
+        <v>96.50325012207031</v>
       </c>
       <c r="D352" t="n">
-        <v>96.51282491283068</v>
+        <v>96.5128401731361</v>
       </c>
       <c r="E352" t="n">
-        <v>96.50323486328125</v>
+        <v>96.50325012207031</v>
       </c>
       <c r="F352" t="n">
-        <v>96.51282491283068</v>
+        <v>96.5128401731361</v>
       </c>
       <c r="G352" t="n">
         <v>10526600</v>
@@ -8591,16 +8591,16 @@
         <v>45807</v>
       </c>
       <c r="C355" t="n">
-        <v>96.56076812744141</v>
+        <v>96.56077575683594</v>
       </c>
       <c r="D355" t="n">
-        <v>96.57035817774533</v>
+        <v>96.57036580789759</v>
       </c>
       <c r="E355" t="n">
-        <v>96.56076812744141</v>
+        <v>96.56077575683594</v>
       </c>
       <c r="F355" t="n">
-        <v>96.56076812744141</v>
+        <v>96.56077575683594</v>
       </c>
       <c r="G355" t="n">
         <v>14209500</v>
@@ -8637,16 +8637,16 @@
         <v>45811</v>
       </c>
       <c r="C357" t="n">
-        <v>96.59732818603516</v>
+        <v>96.59734344482422</v>
       </c>
       <c r="D357" t="n">
-        <v>96.59732818603516</v>
+        <v>96.59734344482422</v>
       </c>
       <c r="E357" t="n">
-        <v>96.58770392423726</v>
+        <v>96.58771918150605</v>
       </c>
       <c r="F357" t="n">
-        <v>96.5925197257166</v>
+        <v>96.59253498374611</v>
       </c>
       <c r="G357" t="n">
         <v>11979500</v>
@@ -8660,16 +8660,16 @@
         <v>45812</v>
       </c>
       <c r="C358" t="n">
-        <v>96.60697174072266</v>
+        <v>96.60696411132812</v>
       </c>
       <c r="D358" t="n">
-        <v>96.60697174072266</v>
+        <v>96.60696411132812</v>
       </c>
       <c r="E358" t="n">
-        <v>96.59734747700276</v>
+        <v>96.59733984836828</v>
       </c>
       <c r="F358" t="n">
-        <v>96.60215593828157</v>
+        <v>96.60214830926736</v>
       </c>
       <c r="G358" t="n">
         <v>8923800</v>
@@ -8706,16 +8706,16 @@
         <v>45814</v>
       </c>
       <c r="C360" t="n">
-        <v>96.64545440673828</v>
+        <v>96.64544677734375</v>
       </c>
       <c r="D360" t="n">
-        <v>96.65507132859463</v>
+        <v>96.65506369844093</v>
       </c>
       <c r="E360" t="n">
-        <v>96.64545440673828</v>
+        <v>96.64544677734375</v>
       </c>
       <c r="F360" t="n">
-        <v>96.65026286766646</v>
+        <v>96.65025523789234</v>
       </c>
       <c r="G360" t="n">
         <v>9122400</v>
@@ -8729,16 +8729,16 @@
         <v>45817</v>
       </c>
       <c r="C361" t="n">
-        <v>96.65506744384766</v>
+        <v>96.65505218505859</v>
       </c>
       <c r="D361" t="n">
-        <v>96.66469170647891</v>
+        <v>96.66467644617047</v>
       </c>
       <c r="E361" t="n">
-        <v>96.65506744384766</v>
+        <v>96.65505218505859</v>
       </c>
       <c r="F361" t="n">
-        <v>96.65506744384766</v>
+        <v>96.65505218505859</v>
       </c>
       <c r="G361" t="n">
         <v>9902100</v>
@@ -8775,16 +8775,16 @@
         <v>45819</v>
       </c>
       <c r="C363" t="n">
-        <v>96.68392944335938</v>
+        <v>96.68394470214844</v>
       </c>
       <c r="D363" t="n">
-        <v>96.68392944335938</v>
+        <v>96.68394470214844</v>
       </c>
       <c r="E363" t="n">
-        <v>96.67430518180203</v>
+        <v>96.67432043907218</v>
       </c>
       <c r="F363" t="n">
-        <v>96.6791136420004</v>
+        <v>96.67912890002943</v>
       </c>
       <c r="G363" t="n">
         <v>10138800</v>
@@ -8798,16 +8798,16 @@
         <v>45820</v>
       </c>
       <c r="C364" t="n">
-        <v>96.69356536865234</v>
+        <v>96.69355010986328</v>
       </c>
       <c r="D364" t="n">
-        <v>96.69356536865234</v>
+        <v>96.69355010986328</v>
       </c>
       <c r="E364" t="n">
-        <v>96.68394844636542</v>
+        <v>96.68393318909396</v>
       </c>
       <c r="F364" t="n">
-        <v>96.69356536865234</v>
+        <v>96.69355010986328</v>
       </c>
       <c r="G364" t="n">
         <v>9574900</v>
@@ -8821,16 +8821,16 @@
         <v>45821</v>
       </c>
       <c r="C365" t="n">
-        <v>96.73203277587891</v>
+        <v>96.73204803466797</v>
       </c>
       <c r="D365" t="n">
-        <v>96.73203277587891</v>
+        <v>96.73204803466797</v>
       </c>
       <c r="E365" t="n">
-        <v>96.7224085146492</v>
+        <v>96.72242377192009</v>
       </c>
       <c r="F365" t="n">
-        <v>96.7224085146492</v>
+        <v>96.72242377192009</v>
       </c>
       <c r="G365" t="n">
         <v>7880300</v>
@@ -8844,16 +8844,16 @@
         <v>45824</v>
       </c>
       <c r="C366" t="n">
-        <v>96.73203277587891</v>
+        <v>96.73204803466797</v>
       </c>
       <c r="D366" t="n">
-        <v>96.74165703710862</v>
+        <v>96.74167229741583</v>
       </c>
       <c r="E366" t="n">
-        <v>96.73203277587891</v>
+        <v>96.73204803466797</v>
       </c>
       <c r="F366" t="n">
-        <v>96.74165703710862</v>
+        <v>96.74167229741583</v>
       </c>
       <c r="G366" t="n">
         <v>10286500</v>
@@ -8867,16 +8867,16 @@
         <v>45825</v>
       </c>
       <c r="C367" t="n">
-        <v>96.74166870117188</v>
+        <v>96.74166107177734</v>
       </c>
       <c r="D367" t="n">
-        <v>96.75129296356198</v>
+        <v>96.75128533340843</v>
       </c>
       <c r="E367" t="n">
-        <v>96.74166870117188</v>
+        <v>96.74166107177734</v>
       </c>
       <c r="F367" t="n">
-        <v>96.75129296356198</v>
+        <v>96.75128533340843</v>
       </c>
       <c r="G367" t="n">
         <v>8734500</v>
@@ -8890,16 +8890,16 @@
         <v>45826</v>
       </c>
       <c r="C368" t="n">
-        <v>96.76090240478516</v>
+        <v>96.76091766357422</v>
       </c>
       <c r="D368" t="n">
-        <v>96.77052666643127</v>
+        <v>96.77054192673803</v>
       </c>
       <c r="E368" t="n">
-        <v>96.76090240478516</v>
+        <v>96.76091766357422</v>
       </c>
       <c r="F368" t="n">
-        <v>96.77052666643127</v>
+        <v>96.77054192673803</v>
       </c>
       <c r="G368" t="n">
         <v>9783400</v>
@@ -8913,16 +8913,16 @@
         <v>45828</v>
       </c>
       <c r="C369" t="n">
-        <v>96.79940032958984</v>
+        <v>96.79940795898438</v>
       </c>
       <c r="D369" t="n">
-        <v>96.80902459205316</v>
+        <v>96.80903222220624</v>
       </c>
       <c r="E369" t="n">
-        <v>96.79940032958984</v>
+        <v>96.79940795898438</v>
       </c>
       <c r="F369" t="n">
-        <v>96.80421613140216</v>
+        <v>96.80422376117625</v>
       </c>
       <c r="G369" t="n">
         <v>9399400</v>
@@ -8959,16 +8959,16 @@
         <v>45832</v>
       </c>
       <c r="C371" t="n">
-        <v>96.82827758789062</v>
+        <v>96.82826232910156</v>
       </c>
       <c r="D371" t="n">
-        <v>96.837901851528</v>
+        <v>96.8378865912223</v>
       </c>
       <c r="E371" t="n">
-        <v>96.82827758789062</v>
+        <v>96.82826232910156</v>
       </c>
       <c r="F371" t="n">
-        <v>96.83309339029041</v>
+        <v>96.83307813074245</v>
       </c>
       <c r="G371" t="n">
         <v>10132100</v>
@@ -8982,16 +8982,16 @@
         <v>45833</v>
       </c>
       <c r="C372" t="n">
-        <v>96.83789825439453</v>
+        <v>96.837890625</v>
       </c>
       <c r="D372" t="n">
-        <v>96.84752251767441</v>
+        <v>96.84751488752164</v>
       </c>
       <c r="E372" t="n">
-        <v>96.83789825439453</v>
+        <v>96.837890625</v>
       </c>
       <c r="F372" t="n">
-        <v>96.8427067154535</v>
+        <v>96.84269908568015</v>
       </c>
       <c r="G372" t="n">
         <v>8015100</v>
@@ -9005,16 +9005,16 @@
         <v>45834</v>
       </c>
       <c r="C373" t="n">
-        <v>96.84751129150391</v>
+        <v>96.84751892089844</v>
       </c>
       <c r="D373" t="n">
-        <v>96.85713555366819</v>
+        <v>96.85714318382088</v>
       </c>
       <c r="E373" t="n">
-        <v>96.84751129150391</v>
+        <v>96.84751892089844</v>
       </c>
       <c r="F373" t="n">
-        <v>96.85713555366819</v>
+        <v>96.85714318382088</v>
       </c>
       <c r="G373" t="n">
         <v>9277700</v>
@@ -9028,16 +9028,16 @@
         <v>45835</v>
       </c>
       <c r="C374" t="n">
-        <v>96.88600921630859</v>
+        <v>96.88600158691406</v>
       </c>
       <c r="D374" t="n">
-        <v>96.88600921630859</v>
+        <v>96.88600158691406</v>
       </c>
       <c r="E374" t="n">
-        <v>96.87638495332804</v>
+        <v>96.87637732469139</v>
       </c>
       <c r="F374" t="n">
-        <v>96.88119341423747</v>
+        <v>96.88118578522216</v>
       </c>
       <c r="G374" t="n">
         <v>9742300</v>
@@ -9051,16 +9051,16 @@
         <v>45838</v>
       </c>
       <c r="C375" t="n">
-        <v>96.88600921630859</v>
+        <v>96.88600158691406</v>
       </c>
       <c r="D375" t="n">
-        <v>96.89562613812744</v>
+        <v>96.89561850797561</v>
       </c>
       <c r="E375" t="n">
-        <v>96.88600921630859</v>
+        <v>96.88600158691406</v>
       </c>
       <c r="F375" t="n">
-        <v>96.88600921630859</v>
+        <v>96.88600158691406</v>
       </c>
       <c r="G375" t="n">
         <v>18195600</v>
@@ -9120,16 +9120,16 @@
         <v>45841</v>
       </c>
       <c r="C378" t="n">
-        <v>96.96035003662109</v>
+        <v>96.96034240722656</v>
       </c>
       <c r="D378" t="n">
-        <v>96.97000758141002</v>
+        <v>96.96999995125557</v>
       </c>
       <c r="E378" t="n">
-        <v>96.96035003662109</v>
+        <v>96.96034240722656</v>
       </c>
       <c r="F378" t="n">
-        <v>96.96035003662109</v>
+        <v>96.96034240722656</v>
       </c>
       <c r="G378" t="n">
         <v>7404700</v>
@@ -9143,16 +9143,16 @@
         <v>45845</v>
       </c>
       <c r="C379" t="n">
-        <v>96.97967529296875</v>
+        <v>96.97966003417969</v>
       </c>
       <c r="D379" t="n">
-        <v>96.97967529296875</v>
+        <v>96.97966003417969</v>
       </c>
       <c r="E379" t="n">
-        <v>96.97001774716739</v>
+        <v>96.97000248989785</v>
       </c>
       <c r="F379" t="n">
-        <v>96.97967529296875</v>
+        <v>96.97966003417969</v>
       </c>
       <c r="G379" t="n">
         <v>12363900</v>
@@ -9166,16 +9166,16 @@
         <v>45846</v>
       </c>
       <c r="C380" t="n">
-        <v>96.99897003173828</v>
+        <v>96.99895477294922</v>
       </c>
       <c r="D380" t="n">
-        <v>96.99897003173828</v>
+        <v>96.99895477294922</v>
       </c>
       <c r="E380" t="n">
-        <v>96.97966230926953</v>
+        <v>96.97964705351775</v>
       </c>
       <c r="F380" t="n">
-        <v>96.98931248722988</v>
+        <v>96.98929722996003</v>
       </c>
       <c r="G380" t="n">
         <v>13107800</v>
@@ -9189,16 +9189,16 @@
         <v>45847</v>
       </c>
       <c r="C381" t="n">
-        <v>96.98930358886719</v>
+        <v>96.98929595947266</v>
       </c>
       <c r="D381" t="n">
-        <v>96.99896113248955</v>
+        <v>96.99895350233534</v>
       </c>
       <c r="E381" t="n">
-        <v>96.98930358886719</v>
+        <v>96.98929595947266</v>
       </c>
       <c r="F381" t="n">
-        <v>96.99896113248955</v>
+        <v>96.99895350233534</v>
       </c>
       <c r="G381" t="n">
         <v>11156600</v>
@@ -9212,16 +9212,16 @@
         <v>45848</v>
       </c>
       <c r="C382" t="n">
-        <v>97.00863647460938</v>
+        <v>97.00862884521484</v>
       </c>
       <c r="D382" t="n">
-        <v>97.01829402000364</v>
+        <v>97.01828638984958</v>
       </c>
       <c r="E382" t="n">
-        <v>96.99897892921511</v>
+        <v>96.99897130058011</v>
       </c>
       <c r="F382" t="n">
-        <v>97.00863647460938</v>
+        <v>97.00862884521484</v>
       </c>
       <c r="G382" t="n">
         <v>10071700</v>
@@ -9304,16 +9304,16 @@
         <v>45854</v>
       </c>
       <c r="C386" t="n">
-        <v>97.08586883544922</v>
+        <v>97.08586120605469</v>
       </c>
       <c r="D386" t="n">
-        <v>97.08586883544922</v>
+        <v>97.08586120605469</v>
       </c>
       <c r="E386" t="n">
-        <v>97.07621129137489</v>
+        <v>97.0762036627393</v>
       </c>
       <c r="F386" t="n">
-        <v>97.07621129137489</v>
+        <v>97.0762036627393</v>
       </c>
       <c r="G386" t="n">
         <v>8117900</v>
@@ -9327,16 +9327,16 @@
         <v>45855</v>
       </c>
       <c r="C387" t="n">
-        <v>97.09552001953125</v>
+        <v>97.09552764892578</v>
       </c>
       <c r="D387" t="n">
-        <v>97.09552001953125</v>
+        <v>97.09552764892578</v>
       </c>
       <c r="E387" t="n">
-        <v>97.08586984190462</v>
+        <v>97.08587747054088</v>
       </c>
       <c r="F387" t="n">
-        <v>97.09069493071793</v>
+        <v>97.09070255973333</v>
       </c>
       <c r="G387" t="n">
         <v>9040400</v>
@@ -9373,16 +9373,16 @@
         <v>45859</v>
       </c>
       <c r="C389" t="n">
-        <v>97.13414001464844</v>
+        <v>97.1341552734375</v>
       </c>
       <c r="D389" t="n">
-        <v>97.13414001464844</v>
+        <v>97.1341552734375</v>
       </c>
       <c r="E389" t="n">
-        <v>97.12448247075388</v>
+        <v>97.12449772802584</v>
       </c>
       <c r="F389" t="n">
-        <v>97.12448247075388</v>
+        <v>97.12449772802584</v>
       </c>
       <c r="G389" t="n">
         <v>12893000</v>
@@ -9419,16 +9419,16 @@
         <v>45861</v>
       </c>
       <c r="C391" t="n">
-        <v>97.16310882568359</v>
+        <v>97.16310119628906</v>
       </c>
       <c r="D391" t="n">
-        <v>97.16310882568359</v>
+        <v>97.16310119628906</v>
       </c>
       <c r="E391" t="n">
-        <v>97.15345864798445</v>
+        <v>97.15345101934767</v>
       </c>
       <c r="F391" t="n">
-        <v>97.16310882568359</v>
+        <v>97.16310119628906</v>
       </c>
       <c r="G391" t="n">
         <v>8056100</v>
@@ -9488,16 +9488,16 @@
         <v>45866</v>
       </c>
       <c r="C394" t="n">
-        <v>97.22105407714844</v>
+        <v>97.22104644775391</v>
       </c>
       <c r="D394" t="n">
-        <v>97.22105407714844</v>
+        <v>97.22104644775391</v>
       </c>
       <c r="E394" t="n">
-        <v>97.21139653217107</v>
+        <v>97.21138890353441</v>
       </c>
       <c r="F394" t="n">
-        <v>97.21622162138554</v>
+        <v>97.21621399237023</v>
       </c>
       <c r="G394" t="n">
         <v>11581000</v>
@@ -9511,16 +9511,16 @@
         <v>45867</v>
       </c>
       <c r="C395" t="n">
-        <v>97.22105407714844</v>
+        <v>97.22104644775391</v>
       </c>
       <c r="D395" t="n">
-        <v>97.23070425557738</v>
+        <v>97.23069662542557</v>
       </c>
       <c r="E395" t="n">
-        <v>97.22105407714844</v>
+        <v>97.22104644775391</v>
       </c>
       <c r="F395" t="n">
-        <v>97.22105407714844</v>
+        <v>97.22104644775391</v>
       </c>
       <c r="G395" t="n">
         <v>8622300</v>
@@ -9534,16 +9534,16 @@
         <v>45868</v>
       </c>
       <c r="C396" t="n">
-        <v>97.24034881591797</v>
+        <v>97.2403564453125</v>
       </c>
       <c r="D396" t="n">
-        <v>97.24034881591797</v>
+        <v>97.2403564453125</v>
       </c>
       <c r="E396" t="n">
-        <v>97.23069127223019</v>
+        <v>97.230698900867</v>
       </c>
       <c r="F396" t="n">
-        <v>97.23069127223019</v>
+        <v>97.230698900867</v>
       </c>
       <c r="G396" t="n">
         <v>9106000</v>
@@ -9580,16 +9580,16 @@
         <v>45870</v>
       </c>
       <c r="C398" t="n">
-        <v>97.28101348876953</v>
+        <v>97.28102874755859</v>
       </c>
       <c r="D398" t="n">
-        <v>97.29070586804504</v>
+        <v>97.29072112835438</v>
       </c>
       <c r="E398" t="n">
-        <v>97.28101348876953</v>
+        <v>97.28102874755859</v>
       </c>
       <c r="F398" t="n">
-        <v>97.28101348876953</v>
+        <v>97.28102874755859</v>
       </c>
       <c r="G398" t="n">
         <v>26832500</v>
@@ -9603,16 +9603,16 @@
         <v>45873</v>
       </c>
       <c r="C399" t="n">
-        <v>97.30040740966797</v>
+        <v>97.3004150390625</v>
       </c>
       <c r="D399" t="n">
-        <v>97.30040740966797</v>
+        <v>97.3004150390625</v>
       </c>
       <c r="E399" t="n">
-        <v>97.29071502947977</v>
+        <v>97.2907226581143</v>
       </c>
       <c r="F399" t="n">
-        <v>97.29555752301393</v>
+        <v>97.29556515202816</v>
       </c>
       <c r="G399" t="n">
         <v>14766400</v>
@@ -9626,16 +9626,16 @@
         <v>45874</v>
       </c>
       <c r="C400" t="n">
-        <v>97.31008911132812</v>
+        <v>97.31008148193359</v>
       </c>
       <c r="D400" t="n">
-        <v>97.31008911132812</v>
+        <v>97.31008148193359</v>
       </c>
       <c r="E400" t="n">
-        <v>97.30040412458681</v>
+        <v>97.30039649595162</v>
       </c>
       <c r="F400" t="n">
-        <v>97.30040412458681</v>
+        <v>97.30039649595162</v>
       </c>
       <c r="G400" t="n">
         <v>12350300</v>
@@ -9695,16 +9695,16 @@
         <v>45877</v>
       </c>
       <c r="C403" t="n">
-        <v>97.36823272705078</v>
+        <v>97.36824798583984</v>
       </c>
       <c r="D403" t="n">
-        <v>97.36823272705078</v>
+        <v>97.36824798583984</v>
       </c>
       <c r="E403" t="n">
-        <v>97.35854034751536</v>
+        <v>97.35855560478551</v>
       </c>
       <c r="F403" t="n">
-        <v>97.36338284072336</v>
+        <v>97.3633980987524</v>
       </c>
       <c r="G403" t="n">
         <v>12066300</v>
@@ -9718,16 +9718,16 @@
         <v>45880</v>
       </c>
       <c r="C404" t="n">
-        <v>97.37793731689453</v>
+        <v>97.37791442871094</v>
       </c>
       <c r="D404" t="n">
-        <v>97.37793731689453</v>
+        <v>97.37791442871094</v>
       </c>
       <c r="E404" t="n">
-        <v>97.3682523285288</v>
+        <v>97.36822944262161</v>
       </c>
       <c r="F404" t="n">
-        <v>97.37793731689453</v>
+        <v>97.37791442871094</v>
       </c>
       <c r="G404" t="n">
         <v>12940300</v>
@@ -9741,16 +9741,16 @@
         <v>45881</v>
       </c>
       <c r="C405" t="n">
-        <v>97.37793731689453</v>
+        <v>97.37791442871094</v>
       </c>
       <c r="D405" t="n">
-        <v>97.38762969838115</v>
+        <v>97.38760680791941</v>
       </c>
       <c r="E405" t="n">
-        <v>97.37793731689453</v>
+        <v>97.37791442871094</v>
       </c>
       <c r="F405" t="n">
-        <v>97.38762969838115</v>
+        <v>97.38760680791941</v>
       </c>
       <c r="G405" t="n">
         <v>12918200</v>
@@ -9764,16 +9764,16 @@
         <v>45882</v>
       </c>
       <c r="C406" t="n">
-        <v>97.39730072021484</v>
+        <v>97.39729309082031</v>
       </c>
       <c r="D406" t="n">
-        <v>97.40698570645661</v>
+        <v>97.40697807630343</v>
       </c>
       <c r="E406" t="n">
-        <v>97.3876083408538</v>
+        <v>97.3876007122185</v>
       </c>
       <c r="F406" t="n">
-        <v>97.39730072021484</v>
+        <v>97.39729309082031</v>
       </c>
       <c r="G406" t="n">
         <v>12144800</v>
@@ -9787,16 +9787,16 @@
         <v>45883</v>
       </c>
       <c r="C407" t="n">
-        <v>97.406982421875</v>
+        <v>97.40699005126953</v>
       </c>
       <c r="D407" t="n">
-        <v>97.41667480090922</v>
+        <v>97.4166824310629</v>
       </c>
       <c r="E407" t="n">
-        <v>97.406982421875</v>
+        <v>97.40699005126953</v>
       </c>
       <c r="F407" t="n">
-        <v>97.406982421875</v>
+        <v>97.40699005126953</v>
       </c>
       <c r="G407" t="n">
         <v>9798900</v>
@@ -9810,16 +9810,16 @@
         <v>45884</v>
       </c>
       <c r="C408" t="n">
-        <v>97.43606567382812</v>
+        <v>97.43605804443359</v>
       </c>
       <c r="D408" t="n">
-        <v>97.44575066035112</v>
+        <v>97.44574303019824</v>
       </c>
       <c r="E408" t="n">
-        <v>97.43606567382812</v>
+        <v>97.43605804443359</v>
       </c>
       <c r="F408" t="n">
-        <v>97.44575066035112</v>
+        <v>97.44574303019824</v>
       </c>
       <c r="G408" t="n">
         <v>9493900</v>
@@ -9833,16 +9833,16 @@
         <v>45887</v>
       </c>
       <c r="C409" t="n">
-        <v>97.46513366699219</v>
+        <v>97.46514129638672</v>
       </c>
       <c r="D409" t="n">
-        <v>97.46513366699219</v>
+        <v>97.46514129638672</v>
       </c>
       <c r="E409" t="n">
-        <v>97.4457489080558</v>
+        <v>97.44575653593293</v>
       </c>
       <c r="F409" t="n">
-        <v>97.455441287524</v>
+        <v>97.45544891615982</v>
       </c>
       <c r="G409" t="n">
         <v>14768500</v>
@@ -9856,16 +9856,16 @@
         <v>45888</v>
       </c>
       <c r="C410" t="n">
-        <v>97.46513366699219</v>
+        <v>97.46514129638672</v>
       </c>
       <c r="D410" t="n">
-        <v>97.47481865334103</v>
+        <v>97.47482628349368</v>
       </c>
       <c r="E410" t="n">
-        <v>97.46513366699219</v>
+        <v>97.46514129638672</v>
       </c>
       <c r="F410" t="n">
-        <v>97.47481865334103</v>
+        <v>97.47482628349368</v>
       </c>
       <c r="G410" t="n">
         <v>10474900</v>
@@ -9879,16 +9879,16 @@
         <v>45889</v>
       </c>
       <c r="C411" t="n">
-        <v>97.48450469970703</v>
+        <v>97.48451995849609</v>
       </c>
       <c r="D411" t="n">
-        <v>97.48450469970703</v>
+        <v>97.48451995849609</v>
       </c>
       <c r="E411" t="n">
-        <v>97.47481232086851</v>
+        <v>97.47482757814046</v>
       </c>
       <c r="F411" t="n">
-        <v>97.48450469970703</v>
+        <v>97.48451995849609</v>
       </c>
       <c r="G411" t="n">
         <v>10922100</v>
@@ -9902,16 +9902,16 @@
         <v>45890</v>
       </c>
       <c r="C412" t="n">
-        <v>97.48450469970703</v>
+        <v>97.48451995849609</v>
       </c>
       <c r="D412" t="n">
-        <v>97.49419707854555</v>
+        <v>97.49421233885172</v>
       </c>
       <c r="E412" t="n">
-        <v>97.48450469970703</v>
+        <v>97.48451995849609</v>
       </c>
       <c r="F412" t="n">
-        <v>97.49419707854555</v>
+        <v>97.49421233885172</v>
       </c>
       <c r="G412" t="n">
         <v>8765300</v>
@@ -9948,16 +9948,16 @@
         <v>45894</v>
       </c>
       <c r="C414" t="n">
-        <v>97.54267120361328</v>
+        <v>97.54266357421875</v>
       </c>
       <c r="D414" t="n">
-        <v>97.54267120361328</v>
+        <v>97.54266357421875</v>
       </c>
       <c r="E414" t="n">
-        <v>97.5329788228248</v>
+        <v>97.53297119418838</v>
       </c>
       <c r="F414" t="n">
-        <v>97.53782131665886</v>
+        <v>97.53781368764366</v>
       </c>
       <c r="G414" t="n">
         <v>13556000</v>
@@ -9971,16 +9971,16 @@
         <v>45895</v>
       </c>
       <c r="C415" t="n">
-        <v>97.54267120361328</v>
+        <v>97.54266357421875</v>
       </c>
       <c r="D415" t="n">
-        <v>97.55235619128139</v>
+        <v>97.55234856112934</v>
       </c>
       <c r="E415" t="n">
-        <v>97.54267120361328</v>
+        <v>97.54266357421875</v>
       </c>
       <c r="F415" t="n">
-        <v>97.54751369744734</v>
+        <v>97.54750606767405</v>
       </c>
       <c r="G415" t="n">
         <v>8741600</v>
@@ -9994,16 +9994,16 @@
         <v>45896</v>
       </c>
       <c r="C416" t="n">
-        <v>97.55235290527344</v>
+        <v>97.55236053466797</v>
       </c>
       <c r="D416" t="n">
-        <v>97.56204528573542</v>
+        <v>97.56205291588799</v>
       </c>
       <c r="E416" t="n">
-        <v>97.55235290527344</v>
+        <v>97.55236053466797</v>
       </c>
       <c r="F416" t="n">
-        <v>97.56204528573542</v>
+        <v>97.56205291588799</v>
       </c>
       <c r="G416" t="n">
         <v>7384600</v>
@@ -10017,16 +10017,16 @@
         <v>45897</v>
       </c>
       <c r="C417" t="n">
-        <v>97.56204223632812</v>
+        <v>97.56202697753906</v>
       </c>
       <c r="D417" t="n">
-        <v>97.57173461648718</v>
+        <v>97.57171935618221</v>
       </c>
       <c r="E417" t="n">
-        <v>97.56204223632812</v>
+        <v>97.56202697753906</v>
       </c>
       <c r="F417" t="n">
-        <v>97.56688472984771</v>
+        <v>97.56686947030127</v>
       </c>
       <c r="G417" t="n">
         <v>8816600</v>
@@ -10040,16 +10040,16 @@
         <v>45898</v>
       </c>
       <c r="C418" t="n">
-        <v>97.62017059326172</v>
+        <v>97.62017822265625</v>
       </c>
       <c r="D418" t="n">
-        <v>97.62017059326172</v>
+        <v>97.62017822265625</v>
       </c>
       <c r="E418" t="n">
-        <v>97.60079322827433</v>
+        <v>97.60080085615444</v>
       </c>
       <c r="F418" t="n">
-        <v>97.60079322827433</v>
+        <v>97.60080085615444</v>
       </c>
       <c r="G418" t="n">
         <v>21369400</v>
@@ -10063,16 +10063,16 @@
         <v>45902</v>
       </c>
       <c r="C419" t="n">
-        <v>97.62989044189453</v>
+        <v>97.62990570068359</v>
       </c>
       <c r="D419" t="n">
-        <v>97.62989044189453</v>
+        <v>97.62990570068359</v>
       </c>
       <c r="E419" t="n">
-        <v>97.62016330303307</v>
+        <v>97.62017856030185</v>
       </c>
       <c r="F419" t="n">
-        <v>97.62989044189453</v>
+        <v>97.62990570068359</v>
       </c>
       <c r="G419" t="n">
         <v>27254500</v>
@@ -10086,16 +10086,16 @@
         <v>45903</v>
       </c>
       <c r="C420" t="n">
-        <v>97.6396484375</v>
+        <v>97.63963317871094</v>
       </c>
       <c r="D420" t="n">
-        <v>97.6396484375</v>
+        <v>97.63963317871094</v>
       </c>
       <c r="E420" t="n">
-        <v>97.62992129556449</v>
+        <v>97.62990603829556</v>
       </c>
       <c r="F420" t="n">
-        <v>97.63478115671457</v>
+        <v>97.63476589868615</v>
       </c>
       <c r="G420" t="n">
         <v>14296000</v>
@@ -10109,16 +10109,16 @@
         <v>45904</v>
       </c>
       <c r="C421" t="n">
-        <v>97.65908813476562</v>
+        <v>97.65908050537109</v>
       </c>
       <c r="D421" t="n">
-        <v>97.65908813476562</v>
+        <v>97.65908050537109</v>
       </c>
       <c r="E421" t="n">
-        <v>97.64936841317878</v>
+        <v>97.64936078454357</v>
       </c>
       <c r="F421" t="n">
-        <v>97.65422827397219</v>
+        <v>97.65422064495733</v>
       </c>
       <c r="G421" t="n">
         <v>11300200</v>
@@ -10155,16 +10155,16 @@
         <v>45908</v>
       </c>
       <c r="C423" t="n">
-        <v>97.70771026611328</v>
+        <v>97.70770263671875</v>
       </c>
       <c r="D423" t="n">
-        <v>97.70771026611328</v>
+        <v>97.70770263671875</v>
       </c>
       <c r="E423" t="n">
-        <v>97.69798312550439</v>
+        <v>97.69797549686939</v>
       </c>
       <c r="F423" t="n">
-        <v>97.70284298599168</v>
+        <v>97.70283535697719</v>
       </c>
       <c r="G423" t="n">
         <v>12715100</v>
@@ -10178,16 +10178,16 @@
         <v>45909</v>
       </c>
       <c r="C424" t="n">
-        <v>97.70771026611328</v>
+        <v>97.70770263671875</v>
       </c>
       <c r="D424" t="n">
-        <v>97.71743740672217</v>
+        <v>97.71742977656811</v>
       </c>
       <c r="E424" t="n">
-        <v>97.70771026611328</v>
+        <v>97.70770263671875</v>
       </c>
       <c r="F424" t="n">
-        <v>97.71743740672217</v>
+        <v>97.71742977656811</v>
       </c>
       <c r="G424" t="n">
         <v>11005500</v>
@@ -10247,16 +10247,16 @@
         <v>45912</v>
       </c>
       <c r="C427" t="n">
-        <v>97.76604461669922</v>
+        <v>97.76605224609375</v>
       </c>
       <c r="D427" t="n">
-        <v>97.77577175594963</v>
+        <v>97.77577938610324</v>
       </c>
       <c r="E427" t="n">
-        <v>97.76604461669922</v>
+        <v>97.76605224609375</v>
       </c>
       <c r="F427" t="n">
-        <v>97.76604461669922</v>
+        <v>97.76605224609375</v>
       </c>
       <c r="G427" t="n">
         <v>10482000</v>
@@ -10270,16 +10270,16 @@
         <v>45915</v>
       </c>
       <c r="C428" t="n">
-        <v>97.76604461669922</v>
+        <v>97.76605224609375</v>
       </c>
       <c r="D428" t="n">
-        <v>97.77577175594963</v>
+        <v>97.77577938610324</v>
       </c>
       <c r="E428" t="n">
-        <v>97.76604461669922</v>
+        <v>97.76605224609375</v>
       </c>
       <c r="F428" t="n">
-        <v>97.76604461669922</v>
+        <v>97.76605224609375</v>
       </c>
       <c r="G428" t="n">
         <v>15288300</v>
@@ -10293,16 +10293,16 @@
         <v>45916</v>
       </c>
       <c r="C429" t="n">
-        <v>97.78549957275391</v>
+        <v>97.78550720214844</v>
       </c>
       <c r="D429" t="n">
-        <v>97.79521929243838</v>
+        <v>97.79522692259125</v>
       </c>
       <c r="E429" t="n">
-        <v>97.78549957275391</v>
+        <v>97.78550720214844</v>
       </c>
       <c r="F429" t="n">
-        <v>97.78549957275391</v>
+        <v>97.78550720214844</v>
       </c>
       <c r="G429" t="n">
         <v>11551900</v>
@@ -10316,16 +10316,16 @@
         <v>45917</v>
       </c>
       <c r="C430" t="n">
-        <v>97.79522705078125</v>
+        <v>97.79523468017578</v>
       </c>
       <c r="D430" t="n">
-        <v>97.80495419087075</v>
+        <v>97.80496182102412</v>
       </c>
       <c r="E430" t="n">
-        <v>97.79522705078125</v>
+        <v>97.79523468017578</v>
       </c>
       <c r="F430" t="n">
-        <v>97.80495419087075</v>
+        <v>97.80496182102412</v>
       </c>
       <c r="G430" t="n">
         <v>10381200</v>
@@ -10339,16 +10339,16 @@
         <v>45918</v>
       </c>
       <c r="C431" t="n">
-        <v>97.81468200683594</v>
+        <v>97.81468963623047</v>
       </c>
       <c r="D431" t="n">
-        <v>97.81468200683594</v>
+        <v>97.81468963623047</v>
       </c>
       <c r="E431" t="n">
-        <v>97.80495486667922</v>
+        <v>97.80496249531507</v>
       </c>
       <c r="F431" t="n">
-        <v>97.81468200683594</v>
+        <v>97.81468963623047</v>
       </c>
       <c r="G431" t="n">
         <v>13414500</v>
@@ -10362,16 +10362,16 @@
         <v>45919</v>
       </c>
       <c r="C432" t="n">
-        <v>97.85357666015625</v>
+        <v>97.85358428955078</v>
       </c>
       <c r="D432" t="n">
-        <v>97.85357666015625</v>
+        <v>97.85358428955078</v>
       </c>
       <c r="E432" t="n">
-        <v>97.84384952064445</v>
+        <v>97.84385714928058</v>
       </c>
       <c r="F432" t="n">
-        <v>97.84384952064445</v>
+        <v>97.84385714928058</v>
       </c>
       <c r="G432" t="n">
         <v>11174000</v>
@@ -10385,16 +10385,16 @@
         <v>45922</v>
       </c>
       <c r="C433" t="n">
-        <v>97.85357666015625</v>
+        <v>97.85358428955078</v>
       </c>
       <c r="D433" t="n">
-        <v>97.86329638003455</v>
+        <v>97.86330401018691</v>
       </c>
       <c r="E433" t="n">
-        <v>97.85357666015625</v>
+        <v>97.85358428955078</v>
       </c>
       <c r="F433" t="n">
-        <v>97.85357666015625</v>
+        <v>97.85358428955078</v>
       </c>
       <c r="G433" t="n">
         <v>12279500</v>
@@ -10408,16 +10408,16 @@
         <v>45923</v>
       </c>
       <c r="C434" t="n">
-        <v>97.87302398681641</v>
+        <v>97.87303924560547</v>
       </c>
       <c r="D434" t="n">
-        <v>97.87302398681641</v>
+        <v>97.87303924560547</v>
       </c>
       <c r="E434" t="n">
-        <v>97.86329684725817</v>
+        <v>97.86331210453073</v>
       </c>
       <c r="F434" t="n">
-        <v>97.86816412685405</v>
+        <v>97.86817938488544</v>
       </c>
       <c r="G434" t="n">
         <v>11191700</v>
@@ -10431,16 +10431,16 @@
         <v>45924</v>
       </c>
       <c r="C435" t="n">
-        <v>97.88275909423828</v>
+        <v>97.88275146484375</v>
       </c>
       <c r="D435" t="n">
-        <v>97.88275909423828</v>
+        <v>97.88275146484375</v>
       </c>
       <c r="E435" t="n">
-        <v>97.87303195388823</v>
+        <v>97.87302432525188</v>
       </c>
       <c r="F435" t="n">
-        <v>97.8778918142462</v>
+        <v>97.87788418523103</v>
       </c>
       <c r="G435" t="n">
         <v>10108500</v>
@@ -10454,16 +10454,16 @@
         <v>45925</v>
       </c>
       <c r="C436" t="n">
-        <v>97.89248657226562</v>
+        <v>97.89247894287109</v>
       </c>
       <c r="D436" t="n">
-        <v>97.89248657226562</v>
+        <v>97.89247894287109</v>
       </c>
       <c r="E436" t="n">
-        <v>97.88275943188202</v>
+        <v>97.88275180324558</v>
       </c>
       <c r="F436" t="n">
-        <v>97.88275943188202</v>
+        <v>97.88275180324558</v>
       </c>
       <c r="G436" t="n">
         <v>10549100</v>
@@ -10477,16 +10477,16 @@
         <v>45926</v>
       </c>
       <c r="C437" t="n">
-        <v>97.92166137695312</v>
+        <v>97.92165374755859</v>
       </c>
       <c r="D437" t="n">
-        <v>97.92166137695312</v>
+        <v>97.92165374755859</v>
       </c>
       <c r="E437" t="n">
-        <v>97.91193423648973</v>
+        <v>97.91192660785308</v>
       </c>
       <c r="F437" t="n">
-        <v>97.91193423648973</v>
+        <v>97.91192660785308</v>
       </c>
       <c r="G437" t="n">
         <v>10688600</v>
@@ -10500,16 +10500,16 @@
         <v>45929</v>
       </c>
       <c r="C438" t="n">
-        <v>97.93137359619141</v>
+        <v>97.93138122558594</v>
       </c>
       <c r="D438" t="n">
-        <v>97.93137359619141</v>
+        <v>97.93138122558594</v>
       </c>
       <c r="E438" t="n">
-        <v>97.92165387610677</v>
+        <v>97.92166150474409</v>
       </c>
       <c r="F438" t="n">
-        <v>97.93137359619141</v>
+        <v>97.93138122558594</v>
       </c>
       <c r="G438" t="n">
         <v>13580800</v>
@@ -10523,16 +10523,16 @@
         <v>45930</v>
       </c>
       <c r="C439" t="n">
-        <v>97.93137359619141</v>
+        <v>97.93138122558594</v>
       </c>
       <c r="D439" t="n">
-        <v>97.94110073590969</v>
+        <v>97.94110836606202</v>
       </c>
       <c r="E439" t="n">
-        <v>97.93137359619141</v>
+        <v>97.93138122558594</v>
       </c>
       <c r="F439" t="n">
-        <v>97.93624087586737</v>
+        <v>97.9362485056411</v>
       </c>
       <c r="G439" t="n">
         <v>22909500</v>
@@ -10546,16 +10546,16 @@
         <v>45931</v>
       </c>
       <c r="C440" t="n">
-        <v>97.94796752929688</v>
+        <v>97.94797515869141</v>
       </c>
       <c r="D440" t="n">
-        <v>97.95772085802308</v>
+        <v>97.95772848817732</v>
       </c>
       <c r="E440" t="n">
-        <v>97.94796752929688</v>
+        <v>97.94797515869141</v>
       </c>
       <c r="F440" t="n">
-        <v>97.95772085802308</v>
+        <v>97.95772848817732</v>
       </c>
       <c r="G440" t="n">
         <v>26613600</v>
@@ -10569,16 +10569,16 @@
         <v>45932</v>
       </c>
       <c r="C441" t="n">
-        <v>97.95771789550781</v>
+        <v>97.95771026611328</v>
       </c>
       <c r="D441" t="n">
-        <v>97.96747866922793</v>
+        <v>97.96747103907319</v>
       </c>
       <c r="E441" t="n">
-        <v>97.95771789550781</v>
+        <v>97.95771026611328</v>
       </c>
       <c r="F441" t="n">
-        <v>97.96747866922793</v>
+        <v>97.96747103907319</v>
       </c>
       <c r="G441" t="n">
         <v>12870100</v>
@@ -10592,16 +10592,16 @@
         <v>45933</v>
       </c>
       <c r="C442" t="n">
-        <v>97.99677276611328</v>
+        <v>97.99675750732422</v>
       </c>
       <c r="D442" t="n">
-        <v>97.99677276611328</v>
+        <v>97.99675750732422</v>
       </c>
       <c r="E442" t="n">
-        <v>97.98701943576903</v>
+        <v>97.98700417849862</v>
       </c>
       <c r="F442" t="n">
-        <v>97.99677276611328</v>
+        <v>97.99675750732422</v>
       </c>
       <c r="G442" t="n">
         <v>13837400</v>
@@ -10615,16 +10615,16 @@
         <v>45936</v>
       </c>
       <c r="C443" t="n">
-        <v>97.99677276611328</v>
+        <v>97.99675750732422</v>
       </c>
       <c r="D443" t="n">
-        <v>98.00653354174787</v>
+        <v>98.00651828143899</v>
       </c>
       <c r="E443" t="n">
-        <v>97.99677276611328</v>
+        <v>97.99675750732422</v>
       </c>
       <c r="F443" t="n">
-        <v>98.00653354174787</v>
+        <v>98.00651828143899</v>
       </c>
       <c r="G443" t="n">
         <v>13944300</v>
@@ -10684,16 +10684,16 @@
         <v>45939</v>
       </c>
       <c r="C446" t="n">
-        <v>98.03580474853516</v>
+        <v>98.03578948974609</v>
       </c>
       <c r="D446" t="n">
-        <v>98.04556552380387</v>
+        <v>98.0455502634956</v>
       </c>
       <c r="E446" t="n">
-        <v>98.02604397326645</v>
+        <v>98.0260287159966</v>
       </c>
       <c r="F446" t="n">
-        <v>98.04556552380387</v>
+        <v>98.0455502634956</v>
       </c>
       <c r="G446" t="n">
         <v>15718900</v>
@@ -10707,16 +10707,16 @@
         <v>45940</v>
       </c>
       <c r="C447" t="n">
-        <v>98.08458709716797</v>
+        <v>98.0845947265625</v>
       </c>
       <c r="D447" t="n">
-        <v>98.08458709716797</v>
+        <v>98.0845947265625</v>
       </c>
       <c r="E447" t="n">
-        <v>98.06506554943334</v>
+        <v>98.06507317730942</v>
       </c>
       <c r="F447" t="n">
-        <v>98.07482632330066</v>
+        <v>98.07483395193596</v>
       </c>
       <c r="G447" t="n">
         <v>18966600</v>
@@ -10730,16 +10730,16 @@
         <v>45943</v>
       </c>
       <c r="C448" t="n">
-        <v>98.0748291015625</v>
+        <v>98.07483673095703</v>
       </c>
       <c r="D448" t="n">
-        <v>98.08458987570631</v>
+        <v>98.08459750586016</v>
       </c>
       <c r="E448" t="n">
-        <v>98.0748291015625</v>
+        <v>98.07483673095703</v>
       </c>
       <c r="F448" t="n">
-        <v>98.0748291015625</v>
+        <v>98.07483673095703</v>
       </c>
       <c r="G448" t="n">
         <v>14453500</v>
@@ -10753,16 +10753,16 @@
         <v>45944</v>
       </c>
       <c r="C449" t="n">
-        <v>98.08458709716797</v>
+        <v>98.0845947265625</v>
       </c>
       <c r="D449" t="n">
-        <v>98.0943404257463</v>
+        <v>98.09434805589947</v>
       </c>
       <c r="E449" t="n">
-        <v>98.08458709716797</v>
+        <v>98.0845947265625</v>
       </c>
       <c r="F449" t="n">
-        <v>98.08458709716797</v>
+        <v>98.0845947265625</v>
       </c>
       <c r="G449" t="n">
         <v>13475000</v>
@@ -10845,16 +10845,16 @@
         <v>45950</v>
       </c>
       <c r="C453" t="n">
-        <v>98.15290832519531</v>
+        <v>98.15291595458984</v>
       </c>
       <c r="D453" t="n">
-        <v>98.15290832519531</v>
+        <v>98.15291595458984</v>
       </c>
       <c r="E453" t="n">
-        <v>98.14314755026379</v>
+        <v>98.14315517889962</v>
       </c>
       <c r="F453" t="n">
-        <v>98.15290832519531</v>
+        <v>98.15291595458984</v>
       </c>
       <c r="G453" t="n">
         <v>16129100</v>
@@ -10914,16 +10914,16 @@
         <v>45953</v>
       </c>
       <c r="C456" t="n">
-        <v>98.19193267822266</v>
+        <v>98.19194793701172</v>
       </c>
       <c r="D456" t="n">
-        <v>98.19193267822266</v>
+        <v>98.19194793701172</v>
       </c>
       <c r="E456" t="n">
-        <v>98.18217190441455</v>
+        <v>98.18218716168681</v>
       </c>
       <c r="F456" t="n">
-        <v>98.19193267822266</v>
+        <v>98.19194793701172</v>
       </c>
       <c r="G456" t="n">
         <v>10658100</v>
@@ -10937,16 +10937,16 @@
         <v>45954</v>
       </c>
       <c r="C457" t="n">
-        <v>98.22122192382812</v>
+        <v>98.22120666503906</v>
       </c>
       <c r="D457" t="n">
-        <v>98.22122192382812</v>
+        <v>98.22120666503906</v>
       </c>
       <c r="E457" t="n">
-        <v>98.21146114859204</v>
+        <v>98.21144589131933</v>
       </c>
       <c r="F457" t="n">
-        <v>98.22122192382812</v>
+        <v>98.22120666503906</v>
       </c>
       <c r="G457" t="n">
         <v>12382000</v>
@@ -10983,16 +10983,16 @@
         <v>45958</v>
       </c>
       <c r="C459" t="n">
-        <v>98.24073028564453</v>
+        <v>98.24072265625</v>
       </c>
       <c r="D459" t="n">
-        <v>98.25049106030998</v>
+        <v>98.25048343015742</v>
       </c>
       <c r="E459" t="n">
-        <v>98.24073028564453</v>
+        <v>98.24072265625</v>
       </c>
       <c r="F459" t="n">
-        <v>98.24073028564453</v>
+        <v>98.24072265625</v>
       </c>
       <c r="G459" t="n">
         <v>11134700</v>
@@ -11006,16 +11006,16 @@
         <v>45959</v>
       </c>
       <c r="C460" t="n">
-        <v>98.25047302246094</v>
+        <v>98.25048828125</v>
       </c>
       <c r="D460" t="n">
-        <v>98.2602337953344</v>
+        <v>98.26024905563935</v>
       </c>
       <c r="E460" t="n">
-        <v>98.25047302246094</v>
+        <v>98.25048828125</v>
       </c>
       <c r="F460" t="n">
-        <v>98.2602337953344</v>
+        <v>98.26024905563935</v>
       </c>
       <c r="G460" t="n">
         <v>14177700</v>
@@ -11075,16 +11075,16 @@
         <v>45964</v>
       </c>
       <c r="C463" t="n">
-        <v>98.31695556640625</v>
+        <v>98.31694793701172</v>
       </c>
       <c r="D463" t="n">
-        <v>98.31695556640625</v>
+        <v>98.31694793701172</v>
       </c>
       <c r="E463" t="n">
-        <v>98.30716094919116</v>
+        <v>98.30715332055669</v>
       </c>
       <c r="F463" t="n">
-        <v>98.31205452224675</v>
+        <v>98.31204689323255</v>
       </c>
       <c r="G463" t="n">
         <v>27049200</v>
@@ -11098,16 +11098,16 @@
         <v>45965</v>
       </c>
       <c r="C464" t="n">
-        <v>98.31695556640625</v>
+        <v>98.31694793701172</v>
       </c>
       <c r="D464" t="n">
-        <v>98.31695556640625</v>
+        <v>98.31694793701172</v>
       </c>
       <c r="E464" t="n">
-        <v>98.31205452224675</v>
+        <v>98.31204689323255</v>
       </c>
       <c r="F464" t="n">
-        <v>98.31695556640625</v>
+        <v>98.31694793701172</v>
       </c>
       <c r="G464" t="n">
         <v>15707500</v>
@@ -11121,16 +11121,16 @@
         <v>45966</v>
       </c>
       <c r="C465" t="n">
-        <v>98.33653259277344</v>
+        <v>98.33652496337891</v>
       </c>
       <c r="D465" t="n">
-        <v>98.33653259277344</v>
+        <v>98.33652496337891</v>
       </c>
       <c r="E465" t="n">
-        <v>98.3267454471337</v>
+        <v>98.32673781849851</v>
       </c>
       <c r="F465" t="n">
-        <v>98.3267454471337</v>
+        <v>98.32673781849851</v>
       </c>
       <c r="G465" t="n">
         <v>11335000</v>
@@ -11167,16 +11167,16 @@
         <v>45968</v>
       </c>
       <c r="C467" t="n">
-        <v>98.37570190429688</v>
+        <v>98.37569427490234</v>
       </c>
       <c r="D467" t="n">
-        <v>98.37570190429688</v>
+        <v>98.37569427490234</v>
       </c>
       <c r="E467" t="n">
-        <v>98.3659072877213</v>
+        <v>98.36589965908638</v>
       </c>
       <c r="F467" t="n">
-        <v>98.37570190429688</v>
+        <v>98.37569427490234</v>
       </c>
       <c r="G467" t="n">
         <v>18799000</v>
@@ -11190,16 +11190,16 @@
         <v>45971</v>
       </c>
       <c r="C468" t="n">
-        <v>98.38549041748047</v>
+        <v>98.38548278808594</v>
       </c>
       <c r="D468" t="n">
-        <v>98.39528503344843</v>
+        <v>98.39527740329436</v>
       </c>
       <c r="E468" t="n">
-        <v>98.38549041748047</v>
+        <v>98.38548278808594</v>
       </c>
       <c r="F468" t="n">
-        <v>98.39528503344843</v>
+        <v>98.39527740329436</v>
       </c>
       <c r="G468" t="n">
         <v>14121900</v>
@@ -11213,16 +11213,16 @@
         <v>45972</v>
       </c>
       <c r="C469" t="n">
-        <v>98.39529418945312</v>
+        <v>98.39528656005859</v>
       </c>
       <c r="D469" t="n">
-        <v>98.39529418945312</v>
+        <v>98.39528656005859</v>
       </c>
       <c r="E469" t="n">
-        <v>98.38549957257375</v>
+        <v>98.38549194393867</v>
       </c>
       <c r="F469" t="n">
-        <v>98.39529418945312</v>
+        <v>98.39528656005859</v>
       </c>
       <c r="G469" t="n">
         <v>8697800</v>
@@ -11282,16 +11282,16 @@
         <v>45975</v>
       </c>
       <c r="C472" t="n">
-        <v>98.44423675537109</v>
+        <v>98.44424438476562</v>
       </c>
       <c r="D472" t="n">
-        <v>98.44423675537109</v>
+        <v>98.44424438476562</v>
       </c>
       <c r="E472" t="n">
-        <v>98.43444214004147</v>
+        <v>98.43444976867691</v>
       </c>
       <c r="F472" t="n">
-        <v>98.44423675537109</v>
+        <v>98.44424438476562</v>
       </c>
       <c r="G472" t="n">
         <v>13522500</v>
@@ -11305,16 +11305,16 @@
         <v>45978</v>
       </c>
       <c r="C473" t="n">
-        <v>98.45404052734375</v>
+        <v>98.45403289794922</v>
       </c>
       <c r="D473" t="n">
-        <v>98.45404052734375</v>
+        <v>98.45403289794922</v>
       </c>
       <c r="E473" t="n">
-        <v>98.44424591110318</v>
+        <v>98.44423828246764</v>
       </c>
       <c r="F473" t="n">
-        <v>98.44914695477505</v>
+        <v>98.44913932575972</v>
       </c>
       <c r="G473" t="n">
         <v>15032800</v>
@@ -11328,16 +11328,16 @@
         <v>45979</v>
       </c>
       <c r="C474" t="n">
-        <v>98.45404052734375</v>
+        <v>98.45403289794922</v>
       </c>
       <c r="D474" t="n">
-        <v>98.46383514358433</v>
+        <v>98.46382751343079</v>
       </c>
       <c r="E474" t="n">
-        <v>98.45404052734375</v>
+        <v>98.45403289794922</v>
       </c>
       <c r="F474" t="n">
-        <v>98.45404052734375</v>
+        <v>98.45403289794922</v>
       </c>
       <c r="G474" t="n">
         <v>13130300</v>
@@ -11351,16 +11351,16 @@
         <v>45980</v>
       </c>
       <c r="C475" t="n">
-        <v>98.47361755371094</v>
+        <v>98.47360992431641</v>
       </c>
       <c r="D475" t="n">
-        <v>98.47361755371094</v>
+        <v>98.47360992431641</v>
       </c>
       <c r="E475" t="n">
-        <v>98.46383040904414</v>
+        <v>98.46382278040787</v>
       </c>
       <c r="F475" t="n">
-        <v>98.46383040904414</v>
+        <v>98.46382278040787</v>
       </c>
       <c r="G475" t="n">
         <v>23022400</v>
@@ -11397,16 +11397,16 @@
         <v>45982</v>
       </c>
       <c r="C477" t="n">
-        <v>98.51279449462891</v>
+        <v>98.51277923583984</v>
       </c>
       <c r="D477" t="n">
-        <v>98.51279449462891</v>
+        <v>98.51277923583984</v>
       </c>
       <c r="E477" t="n">
-        <v>98.50299987826783</v>
+        <v>98.50298462099586</v>
       </c>
       <c r="F477" t="n">
-        <v>98.51279449462891</v>
+        <v>98.51277923583984</v>
       </c>
       <c r="G477" t="n">
         <v>16446900</v>
@@ -11489,16 +11489,16 @@
         <v>45989</v>
       </c>
       <c r="C481" t="n">
-        <v>98.58133697509766</v>
+        <v>98.58132934570312</v>
       </c>
       <c r="D481" t="n">
-        <v>98.59113159097269</v>
+        <v>98.59112396082016</v>
       </c>
       <c r="E481" t="n">
-        <v>98.57154983032548</v>
+        <v>98.5715422016884</v>
       </c>
       <c r="F481" t="n">
-        <v>98.58133697509766</v>
+        <v>98.58132934570312</v>
       </c>
       <c r="G481" t="n">
         <v>24417500</v>
@@ -11512,16 +11512,16 @@
         <v>45992</v>
       </c>
       <c r="C482" t="n">
-        <v>98.60392761230469</v>
+        <v>98.60391998291016</v>
       </c>
       <c r="D482" t="n">
-        <v>98.60392761230469</v>
+        <v>98.60391998291016</v>
       </c>
       <c r="E482" t="n">
-        <v>98.59410994289308</v>
+        <v>98.59410231425819</v>
       </c>
       <c r="F482" t="n">
-        <v>98.60392761230469</v>
+        <v>98.60391998291016</v>
       </c>
       <c r="G482" t="n">
         <v>29025600</v>
@@ -11535,16 +11535,16 @@
         <v>45993</v>
       </c>
       <c r="C483" t="n">
-        <v>98.62359619140625</v>
+        <v>98.62357330322266</v>
       </c>
       <c r="D483" t="n">
-        <v>98.62359619140625</v>
+        <v>98.62357330322266</v>
       </c>
       <c r="E483" t="n">
-        <v>98.61377102577225</v>
+        <v>98.61374813986885</v>
       </c>
       <c r="F483" t="n">
-        <v>98.61377102577225</v>
+        <v>98.61374813986885</v>
       </c>
       <c r="G483" t="n">
         <v>14362600</v>
@@ -11558,16 +11558,16 @@
         <v>45994</v>
       </c>
       <c r="C484" t="n">
-        <v>98.63340759277344</v>
+        <v>98.63339996337891</v>
       </c>
       <c r="D484" t="n">
-        <v>98.63831642770265</v>
+        <v>98.63830879792842</v>
       </c>
       <c r="E484" t="n">
-        <v>98.63340759277344</v>
+        <v>98.63339996337891</v>
       </c>
       <c r="F484" t="n">
-        <v>98.63340759277344</v>
+        <v>98.63339996337891</v>
       </c>
       <c r="G484" t="n">
         <v>15531600</v>
@@ -11581,16 +11581,16 @@
         <v>45995</v>
       </c>
       <c r="C485" t="n">
-        <v>98.65304565429688</v>
+        <v>98.65305328369141</v>
       </c>
       <c r="D485" t="n">
-        <v>98.65304565429688</v>
+        <v>98.65305328369141</v>
       </c>
       <c r="E485" t="n">
-        <v>98.64322049050931</v>
+        <v>98.64322811914398</v>
       </c>
       <c r="F485" t="n">
-        <v>98.64322049050931</v>
+        <v>98.64322811914398</v>
       </c>
       <c r="G485" t="n">
         <v>13689600</v>
@@ -11604,16 +11604,16 @@
         <v>45996</v>
       </c>
       <c r="C486" t="n">
-        <v>98.68252563476562</v>
+        <v>98.68250274658203</v>
       </c>
       <c r="D486" t="n">
-        <v>98.68252563476562</v>
+        <v>98.68250274658203</v>
       </c>
       <c r="E486" t="n">
-        <v>98.67270046978493</v>
+        <v>98.67267758388016</v>
       </c>
       <c r="F486" t="n">
-        <v>98.67270046978493</v>
+        <v>98.67267758388016</v>
       </c>
       <c r="G486" t="n">
         <v>17918100</v>
@@ -11627,16 +11627,16 @@
         <v>45999</v>
       </c>
       <c r="C487" t="n">
-        <v>98.68252563476562</v>
+        <v>98.68250274658203</v>
       </c>
       <c r="D487" t="n">
-        <v>98.68252563476562</v>
+        <v>98.68250274658203</v>
       </c>
       <c r="E487" t="n">
-        <v>98.67270046978493</v>
+        <v>98.67267758388016</v>
       </c>
       <c r="F487" t="n">
-        <v>98.68252563476562</v>
+        <v>98.68250274658203</v>
       </c>
       <c r="G487" t="n">
         <v>16657900</v>
@@ -11719,16 +11719,16 @@
         <v>46003</v>
       </c>
       <c r="C491" t="n">
-        <v>98.75126647949219</v>
+        <v>98.75128173828125</v>
       </c>
       <c r="D491" t="n">
-        <v>98.75126647949219</v>
+        <v>98.75128173828125</v>
       </c>
       <c r="E491" t="n">
-        <v>98.74144131653334</v>
+        <v>98.74145657380426</v>
       </c>
       <c r="F491" t="n">
-        <v>98.74144131653334</v>
+        <v>98.74145657380426</v>
       </c>
       <c r="G491" t="n">
         <v>13320200</v>
@@ -11742,16 +11742,16 @@
         <v>46006</v>
       </c>
       <c r="C492" t="n">
-        <v>98.75126647949219</v>
+        <v>98.75128173828125</v>
       </c>
       <c r="D492" t="n">
-        <v>98.76109164245103</v>
+        <v>98.76110690275826</v>
       </c>
       <c r="E492" t="n">
-        <v>98.75126647949219</v>
+        <v>98.75128173828125</v>
       </c>
       <c r="F492" t="n">
-        <v>98.75126647949219</v>
+        <v>98.75128173828125</v>
       </c>
       <c r="G492" t="n">
         <v>14767900</v>
@@ -11788,16 +11788,16 @@
         <v>46008</v>
       </c>
       <c r="C494" t="n">
-        <v>98.78074645996094</v>
+        <v>98.78073883056641</v>
       </c>
       <c r="D494" t="n">
-        <v>98.78074645996094</v>
+        <v>98.78073883056641</v>
       </c>
       <c r="E494" t="n">
-        <v>98.7709287902143</v>
+        <v>98.77092116157804</v>
       </c>
       <c r="F494" t="n">
-        <v>98.7709287902143</v>
+        <v>98.77092116157804</v>
       </c>
       <c r="G494" t="n">
         <v>13788200</v>
@@ -11811,16 +11811,16 @@
         <v>46009</v>
       </c>
       <c r="C495" t="n">
-        <v>98.78074645996094</v>
+        <v>98.78073883056641</v>
       </c>
       <c r="D495" t="n">
-        <v>98.79057162411196</v>
+        <v>98.79056399395857</v>
       </c>
       <c r="E495" t="n">
-        <v>98.78074645996094</v>
+        <v>98.78073883056641</v>
       </c>
       <c r="F495" t="n">
-        <v>98.79057162411196</v>
+        <v>98.79056399395857</v>
       </c>
       <c r="G495" t="n">
         <v>20890600</v>
@@ -11880,16 +11880,16 @@
         <v>46014</v>
       </c>
       <c r="C498" t="n">
-        <v>98.83297729492188</v>
+        <v>98.83298492431641</v>
       </c>
       <c r="D498" t="n">
-        <v>98.84283411907127</v>
+        <v>98.84284174922669</v>
       </c>
       <c r="E498" t="n">
-        <v>98.83297729492188</v>
+        <v>98.83298492431641</v>
       </c>
       <c r="F498" t="n">
-        <v>98.84283411907127</v>
+        <v>98.84284174922669</v>
       </c>
       <c r="G498" t="n">
         <v>12256200</v>
@@ -11903,16 +11903,16 @@
         <v>46015</v>
       </c>
       <c r="C499" t="n">
-        <v>98.85269165039062</v>
+        <v>98.85268402099609</v>
       </c>
       <c r="D499" t="n">
-        <v>98.86254847536023</v>
+        <v>98.86254084520495</v>
       </c>
       <c r="E499" t="n">
-        <v>98.85269165039062</v>
+        <v>98.85268402099609</v>
       </c>
       <c r="F499" t="n">
-        <v>98.86254847536023</v>
+        <v>98.86254084520495</v>
       </c>
       <c r="G499" t="n">
         <v>7791300</v>
@@ -11926,16 +11926,16 @@
         <v>46017</v>
       </c>
       <c r="C500" t="n">
-        <v>98.88224792480469</v>
+        <v>98.88225555419922</v>
       </c>
       <c r="D500" t="n">
-        <v>98.88718009623345</v>
+        <v>98.88718772600853</v>
       </c>
       <c r="E500" t="n">
-        <v>98.88224792480469</v>
+        <v>98.88225555419922</v>
       </c>
       <c r="F500" t="n">
-        <v>98.88224792480469</v>
+        <v>98.88225555419922</v>
       </c>
       <c r="G500" t="n">
         <v>12664300</v>
@@ -11972,16 +11972,16 @@
         <v>46021</v>
       </c>
       <c r="C502" t="n">
-        <v>98.91181945800781</v>
+        <v>98.91181182861328</v>
       </c>
       <c r="D502" t="n">
-        <v>98.91181945800781</v>
+        <v>98.91181182861328</v>
       </c>
       <c r="E502" t="n">
-        <v>98.90196263359863</v>
+        <v>98.90195500496438</v>
       </c>
       <c r="F502" t="n">
-        <v>98.90688728652617</v>
+        <v>98.90687965751208</v>
       </c>
       <c r="G502" t="n">
         <v>12608900</v>
@@ -11995,16 +11995,16 @@
         <v>46022</v>
       </c>
       <c r="C503" t="n">
-        <v>98.92166137695312</v>
+        <v>98.92166900634766</v>
       </c>
       <c r="D503" t="n">
-        <v>98.93151820062626</v>
+        <v>98.931525830781</v>
       </c>
       <c r="E503" t="n">
-        <v>98.92166137695312</v>
+        <v>98.92166900634766</v>
       </c>
       <c r="F503" t="n">
-        <v>98.93151820062626</v>
+        <v>98.931525830781</v>
       </c>
       <c r="G503" t="n">
         <v>13910900</v>
@@ -12018,16 +12018,16 @@
         <v>46024</v>
       </c>
       <c r="C504" t="n">
-        <v>98.95124816894531</v>
+        <v>98.95124053955078</v>
       </c>
       <c r="D504" t="n">
-        <v>98.96109747568946</v>
+        <v>98.96108984553553</v>
       </c>
       <c r="E504" t="n">
-        <v>98.95124816894531</v>
+        <v>98.95124053955078</v>
       </c>
       <c r="F504" t="n">
-        <v>98.95124816894531</v>
+        <v>98.95124053955078</v>
       </c>
       <c r="G504" t="n">
         <v>19188800</v>
@@ -12087,16 +12087,16 @@
         <v>46029</v>
       </c>
       <c r="C507" t="n">
-        <v>98.98079681396484</v>
+        <v>98.98080444335938</v>
       </c>
       <c r="D507" t="n">
-        <v>98.98079681396484</v>
+        <v>98.98080444335938</v>
       </c>
       <c r="E507" t="n">
-        <v>98.98079681396484</v>
+        <v>98.98080444335938</v>
       </c>
       <c r="F507" t="n">
-        <v>98.98079681396484</v>
+        <v>98.98080444335938</v>
       </c>
       <c r="G507" t="n">
         <v>14062300</v>
@@ -12110,16 +12110,16 @@
         <v>46030</v>
       </c>
       <c r="C508" t="n">
-        <v>98.99065399169922</v>
+        <v>98.99064636230469</v>
       </c>
       <c r="D508" t="n">
-        <v>98.99065399169922</v>
+        <v>98.99064636230469</v>
       </c>
       <c r="E508" t="n">
-        <v>98.99065399169922</v>
+        <v>98.99064636230469</v>
       </c>
       <c r="F508" t="n">
-        <v>98.99065399169922</v>
+        <v>98.99064636230469</v>
       </c>
       <c r="G508" t="n">
         <v>11408800</v>
@@ -12133,16 +12133,16 @@
         <v>46031</v>
       </c>
       <c r="C509" t="n">
-        <v>99.01036834716797</v>
+        <v>99.01036071777344</v>
       </c>
       <c r="D509" t="n">
-        <v>99.0202251718958</v>
+        <v>99.02021754174173</v>
       </c>
       <c r="E509" t="n">
-        <v>99.01036834716797</v>
+        <v>99.01036071777344</v>
       </c>
       <c r="F509" t="n">
-        <v>99.0202251718958</v>
+        <v>99.02021754174173</v>
       </c>
       <c r="G509" t="n">
         <v>15053500</v>
@@ -12156,16 +12156,16 @@
         <v>46034</v>
       </c>
       <c r="C510" t="n">
-        <v>99.03008270263672</v>
+        <v>99.03007507324219</v>
       </c>
       <c r="D510" t="n">
-        <v>99.03008270263672</v>
+        <v>99.03007507324219</v>
       </c>
       <c r="E510" t="n">
-        <v>99.02023339564522</v>
+        <v>99.02022576700949</v>
       </c>
       <c r="F510" t="n">
-        <v>99.02023339564522</v>
+        <v>99.02022576700949</v>
       </c>
       <c r="G510" t="n">
         <v>14819400</v>
@@ -12179,16 +12179,16 @@
         <v>46035</v>
       </c>
       <c r="C511" t="n">
-        <v>99.03992462158203</v>
+        <v>99.03993225097656</v>
       </c>
       <c r="D511" t="n">
-        <v>99.03992462158203</v>
+        <v>99.03993225097656</v>
       </c>
       <c r="E511" t="n">
-        <v>99.03006779751914</v>
+        <v>99.03007542615437</v>
       </c>
       <c r="F511" t="n">
-        <v>99.03006779751914</v>
+        <v>99.03007542615437</v>
       </c>
       <c r="G511" t="n">
         <v>14163000</v>
@@ -12225,16 +12225,16 @@
         <v>46037</v>
       </c>
       <c r="C513" t="n">
-        <v>99.05963134765625</v>
+        <v>99.05964660644531</v>
       </c>
       <c r="D513" t="n">
-        <v>99.05963134765625</v>
+        <v>99.05964660644531</v>
       </c>
       <c r="E513" t="n">
-        <v>99.04978204208787</v>
+        <v>99.04979729935978</v>
       </c>
       <c r="F513" t="n">
-        <v>99.04978204208787</v>
+        <v>99.04979729935978</v>
       </c>
       <c r="G513" t="n">
         <v>11469500</v>
@@ -12248,16 +12248,16 @@
         <v>46038</v>
       </c>
       <c r="C514" t="n">
-        <v>99.09905242919922</v>
+        <v>99.09904479980469</v>
       </c>
       <c r="D514" t="n">
-        <v>99.09905242919922</v>
+        <v>99.09904479980469</v>
       </c>
       <c r="E514" t="n">
-        <v>99.08427095209834</v>
+        <v>99.0842633238418</v>
       </c>
       <c r="F514" t="n">
-        <v>99.08920312350128</v>
+        <v>99.08919549486502</v>
       </c>
       <c r="G514" t="n">
         <v>14766800</v>
@@ -12271,16 +12271,16 @@
         <v>46042</v>
       </c>
       <c r="C515" t="n">
-        <v>99.09905242919922</v>
+        <v>99.09904479980469</v>
       </c>
       <c r="D515" t="n">
-        <v>99.10890925345112</v>
+        <v>99.10890162329774</v>
       </c>
       <c r="E515" t="n">
-        <v>99.09905242919922</v>
+        <v>99.09904479980469</v>
       </c>
       <c r="F515" t="n">
-        <v>99.09905242919922</v>
+        <v>99.09904479980469</v>
       </c>
       <c r="G515" t="n">
         <v>19394600</v>
@@ -12294,16 +12294,16 @@
         <v>46043</v>
       </c>
       <c r="C516" t="n">
-        <v>99.09905242919922</v>
+        <v>99.09904479980469</v>
       </c>
       <c r="D516" t="n">
-        <v>99.11876607770303</v>
+        <v>99.11875844679079</v>
       </c>
       <c r="E516" t="n">
-        <v>99.09905242919922</v>
+        <v>99.09904479980469</v>
       </c>
       <c r="F516" t="n">
-        <v>99.10398460060216</v>
+        <v>99.1039769708279</v>
       </c>
       <c r="G516" t="n">
         <v>17502100</v>
@@ -12317,16 +12317,16 @@
         <v>46044</v>
       </c>
       <c r="C517" t="n">
-        <v>99.11875915527344</v>
+        <v>99.1187744140625</v>
       </c>
       <c r="D517" t="n">
-        <v>99.11875915527344</v>
+        <v>99.1187744140625</v>
       </c>
       <c r="E517" t="n">
-        <v>99.10890233170993</v>
+        <v>99.1089175889816</v>
       </c>
       <c r="F517" t="n">
-        <v>99.11875915527344</v>
+        <v>99.1187744140625</v>
       </c>
       <c r="G517" t="n">
         <v>13618500</v>
@@ -12340,16 +12340,16 @@
         <v>46045</v>
       </c>
       <c r="C518" t="n">
-        <v>99.14833068847656</v>
+        <v>99.14833831787109</v>
       </c>
       <c r="D518" t="n">
-        <v>99.14833068847656</v>
+        <v>99.14833831787109</v>
       </c>
       <c r="E518" t="n">
-        <v>99.13847386405996</v>
+        <v>99.13848149269603</v>
       </c>
       <c r="F518" t="n">
-        <v>99.14833068847656</v>
+        <v>99.14833831787109</v>
       </c>
       <c r="G518" t="n">
         <v>12143000</v>
@@ -12363,16 +12363,16 @@
         <v>46048</v>
       </c>
       <c r="C519" t="n">
-        <v>99.15818023681641</v>
+        <v>99.15818786621094</v>
       </c>
       <c r="D519" t="n">
-        <v>99.15818023681641</v>
+        <v>99.15818786621094</v>
       </c>
       <c r="E519" t="n">
-        <v>99.14832341312308</v>
+        <v>99.14833104175922</v>
       </c>
       <c r="F519" t="n">
-        <v>99.15818023681641</v>
+        <v>99.15818786621094</v>
       </c>
       <c r="G519" t="n">
         <v>16872000</v>
@@ -12386,16 +12386,16 @@
         <v>46049</v>
       </c>
       <c r="C520" t="n">
-        <v>99.15818023681641</v>
+        <v>99.15818786621094</v>
       </c>
       <c r="D520" t="n">
-        <v>99.1729617130796</v>
+        <v>99.17296934361146</v>
       </c>
       <c r="E520" t="n">
-        <v>99.15818023681641</v>
+        <v>99.15818786621094</v>
       </c>
       <c r="F520" t="n">
-        <v>99.16802954195617</v>
+        <v>99.16803717210854</v>
       </c>
       <c r="G520" t="n">
         <v>13393600</v>
@@ -12409,16 +12409,16 @@
         <v>46050</v>
       </c>
       <c r="C521" t="n">
-        <v>99.17788696289062</v>
+        <v>99.17789459228516</v>
       </c>
       <c r="D521" t="n">
-        <v>99.17788696289062</v>
+        <v>99.17789459228516</v>
       </c>
       <c r="E521" t="n">
-        <v>99.16803013913795</v>
+        <v>99.16803776777424</v>
       </c>
       <c r="F521" t="n">
-        <v>99.16803013913795</v>
+        <v>99.16803776777424</v>
       </c>
       <c r="G521" t="n">
         <v>11987500</v>
@@ -12478,16 +12478,16 @@
         <v>46055</v>
       </c>
       <c r="C524" t="n">
-        <v>99.21635437011719</v>
+        <v>99.21636199951172</v>
       </c>
       <c r="D524" t="n">
-        <v>99.22623400053318</v>
+        <v>99.22624163068743</v>
       </c>
       <c r="E524" t="n">
-        <v>99.21635437011719</v>
+        <v>99.21636199951172</v>
       </c>
       <c r="F524" t="n">
-        <v>99.22623400053318</v>
+        <v>99.22624163068743</v>
       </c>
       <c r="G524" t="n">
         <v>31225300</v>
@@ -12593,16 +12593,16 @@
         <v>46062</v>
       </c>
       <c r="C529" t="n">
-        <v>99.29542541503906</v>
+        <v>99.29543304443359</v>
       </c>
       <c r="D529" t="n">
-        <v>99.29542541503906</v>
+        <v>99.29543304443359</v>
       </c>
       <c r="E529" t="n">
-        <v>99.2855457849919</v>
+        <v>99.28555341362733</v>
       </c>
       <c r="F529" t="n">
-        <v>99.2855457849919</v>
+        <v>99.28555341362733</v>
       </c>
       <c r="G529" t="n">
         <v>13991600</v>
@@ -12616,16 +12616,16 @@
         <v>46063</v>
       </c>
       <c r="C530" t="n">
-        <v>99.30532836914062</v>
+        <v>99.30532073974609</v>
       </c>
       <c r="D530" t="n">
-        <v>99.30532836914062</v>
+        <v>99.30532073974609</v>
       </c>
       <c r="E530" t="n">
-        <v>99.29544119581978</v>
+        <v>99.29543356718486</v>
       </c>
       <c r="F530" t="n">
-        <v>99.30532836914062</v>
+        <v>99.30532073974609</v>
       </c>
       <c r="G530" t="n">
         <v>14002700</v>
@@ -12639,16 +12639,16 @@
         <v>46064</v>
       </c>
       <c r="C531" t="n">
-        <v>99.30532836914062</v>
+        <v>99.30532073974609</v>
       </c>
       <c r="D531" t="n">
-        <v>99.31521554246146</v>
+        <v>99.31520791230733</v>
       </c>
       <c r="E531" t="n">
-        <v>99.30532836914062</v>
+        <v>99.30532073974609</v>
       </c>
       <c r="F531" t="n">
-        <v>99.31521554246146</v>
+        <v>99.31520791230733</v>
       </c>
       <c r="G531" t="n">
         <v>12584400</v>
@@ -12662,16 +12662,16 @@
         <v>46065</v>
       </c>
       <c r="C532" t="n">
-        <v>99.32510375976562</v>
+        <v>99.32509613037109</v>
       </c>
       <c r="D532" t="n">
-        <v>99.32510375976562</v>
+        <v>99.32509613037109</v>
       </c>
       <c r="E532" t="n">
-        <v>99.31521658634087</v>
+        <v>99.31520895770579</v>
       </c>
       <c r="F532" t="n">
-        <v>99.31521658634087</v>
+        <v>99.31520895770579</v>
       </c>
       <c r="G532" t="n">
         <v>16593900</v>
@@ -12685,16 +12685,16 @@
         <v>46066</v>
       </c>
       <c r="C533" t="n">
-        <v>99.36463165283203</v>
+        <v>99.36463928222656</v>
       </c>
       <c r="D533" t="n">
-        <v>99.36463165283203</v>
+        <v>99.36463928222656</v>
       </c>
       <c r="E533" t="n">
-        <v>99.35475202167932</v>
+        <v>99.35475965031527</v>
       </c>
       <c r="F533" t="n">
-        <v>99.36463165283203</v>
+        <v>99.36463928222656</v>
       </c>
       <c r="G533" t="n">
         <v>14917200</v>
@@ -12708,16 +12708,16 @@
         <v>46070</v>
       </c>
       <c r="C534" t="n">
-        <v>99.36463165283203</v>
+        <v>99.36463928222656</v>
       </c>
       <c r="D534" t="n">
-        <v>99.3745188256879</v>
+        <v>99.37452645584159</v>
       </c>
       <c r="E534" t="n">
-        <v>99.36463165283203</v>
+        <v>99.36463928222656</v>
       </c>
       <c r="F534" t="n">
-        <v>99.36957901011155</v>
+        <v>99.36958663988595</v>
       </c>
       <c r="G534" t="n">
         <v>14976200</v>
@@ -12731,16 +12731,16 @@
         <v>46071</v>
       </c>
       <c r="C535" t="n">
-        <v>99.38440704345703</v>
+        <v>99.3843994140625</v>
       </c>
       <c r="D535" t="n">
-        <v>99.38440704345703</v>
+        <v>99.3843994140625</v>
       </c>
       <c r="E535" t="n">
-        <v>99.37451987049721</v>
+        <v>99.37451224186168</v>
       </c>
       <c r="F535" t="n">
-        <v>99.38440704345703</v>
+        <v>99.3843994140625</v>
       </c>
       <c r="G535" t="n">
         <v>10207300</v>
@@ -12800,16 +12800,16 @@
         <v>46076</v>
       </c>
       <c r="C538" t="n">
-        <v>99.43382263183594</v>
+        <v>99.43383026123047</v>
       </c>
       <c r="D538" t="n">
-        <v>99.43382263183594</v>
+        <v>99.43383026123047</v>
       </c>
       <c r="E538" t="n">
-        <v>99.42394300109534</v>
+        <v>99.42395062973182</v>
       </c>
       <c r="F538" t="n">
-        <v>99.42888281646563</v>
+        <v>99.42889044548114</v>
       </c>
       <c r="G538" t="n">
         <v>13465400</v>
@@ -12823,16 +12823,16 @@
         <v>46077</v>
       </c>
       <c r="C539" t="n">
-        <v>99.43382263183594</v>
+        <v>99.43383026123047</v>
       </c>
       <c r="D539" t="n">
-        <v>99.44370980427939</v>
+        <v>99.44371743443256</v>
       </c>
       <c r="E539" t="n">
-        <v>99.43382263183594</v>
+        <v>99.43383026123047</v>
       </c>
       <c r="F539" t="n">
-        <v>99.4387699889091</v>
+        <v>99.43877761868323</v>
       </c>
       <c r="G539" t="n">
         <v>12168900</v>
@@ -12892,16 +12892,16 @@
         <v>46080</v>
       </c>
       <c r="C542" t="n">
-        <v>99.48324584960938</v>
+        <v>99.48325347900391</v>
       </c>
       <c r="D542" t="n">
-        <v>99.49313302154569</v>
+        <v>99.49314065169848</v>
       </c>
       <c r="E542" t="n">
-        <v>99.48324584960938</v>
+        <v>99.48325347900391</v>
       </c>
       <c r="F542" t="n">
-        <v>99.4881856647263</v>
+        <v>99.48819329449967</v>
       </c>
       <c r="G542" t="n">
         <v>26602400</v>
@@ -12984,16 +12984,16 @@
         <v>46086</v>
       </c>
       <c r="C546" t="n">
-        <v>99.52489471435547</v>
+        <v>99.52488708496094</v>
       </c>
       <c r="D546" t="n">
-        <v>99.53480112013467</v>
+        <v>99.53479348998074</v>
       </c>
       <c r="E546" t="n">
-        <v>99.52489471435547</v>
+        <v>99.52488708496094</v>
       </c>
       <c r="F546" t="n">
-        <v>99.53480112013467</v>
+        <v>99.53479348998074</v>
       </c>
       <c r="G546" t="n">
         <v>16218200</v>
@@ -13007,16 +13007,16 @@
         <v>46087</v>
       </c>
       <c r="C547" t="n">
-        <v>99.56452178955078</v>
+        <v>99.56452941894531</v>
       </c>
       <c r="D547" t="n">
-        <v>99.56452178955078</v>
+        <v>99.56452941894531</v>
       </c>
       <c r="E547" t="n">
-        <v>99.55461538513191</v>
+        <v>99.55462301376734</v>
       </c>
       <c r="F547" t="n">
-        <v>99.55461538513191</v>
+        <v>99.55462301376734</v>
       </c>
       <c r="G547" t="n">
         <v>18921300</v>
@@ -13030,16 +13030,16 @@
         <v>46090</v>
       </c>
       <c r="C548" t="n">
-        <v>99.57444763183594</v>
+        <v>99.57444000244141</v>
       </c>
       <c r="D548" t="n">
-        <v>99.57444763183594</v>
+        <v>99.57444000244141</v>
       </c>
       <c r="E548" t="n">
-        <v>99.56453366409391</v>
+        <v>99.564526035459</v>
       </c>
       <c r="F548" t="n">
-        <v>99.56949442903577</v>
+        <v>99.56948680002075</v>
       </c>
       <c r="G548" t="n">
         <v>19053900</v>
@@ -13053,16 +13053,16 @@
         <v>46091</v>
       </c>
       <c r="C549" t="n">
-        <v>99.57444763183594</v>
+        <v>99.57444000244141</v>
       </c>
       <c r="D549" t="n">
-        <v>99.58436159957796</v>
+        <v>99.58435396942383</v>
       </c>
       <c r="E549" t="n">
-        <v>99.57444763183594</v>
+        <v>99.57444000244141</v>
       </c>
       <c r="F549" t="n">
-        <v>99.58138967789786</v>
+        <v>99.58138204797143</v>
       </c>
       <c r="G549" t="n">
         <v>13664200</v>
@@ -13076,16 +13076,16 @@
         <v>46092</v>
       </c>
       <c r="C550" t="n">
-        <v>99.59427642822266</v>
+        <v>99.59426116943359</v>
       </c>
       <c r="D550" t="n">
-        <v>99.59427642822266</v>
+        <v>99.59426116943359</v>
       </c>
       <c r="E550" t="n">
-        <v>99.58436246039494</v>
+        <v>99.58434720312479</v>
       </c>
       <c r="F550" t="n">
-        <v>99.58436246039494</v>
+        <v>99.58434720312479</v>
       </c>
       <c r="G550" t="n">
         <v>12287800</v>
@@ -13099,16 +13099,16 @@
         <v>46093</v>
       </c>
       <c r="C551" t="n">
-        <v>99.60417938232422</v>
+        <v>99.60418701171875</v>
       </c>
       <c r="D551" t="n">
-        <v>99.60417938232422</v>
+        <v>99.60418701171875</v>
       </c>
       <c r="E551" t="n">
-        <v>99.59427297698153</v>
+        <v>99.59428060561726</v>
       </c>
       <c r="F551" t="n">
-        <v>99.59922617965287</v>
+        <v>99.599233808668</v>
       </c>
       <c r="G551" t="n">
         <v>17521900</v>
@@ -13329,16 +13329,16 @@
         <v>46107</v>
       </c>
       <c r="C561" t="n">
-        <v>99.73303985595703</v>
+        <v>99.7330322265625</v>
       </c>
       <c r="D561" t="n">
-        <v>99.73303985595703</v>
+        <v>99.7330322265625</v>
       </c>
       <c r="E561" t="n">
-        <v>99.72312588831552</v>
+        <v>99.7231182596794</v>
       </c>
       <c r="F561" t="n">
-        <v>99.73303985595703</v>
+        <v>99.7330322265625</v>
       </c>
       <c r="G561" t="n">
         <v>17499400</v>
@@ -13375,16 +13375,16 @@
         <v>46111</v>
       </c>
       <c r="C563" t="n">
-        <v>99.77268981933594</v>
+        <v>99.77268218994141</v>
       </c>
       <c r="D563" t="n">
-        <v>99.77268981933594</v>
+        <v>99.77268218994141</v>
       </c>
       <c r="E563" t="n">
-        <v>99.76277585152998</v>
+        <v>99.76276822289356</v>
       </c>
       <c r="F563" t="n">
-        <v>99.76277585152998</v>
+        <v>99.76276822289356</v>
       </c>
       <c r="G563" t="n">
         <v>19102700</v>
@@ -13398,16 +13398,16 @@
         <v>46112</v>
       </c>
       <c r="C564" t="n">
-        <v>99.77268981933594</v>
+        <v>99.77268218994141</v>
       </c>
       <c r="D564" t="n">
-        <v>99.78259622500016</v>
+        <v>99.78258859484811</v>
       </c>
       <c r="E564" t="n">
-        <v>99.77268981933594</v>
+        <v>99.77268218994141</v>
       </c>
       <c r="F564" t="n">
-        <v>99.77268981933594</v>
+        <v>99.77268218994141</v>
       </c>
       <c r="G564" t="n">
         <v>36976800</v>
@@ -13559,16 +13559,16 @@
         <v>46122</v>
       </c>
       <c r="C571" t="n">
-        <v>99.90489196777344</v>
+        <v>99.90489959716797</v>
       </c>
       <c r="D571" t="n">
-        <v>99.90489196777344</v>
+        <v>99.90489959716797</v>
       </c>
       <c r="E571" t="n">
-        <v>99.89494905892218</v>
+        <v>99.8949566875574</v>
       </c>
       <c r="F571" t="n">
-        <v>99.89494905892218</v>
+        <v>99.8949566875574</v>
       </c>
       <c r="G571" t="n">
         <v>18783100</v>
@@ -13674,16 +13674,16 @@
         <v>46129</v>
       </c>
       <c r="C576" t="n">
-        <v>99.96453857421875</v>
+        <v>99.96453094482422</v>
       </c>
       <c r="D576" t="n">
-        <v>99.97448148349987</v>
+        <v>99.97447385334648</v>
       </c>
       <c r="E576" t="n">
-        <v>99.96453857421875</v>
+        <v>99.96453094482422</v>
       </c>
       <c r="F576" t="n">
-        <v>99.96453857421875</v>
+        <v>99.96453094482422</v>
       </c>
       <c r="G576" t="n">
         <v>20660500</v>

--- a/Data/sgov.xlsx
+++ b/Data/sgov.xlsx
@@ -472,16 +472,16 @@
         <v>45293</v>
       </c>
       <c r="C2" t="n">
-        <v>90.15837097167969</v>
+        <v>90.15840148925781</v>
       </c>
       <c r="D2" t="n">
-        <v>90.1673626587925</v>
+        <v>90.1673931794142</v>
       </c>
       <c r="E2" t="n">
-        <v>90.14937928456688</v>
+        <v>90.14940979910142</v>
       </c>
       <c r="F2" t="n">
-        <v>90.15837097167969</v>
+        <v>90.15840148925781</v>
       </c>
       <c r="G2" t="n">
         <v>5286200</v>
@@ -495,16 +495,16 @@
         <v>45294</v>
       </c>
       <c r="C3" t="n">
-        <v>90.16738128662109</v>
+        <v>90.16739654541016</v>
       </c>
       <c r="D3" t="n">
-        <v>90.18535780591283</v>
+        <v>90.18537306774401</v>
       </c>
       <c r="E3" t="n">
-        <v>90.16738128662109</v>
+        <v>90.16739654541016</v>
       </c>
       <c r="F3" t="n">
-        <v>90.16738128662109</v>
+        <v>90.16739654541016</v>
       </c>
       <c r="G3" t="n">
         <v>4597300</v>
@@ -518,16 +518,16 @@
         <v>45295</v>
       </c>
       <c r="C4" t="n">
-        <v>90.21231079101562</v>
+        <v>90.21233367919922</v>
       </c>
       <c r="D4" t="n">
-        <v>90.22130247846871</v>
+        <v>90.22132536893363</v>
       </c>
       <c r="E4" t="n">
-        <v>90.21231079101562</v>
+        <v>90.21233367919922</v>
       </c>
       <c r="F4" t="n">
-        <v>90.21231079101562</v>
+        <v>90.21233367919922</v>
       </c>
       <c r="G4" t="n">
         <v>2794100</v>
@@ -541,16 +541,16 @@
         <v>45296</v>
       </c>
       <c r="C5" t="n">
-        <v>90.22130584716797</v>
+        <v>90.22132110595703</v>
       </c>
       <c r="D5" t="n">
-        <v>90.23029753495679</v>
+        <v>90.23031279526658</v>
       </c>
       <c r="E5" t="n">
-        <v>90.22130584716797</v>
+        <v>90.22132110595703</v>
       </c>
       <c r="F5" t="n">
-        <v>90.22130584716797</v>
+        <v>90.22132110595703</v>
       </c>
       <c r="G5" t="n">
         <v>3491200</v>
@@ -564,16 +564,16 @@
         <v>45299</v>
       </c>
       <c r="C6" t="n">
-        <v>90.248291015625</v>
+        <v>90.24831390380859</v>
       </c>
       <c r="D6" t="n">
-        <v>90.248291015625</v>
+        <v>90.24831390380859</v>
       </c>
       <c r="E6" t="n">
-        <v>90.23929932614602</v>
+        <v>90.23932221204922</v>
       </c>
       <c r="F6" t="n">
-        <v>90.248291015625</v>
+        <v>90.24831390380859</v>
       </c>
       <c r="G6" t="n">
         <v>2867500</v>
@@ -587,16 +587,16 @@
         <v>45300</v>
       </c>
       <c r="C7" t="n">
-        <v>90.25727844238281</v>
+        <v>90.25728607177734</v>
       </c>
       <c r="D7" t="n">
-        <v>90.25727844238281</v>
+        <v>90.25728607177734</v>
       </c>
       <c r="E7" t="n">
-        <v>90.24828675332851</v>
+        <v>90.24829438196298</v>
       </c>
       <c r="F7" t="n">
-        <v>90.25727844238281</v>
+        <v>90.25728607177734</v>
       </c>
       <c r="G7" t="n">
         <v>2419800</v>
@@ -610,16 +610,16 @@
         <v>45301</v>
       </c>
       <c r="C8" t="n">
-        <v>90.27524566650391</v>
+        <v>90.27525329589844</v>
       </c>
       <c r="D8" t="n">
-        <v>90.27524566650391</v>
+        <v>90.27525329589844</v>
       </c>
       <c r="E8" t="n">
-        <v>90.26626083702391</v>
+        <v>90.26626846565911</v>
       </c>
       <c r="F8" t="n">
-        <v>90.27524566650391</v>
+        <v>90.27525329589844</v>
       </c>
       <c r="G8" t="n">
         <v>1961400</v>
@@ -679,16 +679,16 @@
         <v>45307</v>
       </c>
       <c r="C11" t="n">
-        <v>90.34715270996094</v>
+        <v>90.34719848632812</v>
       </c>
       <c r="D11" t="n">
-        <v>90.35614439682104</v>
+        <v>90.35619017774405</v>
       </c>
       <c r="E11" t="n">
-        <v>90.34715270996094</v>
+        <v>90.34719848632812</v>
       </c>
       <c r="F11" t="n">
-        <v>90.35614439682104</v>
+        <v>90.35619017774405</v>
       </c>
       <c r="G11" t="n">
         <v>2713000</v>
@@ -702,16 +702,16 @@
         <v>45308</v>
       </c>
       <c r="C12" t="n">
-        <v>90.35617065429688</v>
+        <v>90.35619354248047</v>
       </c>
       <c r="D12" t="n">
-        <v>90.36515548512048</v>
+        <v>90.36517837558002</v>
       </c>
       <c r="E12" t="n">
-        <v>90.35617065429688</v>
+        <v>90.35619354248047</v>
       </c>
       <c r="F12" t="n">
-        <v>90.36515548512048</v>
+        <v>90.36517837558002</v>
       </c>
       <c r="G12" t="n">
         <v>2317700</v>
@@ -725,16 +725,16 @@
         <v>45309</v>
       </c>
       <c r="C13" t="n">
-        <v>90.39213562011719</v>
+        <v>90.39212799072266</v>
       </c>
       <c r="D13" t="n">
-        <v>90.4011204514444</v>
+        <v>90.40111282129152</v>
       </c>
       <c r="E13" t="n">
-        <v>90.39213562011719</v>
+        <v>90.39212799072266</v>
       </c>
       <c r="F13" t="n">
-        <v>90.4011204514444</v>
+        <v>90.40111282129152</v>
       </c>
       <c r="G13" t="n">
         <v>2672000</v>
@@ -748,16 +748,16 @@
         <v>45310</v>
       </c>
       <c r="C14" t="n">
-        <v>90.41909027099609</v>
+        <v>90.41908264160156</v>
       </c>
       <c r="D14" t="n">
-        <v>90.41909027099609</v>
+        <v>90.41908264160156</v>
       </c>
       <c r="E14" t="n">
-        <v>90.40110689373897</v>
+        <v>90.40109926586183</v>
       </c>
       <c r="F14" t="n">
-        <v>90.41009858236752</v>
+        <v>90.4100909537317</v>
       </c>
       <c r="G14" t="n">
         <v>3630100</v>
@@ -771,16 +771,16 @@
         <v>45313</v>
       </c>
       <c r="C15" t="n">
-        <v>90.4281005859375</v>
+        <v>90.42807769775391</v>
       </c>
       <c r="D15" t="n">
-        <v>90.43709227710016</v>
+        <v>90.43706938664067</v>
       </c>
       <c r="E15" t="n">
-        <v>90.41911575342561</v>
+        <v>90.41909286751616</v>
       </c>
       <c r="F15" t="n">
-        <v>90.43259986084422</v>
+        <v>90.43257697152181</v>
       </c>
       <c r="G15" t="n">
         <v>4307000</v>
@@ -794,16 +794,16 @@
         <v>45314</v>
       </c>
       <c r="C16" t="n">
-        <v>90.44606018066406</v>
+        <v>90.44605255126953</v>
       </c>
       <c r="D16" t="n">
-        <v>90.44606018066406</v>
+        <v>90.44605255126953</v>
       </c>
       <c r="E16" t="n">
-        <v>90.43706849186626</v>
+        <v>90.43706086323019</v>
       </c>
       <c r="F16" t="n">
-        <v>90.43706849186626</v>
+        <v>90.43706086323019</v>
       </c>
       <c r="G16" t="n">
         <v>2066200</v>
@@ -817,16 +817,16 @@
         <v>45315</v>
       </c>
       <c r="C17" t="n">
-        <v>90.45506286621094</v>
+        <v>90.45505523681641</v>
       </c>
       <c r="D17" t="n">
-        <v>90.45506286621094</v>
+        <v>90.45505523681641</v>
       </c>
       <c r="E17" t="n">
-        <v>90.44607117631999</v>
+        <v>90.44606354768386</v>
       </c>
       <c r="F17" t="n">
-        <v>90.44607117631999</v>
+        <v>90.44606354768386</v>
       </c>
       <c r="G17" t="n">
         <v>3441600</v>
@@ -840,16 +840,16 @@
         <v>45316</v>
       </c>
       <c r="C18" t="n">
-        <v>90.49999237060547</v>
+        <v>90.50000762939453</v>
       </c>
       <c r="D18" t="n">
-        <v>90.49999237060547</v>
+        <v>90.50000762939453</v>
       </c>
       <c r="E18" t="n">
-        <v>90.48201585249815</v>
+        <v>90.48203110825628</v>
       </c>
       <c r="F18" t="n">
-        <v>90.48201585249815</v>
+        <v>90.48203110825628</v>
       </c>
       <c r="G18" t="n">
         <v>2426000</v>
@@ -863,16 +863,16 @@
         <v>45317</v>
       </c>
       <c r="C19" t="n">
-        <v>90.49999237060547</v>
+        <v>90.50000762939453</v>
       </c>
       <c r="D19" t="n">
-        <v>90.50898405898346</v>
+        <v>90.50899931928856</v>
       </c>
       <c r="E19" t="n">
-        <v>90.49999237060547</v>
+        <v>90.50000762939453</v>
       </c>
       <c r="F19" t="n">
-        <v>90.50898405898346</v>
+        <v>90.50899931928856</v>
       </c>
       <c r="G19" t="n">
         <v>2059100</v>
@@ -886,16 +886,16 @@
         <v>45320</v>
       </c>
       <c r="C20" t="n">
-        <v>90.50899505615234</v>
+        <v>90.50897979736328</v>
       </c>
       <c r="D20" t="n">
-        <v>90.52697157644387</v>
+        <v>90.52695631462417</v>
       </c>
       <c r="E20" t="n">
-        <v>90.50899505615234</v>
+        <v>90.50897979736328</v>
       </c>
       <c r="F20" t="n">
-        <v>90.51798674562285</v>
+        <v>90.51797148531789</v>
       </c>
       <c r="G20" t="n">
         <v>2914400</v>
@@ -909,16 +909,16 @@
         <v>45321</v>
       </c>
       <c r="C21" t="n">
-        <v>90.53594970703125</v>
+        <v>90.53593444824219</v>
       </c>
       <c r="D21" t="n">
-        <v>90.53594970703125</v>
+        <v>90.53593444824219</v>
       </c>
       <c r="E21" t="n">
-        <v>90.52695801890737</v>
+        <v>90.52694276163375</v>
       </c>
       <c r="F21" t="n">
-        <v>90.52695801890737</v>
+        <v>90.52694276163375</v>
       </c>
       <c r="G21" t="n">
         <v>3741000</v>
@@ -932,16 +932,16 @@
         <v>45322</v>
       </c>
       <c r="C22" t="n">
-        <v>90.53594970703125</v>
+        <v>90.53593444824219</v>
       </c>
       <c r="D22" t="n">
-        <v>90.54494139515513</v>
+        <v>90.54492613485063</v>
       </c>
       <c r="E22" t="n">
-        <v>90.53594970703125</v>
+        <v>90.53593444824219</v>
       </c>
       <c r="F22" t="n">
-        <v>90.53594970703125</v>
+        <v>90.53593444824219</v>
       </c>
       <c r="G22" t="n">
         <v>5171300</v>
@@ -955,16 +955,16 @@
         <v>45323</v>
       </c>
       <c r="C23" t="n">
-        <v>90.58834075927734</v>
+        <v>90.58834838867188</v>
       </c>
       <c r="D23" t="n">
-        <v>90.59737352716907</v>
+        <v>90.59738115732434</v>
       </c>
       <c r="E23" t="n">
-        <v>90.58834075927734</v>
+        <v>90.58834838867188</v>
       </c>
       <c r="F23" t="n">
-        <v>90.59737352716907</v>
+        <v>90.59738115732434</v>
       </c>
       <c r="G23" t="n">
         <v>7038600</v>
@@ -978,16 +978,16 @@
         <v>45324</v>
       </c>
       <c r="C24" t="n">
-        <v>90.59735870361328</v>
+        <v>90.59737396240234</v>
       </c>
       <c r="D24" t="n">
-        <v>90.59735870361328</v>
+        <v>90.59737396240234</v>
       </c>
       <c r="E24" t="n">
-        <v>90.5883259371995</v>
+        <v>90.58834119446723</v>
       </c>
       <c r="F24" t="n">
-        <v>90.59735870361328</v>
+        <v>90.59737396240234</v>
       </c>
       <c r="G24" t="n">
         <v>3864800</v>
@@ -1001,16 +1001,16 @@
         <v>45327</v>
       </c>
       <c r="C25" t="n">
-        <v>90.61542510986328</v>
+        <v>90.61540985107422</v>
       </c>
       <c r="D25" t="n">
-        <v>90.61542510986328</v>
+        <v>90.61540985107422</v>
       </c>
       <c r="E25" t="n">
-        <v>90.60639923265822</v>
+        <v>90.60638397538904</v>
       </c>
       <c r="F25" t="n">
-        <v>90.61542510986328</v>
+        <v>90.61540985107422</v>
       </c>
       <c r="G25" t="n">
         <v>3969400</v>
@@ -1024,16 +1024,16 @@
         <v>45328</v>
       </c>
       <c r="C26" t="n">
-        <v>90.62446594238281</v>
+        <v>90.62447357177734</v>
       </c>
       <c r="D26" t="n">
-        <v>90.63349871037437</v>
+        <v>90.63350634052934</v>
       </c>
       <c r="E26" t="n">
-        <v>90.61543317439127</v>
+        <v>90.61544080302535</v>
       </c>
       <c r="F26" t="n">
-        <v>90.62446594238281</v>
+        <v>90.62447357177734</v>
       </c>
       <c r="G26" t="n">
         <v>2167300</v>
@@ -1047,16 +1047,16 @@
         <v>45329</v>
       </c>
       <c r="C27" t="n">
-        <v>90.64250183105469</v>
+        <v>90.64251708984375</v>
       </c>
       <c r="D27" t="n">
-        <v>90.64250183105469</v>
+        <v>90.64251708984375</v>
       </c>
       <c r="E27" t="n">
-        <v>90.63346906601757</v>
+        <v>90.63348432328605</v>
       </c>
       <c r="F27" t="n">
-        <v>90.64250183105469</v>
+        <v>90.64251708984375</v>
       </c>
       <c r="G27" t="n">
         <v>2621200</v>
@@ -1070,16 +1070,16 @@
         <v>45330</v>
       </c>
       <c r="C28" t="n">
-        <v>90.66961669921875</v>
+        <v>90.66960906982422</v>
       </c>
       <c r="D28" t="n">
-        <v>90.68767534398516</v>
+        <v>90.68766771307108</v>
       </c>
       <c r="E28" t="n">
-        <v>90.66961669921875</v>
+        <v>90.66960906982422</v>
       </c>
       <c r="F28" t="n">
-        <v>90.66961669921875</v>
+        <v>90.66960906982422</v>
       </c>
       <c r="G28" t="n">
         <v>3838700</v>
@@ -1093,16 +1093,16 @@
         <v>45331</v>
       </c>
       <c r="C29" t="n">
-        <v>90.69669342041016</v>
+        <v>90.69670104980469</v>
       </c>
       <c r="D29" t="n">
-        <v>90.69669342041016</v>
+        <v>90.69670104980469</v>
       </c>
       <c r="E29" t="n">
-        <v>90.68314771653378</v>
+        <v>90.68315534478884</v>
       </c>
       <c r="F29" t="n">
-        <v>90.6876606544987</v>
+        <v>90.68766828313339</v>
       </c>
       <c r="G29" t="n">
         <v>3232500</v>
@@ -1116,16 +1116,16 @@
         <v>45334</v>
       </c>
       <c r="C30" t="n">
-        <v>90.69669342041016</v>
+        <v>90.69670104980469</v>
       </c>
       <c r="D30" t="n">
-        <v>90.71475206225145</v>
+        <v>90.71475969316506</v>
       </c>
       <c r="E30" t="n">
-        <v>90.69669342041016</v>
+        <v>90.69670104980469</v>
       </c>
       <c r="F30" t="n">
-        <v>90.70572618632161</v>
+        <v>90.70573381647597</v>
       </c>
       <c r="G30" t="n">
         <v>2792700</v>
@@ -1162,16 +1162,16 @@
         <v>45336</v>
       </c>
       <c r="C32" t="n">
-        <v>90.73282623291016</v>
+        <v>90.73281860351562</v>
       </c>
       <c r="D32" t="n">
-        <v>90.73282623291016</v>
+        <v>90.73281860351562</v>
       </c>
       <c r="E32" t="n">
-        <v>90.72379346613867</v>
+        <v>90.72378583750368</v>
       </c>
       <c r="F32" t="n">
-        <v>90.73282623291016</v>
+        <v>90.73281860351562</v>
       </c>
       <c r="G32" t="n">
         <v>2614100</v>
@@ -1185,16 +1185,16 @@
         <v>45337</v>
       </c>
       <c r="C33" t="n">
-        <v>90.77799224853516</v>
+        <v>90.77797698974609</v>
       </c>
       <c r="D33" t="n">
-        <v>90.7870250168949</v>
+        <v>90.78700975658751</v>
       </c>
       <c r="E33" t="n">
-        <v>90.77799224853516</v>
+        <v>90.77797698974609</v>
       </c>
       <c r="F33" t="n">
-        <v>90.7870250168949</v>
+        <v>90.78700975658751</v>
       </c>
       <c r="G33" t="n">
         <v>2577800</v>
@@ -1208,16 +1208,16 @@
         <v>45338</v>
       </c>
       <c r="C34" t="n">
-        <v>90.78701019287109</v>
+        <v>90.78701782226562</v>
       </c>
       <c r="D34" t="n">
-        <v>90.79604295975592</v>
+        <v>90.79605058990954</v>
       </c>
       <c r="E34" t="n">
-        <v>90.78701019287109</v>
+        <v>90.78701782226562</v>
       </c>
       <c r="F34" t="n">
-        <v>90.79604295975592</v>
+        <v>90.79605058990954</v>
       </c>
       <c r="G34" t="n">
         <v>2920700</v>
@@ -1254,16 +1254,16 @@
         <v>45343</v>
       </c>
       <c r="C36" t="n">
-        <v>90.8140869140625</v>
+        <v>90.81410980224609</v>
       </c>
       <c r="D36" t="n">
-        <v>90.83215244491001</v>
+        <v>90.83217533764672</v>
       </c>
       <c r="E36" t="n">
-        <v>90.8140869140625</v>
+        <v>90.81410980224609</v>
       </c>
       <c r="F36" t="n">
-        <v>90.82311967948625</v>
+        <v>90.8231425699464</v>
       </c>
       <c r="G36" t="n">
         <v>2302700</v>
@@ -1277,16 +1277,16 @@
         <v>45344</v>
       </c>
       <c r="C37" t="n">
-        <v>90.85023498535156</v>
+        <v>90.8502197265625</v>
       </c>
       <c r="D37" t="n">
-        <v>90.85926775315153</v>
+        <v>90.85925249284537</v>
       </c>
       <c r="E37" t="n">
-        <v>90.85023498535156</v>
+        <v>90.8502197265625</v>
       </c>
       <c r="F37" t="n">
-        <v>90.85023498535156</v>
+        <v>90.8502197265625</v>
       </c>
       <c r="G37" t="n">
         <v>2452200</v>
@@ -1300,16 +1300,16 @@
         <v>45345</v>
       </c>
       <c r="C38" t="n">
-        <v>90.87731170654297</v>
+        <v>90.8773193359375</v>
       </c>
       <c r="D38" t="n">
-        <v>90.87731170654297</v>
+        <v>90.8773193359375</v>
       </c>
       <c r="E38" t="n">
-        <v>90.8682858301853</v>
+        <v>90.86829345882208</v>
       </c>
       <c r="F38" t="n">
-        <v>90.87731170654297</v>
+        <v>90.8773193359375</v>
       </c>
       <c r="G38" t="n">
         <v>2010100</v>
@@ -1323,16 +1323,16 @@
         <v>45348</v>
       </c>
       <c r="C39" t="n">
-        <v>90.88634490966797</v>
+        <v>90.88636016845703</v>
       </c>
       <c r="D39" t="n">
-        <v>90.89537767605101</v>
+        <v>90.89539293635657</v>
       </c>
       <c r="E39" t="n">
-        <v>90.88634490966797</v>
+        <v>90.88636016845703</v>
       </c>
       <c r="F39" t="n">
-        <v>90.88634490966797</v>
+        <v>90.88636016845703</v>
       </c>
       <c r="G39" t="n">
         <v>2645100</v>
@@ -1346,16 +1346,16 @@
         <v>45349</v>
       </c>
       <c r="C40" t="n">
-        <v>90.9044189453125</v>
+        <v>90.90441131591797</v>
       </c>
       <c r="D40" t="n">
-        <v>90.9044189453125</v>
+        <v>90.90441131591797</v>
       </c>
       <c r="E40" t="n">
-        <v>90.89538617808456</v>
+        <v>90.89537854944814</v>
       </c>
       <c r="F40" t="n">
-        <v>90.9044189453125</v>
+        <v>90.90441131591797</v>
       </c>
       <c r="G40" t="n">
         <v>2360300</v>
@@ -1369,16 +1369,16 @@
         <v>45350</v>
       </c>
       <c r="C41" t="n">
-        <v>90.9134521484375</v>
+        <v>90.91343688964844</v>
       </c>
       <c r="D41" t="n">
-        <v>90.9134521484375</v>
+        <v>90.91343688964844</v>
       </c>
       <c r="E41" t="n">
-        <v>90.90442627046488</v>
+        <v>90.90441101319072</v>
       </c>
       <c r="F41" t="n">
-        <v>90.90442627046488</v>
+        <v>90.90441101319072</v>
       </c>
       <c r="G41" t="n">
         <v>4526200</v>
@@ -1392,16 +1392,16 @@
         <v>45351</v>
       </c>
       <c r="C42" t="n">
-        <v>90.94052886962891</v>
+        <v>90.9405517578125</v>
       </c>
       <c r="D42" t="n">
-        <v>90.94956163612534</v>
+        <v>90.94958452658233</v>
       </c>
       <c r="E42" t="n">
-        <v>90.94052886962891</v>
+        <v>90.9405517578125</v>
       </c>
       <c r="F42" t="n">
-        <v>90.94052886962891</v>
+        <v>90.9405517578125</v>
       </c>
       <c r="G42" t="n">
         <v>5560200</v>
@@ -1484,16 +1484,16 @@
         <v>45357</v>
       </c>
       <c r="C46" t="n">
-        <v>91.00399017333984</v>
+        <v>91.00402069091797</v>
       </c>
       <c r="D46" t="n">
-        <v>91.01305986546514</v>
+        <v>91.01309038608471</v>
       </c>
       <c r="E46" t="n">
-        <v>90.99492048121455</v>
+        <v>90.99495099575121</v>
       </c>
       <c r="F46" t="n">
-        <v>91.00399017333984</v>
+        <v>91.00402069091797</v>
       </c>
       <c r="G46" t="n">
         <v>2760000</v>
@@ -1553,16 +1553,16 @@
         <v>45362</v>
       </c>
       <c r="C49" t="n">
-        <v>91.0765380859375</v>
+        <v>91.07656097412109</v>
       </c>
       <c r="D49" t="n">
-        <v>91.0765380859375</v>
+        <v>91.07656097412109</v>
       </c>
       <c r="E49" t="n">
-        <v>91.06746839339277</v>
+        <v>91.06749127929709</v>
       </c>
       <c r="F49" t="n">
-        <v>91.0765380859375</v>
+        <v>91.07656097412109</v>
       </c>
       <c r="G49" t="n">
         <v>3238400</v>
@@ -1599,16 +1599,16 @@
         <v>45364</v>
       </c>
       <c r="C51" t="n">
-        <v>91.09468078613281</v>
+        <v>91.09467315673828</v>
       </c>
       <c r="D51" t="n">
-        <v>91.1037504796964</v>
+        <v>91.10374284954226</v>
       </c>
       <c r="E51" t="n">
-        <v>91.09468078613281</v>
+        <v>91.09467315673828</v>
       </c>
       <c r="F51" t="n">
-        <v>91.09468078613281</v>
+        <v>91.09467315673828</v>
       </c>
       <c r="G51" t="n">
         <v>2249300</v>
@@ -1622,16 +1622,16 @@
         <v>45365</v>
       </c>
       <c r="C52" t="n">
-        <v>91.13095855712891</v>
+        <v>91.13096618652344</v>
       </c>
       <c r="D52" t="n">
-        <v>91.14002825128117</v>
+        <v>91.140035881435</v>
       </c>
       <c r="E52" t="n">
-        <v>91.13095855712891</v>
+        <v>91.13096618652344</v>
       </c>
       <c r="F52" t="n">
-        <v>91.13095855712891</v>
+        <v>91.13096618652344</v>
       </c>
       <c r="G52" t="n">
         <v>3469600</v>
@@ -1645,16 +1645,16 @@
         <v>45366</v>
       </c>
       <c r="C53" t="n">
-        <v>91.14910125732422</v>
+        <v>91.14907836914062</v>
       </c>
       <c r="D53" t="n">
-        <v>91.14910125732422</v>
+        <v>91.14907836914062</v>
       </c>
       <c r="E53" t="n">
-        <v>91.14003848030443</v>
+        <v>91.14001559439656</v>
       </c>
       <c r="F53" t="n">
-        <v>91.14910125732422</v>
+        <v>91.14907836914062</v>
       </c>
       <c r="G53" t="n">
         <v>3277300</v>
@@ -1668,16 +1668,16 @@
         <v>45369</v>
       </c>
       <c r="C54" t="n">
-        <v>91.15815734863281</v>
+        <v>91.15814208984375</v>
       </c>
       <c r="D54" t="n">
-        <v>91.16722704244948</v>
+        <v>91.16721178214227</v>
       </c>
       <c r="E54" t="n">
-        <v>91.15815734863281</v>
+        <v>91.15814208984375</v>
       </c>
       <c r="F54" t="n">
-        <v>91.16722704244948</v>
+        <v>91.16721178214227</v>
       </c>
       <c r="G54" t="n">
         <v>3576200</v>
@@ -1714,16 +1714,16 @@
         <v>45371</v>
       </c>
       <c r="C56" t="n">
-        <v>91.18534851074219</v>
+        <v>91.18538665771484</v>
       </c>
       <c r="D56" t="n">
-        <v>91.19441820346465</v>
+        <v>91.19445635423156</v>
       </c>
       <c r="E56" t="n">
-        <v>91.18534851074219</v>
+        <v>91.18538665771484</v>
       </c>
       <c r="F56" t="n">
-        <v>91.18534851074219</v>
+        <v>91.18538665771484</v>
       </c>
       <c r="G56" t="n">
         <v>2492700</v>
@@ -1737,16 +1737,16 @@
         <v>45372</v>
       </c>
       <c r="C57" t="n">
-        <v>91.22164916992188</v>
+        <v>91.22164154052734</v>
       </c>
       <c r="D57" t="n">
-        <v>91.23071886550841</v>
+        <v>91.23071123535532</v>
       </c>
       <c r="E57" t="n">
-        <v>91.22164916992188</v>
+        <v>91.22164154052734</v>
       </c>
       <c r="F57" t="n">
-        <v>91.22164916992188</v>
+        <v>91.22164154052734</v>
       </c>
       <c r="G57" t="n">
         <v>3547400</v>
@@ -1806,16 +1806,16 @@
         <v>45377</v>
       </c>
       <c r="C60" t="n">
-        <v>91.26697540283203</v>
+        <v>91.2669677734375</v>
       </c>
       <c r="D60" t="n">
-        <v>91.27604509689544</v>
+        <v>91.27603746674274</v>
       </c>
       <c r="E60" t="n">
-        <v>91.26697540283203</v>
+        <v>91.2669677734375</v>
       </c>
       <c r="F60" t="n">
-        <v>91.26697540283203</v>
+        <v>91.2669677734375</v>
       </c>
       <c r="G60" t="n">
         <v>3181700</v>
@@ -1829,16 +1829,16 @@
         <v>45378</v>
       </c>
       <c r="C61" t="n">
-        <v>91.31230926513672</v>
+        <v>91.31233215332031</v>
       </c>
       <c r="D61" t="n">
-        <v>91.32137895912348</v>
+        <v>91.32140184958047</v>
       </c>
       <c r="E61" t="n">
-        <v>91.31230926513672</v>
+        <v>91.31233215332031</v>
       </c>
       <c r="F61" t="n">
-        <v>91.32137895912348</v>
+        <v>91.32140184958047</v>
       </c>
       <c r="G61" t="n">
         <v>2990800</v>
@@ -1852,16 +1852,16 @@
         <v>45379</v>
       </c>
       <c r="C62" t="n">
-        <v>91.32137298583984</v>
+        <v>91.32138824462891</v>
       </c>
       <c r="D62" t="n">
-        <v>91.33044267923337</v>
+        <v>91.33045793953788</v>
       </c>
       <c r="E62" t="n">
-        <v>91.32137298583984</v>
+        <v>91.32138824462891</v>
       </c>
       <c r="F62" t="n">
-        <v>91.33044267923337</v>
+        <v>91.33045793953788</v>
       </c>
       <c r="G62" t="n">
         <v>5425800</v>
@@ -1898,16 +1898,16 @@
         <v>45384</v>
       </c>
       <c r="C64" t="n">
-        <v>91.366943359375</v>
+        <v>91.36692047119141</v>
       </c>
       <c r="D64" t="n">
-        <v>91.366943359375</v>
+        <v>91.36692047119141</v>
       </c>
       <c r="E64" t="n">
-        <v>91.35783990446313</v>
+        <v>91.35781701856003</v>
       </c>
       <c r="F64" t="n">
-        <v>91.366943359375</v>
+        <v>91.36692047119141</v>
       </c>
       <c r="G64" t="n">
         <v>4202900</v>
@@ -1921,16 +1921,16 @@
         <v>45385</v>
       </c>
       <c r="C65" t="n">
-        <v>91.37602996826172</v>
+        <v>91.37601470947266</v>
       </c>
       <c r="D65" t="n">
-        <v>91.38514037000337</v>
+        <v>91.38512510969296</v>
       </c>
       <c r="E65" t="n">
-        <v>91.37602996826172</v>
+        <v>91.37601470947266</v>
       </c>
       <c r="F65" t="n">
-        <v>91.37602996826172</v>
+        <v>91.37601470947266</v>
       </c>
       <c r="G65" t="n">
         <v>4333600</v>
@@ -1990,16 +1990,16 @@
         <v>45390</v>
       </c>
       <c r="C68" t="n">
-        <v>91.44889831542969</v>
+        <v>91.44889068603516</v>
       </c>
       <c r="D68" t="n">
-        <v>91.44889831542969</v>
+        <v>91.44889068603516</v>
       </c>
       <c r="E68" t="n">
-        <v>91.43978791378451</v>
+        <v>91.43978028515004</v>
       </c>
       <c r="F68" t="n">
-        <v>91.44889831542969</v>
+        <v>91.44889068603516</v>
       </c>
       <c r="G68" t="n">
         <v>3511400</v>
@@ -2036,16 +2036,16 @@
         <v>45392</v>
       </c>
       <c r="C70" t="n">
-        <v>91.47622680664062</v>
+        <v>91.47621917724609</v>
       </c>
       <c r="D70" t="n">
-        <v>91.47622680664062</v>
+        <v>91.47621917724609</v>
       </c>
       <c r="E70" t="n">
-        <v>91.45801295170727</v>
+        <v>91.45800532383184</v>
       </c>
       <c r="F70" t="n">
-        <v>91.46711640457362</v>
+        <v>91.46710877593893</v>
       </c>
       <c r="G70" t="n">
         <v>3893100</v>
@@ -2059,16 +2059,16 @@
         <v>45393</v>
       </c>
       <c r="C71" t="n">
-        <v>91.51263427734375</v>
+        <v>91.51264190673828</v>
       </c>
       <c r="D71" t="n">
-        <v>91.51263427734375</v>
+        <v>91.51264190673828</v>
       </c>
       <c r="E71" t="n">
-        <v>91.50352387798345</v>
+        <v>91.50353150661844</v>
       </c>
       <c r="F71" t="n">
-        <v>91.50352387798345</v>
+        <v>91.50353150661844</v>
       </c>
       <c r="G71" t="n">
         <v>3521100</v>
@@ -2082,16 +2082,16 @@
         <v>45394</v>
       </c>
       <c r="C72" t="n">
-        <v>91.52179718017578</v>
+        <v>91.52177429199219</v>
       </c>
       <c r="D72" t="n">
-        <v>91.52179718017578</v>
+        <v>91.52177429199219</v>
       </c>
       <c r="E72" t="n">
-        <v>91.51268677558909</v>
+        <v>91.51266388968386</v>
       </c>
       <c r="F72" t="n">
-        <v>91.52179718017578</v>
+        <v>91.52177429199219</v>
       </c>
       <c r="G72" t="n">
         <v>4235400</v>
@@ -2105,16 +2105,16 @@
         <v>45397</v>
       </c>
       <c r="C73" t="n">
-        <v>91.53999328613281</v>
+        <v>91.53998565673828</v>
       </c>
       <c r="D73" t="n">
-        <v>91.53999328613281</v>
+        <v>91.53998565673828</v>
       </c>
       <c r="E73" t="n">
-        <v>91.53088288331307</v>
+        <v>91.53087525467784</v>
       </c>
       <c r="F73" t="n">
-        <v>91.53088288331307</v>
+        <v>91.53087525467784</v>
       </c>
       <c r="G73" t="n">
         <v>4144700</v>
@@ -2128,16 +2128,16 @@
         <v>45398</v>
       </c>
       <c r="C74" t="n">
-        <v>91.53999328613281</v>
+        <v>91.53998565673828</v>
       </c>
       <c r="D74" t="n">
-        <v>91.55820714257106</v>
+        <v>91.5581995116585</v>
       </c>
       <c r="E74" t="n">
-        <v>91.53999328613281</v>
+        <v>91.53998565673828</v>
       </c>
       <c r="F74" t="n">
-        <v>91.54910368895256</v>
+        <v>91.54909605879871</v>
       </c>
       <c r="G74" t="n">
         <v>4850000</v>
@@ -2151,16 +2151,16 @@
         <v>45399</v>
       </c>
       <c r="C75" t="n">
-        <v>91.56732177734375</v>
+        <v>91.56729125976562</v>
       </c>
       <c r="D75" t="n">
-        <v>91.56732177734375</v>
+        <v>91.56729125976562</v>
       </c>
       <c r="E75" t="n">
-        <v>91.55821137410295</v>
+        <v>91.55818085956115</v>
       </c>
       <c r="F75" t="n">
-        <v>91.56732177734375</v>
+        <v>91.56729125976562</v>
       </c>
       <c r="G75" t="n">
         <v>3688400</v>
@@ -2174,16 +2174,16 @@
         <v>45400</v>
       </c>
       <c r="C76" t="n">
-        <v>91.59463500976562</v>
+        <v>91.59465026855469</v>
       </c>
       <c r="D76" t="n">
-        <v>91.60374541190951</v>
+        <v>91.6037606722163</v>
       </c>
       <c r="E76" t="n">
-        <v>91.59463500976562</v>
+        <v>91.59465026855469</v>
       </c>
       <c r="F76" t="n">
-        <v>91.60374541190951</v>
+        <v>91.6037606722163</v>
       </c>
       <c r="G76" t="n">
         <v>3235600</v>
@@ -2197,16 +2197,16 @@
         <v>45401</v>
       </c>
       <c r="C77" t="n">
-        <v>91.62195587158203</v>
+        <v>91.62194061279297</v>
       </c>
       <c r="D77" t="n">
-        <v>91.62195587158203</v>
+        <v>91.62194061279297</v>
       </c>
       <c r="E77" t="n">
-        <v>91.60374201716995</v>
+        <v>91.60372676141424</v>
       </c>
       <c r="F77" t="n">
-        <v>91.62195587158203</v>
+        <v>91.62194061279297</v>
       </c>
       <c r="G77" t="n">
         <v>3319500</v>
@@ -2243,16 +2243,16 @@
         <v>45405</v>
       </c>
       <c r="C79" t="n">
-        <v>91.64016723632812</v>
+        <v>91.64015960693359</v>
       </c>
       <c r="D79" t="n">
-        <v>91.64927763719604</v>
+        <v>91.64927000704303</v>
       </c>
       <c r="E79" t="n">
-        <v>91.63105683546023</v>
+        <v>91.63104920682416</v>
       </c>
       <c r="F79" t="n">
-        <v>91.64016723632812</v>
+        <v>91.64015960693359</v>
       </c>
       <c r="G79" t="n">
         <v>4233300</v>
@@ -2266,16 +2266,16 @@
         <v>45406</v>
       </c>
       <c r="C80" t="n">
-        <v>91.6492919921875</v>
+        <v>91.64929962158203</v>
       </c>
       <c r="D80" t="n">
-        <v>91.65839544528153</v>
+        <v>91.65840307543388</v>
       </c>
       <c r="E80" t="n">
-        <v>91.6492919921875</v>
+        <v>91.64929962158203</v>
       </c>
       <c r="F80" t="n">
-        <v>91.65839544528153</v>
+        <v>91.65840307543388</v>
       </c>
       <c r="G80" t="n">
         <v>3200000</v>
@@ -2289,16 +2289,16 @@
         <v>45407</v>
       </c>
       <c r="C81" t="n">
-        <v>91.69483184814453</v>
+        <v>91.69480133056641</v>
       </c>
       <c r="D81" t="n">
-        <v>91.69483184814453</v>
+        <v>91.69480133056641</v>
       </c>
       <c r="E81" t="n">
-        <v>91.68572839487747</v>
+        <v>91.68569788032913</v>
       </c>
       <c r="F81" t="n">
-        <v>91.69483184814453</v>
+        <v>91.69480133056641</v>
       </c>
       <c r="G81" t="n">
         <v>2705900</v>
@@ -2381,16 +2381,16 @@
         <v>45413</v>
       </c>
       <c r="C85" t="n">
-        <v>91.75691986083984</v>
+        <v>91.75690460205078</v>
       </c>
       <c r="D85" t="n">
-        <v>91.75691986083984</v>
+        <v>91.75690460205078</v>
       </c>
       <c r="E85" t="n">
-        <v>91.74777755015184</v>
+        <v>91.7477622928831</v>
       </c>
       <c r="F85" t="n">
-        <v>91.75691986083984</v>
+        <v>91.75690460205078</v>
       </c>
       <c r="G85" t="n">
         <v>8406600</v>
@@ -2404,16 +2404,16 @@
         <v>45414</v>
       </c>
       <c r="C86" t="n">
-        <v>91.79350280761719</v>
+        <v>91.79349517822266</v>
       </c>
       <c r="D86" t="n">
-        <v>91.79350280761719</v>
+        <v>91.79349517822266</v>
       </c>
       <c r="E86" t="n">
-        <v>91.78435351878694</v>
+        <v>91.78434589015285</v>
       </c>
       <c r="F86" t="n">
-        <v>91.79350280761719</v>
+        <v>91.79349517822266</v>
       </c>
       <c r="G86" t="n">
         <v>4369600</v>
@@ -2427,16 +2427,16 @@
         <v>45415</v>
       </c>
       <c r="C87" t="n">
-        <v>91.81178283691406</v>
+        <v>91.81179809570312</v>
       </c>
       <c r="D87" t="n">
-        <v>91.81178283691406</v>
+        <v>91.81179809570312</v>
       </c>
       <c r="E87" t="n">
-        <v>91.79348426295037</v>
+        <v>91.79349951869828</v>
       </c>
       <c r="F87" t="n">
-        <v>91.80263354993221</v>
+        <v>91.8026488072007</v>
       </c>
       <c r="G87" t="n">
         <v>4792400</v>
@@ -2496,16 +2496,16 @@
         <v>45420</v>
       </c>
       <c r="C90" t="n">
-        <v>91.848388671875</v>
+        <v>91.84840393066406</v>
       </c>
       <c r="D90" t="n">
-        <v>91.848388671875</v>
+        <v>91.84840393066406</v>
       </c>
       <c r="E90" t="n">
-        <v>91.83009009479026</v>
+        <v>91.83010535053937</v>
       </c>
       <c r="F90" t="n">
-        <v>91.83923938333263</v>
+        <v>91.83925464060172</v>
       </c>
       <c r="G90" t="n">
         <v>3109400</v>
@@ -2519,16 +2519,16 @@
         <v>45421</v>
       </c>
       <c r="C91" t="n">
-        <v>91.87583160400391</v>
+        <v>91.87582397460938</v>
       </c>
       <c r="D91" t="n">
-        <v>91.88497391388746</v>
+        <v>91.88496628373375</v>
       </c>
       <c r="E91" t="n">
-        <v>91.87583160400391</v>
+        <v>91.87582397460938</v>
       </c>
       <c r="F91" t="n">
-        <v>91.88040275894568</v>
+        <v>91.88039512917156</v>
       </c>
       <c r="G91" t="n">
         <v>2739600</v>
@@ -2542,16 +2542,16 @@
         <v>45422</v>
       </c>
       <c r="C92" t="n">
-        <v>91.90325927734375</v>
+        <v>91.90324401855469</v>
       </c>
       <c r="D92" t="n">
-        <v>91.90325927734375</v>
+        <v>91.90324401855469</v>
       </c>
       <c r="E92" t="n">
-        <v>91.88496070248264</v>
+        <v>91.88494544673172</v>
       </c>
       <c r="F92" t="n">
-        <v>91.90325927734375</v>
+        <v>91.90324401855469</v>
       </c>
       <c r="G92" t="n">
         <v>3005800</v>
@@ -2565,16 +2565,16 @@
         <v>45425</v>
       </c>
       <c r="C93" t="n">
-        <v>91.91244506835938</v>
+        <v>91.91242980957031</v>
       </c>
       <c r="D93" t="n">
-        <v>91.91244506835938</v>
+        <v>91.91242980957031</v>
       </c>
       <c r="E93" t="n">
-        <v>91.90329577729513</v>
+        <v>91.90328052002498</v>
       </c>
       <c r="F93" t="n">
-        <v>91.91244506835938</v>
+        <v>91.91242980957031</v>
       </c>
       <c r="G93" t="n">
         <v>3317000</v>
@@ -2588,16 +2588,16 @@
         <v>45426</v>
       </c>
       <c r="C94" t="n">
-        <v>91.91244506835938</v>
+        <v>91.91242980957031</v>
       </c>
       <c r="D94" t="n">
-        <v>91.92158738055934</v>
+        <v>91.92157212025253</v>
       </c>
       <c r="E94" t="n">
-        <v>91.91244506835938</v>
+        <v>91.91242980957031</v>
       </c>
       <c r="F94" t="n">
-        <v>91.92158738055934</v>
+        <v>91.92157212025253</v>
       </c>
       <c r="G94" t="n">
         <v>2765800</v>
@@ -2634,16 +2634,16 @@
         <v>45428</v>
       </c>
       <c r="C96" t="n">
-        <v>91.97646331787109</v>
+        <v>91.97644805908203</v>
       </c>
       <c r="D96" t="n">
-        <v>91.98560562879577</v>
+        <v>91.98559036849001</v>
       </c>
       <c r="E96" t="n">
-        <v>91.96731402808312</v>
+        <v>91.96729877081192</v>
       </c>
       <c r="F96" t="n">
-        <v>91.97646331787109</v>
+        <v>91.97644805908203</v>
       </c>
       <c r="G96" t="n">
         <v>3699500</v>
@@ -2657,16 +2657,16 @@
         <v>45429</v>
       </c>
       <c r="C97" t="n">
-        <v>91.98558807373047</v>
+        <v>91.98561096191406</v>
       </c>
       <c r="D97" t="n">
-        <v>91.99473736177234</v>
+        <v>91.9947602522325</v>
       </c>
       <c r="E97" t="n">
-        <v>91.98558807373047</v>
+        <v>91.98561096191406</v>
       </c>
       <c r="F97" t="n">
-        <v>91.99473736177234</v>
+        <v>91.9947602522325</v>
       </c>
       <c r="G97" t="n">
         <v>4544200</v>
@@ -2680,16 +2680,16 @@
         <v>45432</v>
       </c>
       <c r="C98" t="n">
-        <v>91.99475860595703</v>
+        <v>91.99474334716797</v>
       </c>
       <c r="D98" t="n">
-        <v>92.00390789611173</v>
+        <v>92.00389263580512</v>
       </c>
       <c r="E98" t="n">
-        <v>91.99475860595703</v>
+        <v>91.99474334716797</v>
       </c>
       <c r="F98" t="n">
-        <v>92.00390789611173</v>
+        <v>92.00389263580512</v>
       </c>
       <c r="G98" t="n">
         <v>3341000</v>
@@ -2703,16 +2703,16 @@
         <v>45433</v>
       </c>
       <c r="C99" t="n">
-        <v>92.01304626464844</v>
+        <v>92.01303100585938</v>
       </c>
       <c r="D99" t="n">
-        <v>92.02219555441108</v>
+        <v>92.02218029410477</v>
       </c>
       <c r="E99" t="n">
-        <v>92.01304626464844</v>
+        <v>92.01303100585938</v>
       </c>
       <c r="F99" t="n">
-        <v>92.01304626464844</v>
+        <v>92.01303100585938</v>
       </c>
       <c r="G99" t="n">
         <v>3774900</v>
@@ -2749,16 +2749,16 @@
         <v>45435</v>
       </c>
       <c r="C101" t="n">
-        <v>92.08621978759766</v>
+        <v>92.08619689941406</v>
       </c>
       <c r="D101" t="n">
-        <v>92.08621978759766</v>
+        <v>92.08619689941406</v>
       </c>
       <c r="E101" t="n">
-        <v>92.0770774773771</v>
+        <v>92.07705459146585</v>
       </c>
       <c r="F101" t="n">
-        <v>92.0770774773771</v>
+        <v>92.07705459146585</v>
       </c>
       <c r="G101" t="n">
         <v>3077800</v>
@@ -2772,16 +2772,16 @@
         <v>45436</v>
       </c>
       <c r="C102" t="n">
-        <v>92.09535217285156</v>
+        <v>92.09537506103516</v>
       </c>
       <c r="D102" t="n">
-        <v>92.09535217285156</v>
+        <v>92.09537506103516</v>
       </c>
       <c r="E102" t="n">
-        <v>92.08620288544756</v>
+        <v>92.08622577135732</v>
       </c>
       <c r="F102" t="n">
-        <v>92.09535217285156</v>
+        <v>92.09537506103516</v>
       </c>
       <c r="G102" t="n">
         <v>2512800</v>
@@ -2795,16 +2795,16 @@
         <v>45440</v>
       </c>
       <c r="C103" t="n">
-        <v>92.10447692871094</v>
+        <v>92.10450744628906</v>
       </c>
       <c r="D103" t="n">
-        <v>92.10447692871094</v>
+        <v>92.10450744628906</v>
       </c>
       <c r="E103" t="n">
-        <v>92.09532764374381</v>
+        <v>92.09535815829045</v>
       </c>
       <c r="F103" t="n">
-        <v>92.09532764374381</v>
+        <v>92.09535815829045</v>
       </c>
       <c r="G103" t="n">
         <v>3684600</v>
@@ -2818,16 +2818,16 @@
         <v>45441</v>
       </c>
       <c r="C104" t="n">
-        <v>92.10447692871094</v>
+        <v>92.10450744628906</v>
       </c>
       <c r="D104" t="n">
-        <v>92.11361923481844</v>
+        <v>92.11364975542574</v>
       </c>
       <c r="E104" t="n">
-        <v>92.10447692871094</v>
+        <v>92.10450744628906</v>
       </c>
       <c r="F104" t="n">
-        <v>92.11361923481844</v>
+        <v>92.11364975542574</v>
       </c>
       <c r="G104" t="n">
         <v>3971700</v>
@@ -2841,16 +2841,16 @@
         <v>45442</v>
       </c>
       <c r="C105" t="n">
-        <v>92.12279510498047</v>
+        <v>92.12281799316406</v>
       </c>
       <c r="D105" t="n">
-        <v>92.13194439258794</v>
+        <v>92.1319672830447</v>
       </c>
       <c r="E105" t="n">
-        <v>92.12279510498047</v>
+        <v>92.12281799316406</v>
       </c>
       <c r="F105" t="n">
-        <v>92.12279510498047</v>
+        <v>92.12281799316406</v>
       </c>
       <c r="G105" t="n">
         <v>3566800</v>
@@ -2864,16 +2864,16 @@
         <v>45443</v>
       </c>
       <c r="C106" t="n">
-        <v>92.15940856933594</v>
+        <v>92.15938568115234</v>
       </c>
       <c r="D106" t="n">
-        <v>92.15940856933594</v>
+        <v>92.15938568115234</v>
       </c>
       <c r="E106" t="n">
-        <v>92.15025927941603</v>
+        <v>92.15023639350471</v>
       </c>
       <c r="F106" t="n">
-        <v>92.15025927941603</v>
+        <v>92.15023639350471</v>
       </c>
       <c r="G106" t="n">
         <v>7082900</v>
@@ -2887,16 +2887,16 @@
         <v>45446</v>
       </c>
       <c r="C107" t="n">
-        <v>92.17778015136719</v>
+        <v>92.17776489257812</v>
       </c>
       <c r="D107" t="n">
-        <v>92.18696256377655</v>
+        <v>92.18694730346745</v>
       </c>
       <c r="E107" t="n">
-        <v>92.17778015136719</v>
+        <v>92.17776489257812</v>
       </c>
       <c r="F107" t="n">
-        <v>92.17778015136719</v>
+        <v>92.17776489257812</v>
       </c>
       <c r="G107" t="n">
         <v>9568200</v>
@@ -2910,16 +2910,16 @@
         <v>45447</v>
       </c>
       <c r="C108" t="n">
-        <v>92.19614410400391</v>
+        <v>92.19613647460938</v>
       </c>
       <c r="D108" t="n">
-        <v>92.19614410400391</v>
+        <v>92.19613647460938</v>
       </c>
       <c r="E108" t="n">
-        <v>92.18695468290501</v>
+        <v>92.18694705427092</v>
       </c>
       <c r="F108" t="n">
-        <v>92.19614410400391</v>
+        <v>92.19613647460938</v>
       </c>
       <c r="G108" t="n">
         <v>5355900</v>
@@ -2933,16 +2933,16 @@
         <v>45448</v>
       </c>
       <c r="C109" t="n">
-        <v>92.21450805664062</v>
+        <v>92.21452331542969</v>
       </c>
       <c r="D109" t="n">
-        <v>92.21450805664062</v>
+        <v>92.21452331542969</v>
       </c>
       <c r="E109" t="n">
-        <v>92.20531863702551</v>
+        <v>92.205333894294</v>
       </c>
       <c r="F109" t="n">
-        <v>92.20531863702551</v>
+        <v>92.205333894294</v>
       </c>
       <c r="G109" t="n">
         <v>4285300</v>
@@ -2956,16 +2956,16 @@
         <v>45449</v>
       </c>
       <c r="C110" t="n">
-        <v>92.21450805664062</v>
+        <v>92.21452331542969</v>
       </c>
       <c r="D110" t="n">
-        <v>92.22369046678234</v>
+        <v>92.22370572709083</v>
       </c>
       <c r="E110" t="n">
-        <v>92.21450805664062</v>
+        <v>92.21452331542969</v>
       </c>
       <c r="F110" t="n">
-        <v>92.22369046678234</v>
+        <v>92.22370572709083</v>
       </c>
       <c r="G110" t="n">
         <v>3376100</v>
@@ -2979,16 +2979,16 @@
         <v>45450</v>
       </c>
       <c r="C111" t="n">
-        <v>92.25127410888672</v>
+        <v>92.25128173828125</v>
       </c>
       <c r="D111" t="n">
-        <v>92.26045652055964</v>
+        <v>92.26046415071357</v>
       </c>
       <c r="E111" t="n">
-        <v>92.25127410888672</v>
+        <v>92.25128173828125</v>
       </c>
       <c r="F111" t="n">
-        <v>92.26045652055964</v>
+        <v>92.26046415071357</v>
       </c>
       <c r="G111" t="n">
         <v>3490400</v>
@@ -3002,16 +3002,16 @@
         <v>45453</v>
       </c>
       <c r="C112" t="n">
-        <v>92.26963806152344</v>
+        <v>92.2696533203125</v>
       </c>
       <c r="D112" t="n">
-        <v>92.27882748188611</v>
+        <v>92.27884274219484</v>
       </c>
       <c r="E112" t="n">
-        <v>92.26963806152344</v>
+        <v>92.2696533203125</v>
       </c>
       <c r="F112" t="n">
-        <v>92.27882748188611</v>
+        <v>92.27884274219484</v>
       </c>
       <c r="G112" t="n">
         <v>2732300</v>
@@ -3025,16 +3025,16 @@
         <v>45454</v>
       </c>
       <c r="C113" t="n">
-        <v>92.28800964355469</v>
+        <v>92.28800201416016</v>
       </c>
       <c r="D113" t="n">
-        <v>92.28800964355469</v>
+        <v>92.28800201416016</v>
       </c>
       <c r="E113" t="n">
-        <v>92.27882723269077</v>
+        <v>92.27881960405534</v>
       </c>
       <c r="F113" t="n">
-        <v>92.28800964355469</v>
+        <v>92.28800201416016</v>
       </c>
       <c r="G113" t="n">
         <v>3320000</v>
@@ -3048,16 +3048,16 @@
         <v>45455</v>
       </c>
       <c r="C114" t="n">
-        <v>92.30638122558594</v>
+        <v>92.30636596679688</v>
       </c>
       <c r="D114" t="n">
-        <v>92.30638122558594</v>
+        <v>92.30636596679688</v>
       </c>
       <c r="E114" t="n">
-        <v>92.28800238635547</v>
+        <v>92.28798713060455</v>
       </c>
       <c r="F114" t="n">
-        <v>92.2971918059707</v>
+        <v>92.29717654870072</v>
       </c>
       <c r="G114" t="n">
         <v>5355700</v>
@@ -3071,16 +3071,16 @@
         <v>45456</v>
       </c>
       <c r="C115" t="n">
-        <v>92.31560516357422</v>
+        <v>92.31558990478516</v>
       </c>
       <c r="D115" t="n">
-        <v>92.32478757714952</v>
+        <v>92.32477231684271</v>
       </c>
       <c r="E115" t="n">
-        <v>92.30641574052291</v>
+        <v>92.30640048325276</v>
       </c>
       <c r="F115" t="n">
-        <v>92.31560516357422</v>
+        <v>92.31558990478516</v>
       </c>
       <c r="G115" t="n">
         <v>3925700</v>
@@ -3094,16 +3094,16 @@
         <v>45457</v>
       </c>
       <c r="C116" t="n">
-        <v>92.36151123046875</v>
+        <v>92.36149597167969</v>
       </c>
       <c r="D116" t="n">
-        <v>92.36151123046875</v>
+        <v>92.36149597167969</v>
       </c>
       <c r="E116" t="n">
-        <v>92.34313939921861</v>
+        <v>92.34312414346471</v>
       </c>
       <c r="F116" t="n">
-        <v>92.3523218101067</v>
+        <v>92.3523065528358</v>
       </c>
       <c r="G116" t="n">
         <v>3505500</v>
@@ -3117,16 +3117,16 @@
         <v>45460</v>
       </c>
       <c r="C117" t="n">
-        <v>92.37068176269531</v>
+        <v>92.37068939208984</v>
       </c>
       <c r="D117" t="n">
-        <v>92.37068176269531</v>
+        <v>92.37068939208984</v>
       </c>
       <c r="E117" t="n">
-        <v>92.36149234421234</v>
+        <v>92.36149997284787</v>
       </c>
       <c r="F117" t="n">
-        <v>92.37068176269531</v>
+        <v>92.37068939208984</v>
       </c>
       <c r="G117" t="n">
         <v>3493700</v>
@@ -3140,16 +3140,16 @@
         <v>45461</v>
       </c>
       <c r="C118" t="n">
-        <v>92.39828491210938</v>
+        <v>92.39826965332031</v>
       </c>
       <c r="D118" t="n">
-        <v>92.39828491210938</v>
+        <v>92.39826965332031</v>
       </c>
       <c r="E118" t="n">
-        <v>92.38909548945891</v>
+        <v>92.3890802321874</v>
       </c>
       <c r="F118" t="n">
-        <v>92.39828491210938</v>
+        <v>92.39826965332031</v>
       </c>
       <c r="G118" t="n">
         <v>2972000</v>
@@ -3163,16 +3163,16 @@
         <v>45463</v>
       </c>
       <c r="C119" t="n">
-        <v>92.40745544433594</v>
+        <v>92.40744781494141</v>
       </c>
       <c r="D119" t="n">
-        <v>92.41663785563358</v>
+        <v>92.41663022548092</v>
       </c>
       <c r="E119" t="n">
-        <v>92.40745544433594</v>
+        <v>92.40744781494141</v>
       </c>
       <c r="F119" t="n">
-        <v>92.40745544433594</v>
+        <v>92.40744781494141</v>
       </c>
       <c r="G119" t="n">
         <v>3580700</v>
@@ -3209,16 +3209,16 @@
         <v>45467</v>
       </c>
       <c r="C121" t="n">
-        <v>92.45337677001953</v>
+        <v>92.453369140625</v>
       </c>
       <c r="D121" t="n">
-        <v>92.46256618962263</v>
+        <v>92.46255855946977</v>
       </c>
       <c r="E121" t="n">
-        <v>92.45337677001953</v>
+        <v>92.453369140625</v>
       </c>
       <c r="F121" t="n">
-        <v>92.46256618962263</v>
+        <v>92.46255855946977</v>
       </c>
       <c r="G121" t="n">
         <v>3369500</v>
@@ -3232,16 +3232,16 @@
         <v>45468</v>
       </c>
       <c r="C122" t="n">
-        <v>92.47177886962891</v>
+        <v>92.47175598144531</v>
       </c>
       <c r="D122" t="n">
-        <v>92.47177886962891</v>
+        <v>92.47175598144531</v>
       </c>
       <c r="E122" t="n">
-        <v>92.46258944771429</v>
+        <v>92.46256656180523</v>
       </c>
       <c r="F122" t="n">
-        <v>92.47177886962891</v>
+        <v>92.47175598144531</v>
       </c>
       <c r="G122" t="n">
         <v>3561700</v>
@@ -3278,16 +3278,16 @@
         <v>45470</v>
       </c>
       <c r="C124" t="n">
-        <v>92.49014282226562</v>
+        <v>92.49011993408203</v>
       </c>
       <c r="D124" t="n">
-        <v>92.49933224339715</v>
+        <v>92.49930935293949</v>
       </c>
       <c r="E124" t="n">
-        <v>92.49014282226562</v>
+        <v>92.49011993408203</v>
       </c>
       <c r="F124" t="n">
-        <v>92.49933224339715</v>
+        <v>92.49930935293949</v>
       </c>
       <c r="G124" t="n">
         <v>3349900</v>
@@ -3301,16 +3301,16 @@
         <v>45471</v>
       </c>
       <c r="C125" t="n">
-        <v>92.52687835693359</v>
+        <v>92.52690887451172</v>
       </c>
       <c r="D125" t="n">
-        <v>92.53606777656142</v>
+        <v>92.53609829717044</v>
       </c>
       <c r="E125" t="n">
-        <v>92.52687835693359</v>
+        <v>92.52690887451172</v>
       </c>
       <c r="F125" t="n">
-        <v>92.52687835693359</v>
+        <v>92.52690887451172</v>
       </c>
       <c r="G125" t="n">
         <v>7427800</v>
@@ -3324,16 +3324,16 @@
         <v>45474</v>
       </c>
       <c r="C126" t="n">
-        <v>92.56288146972656</v>
+        <v>92.56287384033203</v>
       </c>
       <c r="D126" t="n">
-        <v>92.56288146972656</v>
+        <v>92.56287384033203</v>
       </c>
       <c r="E126" t="n">
-        <v>92.55365885608765</v>
+        <v>92.55365122745329</v>
       </c>
       <c r="F126" t="n">
-        <v>92.56288146972656</v>
+        <v>92.56287384033203</v>
       </c>
       <c r="G126" t="n">
         <v>9965300</v>
@@ -3347,16 +3347,16 @@
         <v>45475</v>
       </c>
       <c r="C127" t="n">
-        <v>92.57209014892578</v>
+        <v>92.57210540771484</v>
       </c>
       <c r="D127" t="n">
-        <v>92.57209014892578</v>
+        <v>92.57210540771484</v>
       </c>
       <c r="E127" t="n">
-        <v>92.562860497215</v>
+        <v>92.56287575448273</v>
       </c>
       <c r="F127" t="n">
-        <v>92.57209014892578</v>
+        <v>92.57210540771484</v>
       </c>
       <c r="G127" t="n">
         <v>5720900</v>
@@ -3370,16 +3370,16 @@
         <v>45476</v>
       </c>
       <c r="C128" t="n">
-        <v>92.59979248046875</v>
+        <v>92.59978485107422</v>
       </c>
       <c r="D128" t="n">
-        <v>92.59979248046875</v>
+        <v>92.59978485107422</v>
       </c>
       <c r="E128" t="n">
-        <v>92.590562826723</v>
+        <v>92.59055519808891</v>
       </c>
       <c r="F128" t="n">
-        <v>92.59979248046875</v>
+        <v>92.59978485107422</v>
       </c>
       <c r="G128" t="n">
         <v>3986000</v>
@@ -3393,16 +3393,16 @@
         <v>45478</v>
       </c>
       <c r="C129" t="n">
-        <v>92.63671112060547</v>
+        <v>92.63670349121094</v>
       </c>
       <c r="D129" t="n">
-        <v>92.63671112060547</v>
+        <v>92.63670349121094</v>
       </c>
       <c r="E129" t="n">
-        <v>92.62748146615579</v>
+        <v>92.62747383752138</v>
       </c>
       <c r="F129" t="n">
-        <v>92.62748146615579</v>
+        <v>92.62747383752138</v>
       </c>
       <c r="G129" t="n">
         <v>3742000</v>
@@ -3462,16 +3462,16 @@
         <v>45483</v>
       </c>
       <c r="C132" t="n">
-        <v>92.67361450195312</v>
+        <v>92.67362213134766</v>
       </c>
       <c r="D132" t="n">
-        <v>92.68284415558651</v>
+        <v>92.68285178574088</v>
       </c>
       <c r="E132" t="n">
-        <v>92.67361450195312</v>
+        <v>92.67362213134766</v>
       </c>
       <c r="F132" t="n">
-        <v>92.67361450195312</v>
+        <v>92.67362213134766</v>
       </c>
       <c r="G132" t="n">
         <v>4062200</v>
@@ -3485,16 +3485,16 @@
         <v>45484</v>
       </c>
       <c r="C133" t="n">
-        <v>92.69205474853516</v>
+        <v>92.69204711914062</v>
       </c>
       <c r="D133" t="n">
-        <v>92.69205474853516</v>
+        <v>92.69204711914062</v>
       </c>
       <c r="E133" t="n">
-        <v>92.68283213626073</v>
+        <v>92.6828245076253</v>
       </c>
       <c r="F133" t="n">
-        <v>92.68283213626073</v>
+        <v>92.6828245076253</v>
       </c>
       <c r="G133" t="n">
         <v>4195600</v>
@@ -3508,16 +3508,16 @@
         <v>45485</v>
       </c>
       <c r="C134" t="n">
-        <v>92.73821258544922</v>
+        <v>92.73820495605469</v>
       </c>
       <c r="D134" t="n">
-        <v>92.73821258544922</v>
+        <v>92.73820495605469</v>
       </c>
       <c r="E134" t="n">
-        <v>92.72898293135917</v>
+        <v>92.72897530272394</v>
       </c>
       <c r="F134" t="n">
-        <v>92.73821258544922</v>
+        <v>92.73820495605469</v>
       </c>
       <c r="G134" t="n">
         <v>3369000</v>
@@ -3531,16 +3531,16 @@
         <v>45488</v>
       </c>
       <c r="C135" t="n">
-        <v>92.73821258544922</v>
+        <v>92.73820495605469</v>
       </c>
       <c r="D135" t="n">
-        <v>92.74744223953927</v>
+        <v>92.74743460938542</v>
       </c>
       <c r="E135" t="n">
-        <v>92.73821258544922</v>
+        <v>92.73820495605469</v>
       </c>
       <c r="F135" t="n">
-        <v>92.74744223953927</v>
+        <v>92.74743460938542</v>
       </c>
       <c r="G135" t="n">
         <v>3615100</v>
@@ -3554,16 +3554,16 @@
         <v>45489</v>
       </c>
       <c r="C136" t="n">
-        <v>92.75666046142578</v>
+        <v>92.75664520263672</v>
       </c>
       <c r="D136" t="n">
-        <v>92.75666046142578</v>
+        <v>92.75664520263672</v>
       </c>
       <c r="E136" t="n">
-        <v>92.74743784793573</v>
+        <v>92.74742259066382</v>
       </c>
       <c r="F136" t="n">
-        <v>92.75666046142578</v>
+        <v>92.75664520263672</v>
       </c>
       <c r="G136" t="n">
         <v>3622900</v>
@@ -3577,16 +3577,16 @@
         <v>45490</v>
       </c>
       <c r="C137" t="n">
-        <v>92.76588439941406</v>
+        <v>92.76587677001953</v>
       </c>
       <c r="D137" t="n">
-        <v>92.77050274603751</v>
+        <v>92.77049511626313</v>
       </c>
       <c r="E137" t="n">
-        <v>92.75665474632972</v>
+        <v>92.75664711769426</v>
       </c>
       <c r="F137" t="n">
-        <v>92.76588439941406</v>
+        <v>92.76587677001953</v>
       </c>
       <c r="G137" t="n">
         <v>3822100</v>
@@ -3600,16 +3600,16 @@
         <v>45491</v>
       </c>
       <c r="C138" t="n">
-        <v>92.78435516357422</v>
+        <v>92.78433227539062</v>
       </c>
       <c r="D138" t="n">
-        <v>92.78435516357422</v>
+        <v>92.78433227539062</v>
       </c>
       <c r="E138" t="n">
-        <v>92.77512550935009</v>
+        <v>92.77510262344329</v>
       </c>
       <c r="F138" t="n">
-        <v>92.77512550935009</v>
+        <v>92.77510262344329</v>
       </c>
       <c r="G138" t="n">
         <v>5291400</v>
@@ -3623,16 +3623,16 @@
         <v>45492</v>
       </c>
       <c r="C139" t="n">
-        <v>92.82126617431641</v>
+        <v>92.82124328613281</v>
       </c>
       <c r="D139" t="n">
-        <v>92.82126617431641</v>
+        <v>92.82124328613281</v>
       </c>
       <c r="E139" t="n">
-        <v>92.81204355961242</v>
+        <v>92.81202067370296</v>
       </c>
       <c r="F139" t="n">
-        <v>92.82126617431641</v>
+        <v>92.82124328613281</v>
       </c>
       <c r="G139" t="n">
         <v>2993600</v>
@@ -3646,16 +3646,16 @@
         <v>45495</v>
       </c>
       <c r="C140" t="n">
-        <v>92.8397216796875</v>
+        <v>92.83969116210938</v>
       </c>
       <c r="D140" t="n">
-        <v>92.8397216796875</v>
+        <v>92.83969116210938</v>
       </c>
       <c r="E140" t="n">
-        <v>92.83049202519783</v>
+        <v>92.83046151065361</v>
       </c>
       <c r="F140" t="n">
-        <v>92.8397216796875</v>
+        <v>92.83969116210938</v>
       </c>
       <c r="G140" t="n">
         <v>3386500</v>
@@ -3715,16 +3715,16 @@
         <v>45498</v>
       </c>
       <c r="C143" t="n">
-        <v>92.87662506103516</v>
+        <v>92.87661743164062</v>
       </c>
       <c r="D143" t="n">
-        <v>92.87662506103516</v>
+        <v>92.87661743164062</v>
       </c>
       <c r="E143" t="n">
-        <v>92.86739540736002</v>
+        <v>92.86738777872365</v>
       </c>
       <c r="F143" t="n">
-        <v>92.87662506103516</v>
+        <v>92.87661743164062</v>
       </c>
       <c r="G143" t="n">
         <v>3521700</v>
@@ -3738,16 +3738,16 @@
         <v>45499</v>
       </c>
       <c r="C144" t="n">
-        <v>92.904296875</v>
+        <v>92.90431213378906</v>
       </c>
       <c r="D144" t="n">
-        <v>92.91352652767107</v>
+        <v>92.91354178797603</v>
       </c>
       <c r="E144" t="n">
-        <v>92.904296875</v>
+        <v>92.90431213378906</v>
       </c>
       <c r="F144" t="n">
-        <v>92.904296875</v>
+        <v>92.90431213378906</v>
       </c>
       <c r="G144" t="n">
         <v>3172600</v>
@@ -3761,16 +3761,16 @@
         <v>45502</v>
       </c>
       <c r="C145" t="n">
-        <v>92.93197631835938</v>
+        <v>92.93199920654297</v>
       </c>
       <c r="D145" t="n">
-        <v>92.93197631835938</v>
+        <v>92.93199920654297</v>
       </c>
       <c r="E145" t="n">
-        <v>92.92274666593407</v>
+        <v>92.9227695518445</v>
       </c>
       <c r="F145" t="n">
-        <v>92.92274666593407</v>
+        <v>92.9227695518445</v>
       </c>
       <c r="G145" t="n">
         <v>3259000</v>
@@ -3784,16 +3784,16 @@
         <v>45503</v>
       </c>
       <c r="C146" t="n">
-        <v>92.93197631835938</v>
+        <v>92.93199920654297</v>
       </c>
       <c r="D146" t="n">
-        <v>92.94120597078468</v>
+        <v>92.94122886124144</v>
       </c>
       <c r="E146" t="n">
-        <v>92.93197631835938</v>
+        <v>92.93199920654297</v>
       </c>
       <c r="F146" t="n">
-        <v>92.94120597078468</v>
+        <v>92.94122886124144</v>
       </c>
       <c r="G146" t="n">
         <v>4559900</v>
@@ -3807,16 +3807,16 @@
         <v>45504</v>
       </c>
       <c r="C147" t="n">
-        <v>92.94120788574219</v>
+        <v>92.94123077392578</v>
       </c>
       <c r="D147" t="n">
-        <v>92.95043753835766</v>
+        <v>92.9504604288142</v>
       </c>
       <c r="E147" t="n">
-        <v>92.94120788574219</v>
+        <v>92.94123077392578</v>
       </c>
       <c r="F147" t="n">
-        <v>92.94120788574219</v>
+        <v>92.94123077392578</v>
       </c>
       <c r="G147" t="n">
         <v>7256900</v>
@@ -3830,16 +3830,16 @@
         <v>45505</v>
       </c>
       <c r="C148" t="n">
-        <v>92.97177886962891</v>
+        <v>92.9718017578125</v>
       </c>
       <c r="D148" t="n">
-        <v>92.97177886962891</v>
+        <v>92.9718017578125</v>
       </c>
       <c r="E148" t="n">
-        <v>92.96250751998235</v>
+        <v>92.9625304058835</v>
       </c>
       <c r="F148" t="n">
-        <v>92.97177886962891</v>
+        <v>92.9718017578125</v>
       </c>
       <c r="G148" t="n">
         <v>11015600</v>
@@ -3876,16 +3876,16 @@
         <v>45509</v>
       </c>
       <c r="C150" t="n">
-        <v>93.02742004394531</v>
+        <v>93.02741241455078</v>
       </c>
       <c r="D150" t="n">
-        <v>93.04595567669436</v>
+        <v>93.04594804577968</v>
       </c>
       <c r="E150" t="n">
-        <v>93.01814869158591</v>
+        <v>93.01814106295174</v>
       </c>
       <c r="F150" t="n">
-        <v>93.01814869158591</v>
+        <v>93.01814106295174</v>
       </c>
       <c r="G150" t="n">
         <v>8712900</v>
@@ -3899,16 +3899,16 @@
         <v>45510</v>
       </c>
       <c r="C151" t="n">
-        <v>93.04595947265625</v>
+        <v>93.04595184326172</v>
       </c>
       <c r="D151" t="n">
-        <v>93.04595947265625</v>
+        <v>93.04595184326172</v>
       </c>
       <c r="E151" t="n">
-        <v>93.02742383915101</v>
+        <v>93.02741621127633</v>
       </c>
       <c r="F151" t="n">
-        <v>93.02742383915101</v>
+        <v>93.02741621127633</v>
       </c>
       <c r="G151" t="n">
         <v>5059100</v>
@@ -3922,16 +3922,16 @@
         <v>45511</v>
       </c>
       <c r="C152" t="n">
-        <v>93.04595947265625</v>
+        <v>93.04595184326172</v>
       </c>
       <c r="D152" t="n">
-        <v>93.05523082539389</v>
+        <v>93.05522319523915</v>
       </c>
       <c r="E152" t="n">
-        <v>93.04595947265625</v>
+        <v>93.04595184326172</v>
       </c>
       <c r="F152" t="n">
-        <v>93.04595947265625</v>
+        <v>93.04595184326172</v>
       </c>
       <c r="G152" t="n">
         <v>4611400</v>
@@ -3945,16 +3945,16 @@
         <v>45512</v>
       </c>
       <c r="C153" t="n">
-        <v>93.07377624511719</v>
+        <v>93.07376861572266</v>
       </c>
       <c r="D153" t="n">
-        <v>93.07377624511719</v>
+        <v>93.07376861572266</v>
       </c>
       <c r="E153" t="n">
-        <v>93.05523353910115</v>
+        <v>93.05522591122659</v>
       </c>
       <c r="F153" t="n">
-        <v>93.06450489210917</v>
+        <v>93.06449726347462</v>
       </c>
       <c r="G153" t="n">
         <v>3903300</v>
@@ -3968,16 +3968,16 @@
         <v>45513</v>
       </c>
       <c r="C154" t="n">
-        <v>93.10157012939453</v>
+        <v>93.1015625</v>
       </c>
       <c r="D154" t="n">
-        <v>93.11083440912847</v>
+        <v>93.11082677897475</v>
       </c>
       <c r="E154" t="n">
-        <v>93.09229877769133</v>
+        <v>93.09229114905655</v>
       </c>
       <c r="F154" t="n">
-        <v>93.10157012939453</v>
+        <v>93.1015625</v>
       </c>
       <c r="G154" t="n">
         <v>5548300</v>
@@ -3991,16 +3991,16 @@
         <v>45516</v>
       </c>
       <c r="C155" t="n">
-        <v>93.1201171875</v>
+        <v>93.12010192871094</v>
       </c>
       <c r="D155" t="n">
-        <v>93.12938854034087</v>
+        <v>93.1293732800326</v>
       </c>
       <c r="E155" t="n">
-        <v>93.11084583465912</v>
+        <v>93.11083057738928</v>
       </c>
       <c r="F155" t="n">
-        <v>93.1201171875</v>
+        <v>93.12010192871094</v>
       </c>
       <c r="G155" t="n">
         <v>3845400</v>
@@ -4014,16 +4014,16 @@
         <v>45517</v>
       </c>
       <c r="C156" t="n">
-        <v>93.138671875</v>
+        <v>93.13864898681641</v>
       </c>
       <c r="D156" t="n">
-        <v>93.138671875</v>
+        <v>93.13864898681641</v>
       </c>
       <c r="E156" t="n">
-        <v>93.1294005209664</v>
+        <v>93.12937763506119</v>
       </c>
       <c r="F156" t="n">
-        <v>93.138671875</v>
+        <v>93.13864898681641</v>
       </c>
       <c r="G156" t="n">
         <v>4782200</v>
@@ -4037,16 +4037,16 @@
         <v>45518</v>
       </c>
       <c r="C157" t="n">
-        <v>93.15718841552734</v>
+        <v>93.15720367431641</v>
       </c>
       <c r="D157" t="n">
-        <v>93.15718841552734</v>
+        <v>93.15720367431641</v>
       </c>
       <c r="E157" t="n">
-        <v>93.13865278323068</v>
+        <v>93.13866803898368</v>
       </c>
       <c r="F157" t="n">
-        <v>93.14791706339422</v>
+        <v>93.14793232066467</v>
       </c>
       <c r="G157" t="n">
         <v>4327700</v>
@@ -4060,16 +4060,16 @@
         <v>45519</v>
       </c>
       <c r="C158" t="n">
-        <v>93.16645050048828</v>
+        <v>93.16645812988281</v>
       </c>
       <c r="D158" t="n">
-        <v>93.16645050048828</v>
+        <v>93.16645812988281</v>
       </c>
       <c r="E158" t="n">
-        <v>93.14790779806644</v>
+        <v>93.14791542594251</v>
       </c>
       <c r="F158" t="n">
-        <v>93.14790779806644</v>
+        <v>93.14791542594251</v>
       </c>
       <c r="G158" t="n">
         <v>4217800</v>
@@ -4083,16 +4083,16 @@
         <v>45520</v>
       </c>
       <c r="C159" t="n">
-        <v>93.20354461669922</v>
+        <v>93.20355224609375</v>
       </c>
       <c r="D159" t="n">
-        <v>93.20354461669922</v>
+        <v>93.20355224609375</v>
       </c>
       <c r="E159" t="n">
-        <v>93.19427326391828</v>
+        <v>93.19428089255386</v>
       </c>
       <c r="F159" t="n">
-        <v>93.20354461669922</v>
+        <v>93.20355224609375</v>
       </c>
       <c r="G159" t="n">
         <v>3638900</v>
@@ -4106,16 +4106,16 @@
         <v>45523</v>
       </c>
       <c r="C160" t="n">
-        <v>93.21280670166016</v>
+        <v>93.21279907226562</v>
       </c>
       <c r="D160" t="n">
-        <v>93.22207805422271</v>
+        <v>93.22207042406932</v>
       </c>
       <c r="E160" t="n">
-        <v>93.21280670166016</v>
+        <v>93.21279907226562</v>
       </c>
       <c r="F160" t="n">
-        <v>93.21280670166016</v>
+        <v>93.21279907226562</v>
       </c>
       <c r="G160" t="n">
         <v>3930700</v>
@@ -4129,16 +4129,16 @@
         <v>45524</v>
       </c>
       <c r="C161" t="n">
-        <v>93.22209167480469</v>
+        <v>93.22208404541016</v>
       </c>
       <c r="D161" t="n">
-        <v>93.23136302872186</v>
+        <v>93.23135539856855</v>
       </c>
       <c r="E161" t="n">
-        <v>93.22209167480469</v>
+        <v>93.22208404541016</v>
       </c>
       <c r="F161" t="n">
-        <v>93.23136302872186</v>
+        <v>93.23135539856855</v>
       </c>
       <c r="G161" t="n">
         <v>3084200</v>
@@ -4152,16 +4152,16 @@
         <v>45525</v>
       </c>
       <c r="C162" t="n">
-        <v>93.24988555908203</v>
+        <v>93.2498779296875</v>
       </c>
       <c r="D162" t="n">
-        <v>93.24988555908203</v>
+        <v>93.2498779296875</v>
       </c>
       <c r="E162" t="n">
-        <v>93.23134992582368</v>
+        <v>93.23134229794566</v>
       </c>
       <c r="F162" t="n">
-        <v>93.23134992582368</v>
+        <v>93.23134229794566</v>
       </c>
       <c r="G162" t="n">
         <v>3936000</v>
@@ -4175,16 +4175,16 @@
         <v>45526</v>
       </c>
       <c r="C163" t="n">
-        <v>93.24988555908203</v>
+        <v>93.2498779296875</v>
       </c>
       <c r="D163" t="n">
-        <v>93.25915691169619</v>
+        <v>93.2591492815431</v>
       </c>
       <c r="E163" t="n">
-        <v>93.24988555908203</v>
+        <v>93.2498779296875</v>
       </c>
       <c r="F163" t="n">
-        <v>93.25915691169619</v>
+        <v>93.2591492815431</v>
       </c>
       <c r="G163" t="n">
         <v>3849100</v>
@@ -4198,16 +4198,16 @@
         <v>45527</v>
       </c>
       <c r="C164" t="n">
-        <v>93.28697204589844</v>
+        <v>93.28696441650391</v>
       </c>
       <c r="D164" t="n">
-        <v>93.29624339932242</v>
+        <v>93.29623576916964</v>
       </c>
       <c r="E164" t="n">
-        <v>93.28697204589844</v>
+        <v>93.28696441650391</v>
       </c>
       <c r="F164" t="n">
-        <v>93.29624339932242</v>
+        <v>93.29623576916964</v>
       </c>
       <c r="G164" t="n">
         <v>3549900</v>
@@ -4221,16 +4221,16 @@
         <v>45530</v>
       </c>
       <c r="C165" t="n">
-        <v>93.30547332763672</v>
+        <v>93.30549621582031</v>
       </c>
       <c r="D165" t="n">
-        <v>93.31473760497704</v>
+        <v>93.31476049543321</v>
       </c>
       <c r="E165" t="n">
-        <v>93.30547332763672</v>
+        <v>93.30549621582031</v>
       </c>
       <c r="F165" t="n">
-        <v>93.30547332763672</v>
+        <v>93.30549621582031</v>
       </c>
       <c r="G165" t="n">
         <v>3969000</v>
@@ -4244,16 +4244,16 @@
         <v>45531</v>
       </c>
       <c r="C166" t="n">
-        <v>93.31477355957031</v>
+        <v>93.31478118896484</v>
       </c>
       <c r="D166" t="n">
-        <v>93.32404491245036</v>
+        <v>93.32405254260293</v>
       </c>
       <c r="E166" t="n">
-        <v>93.31477355957031</v>
+        <v>93.31478118896484</v>
       </c>
       <c r="F166" t="n">
-        <v>93.32404491245036</v>
+        <v>93.32405254260293</v>
       </c>
       <c r="G166" t="n">
         <v>2818100</v>
@@ -4267,16 +4267,16 @@
         <v>45532</v>
       </c>
       <c r="C167" t="n">
-        <v>93.32402801513672</v>
+        <v>93.32404327392578</v>
       </c>
       <c r="D167" t="n">
-        <v>93.33329936633808</v>
+        <v>93.33331462664304</v>
       </c>
       <c r="E167" t="n">
-        <v>93.32402801513672</v>
+        <v>93.32404327392578</v>
       </c>
       <c r="F167" t="n">
-        <v>93.33329936633808</v>
+        <v>93.33331462664304</v>
       </c>
       <c r="G167" t="n">
         <v>3500800</v>
@@ -4290,16 +4290,16 @@
         <v>45533</v>
       </c>
       <c r="C168" t="n">
-        <v>93.33329010009766</v>
+        <v>93.33330535888672</v>
       </c>
       <c r="D168" t="n">
-        <v>93.35182572869128</v>
+        <v>93.35184099051068</v>
       </c>
       <c r="E168" t="n">
-        <v>93.33329010009766</v>
+        <v>93.33330535888672</v>
       </c>
       <c r="F168" t="n">
-        <v>93.34255437841038</v>
+        <v>93.34256963871402</v>
       </c>
       <c r="G168" t="n">
         <v>4537700</v>
@@ -4313,16 +4313,16 @@
         <v>45534</v>
       </c>
       <c r="C169" t="n">
-        <v>93.37966918945312</v>
+        <v>93.37966156005859</v>
       </c>
       <c r="D169" t="n">
-        <v>93.3889405433562</v>
+        <v>93.38893291320416</v>
       </c>
       <c r="E169" t="n">
-        <v>93.37966918945312</v>
+        <v>93.37966156005859</v>
       </c>
       <c r="F169" t="n">
-        <v>93.37966918945312</v>
+        <v>93.37966156005859</v>
       </c>
       <c r="G169" t="n">
         <v>8427400</v>
@@ -4336,16 +4336,16 @@
         <v>45538</v>
       </c>
       <c r="C170" t="n">
-        <v>93.42062377929688</v>
+        <v>93.42061614990234</v>
       </c>
       <c r="D170" t="n">
-        <v>93.42062377929688</v>
+        <v>93.42061614990234</v>
       </c>
       <c r="E170" t="n">
-        <v>93.41131848632243</v>
+        <v>93.41131085768782</v>
       </c>
       <c r="F170" t="n">
-        <v>93.42062377929688</v>
+        <v>93.42061614990234</v>
       </c>
       <c r="G170" t="n">
         <v>11846700</v>
@@ -4359,16 +4359,16 @@
         <v>45539</v>
       </c>
       <c r="C171" t="n">
-        <v>93.429931640625</v>
+        <v>93.42992401123047</v>
       </c>
       <c r="D171" t="n">
-        <v>93.43924403642453</v>
+        <v>93.43923640626956</v>
       </c>
       <c r="E171" t="n">
-        <v>93.429931640625</v>
+        <v>93.42992401123047</v>
       </c>
       <c r="F171" t="n">
-        <v>93.43924403642453</v>
+        <v>93.43923640626956</v>
       </c>
       <c r="G171" t="n">
         <v>7218300</v>
@@ -4428,16 +4428,16 @@
         <v>45544</v>
       </c>
       <c r="C174" t="n">
-        <v>93.50440979003906</v>
+        <v>93.50443267822266</v>
       </c>
       <c r="D174" t="n">
-        <v>93.51372218516032</v>
+        <v>93.51374507562342</v>
       </c>
       <c r="E174" t="n">
-        <v>93.50440979003906</v>
+        <v>93.50443267822266</v>
       </c>
       <c r="F174" t="n">
-        <v>93.50440979003906</v>
+        <v>93.50443267822266</v>
       </c>
       <c r="G174" t="n">
         <v>5397400</v>
@@ -4451,16 +4451,16 @@
         <v>45545</v>
       </c>
       <c r="C175" t="n">
-        <v>93.52302551269531</v>
+        <v>93.52303314208984</v>
       </c>
       <c r="D175" t="n">
-        <v>93.52302551269531</v>
+        <v>93.52303314208984</v>
       </c>
       <c r="E175" t="n">
-        <v>93.50440782612006</v>
+        <v>93.50441545399579</v>
       </c>
       <c r="F175" t="n">
-        <v>93.52302551269531</v>
+        <v>93.52303314208984</v>
       </c>
       <c r="G175" t="n">
         <v>4143900</v>
@@ -4474,16 +4474,16 @@
         <v>45546</v>
       </c>
       <c r="C176" t="n">
-        <v>93.52302551269531</v>
+        <v>93.52303314208984</v>
       </c>
       <c r="D176" t="n">
-        <v>93.53233790762097</v>
+        <v>93.53234553777519</v>
       </c>
       <c r="E176" t="n">
-        <v>93.52302551269531</v>
+        <v>93.52303314208984</v>
       </c>
       <c r="F176" t="n">
-        <v>93.52302551269531</v>
+        <v>93.52303314208984</v>
       </c>
       <c r="G176" t="n">
         <v>4500100</v>
@@ -4497,16 +4497,16 @@
         <v>45547</v>
       </c>
       <c r="C177" t="n">
-        <v>93.5323486328125</v>
+        <v>93.53234100341797</v>
       </c>
       <c r="D177" t="n">
-        <v>93.541661028806</v>
+        <v>93.54165339865186</v>
       </c>
       <c r="E177" t="n">
-        <v>93.5323486328125</v>
+        <v>93.53234100341797</v>
       </c>
       <c r="F177" t="n">
-        <v>93.541661028806</v>
+        <v>93.54165339865186</v>
       </c>
       <c r="G177" t="n">
         <v>3912400</v>
@@ -4520,16 +4520,16 @@
         <v>45548</v>
       </c>
       <c r="C178" t="n">
-        <v>93.58821105957031</v>
+        <v>93.58818817138672</v>
       </c>
       <c r="D178" t="n">
-        <v>93.58821105957031</v>
+        <v>93.58818817138672</v>
       </c>
       <c r="E178" t="n">
-        <v>93.56959337041114</v>
+        <v>93.56957048678073</v>
       </c>
       <c r="F178" t="n">
-        <v>93.56959337041114</v>
+        <v>93.56957048678073</v>
       </c>
       <c r="G178" t="n">
         <v>3465200</v>
@@ -4543,16 +4543,16 @@
         <v>45551</v>
       </c>
       <c r="C179" t="n">
-        <v>93.60681915283203</v>
+        <v>93.60684204101562</v>
       </c>
       <c r="D179" t="n">
-        <v>93.60681915283203</v>
+        <v>93.60684204101562</v>
       </c>
       <c r="E179" t="n">
-        <v>93.58819436371842</v>
+        <v>93.58821724734798</v>
       </c>
       <c r="F179" t="n">
-        <v>93.58819436371842</v>
+        <v>93.58821724734798</v>
       </c>
       <c r="G179" t="n">
         <v>3571100</v>
@@ -4566,16 +4566,16 @@
         <v>45552</v>
       </c>
       <c r="C180" t="n">
-        <v>93.60681915283203</v>
+        <v>93.60684204101562</v>
       </c>
       <c r="D180" t="n">
-        <v>93.62543683866987</v>
+        <v>93.62545973140574</v>
       </c>
       <c r="E180" t="n">
-        <v>93.60681915283203</v>
+        <v>93.60684204101562</v>
       </c>
       <c r="F180" t="n">
-        <v>93.61613154738885</v>
+        <v>93.61615443784945</v>
       </c>
       <c r="G180" t="n">
         <v>4452200</v>
@@ -4589,16 +4589,16 @@
         <v>45553</v>
       </c>
       <c r="C181" t="n">
-        <v>93.63477325439453</v>
+        <v>93.634765625</v>
       </c>
       <c r="D181" t="n">
-        <v>93.64408565134035</v>
+        <v>93.64407802118704</v>
       </c>
       <c r="E181" t="n">
-        <v>93.6254608574487</v>
+        <v>93.62545322881296</v>
       </c>
       <c r="F181" t="n">
-        <v>93.6254608574487</v>
+        <v>93.62545322881296</v>
       </c>
       <c r="G181" t="n">
         <v>4077700</v>
@@ -4612,16 +4612,16 @@
         <v>45554</v>
       </c>
       <c r="C182" t="n">
-        <v>93.65339660644531</v>
+        <v>93.65338134765625</v>
       </c>
       <c r="D182" t="n">
-        <v>93.66270900395408</v>
+        <v>93.66269374364776</v>
       </c>
       <c r="E182" t="n">
-        <v>93.64409131221458</v>
+        <v>93.64407605494162</v>
       </c>
       <c r="F182" t="n">
-        <v>93.64409131221458</v>
+        <v>93.64407605494162</v>
       </c>
       <c r="G182" t="n">
         <v>5165800</v>
@@ -4635,16 +4635,16 @@
         <v>45555</v>
       </c>
       <c r="C183" t="n">
-        <v>93.69061279296875</v>
+        <v>93.69062805175781</v>
       </c>
       <c r="D183" t="n">
-        <v>93.6999251878634</v>
+        <v>93.69994044816912</v>
       </c>
       <c r="E183" t="n">
-        <v>93.69061279296875</v>
+        <v>93.69062805175781</v>
       </c>
       <c r="F183" t="n">
-        <v>93.6999251878634</v>
+        <v>93.69994044816912</v>
       </c>
       <c r="G183" t="n">
         <v>4244800</v>
@@ -4658,16 +4658,16 @@
         <v>45558</v>
       </c>
       <c r="C184" t="n">
-        <v>93.71853637695312</v>
+        <v>93.71855926513672</v>
       </c>
       <c r="D184" t="n">
-        <v>93.71853637695312</v>
+        <v>93.71855926513672</v>
       </c>
       <c r="E184" t="n">
-        <v>93.6999115898667</v>
+        <v>93.6999344735017</v>
       </c>
       <c r="F184" t="n">
-        <v>93.70922398340991</v>
+        <v>93.70924686931922</v>
       </c>
       <c r="G184" t="n">
         <v>5220900</v>
@@ -4681,16 +4681,16 @@
         <v>45559</v>
       </c>
       <c r="C185" t="n">
-        <v>93.72786712646484</v>
+        <v>93.72787475585938</v>
       </c>
       <c r="D185" t="n">
-        <v>93.72786712646484</v>
+        <v>93.72787475585938</v>
       </c>
       <c r="E185" t="n">
-        <v>93.71856183366906</v>
+        <v>93.71856946230614</v>
       </c>
       <c r="F185" t="n">
-        <v>93.71856183366906</v>
+        <v>93.71856946230614</v>
       </c>
       <c r="G185" t="n">
         <v>3923500</v>
@@ -4704,16 +4704,16 @@
         <v>45560</v>
       </c>
       <c r="C186" t="n">
-        <v>93.72786712646484</v>
+        <v>93.72787475585938</v>
       </c>
       <c r="D186" t="n">
-        <v>93.7464919186103</v>
+        <v>93.74649954952088</v>
       </c>
       <c r="E186" t="n">
-        <v>93.72786712646484</v>
+        <v>93.72787475585938</v>
       </c>
       <c r="F186" t="n">
-        <v>93.73717952253757</v>
+        <v>93.73718715269013</v>
       </c>
       <c r="G186" t="n">
         <v>3372400</v>
@@ -4727,16 +4727,16 @@
         <v>45561</v>
       </c>
       <c r="C187" t="n">
-        <v>93.73715972900391</v>
+        <v>93.73719024658203</v>
       </c>
       <c r="D187" t="n">
-        <v>93.74647212311024</v>
+        <v>93.74650264372015</v>
       </c>
       <c r="E187" t="n">
-        <v>93.73715972900391</v>
+        <v>93.73719024658203</v>
       </c>
       <c r="F187" t="n">
-        <v>93.73715972900391</v>
+        <v>93.73719024658203</v>
       </c>
       <c r="G187" t="n">
         <v>4364400</v>
@@ -4750,16 +4750,16 @@
         <v>45562</v>
       </c>
       <c r="C188" t="n">
-        <v>93.77442169189453</v>
+        <v>93.77442932128906</v>
       </c>
       <c r="D188" t="n">
-        <v>93.78373408793631</v>
+        <v>93.78374171808849</v>
       </c>
       <c r="E188" t="n">
-        <v>93.77442169189453</v>
+        <v>93.77442932128906</v>
       </c>
       <c r="F188" t="n">
-        <v>93.77442169189453</v>
+        <v>93.77442932128906</v>
       </c>
       <c r="G188" t="n">
         <v>4945400</v>
@@ -4773,16 +4773,16 @@
         <v>45565</v>
       </c>
       <c r="C189" t="n">
-        <v>93.77442169189453</v>
+        <v>93.77442932128906</v>
       </c>
       <c r="D189" t="n">
-        <v>93.79303938070117</v>
+        <v>93.79304701161043</v>
       </c>
       <c r="E189" t="n">
-        <v>93.77442169189453</v>
+        <v>93.77442932128906</v>
       </c>
       <c r="F189" t="n">
-        <v>93.78373408793631</v>
+        <v>93.78374171808849</v>
       </c>
       <c r="G189" t="n">
         <v>9253100</v>
@@ -4842,16 +4842,16 @@
         <v>45568</v>
       </c>
       <c r="C192" t="n">
-        <v>93.82115936279297</v>
+        <v>93.82115173339844</v>
       </c>
       <c r="D192" t="n">
-        <v>93.83051168541103</v>
+        <v>93.83050405525599</v>
       </c>
       <c r="E192" t="n">
-        <v>93.82115936279297</v>
+        <v>93.82115173339844</v>
       </c>
       <c r="F192" t="n">
-        <v>93.83051168541103</v>
+        <v>93.83050405525599</v>
       </c>
       <c r="G192" t="n">
         <v>4066100</v>
@@ -4865,16 +4865,16 @@
         <v>45569</v>
       </c>
       <c r="C193" t="n">
-        <v>93.85856628417969</v>
+        <v>93.85858917236328</v>
       </c>
       <c r="D193" t="n">
-        <v>93.86791860727251</v>
+        <v>93.86794149773675</v>
       </c>
       <c r="E193" t="n">
-        <v>93.85856628417969</v>
+        <v>93.85858917236328</v>
       </c>
       <c r="F193" t="n">
-        <v>93.86324601259227</v>
+        <v>93.86326890191705</v>
       </c>
       <c r="G193" t="n">
         <v>4987100</v>
@@ -4888,16 +4888,16 @@
         <v>45572</v>
       </c>
       <c r="C194" t="n">
-        <v>93.86793518066406</v>
+        <v>93.86790466308594</v>
       </c>
       <c r="D194" t="n">
-        <v>93.87728750540813</v>
+        <v>93.87725698478947</v>
       </c>
       <c r="E194" t="n">
-        <v>93.86793518066406</v>
+        <v>93.86790466308594</v>
       </c>
       <c r="F194" t="n">
-        <v>93.86793518066406</v>
+        <v>93.86790466308594</v>
       </c>
       <c r="G194" t="n">
         <v>4792500</v>
@@ -4911,16 +4911,16 @@
         <v>45573</v>
       </c>
       <c r="C195" t="n">
-        <v>93.87728118896484</v>
+        <v>93.87726593017578</v>
       </c>
       <c r="D195" t="n">
-        <v>93.88663351307966</v>
+        <v>93.88661825277048</v>
       </c>
       <c r="E195" t="n">
-        <v>93.87728118896484</v>
+        <v>93.87726593017578</v>
       </c>
       <c r="F195" t="n">
-        <v>93.87728118896484</v>
+        <v>93.87726593017578</v>
       </c>
       <c r="G195" t="n">
         <v>3923100</v>
@@ -4934,16 +4934,16 @@
         <v>45574</v>
       </c>
       <c r="C196" t="n">
-        <v>93.89596557617188</v>
+        <v>93.89595794677734</v>
       </c>
       <c r="D196" t="n">
-        <v>93.90531789897918</v>
+        <v>93.90531026882472</v>
       </c>
       <c r="E196" t="n">
-        <v>93.8866203870967</v>
+        <v>93.8866127584615</v>
       </c>
       <c r="F196" t="n">
-        <v>93.89596557617188</v>
+        <v>93.89595794677734</v>
       </c>
       <c r="G196" t="n">
         <v>4024800</v>
@@ -4957,16 +4957,16 @@
         <v>45575</v>
       </c>
       <c r="C197" t="n">
-        <v>93.91465759277344</v>
+        <v>93.91468048095703</v>
       </c>
       <c r="D197" t="n">
-        <v>93.91465759277344</v>
+        <v>93.91468048095703</v>
       </c>
       <c r="E197" t="n">
-        <v>93.90530527122378</v>
+        <v>93.9053281571281</v>
       </c>
       <c r="F197" t="n">
-        <v>93.91465759277344</v>
+        <v>93.91468048095703</v>
       </c>
       <c r="G197" t="n">
         <v>3731100</v>
@@ -4980,16 +4980,16 @@
         <v>45576</v>
       </c>
       <c r="C198" t="n">
-        <v>93.95209503173828</v>
+        <v>93.95207214355469</v>
       </c>
       <c r="D198" t="n">
-        <v>93.96144022306665</v>
+        <v>93.96141733260642</v>
       </c>
       <c r="E198" t="n">
-        <v>93.95209503173828</v>
+        <v>93.95207214355469</v>
       </c>
       <c r="F198" t="n">
-        <v>93.95209503173828</v>
+        <v>93.95207214355469</v>
       </c>
       <c r="G198" t="n">
         <v>3778400</v>
@@ -5003,16 +5003,16 @@
         <v>45579</v>
       </c>
       <c r="C199" t="n">
-        <v>93.95209503173828</v>
+        <v>93.95207214355469</v>
       </c>
       <c r="D199" t="n">
-        <v>93.96144022306665</v>
+        <v>93.96141733260642</v>
       </c>
       <c r="E199" t="n">
-        <v>93.95209503173828</v>
+        <v>93.95207214355469</v>
       </c>
       <c r="F199" t="n">
-        <v>93.95209503173828</v>
+        <v>93.95207214355469</v>
       </c>
       <c r="G199" t="n">
         <v>3297100</v>
@@ -5026,16 +5026,16 @@
         <v>45580</v>
       </c>
       <c r="C200" t="n">
-        <v>93.97076416015625</v>
+        <v>93.97077178955078</v>
       </c>
       <c r="D200" t="n">
-        <v>93.97076416015625</v>
+        <v>93.97077178955078</v>
       </c>
       <c r="E200" t="n">
-        <v>93.96141183791931</v>
+        <v>93.96141946655455</v>
       </c>
       <c r="F200" t="n">
-        <v>93.97076416015625</v>
+        <v>93.97077178955078</v>
       </c>
       <c r="G200" t="n">
         <v>3567400</v>
@@ -5095,16 +5095,16 @@
         <v>45583</v>
       </c>
       <c r="C203" t="n">
-        <v>94.02687835693359</v>
+        <v>94.02685546875</v>
       </c>
       <c r="D203" t="n">
-        <v>94.03623068061582</v>
+        <v>94.03620779015567</v>
       </c>
       <c r="E203" t="n">
-        <v>94.01753316698415</v>
+        <v>94.01751028107537</v>
       </c>
       <c r="F203" t="n">
-        <v>94.03623068061582</v>
+        <v>94.03620779015567</v>
       </c>
       <c r="G203" t="n">
         <v>3970200</v>
@@ -5118,16 +5118,16 @@
         <v>45586</v>
       </c>
       <c r="C204" t="n">
-        <v>94.04557800292969</v>
+        <v>94.04556274414062</v>
       </c>
       <c r="D204" t="n">
-        <v>94.04557800292969</v>
+        <v>94.04556274414062</v>
       </c>
       <c r="E204" t="n">
-        <v>94.03622567974483</v>
+        <v>94.03621042247316</v>
       </c>
       <c r="F204" t="n">
-        <v>94.03622567974483</v>
+        <v>94.03621042247316</v>
       </c>
       <c r="G204" t="n">
         <v>3940600</v>
@@ -5141,16 +5141,16 @@
         <v>45587</v>
       </c>
       <c r="C205" t="n">
-        <v>94.054931640625</v>
+        <v>94.05492401123047</v>
       </c>
       <c r="D205" t="n">
-        <v>94.054931640625</v>
+        <v>94.05492401123047</v>
       </c>
       <c r="E205" t="n">
-        <v>94.04558645033313</v>
+        <v>94.04557882169665</v>
       </c>
       <c r="F205" t="n">
-        <v>94.054931640625</v>
+        <v>94.05492401123047</v>
       </c>
       <c r="G205" t="n">
         <v>3462800</v>
@@ -5164,16 +5164,16 @@
         <v>45588</v>
       </c>
       <c r="C206" t="n">
-        <v>94.054931640625</v>
+        <v>94.05492401123047</v>
       </c>
       <c r="D206" t="n">
-        <v>94.07363628867482</v>
+        <v>94.07362865776304</v>
       </c>
       <c r="E206" t="n">
-        <v>94.054931640625</v>
+        <v>94.05492401123047</v>
       </c>
       <c r="F206" t="n">
-        <v>94.07363628867482</v>
+        <v>94.07362865776304</v>
       </c>
       <c r="G206" t="n">
         <v>3927700</v>
@@ -5187,16 +5187,16 @@
         <v>45589</v>
       </c>
       <c r="C207" t="n">
-        <v>94.08296966552734</v>
+        <v>94.08298492431641</v>
       </c>
       <c r="D207" t="n">
-        <v>94.08296966552734</v>
+        <v>94.08298492431641</v>
       </c>
       <c r="E207" t="n">
-        <v>94.07361734338588</v>
+        <v>94.07363260065813</v>
       </c>
       <c r="F207" t="n">
-        <v>94.08296966552734</v>
+        <v>94.08298492431641</v>
       </c>
       <c r="G207" t="n">
         <v>3704500</v>
@@ -5210,16 +5210,16 @@
         <v>45590</v>
       </c>
       <c r="C208" t="n">
-        <v>94.12036895751953</v>
+        <v>94.12039184570312</v>
       </c>
       <c r="D208" t="n">
-        <v>94.12036895751953</v>
+        <v>94.12039184570312</v>
       </c>
       <c r="E208" t="n">
-        <v>94.11101663566252</v>
+        <v>94.11103952157183</v>
       </c>
       <c r="F208" t="n">
-        <v>94.11101663566252</v>
+        <v>94.11103952157183</v>
       </c>
       <c r="G208" t="n">
         <v>5386900</v>
@@ -5233,16 +5233,16 @@
         <v>45593</v>
       </c>
       <c r="C209" t="n">
-        <v>94.12036895751953</v>
+        <v>94.12039184570312</v>
       </c>
       <c r="D209" t="n">
-        <v>94.12971414564514</v>
+        <v>94.12973703610129</v>
       </c>
       <c r="E209" t="n">
-        <v>94.12036895751953</v>
+        <v>94.12039184570312</v>
       </c>
       <c r="F209" t="n">
-        <v>94.12971414564514</v>
+        <v>94.12973703610129</v>
       </c>
       <c r="G209" t="n">
         <v>3471300</v>
@@ -5256,16 +5256,16 @@
         <v>45594</v>
       </c>
       <c r="C210" t="n">
-        <v>94.13906860351562</v>
+        <v>94.13909149169922</v>
       </c>
       <c r="D210" t="n">
-        <v>94.13906860351562</v>
+        <v>94.13909149169922</v>
       </c>
       <c r="E210" t="n">
-        <v>94.1250436872776</v>
+        <v>94.1250665720513</v>
       </c>
       <c r="F210" t="n">
-        <v>94.12971628144642</v>
+        <v>94.12973916735616</v>
       </c>
       <c r="G210" t="n">
         <v>3449900</v>
@@ -5279,16 +5279,16 @@
         <v>45595</v>
       </c>
       <c r="C211" t="n">
-        <v>94.13906860351562</v>
+        <v>94.13909149169922</v>
       </c>
       <c r="D211" t="n">
-        <v>94.15776611392248</v>
+        <v>94.15778900665204</v>
       </c>
       <c r="E211" t="n">
-        <v>94.13906860351562</v>
+        <v>94.13909149169922</v>
       </c>
       <c r="F211" t="n">
-        <v>94.14842092558483</v>
+        <v>94.14844381604227</v>
       </c>
       <c r="G211" t="n">
         <v>7059200</v>
@@ -5302,16 +5302,16 @@
         <v>45596</v>
       </c>
       <c r="C212" t="n">
-        <v>94.15776824951172</v>
+        <v>94.15777587890625</v>
       </c>
       <c r="D212" t="n">
-        <v>94.16712057179303</v>
+        <v>94.16712820194537</v>
       </c>
       <c r="E212" t="n">
-        <v>94.1484230609621</v>
+        <v>94.14843068959942</v>
       </c>
       <c r="F212" t="n">
-        <v>94.1484230609621</v>
+        <v>94.14843068959942</v>
       </c>
       <c r="G212" t="n">
         <v>11321100</v>
@@ -5348,16 +5348,16 @@
         <v>45600</v>
       </c>
       <c r="C214" t="n">
-        <v>94.21881103515625</v>
+        <v>94.21878814697266</v>
       </c>
       <c r="D214" t="n">
-        <v>94.22726367433162</v>
+        <v>94.22724078409466</v>
       </c>
       <c r="E214" t="n">
-        <v>94.20942000976736</v>
+        <v>94.20939712386507</v>
       </c>
       <c r="F214" t="n">
-        <v>94.21881103515625</v>
+        <v>94.21878814697266</v>
       </c>
       <c r="G214" t="n">
         <v>5041500</v>
@@ -5417,16 +5417,16 @@
         <v>45603</v>
       </c>
       <c r="C217" t="n">
-        <v>94.25637054443359</v>
+        <v>94.25636291503906</v>
       </c>
       <c r="D217" t="n">
-        <v>94.25637054443359</v>
+        <v>94.25636291503906</v>
       </c>
       <c r="E217" t="n">
-        <v>94.24697951878854</v>
+        <v>94.24697189015416</v>
       </c>
       <c r="F217" t="n">
-        <v>94.24697951878854</v>
+        <v>94.24697189015416</v>
       </c>
       <c r="G217" t="n">
         <v>6188100</v>
@@ -5440,16 +5440,16 @@
         <v>45604</v>
       </c>
       <c r="C218" t="n">
-        <v>94.30329895019531</v>
+        <v>94.30331420898438</v>
       </c>
       <c r="D218" t="n">
-        <v>94.30329895019531</v>
+        <v>94.30331420898438</v>
       </c>
       <c r="E218" t="n">
-        <v>94.28451690280075</v>
+        <v>94.28453215855077</v>
       </c>
       <c r="F218" t="n">
-        <v>94.29390792649804</v>
+        <v>94.29392318376757</v>
       </c>
       <c r="G218" t="n">
         <v>5624200</v>
@@ -5463,16 +5463,16 @@
         <v>45607</v>
       </c>
       <c r="C219" t="n">
-        <v>94.29391479492188</v>
+        <v>94.29390716552734</v>
       </c>
       <c r="D219" t="n">
-        <v>94.3033058193032</v>
+        <v>94.30329818914883</v>
       </c>
       <c r="E219" t="n">
-        <v>94.2892228643576</v>
+        <v>94.28921523534268</v>
       </c>
       <c r="F219" t="n">
-        <v>94.29391479492188</v>
+        <v>94.29390716552734</v>
       </c>
       <c r="G219" t="n">
         <v>4443700</v>
@@ -5486,16 +5486,16 @@
         <v>45608</v>
       </c>
       <c r="C220" t="n">
-        <v>94.30329895019531</v>
+        <v>94.30331420898438</v>
       </c>
       <c r="D220" t="n">
-        <v>94.31268281064035</v>
+        <v>94.31269807094777</v>
       </c>
       <c r="E220" t="n">
-        <v>94.30329895019531</v>
+        <v>94.30331420898438</v>
       </c>
       <c r="F220" t="n">
-        <v>94.31268281064035</v>
+        <v>94.31269807094777</v>
       </c>
       <c r="G220" t="n">
         <v>4283300</v>
@@ -5509,16 +5509,16 @@
         <v>45609</v>
       </c>
       <c r="C221" t="n">
-        <v>94.33145904541016</v>
+        <v>94.33148956298828</v>
       </c>
       <c r="D221" t="n">
-        <v>94.33145904541016</v>
+        <v>94.33148956298828</v>
       </c>
       <c r="E221" t="n">
-        <v>94.31267699917292</v>
+        <v>94.31270751067478</v>
       </c>
       <c r="F221" t="n">
-        <v>94.32206802229155</v>
+        <v>94.32209853683153</v>
       </c>
       <c r="G221" t="n">
         <v>4818000</v>
@@ -5532,16 +5532,16 @@
         <v>45610</v>
       </c>
       <c r="C222" t="n">
-        <v>94.33145904541016</v>
+        <v>94.33148956298828</v>
       </c>
       <c r="D222" t="n">
-        <v>94.34085006852878</v>
+        <v>94.34088058914503</v>
       </c>
       <c r="E222" t="n">
-        <v>94.33145904541016</v>
+        <v>94.33148956298828</v>
       </c>
       <c r="F222" t="n">
-        <v>94.34085006852878</v>
+        <v>94.34088058914503</v>
       </c>
       <c r="G222" t="n">
         <v>4353200</v>
@@ -5578,16 +5578,16 @@
         <v>45614</v>
       </c>
       <c r="C224" t="n">
-        <v>94.38780212402344</v>
+        <v>94.38782501220703</v>
       </c>
       <c r="D224" t="n">
-        <v>94.38780212402344</v>
+        <v>94.38782501220703</v>
       </c>
       <c r="E224" t="n">
-        <v>94.37841109978388</v>
+        <v>94.37843398569024</v>
       </c>
       <c r="F224" t="n">
-        <v>94.38780212402344</v>
+        <v>94.38782501220703</v>
       </c>
       <c r="G224" t="n">
         <v>5567500</v>
@@ -5601,16 +5601,16 @@
         <v>45615</v>
       </c>
       <c r="C225" t="n">
-        <v>94.39717864990234</v>
+        <v>94.39718627929688</v>
       </c>
       <c r="D225" t="n">
-        <v>94.39717864990234</v>
+        <v>94.39718627929688</v>
       </c>
       <c r="E225" t="n">
-        <v>94.38778762710514</v>
+        <v>94.38779525574067</v>
       </c>
       <c r="F225" t="n">
-        <v>94.39717864990234</v>
+        <v>94.39718627929688</v>
       </c>
       <c r="G225" t="n">
         <v>4310900</v>
@@ -5624,16 +5624,16 @@
         <v>45616</v>
       </c>
       <c r="C226" t="n">
-        <v>94.41598510742188</v>
+        <v>94.41595458984375</v>
       </c>
       <c r="D226" t="n">
-        <v>94.41598510742188</v>
+        <v>94.41595458984375</v>
       </c>
       <c r="E226" t="n">
-        <v>94.39721021880021</v>
+        <v>94.3971797072906</v>
       </c>
       <c r="F226" t="n">
-        <v>94.40660124473803</v>
+        <v>94.406570730193</v>
       </c>
       <c r="G226" t="n">
         <v>4133000</v>
@@ -5647,16 +5647,16 @@
         <v>45617</v>
       </c>
       <c r="C227" t="n">
-        <v>94.41598510742188</v>
+        <v>94.41595458984375</v>
       </c>
       <c r="D227" t="n">
-        <v>94.42537613335968</v>
+        <v>94.42534561274614</v>
       </c>
       <c r="E227" t="n">
-        <v>94.41598510742188</v>
+        <v>94.41595458984375</v>
       </c>
       <c r="F227" t="n">
-        <v>94.42537613335968</v>
+        <v>94.42534561274614</v>
       </c>
       <c r="G227" t="n">
         <v>4410700</v>
@@ -5670,16 +5670,16 @@
         <v>45618</v>
       </c>
       <c r="C228" t="n">
-        <v>94.44414520263672</v>
+        <v>94.44412994384766</v>
       </c>
       <c r="D228" t="n">
-        <v>94.45353622799588</v>
+        <v>94.45352096768957</v>
       </c>
       <c r="E228" t="n">
-        <v>94.44414520263672</v>
+        <v>94.44412994384766</v>
       </c>
       <c r="F228" t="n">
-        <v>94.44414520263672</v>
+        <v>94.44412994384766</v>
       </c>
       <c r="G228" t="n">
         <v>4343900</v>
@@ -5693,16 +5693,16 @@
         <v>45621</v>
       </c>
       <c r="C229" t="n">
-        <v>94.45352935791016</v>
+        <v>94.45352172851562</v>
       </c>
       <c r="D229" t="n">
-        <v>94.46292038258626</v>
+        <v>94.46291275243318</v>
       </c>
       <c r="E229" t="n">
-        <v>94.45352935791016</v>
+        <v>94.45352172851562</v>
       </c>
       <c r="F229" t="n">
-        <v>94.45352935791016</v>
+        <v>94.45352172851562</v>
       </c>
       <c r="G229" t="n">
         <v>6020200</v>
@@ -5716,16 +5716,16 @@
         <v>45622</v>
       </c>
       <c r="C230" t="n">
-        <v>94.47231292724609</v>
+        <v>94.47230529785156</v>
       </c>
       <c r="D230" t="n">
-        <v>94.48169678882019</v>
+        <v>94.48168915866783</v>
       </c>
       <c r="E230" t="n">
-        <v>94.4629219024189</v>
+        <v>94.46291427378277</v>
       </c>
       <c r="F230" t="n">
-        <v>94.47231292724609</v>
+        <v>94.47230529785156</v>
       </c>
       <c r="G230" t="n">
         <v>4586900</v>
@@ -5739,16 +5739,16 @@
         <v>45623</v>
       </c>
       <c r="C231" t="n">
-        <v>94.49109649658203</v>
+        <v>94.4910888671875</v>
       </c>
       <c r="D231" t="n">
-        <v>94.50048752227218</v>
+        <v>94.5004798921194</v>
       </c>
       <c r="E231" t="n">
-        <v>94.49109649658203</v>
+        <v>94.4910888671875</v>
       </c>
       <c r="F231" t="n">
-        <v>94.49109649658203</v>
+        <v>94.4910888671875</v>
       </c>
       <c r="G231" t="n">
         <v>5909000</v>
@@ -5762,16 +5762,16 @@
         <v>45625</v>
       </c>
       <c r="C232" t="n">
-        <v>94.52862548828125</v>
+        <v>94.52866363525391</v>
       </c>
       <c r="D232" t="n">
-        <v>94.5380165111949</v>
+        <v>94.5380546619573</v>
       </c>
       <c r="E232" t="n">
-        <v>94.52862548828125</v>
+        <v>94.52866363525391</v>
       </c>
       <c r="F232" t="n">
-        <v>94.52862548828125</v>
+        <v>94.52866363525391</v>
       </c>
       <c r="G232" t="n">
         <v>6581100</v>
@@ -5785,16 +5785,16 @@
         <v>45628</v>
       </c>
       <c r="C233" t="n">
-        <v>94.54559326171875</v>
+        <v>94.54560852050781</v>
       </c>
       <c r="D233" t="n">
-        <v>94.55501967625894</v>
+        <v>94.55503493656933</v>
       </c>
       <c r="E233" t="n">
-        <v>94.54559326171875</v>
+        <v>94.54560852050781</v>
       </c>
       <c r="F233" t="n">
-        <v>94.55030287386506</v>
+        <v>94.55031813341422</v>
       </c>
       <c r="G233" t="n">
         <v>11471800</v>
@@ -5808,16 +5808,16 @@
         <v>45629</v>
       </c>
       <c r="C234" t="n">
-        <v>94.55504608154297</v>
+        <v>94.5550537109375</v>
       </c>
       <c r="D234" t="n">
-        <v>94.564465308466</v>
+        <v>94.56447293862054</v>
       </c>
       <c r="E234" t="n">
-        <v>94.55504608154297</v>
+        <v>94.5550537109375</v>
       </c>
       <c r="F234" t="n">
-        <v>94.564465308466</v>
+        <v>94.56447293862054</v>
       </c>
       <c r="G234" t="n">
         <v>5734100</v>
@@ -5831,16 +5831,16 @@
         <v>45630</v>
       </c>
       <c r="C235" t="n">
-        <v>94.57389068603516</v>
+        <v>94.57386779785156</v>
       </c>
       <c r="D235" t="n">
-        <v>94.58331710310412</v>
+        <v>94.5832942126392</v>
       </c>
       <c r="E235" t="n">
-        <v>94.56446426896619</v>
+        <v>94.56444138306392</v>
       </c>
       <c r="F235" t="n">
-        <v>94.57389068603516</v>
+        <v>94.57386779785156</v>
       </c>
       <c r="G235" t="n">
         <v>5351100</v>
@@ -5854,16 +5854,16 @@
         <v>45631</v>
       </c>
       <c r="C236" t="n">
-        <v>94.58330535888672</v>
+        <v>94.58329772949219</v>
       </c>
       <c r="D236" t="n">
-        <v>94.59273177478522</v>
+        <v>94.59272414463034</v>
       </c>
       <c r="E236" t="n">
-        <v>94.58330535888672</v>
+        <v>94.58329772949219</v>
       </c>
       <c r="F236" t="n">
-        <v>94.58330535888672</v>
+        <v>94.58329772949219</v>
       </c>
       <c r="G236" t="n">
         <v>4870100</v>
@@ -5877,16 +5877,16 @@
         <v>45632</v>
       </c>
       <c r="C237" t="n">
-        <v>94.63043975830078</v>
+        <v>94.63043212890625</v>
       </c>
       <c r="D237" t="n">
-        <v>94.63043975830078</v>
+        <v>94.63043212890625</v>
       </c>
       <c r="E237" t="n">
-        <v>94.62101334145494</v>
+        <v>94.62100571282039</v>
       </c>
       <c r="F237" t="n">
-        <v>94.63043975830078</v>
+        <v>94.63043212890625</v>
       </c>
       <c r="G237" t="n">
         <v>4779000</v>
@@ -5900,16 +5900,16 @@
         <v>45635</v>
       </c>
       <c r="C238" t="n">
-        <v>94.63985443115234</v>
+        <v>94.63984680175781</v>
       </c>
       <c r="D238" t="n">
-        <v>94.63985443115234</v>
+        <v>94.63984680175781</v>
       </c>
       <c r="E238" t="n">
-        <v>94.63043520500904</v>
+        <v>94.63042757637383</v>
       </c>
       <c r="F238" t="n">
-        <v>94.63043520500904</v>
+        <v>94.63042757637383</v>
       </c>
       <c r="G238" t="n">
         <v>5539800</v>
@@ -5923,16 +5923,16 @@
         <v>45636</v>
       </c>
       <c r="C239" t="n">
-        <v>94.65869140625</v>
+        <v>94.65871429443359</v>
       </c>
       <c r="D239" t="n">
-        <v>94.65869140625</v>
+        <v>94.65871429443359</v>
       </c>
       <c r="E239" t="n">
-        <v>94.64926499143688</v>
+        <v>94.64928787734119</v>
       </c>
       <c r="F239" t="n">
-        <v>94.64926499143688</v>
+        <v>94.64928787734119</v>
       </c>
       <c r="G239" t="n">
         <v>5293500</v>
@@ -5946,16 +5946,16 @@
         <v>45637</v>
       </c>
       <c r="C240" t="n">
-        <v>94.65869140625</v>
+        <v>94.65871429443359</v>
       </c>
       <c r="D240" t="n">
-        <v>94.66811063081535</v>
+        <v>94.66813352127649</v>
       </c>
       <c r="E240" t="n">
-        <v>94.65869140625</v>
+        <v>94.65871429443359</v>
       </c>
       <c r="F240" t="n">
-        <v>94.66811063081535</v>
+        <v>94.66813352127649</v>
       </c>
       <c r="G240" t="n">
         <v>4855300</v>
@@ -5992,16 +5992,16 @@
         <v>45639</v>
       </c>
       <c r="C242" t="n">
-        <v>94.71524047851562</v>
+        <v>94.71524810791016</v>
       </c>
       <c r="D242" t="n">
-        <v>94.71524047851562</v>
+        <v>94.71524810791016</v>
       </c>
       <c r="E242" t="n">
-        <v>94.70581406320848</v>
+        <v>94.70582169184371</v>
       </c>
       <c r="F242" t="n">
-        <v>94.70581406320848</v>
+        <v>94.70582169184371</v>
       </c>
       <c r="G242" t="n">
         <v>4671500</v>
@@ -6015,16 +6015,16 @@
         <v>45642</v>
       </c>
       <c r="C243" t="n">
-        <v>94.72467041015625</v>
+        <v>94.72468566894531</v>
       </c>
       <c r="D243" t="n">
-        <v>94.72467041015625</v>
+        <v>94.72468566894531</v>
       </c>
       <c r="E243" t="n">
-        <v>94.71524399449918</v>
+        <v>94.71525925176978</v>
       </c>
       <c r="F243" t="n">
-        <v>94.72467041015625</v>
+        <v>94.72468566894531</v>
       </c>
       <c r="G243" t="n">
         <v>5598900</v>
@@ -6038,16 +6038,16 @@
         <v>45643</v>
       </c>
       <c r="C244" t="n">
-        <v>94.72467041015625</v>
+        <v>94.72468566894531</v>
       </c>
       <c r="D244" t="n">
-        <v>94.7340896355649</v>
+        <v>94.73410489587128</v>
       </c>
       <c r="E244" t="n">
-        <v>94.72467041015625</v>
+        <v>94.72468566894531</v>
       </c>
       <c r="F244" t="n">
-        <v>94.7340896355649</v>
+        <v>94.73410489587128</v>
       </c>
       <c r="G244" t="n">
         <v>5798500</v>
@@ -6061,16 +6061,16 @@
         <v>45644</v>
       </c>
       <c r="C245" t="n">
-        <v>94.74549865722656</v>
+        <v>94.74549102783203</v>
       </c>
       <c r="D245" t="n">
-        <v>94.74549865722656</v>
+        <v>94.74549102783203</v>
       </c>
       <c r="E245" t="n">
-        <v>94.73603722202144</v>
+        <v>94.73602959338879</v>
       </c>
       <c r="F245" t="n">
-        <v>94.74549865722656</v>
+        <v>94.74549102783203</v>
       </c>
       <c r="G245" t="n">
         <v>11526500</v>
@@ -6107,16 +6107,16 @@
         <v>45646</v>
       </c>
       <c r="C247" t="n">
-        <v>94.78333282470703</v>
+        <v>94.78331756591797</v>
       </c>
       <c r="D247" t="n">
-        <v>94.7927942601977</v>
+        <v>94.79277899988548</v>
       </c>
       <c r="E247" t="n">
-        <v>94.78333282470703</v>
+        <v>94.78331756591797</v>
       </c>
       <c r="F247" t="n">
-        <v>94.78806715093272</v>
+        <v>94.7880518913815</v>
       </c>
       <c r="G247" t="n">
         <v>8898900</v>
@@ -6153,16 +6153,16 @@
         <v>45650</v>
       </c>
       <c r="C249" t="n">
-        <v>94.83061218261719</v>
+        <v>94.83059692382812</v>
       </c>
       <c r="D249" t="n">
-        <v>94.83061218261719</v>
+        <v>94.83059692382812</v>
       </c>
       <c r="E249" t="n">
-        <v>94.82115074918208</v>
+        <v>94.82113549191543</v>
       </c>
       <c r="F249" t="n">
-        <v>94.83061218261719</v>
+        <v>94.83059692382812</v>
       </c>
       <c r="G249" t="n">
         <v>4654300</v>
@@ -6176,16 +6176,16 @@
         <v>45652</v>
       </c>
       <c r="C250" t="n">
-        <v>94.84008026123047</v>
+        <v>94.840087890625</v>
       </c>
       <c r="D250" t="n">
-        <v>94.84008026123047</v>
+        <v>94.840087890625</v>
       </c>
       <c r="E250" t="n">
-        <v>94.83061882713243</v>
+        <v>94.83062645576584</v>
       </c>
       <c r="F250" t="n">
-        <v>94.84008026123047</v>
+        <v>94.840087890625</v>
       </c>
       <c r="G250" t="n">
         <v>4974100</v>
@@ -6199,16 +6199,16 @@
         <v>45653</v>
       </c>
       <c r="C251" t="n">
-        <v>94.86845397949219</v>
+        <v>94.86846160888672</v>
       </c>
       <c r="D251" t="n">
-        <v>94.86845397949219</v>
+        <v>94.86846160888672</v>
       </c>
       <c r="E251" t="n">
-        <v>94.85899254572995</v>
+        <v>94.85900017436359</v>
       </c>
       <c r="F251" t="n">
-        <v>94.85899254572995</v>
+        <v>94.85900017436359</v>
       </c>
       <c r="G251" t="n">
         <v>6558000</v>
@@ -6222,16 +6222,16 @@
         <v>45656</v>
       </c>
       <c r="C252" t="n">
-        <v>94.86845397949219</v>
+        <v>94.86846160888672</v>
       </c>
       <c r="D252" t="n">
-        <v>94.87791541325443</v>
+        <v>94.87792304340985</v>
       </c>
       <c r="E252" t="n">
-        <v>94.86845397949219</v>
+        <v>94.86846160888672</v>
       </c>
       <c r="F252" t="n">
-        <v>94.87791541325443</v>
+        <v>94.87792304340985</v>
       </c>
       <c r="G252" t="n">
         <v>6547600</v>
@@ -6245,16 +6245,16 @@
         <v>45657</v>
       </c>
       <c r="C253" t="n">
-        <v>94.89682006835938</v>
+        <v>94.89684295654297</v>
       </c>
       <c r="D253" t="n">
-        <v>94.91573571673274</v>
+        <v>94.9157586094786</v>
       </c>
       <c r="E253" t="n">
-        <v>94.89682006835938</v>
+        <v>94.89684295654297</v>
       </c>
       <c r="F253" t="n">
-        <v>94.90628150102533</v>
+        <v>94.90630439149093</v>
       </c>
       <c r="G253" t="n">
         <v>7371300</v>
@@ -6268,16 +6268,16 @@
         <v>45659</v>
       </c>
       <c r="C254" t="n">
-        <v>94.91574096679688</v>
+        <v>94.91574859619141</v>
       </c>
       <c r="D254" t="n">
-        <v>94.91574096679688</v>
+        <v>94.91574859619141</v>
       </c>
       <c r="E254" t="n">
-        <v>94.90628675056652</v>
+        <v>94.90629437920111</v>
       </c>
       <c r="F254" t="n">
-        <v>94.91574096679688</v>
+        <v>94.91574859619141</v>
       </c>
       <c r="G254" t="n">
         <v>7533100</v>
@@ -6291,16 +6291,16 @@
         <v>45660</v>
       </c>
       <c r="C255" t="n">
-        <v>94.94413757324219</v>
+        <v>94.94412994384766</v>
       </c>
       <c r="D255" t="n">
-        <v>94.95359179069801</v>
+        <v>94.95358416054377</v>
       </c>
       <c r="E255" t="n">
-        <v>94.94413757324219</v>
+        <v>94.94412994384766</v>
       </c>
       <c r="F255" t="n">
-        <v>94.95359179069801</v>
+        <v>94.95358416054377</v>
       </c>
       <c r="G255" t="n">
         <v>6730100</v>
@@ -6314,16 +6314,16 @@
         <v>45663</v>
       </c>
       <c r="C256" t="n">
-        <v>94.94413757324219</v>
+        <v>94.94412994384766</v>
       </c>
       <c r="D256" t="n">
-        <v>94.96305322511373</v>
+        <v>94.9630455941992</v>
       </c>
       <c r="E256" t="n">
-        <v>94.94413757324219</v>
+        <v>94.94412994384766</v>
       </c>
       <c r="F256" t="n">
-        <v>94.95359179069801</v>
+        <v>94.95358416054377</v>
       </c>
       <c r="G256" t="n">
         <v>6938300</v>
@@ -6360,16 +6360,16 @@
         <v>45665</v>
       </c>
       <c r="C258" t="n">
-        <v>94.98198699951172</v>
+        <v>94.98196411132812</v>
       </c>
       <c r="D258" t="n">
-        <v>94.98198699951172</v>
+        <v>94.98196411132812</v>
       </c>
       <c r="E258" t="n">
-        <v>94.97252556400967</v>
+        <v>94.97250267810604</v>
       </c>
       <c r="F258" t="n">
-        <v>94.97252556400967</v>
+        <v>94.97250267810604</v>
       </c>
       <c r="G258" t="n">
         <v>6101100</v>
@@ -6406,16 +6406,16 @@
         <v>45670</v>
       </c>
       <c r="C260" t="n">
-        <v>95.03871917724609</v>
+        <v>95.03872680664062</v>
       </c>
       <c r="D260" t="n">
-        <v>95.03871917724609</v>
+        <v>95.03872680664062</v>
       </c>
       <c r="E260" t="n">
-        <v>95.02925774393435</v>
+        <v>95.02926537256936</v>
       </c>
       <c r="F260" t="n">
-        <v>95.03398485211071</v>
+        <v>95.03399248112518</v>
       </c>
       <c r="G260" t="n">
         <v>7647300</v>
@@ -6429,16 +6429,16 @@
         <v>45671</v>
       </c>
       <c r="C261" t="n">
-        <v>95.04820251464844</v>
+        <v>95.04818725585938</v>
       </c>
       <c r="D261" t="n">
-        <v>95.04820251464844</v>
+        <v>95.04818725585938</v>
       </c>
       <c r="E261" t="n">
-        <v>95.03874107915628</v>
+        <v>95.03872582188613</v>
       </c>
       <c r="F261" t="n">
-        <v>95.04820251464844</v>
+        <v>95.04818725585938</v>
       </c>
       <c r="G261" t="n">
         <v>7245400</v>
@@ -6452,16 +6452,16 @@
         <v>45672</v>
       </c>
       <c r="C262" t="n">
-        <v>95.05764007568359</v>
+        <v>95.05765533447266</v>
       </c>
       <c r="D262" t="n">
-        <v>95.05764007568359</v>
+        <v>95.05765533447266</v>
       </c>
       <c r="E262" t="n">
-        <v>95.04818585880886</v>
+        <v>95.04820111608032</v>
       </c>
       <c r="F262" t="n">
-        <v>95.05764007568359</v>
+        <v>95.05765533447266</v>
       </c>
       <c r="G262" t="n">
         <v>6878600</v>
@@ -6475,16 +6475,16 @@
         <v>45673</v>
       </c>
       <c r="C263" t="n">
-        <v>95.05764007568359</v>
+        <v>95.05765533447266</v>
       </c>
       <c r="D263" t="n">
-        <v>95.07656294335193</v>
+        <v>95.07657820517852</v>
       </c>
       <c r="E263" t="n">
-        <v>95.05764007568359</v>
+        <v>95.05765533447266</v>
       </c>
       <c r="F263" t="n">
-        <v>95.06710150951776</v>
+        <v>95.06711676982559</v>
       </c>
       <c r="G263" t="n">
         <v>5352500</v>
@@ -6521,16 +6521,16 @@
         <v>45678</v>
       </c>
       <c r="C265" t="n">
-        <v>95.11440277099609</v>
+        <v>95.11439514160156</v>
       </c>
       <c r="D265" t="n">
-        <v>95.12385698800095</v>
+        <v>95.12384935784807</v>
       </c>
       <c r="E265" t="n">
-        <v>95.11440277099609</v>
+        <v>95.11439514160156</v>
       </c>
       <c r="F265" t="n">
-        <v>95.11912987949853</v>
+        <v>95.11912224972482</v>
       </c>
       <c r="G265" t="n">
         <v>7952400</v>
@@ -6544,16 +6544,16 @@
         <v>45679</v>
       </c>
       <c r="C266" t="n">
-        <v>95.13333129882812</v>
+        <v>95.13330078125</v>
       </c>
       <c r="D266" t="n">
-        <v>95.13333129882812</v>
+        <v>95.13330078125</v>
       </c>
       <c r="E266" t="n">
-        <v>95.12386986358305</v>
+        <v>95.12383934904004</v>
       </c>
       <c r="F266" t="n">
-        <v>95.12386986358305</v>
+        <v>95.12383934904004</v>
       </c>
       <c r="G266" t="n">
         <v>5717600</v>
@@ -6567,16 +6567,16 @@
         <v>45680</v>
       </c>
       <c r="C267" t="n">
-        <v>95.14278411865234</v>
+        <v>95.14279937744141</v>
       </c>
       <c r="D267" t="n">
-        <v>95.14278411865234</v>
+        <v>95.14279937744141</v>
       </c>
       <c r="E267" t="n">
-        <v>95.13332268426403</v>
+        <v>95.13333794153569</v>
       </c>
       <c r="F267" t="n">
-        <v>95.14278411865234</v>
+        <v>95.14279937744141</v>
       </c>
       <c r="G267" t="n">
         <v>5085800</v>
@@ -6682,16 +6682,16 @@
         <v>45687</v>
       </c>
       <c r="C272" t="n">
-        <v>95.21846008300781</v>
+        <v>95.21846771240234</v>
       </c>
       <c r="D272" t="n">
-        <v>95.22791430032933</v>
+        <v>95.22792193048139</v>
       </c>
       <c r="E272" t="n">
-        <v>95.20899864872649</v>
+        <v>95.20900627736293</v>
       </c>
       <c r="F272" t="n">
-        <v>95.20899864872649</v>
+        <v>95.20900627736293</v>
       </c>
       <c r="G272" t="n">
         <v>8043500</v>
@@ -6705,16 +6705,16 @@
         <v>45688</v>
       </c>
       <c r="C273" t="n">
-        <v>95.23735809326172</v>
+        <v>95.23738098144531</v>
       </c>
       <c r="D273" t="n">
-        <v>95.24681952579044</v>
+        <v>95.24684241624787</v>
       </c>
       <c r="E273" t="n">
-        <v>95.23735809326172</v>
+        <v>95.23738098144531</v>
       </c>
       <c r="F273" t="n">
-        <v>95.24681952579044</v>
+        <v>95.24684241624787</v>
       </c>
       <c r="G273" t="n">
         <v>12373000</v>
@@ -6728,16 +6728,16 @@
         <v>45691</v>
       </c>
       <c r="C274" t="n">
-        <v>95.25920104980469</v>
+        <v>95.25920867919922</v>
       </c>
       <c r="D274" t="n">
-        <v>95.25920104980469</v>
+        <v>95.25920867919922</v>
       </c>
       <c r="E274" t="n">
-        <v>95.24971262274842</v>
+        <v>95.24972025138301</v>
       </c>
       <c r="F274" t="n">
-        <v>95.24971262274842</v>
+        <v>95.24972025138301</v>
       </c>
       <c r="G274" t="n">
         <v>16436200</v>
@@ -6820,16 +6820,16 @@
         <v>45695</v>
       </c>
       <c r="C278" t="n">
-        <v>95.32567596435547</v>
+        <v>95.32566833496094</v>
       </c>
       <c r="D278" t="n">
-        <v>95.33516439265264</v>
+        <v>95.3351567624987</v>
       </c>
       <c r="E278" t="n">
-        <v>95.31618029298328</v>
+        <v>95.31617266434873</v>
       </c>
       <c r="F278" t="n">
-        <v>95.33516439265264</v>
+        <v>95.3351567624987</v>
       </c>
       <c r="G278" t="n">
         <v>6758700</v>
@@ -6843,16 +6843,16 @@
         <v>45698</v>
       </c>
       <c r="C279" t="n">
-        <v>95.34464263916016</v>
+        <v>95.34467315673828</v>
       </c>
       <c r="D279" t="n">
-        <v>95.34464263916016</v>
+        <v>95.34467315673828</v>
       </c>
       <c r="E279" t="n">
-        <v>95.33514696952335</v>
+        <v>95.33517748406213</v>
       </c>
       <c r="F279" t="n">
-        <v>95.34464263916016</v>
+        <v>95.34467315673828</v>
       </c>
       <c r="G279" t="n">
         <v>7517800</v>
@@ -6866,16 +6866,16 @@
         <v>45699</v>
       </c>
       <c r="C280" t="n">
-        <v>95.34464263916016</v>
+        <v>95.34467315673828</v>
       </c>
       <c r="D280" t="n">
-        <v>95.35413830879696</v>
+        <v>95.35416882941442</v>
       </c>
       <c r="E280" t="n">
-        <v>95.34464263916016</v>
+        <v>95.34467315673828</v>
       </c>
       <c r="F280" t="n">
-        <v>95.35413830879696</v>
+        <v>95.35416882941442</v>
       </c>
       <c r="G280" t="n">
         <v>6424100</v>
@@ -6889,16 +6889,16 @@
         <v>45700</v>
       </c>
       <c r="C281" t="n">
-        <v>95.35414886474609</v>
+        <v>95.35414123535156</v>
       </c>
       <c r="D281" t="n">
-        <v>95.36363729235957</v>
+        <v>95.36362966220587</v>
       </c>
       <c r="E281" t="n">
-        <v>95.35414886474609</v>
+        <v>95.35414123535156</v>
       </c>
       <c r="F281" t="n">
-        <v>95.35414886474609</v>
+        <v>95.35414123535156</v>
       </c>
       <c r="G281" t="n">
         <v>6618800</v>
@@ -6912,16 +6912,16 @@
         <v>45701</v>
       </c>
       <c r="C282" t="n">
-        <v>95.37312316894531</v>
+        <v>95.37313079833984</v>
       </c>
       <c r="D282" t="n">
-        <v>95.37312316894531</v>
+        <v>95.37313079833984</v>
       </c>
       <c r="E282" t="n">
-        <v>95.36362749923244</v>
+        <v>95.36363512786737</v>
       </c>
       <c r="F282" t="n">
-        <v>95.37312316894531</v>
+        <v>95.37313079833984</v>
       </c>
       <c r="G282" t="n">
         <v>5690100</v>
@@ -7004,16 +7004,16 @@
         <v>45708</v>
       </c>
       <c r="C286" t="n">
-        <v>95.44908905029297</v>
+        <v>95.44907379150391</v>
       </c>
       <c r="D286" t="n">
-        <v>95.44908905029297</v>
+        <v>95.44907379150391</v>
       </c>
       <c r="E286" t="n">
-        <v>95.43959337908686</v>
+        <v>95.43957812181581</v>
       </c>
       <c r="F286" t="n">
-        <v>95.44908905029297</v>
+        <v>95.44907379150391</v>
       </c>
       <c r="G286" t="n">
         <v>7608000</v>
@@ -7027,16 +7027,16 @@
         <v>45709</v>
       </c>
       <c r="C287" t="n">
-        <v>95.487060546875</v>
+        <v>95.48707580566406</v>
       </c>
       <c r="D287" t="n">
-        <v>95.487060546875</v>
+        <v>95.48707580566406</v>
       </c>
       <c r="E287" t="n">
-        <v>95.47756487606122</v>
+        <v>95.47758013333288</v>
       </c>
       <c r="F287" t="n">
-        <v>95.47756487606122</v>
+        <v>95.47758013333288</v>
       </c>
       <c r="G287" t="n">
         <v>9111000</v>
@@ -7073,16 +7073,16 @@
         <v>45713</v>
       </c>
       <c r="C289" t="n">
-        <v>95.50605773925781</v>
+        <v>95.50604248046875</v>
       </c>
       <c r="D289" t="n">
-        <v>95.50605773925781</v>
+        <v>95.50604248046875</v>
       </c>
       <c r="E289" t="n">
-        <v>95.49656206714219</v>
+        <v>95.49654680987022</v>
       </c>
       <c r="F289" t="n">
-        <v>95.49656206714219</v>
+        <v>95.49654680987022</v>
       </c>
       <c r="G289" t="n">
         <v>10827700</v>
@@ -7096,16 +7096,16 @@
         <v>45714</v>
       </c>
       <c r="C290" t="n">
-        <v>95.50605773925781</v>
+        <v>95.50604248046875</v>
       </c>
       <c r="D290" t="n">
-        <v>95.51555341137345</v>
+        <v>95.51553815106729</v>
       </c>
       <c r="E290" t="n">
-        <v>95.50605773925781</v>
+        <v>95.50604248046875</v>
       </c>
       <c r="F290" t="n">
-        <v>95.50605773925781</v>
+        <v>95.50604248046875</v>
       </c>
       <c r="G290" t="n">
         <v>9536300</v>
@@ -7119,16 +7119,16 @@
         <v>45715</v>
       </c>
       <c r="C291" t="n">
-        <v>95.53451538085938</v>
+        <v>95.53452301025391</v>
       </c>
       <c r="D291" t="n">
-        <v>95.53451538085938</v>
+        <v>95.53452301025391</v>
       </c>
       <c r="E291" t="n">
-        <v>95.52502695401745</v>
+        <v>95.52503458265423</v>
       </c>
       <c r="F291" t="n">
-        <v>95.53451538085938</v>
+        <v>95.53452301025391</v>
       </c>
       <c r="G291" t="n">
         <v>10807800</v>
@@ -7142,16 +7142,16 @@
         <v>45716</v>
       </c>
       <c r="C292" t="n">
-        <v>95.55351257324219</v>
+        <v>95.55352020263672</v>
       </c>
       <c r="D292" t="n">
-        <v>95.56300824373963</v>
+        <v>95.56301587389234</v>
       </c>
       <c r="E292" t="n">
-        <v>95.55351257324219</v>
+        <v>95.55352020263672</v>
       </c>
       <c r="F292" t="n">
-        <v>95.55351257324219</v>
+        <v>95.55352020263672</v>
       </c>
       <c r="G292" t="n">
         <v>13772600</v>
@@ -7165,16 +7165,16 @@
         <v>45719</v>
       </c>
       <c r="C293" t="n">
-        <v>95.57540893554688</v>
+        <v>95.57542419433594</v>
       </c>
       <c r="D293" t="n">
-        <v>95.57540893554688</v>
+        <v>95.57542419433594</v>
       </c>
       <c r="E293" t="n">
-        <v>95.56588364404985</v>
+        <v>95.56589890131818</v>
       </c>
       <c r="F293" t="n">
-        <v>95.57540893554688</v>
+        <v>95.57542419433594</v>
       </c>
       <c r="G293" t="n">
         <v>17436600</v>
@@ -7234,16 +7234,16 @@
         <v>45722</v>
       </c>
       <c r="C296" t="n">
-        <v>95.61351013183594</v>
+        <v>95.613525390625</v>
       </c>
       <c r="D296" t="n">
-        <v>95.61351013183594</v>
+        <v>95.613525390625</v>
       </c>
       <c r="E296" t="n">
-        <v>95.59445954738818</v>
+        <v>95.59447480313699</v>
       </c>
       <c r="F296" t="n">
-        <v>95.60398483961205</v>
+        <v>95.60400009688099</v>
       </c>
       <c r="G296" t="n">
         <v>9925500</v>
@@ -7257,16 +7257,16 @@
         <v>45723</v>
       </c>
       <c r="C297" t="n">
-        <v>95.64207458496094</v>
+        <v>95.64208221435547</v>
       </c>
       <c r="D297" t="n">
-        <v>95.64207458496094</v>
+        <v>95.64208221435547</v>
       </c>
       <c r="E297" t="n">
-        <v>95.63254929315114</v>
+        <v>95.63255692178585</v>
       </c>
       <c r="F297" t="n">
-        <v>95.64207458496094</v>
+        <v>95.64208221435547</v>
       </c>
       <c r="G297" t="n">
         <v>8962400</v>
@@ -7280,16 +7280,16 @@
         <v>45726</v>
       </c>
       <c r="C298" t="n">
-        <v>95.64207458496094</v>
+        <v>95.64208221435547</v>
       </c>
       <c r="D298" t="n">
-        <v>95.65159987677072</v>
+        <v>95.65160750692509</v>
       </c>
       <c r="E298" t="n">
-        <v>95.64207458496094</v>
+        <v>95.64208221435547</v>
       </c>
       <c r="F298" t="n">
-        <v>95.65159987677072</v>
+        <v>95.65160750692509</v>
       </c>
       <c r="G298" t="n">
         <v>14768100</v>
@@ -7303,16 +7303,16 @@
         <v>45727</v>
       </c>
       <c r="C299" t="n">
-        <v>95.66111755371094</v>
+        <v>95.6611328125</v>
       </c>
       <c r="D299" t="n">
-        <v>95.66111755371094</v>
+        <v>95.6611328125</v>
       </c>
       <c r="E299" t="n">
-        <v>95.65159952760472</v>
+        <v>95.65161478487556</v>
       </c>
       <c r="F299" t="n">
-        <v>95.65159952760472</v>
+        <v>95.65161478487556</v>
       </c>
       <c r="G299" t="n">
         <v>11456900</v>
@@ -7326,16 +7326,16 @@
         <v>45728</v>
       </c>
       <c r="C300" t="n">
-        <v>95.66111755371094</v>
+        <v>95.6611328125</v>
       </c>
       <c r="D300" t="n">
-        <v>95.67064284548596</v>
+        <v>95.67065810579437</v>
       </c>
       <c r="E300" t="n">
-        <v>95.66111755371094</v>
+        <v>95.6611328125</v>
       </c>
       <c r="F300" t="n">
-        <v>95.67064284548596</v>
+        <v>95.67065810579437</v>
       </c>
       <c r="G300" t="n">
         <v>11307300</v>
@@ -7349,16 +7349,16 @@
         <v>45729</v>
       </c>
       <c r="C301" t="n">
-        <v>95.68970489501953</v>
+        <v>95.68971252441406</v>
       </c>
       <c r="D301" t="n">
-        <v>95.68970489501953</v>
+        <v>95.68971252441406</v>
       </c>
       <c r="E301" t="n">
-        <v>95.67065430918677</v>
+        <v>95.67066193706239</v>
       </c>
       <c r="F301" t="n">
-        <v>95.67065430918677</v>
+        <v>95.67066193706239</v>
       </c>
       <c r="G301" t="n">
         <v>13110600</v>
@@ -7372,16 +7372,16 @@
         <v>45730</v>
       </c>
       <c r="C302" t="n">
-        <v>95.71826171875</v>
+        <v>95.71827697753906</v>
       </c>
       <c r="D302" t="n">
-        <v>95.71826171875</v>
+        <v>95.71827697753906</v>
       </c>
       <c r="E302" t="n">
-        <v>95.70873642700683</v>
+        <v>95.70875168427743</v>
       </c>
       <c r="F302" t="n">
-        <v>95.71826171875</v>
+        <v>95.71827697753906</v>
       </c>
       <c r="G302" t="n">
         <v>11421900</v>
@@ -7395,16 +7395,16 @@
         <v>45733</v>
       </c>
       <c r="C303" t="n">
-        <v>95.72779083251953</v>
+        <v>95.72777557373047</v>
       </c>
       <c r="D303" t="n">
-        <v>95.72779083251953</v>
+        <v>95.72777557373047</v>
       </c>
       <c r="E303" t="n">
-        <v>95.71827280534269</v>
+        <v>95.71825754807078</v>
       </c>
       <c r="F303" t="n">
-        <v>95.72779083251953</v>
+        <v>95.72777557373047</v>
       </c>
       <c r="G303" t="n">
         <v>9018300</v>
@@ -7418,16 +7418,16 @@
         <v>45734</v>
       </c>
       <c r="C304" t="n">
-        <v>95.73731231689453</v>
+        <v>95.73731994628906</v>
       </c>
       <c r="D304" t="n">
-        <v>95.73731231689453</v>
+        <v>95.73731994628906</v>
       </c>
       <c r="E304" t="n">
-        <v>95.727787024427</v>
+        <v>95.72779465306246</v>
       </c>
       <c r="F304" t="n">
-        <v>95.73731231689453</v>
+        <v>95.73731994628906</v>
       </c>
       <c r="G304" t="n">
         <v>9213100</v>
@@ -7441,16 +7441,16 @@
         <v>45735</v>
       </c>
       <c r="C305" t="n">
-        <v>95.75636291503906</v>
+        <v>95.75635528564453</v>
       </c>
       <c r="D305" t="n">
-        <v>95.75636291503906</v>
+        <v>95.75635528564453</v>
       </c>
       <c r="E305" t="n">
-        <v>95.74683762257023</v>
+        <v>95.74682999393463</v>
       </c>
       <c r="F305" t="n">
-        <v>95.74683762257023</v>
+        <v>95.74682999393463</v>
       </c>
       <c r="G305" t="n">
         <v>13584800</v>
@@ -7464,16 +7464,16 @@
         <v>45736</v>
       </c>
       <c r="C306" t="n">
-        <v>95.75636291503906</v>
+        <v>95.75635528564453</v>
       </c>
       <c r="D306" t="n">
-        <v>95.76588094183857</v>
+        <v>95.76587331168571</v>
       </c>
       <c r="E306" t="n">
-        <v>95.75636291503906</v>
+        <v>95.75635528564453</v>
       </c>
       <c r="F306" t="n">
-        <v>95.76588094183857</v>
+        <v>95.76587331168571</v>
       </c>
       <c r="G306" t="n">
         <v>12648500</v>
@@ -7487,16 +7487,16 @@
         <v>45737</v>
       </c>
       <c r="C307" t="n">
-        <v>95.78493499755859</v>
+        <v>95.78495025634766</v>
       </c>
       <c r="D307" t="n">
-        <v>95.794453024703</v>
+        <v>95.79446828500832</v>
       </c>
       <c r="E307" t="n">
-        <v>95.78493499755859</v>
+        <v>95.78495025634766</v>
       </c>
       <c r="F307" t="n">
-        <v>95.794453024703</v>
+        <v>95.79446828500832</v>
       </c>
       <c r="G307" t="n">
         <v>13101800</v>
@@ -7510,16 +7510,16 @@
         <v>45740</v>
       </c>
       <c r="C308" t="n">
-        <v>95.80399322509766</v>
+        <v>95.80398559570312</v>
       </c>
       <c r="D308" t="n">
-        <v>95.81351851939382</v>
+        <v>95.81351088924075</v>
       </c>
       <c r="E308" t="n">
-        <v>95.80399322509766</v>
+        <v>95.80398559570312</v>
       </c>
       <c r="F308" t="n">
-        <v>95.8087595050811</v>
+        <v>95.80875187530701</v>
       </c>
       <c r="G308" t="n">
         <v>13854600</v>
@@ -7556,16 +7556,16 @@
         <v>45742</v>
       </c>
       <c r="C310" t="n">
-        <v>95.83253479003906</v>
+        <v>95.83254241943359</v>
       </c>
       <c r="D310" t="n">
-        <v>95.83253479003906</v>
+        <v>95.83254241943359</v>
       </c>
       <c r="E310" t="n">
-        <v>95.82301676410042</v>
+        <v>95.8230243927372</v>
       </c>
       <c r="F310" t="n">
-        <v>95.83253479003906</v>
+        <v>95.83254241943359</v>
       </c>
       <c r="G310" t="n">
         <v>12262200</v>
@@ -7579,16 +7579,16 @@
         <v>45743</v>
       </c>
       <c r="C311" t="n">
-        <v>95.84207916259766</v>
+        <v>95.84206390380859</v>
       </c>
       <c r="D311" t="n">
-        <v>95.84207916259766</v>
+        <v>95.84206390380859</v>
       </c>
       <c r="E311" t="n">
-        <v>95.83255386909399</v>
+        <v>95.83253861182142</v>
       </c>
       <c r="F311" t="n">
-        <v>95.84207916259766</v>
+        <v>95.84206390380859</v>
       </c>
       <c r="G311" t="n">
         <v>10022000</v>
@@ -7602,16 +7602,16 @@
         <v>45744</v>
       </c>
       <c r="C312" t="n">
-        <v>95.87065124511719</v>
+        <v>95.87063598632812</v>
       </c>
       <c r="D312" t="n">
-        <v>95.87065124511719</v>
+        <v>95.87063598632812</v>
       </c>
       <c r="E312" t="n">
-        <v>95.86113321693935</v>
+        <v>95.86111795966518</v>
       </c>
       <c r="F312" t="n">
-        <v>95.86113321693935</v>
+        <v>95.86111795966518</v>
       </c>
       <c r="G312" t="n">
         <v>11747100</v>
@@ -7625,16 +7625,16 @@
         <v>45747</v>
       </c>
       <c r="C313" t="n">
-        <v>95.87065124511719</v>
+        <v>95.87063598632812</v>
       </c>
       <c r="D313" t="n">
-        <v>95.88017653896539</v>
+        <v>95.88016127866028</v>
       </c>
       <c r="E313" t="n">
-        <v>95.87065124511719</v>
+        <v>95.87063598632812</v>
       </c>
       <c r="F313" t="n">
-        <v>95.87065124511719</v>
+        <v>95.87063598632812</v>
       </c>
       <c r="G313" t="n">
         <v>18210800</v>
@@ -7648,16 +7648,16 @@
         <v>45748</v>
       </c>
       <c r="C314" t="n">
-        <v>95.89550018310547</v>
+        <v>95.89547729492188</v>
       </c>
       <c r="D314" t="n">
-        <v>95.89550018310547</v>
+        <v>95.89547729492188</v>
       </c>
       <c r="E314" t="n">
-        <v>95.88594203790063</v>
+        <v>95.88591915199837</v>
       </c>
       <c r="F314" t="n">
-        <v>95.89550018310547</v>
+        <v>95.89547729492188</v>
       </c>
       <c r="G314" t="n">
         <v>21033200</v>
@@ -7694,16 +7694,16 @@
         <v>45750</v>
       </c>
       <c r="C316" t="n">
-        <v>95.92415618896484</v>
+        <v>95.92414855957031</v>
       </c>
       <c r="D316" t="n">
-        <v>95.92415618896484</v>
+        <v>95.92414855957031</v>
       </c>
       <c r="E316" t="n">
-        <v>95.90504719150279</v>
+        <v>95.90503956362811</v>
       </c>
       <c r="F316" t="n">
-        <v>95.9146053355977</v>
+        <v>95.91459770696281</v>
       </c>
       <c r="G316" t="n">
         <v>13988800</v>
@@ -7717,16 +7717,16 @@
         <v>45751</v>
       </c>
       <c r="C317" t="n">
-        <v>95.95285034179688</v>
+        <v>95.95282745361328</v>
       </c>
       <c r="D317" t="n">
-        <v>95.95285034179688</v>
+        <v>95.95282745361328</v>
       </c>
       <c r="E317" t="n">
-        <v>95.94329219573754</v>
+        <v>95.94326930983391</v>
       </c>
       <c r="F317" t="n">
-        <v>95.94329219573754</v>
+        <v>95.94326930983391</v>
       </c>
       <c r="G317" t="n">
         <v>22826300</v>
@@ -7740,16 +7740,16 @@
         <v>45754</v>
       </c>
       <c r="C318" t="n">
-        <v>95.96238708496094</v>
+        <v>95.96237945556641</v>
       </c>
       <c r="D318" t="n">
-        <v>95.96238708496094</v>
+        <v>95.96237945556641</v>
       </c>
       <c r="E318" t="n">
-        <v>95.95283623103541</v>
+        <v>95.95282860240022</v>
       </c>
       <c r="F318" t="n">
-        <v>95.95283623103541</v>
+        <v>95.95282860240022</v>
       </c>
       <c r="G318" t="n">
         <v>22564000</v>
@@ -7763,16 +7763,16 @@
         <v>45755</v>
       </c>
       <c r="C319" t="n">
-        <v>95.96238708496094</v>
+        <v>95.96237945556641</v>
       </c>
       <c r="D319" t="n">
-        <v>95.97194522961465</v>
+        <v>95.97193759946022</v>
       </c>
       <c r="E319" t="n">
-        <v>95.95283623103541</v>
+        <v>95.95282860240022</v>
       </c>
       <c r="F319" t="n">
-        <v>95.95761165799817</v>
+        <v>95.95760402898331</v>
       </c>
       <c r="G319" t="n">
         <v>17116100</v>
@@ -7832,16 +7832,16 @@
         <v>45758</v>
       </c>
       <c r="C322" t="n">
-        <v>96.02928161621094</v>
+        <v>96.02925872802734</v>
       </c>
       <c r="D322" t="n">
-        <v>96.02928161621094</v>
+        <v>96.02925872802734</v>
       </c>
       <c r="E322" t="n">
-        <v>96.01973076207653</v>
+        <v>96.01970787616935</v>
       </c>
       <c r="F322" t="n">
-        <v>96.02450618914374</v>
+        <v>96.02448330209835</v>
       </c>
       <c r="G322" t="n">
         <v>12916600</v>
@@ -7855,16 +7855,16 @@
         <v>45761</v>
       </c>
       <c r="C323" t="n">
-        <v>96.03883361816406</v>
+        <v>96.038818359375</v>
       </c>
       <c r="D323" t="n">
-        <v>96.03883361816406</v>
+        <v>96.038818359375</v>
       </c>
       <c r="E323" t="n">
-        <v>96.02927547391268</v>
+        <v>96.02926021664223</v>
       </c>
       <c r="F323" t="n">
-        <v>96.02927547391268</v>
+        <v>96.02926021664223</v>
       </c>
       <c r="G323" t="n">
         <v>13772300</v>
@@ -7878,16 +7878,16 @@
         <v>45762</v>
       </c>
       <c r="C324" t="n">
-        <v>96.04837799072266</v>
+        <v>96.04839324951172</v>
       </c>
       <c r="D324" t="n">
-        <v>96.04837799072266</v>
+        <v>96.04839324951172</v>
       </c>
       <c r="E324" t="n">
-        <v>96.03881984784175</v>
+        <v>96.03883510511234</v>
       </c>
       <c r="F324" t="n">
-        <v>96.04837799072266</v>
+        <v>96.04839324951172</v>
       </c>
       <c r="G324" t="n">
         <v>10043700</v>
@@ -7901,16 +7901,16 @@
         <v>45763</v>
       </c>
       <c r="C325" t="n">
-        <v>96.06748962402344</v>
+        <v>96.06749725341797</v>
       </c>
       <c r="D325" t="n">
-        <v>96.06748962402344</v>
+        <v>96.06749725341797</v>
       </c>
       <c r="E325" t="n">
-        <v>96.05793148088003</v>
+        <v>96.05793910951549</v>
       </c>
       <c r="F325" t="n">
-        <v>96.06271419781525</v>
+        <v>96.06272182683053</v>
       </c>
       <c r="G325" t="n">
         <v>8840000</v>
@@ -7924,16 +7924,16 @@
         <v>45764</v>
       </c>
       <c r="C326" t="n">
-        <v>96.10572814941406</v>
+        <v>96.10572052001953</v>
       </c>
       <c r="D326" t="n">
-        <v>96.11528629387459</v>
+        <v>96.11527866372128</v>
       </c>
       <c r="E326" t="n">
-        <v>96.10572814941406</v>
+        <v>96.10572052001953</v>
       </c>
       <c r="F326" t="n">
-        <v>96.11050357628031</v>
+        <v>96.11049594650667</v>
       </c>
       <c r="G326" t="n">
         <v>8652700</v>
@@ -7947,16 +7947,16 @@
         <v>45768</v>
       </c>
       <c r="C327" t="n">
-        <v>96.10572814941406</v>
+        <v>96.10572052001953</v>
       </c>
       <c r="D327" t="n">
-        <v>96.11528629387459</v>
+        <v>96.11527866372128</v>
       </c>
       <c r="E327" t="n">
-        <v>96.10572814941406</v>
+        <v>96.10572052001953</v>
       </c>
       <c r="F327" t="n">
-        <v>96.11528629387459</v>
+        <v>96.11527866372128</v>
       </c>
       <c r="G327" t="n">
         <v>10756100</v>
@@ -7970,16 +7970,16 @@
         <v>45769</v>
       </c>
       <c r="C328" t="n">
-        <v>96.11528015136719</v>
+        <v>96.11529541015625</v>
       </c>
       <c r="D328" t="n">
-        <v>96.12483100448931</v>
+        <v>96.12484626479461</v>
       </c>
       <c r="E328" t="n">
-        <v>96.11528015136719</v>
+        <v>96.11529541015625</v>
       </c>
       <c r="F328" t="n">
-        <v>96.12483100448931</v>
+        <v>96.12484626479461</v>
       </c>
       <c r="G328" t="n">
         <v>11603400</v>
@@ -7993,16 +7993,16 @@
         <v>45770</v>
       </c>
       <c r="C329" t="n">
-        <v>96.14396667480469</v>
+        <v>96.14395904541016</v>
       </c>
       <c r="D329" t="n">
-        <v>96.14396667480469</v>
+        <v>96.14395904541016</v>
       </c>
       <c r="E329" t="n">
-        <v>96.12485038325146</v>
+        <v>96.12484275537388</v>
       </c>
       <c r="F329" t="n">
-        <v>96.13440852902808</v>
+        <v>96.13440090039201</v>
       </c>
       <c r="G329" t="n">
         <v>19135100</v>
@@ -8016,16 +8016,16 @@
         <v>45771</v>
       </c>
       <c r="C330" t="n">
-        <v>96.14396667480469</v>
+        <v>96.14395904541016</v>
       </c>
       <c r="D330" t="n">
-        <v>96.15352482058131</v>
+        <v>96.15351719042829</v>
       </c>
       <c r="E330" t="n">
-        <v>96.14396667480469</v>
+        <v>96.14395904541016</v>
       </c>
       <c r="F330" t="n">
-        <v>96.15352482058131</v>
+        <v>96.15351719042829</v>
       </c>
       <c r="G330" t="n">
         <v>12068700</v>
@@ -8085,16 +8085,16 @@
         <v>45776</v>
       </c>
       <c r="C333" t="n">
-        <v>96.19174194335938</v>
+        <v>96.19173431396484</v>
       </c>
       <c r="D333" t="n">
-        <v>96.2012927975958</v>
+        <v>96.20128516744374</v>
       </c>
       <c r="E333" t="n">
-        <v>96.19174194335938</v>
+        <v>96.19173431396484</v>
       </c>
       <c r="F333" t="n">
-        <v>96.19174194335938</v>
+        <v>96.19173431396484</v>
       </c>
       <c r="G333" t="n">
         <v>8555000</v>
@@ -8108,16 +8108,16 @@
         <v>45777</v>
       </c>
       <c r="C334" t="n">
-        <v>96.22039794921875</v>
+        <v>96.22039031982422</v>
       </c>
       <c r="D334" t="n">
-        <v>96.22039794921875</v>
+        <v>96.22039031982422</v>
       </c>
       <c r="E334" t="n">
-        <v>96.20128166150194</v>
+        <v>96.20127403362315</v>
       </c>
       <c r="F334" t="n">
-        <v>96.20128166150194</v>
+        <v>96.20127403362315</v>
       </c>
       <c r="G334" t="n">
         <v>16040200</v>
@@ -8131,16 +8131,16 @@
         <v>45778</v>
       </c>
       <c r="C335" t="n">
-        <v>96.23478698730469</v>
+        <v>96.23479461669922</v>
       </c>
       <c r="D335" t="n">
-        <v>96.23478698730469</v>
+        <v>96.23479461669922</v>
       </c>
       <c r="E335" t="n">
-        <v>96.22519693626137</v>
+        <v>96.22520456489561</v>
       </c>
       <c r="F335" t="n">
-        <v>96.23478698730469</v>
+        <v>96.23479461669922</v>
       </c>
       <c r="G335" t="n">
         <v>21288700</v>
@@ -8154,16 +8154,16 @@
         <v>45779</v>
       </c>
       <c r="C336" t="n">
-        <v>96.26355743408203</v>
+        <v>96.26357269287109</v>
       </c>
       <c r="D336" t="n">
-        <v>96.26355743408203</v>
+        <v>96.26357269287109</v>
       </c>
       <c r="E336" t="n">
-        <v>96.25396738228072</v>
+        <v>96.25398263954965</v>
       </c>
       <c r="F336" t="n">
-        <v>96.25396738228072</v>
+        <v>96.25398263954965</v>
       </c>
       <c r="G336" t="n">
         <v>13930900</v>
@@ -8223,16 +8223,16 @@
         <v>45784</v>
       </c>
       <c r="C339" t="n">
-        <v>96.28271484375</v>
+        <v>96.28272247314453</v>
       </c>
       <c r="D339" t="n">
-        <v>96.29230489401954</v>
+        <v>96.29231252417398</v>
       </c>
       <c r="E339" t="n">
-        <v>96.28271484375</v>
+        <v>96.28272247314453</v>
       </c>
       <c r="F339" t="n">
-        <v>96.29230489401954</v>
+        <v>96.29231252417398</v>
       </c>
       <c r="G339" t="n">
         <v>8509300</v>
@@ -8246,16 +8246,16 @@
         <v>45785</v>
       </c>
       <c r="C340" t="n">
-        <v>96.31147003173828</v>
+        <v>96.31147766113281</v>
       </c>
       <c r="D340" t="n">
-        <v>96.31147003173828</v>
+        <v>96.31147766113281</v>
       </c>
       <c r="E340" t="n">
-        <v>96.29229724778671</v>
+        <v>96.29230487566245</v>
       </c>
       <c r="F340" t="n">
-        <v>96.30188729729473</v>
+        <v>96.30189492593016</v>
       </c>
       <c r="G340" t="n">
         <v>11931100</v>
@@ -8315,16 +8315,16 @@
         <v>45790</v>
       </c>
       <c r="C343" t="n">
-        <v>96.35942077636719</v>
+        <v>96.35941314697266</v>
       </c>
       <c r="D343" t="n">
-        <v>96.35942077636719</v>
+        <v>96.35941314697266</v>
       </c>
       <c r="E343" t="n">
-        <v>96.34983072608168</v>
+        <v>96.34982309744645</v>
       </c>
       <c r="F343" t="n">
-        <v>96.34983072608168</v>
+        <v>96.34982309744645</v>
       </c>
       <c r="G343" t="n">
         <v>18174400</v>
@@ -8384,16 +8384,16 @@
         <v>45793</v>
       </c>
       <c r="C346" t="n">
-        <v>96.40736389160156</v>
+        <v>96.40735626220703</v>
       </c>
       <c r="D346" t="n">
-        <v>96.4169466268398</v>
+        <v>96.41693899668692</v>
       </c>
       <c r="E346" t="n">
-        <v>96.40736389160156</v>
+        <v>96.40735626220703</v>
       </c>
       <c r="F346" t="n">
-        <v>96.40736389160156</v>
+        <v>96.40735626220703</v>
       </c>
       <c r="G346" t="n">
         <v>10109300</v>
@@ -8407,16 +8407,16 @@
         <v>45796</v>
       </c>
       <c r="C347" t="n">
-        <v>96.41695404052734</v>
+        <v>96.41694641113281</v>
       </c>
       <c r="D347" t="n">
-        <v>96.42654409156805</v>
+        <v>96.42653646141467</v>
       </c>
       <c r="E347" t="n">
-        <v>96.41695404052734</v>
+        <v>96.41694641113281</v>
       </c>
       <c r="F347" t="n">
-        <v>96.42654409156805</v>
+        <v>96.42653646141467</v>
       </c>
       <c r="G347" t="n">
         <v>15759100</v>
@@ -8430,16 +8430,16 @@
         <v>45797</v>
       </c>
       <c r="C348" t="n">
-        <v>96.43612670898438</v>
+        <v>96.43613433837891</v>
       </c>
       <c r="D348" t="n">
-        <v>96.43612670898438</v>
+        <v>96.43613433837891</v>
       </c>
       <c r="E348" t="n">
-        <v>96.42653665868291</v>
+        <v>96.42654428731873</v>
       </c>
       <c r="F348" t="n">
-        <v>96.43612670898438</v>
+        <v>96.43613433837891</v>
       </c>
       <c r="G348" t="n">
         <v>9249100</v>
@@ -8453,16 +8453,16 @@
         <v>45798</v>
       </c>
       <c r="C349" t="n">
-        <v>96.44571685791016</v>
+        <v>96.44570922851562</v>
       </c>
       <c r="D349" t="n">
-        <v>96.44571685791016</v>
+        <v>96.44570922851562</v>
       </c>
       <c r="E349" t="n">
-        <v>96.43613412193713</v>
+        <v>96.43612649330065</v>
       </c>
       <c r="F349" t="n">
-        <v>96.44571685791016</v>
+        <v>96.44570922851562</v>
       </c>
       <c r="G349" t="n">
         <v>11325900</v>
@@ -8476,16 +8476,16 @@
         <v>45799</v>
       </c>
       <c r="C350" t="n">
-        <v>96.46489715576172</v>
+        <v>96.46488952636719</v>
       </c>
       <c r="D350" t="n">
-        <v>96.46489715576172</v>
+        <v>96.46488952636719</v>
       </c>
       <c r="E350" t="n">
-        <v>96.45530710470361</v>
+        <v>96.45529947606755</v>
       </c>
       <c r="F350" t="n">
-        <v>96.45530710470361</v>
+        <v>96.45529947606755</v>
       </c>
       <c r="G350" t="n">
         <v>8901700</v>
@@ -8591,16 +8591,16 @@
         <v>45807</v>
       </c>
       <c r="C355" t="n">
-        <v>96.56077575683594</v>
+        <v>96.56076049804688</v>
       </c>
       <c r="D355" t="n">
-        <v>96.57036580789759</v>
+        <v>96.57035054759308</v>
       </c>
       <c r="E355" t="n">
-        <v>96.56077575683594</v>
+        <v>96.56076049804688</v>
       </c>
       <c r="F355" t="n">
-        <v>96.56077575683594</v>
+        <v>96.56076049804688</v>
       </c>
       <c r="G355" t="n">
         <v>14209500</v>
@@ -8614,16 +8614,16 @@
         <v>45810</v>
       </c>
       <c r="C356" t="n">
-        <v>96.58770751953125</v>
+        <v>96.58769989013672</v>
       </c>
       <c r="D356" t="n">
-        <v>96.58770751953125</v>
+        <v>96.58769989013672</v>
       </c>
       <c r="E356" t="n">
-        <v>96.57809059853618</v>
+        <v>96.57808296990129</v>
       </c>
       <c r="F356" t="n">
-        <v>96.58770751953125</v>
+        <v>96.58769989013672</v>
       </c>
       <c r="G356" t="n">
         <v>21934000</v>
@@ -8637,16 +8637,16 @@
         <v>45811</v>
       </c>
       <c r="C357" t="n">
-        <v>96.59734344482422</v>
+        <v>96.59732818603516</v>
       </c>
       <c r="D357" t="n">
-        <v>96.59734344482422</v>
+        <v>96.59732818603516</v>
       </c>
       <c r="E357" t="n">
-        <v>96.58771918150605</v>
+        <v>96.58770392423726</v>
       </c>
       <c r="F357" t="n">
-        <v>96.59253498374611</v>
+        <v>96.5925197257166</v>
       </c>
       <c r="G357" t="n">
         <v>11979500</v>
@@ -8660,16 +8660,16 @@
         <v>45812</v>
       </c>
       <c r="C358" t="n">
-        <v>96.60696411132812</v>
+        <v>96.60697174072266</v>
       </c>
       <c r="D358" t="n">
-        <v>96.60696411132812</v>
+        <v>96.60697174072266</v>
       </c>
       <c r="E358" t="n">
-        <v>96.59733984836828</v>
+        <v>96.59734747700276</v>
       </c>
       <c r="F358" t="n">
-        <v>96.60214830926736</v>
+        <v>96.60215593828157</v>
       </c>
       <c r="G358" t="n">
         <v>8923800</v>
@@ -8683,16 +8683,16 @@
         <v>45813</v>
       </c>
       <c r="C359" t="n">
-        <v>96.61658477783203</v>
+        <v>96.61659240722656</v>
       </c>
       <c r="D359" t="n">
-        <v>96.61658477783203</v>
+        <v>96.61659240722656</v>
       </c>
       <c r="E359" t="n">
-        <v>96.60696051523044</v>
+        <v>96.60696814386499</v>
       </c>
       <c r="F359" t="n">
-        <v>96.61658477783203</v>
+        <v>96.61659240722656</v>
       </c>
       <c r="G359" t="n">
         <v>9915800</v>
@@ -8706,16 +8706,16 @@
         <v>45814</v>
       </c>
       <c r="C360" t="n">
-        <v>96.64544677734375</v>
+        <v>96.64545440673828</v>
       </c>
       <c r="D360" t="n">
-        <v>96.65506369844093</v>
+        <v>96.65507132859463</v>
       </c>
       <c r="E360" t="n">
-        <v>96.64544677734375</v>
+        <v>96.64545440673828</v>
       </c>
       <c r="F360" t="n">
-        <v>96.65025523789234</v>
+        <v>96.65026286766646</v>
       </c>
       <c r="G360" t="n">
         <v>9122400</v>
@@ -8729,16 +8729,16 @@
         <v>45817</v>
       </c>
       <c r="C361" t="n">
-        <v>96.65505218505859</v>
+        <v>96.65505981445312</v>
       </c>
       <c r="D361" t="n">
-        <v>96.66467644617047</v>
+        <v>96.66468407632469</v>
       </c>
       <c r="E361" t="n">
-        <v>96.65505218505859</v>
+        <v>96.65505981445312</v>
       </c>
       <c r="F361" t="n">
-        <v>96.65505218505859</v>
+        <v>96.65505981445312</v>
       </c>
       <c r="G361" t="n">
         <v>9902100</v>
@@ -8752,16 +8752,16 @@
         <v>45818</v>
       </c>
       <c r="C362" t="n">
-        <v>96.66468811035156</v>
+        <v>96.66469573974609</v>
       </c>
       <c r="D362" t="n">
-        <v>96.67431237262477</v>
+        <v>96.67432000277891</v>
       </c>
       <c r="E362" t="n">
-        <v>96.66468811035156</v>
+        <v>96.66469573974609</v>
       </c>
       <c r="F362" t="n">
-        <v>96.6694965709076</v>
+        <v>96.66950420068163</v>
       </c>
       <c r="G362" t="n">
         <v>9201800</v>
@@ -8775,16 +8775,16 @@
         <v>45819</v>
       </c>
       <c r="C363" t="n">
-        <v>96.68394470214844</v>
+        <v>96.68393707275391</v>
       </c>
       <c r="D363" t="n">
-        <v>96.68394470214844</v>
+        <v>96.68393707275391</v>
       </c>
       <c r="E363" t="n">
-        <v>96.67432043907218</v>
+        <v>96.6743128104371</v>
       </c>
       <c r="F363" t="n">
-        <v>96.67912890002943</v>
+        <v>96.67912127101491</v>
       </c>
       <c r="G363" t="n">
         <v>10138800</v>
@@ -8798,16 +8798,16 @@
         <v>45820</v>
       </c>
       <c r="C364" t="n">
-        <v>96.69355010986328</v>
+        <v>96.69355773925781</v>
       </c>
       <c r="D364" t="n">
-        <v>96.69355010986328</v>
+        <v>96.69355773925781</v>
       </c>
       <c r="E364" t="n">
-        <v>96.68393318909396</v>
+        <v>96.68394081772971</v>
       </c>
       <c r="F364" t="n">
-        <v>96.69355010986328</v>
+        <v>96.69355773925781</v>
       </c>
       <c r="G364" t="n">
         <v>9574900</v>
@@ -8821,16 +8821,16 @@
         <v>45821</v>
       </c>
       <c r="C365" t="n">
-        <v>96.73204803466797</v>
+        <v>96.73204040527344</v>
       </c>
       <c r="D365" t="n">
-        <v>96.73204803466797</v>
+        <v>96.73204040527344</v>
       </c>
       <c r="E365" t="n">
-        <v>96.72242377192009</v>
+        <v>96.72241614328465</v>
       </c>
       <c r="F365" t="n">
-        <v>96.72242377192009</v>
+        <v>96.72241614328465</v>
       </c>
       <c r="G365" t="n">
         <v>7880300</v>
@@ -8844,16 +8844,16 @@
         <v>45824</v>
       </c>
       <c r="C366" t="n">
-        <v>96.73204803466797</v>
+        <v>96.73204040527344</v>
       </c>
       <c r="D366" t="n">
-        <v>96.74167229741583</v>
+        <v>96.74166466726223</v>
       </c>
       <c r="E366" t="n">
-        <v>96.73204803466797</v>
+        <v>96.73204040527344</v>
       </c>
       <c r="F366" t="n">
-        <v>96.74167229741583</v>
+        <v>96.74166466726223</v>
       </c>
       <c r="G366" t="n">
         <v>10286500</v>
@@ -8867,16 +8867,16 @@
         <v>45825</v>
       </c>
       <c r="C367" t="n">
-        <v>96.74166107177734</v>
+        <v>96.74166870117188</v>
       </c>
       <c r="D367" t="n">
-        <v>96.75128533340843</v>
+        <v>96.75129296356198</v>
       </c>
       <c r="E367" t="n">
-        <v>96.74166107177734</v>
+        <v>96.74166870117188</v>
       </c>
       <c r="F367" t="n">
-        <v>96.75128533340843</v>
+        <v>96.75129296356198</v>
       </c>
       <c r="G367" t="n">
         <v>8734500</v>
@@ -8913,16 +8913,16 @@
         <v>45828</v>
       </c>
       <c r="C369" t="n">
-        <v>96.79940795898438</v>
+        <v>96.79940032958984</v>
       </c>
       <c r="D369" t="n">
-        <v>96.80903222220624</v>
+        <v>96.80902459205316</v>
       </c>
       <c r="E369" t="n">
-        <v>96.79940795898438</v>
+        <v>96.79940032958984</v>
       </c>
       <c r="F369" t="n">
-        <v>96.80422376117625</v>
+        <v>96.80421613140216</v>
       </c>
       <c r="G369" t="n">
         <v>9399400</v>
@@ -8936,16 +8936,16 @@
         <v>45831</v>
       </c>
       <c r="C370" t="n">
-        <v>96.81864929199219</v>
+        <v>96.81864166259766</v>
       </c>
       <c r="D370" t="n">
-        <v>96.81864929199219</v>
+        <v>96.81864166259766</v>
       </c>
       <c r="E370" t="n">
-        <v>96.80902502948538</v>
+        <v>96.80901740084924</v>
       </c>
       <c r="F370" t="n">
-        <v>96.81383349015812</v>
+        <v>96.81382586114307</v>
       </c>
       <c r="G370" t="n">
         <v>8847300</v>
@@ -8959,16 +8959,16 @@
         <v>45832</v>
       </c>
       <c r="C371" t="n">
-        <v>96.82826232910156</v>
+        <v>96.82827758789062</v>
       </c>
       <c r="D371" t="n">
-        <v>96.8378865912223</v>
+        <v>96.837901851528</v>
       </c>
       <c r="E371" t="n">
-        <v>96.82826232910156</v>
+        <v>96.82827758789062</v>
       </c>
       <c r="F371" t="n">
-        <v>96.83307813074245</v>
+        <v>96.83309339029041</v>
       </c>
       <c r="G371" t="n">
         <v>10132100</v>
@@ -9120,16 +9120,16 @@
         <v>45841</v>
       </c>
       <c r="C378" t="n">
-        <v>96.96034240722656</v>
+        <v>96.96036529541016</v>
       </c>
       <c r="D378" t="n">
-        <v>96.96999995125557</v>
+        <v>96.9700228417189</v>
       </c>
       <c r="E378" t="n">
-        <v>96.96034240722656</v>
+        <v>96.96036529541016</v>
       </c>
       <c r="F378" t="n">
-        <v>96.96034240722656</v>
+        <v>96.96036529541016</v>
       </c>
       <c r="G378" t="n">
         <v>7404700</v>
@@ -9143,16 +9143,16 @@
         <v>45845</v>
       </c>
       <c r="C379" t="n">
-        <v>96.97966003417969</v>
+        <v>96.97965240478516</v>
       </c>
       <c r="D379" t="n">
-        <v>96.97966003417969</v>
+        <v>96.97965240478516</v>
       </c>
       <c r="E379" t="n">
-        <v>96.97000248989785</v>
+        <v>96.96999486126307</v>
       </c>
       <c r="F379" t="n">
-        <v>96.97966003417969</v>
+        <v>96.97965240478516</v>
       </c>
       <c r="G379" t="n">
         <v>12363900</v>
@@ -9166,16 +9166,16 @@
         <v>45846</v>
       </c>
       <c r="C380" t="n">
-        <v>96.99895477294922</v>
+        <v>96.99897003173828</v>
       </c>
       <c r="D380" t="n">
-        <v>96.99895477294922</v>
+        <v>96.99897003173828</v>
       </c>
       <c r="E380" t="n">
-        <v>96.97964705351775</v>
+        <v>96.97966230926953</v>
       </c>
       <c r="F380" t="n">
-        <v>96.98929722996003</v>
+        <v>96.98931248722988</v>
       </c>
       <c r="G380" t="n">
         <v>13107800</v>
@@ -9189,16 +9189,16 @@
         <v>45847</v>
       </c>
       <c r="C381" t="n">
-        <v>96.98929595947266</v>
+        <v>96.98930358886719</v>
       </c>
       <c r="D381" t="n">
-        <v>96.99895350233534</v>
+        <v>96.99896113248955</v>
       </c>
       <c r="E381" t="n">
-        <v>96.98929595947266</v>
+        <v>96.98930358886719</v>
       </c>
       <c r="F381" t="n">
-        <v>96.99895350233534</v>
+        <v>96.99896113248955</v>
       </c>
       <c r="G381" t="n">
         <v>11156600</v>
@@ -9212,16 +9212,16 @@
         <v>45848</v>
       </c>
       <c r="C382" t="n">
-        <v>97.00862884521484</v>
+        <v>97.00861358642578</v>
       </c>
       <c r="D382" t="n">
-        <v>97.01828638984958</v>
+        <v>97.01827112954146</v>
       </c>
       <c r="E382" t="n">
-        <v>96.99897130058011</v>
+        <v>96.99895604331012</v>
       </c>
       <c r="F382" t="n">
-        <v>97.00862884521484</v>
+        <v>97.00861358642578</v>
       </c>
       <c r="G382" t="n">
         <v>10071700</v>
@@ -9235,16 +9235,16 @@
         <v>45849</v>
       </c>
       <c r="C383" t="n">
-        <v>97.0472412109375</v>
+        <v>97.04725646972656</v>
       </c>
       <c r="D383" t="n">
-        <v>97.0472412109375</v>
+        <v>97.04725646972656</v>
       </c>
       <c r="E383" t="n">
-        <v>97.03758366734232</v>
+        <v>97.03759892461291</v>
       </c>
       <c r="F383" t="n">
-        <v>97.03758366734232</v>
+        <v>97.03759892461291</v>
       </c>
       <c r="G383" t="n">
         <v>9288900</v>
@@ -9258,16 +9258,16 @@
         <v>45852</v>
       </c>
       <c r="C384" t="n">
-        <v>97.0472412109375</v>
+        <v>97.04725646972656</v>
       </c>
       <c r="D384" t="n">
-        <v>97.05689138798532</v>
+        <v>97.05690664829169</v>
       </c>
       <c r="E384" t="n">
-        <v>97.0472412109375</v>
+        <v>97.04725646972656</v>
       </c>
       <c r="F384" t="n">
-        <v>97.05689138798532</v>
+        <v>97.05690664829169</v>
       </c>
       <c r="G384" t="n">
         <v>10293900</v>
@@ -9304,16 +9304,16 @@
         <v>45854</v>
       </c>
       <c r="C386" t="n">
-        <v>97.08586120605469</v>
+        <v>97.08586883544922</v>
       </c>
       <c r="D386" t="n">
-        <v>97.08586120605469</v>
+        <v>97.08586883544922</v>
       </c>
       <c r="E386" t="n">
-        <v>97.0762036627393</v>
+        <v>97.07621129137489</v>
       </c>
       <c r="F386" t="n">
-        <v>97.0762036627393</v>
+        <v>97.07621129137489</v>
       </c>
       <c r="G386" t="n">
         <v>8117900</v>
@@ -9327,16 +9327,16 @@
         <v>45855</v>
       </c>
       <c r="C387" t="n">
-        <v>97.09552764892578</v>
+        <v>97.09552001953125</v>
       </c>
       <c r="D387" t="n">
-        <v>97.09552764892578</v>
+        <v>97.09552001953125</v>
       </c>
       <c r="E387" t="n">
-        <v>97.08587747054088</v>
+        <v>97.08586984190462</v>
       </c>
       <c r="F387" t="n">
-        <v>97.09070255973333</v>
+        <v>97.09069493071793</v>
       </c>
       <c r="G387" t="n">
         <v>9040400</v>
@@ -9350,16 +9350,16 @@
         <v>45856</v>
       </c>
       <c r="C388" t="n">
-        <v>97.12448883056641</v>
+        <v>97.12448120117188</v>
       </c>
       <c r="D388" t="n">
-        <v>97.12448883056641</v>
+        <v>97.12448120117188</v>
       </c>
       <c r="E388" t="n">
-        <v>97.11483865258754</v>
+        <v>97.11483102395106</v>
       </c>
       <c r="F388" t="n">
-        <v>97.11483865258754</v>
+        <v>97.11483102395106</v>
       </c>
       <c r="G388" t="n">
         <v>9399500</v>
@@ -9373,16 +9373,16 @@
         <v>45859</v>
       </c>
       <c r="C389" t="n">
-        <v>97.1341552734375</v>
+        <v>97.13414001464844</v>
       </c>
       <c r="D389" t="n">
-        <v>97.1341552734375</v>
+        <v>97.13414001464844</v>
       </c>
       <c r="E389" t="n">
-        <v>97.12449772802584</v>
+        <v>97.12448247075388</v>
       </c>
       <c r="F389" t="n">
-        <v>97.12449772802584</v>
+        <v>97.12448247075388</v>
       </c>
       <c r="G389" t="n">
         <v>12893000</v>
@@ -9396,16 +9396,16 @@
         <v>45860</v>
       </c>
       <c r="C390" t="n">
-        <v>97.15346527099609</v>
+        <v>97.15345764160156</v>
       </c>
       <c r="D390" t="n">
-        <v>97.15346527099609</v>
+        <v>97.15345764160156</v>
       </c>
       <c r="E390" t="n">
-        <v>97.14380772609073</v>
+        <v>97.1438000974546</v>
       </c>
       <c r="F390" t="n">
-        <v>97.15346527099609</v>
+        <v>97.15345764160156</v>
       </c>
       <c r="G390" t="n">
         <v>9340600</v>
@@ -9419,16 +9419,16 @@
         <v>45861</v>
       </c>
       <c r="C391" t="n">
-        <v>97.16310119628906</v>
+        <v>97.16310882568359</v>
       </c>
       <c r="D391" t="n">
-        <v>97.16310119628906</v>
+        <v>97.16310882568359</v>
       </c>
       <c r="E391" t="n">
-        <v>97.15345101934767</v>
+        <v>97.15345864798445</v>
       </c>
       <c r="F391" t="n">
-        <v>97.16310119628906</v>
+        <v>97.16310882568359</v>
       </c>
       <c r="G391" t="n">
         <v>8056100</v>
@@ -9465,16 +9465,16 @@
         <v>45863</v>
       </c>
       <c r="C393" t="n">
-        <v>97.19207763671875</v>
+        <v>97.19209289550781</v>
       </c>
       <c r="D393" t="n">
-        <v>97.20172781403843</v>
+        <v>97.20174307434253</v>
       </c>
       <c r="E393" t="n">
-        <v>97.19207763671875</v>
+        <v>97.19209289550781</v>
       </c>
       <c r="F393" t="n">
-        <v>97.20172781403843</v>
+        <v>97.20174307434253</v>
       </c>
       <c r="G393" t="n">
         <v>9776600</v>
@@ -9488,16 +9488,16 @@
         <v>45866</v>
       </c>
       <c r="C394" t="n">
-        <v>97.22104644775391</v>
+        <v>97.22105407714844</v>
       </c>
       <c r="D394" t="n">
-        <v>97.22104644775391</v>
+        <v>97.22105407714844</v>
       </c>
       <c r="E394" t="n">
-        <v>97.21138890353441</v>
+        <v>97.21139653217107</v>
       </c>
       <c r="F394" t="n">
-        <v>97.21621399237023</v>
+        <v>97.21622162138554</v>
       </c>
       <c r="G394" t="n">
         <v>11581000</v>
@@ -9511,16 +9511,16 @@
         <v>45867</v>
       </c>
       <c r="C395" t="n">
-        <v>97.22104644775391</v>
+        <v>97.22105407714844</v>
       </c>
       <c r="D395" t="n">
-        <v>97.23069662542557</v>
+        <v>97.23070425557738</v>
       </c>
       <c r="E395" t="n">
-        <v>97.22104644775391</v>
+        <v>97.22105407714844</v>
       </c>
       <c r="F395" t="n">
-        <v>97.22104644775391</v>
+        <v>97.22105407714844</v>
       </c>
       <c r="G395" t="n">
         <v>8622300</v>
@@ -9534,16 +9534,16 @@
         <v>45868</v>
       </c>
       <c r="C396" t="n">
-        <v>97.2403564453125</v>
+        <v>97.24034881591797</v>
       </c>
       <c r="D396" t="n">
-        <v>97.2403564453125</v>
+        <v>97.24034881591797</v>
       </c>
       <c r="E396" t="n">
-        <v>97.230698900867</v>
+        <v>97.23069127223019</v>
       </c>
       <c r="F396" t="n">
-        <v>97.230698900867</v>
+        <v>97.23069127223019</v>
       </c>
       <c r="G396" t="n">
         <v>9106000</v>
@@ -9557,16 +9557,16 @@
         <v>45869</v>
       </c>
       <c r="C397" t="n">
-        <v>97.25001525878906</v>
+        <v>97.25000762939453</v>
       </c>
       <c r="D397" t="n">
-        <v>97.25001525878906</v>
+        <v>97.25000762939453</v>
       </c>
       <c r="E397" t="n">
-        <v>97.24035771421754</v>
+        <v>97.24035008558064</v>
       </c>
       <c r="F397" t="n">
-        <v>97.24518280322924</v>
+        <v>97.24517517421383</v>
       </c>
       <c r="G397" t="n">
         <v>19051200</v>
@@ -9580,16 +9580,16 @@
         <v>45870</v>
       </c>
       <c r="C398" t="n">
-        <v>97.28102874755859</v>
+        <v>97.281005859375</v>
       </c>
       <c r="D398" t="n">
-        <v>97.29072112835438</v>
+        <v>97.29069823789037</v>
       </c>
       <c r="E398" t="n">
-        <v>97.28102874755859</v>
+        <v>97.281005859375</v>
       </c>
       <c r="F398" t="n">
-        <v>97.28102874755859</v>
+        <v>97.281005859375</v>
       </c>
       <c r="G398" t="n">
         <v>26832500</v>
@@ -9603,16 +9603,16 @@
         <v>45873</v>
       </c>
       <c r="C399" t="n">
-        <v>97.3004150390625</v>
+        <v>97.30040740966797</v>
       </c>
       <c r="D399" t="n">
-        <v>97.3004150390625</v>
+        <v>97.30040740966797</v>
       </c>
       <c r="E399" t="n">
-        <v>97.2907226581143</v>
+        <v>97.29071502947977</v>
       </c>
       <c r="F399" t="n">
-        <v>97.29556515202816</v>
+        <v>97.29555752301393</v>
       </c>
       <c r="G399" t="n">
         <v>14766400</v>
@@ -9695,16 +9695,16 @@
         <v>45877</v>
       </c>
       <c r="C403" t="n">
-        <v>97.36824798583984</v>
+        <v>97.36824035644531</v>
       </c>
       <c r="D403" t="n">
-        <v>97.36824798583984</v>
+        <v>97.36824035644531</v>
       </c>
       <c r="E403" t="n">
-        <v>97.35855560478551</v>
+        <v>97.35854797615043</v>
       </c>
       <c r="F403" t="n">
-        <v>97.3633980987524</v>
+        <v>97.36339046973788</v>
       </c>
       <c r="G403" t="n">
         <v>12066300</v>
@@ -9718,16 +9718,16 @@
         <v>45880</v>
       </c>
       <c r="C404" t="n">
-        <v>97.37791442871094</v>
+        <v>97.37793731689453</v>
       </c>
       <c r="D404" t="n">
-        <v>97.37791442871094</v>
+        <v>97.37793731689453</v>
       </c>
       <c r="E404" t="n">
-        <v>97.36822944262161</v>
+        <v>97.3682523285288</v>
       </c>
       <c r="F404" t="n">
-        <v>97.37791442871094</v>
+        <v>97.37793731689453</v>
       </c>
       <c r="G404" t="n">
         <v>12940300</v>
@@ -9741,16 +9741,16 @@
         <v>45881</v>
       </c>
       <c r="C405" t="n">
-        <v>97.37791442871094</v>
+        <v>97.37793731689453</v>
       </c>
       <c r="D405" t="n">
-        <v>97.38760680791941</v>
+        <v>97.38762969838115</v>
       </c>
       <c r="E405" t="n">
-        <v>97.37791442871094</v>
+        <v>97.37793731689453</v>
       </c>
       <c r="F405" t="n">
-        <v>97.38760680791941</v>
+        <v>97.38762969838115</v>
       </c>
       <c r="G405" t="n">
         <v>12918200</v>
@@ -9764,16 +9764,16 @@
         <v>45882</v>
       </c>
       <c r="C406" t="n">
-        <v>97.39729309082031</v>
+        <v>97.39730834960938</v>
       </c>
       <c r="D406" t="n">
-        <v>97.40697807630343</v>
+        <v>97.4069933366098</v>
       </c>
       <c r="E406" t="n">
-        <v>97.3876007122185</v>
+        <v>97.3876159694891</v>
       </c>
       <c r="F406" t="n">
-        <v>97.39729309082031</v>
+        <v>97.39730834960938</v>
       </c>
       <c r="G406" t="n">
         <v>12144800</v>
@@ -9787,16 +9787,16 @@
         <v>45883</v>
       </c>
       <c r="C407" t="n">
-        <v>97.40699005126953</v>
+        <v>97.40699768066406</v>
       </c>
       <c r="D407" t="n">
-        <v>97.4166824310629</v>
+        <v>97.41669006121658</v>
       </c>
       <c r="E407" t="n">
-        <v>97.40699005126953</v>
+        <v>97.40699768066406</v>
       </c>
       <c r="F407" t="n">
-        <v>97.40699005126953</v>
+        <v>97.40699768066406</v>
       </c>
       <c r="G407" t="n">
         <v>9798900</v>
@@ -9879,16 +9879,16 @@
         <v>45889</v>
       </c>
       <c r="C411" t="n">
-        <v>97.48451995849609</v>
+        <v>97.48451232910156</v>
       </c>
       <c r="D411" t="n">
-        <v>97.48451995849609</v>
+        <v>97.48451232910156</v>
       </c>
       <c r="E411" t="n">
-        <v>97.47482757814046</v>
+        <v>97.47481994950448</v>
       </c>
       <c r="F411" t="n">
-        <v>97.48451995849609</v>
+        <v>97.48451232910156</v>
       </c>
       <c r="G411" t="n">
         <v>10922100</v>
@@ -9902,16 +9902,16 @@
         <v>45890</v>
       </c>
       <c r="C412" t="n">
-        <v>97.48451995849609</v>
+        <v>97.48451232910156</v>
       </c>
       <c r="D412" t="n">
-        <v>97.49421233885172</v>
+        <v>97.49420470869863</v>
       </c>
       <c r="E412" t="n">
-        <v>97.48451995849609</v>
+        <v>97.48451232910156</v>
       </c>
       <c r="F412" t="n">
-        <v>97.49421233885172</v>
+        <v>97.49420470869863</v>
       </c>
       <c r="G412" t="n">
         <v>8765300</v>
@@ -9994,16 +9994,16 @@
         <v>45896</v>
       </c>
       <c r="C416" t="n">
-        <v>97.55236053466797</v>
+        <v>97.55235290527344</v>
       </c>
       <c r="D416" t="n">
-        <v>97.56205291588799</v>
+        <v>97.56204528573542</v>
       </c>
       <c r="E416" t="n">
-        <v>97.55236053466797</v>
+        <v>97.55235290527344</v>
       </c>
       <c r="F416" t="n">
-        <v>97.56205291588799</v>
+        <v>97.56204528573542</v>
       </c>
       <c r="G416" t="n">
         <v>7384600</v>
@@ -10017,16 +10017,16 @@
         <v>45897</v>
       </c>
       <c r="C417" t="n">
-        <v>97.56202697753906</v>
+        <v>97.56203460693359</v>
       </c>
       <c r="D417" t="n">
-        <v>97.57171935618221</v>
+        <v>97.57172698633468</v>
       </c>
       <c r="E417" t="n">
-        <v>97.56202697753906</v>
+        <v>97.56203460693359</v>
       </c>
       <c r="F417" t="n">
-        <v>97.56686947030127</v>
+        <v>97.56687710007449</v>
       </c>
       <c r="G417" t="n">
         <v>8816600</v>
@@ -10063,16 +10063,16 @@
         <v>45902</v>
       </c>
       <c r="C419" t="n">
-        <v>97.62990570068359</v>
+        <v>97.62989807128906</v>
       </c>
       <c r="D419" t="n">
-        <v>97.62990570068359</v>
+        <v>97.62989807128906</v>
       </c>
       <c r="E419" t="n">
-        <v>97.62017856030185</v>
+        <v>97.62017093166746</v>
       </c>
       <c r="F419" t="n">
-        <v>97.62990570068359</v>
+        <v>97.62989807128906</v>
       </c>
       <c r="G419" t="n">
         <v>27254500</v>
@@ -10109,16 +10109,16 @@
         <v>45904</v>
       </c>
       <c r="C421" t="n">
-        <v>97.65908050537109</v>
+        <v>97.65908813476562</v>
       </c>
       <c r="D421" t="n">
-        <v>97.65908050537109</v>
+        <v>97.65908813476562</v>
       </c>
       <c r="E421" t="n">
-        <v>97.64936078454357</v>
+        <v>97.64936841317878</v>
       </c>
       <c r="F421" t="n">
-        <v>97.65422064495733</v>
+        <v>97.65422827397219</v>
       </c>
       <c r="G421" t="n">
         <v>11300200</v>
@@ -10224,16 +10224,16 @@
         <v>45911</v>
       </c>
       <c r="C426" t="n">
-        <v>97.73687744140625</v>
+        <v>97.73689270019531</v>
       </c>
       <c r="D426" t="n">
-        <v>97.73687744140625</v>
+        <v>97.73689270019531</v>
       </c>
       <c r="E426" t="n">
-        <v>97.7271503014768</v>
+        <v>97.72716555874725</v>
       </c>
       <c r="F426" t="n">
-        <v>97.73201758125843</v>
+        <v>97.73203283928876</v>
       </c>
       <c r="G426" t="n">
         <v>9136600</v>
@@ -10293,16 +10293,16 @@
         <v>45916</v>
       </c>
       <c r="C429" t="n">
-        <v>97.78550720214844</v>
+        <v>97.78551483154297</v>
       </c>
       <c r="D429" t="n">
-        <v>97.79522692259125</v>
+        <v>97.79523455274413</v>
       </c>
       <c r="E429" t="n">
-        <v>97.78550720214844</v>
+        <v>97.78551483154297</v>
       </c>
       <c r="F429" t="n">
-        <v>97.78550720214844</v>
+        <v>97.78551483154297</v>
       </c>
       <c r="G429" t="n">
         <v>11551900</v>
@@ -10316,16 +10316,16 @@
         <v>45917</v>
       </c>
       <c r="C430" t="n">
-        <v>97.79523468017578</v>
+        <v>97.79522705078125</v>
       </c>
       <c r="D430" t="n">
-        <v>97.80496182102412</v>
+        <v>97.80495419087075</v>
       </c>
       <c r="E430" t="n">
-        <v>97.79523468017578</v>
+        <v>97.79522705078125</v>
       </c>
       <c r="F430" t="n">
-        <v>97.80496182102412</v>
+        <v>97.80495419087075</v>
       </c>
       <c r="G430" t="n">
         <v>10381200</v>
@@ -10339,16 +10339,16 @@
         <v>45918</v>
       </c>
       <c r="C431" t="n">
-        <v>97.81468963623047</v>
+        <v>97.81468200683594</v>
       </c>
       <c r="D431" t="n">
-        <v>97.81468963623047</v>
+        <v>97.81468200683594</v>
       </c>
       <c r="E431" t="n">
-        <v>97.80496249531507</v>
+        <v>97.80495486667922</v>
       </c>
       <c r="F431" t="n">
-        <v>97.81468963623047</v>
+        <v>97.81468200683594</v>
       </c>
       <c r="G431" t="n">
         <v>13414500</v>
@@ -10408,16 +10408,16 @@
         <v>45923</v>
       </c>
       <c r="C434" t="n">
-        <v>97.87303924560547</v>
+        <v>97.87301635742188</v>
       </c>
       <c r="D434" t="n">
-        <v>97.87303924560547</v>
+        <v>97.87301635742188</v>
       </c>
       <c r="E434" t="n">
-        <v>97.86331210453073</v>
+        <v>97.86328921862189</v>
       </c>
       <c r="F434" t="n">
-        <v>97.86817938488544</v>
+        <v>97.86815649783836</v>
       </c>
       <c r="G434" t="n">
         <v>11191700</v>
@@ -10431,16 +10431,16 @@
         <v>45924</v>
       </c>
       <c r="C435" t="n">
-        <v>97.88275146484375</v>
+        <v>97.88275909423828</v>
       </c>
       <c r="D435" t="n">
-        <v>97.88275146484375</v>
+        <v>97.88275909423828</v>
       </c>
       <c r="E435" t="n">
-        <v>97.87302432525188</v>
+        <v>97.87303195388823</v>
       </c>
       <c r="F435" t="n">
-        <v>97.87788418523103</v>
+        <v>97.8778918142462</v>
       </c>
       <c r="G435" t="n">
         <v>10108500</v>
@@ -10454,16 +10454,16 @@
         <v>45925</v>
       </c>
       <c r="C436" t="n">
-        <v>97.89247894287109</v>
+        <v>97.89247131347656</v>
       </c>
       <c r="D436" t="n">
-        <v>97.89247894287109</v>
+        <v>97.89247131347656</v>
       </c>
       <c r="E436" t="n">
-        <v>97.88275180324558</v>
+        <v>97.88274417460916</v>
       </c>
       <c r="F436" t="n">
-        <v>97.88275180324558</v>
+        <v>97.88274417460916</v>
       </c>
       <c r="G436" t="n">
         <v>10549100</v>
@@ -10477,16 +10477,16 @@
         <v>45926</v>
       </c>
       <c r="C437" t="n">
-        <v>97.92165374755859</v>
+        <v>97.92166137695312</v>
       </c>
       <c r="D437" t="n">
-        <v>97.92165374755859</v>
+        <v>97.92166137695312</v>
       </c>
       <c r="E437" t="n">
-        <v>97.91192660785308</v>
+        <v>97.91193423648973</v>
       </c>
       <c r="F437" t="n">
-        <v>97.91192660785308</v>
+        <v>97.91193423648973</v>
       </c>
       <c r="G437" t="n">
         <v>10688600</v>
@@ -10546,16 +10546,16 @@
         <v>45931</v>
       </c>
       <c r="C440" t="n">
-        <v>97.94797515869141</v>
+        <v>97.94796752929688</v>
       </c>
       <c r="D440" t="n">
-        <v>97.95772848817732</v>
+        <v>97.95772085802308</v>
       </c>
       <c r="E440" t="n">
-        <v>97.94797515869141</v>
+        <v>97.94796752929688</v>
       </c>
       <c r="F440" t="n">
-        <v>97.95772848817732</v>
+        <v>97.95772085802308</v>
       </c>
       <c r="G440" t="n">
         <v>26613600</v>
@@ -10569,16 +10569,16 @@
         <v>45932</v>
       </c>
       <c r="C441" t="n">
-        <v>97.95771026611328</v>
+        <v>97.95771789550781</v>
       </c>
       <c r="D441" t="n">
-        <v>97.96747103907319</v>
+        <v>97.96747866922793</v>
       </c>
       <c r="E441" t="n">
-        <v>97.95771026611328</v>
+        <v>97.95771789550781</v>
       </c>
       <c r="F441" t="n">
-        <v>97.96747103907319</v>
+        <v>97.96747866922793</v>
       </c>
       <c r="G441" t="n">
         <v>12870100</v>
@@ -10592,16 +10592,16 @@
         <v>45933</v>
       </c>
       <c r="C442" t="n">
-        <v>97.99675750732422</v>
+        <v>97.99677276611328</v>
       </c>
       <c r="D442" t="n">
-        <v>97.99675750732422</v>
+        <v>97.99677276611328</v>
       </c>
       <c r="E442" t="n">
-        <v>97.98700417849862</v>
+        <v>97.98701943576903</v>
       </c>
       <c r="F442" t="n">
-        <v>97.99675750732422</v>
+        <v>97.99677276611328</v>
       </c>
       <c r="G442" t="n">
         <v>13837400</v>
@@ -10615,16 +10615,16 @@
         <v>45936</v>
       </c>
       <c r="C443" t="n">
-        <v>97.99675750732422</v>
+        <v>97.99677276611328</v>
       </c>
       <c r="D443" t="n">
-        <v>98.00651828143899</v>
+        <v>98.00653354174787</v>
       </c>
       <c r="E443" t="n">
-        <v>97.99675750732422</v>
+        <v>97.99677276611328</v>
       </c>
       <c r="F443" t="n">
-        <v>98.00651828143899</v>
+        <v>98.00653354174787</v>
       </c>
       <c r="G443" t="n">
         <v>13944300</v>
@@ -10684,16 +10684,16 @@
         <v>45939</v>
       </c>
       <c r="C446" t="n">
-        <v>98.03578948974609</v>
+        <v>98.03580474853516</v>
       </c>
       <c r="D446" t="n">
-        <v>98.0455502634956</v>
+        <v>98.04556552380387</v>
       </c>
       <c r="E446" t="n">
-        <v>98.0260287159966</v>
+        <v>98.02604397326645</v>
       </c>
       <c r="F446" t="n">
-        <v>98.0455502634956</v>
+        <v>98.04556552380387</v>
       </c>
       <c r="G446" t="n">
         <v>15718900</v>
@@ -10707,16 +10707,16 @@
         <v>45940</v>
       </c>
       <c r="C447" t="n">
-        <v>98.0845947265625</v>
+        <v>98.08458709716797</v>
       </c>
       <c r="D447" t="n">
-        <v>98.0845947265625</v>
+        <v>98.08458709716797</v>
       </c>
       <c r="E447" t="n">
-        <v>98.06507317730942</v>
+        <v>98.06506554943334</v>
       </c>
       <c r="F447" t="n">
-        <v>98.07483395193596</v>
+        <v>98.07482632330066</v>
       </c>
       <c r="G447" t="n">
         <v>18966600</v>
@@ -10730,16 +10730,16 @@
         <v>45943</v>
       </c>
       <c r="C448" t="n">
-        <v>98.07483673095703</v>
+        <v>98.07484436035156</v>
       </c>
       <c r="D448" t="n">
-        <v>98.08459750586016</v>
+        <v>98.08460513601399</v>
       </c>
       <c r="E448" t="n">
-        <v>98.07483673095703</v>
+        <v>98.07484436035156</v>
       </c>
       <c r="F448" t="n">
-        <v>98.07483673095703</v>
+        <v>98.07484436035156</v>
       </c>
       <c r="G448" t="n">
         <v>14453500</v>
@@ -10753,16 +10753,16 @@
         <v>45944</v>
       </c>
       <c r="C449" t="n">
-        <v>98.0845947265625</v>
+        <v>98.08458709716797</v>
       </c>
       <c r="D449" t="n">
-        <v>98.09434805589947</v>
+        <v>98.0943404257463</v>
       </c>
       <c r="E449" t="n">
-        <v>98.0845947265625</v>
+        <v>98.08458709716797</v>
       </c>
       <c r="F449" t="n">
-        <v>98.0845947265625</v>
+        <v>98.08458709716797</v>
       </c>
       <c r="G449" t="n">
         <v>13475000</v>
@@ -10799,16 +10799,16 @@
         <v>45946</v>
       </c>
       <c r="C451" t="n">
-        <v>98.11386871337891</v>
+        <v>98.11387634277344</v>
       </c>
       <c r="D451" t="n">
-        <v>98.11386871337891</v>
+        <v>98.11387634277344</v>
       </c>
       <c r="E451" t="n">
-        <v>98.10410793884108</v>
+        <v>98.1041155674766</v>
       </c>
       <c r="F451" t="n">
-        <v>98.11386871337891</v>
+        <v>98.11387634277344</v>
       </c>
       <c r="G451" t="n">
         <v>12394500</v>
@@ -10822,16 +10822,16 @@
         <v>45947</v>
       </c>
       <c r="C452" t="n">
-        <v>98.14314270019531</v>
+        <v>98.14315032958984</v>
       </c>
       <c r="D452" t="n">
-        <v>98.14314270019531</v>
+        <v>98.14315032958984</v>
       </c>
       <c r="E452" t="n">
-        <v>98.13338192574615</v>
+        <v>98.13338955438189</v>
       </c>
       <c r="F452" t="n">
-        <v>98.13826603561544</v>
+        <v>98.13827366463087</v>
       </c>
       <c r="G452" t="n">
         <v>14603500</v>
@@ -10845,16 +10845,16 @@
         <v>45950</v>
       </c>
       <c r="C453" t="n">
-        <v>98.15291595458984</v>
+        <v>98.15290069580078</v>
       </c>
       <c r="D453" t="n">
-        <v>98.15291595458984</v>
+        <v>98.15290069580078</v>
       </c>
       <c r="E453" t="n">
-        <v>98.14315517889962</v>
+        <v>98.14313992162796</v>
       </c>
       <c r="F453" t="n">
-        <v>98.15291595458984</v>
+        <v>98.15290069580078</v>
       </c>
       <c r="G453" t="n">
         <v>16129100</v>
@@ -10868,16 +10868,16 @@
         <v>45951</v>
       </c>
       <c r="C454" t="n">
-        <v>98.17242431640625</v>
+        <v>98.17241668701172</v>
       </c>
       <c r="D454" t="n">
-        <v>98.17242431640625</v>
+        <v>98.17241668701172</v>
       </c>
       <c r="E454" t="n">
-        <v>98.16266354128715</v>
+        <v>98.16265591265116</v>
       </c>
       <c r="F454" t="n">
-        <v>98.16266354128715</v>
+        <v>98.16265591265116</v>
       </c>
       <c r="G454" t="n">
         <v>12061900</v>
@@ -10891,16 +10891,16 @@
         <v>45952</v>
       </c>
       <c r="C455" t="n">
-        <v>98.18217468261719</v>
+        <v>98.18218231201172</v>
       </c>
       <c r="D455" t="n">
-        <v>98.18217468261719</v>
+        <v>98.18218231201172</v>
       </c>
       <c r="E455" t="n">
-        <v>98.17241390853287</v>
+        <v>98.17242153716894</v>
       </c>
       <c r="F455" t="n">
-        <v>98.18217468261719</v>
+        <v>98.18218231201172</v>
       </c>
       <c r="G455" t="n">
         <v>9089900</v>
@@ -10914,16 +10914,16 @@
         <v>45953</v>
       </c>
       <c r="C456" t="n">
-        <v>98.19194793701172</v>
+        <v>98.19194030761719</v>
       </c>
       <c r="D456" t="n">
-        <v>98.19194793701172</v>
+        <v>98.19194030761719</v>
       </c>
       <c r="E456" t="n">
-        <v>98.18218716168681</v>
+        <v>98.18217953305069</v>
       </c>
       <c r="F456" t="n">
-        <v>98.19194793701172</v>
+        <v>98.19194030761719</v>
       </c>
       <c r="G456" t="n">
         <v>10658100</v>
@@ -10937,16 +10937,16 @@
         <v>45954</v>
       </c>
       <c r="C457" t="n">
-        <v>98.22120666503906</v>
+        <v>98.22121429443359</v>
       </c>
       <c r="D457" t="n">
-        <v>98.22120666503906</v>
+        <v>98.22121429443359</v>
       </c>
       <c r="E457" t="n">
-        <v>98.21144589131933</v>
+        <v>98.21145351995568</v>
       </c>
       <c r="F457" t="n">
-        <v>98.22120666503906</v>
+        <v>98.22121429443359</v>
       </c>
       <c r="G457" t="n">
         <v>12382000</v>
@@ -10960,16 +10960,16 @@
         <v>45957</v>
       </c>
       <c r="C458" t="n">
-        <v>98.23097229003906</v>
+        <v>98.23096466064453</v>
       </c>
       <c r="D458" t="n">
-        <v>98.2407256189516</v>
+        <v>98.24071798879955</v>
       </c>
       <c r="E458" t="n">
-        <v>98.22121151583728</v>
+        <v>98.22120388720086</v>
       </c>
       <c r="F458" t="n">
-        <v>98.22121151583728</v>
+        <v>98.22120388720086</v>
       </c>
       <c r="G458" t="n">
         <v>26389600</v>
@@ -10983,16 +10983,16 @@
         <v>45958</v>
       </c>
       <c r="C459" t="n">
-        <v>98.24072265625</v>
+        <v>98.24073791503906</v>
       </c>
       <c r="D459" t="n">
-        <v>98.25048343015742</v>
+        <v>98.25049869046254</v>
       </c>
       <c r="E459" t="n">
-        <v>98.24072265625</v>
+        <v>98.24073791503906</v>
       </c>
       <c r="F459" t="n">
-        <v>98.24072265625</v>
+        <v>98.24073791503906</v>
       </c>
       <c r="G459" t="n">
         <v>11134700</v>
@@ -11121,16 +11121,16 @@
         <v>45966</v>
       </c>
       <c r="C465" t="n">
-        <v>98.33652496337891</v>
+        <v>98.33653259277344</v>
       </c>
       <c r="D465" t="n">
-        <v>98.33652496337891</v>
+        <v>98.33653259277344</v>
       </c>
       <c r="E465" t="n">
-        <v>98.32673781849851</v>
+        <v>98.3267454471337</v>
       </c>
       <c r="F465" t="n">
-        <v>98.32673781849851</v>
+        <v>98.3267454471337</v>
       </c>
       <c r="G465" t="n">
         <v>11335000</v>
@@ -11144,16 +11144,16 @@
         <v>45967</v>
       </c>
       <c r="C466" t="n">
-        <v>98.3463134765625</v>
+        <v>98.34632110595703</v>
       </c>
       <c r="D466" t="n">
-        <v>98.3463134765625</v>
+        <v>98.34632110595703</v>
       </c>
       <c r="E466" t="n">
-        <v>98.33651886118693</v>
+        <v>98.33652648982164</v>
       </c>
       <c r="F466" t="n">
-        <v>98.3463134765625</v>
+        <v>98.34632110595703</v>
       </c>
       <c r="G466" t="n">
         <v>16658100</v>
@@ -11213,16 +11213,16 @@
         <v>45972</v>
       </c>
       <c r="C469" t="n">
-        <v>98.39528656005859</v>
+        <v>98.39527893066406</v>
       </c>
       <c r="D469" t="n">
-        <v>98.39528656005859</v>
+        <v>98.39527893066406</v>
       </c>
       <c r="E469" t="n">
-        <v>98.38549194393867</v>
+        <v>98.3854843153036</v>
       </c>
       <c r="F469" t="n">
-        <v>98.39528656005859</v>
+        <v>98.39527893066406</v>
       </c>
       <c r="G469" t="n">
         <v>8697800</v>
@@ -11305,16 +11305,16 @@
         <v>45978</v>
       </c>
       <c r="C473" t="n">
-        <v>98.45403289794922</v>
+        <v>98.45402526855469</v>
       </c>
       <c r="D473" t="n">
-        <v>98.45403289794922</v>
+        <v>98.45402526855469</v>
       </c>
       <c r="E473" t="n">
-        <v>98.44423828246764</v>
+        <v>98.44423065383212</v>
       </c>
       <c r="F473" t="n">
-        <v>98.44913932575972</v>
+        <v>98.4491316967444</v>
       </c>
       <c r="G473" t="n">
         <v>15032800</v>
@@ -11328,16 +11328,16 @@
         <v>45979</v>
       </c>
       <c r="C474" t="n">
-        <v>98.45403289794922</v>
+        <v>98.45402526855469</v>
       </c>
       <c r="D474" t="n">
-        <v>98.46382751343079</v>
+        <v>98.46381988327725</v>
       </c>
       <c r="E474" t="n">
-        <v>98.45403289794922</v>
+        <v>98.45402526855469</v>
       </c>
       <c r="F474" t="n">
-        <v>98.45403289794922</v>
+        <v>98.45402526855469</v>
       </c>
       <c r="G474" t="n">
         <v>13130300</v>
@@ -11351,16 +11351,16 @@
         <v>45980</v>
       </c>
       <c r="C475" t="n">
-        <v>98.47360992431641</v>
+        <v>98.47362518310547</v>
       </c>
       <c r="D475" t="n">
-        <v>98.47360992431641</v>
+        <v>98.47362518310547</v>
       </c>
       <c r="E475" t="n">
-        <v>98.46382278040787</v>
+        <v>98.46383803768039</v>
       </c>
       <c r="F475" t="n">
-        <v>98.46382278040787</v>
+        <v>98.46383803768039</v>
       </c>
       <c r="G475" t="n">
         <v>23022400</v>
@@ -11397,16 +11397,16 @@
         <v>45982</v>
       </c>
       <c r="C477" t="n">
-        <v>98.51277923583984</v>
+        <v>98.51278686523438</v>
       </c>
       <c r="D477" t="n">
-        <v>98.51277923583984</v>
+        <v>98.51278686523438</v>
       </c>
       <c r="E477" t="n">
-        <v>98.50298462099586</v>
+        <v>98.50299224963184</v>
       </c>
       <c r="F477" t="n">
-        <v>98.51277923583984</v>
+        <v>98.51278686523438</v>
       </c>
       <c r="G477" t="n">
         <v>16446900</v>
@@ -11466,16 +11466,16 @@
         <v>45987</v>
       </c>
       <c r="C480" t="n">
-        <v>98.55195617675781</v>
+        <v>98.55196380615234</v>
       </c>
       <c r="D480" t="n">
-        <v>98.56175079219341</v>
+        <v>98.56175842234617</v>
       </c>
       <c r="E480" t="n">
-        <v>98.55195617675781</v>
+        <v>98.55196380615234</v>
       </c>
       <c r="F480" t="n">
-        <v>98.55195617675781</v>
+        <v>98.55196380615234</v>
       </c>
       <c r="G480" t="n">
         <v>11948500</v>
@@ -11489,16 +11489,16 @@
         <v>45989</v>
       </c>
       <c r="C481" t="n">
-        <v>98.58132934570312</v>
+        <v>98.58133697509766</v>
       </c>
       <c r="D481" t="n">
-        <v>98.59112396082016</v>
+        <v>98.59113159097269</v>
       </c>
       <c r="E481" t="n">
-        <v>98.5715422016884</v>
+        <v>98.57154983032548</v>
       </c>
       <c r="F481" t="n">
-        <v>98.58132934570312</v>
+        <v>98.58133697509766</v>
       </c>
       <c r="G481" t="n">
         <v>24417500</v>
@@ -11512,16 +11512,16 @@
         <v>45992</v>
       </c>
       <c r="C482" t="n">
-        <v>98.60391998291016</v>
+        <v>98.60392761230469</v>
       </c>
       <c r="D482" t="n">
-        <v>98.60391998291016</v>
+        <v>98.60392761230469</v>
       </c>
       <c r="E482" t="n">
-        <v>98.59410231425819</v>
+        <v>98.59410994289308</v>
       </c>
       <c r="F482" t="n">
-        <v>98.60391998291016</v>
+        <v>98.60392761230469</v>
       </c>
       <c r="G482" t="n">
         <v>29025600</v>
@@ -11535,16 +11535,16 @@
         <v>45993</v>
       </c>
       <c r="C483" t="n">
-        <v>98.62357330322266</v>
+        <v>98.62358093261719</v>
       </c>
       <c r="D483" t="n">
-        <v>98.62357330322266</v>
+        <v>98.62358093261719</v>
       </c>
       <c r="E483" t="n">
-        <v>98.61374813986885</v>
+        <v>98.61375576850331</v>
       </c>
       <c r="F483" t="n">
-        <v>98.61374813986885</v>
+        <v>98.61375576850331</v>
       </c>
       <c r="G483" t="n">
         <v>14362600</v>
@@ -11581,16 +11581,16 @@
         <v>45995</v>
       </c>
       <c r="C485" t="n">
-        <v>98.65305328369141</v>
+        <v>98.65304565429688</v>
       </c>
       <c r="D485" t="n">
-        <v>98.65305328369141</v>
+        <v>98.65304565429688</v>
       </c>
       <c r="E485" t="n">
-        <v>98.64322811914398</v>
+        <v>98.64322049050931</v>
       </c>
       <c r="F485" t="n">
-        <v>98.64322811914398</v>
+        <v>98.64322049050931</v>
       </c>
       <c r="G485" t="n">
         <v>13689600</v>
@@ -11604,16 +11604,16 @@
         <v>45996</v>
       </c>
       <c r="C486" t="n">
-        <v>98.68250274658203</v>
+        <v>98.68251037597656</v>
       </c>
       <c r="D486" t="n">
-        <v>98.68250274658203</v>
+        <v>98.68251037597656</v>
       </c>
       <c r="E486" t="n">
-        <v>98.67267758388016</v>
+        <v>98.67268521251508</v>
       </c>
       <c r="F486" t="n">
-        <v>98.67267758388016</v>
+        <v>98.67268521251508</v>
       </c>
       <c r="G486" t="n">
         <v>17918100</v>
@@ -11627,16 +11627,16 @@
         <v>45999</v>
       </c>
       <c r="C487" t="n">
-        <v>98.68250274658203</v>
+        <v>98.68251037597656</v>
       </c>
       <c r="D487" t="n">
-        <v>98.68250274658203</v>
+        <v>98.68251037597656</v>
       </c>
       <c r="E487" t="n">
-        <v>98.67267758388016</v>
+        <v>98.67268521251508</v>
       </c>
       <c r="F487" t="n">
-        <v>98.68250274658203</v>
+        <v>98.68251037597656</v>
       </c>
       <c r="G487" t="n">
         <v>16657900</v>
@@ -11650,16 +11650,16 @@
         <v>46000</v>
       </c>
       <c r="C488" t="n">
-        <v>98.69233703613281</v>
+        <v>98.69232940673828</v>
       </c>
       <c r="D488" t="n">
-        <v>98.69724587073607</v>
+        <v>98.69723824096205</v>
       </c>
       <c r="E488" t="n">
-        <v>98.69233703613281</v>
+        <v>98.69232940673828</v>
       </c>
       <c r="F488" t="n">
-        <v>98.69233703613281</v>
+        <v>98.69232940673828</v>
       </c>
       <c r="G488" t="n">
         <v>11016400</v>
@@ -11673,16 +11673,16 @@
         <v>46001</v>
       </c>
       <c r="C489" t="n">
-        <v>98.69233703613281</v>
+        <v>98.69232940673828</v>
       </c>
       <c r="D489" t="n">
-        <v>98.7021621997433</v>
+        <v>98.70215456958923</v>
       </c>
       <c r="E489" t="n">
-        <v>98.69233703613281</v>
+        <v>98.69232940673828</v>
       </c>
       <c r="F489" t="n">
-        <v>98.7021621997433</v>
+        <v>98.70215456958923</v>
       </c>
       <c r="G489" t="n">
         <v>12234900</v>
@@ -11788,16 +11788,16 @@
         <v>46008</v>
       </c>
       <c r="C494" t="n">
-        <v>98.78073883056641</v>
+        <v>98.78074645996094</v>
       </c>
       <c r="D494" t="n">
-        <v>98.78073883056641</v>
+        <v>98.78074645996094</v>
       </c>
       <c r="E494" t="n">
-        <v>98.77092116157804</v>
+        <v>98.7709287902143</v>
       </c>
       <c r="F494" t="n">
-        <v>98.77092116157804</v>
+        <v>98.7709287902143</v>
       </c>
       <c r="G494" t="n">
         <v>13788200</v>
@@ -11811,16 +11811,16 @@
         <v>46009</v>
       </c>
       <c r="C495" t="n">
-        <v>98.78073883056641</v>
+        <v>98.78074645996094</v>
       </c>
       <c r="D495" t="n">
-        <v>98.79056399395857</v>
+        <v>98.79057162411196</v>
       </c>
       <c r="E495" t="n">
-        <v>98.78073883056641</v>
+        <v>98.78074645996094</v>
       </c>
       <c r="F495" t="n">
-        <v>98.79056399395857</v>
+        <v>98.79057162411196</v>
       </c>
       <c r="G495" t="n">
         <v>20890600</v>
@@ -11903,16 +11903,16 @@
         <v>46015</v>
       </c>
       <c r="C499" t="n">
-        <v>98.85268402099609</v>
+        <v>98.85269165039062</v>
       </c>
       <c r="D499" t="n">
-        <v>98.86254084520495</v>
+        <v>98.86254847536023</v>
       </c>
       <c r="E499" t="n">
-        <v>98.85268402099609</v>
+        <v>98.85269165039062</v>
       </c>
       <c r="F499" t="n">
-        <v>98.86254084520495</v>
+        <v>98.86254847536023</v>
       </c>
       <c r="G499" t="n">
         <v>7791300</v>
@@ -11972,16 +11972,16 @@
         <v>46021</v>
       </c>
       <c r="C502" t="n">
-        <v>98.91181182861328</v>
+        <v>98.91181945800781</v>
       </c>
       <c r="D502" t="n">
-        <v>98.91181182861328</v>
+        <v>98.91181945800781</v>
       </c>
       <c r="E502" t="n">
-        <v>98.90195500496438</v>
+        <v>98.90196263359863</v>
       </c>
       <c r="F502" t="n">
-        <v>98.90687965751208</v>
+        <v>98.90688728652617</v>
       </c>
       <c r="G502" t="n">
         <v>12608900</v>
@@ -11995,16 +11995,16 @@
         <v>46022</v>
       </c>
       <c r="C503" t="n">
-        <v>98.92166900634766</v>
+        <v>98.92166137695312</v>
       </c>
       <c r="D503" t="n">
-        <v>98.931525830781</v>
+        <v>98.93151820062626</v>
       </c>
       <c r="E503" t="n">
-        <v>98.92166900634766</v>
+        <v>98.92166137695312</v>
       </c>
       <c r="F503" t="n">
-        <v>98.931525830781</v>
+        <v>98.93151820062626</v>
       </c>
       <c r="G503" t="n">
         <v>13910900</v>
@@ -12110,16 +12110,16 @@
         <v>46030</v>
       </c>
       <c r="C508" t="n">
-        <v>98.99064636230469</v>
+        <v>98.99065399169922</v>
       </c>
       <c r="D508" t="n">
-        <v>98.99064636230469</v>
+        <v>98.99065399169922</v>
       </c>
       <c r="E508" t="n">
-        <v>98.99064636230469</v>
+        <v>98.99065399169922</v>
       </c>
       <c r="F508" t="n">
-        <v>98.99064636230469</v>
+        <v>98.99065399169922</v>
       </c>
       <c r="G508" t="n">
         <v>11408800</v>
@@ -12179,16 +12179,16 @@
         <v>46035</v>
       </c>
       <c r="C511" t="n">
-        <v>99.03993225097656</v>
+        <v>99.03992462158203</v>
       </c>
       <c r="D511" t="n">
-        <v>99.03993225097656</v>
+        <v>99.03992462158203</v>
       </c>
       <c r="E511" t="n">
-        <v>99.03007542615437</v>
+        <v>99.03006779751914</v>
       </c>
       <c r="F511" t="n">
-        <v>99.03007542615437</v>
+        <v>99.03006779751914</v>
       </c>
       <c r="G511" t="n">
         <v>14163000</v>
@@ -12202,16 +12202,16 @@
         <v>46036</v>
       </c>
       <c r="C512" t="n">
-        <v>99.04978179931641</v>
+        <v>99.04978942871094</v>
       </c>
       <c r="D512" t="n">
-        <v>99.04978179931641</v>
+        <v>99.04978942871094</v>
       </c>
       <c r="E512" t="n">
-        <v>99.03992497521833</v>
+        <v>99.03993260385363</v>
       </c>
       <c r="F512" t="n">
-        <v>99.04978179931641</v>
+        <v>99.04978942871094</v>
       </c>
       <c r="G512" t="n">
         <v>11851800</v>
@@ -12225,16 +12225,16 @@
         <v>46037</v>
       </c>
       <c r="C513" t="n">
-        <v>99.05964660644531</v>
+        <v>99.05963134765625</v>
       </c>
       <c r="D513" t="n">
-        <v>99.05964660644531</v>
+        <v>99.05963134765625</v>
       </c>
       <c r="E513" t="n">
-        <v>99.04979729935978</v>
+        <v>99.04978204208787</v>
       </c>
       <c r="F513" t="n">
-        <v>99.04979729935978</v>
+        <v>99.04978204208787</v>
       </c>
       <c r="G513" t="n">
         <v>11469500</v>
@@ -12248,16 +12248,16 @@
         <v>46038</v>
       </c>
       <c r="C514" t="n">
-        <v>99.09904479980469</v>
+        <v>99.09905242919922</v>
       </c>
       <c r="D514" t="n">
-        <v>99.09904479980469</v>
+        <v>99.09905242919922</v>
       </c>
       <c r="E514" t="n">
-        <v>99.0842633238418</v>
+        <v>99.08427095209834</v>
       </c>
       <c r="F514" t="n">
-        <v>99.08919549486502</v>
+        <v>99.08920312350128</v>
       </c>
       <c r="G514" t="n">
         <v>14766800</v>
@@ -12271,16 +12271,16 @@
         <v>46042</v>
       </c>
       <c r="C515" t="n">
-        <v>99.09904479980469</v>
+        <v>99.09905242919922</v>
       </c>
       <c r="D515" t="n">
-        <v>99.10890162329774</v>
+        <v>99.10890925345112</v>
       </c>
       <c r="E515" t="n">
-        <v>99.09904479980469</v>
+        <v>99.09905242919922</v>
       </c>
       <c r="F515" t="n">
-        <v>99.09904479980469</v>
+        <v>99.09905242919922</v>
       </c>
       <c r="G515" t="n">
         <v>19394600</v>
@@ -12294,16 +12294,16 @@
         <v>46043</v>
       </c>
       <c r="C516" t="n">
-        <v>99.09904479980469</v>
+        <v>99.09905242919922</v>
       </c>
       <c r="D516" t="n">
-        <v>99.11875844679079</v>
+        <v>99.11876607770303</v>
       </c>
       <c r="E516" t="n">
-        <v>99.09904479980469</v>
+        <v>99.09905242919922</v>
       </c>
       <c r="F516" t="n">
-        <v>99.1039769708279</v>
+        <v>99.10398460060216</v>
       </c>
       <c r="G516" t="n">
         <v>17502100</v>
@@ -12317,16 +12317,16 @@
         <v>46044</v>
       </c>
       <c r="C517" t="n">
-        <v>99.1187744140625</v>
+        <v>99.11876678466797</v>
       </c>
       <c r="D517" t="n">
-        <v>99.1187744140625</v>
+        <v>99.11876678466797</v>
       </c>
       <c r="E517" t="n">
-        <v>99.1089175889816</v>
+        <v>99.10890996034576</v>
       </c>
       <c r="F517" t="n">
-        <v>99.1187744140625</v>
+        <v>99.11876678466797</v>
       </c>
       <c r="G517" t="n">
         <v>13618500</v>
@@ -12340,16 +12340,16 @@
         <v>46045</v>
       </c>
       <c r="C518" t="n">
-        <v>99.14833831787109</v>
+        <v>99.14833068847656</v>
       </c>
       <c r="D518" t="n">
-        <v>99.14833831787109</v>
+        <v>99.14833068847656</v>
       </c>
       <c r="E518" t="n">
-        <v>99.13848149269603</v>
+        <v>99.13847386405996</v>
       </c>
       <c r="F518" t="n">
-        <v>99.14833831787109</v>
+        <v>99.14833068847656</v>
       </c>
       <c r="G518" t="n">
         <v>12143000</v>
@@ -12363,16 +12363,16 @@
         <v>46048</v>
       </c>
       <c r="C519" t="n">
-        <v>99.15818786621094</v>
+        <v>99.15818023681641</v>
       </c>
       <c r="D519" t="n">
-        <v>99.15818786621094</v>
+        <v>99.15818023681641</v>
       </c>
       <c r="E519" t="n">
-        <v>99.14833104175922</v>
+        <v>99.14832341312308</v>
       </c>
       <c r="F519" t="n">
-        <v>99.15818786621094</v>
+        <v>99.15818023681641</v>
       </c>
       <c r="G519" t="n">
         <v>16872000</v>
@@ -12386,16 +12386,16 @@
         <v>46049</v>
       </c>
       <c r="C520" t="n">
-        <v>99.15818786621094</v>
+        <v>99.15818023681641</v>
       </c>
       <c r="D520" t="n">
-        <v>99.17296934361146</v>
+        <v>99.1729617130796</v>
       </c>
       <c r="E520" t="n">
-        <v>99.15818786621094</v>
+        <v>99.15818023681641</v>
       </c>
       <c r="F520" t="n">
-        <v>99.16803717210854</v>
+        <v>99.16802954195617</v>
       </c>
       <c r="G520" t="n">
         <v>13393600</v>
@@ -12409,16 +12409,16 @@
         <v>46050</v>
       </c>
       <c r="C521" t="n">
-        <v>99.17789459228516</v>
+        <v>99.17788696289062</v>
       </c>
       <c r="D521" t="n">
-        <v>99.17789459228516</v>
+        <v>99.17788696289062</v>
       </c>
       <c r="E521" t="n">
-        <v>99.16803776777424</v>
+        <v>99.16803013913795</v>
       </c>
       <c r="F521" t="n">
-        <v>99.16803776777424</v>
+        <v>99.16803013913795</v>
       </c>
       <c r="G521" t="n">
         <v>11987500</v>
@@ -12455,16 +12455,16 @@
         <v>46052</v>
       </c>
       <c r="C523" t="n">
-        <v>99.20745849609375</v>
+        <v>99.20745086669922</v>
       </c>
       <c r="D523" t="n">
-        <v>99.21731532069894</v>
+        <v>99.21730769054639</v>
       </c>
       <c r="E523" t="n">
-        <v>99.20745849609375</v>
+        <v>99.20745086669922</v>
       </c>
       <c r="F523" t="n">
-        <v>99.20745849609375</v>
+        <v>99.20745086669922</v>
       </c>
       <c r="G523" t="n">
         <v>29215200</v>
@@ -12478,16 +12478,16 @@
         <v>46055</v>
       </c>
       <c r="C524" t="n">
-        <v>99.21636199951172</v>
+        <v>99.21635437011719</v>
       </c>
       <c r="D524" t="n">
-        <v>99.22624163068743</v>
+        <v>99.22623400053318</v>
       </c>
       <c r="E524" t="n">
-        <v>99.21636199951172</v>
+        <v>99.21635437011719</v>
       </c>
       <c r="F524" t="n">
-        <v>99.22624163068743</v>
+        <v>99.22623400053318</v>
       </c>
       <c r="G524" t="n">
         <v>31225300</v>
@@ -12662,16 +12662,16 @@
         <v>46065</v>
       </c>
       <c r="C532" t="n">
-        <v>99.32509613037109</v>
+        <v>99.32510375976562</v>
       </c>
       <c r="D532" t="n">
-        <v>99.32509613037109</v>
+        <v>99.32510375976562</v>
       </c>
       <c r="E532" t="n">
-        <v>99.31520895770579</v>
+        <v>99.31521658634087</v>
       </c>
       <c r="F532" t="n">
-        <v>99.31520895770579</v>
+        <v>99.31521658634087</v>
       </c>
       <c r="G532" t="n">
         <v>16593900</v>
@@ -12685,16 +12685,16 @@
         <v>46066</v>
       </c>
       <c r="C533" t="n">
-        <v>99.36463928222656</v>
+        <v>99.36463165283203</v>
       </c>
       <c r="D533" t="n">
-        <v>99.36463928222656</v>
+        <v>99.36463165283203</v>
       </c>
       <c r="E533" t="n">
-        <v>99.35475965031527</v>
+        <v>99.35475202167932</v>
       </c>
       <c r="F533" t="n">
-        <v>99.36463928222656</v>
+        <v>99.36463165283203</v>
       </c>
       <c r="G533" t="n">
         <v>14917200</v>
@@ -12708,16 +12708,16 @@
         <v>46070</v>
       </c>
       <c r="C534" t="n">
-        <v>99.36463928222656</v>
+        <v>99.36463165283203</v>
       </c>
       <c r="D534" t="n">
-        <v>99.37452645584159</v>
+        <v>99.3745188256879</v>
       </c>
       <c r="E534" t="n">
-        <v>99.36463928222656</v>
+        <v>99.36463165283203</v>
       </c>
       <c r="F534" t="n">
-        <v>99.36958663988595</v>
+        <v>99.36957901011155</v>
       </c>
       <c r="G534" t="n">
         <v>14976200</v>
@@ -12731,16 +12731,16 @@
         <v>46071</v>
       </c>
       <c r="C535" t="n">
-        <v>99.3843994140625</v>
+        <v>99.38440704345703</v>
       </c>
       <c r="D535" t="n">
-        <v>99.3843994140625</v>
+        <v>99.38440704345703</v>
       </c>
       <c r="E535" t="n">
-        <v>99.37451224186168</v>
+        <v>99.37451987049721</v>
       </c>
       <c r="F535" t="n">
-        <v>99.3843994140625</v>
+        <v>99.38440704345703</v>
       </c>
       <c r="G535" t="n">
         <v>10207300</v>
@@ -12777,16 +12777,16 @@
         <v>46073</v>
       </c>
       <c r="C537" t="n">
-        <v>99.4140625</v>
+        <v>99.41405487060547</v>
       </c>
       <c r="D537" t="n">
-        <v>99.42394967310696</v>
+        <v>99.42394204295366</v>
       </c>
       <c r="E537" t="n">
-        <v>99.4140625</v>
+        <v>99.41405487060547</v>
       </c>
       <c r="F537" t="n">
-        <v>99.42394967310696</v>
+        <v>99.42394204295366</v>
       </c>
       <c r="G537" t="n">
         <v>13490000</v>
@@ -12846,16 +12846,16 @@
         <v>46078</v>
       </c>
       <c r="C540" t="n">
-        <v>99.44371032714844</v>
+        <v>99.44371795654297</v>
       </c>
       <c r="D540" t="n">
-        <v>99.45359749964389</v>
+        <v>99.45360512979697</v>
       </c>
       <c r="E540" t="n">
-        <v>99.44371032714844</v>
+        <v>99.44371795654297</v>
       </c>
       <c r="F540" t="n">
-        <v>99.45359749964389</v>
+        <v>99.45360512979697</v>
       </c>
       <c r="G540" t="n">
         <v>12532000</v>
@@ -13076,16 +13076,16 @@
         <v>46092</v>
       </c>
       <c r="C550" t="n">
-        <v>99.59426116943359</v>
+        <v>99.59427642822266</v>
       </c>
       <c r="D550" t="n">
-        <v>99.59426116943359</v>
+        <v>99.59427642822266</v>
       </c>
       <c r="E550" t="n">
-        <v>99.58434720312479</v>
+        <v>99.58436246039494</v>
       </c>
       <c r="F550" t="n">
-        <v>99.58434720312479</v>
+        <v>99.58436246039494</v>
       </c>
       <c r="G550" t="n">
         <v>12287800</v>
@@ -13099,16 +13099,16 @@
         <v>46093</v>
       </c>
       <c r="C551" t="n">
-        <v>99.60418701171875</v>
+        <v>99.60417938232422</v>
       </c>
       <c r="D551" t="n">
-        <v>99.60418701171875</v>
+        <v>99.60417938232422</v>
       </c>
       <c r="E551" t="n">
-        <v>99.59428060561726</v>
+        <v>99.59427297698153</v>
       </c>
       <c r="F551" t="n">
-        <v>99.599233808668</v>
+        <v>99.59922617965287</v>
       </c>
       <c r="G551" t="n">
         <v>17521900</v>
@@ -13559,16 +13559,16 @@
         <v>46122</v>
       </c>
       <c r="C571" t="n">
-        <v>99.90489959716797</v>
+        <v>99.90489196777344</v>
       </c>
       <c r="D571" t="n">
-        <v>99.90489959716797</v>
+        <v>99.90489196777344</v>
       </c>
       <c r="E571" t="n">
-        <v>99.8949566875574</v>
+        <v>99.89494905892218</v>
       </c>
       <c r="F571" t="n">
-        <v>99.8949566875574</v>
+        <v>99.89494905892218</v>
       </c>
       <c r="G571" t="n">
         <v>18783100</v>
@@ -13674,16 +13674,16 @@
         <v>46129</v>
       </c>
       <c r="C576" t="n">
-        <v>99.96453094482422</v>
+        <v>99.96453857421875</v>
       </c>
       <c r="D576" t="n">
-        <v>99.97447385334648</v>
+        <v>99.97448148349987</v>
       </c>
       <c r="E576" t="n">
-        <v>99.96453094482422</v>
+        <v>99.96453857421875</v>
       </c>
       <c r="F576" t="n">
-        <v>99.96453094482422</v>
+        <v>99.96453857421875</v>
       </c>
       <c r="G576" t="n">
         <v>20660500</v>
@@ -14514,7 +14514,7 @@
         <v>100.4700012207031</v>
       </c>
       <c r="G612" t="n">
-        <v>24957045</v>
+        <v>25347277</v>
       </c>
     </row>
   </sheetData>

--- a/Data/sgov.xlsx
+++ b/Data/sgov.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G612"/>
+  <dimension ref="A1:G615"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,16 +472,16 @@
         <v>45293</v>
       </c>
       <c r="C2" t="n">
-        <v>90.15840148925781</v>
+        <v>90.15838623046875</v>
       </c>
       <c r="D2" t="n">
-        <v>90.1673931794142</v>
+        <v>90.16737791910336</v>
       </c>
       <c r="E2" t="n">
-        <v>90.14940979910142</v>
+        <v>90.14939454183416</v>
       </c>
       <c r="F2" t="n">
-        <v>90.15840148925781</v>
+        <v>90.15838623046875</v>
       </c>
       <c r="G2" t="n">
         <v>5286200</v>
@@ -495,16 +495,16 @@
         <v>45294</v>
       </c>
       <c r="C3" t="n">
-        <v>90.16739654541016</v>
+        <v>90.16737365722656</v>
       </c>
       <c r="D3" t="n">
-        <v>90.18537306774401</v>
+        <v>90.18535017499724</v>
       </c>
       <c r="E3" t="n">
-        <v>90.16739654541016</v>
+        <v>90.16737365722656</v>
       </c>
       <c r="F3" t="n">
-        <v>90.16739654541016</v>
+        <v>90.16737365722656</v>
       </c>
       <c r="G3" t="n">
         <v>4597300</v>
@@ -518,16 +518,16 @@
         <v>45295</v>
       </c>
       <c r="C4" t="n">
-        <v>90.21233367919922</v>
+        <v>90.21231842041016</v>
       </c>
       <c r="D4" t="n">
-        <v>90.22132536893363</v>
+        <v>90.22131010862368</v>
       </c>
       <c r="E4" t="n">
-        <v>90.21233367919922</v>
+        <v>90.21231842041016</v>
       </c>
       <c r="F4" t="n">
-        <v>90.21233367919922</v>
+        <v>90.21231842041016</v>
       </c>
       <c r="G4" t="n">
         <v>2794100</v>
@@ -541,16 +541,16 @@
         <v>45296</v>
       </c>
       <c r="C5" t="n">
-        <v>90.22132110595703</v>
+        <v>90.22133636474609</v>
       </c>
       <c r="D5" t="n">
-        <v>90.23031279526658</v>
+        <v>90.23032805557638</v>
       </c>
       <c r="E5" t="n">
-        <v>90.22132110595703</v>
+        <v>90.22133636474609</v>
       </c>
       <c r="F5" t="n">
-        <v>90.22132110595703</v>
+        <v>90.22133636474609</v>
       </c>
       <c r="G5" t="n">
         <v>3491200</v>
@@ -564,16 +564,16 @@
         <v>45299</v>
       </c>
       <c r="C6" t="n">
-        <v>90.24831390380859</v>
+        <v>90.24829864501953</v>
       </c>
       <c r="D6" t="n">
-        <v>90.24831390380859</v>
+        <v>90.24829864501953</v>
       </c>
       <c r="E6" t="n">
-        <v>90.23932221204922</v>
+        <v>90.23930695478043</v>
       </c>
       <c r="F6" t="n">
-        <v>90.24831390380859</v>
+        <v>90.24829864501953</v>
       </c>
       <c r="G6" t="n">
         <v>2867500</v>
@@ -587,16 +587,16 @@
         <v>45300</v>
       </c>
       <c r="C7" t="n">
-        <v>90.25728607177734</v>
+        <v>90.25726318359375</v>
       </c>
       <c r="D7" t="n">
-        <v>90.25728607177734</v>
+        <v>90.25726318359375</v>
       </c>
       <c r="E7" t="n">
-        <v>90.24829438196298</v>
+        <v>90.24827149605957</v>
       </c>
       <c r="F7" t="n">
-        <v>90.25728607177734</v>
+        <v>90.25726318359375</v>
       </c>
       <c r="G7" t="n">
         <v>2419800</v>
@@ -610,16 +610,16 @@
         <v>45301</v>
       </c>
       <c r="C8" t="n">
-        <v>90.27525329589844</v>
+        <v>90.27524566650391</v>
       </c>
       <c r="D8" t="n">
-        <v>90.27525329589844</v>
+        <v>90.27524566650391</v>
       </c>
       <c r="E8" t="n">
-        <v>90.26626846565911</v>
+        <v>90.26626083702391</v>
       </c>
       <c r="F8" t="n">
-        <v>90.27525329589844</v>
+        <v>90.27524566650391</v>
       </c>
       <c r="G8" t="n">
         <v>1961400</v>
@@ -633,16 +633,16 @@
         <v>45302</v>
       </c>
       <c r="C9" t="n">
-        <v>90.32918548583984</v>
+        <v>90.32920074462891</v>
       </c>
       <c r="D9" t="n">
-        <v>90.32918548583984</v>
+        <v>90.32920074462891</v>
       </c>
       <c r="E9" t="n">
-        <v>90.31120211026995</v>
+        <v>90.31121736602117</v>
       </c>
       <c r="F9" t="n">
-        <v>90.31120211026995</v>
+        <v>90.31121736602117</v>
       </c>
       <c r="G9" t="n">
         <v>3164900</v>
@@ -656,16 +656,16 @@
         <v>45303</v>
       </c>
       <c r="C10" t="n">
-        <v>90.33816528320312</v>
+        <v>90.33817291259766</v>
       </c>
       <c r="D10" t="n">
-        <v>90.33816528320312</v>
+        <v>90.33817291259766</v>
       </c>
       <c r="E10" t="n">
-        <v>90.32918045456681</v>
+        <v>90.32918808320254</v>
       </c>
       <c r="F10" t="n">
-        <v>90.32918045456681</v>
+        <v>90.32918808320254</v>
       </c>
       <c r="G10" t="n">
         <v>2557900</v>
@@ -679,16 +679,16 @@
         <v>45307</v>
       </c>
       <c r="C11" t="n">
-        <v>90.34719848632812</v>
+        <v>90.34717559814453</v>
       </c>
       <c r="D11" t="n">
-        <v>90.35619017774405</v>
+        <v>90.35616728728255</v>
       </c>
       <c r="E11" t="n">
-        <v>90.34719848632812</v>
+        <v>90.34717559814453</v>
       </c>
       <c r="F11" t="n">
-        <v>90.35619017774405</v>
+        <v>90.35616728728255</v>
       </c>
       <c r="G11" t="n">
         <v>2713000</v>
@@ -702,16 +702,16 @@
         <v>45308</v>
       </c>
       <c r="C12" t="n">
-        <v>90.35619354248047</v>
+        <v>90.35616302490234</v>
       </c>
       <c r="D12" t="n">
-        <v>90.36517837558002</v>
+        <v>90.36514785496729</v>
       </c>
       <c r="E12" t="n">
-        <v>90.35619354248047</v>
+        <v>90.35616302490234</v>
       </c>
       <c r="F12" t="n">
-        <v>90.36517837558002</v>
+        <v>90.36514785496729</v>
       </c>
       <c r="G12" t="n">
         <v>2317700</v>
@@ -725,16 +725,16 @@
         <v>45309</v>
       </c>
       <c r="C13" t="n">
-        <v>90.39212799072266</v>
+        <v>90.39211273193359</v>
       </c>
       <c r="D13" t="n">
-        <v>90.40111282129152</v>
+        <v>90.40109756098575</v>
       </c>
       <c r="E13" t="n">
-        <v>90.39212799072266</v>
+        <v>90.39211273193359</v>
       </c>
       <c r="F13" t="n">
-        <v>90.40111282129152</v>
+        <v>90.40109756098575</v>
       </c>
       <c r="G13" t="n">
         <v>2672000</v>
@@ -748,16 +748,16 @@
         <v>45310</v>
       </c>
       <c r="C14" t="n">
-        <v>90.41908264160156</v>
+        <v>90.41909790039062</v>
       </c>
       <c r="D14" t="n">
-        <v>90.41908264160156</v>
+        <v>90.41909790039062</v>
       </c>
       <c r="E14" t="n">
-        <v>90.40109926586183</v>
+        <v>90.40111452161609</v>
       </c>
       <c r="F14" t="n">
-        <v>90.4100909537317</v>
+        <v>90.41010621100335</v>
       </c>
       <c r="G14" t="n">
         <v>3630100</v>
@@ -794,16 +794,16 @@
         <v>45314</v>
       </c>
       <c r="C16" t="n">
-        <v>90.44605255126953</v>
+        <v>90.44606018066406</v>
       </c>
       <c r="D16" t="n">
-        <v>90.44605255126953</v>
+        <v>90.44606018066406</v>
       </c>
       <c r="E16" t="n">
-        <v>90.43706086323019</v>
+        <v>90.43706849186626</v>
       </c>
       <c r="F16" t="n">
-        <v>90.43706086323019</v>
+        <v>90.43706849186626</v>
       </c>
       <c r="G16" t="n">
         <v>2066200</v>
@@ -817,16 +817,16 @@
         <v>45315</v>
       </c>
       <c r="C17" t="n">
-        <v>90.45505523681641</v>
+        <v>90.45503997802734</v>
       </c>
       <c r="D17" t="n">
-        <v>90.45505523681641</v>
+        <v>90.45503997802734</v>
       </c>
       <c r="E17" t="n">
-        <v>90.44606354768386</v>
+        <v>90.4460482904116</v>
       </c>
       <c r="F17" t="n">
-        <v>90.44606354768386</v>
+        <v>90.4460482904116</v>
       </c>
       <c r="G17" t="n">
         <v>3441600</v>
@@ -840,16 +840,16 @@
         <v>45316</v>
       </c>
       <c r="C18" t="n">
-        <v>90.50000762939453</v>
+        <v>90.5</v>
       </c>
       <c r="D18" t="n">
-        <v>90.50000762939453</v>
+        <v>90.5</v>
       </c>
       <c r="E18" t="n">
-        <v>90.48203110825628</v>
+        <v>90.48202348037722</v>
       </c>
       <c r="F18" t="n">
-        <v>90.48203110825628</v>
+        <v>90.48202348037722</v>
       </c>
       <c r="G18" t="n">
         <v>2426000</v>
@@ -863,16 +863,16 @@
         <v>45317</v>
       </c>
       <c r="C19" t="n">
-        <v>90.50000762939453</v>
+        <v>90.5</v>
       </c>
       <c r="D19" t="n">
-        <v>90.50899931928856</v>
+        <v>90.50899168913601</v>
       </c>
       <c r="E19" t="n">
-        <v>90.50000762939453</v>
+        <v>90.5</v>
       </c>
       <c r="F19" t="n">
-        <v>90.50899931928856</v>
+        <v>90.50899168913601</v>
       </c>
       <c r="G19" t="n">
         <v>2059100</v>
@@ -909,16 +909,16 @@
         <v>45321</v>
       </c>
       <c r="C21" t="n">
-        <v>90.53593444824219</v>
+        <v>90.53595733642578</v>
       </c>
       <c r="D21" t="n">
-        <v>90.53593444824219</v>
+        <v>90.53595733642578</v>
       </c>
       <c r="E21" t="n">
-        <v>90.52694276163375</v>
+        <v>90.52696564754417</v>
       </c>
       <c r="F21" t="n">
-        <v>90.52694276163375</v>
+        <v>90.52696564754417</v>
       </c>
       <c r="G21" t="n">
         <v>3741000</v>
@@ -932,16 +932,16 @@
         <v>45322</v>
       </c>
       <c r="C22" t="n">
-        <v>90.53593444824219</v>
+        <v>90.53595733642578</v>
       </c>
       <c r="D22" t="n">
-        <v>90.54492613485063</v>
+        <v>90.54494902530739</v>
       </c>
       <c r="E22" t="n">
-        <v>90.53593444824219</v>
+        <v>90.53595733642578</v>
       </c>
       <c r="F22" t="n">
-        <v>90.53593444824219</v>
+        <v>90.53595733642578</v>
       </c>
       <c r="G22" t="n">
         <v>5171300</v>
@@ -978,16 +978,16 @@
         <v>45324</v>
       </c>
       <c r="C24" t="n">
-        <v>90.59737396240234</v>
+        <v>90.59736633300781</v>
       </c>
       <c r="D24" t="n">
-        <v>90.59737396240234</v>
+        <v>90.59736633300781</v>
       </c>
       <c r="E24" t="n">
-        <v>90.58834119446723</v>
+        <v>90.58833356583337</v>
       </c>
       <c r="F24" t="n">
-        <v>90.59737396240234</v>
+        <v>90.59736633300781</v>
       </c>
       <c r="G24" t="n">
         <v>3864800</v>
@@ -1001,16 +1001,16 @@
         <v>45327</v>
       </c>
       <c r="C25" t="n">
-        <v>90.61540985107422</v>
+        <v>90.61542510986328</v>
       </c>
       <c r="D25" t="n">
-        <v>90.61540985107422</v>
+        <v>90.61542510986328</v>
       </c>
       <c r="E25" t="n">
-        <v>90.60638397538904</v>
+        <v>90.60639923265822</v>
       </c>
       <c r="F25" t="n">
-        <v>90.61540985107422</v>
+        <v>90.61542510986328</v>
       </c>
       <c r="G25" t="n">
         <v>3969400</v>
@@ -1024,16 +1024,16 @@
         <v>45328</v>
       </c>
       <c r="C26" t="n">
-        <v>90.62447357177734</v>
+        <v>90.62445831298828</v>
       </c>
       <c r="D26" t="n">
-        <v>90.63350634052934</v>
+        <v>90.6334910802194</v>
       </c>
       <c r="E26" t="n">
-        <v>90.61544080302535</v>
+        <v>90.61542554575718</v>
       </c>
       <c r="F26" t="n">
-        <v>90.62447357177734</v>
+        <v>90.62445831298828</v>
       </c>
       <c r="G26" t="n">
         <v>2167300</v>
@@ -1047,16 +1047,16 @@
         <v>45329</v>
       </c>
       <c r="C27" t="n">
-        <v>90.64251708984375</v>
+        <v>90.64250946044922</v>
       </c>
       <c r="D27" t="n">
-        <v>90.64251708984375</v>
+        <v>90.64250946044922</v>
       </c>
       <c r="E27" t="n">
-        <v>90.63348432328605</v>
+        <v>90.63347669465182</v>
       </c>
       <c r="F27" t="n">
-        <v>90.64251708984375</v>
+        <v>90.64250946044922</v>
       </c>
       <c r="G27" t="n">
         <v>2621200</v>
@@ -1070,16 +1070,16 @@
         <v>45330</v>
       </c>
       <c r="C28" t="n">
-        <v>90.66960906982422</v>
+        <v>90.66959381103516</v>
       </c>
       <c r="D28" t="n">
-        <v>90.68766771307108</v>
+        <v>90.68765245124293</v>
       </c>
       <c r="E28" t="n">
-        <v>90.66960906982422</v>
+        <v>90.66959381103516</v>
       </c>
       <c r="F28" t="n">
-        <v>90.66960906982422</v>
+        <v>90.66959381103516</v>
       </c>
       <c r="G28" t="n">
         <v>3838700</v>
@@ -1093,16 +1093,16 @@
         <v>45331</v>
       </c>
       <c r="C29" t="n">
-        <v>90.69670104980469</v>
+        <v>90.69671630859375</v>
       </c>
       <c r="D29" t="n">
-        <v>90.69670104980469</v>
+        <v>90.69671630859375</v>
       </c>
       <c r="E29" t="n">
-        <v>90.68315534478884</v>
+        <v>90.683170601299</v>
       </c>
       <c r="F29" t="n">
-        <v>90.68766828313339</v>
+        <v>90.68768354040279</v>
       </c>
       <c r="G29" t="n">
         <v>3232500</v>
@@ -1116,16 +1116,16 @@
         <v>45334</v>
       </c>
       <c r="C30" t="n">
-        <v>90.69670104980469</v>
+        <v>90.69671630859375</v>
       </c>
       <c r="D30" t="n">
-        <v>90.71475969316506</v>
+        <v>90.71477495499231</v>
       </c>
       <c r="E30" t="n">
-        <v>90.69670104980469</v>
+        <v>90.69671630859375</v>
       </c>
       <c r="F30" t="n">
-        <v>90.70573381647597</v>
+        <v>90.70574907678471</v>
       </c>
       <c r="G30" t="n">
         <v>2792700</v>
@@ -1139,16 +1139,16 @@
         <v>45335</v>
       </c>
       <c r="C31" t="n">
-        <v>90.71475219726562</v>
+        <v>90.71476745605469</v>
       </c>
       <c r="D31" t="n">
-        <v>90.71475219726562</v>
+        <v>90.71476745605469</v>
       </c>
       <c r="E31" t="n">
-        <v>90.70572632132237</v>
+        <v>90.70574157859322</v>
       </c>
       <c r="F31" t="n">
-        <v>90.71475219726562</v>
+        <v>90.71476745605469</v>
       </c>
       <c r="G31" t="n">
         <v>3009000</v>
@@ -1185,16 +1185,16 @@
         <v>45337</v>
       </c>
       <c r="C33" t="n">
-        <v>90.77797698974609</v>
+        <v>90.77799224853516</v>
       </c>
       <c r="D33" t="n">
-        <v>90.78700975658751</v>
+        <v>90.7870250168949</v>
       </c>
       <c r="E33" t="n">
-        <v>90.77797698974609</v>
+        <v>90.77799224853516</v>
       </c>
       <c r="F33" t="n">
-        <v>90.78700975658751</v>
+        <v>90.7870250168949</v>
       </c>
       <c r="G33" t="n">
         <v>2577800</v>
@@ -1231,16 +1231,16 @@
         <v>45342</v>
       </c>
       <c r="C35" t="n">
-        <v>90.80507659912109</v>
+        <v>90.80506896972656</v>
       </c>
       <c r="D35" t="n">
-        <v>90.81410247611029</v>
+        <v>90.8140948459574</v>
       </c>
       <c r="E35" t="n">
-        <v>90.79604383214948</v>
+        <v>90.79603620351386</v>
       </c>
       <c r="F35" t="n">
-        <v>90.80507659912109</v>
+        <v>90.80506896972656</v>
       </c>
       <c r="G35" t="n">
         <v>3268600</v>
@@ -1254,16 +1254,16 @@
         <v>45343</v>
       </c>
       <c r="C36" t="n">
-        <v>90.81410980224609</v>
+        <v>90.81411743164062</v>
       </c>
       <c r="D36" t="n">
-        <v>90.83217533764672</v>
+        <v>90.83218296855895</v>
       </c>
       <c r="E36" t="n">
-        <v>90.81410980224609</v>
+        <v>90.81411743164062</v>
       </c>
       <c r="F36" t="n">
-        <v>90.8231425699464</v>
+        <v>90.82315020009979</v>
       </c>
       <c r="G36" t="n">
         <v>2302700</v>
@@ -1277,16 +1277,16 @@
         <v>45344</v>
       </c>
       <c r="C37" t="n">
-        <v>90.8502197265625</v>
+        <v>90.85023498535156</v>
       </c>
       <c r="D37" t="n">
-        <v>90.85925249284537</v>
+        <v>90.85926775315153</v>
       </c>
       <c r="E37" t="n">
-        <v>90.8502197265625</v>
+        <v>90.85023498535156</v>
       </c>
       <c r="F37" t="n">
-        <v>90.8502197265625</v>
+        <v>90.85023498535156</v>
       </c>
       <c r="G37" t="n">
         <v>2452200</v>
@@ -1323,16 +1323,16 @@
         <v>45348</v>
       </c>
       <c r="C39" t="n">
-        <v>90.88636016845703</v>
+        <v>90.8863525390625</v>
       </c>
       <c r="D39" t="n">
-        <v>90.89539293635657</v>
+        <v>90.89538530620379</v>
       </c>
       <c r="E39" t="n">
-        <v>90.88636016845703</v>
+        <v>90.8863525390625</v>
       </c>
       <c r="F39" t="n">
-        <v>90.88636016845703</v>
+        <v>90.8863525390625</v>
       </c>
       <c r="G39" t="n">
         <v>2645100</v>
@@ -1346,16 +1346,16 @@
         <v>45349</v>
       </c>
       <c r="C40" t="n">
-        <v>90.90441131591797</v>
+        <v>90.9044189453125</v>
       </c>
       <c r="D40" t="n">
-        <v>90.90441131591797</v>
+        <v>90.9044189453125</v>
       </c>
       <c r="E40" t="n">
-        <v>90.89537854944814</v>
+        <v>90.89538617808456</v>
       </c>
       <c r="F40" t="n">
-        <v>90.90441131591797</v>
+        <v>90.9044189453125</v>
       </c>
       <c r="G40" t="n">
         <v>2360300</v>
@@ -1369,16 +1369,16 @@
         <v>45350</v>
       </c>
       <c r="C41" t="n">
-        <v>90.91343688964844</v>
+        <v>90.9134521484375</v>
       </c>
       <c r="D41" t="n">
-        <v>90.91343688964844</v>
+        <v>90.9134521484375</v>
       </c>
       <c r="E41" t="n">
-        <v>90.90441101319072</v>
+        <v>90.90442627046488</v>
       </c>
       <c r="F41" t="n">
-        <v>90.90441101319072</v>
+        <v>90.90442627046488</v>
       </c>
       <c r="G41" t="n">
         <v>4526200</v>
@@ -1392,16 +1392,16 @@
         <v>45351</v>
       </c>
       <c r="C42" t="n">
-        <v>90.9405517578125</v>
+        <v>90.94052124023438</v>
       </c>
       <c r="D42" t="n">
-        <v>90.94958452658233</v>
+        <v>90.94955400597301</v>
       </c>
       <c r="E42" t="n">
-        <v>90.9405517578125</v>
+        <v>90.94052124023438</v>
       </c>
       <c r="F42" t="n">
-        <v>90.9405517578125</v>
+        <v>90.94052124023438</v>
       </c>
       <c r="G42" t="n">
         <v>5560200</v>
@@ -1438,16 +1438,16 @@
         <v>45355</v>
       </c>
       <c r="C44" t="n">
-        <v>90.976806640625</v>
+        <v>90.97682189941406</v>
       </c>
       <c r="D44" t="n">
-        <v>90.98586941645763</v>
+        <v>90.98588467676672</v>
       </c>
       <c r="E44" t="n">
-        <v>90.976806640625</v>
+        <v>90.97682189941406</v>
       </c>
       <c r="F44" t="n">
-        <v>90.976806640625</v>
+        <v>90.97682189941406</v>
       </c>
       <c r="G44" t="n">
         <v>3613500</v>
@@ -1461,16 +1461,16 @@
         <v>45356</v>
       </c>
       <c r="C45" t="n">
-        <v>90.98587036132812</v>
+        <v>90.98586273193359</v>
       </c>
       <c r="D45" t="n">
-        <v>90.99494005540443</v>
+        <v>90.99493242524937</v>
       </c>
       <c r="E45" t="n">
-        <v>90.98587036132812</v>
+        <v>90.98586273193359</v>
       </c>
       <c r="F45" t="n">
-        <v>90.98587036132812</v>
+        <v>90.98586273193359</v>
       </c>
       <c r="G45" t="n">
         <v>3905300</v>
@@ -1484,16 +1484,16 @@
         <v>45357</v>
       </c>
       <c r="C46" t="n">
-        <v>91.00402069091797</v>
+        <v>91.00401306152344</v>
       </c>
       <c r="D46" t="n">
-        <v>91.01309038608471</v>
+        <v>91.01308275592983</v>
       </c>
       <c r="E46" t="n">
-        <v>90.99495099575121</v>
+        <v>90.99494336711705</v>
       </c>
       <c r="F46" t="n">
-        <v>91.00402069091797</v>
+        <v>91.00401306152344</v>
       </c>
       <c r="G46" t="n">
         <v>2760000</v>
@@ -1507,16 +1507,16 @@
         <v>45358</v>
       </c>
       <c r="C47" t="n">
-        <v>91.04936981201172</v>
+        <v>91.04935455322266</v>
       </c>
       <c r="D47" t="n">
-        <v>91.04936981201172</v>
+        <v>91.04935455322266</v>
       </c>
       <c r="E47" t="n">
-        <v>91.04030011609154</v>
+        <v>91.04028485882247</v>
       </c>
       <c r="F47" t="n">
-        <v>91.04936981201172</v>
+        <v>91.04935455322266</v>
       </c>
       <c r="G47" t="n">
         <v>2415500</v>
@@ -1530,16 +1530,16 @@
         <v>45359</v>
       </c>
       <c r="C48" t="n">
-        <v>91.05842590332031</v>
+        <v>91.05841064453125</v>
       </c>
       <c r="D48" t="n">
-        <v>91.06749559857448</v>
+        <v>91.06748033826561</v>
       </c>
       <c r="E48" t="n">
-        <v>91.04936312621659</v>
+        <v>91.0493478689462</v>
       </c>
       <c r="F48" t="n">
-        <v>91.06749559857448</v>
+        <v>91.06748033826561</v>
       </c>
       <c r="G48" t="n">
         <v>3748900</v>
@@ -1553,16 +1553,16 @@
         <v>45362</v>
       </c>
       <c r="C49" t="n">
-        <v>91.07656097412109</v>
+        <v>91.07656860351562</v>
       </c>
       <c r="D49" t="n">
-        <v>91.07656097412109</v>
+        <v>91.07656860351562</v>
       </c>
       <c r="E49" t="n">
-        <v>91.06749127929709</v>
+        <v>91.06749890793186</v>
       </c>
       <c r="F49" t="n">
-        <v>91.07656097412109</v>
+        <v>91.07656860351562</v>
       </c>
       <c r="G49" t="n">
         <v>3238400</v>
@@ -1576,16 +1576,16 @@
         <v>45363</v>
       </c>
       <c r="C50" t="n">
-        <v>91.08560943603516</v>
+        <v>91.08561706542969</v>
       </c>
       <c r="D50" t="n">
-        <v>91.0946791294338</v>
+        <v>91.09468675958801</v>
       </c>
       <c r="E50" t="n">
-        <v>91.08560943603516</v>
+        <v>91.08561706542969</v>
       </c>
       <c r="F50" t="n">
-        <v>91.08560943603516</v>
+        <v>91.08561706542969</v>
       </c>
       <c r="G50" t="n">
         <v>2613300</v>
@@ -1599,16 +1599,16 @@
         <v>45364</v>
       </c>
       <c r="C51" t="n">
-        <v>91.09467315673828</v>
+        <v>91.09470367431641</v>
       </c>
       <c r="D51" t="n">
-        <v>91.10374284954226</v>
+        <v>91.10377337015881</v>
       </c>
       <c r="E51" t="n">
-        <v>91.09467315673828</v>
+        <v>91.09470367431641</v>
       </c>
       <c r="F51" t="n">
-        <v>91.09467315673828</v>
+        <v>91.09470367431641</v>
       </c>
       <c r="G51" t="n">
         <v>2249300</v>
@@ -1622,16 +1622,16 @@
         <v>45365</v>
       </c>
       <c r="C52" t="n">
-        <v>91.13096618652344</v>
+        <v>91.13097381591797</v>
       </c>
       <c r="D52" t="n">
-        <v>91.140035881435</v>
+        <v>91.14004351158884</v>
       </c>
       <c r="E52" t="n">
-        <v>91.13096618652344</v>
+        <v>91.13097381591797</v>
       </c>
       <c r="F52" t="n">
-        <v>91.13096618652344</v>
+        <v>91.13097381591797</v>
       </c>
       <c r="G52" t="n">
         <v>3469600</v>
@@ -1645,16 +1645,16 @@
         <v>45366</v>
       </c>
       <c r="C53" t="n">
-        <v>91.14907836914062</v>
+        <v>91.14909362792969</v>
       </c>
       <c r="D53" t="n">
-        <v>91.14907836914062</v>
+        <v>91.14909362792969</v>
       </c>
       <c r="E53" t="n">
-        <v>91.14001559439656</v>
+        <v>91.14003085166847</v>
       </c>
       <c r="F53" t="n">
-        <v>91.14907836914062</v>
+        <v>91.14909362792969</v>
       </c>
       <c r="G53" t="n">
         <v>3277300</v>
@@ -1668,16 +1668,16 @@
         <v>45369</v>
       </c>
       <c r="C54" t="n">
-        <v>91.15814208984375</v>
+        <v>91.15814971923828</v>
       </c>
       <c r="D54" t="n">
-        <v>91.16721178214227</v>
+        <v>91.16721941229589</v>
       </c>
       <c r="E54" t="n">
-        <v>91.15814208984375</v>
+        <v>91.15814971923828</v>
       </c>
       <c r="F54" t="n">
-        <v>91.16721178214227</v>
+        <v>91.16721941229589</v>
       </c>
       <c r="G54" t="n">
         <v>3576200</v>
@@ -1691,16 +1691,16 @@
         <v>45370</v>
       </c>
       <c r="C55" t="n">
-        <v>91.17630004882812</v>
+        <v>91.17630767822266</v>
       </c>
       <c r="D55" t="n">
-        <v>91.18536282482471</v>
+        <v>91.18537045497759</v>
       </c>
       <c r="E55" t="n">
-        <v>91.17630004882812</v>
+        <v>91.17630767822266</v>
       </c>
       <c r="F55" t="n">
-        <v>91.18536282482471</v>
+        <v>91.18537045497759</v>
       </c>
       <c r="G55" t="n">
         <v>2661900</v>
@@ -1714,16 +1714,16 @@
         <v>45371</v>
       </c>
       <c r="C56" t="n">
-        <v>91.18538665771484</v>
+        <v>91.18535614013672</v>
       </c>
       <c r="D56" t="n">
-        <v>91.19445635423156</v>
+        <v>91.19442583361803</v>
       </c>
       <c r="E56" t="n">
-        <v>91.18538665771484</v>
+        <v>91.18535614013672</v>
       </c>
       <c r="F56" t="n">
-        <v>91.18538665771484</v>
+        <v>91.18535614013672</v>
       </c>
       <c r="G56" t="n">
         <v>2492700</v>
@@ -1737,16 +1737,16 @@
         <v>45372</v>
       </c>
       <c r="C57" t="n">
-        <v>91.22164154052734</v>
+        <v>91.22163391113281</v>
       </c>
       <c r="D57" t="n">
-        <v>91.23071123535532</v>
+        <v>91.23070360520224</v>
       </c>
       <c r="E57" t="n">
-        <v>91.22164154052734</v>
+        <v>91.22163391113281</v>
       </c>
       <c r="F57" t="n">
-        <v>91.22164154052734</v>
+        <v>91.22163391113281</v>
       </c>
       <c r="G57" t="n">
         <v>3547400</v>
@@ -1760,16 +1760,16 @@
         <v>45373</v>
       </c>
       <c r="C58" t="n">
-        <v>91.23977661132812</v>
+        <v>91.23976898193359</v>
       </c>
       <c r="D58" t="n">
-        <v>91.24883938757698</v>
+        <v>91.24883175742463</v>
       </c>
       <c r="E58" t="n">
-        <v>91.23070691692946</v>
+        <v>91.23069928829332</v>
       </c>
       <c r="F58" t="n">
-        <v>91.24883938757698</v>
+        <v>91.24883175742463</v>
       </c>
       <c r="G58" t="n">
         <v>2636700</v>
@@ -1806,16 +1806,16 @@
         <v>45377</v>
       </c>
       <c r="C60" t="n">
-        <v>91.2669677734375</v>
+        <v>91.26699066162109</v>
       </c>
       <c r="D60" t="n">
-        <v>91.27603746674274</v>
+        <v>91.27606035720085</v>
       </c>
       <c r="E60" t="n">
-        <v>91.2669677734375</v>
+        <v>91.26699066162109</v>
       </c>
       <c r="F60" t="n">
-        <v>91.2669677734375</v>
+        <v>91.26699066162109</v>
       </c>
       <c r="G60" t="n">
         <v>3181700</v>
@@ -1829,16 +1829,16 @@
         <v>45378</v>
       </c>
       <c r="C61" t="n">
-        <v>91.31233215332031</v>
+        <v>91.31230926513672</v>
       </c>
       <c r="D61" t="n">
-        <v>91.32140184958047</v>
+        <v>91.32137895912348</v>
       </c>
       <c r="E61" t="n">
-        <v>91.31233215332031</v>
+        <v>91.31230926513672</v>
       </c>
       <c r="F61" t="n">
-        <v>91.32140184958047</v>
+        <v>91.32137895912348</v>
       </c>
       <c r="G61" t="n">
         <v>2990800</v>
@@ -1875,16 +1875,16 @@
         <v>45383</v>
       </c>
       <c r="C63" t="n">
-        <v>91.34870910644531</v>
+        <v>91.34871673583984</v>
       </c>
       <c r="D63" t="n">
-        <v>91.35781950852548</v>
+        <v>91.3578271386809</v>
       </c>
       <c r="E63" t="n">
-        <v>91.34870910644531</v>
+        <v>91.34871673583984</v>
       </c>
       <c r="F63" t="n">
-        <v>91.35781950852548</v>
+        <v>91.3578271386809</v>
       </c>
       <c r="G63" t="n">
         <v>7395400</v>
@@ -1921,16 +1921,16 @@
         <v>45385</v>
       </c>
       <c r="C65" t="n">
-        <v>91.37601470947266</v>
+        <v>91.37602996826172</v>
       </c>
       <c r="D65" t="n">
-        <v>91.38512510969296</v>
+        <v>91.38514037000337</v>
       </c>
       <c r="E65" t="n">
-        <v>91.37601470947266</v>
+        <v>91.37602996826172</v>
       </c>
       <c r="F65" t="n">
-        <v>91.37601470947266</v>
+        <v>91.37602996826172</v>
       </c>
       <c r="G65" t="n">
         <v>4333600</v>
@@ -1967,16 +1967,16 @@
         <v>45387</v>
       </c>
       <c r="C67" t="n">
-        <v>91.43067932128906</v>
+        <v>91.4306640625</v>
       </c>
       <c r="D67" t="n">
-        <v>91.43978972311452</v>
+        <v>91.43977446280502</v>
       </c>
       <c r="E67" t="n">
-        <v>91.43067932128906</v>
+        <v>91.4306640625</v>
       </c>
       <c r="F67" t="n">
-        <v>91.43978972311452</v>
+        <v>91.43977446280502</v>
       </c>
       <c r="G67" t="n">
         <v>3104200</v>
@@ -1990,16 +1990,16 @@
         <v>45390</v>
       </c>
       <c r="C68" t="n">
-        <v>91.44889068603516</v>
+        <v>91.44889831542969</v>
       </c>
       <c r="D68" t="n">
-        <v>91.44889068603516</v>
+        <v>91.44889831542969</v>
       </c>
       <c r="E68" t="n">
-        <v>91.43978028515004</v>
+        <v>91.43978791378451</v>
       </c>
       <c r="F68" t="n">
-        <v>91.44889068603516</v>
+        <v>91.44889831542969</v>
       </c>
       <c r="G68" t="n">
         <v>3511400</v>
@@ -2013,16 +2013,16 @@
         <v>45391</v>
       </c>
       <c r="C69" t="n">
-        <v>91.45802307128906</v>
+        <v>91.4580078125</v>
       </c>
       <c r="D69" t="n">
-        <v>91.45802307128906</v>
+        <v>91.4580078125</v>
       </c>
       <c r="E69" t="n">
-        <v>91.44891266821402</v>
+        <v>91.44889741094494</v>
       </c>
       <c r="F69" t="n">
-        <v>91.45802307128906</v>
+        <v>91.4580078125</v>
       </c>
       <c r="G69" t="n">
         <v>3578500</v>
@@ -2036,16 +2036,16 @@
         <v>45392</v>
       </c>
       <c r="C70" t="n">
-        <v>91.47621917724609</v>
+        <v>91.47624206542969</v>
       </c>
       <c r="D70" t="n">
-        <v>91.47621917724609</v>
+        <v>91.47624206542969</v>
       </c>
       <c r="E70" t="n">
-        <v>91.45800532383184</v>
+        <v>91.45802820745816</v>
       </c>
       <c r="F70" t="n">
-        <v>91.46710877593893</v>
+        <v>91.46713166184301</v>
       </c>
       <c r="G70" t="n">
         <v>3893100</v>
@@ -2059,16 +2059,16 @@
         <v>45393</v>
       </c>
       <c r="C71" t="n">
-        <v>91.51264190673828</v>
+        <v>91.51264953613281</v>
       </c>
       <c r="D71" t="n">
-        <v>91.51264190673828</v>
+        <v>91.51264953613281</v>
       </c>
       <c r="E71" t="n">
-        <v>91.50353150661844</v>
+        <v>91.50353913525345</v>
       </c>
       <c r="F71" t="n">
-        <v>91.50353150661844</v>
+        <v>91.50353913525345</v>
       </c>
       <c r="G71" t="n">
         <v>3521100</v>
@@ -2082,16 +2082,16 @@
         <v>45394</v>
       </c>
       <c r="C72" t="n">
-        <v>91.52177429199219</v>
+        <v>91.52175903320312</v>
       </c>
       <c r="D72" t="n">
-        <v>91.52177429199219</v>
+        <v>91.52175903320312</v>
       </c>
       <c r="E72" t="n">
-        <v>91.51266388968386</v>
+        <v>91.51264863241371</v>
       </c>
       <c r="F72" t="n">
-        <v>91.52177429199219</v>
+        <v>91.52175903320312</v>
       </c>
       <c r="G72" t="n">
         <v>4235400</v>
@@ -2151,16 +2151,16 @@
         <v>45399</v>
       </c>
       <c r="C75" t="n">
-        <v>91.56729125976562</v>
+        <v>91.56730651855469</v>
       </c>
       <c r="D75" t="n">
-        <v>91.56729125976562</v>
+        <v>91.56730651855469</v>
       </c>
       <c r="E75" t="n">
-        <v>91.55818085956115</v>
+        <v>91.55819611683205</v>
       </c>
       <c r="F75" t="n">
-        <v>91.56729125976562</v>
+        <v>91.56730651855469</v>
       </c>
       <c r="G75" t="n">
         <v>3688400</v>
@@ -2174,16 +2174,16 @@
         <v>45400</v>
       </c>
       <c r="C76" t="n">
-        <v>91.59465026855469</v>
+        <v>91.59462738037109</v>
       </c>
       <c r="D76" t="n">
-        <v>91.6037606722163</v>
+        <v>91.60373778175614</v>
       </c>
       <c r="E76" t="n">
-        <v>91.59465026855469</v>
+        <v>91.59462738037109</v>
       </c>
       <c r="F76" t="n">
-        <v>91.6037606722163</v>
+        <v>91.60373778175614</v>
       </c>
       <c r="G76" t="n">
         <v>3235600</v>
@@ -2197,16 +2197,16 @@
         <v>45401</v>
       </c>
       <c r="C77" t="n">
-        <v>91.62194061279297</v>
+        <v>91.62198638916016</v>
       </c>
       <c r="D77" t="n">
-        <v>91.62194061279297</v>
+        <v>91.62198638916016</v>
       </c>
       <c r="E77" t="n">
-        <v>91.60372676141424</v>
+        <v>91.60377252868138</v>
       </c>
       <c r="F77" t="n">
-        <v>91.62194061279297</v>
+        <v>91.62198638916016</v>
       </c>
       <c r="G77" t="n">
         <v>3319500</v>
@@ -2266,16 +2266,16 @@
         <v>45406</v>
       </c>
       <c r="C80" t="n">
-        <v>91.64929962158203</v>
+        <v>91.6492919921875</v>
       </c>
       <c r="D80" t="n">
-        <v>91.65840307543388</v>
+        <v>91.65839544528153</v>
       </c>
       <c r="E80" t="n">
-        <v>91.64929962158203</v>
+        <v>91.6492919921875</v>
       </c>
       <c r="F80" t="n">
-        <v>91.65840307543388</v>
+        <v>91.65839544528153</v>
       </c>
       <c r="G80" t="n">
         <v>3200000</v>
@@ -2289,16 +2289,16 @@
         <v>45407</v>
       </c>
       <c r="C81" t="n">
-        <v>91.69480133056641</v>
+        <v>91.69482421875</v>
       </c>
       <c r="D81" t="n">
-        <v>91.69480133056641</v>
+        <v>91.69482421875</v>
       </c>
       <c r="E81" t="n">
-        <v>91.68569788032913</v>
+        <v>91.68572076624038</v>
       </c>
       <c r="F81" t="n">
-        <v>91.69480133056641</v>
+        <v>91.69482421875</v>
       </c>
       <c r="G81" t="n">
         <v>2705900</v>
@@ -2312,16 +2312,16 @@
         <v>45408</v>
       </c>
       <c r="C82" t="n">
-        <v>91.71304321289062</v>
+        <v>91.71305847167969</v>
       </c>
       <c r="D82" t="n">
-        <v>91.71304321289062</v>
+        <v>91.71305847167969</v>
       </c>
       <c r="E82" t="n">
-        <v>91.70393281136035</v>
+        <v>91.70394806863366</v>
       </c>
       <c r="F82" t="n">
-        <v>91.70393281136035</v>
+        <v>91.70394806863366</v>
       </c>
       <c r="G82" t="n">
         <v>3008600</v>
@@ -2335,16 +2335,16 @@
         <v>45411</v>
       </c>
       <c r="C83" t="n">
-        <v>91.71304321289062</v>
+        <v>91.71305847167969</v>
       </c>
       <c r="D83" t="n">
-        <v>91.72214666522066</v>
+        <v>91.7221619255243</v>
       </c>
       <c r="E83" t="n">
-        <v>91.71304321289062</v>
+        <v>91.71305847167969</v>
       </c>
       <c r="F83" t="n">
-        <v>91.72214666522066</v>
+        <v>91.7221619255243</v>
       </c>
       <c r="G83" t="n">
         <v>2501900</v>
@@ -2358,16 +2358,16 @@
         <v>45412</v>
       </c>
       <c r="C84" t="n">
-        <v>91.72214508056641</v>
+        <v>91.72215270996094</v>
       </c>
       <c r="D84" t="n">
-        <v>91.73125548193929</v>
+        <v>91.73126311209163</v>
       </c>
       <c r="E84" t="n">
-        <v>91.72214508056641</v>
+        <v>91.72215270996094</v>
       </c>
       <c r="F84" t="n">
-        <v>91.72214508056641</v>
+        <v>91.72215270996094</v>
       </c>
       <c r="G84" t="n">
         <v>6488000</v>
@@ -2381,16 +2381,16 @@
         <v>45413</v>
       </c>
       <c r="C85" t="n">
-        <v>91.75690460205078</v>
+        <v>91.75691223144531</v>
       </c>
       <c r="D85" t="n">
-        <v>91.75690460205078</v>
+        <v>91.75691223144531</v>
       </c>
       <c r="E85" t="n">
-        <v>91.7477622928831</v>
+        <v>91.74776992151747</v>
       </c>
       <c r="F85" t="n">
-        <v>91.75690460205078</v>
+        <v>91.75691223144531</v>
       </c>
       <c r="G85" t="n">
         <v>8406600</v>
@@ -2404,16 +2404,16 @@
         <v>45414</v>
       </c>
       <c r="C86" t="n">
-        <v>91.79349517822266</v>
+        <v>91.79348754882812</v>
       </c>
       <c r="D86" t="n">
-        <v>91.79349517822266</v>
+        <v>91.79348754882812</v>
       </c>
       <c r="E86" t="n">
-        <v>91.78434589015285</v>
+        <v>91.78433826151877</v>
       </c>
       <c r="F86" t="n">
-        <v>91.79349517822266</v>
+        <v>91.79348754882812</v>
       </c>
       <c r="G86" t="n">
         <v>4369600</v>
@@ -2496,16 +2496,16 @@
         <v>45420</v>
       </c>
       <c r="C90" t="n">
-        <v>91.84840393066406</v>
+        <v>91.84837341308594</v>
       </c>
       <c r="D90" t="n">
-        <v>91.84840393066406</v>
+        <v>91.84837341308594</v>
       </c>
       <c r="E90" t="n">
-        <v>91.83010535053937</v>
+        <v>91.83007483904115</v>
       </c>
       <c r="F90" t="n">
-        <v>91.83925464060172</v>
+        <v>91.83922412606354</v>
       </c>
       <c r="G90" t="n">
         <v>3109400</v>
@@ -2519,16 +2519,16 @@
         <v>45421</v>
       </c>
       <c r="C91" t="n">
-        <v>91.87582397460938</v>
+        <v>91.87583160400391</v>
       </c>
       <c r="D91" t="n">
-        <v>91.88496628373375</v>
+        <v>91.88497391388746</v>
       </c>
       <c r="E91" t="n">
-        <v>91.87582397460938</v>
+        <v>91.87583160400391</v>
       </c>
       <c r="F91" t="n">
-        <v>91.88039512917156</v>
+        <v>91.88040275894568</v>
       </c>
       <c r="G91" t="n">
         <v>2739600</v>
@@ -2542,16 +2542,16 @@
         <v>45422</v>
       </c>
       <c r="C92" t="n">
-        <v>91.90324401855469</v>
+        <v>91.90327453613281</v>
       </c>
       <c r="D92" t="n">
-        <v>91.90324401855469</v>
+        <v>91.90327453613281</v>
       </c>
       <c r="E92" t="n">
-        <v>91.88494544673172</v>
+        <v>91.88497595823358</v>
       </c>
       <c r="F92" t="n">
-        <v>91.90324401855469</v>
+        <v>91.90327453613281</v>
       </c>
       <c r="G92" t="n">
         <v>3005800</v>
@@ -2565,16 +2565,16 @@
         <v>45425</v>
       </c>
       <c r="C93" t="n">
-        <v>91.91242980957031</v>
+        <v>91.91242218017578</v>
       </c>
       <c r="D93" t="n">
-        <v>91.91242980957031</v>
+        <v>91.91242218017578</v>
       </c>
       <c r="E93" t="n">
-        <v>91.90328052002498</v>
+        <v>91.9032728913899</v>
       </c>
       <c r="F93" t="n">
-        <v>91.91242980957031</v>
+        <v>91.91242218017578</v>
       </c>
       <c r="G93" t="n">
         <v>3317000</v>
@@ -2588,16 +2588,16 @@
         <v>45426</v>
       </c>
       <c r="C94" t="n">
-        <v>91.91242980957031</v>
+        <v>91.91242218017578</v>
       </c>
       <c r="D94" t="n">
-        <v>91.92157212025253</v>
+        <v>91.92156449009912</v>
       </c>
       <c r="E94" t="n">
-        <v>91.91242980957031</v>
+        <v>91.91242218017578</v>
       </c>
       <c r="F94" t="n">
-        <v>91.92157212025253</v>
+        <v>91.92156449009912</v>
       </c>
       <c r="G94" t="n">
         <v>2765800</v>
@@ -2611,16 +2611,16 @@
         <v>45427</v>
       </c>
       <c r="C95" t="n">
-        <v>91.93070983886719</v>
+        <v>91.93070220947266</v>
       </c>
       <c r="D95" t="n">
-        <v>91.93985912726093</v>
+        <v>91.93985149710711</v>
       </c>
       <c r="E95" t="n">
-        <v>91.93070983886719</v>
+        <v>91.93070220947266</v>
       </c>
       <c r="F95" t="n">
-        <v>91.93070983886719</v>
+        <v>91.93070220947266</v>
       </c>
       <c r="G95" t="n">
         <v>4228600</v>
@@ -2657,16 +2657,16 @@
         <v>45429</v>
       </c>
       <c r="C97" t="n">
-        <v>91.98561096191406</v>
+        <v>91.985595703125</v>
       </c>
       <c r="D97" t="n">
-        <v>91.9947602522325</v>
+        <v>91.99474499192573</v>
       </c>
       <c r="E97" t="n">
-        <v>91.98561096191406</v>
+        <v>91.985595703125</v>
       </c>
       <c r="F97" t="n">
-        <v>91.9947602522325</v>
+        <v>91.99474499192573</v>
       </c>
       <c r="G97" t="n">
         <v>4544200</v>
@@ -2680,16 +2680,16 @@
         <v>45432</v>
       </c>
       <c r="C98" t="n">
-        <v>91.99474334716797</v>
+        <v>91.99473571777344</v>
       </c>
       <c r="D98" t="n">
-        <v>92.00389263580512</v>
+        <v>92.0038850056518</v>
       </c>
       <c r="E98" t="n">
-        <v>91.99474334716797</v>
+        <v>91.99473571777344</v>
       </c>
       <c r="F98" t="n">
-        <v>92.00389263580512</v>
+        <v>92.0038850056518</v>
       </c>
       <c r="G98" t="n">
         <v>3341000</v>
@@ -2726,16 +2726,16 @@
         <v>45434</v>
       </c>
       <c r="C100" t="n">
-        <v>92.02217864990234</v>
+        <v>92.02219390869141</v>
       </c>
       <c r="D100" t="n">
-        <v>92.03132793798427</v>
+        <v>92.03134319829043</v>
       </c>
       <c r="E100" t="n">
-        <v>92.02217864990234</v>
+        <v>92.02219390869141</v>
       </c>
       <c r="F100" t="n">
-        <v>92.03132793798427</v>
+        <v>92.03134319829043</v>
       </c>
       <c r="G100" t="n">
         <v>2609000</v>
@@ -2749,16 +2749,16 @@
         <v>45435</v>
       </c>
       <c r="C101" t="n">
-        <v>92.08619689941406</v>
+        <v>92.08620452880859</v>
       </c>
       <c r="D101" t="n">
-        <v>92.08619689941406</v>
+        <v>92.08620452880859</v>
       </c>
       <c r="E101" t="n">
-        <v>92.07705459146585</v>
+        <v>92.07706222010293</v>
       </c>
       <c r="F101" t="n">
-        <v>92.07705459146585</v>
+        <v>92.07706222010293</v>
       </c>
       <c r="G101" t="n">
         <v>3077800</v>
@@ -2772,16 +2772,16 @@
         <v>45436</v>
       </c>
       <c r="C102" t="n">
-        <v>92.09537506103516</v>
+        <v>92.09535980224609</v>
       </c>
       <c r="D102" t="n">
-        <v>92.09537506103516</v>
+        <v>92.09535980224609</v>
       </c>
       <c r="E102" t="n">
-        <v>92.08622577135732</v>
+        <v>92.08621051408414</v>
       </c>
       <c r="F102" t="n">
-        <v>92.09537506103516</v>
+        <v>92.09535980224609</v>
       </c>
       <c r="G102" t="n">
         <v>2512800</v>
@@ -2795,16 +2795,16 @@
         <v>45440</v>
       </c>
       <c r="C103" t="n">
-        <v>92.10450744628906</v>
+        <v>92.10452270507812</v>
       </c>
       <c r="D103" t="n">
-        <v>92.10450744628906</v>
+        <v>92.10452270507812</v>
       </c>
       <c r="E103" t="n">
-        <v>92.09535815829045</v>
+        <v>92.09537341556376</v>
       </c>
       <c r="F103" t="n">
-        <v>92.09535815829045</v>
+        <v>92.09537341556376</v>
       </c>
       <c r="G103" t="n">
         <v>3684600</v>
@@ -2818,16 +2818,16 @@
         <v>45441</v>
       </c>
       <c r="C104" t="n">
-        <v>92.10450744628906</v>
+        <v>92.10452270507812</v>
       </c>
       <c r="D104" t="n">
-        <v>92.11364975542574</v>
+        <v>92.1136650157294</v>
       </c>
       <c r="E104" t="n">
-        <v>92.10450744628906</v>
+        <v>92.10452270507812</v>
       </c>
       <c r="F104" t="n">
-        <v>92.11364975542574</v>
+        <v>92.1136650157294</v>
       </c>
       <c r="G104" t="n">
         <v>3971700</v>
@@ -2841,16 +2841,16 @@
         <v>45442</v>
       </c>
       <c r="C105" t="n">
-        <v>92.12281799316406</v>
+        <v>92.12279510498047</v>
       </c>
       <c r="D105" t="n">
-        <v>92.1319672830447</v>
+        <v>92.13194439258794</v>
       </c>
       <c r="E105" t="n">
-        <v>92.12281799316406</v>
+        <v>92.12279510498047</v>
       </c>
       <c r="F105" t="n">
-        <v>92.12281799316406</v>
+        <v>92.12279510498047</v>
       </c>
       <c r="G105" t="n">
         <v>3566800</v>
@@ -2910,16 +2910,16 @@
         <v>45447</v>
       </c>
       <c r="C108" t="n">
-        <v>92.19613647460938</v>
+        <v>92.19615173339844</v>
       </c>
       <c r="D108" t="n">
-        <v>92.19613647460938</v>
+        <v>92.19615173339844</v>
       </c>
       <c r="E108" t="n">
-        <v>92.18694705427092</v>
+        <v>92.18696231153911</v>
       </c>
       <c r="F108" t="n">
-        <v>92.19613647460938</v>
+        <v>92.19615173339844</v>
       </c>
       <c r="G108" t="n">
         <v>5355900</v>
@@ -2979,16 +2979,16 @@
         <v>45450</v>
       </c>
       <c r="C111" t="n">
-        <v>92.25128173828125</v>
+        <v>92.25126647949219</v>
       </c>
       <c r="D111" t="n">
-        <v>92.26046415071357</v>
+        <v>92.2604488904057</v>
       </c>
       <c r="E111" t="n">
-        <v>92.25128173828125</v>
+        <v>92.25126647949219</v>
       </c>
       <c r="F111" t="n">
-        <v>92.26046415071357</v>
+        <v>92.2604488904057</v>
       </c>
       <c r="G111" t="n">
         <v>3490400</v>
@@ -3002,16 +3002,16 @@
         <v>45453</v>
       </c>
       <c r="C112" t="n">
-        <v>92.2696533203125</v>
+        <v>92.26964569091797</v>
       </c>
       <c r="D112" t="n">
-        <v>92.27884274219484</v>
+        <v>92.27883511204048</v>
       </c>
       <c r="E112" t="n">
-        <v>92.2696533203125</v>
+        <v>92.26964569091797</v>
       </c>
       <c r="F112" t="n">
-        <v>92.27884274219484</v>
+        <v>92.27883511204048</v>
       </c>
       <c r="G112" t="n">
         <v>2732300</v>
@@ -3025,16 +3025,16 @@
         <v>45454</v>
       </c>
       <c r="C113" t="n">
-        <v>92.28800201416016</v>
+        <v>92.28801727294922</v>
       </c>
       <c r="D113" t="n">
-        <v>92.28800201416016</v>
+        <v>92.28801727294922</v>
       </c>
       <c r="E113" t="n">
-        <v>92.27881960405534</v>
+        <v>92.2788348613262</v>
       </c>
       <c r="F113" t="n">
-        <v>92.28800201416016</v>
+        <v>92.28801727294922</v>
       </c>
       <c r="G113" t="n">
         <v>3320000</v>
@@ -3048,16 +3048,16 @@
         <v>45455</v>
       </c>
       <c r="C114" t="n">
-        <v>92.30636596679688</v>
+        <v>92.30638885498047</v>
       </c>
       <c r="D114" t="n">
-        <v>92.30636596679688</v>
+        <v>92.30638885498047</v>
       </c>
       <c r="E114" t="n">
-        <v>92.28798713060455</v>
+        <v>92.28801001423095</v>
       </c>
       <c r="F114" t="n">
-        <v>92.29717654870072</v>
+        <v>92.2971994346057</v>
       </c>
       <c r="G114" t="n">
         <v>5355700</v>
@@ -3071,16 +3071,16 @@
         <v>45456</v>
       </c>
       <c r="C115" t="n">
-        <v>92.31558990478516</v>
+        <v>92.31558227539062</v>
       </c>
       <c r="D115" t="n">
-        <v>92.32477231684271</v>
+        <v>92.32476468668929</v>
       </c>
       <c r="E115" t="n">
-        <v>92.30640048325276</v>
+        <v>92.30639285461768</v>
       </c>
       <c r="F115" t="n">
-        <v>92.31558990478516</v>
+        <v>92.31558227539062</v>
       </c>
       <c r="G115" t="n">
         <v>3925700</v>
@@ -3094,16 +3094,16 @@
         <v>45457</v>
       </c>
       <c r="C116" t="n">
-        <v>92.36149597167969</v>
+        <v>92.36152648925781</v>
       </c>
       <c r="D116" t="n">
-        <v>92.36149597167969</v>
+        <v>92.36152648925781</v>
       </c>
       <c r="E116" t="n">
-        <v>92.34312414346471</v>
+        <v>92.34315465497252</v>
       </c>
       <c r="F116" t="n">
-        <v>92.3523065528358</v>
+        <v>92.3523370673776</v>
       </c>
       <c r="G116" t="n">
         <v>3505500</v>
@@ -3140,16 +3140,16 @@
         <v>45461</v>
       </c>
       <c r="C118" t="n">
-        <v>92.39826965332031</v>
+        <v>92.39827728271484</v>
       </c>
       <c r="D118" t="n">
-        <v>92.39826965332031</v>
+        <v>92.39827728271484</v>
       </c>
       <c r="E118" t="n">
-        <v>92.3890802321874</v>
+        <v>92.38908786082315</v>
       </c>
       <c r="F118" t="n">
-        <v>92.39826965332031</v>
+        <v>92.39827728271484</v>
       </c>
       <c r="G118" t="n">
         <v>2972000</v>
@@ -3163,16 +3163,16 @@
         <v>45463</v>
       </c>
       <c r="C119" t="n">
-        <v>92.40744781494141</v>
+        <v>92.40743255615234</v>
       </c>
       <c r="D119" t="n">
-        <v>92.41663022548092</v>
+        <v>92.41661496517561</v>
       </c>
       <c r="E119" t="n">
-        <v>92.40744781494141</v>
+        <v>92.40743255615234</v>
       </c>
       <c r="F119" t="n">
-        <v>92.40744781494141</v>
+        <v>92.40743255615234</v>
       </c>
       <c r="G119" t="n">
         <v>3580700</v>
@@ -3186,16 +3186,16 @@
         <v>45464</v>
       </c>
       <c r="C120" t="n">
-        <v>92.4442138671875</v>
+        <v>92.44417572021484</v>
       </c>
       <c r="D120" t="n">
-        <v>92.45339627925487</v>
+        <v>92.45335812849311</v>
       </c>
       <c r="E120" t="n">
-        <v>92.4442138671875</v>
+        <v>92.44417572021484</v>
       </c>
       <c r="F120" t="n">
-        <v>92.4442138671875</v>
+        <v>92.44417572021484</v>
       </c>
       <c r="G120" t="n">
         <v>3460900</v>
@@ -3209,16 +3209,16 @@
         <v>45467</v>
       </c>
       <c r="C121" t="n">
-        <v>92.453369140625</v>
+        <v>92.45339202880859</v>
       </c>
       <c r="D121" t="n">
-        <v>92.46255855946977</v>
+        <v>92.46258144992834</v>
       </c>
       <c r="E121" t="n">
-        <v>92.453369140625</v>
+        <v>92.45339202880859</v>
       </c>
       <c r="F121" t="n">
-        <v>92.46255855946977</v>
+        <v>92.46258144992834</v>
       </c>
       <c r="G121" t="n">
         <v>3369500</v>
@@ -3232,16 +3232,16 @@
         <v>45468</v>
       </c>
       <c r="C122" t="n">
-        <v>92.47175598144531</v>
+        <v>92.47176361083984</v>
       </c>
       <c r="D122" t="n">
-        <v>92.47175598144531</v>
+        <v>92.47176361083984</v>
       </c>
       <c r="E122" t="n">
-        <v>92.46256656180523</v>
+        <v>92.46257419044157</v>
       </c>
       <c r="F122" t="n">
-        <v>92.47175598144531</v>
+        <v>92.47176361083984</v>
       </c>
       <c r="G122" t="n">
         <v>3561700</v>
@@ -3255,16 +3255,16 @@
         <v>45469</v>
       </c>
       <c r="C123" t="n">
-        <v>92.48094940185547</v>
+        <v>92.48097991943359</v>
       </c>
       <c r="D123" t="n">
-        <v>92.49013181241939</v>
+        <v>92.4901623330276</v>
       </c>
       <c r="E123" t="n">
-        <v>92.48094940185547</v>
+        <v>92.48097991943359</v>
       </c>
       <c r="F123" t="n">
-        <v>92.48186764291187</v>
+        <v>92.48189816079299</v>
       </c>
       <c r="G123" t="n">
         <v>4815500</v>
@@ -3278,16 +3278,16 @@
         <v>45470</v>
       </c>
       <c r="C124" t="n">
-        <v>92.49011993408203</v>
+        <v>92.49015045166016</v>
       </c>
       <c r="D124" t="n">
-        <v>92.49930935293949</v>
+        <v>92.4993398735497</v>
       </c>
       <c r="E124" t="n">
-        <v>92.49011993408203</v>
+        <v>92.49015045166016</v>
       </c>
       <c r="F124" t="n">
-        <v>92.49930935293949</v>
+        <v>92.4993398735497</v>
       </c>
       <c r="G124" t="n">
         <v>3349900</v>
@@ -3301,16 +3301,16 @@
         <v>45471</v>
       </c>
       <c r="C125" t="n">
-        <v>92.52690887451172</v>
+        <v>92.52687835693359</v>
       </c>
       <c r="D125" t="n">
-        <v>92.53609829717044</v>
+        <v>92.53606777656142</v>
       </c>
       <c r="E125" t="n">
-        <v>92.52690887451172</v>
+        <v>92.52687835693359</v>
       </c>
       <c r="F125" t="n">
-        <v>92.52690887451172</v>
+        <v>92.52687835693359</v>
       </c>
       <c r="G125" t="n">
         <v>7427800</v>
@@ -3324,16 +3324,16 @@
         <v>45474</v>
       </c>
       <c r="C126" t="n">
-        <v>92.56287384033203</v>
+        <v>92.56289672851562</v>
       </c>
       <c r="D126" t="n">
-        <v>92.56287384033203</v>
+        <v>92.56289672851562</v>
       </c>
       <c r="E126" t="n">
-        <v>92.55365122745329</v>
+        <v>92.55367411335638</v>
       </c>
       <c r="F126" t="n">
-        <v>92.56287384033203</v>
+        <v>92.56289672851562</v>
       </c>
       <c r="G126" t="n">
         <v>9965300</v>
@@ -3370,16 +3370,16 @@
         <v>45476</v>
       </c>
       <c r="C128" t="n">
-        <v>92.59978485107422</v>
+        <v>92.59980773925781</v>
       </c>
       <c r="D128" t="n">
-        <v>92.59978485107422</v>
+        <v>92.59980773925781</v>
       </c>
       <c r="E128" t="n">
-        <v>92.59055519808891</v>
+        <v>92.59057808399118</v>
       </c>
       <c r="F128" t="n">
-        <v>92.59978485107422</v>
+        <v>92.59980773925781</v>
       </c>
       <c r="G128" t="n">
         <v>3986000</v>
@@ -3393,16 +3393,16 @@
         <v>45478</v>
       </c>
       <c r="C129" t="n">
-        <v>92.63670349121094</v>
+        <v>92.63669586181641</v>
       </c>
       <c r="D129" t="n">
-        <v>92.63670349121094</v>
+        <v>92.63669586181641</v>
       </c>
       <c r="E129" t="n">
-        <v>92.62747383752138</v>
+        <v>92.627466208887</v>
       </c>
       <c r="F129" t="n">
-        <v>92.62747383752138</v>
+        <v>92.627466208887</v>
       </c>
       <c r="G129" t="n">
         <v>3742000</v>
@@ -3416,16 +3416,16 @@
         <v>45481</v>
       </c>
       <c r="C130" t="n">
-        <v>92.65516662597656</v>
+        <v>92.6551513671875</v>
       </c>
       <c r="D130" t="n">
-        <v>92.65516662597656</v>
+        <v>92.6551513671875</v>
       </c>
       <c r="E130" t="n">
-        <v>92.64593697190575</v>
+        <v>92.64592171463667</v>
       </c>
       <c r="F130" t="n">
-        <v>92.64593697190575</v>
+        <v>92.64592171463667</v>
       </c>
       <c r="G130" t="n">
         <v>3263000</v>
@@ -3439,16 +3439,16 @@
         <v>45482</v>
       </c>
       <c r="C131" t="n">
-        <v>92.65516662597656</v>
+        <v>92.6551513671875</v>
       </c>
       <c r="D131" t="n">
-        <v>92.67361889395488</v>
+        <v>92.67360363212704</v>
       </c>
       <c r="E131" t="n">
-        <v>92.65516662597656</v>
+        <v>92.6551513671875</v>
       </c>
       <c r="F131" t="n">
-        <v>92.66438923988407</v>
+        <v>92.66437397957621</v>
       </c>
       <c r="G131" t="n">
         <v>4508000</v>
@@ -3462,16 +3462,16 @@
         <v>45483</v>
       </c>
       <c r="C132" t="n">
-        <v>92.67362213134766</v>
+        <v>92.67362976074219</v>
       </c>
       <c r="D132" t="n">
-        <v>92.68285178574088</v>
+        <v>92.68285941589525</v>
       </c>
       <c r="E132" t="n">
-        <v>92.67362213134766</v>
+        <v>92.67362976074219</v>
       </c>
       <c r="F132" t="n">
-        <v>92.67362213134766</v>
+        <v>92.67362976074219</v>
       </c>
       <c r="G132" t="n">
         <v>4062200</v>
@@ -3485,16 +3485,16 @@
         <v>45484</v>
       </c>
       <c r="C133" t="n">
-        <v>92.69204711914062</v>
+        <v>92.69206237792969</v>
       </c>
       <c r="D133" t="n">
-        <v>92.69204711914062</v>
+        <v>92.69206237792969</v>
       </c>
       <c r="E133" t="n">
-        <v>92.6828245076253</v>
+        <v>92.68283976489614</v>
       </c>
       <c r="F133" t="n">
-        <v>92.6828245076253</v>
+        <v>92.68283976489614</v>
       </c>
       <c r="G133" t="n">
         <v>4195600</v>
@@ -3508,16 +3508,16 @@
         <v>45485</v>
       </c>
       <c r="C134" t="n">
-        <v>92.73820495605469</v>
+        <v>92.73821258544922</v>
       </c>
       <c r="D134" t="n">
-        <v>92.73820495605469</v>
+        <v>92.73821258544922</v>
       </c>
       <c r="E134" t="n">
-        <v>92.72897530272394</v>
+        <v>92.72898293135917</v>
       </c>
       <c r="F134" t="n">
-        <v>92.73820495605469</v>
+        <v>92.73821258544922</v>
       </c>
       <c r="G134" t="n">
         <v>3369000</v>
@@ -3531,16 +3531,16 @@
         <v>45488</v>
       </c>
       <c r="C135" t="n">
-        <v>92.73820495605469</v>
+        <v>92.73821258544922</v>
       </c>
       <c r="D135" t="n">
-        <v>92.74743460938542</v>
+        <v>92.74744223953927</v>
       </c>
       <c r="E135" t="n">
-        <v>92.73820495605469</v>
+        <v>92.73821258544922</v>
       </c>
       <c r="F135" t="n">
-        <v>92.74743460938542</v>
+        <v>92.74744223953927</v>
       </c>
       <c r="G135" t="n">
         <v>3615100</v>
@@ -3554,16 +3554,16 @@
         <v>45489</v>
       </c>
       <c r="C136" t="n">
-        <v>92.75664520263672</v>
+        <v>92.75666046142578</v>
       </c>
       <c r="D136" t="n">
-        <v>92.75664520263672</v>
+        <v>92.75666046142578</v>
       </c>
       <c r="E136" t="n">
-        <v>92.74742259066382</v>
+        <v>92.74743784793573</v>
       </c>
       <c r="F136" t="n">
-        <v>92.75664520263672</v>
+        <v>92.75666046142578</v>
       </c>
       <c r="G136" t="n">
         <v>3622900</v>
@@ -3577,16 +3577,16 @@
         <v>45490</v>
       </c>
       <c r="C137" t="n">
-        <v>92.76587677001953</v>
+        <v>92.76588439941406</v>
       </c>
       <c r="D137" t="n">
-        <v>92.77049511626313</v>
+        <v>92.77050274603751</v>
       </c>
       <c r="E137" t="n">
-        <v>92.75664711769426</v>
+        <v>92.75665474632972</v>
       </c>
       <c r="F137" t="n">
-        <v>92.76587677001953</v>
+        <v>92.76588439941406</v>
       </c>
       <c r="G137" t="n">
         <v>3822100</v>
@@ -3600,16 +3600,16 @@
         <v>45491</v>
       </c>
       <c r="C138" t="n">
-        <v>92.78433227539062</v>
+        <v>92.78433990478516</v>
       </c>
       <c r="D138" t="n">
-        <v>92.78433227539062</v>
+        <v>92.78433990478516</v>
       </c>
       <c r="E138" t="n">
-        <v>92.77510262344329</v>
+        <v>92.77511025207889</v>
       </c>
       <c r="F138" t="n">
-        <v>92.77510262344329</v>
+        <v>92.77511025207889</v>
       </c>
       <c r="G138" t="n">
         <v>5291400</v>
@@ -3623,16 +3623,16 @@
         <v>45492</v>
       </c>
       <c r="C139" t="n">
-        <v>92.82124328613281</v>
+        <v>92.82125091552734</v>
       </c>
       <c r="D139" t="n">
-        <v>92.82124328613281</v>
+        <v>92.82125091552734</v>
       </c>
       <c r="E139" t="n">
-        <v>92.81202067370296</v>
+        <v>92.81202830233946</v>
       </c>
       <c r="F139" t="n">
-        <v>92.82124328613281</v>
+        <v>92.82125091552734</v>
       </c>
       <c r="G139" t="n">
         <v>2993600</v>
@@ -3646,16 +3646,16 @@
         <v>45495</v>
       </c>
       <c r="C140" t="n">
-        <v>92.83969116210938</v>
+        <v>92.83970642089844</v>
       </c>
       <c r="D140" t="n">
-        <v>92.83969116210938</v>
+        <v>92.83970642089844</v>
       </c>
       <c r="E140" t="n">
-        <v>92.83046151065361</v>
+        <v>92.83047676792572</v>
       </c>
       <c r="F140" t="n">
-        <v>92.83969116210938</v>
+        <v>92.83970642089844</v>
       </c>
       <c r="G140" t="n">
         <v>3386500</v>
@@ -3669,16 +3669,16 @@
         <v>45496</v>
       </c>
       <c r="C141" t="n">
-        <v>92.84894561767578</v>
+        <v>92.84891510009766</v>
       </c>
       <c r="D141" t="n">
-        <v>92.85816823143402</v>
+        <v>92.85813771082462</v>
       </c>
       <c r="E141" t="n">
-        <v>92.83971596375436</v>
+        <v>92.83968544920984</v>
       </c>
       <c r="F141" t="n">
-        <v>92.84894561767578</v>
+        <v>92.84891510009766</v>
       </c>
       <c r="G141" t="n">
         <v>2829200</v>
@@ -3692,16 +3692,16 @@
         <v>45497</v>
       </c>
       <c r="C142" t="n">
-        <v>92.858154296875</v>
+        <v>92.85816955566406</v>
       </c>
       <c r="D142" t="n">
-        <v>92.86738394941139</v>
+        <v>92.86739920971711</v>
       </c>
       <c r="E142" t="n">
-        <v>92.84893168450073</v>
+        <v>92.8489469417743</v>
       </c>
       <c r="F142" t="n">
-        <v>92.858154296875</v>
+        <v>92.85816955566406</v>
       </c>
       <c r="G142" t="n">
         <v>3474500</v>
@@ -3738,16 +3738,16 @@
         <v>45499</v>
       </c>
       <c r="C144" t="n">
-        <v>92.90431213378906</v>
+        <v>92.90430450439453</v>
       </c>
       <c r="D144" t="n">
-        <v>92.91354178797603</v>
+        <v>92.91353415782355</v>
       </c>
       <c r="E144" t="n">
-        <v>92.90431213378906</v>
+        <v>92.90430450439453</v>
       </c>
       <c r="F144" t="n">
-        <v>92.90431213378906</v>
+        <v>92.90430450439453</v>
       </c>
       <c r="G144" t="n">
         <v>3172600</v>
@@ -3761,16 +3761,16 @@
         <v>45502</v>
       </c>
       <c r="C145" t="n">
-        <v>92.93199920654297</v>
+        <v>92.93199157714844</v>
       </c>
       <c r="D145" t="n">
-        <v>92.93199920654297</v>
+        <v>92.93199157714844</v>
       </c>
       <c r="E145" t="n">
-        <v>92.9227695518445</v>
+        <v>92.92276192320769</v>
       </c>
       <c r="F145" t="n">
-        <v>92.9227695518445</v>
+        <v>92.92276192320769</v>
       </c>
       <c r="G145" t="n">
         <v>3259000</v>
@@ -3784,16 +3784,16 @@
         <v>45503</v>
       </c>
       <c r="C146" t="n">
-        <v>92.93199920654297</v>
+        <v>92.93199157714844</v>
       </c>
       <c r="D146" t="n">
-        <v>92.94122886124144</v>
+        <v>92.94122123108919</v>
       </c>
       <c r="E146" t="n">
-        <v>92.93199920654297</v>
+        <v>92.93199157714844</v>
       </c>
       <c r="F146" t="n">
-        <v>92.94122886124144</v>
+        <v>92.94122123108919</v>
       </c>
       <c r="G146" t="n">
         <v>4559900</v>
@@ -3807,16 +3807,16 @@
         <v>45504</v>
       </c>
       <c r="C147" t="n">
-        <v>92.94123077392578</v>
+        <v>92.94121551513672</v>
       </c>
       <c r="D147" t="n">
-        <v>92.9504604288142</v>
+        <v>92.95044516850984</v>
       </c>
       <c r="E147" t="n">
-        <v>92.94123077392578</v>
+        <v>92.94121551513672</v>
       </c>
       <c r="F147" t="n">
-        <v>92.94123077392578</v>
+        <v>92.94121551513672</v>
       </c>
       <c r="G147" t="n">
         <v>7256900</v>
@@ -3830,16 +3830,16 @@
         <v>45505</v>
       </c>
       <c r="C148" t="n">
-        <v>92.9718017578125</v>
+        <v>92.97179412841797</v>
       </c>
       <c r="D148" t="n">
-        <v>92.9718017578125</v>
+        <v>92.97179412841797</v>
       </c>
       <c r="E148" t="n">
-        <v>92.9625304058835</v>
+        <v>92.96252277724977</v>
       </c>
       <c r="F148" t="n">
-        <v>92.9718017578125</v>
+        <v>92.97179412841797</v>
       </c>
       <c r="G148" t="n">
         <v>11015600</v>
@@ -3853,16 +3853,16 @@
         <v>45506</v>
       </c>
       <c r="C149" t="n">
-        <v>93.01814270019531</v>
+        <v>93.01816558837891</v>
       </c>
       <c r="D149" t="n">
-        <v>93.01814270019531</v>
+        <v>93.01816558837891</v>
       </c>
       <c r="E149" t="n">
-        <v>92.99960706864016</v>
+        <v>92.99962995226285</v>
       </c>
       <c r="F149" t="n">
-        <v>93.00887134843308</v>
+        <v>93.00889423433536</v>
       </c>
       <c r="G149" t="n">
         <v>7927400</v>
@@ -3899,16 +3899,16 @@
         <v>45510</v>
       </c>
       <c r="C151" t="n">
-        <v>93.04595184326172</v>
+        <v>93.04596710205078</v>
       </c>
       <c r="D151" t="n">
-        <v>93.04595184326172</v>
+        <v>93.04596710205078</v>
       </c>
       <c r="E151" t="n">
-        <v>93.02741621127633</v>
+        <v>93.02743146702569</v>
       </c>
       <c r="F151" t="n">
-        <v>93.02741621127633</v>
+        <v>93.02743146702569</v>
       </c>
       <c r="G151" t="n">
         <v>5059100</v>
@@ -3922,16 +3922,16 @@
         <v>45511</v>
       </c>
       <c r="C152" t="n">
-        <v>93.04595184326172</v>
+        <v>93.04596710205078</v>
       </c>
       <c r="D152" t="n">
-        <v>93.05522319523915</v>
+        <v>93.05523845554865</v>
       </c>
       <c r="E152" t="n">
-        <v>93.04595184326172</v>
+        <v>93.04596710205078</v>
       </c>
       <c r="F152" t="n">
-        <v>93.04595184326172</v>
+        <v>93.04596710205078</v>
       </c>
       <c r="G152" t="n">
         <v>4611400</v>
@@ -3945,16 +3945,16 @@
         <v>45512</v>
       </c>
       <c r="C153" t="n">
-        <v>93.07376861572266</v>
+        <v>93.07376098632812</v>
       </c>
       <c r="D153" t="n">
-        <v>93.07376861572266</v>
+        <v>93.07376098632812</v>
       </c>
       <c r="E153" t="n">
-        <v>93.05522591122659</v>
+        <v>93.05521828335203</v>
       </c>
       <c r="F153" t="n">
-        <v>93.06449726347462</v>
+        <v>93.06448963484009</v>
       </c>
       <c r="G153" t="n">
         <v>3903300</v>
@@ -3968,16 +3968,16 @@
         <v>45513</v>
       </c>
       <c r="C154" t="n">
-        <v>93.1015625</v>
+        <v>93.10157775878906</v>
       </c>
       <c r="D154" t="n">
-        <v>93.11082677897475</v>
+        <v>93.11084203928218</v>
       </c>
       <c r="E154" t="n">
-        <v>93.09229114905655</v>
+        <v>93.0923064063261</v>
       </c>
       <c r="F154" t="n">
-        <v>93.1015625</v>
+        <v>93.10157775878906</v>
       </c>
       <c r="G154" t="n">
         <v>5548300</v>
@@ -3991,16 +3991,16 @@
         <v>45516</v>
       </c>
       <c r="C155" t="n">
-        <v>93.12010192871094</v>
+        <v>93.1201171875</v>
       </c>
       <c r="D155" t="n">
-        <v>93.1293732800326</v>
+        <v>93.12938854034087</v>
       </c>
       <c r="E155" t="n">
-        <v>93.11083057738928</v>
+        <v>93.11084583465912</v>
       </c>
       <c r="F155" t="n">
-        <v>93.12010192871094</v>
+        <v>93.1201171875</v>
       </c>
       <c r="G155" t="n">
         <v>3845400</v>
@@ -4014,16 +4014,16 @@
         <v>45517</v>
       </c>
       <c r="C156" t="n">
-        <v>93.13864898681641</v>
+        <v>93.13866424560547</v>
       </c>
       <c r="D156" t="n">
-        <v>93.13864898681641</v>
+        <v>93.13866424560547</v>
       </c>
       <c r="E156" t="n">
-        <v>93.12937763506119</v>
+        <v>93.12939289233132</v>
       </c>
       <c r="F156" t="n">
-        <v>93.13864898681641</v>
+        <v>93.13866424560547</v>
       </c>
       <c r="G156" t="n">
         <v>4782200</v>
@@ -4037,16 +4037,16 @@
         <v>45518</v>
       </c>
       <c r="C157" t="n">
-        <v>93.15720367431641</v>
+        <v>93.15719604492188</v>
       </c>
       <c r="D157" t="n">
-        <v>93.15720367431641</v>
+        <v>93.15719604492188</v>
       </c>
       <c r="E157" t="n">
-        <v>93.13866803898368</v>
+        <v>93.13866041110718</v>
       </c>
       <c r="F157" t="n">
-        <v>93.14793232066467</v>
+        <v>93.14792469202943</v>
       </c>
       <c r="G157" t="n">
         <v>4327700</v>
@@ -4083,16 +4083,16 @@
         <v>45520</v>
       </c>
       <c r="C159" t="n">
-        <v>93.20355224609375</v>
+        <v>93.20353698730469</v>
       </c>
       <c r="D159" t="n">
-        <v>93.20355224609375</v>
+        <v>93.20353698730469</v>
       </c>
       <c r="E159" t="n">
-        <v>93.19428089255386</v>
+        <v>93.19426563528266</v>
       </c>
       <c r="F159" t="n">
-        <v>93.20355224609375</v>
+        <v>93.20353698730469</v>
       </c>
       <c r="G159" t="n">
         <v>3638900</v>
@@ -4106,16 +4106,16 @@
         <v>45523</v>
       </c>
       <c r="C160" t="n">
-        <v>93.21279907226562</v>
+        <v>93.21281433105469</v>
       </c>
       <c r="D160" t="n">
-        <v>93.22207042406932</v>
+        <v>93.22208568437608</v>
       </c>
       <c r="E160" t="n">
-        <v>93.21279907226562</v>
+        <v>93.21281433105469</v>
       </c>
       <c r="F160" t="n">
-        <v>93.21279907226562</v>
+        <v>93.21281433105469</v>
       </c>
       <c r="G160" t="n">
         <v>3930700</v>
@@ -4129,16 +4129,16 @@
         <v>45524</v>
       </c>
       <c r="C161" t="n">
-        <v>93.22208404541016</v>
+        <v>93.22207641601562</v>
       </c>
       <c r="D161" t="n">
-        <v>93.23135539856855</v>
+        <v>93.23134776841523</v>
       </c>
       <c r="E161" t="n">
-        <v>93.22208404541016</v>
+        <v>93.22207641601562</v>
       </c>
       <c r="F161" t="n">
-        <v>93.23135539856855</v>
+        <v>93.23134776841523</v>
       </c>
       <c r="G161" t="n">
         <v>3084200</v>
@@ -4221,16 +4221,16 @@
         <v>45530</v>
       </c>
       <c r="C165" t="n">
-        <v>93.30549621582031</v>
+        <v>93.30550384521484</v>
       </c>
       <c r="D165" t="n">
-        <v>93.31476049543321</v>
+        <v>93.31476812558525</v>
       </c>
       <c r="E165" t="n">
-        <v>93.30549621582031</v>
+        <v>93.30550384521484</v>
       </c>
       <c r="F165" t="n">
-        <v>93.30549621582031</v>
+        <v>93.30550384521484</v>
       </c>
       <c r="G165" t="n">
         <v>3969000</v>
@@ -4244,16 +4244,16 @@
         <v>45531</v>
       </c>
       <c r="C166" t="n">
-        <v>93.31478118896484</v>
+        <v>93.31475067138672</v>
       </c>
       <c r="D166" t="n">
-        <v>93.32405254260293</v>
+        <v>93.3240220219927</v>
       </c>
       <c r="E166" t="n">
-        <v>93.31478118896484</v>
+        <v>93.31475067138672</v>
       </c>
       <c r="F166" t="n">
-        <v>93.32405254260293</v>
+        <v>93.3240220219927</v>
       </c>
       <c r="G166" t="n">
         <v>2818100</v>
@@ -4290,16 +4290,16 @@
         <v>45533</v>
       </c>
       <c r="C168" t="n">
-        <v>93.33330535888672</v>
+        <v>93.33331298828125</v>
       </c>
       <c r="D168" t="n">
-        <v>93.35184099051068</v>
+        <v>93.35184862142037</v>
       </c>
       <c r="E168" t="n">
-        <v>93.33330535888672</v>
+        <v>93.33331298828125</v>
       </c>
       <c r="F168" t="n">
-        <v>93.34256963871402</v>
+        <v>93.34257726886585</v>
       </c>
       <c r="G168" t="n">
         <v>4537700</v>
@@ -4313,16 +4313,16 @@
         <v>45534</v>
       </c>
       <c r="C169" t="n">
-        <v>93.37966156005859</v>
+        <v>93.37964630126953</v>
       </c>
       <c r="D169" t="n">
-        <v>93.38893291320416</v>
+        <v>93.3889176529001</v>
       </c>
       <c r="E169" t="n">
-        <v>93.37966156005859</v>
+        <v>93.37964630126953</v>
       </c>
       <c r="F169" t="n">
-        <v>93.37966156005859</v>
+        <v>93.37964630126953</v>
       </c>
       <c r="G169" t="n">
         <v>8427400</v>
@@ -4359,16 +4359,16 @@
         <v>45539</v>
       </c>
       <c r="C171" t="n">
-        <v>93.42992401123047</v>
+        <v>93.429931640625</v>
       </c>
       <c r="D171" t="n">
-        <v>93.43923640626956</v>
+        <v>93.43924403642453</v>
       </c>
       <c r="E171" t="n">
-        <v>93.42992401123047</v>
+        <v>93.429931640625</v>
       </c>
       <c r="F171" t="n">
-        <v>93.43923640626956</v>
+        <v>93.43924403642453</v>
       </c>
       <c r="G171" t="n">
         <v>7218300</v>
@@ -4382,16 +4382,16 @@
         <v>45540</v>
       </c>
       <c r="C172" t="n">
-        <v>93.45786285400391</v>
+        <v>93.45787811279297</v>
       </c>
       <c r="D172" t="n">
-        <v>93.45786285400391</v>
+        <v>93.45787811279297</v>
       </c>
       <c r="E172" t="n">
-        <v>93.43924516545663</v>
+        <v>93.439260421206</v>
       </c>
       <c r="F172" t="n">
-        <v>93.44855756136867</v>
+        <v>93.44857281863847</v>
       </c>
       <c r="G172" t="n">
         <v>4833300</v>
@@ -4405,16 +4405,16 @@
         <v>45541</v>
       </c>
       <c r="C173" t="n">
-        <v>93.49510192871094</v>
+        <v>93.49509429931641</v>
       </c>
       <c r="D173" t="n">
-        <v>93.49510192871094</v>
+        <v>93.49509429931641</v>
       </c>
       <c r="E173" t="n">
-        <v>93.48579663641466</v>
+        <v>93.48578900777946</v>
       </c>
       <c r="F173" t="n">
-        <v>93.49510192871094</v>
+        <v>93.49509429931641</v>
       </c>
       <c r="G173" t="n">
         <v>5534600</v>
@@ -4428,16 +4428,16 @@
         <v>45544</v>
       </c>
       <c r="C174" t="n">
-        <v>93.50443267822266</v>
+        <v>93.50442504882812</v>
       </c>
       <c r="D174" t="n">
-        <v>93.51374507562342</v>
+        <v>93.51373744546905</v>
       </c>
       <c r="E174" t="n">
-        <v>93.50443267822266</v>
+        <v>93.50442504882812</v>
       </c>
       <c r="F174" t="n">
-        <v>93.50443267822266</v>
+        <v>93.50442504882812</v>
       </c>
       <c r="G174" t="n">
         <v>5397400</v>
@@ -4451,16 +4451,16 @@
         <v>45545</v>
       </c>
       <c r="C175" t="n">
-        <v>93.52303314208984</v>
+        <v>93.52304840087891</v>
       </c>
       <c r="D175" t="n">
-        <v>93.52303314208984</v>
+        <v>93.52304840087891</v>
       </c>
       <c r="E175" t="n">
-        <v>93.50441545399579</v>
+        <v>93.5044307097473</v>
       </c>
       <c r="F175" t="n">
-        <v>93.52303314208984</v>
+        <v>93.52304840087891</v>
       </c>
       <c r="G175" t="n">
         <v>4143900</v>
@@ -4474,16 +4474,16 @@
         <v>45546</v>
       </c>
       <c r="C176" t="n">
-        <v>93.52303314208984</v>
+        <v>93.52304840087891</v>
       </c>
       <c r="D176" t="n">
-        <v>93.53234553777519</v>
+        <v>93.53236079808363</v>
       </c>
       <c r="E176" t="n">
-        <v>93.52303314208984</v>
+        <v>93.52304840087891</v>
       </c>
       <c r="F176" t="n">
-        <v>93.52303314208984</v>
+        <v>93.52304840087891</v>
       </c>
       <c r="G176" t="n">
         <v>4500100</v>
@@ -4497,16 +4497,16 @@
         <v>45547</v>
       </c>
       <c r="C177" t="n">
-        <v>93.53234100341797</v>
+        <v>93.5323486328125</v>
       </c>
       <c r="D177" t="n">
-        <v>93.54165339865186</v>
+        <v>93.541661028806</v>
       </c>
       <c r="E177" t="n">
-        <v>93.53234100341797</v>
+        <v>93.5323486328125</v>
       </c>
       <c r="F177" t="n">
-        <v>93.54165339865186</v>
+        <v>93.541661028806</v>
       </c>
       <c r="G177" t="n">
         <v>3912400</v>
@@ -4520,16 +4520,16 @@
         <v>45548</v>
       </c>
       <c r="C178" t="n">
-        <v>93.58818817138672</v>
+        <v>93.58821105957031</v>
       </c>
       <c r="D178" t="n">
-        <v>93.58818817138672</v>
+        <v>93.58821105957031</v>
       </c>
       <c r="E178" t="n">
-        <v>93.56957048678073</v>
+        <v>93.56959337041114</v>
       </c>
       <c r="F178" t="n">
-        <v>93.56957048678073</v>
+        <v>93.56959337041114</v>
       </c>
       <c r="G178" t="n">
         <v>3465200</v>
@@ -4543,16 +4543,16 @@
         <v>45551</v>
       </c>
       <c r="C179" t="n">
-        <v>93.60684204101562</v>
+        <v>93.60682678222656</v>
       </c>
       <c r="D179" t="n">
-        <v>93.60684204101562</v>
+        <v>93.60682678222656</v>
       </c>
       <c r="E179" t="n">
-        <v>93.58821724734798</v>
+        <v>93.58820199159494</v>
       </c>
       <c r="F179" t="n">
-        <v>93.58821724734798</v>
+        <v>93.58820199159494</v>
       </c>
       <c r="G179" t="n">
         <v>3571100</v>
@@ -4566,16 +4566,16 @@
         <v>45552</v>
       </c>
       <c r="C180" t="n">
-        <v>93.60684204101562</v>
+        <v>93.60682678222656</v>
       </c>
       <c r="D180" t="n">
-        <v>93.62545973140574</v>
+        <v>93.62544446958184</v>
       </c>
       <c r="E180" t="n">
-        <v>93.60684204101562</v>
+        <v>93.60682678222656</v>
       </c>
       <c r="F180" t="n">
-        <v>93.61615443784945</v>
+        <v>93.61613917754238</v>
       </c>
       <c r="G180" t="n">
         <v>4452200</v>
@@ -4589,16 +4589,16 @@
         <v>45553</v>
       </c>
       <c r="C181" t="n">
-        <v>93.634765625</v>
+        <v>93.63474273681641</v>
       </c>
       <c r="D181" t="n">
-        <v>93.64407802118704</v>
+        <v>93.64405513072712</v>
       </c>
       <c r="E181" t="n">
-        <v>93.62545322881296</v>
+        <v>93.6254303429057</v>
       </c>
       <c r="F181" t="n">
-        <v>93.62545322881296</v>
+        <v>93.6254303429057</v>
       </c>
       <c r="G181" t="n">
         <v>4077700</v>
@@ -4612,16 +4612,16 @@
         <v>45554</v>
       </c>
       <c r="C182" t="n">
-        <v>93.65338134765625</v>
+        <v>93.65336608886719</v>
       </c>
       <c r="D182" t="n">
-        <v>93.66269374364776</v>
+        <v>93.66267848334145</v>
       </c>
       <c r="E182" t="n">
-        <v>93.64407605494162</v>
+        <v>93.64406079766864</v>
       </c>
       <c r="F182" t="n">
-        <v>93.64407605494162</v>
+        <v>93.64406079766864</v>
       </c>
       <c r="G182" t="n">
         <v>5165800</v>
@@ -4635,16 +4635,16 @@
         <v>45555</v>
       </c>
       <c r="C183" t="n">
-        <v>93.69062805175781</v>
+        <v>93.69062042236328</v>
       </c>
       <c r="D183" t="n">
-        <v>93.69994044816912</v>
+        <v>93.69993281801626</v>
       </c>
       <c r="E183" t="n">
-        <v>93.69062805175781</v>
+        <v>93.69062042236328</v>
       </c>
       <c r="F183" t="n">
-        <v>93.69994044816912</v>
+        <v>93.69993281801626</v>
       </c>
       <c r="G183" t="n">
         <v>4244800</v>
@@ -4658,16 +4658,16 @@
         <v>45558</v>
       </c>
       <c r="C184" t="n">
-        <v>93.71855926513672</v>
+        <v>93.71858215332031</v>
       </c>
       <c r="D184" t="n">
-        <v>93.71855926513672</v>
+        <v>93.71858215332031</v>
       </c>
       <c r="E184" t="n">
-        <v>93.6999344735017</v>
+        <v>93.69995735713671</v>
       </c>
       <c r="F184" t="n">
-        <v>93.70924686931922</v>
+        <v>93.7092697552285</v>
       </c>
       <c r="G184" t="n">
         <v>5220900</v>
@@ -4681,16 +4681,16 @@
         <v>45559</v>
       </c>
       <c r="C185" t="n">
-        <v>93.72787475585938</v>
+        <v>93.72786712646484</v>
       </c>
       <c r="D185" t="n">
-        <v>93.72787475585938</v>
+        <v>93.72786712646484</v>
       </c>
       <c r="E185" t="n">
-        <v>93.71856946230614</v>
+        <v>93.71856183366906</v>
       </c>
       <c r="F185" t="n">
-        <v>93.71856946230614</v>
+        <v>93.71856183366906</v>
       </c>
       <c r="G185" t="n">
         <v>3923500</v>
@@ -4704,16 +4704,16 @@
         <v>45560</v>
       </c>
       <c r="C186" t="n">
-        <v>93.72787475585938</v>
+        <v>93.72786712646484</v>
       </c>
       <c r="D186" t="n">
-        <v>93.74649954952088</v>
+        <v>93.7464919186103</v>
       </c>
       <c r="E186" t="n">
-        <v>93.72787475585938</v>
+        <v>93.72786712646484</v>
       </c>
       <c r="F186" t="n">
-        <v>93.73718715269013</v>
+        <v>93.73717952253757</v>
       </c>
       <c r="G186" t="n">
         <v>3372400</v>
@@ -4727,16 +4727,16 @@
         <v>45561</v>
       </c>
       <c r="C187" t="n">
-        <v>93.73719024658203</v>
+        <v>93.7371826171875</v>
       </c>
       <c r="D187" t="n">
-        <v>93.74650264372015</v>
+        <v>93.74649501356767</v>
       </c>
       <c r="E187" t="n">
-        <v>93.73719024658203</v>
+        <v>93.7371826171875</v>
       </c>
       <c r="F187" t="n">
-        <v>93.73719024658203</v>
+        <v>93.7371826171875</v>
       </c>
       <c r="G187" t="n">
         <v>4364400</v>
@@ -4750,16 +4750,16 @@
         <v>45562</v>
       </c>
       <c r="C188" t="n">
-        <v>93.77442932128906</v>
+        <v>93.7744140625</v>
       </c>
       <c r="D188" t="n">
-        <v>93.78374171808849</v>
+        <v>93.78372645778413</v>
       </c>
       <c r="E188" t="n">
-        <v>93.77442932128906</v>
+        <v>93.7744140625</v>
       </c>
       <c r="F188" t="n">
-        <v>93.77442932128906</v>
+        <v>93.7744140625</v>
       </c>
       <c r="G188" t="n">
         <v>4945400</v>
@@ -4773,16 +4773,16 @@
         <v>45565</v>
       </c>
       <c r="C189" t="n">
-        <v>93.77442932128906</v>
+        <v>93.7744140625</v>
       </c>
       <c r="D189" t="n">
-        <v>93.79304701161043</v>
+        <v>93.79303174979192</v>
       </c>
       <c r="E189" t="n">
-        <v>93.77442932128906</v>
+        <v>93.7744140625</v>
       </c>
       <c r="F189" t="n">
-        <v>93.78374171808849</v>
+        <v>93.78372645778413</v>
       </c>
       <c r="G189" t="n">
         <v>9253100</v>
@@ -4796,16 +4796,16 @@
         <v>45566</v>
       </c>
       <c r="C190" t="n">
-        <v>93.81182861328125</v>
+        <v>93.81181335449219</v>
       </c>
       <c r="D190" t="n">
-        <v>93.81182861328125</v>
+        <v>93.81181335449219</v>
       </c>
       <c r="E190" t="n">
-        <v>93.80247628922369</v>
+        <v>93.80246103195581</v>
       </c>
       <c r="F190" t="n">
-        <v>93.81182861328125</v>
+        <v>93.81181335449219</v>
       </c>
       <c r="G190" t="n">
         <v>11569200</v>
@@ -4819,16 +4819,16 @@
         <v>45567</v>
       </c>
       <c r="C191" t="n">
-        <v>93.81182861328125</v>
+        <v>93.81181335449219</v>
       </c>
       <c r="D191" t="n">
-        <v>93.82117380360573</v>
+        <v>93.82115854329665</v>
       </c>
       <c r="E191" t="n">
-        <v>93.81182861328125</v>
+        <v>93.81181335449219</v>
       </c>
       <c r="F191" t="n">
-        <v>93.82117380360573</v>
+        <v>93.82115854329665</v>
       </c>
       <c r="G191" t="n">
         <v>5170300</v>
@@ -4842,16 +4842,16 @@
         <v>45568</v>
       </c>
       <c r="C192" t="n">
-        <v>93.82115173339844</v>
+        <v>93.82115936279297</v>
       </c>
       <c r="D192" t="n">
-        <v>93.83050405525599</v>
+        <v>93.83051168541103</v>
       </c>
       <c r="E192" t="n">
-        <v>93.82115173339844</v>
+        <v>93.82115936279297</v>
       </c>
       <c r="F192" t="n">
-        <v>93.83050405525599</v>
+        <v>93.83051168541103</v>
       </c>
       <c r="G192" t="n">
         <v>4066100</v>
@@ -4865,16 +4865,16 @@
         <v>45569</v>
       </c>
       <c r="C193" t="n">
-        <v>93.85858917236328</v>
+        <v>93.85858154296875</v>
       </c>
       <c r="D193" t="n">
-        <v>93.86794149773675</v>
+        <v>93.86793386758201</v>
       </c>
       <c r="E193" t="n">
-        <v>93.85858917236328</v>
+        <v>93.85858154296875</v>
       </c>
       <c r="F193" t="n">
-        <v>93.86326890191705</v>
+        <v>93.86326127214213</v>
       </c>
       <c r="G193" t="n">
         <v>4987100</v>
@@ -4888,16 +4888,16 @@
         <v>45572</v>
       </c>
       <c r="C194" t="n">
-        <v>93.86790466308594</v>
+        <v>93.86793518066406</v>
       </c>
       <c r="D194" t="n">
-        <v>93.87725698478947</v>
+        <v>93.87728750540813</v>
       </c>
       <c r="E194" t="n">
-        <v>93.86790466308594</v>
+        <v>93.86793518066406</v>
       </c>
       <c r="F194" t="n">
-        <v>93.86790466308594</v>
+        <v>93.86793518066406</v>
       </c>
       <c r="G194" t="n">
         <v>4792500</v>
@@ -4934,16 +4934,16 @@
         <v>45574</v>
       </c>
       <c r="C196" t="n">
-        <v>93.89595794677734</v>
+        <v>93.89596557617188</v>
       </c>
       <c r="D196" t="n">
-        <v>93.90531026882472</v>
+        <v>93.90531789897918</v>
       </c>
       <c r="E196" t="n">
-        <v>93.8866127584615</v>
+        <v>93.8866203870967</v>
       </c>
       <c r="F196" t="n">
-        <v>93.89595794677734</v>
+        <v>93.89596557617188</v>
       </c>
       <c r="G196" t="n">
         <v>4024800</v>
@@ -4957,16 +4957,16 @@
         <v>45575</v>
       </c>
       <c r="C197" t="n">
-        <v>93.91468048095703</v>
+        <v>93.91468811035156</v>
       </c>
       <c r="D197" t="n">
-        <v>93.91468048095703</v>
+        <v>93.91468811035156</v>
       </c>
       <c r="E197" t="n">
-        <v>93.9053281571281</v>
+        <v>93.90533578576286</v>
       </c>
       <c r="F197" t="n">
-        <v>93.91468048095703</v>
+        <v>93.91468811035156</v>
       </c>
       <c r="G197" t="n">
         <v>3731100</v>
@@ -5049,16 +5049,16 @@
         <v>45581</v>
       </c>
       <c r="C201" t="n">
-        <v>93.98947143554688</v>
+        <v>93.98947906494141</v>
       </c>
       <c r="D201" t="n">
-        <v>93.98947143554688</v>
+        <v>93.98947906494141</v>
       </c>
       <c r="E201" t="n">
-        <v>93.98012624607075</v>
+        <v>93.98013387470671</v>
       </c>
       <c r="F201" t="n">
-        <v>93.98012624607075</v>
+        <v>93.98013387470671</v>
       </c>
       <c r="G201" t="n">
         <v>3809900</v>
@@ -5072,16 +5072,16 @@
         <v>45582</v>
       </c>
       <c r="C202" t="n">
-        <v>93.98947143554688</v>
+        <v>93.98947906494141</v>
       </c>
       <c r="D202" t="n">
-        <v>93.99882375875542</v>
+        <v>93.99883138890911</v>
       </c>
       <c r="E202" t="n">
-        <v>93.98947143554688</v>
+        <v>93.98947906494141</v>
       </c>
       <c r="F202" t="n">
-        <v>93.98947143554688</v>
+        <v>93.98947906494141</v>
       </c>
       <c r="G202" t="n">
         <v>3575500</v>
@@ -5095,16 +5095,16 @@
         <v>45583</v>
       </c>
       <c r="C203" t="n">
-        <v>94.02685546875</v>
+        <v>94.02689361572266</v>
       </c>
       <c r="D203" t="n">
-        <v>94.03620779015567</v>
+        <v>94.03624594092258</v>
       </c>
       <c r="E203" t="n">
-        <v>94.01751028107537</v>
+        <v>94.01754842425666</v>
       </c>
       <c r="F203" t="n">
-        <v>94.03620779015567</v>
+        <v>94.03624594092258</v>
       </c>
       <c r="G203" t="n">
         <v>3970200</v>
@@ -5118,16 +5118,16 @@
         <v>45586</v>
       </c>
       <c r="C204" t="n">
-        <v>94.04556274414062</v>
+        <v>94.04557800292969</v>
       </c>
       <c r="D204" t="n">
-        <v>94.04556274414062</v>
+        <v>94.04557800292969</v>
       </c>
       <c r="E204" t="n">
-        <v>94.03621042247316</v>
+        <v>94.03622567974483</v>
       </c>
       <c r="F204" t="n">
-        <v>94.03621042247316</v>
+        <v>94.03622567974483</v>
       </c>
       <c r="G204" t="n">
         <v>3940600</v>
@@ -5141,16 +5141,16 @@
         <v>45587</v>
       </c>
       <c r="C205" t="n">
-        <v>94.05492401123047</v>
+        <v>94.05490875244141</v>
       </c>
       <c r="D205" t="n">
-        <v>94.05492401123047</v>
+        <v>94.05490875244141</v>
       </c>
       <c r="E205" t="n">
-        <v>94.04557882169665</v>
+        <v>94.04556356442367</v>
       </c>
       <c r="F205" t="n">
-        <v>94.05492401123047</v>
+        <v>94.05490875244141</v>
       </c>
       <c r="G205" t="n">
         <v>3462800</v>
@@ -5164,16 +5164,16 @@
         <v>45588</v>
       </c>
       <c r="C206" t="n">
-        <v>94.05492401123047</v>
+        <v>94.05490875244141</v>
       </c>
       <c r="D206" t="n">
-        <v>94.07362865776304</v>
+        <v>94.07361339593947</v>
       </c>
       <c r="E206" t="n">
-        <v>94.05492401123047</v>
+        <v>94.05490875244141</v>
       </c>
       <c r="F206" t="n">
-        <v>94.07362865776304</v>
+        <v>94.07361339593947</v>
       </c>
       <c r="G206" t="n">
         <v>3927700</v>
@@ -5187,16 +5187,16 @@
         <v>45589</v>
       </c>
       <c r="C207" t="n">
-        <v>94.08298492431641</v>
+        <v>94.08297729492188</v>
       </c>
       <c r="D207" t="n">
-        <v>94.08298492431641</v>
+        <v>94.08297729492188</v>
       </c>
       <c r="E207" t="n">
-        <v>94.07363260065813</v>
+        <v>94.073624972022</v>
       </c>
       <c r="F207" t="n">
-        <v>94.08298492431641</v>
+        <v>94.08297729492188</v>
       </c>
       <c r="G207" t="n">
         <v>3704500</v>
@@ -5210,16 +5210,16 @@
         <v>45590</v>
       </c>
       <c r="C208" t="n">
-        <v>94.12039184570312</v>
+        <v>94.12038421630859</v>
       </c>
       <c r="D208" t="n">
-        <v>94.12039184570312</v>
+        <v>94.12038421630859</v>
       </c>
       <c r="E208" t="n">
-        <v>94.11103952157183</v>
+        <v>94.11103189293539</v>
       </c>
       <c r="F208" t="n">
-        <v>94.11103952157183</v>
+        <v>94.11103189293539</v>
       </c>
       <c r="G208" t="n">
         <v>5386900</v>
@@ -5233,16 +5233,16 @@
         <v>45593</v>
       </c>
       <c r="C209" t="n">
-        <v>94.12039184570312</v>
+        <v>94.12038421630859</v>
       </c>
       <c r="D209" t="n">
-        <v>94.12973703610129</v>
+        <v>94.12972940594925</v>
       </c>
       <c r="E209" t="n">
-        <v>94.12039184570312</v>
+        <v>94.12038421630859</v>
       </c>
       <c r="F209" t="n">
-        <v>94.12973703610129</v>
+        <v>94.12972940594925</v>
       </c>
       <c r="G209" t="n">
         <v>3471300</v>
@@ -5256,16 +5256,16 @@
         <v>45594</v>
       </c>
       <c r="C210" t="n">
-        <v>94.13909149169922</v>
+        <v>94.13908386230469</v>
       </c>
       <c r="D210" t="n">
-        <v>94.13909149169922</v>
+        <v>94.13908386230469</v>
       </c>
       <c r="E210" t="n">
-        <v>94.1250665720513</v>
+        <v>94.12505894379339</v>
       </c>
       <c r="F210" t="n">
-        <v>94.12973916735616</v>
+        <v>94.12973153871958</v>
       </c>
       <c r="G210" t="n">
         <v>3449900</v>
@@ -5279,16 +5279,16 @@
         <v>45595</v>
       </c>
       <c r="C211" t="n">
-        <v>94.13909149169922</v>
+        <v>94.13908386230469</v>
       </c>
       <c r="D211" t="n">
-        <v>94.15778900665204</v>
+        <v>94.15778137574219</v>
       </c>
       <c r="E211" t="n">
-        <v>94.13909149169922</v>
+        <v>94.13908386230469</v>
       </c>
       <c r="F211" t="n">
-        <v>94.14844381604227</v>
+        <v>94.14843618588979</v>
       </c>
       <c r="G211" t="n">
         <v>7059200</v>
@@ -5302,16 +5302,16 @@
         <v>45596</v>
       </c>
       <c r="C212" t="n">
-        <v>94.15777587890625</v>
+        <v>94.15778350830078</v>
       </c>
       <c r="D212" t="n">
-        <v>94.16712820194537</v>
+        <v>94.16713583209771</v>
       </c>
       <c r="E212" t="n">
-        <v>94.14843068959942</v>
+        <v>94.14843831823674</v>
       </c>
       <c r="F212" t="n">
-        <v>94.14843068959942</v>
+        <v>94.14843831823674</v>
       </c>
       <c r="G212" t="n">
         <v>11321100</v>
@@ -5325,16 +5325,16 @@
         <v>45597</v>
       </c>
       <c r="C213" t="n">
-        <v>94.20940399169922</v>
+        <v>94.20941162109375</v>
       </c>
       <c r="D213" t="n">
-        <v>94.20940399169922</v>
+        <v>94.20941162109375</v>
       </c>
       <c r="E213" t="n">
-        <v>94.20002013115936</v>
+        <v>94.20002775979395</v>
       </c>
       <c r="F213" t="n">
-        <v>94.20940399169922</v>
+        <v>94.20941162109375</v>
       </c>
       <c r="G213" t="n">
         <v>13451800</v>
@@ -5348,16 +5348,16 @@
         <v>45600</v>
       </c>
       <c r="C214" t="n">
-        <v>94.21878814697266</v>
+        <v>94.21880340576172</v>
       </c>
       <c r="D214" t="n">
-        <v>94.22724078409466</v>
+        <v>94.22725604425263</v>
       </c>
       <c r="E214" t="n">
-        <v>94.20939712386507</v>
+        <v>94.20941238113326</v>
       </c>
       <c r="F214" t="n">
-        <v>94.21878814697266</v>
+        <v>94.21880340576172</v>
       </c>
       <c r="G214" t="n">
         <v>5041500</v>
@@ -5440,16 +5440,16 @@
         <v>45604</v>
       </c>
       <c r="C218" t="n">
-        <v>94.30331420898438</v>
+        <v>94.30332183837891</v>
       </c>
       <c r="D218" t="n">
-        <v>94.30331420898438</v>
+        <v>94.30332183837891</v>
       </c>
       <c r="E218" t="n">
-        <v>94.28453215855077</v>
+        <v>94.28453978642578</v>
       </c>
       <c r="F218" t="n">
-        <v>94.29392318376757</v>
+        <v>94.29393081240234</v>
       </c>
       <c r="G218" t="n">
         <v>5624200</v>
@@ -5463,16 +5463,16 @@
         <v>45607</v>
       </c>
       <c r="C219" t="n">
-        <v>94.29390716552734</v>
+        <v>94.29392242431641</v>
       </c>
       <c r="D219" t="n">
-        <v>94.30329818914883</v>
+        <v>94.30331344945758</v>
       </c>
       <c r="E219" t="n">
-        <v>94.28921523534268</v>
+        <v>94.2892304933725</v>
       </c>
       <c r="F219" t="n">
-        <v>94.29390716552734</v>
+        <v>94.29392242431641</v>
       </c>
       <c r="G219" t="n">
         <v>4443700</v>
@@ -5486,16 +5486,16 @@
         <v>45608</v>
       </c>
       <c r="C220" t="n">
-        <v>94.30331420898438</v>
+        <v>94.30332183837891</v>
       </c>
       <c r="D220" t="n">
-        <v>94.31269807094777</v>
+        <v>94.31270570110148</v>
       </c>
       <c r="E220" t="n">
-        <v>94.30331420898438</v>
+        <v>94.30332183837891</v>
       </c>
       <c r="F220" t="n">
-        <v>94.31269807094777</v>
+        <v>94.31270570110148</v>
       </c>
       <c r="G220" t="n">
         <v>4283300</v>
@@ -5509,16 +5509,16 @@
         <v>45609</v>
       </c>
       <c r="C221" t="n">
-        <v>94.33148956298828</v>
+        <v>94.33145904541016</v>
       </c>
       <c r="D221" t="n">
-        <v>94.33148956298828</v>
+        <v>94.33145904541016</v>
       </c>
       <c r="E221" t="n">
-        <v>94.31270751067478</v>
+        <v>94.31267699917292</v>
       </c>
       <c r="F221" t="n">
-        <v>94.32209853683153</v>
+        <v>94.32206802229155</v>
       </c>
       <c r="G221" t="n">
         <v>4818000</v>
@@ -5532,16 +5532,16 @@
         <v>45610</v>
       </c>
       <c r="C222" t="n">
-        <v>94.33148956298828</v>
+        <v>94.33145904541016</v>
       </c>
       <c r="D222" t="n">
-        <v>94.34088058914503</v>
+        <v>94.34085006852878</v>
       </c>
       <c r="E222" t="n">
-        <v>94.33148956298828</v>
+        <v>94.33145904541016</v>
       </c>
       <c r="F222" t="n">
-        <v>94.34088058914503</v>
+        <v>94.34085006852878</v>
       </c>
       <c r="G222" t="n">
         <v>4353200</v>
@@ -5555,16 +5555,16 @@
         <v>45611</v>
       </c>
       <c r="C223" t="n">
-        <v>94.37841033935547</v>
+        <v>94.37841796875</v>
       </c>
       <c r="D223" t="n">
-        <v>94.37841033935547</v>
+        <v>94.37841796875</v>
       </c>
       <c r="E223" t="n">
-        <v>94.36902647844418</v>
+        <v>94.36903410708014</v>
       </c>
       <c r="F223" t="n">
-        <v>94.36902647844418</v>
+        <v>94.36903410708014</v>
       </c>
       <c r="G223" t="n">
         <v>5605100</v>
@@ -5578,16 +5578,16 @@
         <v>45614</v>
       </c>
       <c r="C224" t="n">
-        <v>94.38782501220703</v>
+        <v>94.38780975341797</v>
       </c>
       <c r="D224" t="n">
-        <v>94.38782501220703</v>
+        <v>94.38780975341797</v>
       </c>
       <c r="E224" t="n">
-        <v>94.37843398569024</v>
+        <v>94.37841872841933</v>
       </c>
       <c r="F224" t="n">
-        <v>94.38782501220703</v>
+        <v>94.38780975341797</v>
       </c>
       <c r="G224" t="n">
         <v>5567500</v>
@@ -5601,16 +5601,16 @@
         <v>45615</v>
       </c>
       <c r="C225" t="n">
-        <v>94.39718627929688</v>
+        <v>94.39720153808594</v>
       </c>
       <c r="D225" t="n">
-        <v>94.39718627929688</v>
+        <v>94.39720153808594</v>
       </c>
       <c r="E225" t="n">
-        <v>94.38779525574067</v>
+        <v>94.38781051301173</v>
       </c>
       <c r="F225" t="n">
-        <v>94.39718627929688</v>
+        <v>94.39720153808594</v>
       </c>
       <c r="G225" t="n">
         <v>4310900</v>
@@ -5624,16 +5624,16 @@
         <v>45616</v>
       </c>
       <c r="C226" t="n">
-        <v>94.41595458984375</v>
+        <v>94.41597747802734</v>
       </c>
       <c r="D226" t="n">
-        <v>94.41595458984375</v>
+        <v>94.41597747802734</v>
       </c>
       <c r="E226" t="n">
-        <v>94.3971797072906</v>
+        <v>94.39720259092282</v>
       </c>
       <c r="F226" t="n">
-        <v>94.406570730193</v>
+        <v>94.40659361610177</v>
       </c>
       <c r="G226" t="n">
         <v>4133000</v>
@@ -5647,16 +5647,16 @@
         <v>45617</v>
       </c>
       <c r="C227" t="n">
-        <v>94.41595458984375</v>
+        <v>94.41597747802734</v>
       </c>
       <c r="D227" t="n">
-        <v>94.42534561274614</v>
+        <v>94.4253685032063</v>
       </c>
       <c r="E227" t="n">
-        <v>94.41595458984375</v>
+        <v>94.41597747802734</v>
       </c>
       <c r="F227" t="n">
-        <v>94.42534561274614</v>
+        <v>94.4253685032063</v>
       </c>
       <c r="G227" t="n">
         <v>4410700</v>
@@ -5716,16 +5716,16 @@
         <v>45622</v>
       </c>
       <c r="C230" t="n">
-        <v>94.47230529785156</v>
+        <v>94.47229766845703</v>
       </c>
       <c r="D230" t="n">
-        <v>94.48168915866783</v>
+        <v>94.48168152851547</v>
       </c>
       <c r="E230" t="n">
-        <v>94.46291427378277</v>
+        <v>94.46290664514663</v>
       </c>
       <c r="F230" t="n">
-        <v>94.47230529785156</v>
+        <v>94.47229766845703</v>
       </c>
       <c r="G230" t="n">
         <v>4586900</v>
@@ -5739,16 +5739,16 @@
         <v>45623</v>
       </c>
       <c r="C231" t="n">
-        <v>94.4910888671875</v>
+        <v>94.49110412597656</v>
       </c>
       <c r="D231" t="n">
-        <v>94.5004798921194</v>
+        <v>94.50049515242496</v>
       </c>
       <c r="E231" t="n">
-        <v>94.4910888671875</v>
+        <v>94.49110412597656</v>
       </c>
       <c r="F231" t="n">
-        <v>94.4910888671875</v>
+        <v>94.49110412597656</v>
       </c>
       <c r="G231" t="n">
         <v>5909000</v>
@@ -5762,16 +5762,16 @@
         <v>45625</v>
       </c>
       <c r="C232" t="n">
-        <v>94.52866363525391</v>
+        <v>94.52864074707031</v>
       </c>
       <c r="D232" t="n">
-        <v>94.5380546619573</v>
+        <v>94.53803177149987</v>
       </c>
       <c r="E232" t="n">
-        <v>94.52866363525391</v>
+        <v>94.52864074707031</v>
       </c>
       <c r="F232" t="n">
-        <v>94.52866363525391</v>
+        <v>94.52864074707031</v>
       </c>
       <c r="G232" t="n">
         <v>6581100</v>
@@ -5785,16 +5785,16 @@
         <v>45628</v>
       </c>
       <c r="C233" t="n">
-        <v>94.54560852050781</v>
+        <v>94.54560089111328</v>
       </c>
       <c r="D233" t="n">
-        <v>94.55503493656933</v>
+        <v>94.55502730641413</v>
       </c>
       <c r="E233" t="n">
-        <v>94.54560852050781</v>
+        <v>94.54560089111328</v>
       </c>
       <c r="F233" t="n">
-        <v>94.55031813341422</v>
+        <v>94.55031050363964</v>
       </c>
       <c r="G233" t="n">
         <v>11471800</v>
@@ -5808,16 +5808,16 @@
         <v>45629</v>
       </c>
       <c r="C234" t="n">
-        <v>94.5550537109375</v>
+        <v>94.55502319335938</v>
       </c>
       <c r="D234" t="n">
-        <v>94.56447293862054</v>
+        <v>94.56444241800236</v>
       </c>
       <c r="E234" t="n">
-        <v>94.5550537109375</v>
+        <v>94.55502319335938</v>
       </c>
       <c r="F234" t="n">
-        <v>94.56447293862054</v>
+        <v>94.56444241800236</v>
       </c>
       <c r="G234" t="n">
         <v>5734100</v>
@@ -5831,16 +5831,16 @@
         <v>45630</v>
       </c>
       <c r="C235" t="n">
-        <v>94.57386779785156</v>
+        <v>94.57388305664062</v>
       </c>
       <c r="D235" t="n">
-        <v>94.5832942126392</v>
+        <v>94.58330947294915</v>
       </c>
       <c r="E235" t="n">
-        <v>94.56444138306392</v>
+        <v>94.5644566403321</v>
       </c>
       <c r="F235" t="n">
-        <v>94.57386779785156</v>
+        <v>94.57388305664062</v>
       </c>
       <c r="G235" t="n">
         <v>5351100</v>
@@ -5854,16 +5854,16 @@
         <v>45631</v>
       </c>
       <c r="C236" t="n">
-        <v>94.58329772949219</v>
+        <v>94.58330535888672</v>
       </c>
       <c r="D236" t="n">
-        <v>94.59272414463034</v>
+        <v>94.59273177478522</v>
       </c>
       <c r="E236" t="n">
-        <v>94.58329772949219</v>
+        <v>94.58330535888672</v>
       </c>
       <c r="F236" t="n">
-        <v>94.58329772949219</v>
+        <v>94.58330535888672</v>
       </c>
       <c r="G236" t="n">
         <v>4870100</v>
@@ -5877,16 +5877,16 @@
         <v>45632</v>
       </c>
       <c r="C237" t="n">
-        <v>94.63043212890625</v>
+        <v>94.63042449951172</v>
       </c>
       <c r="D237" t="n">
-        <v>94.63043212890625</v>
+        <v>94.63042449951172</v>
       </c>
       <c r="E237" t="n">
-        <v>94.62100571282039</v>
+        <v>94.62099808418584</v>
       </c>
       <c r="F237" t="n">
-        <v>94.63043212890625</v>
+        <v>94.63042449951172</v>
       </c>
       <c r="G237" t="n">
         <v>4779000</v>
@@ -5900,16 +5900,16 @@
         <v>45635</v>
       </c>
       <c r="C238" t="n">
-        <v>94.63984680175781</v>
+        <v>94.63985443115234</v>
       </c>
       <c r="D238" t="n">
-        <v>94.63984680175781</v>
+        <v>94.63985443115234</v>
       </c>
       <c r="E238" t="n">
-        <v>94.63042757637383</v>
+        <v>94.63043520500904</v>
       </c>
       <c r="F238" t="n">
-        <v>94.63042757637383</v>
+        <v>94.63043520500904</v>
       </c>
       <c r="G238" t="n">
         <v>5539800</v>
@@ -5923,16 +5923,16 @@
         <v>45636</v>
       </c>
       <c r="C239" t="n">
-        <v>94.65871429443359</v>
+        <v>94.65872192382812</v>
       </c>
       <c r="D239" t="n">
-        <v>94.65871429443359</v>
+        <v>94.65872192382812</v>
       </c>
       <c r="E239" t="n">
-        <v>94.64928787734119</v>
+        <v>94.64929550597597</v>
       </c>
       <c r="F239" t="n">
-        <v>94.64928787734119</v>
+        <v>94.64929550597597</v>
       </c>
       <c r="G239" t="n">
         <v>5293500</v>
@@ -5946,16 +5946,16 @@
         <v>45637</v>
       </c>
       <c r="C240" t="n">
-        <v>94.65871429443359</v>
+        <v>94.65872192382812</v>
       </c>
       <c r="D240" t="n">
-        <v>94.66813352127649</v>
+        <v>94.66814115143021</v>
       </c>
       <c r="E240" t="n">
-        <v>94.65871429443359</v>
+        <v>94.65872192382812</v>
       </c>
       <c r="F240" t="n">
-        <v>94.66813352127649</v>
+        <v>94.66814115143021</v>
       </c>
       <c r="G240" t="n">
         <v>4855300</v>
@@ -5969,16 +5969,16 @@
         <v>45638</v>
       </c>
       <c r="C241" t="n">
-        <v>94.66812896728516</v>
+        <v>94.66812133789062</v>
       </c>
       <c r="D241" t="n">
-        <v>94.6775553839241</v>
+        <v>94.67754775376989</v>
       </c>
       <c r="E241" t="n">
-        <v>94.66812896728516</v>
+        <v>94.66812133789062</v>
       </c>
       <c r="F241" t="n">
-        <v>94.6775553839241</v>
+        <v>94.67754775376989</v>
       </c>
       <c r="G241" t="n">
         <v>4701000</v>
@@ -5992,16 +5992,16 @@
         <v>45639</v>
       </c>
       <c r="C242" t="n">
-        <v>94.71524810791016</v>
+        <v>94.71525573730469</v>
       </c>
       <c r="D242" t="n">
-        <v>94.71524810791016</v>
+        <v>94.71525573730469</v>
       </c>
       <c r="E242" t="n">
-        <v>94.70582169184371</v>
+        <v>94.70582932047894</v>
       </c>
       <c r="F242" t="n">
-        <v>94.70582169184371</v>
+        <v>94.70582932047894</v>
       </c>
       <c r="G242" t="n">
         <v>4671500</v>
@@ -6015,16 +6015,16 @@
         <v>45642</v>
       </c>
       <c r="C243" t="n">
-        <v>94.72468566894531</v>
+        <v>94.72467041015625</v>
       </c>
       <c r="D243" t="n">
-        <v>94.72468566894531</v>
+        <v>94.72467041015625</v>
       </c>
       <c r="E243" t="n">
-        <v>94.71525925176978</v>
+        <v>94.71524399449918</v>
       </c>
       <c r="F243" t="n">
-        <v>94.72468566894531</v>
+        <v>94.72467041015625</v>
       </c>
       <c r="G243" t="n">
         <v>5598900</v>
@@ -6038,16 +6038,16 @@
         <v>45643</v>
       </c>
       <c r="C244" t="n">
-        <v>94.72468566894531</v>
+        <v>94.72467041015625</v>
       </c>
       <c r="D244" t="n">
-        <v>94.73410489587128</v>
+        <v>94.7340896355649</v>
       </c>
       <c r="E244" t="n">
-        <v>94.72468566894531</v>
+        <v>94.72467041015625</v>
       </c>
       <c r="F244" t="n">
-        <v>94.73410489587128</v>
+        <v>94.7340896355649</v>
       </c>
       <c r="G244" t="n">
         <v>5798500</v>
@@ -6061,16 +6061,16 @@
         <v>45644</v>
       </c>
       <c r="C245" t="n">
-        <v>94.74549102783203</v>
+        <v>94.74547576904297</v>
       </c>
       <c r="D245" t="n">
-        <v>94.74549102783203</v>
+        <v>94.74547576904297</v>
       </c>
       <c r="E245" t="n">
-        <v>94.73602959338879</v>
+        <v>94.7360143361235</v>
       </c>
       <c r="F245" t="n">
-        <v>94.74549102783203</v>
+        <v>94.74547576904297</v>
       </c>
       <c r="G245" t="n">
         <v>11526500</v>
@@ -6107,16 +6107,16 @@
         <v>45646</v>
       </c>
       <c r="C247" t="n">
-        <v>94.78331756591797</v>
+        <v>94.7833251953125</v>
       </c>
       <c r="D247" t="n">
-        <v>94.79277899988548</v>
+        <v>94.79278663004159</v>
       </c>
       <c r="E247" t="n">
-        <v>94.78331756591797</v>
+        <v>94.7833251953125</v>
       </c>
       <c r="F247" t="n">
-        <v>94.7880518913815</v>
+        <v>94.78805952115711</v>
       </c>
       <c r="G247" t="n">
         <v>8898900</v>
@@ -6130,16 +6130,16 @@
         <v>45649</v>
       </c>
       <c r="C248" t="n">
-        <v>94.80223846435547</v>
+        <v>94.80224609375</v>
       </c>
       <c r="D248" t="n">
-        <v>94.80223846435547</v>
+        <v>94.80224609375</v>
       </c>
       <c r="E248" t="n">
-        <v>94.79277703058452</v>
+        <v>94.79278465921763</v>
       </c>
       <c r="F248" t="n">
-        <v>94.80223846435547</v>
+        <v>94.80224609375</v>
       </c>
       <c r="G248" t="n">
         <v>7032500</v>
@@ -6153,16 +6153,16 @@
         <v>45650</v>
       </c>
       <c r="C249" t="n">
-        <v>94.83059692382812</v>
+        <v>94.83062744140625</v>
       </c>
       <c r="D249" t="n">
-        <v>94.83059692382812</v>
+        <v>94.83062744140625</v>
       </c>
       <c r="E249" t="n">
-        <v>94.82113549191543</v>
+        <v>94.82116600644875</v>
       </c>
       <c r="F249" t="n">
-        <v>94.83059692382812</v>
+        <v>94.83062744140625</v>
       </c>
       <c r="G249" t="n">
         <v>4654300</v>
@@ -6176,16 +6176,16 @@
         <v>45652</v>
       </c>
       <c r="C250" t="n">
-        <v>94.840087890625</v>
+        <v>94.84009552001953</v>
       </c>
       <c r="D250" t="n">
-        <v>94.840087890625</v>
+        <v>94.84009552001953</v>
       </c>
       <c r="E250" t="n">
-        <v>94.83062645576584</v>
+        <v>94.83063408439924</v>
       </c>
       <c r="F250" t="n">
-        <v>94.840087890625</v>
+        <v>94.84009552001953</v>
       </c>
       <c r="G250" t="n">
         <v>4974100</v>
@@ -6199,16 +6199,16 @@
         <v>45653</v>
       </c>
       <c r="C251" t="n">
-        <v>94.86846160888672</v>
+        <v>94.86847686767578</v>
       </c>
       <c r="D251" t="n">
-        <v>94.86846160888672</v>
+        <v>94.86847686767578</v>
       </c>
       <c r="E251" t="n">
-        <v>94.85900017436359</v>
+        <v>94.85901543163085</v>
       </c>
       <c r="F251" t="n">
-        <v>94.85900017436359</v>
+        <v>94.85901543163085</v>
       </c>
       <c r="G251" t="n">
         <v>6558000</v>
@@ -6222,16 +6222,16 @@
         <v>45656</v>
       </c>
       <c r="C252" t="n">
-        <v>94.86846160888672</v>
+        <v>94.86847686767578</v>
       </c>
       <c r="D252" t="n">
-        <v>94.87792304340985</v>
+        <v>94.8779383037207</v>
       </c>
       <c r="E252" t="n">
-        <v>94.86846160888672</v>
+        <v>94.86847686767578</v>
       </c>
       <c r="F252" t="n">
-        <v>94.87792304340985</v>
+        <v>94.8779383037207</v>
       </c>
       <c r="G252" t="n">
         <v>6547600</v>
@@ -6245,16 +6245,16 @@
         <v>45657</v>
       </c>
       <c r="C253" t="n">
-        <v>94.89684295654297</v>
+        <v>94.89682769775391</v>
       </c>
       <c r="D253" t="n">
-        <v>94.9157586094786</v>
+        <v>94.91574334764803</v>
       </c>
       <c r="E253" t="n">
-        <v>94.89684295654297</v>
+        <v>94.89682769775391</v>
       </c>
       <c r="F253" t="n">
-        <v>94.90630439149093</v>
+        <v>94.90628913118054</v>
       </c>
       <c r="G253" t="n">
         <v>7371300</v>
@@ -6268,16 +6268,16 @@
         <v>45659</v>
       </c>
       <c r="C254" t="n">
-        <v>94.91574859619141</v>
+        <v>94.91575622558594</v>
       </c>
       <c r="D254" t="n">
-        <v>94.91574859619141</v>
+        <v>94.91575622558594</v>
       </c>
       <c r="E254" t="n">
-        <v>94.90629437920111</v>
+        <v>94.90630200783571</v>
       </c>
       <c r="F254" t="n">
-        <v>94.91574859619141</v>
+        <v>94.91575622558594</v>
       </c>
       <c r="G254" t="n">
         <v>7533100</v>
@@ -6291,16 +6291,16 @@
         <v>45660</v>
       </c>
       <c r="C255" t="n">
-        <v>94.94412994384766</v>
+        <v>94.94414520263672</v>
       </c>
       <c r="D255" t="n">
-        <v>94.95358416054377</v>
+        <v>94.95359942085226</v>
       </c>
       <c r="E255" t="n">
-        <v>94.94412994384766</v>
+        <v>94.94414520263672</v>
       </c>
       <c r="F255" t="n">
-        <v>94.95358416054377</v>
+        <v>94.95359942085226</v>
       </c>
       <c r="G255" t="n">
         <v>6730100</v>
@@ -6314,16 +6314,16 @@
         <v>45663</v>
       </c>
       <c r="C256" t="n">
-        <v>94.94412994384766</v>
+        <v>94.94414520263672</v>
       </c>
       <c r="D256" t="n">
-        <v>94.9630455941992</v>
+        <v>94.96306085602826</v>
       </c>
       <c r="E256" t="n">
-        <v>94.94412994384766</v>
+        <v>94.94414520263672</v>
       </c>
       <c r="F256" t="n">
-        <v>94.95358416054377</v>
+        <v>94.95359942085226</v>
       </c>
       <c r="G256" t="n">
         <v>6938300</v>
@@ -6337,16 +6337,16 @@
         <v>45664</v>
       </c>
       <c r="C257" t="n">
-        <v>94.96304321289062</v>
+        <v>94.96305084228516</v>
       </c>
       <c r="D257" t="n">
-        <v>94.97250464630879</v>
+        <v>94.97251227646346</v>
       </c>
       <c r="E257" t="n">
-        <v>94.96304321289062</v>
+        <v>94.96305084228516</v>
       </c>
       <c r="F257" t="n">
-        <v>94.97250464630879</v>
+        <v>94.97251227646346</v>
       </c>
       <c r="G257" t="n">
         <v>6792100</v>
@@ -6383,16 +6383,16 @@
         <v>45667</v>
       </c>
       <c r="C259" t="n">
-        <v>95.01979827880859</v>
+        <v>95.01980590820312</v>
       </c>
       <c r="D259" t="n">
-        <v>95.0292597123163</v>
+        <v>95.02926734247052</v>
       </c>
       <c r="E259" t="n">
-        <v>95.01034406226007</v>
+        <v>95.0103516908955</v>
       </c>
       <c r="F259" t="n">
-        <v>95.01979827880859</v>
+        <v>95.01980590820312</v>
       </c>
       <c r="G259" t="n">
         <v>7644600</v>
@@ -6406,16 +6406,16 @@
         <v>45670</v>
       </c>
       <c r="C260" t="n">
-        <v>95.03872680664062</v>
+        <v>95.03873443603516</v>
       </c>
       <c r="D260" t="n">
-        <v>95.03872680664062</v>
+        <v>95.03873443603516</v>
       </c>
       <c r="E260" t="n">
-        <v>95.02926537256936</v>
+        <v>95.02927300120436</v>
       </c>
       <c r="F260" t="n">
-        <v>95.03399248112518</v>
+        <v>95.03400011013966</v>
       </c>
       <c r="G260" t="n">
         <v>7647300</v>
@@ -6429,16 +6429,16 @@
         <v>45671</v>
       </c>
       <c r="C261" t="n">
-        <v>95.04818725585938</v>
+        <v>95.04817962646484</v>
       </c>
       <c r="D261" t="n">
-        <v>95.04818725585938</v>
+        <v>95.04817962646484</v>
       </c>
       <c r="E261" t="n">
-        <v>95.03872582188613</v>
+        <v>95.03871819325106</v>
       </c>
       <c r="F261" t="n">
-        <v>95.04818725585938</v>
+        <v>95.04817962646484</v>
       </c>
       <c r="G261" t="n">
         <v>7245400</v>
@@ -6452,16 +6452,16 @@
         <v>45672</v>
       </c>
       <c r="C262" t="n">
-        <v>95.05765533447266</v>
+        <v>95.05764007568359</v>
       </c>
       <c r="D262" t="n">
-        <v>95.05765533447266</v>
+        <v>95.05764007568359</v>
       </c>
       <c r="E262" t="n">
-        <v>95.04820111608032</v>
+        <v>95.04818585880886</v>
       </c>
       <c r="F262" t="n">
-        <v>95.05765533447266</v>
+        <v>95.05764007568359</v>
       </c>
       <c r="G262" t="n">
         <v>6878600</v>
@@ -6475,16 +6475,16 @@
         <v>45673</v>
       </c>
       <c r="C263" t="n">
-        <v>95.05765533447266</v>
+        <v>95.05764007568359</v>
       </c>
       <c r="D263" t="n">
-        <v>95.07657820517852</v>
+        <v>95.07656294335193</v>
       </c>
       <c r="E263" t="n">
-        <v>95.05765533447266</v>
+        <v>95.05764007568359</v>
       </c>
       <c r="F263" t="n">
-        <v>95.06711676982559</v>
+        <v>95.06710150951776</v>
       </c>
       <c r="G263" t="n">
         <v>5352500</v>
@@ -6498,16 +6498,16 @@
         <v>45674</v>
       </c>
       <c r="C264" t="n">
-        <v>95.10493469238281</v>
+        <v>95.10494995117188</v>
       </c>
       <c r="D264" t="n">
-        <v>95.11439612568618</v>
+        <v>95.11441138599326</v>
       </c>
       <c r="E264" t="n">
-        <v>95.09547325907944</v>
+        <v>95.0954885163505</v>
       </c>
       <c r="F264" t="n">
-        <v>95.10493469238281</v>
+        <v>95.10494995117188</v>
       </c>
       <c r="G264" t="n">
         <v>6563000</v>
@@ -6521,16 +6521,16 @@
         <v>45678</v>
       </c>
       <c r="C265" t="n">
-        <v>95.11439514160156</v>
+        <v>95.11440277099609</v>
       </c>
       <c r="D265" t="n">
-        <v>95.12384935784807</v>
+        <v>95.12385698800095</v>
       </c>
       <c r="E265" t="n">
-        <v>95.11439514160156</v>
+        <v>95.11440277099609</v>
       </c>
       <c r="F265" t="n">
-        <v>95.11912224972482</v>
+        <v>95.11912987949853</v>
       </c>
       <c r="G265" t="n">
         <v>7952400</v>
@@ -6544,16 +6544,16 @@
         <v>45679</v>
       </c>
       <c r="C266" t="n">
-        <v>95.13330078125</v>
+        <v>95.13332366943359</v>
       </c>
       <c r="D266" t="n">
-        <v>95.13330078125</v>
+        <v>95.13332366943359</v>
       </c>
       <c r="E266" t="n">
-        <v>95.12383934904004</v>
+        <v>95.12386223494731</v>
       </c>
       <c r="F266" t="n">
-        <v>95.12383934904004</v>
+        <v>95.12386223494731</v>
       </c>
       <c r="G266" t="n">
         <v>5717600</v>
@@ -6590,16 +6590,16 @@
         <v>45681</v>
       </c>
       <c r="C268" t="n">
-        <v>95.17116546630859</v>
+        <v>95.17115783691406</v>
       </c>
       <c r="D268" t="n">
-        <v>95.18062690112056</v>
+        <v>95.18061927096755</v>
       </c>
       <c r="E268" t="n">
-        <v>95.17116546630859</v>
+        <v>95.17115783691406</v>
       </c>
       <c r="F268" t="n">
-        <v>95.17116546630859</v>
+        <v>95.17115783691406</v>
       </c>
       <c r="G268" t="n">
         <v>6380000</v>
@@ -6613,16 +6613,16 @@
         <v>45684</v>
       </c>
       <c r="C269" t="n">
-        <v>95.17116546630859</v>
+        <v>95.17115783691406</v>
       </c>
       <c r="D269" t="n">
-        <v>95.19008111897233</v>
+        <v>95.19007348806143</v>
       </c>
       <c r="E269" t="n">
-        <v>95.17116546630859</v>
+        <v>95.17115783691406</v>
       </c>
       <c r="F269" t="n">
-        <v>95.18062690112056</v>
+        <v>95.18061927096755</v>
       </c>
       <c r="G269" t="n">
         <v>9439800</v>
@@ -6682,16 +6682,16 @@
         <v>45687</v>
       </c>
       <c r="C272" t="n">
-        <v>95.21846771240234</v>
+        <v>95.21847534179688</v>
       </c>
       <c r="D272" t="n">
-        <v>95.22792193048139</v>
+        <v>95.22792956063344</v>
       </c>
       <c r="E272" t="n">
-        <v>95.20900627736293</v>
+        <v>95.20901390599936</v>
       </c>
       <c r="F272" t="n">
-        <v>95.20900627736293</v>
+        <v>95.20901390599936</v>
       </c>
       <c r="G272" t="n">
         <v>8043500</v>
@@ -6728,16 +6728,16 @@
         <v>45691</v>
       </c>
       <c r="C274" t="n">
-        <v>95.25920867919922</v>
+        <v>95.25920104980469</v>
       </c>
       <c r="D274" t="n">
-        <v>95.25920867919922</v>
+        <v>95.25920104980469</v>
       </c>
       <c r="E274" t="n">
-        <v>95.24972025138301</v>
+        <v>95.24971262274842</v>
       </c>
       <c r="F274" t="n">
-        <v>95.24972025138301</v>
+        <v>95.24971262274842</v>
       </c>
       <c r="G274" t="n">
         <v>16436200</v>
@@ -6751,16 +6751,16 @@
         <v>45692</v>
       </c>
       <c r="C275" t="n">
-        <v>95.27819061279297</v>
+        <v>95.2781982421875</v>
       </c>
       <c r="D275" t="n">
-        <v>95.27819061279297</v>
+        <v>95.2781982421875</v>
       </c>
       <c r="E275" t="n">
-        <v>95.26869494283973</v>
+        <v>95.2687025714739</v>
       </c>
       <c r="F275" t="n">
-        <v>95.27819061279297</v>
+        <v>95.2781982421875</v>
       </c>
       <c r="G275" t="n">
         <v>7866600</v>
@@ -6774,16 +6774,16 @@
         <v>45693</v>
       </c>
       <c r="C276" t="n">
-        <v>95.27819061279297</v>
+        <v>95.2781982421875</v>
       </c>
       <c r="D276" t="n">
-        <v>95.28768628274619</v>
+        <v>95.28769391290109</v>
       </c>
       <c r="E276" t="n">
-        <v>95.27819061279297</v>
+        <v>95.2781982421875</v>
       </c>
       <c r="F276" t="n">
-        <v>95.28768628274619</v>
+        <v>95.28769391290109</v>
       </c>
       <c r="G276" t="n">
         <v>7100900</v>
@@ -6797,16 +6797,16 @@
         <v>45694</v>
       </c>
       <c r="C277" t="n">
-        <v>95.29718017578125</v>
+        <v>95.29718780517578</v>
       </c>
       <c r="D277" t="n">
-        <v>95.29718017578125</v>
+        <v>95.29718780517578</v>
       </c>
       <c r="E277" t="n">
-        <v>95.28769174835773</v>
+        <v>95.28769937699263</v>
       </c>
       <c r="F277" t="n">
-        <v>95.29718017578125</v>
+        <v>95.29718780517578</v>
       </c>
       <c r="G277" t="n">
         <v>5804300</v>
@@ -6820,16 +6820,16 @@
         <v>45695</v>
       </c>
       <c r="C278" t="n">
-        <v>95.32566833496094</v>
+        <v>95.32566070556641</v>
       </c>
       <c r="D278" t="n">
-        <v>95.3351567624987</v>
+        <v>95.33514913234477</v>
       </c>
       <c r="E278" t="n">
-        <v>95.31617266434873</v>
+        <v>95.31616503571418</v>
       </c>
       <c r="F278" t="n">
-        <v>95.3351567624987</v>
+        <v>95.33514913234477</v>
       </c>
       <c r="G278" t="n">
         <v>6758700</v>
@@ -6843,16 +6843,16 @@
         <v>45698</v>
       </c>
       <c r="C279" t="n">
-        <v>95.34467315673828</v>
+        <v>95.34464263916016</v>
       </c>
       <c r="D279" t="n">
-        <v>95.34467315673828</v>
+        <v>95.34464263916016</v>
       </c>
       <c r="E279" t="n">
-        <v>95.33517748406213</v>
+        <v>95.33514696952335</v>
       </c>
       <c r="F279" t="n">
-        <v>95.34467315673828</v>
+        <v>95.34464263916016</v>
       </c>
       <c r="G279" t="n">
         <v>7517800</v>
@@ -6866,16 +6866,16 @@
         <v>45699</v>
       </c>
       <c r="C280" t="n">
-        <v>95.34467315673828</v>
+        <v>95.34464263916016</v>
       </c>
       <c r="D280" t="n">
-        <v>95.35416882941442</v>
+        <v>95.35413830879696</v>
       </c>
       <c r="E280" t="n">
-        <v>95.34467315673828</v>
+        <v>95.34464263916016</v>
       </c>
       <c r="F280" t="n">
-        <v>95.35416882941442</v>
+        <v>95.35413830879696</v>
       </c>
       <c r="G280" t="n">
         <v>6424100</v>
@@ -6889,16 +6889,16 @@
         <v>45700</v>
       </c>
       <c r="C281" t="n">
-        <v>95.35414123535156</v>
+        <v>95.35415649414062</v>
       </c>
       <c r="D281" t="n">
-        <v>95.36362966220587</v>
+        <v>95.36364492251329</v>
       </c>
       <c r="E281" t="n">
-        <v>95.35414123535156</v>
+        <v>95.35415649414062</v>
       </c>
       <c r="F281" t="n">
-        <v>95.35414123535156</v>
+        <v>95.35415649414062</v>
       </c>
       <c r="G281" t="n">
         <v>6618800</v>
@@ -6912,16 +6912,16 @@
         <v>45701</v>
       </c>
       <c r="C282" t="n">
-        <v>95.37313079833984</v>
+        <v>95.37313842773438</v>
       </c>
       <c r="D282" t="n">
-        <v>95.37313079833984</v>
+        <v>95.37313842773438</v>
       </c>
       <c r="E282" t="n">
-        <v>95.36363512786737</v>
+        <v>95.3636427565023</v>
       </c>
       <c r="F282" t="n">
-        <v>95.37313079833984</v>
+        <v>95.37313842773438</v>
       </c>
       <c r="G282" t="n">
         <v>5690100</v>
@@ -6958,16 +6958,16 @@
         <v>45706</v>
       </c>
       <c r="C284" t="n">
-        <v>95.43009185791016</v>
+        <v>95.43009948730469</v>
       </c>
       <c r="D284" t="n">
-        <v>95.43009185791016</v>
+        <v>95.43009948730469</v>
       </c>
       <c r="E284" t="n">
-        <v>95.42060343036061</v>
+        <v>95.42061105899657</v>
       </c>
       <c r="F284" t="n">
-        <v>95.43009185791016</v>
+        <v>95.43009948730469</v>
       </c>
       <c r="G284" t="n">
         <v>15815200</v>
@@ -6981,16 +6981,16 @@
         <v>45707</v>
       </c>
       <c r="C285" t="n">
-        <v>95.43009185791016</v>
+        <v>95.43009948730469</v>
       </c>
       <c r="D285" t="n">
-        <v>95.43958752853416</v>
+        <v>95.43959515868785</v>
       </c>
       <c r="E285" t="n">
-        <v>95.43009185791016</v>
+        <v>95.43009948730469</v>
       </c>
       <c r="F285" t="n">
-        <v>95.43958752853416</v>
+        <v>95.43959515868785</v>
       </c>
       <c r="G285" t="n">
         <v>7277600</v>
@@ -7004,16 +7004,16 @@
         <v>45708</v>
       </c>
       <c r="C286" t="n">
-        <v>95.44907379150391</v>
+        <v>95.44908142089844</v>
       </c>
       <c r="D286" t="n">
-        <v>95.44907379150391</v>
+        <v>95.44908142089844</v>
       </c>
       <c r="E286" t="n">
-        <v>95.43957812181581</v>
+        <v>95.43958575045134</v>
       </c>
       <c r="F286" t="n">
-        <v>95.44907379150391</v>
+        <v>95.44908142089844</v>
       </c>
       <c r="G286" t="n">
         <v>7608000</v>
@@ -7027,16 +7027,16 @@
         <v>45709</v>
       </c>
       <c r="C287" t="n">
-        <v>95.48707580566406</v>
+        <v>95.487060546875</v>
       </c>
       <c r="D287" t="n">
-        <v>95.48707580566406</v>
+        <v>95.487060546875</v>
       </c>
       <c r="E287" t="n">
-        <v>95.47758013333288</v>
+        <v>95.47756487606122</v>
       </c>
       <c r="F287" t="n">
-        <v>95.47758013333288</v>
+        <v>95.47756487606122</v>
       </c>
       <c r="G287" t="n">
         <v>9111000</v>
@@ -7050,16 +7050,16 @@
         <v>45712</v>
       </c>
       <c r="C288" t="n">
-        <v>95.49655151367188</v>
+        <v>95.49654388427734</v>
       </c>
       <c r="D288" t="n">
-        <v>95.49655151367188</v>
+        <v>95.49654388427734</v>
       </c>
       <c r="E288" t="n">
-        <v>95.48706308568042</v>
+        <v>95.48705545704394</v>
       </c>
       <c r="F288" t="n">
-        <v>95.49655151367188</v>
+        <v>95.49654388427734</v>
       </c>
       <c r="G288" t="n">
         <v>9734600</v>
@@ -7073,16 +7073,16 @@
         <v>45713</v>
       </c>
       <c r="C289" t="n">
-        <v>95.50604248046875</v>
+        <v>95.50605010986328</v>
       </c>
       <c r="D289" t="n">
-        <v>95.50604248046875</v>
+        <v>95.50605010986328</v>
       </c>
       <c r="E289" t="n">
-        <v>95.49654680987022</v>
+        <v>95.49655443850621</v>
       </c>
       <c r="F289" t="n">
-        <v>95.49654680987022</v>
+        <v>95.49655443850621</v>
       </c>
       <c r="G289" t="n">
         <v>10827700</v>
@@ -7096,16 +7096,16 @@
         <v>45714</v>
       </c>
       <c r="C290" t="n">
-        <v>95.50604248046875</v>
+        <v>95.50605010986328</v>
       </c>
       <c r="D290" t="n">
-        <v>95.51553815106729</v>
+        <v>95.51554578122035</v>
       </c>
       <c r="E290" t="n">
-        <v>95.50604248046875</v>
+        <v>95.50605010986328</v>
       </c>
       <c r="F290" t="n">
-        <v>95.50604248046875</v>
+        <v>95.50605010986328</v>
       </c>
       <c r="G290" t="n">
         <v>9536300</v>
@@ -7119,16 +7119,16 @@
         <v>45715</v>
       </c>
       <c r="C291" t="n">
-        <v>95.53452301025391</v>
+        <v>95.53450775146484</v>
       </c>
       <c r="D291" t="n">
-        <v>95.53452301025391</v>
+        <v>95.53450775146484</v>
       </c>
       <c r="E291" t="n">
-        <v>95.52503458265423</v>
+        <v>95.52501932538067</v>
       </c>
       <c r="F291" t="n">
-        <v>95.53452301025391</v>
+        <v>95.53450775146484</v>
       </c>
       <c r="G291" t="n">
         <v>10807800</v>
@@ -7165,16 +7165,16 @@
         <v>45719</v>
       </c>
       <c r="C293" t="n">
-        <v>95.57542419433594</v>
+        <v>95.57543182373047</v>
       </c>
       <c r="D293" t="n">
-        <v>95.57542419433594</v>
+        <v>95.57543182373047</v>
       </c>
       <c r="E293" t="n">
-        <v>95.56589890131818</v>
+        <v>95.56590652995234</v>
       </c>
       <c r="F293" t="n">
-        <v>95.57542419433594</v>
+        <v>95.57543182373047</v>
       </c>
       <c r="G293" t="n">
         <v>17436600</v>
@@ -7234,16 +7234,16 @@
         <v>45722</v>
       </c>
       <c r="C296" t="n">
-        <v>95.613525390625</v>
+        <v>95.61351013183594</v>
       </c>
       <c r="D296" t="n">
-        <v>95.613525390625</v>
+        <v>95.61351013183594</v>
       </c>
       <c r="E296" t="n">
-        <v>95.59447480313699</v>
+        <v>95.59445954738818</v>
       </c>
       <c r="F296" t="n">
-        <v>95.60400009688099</v>
+        <v>95.60398483961205</v>
       </c>
       <c r="G296" t="n">
         <v>9925500</v>
@@ -7257,16 +7257,16 @@
         <v>45723</v>
       </c>
       <c r="C297" t="n">
-        <v>95.64208221435547</v>
+        <v>95.64208984375</v>
       </c>
       <c r="D297" t="n">
-        <v>95.64208221435547</v>
+        <v>95.64208984375</v>
       </c>
       <c r="E297" t="n">
-        <v>95.63255692178585</v>
+        <v>95.63256455042055</v>
       </c>
       <c r="F297" t="n">
-        <v>95.64208221435547</v>
+        <v>95.64208984375</v>
       </c>
       <c r="G297" t="n">
         <v>8962400</v>
@@ -7280,16 +7280,16 @@
         <v>45726</v>
       </c>
       <c r="C298" t="n">
-        <v>95.64208221435547</v>
+        <v>95.64208984375</v>
       </c>
       <c r="D298" t="n">
-        <v>95.65160750692509</v>
+        <v>95.65161513707946</v>
       </c>
       <c r="E298" t="n">
-        <v>95.64208221435547</v>
+        <v>95.64208984375</v>
       </c>
       <c r="F298" t="n">
-        <v>95.65160750692509</v>
+        <v>95.65161513707946</v>
       </c>
       <c r="G298" t="n">
         <v>14768100</v>
@@ -7303,16 +7303,16 @@
         <v>45727</v>
       </c>
       <c r="C299" t="n">
-        <v>95.6611328125</v>
+        <v>95.66111755371094</v>
       </c>
       <c r="D299" t="n">
-        <v>95.6611328125</v>
+        <v>95.66111755371094</v>
       </c>
       <c r="E299" t="n">
-        <v>95.65161478487556</v>
+        <v>95.65159952760472</v>
       </c>
       <c r="F299" t="n">
-        <v>95.65161478487556</v>
+        <v>95.65159952760472</v>
       </c>
       <c r="G299" t="n">
         <v>11456900</v>
@@ -7326,16 +7326,16 @@
         <v>45728</v>
       </c>
       <c r="C300" t="n">
-        <v>95.6611328125</v>
+        <v>95.66111755371094</v>
       </c>
       <c r="D300" t="n">
-        <v>95.67065810579437</v>
+        <v>95.67064284548596</v>
       </c>
       <c r="E300" t="n">
-        <v>95.6611328125</v>
+        <v>95.66111755371094</v>
       </c>
       <c r="F300" t="n">
-        <v>95.67065810579437</v>
+        <v>95.67064284548596</v>
       </c>
       <c r="G300" t="n">
         <v>11307300</v>
@@ -7349,16 +7349,16 @@
         <v>45729</v>
       </c>
       <c r="C301" t="n">
-        <v>95.68971252441406</v>
+        <v>95.689697265625</v>
       </c>
       <c r="D301" t="n">
-        <v>95.68971252441406</v>
+        <v>95.689697265625</v>
       </c>
       <c r="E301" t="n">
-        <v>95.67066193706239</v>
+        <v>95.67064668131115</v>
       </c>
       <c r="F301" t="n">
-        <v>95.67066193706239</v>
+        <v>95.67064668131115</v>
       </c>
       <c r="G301" t="n">
         <v>13110600</v>
@@ -7395,16 +7395,16 @@
         <v>45733</v>
       </c>
       <c r="C303" t="n">
-        <v>95.72777557373047</v>
+        <v>95.72779083251953</v>
       </c>
       <c r="D303" t="n">
-        <v>95.72777557373047</v>
+        <v>95.72779083251953</v>
       </c>
       <c r="E303" t="n">
-        <v>95.71825754807078</v>
+        <v>95.71827280534269</v>
       </c>
       <c r="F303" t="n">
-        <v>95.72777557373047</v>
+        <v>95.72779083251953</v>
       </c>
       <c r="G303" t="n">
         <v>9018300</v>
@@ -7418,16 +7418,16 @@
         <v>45734</v>
       </c>
       <c r="C304" t="n">
-        <v>95.73731994628906</v>
+        <v>95.7373046875</v>
       </c>
       <c r="D304" t="n">
-        <v>95.73731994628906</v>
+        <v>95.7373046875</v>
       </c>
       <c r="E304" t="n">
-        <v>95.72779465306246</v>
+        <v>95.72777939579156</v>
       </c>
       <c r="F304" t="n">
-        <v>95.73731994628906</v>
+        <v>95.7373046875</v>
       </c>
       <c r="G304" t="n">
         <v>9213100</v>
@@ -7487,16 +7487,16 @@
         <v>45737</v>
       </c>
       <c r="C307" t="n">
-        <v>95.78495025634766</v>
+        <v>95.78492736816406</v>
       </c>
       <c r="D307" t="n">
-        <v>95.79446828500832</v>
+        <v>95.79444539455035</v>
       </c>
       <c r="E307" t="n">
-        <v>95.78495025634766</v>
+        <v>95.78492736816406</v>
       </c>
       <c r="F307" t="n">
-        <v>95.79446828500832</v>
+        <v>95.79444539455035</v>
       </c>
       <c r="G307" t="n">
         <v>13101800</v>
@@ -7510,16 +7510,16 @@
         <v>45740</v>
       </c>
       <c r="C308" t="n">
-        <v>95.80398559570312</v>
+        <v>95.80397796630859</v>
       </c>
       <c r="D308" t="n">
-        <v>95.81351088924075</v>
+        <v>95.81350325908767</v>
       </c>
       <c r="E308" t="n">
-        <v>95.80398559570312</v>
+        <v>95.80397796630859</v>
       </c>
       <c r="F308" t="n">
-        <v>95.80875187530701</v>
+        <v>95.80874424553291</v>
       </c>
       <c r="G308" t="n">
         <v>13854600</v>
@@ -7533,16 +7533,16 @@
         <v>45741</v>
       </c>
       <c r="C309" t="n">
-        <v>95.81350708007812</v>
+        <v>95.81349945068359</v>
       </c>
       <c r="D309" t="n">
-        <v>95.81350708007812</v>
+        <v>95.81349945068359</v>
       </c>
       <c r="E309" t="n">
-        <v>95.80398178691919</v>
+        <v>95.80397415828314</v>
       </c>
       <c r="F309" t="n">
-        <v>95.81350708007812</v>
+        <v>95.81349945068359</v>
       </c>
       <c r="G309" t="n">
         <v>13844800</v>
@@ -7602,16 +7602,16 @@
         <v>45744</v>
       </c>
       <c r="C312" t="n">
-        <v>95.87063598632812</v>
+        <v>95.87062835693359</v>
       </c>
       <c r="D312" t="n">
-        <v>95.87063598632812</v>
+        <v>95.87062835693359</v>
       </c>
       <c r="E312" t="n">
-        <v>95.86111795966518</v>
+        <v>95.86111033102809</v>
       </c>
       <c r="F312" t="n">
-        <v>95.86111795966518</v>
+        <v>95.86111033102809</v>
       </c>
       <c r="G312" t="n">
         <v>11747100</v>
@@ -7625,16 +7625,16 @@
         <v>45747</v>
       </c>
       <c r="C313" t="n">
-        <v>95.87063598632812</v>
+        <v>95.87062835693359</v>
       </c>
       <c r="D313" t="n">
-        <v>95.88016127866028</v>
+        <v>95.88015364850773</v>
       </c>
       <c r="E313" t="n">
-        <v>95.87063598632812</v>
+        <v>95.87062835693359</v>
       </c>
       <c r="F313" t="n">
-        <v>95.87063598632812</v>
+        <v>95.87062835693359</v>
       </c>
       <c r="G313" t="n">
         <v>18210800</v>
@@ -7648,16 +7648,16 @@
         <v>45748</v>
       </c>
       <c r="C314" t="n">
-        <v>95.89547729492188</v>
+        <v>95.89549255371094</v>
       </c>
       <c r="D314" t="n">
-        <v>95.89547729492188</v>
+        <v>95.89549255371094</v>
       </c>
       <c r="E314" t="n">
-        <v>95.88591915199837</v>
+        <v>95.88593440926654</v>
       </c>
       <c r="F314" t="n">
-        <v>95.89547729492188</v>
+        <v>95.89549255371094</v>
       </c>
       <c r="G314" t="n">
         <v>21033200</v>
@@ -7694,16 +7694,16 @@
         <v>45750</v>
       </c>
       <c r="C316" t="n">
-        <v>95.92414855957031</v>
+        <v>95.92415618896484</v>
       </c>
       <c r="D316" t="n">
-        <v>95.92414855957031</v>
+        <v>95.92415618896484</v>
       </c>
       <c r="E316" t="n">
-        <v>95.90503956362811</v>
+        <v>95.90504719150279</v>
       </c>
       <c r="F316" t="n">
-        <v>95.91459770696281</v>
+        <v>95.9146053355977</v>
       </c>
       <c r="G316" t="n">
         <v>13988800</v>
@@ -7740,16 +7740,16 @@
         <v>45754</v>
       </c>
       <c r="C318" t="n">
-        <v>95.96237945556641</v>
+        <v>95.96237182617188</v>
       </c>
       <c r="D318" t="n">
-        <v>95.96237945556641</v>
+        <v>95.96237182617188</v>
       </c>
       <c r="E318" t="n">
-        <v>95.95282860240022</v>
+        <v>95.95282097376501</v>
       </c>
       <c r="F318" t="n">
-        <v>95.95282860240022</v>
+        <v>95.95282097376501</v>
       </c>
       <c r="G318" t="n">
         <v>22564000</v>
@@ -7763,16 +7763,16 @@
         <v>45755</v>
       </c>
       <c r="C319" t="n">
-        <v>95.96237945556641</v>
+        <v>95.96237182617188</v>
       </c>
       <c r="D319" t="n">
-        <v>95.97193759946022</v>
+        <v>95.97192996930578</v>
       </c>
       <c r="E319" t="n">
-        <v>95.95282860240022</v>
+        <v>95.95282097376501</v>
       </c>
       <c r="F319" t="n">
-        <v>95.95760402898331</v>
+        <v>95.95759639996845</v>
       </c>
       <c r="G319" t="n">
         <v>17116100</v>
@@ -7786,16 +7786,16 @@
         <v>45756</v>
       </c>
       <c r="C320" t="n">
-        <v>95.98149108886719</v>
+        <v>95.98150634765625</v>
       </c>
       <c r="D320" t="n">
-        <v>95.98149108886719</v>
+        <v>95.98150634765625</v>
       </c>
       <c r="E320" t="n">
-        <v>95.97193294543689</v>
+        <v>95.97194820270643</v>
       </c>
       <c r="F320" t="n">
-        <v>95.97193294543689</v>
+        <v>95.97194820270643</v>
       </c>
       <c r="G320" t="n">
         <v>21838800</v>
@@ -7809,16 +7809,16 @@
         <v>45757</v>
       </c>
       <c r="C321" t="n">
-        <v>95.98149108886719</v>
+        <v>95.98150634765625</v>
       </c>
       <c r="D321" t="n">
-        <v>95.99104194157023</v>
+        <v>95.99105720187765</v>
       </c>
       <c r="E321" t="n">
-        <v>95.98149108886719</v>
+        <v>95.98150634765625</v>
       </c>
       <c r="F321" t="n">
-        <v>95.98149108886719</v>
+        <v>95.98150634765625</v>
       </c>
       <c r="G321" t="n">
         <v>16851500</v>
@@ -7832,16 +7832,16 @@
         <v>45758</v>
       </c>
       <c r="C322" t="n">
-        <v>96.02925872802734</v>
+        <v>96.02926635742188</v>
       </c>
       <c r="D322" t="n">
-        <v>96.02925872802734</v>
+        <v>96.02926635742188</v>
       </c>
       <c r="E322" t="n">
-        <v>96.01970787616935</v>
+        <v>96.01971550480508</v>
       </c>
       <c r="F322" t="n">
-        <v>96.02448330209835</v>
+        <v>96.02449093111348</v>
       </c>
       <c r="G322" t="n">
         <v>12916600</v>
@@ -7855,16 +7855,16 @@
         <v>45761</v>
       </c>
       <c r="C323" t="n">
-        <v>96.038818359375</v>
+        <v>96.03882598876953</v>
       </c>
       <c r="D323" t="n">
-        <v>96.038818359375</v>
+        <v>96.03882598876953</v>
       </c>
       <c r="E323" t="n">
-        <v>96.02926021664223</v>
+        <v>96.02926784527745</v>
       </c>
       <c r="F323" t="n">
-        <v>96.02926021664223</v>
+        <v>96.02926784527745</v>
       </c>
       <c r="G323" t="n">
         <v>13772300</v>
@@ -7878,16 +7878,16 @@
         <v>45762</v>
       </c>
       <c r="C324" t="n">
-        <v>96.04839324951172</v>
+        <v>96.04838562011719</v>
       </c>
       <c r="D324" t="n">
-        <v>96.04839324951172</v>
+        <v>96.04838562011719</v>
       </c>
       <c r="E324" t="n">
-        <v>96.03883510511234</v>
+        <v>96.03882747647705</v>
       </c>
       <c r="F324" t="n">
-        <v>96.04839324951172</v>
+        <v>96.04838562011719</v>
       </c>
       <c r="G324" t="n">
         <v>10043700</v>
@@ -7901,16 +7901,16 @@
         <v>45763</v>
       </c>
       <c r="C325" t="n">
-        <v>96.06749725341797</v>
+        <v>96.06748199462891</v>
       </c>
       <c r="D325" t="n">
-        <v>96.06749725341797</v>
+        <v>96.06748199462891</v>
       </c>
       <c r="E325" t="n">
-        <v>96.05793910951549</v>
+        <v>96.05792385224458</v>
       </c>
       <c r="F325" t="n">
-        <v>96.06272182683053</v>
+        <v>96.06270656879997</v>
       </c>
       <c r="G325" t="n">
         <v>8840000</v>
@@ -7924,16 +7924,16 @@
         <v>45764</v>
       </c>
       <c r="C326" t="n">
-        <v>96.10572052001953</v>
+        <v>96.10572814941406</v>
       </c>
       <c r="D326" t="n">
-        <v>96.11527866372128</v>
+        <v>96.11528629387459</v>
       </c>
       <c r="E326" t="n">
-        <v>96.10572052001953</v>
+        <v>96.10572814941406</v>
       </c>
       <c r="F326" t="n">
-        <v>96.11049594650667</v>
+        <v>96.11050357628031</v>
       </c>
       <c r="G326" t="n">
         <v>8652700</v>
@@ -7947,16 +7947,16 @@
         <v>45768</v>
       </c>
       <c r="C327" t="n">
-        <v>96.10572052001953</v>
+        <v>96.10572814941406</v>
       </c>
       <c r="D327" t="n">
-        <v>96.11527866372128</v>
+        <v>96.11528629387459</v>
       </c>
       <c r="E327" t="n">
-        <v>96.10572052001953</v>
+        <v>96.10572814941406</v>
       </c>
       <c r="F327" t="n">
-        <v>96.11527866372128</v>
+        <v>96.11528629387459</v>
       </c>
       <c r="G327" t="n">
         <v>10756100</v>
@@ -7970,16 +7970,16 @@
         <v>45769</v>
       </c>
       <c r="C328" t="n">
-        <v>96.11529541015625</v>
+        <v>96.11528778076172</v>
       </c>
       <c r="D328" t="n">
-        <v>96.12484626479461</v>
+        <v>96.12483863464196</v>
       </c>
       <c r="E328" t="n">
-        <v>96.11529541015625</v>
+        <v>96.11528778076172</v>
       </c>
       <c r="F328" t="n">
-        <v>96.12484626479461</v>
+        <v>96.12483863464196</v>
       </c>
       <c r="G328" t="n">
         <v>11603400</v>
@@ -7993,16 +7993,16 @@
         <v>45770</v>
       </c>
       <c r="C329" t="n">
-        <v>96.14395904541016</v>
+        <v>96.14394378662109</v>
       </c>
       <c r="D329" t="n">
-        <v>96.14395904541016</v>
+        <v>96.14394378662109</v>
       </c>
       <c r="E329" t="n">
-        <v>96.12484275537388</v>
+        <v>96.12482749961872</v>
       </c>
       <c r="F329" t="n">
-        <v>96.13440090039201</v>
+        <v>96.13438564311991</v>
       </c>
       <c r="G329" t="n">
         <v>19135100</v>
@@ -8016,16 +8016,16 @@
         <v>45771</v>
       </c>
       <c r="C330" t="n">
-        <v>96.14395904541016</v>
+        <v>96.14394378662109</v>
       </c>
       <c r="D330" t="n">
-        <v>96.15351719042829</v>
+        <v>96.15350193012229</v>
       </c>
       <c r="E330" t="n">
-        <v>96.14395904541016</v>
+        <v>96.14394378662109</v>
       </c>
       <c r="F330" t="n">
-        <v>96.15351719042829</v>
+        <v>96.15350193012229</v>
       </c>
       <c r="G330" t="n">
         <v>12068700</v>
@@ -8039,16 +8039,16 @@
         <v>45772</v>
       </c>
       <c r="C331" t="n">
-        <v>96.18217468261719</v>
+        <v>96.18218231201172</v>
       </c>
       <c r="D331" t="n">
-        <v>96.18217468261719</v>
+        <v>96.18218231201172</v>
       </c>
       <c r="E331" t="n">
-        <v>96.17261653855823</v>
+        <v>96.17262416719458</v>
       </c>
       <c r="F331" t="n">
-        <v>96.18217468261719</v>
+        <v>96.18218231201172</v>
       </c>
       <c r="G331" t="n">
         <v>8822700</v>
@@ -8062,16 +8062,16 @@
         <v>45775</v>
       </c>
       <c r="C332" t="n">
-        <v>96.18217468261719</v>
+        <v>96.18218231201172</v>
       </c>
       <c r="D332" t="n">
-        <v>96.19173282667613</v>
+        <v>96.19174045682885</v>
       </c>
       <c r="E332" t="n">
-        <v>96.18217468261719</v>
+        <v>96.18218231201172</v>
       </c>
       <c r="F332" t="n">
-        <v>96.18217468261719</v>
+        <v>96.18218231201172</v>
       </c>
       <c r="G332" t="n">
         <v>9127900</v>
@@ -8085,16 +8085,16 @@
         <v>45776</v>
       </c>
       <c r="C333" t="n">
-        <v>96.19173431396484</v>
+        <v>96.19174194335938</v>
       </c>
       <c r="D333" t="n">
-        <v>96.20128516744374</v>
+        <v>96.2012927975958</v>
       </c>
       <c r="E333" t="n">
-        <v>96.19173431396484</v>
+        <v>96.19174194335938</v>
       </c>
       <c r="F333" t="n">
-        <v>96.19173431396484</v>
+        <v>96.19174194335938</v>
       </c>
       <c r="G333" t="n">
         <v>8555000</v>
@@ -8108,16 +8108,16 @@
         <v>45777</v>
       </c>
       <c r="C334" t="n">
-        <v>96.22039031982422</v>
+        <v>96.22041320800781</v>
       </c>
       <c r="D334" t="n">
-        <v>96.22039031982422</v>
+        <v>96.22041320800781</v>
       </c>
       <c r="E334" t="n">
-        <v>96.20127403362315</v>
+        <v>96.20129691725951</v>
       </c>
       <c r="F334" t="n">
-        <v>96.20127403362315</v>
+        <v>96.20129691725951</v>
       </c>
       <c r="G334" t="n">
         <v>16040200</v>
@@ -8131,16 +8131,16 @@
         <v>45778</v>
       </c>
       <c r="C335" t="n">
-        <v>96.23479461669922</v>
+        <v>96.23478698730469</v>
       </c>
       <c r="D335" t="n">
-        <v>96.23479461669922</v>
+        <v>96.23478698730469</v>
       </c>
       <c r="E335" t="n">
-        <v>96.22520456489561</v>
+        <v>96.22519693626137</v>
       </c>
       <c r="F335" t="n">
-        <v>96.23479461669922</v>
+        <v>96.23478698730469</v>
       </c>
       <c r="G335" t="n">
         <v>21288700</v>
@@ -8154,16 +8154,16 @@
         <v>45779</v>
       </c>
       <c r="C336" t="n">
-        <v>96.26357269287109</v>
+        <v>96.26355743408203</v>
       </c>
       <c r="D336" t="n">
-        <v>96.26357269287109</v>
+        <v>96.26355743408203</v>
       </c>
       <c r="E336" t="n">
-        <v>96.25398263954965</v>
+        <v>96.25396738228072</v>
       </c>
       <c r="F336" t="n">
-        <v>96.25398263954965</v>
+        <v>96.25396738228072</v>
       </c>
       <c r="G336" t="n">
         <v>13930900</v>
@@ -8177,16 +8177,16 @@
         <v>45782</v>
       </c>
       <c r="C337" t="n">
-        <v>96.27313995361328</v>
+        <v>96.27313232421875</v>
       </c>
       <c r="D337" t="n">
-        <v>96.27313995361328</v>
+        <v>96.27313232421875</v>
       </c>
       <c r="E337" t="n">
-        <v>96.26354990256227</v>
+        <v>96.26354227392774</v>
       </c>
       <c r="F337" t="n">
-        <v>96.27313995361328</v>
+        <v>96.27313232421875</v>
       </c>
       <c r="G337" t="n">
         <v>13223700</v>
@@ -8200,16 +8200,16 @@
         <v>45783</v>
       </c>
       <c r="C338" t="n">
-        <v>96.27313995361328</v>
+        <v>96.27313232421875</v>
       </c>
       <c r="D338" t="n">
-        <v>96.28272268959864</v>
+        <v>96.28271505944471</v>
       </c>
       <c r="E338" t="n">
-        <v>96.27313995361328</v>
+        <v>96.27313232421875</v>
       </c>
       <c r="F338" t="n">
-        <v>96.28272268959864</v>
+        <v>96.28271505944471</v>
       </c>
       <c r="G338" t="n">
         <v>8986000</v>
@@ -8223,16 +8223,16 @@
         <v>45784</v>
       </c>
       <c r="C339" t="n">
-        <v>96.28272247314453</v>
+        <v>96.28273010253906</v>
       </c>
       <c r="D339" t="n">
-        <v>96.29231252417398</v>
+        <v>96.29232015432841</v>
       </c>
       <c r="E339" t="n">
-        <v>96.28272247314453</v>
+        <v>96.28273010253906</v>
       </c>
       <c r="F339" t="n">
-        <v>96.29231252417398</v>
+        <v>96.29232015432841</v>
       </c>
       <c r="G339" t="n">
         <v>8509300</v>
@@ -8246,16 +8246,16 @@
         <v>45785</v>
       </c>
       <c r="C340" t="n">
-        <v>96.31147766113281</v>
+        <v>96.31148529052734</v>
       </c>
       <c r="D340" t="n">
-        <v>96.31147766113281</v>
+        <v>96.31148529052734</v>
       </c>
       <c r="E340" t="n">
-        <v>96.29230487566245</v>
+        <v>96.29231250353818</v>
       </c>
       <c r="F340" t="n">
-        <v>96.30189492593016</v>
+        <v>96.30190255456557</v>
       </c>
       <c r="G340" t="n">
         <v>11931100</v>
@@ -8315,16 +8315,16 @@
         <v>45790</v>
       </c>
       <c r="C343" t="n">
-        <v>96.35941314697266</v>
+        <v>96.35942077636719</v>
       </c>
       <c r="D343" t="n">
-        <v>96.35941314697266</v>
+        <v>96.35942077636719</v>
       </c>
       <c r="E343" t="n">
-        <v>96.34982309744645</v>
+        <v>96.34983072608168</v>
       </c>
       <c r="F343" t="n">
-        <v>96.34982309744645</v>
+        <v>96.34983072608168</v>
       </c>
       <c r="G343" t="n">
         <v>18174400</v>
@@ -8453,16 +8453,16 @@
         <v>45798</v>
       </c>
       <c r="C349" t="n">
-        <v>96.44570922851562</v>
+        <v>96.44571685791016</v>
       </c>
       <c r="D349" t="n">
-        <v>96.44570922851562</v>
+        <v>96.44571685791016</v>
       </c>
       <c r="E349" t="n">
-        <v>96.43612649330065</v>
+        <v>96.43613412193713</v>
       </c>
       <c r="F349" t="n">
-        <v>96.44570922851562</v>
+        <v>96.44571685791016</v>
       </c>
       <c r="G349" t="n">
         <v>11325900</v>
@@ -8476,16 +8476,16 @@
         <v>45799</v>
       </c>
       <c r="C350" t="n">
-        <v>96.46488952636719</v>
+        <v>96.46489715576172</v>
       </c>
       <c r="D350" t="n">
-        <v>96.46488952636719</v>
+        <v>96.46489715576172</v>
       </c>
       <c r="E350" t="n">
-        <v>96.45529947606755</v>
+        <v>96.45530710470361</v>
       </c>
       <c r="F350" t="n">
-        <v>96.45529947606755</v>
+        <v>96.45530710470361</v>
       </c>
       <c r="G350" t="n">
         <v>8901700</v>
@@ -8499,16 +8499,16 @@
         <v>45800</v>
       </c>
       <c r="C351" t="n">
-        <v>96.49365234375</v>
+        <v>96.49364471435547</v>
       </c>
       <c r="D351" t="n">
-        <v>96.5032423940478</v>
+        <v>96.50323476389502</v>
       </c>
       <c r="E351" t="n">
-        <v>96.49365234375</v>
+        <v>96.49364471435547</v>
       </c>
       <c r="F351" t="n">
-        <v>96.5032423940478</v>
+        <v>96.50323476389502</v>
       </c>
       <c r="G351" t="n">
         <v>9119400</v>
@@ -8591,16 +8591,16 @@
         <v>45807</v>
       </c>
       <c r="C355" t="n">
-        <v>96.56076049804688</v>
+        <v>96.56076812744141</v>
       </c>
       <c r="D355" t="n">
-        <v>96.57035054759308</v>
+        <v>96.57035817774533</v>
       </c>
       <c r="E355" t="n">
-        <v>96.56076049804688</v>
+        <v>96.56076812744141</v>
       </c>
       <c r="F355" t="n">
-        <v>96.56076049804688</v>
+        <v>96.56076812744141</v>
       </c>
       <c r="G355" t="n">
         <v>14209500</v>
@@ -8614,16 +8614,16 @@
         <v>45810</v>
       </c>
       <c r="C356" t="n">
-        <v>96.58769989013672</v>
+        <v>96.58770751953125</v>
       </c>
       <c r="D356" t="n">
-        <v>96.58769989013672</v>
+        <v>96.58770751953125</v>
       </c>
       <c r="E356" t="n">
-        <v>96.57808296990129</v>
+        <v>96.57809059853618</v>
       </c>
       <c r="F356" t="n">
-        <v>96.58769989013672</v>
+        <v>96.58770751953125</v>
       </c>
       <c r="G356" t="n">
         <v>21934000</v>
@@ -8637,16 +8637,16 @@
         <v>45811</v>
       </c>
       <c r="C357" t="n">
-        <v>96.59732818603516</v>
+        <v>96.59734344482422</v>
       </c>
       <c r="D357" t="n">
-        <v>96.59732818603516</v>
+        <v>96.59734344482422</v>
       </c>
       <c r="E357" t="n">
-        <v>96.58770392423726</v>
+        <v>96.58771918150605</v>
       </c>
       <c r="F357" t="n">
-        <v>96.5925197257166</v>
+        <v>96.59253498374611</v>
       </c>
       <c r="G357" t="n">
         <v>11979500</v>
@@ -8660,16 +8660,16 @@
         <v>45812</v>
       </c>
       <c r="C358" t="n">
-        <v>96.60697174072266</v>
+        <v>96.60696411132812</v>
       </c>
       <c r="D358" t="n">
-        <v>96.60697174072266</v>
+        <v>96.60696411132812</v>
       </c>
       <c r="E358" t="n">
-        <v>96.59734747700276</v>
+        <v>96.59733984836828</v>
       </c>
       <c r="F358" t="n">
-        <v>96.60215593828157</v>
+        <v>96.60214830926736</v>
       </c>
       <c r="G358" t="n">
         <v>8923800</v>
@@ -8683,16 +8683,16 @@
         <v>45813</v>
       </c>
       <c r="C359" t="n">
-        <v>96.61659240722656</v>
+        <v>96.61660003662109</v>
       </c>
       <c r="D359" t="n">
-        <v>96.61659240722656</v>
+        <v>96.61660003662109</v>
       </c>
       <c r="E359" t="n">
-        <v>96.60696814386499</v>
+        <v>96.60697577249954</v>
       </c>
       <c r="F359" t="n">
-        <v>96.61659240722656</v>
+        <v>96.61660003662109</v>
       </c>
       <c r="G359" t="n">
         <v>9915800</v>
@@ -8706,16 +8706,16 @@
         <v>45814</v>
       </c>
       <c r="C360" t="n">
-        <v>96.64545440673828</v>
+        <v>96.64544677734375</v>
       </c>
       <c r="D360" t="n">
-        <v>96.65507132859463</v>
+        <v>96.65506369844093</v>
       </c>
       <c r="E360" t="n">
-        <v>96.64545440673828</v>
+        <v>96.64544677734375</v>
       </c>
       <c r="F360" t="n">
-        <v>96.65026286766646</v>
+        <v>96.65025523789234</v>
       </c>
       <c r="G360" t="n">
         <v>9122400</v>
@@ -8752,16 +8752,16 @@
         <v>45818</v>
       </c>
       <c r="C362" t="n">
-        <v>96.66469573974609</v>
+        <v>96.66468048095703</v>
       </c>
       <c r="D362" t="n">
-        <v>96.67432000277891</v>
+        <v>96.67430474247064</v>
       </c>
       <c r="E362" t="n">
-        <v>96.66469573974609</v>
+        <v>96.66468048095703</v>
       </c>
       <c r="F362" t="n">
-        <v>96.66950420068163</v>
+        <v>96.66948894113355</v>
       </c>
       <c r="G362" t="n">
         <v>9201800</v>
@@ -8775,16 +8775,16 @@
         <v>45819</v>
       </c>
       <c r="C363" t="n">
-        <v>96.68393707275391</v>
+        <v>96.68395233154297</v>
       </c>
       <c r="D363" t="n">
-        <v>96.68393707275391</v>
+        <v>96.68395233154297</v>
       </c>
       <c r="E363" t="n">
-        <v>96.6743128104371</v>
+        <v>96.67432806770725</v>
       </c>
       <c r="F363" t="n">
-        <v>96.67912127101491</v>
+        <v>96.67913652904394</v>
       </c>
       <c r="G363" t="n">
         <v>10138800</v>
@@ -8821,16 +8821,16 @@
         <v>45821</v>
       </c>
       <c r="C365" t="n">
-        <v>96.73204040527344</v>
+        <v>96.7320556640625</v>
       </c>
       <c r="D365" t="n">
-        <v>96.73204040527344</v>
+        <v>96.7320556640625</v>
       </c>
       <c r="E365" t="n">
-        <v>96.72241614328465</v>
+        <v>96.72243140055555</v>
       </c>
       <c r="F365" t="n">
-        <v>96.72241614328465</v>
+        <v>96.72243140055555</v>
       </c>
       <c r="G365" t="n">
         <v>7880300</v>
@@ -8844,16 +8844,16 @@
         <v>45824</v>
       </c>
       <c r="C366" t="n">
-        <v>96.73204040527344</v>
+        <v>96.7320556640625</v>
       </c>
       <c r="D366" t="n">
-        <v>96.74166466726223</v>
+        <v>96.74167992756945</v>
       </c>
       <c r="E366" t="n">
-        <v>96.73204040527344</v>
+        <v>96.7320556640625</v>
       </c>
       <c r="F366" t="n">
-        <v>96.74166466726223</v>
+        <v>96.74167992756945</v>
       </c>
       <c r="G366" t="n">
         <v>10286500</v>
@@ -8890,16 +8890,16 @@
         <v>45826</v>
       </c>
       <c r="C368" t="n">
-        <v>96.76091766357422</v>
+        <v>96.76091003417969</v>
       </c>
       <c r="D368" t="n">
-        <v>96.77054192673803</v>
+        <v>96.77053429658464</v>
       </c>
       <c r="E368" t="n">
-        <v>96.76091766357422</v>
+        <v>96.76091003417969</v>
       </c>
       <c r="F368" t="n">
-        <v>96.77054192673803</v>
+        <v>96.77053429658464</v>
       </c>
       <c r="G368" t="n">
         <v>9783400</v>
@@ -8913,16 +8913,16 @@
         <v>45828</v>
       </c>
       <c r="C369" t="n">
-        <v>96.79940032958984</v>
+        <v>96.79940795898438</v>
       </c>
       <c r="D369" t="n">
-        <v>96.80902459205316</v>
+        <v>96.80903222220624</v>
       </c>
       <c r="E369" t="n">
-        <v>96.79940032958984</v>
+        <v>96.79940795898438</v>
       </c>
       <c r="F369" t="n">
-        <v>96.80421613140216</v>
+        <v>96.80422376117625</v>
       </c>
       <c r="G369" t="n">
         <v>9399400</v>
@@ -8936,16 +8936,16 @@
         <v>45831</v>
       </c>
       <c r="C370" t="n">
-        <v>96.81864166259766</v>
+        <v>96.81865692138672</v>
       </c>
       <c r="D370" t="n">
-        <v>96.81864166259766</v>
+        <v>96.81865692138672</v>
       </c>
       <c r="E370" t="n">
-        <v>96.80901740084924</v>
+        <v>96.80903265812152</v>
       </c>
       <c r="F370" t="n">
-        <v>96.81382586114307</v>
+        <v>96.81384111917316</v>
       </c>
       <c r="G370" t="n">
         <v>8847300</v>
@@ -8959,16 +8959,16 @@
         <v>45832</v>
       </c>
       <c r="C371" t="n">
-        <v>96.82827758789062</v>
+        <v>96.82826232910156</v>
       </c>
       <c r="D371" t="n">
-        <v>96.837901851528</v>
+        <v>96.8378865912223</v>
       </c>
       <c r="E371" t="n">
-        <v>96.82827758789062</v>
+        <v>96.82826232910156</v>
       </c>
       <c r="F371" t="n">
-        <v>96.83309339029041</v>
+        <v>96.83307813074245</v>
       </c>
       <c r="G371" t="n">
         <v>10132100</v>
@@ -8982,16 +8982,16 @@
         <v>45833</v>
       </c>
       <c r="C372" t="n">
-        <v>96.837890625</v>
+        <v>96.83788299560547</v>
       </c>
       <c r="D372" t="n">
-        <v>96.84751488752164</v>
+        <v>96.84750725736885</v>
       </c>
       <c r="E372" t="n">
-        <v>96.837890625</v>
+        <v>96.83788299560547</v>
       </c>
       <c r="F372" t="n">
-        <v>96.84269908568015</v>
+        <v>96.84269145590677</v>
       </c>
       <c r="G372" t="n">
         <v>8015100</v>
@@ -9120,16 +9120,16 @@
         <v>45841</v>
       </c>
       <c r="C378" t="n">
-        <v>96.96036529541016</v>
+        <v>96.96035003662109</v>
       </c>
       <c r="D378" t="n">
-        <v>96.9700228417189</v>
+        <v>96.97000758141002</v>
       </c>
       <c r="E378" t="n">
-        <v>96.96036529541016</v>
+        <v>96.96035003662109</v>
       </c>
       <c r="F378" t="n">
-        <v>96.96036529541016</v>
+        <v>96.96035003662109</v>
       </c>
       <c r="G378" t="n">
         <v>7404700</v>
@@ -9143,16 +9143,16 @@
         <v>45845</v>
       </c>
       <c r="C379" t="n">
-        <v>96.97965240478516</v>
+        <v>96.97966003417969</v>
       </c>
       <c r="D379" t="n">
-        <v>96.97965240478516</v>
+        <v>96.97966003417969</v>
       </c>
       <c r="E379" t="n">
-        <v>96.96999486126307</v>
+        <v>96.97000248989785</v>
       </c>
       <c r="F379" t="n">
-        <v>96.97965240478516</v>
+        <v>96.97966003417969</v>
       </c>
       <c r="G379" t="n">
         <v>12363900</v>
@@ -9166,16 +9166,16 @@
         <v>45846</v>
       </c>
       <c r="C380" t="n">
-        <v>96.99897003173828</v>
+        <v>96.99896240234375</v>
       </c>
       <c r="D380" t="n">
-        <v>96.99897003173828</v>
+        <v>96.99896240234375</v>
       </c>
       <c r="E380" t="n">
-        <v>96.97966230926953</v>
+        <v>96.97965468139364</v>
       </c>
       <c r="F380" t="n">
-        <v>96.98931248722988</v>
+        <v>96.98930485859495</v>
       </c>
       <c r="G380" t="n">
         <v>13107800</v>
@@ -9212,16 +9212,16 @@
         <v>45848</v>
       </c>
       <c r="C382" t="n">
-        <v>97.00861358642578</v>
+        <v>97.00862884521484</v>
       </c>
       <c r="D382" t="n">
-        <v>97.01827112954146</v>
+        <v>97.01828638984958</v>
       </c>
       <c r="E382" t="n">
-        <v>96.99895604331012</v>
+        <v>96.99897130058011</v>
       </c>
       <c r="F382" t="n">
-        <v>97.00861358642578</v>
+        <v>97.00862884521484</v>
       </c>
       <c r="G382" t="n">
         <v>10071700</v>
@@ -9304,16 +9304,16 @@
         <v>45854</v>
       </c>
       <c r="C386" t="n">
-        <v>97.08586883544922</v>
+        <v>97.08586120605469</v>
       </c>
       <c r="D386" t="n">
-        <v>97.08586883544922</v>
+        <v>97.08586120605469</v>
       </c>
       <c r="E386" t="n">
-        <v>97.07621129137489</v>
+        <v>97.0762036627393</v>
       </c>
       <c r="F386" t="n">
-        <v>97.07621129137489</v>
+        <v>97.0762036627393</v>
       </c>
       <c r="G386" t="n">
         <v>8117900</v>
@@ -9327,16 +9327,16 @@
         <v>45855</v>
       </c>
       <c r="C387" t="n">
-        <v>97.09552001953125</v>
+        <v>97.09552764892578</v>
       </c>
       <c r="D387" t="n">
-        <v>97.09552001953125</v>
+        <v>97.09552764892578</v>
       </c>
       <c r="E387" t="n">
-        <v>97.08586984190462</v>
+        <v>97.08587747054088</v>
       </c>
       <c r="F387" t="n">
-        <v>97.09069493071793</v>
+        <v>97.09070255973333</v>
       </c>
       <c r="G387" t="n">
         <v>9040400</v>
@@ -9350,16 +9350,16 @@
         <v>45856</v>
       </c>
       <c r="C388" t="n">
-        <v>97.12448120117188</v>
+        <v>97.12449645996094</v>
       </c>
       <c r="D388" t="n">
-        <v>97.12448120117188</v>
+        <v>97.12449645996094</v>
       </c>
       <c r="E388" t="n">
-        <v>97.11483102395106</v>
+        <v>97.11484628122402</v>
       </c>
       <c r="F388" t="n">
-        <v>97.11483102395106</v>
+        <v>97.11484628122402</v>
       </c>
       <c r="G388" t="n">
         <v>9399500</v>
@@ -9373,16 +9373,16 @@
         <v>45859</v>
       </c>
       <c r="C389" t="n">
-        <v>97.13414001464844</v>
+        <v>97.1341552734375</v>
       </c>
       <c r="D389" t="n">
-        <v>97.13414001464844</v>
+        <v>97.1341552734375</v>
       </c>
       <c r="E389" t="n">
-        <v>97.12448247075388</v>
+        <v>97.12449772802584</v>
       </c>
       <c r="F389" t="n">
-        <v>97.12448247075388</v>
+        <v>97.12449772802584</v>
       </c>
       <c r="G389" t="n">
         <v>12893000</v>
@@ -9419,16 +9419,16 @@
         <v>45861</v>
       </c>
       <c r="C391" t="n">
-        <v>97.16310882568359</v>
+        <v>97.16311645507812</v>
       </c>
       <c r="D391" t="n">
-        <v>97.16310882568359</v>
+        <v>97.16311645507812</v>
       </c>
       <c r="E391" t="n">
-        <v>97.15345864798445</v>
+        <v>97.15346627662124</v>
       </c>
       <c r="F391" t="n">
-        <v>97.16310882568359</v>
+        <v>97.16311645507812</v>
       </c>
       <c r="G391" t="n">
         <v>8056100</v>
@@ -9442,16 +9442,16 @@
         <v>45862</v>
       </c>
       <c r="C392" t="n">
-        <v>97.17277526855469</v>
+        <v>97.17276000976562</v>
       </c>
       <c r="D392" t="n">
-        <v>97.17277526855469</v>
+        <v>97.17276000976562</v>
       </c>
       <c r="E392" t="n">
-        <v>97.1631177234233</v>
+        <v>97.16310246615073</v>
       </c>
       <c r="F392" t="n">
-        <v>97.1631177234233</v>
+        <v>97.16310246615073</v>
       </c>
       <c r="G392" t="n">
         <v>10701600</v>
@@ -9488,16 +9488,16 @@
         <v>45866</v>
       </c>
       <c r="C394" t="n">
-        <v>97.22105407714844</v>
+        <v>97.22104644775391</v>
       </c>
       <c r="D394" t="n">
-        <v>97.22105407714844</v>
+        <v>97.22104644775391</v>
       </c>
       <c r="E394" t="n">
-        <v>97.21139653217107</v>
+        <v>97.21138890353441</v>
       </c>
       <c r="F394" t="n">
-        <v>97.21622162138554</v>
+        <v>97.21621399237023</v>
       </c>
       <c r="G394" t="n">
         <v>11581000</v>
@@ -9511,16 +9511,16 @@
         <v>45867</v>
       </c>
       <c r="C395" t="n">
-        <v>97.22105407714844</v>
+        <v>97.22104644775391</v>
       </c>
       <c r="D395" t="n">
-        <v>97.23070425557738</v>
+        <v>97.23069662542557</v>
       </c>
       <c r="E395" t="n">
-        <v>97.22105407714844</v>
+        <v>97.22104644775391</v>
       </c>
       <c r="F395" t="n">
-        <v>97.22105407714844</v>
+        <v>97.22104644775391</v>
       </c>
       <c r="G395" t="n">
         <v>8622300</v>
@@ -9557,16 +9557,16 @@
         <v>45869</v>
       </c>
       <c r="C397" t="n">
-        <v>97.25000762939453</v>
+        <v>97.25002288818359</v>
       </c>
       <c r="D397" t="n">
-        <v>97.25000762939453</v>
+        <v>97.25002288818359</v>
       </c>
       <c r="E397" t="n">
-        <v>97.24035008558064</v>
+        <v>97.24036534285442</v>
       </c>
       <c r="F397" t="n">
-        <v>97.24517517421383</v>
+        <v>97.24519043224467</v>
       </c>
       <c r="G397" t="n">
         <v>19051200</v>
@@ -9580,16 +9580,16 @@
         <v>45870</v>
       </c>
       <c r="C398" t="n">
-        <v>97.281005859375</v>
+        <v>97.28102874755859</v>
       </c>
       <c r="D398" t="n">
-        <v>97.29069823789037</v>
+        <v>97.29072112835438</v>
       </c>
       <c r="E398" t="n">
-        <v>97.281005859375</v>
+        <v>97.28102874755859</v>
       </c>
       <c r="F398" t="n">
-        <v>97.281005859375</v>
+        <v>97.28102874755859</v>
       </c>
       <c r="G398" t="n">
         <v>26832500</v>
@@ -9603,16 +9603,16 @@
         <v>45873</v>
       </c>
       <c r="C399" t="n">
-        <v>97.30040740966797</v>
+        <v>97.3004150390625</v>
       </c>
       <c r="D399" t="n">
-        <v>97.30040740966797</v>
+        <v>97.3004150390625</v>
       </c>
       <c r="E399" t="n">
-        <v>97.29071502947977</v>
+        <v>97.2907226581143</v>
       </c>
       <c r="F399" t="n">
-        <v>97.29555752301393</v>
+        <v>97.29556515202816</v>
       </c>
       <c r="G399" t="n">
         <v>14766400</v>
@@ -9626,16 +9626,16 @@
         <v>45874</v>
       </c>
       <c r="C400" t="n">
-        <v>97.31008148193359</v>
+        <v>97.31009674072266</v>
       </c>
       <c r="D400" t="n">
-        <v>97.31008148193359</v>
+        <v>97.31009674072266</v>
       </c>
       <c r="E400" t="n">
-        <v>97.30039649595162</v>
+        <v>97.30041175322201</v>
       </c>
       <c r="F400" t="n">
-        <v>97.30039649595162</v>
+        <v>97.30041175322201</v>
       </c>
       <c r="G400" t="n">
         <v>12350300</v>
@@ -9695,16 +9695,16 @@
         <v>45877</v>
       </c>
       <c r="C403" t="n">
-        <v>97.36824035644531</v>
+        <v>97.36824798583984</v>
       </c>
       <c r="D403" t="n">
-        <v>97.36824035644531</v>
+        <v>97.36824798583984</v>
       </c>
       <c r="E403" t="n">
-        <v>97.35854797615043</v>
+        <v>97.35855560478551</v>
       </c>
       <c r="F403" t="n">
-        <v>97.36339046973788</v>
+        <v>97.3633980987524</v>
       </c>
       <c r="G403" t="n">
         <v>12066300</v>
@@ -9718,16 +9718,16 @@
         <v>45880</v>
       </c>
       <c r="C404" t="n">
-        <v>97.37793731689453</v>
+        <v>97.3779296875</v>
       </c>
       <c r="D404" t="n">
-        <v>97.37793731689453</v>
+        <v>97.3779296875</v>
       </c>
       <c r="E404" t="n">
-        <v>97.3682523285288</v>
+        <v>97.36824469989307</v>
       </c>
       <c r="F404" t="n">
-        <v>97.37793731689453</v>
+        <v>97.3779296875</v>
       </c>
       <c r="G404" t="n">
         <v>12940300</v>
@@ -9741,16 +9741,16 @@
         <v>45881</v>
       </c>
       <c r="C405" t="n">
-        <v>97.37793731689453</v>
+        <v>97.3779296875</v>
       </c>
       <c r="D405" t="n">
-        <v>97.38762969838115</v>
+        <v>97.38762206822724</v>
       </c>
       <c r="E405" t="n">
-        <v>97.37793731689453</v>
+        <v>97.3779296875</v>
       </c>
       <c r="F405" t="n">
-        <v>97.38762969838115</v>
+        <v>97.38762206822724</v>
       </c>
       <c r="G405" t="n">
         <v>12918200</v>
@@ -9787,16 +9787,16 @@
         <v>45883</v>
       </c>
       <c r="C407" t="n">
-        <v>97.40699768066406</v>
+        <v>97.40699005126953</v>
       </c>
       <c r="D407" t="n">
-        <v>97.41669006121658</v>
+        <v>97.4166824310629</v>
       </c>
       <c r="E407" t="n">
-        <v>97.40699768066406</v>
+        <v>97.40699005126953</v>
       </c>
       <c r="F407" t="n">
-        <v>97.40699768066406</v>
+        <v>97.40699005126953</v>
       </c>
       <c r="G407" t="n">
         <v>9798900</v>
@@ -9879,16 +9879,16 @@
         <v>45889</v>
       </c>
       <c r="C411" t="n">
-        <v>97.48451232910156</v>
+        <v>97.48452758789062</v>
       </c>
       <c r="D411" t="n">
-        <v>97.48451232910156</v>
+        <v>97.48452758789062</v>
       </c>
       <c r="E411" t="n">
-        <v>97.47481994950448</v>
+        <v>97.47483520677645</v>
       </c>
       <c r="F411" t="n">
-        <v>97.48451232910156</v>
+        <v>97.48452758789062</v>
       </c>
       <c r="G411" t="n">
         <v>10922100</v>
@@ -9902,16 +9902,16 @@
         <v>45890</v>
       </c>
       <c r="C412" t="n">
-        <v>97.48451232910156</v>
+        <v>97.48452758789062</v>
       </c>
       <c r="D412" t="n">
-        <v>97.49420470869863</v>
+        <v>97.4942199690048</v>
       </c>
       <c r="E412" t="n">
-        <v>97.48451232910156</v>
+        <v>97.48452758789062</v>
       </c>
       <c r="F412" t="n">
-        <v>97.49420470869863</v>
+        <v>97.4942199690048</v>
       </c>
       <c r="G412" t="n">
         <v>8765300</v>
@@ -9925,16 +9925,16 @@
         <v>45891</v>
       </c>
       <c r="C413" t="n">
-        <v>97.52327728271484</v>
+        <v>97.52326965332031</v>
       </c>
       <c r="D413" t="n">
-        <v>97.52327728271484</v>
+        <v>97.52326965332031</v>
       </c>
       <c r="E413" t="n">
-        <v>97.51358490283667</v>
+        <v>97.51357727420039</v>
       </c>
       <c r="F413" t="n">
-        <v>97.52327728271484</v>
+        <v>97.52326965332031</v>
       </c>
       <c r="G413" t="n">
         <v>13160400</v>
@@ -9948,16 +9948,16 @@
         <v>45894</v>
       </c>
       <c r="C414" t="n">
-        <v>97.54266357421875</v>
+        <v>97.54267120361328</v>
       </c>
       <c r="D414" t="n">
-        <v>97.54266357421875</v>
+        <v>97.54267120361328</v>
       </c>
       <c r="E414" t="n">
-        <v>97.53297119418838</v>
+        <v>97.5329788228248</v>
       </c>
       <c r="F414" t="n">
-        <v>97.53781368764366</v>
+        <v>97.53782131665886</v>
       </c>
       <c r="G414" t="n">
         <v>13556000</v>
@@ -9971,16 +9971,16 @@
         <v>45895</v>
       </c>
       <c r="C415" t="n">
-        <v>97.54266357421875</v>
+        <v>97.54267120361328</v>
       </c>
       <c r="D415" t="n">
-        <v>97.55234856112934</v>
+        <v>97.55235619128139</v>
       </c>
       <c r="E415" t="n">
-        <v>97.54266357421875</v>
+        <v>97.54267120361328</v>
       </c>
       <c r="F415" t="n">
-        <v>97.54750606767405</v>
+        <v>97.54751369744734</v>
       </c>
       <c r="G415" t="n">
         <v>8741600</v>
@@ -10017,16 +10017,16 @@
         <v>45897</v>
       </c>
       <c r="C417" t="n">
-        <v>97.56203460693359</v>
+        <v>97.56204223632812</v>
       </c>
       <c r="D417" t="n">
-        <v>97.57172698633468</v>
+        <v>97.57173461648718</v>
       </c>
       <c r="E417" t="n">
-        <v>97.56203460693359</v>
+        <v>97.56204223632812</v>
       </c>
       <c r="F417" t="n">
-        <v>97.56687710007449</v>
+        <v>97.56688472984771</v>
       </c>
       <c r="G417" t="n">
         <v>8816600</v>
@@ -10063,16 +10063,16 @@
         <v>45902</v>
       </c>
       <c r="C419" t="n">
-        <v>97.62989807128906</v>
+        <v>97.62990570068359</v>
       </c>
       <c r="D419" t="n">
-        <v>97.62989807128906</v>
+        <v>97.62990570068359</v>
       </c>
       <c r="E419" t="n">
-        <v>97.62017093166746</v>
+        <v>97.62017856030185</v>
       </c>
       <c r="F419" t="n">
-        <v>97.62989807128906</v>
+        <v>97.62990570068359</v>
       </c>
       <c r="G419" t="n">
         <v>27254500</v>
@@ -10109,16 +10109,16 @@
         <v>45904</v>
       </c>
       <c r="C421" t="n">
-        <v>97.65908813476562</v>
+        <v>97.65908050537109</v>
       </c>
       <c r="D421" t="n">
-        <v>97.65908813476562</v>
+        <v>97.65908050537109</v>
       </c>
       <c r="E421" t="n">
-        <v>97.64936841317878</v>
+        <v>97.64936078454357</v>
       </c>
       <c r="F421" t="n">
-        <v>97.65422827397219</v>
+        <v>97.65422064495733</v>
       </c>
       <c r="G421" t="n">
         <v>11300200</v>
@@ -10132,16 +10132,16 @@
         <v>45905</v>
       </c>
       <c r="C422" t="n">
-        <v>97.67852783203125</v>
+        <v>97.67853546142578</v>
       </c>
       <c r="D422" t="n">
-        <v>97.68824755216677</v>
+        <v>97.68825518232049</v>
       </c>
       <c r="E422" t="n">
-        <v>97.67852783203125</v>
+        <v>97.67853546142578</v>
       </c>
       <c r="F422" t="n">
-        <v>97.68824755216677</v>
+        <v>97.68825518232049</v>
       </c>
       <c r="G422" t="n">
         <v>15312000</v>
@@ -10224,16 +10224,16 @@
         <v>45911</v>
       </c>
       <c r="C426" t="n">
-        <v>97.73689270019531</v>
+        <v>97.73688507080078</v>
       </c>
       <c r="D426" t="n">
-        <v>97.73689270019531</v>
+        <v>97.73688507080078</v>
       </c>
       <c r="E426" t="n">
-        <v>97.72716555874725</v>
+        <v>97.72715793011203</v>
       </c>
       <c r="F426" t="n">
-        <v>97.73203283928876</v>
+        <v>97.7320252102736</v>
       </c>
       <c r="G426" t="n">
         <v>9136600</v>
@@ -10247,16 +10247,16 @@
         <v>45912</v>
       </c>
       <c r="C427" t="n">
-        <v>97.76605224609375</v>
+        <v>97.76605987548828</v>
       </c>
       <c r="D427" t="n">
-        <v>97.77577938610324</v>
+        <v>97.77578701625686</v>
       </c>
       <c r="E427" t="n">
-        <v>97.76605224609375</v>
+        <v>97.76605987548828</v>
       </c>
       <c r="F427" t="n">
-        <v>97.76605224609375</v>
+        <v>97.76605987548828</v>
       </c>
       <c r="G427" t="n">
         <v>10482000</v>
@@ -10270,16 +10270,16 @@
         <v>45915</v>
       </c>
       <c r="C428" t="n">
-        <v>97.76605224609375</v>
+        <v>97.76605987548828</v>
       </c>
       <c r="D428" t="n">
-        <v>97.77577938610324</v>
+        <v>97.77578701625686</v>
       </c>
       <c r="E428" t="n">
-        <v>97.76605224609375</v>
+        <v>97.76605987548828</v>
       </c>
       <c r="F428" t="n">
-        <v>97.76605224609375</v>
+        <v>97.76605987548828</v>
       </c>
       <c r="G428" t="n">
         <v>15288300</v>
@@ -10293,16 +10293,16 @@
         <v>45916</v>
       </c>
       <c r="C429" t="n">
-        <v>97.78551483154297</v>
+        <v>97.78550720214844</v>
       </c>
       <c r="D429" t="n">
-        <v>97.79523455274413</v>
+        <v>97.79522692259125</v>
       </c>
       <c r="E429" t="n">
-        <v>97.78551483154297</v>
+        <v>97.78550720214844</v>
       </c>
       <c r="F429" t="n">
-        <v>97.78551483154297</v>
+        <v>97.78550720214844</v>
       </c>
       <c r="G429" t="n">
         <v>11551900</v>
@@ -10408,16 +10408,16 @@
         <v>45923</v>
       </c>
       <c r="C434" t="n">
-        <v>97.87301635742188</v>
+        <v>97.87302398681641</v>
       </c>
       <c r="D434" t="n">
-        <v>97.87301635742188</v>
+        <v>97.87302398681641</v>
       </c>
       <c r="E434" t="n">
-        <v>97.86328921862189</v>
+        <v>97.86329684725817</v>
       </c>
       <c r="F434" t="n">
-        <v>97.86815649783836</v>
+        <v>97.86816412685405</v>
       </c>
       <c r="G434" t="n">
         <v>11191700</v>
@@ -10454,16 +10454,16 @@
         <v>45925</v>
       </c>
       <c r="C436" t="n">
-        <v>97.89247131347656</v>
+        <v>97.89249420166016</v>
       </c>
       <c r="D436" t="n">
-        <v>97.89247131347656</v>
+        <v>97.89249420166016</v>
       </c>
       <c r="E436" t="n">
-        <v>97.88274417460916</v>
+        <v>97.88276706051846</v>
       </c>
       <c r="F436" t="n">
-        <v>97.88274417460916</v>
+        <v>97.88276706051846</v>
       </c>
       <c r="G436" t="n">
         <v>10549100</v>
@@ -10569,16 +10569,16 @@
         <v>45932</v>
       </c>
       <c r="C441" t="n">
-        <v>97.95771789550781</v>
+        <v>97.95772552490234</v>
       </c>
       <c r="D441" t="n">
-        <v>97.96747866922793</v>
+        <v>97.96748629938267</v>
       </c>
       <c r="E441" t="n">
-        <v>97.95771789550781</v>
+        <v>97.95772552490234</v>
       </c>
       <c r="F441" t="n">
-        <v>97.96747866922793</v>
+        <v>97.96748629938267</v>
       </c>
       <c r="G441" t="n">
         <v>12870100</v>
@@ -10592,16 +10592,16 @@
         <v>45933</v>
       </c>
       <c r="C442" t="n">
-        <v>97.99677276611328</v>
+        <v>97.99676513671875</v>
       </c>
       <c r="D442" t="n">
-        <v>97.99677276611328</v>
+        <v>97.99676513671875</v>
       </c>
       <c r="E442" t="n">
-        <v>97.98701943576903</v>
+        <v>97.98701180713383</v>
       </c>
       <c r="F442" t="n">
-        <v>97.99677276611328</v>
+        <v>97.99676513671875</v>
       </c>
       <c r="G442" t="n">
         <v>13837400</v>
@@ -10615,16 +10615,16 @@
         <v>45936</v>
       </c>
       <c r="C443" t="n">
-        <v>97.99677276611328</v>
+        <v>97.99676513671875</v>
       </c>
       <c r="D443" t="n">
-        <v>98.00653354174787</v>
+        <v>98.00652591159343</v>
       </c>
       <c r="E443" t="n">
-        <v>97.99677276611328</v>
+        <v>97.99676513671875</v>
       </c>
       <c r="F443" t="n">
-        <v>98.00653354174787</v>
+        <v>98.00652591159343</v>
       </c>
       <c r="G443" t="n">
         <v>13944300</v>
@@ -10684,16 +10684,16 @@
         <v>45939</v>
       </c>
       <c r="C446" t="n">
-        <v>98.03580474853516</v>
+        <v>98.03579711914062</v>
       </c>
       <c r="D446" t="n">
-        <v>98.04556552380387</v>
+        <v>98.04555789364973</v>
       </c>
       <c r="E446" t="n">
-        <v>98.02604397326645</v>
+        <v>98.02603634463152</v>
       </c>
       <c r="F446" t="n">
-        <v>98.04556552380387</v>
+        <v>98.04555789364973</v>
       </c>
       <c r="G446" t="n">
         <v>15718900</v>
@@ -10707,16 +10707,16 @@
         <v>45940</v>
       </c>
       <c r="C447" t="n">
-        <v>98.08458709716797</v>
+        <v>98.0845947265625</v>
       </c>
       <c r="D447" t="n">
-        <v>98.08458709716797</v>
+        <v>98.0845947265625</v>
       </c>
       <c r="E447" t="n">
-        <v>98.06506554943334</v>
+        <v>98.06507317730942</v>
       </c>
       <c r="F447" t="n">
-        <v>98.07482632330066</v>
+        <v>98.07483395193596</v>
       </c>
       <c r="G447" t="n">
         <v>18966600</v>
@@ -10753,16 +10753,16 @@
         <v>45944</v>
       </c>
       <c r="C449" t="n">
-        <v>98.08458709716797</v>
+        <v>98.0845947265625</v>
       </c>
       <c r="D449" t="n">
-        <v>98.0943404257463</v>
+        <v>98.09434805589947</v>
       </c>
       <c r="E449" t="n">
-        <v>98.08458709716797</v>
+        <v>98.0845947265625</v>
       </c>
       <c r="F449" t="n">
-        <v>98.08458709716797</v>
+        <v>98.0845947265625</v>
       </c>
       <c r="G449" t="n">
         <v>13475000</v>
@@ -10776,16 +10776,16 @@
         <v>45945</v>
       </c>
       <c r="C450" t="n">
-        <v>98.10410308837891</v>
+        <v>98.10411071777344</v>
       </c>
       <c r="D450" t="n">
-        <v>98.10410308837891</v>
+        <v>98.10411071777344</v>
       </c>
       <c r="E450" t="n">
-        <v>98.09434231432367</v>
+        <v>98.09434994295911</v>
       </c>
       <c r="F450" t="n">
-        <v>98.10410308837891</v>
+        <v>98.10411071777344</v>
       </c>
       <c r="G450" t="n">
         <v>11069100</v>
@@ -10845,16 +10845,16 @@
         <v>45950</v>
       </c>
       <c r="C453" t="n">
-        <v>98.15290069580078</v>
+        <v>98.15290832519531</v>
       </c>
       <c r="D453" t="n">
-        <v>98.15290069580078</v>
+        <v>98.15290832519531</v>
       </c>
       <c r="E453" t="n">
-        <v>98.14313992162796</v>
+        <v>98.14314755026379</v>
       </c>
       <c r="F453" t="n">
-        <v>98.15290069580078</v>
+        <v>98.15290832519531</v>
       </c>
       <c r="G453" t="n">
         <v>16129100</v>
@@ -10868,16 +10868,16 @@
         <v>45951</v>
       </c>
       <c r="C454" t="n">
-        <v>98.17241668701172</v>
+        <v>98.17242431640625</v>
       </c>
       <c r="D454" t="n">
-        <v>98.17241668701172</v>
+        <v>98.17242431640625</v>
       </c>
       <c r="E454" t="n">
-        <v>98.16265591265116</v>
+        <v>98.16266354128715</v>
       </c>
       <c r="F454" t="n">
-        <v>98.16265591265116</v>
+        <v>98.16266354128715</v>
       </c>
       <c r="G454" t="n">
         <v>12061900</v>
@@ -10937,16 +10937,16 @@
         <v>45954</v>
       </c>
       <c r="C457" t="n">
-        <v>98.22121429443359</v>
+        <v>98.22122192382812</v>
       </c>
       <c r="D457" t="n">
-        <v>98.22121429443359</v>
+        <v>98.22122192382812</v>
       </c>
       <c r="E457" t="n">
-        <v>98.21145351995568</v>
+        <v>98.21146114859204</v>
       </c>
       <c r="F457" t="n">
-        <v>98.22121429443359</v>
+        <v>98.22122192382812</v>
       </c>
       <c r="G457" t="n">
         <v>12382000</v>
@@ -10960,16 +10960,16 @@
         <v>45957</v>
       </c>
       <c r="C458" t="n">
-        <v>98.23096466064453</v>
+        <v>98.23098754882812</v>
       </c>
       <c r="D458" t="n">
-        <v>98.24071798879955</v>
+        <v>98.24074087925571</v>
       </c>
       <c r="E458" t="n">
-        <v>98.22120388720086</v>
+        <v>98.22122677311015</v>
       </c>
       <c r="F458" t="n">
-        <v>98.22120388720086</v>
+        <v>98.22122677311015</v>
       </c>
       <c r="G458" t="n">
         <v>26389600</v>
@@ -10983,16 +10983,16 @@
         <v>45958</v>
       </c>
       <c r="C459" t="n">
-        <v>98.24073791503906</v>
+        <v>98.24073028564453</v>
       </c>
       <c r="D459" t="n">
-        <v>98.25049869046254</v>
+        <v>98.25049106030998</v>
       </c>
       <c r="E459" t="n">
-        <v>98.24073791503906</v>
+        <v>98.24073028564453</v>
       </c>
       <c r="F459" t="n">
-        <v>98.24073791503906</v>
+        <v>98.24073028564453</v>
       </c>
       <c r="G459" t="n">
         <v>11134700</v>
@@ -11029,16 +11029,16 @@
         <v>45960</v>
       </c>
       <c r="C461" t="n">
-        <v>98.26025390625</v>
+        <v>98.26024627685547</v>
       </c>
       <c r="D461" t="n">
-        <v>98.27000723583144</v>
+        <v>98.26999960567962</v>
       </c>
       <c r="E461" t="n">
-        <v>98.26025390625</v>
+        <v>98.26024627685547</v>
       </c>
       <c r="F461" t="n">
-        <v>98.26025390625</v>
+        <v>98.26024627685547</v>
       </c>
       <c r="G461" t="n">
         <v>12370700</v>
@@ -11052,16 +11052,16 @@
         <v>45961</v>
       </c>
       <c r="C462" t="n">
-        <v>98.28952026367188</v>
+        <v>98.28952789306641</v>
       </c>
       <c r="D462" t="n">
-        <v>98.29928103769679</v>
+        <v>98.29928866784897</v>
       </c>
       <c r="E462" t="n">
-        <v>98.28952026367188</v>
+        <v>98.28952789306641</v>
       </c>
       <c r="F462" t="n">
-        <v>98.29439692803977</v>
+        <v>98.29440455781285</v>
       </c>
       <c r="G462" t="n">
         <v>23254100</v>
@@ -11144,16 +11144,16 @@
         <v>45967</v>
       </c>
       <c r="C466" t="n">
-        <v>98.34632110595703</v>
+        <v>98.34632873535156</v>
       </c>
       <c r="D466" t="n">
-        <v>98.34632110595703</v>
+        <v>98.34632873535156</v>
       </c>
       <c r="E466" t="n">
-        <v>98.33652648982164</v>
+        <v>98.33653411845633</v>
       </c>
       <c r="F466" t="n">
-        <v>98.34632110595703</v>
+        <v>98.34632873535156</v>
       </c>
       <c r="G466" t="n">
         <v>16658100</v>
@@ -11167,16 +11167,16 @@
         <v>45968</v>
       </c>
       <c r="C467" t="n">
-        <v>98.37569427490234</v>
+        <v>98.37570190429688</v>
       </c>
       <c r="D467" t="n">
-        <v>98.37569427490234</v>
+        <v>98.37570190429688</v>
       </c>
       <c r="E467" t="n">
-        <v>98.36589965908638</v>
+        <v>98.3659072877213</v>
       </c>
       <c r="F467" t="n">
-        <v>98.37569427490234</v>
+        <v>98.37570190429688</v>
       </c>
       <c r="G467" t="n">
         <v>18799000</v>
@@ -11190,16 +11190,16 @@
         <v>45971</v>
       </c>
       <c r="C468" t="n">
-        <v>98.38548278808594</v>
+        <v>98.385498046875</v>
       </c>
       <c r="D468" t="n">
-        <v>98.39527740329436</v>
+        <v>98.39529266360249</v>
       </c>
       <c r="E468" t="n">
-        <v>98.38548278808594</v>
+        <v>98.385498046875</v>
       </c>
       <c r="F468" t="n">
-        <v>98.39527740329436</v>
+        <v>98.39529266360249</v>
       </c>
       <c r="G468" t="n">
         <v>14121900</v>
@@ -11213,16 +11213,16 @@
         <v>45972</v>
       </c>
       <c r="C469" t="n">
-        <v>98.39527893066406</v>
+        <v>98.39529418945312</v>
       </c>
       <c r="D469" t="n">
-        <v>98.39527893066406</v>
+        <v>98.39529418945312</v>
       </c>
       <c r="E469" t="n">
-        <v>98.3854843153036</v>
+        <v>98.38549957257375</v>
       </c>
       <c r="F469" t="n">
-        <v>98.39527893066406</v>
+        <v>98.39529418945312</v>
       </c>
       <c r="G469" t="n">
         <v>8697800</v>
@@ -11236,16 +11236,16 @@
         <v>45973</v>
       </c>
       <c r="C470" t="n">
-        <v>98.40507507324219</v>
+        <v>98.40509033203125</v>
       </c>
       <c r="D470" t="n">
-        <v>98.40507507324219</v>
+        <v>98.40509033203125</v>
       </c>
       <c r="E470" t="n">
-        <v>98.39528792808926</v>
+        <v>98.39530318536072</v>
       </c>
       <c r="F470" t="n">
-        <v>98.39528792808926</v>
+        <v>98.39530318536072</v>
       </c>
       <c r="G470" t="n">
         <v>9067200</v>
@@ -11305,16 +11305,16 @@
         <v>45978</v>
       </c>
       <c r="C473" t="n">
-        <v>98.45402526855469</v>
+        <v>98.45403289794922</v>
       </c>
       <c r="D473" t="n">
-        <v>98.45402526855469</v>
+        <v>98.45403289794922</v>
       </c>
       <c r="E473" t="n">
-        <v>98.44423065383212</v>
+        <v>98.44423828246764</v>
       </c>
       <c r="F473" t="n">
-        <v>98.4491316967444</v>
+        <v>98.44913932575972</v>
       </c>
       <c r="G473" t="n">
         <v>15032800</v>
@@ -11328,16 +11328,16 @@
         <v>45979</v>
       </c>
       <c r="C474" t="n">
-        <v>98.45402526855469</v>
+        <v>98.45403289794922</v>
       </c>
       <c r="D474" t="n">
-        <v>98.46381988327725</v>
+        <v>98.46382751343079</v>
       </c>
       <c r="E474" t="n">
-        <v>98.45402526855469</v>
+        <v>98.45403289794922</v>
       </c>
       <c r="F474" t="n">
-        <v>98.45402526855469</v>
+        <v>98.45403289794922</v>
       </c>
       <c r="G474" t="n">
         <v>13130300</v>
@@ -11351,16 +11351,16 @@
         <v>45980</v>
       </c>
       <c r="C475" t="n">
-        <v>98.47362518310547</v>
+        <v>98.47361755371094</v>
       </c>
       <c r="D475" t="n">
-        <v>98.47362518310547</v>
+        <v>98.47361755371094</v>
       </c>
       <c r="E475" t="n">
-        <v>98.46383803768039</v>
+        <v>98.46383040904414</v>
       </c>
       <c r="F475" t="n">
-        <v>98.46383803768039</v>
+        <v>98.46383040904414</v>
       </c>
       <c r="G475" t="n">
         <v>23022400</v>
@@ -11420,16 +11420,16 @@
         <v>45985</v>
       </c>
       <c r="C478" t="n">
-        <v>98.5225830078125</v>
+        <v>98.52259063720703</v>
       </c>
       <c r="D478" t="n">
-        <v>98.53237762356683</v>
+        <v>98.53238525371985</v>
       </c>
       <c r="E478" t="n">
-        <v>98.5225830078125</v>
+        <v>98.52259063720703</v>
       </c>
       <c r="F478" t="n">
-        <v>98.5225830078125</v>
+        <v>98.52259063720703</v>
       </c>
       <c r="G478" t="n">
         <v>15830800</v>
@@ -11443,16 +11443,16 @@
         <v>45986</v>
       </c>
       <c r="C479" t="n">
-        <v>98.54216003417969</v>
+        <v>98.54216766357422</v>
       </c>
       <c r="D479" t="n">
-        <v>98.54216003417969</v>
+        <v>98.54216766357422</v>
       </c>
       <c r="E479" t="n">
-        <v>98.53237288999831</v>
+        <v>98.53238051863511</v>
       </c>
       <c r="F479" t="n">
-        <v>98.54216003417969</v>
+        <v>98.54216766357422</v>
       </c>
       <c r="G479" t="n">
         <v>19115000</v>
@@ -11466,16 +11466,16 @@
         <v>45987</v>
       </c>
       <c r="C480" t="n">
-        <v>98.55196380615234</v>
+        <v>98.55195617675781</v>
       </c>
       <c r="D480" t="n">
-        <v>98.56175842234617</v>
+        <v>98.56175079219341</v>
       </c>
       <c r="E480" t="n">
-        <v>98.55196380615234</v>
+        <v>98.55195617675781</v>
       </c>
       <c r="F480" t="n">
-        <v>98.55196380615234</v>
+        <v>98.55195617675781</v>
       </c>
       <c r="G480" t="n">
         <v>11948500</v>
@@ -11489,16 +11489,16 @@
         <v>45989</v>
       </c>
       <c r="C481" t="n">
-        <v>98.58133697509766</v>
+        <v>98.58134460449219</v>
       </c>
       <c r="D481" t="n">
-        <v>98.59113159097269</v>
+        <v>98.59113922112526</v>
       </c>
       <c r="E481" t="n">
-        <v>98.57154983032548</v>
+        <v>98.57155745896257</v>
       </c>
       <c r="F481" t="n">
-        <v>98.58133697509766</v>
+        <v>98.58134460449219</v>
       </c>
       <c r="G481" t="n">
         <v>24417500</v>
@@ -11558,16 +11558,16 @@
         <v>45994</v>
       </c>
       <c r="C484" t="n">
-        <v>98.63339996337891</v>
+        <v>98.63340759277344</v>
       </c>
       <c r="D484" t="n">
-        <v>98.63830879792842</v>
+        <v>98.63831642770265</v>
       </c>
       <c r="E484" t="n">
-        <v>98.63339996337891</v>
+        <v>98.63340759277344</v>
       </c>
       <c r="F484" t="n">
-        <v>98.63339996337891</v>
+        <v>98.63340759277344</v>
       </c>
       <c r="G484" t="n">
         <v>15531600</v>
@@ -11581,16 +11581,16 @@
         <v>45995</v>
       </c>
       <c r="C485" t="n">
-        <v>98.65304565429688</v>
+        <v>98.65305328369141</v>
       </c>
       <c r="D485" t="n">
-        <v>98.65304565429688</v>
+        <v>98.65305328369141</v>
       </c>
       <c r="E485" t="n">
-        <v>98.64322049050931</v>
+        <v>98.64322811914398</v>
       </c>
       <c r="F485" t="n">
-        <v>98.64322049050931</v>
+        <v>98.64322811914398</v>
       </c>
       <c r="G485" t="n">
         <v>13689600</v>
@@ -11650,16 +11650,16 @@
         <v>46000</v>
       </c>
       <c r="C488" t="n">
-        <v>98.69232940673828</v>
+        <v>98.69234466552734</v>
       </c>
       <c r="D488" t="n">
-        <v>98.69723824096205</v>
+        <v>98.69725350051007</v>
       </c>
       <c r="E488" t="n">
-        <v>98.69232940673828</v>
+        <v>98.69234466552734</v>
       </c>
       <c r="F488" t="n">
-        <v>98.69232940673828</v>
+        <v>98.69234466552734</v>
       </c>
       <c r="G488" t="n">
         <v>11016400</v>
@@ -11673,16 +11673,16 @@
         <v>46001</v>
       </c>
       <c r="C489" t="n">
-        <v>98.69232940673828</v>
+        <v>98.69234466552734</v>
       </c>
       <c r="D489" t="n">
-        <v>98.70215456958923</v>
+        <v>98.70216982989736</v>
       </c>
       <c r="E489" t="n">
-        <v>98.69232940673828</v>
+        <v>98.69234466552734</v>
       </c>
       <c r="F489" t="n">
-        <v>98.70215456958923</v>
+        <v>98.70216982989736</v>
       </c>
       <c r="G489" t="n">
         <v>12234900</v>
@@ -11719,16 +11719,16 @@
         <v>46003</v>
       </c>
       <c r="C491" t="n">
-        <v>98.75128173828125</v>
+        <v>98.75127410888672</v>
       </c>
       <c r="D491" t="n">
-        <v>98.75128173828125</v>
+        <v>98.75127410888672</v>
       </c>
       <c r="E491" t="n">
-        <v>98.74145657380426</v>
+        <v>98.7414489451688</v>
       </c>
       <c r="F491" t="n">
-        <v>98.74145657380426</v>
+        <v>98.7414489451688</v>
       </c>
       <c r="G491" t="n">
         <v>13320200</v>
@@ -11742,16 +11742,16 @@
         <v>46006</v>
       </c>
       <c r="C492" t="n">
-        <v>98.75128173828125</v>
+        <v>98.75127410888672</v>
       </c>
       <c r="D492" t="n">
-        <v>98.76110690275826</v>
+        <v>98.76109927260465</v>
       </c>
       <c r="E492" t="n">
-        <v>98.75128173828125</v>
+        <v>98.75127410888672</v>
       </c>
       <c r="F492" t="n">
-        <v>98.75128173828125</v>
+        <v>98.75127410888672</v>
       </c>
       <c r="G492" t="n">
         <v>14767900</v>
@@ -11765,16 +11765,16 @@
         <v>46007</v>
       </c>
       <c r="C493" t="n">
-        <v>98.76110076904297</v>
+        <v>98.76109313964844</v>
       </c>
       <c r="D493" t="n">
-        <v>98.77092593290978</v>
+        <v>98.77091830275623</v>
       </c>
       <c r="E493" t="n">
-        <v>98.76110076904297</v>
+        <v>98.76109313964844</v>
       </c>
       <c r="F493" t="n">
-        <v>98.77092593290978</v>
+        <v>98.77091830275623</v>
       </c>
       <c r="G493" t="n">
         <v>10701200</v>
@@ -11834,16 +11834,16 @@
         <v>46010</v>
       </c>
       <c r="C496" t="n">
-        <v>98.8231201171875</v>
+        <v>98.82312774658203</v>
       </c>
       <c r="D496" t="n">
-        <v>98.8231201171875</v>
+        <v>98.82312774658203</v>
       </c>
       <c r="E496" t="n">
-        <v>98.81326329307338</v>
+        <v>98.81327092170693</v>
       </c>
       <c r="F496" t="n">
-        <v>98.8231201171875</v>
+        <v>98.82312774658203</v>
       </c>
       <c r="G496" t="n">
         <v>18203600</v>
@@ -11857,16 +11857,16 @@
         <v>46013</v>
       </c>
       <c r="C497" t="n">
-        <v>98.8231201171875</v>
+        <v>98.82312774658203</v>
       </c>
       <c r="D497" t="n">
-        <v>98.83297694130162</v>
+        <v>98.83298457145713</v>
       </c>
       <c r="E497" t="n">
-        <v>98.8231201171875</v>
+        <v>98.82312774658203</v>
       </c>
       <c r="F497" t="n">
-        <v>98.8231201171875</v>
+        <v>98.82312774658203</v>
       </c>
       <c r="G497" t="n">
         <v>17890900</v>
@@ -11880,16 +11880,16 @@
         <v>46014</v>
       </c>
       <c r="C498" t="n">
-        <v>98.83298492431641</v>
+        <v>98.83297729492188</v>
       </c>
       <c r="D498" t="n">
-        <v>98.84284174922669</v>
+        <v>98.84283411907127</v>
       </c>
       <c r="E498" t="n">
-        <v>98.83298492431641</v>
+        <v>98.83297729492188</v>
       </c>
       <c r="F498" t="n">
-        <v>98.84284174922669</v>
+        <v>98.84283411907127</v>
       </c>
       <c r="G498" t="n">
         <v>12256200</v>
@@ -11926,16 +11926,16 @@
         <v>46017</v>
       </c>
       <c r="C500" t="n">
-        <v>98.88225555419922</v>
+        <v>98.88224792480469</v>
       </c>
       <c r="D500" t="n">
-        <v>98.88718772600853</v>
+        <v>98.88718009623345</v>
       </c>
       <c r="E500" t="n">
-        <v>98.88225555419922</v>
+        <v>98.88224792480469</v>
       </c>
       <c r="F500" t="n">
-        <v>98.88225555419922</v>
+        <v>98.88224792480469</v>
       </c>
       <c r="G500" t="n">
         <v>12664300</v>
@@ -11949,16 +11949,16 @@
         <v>46020</v>
       </c>
       <c r="C501" t="n">
-        <v>98.90196228027344</v>
+        <v>98.90195465087891</v>
       </c>
       <c r="D501" t="n">
-        <v>98.90196228027344</v>
+        <v>98.90195465087891</v>
       </c>
       <c r="E501" t="n">
-        <v>98.89210545589947</v>
+        <v>98.8920978272653</v>
       </c>
       <c r="F501" t="n">
-        <v>98.89210545589947</v>
+        <v>98.8920978272653</v>
       </c>
       <c r="G501" t="n">
         <v>17350200</v>
@@ -11972,16 +11972,16 @@
         <v>46021</v>
       </c>
       <c r="C502" t="n">
-        <v>98.91181945800781</v>
+        <v>98.91182708740234</v>
       </c>
       <c r="D502" t="n">
-        <v>98.91181945800781</v>
+        <v>98.91182708740234</v>
       </c>
       <c r="E502" t="n">
-        <v>98.90196263359863</v>
+        <v>98.90197026223287</v>
       </c>
       <c r="F502" t="n">
-        <v>98.90688728652617</v>
+        <v>98.90689491554026</v>
       </c>
       <c r="G502" t="n">
         <v>12608900</v>
@@ -11995,16 +11995,16 @@
         <v>46022</v>
       </c>
       <c r="C503" t="n">
-        <v>98.92166137695312</v>
+        <v>98.92166900634766</v>
       </c>
       <c r="D503" t="n">
-        <v>98.93151820062626</v>
+        <v>98.931525830781</v>
       </c>
       <c r="E503" t="n">
-        <v>98.92166137695312</v>
+        <v>98.92166900634766</v>
       </c>
       <c r="F503" t="n">
-        <v>98.93151820062626</v>
+        <v>98.931525830781</v>
       </c>
       <c r="G503" t="n">
         <v>13910900</v>
@@ -12018,16 +12018,16 @@
         <v>46024</v>
       </c>
       <c r="C504" t="n">
-        <v>98.95124053955078</v>
+        <v>98.95124816894531</v>
       </c>
       <c r="D504" t="n">
-        <v>98.96108984553553</v>
+        <v>98.96109747568946</v>
       </c>
       <c r="E504" t="n">
-        <v>98.95124053955078</v>
+        <v>98.95124816894531</v>
       </c>
       <c r="F504" t="n">
-        <v>98.95124053955078</v>
+        <v>98.95124816894531</v>
       </c>
       <c r="G504" t="n">
         <v>19188800</v>
@@ -12087,16 +12087,16 @@
         <v>46029</v>
       </c>
       <c r="C507" t="n">
-        <v>98.98080444335938</v>
+        <v>98.98079681396484</v>
       </c>
       <c r="D507" t="n">
-        <v>98.98080444335938</v>
+        <v>98.98079681396484</v>
       </c>
       <c r="E507" t="n">
-        <v>98.98080444335938</v>
+        <v>98.98079681396484</v>
       </c>
       <c r="F507" t="n">
-        <v>98.98080444335938</v>
+        <v>98.98079681396484</v>
       </c>
       <c r="G507" t="n">
         <v>14062300</v>
@@ -12133,16 +12133,16 @@
         <v>46031</v>
       </c>
       <c r="C509" t="n">
-        <v>99.01036071777344</v>
+        <v>99.01036834716797</v>
       </c>
       <c r="D509" t="n">
-        <v>99.02021754174173</v>
+        <v>99.0202251718958</v>
       </c>
       <c r="E509" t="n">
-        <v>99.01036071777344</v>
+        <v>99.01036834716797</v>
       </c>
       <c r="F509" t="n">
-        <v>99.02021754174173</v>
+        <v>99.0202251718958</v>
       </c>
       <c r="G509" t="n">
         <v>15053500</v>
@@ -12202,16 +12202,16 @@
         <v>46036</v>
       </c>
       <c r="C512" t="n">
-        <v>99.04978942871094</v>
+        <v>99.04978179931641</v>
       </c>
       <c r="D512" t="n">
-        <v>99.04978942871094</v>
+        <v>99.04978179931641</v>
       </c>
       <c r="E512" t="n">
-        <v>99.03993260385363</v>
+        <v>99.03992497521833</v>
       </c>
       <c r="F512" t="n">
-        <v>99.04978942871094</v>
+        <v>99.04978179931641</v>
       </c>
       <c r="G512" t="n">
         <v>11851800</v>
@@ -12225,16 +12225,16 @@
         <v>46037</v>
       </c>
       <c r="C513" t="n">
-        <v>99.05963134765625</v>
+        <v>99.05962371826172</v>
       </c>
       <c r="D513" t="n">
-        <v>99.05963134765625</v>
+        <v>99.05962371826172</v>
       </c>
       <c r="E513" t="n">
-        <v>99.04978204208787</v>
+        <v>99.04977441345191</v>
       </c>
       <c r="F513" t="n">
-        <v>99.04978204208787</v>
+        <v>99.04977441345191</v>
       </c>
       <c r="G513" t="n">
         <v>11469500</v>
@@ -12317,16 +12317,16 @@
         <v>46044</v>
       </c>
       <c r="C517" t="n">
-        <v>99.11876678466797</v>
+        <v>99.11875915527344</v>
       </c>
       <c r="D517" t="n">
-        <v>99.11876678466797</v>
+        <v>99.11875915527344</v>
       </c>
       <c r="E517" t="n">
-        <v>99.10890996034576</v>
+        <v>99.10890233170993</v>
       </c>
       <c r="F517" t="n">
-        <v>99.11876678466797</v>
+        <v>99.11875915527344</v>
       </c>
       <c r="G517" t="n">
         <v>13618500</v>
@@ -12455,16 +12455,16 @@
         <v>46052</v>
       </c>
       <c r="C523" t="n">
-        <v>99.20745086669922</v>
+        <v>99.20745849609375</v>
       </c>
       <c r="D523" t="n">
-        <v>99.21730769054639</v>
+        <v>99.21731532069894</v>
       </c>
       <c r="E523" t="n">
-        <v>99.20745086669922</v>
+        <v>99.20745849609375</v>
       </c>
       <c r="F523" t="n">
-        <v>99.20745086669922</v>
+        <v>99.20745849609375</v>
       </c>
       <c r="G523" t="n">
         <v>29215200</v>
@@ -12846,16 +12846,16 @@
         <v>46078</v>
       </c>
       <c r="C540" t="n">
-        <v>99.44371795654297</v>
+        <v>99.44371032714844</v>
       </c>
       <c r="D540" t="n">
-        <v>99.45360512979697</v>
+        <v>99.45359749964389</v>
       </c>
       <c r="E540" t="n">
-        <v>99.44371795654297</v>
+        <v>99.44371032714844</v>
       </c>
       <c r="F540" t="n">
-        <v>99.45360512979697</v>
+        <v>99.45359749964389</v>
       </c>
       <c r="G540" t="n">
         <v>12532000</v>
@@ -12892,16 +12892,16 @@
         <v>46080</v>
       </c>
       <c r="C542" t="n">
-        <v>99.48325347900391</v>
+        <v>99.48324584960938</v>
       </c>
       <c r="D542" t="n">
-        <v>99.49314065169848</v>
+        <v>99.49313302154569</v>
       </c>
       <c r="E542" t="n">
-        <v>99.48325347900391</v>
+        <v>99.48324584960938</v>
       </c>
       <c r="F542" t="n">
-        <v>99.48819329449967</v>
+        <v>99.4881856647263</v>
       </c>
       <c r="G542" t="n">
         <v>26602400</v>
@@ -14514,7 +14514,76 @@
         <v>100.4700012207031</v>
       </c>
       <c r="G612" t="n">
-        <v>25347277</v>
+        <v>25747500</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="1" t="n">
+        <v>611</v>
+      </c>
+      <c r="B613" s="2" t="n">
+        <v>46183</v>
+      </c>
+      <c r="C613" t="n">
+        <v>100.4800033569336</v>
+      </c>
+      <c r="D613" t="n">
+        <v>100.4800033569336</v>
+      </c>
+      <c r="E613" t="n">
+        <v>100.4700012207031</v>
+      </c>
+      <c r="F613" t="n">
+        <v>100.4749984741211</v>
+      </c>
+      <c r="G613" t="n">
+        <v>20362200</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="1" t="n">
+        <v>612</v>
+      </c>
+      <c r="B614" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C614" t="n">
+        <v>100.4899978637695</v>
+      </c>
+      <c r="D614" t="n">
+        <v>100.4899978637695</v>
+      </c>
+      <c r="E614" t="n">
+        <v>100.4800033569336</v>
+      </c>
+      <c r="F614" t="n">
+        <v>100.4899978637695</v>
+      </c>
+      <c r="G614" t="n">
+        <v>24927700</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="1" t="n">
+        <v>613</v>
+      </c>
+      <c r="B615" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="C615" t="n">
+        <v>100.5100021362305</v>
+      </c>
+      <c r="D615" t="n">
+        <v>100.5199966430664</v>
+      </c>
+      <c r="E615" t="n">
+        <v>100.5100021362305</v>
+      </c>
+      <c r="F615" t="n">
+        <v>100.5199966430664</v>
+      </c>
+      <c r="G615" t="n">
+        <v>23026100</v>
       </c>
     </row>
   </sheetData>

--- a/Data/sgov.xlsx
+++ b/Data/sgov.xlsx
@@ -472,16 +472,16 @@
         <v>45293</v>
       </c>
       <c r="C2" t="n">
-        <v>90.15838623046875</v>
+        <v>90.15840148925781</v>
       </c>
       <c r="D2" t="n">
-        <v>90.16737791910336</v>
+        <v>90.1673931794142</v>
       </c>
       <c r="E2" t="n">
-        <v>90.14939454183416</v>
+        <v>90.14940979910142</v>
       </c>
       <c r="F2" t="n">
-        <v>90.15838623046875</v>
+        <v>90.15840148925781</v>
       </c>
       <c r="G2" t="n">
         <v>5286200</v>
@@ -495,16 +495,16 @@
         <v>45294</v>
       </c>
       <c r="C3" t="n">
-        <v>90.16737365722656</v>
+        <v>90.16738128662109</v>
       </c>
       <c r="D3" t="n">
-        <v>90.18535017499724</v>
+        <v>90.18535780591283</v>
       </c>
       <c r="E3" t="n">
-        <v>90.16737365722656</v>
+        <v>90.16738128662109</v>
       </c>
       <c r="F3" t="n">
-        <v>90.16737365722656</v>
+        <v>90.16738128662109</v>
       </c>
       <c r="G3" t="n">
         <v>4597300</v>
@@ -518,16 +518,16 @@
         <v>45295</v>
       </c>
       <c r="C4" t="n">
-        <v>90.21231842041016</v>
+        <v>90.21231079101562</v>
       </c>
       <c r="D4" t="n">
-        <v>90.22131010862368</v>
+        <v>90.22130247846871</v>
       </c>
       <c r="E4" t="n">
-        <v>90.21231842041016</v>
+        <v>90.21231079101562</v>
       </c>
       <c r="F4" t="n">
-        <v>90.21231842041016</v>
+        <v>90.21231079101562</v>
       </c>
       <c r="G4" t="n">
         <v>2794100</v>
@@ -541,16 +541,16 @@
         <v>45296</v>
       </c>
       <c r="C5" t="n">
-        <v>90.22133636474609</v>
+        <v>90.22132873535156</v>
       </c>
       <c r="D5" t="n">
-        <v>90.23032805557638</v>
+        <v>90.23032042542148</v>
       </c>
       <c r="E5" t="n">
-        <v>90.22133636474609</v>
+        <v>90.22132873535156</v>
       </c>
       <c r="F5" t="n">
-        <v>90.22133636474609</v>
+        <v>90.22132873535156</v>
       </c>
       <c r="G5" t="n">
         <v>3491200</v>
@@ -564,16 +564,16 @@
         <v>45299</v>
       </c>
       <c r="C6" t="n">
-        <v>90.24829864501953</v>
+        <v>90.24826812744141</v>
       </c>
       <c r="D6" t="n">
-        <v>90.24829864501953</v>
+        <v>90.24826812744141</v>
       </c>
       <c r="E6" t="n">
-        <v>90.23930695478043</v>
+        <v>90.23927644024286</v>
       </c>
       <c r="F6" t="n">
-        <v>90.24829864501953</v>
+        <v>90.24826812744141</v>
       </c>
       <c r="G6" t="n">
         <v>2867500</v>
@@ -587,16 +587,16 @@
         <v>45300</v>
       </c>
       <c r="C7" t="n">
-        <v>90.25726318359375</v>
+        <v>90.25727844238281</v>
       </c>
       <c r="D7" t="n">
-        <v>90.25726318359375</v>
+        <v>90.25727844238281</v>
       </c>
       <c r="E7" t="n">
-        <v>90.24827149605957</v>
+        <v>90.24828675332851</v>
       </c>
       <c r="F7" t="n">
-        <v>90.25726318359375</v>
+        <v>90.25727844238281</v>
       </c>
       <c r="G7" t="n">
         <v>2419800</v>
@@ -633,16 +633,16 @@
         <v>45302</v>
       </c>
       <c r="C9" t="n">
-        <v>90.32920074462891</v>
+        <v>90.32917785644531</v>
       </c>
       <c r="D9" t="n">
-        <v>90.32920074462891</v>
+        <v>90.32917785644531</v>
       </c>
       <c r="E9" t="n">
-        <v>90.31121736602117</v>
+        <v>90.31119448239433</v>
       </c>
       <c r="F9" t="n">
-        <v>90.31121736602117</v>
+        <v>90.31119448239433</v>
       </c>
       <c r="G9" t="n">
         <v>3164900</v>
@@ -679,16 +679,16 @@
         <v>45307</v>
       </c>
       <c r="C11" t="n">
-        <v>90.34717559814453</v>
+        <v>90.34716796875</v>
       </c>
       <c r="D11" t="n">
-        <v>90.35616728728255</v>
+        <v>90.35615965712871</v>
       </c>
       <c r="E11" t="n">
-        <v>90.34717559814453</v>
+        <v>90.34716796875</v>
       </c>
       <c r="F11" t="n">
-        <v>90.35616728728255</v>
+        <v>90.35615965712871</v>
       </c>
       <c r="G11" t="n">
         <v>2713000</v>
@@ -702,16 +702,16 @@
         <v>45308</v>
       </c>
       <c r="C12" t="n">
-        <v>90.35616302490234</v>
+        <v>90.35614776611328</v>
       </c>
       <c r="D12" t="n">
-        <v>90.36514785496729</v>
+        <v>90.36513259466092</v>
       </c>
       <c r="E12" t="n">
-        <v>90.35616302490234</v>
+        <v>90.35614776611328</v>
       </c>
       <c r="F12" t="n">
-        <v>90.36514785496729</v>
+        <v>90.36513259466092</v>
       </c>
       <c r="G12" t="n">
         <v>2317700</v>
@@ -725,16 +725,16 @@
         <v>45309</v>
       </c>
       <c r="C13" t="n">
-        <v>90.39211273193359</v>
+        <v>90.39212799072266</v>
       </c>
       <c r="D13" t="n">
-        <v>90.40109756098575</v>
+        <v>90.40111282129152</v>
       </c>
       <c r="E13" t="n">
-        <v>90.39211273193359</v>
+        <v>90.39212799072266</v>
       </c>
       <c r="F13" t="n">
-        <v>90.40109756098575</v>
+        <v>90.40111282129152</v>
       </c>
       <c r="G13" t="n">
         <v>2672000</v>
@@ -748,16 +748,16 @@
         <v>45310</v>
       </c>
       <c r="C14" t="n">
-        <v>90.41909790039062</v>
+        <v>90.41909027099609</v>
       </c>
       <c r="D14" t="n">
-        <v>90.41909790039062</v>
+        <v>90.41909027099609</v>
       </c>
       <c r="E14" t="n">
-        <v>90.40111452161609</v>
+        <v>90.40110689373897</v>
       </c>
       <c r="F14" t="n">
-        <v>90.41010621100335</v>
+        <v>90.41009858236752</v>
       </c>
       <c r="G14" t="n">
         <v>3630100</v>
@@ -771,16 +771,16 @@
         <v>45313</v>
       </c>
       <c r="C15" t="n">
-        <v>90.42807769775391</v>
+        <v>90.42806243896484</v>
       </c>
       <c r="D15" t="n">
-        <v>90.43706938664067</v>
+        <v>90.43705412633436</v>
       </c>
       <c r="E15" t="n">
-        <v>90.41909286751616</v>
+        <v>90.41907761024319</v>
       </c>
       <c r="F15" t="n">
-        <v>90.43257697152181</v>
+        <v>90.43256171197355</v>
       </c>
       <c r="G15" t="n">
         <v>4307000</v>
@@ -794,16 +794,16 @@
         <v>45314</v>
       </c>
       <c r="C16" t="n">
-        <v>90.44606018066406</v>
+        <v>90.446044921875</v>
       </c>
       <c r="D16" t="n">
-        <v>90.44606018066406</v>
+        <v>90.446044921875</v>
       </c>
       <c r="E16" t="n">
-        <v>90.43706849186626</v>
+        <v>90.43705323459413</v>
       </c>
       <c r="F16" t="n">
-        <v>90.43706849186626</v>
+        <v>90.43705323459413</v>
       </c>
       <c r="G16" t="n">
         <v>2066200</v>
@@ -817,16 +817,16 @@
         <v>45315</v>
       </c>
       <c r="C17" t="n">
-        <v>90.45503997802734</v>
+        <v>90.45505523681641</v>
       </c>
       <c r="D17" t="n">
-        <v>90.45503997802734</v>
+        <v>90.45505523681641</v>
       </c>
       <c r="E17" t="n">
-        <v>90.4460482904116</v>
+        <v>90.44606354768386</v>
       </c>
       <c r="F17" t="n">
-        <v>90.4460482904116</v>
+        <v>90.44606354768386</v>
       </c>
       <c r="G17" t="n">
         <v>3441600</v>
@@ -840,16 +840,16 @@
         <v>45316</v>
       </c>
       <c r="C18" t="n">
-        <v>90.5</v>
+        <v>90.49999237060547</v>
       </c>
       <c r="D18" t="n">
-        <v>90.5</v>
+        <v>90.49999237060547</v>
       </c>
       <c r="E18" t="n">
-        <v>90.48202348037722</v>
+        <v>90.48201585249815</v>
       </c>
       <c r="F18" t="n">
-        <v>90.48202348037722</v>
+        <v>90.48201585249815</v>
       </c>
       <c r="G18" t="n">
         <v>2426000</v>
@@ -863,16 +863,16 @@
         <v>45317</v>
       </c>
       <c r="C19" t="n">
-        <v>90.5</v>
+        <v>90.49999237060547</v>
       </c>
       <c r="D19" t="n">
-        <v>90.50899168913601</v>
+        <v>90.50898405898346</v>
       </c>
       <c r="E19" t="n">
-        <v>90.5</v>
+        <v>90.49999237060547</v>
       </c>
       <c r="F19" t="n">
-        <v>90.50899168913601</v>
+        <v>90.50898405898346</v>
       </c>
       <c r="G19" t="n">
         <v>2059100</v>
@@ -886,16 +886,16 @@
         <v>45320</v>
       </c>
       <c r="C20" t="n">
-        <v>90.50897979736328</v>
+        <v>90.50898742675781</v>
       </c>
       <c r="D20" t="n">
-        <v>90.52695631462417</v>
+        <v>90.52696394553402</v>
       </c>
       <c r="E20" t="n">
-        <v>90.50897979736328</v>
+        <v>90.50898742675781</v>
       </c>
       <c r="F20" t="n">
-        <v>90.51797148531789</v>
+        <v>90.51797911547037</v>
       </c>
       <c r="G20" t="n">
         <v>2914400</v>
@@ -909,16 +909,16 @@
         <v>45321</v>
       </c>
       <c r="C21" t="n">
-        <v>90.53595733642578</v>
+        <v>90.53594970703125</v>
       </c>
       <c r="D21" t="n">
-        <v>90.53595733642578</v>
+        <v>90.53594970703125</v>
       </c>
       <c r="E21" t="n">
-        <v>90.52696564754417</v>
+        <v>90.52695801890737</v>
       </c>
       <c r="F21" t="n">
-        <v>90.52696564754417</v>
+        <v>90.52695801890737</v>
       </c>
       <c r="G21" t="n">
         <v>3741000</v>
@@ -932,16 +932,16 @@
         <v>45322</v>
       </c>
       <c r="C22" t="n">
-        <v>90.53595733642578</v>
+        <v>90.53594970703125</v>
       </c>
       <c r="D22" t="n">
-        <v>90.54494902530739</v>
+        <v>90.54494139515513</v>
       </c>
       <c r="E22" t="n">
-        <v>90.53595733642578</v>
+        <v>90.53594970703125</v>
       </c>
       <c r="F22" t="n">
-        <v>90.53595733642578</v>
+        <v>90.53594970703125</v>
       </c>
       <c r="G22" t="n">
         <v>5171300</v>
@@ -955,16 +955,16 @@
         <v>45323</v>
       </c>
       <c r="C23" t="n">
-        <v>90.58834838867188</v>
+        <v>90.58834075927734</v>
       </c>
       <c r="D23" t="n">
-        <v>90.59738115732434</v>
+        <v>90.59737352716907</v>
       </c>
       <c r="E23" t="n">
-        <v>90.58834838867188</v>
+        <v>90.58834075927734</v>
       </c>
       <c r="F23" t="n">
-        <v>90.59738115732434</v>
+        <v>90.59737352716907</v>
       </c>
       <c r="G23" t="n">
         <v>7038600</v>
@@ -978,16 +978,16 @@
         <v>45324</v>
       </c>
       <c r="C24" t="n">
-        <v>90.59736633300781</v>
+        <v>90.59735107421875</v>
       </c>
       <c r="D24" t="n">
-        <v>90.59736633300781</v>
+        <v>90.59735107421875</v>
       </c>
       <c r="E24" t="n">
-        <v>90.58833356583337</v>
+        <v>90.58831830856563</v>
       </c>
       <c r="F24" t="n">
-        <v>90.59736633300781</v>
+        <v>90.59735107421875</v>
       </c>
       <c r="G24" t="n">
         <v>3864800</v>
@@ -1001,16 +1001,16 @@
         <v>45327</v>
       </c>
       <c r="C25" t="n">
-        <v>90.61542510986328</v>
+        <v>90.61544036865234</v>
       </c>
       <c r="D25" t="n">
-        <v>90.61542510986328</v>
+        <v>90.61544036865234</v>
       </c>
       <c r="E25" t="n">
-        <v>90.60639923265822</v>
+        <v>90.6064144899274</v>
       </c>
       <c r="F25" t="n">
-        <v>90.61542510986328</v>
+        <v>90.61544036865234</v>
       </c>
       <c r="G25" t="n">
         <v>3969400</v>
@@ -1024,16 +1024,16 @@
         <v>45328</v>
       </c>
       <c r="C26" t="n">
-        <v>90.62445831298828</v>
+        <v>90.62444305419922</v>
       </c>
       <c r="D26" t="n">
-        <v>90.6334910802194</v>
+        <v>90.63347581990945</v>
       </c>
       <c r="E26" t="n">
-        <v>90.61542554575718</v>
+        <v>90.61541028848899</v>
       </c>
       <c r="F26" t="n">
-        <v>90.62445831298828</v>
+        <v>90.62444305419922</v>
       </c>
       <c r="G26" t="n">
         <v>2167300</v>
@@ -1047,16 +1047,16 @@
         <v>45329</v>
       </c>
       <c r="C27" t="n">
-        <v>90.64250946044922</v>
+        <v>90.64253997802734</v>
       </c>
       <c r="D27" t="n">
-        <v>90.64250946044922</v>
+        <v>90.64253997802734</v>
       </c>
       <c r="E27" t="n">
-        <v>90.63347669465182</v>
+        <v>90.63350720918878</v>
       </c>
       <c r="F27" t="n">
-        <v>90.64250946044922</v>
+        <v>90.64253997802734</v>
       </c>
       <c r="G27" t="n">
         <v>2621200</v>
@@ -1070,16 +1070,16 @@
         <v>45330</v>
       </c>
       <c r="C28" t="n">
-        <v>90.66959381103516</v>
+        <v>90.66962432861328</v>
       </c>
       <c r="D28" t="n">
-        <v>90.68765245124293</v>
+        <v>90.68768297489923</v>
       </c>
       <c r="E28" t="n">
-        <v>90.66959381103516</v>
+        <v>90.66962432861328</v>
       </c>
       <c r="F28" t="n">
-        <v>90.66959381103516</v>
+        <v>90.66962432861328</v>
       </c>
       <c r="G28" t="n">
         <v>3838700</v>
@@ -1093,16 +1093,16 @@
         <v>45331</v>
       </c>
       <c r="C29" t="n">
-        <v>90.69671630859375</v>
+        <v>90.69670867919922</v>
       </c>
       <c r="D29" t="n">
-        <v>90.69671630859375</v>
+        <v>90.69670867919922</v>
       </c>
       <c r="E29" t="n">
-        <v>90.683170601299</v>
+        <v>90.68316297304392</v>
       </c>
       <c r="F29" t="n">
-        <v>90.68768354040279</v>
+        <v>90.6876759117681</v>
       </c>
       <c r="G29" t="n">
         <v>3232500</v>
@@ -1116,16 +1116,16 @@
         <v>45334</v>
       </c>
       <c r="C30" t="n">
-        <v>90.69671630859375</v>
+        <v>90.69670867919922</v>
       </c>
       <c r="D30" t="n">
-        <v>90.71477495499231</v>
+        <v>90.71476732407868</v>
       </c>
       <c r="E30" t="n">
-        <v>90.69671630859375</v>
+        <v>90.69670867919922</v>
       </c>
       <c r="F30" t="n">
-        <v>90.70574907678471</v>
+        <v>90.70574144663034</v>
       </c>
       <c r="G30" t="n">
         <v>2792700</v>
@@ -1162,16 +1162,16 @@
         <v>45336</v>
       </c>
       <c r="C32" t="n">
-        <v>90.73281860351562</v>
+        <v>90.73283386230469</v>
       </c>
       <c r="D32" t="n">
-        <v>90.73281860351562</v>
+        <v>90.73283386230469</v>
       </c>
       <c r="E32" t="n">
-        <v>90.72378583750368</v>
+        <v>90.72380109477368</v>
       </c>
       <c r="F32" t="n">
-        <v>90.73281860351562</v>
+        <v>90.73283386230469</v>
       </c>
       <c r="G32" t="n">
         <v>2614100</v>
@@ -1185,16 +1185,16 @@
         <v>45337</v>
       </c>
       <c r="C33" t="n">
-        <v>90.77799224853516</v>
+        <v>90.77798461914062</v>
       </c>
       <c r="D33" t="n">
-        <v>90.7870250168949</v>
+        <v>90.7870173867412</v>
       </c>
       <c r="E33" t="n">
-        <v>90.77799224853516</v>
+        <v>90.77798461914062</v>
       </c>
       <c r="F33" t="n">
-        <v>90.7870250168949</v>
+        <v>90.7870173867412</v>
       </c>
       <c r="G33" t="n">
         <v>2577800</v>
@@ -1231,16 +1231,16 @@
         <v>45342</v>
       </c>
       <c r="C35" t="n">
-        <v>90.80506896972656</v>
+        <v>90.80508422851562</v>
       </c>
       <c r="D35" t="n">
-        <v>90.8140948459574</v>
+        <v>90.81411010626316</v>
       </c>
       <c r="E35" t="n">
-        <v>90.79603620351386</v>
+        <v>90.79605146078508</v>
       </c>
       <c r="F35" t="n">
-        <v>90.80506896972656</v>
+        <v>90.80508422851562</v>
       </c>
       <c r="G35" t="n">
         <v>3268600</v>
@@ -1254,16 +1254,16 @@
         <v>45343</v>
       </c>
       <c r="C36" t="n">
-        <v>90.81411743164062</v>
+        <v>90.81410980224609</v>
       </c>
       <c r="D36" t="n">
-        <v>90.83218296855895</v>
+        <v>90.83217533764672</v>
       </c>
       <c r="E36" t="n">
-        <v>90.81411743164062</v>
+        <v>90.81410980224609</v>
       </c>
       <c r="F36" t="n">
-        <v>90.82315020009979</v>
+        <v>90.8231425699464</v>
       </c>
       <c r="G36" t="n">
         <v>2302700</v>
@@ -1277,16 +1277,16 @@
         <v>45344</v>
       </c>
       <c r="C37" t="n">
-        <v>90.85023498535156</v>
+        <v>90.8502197265625</v>
       </c>
       <c r="D37" t="n">
-        <v>90.85926775315153</v>
+        <v>90.85925249284537</v>
       </c>
       <c r="E37" t="n">
-        <v>90.85023498535156</v>
+        <v>90.8502197265625</v>
       </c>
       <c r="F37" t="n">
-        <v>90.85023498535156</v>
+        <v>90.8502197265625</v>
       </c>
       <c r="G37" t="n">
         <v>2452200</v>
@@ -1300,16 +1300,16 @@
         <v>45345</v>
       </c>
       <c r="C38" t="n">
-        <v>90.8773193359375</v>
+        <v>90.87732696533203</v>
       </c>
       <c r="D38" t="n">
-        <v>90.8773193359375</v>
+        <v>90.87732696533203</v>
       </c>
       <c r="E38" t="n">
-        <v>90.86829345882208</v>
+        <v>90.86830108745886</v>
       </c>
       <c r="F38" t="n">
-        <v>90.8773193359375</v>
+        <v>90.87732696533203</v>
       </c>
       <c r="G38" t="n">
         <v>2010100</v>
@@ -1323,16 +1323,16 @@
         <v>45348</v>
       </c>
       <c r="C39" t="n">
-        <v>90.8863525390625</v>
+        <v>90.88637542724609</v>
       </c>
       <c r="D39" t="n">
-        <v>90.89538530620379</v>
+        <v>90.89540819666213</v>
       </c>
       <c r="E39" t="n">
-        <v>90.8863525390625</v>
+        <v>90.88637542724609</v>
       </c>
       <c r="F39" t="n">
-        <v>90.8863525390625</v>
+        <v>90.88637542724609</v>
       </c>
       <c r="G39" t="n">
         <v>2645100</v>
@@ -1392,16 +1392,16 @@
         <v>45351</v>
       </c>
       <c r="C42" t="n">
-        <v>90.94052124023438</v>
+        <v>90.94053649902344</v>
       </c>
       <c r="D42" t="n">
-        <v>90.94955400597301</v>
+        <v>90.94956926627766</v>
       </c>
       <c r="E42" t="n">
-        <v>90.94052124023438</v>
+        <v>90.94053649902344</v>
       </c>
       <c r="F42" t="n">
-        <v>90.94052124023438</v>
+        <v>90.94053649902344</v>
       </c>
       <c r="G42" t="n">
         <v>5560200</v>
@@ -1415,16 +1415,16 @@
         <v>45352</v>
       </c>
       <c r="C43" t="n">
-        <v>90.96772766113281</v>
+        <v>90.96771240234375</v>
       </c>
       <c r="D43" t="n">
-        <v>90.96772766113281</v>
+        <v>90.96771240234375</v>
       </c>
       <c r="E43" t="n">
-        <v>90.95865796807648</v>
+        <v>90.95864271080876</v>
       </c>
       <c r="F43" t="n">
-        <v>90.96772766113281</v>
+        <v>90.96771240234375</v>
       </c>
       <c r="G43" t="n">
         <v>7579200</v>
@@ -1438,16 +1438,16 @@
         <v>45355</v>
       </c>
       <c r="C44" t="n">
-        <v>90.97682189941406</v>
+        <v>90.97682952880859</v>
       </c>
       <c r="D44" t="n">
-        <v>90.98588467676672</v>
+        <v>90.98589230692126</v>
       </c>
       <c r="E44" t="n">
-        <v>90.97682189941406</v>
+        <v>90.97682952880859</v>
       </c>
       <c r="F44" t="n">
-        <v>90.97682189941406</v>
+        <v>90.97682952880859</v>
       </c>
       <c r="G44" t="n">
         <v>3613500</v>
@@ -1461,16 +1461,16 @@
         <v>45356</v>
       </c>
       <c r="C45" t="n">
-        <v>90.98586273193359</v>
+        <v>90.98587036132812</v>
       </c>
       <c r="D45" t="n">
-        <v>90.99493242524937</v>
+        <v>90.99494005540443</v>
       </c>
       <c r="E45" t="n">
-        <v>90.98586273193359</v>
+        <v>90.98587036132812</v>
       </c>
       <c r="F45" t="n">
-        <v>90.98586273193359</v>
+        <v>90.98587036132812</v>
       </c>
       <c r="G45" t="n">
         <v>3905300</v>
@@ -1484,16 +1484,16 @@
         <v>45357</v>
       </c>
       <c r="C46" t="n">
-        <v>91.00401306152344</v>
+        <v>91.0040283203125</v>
       </c>
       <c r="D46" t="n">
-        <v>91.01308275592983</v>
+        <v>91.01309801623961</v>
       </c>
       <c r="E46" t="n">
-        <v>90.99494336711705</v>
+        <v>90.99495862438538</v>
       </c>
       <c r="F46" t="n">
-        <v>91.00401306152344</v>
+        <v>91.0040283203125</v>
       </c>
       <c r="G46" t="n">
         <v>2760000</v>
@@ -1507,16 +1507,16 @@
         <v>45358</v>
       </c>
       <c r="C47" t="n">
-        <v>91.04935455322266</v>
+        <v>91.04934692382812</v>
       </c>
       <c r="D47" t="n">
-        <v>91.04935455322266</v>
+        <v>91.04934692382812</v>
       </c>
       <c r="E47" t="n">
-        <v>91.04028485882247</v>
+        <v>91.04027723018791</v>
       </c>
       <c r="F47" t="n">
-        <v>91.04935455322266</v>
+        <v>91.04934692382812</v>
       </c>
       <c r="G47" t="n">
         <v>2415500</v>
@@ -1530,16 +1530,16 @@
         <v>45359</v>
       </c>
       <c r="C48" t="n">
-        <v>91.05841064453125</v>
+        <v>91.05840301513672</v>
       </c>
       <c r="D48" t="n">
-        <v>91.06748033826561</v>
+        <v>91.06747270811117</v>
       </c>
       <c r="E48" t="n">
-        <v>91.0493478689462</v>
+        <v>91.04934024031101</v>
       </c>
       <c r="F48" t="n">
-        <v>91.06748033826561</v>
+        <v>91.06747270811117</v>
       </c>
       <c r="G48" t="n">
         <v>3748900</v>
@@ -1553,16 +1553,16 @@
         <v>45362</v>
       </c>
       <c r="C49" t="n">
-        <v>91.07656860351562</v>
+        <v>91.07656097412109</v>
       </c>
       <c r="D49" t="n">
-        <v>91.07656860351562</v>
+        <v>91.07656097412109</v>
       </c>
       <c r="E49" t="n">
-        <v>91.06749890793186</v>
+        <v>91.06749127929709</v>
       </c>
       <c r="F49" t="n">
-        <v>91.07656860351562</v>
+        <v>91.07656097412109</v>
       </c>
       <c r="G49" t="n">
         <v>3238400</v>
@@ -1576,16 +1576,16 @@
         <v>45363</v>
       </c>
       <c r="C50" t="n">
-        <v>91.08561706542969</v>
+        <v>91.08562469482422</v>
       </c>
       <c r="D50" t="n">
-        <v>91.09468675958801</v>
+        <v>91.09469438974223</v>
       </c>
       <c r="E50" t="n">
-        <v>91.08561706542969</v>
+        <v>91.08562469482422</v>
       </c>
       <c r="F50" t="n">
-        <v>91.08561706542969</v>
+        <v>91.08562469482422</v>
       </c>
       <c r="G50" t="n">
         <v>2613300</v>
@@ -1599,16 +1599,16 @@
         <v>45364</v>
       </c>
       <c r="C51" t="n">
-        <v>91.09470367431641</v>
+        <v>91.09468078613281</v>
       </c>
       <c r="D51" t="n">
-        <v>91.10377337015881</v>
+        <v>91.1037504796964</v>
       </c>
       <c r="E51" t="n">
-        <v>91.09470367431641</v>
+        <v>91.09468078613281</v>
       </c>
       <c r="F51" t="n">
-        <v>91.09470367431641</v>
+        <v>91.09468078613281</v>
       </c>
       <c r="G51" t="n">
         <v>2249300</v>
@@ -1622,16 +1622,16 @@
         <v>45365</v>
       </c>
       <c r="C52" t="n">
-        <v>91.13097381591797</v>
+        <v>91.13095855712891</v>
       </c>
       <c r="D52" t="n">
-        <v>91.14004351158884</v>
+        <v>91.14002825128117</v>
       </c>
       <c r="E52" t="n">
-        <v>91.13097381591797</v>
+        <v>91.13095855712891</v>
       </c>
       <c r="F52" t="n">
-        <v>91.13097381591797</v>
+        <v>91.13095855712891</v>
       </c>
       <c r="G52" t="n">
         <v>3469600</v>
@@ -1645,16 +1645,16 @@
         <v>45366</v>
       </c>
       <c r="C53" t="n">
-        <v>91.14909362792969</v>
+        <v>91.14907836914062</v>
       </c>
       <c r="D53" t="n">
-        <v>91.14909362792969</v>
+        <v>91.14907836914062</v>
       </c>
       <c r="E53" t="n">
-        <v>91.14003085166847</v>
+        <v>91.14001559439656</v>
       </c>
       <c r="F53" t="n">
-        <v>91.14909362792969</v>
+        <v>91.14907836914062</v>
       </c>
       <c r="G53" t="n">
         <v>3277300</v>
@@ -1668,16 +1668,16 @@
         <v>45369</v>
       </c>
       <c r="C54" t="n">
-        <v>91.15814971923828</v>
+        <v>91.15817260742188</v>
       </c>
       <c r="D54" t="n">
-        <v>91.16721941229589</v>
+        <v>91.1672423027567</v>
       </c>
       <c r="E54" t="n">
-        <v>91.15814971923828</v>
+        <v>91.15817260742188</v>
       </c>
       <c r="F54" t="n">
-        <v>91.16721941229589</v>
+        <v>91.1672423027567</v>
       </c>
       <c r="G54" t="n">
         <v>3576200</v>
@@ -1714,16 +1714,16 @@
         <v>45371</v>
       </c>
       <c r="C56" t="n">
-        <v>91.18535614013672</v>
+        <v>91.18537902832031</v>
       </c>
       <c r="D56" t="n">
-        <v>91.19442583361803</v>
+        <v>91.19444872407817</v>
       </c>
       <c r="E56" t="n">
-        <v>91.18535614013672</v>
+        <v>91.18537902832031</v>
       </c>
       <c r="F56" t="n">
-        <v>91.18535614013672</v>
+        <v>91.18537902832031</v>
       </c>
       <c r="G56" t="n">
         <v>2492700</v>
@@ -1737,16 +1737,16 @@
         <v>45372</v>
       </c>
       <c r="C57" t="n">
-        <v>91.22163391113281</v>
+        <v>91.22164154052734</v>
       </c>
       <c r="D57" t="n">
-        <v>91.23070360520224</v>
+        <v>91.23071123535532</v>
       </c>
       <c r="E57" t="n">
-        <v>91.22163391113281</v>
+        <v>91.22164154052734</v>
       </c>
       <c r="F57" t="n">
-        <v>91.22163391113281</v>
+        <v>91.22164154052734</v>
       </c>
       <c r="G57" t="n">
         <v>3547400</v>
@@ -1783,16 +1783,16 @@
         <v>45376</v>
       </c>
       <c r="C59" t="n">
-        <v>91.25790405273438</v>
+        <v>91.25791168212891</v>
       </c>
       <c r="D59" t="n">
-        <v>91.26697374663321</v>
+        <v>91.26698137678599</v>
       </c>
       <c r="E59" t="n">
-        <v>91.25790405273438</v>
+        <v>91.25791168212891</v>
       </c>
       <c r="F59" t="n">
-        <v>91.25790405273438</v>
+        <v>91.25791168212891</v>
       </c>
       <c r="G59" t="n">
         <v>2422900</v>
@@ -1806,16 +1806,16 @@
         <v>45377</v>
       </c>
       <c r="C60" t="n">
-        <v>91.26699066162109</v>
+        <v>91.26697540283203</v>
       </c>
       <c r="D60" t="n">
-        <v>91.27606035720085</v>
+        <v>91.27604509689544</v>
       </c>
       <c r="E60" t="n">
-        <v>91.26699066162109</v>
+        <v>91.26697540283203</v>
       </c>
       <c r="F60" t="n">
-        <v>91.26699066162109</v>
+        <v>91.26697540283203</v>
       </c>
       <c r="G60" t="n">
         <v>3181700</v>
@@ -1829,16 +1829,16 @@
         <v>45378</v>
       </c>
       <c r="C61" t="n">
-        <v>91.31230926513672</v>
+        <v>91.31232452392578</v>
       </c>
       <c r="D61" t="n">
-        <v>91.32137895912348</v>
+        <v>91.32139421942814</v>
       </c>
       <c r="E61" t="n">
-        <v>91.31230926513672</v>
+        <v>91.31232452392578</v>
       </c>
       <c r="F61" t="n">
-        <v>91.32137895912348</v>
+        <v>91.32139421942814</v>
       </c>
       <c r="G61" t="n">
         <v>2990800</v>
@@ -1852,16 +1852,16 @@
         <v>45379</v>
       </c>
       <c r="C62" t="n">
-        <v>91.32138824462891</v>
+        <v>91.32138061523438</v>
       </c>
       <c r="D62" t="n">
-        <v>91.33045793953788</v>
+        <v>91.33045030938563</v>
       </c>
       <c r="E62" t="n">
-        <v>91.32138824462891</v>
+        <v>91.32138061523438</v>
       </c>
       <c r="F62" t="n">
-        <v>91.33045793953788</v>
+        <v>91.33045030938563</v>
       </c>
       <c r="G62" t="n">
         <v>5425800</v>
@@ -1898,16 +1898,16 @@
         <v>45384</v>
       </c>
       <c r="C64" t="n">
-        <v>91.36692047119141</v>
+        <v>91.36693572998047</v>
       </c>
       <c r="D64" t="n">
-        <v>91.36692047119141</v>
+        <v>91.36693572998047</v>
       </c>
       <c r="E64" t="n">
-        <v>91.35781701856003</v>
+        <v>91.35783227582876</v>
       </c>
       <c r="F64" t="n">
-        <v>91.36692047119141</v>
+        <v>91.36693572998047</v>
       </c>
       <c r="G64" t="n">
         <v>4202900</v>
@@ -1921,16 +1921,16 @@
         <v>45385</v>
       </c>
       <c r="C65" t="n">
-        <v>91.37602996826172</v>
+        <v>91.37600708007812</v>
       </c>
       <c r="D65" t="n">
-        <v>91.38514037000337</v>
+        <v>91.38511747953777</v>
       </c>
       <c r="E65" t="n">
-        <v>91.37602996826172</v>
+        <v>91.37600708007812</v>
       </c>
       <c r="F65" t="n">
-        <v>91.37602996826172</v>
+        <v>91.37600708007812</v>
       </c>
       <c r="G65" t="n">
         <v>4333600</v>
@@ -1944,16 +1944,16 @@
         <v>45386</v>
       </c>
       <c r="C66" t="n">
-        <v>91.42156982421875</v>
+        <v>91.42158508300781</v>
       </c>
       <c r="D66" t="n">
-        <v>91.42156982421875</v>
+        <v>91.42158508300781</v>
       </c>
       <c r="E66" t="n">
-        <v>91.41245942299565</v>
+        <v>91.41247468026413</v>
       </c>
       <c r="F66" t="n">
-        <v>91.41245942299565</v>
+        <v>91.41247468026413</v>
       </c>
       <c r="G66" t="n">
         <v>3427500</v>
@@ -1967,16 +1967,16 @@
         <v>45387</v>
       </c>
       <c r="C67" t="n">
-        <v>91.4306640625</v>
+        <v>91.43067932128906</v>
       </c>
       <c r="D67" t="n">
-        <v>91.43977446280502</v>
+        <v>91.43978972311452</v>
       </c>
       <c r="E67" t="n">
-        <v>91.4306640625</v>
+        <v>91.43067932128906</v>
       </c>
       <c r="F67" t="n">
-        <v>91.43977446280502</v>
+        <v>91.43978972311452</v>
       </c>
       <c r="G67" t="n">
         <v>3104200</v>
@@ -2036,16 +2036,16 @@
         <v>45392</v>
       </c>
       <c r="C70" t="n">
-        <v>91.47624206542969</v>
+        <v>91.47622680664062</v>
       </c>
       <c r="D70" t="n">
-        <v>91.47624206542969</v>
+        <v>91.47622680664062</v>
       </c>
       <c r="E70" t="n">
-        <v>91.45802820745816</v>
+        <v>91.45801295170727</v>
       </c>
       <c r="F70" t="n">
-        <v>91.46713166184301</v>
+        <v>91.46711640457362</v>
       </c>
       <c r="G70" t="n">
         <v>3893100</v>
@@ -2059,16 +2059,16 @@
         <v>45393</v>
       </c>
       <c r="C71" t="n">
-        <v>91.51264953613281</v>
+        <v>91.51265716552734</v>
       </c>
       <c r="D71" t="n">
-        <v>91.51264953613281</v>
+        <v>91.51265716552734</v>
       </c>
       <c r="E71" t="n">
-        <v>91.50353913525345</v>
+        <v>91.50354676388844</v>
       </c>
       <c r="F71" t="n">
-        <v>91.50353913525345</v>
+        <v>91.50354676388844</v>
       </c>
       <c r="G71" t="n">
         <v>3521100</v>
@@ -2105,16 +2105,16 @@
         <v>45397</v>
       </c>
       <c r="C73" t="n">
-        <v>91.53998565673828</v>
+        <v>91.53999328613281</v>
       </c>
       <c r="D73" t="n">
-        <v>91.53998565673828</v>
+        <v>91.53999328613281</v>
       </c>
       <c r="E73" t="n">
-        <v>91.53087525467784</v>
+        <v>91.53088288331307</v>
       </c>
       <c r="F73" t="n">
-        <v>91.53087525467784</v>
+        <v>91.53088288331307</v>
       </c>
       <c r="G73" t="n">
         <v>4144700</v>
@@ -2128,16 +2128,16 @@
         <v>45398</v>
       </c>
       <c r="C74" t="n">
-        <v>91.53998565673828</v>
+        <v>91.53999328613281</v>
       </c>
       <c r="D74" t="n">
-        <v>91.5581995116585</v>
+        <v>91.55820714257106</v>
       </c>
       <c r="E74" t="n">
-        <v>91.53998565673828</v>
+        <v>91.53999328613281</v>
       </c>
       <c r="F74" t="n">
-        <v>91.54909605879871</v>
+        <v>91.54910368895256</v>
       </c>
       <c r="G74" t="n">
         <v>4850000</v>
@@ -2151,16 +2151,16 @@
         <v>45399</v>
       </c>
       <c r="C75" t="n">
-        <v>91.56730651855469</v>
+        <v>91.56732177734375</v>
       </c>
       <c r="D75" t="n">
-        <v>91.56730651855469</v>
+        <v>91.56732177734375</v>
       </c>
       <c r="E75" t="n">
-        <v>91.55819611683205</v>
+        <v>91.55821137410295</v>
       </c>
       <c r="F75" t="n">
-        <v>91.56730651855469</v>
+        <v>91.56732177734375</v>
       </c>
       <c r="G75" t="n">
         <v>3688400</v>
@@ -2174,16 +2174,16 @@
         <v>45400</v>
       </c>
       <c r="C76" t="n">
-        <v>91.59462738037109</v>
+        <v>91.59464263916016</v>
       </c>
       <c r="D76" t="n">
-        <v>91.60373778175614</v>
+        <v>91.60375304206291</v>
       </c>
       <c r="E76" t="n">
-        <v>91.59462738037109</v>
+        <v>91.59464263916016</v>
       </c>
       <c r="F76" t="n">
-        <v>91.60373778175614</v>
+        <v>91.60375304206291</v>
       </c>
       <c r="G76" t="n">
         <v>3235600</v>
@@ -2197,16 +2197,16 @@
         <v>45401</v>
       </c>
       <c r="C77" t="n">
-        <v>91.62198638916016</v>
+        <v>91.62196350097656</v>
       </c>
       <c r="D77" t="n">
-        <v>91.62198638916016</v>
+        <v>91.62196350097656</v>
       </c>
       <c r="E77" t="n">
-        <v>91.60377252868138</v>
+        <v>91.60374964504781</v>
       </c>
       <c r="F77" t="n">
-        <v>91.62198638916016</v>
+        <v>91.62196350097656</v>
       </c>
       <c r="G77" t="n">
         <v>3319500</v>
@@ -2243,16 +2243,16 @@
         <v>45405</v>
       </c>
       <c r="C79" t="n">
-        <v>91.64015960693359</v>
+        <v>91.64018249511719</v>
       </c>
       <c r="D79" t="n">
-        <v>91.64927000704303</v>
+        <v>91.64929289750205</v>
       </c>
       <c r="E79" t="n">
-        <v>91.63104920682416</v>
+        <v>91.63107209273232</v>
       </c>
       <c r="F79" t="n">
-        <v>91.64015960693359</v>
+        <v>91.64018249511719</v>
       </c>
       <c r="G79" t="n">
         <v>4233300</v>
@@ -2312,16 +2312,16 @@
         <v>45408</v>
       </c>
       <c r="C82" t="n">
-        <v>91.71305847167969</v>
+        <v>91.71306610107422</v>
       </c>
       <c r="D82" t="n">
-        <v>91.71305847167969</v>
+        <v>91.71306610107422</v>
       </c>
       <c r="E82" t="n">
-        <v>91.70394806863366</v>
+        <v>91.70395569727032</v>
       </c>
       <c r="F82" t="n">
-        <v>91.70394806863366</v>
+        <v>91.70395569727032</v>
       </c>
       <c r="G82" t="n">
         <v>3008600</v>
@@ -2335,16 +2335,16 @@
         <v>45411</v>
       </c>
       <c r="C83" t="n">
-        <v>91.71305847167969</v>
+        <v>91.71306610107422</v>
       </c>
       <c r="D83" t="n">
-        <v>91.7221619255243</v>
+        <v>91.72216955567613</v>
       </c>
       <c r="E83" t="n">
-        <v>91.71305847167969</v>
+        <v>91.71306610107422</v>
       </c>
       <c r="F83" t="n">
-        <v>91.7221619255243</v>
+        <v>91.72216955567613</v>
       </c>
       <c r="G83" t="n">
         <v>2501900</v>
@@ -2358,16 +2358,16 @@
         <v>45412</v>
       </c>
       <c r="C84" t="n">
-        <v>91.72215270996094</v>
+        <v>91.72216033935547</v>
       </c>
       <c r="D84" t="n">
-        <v>91.73126311209163</v>
+        <v>91.73127074224395</v>
       </c>
       <c r="E84" t="n">
-        <v>91.72215270996094</v>
+        <v>91.72216033935547</v>
       </c>
       <c r="F84" t="n">
-        <v>91.72215270996094</v>
+        <v>91.72216033935547</v>
       </c>
       <c r="G84" t="n">
         <v>6488000</v>
@@ -2381,16 +2381,16 @@
         <v>45413</v>
       </c>
       <c r="C85" t="n">
-        <v>91.75691223144531</v>
+        <v>91.75691986083984</v>
       </c>
       <c r="D85" t="n">
-        <v>91.75691223144531</v>
+        <v>91.75691986083984</v>
       </c>
       <c r="E85" t="n">
-        <v>91.74776992151747</v>
+        <v>91.74777755015184</v>
       </c>
       <c r="F85" t="n">
-        <v>91.75691223144531</v>
+        <v>91.75691986083984</v>
       </c>
       <c r="G85" t="n">
         <v>8406600</v>
@@ -2404,16 +2404,16 @@
         <v>45414</v>
       </c>
       <c r="C86" t="n">
-        <v>91.79348754882812</v>
+        <v>91.79349517822266</v>
       </c>
       <c r="D86" t="n">
-        <v>91.79348754882812</v>
+        <v>91.79349517822266</v>
       </c>
       <c r="E86" t="n">
-        <v>91.78433826151877</v>
+        <v>91.78434589015285</v>
       </c>
       <c r="F86" t="n">
-        <v>91.79348754882812</v>
+        <v>91.79349517822266</v>
       </c>
       <c r="G86" t="n">
         <v>4369600</v>
@@ -2427,16 +2427,16 @@
         <v>45415</v>
       </c>
       <c r="C87" t="n">
-        <v>91.81179809570312</v>
+        <v>91.81181335449219</v>
       </c>
       <c r="D87" t="n">
-        <v>91.81179809570312</v>
+        <v>91.81181335449219</v>
       </c>
       <c r="E87" t="n">
-        <v>91.79349951869828</v>
+        <v>91.79351477444618</v>
       </c>
       <c r="F87" t="n">
-        <v>91.8026488072007</v>
+        <v>91.80266406446918</v>
       </c>
       <c r="G87" t="n">
         <v>4792400</v>
@@ -2496,16 +2496,16 @@
         <v>45420</v>
       </c>
       <c r="C90" t="n">
-        <v>91.84837341308594</v>
+        <v>91.84840393066406</v>
       </c>
       <c r="D90" t="n">
-        <v>91.84837341308594</v>
+        <v>91.84840393066406</v>
       </c>
       <c r="E90" t="n">
-        <v>91.83007483904115</v>
+        <v>91.83010535053937</v>
       </c>
       <c r="F90" t="n">
-        <v>91.83922412606354</v>
+        <v>91.83925464060172</v>
       </c>
       <c r="G90" t="n">
         <v>3109400</v>
@@ -2519,16 +2519,16 @@
         <v>45421</v>
       </c>
       <c r="C91" t="n">
-        <v>91.87583160400391</v>
+        <v>91.87583923339844</v>
       </c>
       <c r="D91" t="n">
-        <v>91.88497391388746</v>
+        <v>91.88498154404117</v>
       </c>
       <c r="E91" t="n">
-        <v>91.87583160400391</v>
+        <v>91.87583923339844</v>
       </c>
       <c r="F91" t="n">
-        <v>91.88040275894568</v>
+        <v>91.8804103887198</v>
       </c>
       <c r="G91" t="n">
         <v>2739600</v>
@@ -2565,16 +2565,16 @@
         <v>45425</v>
       </c>
       <c r="C93" t="n">
-        <v>91.91242218017578</v>
+        <v>91.91239166259766</v>
       </c>
       <c r="D93" t="n">
-        <v>91.91242218017578</v>
+        <v>91.91239166259766</v>
       </c>
       <c r="E93" t="n">
-        <v>91.9032728913899</v>
+        <v>91.9032423768496</v>
       </c>
       <c r="F93" t="n">
-        <v>91.91242218017578</v>
+        <v>91.91239166259766</v>
       </c>
       <c r="G93" t="n">
         <v>3317000</v>
@@ -2588,16 +2588,16 @@
         <v>45426</v>
       </c>
       <c r="C94" t="n">
-        <v>91.91242218017578</v>
+        <v>91.91239166259766</v>
       </c>
       <c r="D94" t="n">
-        <v>91.92156449009912</v>
+        <v>91.92153396948548</v>
       </c>
       <c r="E94" t="n">
-        <v>91.91242218017578</v>
+        <v>91.91239166259766</v>
       </c>
       <c r="F94" t="n">
-        <v>91.92156449009912</v>
+        <v>91.92153396948548</v>
       </c>
       <c r="G94" t="n">
         <v>2765800</v>
@@ -2611,16 +2611,16 @@
         <v>45427</v>
       </c>
       <c r="C95" t="n">
-        <v>91.93070220947266</v>
+        <v>91.93071746826172</v>
       </c>
       <c r="D95" t="n">
-        <v>91.93985149710711</v>
+        <v>91.93986675741478</v>
       </c>
       <c r="E95" t="n">
-        <v>91.93070220947266</v>
+        <v>91.93071746826172</v>
       </c>
       <c r="F95" t="n">
-        <v>91.93070220947266</v>
+        <v>91.93071746826172</v>
       </c>
       <c r="G95" t="n">
         <v>4228600</v>
@@ -2634,16 +2634,16 @@
         <v>45428</v>
       </c>
       <c r="C96" t="n">
-        <v>91.97644805908203</v>
+        <v>91.97643280029297</v>
       </c>
       <c r="D96" t="n">
-        <v>91.98559036849001</v>
+        <v>91.98557510818425</v>
       </c>
       <c r="E96" t="n">
-        <v>91.96729877081192</v>
+        <v>91.96728351354071</v>
       </c>
       <c r="F96" t="n">
-        <v>91.97644805908203</v>
+        <v>91.97643280029297</v>
       </c>
       <c r="G96" t="n">
         <v>3699500</v>
@@ -2680,16 +2680,16 @@
         <v>45432</v>
       </c>
       <c r="C98" t="n">
-        <v>91.99473571777344</v>
+        <v>91.9947509765625</v>
       </c>
       <c r="D98" t="n">
-        <v>92.0038850056518</v>
+        <v>92.00390026595842</v>
       </c>
       <c r="E98" t="n">
-        <v>91.99473571777344</v>
+        <v>91.9947509765625</v>
       </c>
       <c r="F98" t="n">
-        <v>92.0038850056518</v>
+        <v>92.00390026595842</v>
       </c>
       <c r="G98" t="n">
         <v>3341000</v>
@@ -2703,16 +2703,16 @@
         <v>45433</v>
       </c>
       <c r="C99" t="n">
-        <v>92.01303100585938</v>
+        <v>92.01303863525391</v>
       </c>
       <c r="D99" t="n">
-        <v>92.02218029410477</v>
+        <v>92.02218792425793</v>
       </c>
       <c r="E99" t="n">
-        <v>92.01303100585938</v>
+        <v>92.01303863525391</v>
       </c>
       <c r="F99" t="n">
-        <v>92.01303100585938</v>
+        <v>92.01303863525391</v>
       </c>
       <c r="G99" t="n">
         <v>3774900</v>
@@ -2726,16 +2726,16 @@
         <v>45434</v>
       </c>
       <c r="C100" t="n">
-        <v>92.02219390869141</v>
+        <v>92.02217864990234</v>
       </c>
       <c r="D100" t="n">
-        <v>92.03134319829043</v>
+        <v>92.03132793798427</v>
       </c>
       <c r="E100" t="n">
-        <v>92.02219390869141</v>
+        <v>92.02217864990234</v>
       </c>
       <c r="F100" t="n">
-        <v>92.03134319829043</v>
+        <v>92.03132793798427</v>
       </c>
       <c r="G100" t="n">
         <v>2609000</v>
@@ -2749,16 +2749,16 @@
         <v>45435</v>
       </c>
       <c r="C101" t="n">
-        <v>92.08620452880859</v>
+        <v>92.08622741699219</v>
       </c>
       <c r="D101" t="n">
-        <v>92.08620452880859</v>
+        <v>92.08622741699219</v>
       </c>
       <c r="E101" t="n">
-        <v>92.07706222010293</v>
+        <v>92.0770851060142</v>
       </c>
       <c r="F101" t="n">
-        <v>92.07706222010293</v>
+        <v>92.0770851060142</v>
       </c>
       <c r="G101" t="n">
         <v>3077800</v>
@@ -2795,16 +2795,16 @@
         <v>45440</v>
       </c>
       <c r="C103" t="n">
-        <v>92.10452270507812</v>
+        <v>92.10451507568359</v>
       </c>
       <c r="D103" t="n">
-        <v>92.10452270507812</v>
+        <v>92.10451507568359</v>
       </c>
       <c r="E103" t="n">
-        <v>92.09537341556376</v>
+        <v>92.0953657869271</v>
       </c>
       <c r="F103" t="n">
-        <v>92.09537341556376</v>
+        <v>92.0953657869271</v>
       </c>
       <c r="G103" t="n">
         <v>3684600</v>
@@ -2818,16 +2818,16 @@
         <v>45441</v>
       </c>
       <c r="C104" t="n">
-        <v>92.10452270507812</v>
+        <v>92.10451507568359</v>
       </c>
       <c r="D104" t="n">
-        <v>92.1136650157294</v>
+        <v>92.11365738557757</v>
       </c>
       <c r="E104" t="n">
-        <v>92.10452270507812</v>
+        <v>92.10451507568359</v>
       </c>
       <c r="F104" t="n">
-        <v>92.1136650157294</v>
+        <v>92.11365738557757</v>
       </c>
       <c r="G104" t="n">
         <v>3971700</v>
@@ -2841,16 +2841,16 @@
         <v>45442</v>
       </c>
       <c r="C105" t="n">
-        <v>92.12279510498047</v>
+        <v>92.122802734375</v>
       </c>
       <c r="D105" t="n">
-        <v>92.13194439258794</v>
+        <v>92.13195202274019</v>
       </c>
       <c r="E105" t="n">
-        <v>92.12279510498047</v>
+        <v>92.122802734375</v>
       </c>
       <c r="F105" t="n">
-        <v>92.12279510498047</v>
+        <v>92.122802734375</v>
       </c>
       <c r="G105" t="n">
         <v>3566800</v>
@@ -2864,16 +2864,16 @@
         <v>45443</v>
       </c>
       <c r="C106" t="n">
-        <v>92.15938568115234</v>
+        <v>92.15940856933594</v>
       </c>
       <c r="D106" t="n">
-        <v>92.15938568115234</v>
+        <v>92.15940856933594</v>
       </c>
       <c r="E106" t="n">
-        <v>92.15023639350471</v>
+        <v>92.15025927941603</v>
       </c>
       <c r="F106" t="n">
-        <v>92.15023639350471</v>
+        <v>92.15025927941603</v>
       </c>
       <c r="G106" t="n">
         <v>7082900</v>
@@ -2933,16 +2933,16 @@
         <v>45448</v>
       </c>
       <c r="C109" t="n">
-        <v>92.21452331542969</v>
+        <v>92.21454620361328</v>
       </c>
       <c r="D109" t="n">
-        <v>92.21452331542969</v>
+        <v>92.21454620361328</v>
       </c>
       <c r="E109" t="n">
-        <v>92.205333894294</v>
+        <v>92.20535678019672</v>
       </c>
       <c r="F109" t="n">
-        <v>92.205333894294</v>
+        <v>92.20535678019672</v>
       </c>
       <c r="G109" t="n">
         <v>4285300</v>
@@ -2956,16 +2956,16 @@
         <v>45449</v>
       </c>
       <c r="C110" t="n">
-        <v>92.21452331542969</v>
+        <v>92.21454620361328</v>
       </c>
       <c r="D110" t="n">
-        <v>92.22370572709083</v>
+        <v>92.22372861755355</v>
       </c>
       <c r="E110" t="n">
-        <v>92.21452331542969</v>
+        <v>92.21454620361328</v>
       </c>
       <c r="F110" t="n">
-        <v>92.22370572709083</v>
+        <v>92.22372861755355</v>
       </c>
       <c r="G110" t="n">
         <v>3376100</v>
@@ -2979,16 +2979,16 @@
         <v>45450</v>
       </c>
       <c r="C111" t="n">
-        <v>92.25126647949219</v>
+        <v>92.25128173828125</v>
       </c>
       <c r="D111" t="n">
-        <v>92.2604488904057</v>
+        <v>92.26046415071357</v>
       </c>
       <c r="E111" t="n">
-        <v>92.25126647949219</v>
+        <v>92.25128173828125</v>
       </c>
       <c r="F111" t="n">
-        <v>92.2604488904057</v>
+        <v>92.26046415071357</v>
       </c>
       <c r="G111" t="n">
         <v>3490400</v>
@@ -3002,16 +3002,16 @@
         <v>45453</v>
       </c>
       <c r="C112" t="n">
-        <v>92.26964569091797</v>
+        <v>92.26963806152344</v>
       </c>
       <c r="D112" t="n">
-        <v>92.27883511204048</v>
+        <v>92.27882748188611</v>
       </c>
       <c r="E112" t="n">
-        <v>92.26964569091797</v>
+        <v>92.26963806152344</v>
       </c>
       <c r="F112" t="n">
-        <v>92.27883511204048</v>
+        <v>92.27882748188611</v>
       </c>
       <c r="G112" t="n">
         <v>2732300</v>
@@ -3025,16 +3025,16 @@
         <v>45454</v>
       </c>
       <c r="C113" t="n">
-        <v>92.28801727294922</v>
+        <v>92.28802490234375</v>
       </c>
       <c r="D113" t="n">
-        <v>92.28801727294922</v>
+        <v>92.28802490234375</v>
       </c>
       <c r="E113" t="n">
-        <v>92.2788348613262</v>
+        <v>92.27884248996163</v>
       </c>
       <c r="F113" t="n">
-        <v>92.28801727294922</v>
+        <v>92.28802490234375</v>
       </c>
       <c r="G113" t="n">
         <v>3320000</v>
@@ -3048,16 +3048,16 @@
         <v>45455</v>
       </c>
       <c r="C114" t="n">
-        <v>92.30638885498047</v>
+        <v>92.30638122558594</v>
       </c>
       <c r="D114" t="n">
-        <v>92.30638885498047</v>
+        <v>92.30638122558594</v>
       </c>
       <c r="E114" t="n">
-        <v>92.28801001423095</v>
+        <v>92.28800238635547</v>
       </c>
       <c r="F114" t="n">
-        <v>92.2971994346057</v>
+        <v>92.2971918059707</v>
       </c>
       <c r="G114" t="n">
         <v>5355700</v>
@@ -3071,16 +3071,16 @@
         <v>45456</v>
       </c>
       <c r="C115" t="n">
-        <v>92.31558227539062</v>
+        <v>92.31556701660156</v>
       </c>
       <c r="D115" t="n">
-        <v>92.32476468668929</v>
+        <v>92.32474942638248</v>
       </c>
       <c r="E115" t="n">
-        <v>92.30639285461768</v>
+        <v>92.30637759734753</v>
       </c>
       <c r="F115" t="n">
-        <v>92.31558227539062</v>
+        <v>92.31556701660156</v>
       </c>
       <c r="G115" t="n">
         <v>3925700</v>
@@ -3094,16 +3094,16 @@
         <v>45457</v>
       </c>
       <c r="C116" t="n">
-        <v>92.36152648925781</v>
+        <v>92.36151123046875</v>
       </c>
       <c r="D116" t="n">
-        <v>92.36152648925781</v>
+        <v>92.36151123046875</v>
       </c>
       <c r="E116" t="n">
-        <v>92.34315465497252</v>
+        <v>92.34313939921861</v>
       </c>
       <c r="F116" t="n">
-        <v>92.3523370673776</v>
+        <v>92.3523218101067</v>
       </c>
       <c r="G116" t="n">
         <v>3505500</v>
@@ -3117,16 +3117,16 @@
         <v>45460</v>
       </c>
       <c r="C117" t="n">
-        <v>92.37068939208984</v>
+        <v>92.37071228027344</v>
       </c>
       <c r="D117" t="n">
-        <v>92.37068939208984</v>
+        <v>92.37071228027344</v>
       </c>
       <c r="E117" t="n">
-        <v>92.36149997284787</v>
+        <v>92.36152285875446</v>
       </c>
       <c r="F117" t="n">
-        <v>92.37068939208984</v>
+        <v>92.37071228027344</v>
       </c>
       <c r="G117" t="n">
         <v>3493700</v>
@@ -3163,16 +3163,16 @@
         <v>45463</v>
       </c>
       <c r="C119" t="n">
-        <v>92.40743255615234</v>
+        <v>92.40744781494141</v>
       </c>
       <c r="D119" t="n">
-        <v>92.41661496517561</v>
+        <v>92.41663022548092</v>
       </c>
       <c r="E119" t="n">
-        <v>92.40743255615234</v>
+        <v>92.40744781494141</v>
       </c>
       <c r="F119" t="n">
-        <v>92.40743255615234</v>
+        <v>92.40744781494141</v>
       </c>
       <c r="G119" t="n">
         <v>3580700</v>
@@ -3186,16 +3186,16 @@
         <v>45464</v>
       </c>
       <c r="C120" t="n">
-        <v>92.44417572021484</v>
+        <v>92.44419097900391</v>
       </c>
       <c r="D120" t="n">
-        <v>92.45335812849311</v>
+        <v>92.4533733887978</v>
       </c>
       <c r="E120" t="n">
-        <v>92.44417572021484</v>
+        <v>92.44419097900391</v>
       </c>
       <c r="F120" t="n">
-        <v>92.44417572021484</v>
+        <v>92.44419097900391</v>
       </c>
       <c r="G120" t="n">
         <v>3460900</v>
@@ -3255,16 +3255,16 @@
         <v>45469</v>
       </c>
       <c r="C123" t="n">
-        <v>92.48097991943359</v>
+        <v>92.48094177246094</v>
       </c>
       <c r="D123" t="n">
-        <v>92.4901623330276</v>
+        <v>92.49012418226734</v>
       </c>
       <c r="E123" t="n">
-        <v>92.48097991943359</v>
+        <v>92.48094177246094</v>
       </c>
       <c r="F123" t="n">
-        <v>92.48189816079299</v>
+        <v>92.48186001344158</v>
       </c>
       <c r="G123" t="n">
         <v>4815500</v>
@@ -3324,16 +3324,16 @@
         <v>45474</v>
       </c>
       <c r="C126" t="n">
-        <v>92.56289672851562</v>
+        <v>92.56288909912109</v>
       </c>
       <c r="D126" t="n">
-        <v>92.56289672851562</v>
+        <v>92.56288909912109</v>
       </c>
       <c r="E126" t="n">
-        <v>92.55367411335638</v>
+        <v>92.55366648472202</v>
       </c>
       <c r="F126" t="n">
-        <v>92.56289672851562</v>
+        <v>92.56288909912109</v>
       </c>
       <c r="G126" t="n">
         <v>9965300</v>
@@ -3347,16 +3347,16 @@
         <v>45475</v>
       </c>
       <c r="C127" t="n">
-        <v>92.57210540771484</v>
+        <v>92.57212066650391</v>
       </c>
       <c r="D127" t="n">
-        <v>92.57210540771484</v>
+        <v>92.57212066650391</v>
       </c>
       <c r="E127" t="n">
-        <v>92.56287575448273</v>
+        <v>92.56289101175045</v>
       </c>
       <c r="F127" t="n">
-        <v>92.57210540771484</v>
+        <v>92.57212066650391</v>
       </c>
       <c r="G127" t="n">
         <v>5720900</v>
@@ -3370,16 +3370,16 @@
         <v>45476</v>
       </c>
       <c r="C128" t="n">
-        <v>92.59980773925781</v>
+        <v>92.59977722167969</v>
       </c>
       <c r="D128" t="n">
-        <v>92.59980773925781</v>
+        <v>92.59977722167969</v>
       </c>
       <c r="E128" t="n">
-        <v>92.59057808399118</v>
+        <v>92.59054756945481</v>
       </c>
       <c r="F128" t="n">
-        <v>92.59980773925781</v>
+        <v>92.59977722167969</v>
       </c>
       <c r="G128" t="n">
         <v>3986000</v>
@@ -3416,16 +3416,16 @@
         <v>45481</v>
       </c>
       <c r="C130" t="n">
-        <v>92.6551513671875</v>
+        <v>92.65515899658203</v>
       </c>
       <c r="D130" t="n">
-        <v>92.6551513671875</v>
+        <v>92.65515899658203</v>
       </c>
       <c r="E130" t="n">
-        <v>92.64592171463667</v>
+        <v>92.64592934327121</v>
       </c>
       <c r="F130" t="n">
-        <v>92.64592171463667</v>
+        <v>92.64592934327121</v>
       </c>
       <c r="G130" t="n">
         <v>3263000</v>
@@ -3439,16 +3439,16 @@
         <v>45482</v>
       </c>
       <c r="C131" t="n">
-        <v>92.6551513671875</v>
+        <v>92.65515899658203</v>
       </c>
       <c r="D131" t="n">
-        <v>92.67360363212704</v>
+        <v>92.67361126304097</v>
       </c>
       <c r="E131" t="n">
-        <v>92.6551513671875</v>
+        <v>92.65515899658203</v>
       </c>
       <c r="F131" t="n">
-        <v>92.66437397957621</v>
+        <v>92.66438160973014</v>
       </c>
       <c r="G131" t="n">
         <v>4508000</v>
@@ -3462,16 +3462,16 @@
         <v>45483</v>
       </c>
       <c r="C132" t="n">
-        <v>92.67362976074219</v>
+        <v>92.67362213134766</v>
       </c>
       <c r="D132" t="n">
-        <v>92.68285941589525</v>
+        <v>92.68285178574088</v>
       </c>
       <c r="E132" t="n">
-        <v>92.67362976074219</v>
+        <v>92.67362213134766</v>
       </c>
       <c r="F132" t="n">
-        <v>92.67362976074219</v>
+        <v>92.67362213134766</v>
       </c>
       <c r="G132" t="n">
         <v>4062200</v>
@@ -3485,16 +3485,16 @@
         <v>45484</v>
       </c>
       <c r="C133" t="n">
-        <v>92.69206237792969</v>
+        <v>92.69207000732422</v>
       </c>
       <c r="D133" t="n">
-        <v>92.69206237792969</v>
+        <v>92.69207000732422</v>
       </c>
       <c r="E133" t="n">
-        <v>92.68283976489614</v>
+        <v>92.68284739353157</v>
       </c>
       <c r="F133" t="n">
-        <v>92.68283976489614</v>
+        <v>92.68284739353157</v>
       </c>
       <c r="G133" t="n">
         <v>4195600</v>
@@ -3508,16 +3508,16 @@
         <v>45485</v>
       </c>
       <c r="C134" t="n">
-        <v>92.73821258544922</v>
+        <v>92.73818206787109</v>
       </c>
       <c r="D134" t="n">
-        <v>92.73821258544922</v>
+        <v>92.73818206787109</v>
       </c>
       <c r="E134" t="n">
-        <v>92.72898293135917</v>
+        <v>92.72895241681827</v>
       </c>
       <c r="F134" t="n">
-        <v>92.73821258544922</v>
+        <v>92.73818206787109</v>
       </c>
       <c r="G134" t="n">
         <v>3369000</v>
@@ -3531,16 +3531,16 @@
         <v>45488</v>
       </c>
       <c r="C135" t="n">
-        <v>92.73821258544922</v>
+        <v>92.73818206787109</v>
       </c>
       <c r="D135" t="n">
-        <v>92.74744223953927</v>
+        <v>92.74741171892393</v>
       </c>
       <c r="E135" t="n">
-        <v>92.73821258544922</v>
+        <v>92.73818206787109</v>
       </c>
       <c r="F135" t="n">
-        <v>92.74744223953927</v>
+        <v>92.74741171892393</v>
       </c>
       <c r="G135" t="n">
         <v>3615100</v>
@@ -3577,16 +3577,16 @@
         <v>45490</v>
       </c>
       <c r="C137" t="n">
-        <v>92.76588439941406</v>
+        <v>92.76589965820312</v>
       </c>
       <c r="D137" t="n">
-        <v>92.77050274603751</v>
+        <v>92.77051800558623</v>
       </c>
       <c r="E137" t="n">
-        <v>92.75665474632972</v>
+        <v>92.75667000360062</v>
       </c>
       <c r="F137" t="n">
-        <v>92.76588439941406</v>
+        <v>92.76589965820312</v>
       </c>
       <c r="G137" t="n">
         <v>3822100</v>
@@ -3623,16 +3623,16 @@
         <v>45492</v>
       </c>
       <c r="C139" t="n">
-        <v>92.82125091552734</v>
+        <v>92.82124328613281</v>
       </c>
       <c r="D139" t="n">
-        <v>92.82125091552734</v>
+        <v>92.82124328613281</v>
       </c>
       <c r="E139" t="n">
-        <v>92.81202830233946</v>
+        <v>92.81202067370296</v>
       </c>
       <c r="F139" t="n">
-        <v>92.82125091552734</v>
+        <v>92.82124328613281</v>
       </c>
       <c r="G139" t="n">
         <v>2993600</v>
@@ -3646,16 +3646,16 @@
         <v>45495</v>
       </c>
       <c r="C140" t="n">
-        <v>92.83970642089844</v>
+        <v>92.8397216796875</v>
       </c>
       <c r="D140" t="n">
-        <v>92.83970642089844</v>
+        <v>92.8397216796875</v>
       </c>
       <c r="E140" t="n">
-        <v>92.83047676792572</v>
+        <v>92.83049202519783</v>
       </c>
       <c r="F140" t="n">
-        <v>92.83970642089844</v>
+        <v>92.8397216796875</v>
       </c>
       <c r="G140" t="n">
         <v>3386500</v>
@@ -3669,16 +3669,16 @@
         <v>45496</v>
       </c>
       <c r="C141" t="n">
-        <v>92.84891510009766</v>
+        <v>92.84893798828125</v>
       </c>
       <c r="D141" t="n">
-        <v>92.85813771082462</v>
+        <v>92.85816060128167</v>
       </c>
       <c r="E141" t="n">
-        <v>92.83968544920984</v>
+        <v>92.83970833511823</v>
       </c>
       <c r="F141" t="n">
-        <v>92.84891510009766</v>
+        <v>92.84893798828125</v>
       </c>
       <c r="G141" t="n">
         <v>2829200</v>
@@ -3692,16 +3692,16 @@
         <v>45497</v>
       </c>
       <c r="C142" t="n">
-        <v>92.85816955566406</v>
+        <v>92.85816192626953</v>
       </c>
       <c r="D142" t="n">
-        <v>92.86739920971711</v>
+        <v>92.86739157956426</v>
       </c>
       <c r="E142" t="n">
-        <v>92.8489469417743</v>
+        <v>92.84893931313751</v>
       </c>
       <c r="F142" t="n">
-        <v>92.85816955566406</v>
+        <v>92.85816192626953</v>
       </c>
       <c r="G142" t="n">
         <v>3474500</v>
@@ -3761,16 +3761,16 @@
         <v>45502</v>
       </c>
       <c r="C145" t="n">
-        <v>92.93199157714844</v>
+        <v>92.93197631835938</v>
       </c>
       <c r="D145" t="n">
-        <v>92.93199157714844</v>
+        <v>92.93197631835938</v>
       </c>
       <c r="E145" t="n">
-        <v>92.92276192320769</v>
+        <v>92.92274666593407</v>
       </c>
       <c r="F145" t="n">
-        <v>92.92276192320769</v>
+        <v>92.92274666593407</v>
       </c>
       <c r="G145" t="n">
         <v>3259000</v>
@@ -3784,16 +3784,16 @@
         <v>45503</v>
       </c>
       <c r="C146" t="n">
-        <v>92.93199157714844</v>
+        <v>92.93197631835938</v>
       </c>
       <c r="D146" t="n">
-        <v>92.94122123108919</v>
+        <v>92.94120597078468</v>
       </c>
       <c r="E146" t="n">
-        <v>92.93199157714844</v>
+        <v>92.93197631835938</v>
       </c>
       <c r="F146" t="n">
-        <v>92.94122123108919</v>
+        <v>92.94120597078468</v>
       </c>
       <c r="G146" t="n">
         <v>4559900</v>
@@ -3807,16 +3807,16 @@
         <v>45504</v>
       </c>
       <c r="C147" t="n">
-        <v>92.94121551513672</v>
+        <v>92.94123840332031</v>
       </c>
       <c r="D147" t="n">
-        <v>92.95044516850984</v>
+        <v>92.95046805896638</v>
       </c>
       <c r="E147" t="n">
-        <v>92.94121551513672</v>
+        <v>92.94123840332031</v>
       </c>
       <c r="F147" t="n">
-        <v>92.94121551513672</v>
+        <v>92.94123840332031</v>
       </c>
       <c r="G147" t="n">
         <v>7256900</v>
@@ -3853,16 +3853,16 @@
         <v>45506</v>
       </c>
       <c r="C149" t="n">
-        <v>93.01816558837891</v>
+        <v>93.01814270019531</v>
       </c>
       <c r="D149" t="n">
-        <v>93.01816558837891</v>
+        <v>93.01814270019531</v>
       </c>
       <c r="E149" t="n">
-        <v>92.99962995226285</v>
+        <v>92.99960706864016</v>
       </c>
       <c r="F149" t="n">
-        <v>93.00889423433536</v>
+        <v>93.00887134843308</v>
       </c>
       <c r="G149" t="n">
         <v>7927400</v>
@@ -3899,16 +3899,16 @@
         <v>45510</v>
       </c>
       <c r="C151" t="n">
-        <v>93.04596710205078</v>
+        <v>93.04594421386719</v>
       </c>
       <c r="D151" t="n">
-        <v>93.04596710205078</v>
+        <v>93.04594421386719</v>
       </c>
       <c r="E151" t="n">
-        <v>93.02743146702569</v>
+        <v>93.02740858340164</v>
       </c>
       <c r="F151" t="n">
-        <v>93.02743146702569</v>
+        <v>93.02740858340164</v>
       </c>
       <c r="G151" t="n">
         <v>5059100</v>
@@ -3922,16 +3922,16 @@
         <v>45511</v>
       </c>
       <c r="C152" t="n">
-        <v>93.04596710205078</v>
+        <v>93.04594421386719</v>
       </c>
       <c r="D152" t="n">
-        <v>93.05523845554865</v>
+        <v>93.0552155650844</v>
       </c>
       <c r="E152" t="n">
-        <v>93.04596710205078</v>
+        <v>93.04594421386719</v>
       </c>
       <c r="F152" t="n">
-        <v>93.04596710205078</v>
+        <v>93.04594421386719</v>
       </c>
       <c r="G152" t="n">
         <v>4611400</v>
@@ -4014,16 +4014,16 @@
         <v>45517</v>
       </c>
       <c r="C156" t="n">
-        <v>93.13866424560547</v>
+        <v>93.13864898681641</v>
       </c>
       <c r="D156" t="n">
-        <v>93.13866424560547</v>
+        <v>93.13864898681641</v>
       </c>
       <c r="E156" t="n">
-        <v>93.12939289233132</v>
+        <v>93.12937763506119</v>
       </c>
       <c r="F156" t="n">
-        <v>93.13866424560547</v>
+        <v>93.13864898681641</v>
       </c>
       <c r="G156" t="n">
         <v>4782200</v>
@@ -4037,16 +4037,16 @@
         <v>45518</v>
       </c>
       <c r="C157" t="n">
-        <v>93.15719604492188</v>
+        <v>93.15717315673828</v>
       </c>
       <c r="D157" t="n">
-        <v>93.15719604492188</v>
+        <v>93.15717315673828</v>
       </c>
       <c r="E157" t="n">
-        <v>93.13866041110718</v>
+        <v>93.13863752747767</v>
       </c>
       <c r="F157" t="n">
-        <v>93.14792469202943</v>
+        <v>93.14790180612377</v>
       </c>
       <c r="G157" t="n">
         <v>4327700</v>
@@ -4060,16 +4060,16 @@
         <v>45519</v>
       </c>
       <c r="C158" t="n">
-        <v>93.16645812988281</v>
+        <v>93.16646575927734</v>
       </c>
       <c r="D158" t="n">
-        <v>93.16645812988281</v>
+        <v>93.16646575927734</v>
       </c>
       <c r="E158" t="n">
-        <v>93.14791542594251</v>
+        <v>93.14792305381859</v>
       </c>
       <c r="F158" t="n">
-        <v>93.14791542594251</v>
+        <v>93.14792305381859</v>
       </c>
       <c r="G158" t="n">
         <v>4217800</v>
@@ -4106,16 +4106,16 @@
         <v>45523</v>
       </c>
       <c r="C160" t="n">
-        <v>93.21281433105469</v>
+        <v>93.21280670166016</v>
       </c>
       <c r="D160" t="n">
-        <v>93.22208568437608</v>
+        <v>93.22207805422271</v>
       </c>
       <c r="E160" t="n">
-        <v>93.21281433105469</v>
+        <v>93.21280670166016</v>
       </c>
       <c r="F160" t="n">
-        <v>93.21281433105469</v>
+        <v>93.21280670166016</v>
       </c>
       <c r="G160" t="n">
         <v>3930700</v>
@@ -4129,16 +4129,16 @@
         <v>45524</v>
       </c>
       <c r="C161" t="n">
-        <v>93.22207641601562</v>
+        <v>93.22208404541016</v>
       </c>
       <c r="D161" t="n">
-        <v>93.23134776841523</v>
+        <v>93.23135539856855</v>
       </c>
       <c r="E161" t="n">
-        <v>93.22207641601562</v>
+        <v>93.22208404541016</v>
       </c>
       <c r="F161" t="n">
-        <v>93.23134776841523</v>
+        <v>93.23135539856855</v>
       </c>
       <c r="G161" t="n">
         <v>3084200</v>
@@ -4198,16 +4198,16 @@
         <v>45527</v>
       </c>
       <c r="C164" t="n">
-        <v>93.28696441650391</v>
+        <v>93.28695678710938</v>
       </c>
       <c r="D164" t="n">
-        <v>93.29623576916964</v>
+        <v>93.29622813901686</v>
       </c>
       <c r="E164" t="n">
-        <v>93.28696441650391</v>
+        <v>93.28695678710938</v>
       </c>
       <c r="F164" t="n">
-        <v>93.29623576916964</v>
+        <v>93.29622813901686</v>
       </c>
       <c r="G164" t="n">
         <v>3549900</v>
@@ -4221,16 +4221,16 @@
         <v>45530</v>
       </c>
       <c r="C165" t="n">
-        <v>93.30550384521484</v>
+        <v>93.30548858642578</v>
       </c>
       <c r="D165" t="n">
-        <v>93.31476812558525</v>
+        <v>93.31475286528115</v>
       </c>
       <c r="E165" t="n">
-        <v>93.30550384521484</v>
+        <v>93.30548858642578</v>
       </c>
       <c r="F165" t="n">
-        <v>93.30550384521484</v>
+        <v>93.30548858642578</v>
       </c>
       <c r="G165" t="n">
         <v>3969000</v>
@@ -4244,16 +4244,16 @@
         <v>45531</v>
       </c>
       <c r="C166" t="n">
-        <v>93.31475067138672</v>
+        <v>93.31476593017578</v>
       </c>
       <c r="D166" t="n">
-        <v>93.3240220219927</v>
+        <v>93.32403728229781</v>
       </c>
       <c r="E166" t="n">
-        <v>93.31475067138672</v>
+        <v>93.31476593017578</v>
       </c>
       <c r="F166" t="n">
-        <v>93.3240220219927</v>
+        <v>93.32403728229781</v>
       </c>
       <c r="G166" t="n">
         <v>2818100</v>
@@ -4267,16 +4267,16 @@
         <v>45532</v>
       </c>
       <c r="C167" t="n">
-        <v>93.32404327392578</v>
+        <v>93.32403564453125</v>
       </c>
       <c r="D167" t="n">
-        <v>93.33331462664304</v>
+        <v>93.33330699649056</v>
       </c>
       <c r="E167" t="n">
-        <v>93.32404327392578</v>
+        <v>93.32403564453125</v>
       </c>
       <c r="F167" t="n">
-        <v>93.33331462664304</v>
+        <v>93.33330699649056</v>
       </c>
       <c r="G167" t="n">
         <v>3500800</v>
@@ -4290,16 +4290,16 @@
         <v>45533</v>
       </c>
       <c r="C168" t="n">
-        <v>93.33331298828125</v>
+        <v>93.33332061767578</v>
       </c>
       <c r="D168" t="n">
-        <v>93.35184862142037</v>
+        <v>93.35185625233008</v>
       </c>
       <c r="E168" t="n">
-        <v>93.33331298828125</v>
+        <v>93.33332061767578</v>
       </c>
       <c r="F168" t="n">
-        <v>93.34257726886585</v>
+        <v>93.34258489901768</v>
       </c>
       <c r="G168" t="n">
         <v>4537700</v>
@@ -4336,16 +4336,16 @@
         <v>45538</v>
       </c>
       <c r="C170" t="n">
-        <v>93.42061614990234</v>
+        <v>93.42062377929688</v>
       </c>
       <c r="D170" t="n">
-        <v>93.42061614990234</v>
+        <v>93.42062377929688</v>
       </c>
       <c r="E170" t="n">
-        <v>93.41131085768782</v>
+        <v>93.41131848632243</v>
       </c>
       <c r="F170" t="n">
-        <v>93.42061614990234</v>
+        <v>93.42062377929688</v>
       </c>
       <c r="G170" t="n">
         <v>11846700</v>
@@ -4359,16 +4359,16 @@
         <v>45539</v>
       </c>
       <c r="C171" t="n">
-        <v>93.429931640625</v>
+        <v>93.42992401123047</v>
       </c>
       <c r="D171" t="n">
-        <v>93.43924403642453</v>
+        <v>93.43923640626956</v>
       </c>
       <c r="E171" t="n">
-        <v>93.429931640625</v>
+        <v>93.42992401123047</v>
       </c>
       <c r="F171" t="n">
-        <v>93.43924403642453</v>
+        <v>93.43923640626956</v>
       </c>
       <c r="G171" t="n">
         <v>7218300</v>
@@ -4382,16 +4382,16 @@
         <v>45540</v>
       </c>
       <c r="C172" t="n">
-        <v>93.45787811279297</v>
+        <v>93.45786285400391</v>
       </c>
       <c r="D172" t="n">
-        <v>93.45787811279297</v>
+        <v>93.45786285400391</v>
       </c>
       <c r="E172" t="n">
-        <v>93.439260421206</v>
+        <v>93.43924516545663</v>
       </c>
       <c r="F172" t="n">
-        <v>93.44857281863847</v>
+        <v>93.44855756136867</v>
       </c>
       <c r="G172" t="n">
         <v>4833300</v>
@@ -4405,16 +4405,16 @@
         <v>45541</v>
       </c>
       <c r="C173" t="n">
-        <v>93.49509429931641</v>
+        <v>93.49510192871094</v>
       </c>
       <c r="D173" t="n">
-        <v>93.49509429931641</v>
+        <v>93.49510192871094</v>
       </c>
       <c r="E173" t="n">
-        <v>93.48578900777946</v>
+        <v>93.48579663641466</v>
       </c>
       <c r="F173" t="n">
-        <v>93.49509429931641</v>
+        <v>93.49510192871094</v>
       </c>
       <c r="G173" t="n">
         <v>5534600</v>
@@ -4451,16 +4451,16 @@
         <v>45545</v>
       </c>
       <c r="C175" t="n">
-        <v>93.52304840087891</v>
+        <v>93.52303314208984</v>
       </c>
       <c r="D175" t="n">
-        <v>93.52304840087891</v>
+        <v>93.52303314208984</v>
       </c>
       <c r="E175" t="n">
-        <v>93.5044307097473</v>
+        <v>93.50441545399579</v>
       </c>
       <c r="F175" t="n">
-        <v>93.52304840087891</v>
+        <v>93.52303314208984</v>
       </c>
       <c r="G175" t="n">
         <v>4143900</v>
@@ -4474,16 +4474,16 @@
         <v>45546</v>
       </c>
       <c r="C176" t="n">
-        <v>93.52304840087891</v>
+        <v>93.52303314208984</v>
       </c>
       <c r="D176" t="n">
-        <v>93.53236079808363</v>
+        <v>93.53234553777519</v>
       </c>
       <c r="E176" t="n">
-        <v>93.52304840087891</v>
+        <v>93.52303314208984</v>
       </c>
       <c r="F176" t="n">
-        <v>93.52304840087891</v>
+        <v>93.52303314208984</v>
       </c>
       <c r="G176" t="n">
         <v>4500100</v>
@@ -4497,16 +4497,16 @@
         <v>45547</v>
       </c>
       <c r="C177" t="n">
-        <v>93.5323486328125</v>
+        <v>93.53232574462891</v>
       </c>
       <c r="D177" t="n">
-        <v>93.541661028806</v>
+        <v>93.54163813834359</v>
       </c>
       <c r="E177" t="n">
-        <v>93.5323486328125</v>
+        <v>93.53232574462891</v>
       </c>
       <c r="F177" t="n">
-        <v>93.541661028806</v>
+        <v>93.54163813834359</v>
       </c>
       <c r="G177" t="n">
         <v>3912400</v>
@@ -4543,16 +4543,16 @@
         <v>45551</v>
       </c>
       <c r="C179" t="n">
-        <v>93.60682678222656</v>
+        <v>93.60683441162109</v>
       </c>
       <c r="D179" t="n">
-        <v>93.60682678222656</v>
+        <v>93.60683441162109</v>
       </c>
       <c r="E179" t="n">
-        <v>93.58820199159494</v>
+        <v>93.58820961947146</v>
       </c>
       <c r="F179" t="n">
-        <v>93.58820199159494</v>
+        <v>93.58820961947146</v>
       </c>
       <c r="G179" t="n">
         <v>3571100</v>
@@ -4566,16 +4566,16 @@
         <v>45552</v>
       </c>
       <c r="C180" t="n">
-        <v>93.60682678222656</v>
+        <v>93.60683441162109</v>
       </c>
       <c r="D180" t="n">
-        <v>93.62544446958184</v>
+        <v>93.62545210049379</v>
       </c>
       <c r="E180" t="n">
-        <v>93.60682678222656</v>
+        <v>93.60683441162109</v>
       </c>
       <c r="F180" t="n">
-        <v>93.61613917754238</v>
+        <v>93.61614680769591</v>
       </c>
       <c r="G180" t="n">
         <v>4452200</v>
@@ -4589,16 +4589,16 @@
         <v>45553</v>
       </c>
       <c r="C181" t="n">
-        <v>93.63474273681641</v>
+        <v>93.63475799560547</v>
       </c>
       <c r="D181" t="n">
-        <v>93.64405513072712</v>
+        <v>93.64407039103374</v>
       </c>
       <c r="E181" t="n">
-        <v>93.6254303429057</v>
+        <v>93.6254456001772</v>
       </c>
       <c r="F181" t="n">
-        <v>93.6254303429057</v>
+        <v>93.6254456001772</v>
       </c>
       <c r="G181" t="n">
         <v>4077700</v>
@@ -4612,16 +4612,16 @@
         <v>45554</v>
       </c>
       <c r="C182" t="n">
-        <v>93.65336608886719</v>
+        <v>93.65338134765625</v>
       </c>
       <c r="D182" t="n">
-        <v>93.66267848334145</v>
+        <v>93.66269374364776</v>
       </c>
       <c r="E182" t="n">
-        <v>93.64406079766864</v>
+        <v>93.64407605494162</v>
       </c>
       <c r="F182" t="n">
-        <v>93.64406079766864</v>
+        <v>93.64407605494162</v>
       </c>
       <c r="G182" t="n">
         <v>5165800</v>
@@ -4635,16 +4635,16 @@
         <v>45555</v>
       </c>
       <c r="C183" t="n">
-        <v>93.69062042236328</v>
+        <v>93.69060516357422</v>
       </c>
       <c r="D183" t="n">
-        <v>93.69993281801626</v>
+        <v>93.69991755771055</v>
       </c>
       <c r="E183" t="n">
-        <v>93.69062042236328</v>
+        <v>93.69060516357422</v>
       </c>
       <c r="F183" t="n">
-        <v>93.69993281801626</v>
+        <v>93.69991755771055</v>
       </c>
       <c r="G183" t="n">
         <v>4244800</v>
@@ -4658,16 +4658,16 @@
         <v>45558</v>
       </c>
       <c r="C184" t="n">
-        <v>93.71858215332031</v>
+        <v>93.71856689453125</v>
       </c>
       <c r="D184" t="n">
-        <v>93.71858215332031</v>
+        <v>93.71856689453125</v>
       </c>
       <c r="E184" t="n">
-        <v>93.69995735713671</v>
+        <v>93.69994210138005</v>
       </c>
       <c r="F184" t="n">
-        <v>93.7092697552285</v>
+        <v>93.70925449795564</v>
       </c>
       <c r="G184" t="n">
         <v>5220900</v>
@@ -4681,16 +4681,16 @@
         <v>45559</v>
       </c>
       <c r="C185" t="n">
-        <v>93.72786712646484</v>
+        <v>93.72785186767578</v>
       </c>
       <c r="D185" t="n">
-        <v>93.72786712646484</v>
+        <v>93.72785186767578</v>
       </c>
       <c r="E185" t="n">
-        <v>93.71856183366906</v>
+        <v>93.71854657639489</v>
       </c>
       <c r="F185" t="n">
-        <v>93.71856183366906</v>
+        <v>93.71854657639489</v>
       </c>
       <c r="G185" t="n">
         <v>3923500</v>
@@ -4704,16 +4704,16 @@
         <v>45560</v>
       </c>
       <c r="C186" t="n">
-        <v>93.72786712646484</v>
+        <v>93.72785186767578</v>
       </c>
       <c r="D186" t="n">
-        <v>93.7464919186103</v>
+        <v>93.74647665678914</v>
       </c>
       <c r="E186" t="n">
-        <v>93.72786712646484</v>
+        <v>93.72785186767578</v>
       </c>
       <c r="F186" t="n">
-        <v>93.73717952253757</v>
+        <v>93.73716426223247</v>
       </c>
       <c r="G186" t="n">
         <v>3372400</v>
@@ -4727,16 +4727,16 @@
         <v>45561</v>
       </c>
       <c r="C187" t="n">
-        <v>93.7371826171875</v>
+        <v>93.73716735839844</v>
       </c>
       <c r="D187" t="n">
-        <v>93.74649501356767</v>
+        <v>93.74647975326272</v>
       </c>
       <c r="E187" t="n">
-        <v>93.7371826171875</v>
+        <v>93.73716735839844</v>
       </c>
       <c r="F187" t="n">
-        <v>93.7371826171875</v>
+        <v>93.73716735839844</v>
       </c>
       <c r="G187" t="n">
         <v>4364400</v>
@@ -4750,16 +4750,16 @@
         <v>45562</v>
       </c>
       <c r="C188" t="n">
-        <v>93.7744140625</v>
+        <v>93.77442169189453</v>
       </c>
       <c r="D188" t="n">
-        <v>93.78372645778413</v>
+        <v>93.78373408793631</v>
       </c>
       <c r="E188" t="n">
-        <v>93.7744140625</v>
+        <v>93.77442169189453</v>
       </c>
       <c r="F188" t="n">
-        <v>93.7744140625</v>
+        <v>93.77442169189453</v>
       </c>
       <c r="G188" t="n">
         <v>4945400</v>
@@ -4773,16 +4773,16 @@
         <v>45565</v>
       </c>
       <c r="C189" t="n">
-        <v>93.7744140625</v>
+        <v>93.77442169189453</v>
       </c>
       <c r="D189" t="n">
-        <v>93.79303174979192</v>
+        <v>93.79303938070117</v>
       </c>
       <c r="E189" t="n">
-        <v>93.7744140625</v>
+        <v>93.77442169189453</v>
       </c>
       <c r="F189" t="n">
-        <v>93.78372645778413</v>
+        <v>93.78373408793631</v>
       </c>
       <c r="G189" t="n">
         <v>9253100</v>
@@ -4796,16 +4796,16 @@
         <v>45566</v>
       </c>
       <c r="C190" t="n">
-        <v>93.81181335449219</v>
+        <v>93.81182098388672</v>
       </c>
       <c r="D190" t="n">
-        <v>93.81181335449219</v>
+        <v>93.81182098388672</v>
       </c>
       <c r="E190" t="n">
-        <v>93.80246103195581</v>
+        <v>93.80246866058975</v>
       </c>
       <c r="F190" t="n">
-        <v>93.81181335449219</v>
+        <v>93.81182098388672</v>
       </c>
       <c r="G190" t="n">
         <v>11569200</v>
@@ -4819,16 +4819,16 @@
         <v>45567</v>
       </c>
       <c r="C191" t="n">
-        <v>93.81181335449219</v>
+        <v>93.81182098388672</v>
       </c>
       <c r="D191" t="n">
-        <v>93.82115854329665</v>
+        <v>93.82116617345119</v>
       </c>
       <c r="E191" t="n">
-        <v>93.81181335449219</v>
+        <v>93.81182098388672</v>
       </c>
       <c r="F191" t="n">
-        <v>93.82115854329665</v>
+        <v>93.82116617345119</v>
       </c>
       <c r="G191" t="n">
         <v>5170300</v>
@@ -4842,16 +4842,16 @@
         <v>45568</v>
       </c>
       <c r="C192" t="n">
-        <v>93.82115936279297</v>
+        <v>93.8211669921875</v>
       </c>
       <c r="D192" t="n">
-        <v>93.83051168541103</v>
+        <v>93.83051931556608</v>
       </c>
       <c r="E192" t="n">
-        <v>93.82115936279297</v>
+        <v>93.8211669921875</v>
       </c>
       <c r="F192" t="n">
-        <v>93.83051168541103</v>
+        <v>93.83051931556608</v>
       </c>
       <c r="G192" t="n">
         <v>4066100</v>
@@ -4865,16 +4865,16 @@
         <v>45569</v>
       </c>
       <c r="C193" t="n">
-        <v>93.85858154296875</v>
+        <v>93.85856628417969</v>
       </c>
       <c r="D193" t="n">
-        <v>93.86793386758201</v>
+        <v>93.86791860727251</v>
       </c>
       <c r="E193" t="n">
-        <v>93.85858154296875</v>
+        <v>93.85856628417969</v>
       </c>
       <c r="F193" t="n">
-        <v>93.86326127214213</v>
+        <v>93.86324601259227</v>
       </c>
       <c r="G193" t="n">
         <v>4987100</v>
@@ -4888,16 +4888,16 @@
         <v>45572</v>
       </c>
       <c r="C194" t="n">
-        <v>93.86793518066406</v>
+        <v>93.86791229248047</v>
       </c>
       <c r="D194" t="n">
-        <v>93.87728750540813</v>
+        <v>93.87726461494414</v>
       </c>
       <c r="E194" t="n">
-        <v>93.86793518066406</v>
+        <v>93.86791229248047</v>
       </c>
       <c r="F194" t="n">
-        <v>93.86793518066406</v>
+        <v>93.86791229248047</v>
       </c>
       <c r="G194" t="n">
         <v>4792500</v>
@@ -4911,16 +4911,16 @@
         <v>45573</v>
       </c>
       <c r="C195" t="n">
-        <v>93.87726593017578</v>
+        <v>93.87727355957031</v>
       </c>
       <c r="D195" t="n">
-        <v>93.88661825277048</v>
+        <v>93.88662588292506</v>
       </c>
       <c r="E195" t="n">
-        <v>93.87726593017578</v>
+        <v>93.87727355957031</v>
       </c>
       <c r="F195" t="n">
-        <v>93.87726593017578</v>
+        <v>93.87727355957031</v>
       </c>
       <c r="G195" t="n">
         <v>3923100</v>
@@ -5049,16 +5049,16 @@
         <v>45581</v>
       </c>
       <c r="C201" t="n">
-        <v>93.98947906494141</v>
+        <v>93.98947143554688</v>
       </c>
       <c r="D201" t="n">
-        <v>93.98947906494141</v>
+        <v>93.98947143554688</v>
       </c>
       <c r="E201" t="n">
-        <v>93.98013387470671</v>
+        <v>93.98012624607075</v>
       </c>
       <c r="F201" t="n">
-        <v>93.98013387470671</v>
+        <v>93.98012624607075</v>
       </c>
       <c r="G201" t="n">
         <v>3809900</v>
@@ -5072,16 +5072,16 @@
         <v>45582</v>
       </c>
       <c r="C202" t="n">
-        <v>93.98947906494141</v>
+        <v>93.98947143554688</v>
       </c>
       <c r="D202" t="n">
-        <v>93.99883138890911</v>
+        <v>93.99882375875542</v>
       </c>
       <c r="E202" t="n">
-        <v>93.98947906494141</v>
+        <v>93.98947143554688</v>
       </c>
       <c r="F202" t="n">
-        <v>93.98947906494141</v>
+        <v>93.98947143554688</v>
       </c>
       <c r="G202" t="n">
         <v>3575500</v>
@@ -5095,16 +5095,16 @@
         <v>45583</v>
       </c>
       <c r="C203" t="n">
-        <v>94.02689361572266</v>
+        <v>94.02687072753906</v>
       </c>
       <c r="D203" t="n">
-        <v>94.03624594092258</v>
+        <v>94.03622305046243</v>
       </c>
       <c r="E203" t="n">
-        <v>94.01754842425666</v>
+        <v>94.0175255383479</v>
       </c>
       <c r="F203" t="n">
-        <v>94.03624594092258</v>
+        <v>94.03622305046243</v>
       </c>
       <c r="G203" t="n">
         <v>3970200</v>
@@ -5118,16 +5118,16 @@
         <v>45586</v>
       </c>
       <c r="C204" t="n">
-        <v>94.04557800292969</v>
+        <v>94.04558563232422</v>
       </c>
       <c r="D204" t="n">
-        <v>94.04557800292969</v>
+        <v>94.04558563232422</v>
       </c>
       <c r="E204" t="n">
-        <v>94.03622567974483</v>
+        <v>94.03623330838064</v>
       </c>
       <c r="F204" t="n">
-        <v>94.03622567974483</v>
+        <v>94.03623330838064</v>
       </c>
       <c r="G204" t="n">
         <v>3940600</v>
@@ -5141,16 +5141,16 @@
         <v>45587</v>
       </c>
       <c r="C205" t="n">
-        <v>94.05490875244141</v>
+        <v>94.05492401123047</v>
       </c>
       <c r="D205" t="n">
-        <v>94.05490875244141</v>
+        <v>94.05492401123047</v>
       </c>
       <c r="E205" t="n">
-        <v>94.04556356442367</v>
+        <v>94.04557882169665</v>
       </c>
       <c r="F205" t="n">
-        <v>94.05490875244141</v>
+        <v>94.05492401123047</v>
       </c>
       <c r="G205" t="n">
         <v>3462800</v>
@@ -5164,16 +5164,16 @@
         <v>45588</v>
       </c>
       <c r="C206" t="n">
-        <v>94.05490875244141</v>
+        <v>94.05492401123047</v>
       </c>
       <c r="D206" t="n">
-        <v>94.07361339593947</v>
+        <v>94.07362865776304</v>
       </c>
       <c r="E206" t="n">
-        <v>94.05490875244141</v>
+        <v>94.05492401123047</v>
       </c>
       <c r="F206" t="n">
-        <v>94.07361339593947</v>
+        <v>94.07362865776304</v>
       </c>
       <c r="G206" t="n">
         <v>3927700</v>
@@ -5187,16 +5187,16 @@
         <v>45589</v>
       </c>
       <c r="C207" t="n">
-        <v>94.08297729492188</v>
+        <v>94.08300018310547</v>
       </c>
       <c r="D207" t="n">
-        <v>94.08297729492188</v>
+        <v>94.08300018310547</v>
       </c>
       <c r="E207" t="n">
-        <v>94.073624972022</v>
+        <v>94.0736478579304</v>
       </c>
       <c r="F207" t="n">
-        <v>94.08297729492188</v>
+        <v>94.08300018310547</v>
       </c>
       <c r="G207" t="n">
         <v>3704500</v>
@@ -5210,16 +5210,16 @@
         <v>45590</v>
       </c>
       <c r="C208" t="n">
-        <v>94.12038421630859</v>
+        <v>94.12039184570312</v>
       </c>
       <c r="D208" t="n">
-        <v>94.12038421630859</v>
+        <v>94.12039184570312</v>
       </c>
       <c r="E208" t="n">
-        <v>94.11103189293539</v>
+        <v>94.11103952157183</v>
       </c>
       <c r="F208" t="n">
-        <v>94.11103189293539</v>
+        <v>94.11103952157183</v>
       </c>
       <c r="G208" t="n">
         <v>5386900</v>
@@ -5233,16 +5233,16 @@
         <v>45593</v>
       </c>
       <c r="C209" t="n">
-        <v>94.12038421630859</v>
+        <v>94.12039184570312</v>
       </c>
       <c r="D209" t="n">
-        <v>94.12972940594925</v>
+        <v>94.12973703610129</v>
       </c>
       <c r="E209" t="n">
-        <v>94.12038421630859</v>
+        <v>94.12039184570312</v>
       </c>
       <c r="F209" t="n">
-        <v>94.12972940594925</v>
+        <v>94.12973703610129</v>
       </c>
       <c r="G209" t="n">
         <v>3471300</v>
@@ -5256,16 +5256,16 @@
         <v>45594</v>
       </c>
       <c r="C210" t="n">
-        <v>94.13908386230469</v>
+        <v>94.13906860351562</v>
       </c>
       <c r="D210" t="n">
-        <v>94.13908386230469</v>
+        <v>94.13906860351562</v>
       </c>
       <c r="E210" t="n">
-        <v>94.12505894379339</v>
+        <v>94.1250436872776</v>
       </c>
       <c r="F210" t="n">
-        <v>94.12973153871958</v>
+        <v>94.12971628144642</v>
       </c>
       <c r="G210" t="n">
         <v>3449900</v>
@@ -5279,16 +5279,16 @@
         <v>45595</v>
       </c>
       <c r="C211" t="n">
-        <v>94.13908386230469</v>
+        <v>94.13906860351562</v>
       </c>
       <c r="D211" t="n">
-        <v>94.15778137574219</v>
+        <v>94.15776611392248</v>
       </c>
       <c r="E211" t="n">
-        <v>94.13908386230469</v>
+        <v>94.13906860351562</v>
       </c>
       <c r="F211" t="n">
-        <v>94.14843618588979</v>
+        <v>94.14842092558483</v>
       </c>
       <c r="G211" t="n">
         <v>7059200</v>
@@ -5302,16 +5302,16 @@
         <v>45596</v>
       </c>
       <c r="C212" t="n">
-        <v>94.15778350830078</v>
+        <v>94.15776062011719</v>
       </c>
       <c r="D212" t="n">
-        <v>94.16713583209771</v>
+        <v>94.16711294164071</v>
       </c>
       <c r="E212" t="n">
-        <v>94.14843831823674</v>
+        <v>94.1484154323248</v>
       </c>
       <c r="F212" t="n">
-        <v>94.14843831823674</v>
+        <v>94.1484154323248</v>
       </c>
       <c r="G212" t="n">
         <v>11321100</v>
@@ -5325,16 +5325,16 @@
         <v>45597</v>
       </c>
       <c r="C213" t="n">
-        <v>94.20941162109375</v>
+        <v>94.20941925048828</v>
       </c>
       <c r="D213" t="n">
-        <v>94.20941162109375</v>
+        <v>94.20941925048828</v>
       </c>
       <c r="E213" t="n">
-        <v>94.20002775979395</v>
+        <v>94.20003538842856</v>
       </c>
       <c r="F213" t="n">
-        <v>94.20941162109375</v>
+        <v>94.20941925048828</v>
       </c>
       <c r="G213" t="n">
         <v>13451800</v>
@@ -5348,16 +5348,16 @@
         <v>45600</v>
       </c>
       <c r="C214" t="n">
-        <v>94.21880340576172</v>
+        <v>94.21877288818359</v>
       </c>
       <c r="D214" t="n">
-        <v>94.22725604425263</v>
+        <v>94.22722552393668</v>
       </c>
       <c r="E214" t="n">
-        <v>94.20941238113326</v>
+        <v>94.2093818665969</v>
       </c>
       <c r="F214" t="n">
-        <v>94.21880340576172</v>
+        <v>94.21877288818359</v>
       </c>
       <c r="G214" t="n">
         <v>5041500</v>
@@ -5371,16 +5371,16 @@
         <v>45601</v>
       </c>
       <c r="C215" t="n">
-        <v>94.23757934570312</v>
+        <v>94.23759460449219</v>
       </c>
       <c r="D215" t="n">
-        <v>94.23757934570312</v>
+        <v>94.23759460449219</v>
       </c>
       <c r="E215" t="n">
-        <v>94.21879729766383</v>
+        <v>94.21881255341174</v>
       </c>
       <c r="F215" t="n">
-        <v>94.22818832168348</v>
+        <v>94.22820357895196</v>
       </c>
       <c r="G215" t="n">
         <v>4280500</v>
@@ -5394,16 +5394,16 @@
         <v>45602</v>
       </c>
       <c r="C216" t="n">
-        <v>94.23757934570312</v>
+        <v>94.23759460449219</v>
       </c>
       <c r="D216" t="n">
-        <v>94.24696320647028</v>
+        <v>94.24697846677877</v>
       </c>
       <c r="E216" t="n">
-        <v>94.22818832168348</v>
+        <v>94.22820357895196</v>
       </c>
       <c r="F216" t="n">
-        <v>94.22818832168348</v>
+        <v>94.22820357895196</v>
       </c>
       <c r="G216" t="n">
         <v>9470900</v>
@@ -5417,16 +5417,16 @@
         <v>45603</v>
       </c>
       <c r="C217" t="n">
-        <v>94.25636291503906</v>
+        <v>94.25635528564453</v>
       </c>
       <c r="D217" t="n">
-        <v>94.25636291503906</v>
+        <v>94.25635528564453</v>
       </c>
       <c r="E217" t="n">
-        <v>94.24697189015416</v>
+        <v>94.24696426151975</v>
       </c>
       <c r="F217" t="n">
-        <v>94.24697189015416</v>
+        <v>94.24696426151975</v>
       </c>
       <c r="G217" t="n">
         <v>6188100</v>
@@ -5509,16 +5509,16 @@
         <v>45609</v>
       </c>
       <c r="C221" t="n">
-        <v>94.33145904541016</v>
+        <v>94.33147430419922</v>
       </c>
       <c r="D221" t="n">
-        <v>94.33145904541016</v>
+        <v>94.33147430419922</v>
       </c>
       <c r="E221" t="n">
-        <v>94.31267699917292</v>
+        <v>94.31269225492385</v>
       </c>
       <c r="F221" t="n">
-        <v>94.32206802229155</v>
+        <v>94.32208327956153</v>
       </c>
       <c r="G221" t="n">
         <v>4818000</v>
@@ -5532,16 +5532,16 @@
         <v>45610</v>
       </c>
       <c r="C222" t="n">
-        <v>94.33145904541016</v>
+        <v>94.33147430419922</v>
       </c>
       <c r="D222" t="n">
-        <v>94.34085006852878</v>
+        <v>94.3408653288369</v>
       </c>
       <c r="E222" t="n">
-        <v>94.33145904541016</v>
+        <v>94.33147430419922</v>
       </c>
       <c r="F222" t="n">
-        <v>94.34085006852878</v>
+        <v>94.3408653288369</v>
       </c>
       <c r="G222" t="n">
         <v>4353200</v>
@@ -5601,16 +5601,16 @@
         <v>45615</v>
       </c>
       <c r="C225" t="n">
-        <v>94.39720153808594</v>
+        <v>94.39718627929688</v>
       </c>
       <c r="D225" t="n">
-        <v>94.39720153808594</v>
+        <v>94.39718627929688</v>
       </c>
       <c r="E225" t="n">
-        <v>94.38781051301173</v>
+        <v>94.38779525574067</v>
       </c>
       <c r="F225" t="n">
-        <v>94.39720153808594</v>
+        <v>94.39718627929688</v>
       </c>
       <c r="G225" t="n">
         <v>4310900</v>
@@ -5624,16 +5624,16 @@
         <v>45616</v>
       </c>
       <c r="C226" t="n">
-        <v>94.41597747802734</v>
+        <v>94.41596984863281</v>
       </c>
       <c r="D226" t="n">
-        <v>94.41597747802734</v>
+        <v>94.41596984863281</v>
       </c>
       <c r="E226" t="n">
-        <v>94.39720259092282</v>
+        <v>94.39719496304541</v>
       </c>
       <c r="F226" t="n">
-        <v>94.40659361610177</v>
+        <v>94.4065859874655</v>
       </c>
       <c r="G226" t="n">
         <v>4133000</v>
@@ -5647,16 +5647,16 @@
         <v>45617</v>
       </c>
       <c r="C227" t="n">
-        <v>94.41597747802734</v>
+        <v>94.41596984863281</v>
       </c>
       <c r="D227" t="n">
-        <v>94.4253685032063</v>
+        <v>94.42536087305291</v>
       </c>
       <c r="E227" t="n">
-        <v>94.41597747802734</v>
+        <v>94.41596984863281</v>
       </c>
       <c r="F227" t="n">
-        <v>94.4253685032063</v>
+        <v>94.42536087305291</v>
       </c>
       <c r="G227" t="n">
         <v>4410700</v>
@@ -5670,16 +5670,16 @@
         <v>45618</v>
       </c>
       <c r="C228" t="n">
-        <v>94.44412994384766</v>
+        <v>94.44414520263672</v>
       </c>
       <c r="D228" t="n">
-        <v>94.45352096768957</v>
+        <v>94.45353622799588</v>
       </c>
       <c r="E228" t="n">
-        <v>94.44412994384766</v>
+        <v>94.44414520263672</v>
       </c>
       <c r="F228" t="n">
-        <v>94.44412994384766</v>
+        <v>94.44414520263672</v>
       </c>
       <c r="G228" t="n">
         <v>4343900</v>
@@ -5693,16 +5693,16 @@
         <v>45621</v>
       </c>
       <c r="C229" t="n">
-        <v>94.45352172851562</v>
+        <v>94.45351409912109</v>
       </c>
       <c r="D229" t="n">
-        <v>94.46291275243318</v>
+        <v>94.46290512228009</v>
       </c>
       <c r="E229" t="n">
-        <v>94.45352172851562</v>
+        <v>94.45351409912109</v>
       </c>
       <c r="F229" t="n">
-        <v>94.45352172851562</v>
+        <v>94.45351409912109</v>
       </c>
       <c r="G229" t="n">
         <v>6020200</v>
@@ -5716,16 +5716,16 @@
         <v>45622</v>
       </c>
       <c r="C230" t="n">
-        <v>94.47229766845703</v>
+        <v>94.47230529785156</v>
       </c>
       <c r="D230" t="n">
-        <v>94.48168152851547</v>
+        <v>94.48168915866783</v>
       </c>
       <c r="E230" t="n">
-        <v>94.46290664514663</v>
+        <v>94.46291427378277</v>
       </c>
       <c r="F230" t="n">
-        <v>94.47229766845703</v>
+        <v>94.47230529785156</v>
       </c>
       <c r="G230" t="n">
         <v>4586900</v>
@@ -5739,16 +5739,16 @@
         <v>45623</v>
       </c>
       <c r="C231" t="n">
-        <v>94.49110412597656</v>
+        <v>94.4910888671875</v>
       </c>
       <c r="D231" t="n">
-        <v>94.50049515242496</v>
+        <v>94.5004798921194</v>
       </c>
       <c r="E231" t="n">
-        <v>94.49110412597656</v>
+        <v>94.4910888671875</v>
       </c>
       <c r="F231" t="n">
-        <v>94.49110412597656</v>
+        <v>94.4910888671875</v>
       </c>
       <c r="G231" t="n">
         <v>5909000</v>
@@ -5785,16 +5785,16 @@
         <v>45628</v>
       </c>
       <c r="C233" t="n">
-        <v>94.54560089111328</v>
+        <v>94.54559326171875</v>
       </c>
       <c r="D233" t="n">
-        <v>94.55502730641413</v>
+        <v>94.55501967625894</v>
       </c>
       <c r="E233" t="n">
-        <v>94.54560089111328</v>
+        <v>94.54559326171875</v>
       </c>
       <c r="F233" t="n">
-        <v>94.55031050363964</v>
+        <v>94.55030287386506</v>
       </c>
       <c r="G233" t="n">
         <v>11471800</v>
@@ -5808,16 +5808,16 @@
         <v>45629</v>
       </c>
       <c r="C234" t="n">
-        <v>94.55502319335938</v>
+        <v>94.55503082275391</v>
       </c>
       <c r="D234" t="n">
-        <v>94.56444241800236</v>
+        <v>94.5644500481569</v>
       </c>
       <c r="E234" t="n">
-        <v>94.55502319335938</v>
+        <v>94.55503082275391</v>
       </c>
       <c r="F234" t="n">
-        <v>94.56444241800236</v>
+        <v>94.5644500481569</v>
       </c>
       <c r="G234" t="n">
         <v>5734100</v>
@@ -5831,16 +5831,16 @@
         <v>45630</v>
       </c>
       <c r="C235" t="n">
-        <v>94.57388305664062</v>
+        <v>94.57386016845703</v>
       </c>
       <c r="D235" t="n">
-        <v>94.58330947294915</v>
+        <v>94.58328658248423</v>
       </c>
       <c r="E235" t="n">
-        <v>94.5644566403321</v>
+        <v>94.56443375442983</v>
       </c>
       <c r="F235" t="n">
-        <v>94.57388305664062</v>
+        <v>94.57386016845703</v>
       </c>
       <c r="G235" t="n">
         <v>5351100</v>
@@ -5854,16 +5854,16 @@
         <v>45631</v>
       </c>
       <c r="C236" t="n">
-        <v>94.58330535888672</v>
+        <v>94.58332061767578</v>
       </c>
       <c r="D236" t="n">
-        <v>94.59273177478522</v>
+        <v>94.59274703509502</v>
       </c>
       <c r="E236" t="n">
-        <v>94.58330535888672</v>
+        <v>94.58332061767578</v>
       </c>
       <c r="F236" t="n">
-        <v>94.58330535888672</v>
+        <v>94.58332061767578</v>
       </c>
       <c r="G236" t="n">
         <v>4870100</v>
@@ -5877,16 +5877,16 @@
         <v>45632</v>
       </c>
       <c r="C237" t="n">
-        <v>94.63042449951172</v>
+        <v>94.63043212890625</v>
       </c>
       <c r="D237" t="n">
-        <v>94.63042449951172</v>
+        <v>94.63043212890625</v>
       </c>
       <c r="E237" t="n">
-        <v>94.62099808418584</v>
+        <v>94.62100571282039</v>
       </c>
       <c r="F237" t="n">
-        <v>94.63042449951172</v>
+        <v>94.63043212890625</v>
       </c>
       <c r="G237" t="n">
         <v>4779000</v>
@@ -5900,16 +5900,16 @@
         <v>45635</v>
       </c>
       <c r="C238" t="n">
-        <v>94.63985443115234</v>
+        <v>94.63984680175781</v>
       </c>
       <c r="D238" t="n">
-        <v>94.63985443115234</v>
+        <v>94.63984680175781</v>
       </c>
       <c r="E238" t="n">
-        <v>94.63043520500904</v>
+        <v>94.63042757637383</v>
       </c>
       <c r="F238" t="n">
-        <v>94.63043520500904</v>
+        <v>94.63042757637383</v>
       </c>
       <c r="G238" t="n">
         <v>5539800</v>
@@ -5923,16 +5923,16 @@
         <v>45636</v>
       </c>
       <c r="C239" t="n">
-        <v>94.65872192382812</v>
+        <v>94.65871429443359</v>
       </c>
       <c r="D239" t="n">
-        <v>94.65872192382812</v>
+        <v>94.65871429443359</v>
       </c>
       <c r="E239" t="n">
-        <v>94.64929550597597</v>
+        <v>94.64928787734119</v>
       </c>
       <c r="F239" t="n">
-        <v>94.64929550597597</v>
+        <v>94.64928787734119</v>
       </c>
       <c r="G239" t="n">
         <v>5293500</v>
@@ -5946,16 +5946,16 @@
         <v>45637</v>
       </c>
       <c r="C240" t="n">
-        <v>94.65872192382812</v>
+        <v>94.65871429443359</v>
       </c>
       <c r="D240" t="n">
-        <v>94.66814115143021</v>
+        <v>94.66813352127649</v>
       </c>
       <c r="E240" t="n">
-        <v>94.65872192382812</v>
+        <v>94.65871429443359</v>
       </c>
       <c r="F240" t="n">
-        <v>94.66814115143021</v>
+        <v>94.66813352127649</v>
       </c>
       <c r="G240" t="n">
         <v>4855300</v>
@@ -6061,16 +6061,16 @@
         <v>45644</v>
       </c>
       <c r="C245" t="n">
-        <v>94.74547576904297</v>
+        <v>94.74549102783203</v>
       </c>
       <c r="D245" t="n">
-        <v>94.74547576904297</v>
+        <v>94.74549102783203</v>
       </c>
       <c r="E245" t="n">
-        <v>94.7360143361235</v>
+        <v>94.73602959338879</v>
       </c>
       <c r="F245" t="n">
-        <v>94.74547576904297</v>
+        <v>94.74549102783203</v>
       </c>
       <c r="G245" t="n">
         <v>11526500</v>
@@ -6107,16 +6107,16 @@
         <v>45646</v>
       </c>
       <c r="C247" t="n">
-        <v>94.7833251953125</v>
+        <v>94.78331756591797</v>
       </c>
       <c r="D247" t="n">
-        <v>94.79278663004159</v>
+        <v>94.79277899988548</v>
       </c>
       <c r="E247" t="n">
-        <v>94.7833251953125</v>
+        <v>94.78331756591797</v>
       </c>
       <c r="F247" t="n">
-        <v>94.78805952115711</v>
+        <v>94.7880518913815</v>
       </c>
       <c r="G247" t="n">
         <v>8898900</v>
@@ -6130,16 +6130,16 @@
         <v>45649</v>
       </c>
       <c r="C248" t="n">
-        <v>94.80224609375</v>
+        <v>94.80223846435547</v>
       </c>
       <c r="D248" t="n">
-        <v>94.80224609375</v>
+        <v>94.80223846435547</v>
       </c>
       <c r="E248" t="n">
-        <v>94.79278465921763</v>
+        <v>94.79277703058452</v>
       </c>
       <c r="F248" t="n">
-        <v>94.80224609375</v>
+        <v>94.80223846435547</v>
       </c>
       <c r="G248" t="n">
         <v>7032500</v>
@@ -6153,16 +6153,16 @@
         <v>45650</v>
       </c>
       <c r="C249" t="n">
-        <v>94.83062744140625</v>
+        <v>94.83061981201172</v>
       </c>
       <c r="D249" t="n">
-        <v>94.83062744140625</v>
+        <v>94.83061981201172</v>
       </c>
       <c r="E249" t="n">
-        <v>94.82116600644875</v>
+        <v>94.82115837781542</v>
       </c>
       <c r="F249" t="n">
-        <v>94.83062744140625</v>
+        <v>94.83061981201172</v>
       </c>
       <c r="G249" t="n">
         <v>4654300</v>
@@ -6176,16 +6176,16 @@
         <v>45652</v>
       </c>
       <c r="C250" t="n">
-        <v>94.84009552001953</v>
+        <v>94.84007263183594</v>
       </c>
       <c r="D250" t="n">
-        <v>94.84009552001953</v>
+        <v>94.84007263183594</v>
       </c>
       <c r="E250" t="n">
-        <v>94.83063408439924</v>
+        <v>94.83061119849903</v>
       </c>
       <c r="F250" t="n">
-        <v>94.84009552001953</v>
+        <v>94.84007263183594</v>
       </c>
       <c r="G250" t="n">
         <v>4974100</v>
@@ -6199,16 +6199,16 @@
         <v>45653</v>
       </c>
       <c r="C251" t="n">
-        <v>94.86847686767578</v>
+        <v>94.86845397949219</v>
       </c>
       <c r="D251" t="n">
-        <v>94.86847686767578</v>
+        <v>94.86845397949219</v>
       </c>
       <c r="E251" t="n">
-        <v>94.85901543163085</v>
+        <v>94.85899254572995</v>
       </c>
       <c r="F251" t="n">
-        <v>94.85901543163085</v>
+        <v>94.85899254572995</v>
       </c>
       <c r="G251" t="n">
         <v>6558000</v>
@@ -6222,16 +6222,16 @@
         <v>45656</v>
       </c>
       <c r="C252" t="n">
-        <v>94.86847686767578</v>
+        <v>94.86845397949219</v>
       </c>
       <c r="D252" t="n">
-        <v>94.8779383037207</v>
+        <v>94.87791541325443</v>
       </c>
       <c r="E252" t="n">
-        <v>94.86847686767578</v>
+        <v>94.86845397949219</v>
       </c>
       <c r="F252" t="n">
-        <v>94.8779383037207</v>
+        <v>94.87791541325443</v>
       </c>
       <c r="G252" t="n">
         <v>6547600</v>
@@ -6245,16 +6245,16 @@
         <v>45657</v>
       </c>
       <c r="C253" t="n">
-        <v>94.89682769775391</v>
+        <v>94.89683532714844</v>
       </c>
       <c r="D253" t="n">
-        <v>94.91574334764803</v>
+        <v>94.91575097856332</v>
       </c>
       <c r="E253" t="n">
-        <v>94.89682769775391</v>
+        <v>94.89683532714844</v>
       </c>
       <c r="F253" t="n">
-        <v>94.90628913118054</v>
+        <v>94.90629676133574</v>
       </c>
       <c r="G253" t="n">
         <v>7371300</v>
@@ -6268,16 +6268,16 @@
         <v>45659</v>
       </c>
       <c r="C254" t="n">
-        <v>94.91575622558594</v>
+        <v>94.91574096679688</v>
       </c>
       <c r="D254" t="n">
-        <v>94.91575622558594</v>
+        <v>94.91574096679688</v>
       </c>
       <c r="E254" t="n">
-        <v>94.90630200783571</v>
+        <v>94.90628675056652</v>
       </c>
       <c r="F254" t="n">
-        <v>94.91575622558594</v>
+        <v>94.91574096679688</v>
       </c>
       <c r="G254" t="n">
         <v>7533100</v>
@@ -6291,16 +6291,16 @@
         <v>45660</v>
       </c>
       <c r="C255" t="n">
-        <v>94.94414520263672</v>
+        <v>94.94412994384766</v>
       </c>
       <c r="D255" t="n">
-        <v>94.95359942085226</v>
+        <v>94.95358416054377</v>
       </c>
       <c r="E255" t="n">
-        <v>94.94414520263672</v>
+        <v>94.94412994384766</v>
       </c>
       <c r="F255" t="n">
-        <v>94.95359942085226</v>
+        <v>94.95358416054377</v>
       </c>
       <c r="G255" t="n">
         <v>6730100</v>
@@ -6314,16 +6314,16 @@
         <v>45663</v>
       </c>
       <c r="C256" t="n">
-        <v>94.94414520263672</v>
+        <v>94.94412994384766</v>
       </c>
       <c r="D256" t="n">
-        <v>94.96306085602826</v>
+        <v>94.9630455941992</v>
       </c>
       <c r="E256" t="n">
-        <v>94.94414520263672</v>
+        <v>94.94412994384766</v>
       </c>
       <c r="F256" t="n">
-        <v>94.95359942085226</v>
+        <v>94.95358416054377</v>
       </c>
       <c r="G256" t="n">
         <v>6938300</v>
@@ -6360,16 +6360,16 @@
         <v>45665</v>
       </c>
       <c r="C258" t="n">
-        <v>94.98196411132812</v>
+        <v>94.98197174072266</v>
       </c>
       <c r="D258" t="n">
-        <v>94.98196411132812</v>
+        <v>94.98197174072266</v>
       </c>
       <c r="E258" t="n">
-        <v>94.97250267810604</v>
+        <v>94.97251030674057</v>
       </c>
       <c r="F258" t="n">
-        <v>94.97250267810604</v>
+        <v>94.97251030674057</v>
       </c>
       <c r="G258" t="n">
         <v>6101100</v>
@@ -6406,16 +6406,16 @@
         <v>45670</v>
       </c>
       <c r="C260" t="n">
-        <v>95.03873443603516</v>
+        <v>95.03871917724609</v>
       </c>
       <c r="D260" t="n">
-        <v>95.03873443603516</v>
+        <v>95.03871917724609</v>
       </c>
       <c r="E260" t="n">
-        <v>95.02927300120436</v>
+        <v>95.02925774393435</v>
       </c>
       <c r="F260" t="n">
-        <v>95.03400011013966</v>
+        <v>95.03398485211071</v>
       </c>
       <c r="G260" t="n">
         <v>7647300</v>
@@ -6429,16 +6429,16 @@
         <v>45671</v>
       </c>
       <c r="C261" t="n">
-        <v>95.04817962646484</v>
+        <v>95.04818725585938</v>
       </c>
       <c r="D261" t="n">
-        <v>95.04817962646484</v>
+        <v>95.04818725585938</v>
       </c>
       <c r="E261" t="n">
-        <v>95.03871819325106</v>
+        <v>95.03872582188613</v>
       </c>
       <c r="F261" t="n">
-        <v>95.04817962646484</v>
+        <v>95.04818725585938</v>
       </c>
       <c r="G261" t="n">
         <v>7245400</v>
@@ -6567,16 +6567,16 @@
         <v>45680</v>
       </c>
       <c r="C267" t="n">
-        <v>95.14279937744141</v>
+        <v>95.14278411865234</v>
       </c>
       <c r="D267" t="n">
-        <v>95.14279937744141</v>
+        <v>95.14278411865234</v>
       </c>
       <c r="E267" t="n">
-        <v>95.13333794153569</v>
+        <v>95.13332268426403</v>
       </c>
       <c r="F267" t="n">
-        <v>95.14279937744141</v>
+        <v>95.14278411865234</v>
       </c>
       <c r="G267" t="n">
         <v>5085800</v>
@@ -6590,16 +6590,16 @@
         <v>45681</v>
       </c>
       <c r="C268" t="n">
-        <v>95.17115783691406</v>
+        <v>95.17117309570312</v>
       </c>
       <c r="D268" t="n">
-        <v>95.18061927096755</v>
+        <v>95.18063453127357</v>
       </c>
       <c r="E268" t="n">
-        <v>95.17115783691406</v>
+        <v>95.17117309570312</v>
       </c>
       <c r="F268" t="n">
-        <v>95.17115783691406</v>
+        <v>95.17117309570312</v>
       </c>
       <c r="G268" t="n">
         <v>6380000</v>
@@ -6613,16 +6613,16 @@
         <v>45684</v>
       </c>
       <c r="C269" t="n">
-        <v>95.17115783691406</v>
+        <v>95.17117309570312</v>
       </c>
       <c r="D269" t="n">
-        <v>95.19007348806143</v>
+        <v>95.19008874988323</v>
       </c>
       <c r="E269" t="n">
-        <v>95.17115783691406</v>
+        <v>95.17117309570312</v>
       </c>
       <c r="F269" t="n">
-        <v>95.18061927096755</v>
+        <v>95.18063453127357</v>
       </c>
       <c r="G269" t="n">
         <v>9439800</v>
@@ -6636,16 +6636,16 @@
         <v>45685</v>
       </c>
       <c r="C270" t="n">
-        <v>95.19954681396484</v>
+        <v>95.19953918457031</v>
       </c>
       <c r="D270" t="n">
-        <v>95.19954681396484</v>
+        <v>95.19953918457031</v>
       </c>
       <c r="E270" t="n">
-        <v>95.18063116045464</v>
+        <v>95.18062353257602</v>
       </c>
       <c r="F270" t="n">
-        <v>95.19008537872948</v>
+        <v>95.1900777500932</v>
       </c>
       <c r="G270" t="n">
         <v>5857900</v>
@@ -6659,16 +6659,16 @@
         <v>45686</v>
       </c>
       <c r="C271" t="n">
-        <v>95.19954681396484</v>
+        <v>95.19953918457031</v>
       </c>
       <c r="D271" t="n">
-        <v>95.20900824920021</v>
+        <v>95.20900061904742</v>
       </c>
       <c r="E271" t="n">
-        <v>95.19954681396484</v>
+        <v>95.19953918457031</v>
       </c>
       <c r="F271" t="n">
-        <v>95.19954681396484</v>
+        <v>95.19953918457031</v>
       </c>
       <c r="G271" t="n">
         <v>3978700</v>
@@ -6682,16 +6682,16 @@
         <v>45687</v>
       </c>
       <c r="C272" t="n">
-        <v>95.21847534179688</v>
+        <v>95.21845245361328</v>
       </c>
       <c r="D272" t="n">
-        <v>95.22792956063344</v>
+        <v>95.22790667017728</v>
       </c>
       <c r="E272" t="n">
-        <v>95.20901390599936</v>
+        <v>95.20899102009007</v>
       </c>
       <c r="F272" t="n">
-        <v>95.20901390599936</v>
+        <v>95.20899102009007</v>
       </c>
       <c r="G272" t="n">
         <v>8043500</v>
@@ -6751,16 +6751,16 @@
         <v>45692</v>
       </c>
       <c r="C275" t="n">
-        <v>95.2781982421875</v>
+        <v>95.27821350097656</v>
       </c>
       <c r="D275" t="n">
-        <v>95.2781982421875</v>
+        <v>95.27821350097656</v>
       </c>
       <c r="E275" t="n">
-        <v>95.2687025714739</v>
+        <v>95.26871782874224</v>
       </c>
       <c r="F275" t="n">
-        <v>95.2781982421875</v>
+        <v>95.27821350097656</v>
       </c>
       <c r="G275" t="n">
         <v>7866600</v>
@@ -6774,16 +6774,16 @@
         <v>45693</v>
       </c>
       <c r="C276" t="n">
-        <v>95.2781982421875</v>
+        <v>95.27821350097656</v>
       </c>
       <c r="D276" t="n">
-        <v>95.28769391290109</v>
+        <v>95.28770917321089</v>
       </c>
       <c r="E276" t="n">
-        <v>95.2781982421875</v>
+        <v>95.27821350097656</v>
       </c>
       <c r="F276" t="n">
-        <v>95.28769391290109</v>
+        <v>95.28770917321089</v>
       </c>
       <c r="G276" t="n">
         <v>7100900</v>
@@ -6843,16 +6843,16 @@
         <v>45698</v>
       </c>
       <c r="C279" t="n">
-        <v>95.34464263916016</v>
+        <v>95.34466552734375</v>
       </c>
       <c r="D279" t="n">
-        <v>95.34464263916016</v>
+        <v>95.34466552734375</v>
       </c>
       <c r="E279" t="n">
-        <v>95.33514696952335</v>
+        <v>95.33516985542744</v>
       </c>
       <c r="F279" t="n">
-        <v>95.34464263916016</v>
+        <v>95.34466552734375</v>
       </c>
       <c r="G279" t="n">
         <v>7517800</v>
@@ -6866,16 +6866,16 @@
         <v>45699</v>
       </c>
       <c r="C280" t="n">
-        <v>95.34464263916016</v>
+        <v>95.34466552734375</v>
       </c>
       <c r="D280" t="n">
-        <v>95.35413830879696</v>
+        <v>95.35416119926006</v>
       </c>
       <c r="E280" t="n">
-        <v>95.34464263916016</v>
+        <v>95.34466552734375</v>
       </c>
       <c r="F280" t="n">
-        <v>95.35413830879696</v>
+        <v>95.35416119926006</v>
       </c>
       <c r="G280" t="n">
         <v>6424100</v>
@@ -6889,16 +6889,16 @@
         <v>45700</v>
       </c>
       <c r="C281" t="n">
-        <v>95.35415649414062</v>
+        <v>95.35416412353516</v>
       </c>
       <c r="D281" t="n">
-        <v>95.36364492251329</v>
+        <v>95.36365255266701</v>
       </c>
       <c r="E281" t="n">
-        <v>95.35415649414062</v>
+        <v>95.35416412353516</v>
       </c>
       <c r="F281" t="n">
-        <v>95.35415649414062</v>
+        <v>95.35416412353516</v>
       </c>
       <c r="G281" t="n">
         <v>6618800</v>
@@ -6935,16 +6935,16 @@
         <v>45702</v>
       </c>
       <c r="C283" t="n">
-        <v>95.41110992431641</v>
+        <v>95.41112518310547</v>
       </c>
       <c r="D283" t="n">
-        <v>95.42060559515583</v>
+        <v>95.42062085546351</v>
       </c>
       <c r="E283" t="n">
-        <v>95.41110992431641</v>
+        <v>95.41112518310547</v>
       </c>
       <c r="F283" t="n">
-        <v>95.41585413819881</v>
+        <v>95.41586939774659</v>
       </c>
       <c r="G283" t="n">
         <v>7648100</v>
@@ -6958,16 +6958,16 @@
         <v>45706</v>
       </c>
       <c r="C284" t="n">
-        <v>95.43009948730469</v>
+        <v>95.43008422851562</v>
       </c>
       <c r="D284" t="n">
-        <v>95.43009948730469</v>
+        <v>95.43008422851562</v>
       </c>
       <c r="E284" t="n">
-        <v>95.42061105899657</v>
+        <v>95.42059580172466</v>
       </c>
       <c r="F284" t="n">
-        <v>95.43009948730469</v>
+        <v>95.43008422851562</v>
       </c>
       <c r="G284" t="n">
         <v>15815200</v>
@@ -6981,16 +6981,16 @@
         <v>45707</v>
       </c>
       <c r="C285" t="n">
-        <v>95.43009948730469</v>
+        <v>95.43008422851562</v>
       </c>
       <c r="D285" t="n">
-        <v>95.43959515868785</v>
+        <v>95.43957989838049</v>
       </c>
       <c r="E285" t="n">
-        <v>95.43009948730469</v>
+        <v>95.43008422851562</v>
       </c>
       <c r="F285" t="n">
-        <v>95.43959515868785</v>
+        <v>95.43957989838049</v>
       </c>
       <c r="G285" t="n">
         <v>7277600</v>
@@ -7004,16 +7004,16 @@
         <v>45708</v>
       </c>
       <c r="C286" t="n">
-        <v>95.44908142089844</v>
+        <v>95.44908905029297</v>
       </c>
       <c r="D286" t="n">
-        <v>95.44908142089844</v>
+        <v>95.44908905029297</v>
       </c>
       <c r="E286" t="n">
-        <v>95.43958575045134</v>
+        <v>95.43959337908686</v>
       </c>
       <c r="F286" t="n">
-        <v>95.44908142089844</v>
+        <v>95.44908905029297</v>
       </c>
       <c r="G286" t="n">
         <v>7608000</v>
@@ -7027,16 +7027,16 @@
         <v>45709</v>
       </c>
       <c r="C287" t="n">
-        <v>95.487060546875</v>
+        <v>95.48705291748047</v>
       </c>
       <c r="D287" t="n">
-        <v>95.487060546875</v>
+        <v>95.48705291748047</v>
       </c>
       <c r="E287" t="n">
-        <v>95.47756487606122</v>
+        <v>95.47755724742539</v>
       </c>
       <c r="F287" t="n">
-        <v>95.47756487606122</v>
+        <v>95.47755724742539</v>
       </c>
       <c r="G287" t="n">
         <v>9111000</v>
@@ -7050,16 +7050,16 @@
         <v>45712</v>
       </c>
       <c r="C288" t="n">
-        <v>95.49654388427734</v>
+        <v>95.49656677246094</v>
       </c>
       <c r="D288" t="n">
-        <v>95.49654388427734</v>
+        <v>95.49656677246094</v>
       </c>
       <c r="E288" t="n">
-        <v>95.48705545704394</v>
+        <v>95.4870783429534</v>
       </c>
       <c r="F288" t="n">
-        <v>95.49654388427734</v>
+        <v>95.49656677246094</v>
       </c>
       <c r="G288" t="n">
         <v>9734600</v>
@@ -7073,16 +7073,16 @@
         <v>45713</v>
       </c>
       <c r="C289" t="n">
-        <v>95.50605010986328</v>
+        <v>95.50601959228516</v>
       </c>
       <c r="D289" t="n">
-        <v>95.50605010986328</v>
+        <v>95.50601959228516</v>
       </c>
       <c r="E289" t="n">
-        <v>95.49655443850621</v>
+        <v>95.49652392396229</v>
       </c>
       <c r="F289" t="n">
-        <v>95.49655443850621</v>
+        <v>95.49652392396229</v>
       </c>
       <c r="G289" t="n">
         <v>10827700</v>
@@ -7096,16 +7096,16 @@
         <v>45714</v>
       </c>
       <c r="C290" t="n">
-        <v>95.50605010986328</v>
+        <v>95.50601959228516</v>
       </c>
       <c r="D290" t="n">
-        <v>95.51554578122035</v>
+        <v>95.51551526060803</v>
       </c>
       <c r="E290" t="n">
-        <v>95.50605010986328</v>
+        <v>95.50601959228516</v>
       </c>
       <c r="F290" t="n">
-        <v>95.50605010986328</v>
+        <v>95.50601959228516</v>
       </c>
       <c r="G290" t="n">
         <v>9536300</v>
@@ -7119,16 +7119,16 @@
         <v>45715</v>
       </c>
       <c r="C291" t="n">
-        <v>95.53450775146484</v>
+        <v>95.53452301025391</v>
       </c>
       <c r="D291" t="n">
-        <v>95.53450775146484</v>
+        <v>95.53452301025391</v>
       </c>
       <c r="E291" t="n">
-        <v>95.52501932538067</v>
+        <v>95.52503458265423</v>
       </c>
       <c r="F291" t="n">
-        <v>95.53450775146484</v>
+        <v>95.53452301025391</v>
       </c>
       <c r="G291" t="n">
         <v>10807800</v>
@@ -7142,16 +7142,16 @@
         <v>45716</v>
       </c>
       <c r="C292" t="n">
-        <v>95.55352020263672</v>
+        <v>95.55352783203125</v>
       </c>
       <c r="D292" t="n">
-        <v>95.56301587389234</v>
+        <v>95.56302350404505</v>
       </c>
       <c r="E292" t="n">
-        <v>95.55352020263672</v>
+        <v>95.55352783203125</v>
       </c>
       <c r="F292" t="n">
-        <v>95.55352020263672</v>
+        <v>95.55352783203125</v>
       </c>
       <c r="G292" t="n">
         <v>13772600</v>
@@ -7165,16 +7165,16 @@
         <v>45719</v>
       </c>
       <c r="C293" t="n">
-        <v>95.57543182373047</v>
+        <v>95.57542419433594</v>
       </c>
       <c r="D293" t="n">
-        <v>95.57543182373047</v>
+        <v>95.57542419433594</v>
       </c>
       <c r="E293" t="n">
-        <v>95.56590652995234</v>
+        <v>95.56589890131818</v>
       </c>
       <c r="F293" t="n">
-        <v>95.57543182373047</v>
+        <v>95.57542419433594</v>
       </c>
       <c r="G293" t="n">
         <v>17436600</v>
@@ -7188,16 +7188,16 @@
         <v>45720</v>
       </c>
       <c r="C294" t="n">
-        <v>95.58494567871094</v>
+        <v>95.58493041992188</v>
       </c>
       <c r="D294" t="n">
-        <v>95.58494567871094</v>
+        <v>95.58493041992188</v>
       </c>
       <c r="E294" t="n">
-        <v>95.57542038607271</v>
+        <v>95.57540512880422</v>
       </c>
       <c r="F294" t="n">
-        <v>95.58494567871094</v>
+        <v>95.58493041992188</v>
       </c>
       <c r="G294" t="n">
         <v>11543100</v>
@@ -7211,16 +7211,16 @@
         <v>45721</v>
       </c>
       <c r="C295" t="n">
-        <v>95.58494567871094</v>
+        <v>95.58493041992188</v>
       </c>
       <c r="D295" t="n">
-        <v>95.59446370567971</v>
+        <v>95.59444844537123</v>
       </c>
       <c r="E295" t="n">
-        <v>95.58494567871094</v>
+        <v>95.58493041992188</v>
       </c>
       <c r="F295" t="n">
-        <v>95.58494567871094</v>
+        <v>95.58493041992188</v>
       </c>
       <c r="G295" t="n">
         <v>7162600</v>
@@ -7257,16 +7257,16 @@
         <v>45723</v>
       </c>
       <c r="C297" t="n">
-        <v>95.64208984375</v>
+        <v>95.64208221435547</v>
       </c>
       <c r="D297" t="n">
-        <v>95.64208984375</v>
+        <v>95.64208221435547</v>
       </c>
       <c r="E297" t="n">
-        <v>95.63256455042055</v>
+        <v>95.63255692178585</v>
       </c>
       <c r="F297" t="n">
-        <v>95.64208984375</v>
+        <v>95.64208221435547</v>
       </c>
       <c r="G297" t="n">
         <v>8962400</v>
@@ -7280,16 +7280,16 @@
         <v>45726</v>
       </c>
       <c r="C298" t="n">
-        <v>95.64208984375</v>
+        <v>95.64208221435547</v>
       </c>
       <c r="D298" t="n">
-        <v>95.65161513707946</v>
+        <v>95.65160750692509</v>
       </c>
       <c r="E298" t="n">
-        <v>95.64208984375</v>
+        <v>95.64208221435547</v>
       </c>
       <c r="F298" t="n">
-        <v>95.65161513707946</v>
+        <v>95.65160750692509</v>
       </c>
       <c r="G298" t="n">
         <v>14768100</v>
@@ -7303,16 +7303,16 @@
         <v>45727</v>
       </c>
       <c r="C299" t="n">
-        <v>95.66111755371094</v>
+        <v>95.66112518310547</v>
       </c>
       <c r="D299" t="n">
-        <v>95.66111755371094</v>
+        <v>95.66112518310547</v>
       </c>
       <c r="E299" t="n">
-        <v>95.65159952760472</v>
+        <v>95.65160715624013</v>
       </c>
       <c r="F299" t="n">
-        <v>95.65159952760472</v>
+        <v>95.65160715624013</v>
       </c>
       <c r="G299" t="n">
         <v>11456900</v>
@@ -7326,16 +7326,16 @@
         <v>45728</v>
       </c>
       <c r="C300" t="n">
-        <v>95.66111755371094</v>
+        <v>95.66112518310547</v>
       </c>
       <c r="D300" t="n">
-        <v>95.67064284548596</v>
+        <v>95.67065047564017</v>
       </c>
       <c r="E300" t="n">
-        <v>95.66111755371094</v>
+        <v>95.66112518310547</v>
       </c>
       <c r="F300" t="n">
-        <v>95.67064284548596</v>
+        <v>95.67065047564017</v>
       </c>
       <c r="G300" t="n">
         <v>11307300</v>
@@ -7349,16 +7349,16 @@
         <v>45729</v>
       </c>
       <c r="C301" t="n">
-        <v>95.689697265625</v>
+        <v>95.68971252441406</v>
       </c>
       <c r="D301" t="n">
-        <v>95.689697265625</v>
+        <v>95.68971252441406</v>
       </c>
       <c r="E301" t="n">
-        <v>95.67064668131115</v>
+        <v>95.67066193706239</v>
       </c>
       <c r="F301" t="n">
-        <v>95.67064668131115</v>
+        <v>95.67066193706239</v>
       </c>
       <c r="G301" t="n">
         <v>13110600</v>
@@ -7372,16 +7372,16 @@
         <v>45730</v>
       </c>
       <c r="C302" t="n">
-        <v>95.71827697753906</v>
+        <v>95.71824645996094</v>
       </c>
       <c r="D302" t="n">
-        <v>95.71827697753906</v>
+        <v>95.71824645996094</v>
       </c>
       <c r="E302" t="n">
-        <v>95.70875168427743</v>
+        <v>95.70872116973622</v>
       </c>
       <c r="F302" t="n">
-        <v>95.71827697753906</v>
+        <v>95.71824645996094</v>
       </c>
       <c r="G302" t="n">
         <v>11421900</v>
@@ -7395,16 +7395,16 @@
         <v>45733</v>
       </c>
       <c r="C303" t="n">
-        <v>95.72779083251953</v>
+        <v>95.72779846191406</v>
       </c>
       <c r="D303" t="n">
-        <v>95.72779083251953</v>
+        <v>95.72779846191406</v>
       </c>
       <c r="E303" t="n">
-        <v>95.71827280534269</v>
+        <v>95.71828043397865</v>
       </c>
       <c r="F303" t="n">
-        <v>95.72779083251953</v>
+        <v>95.72779846191406</v>
       </c>
       <c r="G303" t="n">
         <v>9018300</v>
@@ -7418,16 +7418,16 @@
         <v>45734</v>
       </c>
       <c r="C304" t="n">
-        <v>95.7373046875</v>
+        <v>95.73731231689453</v>
       </c>
       <c r="D304" t="n">
-        <v>95.7373046875</v>
+        <v>95.73731231689453</v>
       </c>
       <c r="E304" t="n">
-        <v>95.72777939579156</v>
+        <v>95.727787024427</v>
       </c>
       <c r="F304" t="n">
-        <v>95.7373046875</v>
+        <v>95.73731231689453</v>
       </c>
       <c r="G304" t="n">
         <v>9213100</v>
@@ -7441,16 +7441,16 @@
         <v>45735</v>
       </c>
       <c r="C305" t="n">
-        <v>95.75635528564453</v>
+        <v>95.75636291503906</v>
       </c>
       <c r="D305" t="n">
-        <v>95.75635528564453</v>
+        <v>95.75636291503906</v>
       </c>
       <c r="E305" t="n">
-        <v>95.74682999393463</v>
+        <v>95.74683762257023</v>
       </c>
       <c r="F305" t="n">
-        <v>95.74682999393463</v>
+        <v>95.74683762257023</v>
       </c>
       <c r="G305" t="n">
         <v>13584800</v>
@@ -7464,16 +7464,16 @@
         <v>45736</v>
       </c>
       <c r="C306" t="n">
-        <v>95.75635528564453</v>
+        <v>95.75636291503906</v>
       </c>
       <c r="D306" t="n">
-        <v>95.76587331168571</v>
+        <v>95.76588094183857</v>
       </c>
       <c r="E306" t="n">
-        <v>95.75635528564453</v>
+        <v>95.75636291503906</v>
       </c>
       <c r="F306" t="n">
-        <v>95.76587331168571</v>
+        <v>95.76588094183857</v>
       </c>
       <c r="G306" t="n">
         <v>12648500</v>
@@ -7487,16 +7487,16 @@
         <v>45737</v>
       </c>
       <c r="C307" t="n">
-        <v>95.78492736816406</v>
+        <v>95.78494262695312</v>
       </c>
       <c r="D307" t="n">
-        <v>95.79444539455035</v>
+        <v>95.79446065485567</v>
       </c>
       <c r="E307" t="n">
-        <v>95.78492736816406</v>
+        <v>95.78494262695312</v>
       </c>
       <c r="F307" t="n">
-        <v>95.79444539455035</v>
+        <v>95.79446065485567</v>
       </c>
       <c r="G307" t="n">
         <v>13101800</v>
@@ -7510,16 +7510,16 @@
         <v>45740</v>
       </c>
       <c r="C308" t="n">
-        <v>95.80397796630859</v>
+        <v>95.80396270751953</v>
       </c>
       <c r="D308" t="n">
-        <v>95.81350325908767</v>
+        <v>95.8134879987815</v>
       </c>
       <c r="E308" t="n">
-        <v>95.80397796630859</v>
+        <v>95.80396270751953</v>
       </c>
       <c r="F308" t="n">
-        <v>95.80874424553291</v>
+        <v>95.80872898598471</v>
       </c>
       <c r="G308" t="n">
         <v>13854600</v>
@@ -7533,16 +7533,16 @@
         <v>45741</v>
       </c>
       <c r="C309" t="n">
-        <v>95.81349945068359</v>
+        <v>95.81350708007812</v>
       </c>
       <c r="D309" t="n">
-        <v>95.81349945068359</v>
+        <v>95.81350708007812</v>
       </c>
       <c r="E309" t="n">
-        <v>95.80397415828314</v>
+        <v>95.80398178691919</v>
       </c>
       <c r="F309" t="n">
-        <v>95.81349945068359</v>
+        <v>95.81350708007812</v>
       </c>
       <c r="G309" t="n">
         <v>13844800</v>
@@ -7556,16 +7556,16 @@
         <v>45742</v>
       </c>
       <c r="C310" t="n">
-        <v>95.83254241943359</v>
+        <v>95.83255004882812</v>
       </c>
       <c r="D310" t="n">
-        <v>95.83254241943359</v>
+        <v>95.83255004882812</v>
       </c>
       <c r="E310" t="n">
-        <v>95.8230243927372</v>
+        <v>95.82303202137399</v>
       </c>
       <c r="F310" t="n">
-        <v>95.83254241943359</v>
+        <v>95.83255004882812</v>
       </c>
       <c r="G310" t="n">
         <v>12262200</v>
@@ -7602,16 +7602,16 @@
         <v>45744</v>
       </c>
       <c r="C312" t="n">
-        <v>95.87062835693359</v>
+        <v>95.87065124511719</v>
       </c>
       <c r="D312" t="n">
-        <v>95.87062835693359</v>
+        <v>95.87065124511719</v>
       </c>
       <c r="E312" t="n">
-        <v>95.86111033102809</v>
+        <v>95.86113321693935</v>
       </c>
       <c r="F312" t="n">
-        <v>95.86111033102809</v>
+        <v>95.86113321693935</v>
       </c>
       <c r="G312" t="n">
         <v>11747100</v>
@@ -7625,16 +7625,16 @@
         <v>45747</v>
       </c>
       <c r="C313" t="n">
-        <v>95.87062835693359</v>
+        <v>95.87065124511719</v>
       </c>
       <c r="D313" t="n">
-        <v>95.88015364850773</v>
+        <v>95.88017653896539</v>
       </c>
       <c r="E313" t="n">
-        <v>95.87062835693359</v>
+        <v>95.87065124511719</v>
       </c>
       <c r="F313" t="n">
-        <v>95.87062835693359</v>
+        <v>95.87065124511719</v>
       </c>
       <c r="G313" t="n">
         <v>18210800</v>
@@ -7694,16 +7694,16 @@
         <v>45750</v>
       </c>
       <c r="C316" t="n">
-        <v>95.92415618896484</v>
+        <v>95.92416381835938</v>
       </c>
       <c r="D316" t="n">
-        <v>95.92415618896484</v>
+        <v>95.92416381835938</v>
       </c>
       <c r="E316" t="n">
-        <v>95.90504719150279</v>
+        <v>95.90505481937747</v>
       </c>
       <c r="F316" t="n">
-        <v>95.9146053355977</v>
+        <v>95.9146129642326</v>
       </c>
       <c r="G316" t="n">
         <v>13988800</v>
@@ -7717,16 +7717,16 @@
         <v>45751</v>
       </c>
       <c r="C317" t="n">
-        <v>95.95282745361328</v>
+        <v>95.95281982421875</v>
       </c>
       <c r="D317" t="n">
-        <v>95.95282745361328</v>
+        <v>95.95281982421875</v>
       </c>
       <c r="E317" t="n">
-        <v>95.94326930983391</v>
+        <v>95.94326168119937</v>
       </c>
       <c r="F317" t="n">
-        <v>95.94326930983391</v>
+        <v>95.94326168119937</v>
       </c>
       <c r="G317" t="n">
         <v>22826300</v>
@@ -7740,16 +7740,16 @@
         <v>45754</v>
       </c>
       <c r="C318" t="n">
-        <v>95.96237182617188</v>
+        <v>95.96238708496094</v>
       </c>
       <c r="D318" t="n">
-        <v>95.96237182617188</v>
+        <v>95.96238708496094</v>
       </c>
       <c r="E318" t="n">
-        <v>95.95282097376501</v>
+        <v>95.95283623103541</v>
       </c>
       <c r="F318" t="n">
-        <v>95.95282097376501</v>
+        <v>95.95283623103541</v>
       </c>
       <c r="G318" t="n">
         <v>22564000</v>
@@ -7763,16 +7763,16 @@
         <v>45755</v>
       </c>
       <c r="C319" t="n">
-        <v>95.96237182617188</v>
+        <v>95.96238708496094</v>
       </c>
       <c r="D319" t="n">
-        <v>95.97192996930578</v>
+        <v>95.97194522961465</v>
       </c>
       <c r="E319" t="n">
-        <v>95.95282097376501</v>
+        <v>95.95283623103541</v>
       </c>
       <c r="F319" t="n">
-        <v>95.95759639996845</v>
+        <v>95.95761165799817</v>
       </c>
       <c r="G319" t="n">
         <v>17116100</v>
@@ -7786,16 +7786,16 @@
         <v>45756</v>
       </c>
       <c r="C320" t="n">
-        <v>95.98150634765625</v>
+        <v>95.98149108886719</v>
       </c>
       <c r="D320" t="n">
-        <v>95.98150634765625</v>
+        <v>95.98149108886719</v>
       </c>
       <c r="E320" t="n">
-        <v>95.97194820270643</v>
+        <v>95.97193294543689</v>
       </c>
       <c r="F320" t="n">
-        <v>95.97194820270643</v>
+        <v>95.97193294543689</v>
       </c>
       <c r="G320" t="n">
         <v>21838800</v>
@@ -7809,16 +7809,16 @@
         <v>45757</v>
       </c>
       <c r="C321" t="n">
-        <v>95.98150634765625</v>
+        <v>95.98149108886719</v>
       </c>
       <c r="D321" t="n">
-        <v>95.99105720187765</v>
+        <v>95.99104194157023</v>
       </c>
       <c r="E321" t="n">
-        <v>95.98150634765625</v>
+        <v>95.98149108886719</v>
       </c>
       <c r="F321" t="n">
-        <v>95.98150634765625</v>
+        <v>95.98149108886719</v>
       </c>
       <c r="G321" t="n">
         <v>16851500</v>
@@ -7832,16 +7832,16 @@
         <v>45758</v>
       </c>
       <c r="C322" t="n">
-        <v>96.02926635742188</v>
+        <v>96.02927398681641</v>
       </c>
       <c r="D322" t="n">
-        <v>96.02926635742188</v>
+        <v>96.02927398681641</v>
       </c>
       <c r="E322" t="n">
-        <v>96.01971550480508</v>
+        <v>96.01972313344081</v>
       </c>
       <c r="F322" t="n">
-        <v>96.02449093111348</v>
+        <v>96.02449856012861</v>
       </c>
       <c r="G322" t="n">
         <v>12916600</v>
@@ -7855,16 +7855,16 @@
         <v>45761</v>
       </c>
       <c r="C323" t="n">
-        <v>96.03882598876953</v>
+        <v>96.038818359375</v>
       </c>
       <c r="D323" t="n">
-        <v>96.03882598876953</v>
+        <v>96.038818359375</v>
       </c>
       <c r="E323" t="n">
-        <v>96.02926784527745</v>
+        <v>96.02926021664223</v>
       </c>
       <c r="F323" t="n">
-        <v>96.02926784527745</v>
+        <v>96.02926021664223</v>
       </c>
       <c r="G323" t="n">
         <v>13772300</v>
@@ -7878,16 +7878,16 @@
         <v>45762</v>
       </c>
       <c r="C324" t="n">
-        <v>96.04838562011719</v>
+        <v>96.04837036132812</v>
       </c>
       <c r="D324" t="n">
-        <v>96.04838562011719</v>
+        <v>96.04837036132812</v>
       </c>
       <c r="E324" t="n">
-        <v>96.03882747647705</v>
+        <v>96.03881221920645</v>
       </c>
       <c r="F324" t="n">
-        <v>96.04838562011719</v>
+        <v>96.04837036132812</v>
       </c>
       <c r="G324" t="n">
         <v>10043700</v>
@@ -7901,16 +7901,16 @@
         <v>45763</v>
       </c>
       <c r="C325" t="n">
-        <v>96.06748199462891</v>
+        <v>96.06748962402344</v>
       </c>
       <c r="D325" t="n">
-        <v>96.06748199462891</v>
+        <v>96.06748962402344</v>
       </c>
       <c r="E325" t="n">
-        <v>96.05792385224458</v>
+        <v>96.05793148088003</v>
       </c>
       <c r="F325" t="n">
-        <v>96.06270656879997</v>
+        <v>96.06271419781525</v>
       </c>
       <c r="G325" t="n">
         <v>8840000</v>
@@ -8039,16 +8039,16 @@
         <v>45772</v>
       </c>
       <c r="C331" t="n">
-        <v>96.18218231201172</v>
+        <v>96.18217468261719</v>
       </c>
       <c r="D331" t="n">
-        <v>96.18218231201172</v>
+        <v>96.18217468261719</v>
       </c>
       <c r="E331" t="n">
-        <v>96.17262416719458</v>
+        <v>96.17261653855823</v>
       </c>
       <c r="F331" t="n">
-        <v>96.18218231201172</v>
+        <v>96.18217468261719</v>
       </c>
       <c r="G331" t="n">
         <v>8822700</v>
@@ -8062,16 +8062,16 @@
         <v>45775</v>
       </c>
       <c r="C332" t="n">
-        <v>96.18218231201172</v>
+        <v>96.18217468261719</v>
       </c>
       <c r="D332" t="n">
-        <v>96.19174045682885</v>
+        <v>96.19173282667613</v>
       </c>
       <c r="E332" t="n">
-        <v>96.18218231201172</v>
+        <v>96.18217468261719</v>
       </c>
       <c r="F332" t="n">
-        <v>96.18218231201172</v>
+        <v>96.18217468261719</v>
       </c>
       <c r="G332" t="n">
         <v>9127900</v>
@@ -8085,16 +8085,16 @@
         <v>45776</v>
       </c>
       <c r="C333" t="n">
-        <v>96.19174194335938</v>
+        <v>96.19172668457031</v>
       </c>
       <c r="D333" t="n">
-        <v>96.2012927975958</v>
+        <v>96.20127753729169</v>
       </c>
       <c r="E333" t="n">
-        <v>96.19174194335938</v>
+        <v>96.19172668457031</v>
       </c>
       <c r="F333" t="n">
-        <v>96.19174194335938</v>
+        <v>96.19172668457031</v>
       </c>
       <c r="G333" t="n">
         <v>8555000</v>
@@ -8108,16 +8108,16 @@
         <v>45777</v>
       </c>
       <c r="C334" t="n">
-        <v>96.22041320800781</v>
+        <v>96.22040557861328</v>
       </c>
       <c r="D334" t="n">
-        <v>96.22041320800781</v>
+        <v>96.22040557861328</v>
       </c>
       <c r="E334" t="n">
-        <v>96.20129691725951</v>
+        <v>96.20128928938072</v>
       </c>
       <c r="F334" t="n">
-        <v>96.20129691725951</v>
+        <v>96.20128928938072</v>
       </c>
       <c r="G334" t="n">
         <v>16040200</v>
@@ -8154,16 +8154,16 @@
         <v>45779</v>
       </c>
       <c r="C336" t="n">
-        <v>96.26355743408203</v>
+        <v>96.2635498046875</v>
       </c>
       <c r="D336" t="n">
-        <v>96.26355743408203</v>
+        <v>96.2635498046875</v>
       </c>
       <c r="E336" t="n">
-        <v>96.25396738228072</v>
+        <v>96.25395975364626</v>
       </c>
       <c r="F336" t="n">
-        <v>96.25396738228072</v>
+        <v>96.25395975364626</v>
       </c>
       <c r="G336" t="n">
         <v>13930900</v>
@@ -8177,16 +8177,16 @@
         <v>45782</v>
       </c>
       <c r="C337" t="n">
-        <v>96.27313232421875</v>
+        <v>96.27312469482422</v>
       </c>
       <c r="D337" t="n">
-        <v>96.27313232421875</v>
+        <v>96.27312469482422</v>
       </c>
       <c r="E337" t="n">
-        <v>96.26354227392774</v>
+        <v>96.26353464529318</v>
       </c>
       <c r="F337" t="n">
-        <v>96.27313232421875</v>
+        <v>96.27312469482422</v>
       </c>
       <c r="G337" t="n">
         <v>13223700</v>
@@ -8200,16 +8200,16 @@
         <v>45783</v>
       </c>
       <c r="C338" t="n">
-        <v>96.27313232421875</v>
+        <v>96.27312469482422</v>
       </c>
       <c r="D338" t="n">
-        <v>96.28271505944471</v>
+        <v>96.28270742929077</v>
       </c>
       <c r="E338" t="n">
-        <v>96.27313232421875</v>
+        <v>96.27312469482422</v>
       </c>
       <c r="F338" t="n">
-        <v>96.28271505944471</v>
+        <v>96.28270742929077</v>
       </c>
       <c r="G338" t="n">
         <v>8986000</v>
@@ -8223,16 +8223,16 @@
         <v>45784</v>
       </c>
       <c r="C339" t="n">
-        <v>96.28273010253906</v>
+        <v>96.28271484375</v>
       </c>
       <c r="D339" t="n">
-        <v>96.29232015432841</v>
+        <v>96.29230489401954</v>
       </c>
       <c r="E339" t="n">
-        <v>96.28273010253906</v>
+        <v>96.28271484375</v>
       </c>
       <c r="F339" t="n">
-        <v>96.29232015432841</v>
+        <v>96.29230489401954</v>
       </c>
       <c r="G339" t="n">
         <v>8509300</v>
@@ -8269,16 +8269,16 @@
         <v>45786</v>
       </c>
       <c r="C341" t="n">
-        <v>96.34025573730469</v>
+        <v>96.34026336669922</v>
       </c>
       <c r="D341" t="n">
-        <v>96.34025573730469</v>
+        <v>96.34026336669922</v>
       </c>
       <c r="E341" t="n">
-        <v>96.33066568624807</v>
+        <v>96.33067331488314</v>
       </c>
       <c r="F341" t="n">
-        <v>96.33066568624807</v>
+        <v>96.33067331488314</v>
       </c>
       <c r="G341" t="n">
         <v>11793700</v>
@@ -8292,16 +8292,16 @@
         <v>45789</v>
       </c>
       <c r="C342" t="n">
-        <v>96.34025573730469</v>
+        <v>96.34026336669922</v>
       </c>
       <c r="D342" t="n">
-        <v>96.34983847329568</v>
+        <v>96.34984610344908</v>
       </c>
       <c r="E342" t="n">
-        <v>96.34025573730469</v>
+        <v>96.34026336669922</v>
       </c>
       <c r="F342" t="n">
-        <v>96.34025573730469</v>
+        <v>96.34026336669922</v>
       </c>
       <c r="G342" t="n">
         <v>16808300</v>
@@ -8315,16 +8315,16 @@
         <v>45790</v>
       </c>
       <c r="C343" t="n">
-        <v>96.35942077636719</v>
+        <v>96.35942840576172</v>
       </c>
       <c r="D343" t="n">
-        <v>96.35942077636719</v>
+        <v>96.35942840576172</v>
       </c>
       <c r="E343" t="n">
-        <v>96.34983072608168</v>
+        <v>96.34983835471689</v>
       </c>
       <c r="F343" t="n">
-        <v>96.34983072608168</v>
+        <v>96.34983835471689</v>
       </c>
       <c r="G343" t="n">
         <v>18174400</v>
@@ -8338,16 +8338,16 @@
         <v>45791</v>
       </c>
       <c r="C344" t="n">
-        <v>96.3690185546875</v>
+        <v>96.36900329589844</v>
       </c>
       <c r="D344" t="n">
-        <v>96.3690185546875</v>
+        <v>96.36900329589844</v>
       </c>
       <c r="E344" t="n">
-        <v>96.35942850363294</v>
+        <v>96.35941324636234</v>
       </c>
       <c r="F344" t="n">
-        <v>96.35942850363294</v>
+        <v>96.35941324636234</v>
       </c>
       <c r="G344" t="n">
         <v>9821100</v>
@@ -8361,16 +8361,16 @@
         <v>45792</v>
       </c>
       <c r="C345" t="n">
-        <v>96.3690185546875</v>
+        <v>96.36900329589844</v>
       </c>
       <c r="D345" t="n">
-        <v>96.37860129067643</v>
+        <v>96.37858603037006</v>
       </c>
       <c r="E345" t="n">
-        <v>96.3690185546875</v>
+        <v>96.36900329589844</v>
       </c>
       <c r="F345" t="n">
-        <v>96.37860129067643</v>
+        <v>96.37858603037006</v>
       </c>
       <c r="G345" t="n">
         <v>10057600</v>
@@ -8384,16 +8384,16 @@
         <v>45793</v>
       </c>
       <c r="C346" t="n">
-        <v>96.40735626220703</v>
+        <v>96.40736389160156</v>
       </c>
       <c r="D346" t="n">
-        <v>96.41693899668692</v>
+        <v>96.4169466268398</v>
       </c>
       <c r="E346" t="n">
-        <v>96.40735626220703</v>
+        <v>96.40736389160156</v>
       </c>
       <c r="F346" t="n">
-        <v>96.40735626220703</v>
+        <v>96.40736389160156</v>
       </c>
       <c r="G346" t="n">
         <v>10109300</v>
@@ -8453,16 +8453,16 @@
         <v>45798</v>
       </c>
       <c r="C349" t="n">
-        <v>96.44571685791016</v>
+        <v>96.44570922851562</v>
       </c>
       <c r="D349" t="n">
-        <v>96.44571685791016</v>
+        <v>96.44570922851562</v>
       </c>
       <c r="E349" t="n">
-        <v>96.43613412193713</v>
+        <v>96.43612649330065</v>
       </c>
       <c r="F349" t="n">
-        <v>96.44571685791016</v>
+        <v>96.44570922851562</v>
       </c>
       <c r="G349" t="n">
         <v>11325900</v>
@@ -8499,16 +8499,16 @@
         <v>45800</v>
       </c>
       <c r="C351" t="n">
-        <v>96.49364471435547</v>
+        <v>96.49365997314453</v>
       </c>
       <c r="D351" t="n">
-        <v>96.50323476389502</v>
+        <v>96.50325002420058</v>
       </c>
       <c r="E351" t="n">
-        <v>96.49364471435547</v>
+        <v>96.49365997314453</v>
       </c>
       <c r="F351" t="n">
-        <v>96.50323476389502</v>
+        <v>96.50325002420058</v>
       </c>
       <c r="G351" t="n">
         <v>9119400</v>
@@ -8545,16 +8545,16 @@
         <v>45805</v>
       </c>
       <c r="C353" t="n">
-        <v>96.53200531005859</v>
+        <v>96.53201293945312</v>
       </c>
       <c r="D353" t="n">
-        <v>96.53200531005859</v>
+        <v>96.53201293945312</v>
       </c>
       <c r="E353" t="n">
-        <v>96.52241525975282</v>
+        <v>96.5224228883894</v>
       </c>
       <c r="F353" t="n">
-        <v>96.52721394243824</v>
+        <v>96.52722157145408</v>
       </c>
       <c r="G353" t="n">
         <v>8415200</v>
@@ -8568,16 +8568,16 @@
         <v>45806</v>
       </c>
       <c r="C354" t="n">
-        <v>96.53200531005859</v>
+        <v>96.53201293945312</v>
       </c>
       <c r="D354" t="n">
-        <v>96.54159536036435</v>
+        <v>96.54160299051684</v>
       </c>
       <c r="E354" t="n">
-        <v>96.52241525975282</v>
+        <v>96.5224228883894</v>
       </c>
       <c r="F354" t="n">
-        <v>96.53200531005859</v>
+        <v>96.53201293945312</v>
       </c>
       <c r="G354" t="n">
         <v>10387000</v>
@@ -8591,16 +8591,16 @@
         <v>45807</v>
       </c>
       <c r="C355" t="n">
-        <v>96.56076812744141</v>
+        <v>96.56077575683594</v>
       </c>
       <c r="D355" t="n">
-        <v>96.57035817774533</v>
+        <v>96.57036580789759</v>
       </c>
       <c r="E355" t="n">
-        <v>96.56076812744141</v>
+        <v>96.56077575683594</v>
       </c>
       <c r="F355" t="n">
-        <v>96.56076812744141</v>
+        <v>96.56077575683594</v>
       </c>
       <c r="G355" t="n">
         <v>14209500</v>
@@ -8614,16 +8614,16 @@
         <v>45810</v>
       </c>
       <c r="C356" t="n">
-        <v>96.58770751953125</v>
+        <v>96.58769989013672</v>
       </c>
       <c r="D356" t="n">
-        <v>96.58770751953125</v>
+        <v>96.58769989013672</v>
       </c>
       <c r="E356" t="n">
-        <v>96.57809059853618</v>
+        <v>96.57808296990129</v>
       </c>
       <c r="F356" t="n">
-        <v>96.58770751953125</v>
+        <v>96.58769989013672</v>
       </c>
       <c r="G356" t="n">
         <v>21934000</v>
@@ -8683,16 +8683,16 @@
         <v>45813</v>
       </c>
       <c r="C359" t="n">
-        <v>96.61660003662109</v>
+        <v>96.61659240722656</v>
       </c>
       <c r="D359" t="n">
-        <v>96.61660003662109</v>
+        <v>96.61659240722656</v>
       </c>
       <c r="E359" t="n">
-        <v>96.60697577249954</v>
+        <v>96.60696814386499</v>
       </c>
       <c r="F359" t="n">
-        <v>96.61660003662109</v>
+        <v>96.61659240722656</v>
       </c>
       <c r="G359" t="n">
         <v>9915800</v>
@@ -8706,16 +8706,16 @@
         <v>45814</v>
       </c>
       <c r="C360" t="n">
-        <v>96.64544677734375</v>
+        <v>96.64545440673828</v>
       </c>
       <c r="D360" t="n">
-        <v>96.65506369844093</v>
+        <v>96.65507132859463</v>
       </c>
       <c r="E360" t="n">
-        <v>96.64544677734375</v>
+        <v>96.64545440673828</v>
       </c>
       <c r="F360" t="n">
-        <v>96.65025523789234</v>
+        <v>96.65026286766646</v>
       </c>
       <c r="G360" t="n">
         <v>9122400</v>
@@ -8729,16 +8729,16 @@
         <v>45817</v>
       </c>
       <c r="C361" t="n">
-        <v>96.65505981445312</v>
+        <v>96.65506744384766</v>
       </c>
       <c r="D361" t="n">
-        <v>96.66468407632469</v>
+        <v>96.66469170647891</v>
       </c>
       <c r="E361" t="n">
-        <v>96.65505981445312</v>
+        <v>96.65506744384766</v>
       </c>
       <c r="F361" t="n">
-        <v>96.65505981445312</v>
+        <v>96.65506744384766</v>
       </c>
       <c r="G361" t="n">
         <v>9902100</v>
@@ -8752,16 +8752,16 @@
         <v>45818</v>
       </c>
       <c r="C362" t="n">
-        <v>96.66468048095703</v>
+        <v>96.66468811035156</v>
       </c>
       <c r="D362" t="n">
-        <v>96.67430474247064</v>
+        <v>96.67431237262477</v>
       </c>
       <c r="E362" t="n">
-        <v>96.66468048095703</v>
+        <v>96.66468811035156</v>
       </c>
       <c r="F362" t="n">
-        <v>96.66948894113355</v>
+        <v>96.6694965709076</v>
       </c>
       <c r="G362" t="n">
         <v>9201800</v>
@@ -8775,16 +8775,16 @@
         <v>45819</v>
       </c>
       <c r="C363" t="n">
-        <v>96.68395233154297</v>
+        <v>96.68393707275391</v>
       </c>
       <c r="D363" t="n">
-        <v>96.68395233154297</v>
+        <v>96.68393707275391</v>
       </c>
       <c r="E363" t="n">
-        <v>96.67432806770725</v>
+        <v>96.6743128104371</v>
       </c>
       <c r="F363" t="n">
-        <v>96.67913652904394</v>
+        <v>96.67912127101491</v>
       </c>
       <c r="G363" t="n">
         <v>10138800</v>
@@ -8798,16 +8798,16 @@
         <v>45820</v>
       </c>
       <c r="C364" t="n">
-        <v>96.69355773925781</v>
+        <v>96.69356536865234</v>
       </c>
       <c r="D364" t="n">
-        <v>96.69355773925781</v>
+        <v>96.69356536865234</v>
       </c>
       <c r="E364" t="n">
-        <v>96.68394081772971</v>
+        <v>96.68394844636542</v>
       </c>
       <c r="F364" t="n">
-        <v>96.69355773925781</v>
+        <v>96.69356536865234</v>
       </c>
       <c r="G364" t="n">
         <v>9574900</v>
@@ -8821,16 +8821,16 @@
         <v>45821</v>
       </c>
       <c r="C365" t="n">
-        <v>96.7320556640625</v>
+        <v>96.73204803466797</v>
       </c>
       <c r="D365" t="n">
-        <v>96.7320556640625</v>
+        <v>96.73204803466797</v>
       </c>
       <c r="E365" t="n">
-        <v>96.72243140055555</v>
+        <v>96.72242377192009</v>
       </c>
       <c r="F365" t="n">
-        <v>96.72243140055555</v>
+        <v>96.72242377192009</v>
       </c>
       <c r="G365" t="n">
         <v>7880300</v>
@@ -8844,16 +8844,16 @@
         <v>45824</v>
       </c>
       <c r="C366" t="n">
-        <v>96.7320556640625</v>
+        <v>96.73204803466797</v>
       </c>
       <c r="D366" t="n">
-        <v>96.74167992756945</v>
+        <v>96.74167229741583</v>
       </c>
       <c r="E366" t="n">
-        <v>96.7320556640625</v>
+        <v>96.73204803466797</v>
       </c>
       <c r="F366" t="n">
-        <v>96.74167992756945</v>
+        <v>96.74167229741583</v>
       </c>
       <c r="G366" t="n">
         <v>10286500</v>
@@ -8867,16 +8867,16 @@
         <v>45825</v>
       </c>
       <c r="C367" t="n">
-        <v>96.74166870117188</v>
+        <v>96.74167633056641</v>
       </c>
       <c r="D367" t="n">
-        <v>96.75129296356198</v>
+        <v>96.75130059371551</v>
       </c>
       <c r="E367" t="n">
-        <v>96.74166870117188</v>
+        <v>96.74167633056641</v>
       </c>
       <c r="F367" t="n">
-        <v>96.75129296356198</v>
+        <v>96.75130059371551</v>
       </c>
       <c r="G367" t="n">
         <v>8734500</v>
@@ -8913,16 +8913,16 @@
         <v>45828</v>
       </c>
       <c r="C369" t="n">
-        <v>96.79940795898438</v>
+        <v>96.79939270019531</v>
       </c>
       <c r="D369" t="n">
-        <v>96.80903222220624</v>
+        <v>96.80901696190008</v>
       </c>
       <c r="E369" t="n">
-        <v>96.79940795898438</v>
+        <v>96.79939270019531</v>
       </c>
       <c r="F369" t="n">
-        <v>96.80422376117625</v>
+        <v>96.80420850162805</v>
       </c>
       <c r="G369" t="n">
         <v>9399400</v>
@@ -9005,16 +9005,16 @@
         <v>45834</v>
       </c>
       <c r="C373" t="n">
-        <v>96.84751892089844</v>
+        <v>96.84750366210938</v>
       </c>
       <c r="D373" t="n">
-        <v>96.85714318382088</v>
+        <v>96.85712792351548</v>
       </c>
       <c r="E373" t="n">
-        <v>96.84751892089844</v>
+        <v>96.84750366210938</v>
       </c>
       <c r="F373" t="n">
-        <v>96.85714318382088</v>
+        <v>96.85712792351548</v>
       </c>
       <c r="G373" t="n">
         <v>9277700</v>
@@ -9143,16 +9143,16 @@
         <v>45845</v>
       </c>
       <c r="C379" t="n">
-        <v>96.97966003417969</v>
+        <v>96.97965240478516</v>
       </c>
       <c r="D379" t="n">
-        <v>96.97966003417969</v>
+        <v>96.97965240478516</v>
       </c>
       <c r="E379" t="n">
-        <v>96.97000248989785</v>
+        <v>96.96999486126307</v>
       </c>
       <c r="F379" t="n">
-        <v>96.97966003417969</v>
+        <v>96.97965240478516</v>
       </c>
       <c r="G379" t="n">
         <v>12363900</v>
@@ -9166,16 +9166,16 @@
         <v>45846</v>
       </c>
       <c r="C380" t="n">
-        <v>96.99896240234375</v>
+        <v>96.99897003173828</v>
       </c>
       <c r="D380" t="n">
-        <v>96.99896240234375</v>
+        <v>96.99897003173828</v>
       </c>
       <c r="E380" t="n">
-        <v>96.97965468139364</v>
+        <v>96.97966230926953</v>
       </c>
       <c r="F380" t="n">
-        <v>96.98930485859495</v>
+        <v>96.98931248722988</v>
       </c>
       <c r="G380" t="n">
         <v>13107800</v>
@@ -9212,16 +9212,16 @@
         <v>45848</v>
       </c>
       <c r="C382" t="n">
-        <v>97.00862884521484</v>
+        <v>97.00862121582031</v>
       </c>
       <c r="D382" t="n">
-        <v>97.01828638984958</v>
+        <v>97.01827875969551</v>
       </c>
       <c r="E382" t="n">
-        <v>96.99897130058011</v>
+        <v>96.99896367194511</v>
       </c>
       <c r="F382" t="n">
-        <v>97.00862884521484</v>
+        <v>97.00862121582031</v>
       </c>
       <c r="G382" t="n">
         <v>10071700</v>
@@ -9235,16 +9235,16 @@
         <v>45849</v>
       </c>
       <c r="C383" t="n">
-        <v>97.04725646972656</v>
+        <v>97.0472412109375</v>
       </c>
       <c r="D383" t="n">
-        <v>97.04725646972656</v>
+        <v>97.0472412109375</v>
       </c>
       <c r="E383" t="n">
-        <v>97.03759892461291</v>
+        <v>97.03758366734232</v>
       </c>
       <c r="F383" t="n">
-        <v>97.03759892461291</v>
+        <v>97.03758366734232</v>
       </c>
       <c r="G383" t="n">
         <v>9288900</v>
@@ -9258,16 +9258,16 @@
         <v>45852</v>
       </c>
       <c r="C384" t="n">
-        <v>97.04725646972656</v>
+        <v>97.0472412109375</v>
       </c>
       <c r="D384" t="n">
-        <v>97.05690664829169</v>
+        <v>97.05689138798532</v>
       </c>
       <c r="E384" t="n">
-        <v>97.04725646972656</v>
+        <v>97.0472412109375</v>
       </c>
       <c r="F384" t="n">
-        <v>97.05690664829169</v>
+        <v>97.05689138798532</v>
       </c>
       <c r="G384" t="n">
         <v>10293900</v>
@@ -9281,16 +9281,16 @@
         <v>45853</v>
       </c>
       <c r="C385" t="n">
-        <v>97.05690002441406</v>
+        <v>97.05690765380859</v>
       </c>
       <c r="D385" t="n">
-        <v>97.06655756886862</v>
+        <v>97.06656519902229</v>
       </c>
       <c r="E385" t="n">
-        <v>97.05690002441406</v>
+        <v>97.05690765380859</v>
       </c>
       <c r="F385" t="n">
-        <v>97.06655756886862</v>
+        <v>97.06656519902229</v>
       </c>
       <c r="G385" t="n">
         <v>10207100</v>
@@ -9304,16 +9304,16 @@
         <v>45854</v>
       </c>
       <c r="C386" t="n">
-        <v>97.08586120605469</v>
+        <v>97.08587646484375</v>
       </c>
       <c r="D386" t="n">
-        <v>97.08586120605469</v>
+        <v>97.08587646484375</v>
       </c>
       <c r="E386" t="n">
-        <v>97.0762036627393</v>
+        <v>97.07621892001049</v>
       </c>
       <c r="F386" t="n">
-        <v>97.0762036627393</v>
+        <v>97.07621892001049</v>
       </c>
       <c r="G386" t="n">
         <v>8117900</v>
@@ -9350,16 +9350,16 @@
         <v>45856</v>
       </c>
       <c r="C388" t="n">
-        <v>97.12449645996094</v>
+        <v>97.12448120117188</v>
       </c>
       <c r="D388" t="n">
-        <v>97.12449645996094</v>
+        <v>97.12448120117188</v>
       </c>
       <c r="E388" t="n">
-        <v>97.11484628122402</v>
+        <v>97.11483102395106</v>
       </c>
       <c r="F388" t="n">
-        <v>97.11484628122402</v>
+        <v>97.11483102395106</v>
       </c>
       <c r="G388" t="n">
         <v>9399500</v>
@@ -9373,16 +9373,16 @@
         <v>45859</v>
       </c>
       <c r="C389" t="n">
-        <v>97.1341552734375</v>
+        <v>97.13416290283203</v>
       </c>
       <c r="D389" t="n">
-        <v>97.1341552734375</v>
+        <v>97.13416290283203</v>
       </c>
       <c r="E389" t="n">
-        <v>97.12449772802584</v>
+        <v>97.12450535666183</v>
       </c>
       <c r="F389" t="n">
-        <v>97.12449772802584</v>
+        <v>97.12450535666183</v>
       </c>
       <c r="G389" t="n">
         <v>12893000</v>
@@ -9442,16 +9442,16 @@
         <v>45862</v>
       </c>
       <c r="C392" t="n">
-        <v>97.17276000976562</v>
+        <v>97.17276763916016</v>
       </c>
       <c r="D392" t="n">
-        <v>97.17276000976562</v>
+        <v>97.17276763916016</v>
       </c>
       <c r="E392" t="n">
-        <v>97.16310246615073</v>
+        <v>97.16311009478702</v>
       </c>
       <c r="F392" t="n">
-        <v>97.16310246615073</v>
+        <v>97.16311009478702</v>
       </c>
       <c r="G392" t="n">
         <v>10701600</v>
@@ -9465,16 +9465,16 @@
         <v>45863</v>
       </c>
       <c r="C393" t="n">
-        <v>97.19209289550781</v>
+        <v>97.19207000732422</v>
       </c>
       <c r="D393" t="n">
-        <v>97.20174307434253</v>
+        <v>97.20172018388638</v>
       </c>
       <c r="E393" t="n">
-        <v>97.19209289550781</v>
+        <v>97.19207000732422</v>
       </c>
       <c r="F393" t="n">
-        <v>97.20174307434253</v>
+        <v>97.20172018388638</v>
       </c>
       <c r="G393" t="n">
         <v>9776600</v>
@@ -9488,16 +9488,16 @@
         <v>45866</v>
       </c>
       <c r="C394" t="n">
-        <v>97.22104644775391</v>
+        <v>97.22105407714844</v>
       </c>
       <c r="D394" t="n">
-        <v>97.22104644775391</v>
+        <v>97.22105407714844</v>
       </c>
       <c r="E394" t="n">
-        <v>97.21138890353441</v>
+        <v>97.21139653217107</v>
       </c>
       <c r="F394" t="n">
-        <v>97.21621399237023</v>
+        <v>97.21622162138554</v>
       </c>
       <c r="G394" t="n">
         <v>11581000</v>
@@ -9511,16 +9511,16 @@
         <v>45867</v>
       </c>
       <c r="C395" t="n">
-        <v>97.22104644775391</v>
+        <v>97.22105407714844</v>
       </c>
       <c r="D395" t="n">
-        <v>97.23069662542557</v>
+        <v>97.23070425557738</v>
       </c>
       <c r="E395" t="n">
-        <v>97.22104644775391</v>
+        <v>97.22105407714844</v>
       </c>
       <c r="F395" t="n">
-        <v>97.22104644775391</v>
+        <v>97.22105407714844</v>
       </c>
       <c r="G395" t="n">
         <v>8622300</v>
@@ -9534,16 +9534,16 @@
         <v>45868</v>
       </c>
       <c r="C396" t="n">
-        <v>97.24034881591797</v>
+        <v>97.24034118652344</v>
       </c>
       <c r="D396" t="n">
-        <v>97.24034881591797</v>
+        <v>97.24034118652344</v>
       </c>
       <c r="E396" t="n">
-        <v>97.23069127223019</v>
+        <v>97.23068364359338</v>
       </c>
       <c r="F396" t="n">
-        <v>97.23069127223019</v>
+        <v>97.23068364359338</v>
       </c>
       <c r="G396" t="n">
         <v>9106000</v>
@@ -9557,16 +9557,16 @@
         <v>45869</v>
       </c>
       <c r="C397" t="n">
-        <v>97.25002288818359</v>
+        <v>97.25001525878906</v>
       </c>
       <c r="D397" t="n">
-        <v>97.25002288818359</v>
+        <v>97.25001525878906</v>
       </c>
       <c r="E397" t="n">
-        <v>97.24036534285442</v>
+        <v>97.24035771421754</v>
       </c>
       <c r="F397" t="n">
-        <v>97.24519043224467</v>
+        <v>97.24518280322924</v>
       </c>
       <c r="G397" t="n">
         <v>19051200</v>
@@ -9603,16 +9603,16 @@
         <v>45873</v>
       </c>
       <c r="C399" t="n">
-        <v>97.3004150390625</v>
+        <v>97.30042266845703</v>
       </c>
       <c r="D399" t="n">
-        <v>97.3004150390625</v>
+        <v>97.30042266845703</v>
       </c>
       <c r="E399" t="n">
-        <v>97.2907226581143</v>
+        <v>97.29073028674887</v>
       </c>
       <c r="F399" t="n">
-        <v>97.29556515202816</v>
+        <v>97.29557278104242</v>
       </c>
       <c r="G399" t="n">
         <v>14766400</v>
@@ -9649,16 +9649,16 @@
         <v>45875</v>
       </c>
       <c r="C401" t="n">
-        <v>97.31978607177734</v>
+        <v>97.31979370117188</v>
       </c>
       <c r="D401" t="n">
-        <v>97.31978607177734</v>
+        <v>97.31979370117188</v>
       </c>
       <c r="E401" t="n">
-        <v>97.31009369146018</v>
+        <v>97.31010132009489</v>
       </c>
       <c r="F401" t="n">
-        <v>97.31978607177734</v>
+        <v>97.31979370117188</v>
       </c>
       <c r="G401" t="n">
         <v>10653900</v>
@@ -9672,16 +9672,16 @@
         <v>45876</v>
       </c>
       <c r="C402" t="n">
-        <v>97.31978607177734</v>
+        <v>97.31979370117188</v>
       </c>
       <c r="D402" t="n">
-        <v>97.32947845209449</v>
+        <v>97.32948608224886</v>
       </c>
       <c r="E402" t="n">
-        <v>97.31978607177734</v>
+        <v>97.31979370117188</v>
       </c>
       <c r="F402" t="n">
-        <v>97.32947845209449</v>
+        <v>97.32948608224886</v>
       </c>
       <c r="G402" t="n">
         <v>10823000</v>
@@ -9718,16 +9718,16 @@
         <v>45880</v>
       </c>
       <c r="C404" t="n">
-        <v>97.3779296875</v>
+        <v>97.37792205810547</v>
       </c>
       <c r="D404" t="n">
-        <v>97.3779296875</v>
+        <v>97.37792205810547</v>
       </c>
       <c r="E404" t="n">
-        <v>97.36824469989307</v>
+        <v>97.36823707125734</v>
       </c>
       <c r="F404" t="n">
-        <v>97.3779296875</v>
+        <v>97.37792205810547</v>
       </c>
       <c r="G404" t="n">
         <v>12940300</v>
@@ -9741,16 +9741,16 @@
         <v>45881</v>
       </c>
       <c r="C405" t="n">
-        <v>97.3779296875</v>
+        <v>97.37792205810547</v>
       </c>
       <c r="D405" t="n">
-        <v>97.38762206822724</v>
+        <v>97.38761443807333</v>
       </c>
       <c r="E405" t="n">
-        <v>97.3779296875</v>
+        <v>97.37792205810547</v>
       </c>
       <c r="F405" t="n">
-        <v>97.38762206822724</v>
+        <v>97.38761443807333</v>
       </c>
       <c r="G405" t="n">
         <v>12918200</v>
@@ -9764,16 +9764,16 @@
         <v>45882</v>
       </c>
       <c r="C406" t="n">
-        <v>97.39730834960938</v>
+        <v>97.39730072021484</v>
       </c>
       <c r="D406" t="n">
-        <v>97.4069933366098</v>
+        <v>97.40698570645661</v>
       </c>
       <c r="E406" t="n">
-        <v>97.3876159694891</v>
+        <v>97.3876083408538</v>
       </c>
       <c r="F406" t="n">
-        <v>97.39730834960938</v>
+        <v>97.39730072021484</v>
       </c>
       <c r="G406" t="n">
         <v>12144800</v>
@@ -9787,16 +9787,16 @@
         <v>45883</v>
       </c>
       <c r="C407" t="n">
-        <v>97.40699005126953</v>
+        <v>97.406982421875</v>
       </c>
       <c r="D407" t="n">
-        <v>97.4166824310629</v>
+        <v>97.41667480090922</v>
       </c>
       <c r="E407" t="n">
-        <v>97.40699005126953</v>
+        <v>97.406982421875</v>
       </c>
       <c r="F407" t="n">
-        <v>97.40699005126953</v>
+        <v>97.406982421875</v>
       </c>
       <c r="G407" t="n">
         <v>9798900</v>
@@ -9810,16 +9810,16 @@
         <v>45884</v>
       </c>
       <c r="C408" t="n">
-        <v>97.43605804443359</v>
+        <v>97.43606567382812</v>
       </c>
       <c r="D408" t="n">
-        <v>97.44574303019824</v>
+        <v>97.44575066035112</v>
       </c>
       <c r="E408" t="n">
-        <v>97.43605804443359</v>
+        <v>97.43606567382812</v>
       </c>
       <c r="F408" t="n">
-        <v>97.44574303019824</v>
+        <v>97.44575066035112</v>
       </c>
       <c r="G408" t="n">
         <v>9493900</v>
@@ -9879,16 +9879,16 @@
         <v>45889</v>
       </c>
       <c r="C411" t="n">
-        <v>97.48452758789062</v>
+        <v>97.48450469970703</v>
       </c>
       <c r="D411" t="n">
-        <v>97.48452758789062</v>
+        <v>97.48450469970703</v>
       </c>
       <c r="E411" t="n">
-        <v>97.47483520677645</v>
+        <v>97.47481232086851</v>
       </c>
       <c r="F411" t="n">
-        <v>97.48452758789062</v>
+        <v>97.48450469970703</v>
       </c>
       <c r="G411" t="n">
         <v>10922100</v>
@@ -9902,16 +9902,16 @@
         <v>45890</v>
       </c>
       <c r="C412" t="n">
-        <v>97.48452758789062</v>
+        <v>97.48450469970703</v>
       </c>
       <c r="D412" t="n">
-        <v>97.4942199690048</v>
+        <v>97.49419707854555</v>
       </c>
       <c r="E412" t="n">
-        <v>97.48452758789062</v>
+        <v>97.48450469970703</v>
       </c>
       <c r="F412" t="n">
-        <v>97.4942199690048</v>
+        <v>97.49419707854555</v>
       </c>
       <c r="G412" t="n">
         <v>8765300</v>
@@ -9925,16 +9925,16 @@
         <v>45891</v>
       </c>
       <c r="C413" t="n">
-        <v>97.52326965332031</v>
+        <v>97.52327728271484</v>
       </c>
       <c r="D413" t="n">
-        <v>97.52326965332031</v>
+        <v>97.52327728271484</v>
       </c>
       <c r="E413" t="n">
-        <v>97.51357727420039</v>
+        <v>97.51358490283667</v>
       </c>
       <c r="F413" t="n">
-        <v>97.52326965332031</v>
+        <v>97.52327728271484</v>
       </c>
       <c r="G413" t="n">
         <v>13160400</v>
@@ -9948,16 +9948,16 @@
         <v>45894</v>
       </c>
       <c r="C414" t="n">
-        <v>97.54267120361328</v>
+        <v>97.54265594482422</v>
       </c>
       <c r="D414" t="n">
-        <v>97.54267120361328</v>
+        <v>97.54265594482422</v>
       </c>
       <c r="E414" t="n">
-        <v>97.5329788228248</v>
+        <v>97.53296356555194</v>
       </c>
       <c r="F414" t="n">
-        <v>97.53782131665886</v>
+        <v>97.53780605862848</v>
       </c>
       <c r="G414" t="n">
         <v>13556000</v>
@@ -9971,16 +9971,16 @@
         <v>45895</v>
       </c>
       <c r="C415" t="n">
-        <v>97.54267120361328</v>
+        <v>97.54265594482422</v>
       </c>
       <c r="D415" t="n">
-        <v>97.55235619128139</v>
+        <v>97.55234093097729</v>
       </c>
       <c r="E415" t="n">
-        <v>97.54267120361328</v>
+        <v>97.54265594482422</v>
       </c>
       <c r="F415" t="n">
-        <v>97.54751369744734</v>
+        <v>97.54749843790076</v>
       </c>
       <c r="G415" t="n">
         <v>8741600</v>
@@ -10017,16 +10017,16 @@
         <v>45897</v>
       </c>
       <c r="C417" t="n">
-        <v>97.56204223632812</v>
+        <v>97.56204986572266</v>
       </c>
       <c r="D417" t="n">
-        <v>97.57173461648718</v>
+        <v>97.57174224663966</v>
       </c>
       <c r="E417" t="n">
-        <v>97.56204223632812</v>
+        <v>97.56204986572266</v>
       </c>
       <c r="F417" t="n">
-        <v>97.56688472984771</v>
+        <v>97.56689235962092</v>
       </c>
       <c r="G417" t="n">
         <v>8816600</v>
@@ -10063,16 +10063,16 @@
         <v>45902</v>
       </c>
       <c r="C419" t="n">
-        <v>97.62990570068359</v>
+        <v>97.62992095947266</v>
       </c>
       <c r="D419" t="n">
-        <v>97.62990570068359</v>
+        <v>97.62992095947266</v>
       </c>
       <c r="E419" t="n">
-        <v>97.62017856030185</v>
+        <v>97.62019381757064</v>
       </c>
       <c r="F419" t="n">
-        <v>97.62990570068359</v>
+        <v>97.62992095947266</v>
       </c>
       <c r="G419" t="n">
         <v>27254500</v>
@@ -10109,16 +10109,16 @@
         <v>45904</v>
       </c>
       <c r="C421" t="n">
-        <v>97.65908050537109</v>
+        <v>97.65907287597656</v>
       </c>
       <c r="D421" t="n">
-        <v>97.65908050537109</v>
+        <v>97.65907287597656</v>
       </c>
       <c r="E421" t="n">
-        <v>97.64936078454357</v>
+        <v>97.64935315590837</v>
       </c>
       <c r="F421" t="n">
-        <v>97.65422064495733</v>
+        <v>97.65421301594246</v>
       </c>
       <c r="G421" t="n">
         <v>11300200</v>
@@ -10132,16 +10132,16 @@
         <v>45905</v>
       </c>
       <c r="C422" t="n">
-        <v>97.67853546142578</v>
+        <v>97.67854309082031</v>
       </c>
       <c r="D422" t="n">
-        <v>97.68825518232049</v>
+        <v>97.68826281247419</v>
       </c>
       <c r="E422" t="n">
-        <v>97.67853546142578</v>
+        <v>97.67854309082031</v>
       </c>
       <c r="F422" t="n">
-        <v>97.68825518232049</v>
+        <v>97.68826281247419</v>
       </c>
       <c r="G422" t="n">
         <v>15312000</v>
@@ -10155,16 +10155,16 @@
         <v>45908</v>
       </c>
       <c r="C423" t="n">
-        <v>97.70770263671875</v>
+        <v>97.70769500732422</v>
       </c>
       <c r="D423" t="n">
-        <v>97.70770263671875</v>
+        <v>97.70769500732422</v>
       </c>
       <c r="E423" t="n">
-        <v>97.69797549686939</v>
+        <v>97.6979678682344</v>
       </c>
       <c r="F423" t="n">
-        <v>97.70283535697719</v>
+        <v>97.70282772796271</v>
       </c>
       <c r="G423" t="n">
         <v>12715100</v>
@@ -10178,16 +10178,16 @@
         <v>45909</v>
       </c>
       <c r="C424" t="n">
-        <v>97.70770263671875</v>
+        <v>97.70769500732422</v>
       </c>
       <c r="D424" t="n">
-        <v>97.71742977656811</v>
+        <v>97.71742214641404</v>
       </c>
       <c r="E424" t="n">
-        <v>97.70770263671875</v>
+        <v>97.70769500732422</v>
       </c>
       <c r="F424" t="n">
-        <v>97.71742977656811</v>
+        <v>97.71742214641404</v>
       </c>
       <c r="G424" t="n">
         <v>11005500</v>
@@ -10201,16 +10201,16 @@
         <v>45910</v>
       </c>
       <c r="C425" t="n">
-        <v>97.71744537353516</v>
+        <v>97.71743774414062</v>
       </c>
       <c r="D425" t="n">
-        <v>97.72716509530215</v>
+        <v>97.72715746514874</v>
       </c>
       <c r="E425" t="n">
-        <v>97.71744537353516</v>
+        <v>97.71743774414062</v>
       </c>
       <c r="F425" t="n">
-        <v>97.71744537353516</v>
+        <v>97.71743774414062</v>
       </c>
       <c r="G425" t="n">
         <v>9356600</v>
@@ -10247,16 +10247,16 @@
         <v>45912</v>
       </c>
       <c r="C427" t="n">
-        <v>97.76605987548828</v>
+        <v>97.76605224609375</v>
       </c>
       <c r="D427" t="n">
-        <v>97.77578701625686</v>
+        <v>97.77577938610324</v>
       </c>
       <c r="E427" t="n">
-        <v>97.76605987548828</v>
+        <v>97.76605224609375</v>
       </c>
       <c r="F427" t="n">
-        <v>97.76605987548828</v>
+        <v>97.76605224609375</v>
       </c>
       <c r="G427" t="n">
         <v>10482000</v>
@@ -10270,16 +10270,16 @@
         <v>45915</v>
       </c>
       <c r="C428" t="n">
-        <v>97.76605987548828</v>
+        <v>97.76605224609375</v>
       </c>
       <c r="D428" t="n">
-        <v>97.77578701625686</v>
+        <v>97.77577938610324</v>
       </c>
       <c r="E428" t="n">
-        <v>97.76605987548828</v>
+        <v>97.76605224609375</v>
       </c>
       <c r="F428" t="n">
-        <v>97.76605987548828</v>
+        <v>97.76605224609375</v>
       </c>
       <c r="G428" t="n">
         <v>15288300</v>
@@ -10293,16 +10293,16 @@
         <v>45916</v>
       </c>
       <c r="C429" t="n">
-        <v>97.78550720214844</v>
+        <v>97.78551483154297</v>
       </c>
       <c r="D429" t="n">
-        <v>97.79522692259125</v>
+        <v>97.79523455274413</v>
       </c>
       <c r="E429" t="n">
-        <v>97.78550720214844</v>
+        <v>97.78551483154297</v>
       </c>
       <c r="F429" t="n">
-        <v>97.78550720214844</v>
+        <v>97.78551483154297</v>
       </c>
       <c r="G429" t="n">
         <v>11551900</v>
@@ -10316,16 +10316,16 @@
         <v>45917</v>
       </c>
       <c r="C430" t="n">
-        <v>97.79522705078125</v>
+        <v>97.79523468017578</v>
       </c>
       <c r="D430" t="n">
-        <v>97.80495419087075</v>
+        <v>97.80496182102412</v>
       </c>
       <c r="E430" t="n">
-        <v>97.79522705078125</v>
+        <v>97.79523468017578</v>
       </c>
       <c r="F430" t="n">
-        <v>97.80495419087075</v>
+        <v>97.80496182102412</v>
       </c>
       <c r="G430" t="n">
         <v>10381200</v>
@@ -10362,16 +10362,16 @@
         <v>45919</v>
       </c>
       <c r="C432" t="n">
-        <v>97.85358428955078</v>
+        <v>97.85359191894531</v>
       </c>
       <c r="D432" t="n">
-        <v>97.85358428955078</v>
+        <v>97.85359191894531</v>
       </c>
       <c r="E432" t="n">
-        <v>97.84385714928058</v>
+        <v>97.84386477791671</v>
       </c>
       <c r="F432" t="n">
-        <v>97.84385714928058</v>
+        <v>97.84386477791671</v>
       </c>
       <c r="G432" t="n">
         <v>11174000</v>
@@ -10385,16 +10385,16 @@
         <v>45922</v>
       </c>
       <c r="C433" t="n">
-        <v>97.85358428955078</v>
+        <v>97.85359191894531</v>
       </c>
       <c r="D433" t="n">
-        <v>97.86330401018691</v>
+        <v>97.86331164033926</v>
       </c>
       <c r="E433" t="n">
-        <v>97.85358428955078</v>
+        <v>97.85359191894531</v>
       </c>
       <c r="F433" t="n">
-        <v>97.85358428955078</v>
+        <v>97.85359191894531</v>
       </c>
       <c r="G433" t="n">
         <v>12279500</v>
@@ -10500,16 +10500,16 @@
         <v>45929</v>
       </c>
       <c r="C438" t="n">
-        <v>97.93138122558594</v>
+        <v>97.93137359619141</v>
       </c>
       <c r="D438" t="n">
-        <v>97.93138122558594</v>
+        <v>97.93137359619141</v>
       </c>
       <c r="E438" t="n">
-        <v>97.92166150474409</v>
+        <v>97.92165387610677</v>
       </c>
       <c r="F438" t="n">
-        <v>97.93138122558594</v>
+        <v>97.93137359619141</v>
       </c>
       <c r="G438" t="n">
         <v>13580800</v>
@@ -10523,16 +10523,16 @@
         <v>45930</v>
       </c>
       <c r="C439" t="n">
-        <v>97.93138122558594</v>
+        <v>97.93137359619141</v>
       </c>
       <c r="D439" t="n">
-        <v>97.94110836606202</v>
+        <v>97.94110073590969</v>
       </c>
       <c r="E439" t="n">
-        <v>97.93138122558594</v>
+        <v>97.93137359619141</v>
       </c>
       <c r="F439" t="n">
-        <v>97.9362485056411</v>
+        <v>97.93624087586737</v>
       </c>
       <c r="G439" t="n">
         <v>22909500</v>
@@ -10546,16 +10546,16 @@
         <v>45931</v>
       </c>
       <c r="C440" t="n">
-        <v>97.94796752929688</v>
+        <v>97.94797515869141</v>
       </c>
       <c r="D440" t="n">
-        <v>97.95772085802308</v>
+        <v>97.95772848817732</v>
       </c>
       <c r="E440" t="n">
-        <v>97.94796752929688</v>
+        <v>97.94797515869141</v>
       </c>
       <c r="F440" t="n">
-        <v>97.95772085802308</v>
+        <v>97.95772848817732</v>
       </c>
       <c r="G440" t="n">
         <v>26613600</v>
@@ -10569,16 +10569,16 @@
         <v>45932</v>
       </c>
       <c r="C441" t="n">
-        <v>97.95772552490234</v>
+        <v>97.95771789550781</v>
       </c>
       <c r="D441" t="n">
-        <v>97.96748629938267</v>
+        <v>97.96747866922793</v>
       </c>
       <c r="E441" t="n">
-        <v>97.95772552490234</v>
+        <v>97.95771789550781</v>
       </c>
       <c r="F441" t="n">
-        <v>97.96748629938267</v>
+        <v>97.96747866922793</v>
       </c>
       <c r="G441" t="n">
         <v>12870100</v>
@@ -10592,16 +10592,16 @@
         <v>45933</v>
       </c>
       <c r="C442" t="n">
-        <v>97.99676513671875</v>
+        <v>97.99675750732422</v>
       </c>
       <c r="D442" t="n">
-        <v>97.99676513671875</v>
+        <v>97.99675750732422</v>
       </c>
       <c r="E442" t="n">
-        <v>97.98701180713383</v>
+        <v>97.98700417849862</v>
       </c>
       <c r="F442" t="n">
-        <v>97.99676513671875</v>
+        <v>97.99675750732422</v>
       </c>
       <c r="G442" t="n">
         <v>13837400</v>
@@ -10615,16 +10615,16 @@
         <v>45936</v>
       </c>
       <c r="C443" t="n">
-        <v>97.99676513671875</v>
+        <v>97.99675750732422</v>
       </c>
       <c r="D443" t="n">
-        <v>98.00652591159343</v>
+        <v>98.00651828143899</v>
       </c>
       <c r="E443" t="n">
-        <v>97.99676513671875</v>
+        <v>97.99675750732422</v>
       </c>
       <c r="F443" t="n">
-        <v>98.00652591159343</v>
+        <v>98.00651828143899</v>
       </c>
       <c r="G443" t="n">
         <v>13944300</v>
@@ -10638,16 +10638,16 @@
         <v>45937</v>
       </c>
       <c r="C444" t="n">
-        <v>98.01628112792969</v>
+        <v>98.01628875732422</v>
       </c>
       <c r="D444" t="n">
-        <v>98.01628112792969</v>
+        <v>98.01628875732422</v>
       </c>
       <c r="E444" t="n">
-        <v>98.00652035360855</v>
+        <v>98.00652798224331</v>
       </c>
       <c r="F444" t="n">
-        <v>98.01628112792969</v>
+        <v>98.01628875732422</v>
       </c>
       <c r="G444" t="n">
         <v>14289100</v>
@@ -10661,16 +10661,16 @@
         <v>45938</v>
       </c>
       <c r="C445" t="n">
-        <v>98.02603149414062</v>
+        <v>98.02603912353516</v>
       </c>
       <c r="D445" t="n">
-        <v>98.02603149414062</v>
+        <v>98.02603912353516</v>
       </c>
       <c r="E445" t="n">
-        <v>98.01627816540361</v>
+        <v>98.01628579403904</v>
       </c>
       <c r="F445" t="n">
-        <v>98.02603149414062</v>
+        <v>98.02603912353516</v>
       </c>
       <c r="G445" t="n">
         <v>16811200</v>
@@ -10707,16 +10707,16 @@
         <v>45940</v>
       </c>
       <c r="C447" t="n">
-        <v>98.0845947265625</v>
+        <v>98.08458709716797</v>
       </c>
       <c r="D447" t="n">
-        <v>98.0845947265625</v>
+        <v>98.08458709716797</v>
       </c>
       <c r="E447" t="n">
-        <v>98.06507317730942</v>
+        <v>98.06506554943334</v>
       </c>
       <c r="F447" t="n">
-        <v>98.07483395193596</v>
+        <v>98.07482632330066</v>
       </c>
       <c r="G447" t="n">
         <v>18966600</v>
@@ -10730,16 +10730,16 @@
         <v>45943</v>
       </c>
       <c r="C448" t="n">
-        <v>98.07484436035156</v>
+        <v>98.07483673095703</v>
       </c>
       <c r="D448" t="n">
-        <v>98.08460513601399</v>
+        <v>98.08459750586016</v>
       </c>
       <c r="E448" t="n">
-        <v>98.07484436035156</v>
+        <v>98.07483673095703</v>
       </c>
       <c r="F448" t="n">
-        <v>98.07484436035156</v>
+        <v>98.07483673095703</v>
       </c>
       <c r="G448" t="n">
         <v>14453500</v>
@@ -10753,16 +10753,16 @@
         <v>45944</v>
       </c>
       <c r="C449" t="n">
-        <v>98.0845947265625</v>
+        <v>98.08458709716797</v>
       </c>
       <c r="D449" t="n">
-        <v>98.09434805589947</v>
+        <v>98.0943404257463</v>
       </c>
       <c r="E449" t="n">
-        <v>98.0845947265625</v>
+        <v>98.08458709716797</v>
       </c>
       <c r="F449" t="n">
-        <v>98.0845947265625</v>
+        <v>98.08458709716797</v>
       </c>
       <c r="G449" t="n">
         <v>13475000</v>
@@ -10776,16 +10776,16 @@
         <v>45945</v>
       </c>
       <c r="C450" t="n">
-        <v>98.10411071777344</v>
+        <v>98.10409545898438</v>
       </c>
       <c r="D450" t="n">
-        <v>98.10411071777344</v>
+        <v>98.10409545898438</v>
       </c>
       <c r="E450" t="n">
-        <v>98.09434994295911</v>
+        <v>98.09433468568822</v>
       </c>
       <c r="F450" t="n">
-        <v>98.10411071777344</v>
+        <v>98.10409545898438</v>
       </c>
       <c r="G450" t="n">
         <v>11069100</v>
@@ -10822,16 +10822,16 @@
         <v>45947</v>
       </c>
       <c r="C452" t="n">
-        <v>98.14315032958984</v>
+        <v>98.14314270019531</v>
       </c>
       <c r="D452" t="n">
-        <v>98.14315032958984</v>
+        <v>98.14314270019531</v>
       </c>
       <c r="E452" t="n">
-        <v>98.13338955438189</v>
+        <v>98.13338192574615</v>
       </c>
       <c r="F452" t="n">
-        <v>98.13827366463087</v>
+        <v>98.13826603561544</v>
       </c>
       <c r="G452" t="n">
         <v>14603500</v>
@@ -10868,16 +10868,16 @@
         <v>45951</v>
       </c>
       <c r="C454" t="n">
-        <v>98.17242431640625</v>
+        <v>98.17241668701172</v>
       </c>
       <c r="D454" t="n">
-        <v>98.17242431640625</v>
+        <v>98.17241668701172</v>
       </c>
       <c r="E454" t="n">
-        <v>98.16266354128715</v>
+        <v>98.16265591265116</v>
       </c>
       <c r="F454" t="n">
-        <v>98.16266354128715</v>
+        <v>98.16265591265116</v>
       </c>
       <c r="G454" t="n">
         <v>12061900</v>
@@ -10914,16 +10914,16 @@
         <v>45953</v>
       </c>
       <c r="C456" t="n">
-        <v>98.19194030761719</v>
+        <v>98.19194793701172</v>
       </c>
       <c r="D456" t="n">
-        <v>98.19194030761719</v>
+        <v>98.19194793701172</v>
       </c>
       <c r="E456" t="n">
-        <v>98.18217953305069</v>
+        <v>98.18218716168681</v>
       </c>
       <c r="F456" t="n">
-        <v>98.19194030761719</v>
+        <v>98.19194793701172</v>
       </c>
       <c r="G456" t="n">
         <v>10658100</v>
@@ -10937,16 +10937,16 @@
         <v>45954</v>
       </c>
       <c r="C457" t="n">
-        <v>98.22122192382812</v>
+        <v>98.22121429443359</v>
       </c>
       <c r="D457" t="n">
-        <v>98.22122192382812</v>
+        <v>98.22121429443359</v>
       </c>
       <c r="E457" t="n">
-        <v>98.21146114859204</v>
+        <v>98.21145351995568</v>
       </c>
       <c r="F457" t="n">
-        <v>98.22122192382812</v>
+        <v>98.22121429443359</v>
       </c>
       <c r="G457" t="n">
         <v>12382000</v>
@@ -10960,16 +10960,16 @@
         <v>45957</v>
       </c>
       <c r="C458" t="n">
-        <v>98.23098754882812</v>
+        <v>98.23097991943359</v>
       </c>
       <c r="D458" t="n">
-        <v>98.24074087925571</v>
+        <v>98.24073324910366</v>
       </c>
       <c r="E458" t="n">
-        <v>98.22122677311015</v>
+        <v>98.22121914447372</v>
       </c>
       <c r="F458" t="n">
-        <v>98.22122677311015</v>
+        <v>98.22121914447372</v>
       </c>
       <c r="G458" t="n">
         <v>26389600</v>
@@ -10983,16 +10983,16 @@
         <v>45958</v>
       </c>
       <c r="C459" t="n">
-        <v>98.24073028564453</v>
+        <v>98.24073791503906</v>
       </c>
       <c r="D459" t="n">
-        <v>98.25049106030998</v>
+        <v>98.25049869046254</v>
       </c>
       <c r="E459" t="n">
-        <v>98.24073028564453</v>
+        <v>98.24073791503906</v>
       </c>
       <c r="F459" t="n">
-        <v>98.24073028564453</v>
+        <v>98.24073791503906</v>
       </c>
       <c r="G459" t="n">
         <v>11134700</v>
@@ -11006,16 +11006,16 @@
         <v>45959</v>
       </c>
       <c r="C460" t="n">
-        <v>98.25048828125</v>
+        <v>98.25049591064453</v>
       </c>
       <c r="D460" t="n">
-        <v>98.26024905563935</v>
+        <v>98.26025668579183</v>
       </c>
       <c r="E460" t="n">
-        <v>98.25048828125</v>
+        <v>98.25049591064453</v>
       </c>
       <c r="F460" t="n">
-        <v>98.26024905563935</v>
+        <v>98.26025668579183</v>
       </c>
       <c r="G460" t="n">
         <v>14177700</v>
@@ -11052,16 +11052,16 @@
         <v>45961</v>
       </c>
       <c r="C462" t="n">
-        <v>98.28952789306641</v>
+        <v>98.28952026367188</v>
       </c>
       <c r="D462" t="n">
-        <v>98.29928866784897</v>
+        <v>98.29928103769679</v>
       </c>
       <c r="E462" t="n">
-        <v>98.28952789306641</v>
+        <v>98.28952026367188</v>
       </c>
       <c r="F462" t="n">
-        <v>98.29440455781285</v>
+        <v>98.29439692803977</v>
       </c>
       <c r="G462" t="n">
         <v>23254100</v>
@@ -11075,16 +11075,16 @@
         <v>45964</v>
       </c>
       <c r="C463" t="n">
-        <v>98.31694793701172</v>
+        <v>98.31694030761719</v>
       </c>
       <c r="D463" t="n">
-        <v>98.31694793701172</v>
+        <v>98.31694030761719</v>
       </c>
       <c r="E463" t="n">
-        <v>98.30715332055669</v>
+        <v>98.30714569192223</v>
       </c>
       <c r="F463" t="n">
-        <v>98.31204689323255</v>
+        <v>98.31203926421834</v>
       </c>
       <c r="G463" t="n">
         <v>27049200</v>
@@ -11098,16 +11098,16 @@
         <v>45965</v>
       </c>
       <c r="C464" t="n">
-        <v>98.31694793701172</v>
+        <v>98.31694030761719</v>
       </c>
       <c r="D464" t="n">
-        <v>98.31694793701172</v>
+        <v>98.31694030761719</v>
       </c>
       <c r="E464" t="n">
-        <v>98.31204689323255</v>
+        <v>98.31203926421834</v>
       </c>
       <c r="F464" t="n">
-        <v>98.31694793701172</v>
+        <v>98.31694030761719</v>
       </c>
       <c r="G464" t="n">
         <v>15707500</v>
@@ -11121,16 +11121,16 @@
         <v>45966</v>
       </c>
       <c r="C465" t="n">
-        <v>98.33653259277344</v>
+        <v>98.33652496337891</v>
       </c>
       <c r="D465" t="n">
-        <v>98.33653259277344</v>
+        <v>98.33652496337891</v>
       </c>
       <c r="E465" t="n">
-        <v>98.3267454471337</v>
+        <v>98.32673781849851</v>
       </c>
       <c r="F465" t="n">
-        <v>98.3267454471337</v>
+        <v>98.32673781849851</v>
       </c>
       <c r="G465" t="n">
         <v>11335000</v>
@@ -11144,16 +11144,16 @@
         <v>45967</v>
       </c>
       <c r="C466" t="n">
-        <v>98.34632873535156</v>
+        <v>98.34632110595703</v>
       </c>
       <c r="D466" t="n">
-        <v>98.34632873535156</v>
+        <v>98.34632110595703</v>
       </c>
       <c r="E466" t="n">
-        <v>98.33653411845633</v>
+        <v>98.33652648982164</v>
       </c>
       <c r="F466" t="n">
-        <v>98.34632873535156</v>
+        <v>98.34632110595703</v>
       </c>
       <c r="G466" t="n">
         <v>16658100</v>
@@ -11190,16 +11190,16 @@
         <v>45971</v>
       </c>
       <c r="C468" t="n">
-        <v>98.385498046875</v>
+        <v>98.38550567626953</v>
       </c>
       <c r="D468" t="n">
-        <v>98.39529266360249</v>
+        <v>98.39530029375656</v>
       </c>
       <c r="E468" t="n">
-        <v>98.385498046875</v>
+        <v>98.38550567626953</v>
       </c>
       <c r="F468" t="n">
-        <v>98.39529266360249</v>
+        <v>98.39530029375656</v>
       </c>
       <c r="G468" t="n">
         <v>14121900</v>
@@ -11213,16 +11213,16 @@
         <v>45972</v>
       </c>
       <c r="C469" t="n">
-        <v>98.39529418945312</v>
+        <v>98.39528656005859</v>
       </c>
       <c r="D469" t="n">
-        <v>98.39529418945312</v>
+        <v>98.39528656005859</v>
       </c>
       <c r="E469" t="n">
-        <v>98.38549957257375</v>
+        <v>98.38549194393867</v>
       </c>
       <c r="F469" t="n">
-        <v>98.39529418945312</v>
+        <v>98.39528656005859</v>
       </c>
       <c r="G469" t="n">
         <v>8697800</v>
@@ -11236,16 +11236,16 @@
         <v>45973</v>
       </c>
       <c r="C470" t="n">
-        <v>98.40509033203125</v>
+        <v>98.40507507324219</v>
       </c>
       <c r="D470" t="n">
-        <v>98.40509033203125</v>
+        <v>98.40507507324219</v>
       </c>
       <c r="E470" t="n">
-        <v>98.39530318536072</v>
+        <v>98.39528792808926</v>
       </c>
       <c r="F470" t="n">
-        <v>98.39530318536072</v>
+        <v>98.39528792808926</v>
       </c>
       <c r="G470" t="n">
         <v>9067200</v>
@@ -11259,16 +11259,16 @@
         <v>45974</v>
       </c>
       <c r="C471" t="n">
-        <v>98.41486358642578</v>
+        <v>98.41487121582031</v>
       </c>
       <c r="D471" t="n">
-        <v>98.41486358642578</v>
+        <v>98.41487121582031</v>
       </c>
       <c r="E471" t="n">
-        <v>98.40506897077708</v>
+        <v>98.4050765994123</v>
       </c>
       <c r="F471" t="n">
-        <v>98.40506897077708</v>
+        <v>98.4050765994123</v>
       </c>
       <c r="G471" t="n">
         <v>11255600</v>
@@ -11282,16 +11282,16 @@
         <v>45975</v>
       </c>
       <c r="C472" t="n">
-        <v>98.44424438476562</v>
+        <v>98.44423675537109</v>
       </c>
       <c r="D472" t="n">
-        <v>98.44424438476562</v>
+        <v>98.44423675537109</v>
       </c>
       <c r="E472" t="n">
-        <v>98.43444976867691</v>
+        <v>98.43444214004147</v>
       </c>
       <c r="F472" t="n">
-        <v>98.44424438476562</v>
+        <v>98.44423675537109</v>
       </c>
       <c r="G472" t="n">
         <v>13522500</v>
@@ -11305,16 +11305,16 @@
         <v>45978</v>
       </c>
       <c r="C473" t="n">
-        <v>98.45403289794922</v>
+        <v>98.45404052734375</v>
       </c>
       <c r="D473" t="n">
-        <v>98.45403289794922</v>
+        <v>98.45404052734375</v>
       </c>
       <c r="E473" t="n">
-        <v>98.44423828246764</v>
+        <v>98.44424591110318</v>
       </c>
       <c r="F473" t="n">
-        <v>98.44913932575972</v>
+        <v>98.44914695477505</v>
       </c>
       <c r="G473" t="n">
         <v>15032800</v>
@@ -11328,16 +11328,16 @@
         <v>45979</v>
       </c>
       <c r="C474" t="n">
-        <v>98.45403289794922</v>
+        <v>98.45404052734375</v>
       </c>
       <c r="D474" t="n">
-        <v>98.46382751343079</v>
+        <v>98.46383514358433</v>
       </c>
       <c r="E474" t="n">
-        <v>98.45403289794922</v>
+        <v>98.45404052734375</v>
       </c>
       <c r="F474" t="n">
-        <v>98.45403289794922</v>
+        <v>98.45404052734375</v>
       </c>
       <c r="G474" t="n">
         <v>13130300</v>
@@ -11351,16 +11351,16 @@
         <v>45980</v>
       </c>
       <c r="C475" t="n">
-        <v>98.47361755371094</v>
+        <v>98.4736328125</v>
       </c>
       <c r="D475" t="n">
-        <v>98.47361755371094</v>
+        <v>98.4736328125</v>
       </c>
       <c r="E475" t="n">
-        <v>98.46383040904414</v>
+        <v>98.46384566631664</v>
       </c>
       <c r="F475" t="n">
-        <v>98.46383040904414</v>
+        <v>98.46384566631664</v>
       </c>
       <c r="G475" t="n">
         <v>23022400</v>
@@ -11397,16 +11397,16 @@
         <v>45982</v>
       </c>
       <c r="C477" t="n">
-        <v>98.51278686523438</v>
+        <v>98.51277923583984</v>
       </c>
       <c r="D477" t="n">
-        <v>98.51278686523438</v>
+        <v>98.51277923583984</v>
       </c>
       <c r="E477" t="n">
-        <v>98.50299224963184</v>
+        <v>98.50298462099586</v>
       </c>
       <c r="F477" t="n">
-        <v>98.51278686523438</v>
+        <v>98.51277923583984</v>
       </c>
       <c r="G477" t="n">
         <v>16446900</v>
@@ -11443,16 +11443,16 @@
         <v>45986</v>
       </c>
       <c r="C479" t="n">
-        <v>98.54216766357422</v>
+        <v>98.54216003417969</v>
       </c>
       <c r="D479" t="n">
-        <v>98.54216766357422</v>
+        <v>98.54216003417969</v>
       </c>
       <c r="E479" t="n">
-        <v>98.53238051863511</v>
+        <v>98.53237288999831</v>
       </c>
       <c r="F479" t="n">
-        <v>98.54216766357422</v>
+        <v>98.54216003417969</v>
       </c>
       <c r="G479" t="n">
         <v>19115000</v>
@@ -11466,16 +11466,16 @@
         <v>45987</v>
       </c>
       <c r="C480" t="n">
-        <v>98.55195617675781</v>
+        <v>98.55194854736328</v>
       </c>
       <c r="D480" t="n">
-        <v>98.56175079219341</v>
+        <v>98.56174316204061</v>
       </c>
       <c r="E480" t="n">
-        <v>98.55195617675781</v>
+        <v>98.55194854736328</v>
       </c>
       <c r="F480" t="n">
-        <v>98.55195617675781</v>
+        <v>98.55194854736328</v>
       </c>
       <c r="G480" t="n">
         <v>11948500</v>
@@ -11512,16 +11512,16 @@
         <v>45992</v>
       </c>
       <c r="C482" t="n">
-        <v>98.60392761230469</v>
+        <v>98.60391998291016</v>
       </c>
       <c r="D482" t="n">
-        <v>98.60392761230469</v>
+        <v>98.60391998291016</v>
       </c>
       <c r="E482" t="n">
-        <v>98.59410994289308</v>
+        <v>98.59410231425819</v>
       </c>
       <c r="F482" t="n">
-        <v>98.60392761230469</v>
+        <v>98.60391998291016</v>
       </c>
       <c r="G482" t="n">
         <v>29025600</v>
@@ -11604,16 +11604,16 @@
         <v>45996</v>
       </c>
       <c r="C486" t="n">
-        <v>98.68251037597656</v>
+        <v>98.68251800537109</v>
       </c>
       <c r="D486" t="n">
-        <v>98.68251037597656</v>
+        <v>98.68251800537109</v>
       </c>
       <c r="E486" t="n">
-        <v>98.67268521251508</v>
+        <v>98.67269284115001</v>
       </c>
       <c r="F486" t="n">
-        <v>98.67268521251508</v>
+        <v>98.67269284115001</v>
       </c>
       <c r="G486" t="n">
         <v>17918100</v>
@@ -11627,16 +11627,16 @@
         <v>45999</v>
       </c>
       <c r="C487" t="n">
-        <v>98.68251037597656</v>
+        <v>98.68251800537109</v>
       </c>
       <c r="D487" t="n">
-        <v>98.68251037597656</v>
+        <v>98.68251800537109</v>
       </c>
       <c r="E487" t="n">
-        <v>98.67268521251508</v>
+        <v>98.67269284115001</v>
       </c>
       <c r="F487" t="n">
-        <v>98.68251037597656</v>
+        <v>98.68251800537109</v>
       </c>
       <c r="G487" t="n">
         <v>16657900</v>
@@ -11650,16 +11650,16 @@
         <v>46000</v>
       </c>
       <c r="C488" t="n">
-        <v>98.69234466552734</v>
+        <v>98.69235229492188</v>
       </c>
       <c r="D488" t="n">
-        <v>98.69725350051007</v>
+        <v>98.69726113028409</v>
       </c>
       <c r="E488" t="n">
-        <v>98.69234466552734</v>
+        <v>98.69235229492188</v>
       </c>
       <c r="F488" t="n">
-        <v>98.69234466552734</v>
+        <v>98.69235229492188</v>
       </c>
       <c r="G488" t="n">
         <v>11016400</v>
@@ -11673,16 +11673,16 @@
         <v>46001</v>
       </c>
       <c r="C489" t="n">
-        <v>98.69234466552734</v>
+        <v>98.69235229492188</v>
       </c>
       <c r="D489" t="n">
-        <v>98.70216982989736</v>
+        <v>98.70217746005143</v>
       </c>
       <c r="E489" t="n">
-        <v>98.69234466552734</v>
+        <v>98.69235229492188</v>
       </c>
       <c r="F489" t="n">
-        <v>98.70216982989736</v>
+        <v>98.70217746005143</v>
       </c>
       <c r="G489" t="n">
         <v>12234900</v>
@@ -11696,16 +11696,16 @@
         <v>46002</v>
       </c>
       <c r="C490" t="n">
-        <v>98.71199035644531</v>
+        <v>98.71198272705078</v>
       </c>
       <c r="D490" t="n">
-        <v>98.72181552109964</v>
+        <v>98.72180789094574</v>
       </c>
       <c r="E490" t="n">
-        <v>98.71199035644531</v>
+        <v>98.71198272705078</v>
       </c>
       <c r="F490" t="n">
-        <v>98.71199035644531</v>
+        <v>98.71198272705078</v>
       </c>
       <c r="G490" t="n">
         <v>22343500</v>
@@ -11719,16 +11719,16 @@
         <v>46003</v>
       </c>
       <c r="C491" t="n">
-        <v>98.75127410888672</v>
+        <v>98.75126647949219</v>
       </c>
       <c r="D491" t="n">
-        <v>98.75127410888672</v>
+        <v>98.75126647949219</v>
       </c>
       <c r="E491" t="n">
-        <v>98.7414489451688</v>
+        <v>98.74144131653334</v>
       </c>
       <c r="F491" t="n">
-        <v>98.7414489451688</v>
+        <v>98.74144131653334</v>
       </c>
       <c r="G491" t="n">
         <v>13320200</v>
@@ -11742,16 +11742,16 @@
         <v>46006</v>
       </c>
       <c r="C492" t="n">
-        <v>98.75127410888672</v>
+        <v>98.75126647949219</v>
       </c>
       <c r="D492" t="n">
-        <v>98.76109927260465</v>
+        <v>98.76109164245103</v>
       </c>
       <c r="E492" t="n">
-        <v>98.75127410888672</v>
+        <v>98.75126647949219</v>
       </c>
       <c r="F492" t="n">
-        <v>98.75127410888672</v>
+        <v>98.75126647949219</v>
       </c>
       <c r="G492" t="n">
         <v>14767900</v>
@@ -11765,16 +11765,16 @@
         <v>46007</v>
       </c>
       <c r="C493" t="n">
-        <v>98.76109313964844</v>
+        <v>98.76110076904297</v>
       </c>
       <c r="D493" t="n">
-        <v>98.77091830275623</v>
+        <v>98.77092593290978</v>
       </c>
       <c r="E493" t="n">
-        <v>98.76109313964844</v>
+        <v>98.76110076904297</v>
       </c>
       <c r="F493" t="n">
-        <v>98.77091830275623</v>
+        <v>98.77092593290978</v>
       </c>
       <c r="G493" t="n">
         <v>10701200</v>
@@ -11788,16 +11788,16 @@
         <v>46008</v>
       </c>
       <c r="C494" t="n">
-        <v>98.78074645996094</v>
+        <v>98.78075408935547</v>
       </c>
       <c r="D494" t="n">
-        <v>98.78074645996094</v>
+        <v>98.78075408935547</v>
       </c>
       <c r="E494" t="n">
-        <v>98.7709287902143</v>
+        <v>98.77093641885057</v>
       </c>
       <c r="F494" t="n">
-        <v>98.7709287902143</v>
+        <v>98.77093641885057</v>
       </c>
       <c r="G494" t="n">
         <v>13788200</v>
@@ -11811,16 +11811,16 @@
         <v>46009</v>
       </c>
       <c r="C495" t="n">
-        <v>98.78074645996094</v>
+        <v>98.78075408935547</v>
       </c>
       <c r="D495" t="n">
-        <v>98.79057162411196</v>
+        <v>98.79057925426535</v>
       </c>
       <c r="E495" t="n">
-        <v>98.78074645996094</v>
+        <v>98.78075408935547</v>
       </c>
       <c r="F495" t="n">
-        <v>98.79057162411196</v>
+        <v>98.79057925426535</v>
       </c>
       <c r="G495" t="n">
         <v>20890600</v>
@@ -11834,16 +11834,16 @@
         <v>46010</v>
       </c>
       <c r="C496" t="n">
-        <v>98.82312774658203</v>
+        <v>98.8231201171875</v>
       </c>
       <c r="D496" t="n">
-        <v>98.82312774658203</v>
+        <v>98.8231201171875</v>
       </c>
       <c r="E496" t="n">
-        <v>98.81327092170693</v>
+        <v>98.81326329307338</v>
       </c>
       <c r="F496" t="n">
-        <v>98.82312774658203</v>
+        <v>98.8231201171875</v>
       </c>
       <c r="G496" t="n">
         <v>18203600</v>
@@ -11857,16 +11857,16 @@
         <v>46013</v>
       </c>
       <c r="C497" t="n">
-        <v>98.82312774658203</v>
+        <v>98.8231201171875</v>
       </c>
       <c r="D497" t="n">
-        <v>98.83298457145713</v>
+        <v>98.83297694130162</v>
       </c>
       <c r="E497" t="n">
-        <v>98.82312774658203</v>
+        <v>98.8231201171875</v>
       </c>
       <c r="F497" t="n">
-        <v>98.82312774658203</v>
+        <v>98.8231201171875</v>
       </c>
       <c r="G497" t="n">
         <v>17890900</v>
@@ -11880,16 +11880,16 @@
         <v>46014</v>
       </c>
       <c r="C498" t="n">
-        <v>98.83297729492188</v>
+        <v>98.83296966552734</v>
       </c>
       <c r="D498" t="n">
-        <v>98.84283411907127</v>
+        <v>98.84282648891585</v>
       </c>
       <c r="E498" t="n">
-        <v>98.83297729492188</v>
+        <v>98.83296966552734</v>
       </c>
       <c r="F498" t="n">
-        <v>98.84283411907127</v>
+        <v>98.84282648891585</v>
       </c>
       <c r="G498" t="n">
         <v>12256200</v>
@@ -11972,16 +11972,16 @@
         <v>46021</v>
       </c>
       <c r="C502" t="n">
-        <v>98.91182708740234</v>
+        <v>98.91181945800781</v>
       </c>
       <c r="D502" t="n">
-        <v>98.91182708740234</v>
+        <v>98.91181945800781</v>
       </c>
       <c r="E502" t="n">
-        <v>98.90197026223287</v>
+        <v>98.90196263359863</v>
       </c>
       <c r="F502" t="n">
-        <v>98.90689491554026</v>
+        <v>98.90688728652617</v>
       </c>
       <c r="G502" t="n">
         <v>12608900</v>
@@ -11995,16 +11995,16 @@
         <v>46022</v>
       </c>
       <c r="C503" t="n">
-        <v>98.92166900634766</v>
+        <v>98.92166137695312</v>
       </c>
       <c r="D503" t="n">
-        <v>98.931525830781</v>
+        <v>98.93151820062626</v>
       </c>
       <c r="E503" t="n">
-        <v>98.92166900634766</v>
+        <v>98.92166137695312</v>
       </c>
       <c r="F503" t="n">
-        <v>98.931525830781</v>
+        <v>98.93151820062626</v>
       </c>
       <c r="G503" t="n">
         <v>13910900</v>
@@ -12018,16 +12018,16 @@
         <v>46024</v>
       </c>
       <c r="C504" t="n">
-        <v>98.95124816894531</v>
+        <v>98.95124053955078</v>
       </c>
       <c r="D504" t="n">
-        <v>98.96109747568946</v>
+        <v>98.96108984553553</v>
       </c>
       <c r="E504" t="n">
-        <v>98.95124816894531</v>
+        <v>98.95124053955078</v>
       </c>
       <c r="F504" t="n">
-        <v>98.95124816894531</v>
+        <v>98.95124053955078</v>
       </c>
       <c r="G504" t="n">
         <v>19188800</v>
@@ -12041,16 +12041,16 @@
         <v>46027</v>
       </c>
       <c r="C505" t="n">
-        <v>98.96109008789062</v>
+        <v>98.96108245849609</v>
       </c>
       <c r="D505" t="n">
-        <v>98.96602225944926</v>
+        <v>98.96601462967449</v>
       </c>
       <c r="E505" t="n">
-        <v>98.96109008789062</v>
+        <v>98.96108245849609</v>
       </c>
       <c r="F505" t="n">
-        <v>98.96109008789062</v>
+        <v>98.96108245849609</v>
       </c>
       <c r="G505" t="n">
         <v>25006600</v>
@@ -12064,16 +12064,16 @@
         <v>46028</v>
       </c>
       <c r="C506" t="n">
-        <v>98.970947265625</v>
+        <v>98.97093963623047</v>
       </c>
       <c r="D506" t="n">
-        <v>98.970947265625</v>
+        <v>98.97093963623047</v>
       </c>
       <c r="E506" t="n">
-        <v>98.970947265625</v>
+        <v>98.97093963623047</v>
       </c>
       <c r="F506" t="n">
-        <v>98.970947265625</v>
+        <v>98.97093963623047</v>
       </c>
       <c r="G506" t="n">
         <v>17635000</v>
@@ -12156,16 +12156,16 @@
         <v>46034</v>
       </c>
       <c r="C510" t="n">
-        <v>99.03007507324219</v>
+        <v>99.03006744384766</v>
       </c>
       <c r="D510" t="n">
-        <v>99.03007507324219</v>
+        <v>99.03006744384766</v>
       </c>
       <c r="E510" t="n">
-        <v>99.02022576700949</v>
+        <v>99.02021813837376</v>
       </c>
       <c r="F510" t="n">
-        <v>99.02022576700949</v>
+        <v>99.02021813837376</v>
       </c>
       <c r="G510" t="n">
         <v>14819400</v>
@@ -12179,16 +12179,16 @@
         <v>46035</v>
       </c>
       <c r="C511" t="n">
-        <v>99.03992462158203</v>
+        <v>99.03993988037109</v>
       </c>
       <c r="D511" t="n">
-        <v>99.03992462158203</v>
+        <v>99.03993988037109</v>
       </c>
       <c r="E511" t="n">
-        <v>99.03006779751914</v>
+        <v>99.0300830547896</v>
       </c>
       <c r="F511" t="n">
-        <v>99.03006779751914</v>
+        <v>99.0300830547896</v>
       </c>
       <c r="G511" t="n">
         <v>14163000</v>
@@ -12202,16 +12202,16 @@
         <v>46036</v>
       </c>
       <c r="C512" t="n">
-        <v>99.04978179931641</v>
+        <v>99.04978942871094</v>
       </c>
       <c r="D512" t="n">
-        <v>99.04978179931641</v>
+        <v>99.04978942871094</v>
       </c>
       <c r="E512" t="n">
-        <v>99.03992497521833</v>
+        <v>99.03993260385363</v>
       </c>
       <c r="F512" t="n">
-        <v>99.04978179931641</v>
+        <v>99.04978942871094</v>
       </c>
       <c r="G512" t="n">
         <v>11851800</v>
@@ -12225,16 +12225,16 @@
         <v>46037</v>
       </c>
       <c r="C513" t="n">
-        <v>99.05962371826172</v>
+        <v>99.05963897705078</v>
       </c>
       <c r="D513" t="n">
-        <v>99.05962371826172</v>
+        <v>99.05963897705078</v>
       </c>
       <c r="E513" t="n">
-        <v>99.04977441345191</v>
+        <v>99.04978967072383</v>
       </c>
       <c r="F513" t="n">
-        <v>99.04977441345191</v>
+        <v>99.04978967072383</v>
       </c>
       <c r="G513" t="n">
         <v>11469500</v>
@@ -12248,16 +12248,16 @@
         <v>46038</v>
       </c>
       <c r="C514" t="n">
-        <v>99.09905242919922</v>
+        <v>99.09906005859375</v>
       </c>
       <c r="D514" t="n">
-        <v>99.09905242919922</v>
+        <v>99.09906005859375</v>
       </c>
       <c r="E514" t="n">
-        <v>99.08427095209834</v>
+        <v>99.08427858035489</v>
       </c>
       <c r="F514" t="n">
-        <v>99.08920312350128</v>
+        <v>99.08921075213753</v>
       </c>
       <c r="G514" t="n">
         <v>14766800</v>
@@ -12271,16 +12271,16 @@
         <v>46042</v>
       </c>
       <c r="C515" t="n">
-        <v>99.09905242919922</v>
+        <v>99.09906005859375</v>
       </c>
       <c r="D515" t="n">
-        <v>99.10890925345112</v>
+        <v>99.10891688360451</v>
       </c>
       <c r="E515" t="n">
-        <v>99.09905242919922</v>
+        <v>99.09906005859375</v>
       </c>
       <c r="F515" t="n">
-        <v>99.09905242919922</v>
+        <v>99.09906005859375</v>
       </c>
       <c r="G515" t="n">
         <v>19394600</v>
@@ -12294,16 +12294,16 @@
         <v>46043</v>
       </c>
       <c r="C516" t="n">
-        <v>99.09905242919922</v>
+        <v>99.09906005859375</v>
       </c>
       <c r="D516" t="n">
-        <v>99.11876607770303</v>
+        <v>99.11877370861527</v>
       </c>
       <c r="E516" t="n">
-        <v>99.09905242919922</v>
+        <v>99.09906005859375</v>
       </c>
       <c r="F516" t="n">
-        <v>99.10398460060216</v>
+        <v>99.10399223037641</v>
       </c>
       <c r="G516" t="n">
         <v>17502100</v>
@@ -12317,16 +12317,16 @@
         <v>46044</v>
       </c>
       <c r="C517" t="n">
-        <v>99.11875915527344</v>
+        <v>99.1187744140625</v>
       </c>
       <c r="D517" t="n">
-        <v>99.11875915527344</v>
+        <v>99.1187744140625</v>
       </c>
       <c r="E517" t="n">
-        <v>99.10890233170993</v>
+        <v>99.1089175889816</v>
       </c>
       <c r="F517" t="n">
-        <v>99.11875915527344</v>
+        <v>99.1187744140625</v>
       </c>
       <c r="G517" t="n">
         <v>13618500</v>
@@ -12363,16 +12363,16 @@
         <v>46048</v>
       </c>
       <c r="C519" t="n">
-        <v>99.15818023681641</v>
+        <v>99.15818786621094</v>
       </c>
       <c r="D519" t="n">
-        <v>99.15818023681641</v>
+        <v>99.15818786621094</v>
       </c>
       <c r="E519" t="n">
-        <v>99.14832341312308</v>
+        <v>99.14833104175922</v>
       </c>
       <c r="F519" t="n">
-        <v>99.15818023681641</v>
+        <v>99.15818786621094</v>
       </c>
       <c r="G519" t="n">
         <v>16872000</v>
@@ -12386,16 +12386,16 @@
         <v>46049</v>
       </c>
       <c r="C520" t="n">
-        <v>99.15818023681641</v>
+        <v>99.15818786621094</v>
       </c>
       <c r="D520" t="n">
-        <v>99.1729617130796</v>
+        <v>99.17296934361146</v>
       </c>
       <c r="E520" t="n">
-        <v>99.15818023681641</v>
+        <v>99.15818786621094</v>
       </c>
       <c r="F520" t="n">
-        <v>99.16802954195617</v>
+        <v>99.16803717210854</v>
       </c>
       <c r="G520" t="n">
         <v>13393600</v>
@@ -12409,16 +12409,16 @@
         <v>46050</v>
       </c>
       <c r="C521" t="n">
-        <v>99.17788696289062</v>
+        <v>99.17789459228516</v>
       </c>
       <c r="D521" t="n">
-        <v>99.17788696289062</v>
+        <v>99.17789459228516</v>
       </c>
       <c r="E521" t="n">
-        <v>99.16803013913795</v>
+        <v>99.16803776777424</v>
       </c>
       <c r="F521" t="n">
-        <v>99.16803013913795</v>
+        <v>99.16803776777424</v>
       </c>
       <c r="G521" t="n">
         <v>11987500</v>
@@ -12478,16 +12478,16 @@
         <v>46055</v>
       </c>
       <c r="C524" t="n">
-        <v>99.21635437011719</v>
+        <v>99.21636199951172</v>
       </c>
       <c r="D524" t="n">
-        <v>99.22623400053318</v>
+        <v>99.22624163068743</v>
       </c>
       <c r="E524" t="n">
-        <v>99.21635437011719</v>
+        <v>99.21636199951172</v>
       </c>
       <c r="F524" t="n">
-        <v>99.22623400053318</v>
+        <v>99.22624163068743</v>
       </c>
       <c r="G524" t="n">
         <v>31225300</v>
@@ -12501,16 +12501,16 @@
         <v>46056</v>
       </c>
       <c r="C525" t="n">
-        <v>99.23612213134766</v>
+        <v>99.23612976074219</v>
       </c>
       <c r="D525" t="n">
-        <v>99.23612213134766</v>
+        <v>99.23612976074219</v>
       </c>
       <c r="E525" t="n">
-        <v>99.22623495913354</v>
+        <v>99.22624258776793</v>
       </c>
       <c r="F525" t="n">
-        <v>99.23612213134766</v>
+        <v>99.23612976074219</v>
       </c>
       <c r="G525" t="n">
         <v>18150800</v>
@@ -12593,16 +12593,16 @@
         <v>46062</v>
       </c>
       <c r="C529" t="n">
-        <v>99.29543304443359</v>
+        <v>99.29544067382812</v>
       </c>
       <c r="D529" t="n">
-        <v>99.29543304443359</v>
+        <v>99.29544067382812</v>
       </c>
       <c r="E529" t="n">
-        <v>99.28555341362733</v>
+        <v>99.28556104226274</v>
       </c>
       <c r="F529" t="n">
-        <v>99.28555341362733</v>
+        <v>99.28556104226274</v>
       </c>
       <c r="G529" t="n">
         <v>13991600</v>
@@ -12662,16 +12662,16 @@
         <v>46065</v>
       </c>
       <c r="C532" t="n">
-        <v>99.32510375976562</v>
+        <v>99.32509613037109</v>
       </c>
       <c r="D532" t="n">
-        <v>99.32510375976562</v>
+        <v>99.32509613037109</v>
       </c>
       <c r="E532" t="n">
-        <v>99.31521658634087</v>
+        <v>99.31520895770579</v>
       </c>
       <c r="F532" t="n">
-        <v>99.31521658634087</v>
+        <v>99.31520895770579</v>
       </c>
       <c r="G532" t="n">
         <v>16593900</v>
@@ -12731,16 +12731,16 @@
         <v>46071</v>
       </c>
       <c r="C535" t="n">
-        <v>99.38440704345703</v>
+        <v>99.3843994140625</v>
       </c>
       <c r="D535" t="n">
-        <v>99.38440704345703</v>
+        <v>99.3843994140625</v>
       </c>
       <c r="E535" t="n">
-        <v>99.37451987049721</v>
+        <v>99.37451224186168</v>
       </c>
       <c r="F535" t="n">
-        <v>99.38440704345703</v>
+        <v>99.3843994140625</v>
       </c>
       <c r="G535" t="n">
         <v>10207300</v>
@@ -12777,16 +12777,16 @@
         <v>46073</v>
       </c>
       <c r="C537" t="n">
-        <v>99.41405487060547</v>
+        <v>99.4140625</v>
       </c>
       <c r="D537" t="n">
-        <v>99.42394204295366</v>
+        <v>99.42394967310696</v>
       </c>
       <c r="E537" t="n">
-        <v>99.41405487060547</v>
+        <v>99.4140625</v>
       </c>
       <c r="F537" t="n">
-        <v>99.42394204295366</v>
+        <v>99.42394967310696</v>
       </c>
       <c r="G537" t="n">
         <v>13490000</v>
@@ -12800,16 +12800,16 @@
         <v>46076</v>
       </c>
       <c r="C538" t="n">
-        <v>99.43383026123047</v>
+        <v>99.43382263183594</v>
       </c>
       <c r="D538" t="n">
-        <v>99.43383026123047</v>
+        <v>99.43382263183594</v>
       </c>
       <c r="E538" t="n">
-        <v>99.42395062973182</v>
+        <v>99.42394300109534</v>
       </c>
       <c r="F538" t="n">
-        <v>99.42889044548114</v>
+        <v>99.42888281646563</v>
       </c>
       <c r="G538" t="n">
         <v>13465400</v>
@@ -12823,16 +12823,16 @@
         <v>46077</v>
       </c>
       <c r="C539" t="n">
-        <v>99.43383026123047</v>
+        <v>99.43382263183594</v>
       </c>
       <c r="D539" t="n">
-        <v>99.44371743443256</v>
+        <v>99.44370980427939</v>
       </c>
       <c r="E539" t="n">
-        <v>99.43383026123047</v>
+        <v>99.43382263183594</v>
       </c>
       <c r="F539" t="n">
-        <v>99.43877761868323</v>
+        <v>99.4387699889091</v>
       </c>
       <c r="G539" t="n">
         <v>12168900</v>
@@ -12846,16 +12846,16 @@
         <v>46078</v>
       </c>
       <c r="C540" t="n">
-        <v>99.44371032714844</v>
+        <v>99.44370269775391</v>
       </c>
       <c r="D540" t="n">
-        <v>99.45359749964389</v>
+        <v>99.4535898694908</v>
       </c>
       <c r="E540" t="n">
-        <v>99.44371032714844</v>
+        <v>99.44370269775391</v>
       </c>
       <c r="F540" t="n">
-        <v>99.45359749964389</v>
+        <v>99.4535898694908</v>
       </c>
       <c r="G540" t="n">
         <v>12532000</v>
@@ -12892,16 +12892,16 @@
         <v>46080</v>
       </c>
       <c r="C542" t="n">
-        <v>99.48324584960938</v>
+        <v>99.48325347900391</v>
       </c>
       <c r="D542" t="n">
-        <v>99.49313302154569</v>
+        <v>99.49314065169848</v>
       </c>
       <c r="E542" t="n">
-        <v>99.48324584960938</v>
+        <v>99.48325347900391</v>
       </c>
       <c r="F542" t="n">
-        <v>99.4881856647263</v>
+        <v>99.48819329449967</v>
       </c>
       <c r="G542" t="n">
         <v>26602400</v>
@@ -12915,16 +12915,16 @@
         <v>46083</v>
       </c>
       <c r="C543" t="n">
-        <v>99.49514007568359</v>
+        <v>99.49514770507812</v>
       </c>
       <c r="D543" t="n">
-        <v>99.50505404233567</v>
+        <v>99.50506167249043</v>
       </c>
       <c r="E543" t="n">
-        <v>99.49514007568359</v>
+        <v>99.49514770507812</v>
       </c>
       <c r="F543" t="n">
-        <v>99.50010084008005</v>
+        <v>99.50010846985499</v>
       </c>
       <c r="G543" t="n">
         <v>33993400</v>
@@ -12938,16 +12938,16 @@
         <v>46084</v>
       </c>
       <c r="C544" t="n">
-        <v>99.51497650146484</v>
+        <v>99.51496887207031</v>
       </c>
       <c r="D544" t="n">
-        <v>99.51497650146484</v>
+        <v>99.51496887207031</v>
       </c>
       <c r="E544" t="n">
-        <v>99.50506253396671</v>
+        <v>99.50505490533224</v>
       </c>
       <c r="F544" t="n">
-        <v>99.51001573664503</v>
+        <v>99.51000810763082</v>
       </c>
       <c r="G544" t="n">
         <v>19224400</v>
@@ -12961,16 +12961,16 @@
         <v>46085</v>
       </c>
       <c r="C545" t="n">
-        <v>99.51497650146484</v>
+        <v>99.51496887207031</v>
       </c>
       <c r="D545" t="n">
-        <v>99.52489046896297</v>
+        <v>99.52488283880838</v>
       </c>
       <c r="E545" t="n">
-        <v>99.51497650146484</v>
+        <v>99.51496887207031</v>
       </c>
       <c r="F545" t="n">
-        <v>99.51992970414315</v>
+        <v>99.51992207436889</v>
       </c>
       <c r="G545" t="n">
         <v>14325400</v>
@@ -12984,16 +12984,16 @@
         <v>46086</v>
       </c>
       <c r="C546" t="n">
-        <v>99.52488708496094</v>
+        <v>99.52487945556641</v>
       </c>
       <c r="D546" t="n">
-        <v>99.53479348998074</v>
+        <v>99.53478585982681</v>
       </c>
       <c r="E546" t="n">
-        <v>99.52488708496094</v>
+        <v>99.52487945556641</v>
       </c>
       <c r="F546" t="n">
-        <v>99.53479348998074</v>
+        <v>99.53478585982681</v>
       </c>
       <c r="G546" t="n">
         <v>16218200</v>
@@ -13076,16 +13076,16 @@
         <v>46092</v>
       </c>
       <c r="C550" t="n">
-        <v>99.59427642822266</v>
+        <v>99.59426879882812</v>
       </c>
       <c r="D550" t="n">
-        <v>99.59427642822266</v>
+        <v>99.59426879882812</v>
       </c>
       <c r="E550" t="n">
-        <v>99.58436246039494</v>
+        <v>99.58435483175987</v>
       </c>
       <c r="F550" t="n">
-        <v>99.58436246039494</v>
+        <v>99.58435483175987</v>
       </c>
       <c r="G550" t="n">
         <v>12287800</v>
@@ -13237,16 +13237,16 @@
         <v>46101</v>
       </c>
       <c r="C557" t="n">
-        <v>99.69338989257812</v>
+        <v>99.69338226318359</v>
       </c>
       <c r="D557" t="n">
-        <v>99.69338989257812</v>
+        <v>99.69338226318359</v>
       </c>
       <c r="E557" t="n">
-        <v>99.68347592510119</v>
+        <v>99.68346829646536</v>
       </c>
       <c r="F557" t="n">
-        <v>99.69338989257812</v>
+        <v>99.69338226318359</v>
       </c>
       <c r="G557" t="n">
         <v>23039600</v>
@@ -13260,16 +13260,16 @@
         <v>46104</v>
       </c>
       <c r="C558" t="n">
-        <v>99.69338989257812</v>
+        <v>99.69338226318359</v>
       </c>
       <c r="D558" t="n">
-        <v>99.71321026539052</v>
+        <v>99.71320263447916</v>
       </c>
       <c r="E558" t="n">
-        <v>99.69338989257812</v>
+        <v>99.69338226318359</v>
       </c>
       <c r="F558" t="n">
-        <v>99.70329629791358</v>
+        <v>99.70328866776093</v>
       </c>
       <c r="G558" t="n">
         <v>33994300</v>
@@ -13559,16 +13559,16 @@
         <v>46122</v>
       </c>
       <c r="C571" t="n">
-        <v>99.90489196777344</v>
+        <v>99.90489959716797</v>
       </c>
       <c r="D571" t="n">
-        <v>99.90489196777344</v>
+        <v>99.90489959716797</v>
       </c>
       <c r="E571" t="n">
-        <v>99.89494905892218</v>
+        <v>99.8949566875574</v>
       </c>
       <c r="F571" t="n">
-        <v>99.89494905892218</v>
+        <v>99.8949566875574</v>
       </c>
       <c r="G571" t="n">
         <v>18783100</v>
@@ -13674,16 +13674,16 @@
         <v>46129</v>
       </c>
       <c r="C576" t="n">
-        <v>99.96453857421875</v>
+        <v>99.96453094482422</v>
       </c>
       <c r="D576" t="n">
-        <v>99.97448148349987</v>
+        <v>99.97447385334648</v>
       </c>
       <c r="E576" t="n">
-        <v>99.96453857421875</v>
+        <v>99.96453094482422</v>
       </c>
       <c r="F576" t="n">
-        <v>99.96453857421875</v>
+        <v>99.96453094482422</v>
       </c>
       <c r="G576" t="n">
         <v>20660500</v>

--- a/Data/sgov.xlsx
+++ b/Data/sgov.xlsx
@@ -472,16 +472,16 @@
         <v>45293</v>
       </c>
       <c r="C2" t="n">
-        <v>90.15840148925781</v>
+        <v>90.15837860107422</v>
       </c>
       <c r="D2" t="n">
-        <v>90.1673931794142</v>
+        <v>90.16737028894792</v>
       </c>
       <c r="E2" t="n">
-        <v>90.14940979910142</v>
+        <v>90.14938691320052</v>
       </c>
       <c r="F2" t="n">
-        <v>90.15840148925781</v>
+        <v>90.15837860107422</v>
       </c>
       <c r="G2" t="n">
         <v>5286200</v>
@@ -495,16 +495,16 @@
         <v>45294</v>
       </c>
       <c r="C3" t="n">
-        <v>90.16738128662109</v>
+        <v>90.16737365722656</v>
       </c>
       <c r="D3" t="n">
-        <v>90.18535780591283</v>
+        <v>90.18535017499724</v>
       </c>
       <c r="E3" t="n">
-        <v>90.16738128662109</v>
+        <v>90.16737365722656</v>
       </c>
       <c r="F3" t="n">
-        <v>90.16738128662109</v>
+        <v>90.16737365722656</v>
       </c>
       <c r="G3" t="n">
         <v>4597300</v>
@@ -518,16 +518,16 @@
         <v>45295</v>
       </c>
       <c r="C4" t="n">
-        <v>90.21231079101562</v>
+        <v>90.21234130859375</v>
       </c>
       <c r="D4" t="n">
-        <v>90.22130247846871</v>
+        <v>90.2213329990886</v>
       </c>
       <c r="E4" t="n">
-        <v>90.21231079101562</v>
+        <v>90.21234130859375</v>
       </c>
       <c r="F4" t="n">
-        <v>90.21231079101562</v>
+        <v>90.21234130859375</v>
       </c>
       <c r="G4" t="n">
         <v>2794100</v>
@@ -541,16 +541,16 @@
         <v>45296</v>
       </c>
       <c r="C5" t="n">
-        <v>90.22132873535156</v>
+        <v>90.2213134765625</v>
       </c>
       <c r="D5" t="n">
-        <v>90.23032042542148</v>
+        <v>90.23030516511169</v>
       </c>
       <c r="E5" t="n">
-        <v>90.22132873535156</v>
+        <v>90.2213134765625</v>
       </c>
       <c r="F5" t="n">
-        <v>90.22132873535156</v>
+        <v>90.2213134765625</v>
       </c>
       <c r="G5" t="n">
         <v>3491200</v>
@@ -564,16 +564,16 @@
         <v>45299</v>
       </c>
       <c r="C6" t="n">
-        <v>90.24826812744141</v>
+        <v>90.24827575683594</v>
       </c>
       <c r="D6" t="n">
-        <v>90.24826812744141</v>
+        <v>90.24827575683594</v>
       </c>
       <c r="E6" t="n">
-        <v>90.23927644024286</v>
+        <v>90.23928406887724</v>
       </c>
       <c r="F6" t="n">
-        <v>90.24826812744141</v>
+        <v>90.24827575683594</v>
       </c>
       <c r="G6" t="n">
         <v>2867500</v>
@@ -587,16 +587,16 @@
         <v>45300</v>
       </c>
       <c r="C7" t="n">
-        <v>90.25727844238281</v>
+        <v>90.25727081298828</v>
       </c>
       <c r="D7" t="n">
-        <v>90.25727844238281</v>
+        <v>90.25727081298828</v>
       </c>
       <c r="E7" t="n">
-        <v>90.24828675332851</v>
+        <v>90.24827912469404</v>
       </c>
       <c r="F7" t="n">
-        <v>90.25727844238281</v>
+        <v>90.25727081298828</v>
       </c>
       <c r="G7" t="n">
         <v>2419800</v>
@@ -610,16 +610,16 @@
         <v>45301</v>
       </c>
       <c r="C8" t="n">
-        <v>90.27524566650391</v>
+        <v>90.27526092529297</v>
       </c>
       <c r="D8" t="n">
-        <v>90.27524566650391</v>
+        <v>90.27526092529297</v>
       </c>
       <c r="E8" t="n">
-        <v>90.26626083702391</v>
+        <v>90.26627609429431</v>
       </c>
       <c r="F8" t="n">
-        <v>90.27524566650391</v>
+        <v>90.27526092529297</v>
       </c>
       <c r="G8" t="n">
         <v>1961400</v>
@@ -633,16 +633,16 @@
         <v>45302</v>
       </c>
       <c r="C9" t="n">
-        <v>90.32917785644531</v>
+        <v>90.32918548583984</v>
       </c>
       <c r="D9" t="n">
-        <v>90.32917785644531</v>
+        <v>90.32918548583984</v>
       </c>
       <c r="E9" t="n">
-        <v>90.31119448239433</v>
+        <v>90.31120211026995</v>
       </c>
       <c r="F9" t="n">
-        <v>90.31119448239433</v>
+        <v>90.31120211026995</v>
       </c>
       <c r="G9" t="n">
         <v>3164900</v>
@@ -679,16 +679,16 @@
         <v>45307</v>
       </c>
       <c r="C11" t="n">
-        <v>90.34716796875</v>
+        <v>90.34718322753906</v>
       </c>
       <c r="D11" t="n">
-        <v>90.35615965712871</v>
+        <v>90.35617491743638</v>
       </c>
       <c r="E11" t="n">
-        <v>90.34716796875</v>
+        <v>90.34718322753906</v>
       </c>
       <c r="F11" t="n">
-        <v>90.35615965712871</v>
+        <v>90.35617491743638</v>
       </c>
       <c r="G11" t="n">
         <v>2713000</v>
@@ -702,16 +702,16 @@
         <v>45308</v>
       </c>
       <c r="C12" t="n">
-        <v>90.35614776611328</v>
+        <v>90.35615539550781</v>
       </c>
       <c r="D12" t="n">
-        <v>90.36513259466092</v>
+        <v>90.36514022481411</v>
       </c>
       <c r="E12" t="n">
-        <v>90.35614776611328</v>
+        <v>90.35615539550781</v>
       </c>
       <c r="F12" t="n">
-        <v>90.36513259466092</v>
+        <v>90.36514022481411</v>
       </c>
       <c r="G12" t="n">
         <v>2317700</v>
@@ -725,16 +725,16 @@
         <v>45309</v>
       </c>
       <c r="C13" t="n">
-        <v>90.39212799072266</v>
+        <v>90.39215087890625</v>
       </c>
       <c r="D13" t="n">
-        <v>90.40111282129152</v>
+        <v>90.40113571175016</v>
       </c>
       <c r="E13" t="n">
-        <v>90.39212799072266</v>
+        <v>90.39215087890625</v>
       </c>
       <c r="F13" t="n">
-        <v>90.40111282129152</v>
+        <v>90.40113571175016</v>
       </c>
       <c r="G13" t="n">
         <v>2672000</v>
@@ -748,16 +748,16 @@
         <v>45310</v>
       </c>
       <c r="C14" t="n">
-        <v>90.41909027099609</v>
+        <v>90.41909790039062</v>
       </c>
       <c r="D14" t="n">
-        <v>90.41909027099609</v>
+        <v>90.41909790039062</v>
       </c>
       <c r="E14" t="n">
-        <v>90.40110689373897</v>
+        <v>90.40111452161609</v>
       </c>
       <c r="F14" t="n">
-        <v>90.41009858236752</v>
+        <v>90.41010621100335</v>
       </c>
       <c r="G14" t="n">
         <v>3630100</v>
@@ -794,16 +794,16 @@
         <v>45314</v>
       </c>
       <c r="C16" t="n">
-        <v>90.446044921875</v>
+        <v>90.44606018066406</v>
       </c>
       <c r="D16" t="n">
-        <v>90.446044921875</v>
+        <v>90.44606018066406</v>
       </c>
       <c r="E16" t="n">
-        <v>90.43705323459413</v>
+        <v>90.43706849186626</v>
       </c>
       <c r="F16" t="n">
-        <v>90.43705323459413</v>
+        <v>90.43706849186626</v>
       </c>
       <c r="G16" t="n">
         <v>2066200</v>
@@ -817,16 +817,16 @@
         <v>45315</v>
       </c>
       <c r="C17" t="n">
-        <v>90.45505523681641</v>
+        <v>90.45504760742188</v>
       </c>
       <c r="D17" t="n">
-        <v>90.45505523681641</v>
+        <v>90.45504760742188</v>
       </c>
       <c r="E17" t="n">
-        <v>90.44606354768386</v>
+        <v>90.44605591904774</v>
       </c>
       <c r="F17" t="n">
-        <v>90.44606354768386</v>
+        <v>90.44605591904774</v>
       </c>
       <c r="G17" t="n">
         <v>3441600</v>
@@ -840,16 +840,16 @@
         <v>45316</v>
       </c>
       <c r="C18" t="n">
-        <v>90.49999237060547</v>
+        <v>90.50000762939453</v>
       </c>
       <c r="D18" t="n">
-        <v>90.49999237060547</v>
+        <v>90.50000762939453</v>
       </c>
       <c r="E18" t="n">
-        <v>90.48201585249815</v>
+        <v>90.48203110825628</v>
       </c>
       <c r="F18" t="n">
-        <v>90.48201585249815</v>
+        <v>90.48203110825628</v>
       </c>
       <c r="G18" t="n">
         <v>2426000</v>
@@ -863,16 +863,16 @@
         <v>45317</v>
       </c>
       <c r="C19" t="n">
-        <v>90.49999237060547</v>
+        <v>90.50000762939453</v>
       </c>
       <c r="D19" t="n">
-        <v>90.50898405898346</v>
+        <v>90.50899931928856</v>
       </c>
       <c r="E19" t="n">
-        <v>90.49999237060547</v>
+        <v>90.50000762939453</v>
       </c>
       <c r="F19" t="n">
-        <v>90.50898405898346</v>
+        <v>90.50899931928856</v>
       </c>
       <c r="G19" t="n">
         <v>2059100</v>
@@ -955,16 +955,16 @@
         <v>45323</v>
       </c>
       <c r="C23" t="n">
-        <v>90.58834075927734</v>
+        <v>90.58834838867188</v>
       </c>
       <c r="D23" t="n">
-        <v>90.59737352716907</v>
+        <v>90.59738115732434</v>
       </c>
       <c r="E23" t="n">
-        <v>90.58834075927734</v>
+        <v>90.58834838867188</v>
       </c>
       <c r="F23" t="n">
-        <v>90.59737352716907</v>
+        <v>90.59738115732434</v>
       </c>
       <c r="G23" t="n">
         <v>7038600</v>
@@ -978,16 +978,16 @@
         <v>45324</v>
       </c>
       <c r="C24" t="n">
-        <v>90.59735107421875</v>
+        <v>90.59734344482422</v>
       </c>
       <c r="D24" t="n">
-        <v>90.59735107421875</v>
+        <v>90.59734344482422</v>
       </c>
       <c r="E24" t="n">
-        <v>90.58831830856563</v>
+        <v>90.58831067993177</v>
       </c>
       <c r="F24" t="n">
-        <v>90.59735107421875</v>
+        <v>90.59734344482422</v>
       </c>
       <c r="G24" t="n">
         <v>3864800</v>
@@ -1001,16 +1001,16 @@
         <v>45327</v>
       </c>
       <c r="C25" t="n">
-        <v>90.61544036865234</v>
+        <v>90.61542510986328</v>
       </c>
       <c r="D25" t="n">
-        <v>90.61544036865234</v>
+        <v>90.61542510986328</v>
       </c>
       <c r="E25" t="n">
-        <v>90.6064144899274</v>
+        <v>90.60639923265822</v>
       </c>
       <c r="F25" t="n">
-        <v>90.61544036865234</v>
+        <v>90.61542510986328</v>
       </c>
       <c r="G25" t="n">
         <v>3969400</v>
@@ -1024,16 +1024,16 @@
         <v>45328</v>
       </c>
       <c r="C26" t="n">
-        <v>90.62444305419922</v>
+        <v>90.62446594238281</v>
       </c>
       <c r="D26" t="n">
-        <v>90.63347581990945</v>
+        <v>90.63349871037437</v>
       </c>
       <c r="E26" t="n">
-        <v>90.61541028848899</v>
+        <v>90.61543317439127</v>
       </c>
       <c r="F26" t="n">
-        <v>90.62444305419922</v>
+        <v>90.62446594238281</v>
       </c>
       <c r="G26" t="n">
         <v>2167300</v>
@@ -1047,16 +1047,16 @@
         <v>45329</v>
       </c>
       <c r="C27" t="n">
-        <v>90.64253997802734</v>
+        <v>90.64250946044922</v>
       </c>
       <c r="D27" t="n">
-        <v>90.64253997802734</v>
+        <v>90.64250946044922</v>
       </c>
       <c r="E27" t="n">
-        <v>90.63350720918878</v>
+        <v>90.63347669465182</v>
       </c>
       <c r="F27" t="n">
-        <v>90.64253997802734</v>
+        <v>90.64250946044922</v>
       </c>
       <c r="G27" t="n">
         <v>2621200</v>
@@ -1070,16 +1070,16 @@
         <v>45330</v>
       </c>
       <c r="C28" t="n">
-        <v>90.66962432861328</v>
+        <v>90.66960906982422</v>
       </c>
       <c r="D28" t="n">
-        <v>90.68768297489923</v>
+        <v>90.68766771307108</v>
       </c>
       <c r="E28" t="n">
-        <v>90.66962432861328</v>
+        <v>90.66960906982422</v>
       </c>
       <c r="F28" t="n">
-        <v>90.66962432861328</v>
+        <v>90.66960906982422</v>
       </c>
       <c r="G28" t="n">
         <v>3838700</v>
@@ -1093,16 +1093,16 @@
         <v>45331</v>
       </c>
       <c r="C29" t="n">
-        <v>90.69670867919922</v>
+        <v>90.69670104980469</v>
       </c>
       <c r="D29" t="n">
-        <v>90.69670867919922</v>
+        <v>90.69670104980469</v>
       </c>
       <c r="E29" t="n">
-        <v>90.68316297304392</v>
+        <v>90.68315534478884</v>
       </c>
       <c r="F29" t="n">
-        <v>90.6876759117681</v>
+        <v>90.68766828313339</v>
       </c>
       <c r="G29" t="n">
         <v>3232500</v>
@@ -1116,16 +1116,16 @@
         <v>45334</v>
       </c>
       <c r="C30" t="n">
-        <v>90.69670867919922</v>
+        <v>90.69670104980469</v>
       </c>
       <c r="D30" t="n">
-        <v>90.71476732407868</v>
+        <v>90.71475969316506</v>
       </c>
       <c r="E30" t="n">
-        <v>90.69670867919922</v>
+        <v>90.69670104980469</v>
       </c>
       <c r="F30" t="n">
-        <v>90.70574144663034</v>
+        <v>90.70573381647597</v>
       </c>
       <c r="G30" t="n">
         <v>2792700</v>
@@ -1185,16 +1185,16 @@
         <v>45337</v>
       </c>
       <c r="C33" t="n">
-        <v>90.77798461914062</v>
+        <v>90.77797698974609</v>
       </c>
       <c r="D33" t="n">
-        <v>90.7870173867412</v>
+        <v>90.78700975658751</v>
       </c>
       <c r="E33" t="n">
-        <v>90.77798461914062</v>
+        <v>90.77797698974609</v>
       </c>
       <c r="F33" t="n">
-        <v>90.7870173867412</v>
+        <v>90.78700975658751</v>
       </c>
       <c r="G33" t="n">
         <v>2577800</v>
@@ -1208,16 +1208,16 @@
         <v>45338</v>
       </c>
       <c r="C34" t="n">
-        <v>90.78701782226562</v>
+        <v>90.78702545166016</v>
       </c>
       <c r="D34" t="n">
-        <v>90.79605058990954</v>
+        <v>90.79605822006314</v>
       </c>
       <c r="E34" t="n">
-        <v>90.78701782226562</v>
+        <v>90.78702545166016</v>
       </c>
       <c r="F34" t="n">
-        <v>90.79605058990954</v>
+        <v>90.79605822006314</v>
       </c>
       <c r="G34" t="n">
         <v>2920700</v>
@@ -1231,16 +1231,16 @@
         <v>45342</v>
       </c>
       <c r="C35" t="n">
-        <v>90.80508422851562</v>
+        <v>90.80509185791016</v>
       </c>
       <c r="D35" t="n">
-        <v>90.81411010626316</v>
+        <v>90.81411773641604</v>
       </c>
       <c r="E35" t="n">
-        <v>90.79605146078508</v>
+        <v>90.79605908942068</v>
       </c>
       <c r="F35" t="n">
-        <v>90.80508422851562</v>
+        <v>90.80509185791016</v>
       </c>
       <c r="G35" t="n">
         <v>3268600</v>
@@ -1254,16 +1254,16 @@
         <v>45343</v>
       </c>
       <c r="C36" t="n">
-        <v>90.81410980224609</v>
+        <v>90.81407165527344</v>
       </c>
       <c r="D36" t="n">
-        <v>90.83217533764672</v>
+        <v>90.83213718308554</v>
       </c>
       <c r="E36" t="n">
-        <v>90.81410980224609</v>
+        <v>90.81407165527344</v>
       </c>
       <c r="F36" t="n">
-        <v>90.8231425699464</v>
+        <v>90.82310441917949</v>
       </c>
       <c r="G36" t="n">
         <v>2302700</v>
@@ -1277,16 +1277,16 @@
         <v>45344</v>
       </c>
       <c r="C37" t="n">
-        <v>90.8502197265625</v>
+        <v>90.85024261474609</v>
       </c>
       <c r="D37" t="n">
-        <v>90.85925249284537</v>
+        <v>90.85927538330462</v>
       </c>
       <c r="E37" t="n">
-        <v>90.8502197265625</v>
+        <v>90.85024261474609</v>
       </c>
       <c r="F37" t="n">
-        <v>90.8502197265625</v>
+        <v>90.85024261474609</v>
       </c>
       <c r="G37" t="n">
         <v>2452200</v>
@@ -1300,16 +1300,16 @@
         <v>45345</v>
       </c>
       <c r="C38" t="n">
-        <v>90.87732696533203</v>
+        <v>90.8773193359375</v>
       </c>
       <c r="D38" t="n">
-        <v>90.87732696533203</v>
+        <v>90.8773193359375</v>
       </c>
       <c r="E38" t="n">
-        <v>90.86830108745886</v>
+        <v>90.86829345882208</v>
       </c>
       <c r="F38" t="n">
-        <v>90.87732696533203</v>
+        <v>90.8773193359375</v>
       </c>
       <c r="G38" t="n">
         <v>2010100</v>
@@ -1323,16 +1323,16 @@
         <v>45348</v>
       </c>
       <c r="C39" t="n">
-        <v>90.88637542724609</v>
+        <v>90.8863525390625</v>
       </c>
       <c r="D39" t="n">
-        <v>90.89540819666213</v>
+        <v>90.89538530620379</v>
       </c>
       <c r="E39" t="n">
-        <v>90.88637542724609</v>
+        <v>90.8863525390625</v>
       </c>
       <c r="F39" t="n">
-        <v>90.88637542724609</v>
+        <v>90.8863525390625</v>
       </c>
       <c r="G39" t="n">
         <v>2645100</v>
@@ -1346,16 +1346,16 @@
         <v>45349</v>
       </c>
       <c r="C40" t="n">
-        <v>90.9044189453125</v>
+        <v>90.90443420410156</v>
       </c>
       <c r="D40" t="n">
-        <v>90.9044189453125</v>
+        <v>90.90443420410156</v>
       </c>
       <c r="E40" t="n">
-        <v>90.89538617808456</v>
+        <v>90.89540143535743</v>
       </c>
       <c r="F40" t="n">
-        <v>90.9044189453125</v>
+        <v>90.90443420410156</v>
       </c>
       <c r="G40" t="n">
         <v>2360300</v>
@@ -1369,16 +1369,16 @@
         <v>45350</v>
       </c>
       <c r="C41" t="n">
-        <v>90.9134521484375</v>
+        <v>90.91346740722656</v>
       </c>
       <c r="D41" t="n">
-        <v>90.9134521484375</v>
+        <v>90.91346740722656</v>
       </c>
       <c r="E41" t="n">
-        <v>90.90442627046488</v>
+        <v>90.90444152773905</v>
       </c>
       <c r="F41" t="n">
-        <v>90.90442627046488</v>
+        <v>90.90444152773905</v>
       </c>
       <c r="G41" t="n">
         <v>4526200</v>
@@ -1415,16 +1415,16 @@
         <v>45352</v>
       </c>
       <c r="C43" t="n">
-        <v>90.96771240234375</v>
+        <v>90.96775054931641</v>
       </c>
       <c r="D43" t="n">
-        <v>90.96771240234375</v>
+        <v>90.96775054931641</v>
       </c>
       <c r="E43" t="n">
-        <v>90.95864271080876</v>
+        <v>90.95868085397808</v>
       </c>
       <c r="F43" t="n">
-        <v>90.96771240234375</v>
+        <v>90.96775054931641</v>
       </c>
       <c r="G43" t="n">
         <v>7579200</v>
@@ -1438,16 +1438,16 @@
         <v>45355</v>
       </c>
       <c r="C44" t="n">
-        <v>90.97682952880859</v>
+        <v>90.97678375244141</v>
       </c>
       <c r="D44" t="n">
-        <v>90.98589230692126</v>
+        <v>90.98584652599399</v>
       </c>
       <c r="E44" t="n">
-        <v>90.97682952880859</v>
+        <v>90.97678375244141</v>
       </c>
       <c r="F44" t="n">
-        <v>90.97682952880859</v>
+        <v>90.97678375244141</v>
       </c>
       <c r="G44" t="n">
         <v>3613500</v>
@@ -1461,16 +1461,16 @@
         <v>45356</v>
       </c>
       <c r="C45" t="n">
-        <v>90.98587036132812</v>
+        <v>90.98587799072266</v>
       </c>
       <c r="D45" t="n">
-        <v>90.99494005540443</v>
+        <v>90.99494768555948</v>
       </c>
       <c r="E45" t="n">
-        <v>90.98587036132812</v>
+        <v>90.98587799072266</v>
       </c>
       <c r="F45" t="n">
-        <v>90.98587036132812</v>
+        <v>90.98587799072266</v>
       </c>
       <c r="G45" t="n">
         <v>3905300</v>
@@ -1507,16 +1507,16 @@
         <v>45358</v>
       </c>
       <c r="C47" t="n">
-        <v>91.04934692382812</v>
+        <v>91.04936218261719</v>
       </c>
       <c r="D47" t="n">
-        <v>91.04934692382812</v>
+        <v>91.04936218261719</v>
       </c>
       <c r="E47" t="n">
-        <v>91.04027723018791</v>
+        <v>91.04029248745701</v>
       </c>
       <c r="F47" t="n">
-        <v>91.04934692382812</v>
+        <v>91.04936218261719</v>
       </c>
       <c r="G47" t="n">
         <v>2415500</v>
@@ -1530,16 +1530,16 @@
         <v>45359</v>
       </c>
       <c r="C48" t="n">
-        <v>91.05840301513672</v>
+        <v>91.05841064453125</v>
       </c>
       <c r="D48" t="n">
-        <v>91.06747270811117</v>
+        <v>91.06748033826561</v>
       </c>
       <c r="E48" t="n">
-        <v>91.04934024031101</v>
+        <v>91.0493478689462</v>
       </c>
       <c r="F48" t="n">
-        <v>91.06747270811117</v>
+        <v>91.06748033826561</v>
       </c>
       <c r="G48" t="n">
         <v>3748900</v>
@@ -1553,16 +1553,16 @@
         <v>45362</v>
       </c>
       <c r="C49" t="n">
-        <v>91.07656097412109</v>
+        <v>91.07653045654297</v>
       </c>
       <c r="D49" t="n">
-        <v>91.07656097412109</v>
+        <v>91.07653045654297</v>
       </c>
       <c r="E49" t="n">
-        <v>91.06749127929709</v>
+        <v>91.067460764758</v>
       </c>
       <c r="F49" t="n">
-        <v>91.07656097412109</v>
+        <v>91.07653045654297</v>
       </c>
       <c r="G49" t="n">
         <v>3238400</v>
@@ -1576,16 +1576,16 @@
         <v>45363</v>
       </c>
       <c r="C50" t="n">
-        <v>91.08562469482422</v>
+        <v>91.08561706542969</v>
       </c>
       <c r="D50" t="n">
-        <v>91.09469438974223</v>
+        <v>91.09468675958801</v>
       </c>
       <c r="E50" t="n">
-        <v>91.08562469482422</v>
+        <v>91.08561706542969</v>
       </c>
       <c r="F50" t="n">
-        <v>91.08562469482422</v>
+        <v>91.08561706542969</v>
       </c>
       <c r="G50" t="n">
         <v>2613300</v>
@@ -1599,16 +1599,16 @@
         <v>45364</v>
       </c>
       <c r="C51" t="n">
-        <v>91.09468078613281</v>
+        <v>91.09469604492188</v>
       </c>
       <c r="D51" t="n">
-        <v>91.1037504796964</v>
+        <v>91.10376574000468</v>
       </c>
       <c r="E51" t="n">
-        <v>91.09468078613281</v>
+        <v>91.09469604492188</v>
       </c>
       <c r="F51" t="n">
-        <v>91.09468078613281</v>
+        <v>91.09469604492188</v>
       </c>
       <c r="G51" t="n">
         <v>2249300</v>
@@ -1622,16 +1622,16 @@
         <v>45365</v>
       </c>
       <c r="C52" t="n">
-        <v>91.13095855712891</v>
+        <v>91.13095092773438</v>
       </c>
       <c r="D52" t="n">
-        <v>91.14002825128117</v>
+        <v>91.14002062112732</v>
       </c>
       <c r="E52" t="n">
-        <v>91.13095855712891</v>
+        <v>91.13095092773438</v>
       </c>
       <c r="F52" t="n">
-        <v>91.13095855712891</v>
+        <v>91.13095092773438</v>
       </c>
       <c r="G52" t="n">
         <v>3469600</v>
@@ -1645,16 +1645,16 @@
         <v>45366</v>
       </c>
       <c r="C53" t="n">
-        <v>91.14907836914062</v>
+        <v>91.14908599853516</v>
       </c>
       <c r="D53" t="n">
-        <v>91.14907836914062</v>
+        <v>91.14908599853516</v>
       </c>
       <c r="E53" t="n">
-        <v>91.14001559439656</v>
+        <v>91.14002322303251</v>
       </c>
       <c r="F53" t="n">
-        <v>91.14907836914062</v>
+        <v>91.14908599853516</v>
       </c>
       <c r="G53" t="n">
         <v>3277300</v>
@@ -1668,16 +1668,16 @@
         <v>45369</v>
       </c>
       <c r="C54" t="n">
-        <v>91.15817260742188</v>
+        <v>91.15816497802734</v>
       </c>
       <c r="D54" t="n">
-        <v>91.1672423027567</v>
+        <v>91.1672346726031</v>
       </c>
       <c r="E54" t="n">
-        <v>91.15817260742188</v>
+        <v>91.15816497802734</v>
       </c>
       <c r="F54" t="n">
-        <v>91.1672423027567</v>
+        <v>91.1672346726031</v>
       </c>
       <c r="G54" t="n">
         <v>3576200</v>
@@ -1714,16 +1714,16 @@
         <v>45371</v>
       </c>
       <c r="C56" t="n">
-        <v>91.18537902832031</v>
+        <v>91.18536376953125</v>
       </c>
       <c r="D56" t="n">
-        <v>91.19444872407817</v>
+        <v>91.19443346377142</v>
       </c>
       <c r="E56" t="n">
-        <v>91.18537902832031</v>
+        <v>91.18536376953125</v>
       </c>
       <c r="F56" t="n">
-        <v>91.18537902832031</v>
+        <v>91.18536376953125</v>
       </c>
       <c r="G56" t="n">
         <v>2492700</v>
@@ -1737,16 +1737,16 @@
         <v>45372</v>
       </c>
       <c r="C57" t="n">
-        <v>91.22164154052734</v>
+        <v>91.22163391113281</v>
       </c>
       <c r="D57" t="n">
-        <v>91.23071123535532</v>
+        <v>91.23070360520224</v>
       </c>
       <c r="E57" t="n">
-        <v>91.22164154052734</v>
+        <v>91.22163391113281</v>
       </c>
       <c r="F57" t="n">
-        <v>91.22164154052734</v>
+        <v>91.22163391113281</v>
       </c>
       <c r="G57" t="n">
         <v>3547400</v>
@@ -1760,16 +1760,16 @@
         <v>45373</v>
       </c>
       <c r="C58" t="n">
-        <v>91.23976898193359</v>
+        <v>91.23978424072266</v>
       </c>
       <c r="D58" t="n">
-        <v>91.24883175742463</v>
+        <v>91.24884701772933</v>
       </c>
       <c r="E58" t="n">
-        <v>91.23069928829332</v>
+        <v>91.2307145455656</v>
       </c>
       <c r="F58" t="n">
-        <v>91.24883175742463</v>
+        <v>91.24884701772933</v>
       </c>
       <c r="G58" t="n">
         <v>2636700</v>
@@ -1806,16 +1806,16 @@
         <v>45377</v>
       </c>
       <c r="C60" t="n">
-        <v>91.26697540283203</v>
+        <v>91.26698303222656</v>
       </c>
       <c r="D60" t="n">
-        <v>91.27604509689544</v>
+        <v>91.27605272704815</v>
       </c>
       <c r="E60" t="n">
-        <v>91.26697540283203</v>
+        <v>91.26698303222656</v>
       </c>
       <c r="F60" t="n">
-        <v>91.26697540283203</v>
+        <v>91.26698303222656</v>
       </c>
       <c r="G60" t="n">
         <v>3181700</v>
@@ -1829,16 +1829,16 @@
         <v>45378</v>
       </c>
       <c r="C61" t="n">
-        <v>91.31232452392578</v>
+        <v>91.31230163574219</v>
       </c>
       <c r="D61" t="n">
-        <v>91.32139421942814</v>
+        <v>91.32137132897115</v>
       </c>
       <c r="E61" t="n">
-        <v>91.31232452392578</v>
+        <v>91.31230163574219</v>
       </c>
       <c r="F61" t="n">
-        <v>91.32139421942814</v>
+        <v>91.32137132897115</v>
       </c>
       <c r="G61" t="n">
         <v>2990800</v>
@@ -1852,16 +1852,16 @@
         <v>45379</v>
       </c>
       <c r="C62" t="n">
-        <v>91.32138061523438</v>
+        <v>91.32137298583984</v>
       </c>
       <c r="D62" t="n">
-        <v>91.33045030938563</v>
+        <v>91.33044267923337</v>
       </c>
       <c r="E62" t="n">
-        <v>91.32138061523438</v>
+        <v>91.32137298583984</v>
       </c>
       <c r="F62" t="n">
-        <v>91.33045030938563</v>
+        <v>91.33044267923337</v>
       </c>
       <c r="G62" t="n">
         <v>5425800</v>
@@ -1875,16 +1875,16 @@
         <v>45383</v>
       </c>
       <c r="C63" t="n">
-        <v>91.34871673583984</v>
+        <v>91.34870147705078</v>
       </c>
       <c r="D63" t="n">
-        <v>91.3578271386809</v>
+        <v>91.35781187837004</v>
       </c>
       <c r="E63" t="n">
-        <v>91.34871673583984</v>
+        <v>91.34870147705078</v>
       </c>
       <c r="F63" t="n">
-        <v>91.3578271386809</v>
+        <v>91.35781187837004</v>
       </c>
       <c r="G63" t="n">
         <v>7395400</v>
@@ -1898,16 +1898,16 @@
         <v>45384</v>
       </c>
       <c r="C64" t="n">
-        <v>91.36693572998047</v>
+        <v>91.36691284179688</v>
       </c>
       <c r="D64" t="n">
-        <v>91.36693572998047</v>
+        <v>91.36691284179688</v>
       </c>
       <c r="E64" t="n">
-        <v>91.35783227582876</v>
+        <v>91.35780938992566</v>
       </c>
       <c r="F64" t="n">
-        <v>91.36693572998047</v>
+        <v>91.36691284179688</v>
       </c>
       <c r="G64" t="n">
         <v>4202900</v>
@@ -1921,16 +1921,16 @@
         <v>45385</v>
       </c>
       <c r="C65" t="n">
-        <v>91.37600708007812</v>
+        <v>91.37602996826172</v>
       </c>
       <c r="D65" t="n">
-        <v>91.38511747953777</v>
+        <v>91.38514037000337</v>
       </c>
       <c r="E65" t="n">
-        <v>91.37600708007812</v>
+        <v>91.37602996826172</v>
       </c>
       <c r="F65" t="n">
-        <v>91.37600708007812</v>
+        <v>91.37602996826172</v>
       </c>
       <c r="G65" t="n">
         <v>4333600</v>
@@ -1944,16 +1944,16 @@
         <v>45386</v>
       </c>
       <c r="C66" t="n">
-        <v>91.42158508300781</v>
+        <v>91.42156219482422</v>
       </c>
       <c r="D66" t="n">
-        <v>91.42158508300781</v>
+        <v>91.42156219482422</v>
       </c>
       <c r="E66" t="n">
-        <v>91.41247468026413</v>
+        <v>91.4124517943614</v>
       </c>
       <c r="F66" t="n">
-        <v>91.41247468026413</v>
+        <v>91.4124517943614</v>
       </c>
       <c r="G66" t="n">
         <v>3427500</v>
@@ -1967,16 +1967,16 @@
         <v>45387</v>
       </c>
       <c r="C67" t="n">
-        <v>91.43067932128906</v>
+        <v>91.4306640625</v>
       </c>
       <c r="D67" t="n">
-        <v>91.43978972311452</v>
+        <v>91.43977446280502</v>
       </c>
       <c r="E67" t="n">
-        <v>91.43067932128906</v>
+        <v>91.4306640625</v>
       </c>
       <c r="F67" t="n">
-        <v>91.43978972311452</v>
+        <v>91.43977446280502</v>
       </c>
       <c r="G67" t="n">
         <v>3104200</v>
@@ -1990,16 +1990,16 @@
         <v>45390</v>
       </c>
       <c r="C68" t="n">
-        <v>91.44889831542969</v>
+        <v>91.44889068603516</v>
       </c>
       <c r="D68" t="n">
-        <v>91.44889831542969</v>
+        <v>91.44889068603516</v>
       </c>
       <c r="E68" t="n">
-        <v>91.43978791378451</v>
+        <v>91.43978028515004</v>
       </c>
       <c r="F68" t="n">
-        <v>91.44889831542969</v>
+        <v>91.44889068603516</v>
       </c>
       <c r="G68" t="n">
         <v>3511400</v>
@@ -2036,16 +2036,16 @@
         <v>45392</v>
       </c>
       <c r="C70" t="n">
-        <v>91.47622680664062</v>
+        <v>91.47621154785156</v>
       </c>
       <c r="D70" t="n">
-        <v>91.47622680664062</v>
+        <v>91.47621154785156</v>
       </c>
       <c r="E70" t="n">
-        <v>91.45801295170727</v>
+        <v>91.45799769595641</v>
       </c>
       <c r="F70" t="n">
-        <v>91.46711640457362</v>
+        <v>91.46710114730423</v>
       </c>
       <c r="G70" t="n">
         <v>3893100</v>
@@ -2082,16 +2082,16 @@
         <v>45394</v>
       </c>
       <c r="C72" t="n">
-        <v>91.52175903320312</v>
+        <v>91.52178192138672</v>
       </c>
       <c r="D72" t="n">
-        <v>91.52175903320312</v>
+        <v>91.52178192138672</v>
       </c>
       <c r="E72" t="n">
-        <v>91.51264863241371</v>
+        <v>91.51267151831894</v>
       </c>
       <c r="F72" t="n">
-        <v>91.52175903320312</v>
+        <v>91.52178192138672</v>
       </c>
       <c r="G72" t="n">
         <v>4235400</v>
@@ -2105,16 +2105,16 @@
         <v>45397</v>
       </c>
       <c r="C73" t="n">
-        <v>91.53999328613281</v>
+        <v>91.53997039794922</v>
       </c>
       <c r="D73" t="n">
-        <v>91.53999328613281</v>
+        <v>91.53997039794922</v>
       </c>
       <c r="E73" t="n">
-        <v>91.53088288331307</v>
+        <v>91.53085999740739</v>
       </c>
       <c r="F73" t="n">
-        <v>91.53088288331307</v>
+        <v>91.53085999740739</v>
       </c>
       <c r="G73" t="n">
         <v>4144700</v>
@@ -2128,16 +2128,16 @@
         <v>45398</v>
       </c>
       <c r="C74" t="n">
-        <v>91.53999328613281</v>
+        <v>91.53997039794922</v>
       </c>
       <c r="D74" t="n">
-        <v>91.55820714257106</v>
+        <v>91.55818424983336</v>
       </c>
       <c r="E74" t="n">
-        <v>91.53999328613281</v>
+        <v>91.53997039794922</v>
       </c>
       <c r="F74" t="n">
-        <v>91.54910368895256</v>
+        <v>91.54908079849103</v>
       </c>
       <c r="G74" t="n">
         <v>4850000</v>
@@ -2151,16 +2151,16 @@
         <v>45399</v>
       </c>
       <c r="C75" t="n">
-        <v>91.56732177734375</v>
+        <v>91.56730651855469</v>
       </c>
       <c r="D75" t="n">
-        <v>91.56732177734375</v>
+        <v>91.56730651855469</v>
       </c>
       <c r="E75" t="n">
-        <v>91.55821137410295</v>
+        <v>91.55819611683205</v>
       </c>
       <c r="F75" t="n">
-        <v>91.56732177734375</v>
+        <v>91.56730651855469</v>
       </c>
       <c r="G75" t="n">
         <v>3688400</v>
@@ -2174,16 +2174,16 @@
         <v>45400</v>
       </c>
       <c r="C76" t="n">
-        <v>91.59464263916016</v>
+        <v>91.59463500976562</v>
       </c>
       <c r="D76" t="n">
-        <v>91.60375304206291</v>
+        <v>91.60374541190951</v>
       </c>
       <c r="E76" t="n">
-        <v>91.59464263916016</v>
+        <v>91.59463500976562</v>
       </c>
       <c r="F76" t="n">
-        <v>91.60375304206291</v>
+        <v>91.60374541190951</v>
       </c>
       <c r="G76" t="n">
         <v>3235600</v>
@@ -2197,16 +2197,16 @@
         <v>45401</v>
       </c>
       <c r="C77" t="n">
-        <v>91.62196350097656</v>
+        <v>91.62197875976562</v>
       </c>
       <c r="D77" t="n">
-        <v>91.62196350097656</v>
+        <v>91.62197875976562</v>
       </c>
       <c r="E77" t="n">
-        <v>91.60374964504781</v>
+        <v>91.60376490080353</v>
       </c>
       <c r="F77" t="n">
-        <v>91.62196350097656</v>
+        <v>91.62197875976562</v>
       </c>
       <c r="G77" t="n">
         <v>3319500</v>
@@ -2243,16 +2243,16 @@
         <v>45405</v>
       </c>
       <c r="C79" t="n">
-        <v>91.64018249511719</v>
+        <v>91.64017486572266</v>
       </c>
       <c r="D79" t="n">
-        <v>91.64929289750205</v>
+        <v>91.64928526734903</v>
       </c>
       <c r="E79" t="n">
-        <v>91.63107209273232</v>
+        <v>91.63106446409627</v>
       </c>
       <c r="F79" t="n">
-        <v>91.64018249511719</v>
+        <v>91.64017486572266</v>
       </c>
       <c r="G79" t="n">
         <v>4233300</v>
@@ -2266,16 +2266,16 @@
         <v>45406</v>
       </c>
       <c r="C80" t="n">
-        <v>91.6492919921875</v>
+        <v>91.64927673339844</v>
       </c>
       <c r="D80" t="n">
-        <v>91.65839544528153</v>
+        <v>91.65838018497682</v>
       </c>
       <c r="E80" t="n">
-        <v>91.6492919921875</v>
+        <v>91.64927673339844</v>
       </c>
       <c r="F80" t="n">
-        <v>91.65839544528153</v>
+        <v>91.65838018497682</v>
       </c>
       <c r="G80" t="n">
         <v>3200000</v>
@@ -2289,16 +2289,16 @@
         <v>45407</v>
       </c>
       <c r="C81" t="n">
-        <v>91.69482421875</v>
+        <v>91.69483184814453</v>
       </c>
       <c r="D81" t="n">
-        <v>91.69482421875</v>
+        <v>91.69483184814453</v>
       </c>
       <c r="E81" t="n">
-        <v>91.68572076624038</v>
+        <v>91.68572839487747</v>
       </c>
       <c r="F81" t="n">
-        <v>91.69482421875</v>
+        <v>91.69483184814453</v>
       </c>
       <c r="G81" t="n">
         <v>2705900</v>
@@ -2312,16 +2312,16 @@
         <v>45408</v>
       </c>
       <c r="C82" t="n">
-        <v>91.71306610107422</v>
+        <v>91.71305847167969</v>
       </c>
       <c r="D82" t="n">
-        <v>91.71306610107422</v>
+        <v>91.71305847167969</v>
       </c>
       <c r="E82" t="n">
-        <v>91.70395569727032</v>
+        <v>91.70394806863366</v>
       </c>
       <c r="F82" t="n">
-        <v>91.70395569727032</v>
+        <v>91.70394806863366</v>
       </c>
       <c r="G82" t="n">
         <v>3008600</v>
@@ -2335,16 +2335,16 @@
         <v>45411</v>
       </c>
       <c r="C83" t="n">
-        <v>91.71306610107422</v>
+        <v>91.71305847167969</v>
       </c>
       <c r="D83" t="n">
-        <v>91.72216955567613</v>
+        <v>91.7221619255243</v>
       </c>
       <c r="E83" t="n">
-        <v>91.71306610107422</v>
+        <v>91.71305847167969</v>
       </c>
       <c r="F83" t="n">
-        <v>91.72216955567613</v>
+        <v>91.7221619255243</v>
       </c>
       <c r="G83" t="n">
         <v>2501900</v>
@@ -2358,16 +2358,16 @@
         <v>45412</v>
       </c>
       <c r="C84" t="n">
-        <v>91.72216033935547</v>
+        <v>91.72214508056641</v>
       </c>
       <c r="D84" t="n">
-        <v>91.73127074224395</v>
+        <v>91.73125548193929</v>
       </c>
       <c r="E84" t="n">
-        <v>91.72216033935547</v>
+        <v>91.72214508056641</v>
       </c>
       <c r="F84" t="n">
-        <v>91.72216033935547</v>
+        <v>91.72214508056641</v>
       </c>
       <c r="G84" t="n">
         <v>6488000</v>
@@ -2381,16 +2381,16 @@
         <v>45413</v>
       </c>
       <c r="C85" t="n">
-        <v>91.75691986083984</v>
+        <v>91.75691223144531</v>
       </c>
       <c r="D85" t="n">
-        <v>91.75691986083984</v>
+        <v>91.75691223144531</v>
       </c>
       <c r="E85" t="n">
-        <v>91.74777755015184</v>
+        <v>91.74776992151747</v>
       </c>
       <c r="F85" t="n">
-        <v>91.75691986083984</v>
+        <v>91.75691223144531</v>
       </c>
       <c r="G85" t="n">
         <v>8406600</v>
@@ -2404,16 +2404,16 @@
         <v>45414</v>
       </c>
       <c r="C86" t="n">
-        <v>91.79349517822266</v>
+        <v>91.79351043701172</v>
       </c>
       <c r="D86" t="n">
-        <v>91.79349517822266</v>
+        <v>91.79351043701172</v>
       </c>
       <c r="E86" t="n">
-        <v>91.78434589015285</v>
+        <v>91.78436114742104</v>
       </c>
       <c r="F86" t="n">
-        <v>91.79349517822266</v>
+        <v>91.79351043701172</v>
       </c>
       <c r="G86" t="n">
         <v>4369600</v>
@@ -2427,16 +2427,16 @@
         <v>45415</v>
       </c>
       <c r="C87" t="n">
-        <v>91.81181335449219</v>
+        <v>91.81178283691406</v>
       </c>
       <c r="D87" t="n">
-        <v>91.81181335449219</v>
+        <v>91.81178283691406</v>
       </c>
       <c r="E87" t="n">
-        <v>91.79351477444618</v>
+        <v>91.79348426295037</v>
       </c>
       <c r="F87" t="n">
-        <v>91.80266406446918</v>
+        <v>91.80263354993221</v>
       </c>
       <c r="G87" t="n">
         <v>4792400</v>
@@ -2496,16 +2496,16 @@
         <v>45420</v>
       </c>
       <c r="C90" t="n">
-        <v>91.84840393066406</v>
+        <v>91.848388671875</v>
       </c>
       <c r="D90" t="n">
-        <v>91.84840393066406</v>
+        <v>91.848388671875</v>
       </c>
       <c r="E90" t="n">
-        <v>91.83010535053937</v>
+        <v>91.83009009479026</v>
       </c>
       <c r="F90" t="n">
-        <v>91.83925464060172</v>
+        <v>91.83923938333263</v>
       </c>
       <c r="G90" t="n">
         <v>3109400</v>
@@ -2519,16 +2519,16 @@
         <v>45421</v>
       </c>
       <c r="C91" t="n">
-        <v>91.87583923339844</v>
+        <v>91.87580871582031</v>
       </c>
       <c r="D91" t="n">
-        <v>91.88498154404117</v>
+        <v>91.88495102342632</v>
       </c>
       <c r="E91" t="n">
-        <v>91.87583923339844</v>
+        <v>91.87580871582031</v>
       </c>
       <c r="F91" t="n">
-        <v>91.8804103887198</v>
+        <v>91.88037986962331</v>
       </c>
       <c r="G91" t="n">
         <v>2739600</v>
@@ -2542,16 +2542,16 @@
         <v>45422</v>
       </c>
       <c r="C92" t="n">
-        <v>91.90327453613281</v>
+        <v>91.90326690673828</v>
       </c>
       <c r="D92" t="n">
-        <v>91.90327453613281</v>
+        <v>91.90326690673828</v>
       </c>
       <c r="E92" t="n">
-        <v>91.88497595823358</v>
+        <v>91.88496833035812</v>
       </c>
       <c r="F92" t="n">
-        <v>91.90327453613281</v>
+        <v>91.90326690673828</v>
       </c>
       <c r="G92" t="n">
         <v>3005800</v>
@@ -2565,16 +2565,16 @@
         <v>45425</v>
       </c>
       <c r="C93" t="n">
-        <v>91.91239166259766</v>
+        <v>91.91242980957031</v>
       </c>
       <c r="D93" t="n">
-        <v>91.91239166259766</v>
+        <v>91.91242980957031</v>
       </c>
       <c r="E93" t="n">
-        <v>91.9032423768496</v>
+        <v>91.90328052002498</v>
       </c>
       <c r="F93" t="n">
-        <v>91.91239166259766</v>
+        <v>91.91242980957031</v>
       </c>
       <c r="G93" t="n">
         <v>3317000</v>
@@ -2588,16 +2588,16 @@
         <v>45426</v>
       </c>
       <c r="C94" t="n">
-        <v>91.91239166259766</v>
+        <v>91.91242980957031</v>
       </c>
       <c r="D94" t="n">
-        <v>91.92153396948548</v>
+        <v>91.92157212025253</v>
       </c>
       <c r="E94" t="n">
-        <v>91.91239166259766</v>
+        <v>91.91242980957031</v>
       </c>
       <c r="F94" t="n">
-        <v>91.92153396948548</v>
+        <v>91.92157212025253</v>
       </c>
       <c r="G94" t="n">
         <v>2765800</v>
@@ -2611,16 +2611,16 @@
         <v>45427</v>
       </c>
       <c r="C95" t="n">
-        <v>91.93071746826172</v>
+        <v>91.93070220947266</v>
       </c>
       <c r="D95" t="n">
-        <v>91.93986675741478</v>
+        <v>91.93985149710711</v>
       </c>
       <c r="E95" t="n">
-        <v>91.93071746826172</v>
+        <v>91.93070220947266</v>
       </c>
       <c r="F95" t="n">
-        <v>91.93071746826172</v>
+        <v>91.93070220947266</v>
       </c>
       <c r="G95" t="n">
         <v>4228600</v>
@@ -2634,16 +2634,16 @@
         <v>45428</v>
       </c>
       <c r="C96" t="n">
-        <v>91.97643280029297</v>
+        <v>91.97644805908203</v>
       </c>
       <c r="D96" t="n">
-        <v>91.98557510818425</v>
+        <v>91.98559036849001</v>
       </c>
       <c r="E96" t="n">
-        <v>91.96728351354071</v>
+        <v>91.96729877081192</v>
       </c>
       <c r="F96" t="n">
-        <v>91.97643280029297</v>
+        <v>91.97644805908203</v>
       </c>
       <c r="G96" t="n">
         <v>3699500</v>
@@ -2657,16 +2657,16 @@
         <v>45429</v>
       </c>
       <c r="C97" t="n">
-        <v>91.985595703125</v>
+        <v>91.98558044433594</v>
       </c>
       <c r="D97" t="n">
-        <v>91.99474499192573</v>
+        <v>91.99472973161895</v>
       </c>
       <c r="E97" t="n">
-        <v>91.985595703125</v>
+        <v>91.98558044433594</v>
       </c>
       <c r="F97" t="n">
-        <v>91.99474499192573</v>
+        <v>91.99472973161895</v>
       </c>
       <c r="G97" t="n">
         <v>4544200</v>
@@ -2680,16 +2680,16 @@
         <v>45432</v>
       </c>
       <c r="C98" t="n">
-        <v>91.9947509765625</v>
+        <v>91.99474334716797</v>
       </c>
       <c r="D98" t="n">
-        <v>92.00390026595842</v>
+        <v>92.00389263580512</v>
       </c>
       <c r="E98" t="n">
-        <v>91.9947509765625</v>
+        <v>91.99474334716797</v>
       </c>
       <c r="F98" t="n">
-        <v>92.00390026595842</v>
+        <v>92.00389263580512</v>
       </c>
       <c r="G98" t="n">
         <v>3341000</v>
@@ -2703,16 +2703,16 @@
         <v>45433</v>
       </c>
       <c r="C99" t="n">
-        <v>92.01303863525391</v>
+        <v>92.01303100585938</v>
       </c>
       <c r="D99" t="n">
-        <v>92.02218792425793</v>
+        <v>92.02218029410477</v>
       </c>
       <c r="E99" t="n">
-        <v>92.01303863525391</v>
+        <v>92.01303100585938</v>
       </c>
       <c r="F99" t="n">
-        <v>92.01303863525391</v>
+        <v>92.01303100585938</v>
       </c>
       <c r="G99" t="n">
         <v>3774900</v>
@@ -2749,16 +2749,16 @@
         <v>45435</v>
       </c>
       <c r="C101" t="n">
-        <v>92.08622741699219</v>
+        <v>92.08621978759766</v>
       </c>
       <c r="D101" t="n">
-        <v>92.08622741699219</v>
+        <v>92.08621978759766</v>
       </c>
       <c r="E101" t="n">
-        <v>92.0770851060142</v>
+        <v>92.0770774773771</v>
       </c>
       <c r="F101" t="n">
-        <v>92.0770851060142</v>
+        <v>92.0770774773771</v>
       </c>
       <c r="G101" t="n">
         <v>3077800</v>
@@ -2772,16 +2772,16 @@
         <v>45436</v>
       </c>
       <c r="C102" t="n">
-        <v>92.09535980224609</v>
+        <v>92.09535217285156</v>
       </c>
       <c r="D102" t="n">
-        <v>92.09535980224609</v>
+        <v>92.09535217285156</v>
       </c>
       <c r="E102" t="n">
-        <v>92.08621051408414</v>
+        <v>92.08620288544756</v>
       </c>
       <c r="F102" t="n">
-        <v>92.09535980224609</v>
+        <v>92.09535217285156</v>
       </c>
       <c r="G102" t="n">
         <v>2512800</v>
@@ -2795,16 +2795,16 @@
         <v>45440</v>
       </c>
       <c r="C103" t="n">
-        <v>92.10451507568359</v>
+        <v>92.10449981689453</v>
       </c>
       <c r="D103" t="n">
-        <v>92.10451507568359</v>
+        <v>92.10449981689453</v>
       </c>
       <c r="E103" t="n">
-        <v>92.0953657869271</v>
+        <v>92.09535052965379</v>
       </c>
       <c r="F103" t="n">
-        <v>92.0953657869271</v>
+        <v>92.09535052965379</v>
       </c>
       <c r="G103" t="n">
         <v>3684600</v>
@@ -2818,16 +2818,16 @@
         <v>45441</v>
       </c>
       <c r="C104" t="n">
-        <v>92.10451507568359</v>
+        <v>92.10449981689453</v>
       </c>
       <c r="D104" t="n">
-        <v>92.11365738557757</v>
+        <v>92.11364212527393</v>
       </c>
       <c r="E104" t="n">
-        <v>92.10451507568359</v>
+        <v>92.10449981689453</v>
       </c>
       <c r="F104" t="n">
-        <v>92.11365738557757</v>
+        <v>92.11364212527393</v>
       </c>
       <c r="G104" t="n">
         <v>3971700</v>
@@ -2841,16 +2841,16 @@
         <v>45442</v>
       </c>
       <c r="C105" t="n">
-        <v>92.122802734375</v>
+        <v>92.12279510498047</v>
       </c>
       <c r="D105" t="n">
-        <v>92.13195202274019</v>
+        <v>92.13194439258794</v>
       </c>
       <c r="E105" t="n">
-        <v>92.122802734375</v>
+        <v>92.12279510498047</v>
       </c>
       <c r="F105" t="n">
-        <v>92.122802734375</v>
+        <v>92.12279510498047</v>
       </c>
       <c r="G105" t="n">
         <v>3566800</v>
@@ -2864,16 +2864,16 @@
         <v>45443</v>
       </c>
       <c r="C106" t="n">
-        <v>92.15940856933594</v>
+        <v>92.15937805175781</v>
       </c>
       <c r="D106" t="n">
-        <v>92.15940856933594</v>
+        <v>92.15937805175781</v>
       </c>
       <c r="E106" t="n">
-        <v>92.15025927941603</v>
+        <v>92.15022876486761</v>
       </c>
       <c r="F106" t="n">
-        <v>92.15025927941603</v>
+        <v>92.15022876486761</v>
       </c>
       <c r="G106" t="n">
         <v>7082900</v>
@@ -2910,16 +2910,16 @@
         <v>45447</v>
       </c>
       <c r="C108" t="n">
-        <v>92.19615173339844</v>
+        <v>92.19612121582031</v>
       </c>
       <c r="D108" t="n">
-        <v>92.19615173339844</v>
+        <v>92.19612121582031</v>
       </c>
       <c r="E108" t="n">
-        <v>92.18696231153911</v>
+        <v>92.18693179700274</v>
       </c>
       <c r="F108" t="n">
-        <v>92.19615173339844</v>
+        <v>92.19612121582031</v>
       </c>
       <c r="G108" t="n">
         <v>5355900</v>
@@ -2933,16 +2933,16 @@
         <v>45448</v>
       </c>
       <c r="C109" t="n">
-        <v>92.21454620361328</v>
+        <v>92.21450042724609</v>
       </c>
       <c r="D109" t="n">
-        <v>92.21454620361328</v>
+        <v>92.21450042724609</v>
       </c>
       <c r="E109" t="n">
-        <v>92.20535678019672</v>
+        <v>92.20531100839128</v>
       </c>
       <c r="F109" t="n">
-        <v>92.20535678019672</v>
+        <v>92.20531100839128</v>
       </c>
       <c r="G109" t="n">
         <v>4285300</v>
@@ -2956,16 +2956,16 @@
         <v>45449</v>
       </c>
       <c r="C110" t="n">
-        <v>92.21454620361328</v>
+        <v>92.21450042724609</v>
       </c>
       <c r="D110" t="n">
-        <v>92.22372861755355</v>
+        <v>92.22368283662811</v>
       </c>
       <c r="E110" t="n">
-        <v>92.21454620361328</v>
+        <v>92.21450042724609</v>
       </c>
       <c r="F110" t="n">
-        <v>92.22372861755355</v>
+        <v>92.22368283662811</v>
       </c>
       <c r="G110" t="n">
         <v>3376100</v>
@@ -2979,16 +2979,16 @@
         <v>45450</v>
       </c>
       <c r="C111" t="n">
-        <v>92.25128173828125</v>
+        <v>92.25127410888672</v>
       </c>
       <c r="D111" t="n">
-        <v>92.26046415071357</v>
+        <v>92.26045652055964</v>
       </c>
       <c r="E111" t="n">
-        <v>92.25128173828125</v>
+        <v>92.25127410888672</v>
       </c>
       <c r="F111" t="n">
-        <v>92.26046415071357</v>
+        <v>92.26045652055964</v>
       </c>
       <c r="G111" t="n">
         <v>3490400</v>
@@ -3002,16 +3002,16 @@
         <v>45453</v>
       </c>
       <c r="C112" t="n">
-        <v>92.26963806152344</v>
+        <v>92.2696533203125</v>
       </c>
       <c r="D112" t="n">
-        <v>92.27882748188611</v>
+        <v>92.27884274219484</v>
       </c>
       <c r="E112" t="n">
-        <v>92.26963806152344</v>
+        <v>92.2696533203125</v>
       </c>
       <c r="F112" t="n">
-        <v>92.27882748188611</v>
+        <v>92.27884274219484</v>
       </c>
       <c r="G112" t="n">
         <v>2732300</v>
@@ -3025,16 +3025,16 @@
         <v>45454</v>
       </c>
       <c r="C113" t="n">
-        <v>92.28802490234375</v>
+        <v>92.28801727294922</v>
       </c>
       <c r="D113" t="n">
-        <v>92.28802490234375</v>
+        <v>92.28801727294922</v>
       </c>
       <c r="E113" t="n">
-        <v>92.27884248996163</v>
+        <v>92.2788348613262</v>
       </c>
       <c r="F113" t="n">
-        <v>92.28802490234375</v>
+        <v>92.28801727294922</v>
       </c>
       <c r="G113" t="n">
         <v>3320000</v>
@@ -3048,16 +3048,16 @@
         <v>45455</v>
       </c>
       <c r="C114" t="n">
-        <v>92.30638122558594</v>
+        <v>92.30640411376953</v>
       </c>
       <c r="D114" t="n">
-        <v>92.30638122558594</v>
+        <v>92.30640411376953</v>
       </c>
       <c r="E114" t="n">
-        <v>92.28800238635547</v>
+        <v>92.28802526998187</v>
       </c>
       <c r="F114" t="n">
-        <v>92.2971918059707</v>
+        <v>92.29721469187569</v>
       </c>
       <c r="G114" t="n">
         <v>5355700</v>
@@ -3071,16 +3071,16 @@
         <v>45456</v>
       </c>
       <c r="C115" t="n">
-        <v>92.31556701660156</v>
+        <v>92.31558990478516</v>
       </c>
       <c r="D115" t="n">
-        <v>92.32474942638248</v>
+        <v>92.32477231684271</v>
       </c>
       <c r="E115" t="n">
-        <v>92.30637759734753</v>
+        <v>92.30640048325276</v>
       </c>
       <c r="F115" t="n">
-        <v>92.31556701660156</v>
+        <v>92.31558990478516</v>
       </c>
       <c r="G115" t="n">
         <v>3925700</v>
@@ -3094,16 +3094,16 @@
         <v>45457</v>
       </c>
       <c r="C116" t="n">
-        <v>92.36151123046875</v>
+        <v>92.36152648925781</v>
       </c>
       <c r="D116" t="n">
-        <v>92.36151123046875</v>
+        <v>92.36152648925781</v>
       </c>
       <c r="E116" t="n">
-        <v>92.34313939921861</v>
+        <v>92.34315465497252</v>
       </c>
       <c r="F116" t="n">
-        <v>92.3523218101067</v>
+        <v>92.3523370673776</v>
       </c>
       <c r="G116" t="n">
         <v>3505500</v>
@@ -3117,16 +3117,16 @@
         <v>45460</v>
       </c>
       <c r="C117" t="n">
-        <v>92.37071228027344</v>
+        <v>92.37069702148438</v>
       </c>
       <c r="D117" t="n">
-        <v>92.37071228027344</v>
+        <v>92.37069702148438</v>
       </c>
       <c r="E117" t="n">
-        <v>92.36152285875446</v>
+        <v>92.3615076014834</v>
       </c>
       <c r="F117" t="n">
-        <v>92.37071228027344</v>
+        <v>92.37069702148438</v>
       </c>
       <c r="G117" t="n">
         <v>3493700</v>
@@ -3140,16 +3140,16 @@
         <v>45461</v>
       </c>
       <c r="C118" t="n">
-        <v>92.39827728271484</v>
+        <v>92.39825439453125</v>
       </c>
       <c r="D118" t="n">
-        <v>92.39827728271484</v>
+        <v>92.39825439453125</v>
       </c>
       <c r="E118" t="n">
-        <v>92.38908786082315</v>
+        <v>92.3890649749159</v>
       </c>
       <c r="F118" t="n">
-        <v>92.39827728271484</v>
+        <v>92.39825439453125</v>
       </c>
       <c r="G118" t="n">
         <v>2972000</v>
@@ -3186,16 +3186,16 @@
         <v>45464</v>
       </c>
       <c r="C120" t="n">
-        <v>92.44419097900391</v>
+        <v>92.44419860839844</v>
       </c>
       <c r="D120" t="n">
-        <v>92.4533733887978</v>
+        <v>92.45338101895015</v>
       </c>
       <c r="E120" t="n">
-        <v>92.44419097900391</v>
+        <v>92.44419860839844</v>
       </c>
       <c r="F120" t="n">
-        <v>92.44419097900391</v>
+        <v>92.44419860839844</v>
       </c>
       <c r="G120" t="n">
         <v>3460900</v>
@@ -3255,16 +3255,16 @@
         <v>45469</v>
       </c>
       <c r="C123" t="n">
-        <v>92.48094177246094</v>
+        <v>92.48097229003906</v>
       </c>
       <c r="D123" t="n">
-        <v>92.49012418226734</v>
+        <v>92.49015470287554</v>
       </c>
       <c r="E123" t="n">
-        <v>92.48094177246094</v>
+        <v>92.48097229003906</v>
       </c>
       <c r="F123" t="n">
-        <v>92.48186001344158</v>
+        <v>92.4818905313227</v>
       </c>
       <c r="G123" t="n">
         <v>4815500</v>
@@ -3301,16 +3301,16 @@
         <v>45471</v>
       </c>
       <c r="C125" t="n">
-        <v>92.52687835693359</v>
+        <v>92.52688598632812</v>
       </c>
       <c r="D125" t="n">
-        <v>92.53606777656142</v>
+        <v>92.53607540671368</v>
       </c>
       <c r="E125" t="n">
-        <v>92.52687835693359</v>
+        <v>92.52688598632812</v>
       </c>
       <c r="F125" t="n">
-        <v>92.52687835693359</v>
+        <v>92.52688598632812</v>
       </c>
       <c r="G125" t="n">
         <v>7427800</v>
@@ -3324,16 +3324,16 @@
         <v>45474</v>
       </c>
       <c r="C126" t="n">
-        <v>92.56288909912109</v>
+        <v>92.56288146972656</v>
       </c>
       <c r="D126" t="n">
-        <v>92.56288909912109</v>
+        <v>92.56288146972656</v>
       </c>
       <c r="E126" t="n">
-        <v>92.55366648472202</v>
+        <v>92.55365885608765</v>
       </c>
       <c r="F126" t="n">
-        <v>92.56288909912109</v>
+        <v>92.56288146972656</v>
       </c>
       <c r="G126" t="n">
         <v>9965300</v>
@@ -3347,16 +3347,16 @@
         <v>45475</v>
       </c>
       <c r="C127" t="n">
-        <v>92.57212066650391</v>
+        <v>92.57211303710938</v>
       </c>
       <c r="D127" t="n">
-        <v>92.57212066650391</v>
+        <v>92.57211303710938</v>
       </c>
       <c r="E127" t="n">
-        <v>92.56289101175045</v>
+        <v>92.5628833831166</v>
       </c>
       <c r="F127" t="n">
-        <v>92.57212066650391</v>
+        <v>92.57211303710938</v>
       </c>
       <c r="G127" t="n">
         <v>5720900</v>
@@ -3416,16 +3416,16 @@
         <v>45481</v>
       </c>
       <c r="C130" t="n">
-        <v>92.65515899658203</v>
+        <v>92.6551513671875</v>
       </c>
       <c r="D130" t="n">
-        <v>92.65515899658203</v>
+        <v>92.6551513671875</v>
       </c>
       <c r="E130" t="n">
-        <v>92.64592934327121</v>
+        <v>92.64592171463667</v>
       </c>
       <c r="F130" t="n">
-        <v>92.64592934327121</v>
+        <v>92.64592171463667</v>
       </c>
       <c r="G130" t="n">
         <v>3263000</v>
@@ -3439,16 +3439,16 @@
         <v>45482</v>
       </c>
       <c r="C131" t="n">
-        <v>92.65515899658203</v>
+        <v>92.6551513671875</v>
       </c>
       <c r="D131" t="n">
-        <v>92.67361126304097</v>
+        <v>92.67360363212704</v>
       </c>
       <c r="E131" t="n">
-        <v>92.65515899658203</v>
+        <v>92.6551513671875</v>
       </c>
       <c r="F131" t="n">
-        <v>92.66438160973014</v>
+        <v>92.66437397957621</v>
       </c>
       <c r="G131" t="n">
         <v>4508000</v>
@@ -3462,16 +3462,16 @@
         <v>45483</v>
       </c>
       <c r="C132" t="n">
-        <v>92.67362213134766</v>
+        <v>92.673583984375</v>
       </c>
       <c r="D132" t="n">
-        <v>92.68285178574088</v>
+        <v>92.68281363496905</v>
       </c>
       <c r="E132" t="n">
-        <v>92.67362213134766</v>
+        <v>92.673583984375</v>
       </c>
       <c r="F132" t="n">
-        <v>92.67362213134766</v>
+        <v>92.673583984375</v>
       </c>
       <c r="G132" t="n">
         <v>4062200</v>
@@ -3485,16 +3485,16 @@
         <v>45484</v>
       </c>
       <c r="C133" t="n">
-        <v>92.69207000732422</v>
+        <v>92.69205474853516</v>
       </c>
       <c r="D133" t="n">
-        <v>92.69207000732422</v>
+        <v>92.69205474853516</v>
       </c>
       <c r="E133" t="n">
-        <v>92.68284739353157</v>
+        <v>92.68283213626073</v>
       </c>
       <c r="F133" t="n">
-        <v>92.68284739353157</v>
+        <v>92.68283213626073</v>
       </c>
       <c r="G133" t="n">
         <v>4195600</v>
@@ -3508,16 +3508,16 @@
         <v>45485</v>
       </c>
       <c r="C134" t="n">
-        <v>92.73818206787109</v>
+        <v>92.73819732666016</v>
       </c>
       <c r="D134" t="n">
-        <v>92.73818206787109</v>
+        <v>92.73819732666016</v>
       </c>
       <c r="E134" t="n">
-        <v>92.72895241681827</v>
+        <v>92.72896767408872</v>
       </c>
       <c r="F134" t="n">
-        <v>92.73818206787109</v>
+        <v>92.73819732666016</v>
       </c>
       <c r="G134" t="n">
         <v>3369000</v>
@@ -3531,16 +3531,16 @@
         <v>45488</v>
       </c>
       <c r="C135" t="n">
-        <v>92.73818206787109</v>
+        <v>92.73819732666016</v>
       </c>
       <c r="D135" t="n">
-        <v>92.74741171892393</v>
+        <v>92.74742697923159</v>
       </c>
       <c r="E135" t="n">
-        <v>92.73818206787109</v>
+        <v>92.73819732666016</v>
       </c>
       <c r="F135" t="n">
-        <v>92.74741171892393</v>
+        <v>92.74742697923159</v>
       </c>
       <c r="G135" t="n">
         <v>3615100</v>
@@ -3577,16 +3577,16 @@
         <v>45490</v>
       </c>
       <c r="C137" t="n">
-        <v>92.76589965820312</v>
+        <v>92.76588439941406</v>
       </c>
       <c r="D137" t="n">
-        <v>92.77051800558623</v>
+        <v>92.77050274603751</v>
       </c>
       <c r="E137" t="n">
-        <v>92.75667000360062</v>
+        <v>92.75665474632972</v>
       </c>
       <c r="F137" t="n">
-        <v>92.76589965820312</v>
+        <v>92.76588439941406</v>
       </c>
       <c r="G137" t="n">
         <v>3822100</v>
@@ -3600,16 +3600,16 @@
         <v>45491</v>
       </c>
       <c r="C138" t="n">
-        <v>92.78433990478516</v>
+        <v>92.78434753417969</v>
       </c>
       <c r="D138" t="n">
-        <v>92.78433990478516</v>
+        <v>92.78434753417969</v>
       </c>
       <c r="E138" t="n">
-        <v>92.77511025207889</v>
+        <v>92.77511788071449</v>
       </c>
       <c r="F138" t="n">
-        <v>92.77511025207889</v>
+        <v>92.77511788071449</v>
       </c>
       <c r="G138" t="n">
         <v>5291400</v>
@@ -3623,16 +3623,16 @@
         <v>45492</v>
       </c>
       <c r="C139" t="n">
-        <v>92.82124328613281</v>
+        <v>92.82125854492188</v>
       </c>
       <c r="D139" t="n">
-        <v>92.82124328613281</v>
+        <v>92.82125854492188</v>
       </c>
       <c r="E139" t="n">
-        <v>92.81202067370296</v>
+        <v>92.81203593097594</v>
       </c>
       <c r="F139" t="n">
-        <v>92.82124328613281</v>
+        <v>92.82125854492188</v>
       </c>
       <c r="G139" t="n">
         <v>2993600</v>
@@ -3646,16 +3646,16 @@
         <v>45495</v>
       </c>
       <c r="C140" t="n">
-        <v>92.8397216796875</v>
+        <v>92.83971405029297</v>
       </c>
       <c r="D140" t="n">
-        <v>92.8397216796875</v>
+        <v>92.83971405029297</v>
       </c>
       <c r="E140" t="n">
-        <v>92.83049202519783</v>
+        <v>92.83048439656177</v>
       </c>
       <c r="F140" t="n">
-        <v>92.8397216796875</v>
+        <v>92.83971405029297</v>
       </c>
       <c r="G140" t="n">
         <v>3386500</v>
@@ -3669,16 +3669,16 @@
         <v>45496</v>
       </c>
       <c r="C141" t="n">
-        <v>92.84893798828125</v>
+        <v>92.84896087646484</v>
       </c>
       <c r="D141" t="n">
-        <v>92.85816060128167</v>
+        <v>92.85818349173874</v>
       </c>
       <c r="E141" t="n">
-        <v>92.83970833511823</v>
+        <v>92.83973122102663</v>
       </c>
       <c r="F141" t="n">
-        <v>92.84893798828125</v>
+        <v>92.84896087646484</v>
       </c>
       <c r="G141" t="n">
         <v>2829200</v>
@@ -3715,16 +3715,16 @@
         <v>45498</v>
       </c>
       <c r="C143" t="n">
-        <v>92.87661743164062</v>
+        <v>92.87662506103516</v>
       </c>
       <c r="D143" t="n">
-        <v>92.87661743164062</v>
+        <v>92.87662506103516</v>
       </c>
       <c r="E143" t="n">
-        <v>92.86738777872365</v>
+        <v>92.86739540736002</v>
       </c>
       <c r="F143" t="n">
-        <v>92.87661743164062</v>
+        <v>92.87662506103516</v>
       </c>
       <c r="G143" t="n">
         <v>3521700</v>
@@ -3738,16 +3738,16 @@
         <v>45499</v>
       </c>
       <c r="C144" t="n">
-        <v>92.90430450439453</v>
+        <v>92.904296875</v>
       </c>
       <c r="D144" t="n">
-        <v>92.91353415782355</v>
+        <v>92.91352652767107</v>
       </c>
       <c r="E144" t="n">
-        <v>92.90430450439453</v>
+        <v>92.904296875</v>
       </c>
       <c r="F144" t="n">
-        <v>92.90430450439453</v>
+        <v>92.904296875</v>
       </c>
       <c r="G144" t="n">
         <v>3172600</v>
@@ -3761,16 +3761,16 @@
         <v>45502</v>
       </c>
       <c r="C145" t="n">
-        <v>92.93197631835938</v>
+        <v>92.93198394775391</v>
       </c>
       <c r="D145" t="n">
-        <v>92.93197631835938</v>
+        <v>92.93198394775391</v>
       </c>
       <c r="E145" t="n">
-        <v>92.92274666593407</v>
+        <v>92.92275429457088</v>
       </c>
       <c r="F145" t="n">
-        <v>92.92274666593407</v>
+        <v>92.92275429457088</v>
       </c>
       <c r="G145" t="n">
         <v>3259000</v>
@@ -3784,16 +3784,16 @@
         <v>45503</v>
       </c>
       <c r="C146" t="n">
-        <v>92.93197631835938</v>
+        <v>92.93198394775391</v>
       </c>
       <c r="D146" t="n">
-        <v>92.94120597078468</v>
+        <v>92.94121360093693</v>
       </c>
       <c r="E146" t="n">
-        <v>92.93197631835938</v>
+        <v>92.93198394775391</v>
       </c>
       <c r="F146" t="n">
-        <v>92.94120597078468</v>
+        <v>92.94121360093693</v>
       </c>
       <c r="G146" t="n">
         <v>4559900</v>
@@ -3830,16 +3830,16 @@
         <v>45505</v>
       </c>
       <c r="C148" t="n">
-        <v>92.97179412841797</v>
+        <v>92.97180938720703</v>
       </c>
       <c r="D148" t="n">
-        <v>92.97179412841797</v>
+        <v>92.97180938720703</v>
       </c>
       <c r="E148" t="n">
-        <v>92.96252277724977</v>
+        <v>92.96253803451719</v>
       </c>
       <c r="F148" t="n">
-        <v>92.97179412841797</v>
+        <v>92.97180938720703</v>
       </c>
       <c r="G148" t="n">
         <v>11015600</v>
@@ -3853,16 +3853,16 @@
         <v>45506</v>
       </c>
       <c r="C149" t="n">
-        <v>93.01814270019531</v>
+        <v>93.01812744140625</v>
       </c>
       <c r="D149" t="n">
-        <v>93.01814270019531</v>
+        <v>93.01812744140625</v>
       </c>
       <c r="E149" t="n">
-        <v>92.99960706864016</v>
+        <v>92.99959181289171</v>
       </c>
       <c r="F149" t="n">
-        <v>93.00887134843308</v>
+        <v>93.00885609116492</v>
       </c>
       <c r="G149" t="n">
         <v>7927400</v>
@@ -3876,16 +3876,16 @@
         <v>45509</v>
       </c>
       <c r="C150" t="n">
-        <v>93.02741241455078</v>
+        <v>93.02742767333984</v>
       </c>
       <c r="D150" t="n">
-        <v>93.04594804577968</v>
+        <v>93.04596330760904</v>
       </c>
       <c r="E150" t="n">
-        <v>93.01814106295174</v>
+        <v>93.01815632022007</v>
       </c>
       <c r="F150" t="n">
-        <v>93.01814106295174</v>
+        <v>93.01815632022007</v>
       </c>
       <c r="G150" t="n">
         <v>8712900</v>
@@ -3945,16 +3945,16 @@
         <v>45512</v>
       </c>
       <c r="C153" t="n">
-        <v>93.07376098632812</v>
+        <v>93.07375335693359</v>
       </c>
       <c r="D153" t="n">
-        <v>93.07376098632812</v>
+        <v>93.07375335693359</v>
       </c>
       <c r="E153" t="n">
-        <v>93.05521828335203</v>
+        <v>93.05521065547747</v>
       </c>
       <c r="F153" t="n">
-        <v>93.06448963484009</v>
+        <v>93.06448200620552</v>
       </c>
       <c r="G153" t="n">
         <v>3903300</v>
@@ -3968,16 +3968,16 @@
         <v>45513</v>
       </c>
       <c r="C154" t="n">
-        <v>93.10157775878906</v>
+        <v>93.10158538818359</v>
       </c>
       <c r="D154" t="n">
-        <v>93.11084203928218</v>
+        <v>93.11084966943589</v>
       </c>
       <c r="E154" t="n">
-        <v>93.0923064063261</v>
+        <v>93.09231403496088</v>
       </c>
       <c r="F154" t="n">
-        <v>93.10157775878906</v>
+        <v>93.10158538818359</v>
       </c>
       <c r="G154" t="n">
         <v>5548300</v>
@@ -4014,16 +4014,16 @@
         <v>45517</v>
       </c>
       <c r="C156" t="n">
-        <v>93.13864898681641</v>
+        <v>93.13865661621094</v>
       </c>
       <c r="D156" t="n">
-        <v>93.13864898681641</v>
+        <v>93.13865661621094</v>
       </c>
       <c r="E156" t="n">
-        <v>93.12937763506119</v>
+        <v>93.12938526369626</v>
       </c>
       <c r="F156" t="n">
-        <v>93.13864898681641</v>
+        <v>93.13865661621094</v>
       </c>
       <c r="G156" t="n">
         <v>4782200</v>
@@ -4037,16 +4037,16 @@
         <v>45518</v>
       </c>
       <c r="C157" t="n">
-        <v>93.15717315673828</v>
+        <v>93.15718078613281</v>
       </c>
       <c r="D157" t="n">
-        <v>93.15717315673828</v>
+        <v>93.15718078613281</v>
       </c>
       <c r="E157" t="n">
-        <v>93.13863752747767</v>
+        <v>93.13864515535418</v>
       </c>
       <c r="F157" t="n">
-        <v>93.14790180612377</v>
+        <v>93.14790943475899</v>
       </c>
       <c r="G157" t="n">
         <v>4327700</v>
@@ -4106,16 +4106,16 @@
         <v>45523</v>
       </c>
       <c r="C160" t="n">
-        <v>93.21280670166016</v>
+        <v>93.21282196044922</v>
       </c>
       <c r="D160" t="n">
-        <v>93.22207805422271</v>
+        <v>93.22209331452947</v>
       </c>
       <c r="E160" t="n">
-        <v>93.21280670166016</v>
+        <v>93.21282196044922</v>
       </c>
       <c r="F160" t="n">
-        <v>93.21280670166016</v>
+        <v>93.21282196044922</v>
       </c>
       <c r="G160" t="n">
         <v>3930700</v>
@@ -4129,16 +4129,16 @@
         <v>45524</v>
       </c>
       <c r="C161" t="n">
-        <v>93.22208404541016</v>
+        <v>93.22206878662109</v>
       </c>
       <c r="D161" t="n">
-        <v>93.23135539856855</v>
+        <v>93.23134013826194</v>
       </c>
       <c r="E161" t="n">
-        <v>93.22208404541016</v>
+        <v>93.22206878662109</v>
       </c>
       <c r="F161" t="n">
-        <v>93.23135539856855</v>
+        <v>93.23134013826194</v>
       </c>
       <c r="G161" t="n">
         <v>3084200</v>
@@ -4152,16 +4152,16 @@
         <v>45525</v>
       </c>
       <c r="C162" t="n">
-        <v>93.2498779296875</v>
+        <v>93.24988555908203</v>
       </c>
       <c r="D162" t="n">
-        <v>93.2498779296875</v>
+        <v>93.24988555908203</v>
       </c>
       <c r="E162" t="n">
-        <v>93.23134229794566</v>
+        <v>93.23134992582368</v>
       </c>
       <c r="F162" t="n">
-        <v>93.23134229794566</v>
+        <v>93.23134992582368</v>
       </c>
       <c r="G162" t="n">
         <v>3936000</v>
@@ -4175,16 +4175,16 @@
         <v>45526</v>
       </c>
       <c r="C163" t="n">
-        <v>93.2498779296875</v>
+        <v>93.24988555908203</v>
       </c>
       <c r="D163" t="n">
-        <v>93.2591492815431</v>
+        <v>93.25915691169619</v>
       </c>
       <c r="E163" t="n">
-        <v>93.2498779296875</v>
+        <v>93.24988555908203</v>
       </c>
       <c r="F163" t="n">
-        <v>93.2591492815431</v>
+        <v>93.25915691169619</v>
       </c>
       <c r="G163" t="n">
         <v>3849100</v>
@@ -4221,16 +4221,16 @@
         <v>45530</v>
       </c>
       <c r="C165" t="n">
-        <v>93.30548858642578</v>
+        <v>93.30550384521484</v>
       </c>
       <c r="D165" t="n">
-        <v>93.31475286528115</v>
+        <v>93.31476812558525</v>
       </c>
       <c r="E165" t="n">
-        <v>93.30548858642578</v>
+        <v>93.30550384521484</v>
       </c>
       <c r="F165" t="n">
-        <v>93.30548858642578</v>
+        <v>93.30550384521484</v>
       </c>
       <c r="G165" t="n">
         <v>3969000</v>
@@ -4244,16 +4244,16 @@
         <v>45531</v>
       </c>
       <c r="C166" t="n">
-        <v>93.31476593017578</v>
+        <v>93.31477355957031</v>
       </c>
       <c r="D166" t="n">
-        <v>93.32403728229781</v>
+        <v>93.32404491245036</v>
       </c>
       <c r="E166" t="n">
-        <v>93.31476593017578</v>
+        <v>93.31477355957031</v>
       </c>
       <c r="F166" t="n">
-        <v>93.32403728229781</v>
+        <v>93.32404491245036</v>
       </c>
       <c r="G166" t="n">
         <v>2818100</v>
@@ -4267,16 +4267,16 @@
         <v>45532</v>
       </c>
       <c r="C167" t="n">
-        <v>93.32403564453125</v>
+        <v>93.32404327392578</v>
       </c>
       <c r="D167" t="n">
-        <v>93.33330699649056</v>
+        <v>93.33331462664304</v>
       </c>
       <c r="E167" t="n">
-        <v>93.32403564453125</v>
+        <v>93.32404327392578</v>
       </c>
       <c r="F167" t="n">
-        <v>93.33330699649056</v>
+        <v>93.33331462664304</v>
       </c>
       <c r="G167" t="n">
         <v>3500800</v>
@@ -4290,16 +4290,16 @@
         <v>45533</v>
       </c>
       <c r="C168" t="n">
-        <v>93.33332061767578</v>
+        <v>93.33330535888672</v>
       </c>
       <c r="D168" t="n">
-        <v>93.35185625233008</v>
+        <v>93.35184099051068</v>
       </c>
       <c r="E168" t="n">
-        <v>93.33332061767578</v>
+        <v>93.33330535888672</v>
       </c>
       <c r="F168" t="n">
-        <v>93.34258489901768</v>
+        <v>93.34256963871402</v>
       </c>
       <c r="G168" t="n">
         <v>4537700</v>
@@ -4313,16 +4313,16 @@
         <v>45534</v>
       </c>
       <c r="C169" t="n">
-        <v>93.37964630126953</v>
+        <v>93.37966918945312</v>
       </c>
       <c r="D169" t="n">
-        <v>93.3889176529001</v>
+        <v>93.3889405433562</v>
       </c>
       <c r="E169" t="n">
-        <v>93.37964630126953</v>
+        <v>93.37966918945312</v>
       </c>
       <c r="F169" t="n">
-        <v>93.37964630126953</v>
+        <v>93.37966918945312</v>
       </c>
       <c r="G169" t="n">
         <v>8427400</v>
@@ -4359,16 +4359,16 @@
         <v>45539</v>
       </c>
       <c r="C171" t="n">
-        <v>93.42992401123047</v>
+        <v>93.42990875244141</v>
       </c>
       <c r="D171" t="n">
-        <v>93.43923640626956</v>
+        <v>93.43922114595962</v>
       </c>
       <c r="E171" t="n">
-        <v>93.42992401123047</v>
+        <v>93.42990875244141</v>
       </c>
       <c r="F171" t="n">
-        <v>93.43923640626956</v>
+        <v>93.43922114595962</v>
       </c>
       <c r="G171" t="n">
         <v>7218300</v>
@@ -4382,16 +4382,16 @@
         <v>45540</v>
       </c>
       <c r="C172" t="n">
-        <v>93.45786285400391</v>
+        <v>93.45784759521484</v>
       </c>
       <c r="D172" t="n">
-        <v>93.45786285400391</v>
+        <v>93.45784759521484</v>
       </c>
       <c r="E172" t="n">
-        <v>93.43924516545663</v>
+        <v>93.43922990970727</v>
       </c>
       <c r="F172" t="n">
-        <v>93.44855756136867</v>
+        <v>93.44854230409888</v>
       </c>
       <c r="G172" t="n">
         <v>4833300</v>
@@ -4428,16 +4428,16 @@
         <v>45544</v>
       </c>
       <c r="C174" t="n">
-        <v>93.50442504882812</v>
+        <v>93.50439453125</v>
       </c>
       <c r="D174" t="n">
-        <v>93.51373744546905</v>
+        <v>93.51370692485159</v>
       </c>
       <c r="E174" t="n">
-        <v>93.50442504882812</v>
+        <v>93.50439453125</v>
       </c>
       <c r="F174" t="n">
-        <v>93.50442504882812</v>
+        <v>93.50439453125</v>
       </c>
       <c r="G174" t="n">
         <v>5397400</v>
@@ -4497,16 +4497,16 @@
         <v>45547</v>
       </c>
       <c r="C177" t="n">
-        <v>93.53232574462891</v>
+        <v>93.53235626220703</v>
       </c>
       <c r="D177" t="n">
-        <v>93.54163813834359</v>
+        <v>93.54166865896013</v>
       </c>
       <c r="E177" t="n">
-        <v>93.53232574462891</v>
+        <v>93.53235626220703</v>
       </c>
       <c r="F177" t="n">
-        <v>93.54163813834359</v>
+        <v>93.54166865896013</v>
       </c>
       <c r="G177" t="n">
         <v>3912400</v>
@@ -4589,16 +4589,16 @@
         <v>45553</v>
       </c>
       <c r="C181" t="n">
-        <v>93.63475799560547</v>
+        <v>93.634765625</v>
       </c>
       <c r="D181" t="n">
-        <v>93.64407039103374</v>
+        <v>93.64407802118704</v>
       </c>
       <c r="E181" t="n">
-        <v>93.6254456001772</v>
+        <v>93.62545322881296</v>
       </c>
       <c r="F181" t="n">
-        <v>93.6254456001772</v>
+        <v>93.62545322881296</v>
       </c>
       <c r="G181" t="n">
         <v>4077700</v>
@@ -4612,16 +4612,16 @@
         <v>45554</v>
       </c>
       <c r="C182" t="n">
-        <v>93.65338134765625</v>
+        <v>93.65338897705078</v>
       </c>
       <c r="D182" t="n">
-        <v>93.66269374364776</v>
+        <v>93.66270137380091</v>
       </c>
       <c r="E182" t="n">
-        <v>93.64407605494162</v>
+        <v>93.6440836835781</v>
       </c>
       <c r="F182" t="n">
-        <v>93.64407605494162</v>
+        <v>93.6440836835781</v>
       </c>
       <c r="G182" t="n">
         <v>5165800</v>
@@ -4658,16 +4658,16 @@
         <v>45558</v>
       </c>
       <c r="C184" t="n">
-        <v>93.71856689453125</v>
+        <v>93.71855163574219</v>
       </c>
       <c r="D184" t="n">
-        <v>93.71856689453125</v>
+        <v>93.71855163574219</v>
       </c>
       <c r="E184" t="n">
-        <v>93.69994210138005</v>
+        <v>93.69992684562337</v>
       </c>
       <c r="F184" t="n">
-        <v>93.70925449795564</v>
+        <v>93.70923924068278</v>
       </c>
       <c r="G184" t="n">
         <v>5220900</v>
@@ -4681,16 +4681,16 @@
         <v>45559</v>
       </c>
       <c r="C185" t="n">
-        <v>93.72785186767578</v>
+        <v>93.72787475585938</v>
       </c>
       <c r="D185" t="n">
-        <v>93.72785186767578</v>
+        <v>93.72787475585938</v>
       </c>
       <c r="E185" t="n">
-        <v>93.71854657639489</v>
+        <v>93.71856946230614</v>
       </c>
       <c r="F185" t="n">
-        <v>93.71854657639489</v>
+        <v>93.71856946230614</v>
       </c>
       <c r="G185" t="n">
         <v>3923500</v>
@@ -4704,16 +4704,16 @@
         <v>45560</v>
       </c>
       <c r="C186" t="n">
-        <v>93.72785186767578</v>
+        <v>93.72787475585938</v>
       </c>
       <c r="D186" t="n">
-        <v>93.74647665678914</v>
+        <v>93.74649954952088</v>
       </c>
       <c r="E186" t="n">
-        <v>93.72785186767578</v>
+        <v>93.72787475585938</v>
       </c>
       <c r="F186" t="n">
-        <v>93.73716426223247</v>
+        <v>93.73718715269013</v>
       </c>
       <c r="G186" t="n">
         <v>3372400</v>
@@ -4727,16 +4727,16 @@
         <v>45561</v>
       </c>
       <c r="C187" t="n">
-        <v>93.73716735839844</v>
+        <v>93.73717498779297</v>
       </c>
       <c r="D187" t="n">
-        <v>93.74647975326272</v>
+        <v>93.74648738341519</v>
       </c>
       <c r="E187" t="n">
-        <v>93.73716735839844</v>
+        <v>93.73717498779297</v>
       </c>
       <c r="F187" t="n">
-        <v>93.73716735839844</v>
+        <v>93.73717498779297</v>
       </c>
       <c r="G187" t="n">
         <v>4364400</v>
@@ -4796,16 +4796,16 @@
         <v>45566</v>
       </c>
       <c r="C190" t="n">
-        <v>93.81182098388672</v>
+        <v>93.81180572509766</v>
       </c>
       <c r="D190" t="n">
-        <v>93.81182098388672</v>
+        <v>93.81180572509766</v>
       </c>
       <c r="E190" t="n">
-        <v>93.80246866058975</v>
+        <v>93.80245340332188</v>
       </c>
       <c r="F190" t="n">
-        <v>93.81182098388672</v>
+        <v>93.81180572509766</v>
       </c>
       <c r="G190" t="n">
         <v>11569200</v>
@@ -4819,16 +4819,16 @@
         <v>45567</v>
       </c>
       <c r="C191" t="n">
-        <v>93.81182098388672</v>
+        <v>93.81180572509766</v>
       </c>
       <c r="D191" t="n">
-        <v>93.82116617345119</v>
+        <v>93.82115091314211</v>
       </c>
       <c r="E191" t="n">
-        <v>93.81182098388672</v>
+        <v>93.81180572509766</v>
       </c>
       <c r="F191" t="n">
-        <v>93.82116617345119</v>
+        <v>93.82115091314211</v>
       </c>
       <c r="G191" t="n">
         <v>5170300</v>
@@ -4842,16 +4842,16 @@
         <v>45568</v>
       </c>
       <c r="C192" t="n">
-        <v>93.8211669921875</v>
+        <v>93.82115936279297</v>
       </c>
       <c r="D192" t="n">
-        <v>93.83051931556608</v>
+        <v>93.83051168541103</v>
       </c>
       <c r="E192" t="n">
-        <v>93.8211669921875</v>
+        <v>93.82115936279297</v>
       </c>
       <c r="F192" t="n">
-        <v>93.83051931556608</v>
+        <v>93.83051168541103</v>
       </c>
       <c r="G192" t="n">
         <v>4066100</v>
@@ -4865,16 +4865,16 @@
         <v>45569</v>
       </c>
       <c r="C193" t="n">
-        <v>93.85856628417969</v>
+        <v>93.85855865478516</v>
       </c>
       <c r="D193" t="n">
-        <v>93.86791860727251</v>
+        <v>93.86791097711776</v>
       </c>
       <c r="E193" t="n">
-        <v>93.85856628417969</v>
+        <v>93.85855865478516</v>
       </c>
       <c r="F193" t="n">
-        <v>93.86324601259227</v>
+        <v>93.86323838281734</v>
       </c>
       <c r="G193" t="n">
         <v>4987100</v>
@@ -4911,16 +4911,16 @@
         <v>45573</v>
       </c>
       <c r="C195" t="n">
-        <v>93.87727355957031</v>
+        <v>93.87725830078125</v>
       </c>
       <c r="D195" t="n">
-        <v>93.88662588292506</v>
+        <v>93.88661062261588</v>
       </c>
       <c r="E195" t="n">
-        <v>93.87727355957031</v>
+        <v>93.87725830078125</v>
       </c>
       <c r="F195" t="n">
-        <v>93.87727355957031</v>
+        <v>93.87725830078125</v>
       </c>
       <c r="G195" t="n">
         <v>3923100</v>
@@ -4934,16 +4934,16 @@
         <v>45574</v>
       </c>
       <c r="C196" t="n">
-        <v>93.89596557617188</v>
+        <v>93.89597320556641</v>
       </c>
       <c r="D196" t="n">
-        <v>93.90531789897918</v>
+        <v>93.90532552913362</v>
       </c>
       <c r="E196" t="n">
-        <v>93.8866203870967</v>
+        <v>93.8866280157319</v>
       </c>
       <c r="F196" t="n">
-        <v>93.89596557617188</v>
+        <v>93.89597320556641</v>
       </c>
       <c r="G196" t="n">
         <v>4024800</v>
@@ -4980,16 +4980,16 @@
         <v>45576</v>
       </c>
       <c r="C198" t="n">
-        <v>93.95207214355469</v>
+        <v>93.95207977294922</v>
       </c>
       <c r="D198" t="n">
-        <v>93.96141733260642</v>
+        <v>93.96142496275984</v>
       </c>
       <c r="E198" t="n">
-        <v>93.95207214355469</v>
+        <v>93.95207977294922</v>
       </c>
       <c r="F198" t="n">
-        <v>93.95207214355469</v>
+        <v>93.95207977294922</v>
       </c>
       <c r="G198" t="n">
         <v>3778400</v>
@@ -5003,16 +5003,16 @@
         <v>45579</v>
       </c>
       <c r="C199" t="n">
-        <v>93.95207214355469</v>
+        <v>93.95207977294922</v>
       </c>
       <c r="D199" t="n">
-        <v>93.96141733260642</v>
+        <v>93.96142496275984</v>
       </c>
       <c r="E199" t="n">
-        <v>93.95207214355469</v>
+        <v>93.95207977294922</v>
       </c>
       <c r="F199" t="n">
-        <v>93.95207214355469</v>
+        <v>93.95207977294922</v>
       </c>
       <c r="G199" t="n">
         <v>3297100</v>
@@ -5026,16 +5026,16 @@
         <v>45580</v>
       </c>
       <c r="C200" t="n">
-        <v>93.97077178955078</v>
+        <v>93.97075653076172</v>
       </c>
       <c r="D200" t="n">
-        <v>93.97077178955078</v>
+        <v>93.97075653076172</v>
       </c>
       <c r="E200" t="n">
-        <v>93.96141946655455</v>
+        <v>93.9614042092841</v>
       </c>
       <c r="F200" t="n">
-        <v>93.97077178955078</v>
+        <v>93.97075653076172</v>
       </c>
       <c r="G200" t="n">
         <v>3567400</v>
@@ -5049,16 +5049,16 @@
         <v>45581</v>
       </c>
       <c r="C201" t="n">
-        <v>93.98947143554688</v>
+        <v>93.98947906494141</v>
       </c>
       <c r="D201" t="n">
-        <v>93.98947143554688</v>
+        <v>93.98947906494141</v>
       </c>
       <c r="E201" t="n">
-        <v>93.98012624607075</v>
+        <v>93.98013387470671</v>
       </c>
       <c r="F201" t="n">
-        <v>93.98012624607075</v>
+        <v>93.98013387470671</v>
       </c>
       <c r="G201" t="n">
         <v>3809900</v>
@@ -5072,16 +5072,16 @@
         <v>45582</v>
       </c>
       <c r="C202" t="n">
-        <v>93.98947143554688</v>
+        <v>93.98947906494141</v>
       </c>
       <c r="D202" t="n">
-        <v>93.99882375875542</v>
+        <v>93.99883138890911</v>
       </c>
       <c r="E202" t="n">
-        <v>93.98947143554688</v>
+        <v>93.98947906494141</v>
       </c>
       <c r="F202" t="n">
-        <v>93.98947143554688</v>
+        <v>93.98947906494141</v>
       </c>
       <c r="G202" t="n">
         <v>3575500</v>
@@ -5095,16 +5095,16 @@
         <v>45583</v>
       </c>
       <c r="C203" t="n">
-        <v>94.02687072753906</v>
+        <v>94.02687835693359</v>
       </c>
       <c r="D203" t="n">
-        <v>94.03622305046243</v>
+        <v>94.03623068061582</v>
       </c>
       <c r="E203" t="n">
-        <v>94.0175255383479</v>
+        <v>94.01753316698415</v>
       </c>
       <c r="F203" t="n">
-        <v>94.03622305046243</v>
+        <v>94.03623068061582</v>
       </c>
       <c r="G203" t="n">
         <v>3970200</v>
@@ -5118,16 +5118,16 @@
         <v>45586</v>
       </c>
       <c r="C204" t="n">
-        <v>94.04558563232422</v>
+        <v>94.04557800292969</v>
       </c>
       <c r="D204" t="n">
-        <v>94.04558563232422</v>
+        <v>94.04557800292969</v>
       </c>
       <c r="E204" t="n">
-        <v>94.03623330838064</v>
+        <v>94.03622567974483</v>
       </c>
       <c r="F204" t="n">
-        <v>94.03623330838064</v>
+        <v>94.03622567974483</v>
       </c>
       <c r="G204" t="n">
         <v>3940600</v>
@@ -5141,16 +5141,16 @@
         <v>45587</v>
       </c>
       <c r="C205" t="n">
-        <v>94.05492401123047</v>
+        <v>94.054931640625</v>
       </c>
       <c r="D205" t="n">
-        <v>94.05492401123047</v>
+        <v>94.054931640625</v>
       </c>
       <c r="E205" t="n">
-        <v>94.04557882169665</v>
+        <v>94.04558645033313</v>
       </c>
       <c r="F205" t="n">
-        <v>94.05492401123047</v>
+        <v>94.054931640625</v>
       </c>
       <c r="G205" t="n">
         <v>3462800</v>
@@ -5164,16 +5164,16 @@
         <v>45588</v>
       </c>
       <c r="C206" t="n">
-        <v>94.05492401123047</v>
+        <v>94.054931640625</v>
       </c>
       <c r="D206" t="n">
-        <v>94.07362865776304</v>
+        <v>94.07363628867482</v>
       </c>
       <c r="E206" t="n">
-        <v>94.05492401123047</v>
+        <v>94.054931640625</v>
       </c>
       <c r="F206" t="n">
-        <v>94.07362865776304</v>
+        <v>94.07363628867482</v>
       </c>
       <c r="G206" t="n">
         <v>3927700</v>
@@ -5187,16 +5187,16 @@
         <v>45589</v>
       </c>
       <c r="C207" t="n">
-        <v>94.08300018310547</v>
+        <v>94.08298492431641</v>
       </c>
       <c r="D207" t="n">
-        <v>94.08300018310547</v>
+        <v>94.08298492431641</v>
       </c>
       <c r="E207" t="n">
-        <v>94.0736478579304</v>
+        <v>94.07363260065813</v>
       </c>
       <c r="F207" t="n">
-        <v>94.08300018310547</v>
+        <v>94.08298492431641</v>
       </c>
       <c r="G207" t="n">
         <v>3704500</v>
@@ -5210,16 +5210,16 @@
         <v>45590</v>
       </c>
       <c r="C208" t="n">
-        <v>94.12039184570312</v>
+        <v>94.12037658691406</v>
       </c>
       <c r="D208" t="n">
-        <v>94.12039184570312</v>
+        <v>94.12037658691406</v>
       </c>
       <c r="E208" t="n">
-        <v>94.11103952157183</v>
+        <v>94.11102426429896</v>
       </c>
       <c r="F208" t="n">
-        <v>94.11103952157183</v>
+        <v>94.11102426429896</v>
       </c>
       <c r="G208" t="n">
         <v>5386900</v>
@@ -5233,16 +5233,16 @@
         <v>45593</v>
       </c>
       <c r="C209" t="n">
-        <v>94.12039184570312</v>
+        <v>94.12037658691406</v>
       </c>
       <c r="D209" t="n">
-        <v>94.12973703610129</v>
+        <v>94.12972177579719</v>
       </c>
       <c r="E209" t="n">
-        <v>94.12039184570312</v>
+        <v>94.12037658691406</v>
       </c>
       <c r="F209" t="n">
-        <v>94.12973703610129</v>
+        <v>94.12972177579719</v>
       </c>
       <c r="G209" t="n">
         <v>3471300</v>
@@ -5256,16 +5256,16 @@
         <v>45594</v>
       </c>
       <c r="C210" t="n">
-        <v>94.13906860351562</v>
+        <v>94.13908386230469</v>
       </c>
       <c r="D210" t="n">
-        <v>94.13906860351562</v>
+        <v>94.13908386230469</v>
       </c>
       <c r="E210" t="n">
-        <v>94.1250436872776</v>
+        <v>94.12505894379339</v>
       </c>
       <c r="F210" t="n">
-        <v>94.12971628144642</v>
+        <v>94.12973153871958</v>
       </c>
       <c r="G210" t="n">
         <v>3449900</v>
@@ -5279,16 +5279,16 @@
         <v>45595</v>
       </c>
       <c r="C211" t="n">
-        <v>94.13906860351562</v>
+        <v>94.13908386230469</v>
       </c>
       <c r="D211" t="n">
-        <v>94.15776611392248</v>
+        <v>94.15778137574219</v>
       </c>
       <c r="E211" t="n">
-        <v>94.13906860351562</v>
+        <v>94.13908386230469</v>
       </c>
       <c r="F211" t="n">
-        <v>94.14842092558483</v>
+        <v>94.14843618588979</v>
       </c>
       <c r="G211" t="n">
         <v>7059200</v>
@@ -5302,16 +5302,16 @@
         <v>45596</v>
       </c>
       <c r="C212" t="n">
-        <v>94.15776062011719</v>
+        <v>94.15775299072266</v>
       </c>
       <c r="D212" t="n">
-        <v>94.16711294164071</v>
+        <v>94.16710531148838</v>
       </c>
       <c r="E212" t="n">
-        <v>94.1484154323248</v>
+        <v>94.14840780368749</v>
       </c>
       <c r="F212" t="n">
-        <v>94.1484154323248</v>
+        <v>94.14840780368749</v>
       </c>
       <c r="G212" t="n">
         <v>11321100</v>
@@ -5325,16 +5325,16 @@
         <v>45597</v>
       </c>
       <c r="C213" t="n">
-        <v>94.20941925048828</v>
+        <v>94.20939636230469</v>
       </c>
       <c r="D213" t="n">
-        <v>94.20941925048828</v>
+        <v>94.20939636230469</v>
       </c>
       <c r="E213" t="n">
-        <v>94.20003538842856</v>
+        <v>94.20001250252477</v>
       </c>
       <c r="F213" t="n">
-        <v>94.20941925048828</v>
+        <v>94.20939636230469</v>
       </c>
       <c r="G213" t="n">
         <v>13451800</v>
@@ -5348,16 +5348,16 @@
         <v>45600</v>
       </c>
       <c r="C214" t="n">
-        <v>94.21877288818359</v>
+        <v>94.21878051757812</v>
       </c>
       <c r="D214" t="n">
-        <v>94.22722552393668</v>
+        <v>94.22723315401566</v>
       </c>
       <c r="E214" t="n">
-        <v>94.2093818665969</v>
+        <v>94.20938949523099</v>
       </c>
       <c r="F214" t="n">
-        <v>94.21877288818359</v>
+        <v>94.21878051757812</v>
       </c>
       <c r="G214" t="n">
         <v>5041500</v>
@@ -5371,16 +5371,16 @@
         <v>45601</v>
       </c>
       <c r="C215" t="n">
-        <v>94.23759460449219</v>
+        <v>94.23760223388672</v>
       </c>
       <c r="D215" t="n">
-        <v>94.23759460449219</v>
+        <v>94.23760223388672</v>
       </c>
       <c r="E215" t="n">
-        <v>94.21881255341174</v>
+        <v>94.21882018128569</v>
       </c>
       <c r="F215" t="n">
-        <v>94.22820357895196</v>
+        <v>94.22821120758621</v>
       </c>
       <c r="G215" t="n">
         <v>4280500</v>
@@ -5394,16 +5394,16 @@
         <v>45602</v>
       </c>
       <c r="C216" t="n">
-        <v>94.23759460449219</v>
+        <v>94.23760223388672</v>
       </c>
       <c r="D216" t="n">
-        <v>94.24697846677877</v>
+        <v>94.246986096933</v>
       </c>
       <c r="E216" t="n">
-        <v>94.22820357895196</v>
+        <v>94.22821120758621</v>
       </c>
       <c r="F216" t="n">
-        <v>94.22820357895196</v>
+        <v>94.22821120758621</v>
       </c>
       <c r="G216" t="n">
         <v>9470900</v>
@@ -5417,16 +5417,16 @@
         <v>45603</v>
       </c>
       <c r="C217" t="n">
-        <v>94.25635528564453</v>
+        <v>94.25636291503906</v>
       </c>
       <c r="D217" t="n">
-        <v>94.25635528564453</v>
+        <v>94.25636291503906</v>
       </c>
       <c r="E217" t="n">
-        <v>94.24696426151975</v>
+        <v>94.24697189015416</v>
       </c>
       <c r="F217" t="n">
-        <v>94.24696426151975</v>
+        <v>94.24697189015416</v>
       </c>
       <c r="G217" t="n">
         <v>6188100</v>
@@ -5463,16 +5463,16 @@
         <v>45607</v>
       </c>
       <c r="C219" t="n">
-        <v>94.29392242431641</v>
+        <v>94.29389190673828</v>
       </c>
       <c r="D219" t="n">
-        <v>94.30331344945758</v>
+        <v>94.3032829288401</v>
       </c>
       <c r="E219" t="n">
-        <v>94.2892304933725</v>
+        <v>94.28919997731288</v>
       </c>
       <c r="F219" t="n">
-        <v>94.29392242431641</v>
+        <v>94.29389190673828</v>
       </c>
       <c r="G219" t="n">
         <v>4443700</v>
@@ -5509,16 +5509,16 @@
         <v>45609</v>
       </c>
       <c r="C221" t="n">
-        <v>94.33147430419922</v>
+        <v>94.33146667480469</v>
       </c>
       <c r="D221" t="n">
-        <v>94.33147430419922</v>
+        <v>94.33146667480469</v>
       </c>
       <c r="E221" t="n">
-        <v>94.31269225492385</v>
+        <v>94.3126846270484</v>
       </c>
       <c r="F221" t="n">
-        <v>94.32208327956153</v>
+        <v>94.32207565092654</v>
       </c>
       <c r="G221" t="n">
         <v>4818000</v>
@@ -5532,16 +5532,16 @@
         <v>45610</v>
       </c>
       <c r="C222" t="n">
-        <v>94.33147430419922</v>
+        <v>94.33146667480469</v>
       </c>
       <c r="D222" t="n">
-        <v>94.3408653288369</v>
+        <v>94.34085769868284</v>
       </c>
       <c r="E222" t="n">
-        <v>94.33147430419922</v>
+        <v>94.33146667480469</v>
       </c>
       <c r="F222" t="n">
-        <v>94.3408653288369</v>
+        <v>94.34085769868284</v>
       </c>
       <c r="G222" t="n">
         <v>4353200</v>
@@ -5555,16 +5555,16 @@
         <v>45611</v>
       </c>
       <c r="C223" t="n">
-        <v>94.37841796875</v>
+        <v>94.37843322753906</v>
       </c>
       <c r="D223" t="n">
-        <v>94.37841796875</v>
+        <v>94.37843322753906</v>
       </c>
       <c r="E223" t="n">
-        <v>94.36903410708014</v>
+        <v>94.36904936435205</v>
       </c>
       <c r="F223" t="n">
-        <v>94.36903410708014</v>
+        <v>94.36904936435205</v>
       </c>
       <c r="G223" t="n">
         <v>5605100</v>
@@ -5601,16 +5601,16 @@
         <v>45615</v>
       </c>
       <c r="C225" t="n">
-        <v>94.39718627929688</v>
+        <v>94.39720916748047</v>
       </c>
       <c r="D225" t="n">
-        <v>94.39718627929688</v>
+        <v>94.39720916748047</v>
       </c>
       <c r="E225" t="n">
-        <v>94.38779525574067</v>
+        <v>94.38781814164726</v>
       </c>
       <c r="F225" t="n">
-        <v>94.39718627929688</v>
+        <v>94.39720916748047</v>
       </c>
       <c r="G225" t="n">
         <v>4310900</v>
@@ -5624,16 +5624,16 @@
         <v>45616</v>
       </c>
       <c r="C226" t="n">
-        <v>94.41596984863281</v>
+        <v>94.41597747802734</v>
       </c>
       <c r="D226" t="n">
-        <v>94.41596984863281</v>
+        <v>94.41597747802734</v>
       </c>
       <c r="E226" t="n">
-        <v>94.39719496304541</v>
+        <v>94.39720259092282</v>
       </c>
       <c r="F226" t="n">
-        <v>94.4065859874655</v>
+        <v>94.40659361610177</v>
       </c>
       <c r="G226" t="n">
         <v>4133000</v>
@@ -5647,16 +5647,16 @@
         <v>45617</v>
       </c>
       <c r="C227" t="n">
-        <v>94.41596984863281</v>
+        <v>94.41597747802734</v>
       </c>
       <c r="D227" t="n">
-        <v>94.42536087305291</v>
+        <v>94.4253685032063</v>
       </c>
       <c r="E227" t="n">
-        <v>94.41596984863281</v>
+        <v>94.41597747802734</v>
       </c>
       <c r="F227" t="n">
-        <v>94.42536087305291</v>
+        <v>94.4253685032063</v>
       </c>
       <c r="G227" t="n">
         <v>4410700</v>
@@ -5670,16 +5670,16 @@
         <v>45618</v>
       </c>
       <c r="C228" t="n">
-        <v>94.44414520263672</v>
+        <v>94.44415283203125</v>
       </c>
       <c r="D228" t="n">
-        <v>94.45353622799588</v>
+        <v>94.45354385814905</v>
       </c>
       <c r="E228" t="n">
-        <v>94.44414520263672</v>
+        <v>94.44415283203125</v>
       </c>
       <c r="F228" t="n">
-        <v>94.44414520263672</v>
+        <v>94.44415283203125</v>
       </c>
       <c r="G228" t="n">
         <v>4343900</v>
@@ -5693,16 +5693,16 @@
         <v>45621</v>
       </c>
       <c r="C229" t="n">
-        <v>94.45351409912109</v>
+        <v>94.45354461669922</v>
       </c>
       <c r="D229" t="n">
-        <v>94.46290512228009</v>
+        <v>94.46293564289242</v>
       </c>
       <c r="E229" t="n">
-        <v>94.45351409912109</v>
+        <v>94.45354461669922</v>
       </c>
       <c r="F229" t="n">
-        <v>94.45351409912109</v>
+        <v>94.45354461669922</v>
       </c>
       <c r="G229" t="n">
         <v>6020200</v>
@@ -5739,16 +5739,16 @@
         <v>45623</v>
       </c>
       <c r="C231" t="n">
-        <v>94.4910888671875</v>
+        <v>94.49107360839844</v>
       </c>
       <c r="D231" t="n">
-        <v>94.5004798921194</v>
+        <v>94.50046463181384</v>
       </c>
       <c r="E231" t="n">
-        <v>94.4910888671875</v>
+        <v>94.49107360839844</v>
       </c>
       <c r="F231" t="n">
-        <v>94.4910888671875</v>
+        <v>94.49107360839844</v>
       </c>
       <c r="G231" t="n">
         <v>5909000</v>
@@ -5762,16 +5762,16 @@
         <v>45625</v>
       </c>
       <c r="C232" t="n">
-        <v>94.52864074707031</v>
+        <v>94.52863311767578</v>
       </c>
       <c r="D232" t="n">
-        <v>94.53803177149987</v>
+        <v>94.53802414134739</v>
       </c>
       <c r="E232" t="n">
-        <v>94.52864074707031</v>
+       